--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R7b7f358803724155"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R7e95a007b0a24f35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Ra2eef41f61284ead"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R5e8bf58bde5744e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Ra12eb23b874b466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Ra4c7078e67ba4b11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rec4bf2072ca54332"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rc316c156003643da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R875e8779a87b47d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rcecc292d42934cd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rca3f9eade7b04dbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R7ecfa61695fb4cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4f2a5e8e3c5d4184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rb45b06b327414d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rd36281ea58b14510"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R7cad496acbcb4a91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R2ebc769276444ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R3af1d3e64dd74476"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R8d96019120bb4c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R3eeefe53ba2840e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7689.4</x:v>
+        <x:v>7662.2</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7432</x:v>
+        <x:v>7512.6</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>257.4</x:v>
+        <x:v>149.6</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>31075.2</x:v>
+        <x:v>31224.8</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>189.5</x:v>
+        <x:v>189.2</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>152400</x:v>
+        <x:v>142800</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>140940</x:v>
+        <x:v>139880</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>11460</x:v>
+        <x:v>2920</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1387980</x:v>
+        <x:v>1390900</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8463.3</x:v>
+        <x:v>8429.7</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -7561,30 +7561,48 @@
       </x:c>
     </x:row>
     <x:row r="209">
-      <x:c r="A209" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B209" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C209" s="30"/>
-      <x:c r="D209" s="30"/>
-      <x:c r="E209" s="30"/>
-      <x:c r="F209" s="30"/>
-      <x:c r="G209" s="30"/>
-      <x:c r="H209" s="30"/>
-      <x:c r="I209" s="30"/>
-      <x:c r="J209" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J208),1)</x:f>
-        <x:v>26220</x:v>
-      </x:c>
-      <x:c r="K209" s="30"/>
+      <x:c r="A209" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B209" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C209" s="22" t="str">
+        <x:v>9月7日</x:v>
+      </x:c>
+      <x:c r="D209" s="23" t="n">
+        <x:v>142120</x:v>
+      </x:c>
+      <x:c r="E209" s="23" t="n">
+        <x:v>142800</x:v>
+      </x:c>
+      <x:c r="F209" s="23" t="n">
+        <x:v>139880</x:v>
+      </x:c>
+      <x:c r="G209" s="23" t="n">
+        <x:v>140500</x:v>
+      </x:c>
+      <x:c r="H209" s="28" t="n">
+        <x:v>-480</x:v>
+      </x:c>
+      <x:c r="I209" s="24" t="n">
+        <x:v>-0.003404738260746165</x:v>
+      </x:c>
+      <x:c r="J209" s="23" t="n">
+        <x:f>ROUND(E209-F209,1)</x:f>
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="K209" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B210" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B210" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C210" s="30"/>
       <x:c r="D210" s="30"/>
       <x:c r="E210" s="30"/>
@@ -7592,11 +7610,29 @@
       <x:c r="G210" s="30"/>
       <x:c r="H210" s="30"/>
       <x:c r="I210" s="30"/>
-      <x:c r="J210" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J208),0),1)</x:f>
-        <x:v>6555</x:v>
+      <x:c r="J210" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J209),1)</x:f>
+        <x:v>29140</x:v>
       </x:c>
       <x:c r="K210" s="30"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B211" s="30"/>
+      <x:c r="C211" s="30"/>
+      <x:c r="D211" s="30"/>
+      <x:c r="E211" s="30"/>
+      <x:c r="F211" s="30"/>
+      <x:c r="G211" s="30"/>
+      <x:c r="H211" s="30"/>
+      <x:c r="I211" s="30"/>
+      <x:c r="J211" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
+        <x:v>5828</x:v>
+      </x:c>
+      <x:c r="K211" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13210,155 +13246,155 @@
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B159" s="30" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C159" s="30"/>
-      <x:c r="D159" s="30"/>
-      <x:c r="E159" s="30"/>
-      <x:c r="F159" s="30"/>
-      <x:c r="G159" s="30"/>
-      <x:c r="H159" s="30"/>
-      <x:c r="I159" s="32" t="n">
-        <x:f>ROUND(SUM(I125:I158),1)</x:f>
-        <x:v>14828.6</x:v>
-      </x:c>
-      <x:c r="J159" s="30"/>
-      <x:c r="K159" s="30"/>
+      <x:c r="A159" s="22" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B159" s="22" t="str">
+        <x:v>9月7日</x:v>
+      </x:c>
+      <x:c r="C159" s="23" t="n">
+        <x:v>7527.2</x:v>
+      </x:c>
+      <x:c r="D159" s="23" t="n">
+        <x:v>7662.2</x:v>
+      </x:c>
+      <x:c r="E159" s="23" t="n">
+        <x:v>7512.6</x:v>
+      </x:c>
+      <x:c r="F159" s="23" t="n">
+        <x:v>7604</x:v>
+      </x:c>
+      <x:c r="G159" s="23" t="n">
+        <x:f>ROUND(F159-F158,1)</x:f>
+        <x:v>135.8</x:v>
+      </x:c>
+      <x:c r="H159" s="24" t="n">
+        <x:f>IFERROR(F159/F158-1,"")</x:f>
+        <x:v>0.01818376583380199</x:v>
+      </x:c>
+      <x:c r="I159" s="23" t="n">
+        <x:f>ROUND(D159-E159,1)</x:f>
+        <x:v>149.6</x:v>
+      </x:c>
+      <x:c r="J159" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
+      <x:c r="K159" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B160" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B160" s="30" t="n">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="C160" s="30"/>
       <x:c r="D160" s="30"/>
       <x:c r="E160" s="30"/>
       <x:c r="F160" s="30"/>
       <x:c r="G160" s="30"/>
       <x:c r="H160" s="30"/>
-      <x:c r="I160" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I125:I158),0),1)</x:f>
-        <x:v>436.1</x:v>
+      <x:c r="I160" s="32" t="n">
+        <x:f>ROUND(SUM(I125:I159),1)</x:f>
+        <x:v>14978.2</x:v>
       </x:c>
       <x:c r="J160" s="30"/>
       <x:c r="K160" s="30"/>
     </x:row>
-    <x:row r="162">
-      <x:c r="A162" s="17" t="str">
+    <x:row r="161">
+      <x:c r="A161" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B161" s="30"/>
+      <x:c r="C161" s="30"/>
+      <x:c r="D161" s="30"/>
+      <x:c r="E161" s="30"/>
+      <x:c r="F161" s="30"/>
+      <x:c r="G161" s="30"/>
+      <x:c r="H161" s="30"/>
+      <x:c r="I161" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I125:I159),0),1)</x:f>
+        <x:v>427.9</x:v>
+      </x:c>
+      <x:c r="J161" s="30"/>
+      <x:c r="K161" s="30"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="17" t="str">
         <x:v>IC主力</x:v>
       </x:c>
-      <x:c r="B162" s="17"/>
-      <x:c r="C162" s="17"/>
-      <x:c r="D162" s="17"/>
-      <x:c r="E162" s="17"/>
-      <x:c r="F162" s="17"/>
-      <x:c r="G162" s="17"/>
-      <x:c r="H162" s="17"/>
-      <x:c r="I162" s="17"/>
-      <x:c r="J162" s="17"/>
-      <x:c r="K162" s="17"/>
-    </x:row>
-    <x:row r="163">
-      <x:c r="A163" s="20" t="str">
+      <x:c r="B163" s="17"/>
+      <x:c r="C163" s="17"/>
+      <x:c r="D163" s="17"/>
+      <x:c r="E163" s="17"/>
+      <x:c r="F163" s="17"/>
+      <x:c r="G163" s="17"/>
+      <x:c r="H163" s="17"/>
+      <x:c r="I163" s="17"/>
+      <x:c r="J163" s="17"/>
+      <x:c r="K163" s="17"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B163" s="20" t="str">
+      <x:c r="B164" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C163" s="20" t="str">
+      <x:c r="C164" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D163" s="20" t="str">
+      <x:c r="D164" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E163" s="20" t="str">
+      <x:c r="E164" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F163" s="20" t="str">
+      <x:c r="F164" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G163" s="20" t="str">
+      <x:c r="G164" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H163" s="20" t="str">
+      <x:c r="H164" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I163" s="20" t="str">
+      <x:c r="I164" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J163" s="20" t="str">
+      <x:c r="J164" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K163" s="20" t="str">
+      <x:c r="K164" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164">
-      <x:c r="A164" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B164" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C164" s="23" t="n">
-        <x:v>7424.4</x:v>
-      </x:c>
-      <x:c r="D164" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="E164" s="23" t="n">
-        <x:v>7422</x:v>
-      </x:c>
-      <x:c r="F164" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="G164" s="23"/>
-      <x:c r="H164" s="24"/>
-      <x:c r="I164" s="26" t="n">
-        <x:f>ROUND(D164-E164,1)</x:f>
-        <x:v>615.8</x:v>
-      </x:c>
-      <x:c r="J164" s="22" t="str">
-        <x:v>IC2603</x:v>
-      </x:c>
-      <x:c r="K164" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B165" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C165" s="23" t="n">
-        <x:v>8099</x:v>
+        <x:v>7424.4</x:v>
       </x:c>
       <x:c r="D165" s="23" t="n">
-        <x:v>8388.6</x:v>
+        <x:v>8037.8</x:v>
       </x:c>
       <x:c r="E165" s="23" t="n">
-        <x:v>8044</x:v>
+        <x:v>7422</x:v>
       </x:c>
       <x:c r="F165" s="23" t="n">
-        <x:v>8210.4</x:v>
-      </x:c>
-      <x:c r="G165" s="28" t="n">
-        <x:f>ROUND(F165-F164,1)</x:f>
-        <x:v>172.6</x:v>
-      </x:c>
-      <x:c r="H165" s="24" t="n">
-        <x:f>IFERROR(F165/F164-1,"")</x:f>
-        <x:v>0.02147353753514647</x:v>
-      </x:c>
+        <x:v>8037.8</x:v>
+      </x:c>
+      <x:c r="G165" s="23"/>
+      <x:c r="H165" s="24"/>
       <x:c r="I165" s="26" t="n">
         <x:f>ROUND(D165-E165,1)</x:f>
-        <x:v>344.6</x:v>
+        <x:v>615.8</x:v>
       </x:c>
       <x:c r="J165" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -13369,34 +13405,34 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B166" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C166" s="23" t="n">
-        <x:v>8182.6</x:v>
+        <x:v>8099</x:v>
       </x:c>
       <x:c r="D166" s="23" t="n">
-        <x:v>8660</x:v>
+        <x:v>8388.6</x:v>
       </x:c>
       <x:c r="E166" s="23" t="n">
-        <x:v>8112</x:v>
+        <x:v>8044</x:v>
       </x:c>
       <x:c r="F166" s="23" t="n">
-        <x:v>8658.2</x:v>
+        <x:v>8210.4</x:v>
       </x:c>
       <x:c r="G166" s="28" t="n">
         <x:f>ROUND(F166-F165,1)</x:f>
-        <x:v>447.8</x:v>
+        <x:v>172.6</x:v>
       </x:c>
       <x:c r="H166" s="24" t="n">
         <x:f>IFERROR(F166/F165-1,"")</x:f>
-        <x:v>0.05454058267563111</x:v>
+        <x:v>0.02147353753514647</x:v>
       </x:c>
       <x:c r="I166" s="26" t="n">
         <x:f>ROUND(D166-E166,1)</x:f>
-        <x:v>548</x:v>
+        <x:v>344.6</x:v>
       </x:c>
       <x:c r="J166" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -13407,34 +13443,34 @@
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B167" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C167" s="23" t="n">
-        <x:v>8695</x:v>
+        <x:v>8182.6</x:v>
       </x:c>
       <x:c r="D167" s="23" t="n">
-        <x:v>8728.2</x:v>
+        <x:v>8660</x:v>
       </x:c>
       <x:c r="E167" s="23" t="n">
-        <x:v>8135</x:v>
+        <x:v>8112</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>8362.4</x:v>
+        <x:v>8658.2</x:v>
       </x:c>
       <x:c r="G167" s="28" t="n">
         <x:f>ROUND(F167-F166,1)</x:f>
-        <x:v>-295.8</x:v>
+        <x:v>447.8</x:v>
       </x:c>
       <x:c r="H167" s="24" t="n">
         <x:f>IFERROR(F167/F166-1,"")</x:f>
-        <x:v>-0.03416414497239628</x:v>
+        <x:v>0.05454058267563111</x:v>
       </x:c>
       <x:c r="I167" s="26" t="n">
         <x:f>ROUND(D167-E167,1)</x:f>
-        <x:v>593.2</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="J167" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -13445,34 +13481,34 @@
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B168" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C168" s="23" t="n">
-        <x:v>8262.2</x:v>
+        <x:v>8695</x:v>
       </x:c>
       <x:c r="D168" s="23" t="n">
-        <x:v>8334.4</x:v>
+        <x:v>8728.2</x:v>
       </x:c>
       <x:c r="E168" s="23" t="n">
-        <x:v>7832</x:v>
+        <x:v>8135</x:v>
       </x:c>
       <x:c r="F168" s="23" t="n">
-        <x:v>8117.4</x:v>
+        <x:v>8362.4</x:v>
       </x:c>
       <x:c r="G168" s="28" t="n">
         <x:f>ROUND(F168-F167,1)</x:f>
-        <x:v>-245</x:v>
+        <x:v>-295.8</x:v>
       </x:c>
       <x:c r="H168" s="24" t="n">
         <x:f>IFERROR(F168/F167-1,"")</x:f>
-        <x:v>-0.029297809241366157</x:v>
+        <x:v>-0.03416414497239628</x:v>
       </x:c>
       <x:c r="I168" s="26" t="n">
         <x:f>ROUND(D168-E168,1)</x:f>
-        <x:v>502.4</x:v>
+        <x:v>593.2</x:v>
       </x:c>
       <x:c r="J168" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -13483,34 +13519,34 @@
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B169" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C169" s="23" t="n">
-        <x:v>8260</x:v>
+        <x:v>8262.2</x:v>
       </x:c>
       <x:c r="D169" s="23" t="n">
-        <x:v>8458.8</x:v>
+        <x:v>8334.4</x:v>
       </x:c>
       <x:c r="E169" s="23" t="n">
-        <x:v>8220</x:v>
+        <x:v>7832</x:v>
       </x:c>
       <x:c r="F169" s="23" t="n">
-        <x:v>8274.8</x:v>
+        <x:v>8117.4</x:v>
       </x:c>
       <x:c r="G169" s="28" t="n">
         <x:f>ROUND(F169-F168,1)</x:f>
-        <x:v>157.4</x:v>
+        <x:v>-245</x:v>
       </x:c>
       <x:c r="H169" s="24" t="n">
         <x:f>IFERROR(F169/F168-1,"")</x:f>
-        <x:v>0.019390445216448615</x:v>
+        <x:v>-0.029297809241366157</x:v>
       </x:c>
       <x:c r="I169" s="26" t="n">
         <x:f>ROUND(D169-E169,1)</x:f>
-        <x:v>238.8</x:v>
+        <x:v>502.4</x:v>
       </x:c>
       <x:c r="J169" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -13521,110 +13557,110 @@
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B170" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C170" s="23" t="n">
-        <x:v>8360</x:v>
+        <x:v>8260</x:v>
       </x:c>
       <x:c r="D170" s="23" t="n">
-        <x:v>8650</x:v>
+        <x:v>8458.8</x:v>
       </x:c>
       <x:c r="E170" s="23" t="n">
-        <x:v>8314</x:v>
+        <x:v>8220</x:v>
       </x:c>
       <x:c r="F170" s="23" t="n">
-        <x:v>8645.4</x:v>
+        <x:v>8274.8</x:v>
       </x:c>
       <x:c r="G170" s="28" t="n">
         <x:f>ROUND(F170-F169,1)</x:f>
-        <x:v>370.6</x:v>
+        <x:v>157.4</x:v>
       </x:c>
       <x:c r="H170" s="24" t="n">
         <x:f>IFERROR(F170/F169-1,"")</x:f>
-        <x:v>0.04478658094455468</x:v>
+        <x:v>0.019390445216448615</x:v>
       </x:c>
       <x:c r="I170" s="26" t="n">
         <x:f>ROUND(D170-E170,1)</x:f>
-        <x:v>336</x:v>
+        <x:v>238.8</x:v>
       </x:c>
       <x:c r="J170" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K170" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B171" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C171" s="23" t="n">
-        <x:v>8600</x:v>
+        <x:v>8360</x:v>
       </x:c>
       <x:c r="D171" s="23" t="n">
-        <x:v>8686</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="E171" s="23" t="n">
-        <x:v>8180.6</x:v>
+        <x:v>8314</x:v>
       </x:c>
       <x:c r="F171" s="23" t="n">
-        <x:v>8322.6</x:v>
+        <x:v>8645.4</x:v>
       </x:c>
       <x:c r="G171" s="28" t="n">
         <x:f>ROUND(F171-F170,1)</x:f>
-        <x:v>-322.8</x:v>
+        <x:v>370.6</x:v>
       </x:c>
       <x:c r="H171" s="24" t="n">
         <x:f>IFERROR(F171/F170-1,"")</x:f>
-        <x:v>-0.03733777500173496</x:v>
+        <x:v>0.04478658094455468</x:v>
       </x:c>
       <x:c r="I171" s="26" t="n">
         <x:f>ROUND(D171-E171,1)</x:f>
-        <x:v>505.4</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="J171" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K171" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B172" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C172" s="23" t="n">
-        <x:v>8201.8</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="D172" s="23" t="n">
-        <x:v>8434.4</x:v>
+        <x:v>8686</x:v>
       </x:c>
       <x:c r="E172" s="23" t="n">
-        <x:v>7710</x:v>
+        <x:v>8180.6</x:v>
       </x:c>
       <x:c r="F172" s="23" t="n">
-        <x:v>8213.8</x:v>
-      </x:c>
-      <x:c r="G172" s="23" t="n">
+        <x:v>8322.6</x:v>
+      </x:c>
+      <x:c r="G172" s="28" t="n">
         <x:f>ROUND(F172-F171,1)</x:f>
-        <x:v>-108.8</x:v>
+        <x:v>-322.8</x:v>
       </x:c>
       <x:c r="H172" s="24" t="n">
         <x:f>IFERROR(F172/F171-1,"")</x:f>
-        <x:v>-0.013072837815106042</x:v>
+        <x:v>-0.03733777500173496</x:v>
       </x:c>
       <x:c r="I172" s="26" t="n">
         <x:f>ROUND(D172-E172,1)</x:f>
-        <x:v>724.4</x:v>
+        <x:v>505.4</x:v>
       </x:c>
       <x:c r="J172" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -13635,34 +13671,34 @@
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B173" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C173" s="23" t="n">
-        <x:v>8225.2</x:v>
+        <x:v>8201.8</x:v>
       </x:c>
       <x:c r="D173" s="23" t="n">
-        <x:v>8229.6</x:v>
+        <x:v>8434.4</x:v>
       </x:c>
       <x:c r="E173" s="23" t="n">
-        <x:v>7827.8</x:v>
+        <x:v>7710</x:v>
       </x:c>
       <x:c r="F173" s="23" t="n">
-        <x:v>7844.4</x:v>
-      </x:c>
-      <x:c r="G173" s="28" t="n">
+        <x:v>8213.8</x:v>
+      </x:c>
+      <x:c r="G173" s="23" t="n">
         <x:f>ROUND(F173-F172,1)</x:f>
-        <x:v>-369.4</x:v>
+        <x:v>-108.8</x:v>
       </x:c>
       <x:c r="H173" s="24" t="n">
         <x:f>IFERROR(F173/F172-1,"")</x:f>
-        <x:v>-0.04497309406121397</x:v>
+        <x:v>-0.013072837815106042</x:v>
       </x:c>
       <x:c r="I173" s="26" t="n">
         <x:f>ROUND(D173-E173,1)</x:f>
-        <x:v>401.8</x:v>
+        <x:v>724.4</x:v>
       </x:c>
       <x:c r="J173" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -13673,37 +13709,37 @@
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B174" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C174" s="23" t="n">
-        <x:v>7460</x:v>
+        <x:v>8225.2</x:v>
       </x:c>
       <x:c r="D174" s="23" t="n">
-        <x:v>7652</x:v>
+        <x:v>8229.6</x:v>
       </x:c>
       <x:c r="E174" s="23" t="n">
-        <x:v>7171</x:v>
+        <x:v>7827.8</x:v>
       </x:c>
       <x:c r="F174" s="23" t="n">
-        <x:v>7559.2</x:v>
+        <x:v>7844.4</x:v>
       </x:c>
       <x:c r="G174" s="28" t="n">
         <x:f>ROUND(F174-F173,1)</x:f>
-        <x:v>-285.2</x:v>
+        <x:v>-369.4</x:v>
       </x:c>
       <x:c r="H174" s="24" t="n">
         <x:f>IFERROR(F174/F173-1,"")</x:f>
-        <x:v>-0.03635714649941357</x:v>
+        <x:v>-0.04497309406121397</x:v>
       </x:c>
       <x:c r="I174" s="26" t="n">
         <x:f>ROUND(D174-E174,1)</x:f>
-        <x:v>481</x:v>
+        <x:v>401.8</x:v>
       </x:c>
       <x:c r="J174" s="22" t="str">
-        <x:v>IC2606</x:v>
+        <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K174" s="22" t="n">
         <x:v>5</x:v>
@@ -13711,34 +13747,34 @@
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B175" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C175" s="23" t="n">
-        <x:v>7470.8</x:v>
+        <x:v>7460</x:v>
       </x:c>
       <x:c r="D175" s="23" t="n">
-        <x:v>7619</x:v>
+        <x:v>7652</x:v>
       </x:c>
       <x:c r="E175" s="23" t="n">
-        <x:v>7325.2</x:v>
+        <x:v>7171</x:v>
       </x:c>
       <x:c r="F175" s="23" t="n">
-        <x:v>7352</x:v>
+        <x:v>7559.2</x:v>
       </x:c>
       <x:c r="G175" s="28" t="n">
         <x:f>ROUND(F175-F174,1)</x:f>
-        <x:v>-207.2</x:v>
+        <x:v>-285.2</x:v>
       </x:c>
       <x:c r="H175" s="24" t="n">
         <x:f>IFERROR(F175/F174-1,"")</x:f>
-        <x:v>-0.02741030796909727</x:v>
+        <x:v>-0.03635714649941357</x:v>
       </x:c>
       <x:c r="I175" s="26" t="n">
         <x:f>ROUND(D175-E175,1)</x:f>
-        <x:v>293.8</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="J175" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -13749,110 +13785,110 @@
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B176" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C176" s="23" t="n">
-        <x:v>7380</x:v>
+        <x:v>7470.8</x:v>
       </x:c>
       <x:c r="D176" s="23" t="n">
-        <x:v>7945.4</x:v>
+        <x:v>7619</x:v>
       </x:c>
       <x:c r="E176" s="23" t="n">
-        <x:v>7355.6</x:v>
+        <x:v>7325.2</x:v>
       </x:c>
       <x:c r="F176" s="23" t="n">
-        <x:v>7828.6</x:v>
+        <x:v>7352</x:v>
       </x:c>
       <x:c r="G176" s="28" t="n">
         <x:f>ROUND(F176-F175,1)</x:f>
-        <x:v>476.6</x:v>
+        <x:v>-207.2</x:v>
       </x:c>
       <x:c r="H176" s="24" t="n">
         <x:f>IFERROR(F176/F175-1,"")</x:f>
-        <x:v>0.06482589771490765</x:v>
+        <x:v>-0.02741030796909727</x:v>
       </x:c>
       <x:c r="I176" s="26" t="n">
         <x:f>ROUND(D176-E176,1)</x:f>
-        <x:v>589.8</x:v>
+        <x:v>293.8</x:v>
       </x:c>
       <x:c r="J176" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K176" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B177" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C177" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7380</x:v>
       </x:c>
       <x:c r="D177" s="23" t="n">
-        <x:v>8119.6</x:v>
+        <x:v>7945.4</x:v>
       </x:c>
       <x:c r="E177" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7355.6</x:v>
       </x:c>
       <x:c r="F177" s="23" t="n">
-        <x:v>8098.8</x:v>
+        <x:v>7828.6</x:v>
       </x:c>
       <x:c r="G177" s="28" t="n">
         <x:f>ROUND(F177-F176,1)</x:f>
-        <x:v>270.2</x:v>
+        <x:v>476.6</x:v>
       </x:c>
       <x:c r="H177" s="24" t="n">
         <x:f>IFERROR(F177/F176-1,"")</x:f>
-        <x:v>0.034514472574917576</x:v>
+        <x:v>0.06482589771490765</x:v>
       </x:c>
       <x:c r="I177" s="26" t="n">
         <x:f>ROUND(D177-E177,1)</x:f>
-        <x:v>327.6</x:v>
+        <x:v>589.8</x:v>
       </x:c>
       <x:c r="J177" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K177" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B178" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C178" s="23" t="n">
-        <x:v>8076.4</x:v>
+        <x:v>7792</x:v>
       </x:c>
       <x:c r="D178" s="23" t="n">
-        <x:v>8288.2</x:v>
+        <x:v>8119.6</x:v>
       </x:c>
       <x:c r="E178" s="23" t="n">
-        <x:v>8042</x:v>
+        <x:v>7792</x:v>
       </x:c>
       <x:c r="F178" s="23" t="n">
-        <x:v>8132.8</x:v>
-      </x:c>
-      <x:c r="G178" s="23" t="n">
+        <x:v>8098.8</x:v>
+      </x:c>
+      <x:c r="G178" s="28" t="n">
         <x:f>ROUND(F178-F177,1)</x:f>
-        <x:v>34</x:v>
+        <x:v>270.2</x:v>
       </x:c>
       <x:c r="H178" s="24" t="n">
         <x:f>IFERROR(F178/F177-1,"")</x:f>
-        <x:v>0.004198152812762368</x:v>
+        <x:v>0.034514472574917576</x:v>
       </x:c>
       <x:c r="I178" s="26" t="n">
         <x:f>ROUND(D178-E178,1)</x:f>
-        <x:v>246.2</x:v>
+        <x:v>327.6</x:v>
       </x:c>
       <x:c r="J178" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -13863,148 +13899,148 @@
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B179" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C179" s="23" t="n">
-        <x:v>8145.2</x:v>
+        <x:v>8076.4</x:v>
       </x:c>
       <x:c r="D179" s="23" t="n">
-        <x:v>8287.8</x:v>
+        <x:v>8288.2</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
-        <x:v>8056.2</x:v>
+        <x:v>8042</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>8270</x:v>
+        <x:v>8132.8</x:v>
       </x:c>
       <x:c r="G179" s="23" t="n">
         <x:f>ROUND(F179-F178,1)</x:f>
-        <x:v>137.2</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H179" s="24" t="n">
         <x:f>IFERROR(F179/F178-1,"")</x:f>
-        <x:v>0.016869958685815423</x:v>
+        <x:v>0.004198152812762368</x:v>
       </x:c>
       <x:c r="I179" s="26" t="n">
         <x:f>ROUND(D179-E179,1)</x:f>
-        <x:v>231.6</x:v>
+        <x:v>246.2</x:v>
       </x:c>
       <x:c r="J179" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K179" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B180" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C180" s="23" t="n">
-        <x:v>8377.6</x:v>
+        <x:v>8145.2</x:v>
       </x:c>
       <x:c r="D180" s="23" t="n">
-        <x:v>8648</x:v>
+        <x:v>8287.8</x:v>
       </x:c>
       <x:c r="E180" s="23" t="n">
-        <x:v>8375.4</x:v>
+        <x:v>8056.2</x:v>
       </x:c>
       <x:c r="F180" s="23" t="n">
-        <x:v>8620.8</x:v>
-      </x:c>
-      <x:c r="G180" s="28" t="n">
+        <x:v>8270</x:v>
+      </x:c>
+      <x:c r="G180" s="23" t="n">
         <x:f>ROUND(F180-F179,1)</x:f>
-        <x:v>350.8</x:v>
+        <x:v>137.2</x:v>
       </x:c>
       <x:c r="H180" s="24" t="n">
         <x:f>IFERROR(F180/F179-1,"")</x:f>
-        <x:v>0.042418379685610574</x:v>
+        <x:v>0.016869958685815423</x:v>
       </x:c>
       <x:c r="I180" s="26" t="n">
         <x:f>ROUND(D180-E180,1)</x:f>
-        <x:v>272.6</x:v>
+        <x:v>231.6</x:v>
       </x:c>
       <x:c r="J180" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K180" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B181" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C181" s="23" t="n">
-        <x:v>8691</x:v>
+        <x:v>8377.6</x:v>
       </x:c>
       <x:c r="D181" s="23" t="n">
-        <x:v>8886.8</x:v>
+        <x:v>8648</x:v>
       </x:c>
       <x:c r="E181" s="23" t="n">
-        <x:v>8378.2</x:v>
+        <x:v>8375.4</x:v>
       </x:c>
       <x:c r="F181" s="23" t="n">
-        <x:v>8448.8</x:v>
+        <x:v>8620.8</x:v>
       </x:c>
       <x:c r="G181" s="28" t="n">
         <x:f>ROUND(F181-F180,1)</x:f>
-        <x:v>-172</x:v>
+        <x:v>350.8</x:v>
       </x:c>
       <x:c r="H181" s="24" t="n">
         <x:f>IFERROR(F181/F180-1,"")</x:f>
-        <x:v>-0.01995174461766891</x:v>
+        <x:v>0.042418379685610574</x:v>
       </x:c>
       <x:c r="I181" s="26" t="n">
         <x:f>ROUND(D181-E181,1)</x:f>
-        <x:v>508.6</x:v>
+        <x:v>272.6</x:v>
       </x:c>
       <x:c r="J181" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K181" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B182" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C182" s="23" t="n">
-        <x:v>8418.4</x:v>
+        <x:v>8691</x:v>
       </x:c>
       <x:c r="D182" s="23" t="n">
-        <x:v>8728</x:v>
+        <x:v>8886.8</x:v>
       </x:c>
       <x:c r="E182" s="23" t="n">
-        <x:v>8310</x:v>
+        <x:v>8378.2</x:v>
       </x:c>
       <x:c r="F182" s="23" t="n">
-        <x:v>8469.2</x:v>
-      </x:c>
-      <x:c r="G182" s="23" t="n">
+        <x:v>8448.8</x:v>
+      </x:c>
+      <x:c r="G182" s="28" t="n">
         <x:f>ROUND(F182-F181,1)</x:f>
-        <x:v>20.4</x:v>
+        <x:v>-172</x:v>
       </x:c>
       <x:c r="H182" s="24" t="n">
         <x:f>IFERROR(F182/F181-1,"")</x:f>
-        <x:v>0.0024145440772656013</x:v>
+        <x:v>-0.01995174461766891</x:v>
       </x:c>
       <x:c r="I182" s="26" t="n">
         <x:f>ROUND(D182-E182,1)</x:f>
-        <x:v>418</x:v>
+        <x:v>508.6</x:v>
       </x:c>
       <x:c r="J182" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14015,34 +14051,34 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B183" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C183" s="23" t="n">
-        <x:v>8543</x:v>
+        <x:v>8418.4</x:v>
       </x:c>
       <x:c r="D183" s="23" t="n">
-        <x:v>8658.2</x:v>
+        <x:v>8728</x:v>
       </x:c>
       <x:c r="E183" s="23" t="n">
-        <x:v>8218.2</x:v>
+        <x:v>8310</x:v>
       </x:c>
       <x:c r="F183" s="23" t="n">
-        <x:v>8274.6</x:v>
-      </x:c>
-      <x:c r="G183" s="28" t="n">
+        <x:v>8469.2</x:v>
+      </x:c>
+      <x:c r="G183" s="23" t="n">
         <x:f>ROUND(F183-F182,1)</x:f>
-        <x:v>-194.6</x:v>
+        <x:v>20.4</x:v>
       </x:c>
       <x:c r="H183" s="24" t="n">
         <x:f>IFERROR(F183/F182-1,"")</x:f>
-        <x:v>-0.022977376847872377</x:v>
+        <x:v>0.0024145440772656013</x:v>
       </x:c>
       <x:c r="I183" s="26" t="n">
         <x:f>ROUND(D183-E183,1)</x:f>
-        <x:v>440</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="J183" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14053,34 +14089,34 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B184" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C184" s="23" t="n">
-        <x:v>8298</x:v>
+        <x:v>8543</x:v>
       </x:c>
       <x:c r="D184" s="23" t="n">
-        <x:v>8425</x:v>
+        <x:v>8658.2</x:v>
       </x:c>
       <x:c r="E184" s="23" t="n">
-        <x:v>8101.6</x:v>
+        <x:v>8218.2</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
-        <x:v>8190.6</x:v>
-      </x:c>
-      <x:c r="G184" s="23" t="n">
+        <x:v>8274.6</x:v>
+      </x:c>
+      <x:c r="G184" s="28" t="n">
         <x:f>ROUND(F184-F183,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-194.6</x:v>
       </x:c>
       <x:c r="H184" s="24" t="n">
         <x:f>IFERROR(F184/F183-1,"")</x:f>
-        <x:v>-0.010151548111086983</x:v>
+        <x:v>-0.022977376847872377</x:v>
       </x:c>
       <x:c r="I184" s="26" t="n">
         <x:f>ROUND(D184-E184,1)</x:f>
-        <x:v>323.4</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="J184" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14091,34 +14127,34 @@
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B185" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C185" s="23" t="n">
-        <x:v>8050</x:v>
+        <x:v>8298</x:v>
       </x:c>
       <x:c r="D185" s="23" t="n">
-        <x:v>8237.6</x:v>
+        <x:v>8425</x:v>
       </x:c>
       <x:c r="E185" s="23" t="n">
-        <x:v>7838</x:v>
+        <x:v>8101.6</x:v>
       </x:c>
       <x:c r="F185" s="23" t="n">
-        <x:v>8117.2</x:v>
+        <x:v>8190.6</x:v>
       </x:c>
       <x:c r="G185" s="23" t="n">
         <x:f>ROUND(F185-F184,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H185" s="24" t="n">
         <x:f>IFERROR(F185/F184-1,"")</x:f>
-        <x:v>-0.008961492442556174</x:v>
+        <x:v>-0.010151548111086983</x:v>
       </x:c>
       <x:c r="I185" s="26" t="n">
         <x:f>ROUND(D185-E185,1)</x:f>
-        <x:v>399.6</x:v>
+        <x:v>323.4</x:v>
       </x:c>
       <x:c r="J185" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14129,113 +14165,113 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B186" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C186" s="23" t="n">
-        <x:v>8181.2</x:v>
+        <x:v>8050</x:v>
       </x:c>
       <x:c r="D186" s="23" t="n">
-        <x:v>8718</x:v>
+        <x:v>8237.6</x:v>
       </x:c>
       <x:c r="E186" s="23" t="n">
-        <x:v>8181.2</x:v>
+        <x:v>7838</x:v>
       </x:c>
       <x:c r="F186" s="23" t="n">
-        <x:v>8682.8</x:v>
-      </x:c>
-      <x:c r="G186" s="28" t="n">
+        <x:v>8117.2</x:v>
+      </x:c>
+      <x:c r="G186" s="23" t="n">
         <x:f>ROUND(F186-F185,1)</x:f>
-        <x:v>565.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H186" s="24" t="n">
         <x:f>IFERROR(F186/F185-1,"")</x:f>
-        <x:v>0.06967919972404268</x:v>
+        <x:v>-0.008961492442556174</x:v>
       </x:c>
       <x:c r="I186" s="26" t="n">
         <x:f>ROUND(D186-E186,1)</x:f>
-        <x:v>536.8</x:v>
+        <x:v>399.6</x:v>
       </x:c>
       <x:c r="J186" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K186" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B187" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C187" s="23" t="n">
-        <x:v>8692.8</x:v>
+        <x:v>8181.2</x:v>
       </x:c>
       <x:c r="D187" s="23" t="n">
-        <x:v>8778.8</x:v>
+        <x:v>8718</x:v>
       </x:c>
       <x:c r="E187" s="23" t="n">
-        <x:v>8377</x:v>
+        <x:v>8181.2</x:v>
       </x:c>
       <x:c r="F187" s="23" t="n">
-        <x:v>8447</x:v>
+        <x:v>8682.8</x:v>
       </x:c>
       <x:c r="G187" s="28" t="n">
         <x:f>ROUND(F187-F186,1)</x:f>
-        <x:v>-235.8</x:v>
+        <x:v>565.6</x:v>
       </x:c>
       <x:c r="H187" s="24" t="n">
         <x:f>IFERROR(F187/F186-1,"")</x:f>
-        <x:v>-0.027157138250333945</x:v>
+        <x:v>0.06967919972404268</x:v>
       </x:c>
       <x:c r="I187" s="26" t="n">
         <x:f>ROUND(D187-E187,1)</x:f>
-        <x:v>401.8</x:v>
+        <x:v>536.8</x:v>
       </x:c>
       <x:c r="J187" s="22" t="str">
-        <x:v>IC2606/IC2609</x:v>
+        <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K187" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B188" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C188" s="23" t="n">
-        <x:v>8463.8</x:v>
+        <x:v>8692.8</x:v>
       </x:c>
       <x:c r="D188" s="23" t="n">
-        <x:v>8873.8</x:v>
+        <x:v>8778.8</x:v>
       </x:c>
       <x:c r="E188" s="23" t="n">
-        <x:v>8350.4</x:v>
+        <x:v>8377</x:v>
       </x:c>
       <x:c r="F188" s="23" t="n">
-        <x:v>8538</x:v>
-      </x:c>
-      <x:c r="G188" s="23" t="n">
+        <x:v>8447</x:v>
+      </x:c>
+      <x:c r="G188" s="28" t="n">
         <x:f>ROUND(F188-F187,1)</x:f>
-        <x:v>91</x:v>
+        <x:v>-235.8</x:v>
       </x:c>
       <x:c r="H188" s="24" t="n">
         <x:f>IFERROR(F188/F187-1,"")</x:f>
-        <x:v>0.010773055522670827</x:v>
+        <x:v>-0.027157138250333945</x:v>
       </x:c>
       <x:c r="I188" s="26" t="n">
         <x:f>ROUND(D188-E188,1)</x:f>
-        <x:v>523.4</x:v>
+        <x:v>401.8</x:v>
       </x:c>
       <x:c r="J188" s="22" t="str">
-        <x:v>IC2609</x:v>
+        <x:v>IC2606/IC2609</x:v>
       </x:c>
       <x:c r="K188" s="22" t="n">
         <x:v>5</x:v>
@@ -14243,34 +14279,34 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B189" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C189" s="23" t="n">
-        <x:v>8574.4</x:v>
+        <x:v>8463.8</x:v>
       </x:c>
       <x:c r="D189" s="23" t="n">
-        <x:v>8618</x:v>
+        <x:v>8873.8</x:v>
       </x:c>
       <x:c r="E189" s="23" t="n">
-        <x:v>8173</x:v>
+        <x:v>8350.4</x:v>
       </x:c>
       <x:c r="F189" s="23" t="n">
-        <x:v>8333</x:v>
-      </x:c>
-      <x:c r="G189" s="28" t="n">
+        <x:v>8538</x:v>
+      </x:c>
+      <x:c r="G189" s="23" t="n">
         <x:f>ROUND(F189-F188,1)</x:f>
-        <x:v>-205</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H189" s="24" t="n">
         <x:f>IFERROR(F189/F188-1,"")</x:f>
-        <x:v>-0.024010306863434083</x:v>
+        <x:v>0.010773055522670827</x:v>
       </x:c>
       <x:c r="I189" s="26" t="n">
         <x:f>ROUND(D189-E189,1)</x:f>
-        <x:v>445</x:v>
+        <x:v>523.4</x:v>
       </x:c>
       <x:c r="J189" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14281,34 +14317,34 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B190" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C190" s="23" t="n">
-        <x:v>8303</x:v>
+        <x:v>8574.4</x:v>
       </x:c>
       <x:c r="D190" s="23" t="n">
-        <x:v>8328</x:v>
+        <x:v>8618</x:v>
       </x:c>
       <x:c r="E190" s="23" t="n">
-        <x:v>7362.8</x:v>
+        <x:v>8173</x:v>
       </x:c>
       <x:c r="F190" s="23" t="n">
-        <x:v>7389</x:v>
+        <x:v>8333</x:v>
       </x:c>
       <x:c r="G190" s="28" t="n">
         <x:f>ROUND(F190-F189,1)</x:f>
-        <x:v>-944</x:v>
+        <x:v>-205</x:v>
       </x:c>
       <x:c r="H190" s="24" t="n">
         <x:f>IFERROR(F190/F189-1,"")</x:f>
-        <x:v>-0.11328453138125527</x:v>
+        <x:v>-0.024010306863434083</x:v>
       </x:c>
       <x:c r="I190" s="26" t="n">
         <x:f>ROUND(D190-E190,1)</x:f>
-        <x:v>965.2</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="J190" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14319,34 +14355,34 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B191" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C191" s="23" t="n">
-        <x:v>7490</x:v>
+        <x:v>8303</x:v>
       </x:c>
       <x:c r="D191" s="23" t="n">
-        <x:v>7765.6</x:v>
+        <x:v>8328</x:v>
       </x:c>
       <x:c r="E191" s="23" t="n">
-        <x:v>7092</x:v>
+        <x:v>7362.8</x:v>
       </x:c>
       <x:c r="F191" s="23" t="n">
-        <x:v>7416</x:v>
-      </x:c>
-      <x:c r="G191" s="23" t="n">
+        <x:v>7389</x:v>
+      </x:c>
+      <x:c r="G191" s="28" t="n">
         <x:f>ROUND(F191-F190,1)</x:f>
-        <x:v>27</x:v>
+        <x:v>-944</x:v>
       </x:c>
       <x:c r="H191" s="24" t="n">
         <x:f>IFERROR(F191/F190-1,"")</x:f>
-        <x:v>0.0036540803897686658</x:v>
+        <x:v>-0.11328453138125527</x:v>
       </x:c>
       <x:c r="I191" s="26" t="n">
         <x:f>ROUND(D191-E191,1)</x:f>
-        <x:v>673.6</x:v>
+        <x:v>965.2</x:v>
       </x:c>
       <x:c r="J191" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14357,34 +14393,34 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B192" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C192" s="23" t="n">
-        <x:v>7447</x:v>
+        <x:v>7490</x:v>
       </x:c>
       <x:c r="D192" s="23" t="n">
-        <x:v>7666.6</x:v>
+        <x:v>7765.6</x:v>
       </x:c>
       <x:c r="E192" s="23" t="n">
-        <x:v>7106</x:v>
+        <x:v>7092</x:v>
       </x:c>
       <x:c r="F192" s="23" t="n">
-        <x:v>7395</x:v>
+        <x:v>7416</x:v>
       </x:c>
       <x:c r="G192" s="23" t="n">
         <x:f>ROUND(F192-F191,1)</x:f>
-        <x:v>-21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H192" s="24" t="n">
         <x:f>IFERROR(F192/F191-1,"")</x:f>
-        <x:v>-0.0028317152103559673</x:v>
+        <x:v>0.0036540803897686658</x:v>
       </x:c>
       <x:c r="I192" s="26" t="n">
         <x:f>ROUND(D192-E192,1)</x:f>
-        <x:v>560.6</x:v>
+        <x:v>673.6</x:v>
       </x:c>
       <x:c r="J192" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14395,34 +14431,34 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B193" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C193" s="23" t="n">
-        <x:v>7391</x:v>
+        <x:v>7447</x:v>
       </x:c>
       <x:c r="D193" s="23" t="n">
-        <x:v>7882.6</x:v>
+        <x:v>7666.6</x:v>
       </x:c>
       <x:c r="E193" s="23" t="n">
-        <x:v>7335</x:v>
+        <x:v>7106</x:v>
       </x:c>
       <x:c r="F193" s="23" t="n">
-        <x:v>7877.8</x:v>
-      </x:c>
-      <x:c r="G193" s="28" t="n">
+        <x:v>7395</x:v>
+      </x:c>
+      <x:c r="G193" s="23" t="n">
         <x:f>ROUND(F193-F192,1)</x:f>
-        <x:v>482.8</x:v>
+        <x:v>-21</x:v>
       </x:c>
       <x:c r="H193" s="24" t="n">
         <x:f>IFERROR(F193/F192-1,"")</x:f>
-        <x:v>0.06528735632183902</x:v>
+        <x:v>-0.0028317152103559673</x:v>
       </x:c>
       <x:c r="I193" s="26" t="n">
         <x:f>ROUND(D193-E193,1)</x:f>
-        <x:v>547.6</x:v>
+        <x:v>560.6</x:v>
       </x:c>
       <x:c r="J193" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14433,34 +14469,34 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B194" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C194" s="23" t="n">
-        <x:v>7888</x:v>
+        <x:v>7391</x:v>
       </x:c>
       <x:c r="D194" s="23" t="n">
-        <x:v>8024</x:v>
+        <x:v>7882.6</x:v>
       </x:c>
       <x:c r="E194" s="23" t="n">
-        <x:v>7795.8</x:v>
+        <x:v>7335</x:v>
       </x:c>
       <x:c r="F194" s="23" t="n">
-        <x:v>7861.2</x:v>
-      </x:c>
-      <x:c r="G194" s="23" t="n">
+        <x:v>7877.8</x:v>
+      </x:c>
+      <x:c r="G194" s="28" t="n">
         <x:f>ROUND(F194-F193,1)</x:f>
-        <x:v>-16.6</x:v>
+        <x:v>482.8</x:v>
       </x:c>
       <x:c r="H194" s="24" t="n">
         <x:f>IFERROR(F194/F193-1,"")</x:f>
-        <x:v>-0.0021071872857905127</x:v>
+        <x:v>0.06528735632183902</x:v>
       </x:c>
       <x:c r="I194" s="26" t="n">
         <x:f>ROUND(D194-E194,1)</x:f>
-        <x:v>228.2</x:v>
+        <x:v>547.6</x:v>
       </x:c>
       <x:c r="J194" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14471,34 +14507,34 @@
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B195" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C195" s="23" t="n">
-        <x:v>7885</x:v>
+        <x:v>7888</x:v>
       </x:c>
       <x:c r="D195" s="23" t="n">
-        <x:v>8091.8</x:v>
+        <x:v>8024</x:v>
       </x:c>
       <x:c r="E195" s="23" t="n">
-        <x:v>7669.6</x:v>
+        <x:v>7795.8</x:v>
       </x:c>
       <x:c r="F195" s="23" t="n">
-        <x:v>7762</x:v>
+        <x:v>7861.2</x:v>
       </x:c>
       <x:c r="G195" s="23" t="n">
         <x:f>ROUND(F195-F194,1)</x:f>
-        <x:v>-99.2</x:v>
+        <x:v>-16.6</x:v>
       </x:c>
       <x:c r="H195" s="24" t="n">
         <x:f>IFERROR(F195/F194-1,"")</x:f>
-        <x:v>-0.012618938584439965</x:v>
+        <x:v>-0.0021071872857905127</x:v>
       </x:c>
       <x:c r="I195" s="26" t="n">
         <x:f>ROUND(D195-E195,1)</x:f>
-        <x:v>422.2</x:v>
+        <x:v>228.2</x:v>
       </x:c>
       <x:c r="J195" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14509,34 +14545,34 @@
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B196" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C196" s="23" t="n">
-        <x:v>7757</x:v>
+        <x:v>7885</x:v>
       </x:c>
       <x:c r="D196" s="23" t="n">
-        <x:v>7931</x:v>
+        <x:v>8091.8</x:v>
       </x:c>
       <x:c r="E196" s="23" t="n">
-        <x:v>7496</x:v>
+        <x:v>7669.6</x:v>
       </x:c>
       <x:c r="F196" s="23" t="n">
-        <x:v>7853.8</x:v>
+        <x:v>7762</x:v>
       </x:c>
       <x:c r="G196" s="23" t="n">
         <x:f>ROUND(F196-F195,1)</x:f>
-        <x:v>91.8</x:v>
+        <x:v>-99.2</x:v>
       </x:c>
       <x:c r="H196" s="24" t="n">
         <x:f>IFERROR(F196/F195-1,"")</x:f>
-        <x:v>0.011826848750322139</x:v>
+        <x:v>-0.012618938584439965</x:v>
       </x:c>
       <x:c r="I196" s="26" t="n">
         <x:f>ROUND(D196-E196,1)</x:f>
-        <x:v>435</x:v>
+        <x:v>422.2</x:v>
       </x:c>
       <x:c r="J196" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14547,34 +14583,34 @@
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B197" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C197" s="23" t="n">
-        <x:v>7761</x:v>
+        <x:v>7757</x:v>
       </x:c>
       <x:c r="D197" s="23" t="n">
-        <x:v>7913</x:v>
+        <x:v>7931</x:v>
       </x:c>
       <x:c r="E197" s="23" t="n">
-        <x:v>7568</x:v>
+        <x:v>7496</x:v>
       </x:c>
       <x:c r="F197" s="23" t="n">
-        <x:v>7608</x:v>
-      </x:c>
-      <x:c r="G197" s="28" t="n">
+        <x:v>7853.8</x:v>
+      </x:c>
+      <x:c r="G197" s="23" t="n">
         <x:f>ROUND(F197-F196,1)</x:f>
-        <x:v>-245.8</x:v>
+        <x:v>91.8</x:v>
       </x:c>
       <x:c r="H197" s="24" t="n">
         <x:f>IFERROR(F197/F196-1,"")</x:f>
-        <x:v>-0.03129695179403602</x:v>
+        <x:v>0.011826848750322139</x:v>
       </x:c>
       <x:c r="I197" s="26" t="n">
         <x:f>ROUND(D197-E197,1)</x:f>
-        <x:v>345</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="J197" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14585,192 +14621,192 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B198" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C198" s="23" t="n">
-        <x:v>7665.6</x:v>
+        <x:v>7761</x:v>
       </x:c>
       <x:c r="D198" s="23" t="n">
-        <x:v>7784.2</x:v>
+        <x:v>7913</x:v>
       </x:c>
       <x:c r="E198" s="23" t="n">
-        <x:v>7651.2</x:v>
+        <x:v>7568</x:v>
       </x:c>
       <x:c r="F198" s="23" t="n">
-        <x:v>7716.2</x:v>
-      </x:c>
-      <x:c r="G198" s="23" t="n">
+        <x:v>7608</x:v>
+      </x:c>
+      <x:c r="G198" s="28" t="n">
         <x:f>ROUND(F198-F197,1)</x:f>
-        <x:v>108.2</x:v>
+        <x:v>-245.8</x:v>
       </x:c>
       <x:c r="H198" s="24" t="n">
         <x:f>IFERROR(F198/F197-1,"")</x:f>
-        <x:v>0.014221871713985257</x:v>
-      </x:c>
-      <x:c r="I198" s="23" t="n">
+        <x:v>-0.03129695179403602</x:v>
+      </x:c>
+      <x:c r="I198" s="26" t="n">
         <x:f>ROUND(D198-E198,1)</x:f>
-        <x:v>133</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="J198" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K198" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="22" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B199" s="22" t="str">
+        <x:v>9月7日</x:v>
+      </x:c>
+      <x:c r="C199" s="23" t="n">
+        <x:v>7665.6</x:v>
+      </x:c>
+      <x:c r="D199" s="23" t="n">
+        <x:v>7784.2</x:v>
+      </x:c>
+      <x:c r="E199" s="23" t="n">
+        <x:v>7651.2</x:v>
+      </x:c>
+      <x:c r="F199" s="23" t="n">
+        <x:v>7716.2</x:v>
+      </x:c>
+      <x:c r="G199" s="23" t="n">
+        <x:f>ROUND(F199-F198,1)</x:f>
+        <x:v>108.2</x:v>
+      </x:c>
+      <x:c r="H199" s="24" t="n">
+        <x:f>IFERROR(F199/F198-1,"")</x:f>
+        <x:v>0.014221871713985257</x:v>
+      </x:c>
+      <x:c r="I199" s="23" t="n">
+        <x:f>ROUND(D199-E199,1)</x:f>
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="J199" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+      <x:c r="K199" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="199">
-      <x:c r="A199" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B199" s="30" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C199" s="30"/>
-      <x:c r="D199" s="30"/>
-      <x:c r="E199" s="30"/>
-      <x:c r="F199" s="30"/>
-      <x:c r="G199" s="30"/>
-      <x:c r="H199" s="30"/>
-      <x:c r="I199" s="32" t="n">
-        <x:f>ROUND(SUM(I164:I198),1)</x:f>
-        <x:v>15560</x:v>
-      </x:c>
-      <x:c r="J199" s="30"/>
-      <x:c r="K199" s="30"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B200" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B200" s="30" t="n">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="C200" s="30"/>
       <x:c r="D200" s="30"/>
       <x:c r="E200" s="30"/>
       <x:c r="F200" s="30"/>
       <x:c r="G200" s="30"/>
       <x:c r="H200" s="30"/>
-      <x:c r="I200" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I164:I198),0),1)</x:f>
-        <x:v>444.6</x:v>
+      <x:c r="I200" s="32" t="n">
+        <x:f>ROUND(SUM(I165:I199),1)</x:f>
+        <x:v>15560</x:v>
       </x:c>
       <x:c r="J200" s="30"/>
       <x:c r="K200" s="30"/>
     </x:row>
-    <x:row r="202">
-      <x:c r="A202" s="17" t="str">
+    <x:row r="201">
+      <x:c r="A201" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B201" s="30"/>
+      <x:c r="C201" s="30"/>
+      <x:c r="D201" s="30"/>
+      <x:c r="E201" s="30"/>
+      <x:c r="F201" s="30"/>
+      <x:c r="G201" s="30"/>
+      <x:c r="H201" s="30"/>
+      <x:c r="I201" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I165:I199),0),1)</x:f>
+        <x:v>444.6</x:v>
+      </x:c>
+      <x:c r="J201" s="30"/>
+      <x:c r="K201" s="30"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="17" t="str">
         <x:v>IF主力</x:v>
       </x:c>
-      <x:c r="B202" s="17"/>
-      <x:c r="C202" s="17"/>
-      <x:c r="D202" s="17"/>
-      <x:c r="E202" s="17"/>
-      <x:c r="F202" s="17"/>
-      <x:c r="G202" s="17"/>
-      <x:c r="H202" s="17"/>
-      <x:c r="I202" s="17"/>
-      <x:c r="J202" s="17"/>
-      <x:c r="K202" s="17"/>
-    </x:row>
-    <x:row r="203">
-      <x:c r="A203" s="20" t="str">
+      <x:c r="B203" s="17"/>
+      <x:c r="C203" s="17"/>
+      <x:c r="D203" s="17"/>
+      <x:c r="E203" s="17"/>
+      <x:c r="F203" s="17"/>
+      <x:c r="G203" s="17"/>
+      <x:c r="H203" s="17"/>
+      <x:c r="I203" s="17"/>
+      <x:c r="J203" s="17"/>
+      <x:c r="K203" s="17"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B203" s="20" t="str">
+      <x:c r="B204" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C203" s="20" t="str">
+      <x:c r="C204" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D203" s="20" t="str">
+      <x:c r="D204" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E203" s="20" t="str">
+      <x:c r="E204" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F203" s="20" t="str">
+      <x:c r="F204" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G203" s="20" t="str">
+      <x:c r="G204" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H203" s="20" t="str">
+      <x:c r="H204" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I203" s="20" t="str">
+      <x:c r="I204" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J203" s="20" t="str">
+      <x:c r="J204" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K203" s="20" t="str">
+      <x:c r="K204" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204">
-      <x:c r="A204" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B204" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C204" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="D204" s="23" t="n">
-        <x:v>4785.8</x:v>
-      </x:c>
-      <x:c r="E204" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="F204" s="23" t="n">
-        <x:v>4743.8</x:v>
-      </x:c>
-      <x:c r="G204" s="23"/>
-      <x:c r="H204" s="24"/>
-      <x:c r="I204" s="26" t="n">
-        <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>158.8</x:v>
-      </x:c>
-      <x:c r="J204" s="22" t="str">
-        <x:v>IF2603</x:v>
-      </x:c>
-      <x:c r="K204" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B205" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C205" s="23" t="n">
-        <x:v>4762</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="D205" s="23" t="n">
-        <x:v>4833.2</x:v>
+        <x:v>4785.8</x:v>
       </x:c>
       <x:c r="E205" s="23" t="n">
-        <x:v>4707</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="F205" s="23" t="n">
-        <x:v>4723.2</x:v>
-      </x:c>
-      <x:c r="G205" s="23" t="n">
-        <x:f>ROUND(F205-F204,1)</x:f>
-        <x:v>-20.6</x:v>
-      </x:c>
-      <x:c r="H205" s="24" t="n">
-        <x:f>IFERROR(F205/F204-1,"")</x:f>
-        <x:v>-0.004342510223871221</x:v>
-      </x:c>
+        <x:v>4743.8</x:v>
+      </x:c>
+      <x:c r="G205" s="23"/>
+      <x:c r="H205" s="24"/>
       <x:c r="I205" s="26" t="n">
         <x:f>ROUND(D205-E205,1)</x:f>
-        <x:v>126.2</x:v>
+        <x:v>158.8</x:v>
       </x:c>
       <x:c r="J205" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -14781,34 +14817,34 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B206" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C206" s="23" t="n">
-        <x:v>4711.8</x:v>
+        <x:v>4762</x:v>
       </x:c>
       <x:c r="D206" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4833.2</x:v>
       </x:c>
       <x:c r="E206" s="23" t="n">
-        <x:v>4672.8</x:v>
+        <x:v>4707</x:v>
       </x:c>
       <x:c r="F206" s="23" t="n">
-        <x:v>4709.2</x:v>
+        <x:v>4723.2</x:v>
       </x:c>
       <x:c r="G206" s="23" t="n">
         <x:f>ROUND(F206-F205,1)</x:f>
-        <x:v>-14</x:v>
+        <x:v>-20.6</x:v>
       </x:c>
       <x:c r="H206" s="24" t="n">
         <x:f>IFERROR(F206/F205-1,"")</x:f>
-        <x:v>-0.002964092140921415</x:v>
+        <x:v>-0.004342510223871221</x:v>
       </x:c>
       <x:c r="I206" s="26" t="n">
         <x:f>ROUND(D206-E206,1)</x:f>
-        <x:v>90.2</x:v>
+        <x:v>126.2</x:v>
       </x:c>
       <x:c r="J206" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -14819,34 +14855,34 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B207" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C207" s="23" t="n">
-        <x:v>4726.8</x:v>
+        <x:v>4711.8</x:v>
       </x:c>
       <x:c r="D207" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E207" s="23" t="n">
-        <x:v>4640</x:v>
+        <x:v>4672.8</x:v>
       </x:c>
       <x:c r="F207" s="23" t="n">
-        <x:v>4711</x:v>
+        <x:v>4709.2</x:v>
       </x:c>
       <x:c r="G207" s="23" t="n">
         <x:f>ROUND(F207-F206,1)</x:f>
-        <x:v>1.8</x:v>
+        <x:v>-14</x:v>
       </x:c>
       <x:c r="H207" s="24" t="n">
         <x:f>IFERROR(F207/F206-1,"")</x:f>
-        <x:v>0.00038223052747810016</x:v>
+        <x:v>-0.002964092140921415</x:v>
       </x:c>
       <x:c r="I207" s="26" t="n">
         <x:f>ROUND(D207-E207,1)</x:f>
-        <x:v>153</x:v>
+        <x:v>90.2</x:v>
       </x:c>
       <x:c r="J207" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -14857,34 +14893,34 @@
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B208" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C208" s="23" t="n">
-        <x:v>4680.6</x:v>
+        <x:v>4726.8</x:v>
       </x:c>
       <x:c r="D208" s="23" t="n">
-        <x:v>4724</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E208" s="23" t="n">
-        <x:v>4555.6</x:v>
+        <x:v>4640</x:v>
       </x:c>
       <x:c r="F208" s="23" t="n">
-        <x:v>4637.6</x:v>
+        <x:v>4711</x:v>
       </x:c>
       <x:c r="G208" s="23" t="n">
         <x:f>ROUND(F208-F207,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="H208" s="24" t="n">
         <x:f>IFERROR(F208/F207-1,"")</x:f>
-        <x:v>-0.015580556145192048</x:v>
+        <x:v>0.00038223052747810016</x:v>
       </x:c>
       <x:c r="I208" s="26" t="n">
         <x:f>ROUND(D208-E208,1)</x:f>
-        <x:v>168.4</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="J208" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -14895,34 +14931,34 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
-        <x:v>4688.8</x:v>
+        <x:v>4680.6</x:v>
       </x:c>
       <x:c r="D209" s="23" t="n">
-        <x:v>4733.8</x:v>
+        <x:v>4724</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4555.6</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>4627</x:v>
+        <x:v>4637.6</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>-10.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>-0.0022856649991375155</x:v>
+        <x:v>-0.015580556145192048</x:v>
       </x:c>
       <x:c r="I209" s="26" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>109.8</x:v>
+        <x:v>168.4</x:v>
       </x:c>
       <x:c r="J209" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -14933,110 +14969,110 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B210" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C210" s="23" t="n">
-        <x:v>4680.2</x:v>
+        <x:v>4688.8</x:v>
       </x:c>
       <x:c r="D210" s="23" t="n">
-        <x:v>4768</x:v>
+        <x:v>4733.8</x:v>
       </x:c>
       <x:c r="E210" s="23" t="n">
-        <x:v>4671.2</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="F210" s="23" t="n">
-        <x:v>4713.8</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="G210" s="23" t="n">
         <x:f>ROUND(F210-F209,1)</x:f>
-        <x:v>86.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="H210" s="24" t="n">
         <x:f>IFERROR(F210/F209-1,"")</x:f>
-        <x:v>0.01875945537065049</x:v>
+        <x:v>-0.0022856649991375155</x:v>
       </x:c>
       <x:c r="I210" s="26" t="n">
         <x:f>ROUND(D210-E210,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J210" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K210" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B211" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C211" s="23" t="n">
-        <x:v>4681.2</x:v>
+        <x:v>4680.2</x:v>
       </x:c>
       <x:c r="D211" s="23" t="n">
-        <x:v>4725</x:v>
+        <x:v>4768</x:v>
       </x:c>
       <x:c r="E211" s="23" t="n">
-        <x:v>4560.2</x:v>
+        <x:v>4671.2</x:v>
       </x:c>
       <x:c r="F211" s="23" t="n">
-        <x:v>4646</x:v>
+        <x:v>4713.8</x:v>
       </x:c>
       <x:c r="G211" s="23" t="n">
         <x:f>ROUND(F211-F210,1)</x:f>
-        <x:v>-67.8</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="H211" s="24" t="n">
         <x:f>IFERROR(F211/F210-1,"")</x:f>
-        <x:v>-0.014383300097585816</x:v>
+        <x:v>0.01875945537065049</x:v>
       </x:c>
       <x:c r="I211" s="26" t="n">
         <x:f>ROUND(D211-E211,1)</x:f>
-        <x:v>164.8</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J211" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K211" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B212" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C212" s="23" t="n">
-        <x:v>4600</x:v>
+        <x:v>4681.2</x:v>
       </x:c>
       <x:c r="D212" s="23" t="n">
-        <x:v>4699</x:v>
+        <x:v>4725</x:v>
       </x:c>
       <x:c r="E212" s="23" t="n">
-        <x:v>4500</x:v>
+        <x:v>4560.2</x:v>
       </x:c>
       <x:c r="F212" s="23" t="n">
-        <x:v>4658</x:v>
+        <x:v>4646</x:v>
       </x:c>
       <x:c r="G212" s="23" t="n">
         <x:f>ROUND(F212-F211,1)</x:f>
-        <x:v>12</x:v>
+        <x:v>-67.8</x:v>
       </x:c>
       <x:c r="H212" s="24" t="n">
         <x:f>IFERROR(F212/F211-1,"")</x:f>
-        <x:v>0.00258286698235044</x:v>
+        <x:v>-0.014383300097585816</x:v>
       </x:c>
       <x:c r="I212" s="26" t="n">
         <x:f>ROUND(D212-E212,1)</x:f>
-        <x:v>199</x:v>
+        <x:v>164.8</x:v>
       </x:c>
       <x:c r="J212" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15047,34 +15083,34 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B213" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C213" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="D213" s="23" t="n">
-        <x:v>4718.4</x:v>
+        <x:v>4699</x:v>
       </x:c>
       <x:c r="E213" s="23" t="n">
-        <x:v>4570</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="F213" s="23" t="n">
-        <x:v>4596.8</x:v>
+        <x:v>4658</x:v>
       </x:c>
       <x:c r="G213" s="23" t="n">
         <x:f>ROUND(F213-F212,1)</x:f>
-        <x:v>-61.2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H213" s="24" t="n">
         <x:f>IFERROR(F213/F212-1,"")</x:f>
-        <x:v>-0.0131386861313868</x:v>
+        <x:v>0.00258286698235044</x:v>
       </x:c>
       <x:c r="I213" s="26" t="n">
         <x:f>ROUND(D213-E213,1)</x:f>
-        <x:v>148.4</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="J213" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15085,37 +15121,37 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B214" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C214" s="23" t="n">
-        <x:v>4434.4</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D214" s="23" t="n">
-        <x:v>4466.2</x:v>
+        <x:v>4718.4</x:v>
       </x:c>
       <x:c r="E214" s="23" t="n">
-        <x:v>4307.2</x:v>
+        <x:v>4570</x:v>
       </x:c>
       <x:c r="F214" s="23" t="n">
-        <x:v>4427.4</x:v>
-      </x:c>
-      <x:c r="G214" s="28" t="n">
+        <x:v>4596.8</x:v>
+      </x:c>
+      <x:c r="G214" s="23" t="n">
         <x:f>ROUND(F214-F213,1)</x:f>
-        <x:v>-169.4</x:v>
+        <x:v>-61.2</x:v>
       </x:c>
       <x:c r="H214" s="24" t="n">
         <x:f>IFERROR(F214/F213-1,"")</x:f>
-        <x:v>-0.0368517229376959</x:v>
+        <x:v>-0.0131386861313868</x:v>
       </x:c>
       <x:c r="I214" s="26" t="n">
         <x:f>ROUND(D214-E214,1)</x:f>
-        <x:v>159</x:v>
+        <x:v>148.4</x:v>
       </x:c>
       <x:c r="J214" s="22" t="str">
-        <x:v>IF2606</x:v>
+        <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K214" s="22" t="n">
         <x:v>5</x:v>
@@ -15123,34 +15159,34 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B215" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C215" s="23" t="n">
-        <x:v>4387.2</x:v>
+        <x:v>4434.4</x:v>
       </x:c>
       <x:c r="D215" s="23" t="n">
-        <x:v>4459.8</x:v>
+        <x:v>4466.2</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
-        <x:v>4346</x:v>
+        <x:v>4307.2</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>4362.2</x:v>
-      </x:c>
-      <x:c r="G215" s="23" t="n">
+        <x:v>4427.4</x:v>
+      </x:c>
+      <x:c r="G215" s="28" t="n">
         <x:f>ROUND(F215-F214,1)</x:f>
-        <x:v>-65.2</x:v>
+        <x:v>-169.4</x:v>
       </x:c>
       <x:c r="H215" s="24" t="n">
         <x:f>IFERROR(F215/F214-1,"")</x:f>
-        <x:v>-0.014726476035596514</x:v>
+        <x:v>-0.0368517229376959</x:v>
       </x:c>
       <x:c r="I215" s="26" t="n">
         <x:f>ROUND(D215-E215,1)</x:f>
-        <x:v>113.8</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J215" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15161,110 +15197,110 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B216" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C216" s="23" t="n">
-        <x:v>4369.8</x:v>
+        <x:v>4387.2</x:v>
       </x:c>
       <x:c r="D216" s="23" t="n">
-        <x:v>4591.8</x:v>
+        <x:v>4459.8</x:v>
       </x:c>
       <x:c r="E216" s="23" t="n">
-        <x:v>4347</x:v>
+        <x:v>4346</x:v>
       </x:c>
       <x:c r="F216" s="23" t="n">
-        <x:v>4562</x:v>
-      </x:c>
-      <x:c r="G216" s="28" t="n">
+        <x:v>4362.2</x:v>
+      </x:c>
+      <x:c r="G216" s="23" t="n">
         <x:f>ROUND(F216-F215,1)</x:f>
-        <x:v>199.8</x:v>
+        <x:v>-65.2</x:v>
       </x:c>
       <x:c r="H216" s="24" t="n">
         <x:f>IFERROR(F216/F215-1,"")</x:f>
-        <x:v>0.045802576681491125</x:v>
+        <x:v>-0.014726476035596514</x:v>
       </x:c>
       <x:c r="I216" s="26" t="n">
         <x:f>ROUND(D216-E216,1)</x:f>
-        <x:v>244.8</x:v>
+        <x:v>113.8</x:v>
       </x:c>
       <x:c r="J216" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K216" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B217" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C217" s="23" t="n">
-        <x:v>4542</x:v>
+        <x:v>4369.8</x:v>
       </x:c>
       <x:c r="D217" s="23" t="n">
-        <x:v>4685</x:v>
+        <x:v>4591.8</x:v>
       </x:c>
       <x:c r="E217" s="23" t="n">
-        <x:v>4541.6</x:v>
+        <x:v>4347</x:v>
       </x:c>
       <x:c r="F217" s="23" t="n">
-        <x:v>4667</x:v>
-      </x:c>
-      <x:c r="G217" s="23" t="n">
+        <x:v>4562</x:v>
+      </x:c>
+      <x:c r="G217" s="28" t="n">
         <x:f>ROUND(F217-F216,1)</x:f>
-        <x:v>105</x:v>
+        <x:v>199.8</x:v>
       </x:c>
       <x:c r="H217" s="24" t="n">
         <x:f>IFERROR(F217/F216-1,"")</x:f>
-        <x:v>0.0230162209557212</x:v>
+        <x:v>0.045802576681491125</x:v>
       </x:c>
       <x:c r="I217" s="26" t="n">
         <x:f>ROUND(D217-E217,1)</x:f>
-        <x:v>143.4</x:v>
+        <x:v>244.8</x:v>
       </x:c>
       <x:c r="J217" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K217" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B218" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C218" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4542</x:v>
       </x:c>
       <x:c r="D218" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4685</x:v>
       </x:c>
       <x:c r="E218" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4541.6</x:v>
       </x:c>
       <x:c r="F218" s="23" t="n">
-        <x:v>4713.6</x:v>
+        <x:v>4667</x:v>
       </x:c>
       <x:c r="G218" s="23" t="n">
         <x:f>ROUND(F218-F217,1)</x:f>
-        <x:v>46.6</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H218" s="24" t="n">
         <x:f>IFERROR(F218/F217-1,"")</x:f>
-        <x:v>0.009985001071352029</x:v>
+        <x:v>0.0230162209557212</x:v>
       </x:c>
       <x:c r="I218" s="26" t="n">
         <x:f>ROUND(D218-E218,1)</x:f>
-        <x:v>106.2</x:v>
+        <x:v>143.4</x:v>
       </x:c>
       <x:c r="J218" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15275,148 +15311,148 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B219" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C219" s="23" t="n">
-        <x:v>4720</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D219" s="23" t="n">
-        <x:v>4776.6</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E219" s="23" t="n">
-        <x:v>4687.2</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="F219" s="23" t="n">
-        <x:v>4763.4</x:v>
+        <x:v>4713.6</x:v>
       </x:c>
       <x:c r="G219" s="23" t="n">
         <x:f>ROUND(F219-F218,1)</x:f>
-        <x:v>49.8</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="H219" s="24" t="n">
         <x:f>IFERROR(F219/F218-1,"")</x:f>
-        <x:v>0.010565173116089399</x:v>
-      </x:c>
-      <x:c r="I219" s="23" t="n">
+        <x:v>0.009985001071352029</x:v>
+      </x:c>
+      <x:c r="I219" s="26" t="n">
         <x:f>ROUND(D219-E219,1)</x:f>
-        <x:v>89.4</x:v>
+        <x:v>106.2</x:v>
       </x:c>
       <x:c r="J219" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K219" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B220" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C220" s="23" t="n">
-        <x:v>4808.2</x:v>
+        <x:v>4720</x:v>
       </x:c>
       <x:c r="D220" s="23" t="n">
-        <x:v>4869</x:v>
+        <x:v>4776.6</x:v>
       </x:c>
       <x:c r="E220" s="23" t="n">
-        <x:v>4797</x:v>
+        <x:v>4687.2</x:v>
       </x:c>
       <x:c r="F220" s="23" t="n">
-        <x:v>4836.8</x:v>
+        <x:v>4763.4</x:v>
       </x:c>
       <x:c r="G220" s="23" t="n">
         <x:f>ROUND(F220-F219,1)</x:f>
-        <x:v>73.4</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="H220" s="24" t="n">
         <x:f>IFERROR(F220/F219-1,"")</x:f>
-        <x:v>0.015409161523281867</x:v>
+        <x:v>0.010565173116089399</x:v>
       </x:c>
       <x:c r="I220" s="23" t="n">
         <x:f>ROUND(D220-E220,1)</x:f>
-        <x:v>72</x:v>
+        <x:v>89.4</x:v>
       </x:c>
       <x:c r="J220" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K220" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B221" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C221" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4808.2</x:v>
       </x:c>
       <x:c r="D221" s="23" t="n">
-        <x:v>4995</x:v>
+        <x:v>4869</x:v>
       </x:c>
       <x:c r="E221" s="23" t="n">
-        <x:v>4794</x:v>
+        <x:v>4797</x:v>
       </x:c>
       <x:c r="F221" s="23" t="n">
-        <x:v>4824</x:v>
+        <x:v>4836.8</x:v>
       </x:c>
       <x:c r="G221" s="23" t="n">
         <x:f>ROUND(F221-F220,1)</x:f>
-        <x:v>-12.8</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="H221" s="24" t="n">
         <x:f>IFERROR(F221/F220-1,"")</x:f>
-        <x:v>-0.0026463777704267555</x:v>
-      </x:c>
-      <x:c r="I221" s="26" t="n">
+        <x:v>0.015409161523281867</x:v>
+      </x:c>
+      <x:c r="I221" s="23" t="n">
         <x:f>ROUND(D221-E221,1)</x:f>
-        <x:v>201</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J221" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K221" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B222" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C222" s="23" t="n">
-        <x:v>4810</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D222" s="23" t="n">
-        <x:v>4900.8</x:v>
+        <x:v>4995</x:v>
       </x:c>
       <x:c r="E222" s="23" t="n">
-        <x:v>4735</x:v>
+        <x:v>4794</x:v>
       </x:c>
       <x:c r="F222" s="23" t="n">
-        <x:v>4788.2</x:v>
+        <x:v>4824</x:v>
       </x:c>
       <x:c r="G222" s="23" t="n">
         <x:f>ROUND(F222-F221,1)</x:f>
-        <x:v>-35.8</x:v>
+        <x:v>-12.8</x:v>
       </x:c>
       <x:c r="H222" s="24" t="n">
         <x:f>IFERROR(F222/F221-1,"")</x:f>
-        <x:v>-0.007421227197346614</x:v>
+        <x:v>-0.0026463777704267555</x:v>
       </x:c>
       <x:c r="I222" s="26" t="n">
         <x:f>ROUND(D222-E222,1)</x:f>
-        <x:v>165.8</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="J222" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15427,34 +15463,34 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B223" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C223" s="23" t="n">
-        <x:v>4817.8</x:v>
+        <x:v>4810</x:v>
       </x:c>
       <x:c r="D223" s="23" t="n">
-        <x:v>4928.4</x:v>
+        <x:v>4900.8</x:v>
       </x:c>
       <x:c r="E223" s="23" t="n">
-        <x:v>4793.2</x:v>
+        <x:v>4735</x:v>
       </x:c>
       <x:c r="F223" s="23" t="n">
-        <x:v>4847.8</x:v>
+        <x:v>4788.2</x:v>
       </x:c>
       <x:c r="G223" s="23" t="n">
         <x:f>ROUND(F223-F222,1)</x:f>
-        <x:v>59.6</x:v>
+        <x:v>-35.8</x:v>
       </x:c>
       <x:c r="H223" s="24" t="n">
         <x:f>IFERROR(F223/F222-1,"")</x:f>
-        <x:v>0.01244726619606551</x:v>
+        <x:v>-0.007421227197346614</x:v>
       </x:c>
       <x:c r="I223" s="26" t="n">
         <x:f>ROUND(D223-E223,1)</x:f>
-        <x:v>135.2</x:v>
+        <x:v>165.8</x:v>
       </x:c>
       <x:c r="J223" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15465,34 +15501,34 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B224" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C224" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4817.8</x:v>
       </x:c>
       <x:c r="D224" s="23" t="n">
-        <x:v>4964.6</x:v>
+        <x:v>4928.4</x:v>
       </x:c>
       <x:c r="E224" s="23" t="n">
-        <x:v>4762.2</x:v>
+        <x:v>4793.2</x:v>
       </x:c>
       <x:c r="F224" s="23" t="n">
-        <x:v>4776.8</x:v>
+        <x:v>4847.8</x:v>
       </x:c>
       <x:c r="G224" s="23" t="n">
         <x:f>ROUND(F224-F223,1)</x:f>
-        <x:v>-71</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="H224" s="24" t="n">
         <x:f>IFERROR(F224/F223-1,"")</x:f>
-        <x:v>-0.014645818721894521</x:v>
+        <x:v>0.01244726619606551</x:v>
       </x:c>
       <x:c r="I224" s="26" t="n">
         <x:f>ROUND(D224-E224,1)</x:f>
-        <x:v>202.4</x:v>
+        <x:v>135.2</x:v>
       </x:c>
       <x:c r="J224" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15503,34 +15539,34 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B225" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C225" s="23" t="n">
-        <x:v>4700</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D225" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4964.6</x:v>
       </x:c>
       <x:c r="E225" s="23" t="n">
-        <x:v>4640.2</x:v>
+        <x:v>4762.2</x:v>
       </x:c>
       <x:c r="F225" s="23" t="n">
-        <x:v>4769.8</x:v>
+        <x:v>4776.8</x:v>
       </x:c>
       <x:c r="G225" s="23" t="n">
         <x:f>ROUND(F225-F224,1)</x:f>
-        <x:v>-7</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="H225" s="24" t="n">
         <x:f>IFERROR(F225/F224-1,"")</x:f>
-        <x:v>-0.0014654161781946229</x:v>
+        <x:v>-0.014645818721894521</x:v>
       </x:c>
       <x:c r="I225" s="26" t="n">
         <x:f>ROUND(D225-E225,1)</x:f>
-        <x:v>152.8</x:v>
+        <x:v>202.4</x:v>
       </x:c>
       <x:c r="J225" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15541,113 +15577,113 @@
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B226" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C226" s="23" t="n">
-        <x:v>4819</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="D226" s="23" t="n">
-        <x:v>4971</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E226" s="23" t="n">
-        <x:v>4804.8</x:v>
+        <x:v>4640.2</x:v>
       </x:c>
       <x:c r="F226" s="23" t="n">
-        <x:v>4960.6</x:v>
-      </x:c>
-      <x:c r="G226" s="28" t="n">
+        <x:v>4769.8</x:v>
+      </x:c>
+      <x:c r="G226" s="23" t="n">
         <x:f>ROUND(F226-F225,1)</x:f>
-        <x:v>190.8</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="H226" s="24" t="n">
         <x:f>IFERROR(F226/F225-1,"")</x:f>
-        <x:v>0.040001677219170695</x:v>
+        <x:v>-0.0014654161781946229</x:v>
       </x:c>
       <x:c r="I226" s="26" t="n">
         <x:f>ROUND(D226-E226,1)</x:f>
-        <x:v>166.2</x:v>
+        <x:v>152.8</x:v>
       </x:c>
       <x:c r="J226" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K226" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B227" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C227" s="23" t="n">
-        <x:v>4956</x:v>
+        <x:v>4819</x:v>
       </x:c>
       <x:c r="D227" s="23" t="n">
-        <x:v>5030.2</x:v>
+        <x:v>4971</x:v>
       </x:c>
       <x:c r="E227" s="23" t="n">
-        <x:v>4717</x:v>
+        <x:v>4804.8</x:v>
       </x:c>
       <x:c r="F227" s="23" t="n">
-        <x:v>4748.2</x:v>
+        <x:v>4960.6</x:v>
       </x:c>
       <x:c r="G227" s="28" t="n">
         <x:f>ROUND(F227-F226,1)</x:f>
-        <x:v>-212.4</x:v>
+        <x:v>190.8</x:v>
       </x:c>
       <x:c r="H227" s="24" t="n">
         <x:f>IFERROR(F227/F226-1,"")</x:f>
-        <x:v>-0.04281740112083221</x:v>
+        <x:v>0.040001677219170695</x:v>
       </x:c>
       <x:c r="I227" s="26" t="n">
         <x:f>ROUND(D227-E227,1)</x:f>
-        <x:v>313.2</x:v>
+        <x:v>166.2</x:v>
       </x:c>
       <x:c r="J227" s="22" t="str">
-        <x:v>IF2606/IF2609</x:v>
+        <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K227" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B228" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C228" s="23" t="n">
-        <x:v>4759.4</x:v>
+        <x:v>4956</x:v>
       </x:c>
       <x:c r="D228" s="23" t="n">
-        <x:v>4899.6</x:v>
+        <x:v>5030.2</x:v>
       </x:c>
       <x:c r="E228" s="23" t="n">
-        <x:v>4705</x:v>
+        <x:v>4717</x:v>
       </x:c>
       <x:c r="F228" s="23" t="n">
-        <x:v>4752.2</x:v>
-      </x:c>
-      <x:c r="G228" s="23" t="n">
+        <x:v>4748.2</x:v>
+      </x:c>
+      <x:c r="G228" s="28" t="n">
         <x:f>ROUND(F228-F227,1)</x:f>
-        <x:v>4</x:v>
+        <x:v>-212.4</x:v>
       </x:c>
       <x:c r="H228" s="24" t="n">
         <x:f>IFERROR(F228/F227-1,"")</x:f>
-        <x:v>0.0008424244977043305</x:v>
+        <x:v>-0.04281740112083221</x:v>
       </x:c>
       <x:c r="I228" s="26" t="n">
         <x:f>ROUND(D228-E228,1)</x:f>
-        <x:v>194.6</x:v>
+        <x:v>313.2</x:v>
       </x:c>
       <x:c r="J228" s="22" t="str">
-        <x:v>IF2609</x:v>
+        <x:v>IF2606/IF2609</x:v>
       </x:c>
       <x:c r="K228" s="22" t="n">
         <x:v>5</x:v>
@@ -15655,34 +15691,34 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B229" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C229" s="23" t="n">
-        <x:v>4781</x:v>
+        <x:v>4759.4</x:v>
       </x:c>
       <x:c r="D229" s="23" t="n">
-        <x:v>4822.2</x:v>
+        <x:v>4899.6</x:v>
       </x:c>
       <x:c r="E229" s="23" t="n">
-        <x:v>4665.2</x:v>
+        <x:v>4705</x:v>
       </x:c>
       <x:c r="F229" s="23" t="n">
-        <x:v>4704.6</x:v>
+        <x:v>4752.2</x:v>
       </x:c>
       <x:c r="G229" s="23" t="n">
         <x:f>ROUND(F229-F228,1)</x:f>
-        <x:v>-47.6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H229" s="24" t="n">
         <x:f>IFERROR(F229/F228-1,"")</x:f>
-        <x:v>-0.010016413450612216</x:v>
+        <x:v>0.0008424244977043305</x:v>
       </x:c>
       <x:c r="I229" s="26" t="n">
         <x:f>ROUND(D229-E229,1)</x:f>
-        <x:v>157</x:v>
+        <x:v>194.6</x:v>
       </x:c>
       <x:c r="J229" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -15693,34 +15729,34 @@
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B230" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C230" s="23" t="n">
-        <x:v>4691</x:v>
+        <x:v>4781</x:v>
       </x:c>
       <x:c r="D230" s="23" t="n">
-        <x:v>4739.4</x:v>
+        <x:v>4822.2</x:v>
       </x:c>
       <x:c r="E230" s="23" t="n">
-        <x:v>4441.4</x:v>
+        <x:v>4665.2</x:v>
       </x:c>
       <x:c r="F230" s="23" t="n">
-        <x:v>4473.8</x:v>
-      </x:c>
-      <x:c r="G230" s="28" t="n">
+        <x:v>4704.6</x:v>
+      </x:c>
+      <x:c r="G230" s="23" t="n">
         <x:f>ROUND(F230-F229,1)</x:f>
-        <x:v>-230.8</x:v>
+        <x:v>-47.6</x:v>
       </x:c>
       <x:c r="H230" s="24" t="n">
         <x:f>IFERROR(F230/F229-1,"")</x:f>
-        <x:v>-0.04905836840539046</x:v>
+        <x:v>-0.010016413450612216</x:v>
       </x:c>
       <x:c r="I230" s="26" t="n">
         <x:f>ROUND(D230-E230,1)</x:f>
-        <x:v>298</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="J230" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -15731,34 +15767,34 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B231" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C231" s="23" t="n">
-        <x:v>4530</x:v>
+        <x:v>4691</x:v>
       </x:c>
       <x:c r="D231" s="23" t="n">
-        <x:v>4707.8</x:v>
+        <x:v>4739.4</x:v>
       </x:c>
       <x:c r="E231" s="23" t="n">
-        <x:v>4465</x:v>
+        <x:v>4441.4</x:v>
       </x:c>
       <x:c r="F231" s="23" t="n">
-        <x:v>4578.2</x:v>
-      </x:c>
-      <x:c r="G231" s="23" t="n">
+        <x:v>4473.8</x:v>
+      </x:c>
+      <x:c r="G231" s="28" t="n">
         <x:f>ROUND(F231-F230,1)</x:f>
-        <x:v>104.4</x:v>
+        <x:v>-230.8</x:v>
       </x:c>
       <x:c r="H231" s="24" t="n">
         <x:f>IFERROR(F231/F230-1,"")</x:f>
-        <x:v>0.023335866601099653</x:v>
+        <x:v>-0.04905836840539046</x:v>
       </x:c>
       <x:c r="I231" s="26" t="n">
         <x:f>ROUND(D231-E231,1)</x:f>
-        <x:v>242.8</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="J231" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -15769,34 +15805,34 @@
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B232" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C232" s="23" t="n">
-        <x:v>4589.4</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="D232" s="23" t="n">
-        <x:v>4652.2</x:v>
+        <x:v>4707.8</x:v>
       </x:c>
       <x:c r="E232" s="23" t="n">
-        <x:v>4420</x:v>
+        <x:v>4465</x:v>
       </x:c>
       <x:c r="F232" s="23" t="n">
-        <x:v>4538</x:v>
+        <x:v>4578.2</x:v>
       </x:c>
       <x:c r="G232" s="23" t="n">
         <x:f>ROUND(F232-F231,1)</x:f>
-        <x:v>-40.2</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="H232" s="24" t="n">
         <x:f>IFERROR(F232/F231-1,"")</x:f>
-        <x:v>-0.008780743523655543</x:v>
+        <x:v>0.023335866601099653</x:v>
       </x:c>
       <x:c r="I232" s="26" t="n">
         <x:f>ROUND(D232-E232,1)</x:f>
-        <x:v>232.2</x:v>
+        <x:v>242.8</x:v>
       </x:c>
       <x:c r="J232" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -15807,34 +15843,34 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B233" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C233" s="23" t="n">
-        <x:v>4526.4</x:v>
+        <x:v>4589.4</x:v>
       </x:c>
       <x:c r="D233" s="23" t="n">
-        <x:v>4656.2</x:v>
+        <x:v>4652.2</x:v>
       </x:c>
       <x:c r="E233" s="23" t="n">
-        <x:v>4494.2</x:v>
+        <x:v>4420</x:v>
       </x:c>
       <x:c r="F233" s="23" t="n">
-        <x:v>4645.6</x:v>
+        <x:v>4538</x:v>
       </x:c>
       <x:c r="G233" s="23" t="n">
         <x:f>ROUND(F233-F232,1)</x:f>
-        <x:v>107.6</x:v>
+        <x:v>-40.2</x:v>
       </x:c>
       <x:c r="H233" s="24" t="n">
         <x:f>IFERROR(F233/F232-1,"")</x:f>
-        <x:v>0.02371088585279857</x:v>
+        <x:v>-0.008780743523655543</x:v>
       </x:c>
       <x:c r="I233" s="26" t="n">
         <x:f>ROUND(D233-E233,1)</x:f>
-        <x:v>162</x:v>
+        <x:v>232.2</x:v>
       </x:c>
       <x:c r="J233" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -15845,34 +15881,34 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B234" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C234" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4526.4</x:v>
       </x:c>
       <x:c r="D234" s="23" t="n">
-        <x:v>4681</x:v>
+        <x:v>4656.2</x:v>
       </x:c>
       <x:c r="E234" s="23" t="n">
-        <x:v>4598</x:v>
+        <x:v>4494.2</x:v>
       </x:c>
       <x:c r="F234" s="23" t="n">
-        <x:v>4620.4</x:v>
+        <x:v>4645.6</x:v>
       </x:c>
       <x:c r="G234" s="23" t="n">
         <x:f>ROUND(F234-F233,1)</x:f>
-        <x:v>-25.2</x:v>
+        <x:v>107.6</x:v>
       </x:c>
       <x:c r="H234" s="24" t="n">
         <x:f>IFERROR(F234/F233-1,"")</x:f>
-        <x:v>-0.005424487687274104</x:v>
-      </x:c>
-      <x:c r="I234" s="23" t="n">
+        <x:v>0.02371088585279857</x:v>
+      </x:c>
+      <x:c r="I234" s="26" t="n">
         <x:f>ROUND(D234-E234,1)</x:f>
-        <x:v>83</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J234" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -15883,34 +15919,34 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B235" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C235" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="D235" s="23" t="n">
-        <x:v>4700.6</x:v>
+        <x:v>4681</x:v>
       </x:c>
       <x:c r="E235" s="23" t="n">
-        <x:v>4531.8</x:v>
+        <x:v>4598</x:v>
       </x:c>
       <x:c r="F235" s="23" t="n">
-        <x:v>4576</x:v>
+        <x:v>4620.4</x:v>
       </x:c>
       <x:c r="G235" s="23" t="n">
         <x:f>ROUND(F235-F234,1)</x:f>
-        <x:v>-44.4</x:v>
+        <x:v>-25.2</x:v>
       </x:c>
       <x:c r="H235" s="24" t="n">
         <x:f>IFERROR(F235/F234-1,"")</x:f>
-        <x:v>-0.00960955761405935</x:v>
-      </x:c>
-      <x:c r="I235" s="26" t="n">
+        <x:v>-0.005424487687274104</x:v>
+      </x:c>
+      <x:c r="I235" s="23" t="n">
         <x:f>ROUND(D235-E235,1)</x:f>
-        <x:v>168.8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J235" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -15921,34 +15957,34 @@
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B236" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C236" s="23" t="n">
-        <x:v>4607.4</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="D236" s="23" t="n">
-        <x:v>4620</x:v>
+        <x:v>4700.6</x:v>
       </x:c>
       <x:c r="E236" s="23" t="n">
-        <x:v>4486.4</x:v>
+        <x:v>4531.8</x:v>
       </x:c>
       <x:c r="F236" s="23" t="n">
-        <x:v>4593.6</x:v>
+        <x:v>4576</x:v>
       </x:c>
       <x:c r="G236" s="23" t="n">
         <x:f>ROUND(F236-F235,1)</x:f>
-        <x:v>17.6</x:v>
+        <x:v>-44.4</x:v>
       </x:c>
       <x:c r="H236" s="24" t="n">
         <x:f>IFERROR(F236/F235-1,"")</x:f>
-        <x:v>0.0038461538461538325</x:v>
+        <x:v>-0.00960955761405935</x:v>
       </x:c>
       <x:c r="I236" s="26" t="n">
         <x:f>ROUND(D236-E236,1)</x:f>
-        <x:v>133.6</x:v>
+        <x:v>168.8</x:v>
       </x:c>
       <x:c r="J236" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -15959,34 +15995,34 @@
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B237" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C237" s="23" t="n">
-        <x:v>4553</x:v>
+        <x:v>4607.4</x:v>
       </x:c>
       <x:c r="D237" s="23" t="n">
-        <x:v>4617.8</x:v>
+        <x:v>4620</x:v>
       </x:c>
       <x:c r="E237" s="23" t="n">
-        <x:v>4497.6</x:v>
+        <x:v>4486.4</x:v>
       </x:c>
       <x:c r="F237" s="23" t="n">
-        <x:v>4537.4</x:v>
+        <x:v>4593.6</x:v>
       </x:c>
       <x:c r="G237" s="23" t="n">
         <x:f>ROUND(F237-F236,1)</x:f>
-        <x:v>-56.2</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="H237" s="24" t="n">
         <x:f>IFERROR(F237/F236-1,"")</x:f>
-        <x:v>-0.01223441309648221</x:v>
+        <x:v>0.0038461538461538325</x:v>
       </x:c>
       <x:c r="I237" s="26" t="n">
         <x:f>ROUND(D237-E237,1)</x:f>
-        <x:v>120.2</x:v>
+        <x:v>133.6</x:v>
       </x:c>
       <x:c r="J237" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -15997,192 +16033,192 @@
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B238" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C238" s="23" t="n">
-        <x:v>4562</x:v>
+        <x:v>4553</x:v>
       </x:c>
       <x:c r="D238" s="23" t="n">
-        <x:v>4576.8</x:v>
+        <x:v>4617.8</x:v>
       </x:c>
       <x:c r="E238" s="23" t="n">
+        <x:v>4497.6</x:v>
+      </x:c>
+      <x:c r="F238" s="23" t="n">
         <x:v>4537.4</x:v>
-      </x:c>
-      <x:c r="F238" s="23" t="n">
-        <x:v>4555.6</x:v>
       </x:c>
       <x:c r="G238" s="23" t="n">
         <x:f>ROUND(F238-F237,1)</x:f>
-        <x:v>18.2</x:v>
+        <x:v>-56.2</x:v>
       </x:c>
       <x:c r="H238" s="24" t="n">
         <x:f>IFERROR(F238/F237-1,"")</x:f>
-        <x:v>0.004011107682814208</x:v>
-      </x:c>
-      <x:c r="I238" s="23" t="n">
+        <x:v>-0.01223441309648221</x:v>
+      </x:c>
+      <x:c r="I238" s="26" t="n">
         <x:f>ROUND(D238-E238,1)</x:f>
-        <x:v>39.4</x:v>
+        <x:v>120.2</x:v>
       </x:c>
       <x:c r="J238" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K238" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="22" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B239" s="22" t="str">
+        <x:v>9月7日</x:v>
+      </x:c>
+      <x:c r="C239" s="23" t="n">
+        <x:v>4562</x:v>
+      </x:c>
+      <x:c r="D239" s="23" t="n">
+        <x:v>4576.8</x:v>
+      </x:c>
+      <x:c r="E239" s="23" t="n">
+        <x:v>4537.4</x:v>
+      </x:c>
+      <x:c r="F239" s="23" t="n">
+        <x:v>4555.6</x:v>
+      </x:c>
+      <x:c r="G239" s="23" t="n">
+        <x:f>ROUND(F239-F238,1)</x:f>
+        <x:v>18.2</x:v>
+      </x:c>
+      <x:c r="H239" s="24" t="n">
+        <x:f>IFERROR(F239/F238-1,"")</x:f>
+        <x:v>0.004011107682814208</x:v>
+      </x:c>
+      <x:c r="I239" s="23" t="n">
+        <x:f>ROUND(D239-E239,1)</x:f>
+        <x:v>39.4</x:v>
+      </x:c>
+      <x:c r="J239" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+      <x:c r="K239" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="239">
-      <x:c r="A239" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B239" s="30" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C239" s="30"/>
-      <x:c r="D239" s="30"/>
-      <x:c r="E239" s="30"/>
-      <x:c r="F239" s="30"/>
-      <x:c r="G239" s="30"/>
-      <x:c r="H239" s="30"/>
-      <x:c r="I239" s="32" t="n">
-        <x:f>ROUND(SUM(I204:I238),1)</x:f>
-        <x:v>5512.2</x:v>
-      </x:c>
-      <x:c r="J239" s="30"/>
-      <x:c r="K239" s="30"/>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B240" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B240" s="30" t="n">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="C240" s="30"/>
       <x:c r="D240" s="30"/>
       <x:c r="E240" s="30"/>
       <x:c r="F240" s="30"/>
       <x:c r="G240" s="30"/>
       <x:c r="H240" s="30"/>
-      <x:c r="I240" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I204:I238),0),1)</x:f>
-        <x:v>157.5</x:v>
+      <x:c r="I240" s="32" t="n">
+        <x:f>ROUND(SUM(I205:I239),1)</x:f>
+        <x:v>5512.2</x:v>
       </x:c>
       <x:c r="J240" s="30"/>
       <x:c r="K240" s="30"/>
     </x:row>
-    <x:row r="242">
-      <x:c r="A242" s="17" t="str">
+    <x:row r="241">
+      <x:c r="A241" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B241" s="30"/>
+      <x:c r="C241" s="30"/>
+      <x:c r="D241" s="30"/>
+      <x:c r="E241" s="30"/>
+      <x:c r="F241" s="30"/>
+      <x:c r="G241" s="30"/>
+      <x:c r="H241" s="30"/>
+      <x:c r="I241" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I205:I239),0),1)</x:f>
+        <x:v>157.5</x:v>
+      </x:c>
+      <x:c r="J241" s="30"/>
+      <x:c r="K241" s="30"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="17" t="str">
         <x:v>IH主力</x:v>
       </x:c>
-      <x:c r="B242" s="17"/>
-      <x:c r="C242" s="17"/>
-      <x:c r="D242" s="17"/>
-      <x:c r="E242" s="17"/>
-      <x:c r="F242" s="17"/>
-      <x:c r="G242" s="17"/>
-      <x:c r="H242" s="17"/>
-      <x:c r="I242" s="17"/>
-      <x:c r="J242" s="17"/>
-      <x:c r="K242" s="17"/>
-    </x:row>
-    <x:row r="243">
-      <x:c r="A243" s="20" t="str">
+      <x:c r="B243" s="17"/>
+      <x:c r="C243" s="17"/>
+      <x:c r="D243" s="17"/>
+      <x:c r="E243" s="17"/>
+      <x:c r="F243" s="17"/>
+      <x:c r="G243" s="17"/>
+      <x:c r="H243" s="17"/>
+      <x:c r="I243" s="17"/>
+      <x:c r="J243" s="17"/>
+      <x:c r="K243" s="17"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B243" s="20" t="str">
+      <x:c r="B244" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C243" s="20" t="str">
+      <x:c r="C244" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D243" s="20" t="str">
+      <x:c r="D244" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E243" s="20" t="str">
+      <x:c r="E244" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F243" s="20" t="str">
+      <x:c r="F244" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G243" s="20" t="str">
+      <x:c r="G244" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H243" s="20" t="str">
+      <x:c r="H244" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I243" s="20" t="str">
+      <x:c r="I244" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J243" s="20" t="str">
+      <x:c r="J244" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K243" s="20" t="str">
+      <x:c r="K244" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="244">
-      <x:c r="A244" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B244" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C244" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="D244" s="23" t="n">
-        <x:v>3165.6</x:v>
-      </x:c>
-      <x:c r="E244" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="F244" s="23" t="n">
-        <x:v>3134.8</x:v>
-      </x:c>
-      <x:c r="G244" s="23"/>
-      <x:c r="H244" s="24"/>
-      <x:c r="I244" s="26" t="n">
-        <x:f>ROUND(D244-E244,1)</x:f>
-        <x:v>124.8</x:v>
-      </x:c>
-      <x:c r="J244" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K244" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B245" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C245" s="23" t="n">
-        <x:v>3148.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="D245" s="23" t="n">
-        <x:v>3181.2</x:v>
+        <x:v>3165.6</x:v>
       </x:c>
       <x:c r="E245" s="23" t="n">
-        <x:v>3074.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="F245" s="23" t="n">
-        <x:v>3084.4</x:v>
-      </x:c>
-      <x:c r="G245" s="23" t="n">
-        <x:f>ROUND(F245-F244,1)</x:f>
-        <x:v>-50.4</x:v>
-      </x:c>
-      <x:c r="H245" s="24" t="n">
-        <x:f>IFERROR(F245/F244-1,"")</x:f>
-        <x:v>-0.016077580706903127</x:v>
-      </x:c>
+        <x:v>3134.8</x:v>
+      </x:c>
+      <x:c r="G245" s="23"/>
+      <x:c r="H245" s="24"/>
       <x:c r="I245" s="26" t="n">
         <x:f>ROUND(D245-E245,1)</x:f>
-        <x:v>106.8</x:v>
+        <x:v>124.8</x:v>
       </x:c>
       <x:c r="J245" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16193,34 +16229,34 @@
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B246" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C246" s="23" t="n">
-        <x:v>3081.2</x:v>
+        <x:v>3148.4</x:v>
       </x:c>
       <x:c r="D246" s="23" t="n">
-        <x:v>3102.6</x:v>
+        <x:v>3181.2</x:v>
       </x:c>
       <x:c r="E246" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074.4</x:v>
       </x:c>
       <x:c r="F246" s="23" t="n">
-        <x:v>3037.8</x:v>
+        <x:v>3084.4</x:v>
       </x:c>
       <x:c r="G246" s="23" t="n">
         <x:f>ROUND(F246-F245,1)</x:f>
-        <x:v>-46.6</x:v>
+        <x:v>-50.4</x:v>
       </x:c>
       <x:c r="H246" s="24" t="n">
         <x:f>IFERROR(F246/F245-1,"")</x:f>
-        <x:v>-0.015108286862923093</x:v>
+        <x:v>-0.016077580706903127</x:v>
       </x:c>
       <x:c r="I246" s="26" t="n">
         <x:f>ROUND(D246-E246,1)</x:f>
-        <x:v>66.4</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J246" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16231,34 +16267,34 @@
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B247" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C247" s="23" t="n">
-        <x:v>3049.8</x:v>
+        <x:v>3081.2</x:v>
       </x:c>
       <x:c r="D247" s="23" t="n">
-        <x:v>3136.6</x:v>
+        <x:v>3102.6</x:v>
       </x:c>
       <x:c r="E247" s="23" t="n">
-        <x:v>3044</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="F247" s="23" t="n">
-        <x:v>3074</x:v>
+        <x:v>3037.8</x:v>
       </x:c>
       <x:c r="G247" s="23" t="n">
         <x:f>ROUND(F247-F246,1)</x:f>
-        <x:v>36.2</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H247" s="24" t="n">
         <x:f>IFERROR(F247/F246-1,"")</x:f>
-        <x:v>0.011916518533148901</x:v>
+        <x:v>-0.015108286862923093</x:v>
       </x:c>
       <x:c r="I247" s="26" t="n">
         <x:f>ROUND(D247-E247,1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J247" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16269,34 +16305,34 @@
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B248" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C248" s="23" t="n">
-        <x:v>3039.4</x:v>
+        <x:v>3049.8</x:v>
       </x:c>
       <x:c r="D248" s="23" t="n">
-        <x:v>3081</x:v>
+        <x:v>3136.6</x:v>
       </x:c>
       <x:c r="E248" s="23" t="n">
-        <x:v>2984</x:v>
+        <x:v>3044</x:v>
       </x:c>
       <x:c r="F248" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074</x:v>
       </x:c>
       <x:c r="G248" s="23" t="n">
         <x:f>ROUND(F248-F247,1)</x:f>
-        <x:v>-37.8</x:v>
+        <x:v>36.2</x:v>
       </x:c>
       <x:c r="H248" s="24" t="n">
         <x:f>IFERROR(F248/F247-1,"")</x:f>
-        <x:v>-0.012296681847755453</x:v>
+        <x:v>0.011916518533148901</x:v>
       </x:c>
       <x:c r="I248" s="26" t="n">
         <x:f>ROUND(D248-E248,1)</x:f>
-        <x:v>97</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="J248" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16307,34 +16343,34 @@
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B249" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C249" s="23" t="n">
-        <x:v>3060.6</x:v>
+        <x:v>3039.4</x:v>
       </x:c>
       <x:c r="D249" s="23" t="n">
-        <x:v>3098</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E249" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="F249" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="G249" s="23" t="n">
         <x:f>ROUND(F249-F248,1)</x:f>
-        <x:v>-16.2</x:v>
+        <x:v>-37.8</x:v>
       </x:c>
       <x:c r="H249" s="24" t="n">
         <x:f>IFERROR(F249/F248-1,"")</x:f>
-        <x:v>-0.005335616889532879</x:v>
+        <x:v>-0.012296681847755453</x:v>
       </x:c>
       <x:c r="I249" s="26" t="n">
         <x:f>ROUND(D249-E249,1)</x:f>
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J249" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16345,110 +16381,110 @@
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B250" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C250" s="23" t="n">
-        <x:v>3049.2</x:v>
+        <x:v>3060.6</x:v>
       </x:c>
       <x:c r="D250" s="23" t="n">
-        <x:v>3086.4</x:v>
+        <x:v>3098</x:v>
       </x:c>
       <x:c r="E250" s="23" t="n">
-        <x:v>3022</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="F250" s="23" t="n">
-        <x:v>3045.4</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="G250" s="23" t="n">
         <x:f>ROUND(F250-F249,1)</x:f>
-        <x:v>25.4</x:v>
+        <x:v>-16.2</x:v>
       </x:c>
       <x:c r="H250" s="24" t="n">
         <x:f>IFERROR(F250/F249-1,"")</x:f>
-        <x:v>0.008410596026490191</x:v>
+        <x:v>-0.005335616889532879</x:v>
       </x:c>
       <x:c r="I250" s="26" t="n">
         <x:f>ROUND(D250-E250,1)</x:f>
-        <x:v>64.4</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J250" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K250" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
-        <x:v>3038</x:v>
+        <x:v>3049.2</x:v>
       </x:c>
       <x:c r="D251" s="23" t="n">
-        <x:v>3056</x:v>
+        <x:v>3086.4</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
-        <x:v>2950</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>2990</x:v>
+        <x:v>3045.4</x:v>
       </x:c>
       <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>-55.4</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>-0.018191370591712164</x:v>
+        <x:v>0.008410596026490191</x:v>
       </x:c>
       <x:c r="I251" s="26" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>106</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K251" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B252" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C252" s="23" t="n">
-        <x:v>2965.4</x:v>
+        <x:v>3038</x:v>
       </x:c>
       <x:c r="D252" s="23" t="n">
-        <x:v>2989</x:v>
+        <x:v>3056</x:v>
       </x:c>
       <x:c r="E252" s="23" t="n">
-        <x:v>2912.6</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="F252" s="23" t="n">
-        <x:v>2957</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="G252" s="23" t="n">
         <x:f>ROUND(F252-F251,1)</x:f>
-        <x:v>-33</x:v>
+        <x:v>-55.4</x:v>
       </x:c>
       <x:c r="H252" s="24" t="n">
         <x:f>IFERROR(F252/F251-1,"")</x:f>
-        <x:v>-0.011036789297658833</x:v>
+        <x:v>-0.018191370591712164</x:v>
       </x:c>
       <x:c r="I252" s="26" t="n">
         <x:f>ROUND(D252-E252,1)</x:f>
-        <x:v>76.4</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J252" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16459,34 +16495,34 @@
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B253" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C253" s="23" t="n">
-        <x:v>2953</x:v>
+        <x:v>2965.4</x:v>
       </x:c>
       <x:c r="D253" s="23" t="n">
-        <x:v>2996.6</x:v>
+        <x:v>2989</x:v>
       </x:c>
       <x:c r="E253" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2912.6</x:v>
       </x:c>
       <x:c r="F253" s="23" t="n">
-        <x:v>2898.4</x:v>
+        <x:v>2957</x:v>
       </x:c>
       <x:c r="G253" s="23" t="n">
         <x:f>ROUND(F253-F252,1)</x:f>
-        <x:v>-58.6</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="H253" s="24" t="n">
         <x:f>IFERROR(F253/F252-1,"")</x:f>
-        <x:v>-0.019817382482245516</x:v>
+        <x:v>-0.011036789297658833</x:v>
       </x:c>
       <x:c r="I253" s="26" t="n">
         <x:f>ROUND(D253-E253,1)</x:f>
-        <x:v>100.6</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="J253" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16497,37 +16533,37 @@
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B254" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C254" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2953</x:v>
       </x:c>
       <x:c r="D254" s="23" t="n">
-        <x:v>2847.6</x:v>
+        <x:v>2996.6</x:v>
       </x:c>
       <x:c r="E254" s="23" t="n">
-        <x:v>2750.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="F254" s="23" t="n">
-        <x:v>2814.4</x:v>
+        <x:v>2898.4</x:v>
       </x:c>
       <x:c r="G254" s="23" t="n">
         <x:f>ROUND(F254-F253,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-58.6</x:v>
       </x:c>
       <x:c r="H254" s="24" t="n">
         <x:f>IFERROR(F254/F253-1,"")</x:f>
-        <x:v>-0.028981507038365995</x:v>
+        <x:v>-0.019817382482245516</x:v>
       </x:c>
       <x:c r="I254" s="26" t="n">
         <x:f>ROUND(D254-E254,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="J254" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K254" s="22" t="n">
         <x:v>5</x:v>
@@ -16535,34 +16571,34 @@
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B255" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C255" s="23" t="n">
-        <x:v>2794.8</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D255" s="23" t="n">
-        <x:v>2865.4</x:v>
+        <x:v>2847.6</x:v>
       </x:c>
       <x:c r="E255" s="23" t="n">
-        <x:v>2780.4</x:v>
+        <x:v>2750.8</x:v>
       </x:c>
       <x:c r="F255" s="23" t="n">
-        <x:v>2804.4</x:v>
+        <x:v>2814.4</x:v>
       </x:c>
       <x:c r="G255" s="23" t="n">
         <x:f>ROUND(F255-F254,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H255" s="24" t="n">
         <x:f>IFERROR(F255/F254-1,"")</x:f>
-        <x:v>-0.0035531552018192025</x:v>
+        <x:v>-0.028981507038365995</x:v>
       </x:c>
       <x:c r="I255" s="26" t="n">
         <x:f>ROUND(D255-E255,1)</x:f>
-        <x:v>85</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J255" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -16573,110 +16609,110 @@
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B256" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C256" s="23" t="n">
-        <x:v>2810.4</x:v>
+        <x:v>2794.8</x:v>
       </x:c>
       <x:c r="D256" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2865.4</x:v>
       </x:c>
       <x:c r="E256" s="23" t="n">
-        <x:v>2797.2</x:v>
+        <x:v>2780.4</x:v>
       </x:c>
       <x:c r="F256" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2804.4</x:v>
       </x:c>
       <x:c r="G256" s="23" t="n">
         <x:f>ROUND(F256-F255,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H256" s="24" t="n">
         <x:f>IFERROR(F256/F255-1,"")</x:f>
-        <x:v>0.02453287690771644</x:v>
+        <x:v>-0.0035531552018192025</x:v>
       </x:c>
       <x:c r="I256" s="26" t="n">
         <x:f>ROUND(D256-E256,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J256" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K256" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B257" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C257" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2810.4</x:v>
       </x:c>
       <x:c r="D257" s="23" t="n">
-        <x:v>2930.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="E257" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2797.2</x:v>
       </x:c>
       <x:c r="F257" s="23" t="n">
-        <x:v>2888</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="G257" s="23" t="n">
         <x:f>ROUND(F257-F256,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>68.8</x:v>
       </x:c>
       <x:c r="H257" s="24" t="n">
         <x:f>IFERROR(F257/F256-1,"")</x:f>
-        <x:v>0.005151051092858294</x:v>
+        <x:v>0.02453287690771644</x:v>
       </x:c>
       <x:c r="I257" s="26" t="n">
         <x:f>ROUND(D257-E257,1)</x:f>
-        <x:v>70.8</x:v>
+        <x:v>98.8</x:v>
       </x:c>
       <x:c r="J257" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K257" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B258" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C258" s="23" t="n">
-        <x:v>2900.8</x:v>
+        <x:v>2864.6</x:v>
       </x:c>
       <x:c r="D258" s="23" t="n">
-        <x:v>2934.2</x:v>
+        <x:v>2930.8</x:v>
       </x:c>
       <x:c r="E258" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="F258" s="23" t="n">
-        <x:v>2929</x:v>
+        <x:v>2888</x:v>
       </x:c>
       <x:c r="G258" s="23" t="n">
         <x:f>ROUND(F258-F257,1)</x:f>
-        <x:v>41</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H258" s="24" t="n">
         <x:f>IFERROR(F258/F257-1,"")</x:f>
-        <x:v>0.014196675900276956</x:v>
-      </x:c>
-      <x:c r="I258" s="23" t="n">
+        <x:v>0.005151051092858294</x:v>
+      </x:c>
+      <x:c r="I258" s="26" t="n">
         <x:f>ROUND(D258-E258,1)</x:f>
-        <x:v>43.2</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="J258" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -16687,148 +16723,148 @@
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B259" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C259" s="23" t="n">
-        <x:v>2929.2</x:v>
+        <x:v>2900.8</x:v>
       </x:c>
       <x:c r="D259" s="23" t="n">
-        <x:v>2970</x:v>
+        <x:v>2934.2</x:v>
       </x:c>
       <x:c r="E259" s="23" t="n">
-        <x:v>2917</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F259" s="23" t="n">
-        <x:v>2968.8</x:v>
+        <x:v>2929</x:v>
       </x:c>
       <x:c r="G259" s="23" t="n">
         <x:f>ROUND(F259-F258,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H259" s="24" t="n">
         <x:f>IFERROR(F259/F258-1,"")</x:f>
-        <x:v>0.013588255377261937</x:v>
+        <x:v>0.014196675900276956</x:v>
       </x:c>
       <x:c r="I259" s="23" t="n">
         <x:f>ROUND(D259-E259,1)</x:f>
-        <x:v>53</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J259" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K259" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B260" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C260" s="23" t="n">
-        <x:v>2995.2</x:v>
+        <x:v>2929.2</x:v>
       </x:c>
       <x:c r="D260" s="23" t="n">
-        <x:v>3024.8</x:v>
+        <x:v>2970</x:v>
       </x:c>
       <x:c r="E260" s="23" t="n">
-        <x:v>2969.2</x:v>
+        <x:v>2917</x:v>
       </x:c>
       <x:c r="F260" s="23" t="n">
-        <x:v>2981.6</x:v>
+        <x:v>2968.8</x:v>
       </x:c>
       <x:c r="G260" s="23" t="n">
         <x:f>ROUND(F260-F259,1)</x:f>
-        <x:v>12.8</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="H260" s="24" t="n">
         <x:f>IFERROR(F260/F259-1,"")</x:f>
-        <x:v>0.0043115063325247505</x:v>
+        <x:v>0.013588255377261937</x:v>
       </x:c>
       <x:c r="I260" s="23" t="n">
         <x:f>ROUND(D260-E260,1)</x:f>
-        <x:v>55.6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J260" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K260" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B261" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C261" s="23" t="n">
-        <x:v>2997.6</x:v>
+        <x:v>2995.2</x:v>
       </x:c>
       <x:c r="D261" s="23" t="n">
-        <x:v>3041.8</x:v>
+        <x:v>3024.8</x:v>
       </x:c>
       <x:c r="E261" s="23" t="n">
-        <x:v>2927</x:v>
+        <x:v>2969.2</x:v>
       </x:c>
       <x:c r="F261" s="23" t="n">
-        <x:v>2945</x:v>
+        <x:v>2981.6</x:v>
       </x:c>
       <x:c r="G261" s="23" t="n">
         <x:f>ROUND(F261-F260,1)</x:f>
-        <x:v>-36.6</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="H261" s="24" t="n">
         <x:f>IFERROR(F261/F260-1,"")</x:f>
-        <x:v>-0.012275288435739218</x:v>
-      </x:c>
-      <x:c r="I261" s="26" t="n">
+        <x:v>0.0043115063325247505</x:v>
+      </x:c>
+      <x:c r="I261" s="23" t="n">
         <x:f>ROUND(D261-E261,1)</x:f>
-        <x:v>114.8</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="J261" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K261" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B262" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C262" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2997.6</x:v>
       </x:c>
       <x:c r="D262" s="23" t="n">
-        <x:v>2981.8</x:v>
+        <x:v>3041.8</x:v>
       </x:c>
       <x:c r="E262" s="23" t="n">
-        <x:v>2893.2</x:v>
+        <x:v>2927</x:v>
       </x:c>
       <x:c r="F262" s="23" t="n">
-        <x:v>2899.2</x:v>
+        <x:v>2945</x:v>
       </x:c>
       <x:c r="G262" s="23" t="n">
         <x:f>ROUND(F262-F261,1)</x:f>
-        <x:v>-45.8</x:v>
+        <x:v>-36.6</x:v>
       </x:c>
       <x:c r="H262" s="24" t="n">
         <x:f>IFERROR(F262/F261-1,"")</x:f>
-        <x:v>-0.015551782682512783</x:v>
+        <x:v>-0.012275288435739218</x:v>
       </x:c>
       <x:c r="I262" s="26" t="n">
         <x:f>ROUND(D262-E262,1)</x:f>
-        <x:v>88.6</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="J262" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -16839,34 +16875,34 @@
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B263" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C263" s="23" t="n">
-        <x:v>2910.8</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D263" s="23" t="n">
-        <x:v>2960</x:v>
+        <x:v>2981.8</x:v>
       </x:c>
       <x:c r="E263" s="23" t="n">
-        <x:v>2871</x:v>
+        <x:v>2893.2</x:v>
       </x:c>
       <x:c r="F263" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2899.2</x:v>
       </x:c>
       <x:c r="G263" s="23" t="n">
         <x:f>ROUND(F263-F262,1)</x:f>
-        <x:v>1.4</x:v>
+        <x:v>-45.8</x:v>
       </x:c>
       <x:c r="H263" s="24" t="n">
         <x:f>IFERROR(F263/F262-1,"")</x:f>
-        <x:v>0.0004828918322297149</x:v>
+        <x:v>-0.015551782682512783</x:v>
       </x:c>
       <x:c r="I263" s="26" t="n">
         <x:f>ROUND(D263-E263,1)</x:f>
-        <x:v>89</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="J263" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -16877,34 +16913,34 @@
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B264" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C264" s="23" t="n">
-        <x:v>2901</x:v>
+        <x:v>2910.8</x:v>
       </x:c>
       <x:c r="D264" s="23" t="n">
-        <x:v>2924.2</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="E264" s="23" t="n">
-        <x:v>2841.6</x:v>
+        <x:v>2871</x:v>
       </x:c>
       <x:c r="F264" s="23" t="n">
-        <x:v>2844</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="G264" s="23" t="n">
         <x:f>ROUND(F264-F263,1)</x:f>
-        <x:v>-56.6</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H264" s="24" t="n">
         <x:f>IFERROR(F264/F263-1,"")</x:f>
-        <x:v>-0.019513204164655518</x:v>
+        <x:v>0.0004828918322297149</x:v>
       </x:c>
       <x:c r="I264" s="26" t="n">
         <x:f>ROUND(D264-E264,1)</x:f>
-        <x:v>82.6</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J264" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -16915,34 +16951,34 @@
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B265" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C265" s="23" t="n">
-        <x:v>2808.4</x:v>
+        <x:v>2901</x:v>
       </x:c>
       <x:c r="D265" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2924.2</x:v>
       </x:c>
       <x:c r="E265" s="23" t="n">
-        <x:v>2791.2</x:v>
+        <x:v>2841.6</x:v>
       </x:c>
       <x:c r="F265" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G265" s="23" t="n">
         <x:f>ROUND(F265-F264,1)</x:f>
-        <x:v>53.2</x:v>
+        <x:v>-56.6</x:v>
       </x:c>
       <x:c r="H265" s="24" t="n">
         <x:f>IFERROR(F265/F264-1,"")</x:f>
-        <x:v>0.01870604781997187</x:v>
+        <x:v>-0.019513204164655518</x:v>
       </x:c>
       <x:c r="I265" s="26" t="n">
         <x:f>ROUND(D265-E265,1)</x:f>
-        <x:v>111.4</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J265" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -16953,113 +16989,113 @@
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B266" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C266" s="23" t="n">
-        <x:v>2926.2</x:v>
+        <x:v>2808.4</x:v>
       </x:c>
       <x:c r="D266" s="23" t="n">
-        <x:v>2954.6</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="E266" s="23" t="n">
-        <x:v>2903.4</x:v>
+        <x:v>2791.2</x:v>
       </x:c>
       <x:c r="F266" s="23" t="n">
-        <x:v>2941</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G266" s="23" t="n">
         <x:f>ROUND(F266-F265,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="H266" s="24" t="n">
         <x:f>IFERROR(F266/F265-1,"")</x:f>
-        <x:v>0.01511804500897429</x:v>
-      </x:c>
-      <x:c r="I266" s="23" t="n">
+        <x:v>0.01870604781997187</x:v>
+      </x:c>
+      <x:c r="I266" s="26" t="n">
         <x:f>ROUND(D266-E266,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="J266" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K266" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B267" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C267" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2926.2</x:v>
       </x:c>
       <x:c r="D267" s="23" t="n">
-        <x:v>2996</x:v>
+        <x:v>2954.6</x:v>
       </x:c>
       <x:c r="E267" s="23" t="n">
-        <x:v>2834.8</x:v>
+        <x:v>2903.4</x:v>
       </x:c>
       <x:c r="F267" s="23" t="n">
-        <x:v>2859</x:v>
+        <x:v>2941</x:v>
       </x:c>
       <x:c r="G267" s="23" t="n">
         <x:f>ROUND(F267-F266,1)</x:f>
-        <x:v>-82</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="H267" s="24" t="n">
         <x:f>IFERROR(F267/F266-1,"")</x:f>
-        <x:v>-0.02788167290037402</x:v>
-      </x:c>
-      <x:c r="I267" s="26" t="n">
+        <x:v>0.01511804500897429</x:v>
+      </x:c>
+      <x:c r="I267" s="23" t="n">
         <x:f>ROUND(D267-E267,1)</x:f>
-        <x:v>161.2</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J267" s="22" t="str">
-        <x:v>IH2606/IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K267" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B268" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C268" s="23" t="n">
-        <x:v>2870</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D268" s="23" t="n">
-        <x:v>2976</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="E268" s="23" t="n">
-        <x:v>2861.8</x:v>
+        <x:v>2834.8</x:v>
       </x:c>
       <x:c r="F268" s="23" t="n">
-        <x:v>2886.6</x:v>
+        <x:v>2859</x:v>
       </x:c>
       <x:c r="G268" s="23" t="n">
         <x:f>ROUND(F268-F267,1)</x:f>
-        <x:v>27.6</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="H268" s="24" t="n">
         <x:f>IFERROR(F268/F267-1,"")</x:f>
-        <x:v>0.009653725078698772</x:v>
+        <x:v>-0.02788167290037402</x:v>
       </x:c>
       <x:c r="I268" s="26" t="n">
         <x:f>ROUND(D268-E268,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>161.2</x:v>
       </x:c>
       <x:c r="J268" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606/IH2609</x:v>
       </x:c>
       <x:c r="K268" s="22" t="n">
         <x:v>5</x:v>
@@ -17067,34 +17103,34 @@
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B269" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C269" s="23" t="n">
-        <x:v>2899</x:v>
+        <x:v>2870</x:v>
       </x:c>
       <x:c r="D269" s="23" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="E269" s="23" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2861.8</x:v>
       </x:c>
       <x:c r="F269" s="23" t="n">
-        <x:v>2910.2</x:v>
+        <x:v>2886.6</x:v>
       </x:c>
       <x:c r="G269" s="23" t="n">
         <x:f>ROUND(F269-F268,1)</x:f>
-        <x:v>23.6</x:v>
+        <x:v>27.6</x:v>
       </x:c>
       <x:c r="H269" s="24" t="n">
         <x:f>IFERROR(F269/F268-1,"")</x:f>
-        <x:v>0.008175708445922414</x:v>
+        <x:v>0.009653725078698772</x:v>
       </x:c>
       <x:c r="I269" s="26" t="n">
         <x:f>ROUND(D269-E269,1)</x:f>
-        <x:v>121.4</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="J269" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17105,34 +17141,34 @@
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B270" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C270" s="23" t="n">
-        <x:v>2895.8</x:v>
+        <x:v>2899</x:v>
       </x:c>
       <x:c r="D270" s="23" t="n">
-        <x:v>2924</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="E270" s="23" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="F270" s="23" t="n">
-        <x:v>2796.4</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="G270" s="23" t="n">
         <x:f>ROUND(F270-F269,1)</x:f>
-        <x:v>-113.8</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="H270" s="24" t="n">
         <x:f>IFERROR(F270/F269-1,"")</x:f>
-        <x:v>-0.039103841660366845</x:v>
+        <x:v>0.008175708445922414</x:v>
       </x:c>
       <x:c r="I270" s="26" t="n">
         <x:f>ROUND(D270-E270,1)</x:f>
-        <x:v>141.4</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J270" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17143,34 +17179,34 @@
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B271" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C271" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2895.8</x:v>
       </x:c>
       <x:c r="D271" s="23" t="n">
-        <x:v>2978</x:v>
+        <x:v>2924</x:v>
       </x:c>
       <x:c r="E271" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="F271" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2796.4</x:v>
       </x:c>
       <x:c r="G271" s="23" t="n">
         <x:f>ROUND(F271-F270,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>-113.8</x:v>
       </x:c>
       <x:c r="H271" s="24" t="n">
         <x:f>IFERROR(F271/F270-1,"")</x:f>
-        <x:v>0.040623658990130096</x:v>
+        <x:v>-0.039103841660366845</x:v>
       </x:c>
       <x:c r="I271" s="26" t="n">
         <x:f>ROUND(D271-E271,1)</x:f>
-        <x:v>158</x:v>
+        <x:v>141.4</x:v>
       </x:c>
       <x:c r="J271" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17181,34 +17217,34 @@
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B272" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C272" s="23" t="n">
-        <x:v>2929.6</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="D272" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E272" s="23" t="n">
-        <x:v>2847.2</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="F272" s="23" t="n">
-        <x:v>2891.8</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G272" s="23" t="n">
         <x:f>ROUND(F272-F271,1)</x:f>
-        <x:v>-18.2</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="H272" s="24" t="n">
         <x:f>IFERROR(F272/F271-1,"")</x:f>
-        <x:v>-0.006254295532646004</x:v>
+        <x:v>0.040623658990130096</x:v>
       </x:c>
       <x:c r="I272" s="26" t="n">
         <x:f>ROUND(D272-E272,1)</x:f>
-        <x:v>82.8</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J272" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17219,34 +17255,34 @@
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B273" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C273" s="23" t="n">
-        <x:v>2882.4</x:v>
+        <x:v>2929.6</x:v>
       </x:c>
       <x:c r="D273" s="23" t="n">
-        <x:v>2930.6</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="E273" s="23" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2847.2</x:v>
       </x:c>
       <x:c r="F273" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2891.8</x:v>
       </x:c>
       <x:c r="G273" s="23" t="n">
         <x:f>ROUND(F273-F272,1)</x:f>
-        <x:v>38.2</x:v>
+        <x:v>-18.2</x:v>
       </x:c>
       <x:c r="H273" s="24" t="n">
         <x:f>IFERROR(F273/F272-1,"")</x:f>
-        <x:v>0.013209765543951812</x:v>
+        <x:v>-0.006254295532646004</x:v>
       </x:c>
       <x:c r="I273" s="26" t="n">
         <x:f>ROUND(D273-E273,1)</x:f>
-        <x:v>84.8</x:v>
+        <x:v>82.8</x:v>
       </x:c>
       <x:c r="J273" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17257,34 +17293,34 @@
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B274" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C274" s="23" t="n">
+        <x:v>2882.4</x:v>
+      </x:c>
+      <x:c r="D274" s="23" t="n">
+        <x:v>2930.6</x:v>
+      </x:c>
+      <x:c r="E274" s="23" t="n">
+        <x:v>2845.8</x:v>
+      </x:c>
+      <x:c r="F274" s="23" t="n">
         <x:v>2930</x:v>
-      </x:c>
-      <x:c r="D274" s="23" t="n">
-        <x:v>2949.6</x:v>
-      </x:c>
-      <x:c r="E274" s="23" t="n">
-        <x:v>2877</x:v>
-      </x:c>
-      <x:c r="F274" s="23" t="n">
-        <x:v>2890</x:v>
       </x:c>
       <x:c r="G274" s="23" t="n">
         <x:f>ROUND(F274-F273,1)</x:f>
-        <x:v>-40</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="H274" s="24" t="n">
         <x:f>IFERROR(F274/F273-1,"")</x:f>
-        <x:v>-0.013651877133105783</x:v>
+        <x:v>0.013209765543951812</x:v>
       </x:c>
       <x:c r="I274" s="26" t="n">
         <x:f>ROUND(D274-E274,1)</x:f>
-        <x:v>72.6</x:v>
+        <x:v>84.8</x:v>
       </x:c>
       <x:c r="J274" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17295,34 +17331,34 @@
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B275" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C275" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="D275" s="23" t="n">
-        <x:v>2921.2</x:v>
+        <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E275" s="23" t="n">
-        <x:v>2843</x:v>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="F275" s="23" t="n">
-        <x:v>2861</x:v>
+        <x:v>2890</x:v>
       </x:c>
       <x:c r="G275" s="23" t="n">
         <x:f>ROUND(F275-F274,1)</x:f>
-        <x:v>-29</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="H275" s="24" t="n">
         <x:f>IFERROR(F275/F274-1,"")</x:f>
-        <x:v>-0.01003460207612461</x:v>
+        <x:v>-0.013651877133105783</x:v>
       </x:c>
       <x:c r="I275" s="26" t="n">
         <x:f>ROUND(D275-E275,1)</x:f>
-        <x:v>78.2</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="J275" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17333,34 +17369,34 @@
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B276" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C276" s="23" t="n">
-        <x:v>2856.4</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D276" s="23" t="n">
-        <x:v>2918.2</x:v>
+        <x:v>2921.2</x:v>
       </x:c>
       <x:c r="E276" s="23" t="n">
-        <x:v>2837.4</x:v>
+        <x:v>2843</x:v>
       </x:c>
       <x:c r="F276" s="23" t="n">
-        <x:v>2911.4</x:v>
+        <x:v>2861</x:v>
       </x:c>
       <x:c r="G276" s="23" t="n">
         <x:f>ROUND(F276-F275,1)</x:f>
-        <x:v>50.4</x:v>
+        <x:v>-29</x:v>
       </x:c>
       <x:c r="H276" s="24" t="n">
         <x:f>IFERROR(F276/F275-1,"")</x:f>
-        <x:v>0.01761621810555747</x:v>
+        <x:v>-0.01003460207612461</x:v>
       </x:c>
       <x:c r="I276" s="26" t="n">
         <x:f>ROUND(D276-E276,1)</x:f>
-        <x:v>80.8</x:v>
+        <x:v>78.2</x:v>
       </x:c>
       <x:c r="J276" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17371,34 +17407,34 @@
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B277" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C277" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2856.4</x:v>
       </x:c>
       <x:c r="D277" s="23" t="n">
-        <x:v>2949.4</x:v>
+        <x:v>2918.2</x:v>
       </x:c>
       <x:c r="E277" s="23" t="n">
-        <x:v>2877.6</x:v>
+        <x:v>2837.4</x:v>
       </x:c>
       <x:c r="F277" s="23" t="n">
-        <x:v>2915.8</x:v>
+        <x:v>2911.4</x:v>
       </x:c>
       <x:c r="G277" s="23" t="n">
         <x:f>ROUND(F277-F276,1)</x:f>
-        <x:v>4.4</x:v>
+        <x:v>50.4</x:v>
       </x:c>
       <x:c r="H277" s="24" t="n">
         <x:f>IFERROR(F277/F276-1,"")</x:f>
-        <x:v>0.0015113004053033396</x:v>
+        <x:v>0.01761621810555747</x:v>
       </x:c>
       <x:c r="I277" s="26" t="n">
         <x:f>ROUND(D277-E277,1)</x:f>
-        <x:v>71.8</x:v>
+        <x:v>80.8</x:v>
       </x:c>
       <x:c r="J277" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17409,192 +17445,192 @@
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B278" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C278" s="23" t="n">
-        <x:v>2923.2</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D278" s="23" t="n">
-        <x:v>2931.4</x:v>
+        <x:v>2949.4</x:v>
       </x:c>
       <x:c r="E278" s="23" t="n">
-        <x:v>2892.2</x:v>
+        <x:v>2877.6</x:v>
       </x:c>
       <x:c r="F278" s="23" t="n">
-        <x:v>2898.8</x:v>
+        <x:v>2915.8</x:v>
       </x:c>
       <x:c r="G278" s="23" t="n">
         <x:f>ROUND(F278-F277,1)</x:f>
-        <x:v>-17</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="H278" s="24" t="n">
         <x:f>IFERROR(F278/F277-1,"")</x:f>
-        <x:v>-0.0058303038617189</x:v>
-      </x:c>
-      <x:c r="I278" s="23" t="n">
+        <x:v>0.0015113004053033396</x:v>
+      </x:c>
+      <x:c r="I278" s="26" t="n">
         <x:f>ROUND(D278-E278,1)</x:f>
-        <x:v>39.2</x:v>
+        <x:v>71.8</x:v>
       </x:c>
       <x:c r="J278" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K278" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" s="22" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B279" s="22" t="str">
+        <x:v>9月7日</x:v>
+      </x:c>
+      <x:c r="C279" s="23" t="n">
+        <x:v>2923.2</x:v>
+      </x:c>
+      <x:c r="D279" s="23" t="n">
+        <x:v>2931.4</x:v>
+      </x:c>
+      <x:c r="E279" s="23" t="n">
+        <x:v>2892.2</x:v>
+      </x:c>
+      <x:c r="F279" s="23" t="n">
+        <x:v>2898.8</x:v>
+      </x:c>
+      <x:c r="G279" s="23" t="n">
+        <x:f>ROUND(F279-F278,1)</x:f>
+        <x:v>-17</x:v>
+      </x:c>
+      <x:c r="H279" s="24" t="n">
+        <x:f>IFERROR(F279/F278-1,"")</x:f>
+        <x:v>-0.0058303038617189</x:v>
+      </x:c>
+      <x:c r="I279" s="23" t="n">
+        <x:f>ROUND(D279-E279,1)</x:f>
+        <x:v>39.2</x:v>
+      </x:c>
+      <x:c r="J279" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K279" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="279">
-      <x:c r="A279" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B279" s="30" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C279" s="30"/>
-      <x:c r="D279" s="30"/>
-      <x:c r="E279" s="30"/>
-      <x:c r="F279" s="30"/>
-      <x:c r="G279" s="30"/>
-      <x:c r="H279" s="30"/>
-      <x:c r="I279" s="32" t="n">
-        <x:f>ROUND(SUM(I244:I278),1)</x:f>
-        <x:v>3160.2</x:v>
-      </x:c>
-      <x:c r="J279" s="30"/>
-      <x:c r="K279" s="30"/>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B280" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B280" s="30" t="n">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="C280" s="30"/>
       <x:c r="D280" s="30"/>
       <x:c r="E280" s="30"/>
       <x:c r="F280" s="30"/>
       <x:c r="G280" s="30"/>
       <x:c r="H280" s="30"/>
-      <x:c r="I280" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I244:I278),0),1)</x:f>
-        <x:v>90.3</x:v>
+      <x:c r="I280" s="32" t="n">
+        <x:f>ROUND(SUM(I245:I279),1)</x:f>
+        <x:v>3160.2</x:v>
       </x:c>
       <x:c r="J280" s="30"/>
       <x:c r="K280" s="30"/>
     </x:row>
-    <x:row r="282">
-      <x:c r="A282" s="17" t="str">
+    <x:row r="281">
+      <x:c r="A281" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B281" s="30"/>
+      <x:c r="C281" s="30"/>
+      <x:c r="D281" s="30"/>
+      <x:c r="E281" s="30"/>
+      <x:c r="F281" s="30"/>
+      <x:c r="G281" s="30"/>
+      <x:c r="H281" s="30"/>
+      <x:c r="I281" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I245:I279),0),1)</x:f>
+        <x:v>90.3</x:v>
+      </x:c>
+      <x:c r="J281" s="30"/>
+      <x:c r="K281" s="30"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" s="17" t="str">
         <x:v>碳酸锂2609</x:v>
       </x:c>
-      <x:c r="B282" s="17"/>
-      <x:c r="C282" s="17"/>
-      <x:c r="D282" s="17"/>
-      <x:c r="E282" s="17"/>
-      <x:c r="F282" s="17"/>
-      <x:c r="G282" s="17"/>
-      <x:c r="H282" s="17"/>
-      <x:c r="I282" s="17"/>
-      <x:c r="J282" s="17"/>
-      <x:c r="K282" s="17"/>
-    </x:row>
-    <x:row r="283">
-      <x:c r="A283" s="20" t="str">
+      <x:c r="B283" s="17"/>
+      <x:c r="C283" s="17"/>
+      <x:c r="D283" s="17"/>
+      <x:c r="E283" s="17"/>
+      <x:c r="F283" s="17"/>
+      <x:c r="G283" s="17"/>
+      <x:c r="H283" s="17"/>
+      <x:c r="I283" s="17"/>
+      <x:c r="J283" s="17"/>
+      <x:c r="K283" s="17"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B283" s="20" t="str">
+      <x:c r="B284" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C283" s="20" t="str">
+      <x:c r="C284" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D283" s="20" t="str">
+      <x:c r="D284" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E283" s="20" t="str">
+      <x:c r="E284" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F283" s="20" t="str">
+      <x:c r="F284" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G283" s="20" t="str">
+      <x:c r="G284" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H283" s="20" t="str">
+      <x:c r="H284" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I283" s="20" t="str">
+      <x:c r="I284" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J283" s="20" t="str">
+      <x:c r="J284" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K283" s="20" t="str">
+      <x:c r="K284" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="284">
-      <x:c r="A284" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B284" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C284" s="23" t="n">
-        <x:v>126360</x:v>
-      </x:c>
-      <x:c r="D284" s="23" t="n">
-        <x:v>150760</x:v>
-      </x:c>
-      <x:c r="E284" s="23" t="n">
-        <x:v>125160</x:v>
-      </x:c>
-      <x:c r="F284" s="23" t="n">
-        <x:v>145380</x:v>
-      </x:c>
-      <x:c r="G284" s="23"/>
-      <x:c r="H284" s="24"/>
-      <x:c r="I284" s="26" t="n">
-        <x:f>ROUND(D284-E284,1)</x:f>
-        <x:v>25600</x:v>
-      </x:c>
-      <x:c r="J284" s="22" t="str">
-        <x:v>LC2609</x:v>
-      </x:c>
-      <x:c r="K284" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B285" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C285" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>126360</x:v>
       </x:c>
       <x:c r="D285" s="23" t="n">
-        <x:v>176120</x:v>
+        <x:v>150760</x:v>
       </x:c>
       <x:c r="E285" s="23" t="n">
-        <x:v>147740</x:v>
+        <x:v>125160</x:v>
       </x:c>
       <x:c r="F285" s="23" t="n">
-        <x:v>147740</x:v>
-      </x:c>
-      <x:c r="G285" s="28" t="n">
-        <x:f>ROUND(F285-F284,1)</x:f>
-        <x:v>2360</x:v>
-      </x:c>
-      <x:c r="H285" s="24" t="n">
-        <x:f>IFERROR(F285/F284-1,"")</x:f>
-        <x:v>0.016233319576282934</x:v>
-      </x:c>
+        <x:v>145380</x:v>
+      </x:c>
+      <x:c r="G285" s="23"/>
+      <x:c r="H285" s="24"/>
       <x:c r="I285" s="26" t="n">
         <x:f>ROUND(D285-E285,1)</x:f>
-        <x:v>28380</x:v>
+        <x:v>25600</x:v>
       </x:c>
       <x:c r="J285" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17605,34 +17641,34 @@
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B286" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C286" s="23" t="n">
-        <x:v>150720</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="D286" s="23" t="n">
-        <x:v>183780</x:v>
+        <x:v>176120</x:v>
       </x:c>
       <x:c r="E286" s="23" t="n">
-        <x:v>143820</x:v>
+        <x:v>147740</x:v>
       </x:c>
       <x:c r="F286" s="23" t="n">
-        <x:v>183380</x:v>
+        <x:v>147740</x:v>
       </x:c>
       <x:c r="G286" s="28" t="n">
         <x:f>ROUND(F286-F285,1)</x:f>
-        <x:v>35640</x:v>
+        <x:v>2360</x:v>
       </x:c>
       <x:c r="H286" s="24" t="n">
         <x:f>IFERROR(F286/F285-1,"")</x:f>
-        <x:v>0.24123460132665486</x:v>
+        <x:v>0.016233319576282934</x:v>
       </x:c>
       <x:c r="I286" s="26" t="n">
         <x:f>ROUND(D286-E286,1)</x:f>
-        <x:v>39960</x:v>
+        <x:v>28380</x:v>
       </x:c>
       <x:c r="J286" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17643,34 +17679,34 @@
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
-        <x:v>187000</x:v>
+        <x:v>150720</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>190600</x:v>
+        <x:v>183780</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>143820</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>183380</x:v>
       </x:c>
       <x:c r="G287" s="28" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>-34820</x:v>
+        <x:v>35640</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>-0.18987893990620575</x:v>
+        <x:v>0.24123460132665486</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>42040</x:v>
+        <x:v>39960</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17681,34 +17717,34 @@
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B288" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C288" s="23" t="n">
-        <x:v>148040</x:v>
+        <x:v>187000</x:v>
       </x:c>
       <x:c r="D288" s="23" t="n">
-        <x:v>153200</x:v>
+        <x:v>190600</x:v>
       </x:c>
       <x:c r="E288" s="23" t="n">
-        <x:v>124480</x:v>
+        <x:v>148560</x:v>
       </x:c>
       <x:c r="F288" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>148560</x:v>
       </x:c>
       <x:c r="G288" s="28" t="n">
         <x:f>ROUND(F288-F287,1)</x:f>
-        <x:v>-15060</x:v>
+        <x:v>-34820</x:v>
       </x:c>
       <x:c r="H288" s="24" t="n">
         <x:f>IFERROR(F288/F287-1,"")</x:f>
-        <x:v>-0.10137318255250405</x:v>
+        <x:v>-0.18987893990620575</x:v>
       </x:c>
       <x:c r="I288" s="26" t="n">
         <x:f>ROUND(D288-E288,1)</x:f>
-        <x:v>28720</x:v>
+        <x:v>42040</x:v>
       </x:c>
       <x:c r="J288" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17719,34 +17755,34 @@
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B289" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C289" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>148040</x:v>
       </x:c>
       <x:c r="D289" s="23" t="n">
-        <x:v>153700</x:v>
+        <x:v>153200</x:v>
       </x:c>
       <x:c r="E289" s="23" t="n">
+        <x:v>124480</x:v>
+      </x:c>
+      <x:c r="F289" s="23" t="n">
         <x:v>133500</x:v>
-      </x:c>
-      <x:c r="F289" s="23" t="n">
-        <x:v>153500</x:v>
       </x:c>
       <x:c r="G289" s="28" t="n">
         <x:f>ROUND(F289-F288,1)</x:f>
-        <x:v>20000</x:v>
+        <x:v>-15060</x:v>
       </x:c>
       <x:c r="H289" s="24" t="n">
         <x:f>IFERROR(F289/F288-1,"")</x:f>
-        <x:v>0.14981273408239693</x:v>
+        <x:v>-0.10137318255250405</x:v>
       </x:c>
       <x:c r="I289" s="26" t="n">
         <x:f>ROUND(D289-E289,1)</x:f>
-        <x:v>20200</x:v>
+        <x:v>28720</x:v>
       </x:c>
       <x:c r="J289" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17757,110 +17793,110 @@
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B290" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C290" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="D290" s="23" t="n">
-        <x:v>186900</x:v>
+        <x:v>153700</x:v>
       </x:c>
       <x:c r="E290" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>133500</x:v>
       </x:c>
       <x:c r="F290" s="23" t="n">
-        <x:v>177200</x:v>
+        <x:v>153500</x:v>
       </x:c>
       <x:c r="G290" s="28" t="n">
         <x:f>ROUND(F290-F289,1)</x:f>
-        <x:v>23700</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="H290" s="24" t="n">
         <x:f>IFERROR(F290/F289-1,"")</x:f>
-        <x:v>0.15439739413680775</x:v>
+        <x:v>0.14981273408239693</x:v>
       </x:c>
       <x:c r="I290" s="26" t="n">
         <x:f>ROUND(D290-E290,1)</x:f>
-        <x:v>28560</x:v>
+        <x:v>20200</x:v>
       </x:c>
       <x:c r="J290" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K290" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B291" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C291" s="23" t="n">
-        <x:v>180000</x:v>
+        <x:v>158340</x:v>
       </x:c>
       <x:c r="D291" s="23" t="n">
-        <x:v>180060</x:v>
+        <x:v>186900</x:v>
       </x:c>
       <x:c r="E291" s="23" t="n">
-        <x:v>146040</x:v>
+        <x:v>158340</x:v>
       </x:c>
       <x:c r="F291" s="23" t="n">
-        <x:v>156700</x:v>
+        <x:v>177200</x:v>
       </x:c>
       <x:c r="G291" s="28" t="n">
         <x:f>ROUND(F291-F290,1)</x:f>
-        <x:v>-20500</x:v>
+        <x:v>23700</x:v>
       </x:c>
       <x:c r="H291" s="24" t="n">
         <x:f>IFERROR(F291/F290-1,"")</x:f>
-        <x:v>-0.11568848758465011</x:v>
+        <x:v>0.15439739413680775</x:v>
       </x:c>
       <x:c r="I291" s="26" t="n">
         <x:f>ROUND(D291-E291,1)</x:f>
-        <x:v>34020</x:v>
+        <x:v>28560</x:v>
       </x:c>
       <x:c r="J291" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K291" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B292" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C292" s="23" t="n">
-        <x:v>149000</x:v>
+        <x:v>180000</x:v>
       </x:c>
       <x:c r="D292" s="23" t="n">
-        <x:v>167400</x:v>
+        <x:v>180060</x:v>
       </x:c>
       <x:c r="E292" s="23" t="n">
-        <x:v>142600</x:v>
+        <x:v>146040</x:v>
       </x:c>
       <x:c r="F292" s="23" t="n">
-        <x:v>152100</x:v>
+        <x:v>156700</x:v>
       </x:c>
       <x:c r="G292" s="28" t="n">
         <x:f>ROUND(F292-F291,1)</x:f>
-        <x:v>-4600</x:v>
+        <x:v>-20500</x:v>
       </x:c>
       <x:c r="H292" s="24" t="n">
         <x:f>IFERROR(F292/F291-1,"")</x:f>
-        <x:v>-0.02935545628589664</x:v>
+        <x:v>-0.11568848758465011</x:v>
       </x:c>
       <x:c r="I292" s="26" t="n">
         <x:f>ROUND(D292-E292,1)</x:f>
-        <x:v>24800</x:v>
+        <x:v>34020</x:v>
       </x:c>
       <x:c r="J292" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17871,34 +17907,34 @@
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B293" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
-        <x:v>150880</x:v>
+        <x:v>149000</x:v>
       </x:c>
       <x:c r="D293" s="23" t="n">
-        <x:v>160800</x:v>
+        <x:v>167400</x:v>
       </x:c>
       <x:c r="E293" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>142600</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>143520</x:v>
+        <x:v>152100</x:v>
       </x:c>
       <x:c r="G293" s="28" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>-8580</x:v>
+        <x:v>-4600</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>-0.05641025641025643</x:v>
+        <x:v>-0.02935545628589664</x:v>
       </x:c>
       <x:c r="I293" s="26" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
-        <x:v>20800</x:v>
+        <x:v>24800</x:v>
       </x:c>
       <x:c r="J293" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17909,34 +17945,34 @@
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B294" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C294" s="23" t="n">
-        <x:v>141220</x:v>
+        <x:v>150880</x:v>
       </x:c>
       <x:c r="D294" s="23" t="n">
-        <x:v>172220</x:v>
+        <x:v>160800</x:v>
       </x:c>
       <x:c r="E294" s="23" t="n">
-        <x:v>140020</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="F294" s="23" t="n">
-        <x:v>169400</x:v>
+        <x:v>143520</x:v>
       </x:c>
       <x:c r="G294" s="28" t="n">
         <x:f>ROUND(F294-F293,1)</x:f>
-        <x:v>25880</x:v>
+        <x:v>-8580</x:v>
       </x:c>
       <x:c r="H294" s="24" t="n">
         <x:f>IFERROR(F294/F293-1,"")</x:f>
-        <x:v>0.18032329988851736</x:v>
+        <x:v>-0.05641025641025643</x:v>
       </x:c>
       <x:c r="I294" s="26" t="n">
         <x:f>ROUND(D294-E294,1)</x:f>
-        <x:v>32200</x:v>
+        <x:v>20800</x:v>
       </x:c>
       <x:c r="J294" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17947,34 +17983,34 @@
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B295" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
-        <x:v>170000</x:v>
+        <x:v>141220</x:v>
       </x:c>
       <x:c r="D295" s="23" t="n">
-        <x:v>175000</x:v>
+        <x:v>172220</x:v>
       </x:c>
       <x:c r="E295" s="23" t="n">
-        <x:v>154560</x:v>
+        <x:v>140020</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>157860</x:v>
+        <x:v>169400</x:v>
       </x:c>
       <x:c r="G295" s="28" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>-11540</x:v>
+        <x:v>25880</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>-0.06812278630460444</x:v>
+        <x:v>0.18032329988851736</x:v>
       </x:c>
       <x:c r="I295" s="26" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>20440</x:v>
+        <x:v>32200</x:v>
       </x:c>
       <x:c r="J295" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -17985,110 +18021,110 @@
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B296" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C296" s="23" t="n">
-        <x:v>158440</x:v>
+        <x:v>170000</x:v>
       </x:c>
       <x:c r="D296" s="23" t="n">
-        <x:v>165500</x:v>
+        <x:v>175000</x:v>
       </x:c>
       <x:c r="E296" s="23" t="n">
-        <x:v>152500</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="F296" s="23" t="n">
-        <x:v>157600</x:v>
+        <x:v>157860</x:v>
       </x:c>
       <x:c r="G296" s="28" t="n">
         <x:f>ROUND(F296-F295,1)</x:f>
-        <x:v>-260</x:v>
+        <x:v>-11540</x:v>
       </x:c>
       <x:c r="H296" s="24" t="n">
         <x:f>IFERROR(F296/F295-1,"")</x:f>
-        <x:v>-0.0016470290130495835</x:v>
+        <x:v>-0.06812278630460444</x:v>
       </x:c>
       <x:c r="I296" s="26" t="n">
         <x:f>ROUND(D296-E296,1)</x:f>
-        <x:v>13000</x:v>
+        <x:v>20440</x:v>
       </x:c>
       <x:c r="J296" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K296" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B297" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C297" s="23" t="n">
-        <x:v>155020</x:v>
+        <x:v>158440</x:v>
       </x:c>
       <x:c r="D297" s="23" t="n">
-        <x:v>178000</x:v>
+        <x:v>165500</x:v>
       </x:c>
       <x:c r="E297" s="23" t="n">
-        <x:v>154780</x:v>
+        <x:v>152500</x:v>
       </x:c>
       <x:c r="F297" s="23" t="n">
-        <x:v>177560</x:v>
+        <x:v>157600</x:v>
       </x:c>
       <x:c r="G297" s="28" t="n">
         <x:f>ROUND(F297-F296,1)</x:f>
-        <x:v>19960</x:v>
+        <x:v>-260</x:v>
       </x:c>
       <x:c r="H297" s="24" t="n">
         <x:f>IFERROR(F297/F296-1,"")</x:f>
-        <x:v>0.1266497461928935</x:v>
+        <x:v>-0.0016470290130495835</x:v>
       </x:c>
       <x:c r="I297" s="26" t="n">
         <x:f>ROUND(D297-E297,1)</x:f>
-        <x:v>23220</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="J297" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K297" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B298" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C298" s="23" t="n">
-        <x:v>177000</x:v>
+        <x:v>155020</x:v>
       </x:c>
       <x:c r="D298" s="23" t="n">
-        <x:v>181440</x:v>
+        <x:v>178000</x:v>
       </x:c>
       <x:c r="E298" s="23" t="n">
-        <x:v>169500</x:v>
+        <x:v>154780</x:v>
       </x:c>
       <x:c r="F298" s="23" t="n">
-        <x:v>177900</x:v>
+        <x:v>177560</x:v>
       </x:c>
       <x:c r="G298" s="28" t="n">
         <x:f>ROUND(F298-F297,1)</x:f>
-        <x:v>340</x:v>
+        <x:v>19960</x:v>
       </x:c>
       <x:c r="H298" s="24" t="n">
         <x:f>IFERROR(F298/F297-1,"")</x:f>
-        <x:v>0.0019148456859652274</x:v>
+        <x:v>0.1266497461928935</x:v>
       </x:c>
       <x:c r="I298" s="26" t="n">
         <x:f>ROUND(D298-E298,1)</x:f>
-        <x:v>11940</x:v>
+        <x:v>23220</x:v>
       </x:c>
       <x:c r="J298" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18099,148 +18135,148 @@
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B299" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C299" s="23" t="n">
-        <x:v>182000</x:v>
+        <x:v>177000</x:v>
       </x:c>
       <x:c r="D299" s="23" t="n">
-        <x:v>189500</x:v>
+        <x:v>181440</x:v>
       </x:c>
       <x:c r="E299" s="23" t="n">
-        <x:v>173400</x:v>
+        <x:v>169500</x:v>
       </x:c>
       <x:c r="F299" s="23" t="n">
-        <x:v>189080</x:v>
+        <x:v>177900</x:v>
       </x:c>
       <x:c r="G299" s="28" t="n">
         <x:f>ROUND(F299-F298,1)</x:f>
-        <x:v>11180</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="H299" s="24" t="n">
         <x:f>IFERROR(F299/F298-1,"")</x:f>
-        <x:v>0.06284429454749851</x:v>
+        <x:v>0.0019148456859652274</x:v>
       </x:c>
       <x:c r="I299" s="26" t="n">
         <x:f>ROUND(D299-E299,1)</x:f>
-        <x:v>16100</x:v>
+        <x:v>11940</x:v>
       </x:c>
       <x:c r="J299" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K299" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B300" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C300" s="23" t="n">
-        <x:v>191500</x:v>
+        <x:v>182000</x:v>
       </x:c>
       <x:c r="D300" s="23" t="n">
-        <x:v>201480</x:v>
+        <x:v>189500</x:v>
       </x:c>
       <x:c r="E300" s="23" t="n">
-        <x:v>191040</x:v>
+        <x:v>173400</x:v>
       </x:c>
       <x:c r="F300" s="23" t="n">
-        <x:v>196560</x:v>
+        <x:v>189080</x:v>
       </x:c>
       <x:c r="G300" s="28" t="n">
         <x:f>ROUND(F300-F299,1)</x:f>
-        <x:v>7480</x:v>
+        <x:v>11180</x:v>
       </x:c>
       <x:c r="H300" s="24" t="n">
         <x:f>IFERROR(F300/F299-1,"")</x:f>
-        <x:v>0.039559974613920135</x:v>
+        <x:v>0.06284429454749851</x:v>
       </x:c>
       <x:c r="I300" s="26" t="n">
         <x:f>ROUND(D300-E300,1)</x:f>
-        <x:v>10440</x:v>
+        <x:v>16100</x:v>
       </x:c>
       <x:c r="J300" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K300" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B301" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C301" s="23" t="n">
+        <x:v>191500</x:v>
+      </x:c>
+      <x:c r="D301" s="23" t="n">
+        <x:v>201480</x:v>
+      </x:c>
+      <x:c r="E301" s="23" t="n">
+        <x:v>191040</x:v>
+      </x:c>
+      <x:c r="F301" s="23" t="n">
         <x:v>196560</x:v>
-      </x:c>
-      <x:c r="D301" s="23" t="n">
-        <x:v>209880</x:v>
-      </x:c>
-      <x:c r="E301" s="23" t="n">
-        <x:v>186800</x:v>
-      </x:c>
-      <x:c r="F301" s="23" t="n">
-        <x:v>188800</x:v>
       </x:c>
       <x:c r="G301" s="28" t="n">
         <x:f>ROUND(F301-F300,1)</x:f>
-        <x:v>-7760</x:v>
+        <x:v>7480</x:v>
       </x:c>
       <x:c r="H301" s="24" t="n">
         <x:f>IFERROR(F301/F300-1,"")</x:f>
-        <x:v>-0.039479039479039524</x:v>
+        <x:v>0.039559974613920135</x:v>
       </x:c>
       <x:c r="I301" s="26" t="n">
         <x:f>ROUND(D301-E301,1)</x:f>
-        <x:v>23080</x:v>
+        <x:v>10440</x:v>
       </x:c>
       <x:c r="J301" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K301" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B302" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C302" s="23" t="n">
-        <x:v>189000</x:v>
+        <x:v>196560</x:v>
       </x:c>
       <x:c r="D302" s="23" t="n">
-        <x:v>193900</x:v>
+        <x:v>209880</x:v>
       </x:c>
       <x:c r="E302" s="23" t="n">
-        <x:v>175200</x:v>
+        <x:v>186800</x:v>
       </x:c>
       <x:c r="F302" s="23" t="n">
-        <x:v>184460</x:v>
+        <x:v>188800</x:v>
       </x:c>
       <x:c r="G302" s="28" t="n">
         <x:f>ROUND(F302-F301,1)</x:f>
-        <x:v>-4340</x:v>
+        <x:v>-7760</x:v>
       </x:c>
       <x:c r="H302" s="24" t="n">
         <x:f>IFERROR(F302/F301-1,"")</x:f>
-        <x:v>-0.022987288135593253</x:v>
+        <x:v>-0.039479039479039524</x:v>
       </x:c>
       <x:c r="I302" s="26" t="n">
         <x:f>ROUND(D302-E302,1)</x:f>
-        <x:v>18700</x:v>
+        <x:v>23080</x:v>
       </x:c>
       <x:c r="J302" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18251,34 +18287,34 @@
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B303" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C303" s="23" t="n">
-        <x:v>185500</x:v>
+        <x:v>189000</x:v>
       </x:c>
       <x:c r="D303" s="23" t="n">
-        <x:v>187900</x:v>
+        <x:v>193900</x:v>
       </x:c>
       <x:c r="E303" s="23" t="n">
-        <x:v>172080</x:v>
+        <x:v>175200</x:v>
       </x:c>
       <x:c r="F303" s="23" t="n">
-        <x:v>179740</x:v>
+        <x:v>184460</x:v>
       </x:c>
       <x:c r="G303" s="28" t="n">
         <x:f>ROUND(F303-F302,1)</x:f>
-        <x:v>-4720</x:v>
+        <x:v>-4340</x:v>
       </x:c>
       <x:c r="H303" s="24" t="n">
         <x:f>IFERROR(F303/F302-1,"")</x:f>
-        <x:v>-0.02558820340453216</x:v>
+        <x:v>-0.022987288135593253</x:v>
       </x:c>
       <x:c r="I303" s="26" t="n">
         <x:f>ROUND(D303-E303,1)</x:f>
-        <x:v>15820</x:v>
+        <x:v>18700</x:v>
       </x:c>
       <x:c r="J303" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18289,34 +18325,34 @@
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B304" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C304" s="23" t="n">
-        <x:v>181000</x:v>
+        <x:v>185500</x:v>
       </x:c>
       <x:c r="D304" s="23" t="n">
-        <x:v>182100</x:v>
+        <x:v>187900</x:v>
       </x:c>
       <x:c r="E304" s="23" t="n">
-        <x:v>157180</x:v>
+        <x:v>172080</x:v>
       </x:c>
       <x:c r="F304" s="23" t="n">
-        <x:v>164360</x:v>
+        <x:v>179740</x:v>
       </x:c>
       <x:c r="G304" s="28" t="n">
         <x:f>ROUND(F304-F303,1)</x:f>
-        <x:v>-15380</x:v>
+        <x:v>-4720</x:v>
       </x:c>
       <x:c r="H304" s="24" t="n">
         <x:f>IFERROR(F304/F303-1,"")</x:f>
-        <x:v>-0.08556804272838547</x:v>
+        <x:v>-0.02558820340453216</x:v>
       </x:c>
       <x:c r="I304" s="26" t="n">
         <x:f>ROUND(D304-E304,1)</x:f>
-        <x:v>24920</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="J304" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18327,34 +18363,34 @@
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B305" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C305" s="23" t="n">
-        <x:v>161500</x:v>
+        <x:v>181000</x:v>
       </x:c>
       <x:c r="D305" s="23" t="n">
-        <x:v>178740</x:v>
+        <x:v>182100</x:v>
       </x:c>
       <x:c r="E305" s="23" t="n">
-        <x:v>160260</x:v>
+        <x:v>157180</x:v>
       </x:c>
       <x:c r="F305" s="23" t="n">
-        <x:v>175300</x:v>
+        <x:v>164360</x:v>
       </x:c>
       <x:c r="G305" s="28" t="n">
         <x:f>ROUND(F305-F304,1)</x:f>
-        <x:v>10940</x:v>
+        <x:v>-15380</x:v>
       </x:c>
       <x:c r="H305" s="24" t="n">
         <x:f>IFERROR(F305/F304-1,"")</x:f>
-        <x:v>0.06656120710635194</x:v>
+        <x:v>-0.08556804272838547</x:v>
       </x:c>
       <x:c r="I305" s="26" t="n">
         <x:f>ROUND(D305-E305,1)</x:f>
-        <x:v>18480</x:v>
+        <x:v>24920</x:v>
       </x:c>
       <x:c r="J305" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18365,110 +18401,110 @@
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B306" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C306" s="23" t="n">
-        <x:v>177600</x:v>
+        <x:v>161500</x:v>
       </x:c>
       <x:c r="D306" s="23" t="n">
-        <x:v>177920</x:v>
+        <x:v>178740</x:v>
       </x:c>
       <x:c r="E306" s="23" t="n">
-        <x:v>160100</x:v>
+        <x:v>160260</x:v>
       </x:c>
       <x:c r="F306" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>175300</x:v>
       </x:c>
       <x:c r="G306" s="28" t="n">
         <x:f>ROUND(F306-F305,1)</x:f>
-        <x:v>-14800</x:v>
+        <x:v>10940</x:v>
       </x:c>
       <x:c r="H306" s="24" t="n">
         <x:f>IFERROR(F306/F305-1,"")</x:f>
-        <x:v>-0.08442669709070161</x:v>
+        <x:v>0.06656120710635194</x:v>
       </x:c>
       <x:c r="I306" s="26" t="n">
         <x:f>ROUND(D306-E306,1)</x:f>
-        <x:v>17820</x:v>
+        <x:v>18480</x:v>
       </x:c>
       <x:c r="J306" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K306" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B307" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C307" s="23" t="n">
-        <x:v>157220</x:v>
+        <x:v>177600</x:v>
       </x:c>
       <x:c r="D307" s="23" t="n">
-        <x:v>163940</x:v>
+        <x:v>177920</x:v>
       </x:c>
       <x:c r="E307" s="23" t="n">
-        <x:v>145000</x:v>
+        <x:v>160100</x:v>
       </x:c>
       <x:c r="F307" s="23" t="n">
-        <x:v>150220</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="G307" s="28" t="n">
         <x:f>ROUND(F307-F306,1)</x:f>
-        <x:v>-10280</x:v>
+        <x:v>-14800</x:v>
       </x:c>
       <x:c r="H307" s="24" t="n">
         <x:f>IFERROR(F307/F306-1,"")</x:f>
-        <x:v>-0.06404984423676008</x:v>
+        <x:v>-0.08442669709070161</x:v>
       </x:c>
       <x:c r="I307" s="26" t="n">
         <x:f>ROUND(D307-E307,1)</x:f>
-        <x:v>18940</x:v>
+        <x:v>17820</x:v>
       </x:c>
       <x:c r="J307" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K307" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B308" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C308" s="23" t="n">
-        <x:v>148000</x:v>
+        <x:v>157220</x:v>
       </x:c>
       <x:c r="D308" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>163940</x:v>
       </x:c>
       <x:c r="E308" s="23" t="n">
-        <x:v>145300</x:v>
+        <x:v>145000</x:v>
       </x:c>
       <x:c r="F308" s="23" t="n">
-        <x:v>168780</x:v>
+        <x:v>150220</x:v>
       </x:c>
       <x:c r="G308" s="28" t="n">
         <x:f>ROUND(F308-F307,1)</x:f>
-        <x:v>18560</x:v>
+        <x:v>-10280</x:v>
       </x:c>
       <x:c r="H308" s="24" t="n">
         <x:f>IFERROR(F308/F307-1,"")</x:f>
-        <x:v>0.12355212355212353</x:v>
+        <x:v>-0.06404984423676008</x:v>
       </x:c>
       <x:c r="I308" s="26" t="n">
         <x:f>ROUND(D308-E308,1)</x:f>
-        <x:v>26700</x:v>
+        <x:v>18940</x:v>
       </x:c>
       <x:c r="J308" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18479,34 +18515,34 @@
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B309" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C309" s="23" t="n">
-        <x:v>166980</x:v>
+        <x:v>148000</x:v>
       </x:c>
       <x:c r="D309" s="23" t="n">
-        <x:v>168720</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="E309" s="23" t="n">
-        <x:v>150260</x:v>
+        <x:v>145300</x:v>
       </x:c>
       <x:c r="F309" s="23" t="n">
-        <x:v>151600</x:v>
+        <x:v>168780</x:v>
       </x:c>
       <x:c r="G309" s="28" t="n">
         <x:f>ROUND(F309-F308,1)</x:f>
-        <x:v>-17180</x:v>
+        <x:v>18560</x:v>
       </x:c>
       <x:c r="H309" s="24" t="n">
         <x:f>IFERROR(F309/F308-1,"")</x:f>
-        <x:v>-0.10178931152980208</x:v>
+        <x:v>0.12355212355212353</x:v>
       </x:c>
       <x:c r="I309" s="26" t="n">
         <x:f>ROUND(D309-E309,1)</x:f>
-        <x:v>18460</x:v>
+        <x:v>26700</x:v>
       </x:c>
       <x:c r="J309" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18517,34 +18553,34 @@
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B310" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C310" s="23" t="n">
-        <x:v>150500</x:v>
+        <x:v>166980</x:v>
       </x:c>
       <x:c r="D310" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>168720</x:v>
       </x:c>
       <x:c r="E310" s="23" t="n">
-        <x:v>145860</x:v>
+        <x:v>150260</x:v>
       </x:c>
       <x:c r="F310" s="23" t="n">
-        <x:v>150140</x:v>
+        <x:v>151600</x:v>
       </x:c>
       <x:c r="G310" s="28" t="n">
         <x:f>ROUND(F310-F309,1)</x:f>
-        <x:v>-1460</x:v>
+        <x:v>-17180</x:v>
       </x:c>
       <x:c r="H310" s="24" t="n">
         <x:f>IFERROR(F310/F309-1,"")</x:f>
-        <x:v>-0.009630606860158264</x:v>
+        <x:v>-0.10178931152980208</x:v>
       </x:c>
       <x:c r="I310" s="26" t="n">
         <x:f>ROUND(D310-E310,1)</x:f>
-        <x:v>10640</x:v>
+        <x:v>18460</x:v>
       </x:c>
       <x:c r="J310" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18555,34 +18591,34 @@
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B311" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C311" s="23" t="n">
-        <x:v>151500</x:v>
+        <x:v>150500</x:v>
       </x:c>
       <x:c r="D311" s="23" t="n">
-        <x:v>154800</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="E311" s="23" t="n">
-        <x:v>136800</x:v>
+        <x:v>145860</x:v>
       </x:c>
       <x:c r="F311" s="23" t="n">
-        <x:v>144280</x:v>
+        <x:v>150140</x:v>
       </x:c>
       <x:c r="G311" s="28" t="n">
         <x:f>ROUND(F311-F310,1)</x:f>
-        <x:v>-5860</x:v>
+        <x:v>-1460</x:v>
       </x:c>
       <x:c r="H311" s="24" t="n">
         <x:f>IFERROR(F311/F310-1,"")</x:f>
-        <x:v>-0.03903023844411879</x:v>
+        <x:v>-0.009630606860158264</x:v>
       </x:c>
       <x:c r="I311" s="26" t="n">
         <x:f>ROUND(D311-E311,1)</x:f>
-        <x:v>18000</x:v>
+        <x:v>10640</x:v>
       </x:c>
       <x:c r="J311" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18593,34 +18629,34 @@
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B312" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C312" s="23" t="n">
-        <x:v>145780</x:v>
+        <x:v>151500</x:v>
       </x:c>
       <x:c r="D312" s="23" t="n">
-        <x:v>149400</x:v>
+        <x:v>154800</x:v>
       </x:c>
       <x:c r="E312" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>136800</x:v>
       </x:c>
       <x:c r="F312" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>144280</x:v>
       </x:c>
       <x:c r="G312" s="28" t="n">
         <x:f>ROUND(F312-F311,1)</x:f>
-        <x:v>-6520</x:v>
+        <x:v>-5860</x:v>
       </x:c>
       <x:c r="H312" s="24" t="n">
         <x:f>IFERROR(F312/F311-1,"")</x:f>
-        <x:v>-0.04518990851122817</x:v>
+        <x:v>-0.03903023844411879</x:v>
       </x:c>
       <x:c r="I312" s="26" t="n">
         <x:f>ROUND(D312-E312,1)</x:f>
-        <x:v>11640</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="J312" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18631,34 +18667,34 @@
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B313" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C313" s="23" t="n">
-        <x:v>137500</x:v>
+        <x:v>145780</x:v>
       </x:c>
       <x:c r="D313" s="23" t="n">
-        <x:v>144800</x:v>
+        <x:v>149400</x:v>
       </x:c>
       <x:c r="E313" s="23" t="n">
-        <x:v>135560</x:v>
+        <x:v>137760</x:v>
       </x:c>
       <x:c r="F313" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>137760</x:v>
       </x:c>
       <x:c r="G313" s="28" t="n">
         <x:f>ROUND(F313-F312,1)</x:f>
-        <x:v>2240</x:v>
+        <x:v>-6520</x:v>
       </x:c>
       <x:c r="H313" s="24" t="n">
         <x:f>IFERROR(F313/F312-1,"")</x:f>
-        <x:v>0.016260162601626105</x:v>
+        <x:v>-0.04518990851122817</x:v>
       </x:c>
       <x:c r="I313" s="26" t="n">
         <x:f>ROUND(D313-E313,1)</x:f>
-        <x:v>9240</x:v>
+        <x:v>11640</x:v>
       </x:c>
       <x:c r="J313" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18669,34 +18705,34 @@
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B314" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C314" s="23" t="n">
-        <x:v>140500</x:v>
+        <x:v>137500</x:v>
       </x:c>
       <x:c r="D314" s="23" t="n">
-        <x:v>154500</x:v>
+        <x:v>144800</x:v>
       </x:c>
       <x:c r="E314" s="23" t="n">
-        <x:v>139280</x:v>
+        <x:v>135560</x:v>
       </x:c>
       <x:c r="F314" s="23" t="n">
-        <x:v>153940</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="G314" s="28" t="n">
         <x:f>ROUND(F314-F313,1)</x:f>
-        <x:v>13940</x:v>
+        <x:v>2240</x:v>
       </x:c>
       <x:c r="H314" s="24" t="n">
         <x:f>IFERROR(F314/F313-1,"")</x:f>
-        <x:v>0.09957142857142864</x:v>
+        <x:v>0.016260162601626105</x:v>
       </x:c>
       <x:c r="I314" s="26" t="n">
         <x:f>ROUND(D314-E314,1)</x:f>
-        <x:v>15220</x:v>
+        <x:v>9240</x:v>
       </x:c>
       <x:c r="J314" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18707,34 +18743,34 @@
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B315" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C315" s="23" t="n">
-        <x:v>154300</x:v>
+        <x:v>140500</x:v>
       </x:c>
       <x:c r="D315" s="23" t="n">
-        <x:v>157000</x:v>
+        <x:v>154500</x:v>
       </x:c>
       <x:c r="E315" s="23" t="n">
-        <x:v>148400</x:v>
+        <x:v>139280</x:v>
       </x:c>
       <x:c r="F315" s="23" t="n">
-        <x:v>156140</x:v>
+        <x:v>153940</x:v>
       </x:c>
       <x:c r="G315" s="28" t="n">
         <x:f>ROUND(F315-F314,1)</x:f>
-        <x:v>2200</x:v>
+        <x:v>13940</x:v>
       </x:c>
       <x:c r="H315" s="24" t="n">
         <x:f>IFERROR(F315/F314-1,"")</x:f>
-        <x:v>0.014291282317786091</x:v>
+        <x:v>0.09957142857142864</x:v>
       </x:c>
       <x:c r="I315" s="26" t="n">
         <x:f>ROUND(D315-E315,1)</x:f>
-        <x:v>8600</x:v>
+        <x:v>15220</x:v>
       </x:c>
       <x:c r="J315" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18745,34 +18781,34 @@
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B316" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C316" s="23" t="n">
-        <x:v>158500</x:v>
+        <x:v>154300</x:v>
       </x:c>
       <x:c r="D316" s="23" t="n">
-        <x:v>160000</x:v>
+        <x:v>157000</x:v>
       </x:c>
       <x:c r="E316" s="23" t="n">
-        <x:v>147000</x:v>
+        <x:v>148400</x:v>
       </x:c>
       <x:c r="F316" s="23" t="n">
-        <x:v>157080</x:v>
+        <x:v>156140</x:v>
       </x:c>
       <x:c r="G316" s="28" t="n">
         <x:f>ROUND(F316-F315,1)</x:f>
-        <x:v>940</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="H316" s="24" t="n">
         <x:f>IFERROR(F316/F315-1,"")</x:f>
-        <x:v>0.0060202382477263505</x:v>
+        <x:v>0.014291282317786091</x:v>
       </x:c>
       <x:c r="I316" s="26" t="n">
         <x:f>ROUND(D316-E316,1)</x:f>
-        <x:v>13000</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="J316" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18783,34 +18819,34 @@
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B317" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C317" s="23" t="n">
-        <x:v>158000</x:v>
+        <x:v>158500</x:v>
       </x:c>
       <x:c r="D317" s="23" t="n">
-        <x:v>160480</x:v>
+        <x:v>160000</x:v>
       </x:c>
       <x:c r="E317" s="23" t="n">
-        <x:v>140940</x:v>
+        <x:v>147000</x:v>
       </x:c>
       <x:c r="F317" s="23" t="n">
-        <x:v>140980</x:v>
+        <x:v>157080</x:v>
       </x:c>
       <x:c r="G317" s="28" t="n">
         <x:f>ROUND(F317-F316,1)</x:f>
-        <x:v>-16100</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="H317" s="24" t="n">
         <x:f>IFERROR(F317/F316-1,"")</x:f>
-        <x:v>-0.1024955436720143</x:v>
+        <x:v>0.0060202382477263505</x:v>
       </x:c>
       <x:c r="I317" s="26" t="n">
         <x:f>ROUND(D317-E317,1)</x:f>
-        <x:v>19540</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="J317" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18820,42 +18856,118 @@
       </x:c>
     </x:row>
     <x:row r="318">
-      <x:c r="A318" s="31" t="str">
+      <x:c r="A318" s="22" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B318" s="22" t="str">
+        <x:v>8月31日-9月4日</x:v>
+      </x:c>
+      <x:c r="C318" s="23" t="n">
+        <x:v>158000</x:v>
+      </x:c>
+      <x:c r="D318" s="23" t="n">
+        <x:v>160480</x:v>
+      </x:c>
+      <x:c r="E318" s="23" t="n">
+        <x:v>140940</x:v>
+      </x:c>
+      <x:c r="F318" s="23" t="n">
+        <x:v>140980</x:v>
+      </x:c>
+      <x:c r="G318" s="28" t="n">
+        <x:f>ROUND(F318-F317,1)</x:f>
+        <x:v>-16100</x:v>
+      </x:c>
+      <x:c r="H318" s="24" t="n">
+        <x:f>IFERROR(F318/F317-1,"")</x:f>
+        <x:v>-0.1024955436720143</x:v>
+      </x:c>
+      <x:c r="I318" s="26" t="n">
+        <x:f>ROUND(D318-E318,1)</x:f>
+        <x:v>19540</x:v>
+      </x:c>
+      <x:c r="J318" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K318" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319" s="22" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B319" s="22" t="str">
+        <x:v>9月7日</x:v>
+      </x:c>
+      <x:c r="C319" s="23" t="n">
+        <x:v>142120</x:v>
+      </x:c>
+      <x:c r="D319" s="23" t="n">
+        <x:v>142800</x:v>
+      </x:c>
+      <x:c r="E319" s="23" t="n">
+        <x:v>139880</x:v>
+      </x:c>
+      <x:c r="F319" s="23" t="n">
+        <x:v>140500</x:v>
+      </x:c>
+      <x:c r="G319" s="28" t="n">
+        <x:f>ROUND(F319-F318,1)</x:f>
+        <x:v>-480</x:v>
+      </x:c>
+      <x:c r="H319" s="24" t="n">
+        <x:f>IFERROR(F319/F318-1,"")</x:f>
+        <x:v>-0.003404738260746165</x:v>
+      </x:c>
+      <x:c r="I319" s="23" t="n">
+        <x:f>ROUND(D319-E319,1)</x:f>
+        <x:v>2920</x:v>
+      </x:c>
+      <x:c r="J319" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K319" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320">
+      <x:c r="A320" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B318" s="30" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C318" s="30"/>
-      <x:c r="D318" s="30"/>
-      <x:c r="E318" s="30"/>
-      <x:c r="F318" s="30"/>
-      <x:c r="G318" s="30"/>
-      <x:c r="H318" s="30"/>
-      <x:c r="I318" s="32" t="n">
-        <x:f>ROUND(SUM(I284:I317),1)</x:f>
-        <x:v>709220</x:v>
-      </x:c>
-      <x:c r="J318" s="30"/>
-      <x:c r="K318" s="30"/>
-    </x:row>
-    <x:row r="319">
-      <x:c r="A319" s="31" t="str">
+      <x:c r="B320" s="30" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C320" s="30"/>
+      <x:c r="D320" s="30"/>
+      <x:c r="E320" s="30"/>
+      <x:c r="F320" s="30"/>
+      <x:c r="G320" s="30"/>
+      <x:c r="H320" s="30"/>
+      <x:c r="I320" s="32" t="n">
+        <x:f>ROUND(SUM(I285:I319),1)</x:f>
+        <x:v>712140</x:v>
+      </x:c>
+      <x:c r="J320" s="30"/>
+      <x:c r="K320" s="30"/>
+    </x:row>
+    <x:row r="321">
+      <x:c r="A321" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B319" s="30"/>
-      <x:c r="C319" s="30"/>
-      <x:c r="D319" s="30"/>
-      <x:c r="E319" s="30"/>
-      <x:c r="F319" s="30"/>
-      <x:c r="G319" s="30"/>
-      <x:c r="H319" s="30"/>
-      <x:c r="I319" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I284:I317),0),1)</x:f>
-        <x:v>20859.4</x:v>
-      </x:c>
-      <x:c r="J319" s="30"/>
-      <x:c r="K319" s="30"/>
+      <x:c r="B321" s="30"/>
+      <x:c r="C321" s="30"/>
+      <x:c r="D321" s="30"/>
+      <x:c r="E321" s="30"/>
+      <x:c r="F321" s="30"/>
+      <x:c r="G321" s="30"/>
+      <x:c r="H321" s="30"/>
+      <x:c r="I321" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I285:I319),0),1)</x:f>
+        <x:v>20346.9</x:v>
+      </x:c>
+      <x:c r="J321" s="30"/>
+      <x:c r="K321" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -18864,10 +18976,10 @@
     <x:mergeCell ref="A43:K43"/>
     <x:mergeCell ref="A83:K83"/>
     <x:mergeCell ref="A123:K123"/>
-    <x:mergeCell ref="A162:K162"/>
-    <x:mergeCell ref="A202:K202"/>
-    <x:mergeCell ref="A242:K242"/>
-    <x:mergeCell ref="A282:K282"/>
+    <x:mergeCell ref="A163:K163"/>
+    <x:mergeCell ref="A203:K203"/>
+    <x:mergeCell ref="A243:K243"/>
+    <x:mergeCell ref="A283:K283"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -45867,30 +45979,48 @@
       </x:c>
     </x:row>
     <x:row r="209">
-      <x:c r="A209" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B209" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C209" s="30"/>
-      <x:c r="D209" s="30"/>
-      <x:c r="E209" s="30"/>
-      <x:c r="F209" s="30"/>
-      <x:c r="G209" s="30"/>
-      <x:c r="H209" s="30"/>
-      <x:c r="I209" s="30"/>
-      <x:c r="J209" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J208),1)</x:f>
-        <x:v>631.4</x:v>
-      </x:c>
-      <x:c r="K209" s="30"/>
+      <x:c r="A209" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B209" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C209" s="22" t="str">
+        <x:v>9月7日</x:v>
+      </x:c>
+      <x:c r="D209" s="23" t="n">
+        <x:v>7527.2</x:v>
+      </x:c>
+      <x:c r="E209" s="23" t="n">
+        <x:v>7662.2</x:v>
+      </x:c>
+      <x:c r="F209" s="23" t="n">
+        <x:v>7512.6</x:v>
+      </x:c>
+      <x:c r="G209" s="23" t="n">
+        <x:v>7604</x:v>
+      </x:c>
+      <x:c r="H209" s="23" t="n">
+        <x:v>135.8</x:v>
+      </x:c>
+      <x:c r="I209" s="24" t="n">
+        <x:v>0.01818376583380199</x:v>
+      </x:c>
+      <x:c r="J209" s="23" t="n">
+        <x:f>ROUND(E209-F209,1)</x:f>
+        <x:v>149.6</x:v>
+      </x:c>
+      <x:c r="K209" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B210" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B210" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C210" s="30"/>
       <x:c r="D210" s="30"/>
       <x:c r="E210" s="30"/>
@@ -45898,11 +46028,29 @@
       <x:c r="G210" s="30"/>
       <x:c r="H210" s="30"/>
       <x:c r="I210" s="30"/>
-      <x:c r="J210" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J208),0),1)</x:f>
-        <x:v>157.9</x:v>
+      <x:c r="J210" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J209),1)</x:f>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="K210" s="30"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B211" s="30"/>
+      <x:c r="C211" s="30"/>
+      <x:c r="D211" s="30"/>
+      <x:c r="E211" s="30"/>
+      <x:c r="F211" s="30"/>
+      <x:c r="G211" s="30"/>
+      <x:c r="H211" s="30"/>
+      <x:c r="I211" s="30"/>
+      <x:c r="J211" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
+        <x:v>156.2</x:v>
+      </x:c>
+      <x:c r="K211" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rca3f9eade7b04dbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R7ecfa61695fb4cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4f2a5e8e3c5d4184"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rb45b06b327414d0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rd36281ea58b14510"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R7cad496acbcb4a91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R2ebc769276444ca0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R3af1d3e64dd74476"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R8d96019120bb4c53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R3eeefe53ba2840e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R1a448288066d46b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Re77bc50e80fb4cb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R90052e4ea6ca4ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R1b6b42e267ab466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R844348eb6b9d46cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rad2e135c85dc4a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R65886dd9eaf84936"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Re2b7de78aed64ce8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R7f04e2c5d6c142c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R9c4bb4f827d346a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7669.84</x:v>
+        <x:v>7724.94</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7541.14</x:v>
+        <x:v>7622.9</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>128.7</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>29429.9</x:v>
+        <x:v>29531.9</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>178.4</x:v>
+        <x:v>177.9</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7791.79</x:v>
+        <x:v>7830.16</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7672.99</x:v>
+        <x:v>7736.44</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>118.8</x:v>
+        <x:v>93.7</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>29449.1</x:v>
+        <x:v>29542.8</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>178.5</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3948.42</x:v>
+        <x:v>3951.32</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3916.49</x:v>
+        <x:v>3925.72</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>31.9</x:v>
+        <x:v>25.6</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8068</x:v>
+        <x:v>8093.6</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>48.9</x:v>
+        <x:v>48.8</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7784.2</x:v>
+        <x:v>7817.2</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7651.2</x:v>
+        <x:v>7703.2</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>133</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>32549.6</x:v>
+        <x:v>32663.6</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>197.3</x:v>
+        <x:v>196.8</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2931.4</x:v>
+        <x:v>2917.4</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2892.2</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>39.2</x:v>
+        <x:v>26.4</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6748.4</x:v>
+        <x:v>6774.8</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.9</x:v>
+        <x:v>40.8</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>142800</x:v>
+        <x:v>143200</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>139880</x:v>
+        <x:v>141320</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>2920</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1390900</x:v>
+        <x:v>1392780</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8429.7</x:v>
+        <x:v>8390.2</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -7597,30 +7597,48 @@
       </x:c>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B210" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C210" s="30"/>
-      <x:c r="D210" s="30"/>
-      <x:c r="E210" s="30"/>
-      <x:c r="F210" s="30"/>
-      <x:c r="G210" s="30"/>
-      <x:c r="H210" s="30"/>
-      <x:c r="I210" s="30"/>
-      <x:c r="J210" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J209),1)</x:f>
-        <x:v>29140</x:v>
-      </x:c>
-      <x:c r="K210" s="30"/>
+      <x:c r="A210" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B210" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C210" s="22" t="str">
+        <x:v>9月8日</x:v>
+      </x:c>
+      <x:c r="D210" s="23" t="n">
+        <x:v>143200</x:v>
+      </x:c>
+      <x:c r="E210" s="23" t="n">
+        <x:v>143200</x:v>
+      </x:c>
+      <x:c r="F210" s="23" t="n">
+        <x:v>141320</x:v>
+      </x:c>
+      <x:c r="G210" s="23" t="n">
+        <x:v>141320</x:v>
+      </x:c>
+      <x:c r="H210" s="28" t="n">
+        <x:v>820</x:v>
+      </x:c>
+      <x:c r="I210" s="24" t="n">
+        <x:v>0.005836298932384354</x:v>
+      </x:c>
+      <x:c r="J210" s="23" t="n">
+        <x:f>ROUND(E210-F210,1)</x:f>
+        <x:v>1880</x:v>
+      </x:c>
+      <x:c r="K210" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B211" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B211" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C211" s="30"/>
       <x:c r="D211" s="30"/>
       <x:c r="E211" s="30"/>
@@ -7628,11 +7646,29 @@
       <x:c r="G211" s="30"/>
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="30"/>
-      <x:c r="J211" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
-        <x:v>5828</x:v>
+      <x:c r="J211" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J210),1)</x:f>
+        <x:v>31020</x:v>
       </x:c>
       <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B212" s="30"/>
+      <x:c r="C212" s="30"/>
+      <x:c r="D212" s="30"/>
+      <x:c r="E212" s="30"/>
+      <x:c r="F212" s="30"/>
+      <x:c r="G212" s="30"/>
+      <x:c r="H212" s="30"/>
+      <x:c r="I212" s="30"/>
+      <x:c r="J212" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
+        <x:v>5170</x:v>
+      </x:c>
+      <x:c r="K212" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9014,37 +9050,37 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>9月7日-9月8日</x:v>
       </x:c>
       <x:c r="C39" s="23" t="n">
         <x:v>7551.02</x:v>
       </x:c>
       <x:c r="D39" s="23" t="n">
-        <x:v>7669.84</x:v>
+        <x:v>7724.94</x:v>
       </x:c>
       <x:c r="E39" s="23" t="n">
         <x:v>7541.14</x:v>
       </x:c>
       <x:c r="F39" s="23" t="n">
-        <x:v>7639.36</x:v>
-      </x:c>
-      <x:c r="G39" s="23" t="n">
+        <x:v>7659.61</x:v>
+      </x:c>
+      <x:c r="G39" s="28" t="n">
         <x:f>ROUND(F39-F38,1)</x:f>
-        <x:v>131.3</x:v>
+        <x:v>151.5</x:v>
       </x:c>
       <x:c r="H39" s="24" t="n">
         <x:f>IFERROR(F39/F38-1,"")</x:f>
-        <x:v>0.017483807466346146</x:v>
-      </x:c>
-      <x:c r="I39" s="23" t="n">
+        <x:v>0.02018089820447</x:v>
+      </x:c>
+      <x:c r="I39" s="26" t="n">
         <x:f>ROUND(D39-E39,1)</x:f>
-        <x:v>128.7</x:v>
+        <x:v>183.8</x:v>
       </x:c>
       <x:c r="J39" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K39" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -9062,7 +9098,7 @@
       <x:c r="H40" s="30"/>
       <x:c r="I40" s="32" t="n">
         <x:f>ROUND(SUM(I5:I39),1)</x:f>
-        <x:v>14384.9</x:v>
+        <x:v>14440</x:v>
       </x:c>
       <x:c r="J40" s="30"/>
       <x:c r="K40" s="30"/>
@@ -9080,7 +9116,7 @@
       <x:c r="H41" s="30"/>
       <x:c r="I41" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I39),0),1)</x:f>
-        <x:v>411</x:v>
+        <x:v>412.6</x:v>
       </x:c>
       <x:c r="J41" s="30"/>
       <x:c r="K41" s="30"/>
@@ -10426,37 +10462,37 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>9月7日-9月8日</x:v>
       </x:c>
       <x:c r="C79" s="23" t="n">
         <x:v>7687.47</x:v>
       </x:c>
       <x:c r="D79" s="23" t="n">
-        <x:v>7791.79</x:v>
+        <x:v>7830.16</x:v>
       </x:c>
       <x:c r="E79" s="23" t="n">
         <x:v>7672.99</x:v>
       </x:c>
       <x:c r="F79" s="23" t="n">
-        <x:v>7759.37</x:v>
+        <x:v>7770.73</x:v>
       </x:c>
       <x:c r="G79" s="23" t="n">
         <x:f>ROUND(F79-F78,1)</x:f>
-        <x:v>106.7</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H79" s="24" t="n">
         <x:f>IFERROR(F79/F78-1,"")</x:f>
-        <x:v>0.013940196192449905</x:v>
+        <x:v>0.015424641531278649</x:v>
       </x:c>
       <x:c r="I79" s="23" t="n">
         <x:f>ROUND(D79-E79,1)</x:f>
-        <x:v>118.8</x:v>
+        <x:v>157.2</x:v>
       </x:c>
       <x:c r="J79" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K79" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -10474,7 +10510,7 @@
       <x:c r="H80" s="30"/>
       <x:c r="I80" s="32" t="n">
         <x:f>ROUND(SUM(I45:I79),1)</x:f>
-        <x:v>14457.8</x:v>
+        <x:v>14496.2</x:v>
       </x:c>
       <x:c r="J80" s="30"/>
       <x:c r="K80" s="30"/>
@@ -10492,7 +10528,7 @@
       <x:c r="H81" s="30"/>
       <x:c r="I81" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I45:I79),0),1)</x:f>
-        <x:v>413.1</x:v>
+        <x:v>414.2</x:v>
       </x:c>
       <x:c r="J81" s="30"/>
       <x:c r="K81" s="30"/>
@@ -11838,37 +11874,37 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B119" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>9月7日-9月8日</x:v>
       </x:c>
       <x:c r="C119" s="23" t="n">
         <x:v>3942.51</x:v>
       </x:c>
       <x:c r="D119" s="23" t="n">
-        <x:v>3948.42</x:v>
+        <x:v>3951.32</x:v>
       </x:c>
       <x:c r="E119" s="23" t="n">
         <x:v>3916.49</x:v>
       </x:c>
       <x:c r="F119" s="23" t="n">
-        <x:v>3932.7</x:v>
+        <x:v>3940.55</x:v>
       </x:c>
       <x:c r="G119" s="23" t="n">
         <x:f>ROUND(F119-F118,1)</x:f>
-        <x:v>2.6</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="H119" s="24" t="n">
         <x:f>IFERROR(F119/F118-1,"")</x:f>
-        <x:v>0.0006564685047785179</x:v>
+        <x:v>0.0026538629863719354</x:v>
       </x:c>
       <x:c r="I119" s="23" t="n">
         <x:f>ROUND(D119-E119,1)</x:f>
-        <x:v>31.9</x:v>
+        <x:v>34.8</x:v>
       </x:c>
       <x:c r="J119" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K119" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -11886,7 +11922,7 @@
       <x:c r="H120" s="30"/>
       <x:c r="I120" s="32" t="n">
         <x:f>ROUND(SUM(I85:I119),1)</x:f>
-        <x:v>3789.9</x:v>
+        <x:v>3792.8</x:v>
       </x:c>
       <x:c r="J120" s="30"/>
       <x:c r="K120" s="30"/>
@@ -11904,7 +11940,7 @@
       <x:c r="H121" s="30"/>
       <x:c r="I121" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I85:I119),0),1)</x:f>
-        <x:v>108.3</x:v>
+        <x:v>108.4</x:v>
       </x:c>
       <x:c r="J121" s="30"/>
       <x:c r="K121" s="30"/>
@@ -14662,37 +14698,37 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B199" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>9月7日-9月8日</x:v>
       </x:c>
       <x:c r="C199" s="23" t="n">
         <x:v>7665.6</x:v>
       </x:c>
       <x:c r="D199" s="23" t="n">
-        <x:v>7784.2</x:v>
+        <x:v>7817.2</x:v>
       </x:c>
       <x:c r="E199" s="23" t="n">
         <x:v>7651.2</x:v>
       </x:c>
       <x:c r="F199" s="23" t="n">
-        <x:v>7716.2</x:v>
+        <x:v>7743.4</x:v>
       </x:c>
       <x:c r="G199" s="23" t="n">
         <x:f>ROUND(F199-F198,1)</x:f>
-        <x:v>108.2</x:v>
+        <x:v>135.4</x:v>
       </x:c>
       <x:c r="H199" s="24" t="n">
         <x:f>IFERROR(F199/F198-1,"")</x:f>
-        <x:v>0.014221871713985257</x:v>
-      </x:c>
-      <x:c r="I199" s="23" t="n">
+        <x:v>0.017797055730809586</x:v>
+      </x:c>
+      <x:c r="I199" s="26" t="n">
         <x:f>ROUND(D199-E199,1)</x:f>
-        <x:v>133</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="J199" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K199" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -14710,7 +14746,7 @@
       <x:c r="H200" s="30"/>
       <x:c r="I200" s="32" t="n">
         <x:f>ROUND(SUM(I165:I199),1)</x:f>
-        <x:v>15560</x:v>
+        <x:v>15593</x:v>
       </x:c>
       <x:c r="J200" s="30"/>
       <x:c r="K200" s="30"/>
@@ -14728,7 +14764,7 @@
       <x:c r="H201" s="30"/>
       <x:c r="I201" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I165:I199),0),1)</x:f>
-        <x:v>444.6</x:v>
+        <x:v>445.5</x:v>
       </x:c>
       <x:c r="J201" s="30"/>
       <x:c r="K201" s="30"/>
@@ -17486,7 +17522,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>9月7日-9月8日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
         <x:v>2923.2</x:v>
@@ -17495,28 +17531,28 @@
         <x:v>2931.4</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>2892.2</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>2898.8</x:v>
+        <x:v>2897</x:v>
       </x:c>
       <x:c r="G279" s="23" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>-17</x:v>
+        <x:v>-18.8</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>-0.0058303038617189</x:v>
+        <x:v>-0.0064476301529597935</x:v>
       </x:c>
       <x:c r="I279" s="23" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>39.2</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -17534,7 +17570,7 @@
       <x:c r="H280" s="30"/>
       <x:c r="I280" s="32" t="n">
         <x:f>ROUND(SUM(I245:I279),1)</x:f>
-        <x:v>3160.2</x:v>
+        <x:v>3161.4</x:v>
       </x:c>
       <x:c r="J280" s="30"/>
       <x:c r="K280" s="30"/>
@@ -18898,37 +18934,37 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B319" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>9月7日-9月8日</x:v>
       </x:c>
       <x:c r="C319" s="23" t="n">
         <x:v>142120</x:v>
       </x:c>
       <x:c r="D319" s="23" t="n">
-        <x:v>142800</x:v>
+        <x:v>143200</x:v>
       </x:c>
       <x:c r="E319" s="23" t="n">
         <x:v>139880</x:v>
       </x:c>
       <x:c r="F319" s="23" t="n">
-        <x:v>140500</x:v>
+        <x:v>141320</x:v>
       </x:c>
       <x:c r="G319" s="28" t="n">
         <x:f>ROUND(F319-F318,1)</x:f>
-        <x:v>-480</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="H319" s="24" t="n">
         <x:f>IFERROR(F319/F318-1,"")</x:f>
-        <x:v>-0.003404738260746165</x:v>
+        <x:v>0.002411689601361955</x:v>
       </x:c>
       <x:c r="I319" s="23" t="n">
         <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>2920</x:v>
+        <x:v>3320</x:v>
       </x:c>
       <x:c r="J319" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K319" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
@@ -18946,7 +18982,7 @@
       <x:c r="H320" s="30"/>
       <x:c r="I320" s="32" t="n">
         <x:f>ROUND(SUM(I285:I319),1)</x:f>
-        <x:v>712140</x:v>
+        <x:v>712540</x:v>
       </x:c>
       <x:c r="J320" s="30"/>
       <x:c r="K320" s="30"/>
@@ -18964,7 +19000,7 @@
       <x:c r="H321" s="30"/>
       <x:c r="I321" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I285:I319),0),1)</x:f>
-        <x:v>20346.9</x:v>
+        <x:v>20358.3</x:v>
       </x:c>
       <x:c r="J321" s="30"/>
       <x:c r="K321" s="30"/>
@@ -25702,30 +25738,48 @@
       </x:c>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B210" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C210" s="30"/>
-      <x:c r="D210" s="30"/>
-      <x:c r="E210" s="30"/>
-      <x:c r="F210" s="30"/>
-      <x:c r="G210" s="30"/>
-      <x:c r="H210" s="30"/>
-      <x:c r="I210" s="30"/>
-      <x:c r="J210" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J209),1)</x:f>
-        <x:v>699.1</x:v>
-      </x:c>
-      <x:c r="K210" s="30"/>
+      <x:c r="A210" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B210" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C210" s="22" t="str">
+        <x:v>9月8日</x:v>
+      </x:c>
+      <x:c r="D210" s="23" t="n">
+        <x:v>7650.06</x:v>
+      </x:c>
+      <x:c r="E210" s="23" t="n">
+        <x:v>7724.94</x:v>
+      </x:c>
+      <x:c r="F210" s="23" t="n">
+        <x:v>7622.9</x:v>
+      </x:c>
+      <x:c r="G210" s="23" t="n">
+        <x:v>7659.61</x:v>
+      </x:c>
+      <x:c r="H210" s="23" t="n">
+        <x:v>20.3</x:v>
+      </x:c>
+      <x:c r="I210" s="24" t="n">
+        <x:v>0.0026507456121978024</x:v>
+      </x:c>
+      <x:c r="J210" s="23" t="n">
+        <x:f>ROUND(E210-F210,1)</x:f>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K210" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B211" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B211" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C211" s="30"/>
       <x:c r="D211" s="30"/>
       <x:c r="E211" s="30"/>
@@ -25733,11 +25787,29 @@
       <x:c r="G211" s="30"/>
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="30"/>
-      <x:c r="J211" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
-        <x:v>139.8</x:v>
+      <x:c r="J211" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J210),1)</x:f>
+        <x:v>801.1</x:v>
       </x:c>
       <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B212" s="30"/>
+      <x:c r="C212" s="30"/>
+      <x:c r="D212" s="30"/>
+      <x:c r="E212" s="30"/>
+      <x:c r="F212" s="30"/>
+      <x:c r="G212" s="30"/>
+      <x:c r="H212" s="30"/>
+      <x:c r="I212" s="30"/>
+      <x:c r="J212" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
+        <x:v>133.5</x:v>
+      </x:c>
+      <x:c r="K212" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32473,30 +32545,48 @@
       </x:c>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B210" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C210" s="30"/>
-      <x:c r="D210" s="30"/>
-      <x:c r="E210" s="30"/>
-      <x:c r="F210" s="30"/>
-      <x:c r="G210" s="30"/>
-      <x:c r="H210" s="30"/>
-      <x:c r="I210" s="30"/>
-      <x:c r="J210" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J209),1)</x:f>
-        <x:v>665.4</x:v>
-      </x:c>
-      <x:c r="K210" s="30"/>
+      <x:c r="A210" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B210" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C210" s="22" t="str">
+        <x:v>9月8日</x:v>
+      </x:c>
+      <x:c r="D210" s="23" t="n">
+        <x:v>7773.28</x:v>
+      </x:c>
+      <x:c r="E210" s="23" t="n">
+        <x:v>7830.16</x:v>
+      </x:c>
+      <x:c r="F210" s="23" t="n">
+        <x:v>7736.44</x:v>
+      </x:c>
+      <x:c r="G210" s="23" t="n">
+        <x:v>7770.73</x:v>
+      </x:c>
+      <x:c r="H210" s="23" t="n">
+        <x:v>11.4</x:v>
+      </x:c>
+      <x:c r="I210" s="24" t="n">
+        <x:v>0.0014640363843971826</x:v>
+      </x:c>
+      <x:c r="J210" s="23" t="n">
+        <x:f>ROUND(E210-F210,1)</x:f>
+        <x:v>93.7</x:v>
+      </x:c>
+      <x:c r="K210" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B211" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B211" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C211" s="30"/>
       <x:c r="D211" s="30"/>
       <x:c r="E211" s="30"/>
@@ -32504,11 +32594,29 @@
       <x:c r="G211" s="30"/>
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="30"/>
-      <x:c r="J211" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
-        <x:v>133.1</x:v>
+      <x:c r="J211" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J210),1)</x:f>
+        <x:v>759.1</x:v>
       </x:c>
       <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B212" s="30"/>
+      <x:c r="C212" s="30"/>
+      <x:c r="D212" s="30"/>
+      <x:c r="E212" s="30"/>
+      <x:c r="F212" s="30"/>
+      <x:c r="G212" s="30"/>
+      <x:c r="H212" s="30"/>
+      <x:c r="I212" s="30"/>
+      <x:c r="J212" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
+        <x:v>126.5</x:v>
+      </x:c>
+      <x:c r="K212" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -39244,30 +39352,48 @@
       </x:c>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B210" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C210" s="30"/>
-      <x:c r="D210" s="30"/>
-      <x:c r="E210" s="30"/>
-      <x:c r="F210" s="30"/>
-      <x:c r="G210" s="30"/>
-      <x:c r="H210" s="30"/>
-      <x:c r="I210" s="30"/>
-      <x:c r="J210" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J209),1)</x:f>
-        <x:v>186.9</x:v>
-      </x:c>
-      <x:c r="K210" s="30"/>
+      <x:c r="A210" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B210" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C210" s="22" t="str">
+        <x:v>9月8日</x:v>
+      </x:c>
+      <x:c r="D210" s="23" t="n">
+        <x:v>3935.55</x:v>
+      </x:c>
+      <x:c r="E210" s="23" t="n">
+        <x:v>3951.32</x:v>
+      </x:c>
+      <x:c r="F210" s="23" t="n">
+        <x:v>3925.72</x:v>
+      </x:c>
+      <x:c r="G210" s="23" t="n">
+        <x:v>3940.55</x:v>
+      </x:c>
+      <x:c r="H210" s="23" t="n">
+        <x:v>7.9</x:v>
+      </x:c>
+      <x:c r="I210" s="24" t="n">
+        <x:v>0.001996084115238883</x:v>
+      </x:c>
+      <x:c r="J210" s="23" t="n">
+        <x:f>ROUND(E210-F210,1)</x:f>
+        <x:v>25.6</x:v>
+      </x:c>
+      <x:c r="K210" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B211" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B211" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C211" s="30"/>
       <x:c r="D211" s="30"/>
       <x:c r="E211" s="30"/>
@@ -39275,11 +39401,29 @@
       <x:c r="G211" s="30"/>
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="30"/>
-      <x:c r="J211" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
-        <x:v>37.4</x:v>
+      <x:c r="J211" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J210),1)</x:f>
+        <x:v>212.5</x:v>
       </x:c>
       <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B212" s="30"/>
+      <x:c r="C212" s="30"/>
+      <x:c r="D212" s="30"/>
+      <x:c r="E212" s="30"/>
+      <x:c r="F212" s="30"/>
+      <x:c r="G212" s="30"/>
+      <x:c r="H212" s="30"/>
+      <x:c r="I212" s="30"/>
+      <x:c r="J212" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
+        <x:v>35.4</x:v>
+      </x:c>
+      <x:c r="K212" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -52786,30 +52930,48 @@
       </x:c>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B210" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C210" s="30"/>
-      <x:c r="D210" s="30"/>
-      <x:c r="E210" s="30"/>
-      <x:c r="F210" s="30"/>
-      <x:c r="G210" s="30"/>
-      <x:c r="H210" s="30"/>
-      <x:c r="I210" s="30"/>
-      <x:c r="J210" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J209),1)</x:f>
-        <x:v>805.4</x:v>
-      </x:c>
-      <x:c r="K210" s="30"/>
+      <x:c r="A210" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B210" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C210" s="22" t="str">
+        <x:v>9月8日</x:v>
+      </x:c>
+      <x:c r="D210" s="23" t="n">
+        <x:v>7734</x:v>
+      </x:c>
+      <x:c r="E210" s="23" t="n">
+        <x:v>7817.2</x:v>
+      </x:c>
+      <x:c r="F210" s="23" t="n">
+        <x:v>7703.2</x:v>
+      </x:c>
+      <x:c r="G210" s="23" t="n">
+        <x:v>7743.4</x:v>
+      </x:c>
+      <x:c r="H210" s="23" t="n">
+        <x:v>27.2</x:v>
+      </x:c>
+      <x:c r="I210" s="24" t="n">
+        <x:v>0.003525051191000772</x:v>
+      </x:c>
+      <x:c r="J210" s="23" t="n">
+        <x:f>ROUND(E210-F210,1)</x:f>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="K210" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B211" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B211" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C211" s="30"/>
       <x:c r="D211" s="30"/>
       <x:c r="E211" s="30"/>
@@ -52817,11 +52979,29 @@
       <x:c r="G211" s="30"/>
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="30"/>
-      <x:c r="J211" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
-        <x:v>161.1</x:v>
+      <x:c r="J211" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J210),1)</x:f>
+        <x:v>919.4</x:v>
       </x:c>
       <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B212" s="30"/>
+      <x:c r="C212" s="30"/>
+      <x:c r="D212" s="30"/>
+      <x:c r="E212" s="30"/>
+      <x:c r="F212" s="30"/>
+      <x:c r="G212" s="30"/>
+      <x:c r="H212" s="30"/>
+      <x:c r="I212" s="30"/>
+      <x:c r="J212" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
+        <x:v>153.2</x:v>
+      </x:c>
+      <x:c r="K212" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -66328,30 +66508,48 @@
       </x:c>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B210" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C210" s="30"/>
-      <x:c r="D210" s="30"/>
-      <x:c r="E210" s="30"/>
-      <x:c r="F210" s="30"/>
-      <x:c r="G210" s="30"/>
-      <x:c r="H210" s="30"/>
-      <x:c r="I210" s="30"/>
-      <x:c r="J210" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J209),1)</x:f>
-        <x:v>171.8</x:v>
-      </x:c>
-      <x:c r="K210" s="30"/>
+      <x:c r="A210" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B210" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C210" s="22" t="str">
+        <x:v>9月8日</x:v>
+      </x:c>
+      <x:c r="D210" s="23" t="n">
+        <x:v>2904.8</x:v>
+      </x:c>
+      <x:c r="E210" s="23" t="n">
+        <x:v>2917.4</x:v>
+      </x:c>
+      <x:c r="F210" s="23" t="n">
+        <x:v>2891</x:v>
+      </x:c>
+      <x:c r="G210" s="23" t="n">
+        <x:v>2897</x:v>
+      </x:c>
+      <x:c r="H210" s="23" t="n">
+        <x:v>-1.8</x:v>
+      </x:c>
+      <x:c r="I210" s="24" t="n">
+        <x:v>-0.0006209465985925755</x:v>
+      </x:c>
+      <x:c r="J210" s="23" t="n">
+        <x:f>ROUND(E210-F210,1)</x:f>
+        <x:v>26.4</x:v>
+      </x:c>
+      <x:c r="K210" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B211" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B211" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C211" s="30"/>
       <x:c r="D211" s="30"/>
       <x:c r="E211" s="30"/>
@@ -66359,11 +66557,29 @@
       <x:c r="G211" s="30"/>
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="30"/>
-      <x:c r="J211" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
-        <x:v>34.4</x:v>
+      <x:c r="J211" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J210),1)</x:f>
+        <x:v>198.2</x:v>
       </x:c>
       <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B212" s="30"/>
+      <x:c r="C212" s="30"/>
+      <x:c r="D212" s="30"/>
+      <x:c r="E212" s="30"/>
+      <x:c r="F212" s="30"/>
+      <x:c r="G212" s="30"/>
+      <x:c r="H212" s="30"/>
+      <x:c r="I212" s="30"/>
+      <x:c r="J212" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K212" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R1a448288066d46b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Re77bc50e80fb4cb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R90052e4ea6ca4ea1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R1b6b42e267ab466f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R844348eb6b9d46cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rad2e135c85dc4a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R65886dd9eaf84936"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Re2b7de78aed64ce8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R7f04e2c5d6c142c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R9c4bb4f827d346a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R45a60a68df864de2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R781f304add6847b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R90a6905469814229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R1cc81e603ffa48a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R2f3f839bff454147"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rf75aa9912d9a48b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rfeac91d677074cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2313871335e746c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R08b763e8df18469a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R683e5f0640b04c87"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7662.2</x:v>
+        <x:v>7714.6</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7512.6</x:v>
+        <x:v>7592.4</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>149.6</x:v>
+        <x:v>122.2</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>31224.8</x:v>
+        <x:v>31347</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>189.2</x:v>
+        <x:v>188.8</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4576.8</x:v>
+        <x:v>4584</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4537.4</x:v>
+        <x:v>4532.8</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>39.4</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12163</x:v>
+        <x:v>12214.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>73.7</x:v>
+        <x:v>73.6</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -13286,37 +13286,37 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B159" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>9月7日-9月8日</x:v>
       </x:c>
       <x:c r="C159" s="23" t="n">
         <x:v>7527.2</x:v>
       </x:c>
       <x:c r="D159" s="23" t="n">
-        <x:v>7662.2</x:v>
+        <x:v>7714.6</x:v>
       </x:c>
       <x:c r="E159" s="23" t="n">
         <x:v>7512.6</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>7604</x:v>
-      </x:c>
-      <x:c r="G159" s="23" t="n">
+        <x:v>7633.4</x:v>
+      </x:c>
+      <x:c r="G159" s="28" t="n">
         <x:f>ROUND(F159-F158,1)</x:f>
-        <x:v>135.8</x:v>
+        <x:v>165.2</x:v>
       </x:c>
       <x:c r="H159" s="24" t="n">
         <x:f>IFERROR(F159/F158-1,"")</x:f>
-        <x:v>0.01818376583380199</x:v>
-      </x:c>
-      <x:c r="I159" s="23" t="n">
+        <x:v>0.022120457406068272</x:v>
+      </x:c>
+      <x:c r="I159" s="26" t="n">
         <x:f>ROUND(D159-E159,1)</x:f>
-        <x:v>149.6</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="J159" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K159" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -13334,7 +13334,7 @@
       <x:c r="H160" s="30"/>
       <x:c r="I160" s="32" t="n">
         <x:f>ROUND(SUM(I125:I159),1)</x:f>
-        <x:v>14978.2</x:v>
+        <x:v>15030.6</x:v>
       </x:c>
       <x:c r="J160" s="30"/>
       <x:c r="K160" s="30"/>
@@ -13352,7 +13352,7 @@
       <x:c r="H161" s="30"/>
       <x:c r="I161" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I125:I159),0),1)</x:f>
-        <x:v>427.9</x:v>
+        <x:v>429.4</x:v>
       </x:c>
       <x:c r="J161" s="30"/>
       <x:c r="K161" s="30"/>
@@ -16110,37 +16110,37 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>9月7日</x:v>
+        <x:v>9月7日-9月8日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
         <x:v>4562</x:v>
       </x:c>
       <x:c r="D239" s="23" t="n">
-        <x:v>4576.8</x:v>
+        <x:v>4584</x:v>
       </x:c>
       <x:c r="E239" s="23" t="n">
-        <x:v>4537.4</x:v>
+        <x:v>4532.8</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>4555.6</x:v>
+        <x:v>4547</x:v>
       </x:c>
       <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>18.2</x:v>
+        <x:v>9.6</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>0.004011107682814208</x:v>
+        <x:v>0.0021157491074184076</x:v>
       </x:c>
       <x:c r="I239" s="23" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
-        <x:v>39.4</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J239" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K239" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -16158,7 +16158,7 @@
       <x:c r="H240" s="30"/>
       <x:c r="I240" s="32" t="n">
         <x:f>ROUND(SUM(I205:I239),1)</x:f>
-        <x:v>5512.2</x:v>
+        <x:v>5524</x:v>
       </x:c>
       <x:c r="J240" s="30"/>
       <x:c r="K240" s="30"/>
@@ -16176,7 +16176,7 @@
       <x:c r="H241" s="30"/>
       <x:c r="I241" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I205:I239),0),1)</x:f>
-        <x:v>157.5</x:v>
+        <x:v>157.8</x:v>
       </x:c>
       <x:c r="J241" s="30"/>
       <x:c r="K241" s="30"/>
@@ -46159,30 +46159,48 @@
       </x:c>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B210" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C210" s="30"/>
-      <x:c r="D210" s="30"/>
-      <x:c r="E210" s="30"/>
-      <x:c r="F210" s="30"/>
-      <x:c r="G210" s="30"/>
-      <x:c r="H210" s="30"/>
-      <x:c r="I210" s="30"/>
-      <x:c r="J210" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J209),1)</x:f>
-        <x:v>781</x:v>
-      </x:c>
-      <x:c r="K210" s="30"/>
+      <x:c r="A210" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B210" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C210" s="22" t="str">
+        <x:v>9月8日</x:v>
+      </x:c>
+      <x:c r="D210" s="23" t="n">
+        <x:v>7625.8</x:v>
+      </x:c>
+      <x:c r="E210" s="23" t="n">
+        <x:v>7714.6</x:v>
+      </x:c>
+      <x:c r="F210" s="23" t="n">
+        <x:v>7592.4</x:v>
+      </x:c>
+      <x:c r="G210" s="23" t="n">
+        <x:v>7633.4</x:v>
+      </x:c>
+      <x:c r="H210" s="23" t="n">
+        <x:v>29.4</x:v>
+      </x:c>
+      <x:c r="I210" s="24" t="n">
+        <x:v>0.0038663861125722843</x:v>
+      </x:c>
+      <x:c r="J210" s="23" t="n">
+        <x:f>ROUND(E210-F210,1)</x:f>
+        <x:v>122.2</x:v>
+      </x:c>
+      <x:c r="K210" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B211" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B211" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C211" s="30"/>
       <x:c r="D211" s="30"/>
       <x:c r="E211" s="30"/>
@@ -46190,11 +46208,29 @@
       <x:c r="G211" s="30"/>
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="30"/>
-      <x:c r="J211" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
-        <x:v>156.2</x:v>
+      <x:c r="J211" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J210),1)</x:f>
+        <x:v>903.2</x:v>
       </x:c>
       <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B212" s="30"/>
+      <x:c r="C212" s="30"/>
+      <x:c r="D212" s="30"/>
+      <x:c r="E212" s="30"/>
+      <x:c r="F212" s="30"/>
+      <x:c r="G212" s="30"/>
+      <x:c r="H212" s="30"/>
+      <x:c r="I212" s="30"/>
+      <x:c r="J212" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
+        <x:v>150.5</x:v>
+      </x:c>
+      <x:c r="K212" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -59737,30 +59773,48 @@
       </x:c>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B210" s="30" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C210" s="30"/>
-      <x:c r="D210" s="30"/>
-      <x:c r="E210" s="30"/>
-      <x:c r="F210" s="30"/>
-      <x:c r="G210" s="30"/>
-      <x:c r="H210" s="30"/>
-      <x:c r="I210" s="30"/>
-      <x:c r="J210" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J209),1)</x:f>
-        <x:v>276.4</x:v>
-      </x:c>
-      <x:c r="K210" s="30"/>
+      <x:c r="A210" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B210" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C210" s="22" t="str">
+        <x:v>9月8日</x:v>
+      </x:c>
+      <x:c r="D210" s="23" t="n">
+        <x:v>4559</x:v>
+      </x:c>
+      <x:c r="E210" s="23" t="n">
+        <x:v>4584</x:v>
+      </x:c>
+      <x:c r="F210" s="23" t="n">
+        <x:v>4532.8</x:v>
+      </x:c>
+      <x:c r="G210" s="23" t="n">
+        <x:v>4547</x:v>
+      </x:c>
+      <x:c r="H210" s="23" t="n">
+        <x:v>-8.6</x:v>
+      </x:c>
+      <x:c r="I210" s="24" t="n">
+        <x:v>-0.0018877864606199335</x:v>
+      </x:c>
+      <x:c r="J210" s="23" t="n">
+        <x:f>ROUND(E210-F210,1)</x:f>
+        <x:v>51.2</x:v>
+      </x:c>
+      <x:c r="K210" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B211" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B211" s="30" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C211" s="30"/>
       <x:c r="D211" s="30"/>
       <x:c r="E211" s="30"/>
@@ -59768,11 +59822,29 @@
       <x:c r="G211" s="30"/>
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="30"/>
-      <x:c r="J211" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J209),0),1)</x:f>
-        <x:v>55.3</x:v>
+      <x:c r="J211" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J210),1)</x:f>
+        <x:v>327.6</x:v>
       </x:c>
       <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B212" s="30"/>
+      <x:c r="C212" s="30"/>
+      <x:c r="D212" s="30"/>
+      <x:c r="E212" s="30"/>
+      <x:c r="F212" s="30"/>
+      <x:c r="G212" s="30"/>
+      <x:c r="H212" s="30"/>
+      <x:c r="I212" s="30"/>
+      <x:c r="J212" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
+        <x:v>54.6</x:v>
+      </x:c>
+      <x:c r="K212" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R45a60a68df864de2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R781f304add6847b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R90a6905469814229"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R1cc81e603ffa48a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R2f3f839bff454147"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rf75aa9912d9a48b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rfeac91d677074cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2313871335e746c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R08b763e8df18469a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R683e5f0640b04c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R033c816c5ac347d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R9342bee0f9ee4b9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb9cbdd1b003d4cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rdf74b9e183dc4235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R4bc4bec7345e42ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2aac21c4ea024a78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R9109a7df31aa4b17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R259835087c2f44ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rdafe546eacc5482c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R675c97fe5ad0495e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7724.94</x:v>
+        <x:v>7715.08</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7622.9</x:v>
+        <x:v>7602.5</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>102</x:v>
+        <x:v>112.6</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>29531.9</x:v>
+        <x:v>29644.5</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>177.9</x:v>
+        <x:v>177.5</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7830.16</x:v>
+        <x:v>7816.66</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7736.44</x:v>
+        <x:v>7723.82</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>93.7</x:v>
+        <x:v>92.8</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>29542.8</x:v>
+        <x:v>29635.6</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>178</x:v>
+        <x:v>177.5</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3951.32</x:v>
+        <x:v>3958.12</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3925.72</x:v>
+        <x:v>3933.47</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>25.6</x:v>
+        <x:v>24.7</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8093.6</x:v>
+        <x:v>8118.3</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>48.8</x:v>
+        <x:v>48.6</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7714.6</x:v>
+        <x:v>7705</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7592.4</x:v>
+        <x:v>7575</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>122.2</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>31347</x:v>
+        <x:v>31477</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>188.8</x:v>
+        <x:v>188.5</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4584</x:v>
+        <x:v>4574.2</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4532.8</x:v>
+        <x:v>4535.6</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>51.2</x:v>
+        <x:v>38.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12214.2</x:v>
+        <x:v>12252.8</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>73.6</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -9050,7 +9050,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" s="22" t="str">
-        <x:v>9月7日-9月8日</x:v>
+        <x:v>9月7日-9月9日</x:v>
       </x:c>
       <x:c r="C39" s="23" t="n">
         <x:v>7551.02</x:v>
@@ -9062,15 +9062,15 @@
         <x:v>7541.14</x:v>
       </x:c>
       <x:c r="F39" s="23" t="n">
-        <x:v>7659.61</x:v>
-      </x:c>
-      <x:c r="G39" s="28" t="n">
+        <x:v>7648.8</x:v>
+      </x:c>
+      <x:c r="G39" s="23" t="n">
         <x:f>ROUND(F39-F38,1)</x:f>
-        <x:v>151.5</x:v>
+        <x:v>140.7</x:v>
       </x:c>
       <x:c r="H39" s="24" t="n">
         <x:f>IFERROR(F39/F38-1,"")</x:f>
-        <x:v>0.02018089820447</x:v>
+        <x:v>0.018741117914143235</x:v>
       </x:c>
       <x:c r="I39" s="26" t="n">
         <x:f>ROUND(D39-E39,1)</x:f>
@@ -9080,7 +9080,7 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K39" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -10462,7 +10462,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="22" t="str">
-        <x:v>9月7日-9月8日</x:v>
+        <x:v>9月7日-9月9日</x:v>
       </x:c>
       <x:c r="C79" s="23" t="n">
         <x:v>7687.47</x:v>
@@ -10474,15 +10474,15 @@
         <x:v>7672.99</x:v>
       </x:c>
       <x:c r="F79" s="23" t="n">
-        <x:v>7770.73</x:v>
+        <x:v>7768.11</x:v>
       </x:c>
       <x:c r="G79" s="23" t="n">
         <x:f>ROUND(F79-F78,1)</x:f>
-        <x:v>118</x:v>
+        <x:v>115.4</x:v>
       </x:c>
       <x:c r="H79" s="24" t="n">
         <x:f>IFERROR(F79/F78-1,"")</x:f>
-        <x:v>0.015424641531278649</x:v>
+        <x:v>0.01508227825771069</x:v>
       </x:c>
       <x:c r="I79" s="23" t="n">
         <x:f>ROUND(D79-E79,1)</x:f>
@@ -10492,7 +10492,7 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K79" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -11874,37 +11874,37 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B119" s="22" t="str">
-        <x:v>9月7日-9月8日</x:v>
+        <x:v>9月7日-9月9日</x:v>
       </x:c>
       <x:c r="C119" s="23" t="n">
         <x:v>3942.51</x:v>
       </x:c>
       <x:c r="D119" s="23" t="n">
-        <x:v>3951.32</x:v>
+        <x:v>3958.12</x:v>
       </x:c>
       <x:c r="E119" s="23" t="n">
         <x:v>3916.49</x:v>
       </x:c>
       <x:c r="F119" s="23" t="n">
-        <x:v>3940.55</x:v>
+        <x:v>3951.51</x:v>
       </x:c>
       <x:c r="G119" s="23" t="n">
         <x:f>ROUND(F119-F118,1)</x:f>
-        <x:v>10.4</x:v>
+        <x:v>21.4</x:v>
       </x:c>
       <x:c r="H119" s="24" t="n">
         <x:f>IFERROR(F119/F118-1,"")</x:f>
-        <x:v>0.0026538629863719354</x:v>
+        <x:v>0.005442581905896082</x:v>
       </x:c>
       <x:c r="I119" s="23" t="n">
         <x:f>ROUND(D119-E119,1)</x:f>
-        <x:v>34.8</x:v>
+        <x:v>41.6</x:v>
       </x:c>
       <x:c r="J119" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K119" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -11922,7 +11922,7 @@
       <x:c r="H120" s="30"/>
       <x:c r="I120" s="32" t="n">
         <x:f>ROUND(SUM(I85:I119),1)</x:f>
-        <x:v>3792.8</x:v>
+        <x:v>3799.6</x:v>
       </x:c>
       <x:c r="J120" s="30"/>
       <x:c r="K120" s="30"/>
@@ -11940,7 +11940,7 @@
       <x:c r="H121" s="30"/>
       <x:c r="I121" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I85:I119),0),1)</x:f>
-        <x:v>108.4</x:v>
+        <x:v>108.6</x:v>
       </x:c>
       <x:c r="J121" s="30"/>
       <x:c r="K121" s="30"/>
@@ -13286,7 +13286,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B159" s="22" t="str">
-        <x:v>9月7日-9月8日</x:v>
+        <x:v>9月7日-9月9日</x:v>
       </x:c>
       <x:c r="C159" s="23" t="n">
         <x:v>7527.2</x:v>
@@ -13298,15 +13298,15 @@
         <x:v>7512.6</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>7633.4</x:v>
+        <x:v>7618.6</x:v>
       </x:c>
       <x:c r="G159" s="28" t="n">
         <x:f>ROUND(F159-F158,1)</x:f>
-        <x:v>165.2</x:v>
+        <x:v>150.4</x:v>
       </x:c>
       <x:c r="H159" s="24" t="n">
         <x:f>IFERROR(F159/F158-1,"")</x:f>
-        <x:v>0.022120457406068272</x:v>
+        <x:v>0.020138721512546587</x:v>
       </x:c>
       <x:c r="I159" s="26" t="n">
         <x:f>ROUND(D159-E159,1)</x:f>
@@ -13316,7 +13316,7 @@
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K159" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -16110,7 +16110,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>9月7日-9月8日</x:v>
+        <x:v>9月7日-9月9日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
         <x:v>4562</x:v>
@@ -16122,15 +16122,15 @@
         <x:v>4532.8</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>4547</x:v>
+        <x:v>4560</x:v>
       </x:c>
       <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>9.6</x:v>
+        <x:v>22.6</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>0.0021157491074184076</x:v>
+        <x:v>0.00498082602371408</x:v>
       </x:c>
       <x:c r="I239" s="23" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
@@ -16140,7 +16140,7 @@
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K239" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -25774,30 +25774,48 @@
       </x:c>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B211" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C211" s="30"/>
-      <x:c r="D211" s="30"/>
-      <x:c r="E211" s="30"/>
-      <x:c r="F211" s="30"/>
-      <x:c r="G211" s="30"/>
-      <x:c r="H211" s="30"/>
-      <x:c r="I211" s="30"/>
-      <x:c r="J211" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J210),1)</x:f>
-        <x:v>801.1</x:v>
-      </x:c>
-      <x:c r="K211" s="30"/>
+      <x:c r="A211" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B211" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C211" s="22" t="str">
+        <x:v>9月9日</x:v>
+      </x:c>
+      <x:c r="D211" s="23" t="n">
+        <x:v>7676.86</x:v>
+      </x:c>
+      <x:c r="E211" s="23" t="n">
+        <x:v>7715.08</x:v>
+      </x:c>
+      <x:c r="F211" s="23" t="n">
+        <x:v>7602.5</x:v>
+      </x:c>
+      <x:c r="G211" s="23" t="n">
+        <x:v>7648.8</x:v>
+      </x:c>
+      <x:c r="H211" s="23" t="n">
+        <x:v>-10.8</x:v>
+      </x:c>
+      <x:c r="I211" s="24" t="n">
+        <x:v>-0.0014112990086961874</x:v>
+      </x:c>
+      <x:c r="J211" s="23" t="n">
+        <x:f>ROUND(E211-F211,1)</x:f>
+        <x:v>112.6</x:v>
+      </x:c>
+      <x:c r="K211" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B212" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B212" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C212" s="30"/>
       <x:c r="D212" s="30"/>
       <x:c r="E212" s="30"/>
@@ -25805,11 +25823,29 @@
       <x:c r="G212" s="30"/>
       <x:c r="H212" s="30"/>
       <x:c r="I212" s="30"/>
-      <x:c r="J212" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
-        <x:v>133.5</x:v>
+      <x:c r="J212" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J211),1)</x:f>
+        <x:v>913.7</x:v>
       </x:c>
       <x:c r="K212" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B213" s="30"/>
+      <x:c r="C213" s="30"/>
+      <x:c r="D213" s="30"/>
+      <x:c r="E213" s="30"/>
+      <x:c r="F213" s="30"/>
+      <x:c r="G213" s="30"/>
+      <x:c r="H213" s="30"/>
+      <x:c r="I213" s="30"/>
+      <x:c r="J213" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
+        <x:v>130.5</x:v>
+      </x:c>
+      <x:c r="K213" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32581,30 +32617,48 @@
       </x:c>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B211" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C211" s="30"/>
-      <x:c r="D211" s="30"/>
-      <x:c r="E211" s="30"/>
-      <x:c r="F211" s="30"/>
-      <x:c r="G211" s="30"/>
-      <x:c r="H211" s="30"/>
-      <x:c r="I211" s="30"/>
-      <x:c r="J211" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J210),1)</x:f>
-        <x:v>759.1</x:v>
-      </x:c>
-      <x:c r="K211" s="30"/>
+      <x:c r="A211" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B211" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C211" s="22" t="str">
+        <x:v>9月9日</x:v>
+      </x:c>
+      <x:c r="D211" s="23" t="n">
+        <x:v>7793.04</x:v>
+      </x:c>
+      <x:c r="E211" s="23" t="n">
+        <x:v>7816.66</x:v>
+      </x:c>
+      <x:c r="F211" s="23" t="n">
+        <x:v>7723.82</x:v>
+      </x:c>
+      <x:c r="G211" s="23" t="n">
+        <x:v>7768.11</x:v>
+      </x:c>
+      <x:c r="H211" s="23" t="n">
+        <x:v>-2.6</x:v>
+      </x:c>
+      <x:c r="I211" s="24" t="n">
+        <x:v>-0.0003371626603935196</x:v>
+      </x:c>
+      <x:c r="J211" s="23" t="n">
+        <x:f>ROUND(E211-F211,1)</x:f>
+        <x:v>92.8</x:v>
+      </x:c>
+      <x:c r="K211" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B212" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B212" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C212" s="30"/>
       <x:c r="D212" s="30"/>
       <x:c r="E212" s="30"/>
@@ -32612,11 +32666,29 @@
       <x:c r="G212" s="30"/>
       <x:c r="H212" s="30"/>
       <x:c r="I212" s="30"/>
-      <x:c r="J212" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
-        <x:v>126.5</x:v>
+      <x:c r="J212" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J211),1)</x:f>
+        <x:v>851.9</x:v>
       </x:c>
       <x:c r="K212" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B213" s="30"/>
+      <x:c r="C213" s="30"/>
+      <x:c r="D213" s="30"/>
+      <x:c r="E213" s="30"/>
+      <x:c r="F213" s="30"/>
+      <x:c r="G213" s="30"/>
+      <x:c r="H213" s="30"/>
+      <x:c r="I213" s="30"/>
+      <x:c r="J213" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
+        <x:v>121.7</x:v>
+      </x:c>
+      <x:c r="K213" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -39388,30 +39460,48 @@
       </x:c>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B211" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C211" s="30"/>
-      <x:c r="D211" s="30"/>
-      <x:c r="E211" s="30"/>
-      <x:c r="F211" s="30"/>
-      <x:c r="G211" s="30"/>
-      <x:c r="H211" s="30"/>
-      <x:c r="I211" s="30"/>
-      <x:c r="J211" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J210),1)</x:f>
-        <x:v>212.5</x:v>
-      </x:c>
-      <x:c r="K211" s="30"/>
+      <x:c r="A211" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B211" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C211" s="22" t="str">
+        <x:v>9月9日</x:v>
+      </x:c>
+      <x:c r="D211" s="23" t="n">
+        <x:v>3943.92</x:v>
+      </x:c>
+      <x:c r="E211" s="23" t="n">
+        <x:v>3958.12</x:v>
+      </x:c>
+      <x:c r="F211" s="23" t="n">
+        <x:v>3933.47</x:v>
+      </x:c>
+      <x:c r="G211" s="23" t="n">
+        <x:v>3951.51</x:v>
+      </x:c>
+      <x:c r="H211" s="23" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I211" s="24" t="n">
+        <x:v>0.0027813376305338977</x:v>
+      </x:c>
+      <x:c r="J211" s="23" t="n">
+        <x:f>ROUND(E211-F211,1)</x:f>
+        <x:v>24.7</x:v>
+      </x:c>
+      <x:c r="K211" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B212" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B212" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C212" s="30"/>
       <x:c r="D212" s="30"/>
       <x:c r="E212" s="30"/>
@@ -39419,11 +39509,29 @@
       <x:c r="G212" s="30"/>
       <x:c r="H212" s="30"/>
       <x:c r="I212" s="30"/>
-      <x:c r="J212" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
-        <x:v>35.4</x:v>
+      <x:c r="J212" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J211),1)</x:f>
+        <x:v>237.2</x:v>
       </x:c>
       <x:c r="K212" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B213" s="30"/>
+      <x:c r="C213" s="30"/>
+      <x:c r="D213" s="30"/>
+      <x:c r="E213" s="30"/>
+      <x:c r="F213" s="30"/>
+      <x:c r="G213" s="30"/>
+      <x:c r="H213" s="30"/>
+      <x:c r="I213" s="30"/>
+      <x:c r="J213" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
+        <x:v>33.9</x:v>
+      </x:c>
+      <x:c r="K213" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -46195,30 +46303,48 @@
       </x:c>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B211" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C211" s="30"/>
-      <x:c r="D211" s="30"/>
-      <x:c r="E211" s="30"/>
-      <x:c r="F211" s="30"/>
-      <x:c r="G211" s="30"/>
-      <x:c r="H211" s="30"/>
-      <x:c r="I211" s="30"/>
-      <x:c r="J211" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J210),1)</x:f>
-        <x:v>903.2</x:v>
-      </x:c>
-      <x:c r="K211" s="30"/>
+      <x:c r="A211" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B211" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C211" s="22" t="str">
+        <x:v>9月9日</x:v>
+      </x:c>
+      <x:c r="D211" s="23" t="n">
+        <x:v>7671.8</x:v>
+      </x:c>
+      <x:c r="E211" s="23" t="n">
+        <x:v>7705</x:v>
+      </x:c>
+      <x:c r="F211" s="23" t="n">
+        <x:v>7575</x:v>
+      </x:c>
+      <x:c r="G211" s="23" t="n">
+        <x:v>7618.6</x:v>
+      </x:c>
+      <x:c r="H211" s="23" t="n">
+        <x:v>-14.8</x:v>
+      </x:c>
+      <x:c r="I211" s="24" t="n">
+        <x:v>-0.001938847695653223</x:v>
+      </x:c>
+      <x:c r="J211" s="23" t="n">
+        <x:f>ROUND(E211-F211,1)</x:f>
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="K211" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B212" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B212" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C212" s="30"/>
       <x:c r="D212" s="30"/>
       <x:c r="E212" s="30"/>
@@ -46226,11 +46352,29 @@
       <x:c r="G212" s="30"/>
       <x:c r="H212" s="30"/>
       <x:c r="I212" s="30"/>
-      <x:c r="J212" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
-        <x:v>150.5</x:v>
+      <x:c r="J212" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J211),1)</x:f>
+        <x:v>1033.2</x:v>
       </x:c>
       <x:c r="K212" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B213" s="30"/>
+      <x:c r="C213" s="30"/>
+      <x:c r="D213" s="30"/>
+      <x:c r="E213" s="30"/>
+      <x:c r="F213" s="30"/>
+      <x:c r="G213" s="30"/>
+      <x:c r="H213" s="30"/>
+      <x:c r="I213" s="30"/>
+      <x:c r="J213" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
+        <x:v>147.6</x:v>
+      </x:c>
+      <x:c r="K213" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -59809,30 +59953,48 @@
       </x:c>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B211" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C211" s="30"/>
-      <x:c r="D211" s="30"/>
-      <x:c r="E211" s="30"/>
-      <x:c r="F211" s="30"/>
-      <x:c r="G211" s="30"/>
-      <x:c r="H211" s="30"/>
-      <x:c r="I211" s="30"/>
-      <x:c r="J211" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J210),1)</x:f>
-        <x:v>327.6</x:v>
-      </x:c>
-      <x:c r="K211" s="30"/>
+      <x:c r="A211" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B211" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C211" s="22" t="str">
+        <x:v>9月9日</x:v>
+      </x:c>
+      <x:c r="D211" s="23" t="n">
+        <x:v>4564.2</x:v>
+      </x:c>
+      <x:c r="E211" s="23" t="n">
+        <x:v>4574.2</x:v>
+      </x:c>
+      <x:c r="F211" s="23" t="n">
+        <x:v>4535.6</x:v>
+      </x:c>
+      <x:c r="G211" s="23" t="n">
+        <x:v>4560</x:v>
+      </x:c>
+      <x:c r="H211" s="23" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I211" s="24" t="n">
+        <x:v>0.0028590279305036326</x:v>
+      </x:c>
+      <x:c r="J211" s="23" t="n">
+        <x:f>ROUND(E211-F211,1)</x:f>
+        <x:v>38.6</x:v>
+      </x:c>
+      <x:c r="K211" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B212" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B212" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C212" s="30"/>
       <x:c r="D212" s="30"/>
       <x:c r="E212" s="30"/>
@@ -59840,11 +60002,29 @@
       <x:c r="G212" s="30"/>
       <x:c r="H212" s="30"/>
       <x:c r="I212" s="30"/>
-      <x:c r="J212" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
-        <x:v>54.6</x:v>
+      <x:c r="J212" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J211),1)</x:f>
+        <x:v>366.2</x:v>
       </x:c>
       <x:c r="K212" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B213" s="30"/>
+      <x:c r="C213" s="30"/>
+      <x:c r="D213" s="30"/>
+      <x:c r="E213" s="30"/>
+      <x:c r="F213" s="30"/>
+      <x:c r="G213" s="30"/>
+      <x:c r="H213" s="30"/>
+      <x:c r="I213" s="30"/>
+      <x:c r="J213" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
+        <x:v>52.3</x:v>
+      </x:c>
+      <x:c r="K213" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R033c816c5ac347d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R9342bee0f9ee4b9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb9cbdd1b003d4cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rdf74b9e183dc4235"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R4bc4bec7345e42ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2aac21c4ea024a78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R9109a7df31aa4b17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R259835087c2f44ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rdafe546eacc5482c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R675c97fe5ad0495e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R40190822797a4e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Ra4442e681ed243db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rc5a0b1e232b5414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rfccecf9c4b404d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rbec2751100cb4819"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rbbb908e53d1e4377"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd00a35fa0b944639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Re8596edf54f24535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R9cd030afe5f648f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Re9e42f985c304b95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7817.2</x:v>
+        <x:v>7804.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7703.2</x:v>
+        <x:v>7695.4</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>114</x:v>
+        <x:v>109.4</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>32663.6</x:v>
+        <x:v>32773</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>196.8</x:v>
+        <x:v>196.2</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2917.4</x:v>
+        <x:v>2909.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2891</x:v>
+        <x:v>2887.6</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>26.4</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6774.8</x:v>
+        <x:v>6797</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.8</x:v>
+        <x:v>40.7</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>143200</x:v>
+        <x:v>142880</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>141320</x:v>
+        <x:v>139800</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>1880</x:v>
+        <x:v>3080</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1392780</x:v>
+        <x:v>1395860</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8390.2</x:v>
+        <x:v>8358.4</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -7633,30 +7633,48 @@
       </x:c>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B211" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C211" s="30"/>
-      <x:c r="D211" s="30"/>
-      <x:c r="E211" s="30"/>
-      <x:c r="F211" s="30"/>
-      <x:c r="G211" s="30"/>
-      <x:c r="H211" s="30"/>
-      <x:c r="I211" s="30"/>
-      <x:c r="J211" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J210),1)</x:f>
-        <x:v>31020</x:v>
-      </x:c>
-      <x:c r="K211" s="30"/>
+      <x:c r="A211" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B211" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C211" s="22" t="str">
+        <x:v>9月9日</x:v>
+      </x:c>
+      <x:c r="D211" s="23" t="n">
+        <x:v>140000</x:v>
+      </x:c>
+      <x:c r="E211" s="23" t="n">
+        <x:v>142880</x:v>
+      </x:c>
+      <x:c r="F211" s="23" t="n">
+        <x:v>139800</x:v>
+      </x:c>
+      <x:c r="G211" s="23" t="n">
+        <x:v>141260</x:v>
+      </x:c>
+      <x:c r="H211" s="23" t="n">
+        <x:v>-60</x:v>
+      </x:c>
+      <x:c r="I211" s="24" t="n">
+        <x:v>-0.0004245683555051949</x:v>
+      </x:c>
+      <x:c r="J211" s="23" t="n">
+        <x:f>ROUND(E211-F211,1)</x:f>
+        <x:v>3080</x:v>
+      </x:c>
+      <x:c r="K211" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B212" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B212" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C212" s="30"/>
       <x:c r="D212" s="30"/>
       <x:c r="E212" s="30"/>
@@ -7664,11 +7682,29 @@
       <x:c r="G212" s="30"/>
       <x:c r="H212" s="30"/>
       <x:c r="I212" s="30"/>
-      <x:c r="J212" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
-        <x:v>5170</x:v>
+      <x:c r="J212" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J211),1)</x:f>
+        <x:v>34100</x:v>
       </x:c>
       <x:c r="K212" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B213" s="30"/>
+      <x:c r="C213" s="30"/>
+      <x:c r="D213" s="30"/>
+      <x:c r="E213" s="30"/>
+      <x:c r="F213" s="30"/>
+      <x:c r="G213" s="30"/>
+      <x:c r="H213" s="30"/>
+      <x:c r="I213" s="30"/>
+      <x:c r="J213" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
+        <x:v>4871.4</x:v>
+      </x:c>
+      <x:c r="K213" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -14698,7 +14734,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B199" s="22" t="str">
-        <x:v>9月7日-9月8日</x:v>
+        <x:v>9月7日-9月9日</x:v>
       </x:c>
       <x:c r="C199" s="23" t="n">
         <x:v>7665.6</x:v>
@@ -14710,15 +14746,15 @@
         <x:v>7651.2</x:v>
       </x:c>
       <x:c r="F199" s="23" t="n">
-        <x:v>7743.4</x:v>
+        <x:v>7738.6</x:v>
       </x:c>
       <x:c r="G199" s="23" t="n">
         <x:f>ROUND(F199-F198,1)</x:f>
-        <x:v>135.4</x:v>
+        <x:v>130.6</x:v>
       </x:c>
       <x:c r="H199" s="24" t="n">
         <x:f>IFERROR(F199/F198-1,"")</x:f>
-        <x:v>0.017797055730809586</x:v>
+        <x:v>0.017166140904311344</x:v>
       </x:c>
       <x:c r="I199" s="26" t="n">
         <x:f>ROUND(D199-E199,1)</x:f>
@@ -14728,7 +14764,7 @@
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K199" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -17522,7 +17558,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>9月7日-9月8日</x:v>
+        <x:v>9月7日-9月9日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
         <x:v>2923.2</x:v>
@@ -17531,28 +17567,28 @@
         <x:v>2931.4</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2887.6</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>2897</x:v>
+        <x:v>2901.2</x:v>
       </x:c>
       <x:c r="G279" s="23" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>-18.8</x:v>
+        <x:v>-14.6</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>-0.0064476301529597935</x:v>
+        <x:v>-0.0050072021400645594</x:v>
       </x:c>
       <x:c r="I279" s="23" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>40.4</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -17570,7 +17606,7 @@
       <x:c r="H280" s="30"/>
       <x:c r="I280" s="32" t="n">
         <x:f>ROUND(SUM(I245:I279),1)</x:f>
-        <x:v>3161.4</x:v>
+        <x:v>3164.8</x:v>
       </x:c>
       <x:c r="J280" s="30"/>
       <x:c r="K280" s="30"/>
@@ -17588,7 +17624,7 @@
       <x:c r="H281" s="30"/>
       <x:c r="I281" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I245:I279),0),1)</x:f>
-        <x:v>90.3</x:v>
+        <x:v>90.4</x:v>
       </x:c>
       <x:c r="J281" s="30"/>
       <x:c r="K281" s="30"/>
@@ -18934,7 +18970,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B319" s="22" t="str">
-        <x:v>9月7日-9月8日</x:v>
+        <x:v>9月7日-9月9日</x:v>
       </x:c>
       <x:c r="C319" s="23" t="n">
         <x:v>142120</x:v>
@@ -18943,28 +18979,28 @@
         <x:v>143200</x:v>
       </x:c>
       <x:c r="E319" s="23" t="n">
-        <x:v>139880</x:v>
+        <x:v>139800</x:v>
       </x:c>
       <x:c r="F319" s="23" t="n">
-        <x:v>141320</x:v>
+        <x:v>141260</x:v>
       </x:c>
       <x:c r="G319" s="28" t="n">
         <x:f>ROUND(F319-F318,1)</x:f>
-        <x:v>340</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="H319" s="24" t="n">
         <x:f>IFERROR(F319/F318-1,"")</x:f>
-        <x:v>0.002411689601361955</x:v>
+        <x:v>0.0019860973187686426</x:v>
       </x:c>
       <x:c r="I319" s="23" t="n">
         <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>3320</x:v>
+        <x:v>3400</x:v>
       </x:c>
       <x:c r="J319" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K319" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
@@ -18982,7 +19018,7 @@
       <x:c r="H320" s="30"/>
       <x:c r="I320" s="32" t="n">
         <x:f>ROUND(SUM(I285:I319),1)</x:f>
-        <x:v>712540</x:v>
+        <x:v>712620</x:v>
       </x:c>
       <x:c r="J320" s="30"/>
       <x:c r="K320" s="30"/>
@@ -19000,7 +19036,7 @@
       <x:c r="H321" s="30"/>
       <x:c r="I321" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I285:I319),0),1)</x:f>
-        <x:v>20358.3</x:v>
+        <x:v>20360.6</x:v>
       </x:c>
       <x:c r="J321" s="30"/>
       <x:c r="K321" s="30"/>
@@ -53146,30 +53182,48 @@
       </x:c>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B211" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C211" s="30"/>
-      <x:c r="D211" s="30"/>
-      <x:c r="E211" s="30"/>
-      <x:c r="F211" s="30"/>
-      <x:c r="G211" s="30"/>
-      <x:c r="H211" s="30"/>
-      <x:c r="I211" s="30"/>
-      <x:c r="J211" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J210),1)</x:f>
-        <x:v>919.4</x:v>
-      </x:c>
-      <x:c r="K211" s="30"/>
+      <x:c r="A211" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B211" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C211" s="22" t="str">
+        <x:v>9月9日</x:v>
+      </x:c>
+      <x:c r="D211" s="23" t="n">
+        <x:v>7771</x:v>
+      </x:c>
+      <x:c r="E211" s="23" t="n">
+        <x:v>7804.8</x:v>
+      </x:c>
+      <x:c r="F211" s="23" t="n">
+        <x:v>7695.4</x:v>
+      </x:c>
+      <x:c r="G211" s="23" t="n">
+        <x:v>7738.6</x:v>
+      </x:c>
+      <x:c r="H211" s="23" t="n">
+        <x:v>-4.8</x:v>
+      </x:c>
+      <x:c r="I211" s="24" t="n">
+        <x:v>-0.0006198827388484984</x:v>
+      </x:c>
+      <x:c r="J211" s="23" t="n">
+        <x:f>ROUND(E211-F211,1)</x:f>
+        <x:v>109.4</x:v>
+      </x:c>
+      <x:c r="K211" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B212" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B212" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C212" s="30"/>
       <x:c r="D212" s="30"/>
       <x:c r="E212" s="30"/>
@@ -53177,11 +53231,29 @@
       <x:c r="G212" s="30"/>
       <x:c r="H212" s="30"/>
       <x:c r="I212" s="30"/>
-      <x:c r="J212" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
-        <x:v>153.2</x:v>
+      <x:c r="J212" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J211),1)</x:f>
+        <x:v>1028.8</x:v>
       </x:c>
       <x:c r="K212" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B213" s="30"/>
+      <x:c r="C213" s="30"/>
+      <x:c r="D213" s="30"/>
+      <x:c r="E213" s="30"/>
+      <x:c r="F213" s="30"/>
+      <x:c r="G213" s="30"/>
+      <x:c r="H213" s="30"/>
+      <x:c r="I213" s="30"/>
+      <x:c r="J213" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="K213" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -66796,30 +66868,48 @@
       </x:c>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B211" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C211" s="30"/>
-      <x:c r="D211" s="30"/>
-      <x:c r="E211" s="30"/>
-      <x:c r="F211" s="30"/>
-      <x:c r="G211" s="30"/>
-      <x:c r="H211" s="30"/>
-      <x:c r="I211" s="30"/>
-      <x:c r="J211" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J210),1)</x:f>
-        <x:v>198.2</x:v>
-      </x:c>
-      <x:c r="K211" s="30"/>
+      <x:c r="A211" s="22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B211" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C211" s="22" t="str">
+        <x:v>9月9日</x:v>
+      </x:c>
+      <x:c r="D211" s="23" t="n">
+        <x:v>2903.2</x:v>
+      </x:c>
+      <x:c r="E211" s="23" t="n">
+        <x:v>2909.8</x:v>
+      </x:c>
+      <x:c r="F211" s="23" t="n">
+        <x:v>2887.6</x:v>
+      </x:c>
+      <x:c r="G211" s="23" t="n">
+        <x:v>2901.2</x:v>
+      </x:c>
+      <x:c r="H211" s="23" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="I211" s="24" t="n">
+        <x:v>0.001449775629962069</x:v>
+      </x:c>
+      <x:c r="J211" s="23" t="n">
+        <x:f>ROUND(E211-F211,1)</x:f>
+        <x:v>22.2</x:v>
+      </x:c>
+      <x:c r="K211" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B212" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B212" s="30" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C212" s="30"/>
       <x:c r="D212" s="30"/>
       <x:c r="E212" s="30"/>
@@ -66827,11 +66917,29 @@
       <x:c r="G212" s="30"/>
       <x:c r="H212" s="30"/>
       <x:c r="I212" s="30"/>
-      <x:c r="J212" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J210),0),1)</x:f>
-        <x:v>33</x:v>
+      <x:c r="J212" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J211),1)</x:f>
+        <x:v>220.4</x:v>
       </x:c>
       <x:c r="K212" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B213" s="30"/>
+      <x:c r="C213" s="30"/>
+      <x:c r="D213" s="30"/>
+      <x:c r="E213" s="30"/>
+      <x:c r="F213" s="30"/>
+      <x:c r="G213" s="30"/>
+      <x:c r="H213" s="30"/>
+      <x:c r="I213" s="30"/>
+      <x:c r="J213" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
+        <x:v>31.5</x:v>
+      </x:c>
+      <x:c r="K213" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R40190822797a4e6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Ra4442e681ed243db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rc5a0b1e232b5414f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rfccecf9c4b404d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rbec2751100cb4819"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rbbb908e53d1e4377"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd00a35fa0b944639"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Re8596edf54f24535"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R9cd030afe5f648f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Re9e42f985c304b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rcc8dff2184b04c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Re6fd934221c54177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R0994ff9a89ef4ff4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R17d2dbc586834072"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Raba888b2e2ec4388"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rf90da8fc6ad4405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Radf12ab8170a4f4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rb11f368185084d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R3b2f66bfc2514df4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R13e37608116d409a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7715.08</x:v>
+        <x:v>7641.86</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7602.5</x:v>
+        <x:v>7564.67</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>112.6</x:v>
+        <x:v>77.2</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>29644.5</x:v>
+        <x:v>29721.7</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>177.5</x:v>
+        <x:v>176.9</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7816.66</x:v>
+        <x:v>7766.35</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7723.82</x:v>
+        <x:v>7696.55</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>92.8</x:v>
+        <x:v>69.8</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>29635.6</x:v>
+        <x:v>29705.4</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>177.5</x:v>
+        <x:v>176.8</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3958.12</x:v>
+        <x:v>3949.25</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3933.47</x:v>
+        <x:v>3927.35</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>24.7</x:v>
+        <x:v>21.9</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8118.3</x:v>
+        <x:v>8140.2</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>48.6</x:v>
+        <x:v>48.5</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4574.2</x:v>
+        <x:v>4565.8</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4535.6</x:v>
+        <x:v>4517.6</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>38.6</x:v>
+        <x:v>48.2</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12252.8</x:v>
+        <x:v>12301</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>73.4</x:v>
+        <x:v>73.2</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2909.8</x:v>
+        <x:v>2908.4</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2887.6</x:v>
+        <x:v>2879.2</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>22.2</x:v>
+        <x:v>29.2</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6797</x:v>
+        <x:v>6826.2</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.7</x:v>
+        <x:v>40.6</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -9086,7 +9086,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" s="22" t="str">
-        <x:v>9月7日-9月9日</x:v>
+        <x:v>9月7日-9月10日</x:v>
       </x:c>
       <x:c r="C39" s="23" t="n">
         <x:v>7551.02</x:v>
@@ -9098,15 +9098,15 @@
         <x:v>7541.14</x:v>
       </x:c>
       <x:c r="F39" s="23" t="n">
-        <x:v>7648.8</x:v>
+        <x:v>7587.75</x:v>
       </x:c>
       <x:c r="G39" s="23" t="n">
         <x:f>ROUND(F39-F38,1)</x:f>
-        <x:v>140.7</x:v>
+        <x:v>79.7</x:v>
       </x:c>
       <x:c r="H39" s="24" t="n">
         <x:f>IFERROR(F39/F38-1,"")</x:f>
-        <x:v>0.018741117914143235</x:v>
+        <x:v>0.010609888799947731</x:v>
       </x:c>
       <x:c r="I39" s="26" t="n">
         <x:f>ROUND(D39-E39,1)</x:f>
@@ -9116,7 +9116,7 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K39" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -10498,7 +10498,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="22" t="str">
-        <x:v>9月7日-9月9日</x:v>
+        <x:v>9月7日-9月10日</x:v>
       </x:c>
       <x:c r="C79" s="23" t="n">
         <x:v>7687.47</x:v>
@@ -10510,15 +10510,15 @@
         <x:v>7672.99</x:v>
       </x:c>
       <x:c r="F79" s="23" t="n">
-        <x:v>7768.11</x:v>
+        <x:v>7717.8</x:v>
       </x:c>
       <x:c r="G79" s="23" t="n">
         <x:f>ROUND(F79-F78,1)</x:f>
-        <x:v>115.4</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="H79" s="24" t="n">
         <x:f>IFERROR(F79/F78-1,"")</x:f>
-        <x:v>0.01508227825771069</x:v>
+        <x:v>0.00850811936717677</x:v>
       </x:c>
       <x:c r="I79" s="23" t="n">
         <x:f>ROUND(D79-E79,1)</x:f>
@@ -10528,7 +10528,7 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K79" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -11910,7 +11910,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B119" s="22" t="str">
-        <x:v>9月7日-9月9日</x:v>
+        <x:v>9月7日-9月10日</x:v>
       </x:c>
       <x:c r="C119" s="23" t="n">
         <x:v>3942.51</x:v>
@@ -11922,15 +11922,15 @@
         <x:v>3916.49</x:v>
       </x:c>
       <x:c r="F119" s="23" t="n">
-        <x:v>3951.51</x:v>
+        <x:v>3934.4</x:v>
       </x:c>
       <x:c r="G119" s="23" t="n">
         <x:f>ROUND(F119-F118,1)</x:f>
-        <x:v>21.4</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="H119" s="24" t="n">
         <x:f>IFERROR(F119/F118-1,"")</x:f>
-        <x:v>0.005442581905896082</x:v>
+        <x:v>0.001089025271493016</x:v>
       </x:c>
       <x:c r="I119" s="23" t="n">
         <x:f>ROUND(D119-E119,1)</x:f>
@@ -11940,7 +11940,7 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K119" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -16146,7 +16146,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>9月7日-9月9日</x:v>
+        <x:v>9月7日-9月10日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
         <x:v>4562</x:v>
@@ -16155,28 +16155,28 @@
         <x:v>4584</x:v>
       </x:c>
       <x:c r="E239" s="23" t="n">
-        <x:v>4532.8</x:v>
+        <x:v>4517.6</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>4560</x:v>
+        <x:v>4542.2</x:v>
       </x:c>
       <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>22.6</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>0.00498082602371408</x:v>
+        <x:v>0.0010578745537093148</x:v>
       </x:c>
       <x:c r="I239" s="23" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J239" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K239" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -16194,7 +16194,7 @@
       <x:c r="H240" s="30"/>
       <x:c r="I240" s="32" t="n">
         <x:f>ROUND(SUM(I205:I239),1)</x:f>
-        <x:v>5524</x:v>
+        <x:v>5539.2</x:v>
       </x:c>
       <x:c r="J240" s="30"/>
       <x:c r="K240" s="30"/>
@@ -16212,7 +16212,7 @@
       <x:c r="H241" s="30"/>
       <x:c r="I241" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I205:I239),0),1)</x:f>
-        <x:v>157.8</x:v>
+        <x:v>158.3</x:v>
       </x:c>
       <x:c r="J241" s="30"/>
       <x:c r="K241" s="30"/>
@@ -17558,7 +17558,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>9月7日-9月9日</x:v>
+        <x:v>9月7日-9月10日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
         <x:v>2923.2</x:v>
@@ -17567,28 +17567,28 @@
         <x:v>2931.4</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>2887.6</x:v>
+        <x:v>2879.2</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>2901.2</x:v>
+        <x:v>2897</x:v>
       </x:c>
       <x:c r="G279" s="23" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>-14.6</x:v>
+        <x:v>-18.8</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>-0.0050072021400645594</x:v>
+        <x:v>-0.0064476301529597935</x:v>
       </x:c>
       <x:c r="I279" s="23" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>52.2</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -17606,7 +17606,7 @@
       <x:c r="H280" s="30"/>
       <x:c r="I280" s="32" t="n">
         <x:f>ROUND(SUM(I245:I279),1)</x:f>
-        <x:v>3164.8</x:v>
+        <x:v>3173.2</x:v>
       </x:c>
       <x:c r="J280" s="30"/>
       <x:c r="K280" s="30"/>
@@ -17624,7 +17624,7 @@
       <x:c r="H281" s="30"/>
       <x:c r="I281" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I245:I279),0),1)</x:f>
-        <x:v>90.4</x:v>
+        <x:v>90.7</x:v>
       </x:c>
       <x:c r="J281" s="30"/>
       <x:c r="K281" s="30"/>
@@ -25846,30 +25846,48 @@
       </x:c>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B212" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C212" s="30"/>
-      <x:c r="D212" s="30"/>
-      <x:c r="E212" s="30"/>
-      <x:c r="F212" s="30"/>
-      <x:c r="G212" s="30"/>
-      <x:c r="H212" s="30"/>
-      <x:c r="I212" s="30"/>
-      <x:c r="J212" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J211),1)</x:f>
-        <x:v>913.7</x:v>
-      </x:c>
-      <x:c r="K212" s="30"/>
+      <x:c r="A212" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B212" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C212" s="22" t="str">
+        <x:v>9月10日</x:v>
+      </x:c>
+      <x:c r="D212" s="23" t="n">
+        <x:v>7611.52</x:v>
+      </x:c>
+      <x:c r="E212" s="23" t="n">
+        <x:v>7641.86</x:v>
+      </x:c>
+      <x:c r="F212" s="23" t="n">
+        <x:v>7564.67</x:v>
+      </x:c>
+      <x:c r="G212" s="23" t="n">
+        <x:v>7587.75</x:v>
+      </x:c>
+      <x:c r="H212" s="23" t="n">
+        <x:v>-61.1</x:v>
+      </x:c>
+      <x:c r="I212" s="24" t="n">
+        <x:v>-0.007981644179479108</x:v>
+      </x:c>
+      <x:c r="J212" s="23" t="n">
+        <x:f>ROUND(E212-F212,1)</x:f>
+        <x:v>77.2</x:v>
+      </x:c>
+      <x:c r="K212" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B213" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B213" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C213" s="30"/>
       <x:c r="D213" s="30"/>
       <x:c r="E213" s="30"/>
@@ -25877,11 +25895,29 @@
       <x:c r="G213" s="30"/>
       <x:c r="H213" s="30"/>
       <x:c r="I213" s="30"/>
-      <x:c r="J213" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
-        <x:v>130.5</x:v>
+      <x:c r="J213" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J212),1)</x:f>
+        <x:v>990.9</x:v>
       </x:c>
       <x:c r="K213" s="30"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B214" s="30"/>
+      <x:c r="C214" s="30"/>
+      <x:c r="D214" s="30"/>
+      <x:c r="E214" s="30"/>
+      <x:c r="F214" s="30"/>
+      <x:c r="G214" s="30"/>
+      <x:c r="H214" s="30"/>
+      <x:c r="I214" s="30"/>
+      <x:c r="J214" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
+        <x:v>123.9</x:v>
+      </x:c>
+      <x:c r="K214" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32689,30 +32725,48 @@
       </x:c>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B212" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C212" s="30"/>
-      <x:c r="D212" s="30"/>
-      <x:c r="E212" s="30"/>
-      <x:c r="F212" s="30"/>
-      <x:c r="G212" s="30"/>
-      <x:c r="H212" s="30"/>
-      <x:c r="I212" s="30"/>
-      <x:c r="J212" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J211),1)</x:f>
-        <x:v>851.9</x:v>
-      </x:c>
-      <x:c r="K212" s="30"/>
+      <x:c r="A212" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B212" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C212" s="22" t="str">
+        <x:v>9月10日</x:v>
+      </x:c>
+      <x:c r="D212" s="23" t="n">
+        <x:v>7731.63</x:v>
+      </x:c>
+      <x:c r="E212" s="23" t="n">
+        <x:v>7766.35</x:v>
+      </x:c>
+      <x:c r="F212" s="23" t="n">
+        <x:v>7696.55</x:v>
+      </x:c>
+      <x:c r="G212" s="23" t="n">
+        <x:v>7717.8</x:v>
+      </x:c>
+      <x:c r="H212" s="23" t="n">
+        <x:v>-50.3</x:v>
+      </x:c>
+      <x:c r="I212" s="24" t="n">
+        <x:v>-0.006476478834619992</x:v>
+      </x:c>
+      <x:c r="J212" s="23" t="n">
+        <x:f>ROUND(E212-F212,1)</x:f>
+        <x:v>69.8</x:v>
+      </x:c>
+      <x:c r="K212" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B213" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B213" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C213" s="30"/>
       <x:c r="D213" s="30"/>
       <x:c r="E213" s="30"/>
@@ -32720,11 +32774,29 @@
       <x:c r="G213" s="30"/>
       <x:c r="H213" s="30"/>
       <x:c r="I213" s="30"/>
-      <x:c r="J213" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
-        <x:v>121.7</x:v>
+      <x:c r="J213" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J212),1)</x:f>
+        <x:v>921.7</x:v>
       </x:c>
       <x:c r="K213" s="30"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B214" s="30"/>
+      <x:c r="C214" s="30"/>
+      <x:c r="D214" s="30"/>
+      <x:c r="E214" s="30"/>
+      <x:c r="F214" s="30"/>
+      <x:c r="G214" s="30"/>
+      <x:c r="H214" s="30"/>
+      <x:c r="I214" s="30"/>
+      <x:c r="J214" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
+        <x:v>115.2</x:v>
+      </x:c>
+      <x:c r="K214" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -39532,30 +39604,48 @@
       </x:c>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B212" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C212" s="30"/>
-      <x:c r="D212" s="30"/>
-      <x:c r="E212" s="30"/>
-      <x:c r="F212" s="30"/>
-      <x:c r="G212" s="30"/>
-      <x:c r="H212" s="30"/>
-      <x:c r="I212" s="30"/>
-      <x:c r="J212" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J211),1)</x:f>
-        <x:v>237.2</x:v>
-      </x:c>
-      <x:c r="K212" s="30"/>
+      <x:c r="A212" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B212" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C212" s="22" t="str">
+        <x:v>9月10日</x:v>
+      </x:c>
+      <x:c r="D212" s="23" t="n">
+        <x:v>3939.09</x:v>
+      </x:c>
+      <x:c r="E212" s="23" t="n">
+        <x:v>3949.25</x:v>
+      </x:c>
+      <x:c r="F212" s="23" t="n">
+        <x:v>3927.35</x:v>
+      </x:c>
+      <x:c r="G212" s="23" t="n">
+        <x:v>3934.4</x:v>
+      </x:c>
+      <x:c r="H212" s="23" t="n">
+        <x:v>-17.1</x:v>
+      </x:c>
+      <x:c r="I212" s="24" t="n">
+        <x:v>-0.004329990307502696</x:v>
+      </x:c>
+      <x:c r="J212" s="23" t="n">
+        <x:f>ROUND(E212-F212,1)</x:f>
+        <x:v>21.9</x:v>
+      </x:c>
+      <x:c r="K212" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B213" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B213" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C213" s="30"/>
       <x:c r="D213" s="30"/>
       <x:c r="E213" s="30"/>
@@ -39563,11 +39653,29 @@
       <x:c r="G213" s="30"/>
       <x:c r="H213" s="30"/>
       <x:c r="I213" s="30"/>
-      <x:c r="J213" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
-        <x:v>33.9</x:v>
+      <x:c r="J213" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J212),1)</x:f>
+        <x:v>259.1</x:v>
       </x:c>
       <x:c r="K213" s="30"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B214" s="30"/>
+      <x:c r="C214" s="30"/>
+      <x:c r="D214" s="30"/>
+      <x:c r="E214" s="30"/>
+      <x:c r="F214" s="30"/>
+      <x:c r="G214" s="30"/>
+      <x:c r="H214" s="30"/>
+      <x:c r="I214" s="30"/>
+      <x:c r="J214" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
+        <x:v>32.4</x:v>
+      </x:c>
+      <x:c r="K214" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -60061,30 +60169,48 @@
       </x:c>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B212" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C212" s="30"/>
-      <x:c r="D212" s="30"/>
-      <x:c r="E212" s="30"/>
-      <x:c r="F212" s="30"/>
-      <x:c r="G212" s="30"/>
-      <x:c r="H212" s="30"/>
-      <x:c r="I212" s="30"/>
-      <x:c r="J212" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J211),1)</x:f>
-        <x:v>366.2</x:v>
-      </x:c>
-      <x:c r="K212" s="30"/>
+      <x:c r="A212" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B212" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C212" s="22" t="str">
+        <x:v>9月10日</x:v>
+      </x:c>
+      <x:c r="D212" s="23" t="n">
+        <x:v>4535.6</x:v>
+      </x:c>
+      <x:c r="E212" s="23" t="n">
+        <x:v>4565.8</x:v>
+      </x:c>
+      <x:c r="F212" s="23" t="n">
+        <x:v>4517.6</x:v>
+      </x:c>
+      <x:c r="G212" s="23" t="n">
+        <x:v>4542.2</x:v>
+      </x:c>
+      <x:c r="H212" s="23" t="n">
+        <x:v>-17.8</x:v>
+      </x:c>
+      <x:c r="I212" s="24" t="n">
+        <x:v>-0.003903508771929909</x:v>
+      </x:c>
+      <x:c r="J212" s="23" t="n">
+        <x:f>ROUND(E212-F212,1)</x:f>
+        <x:v>48.2</x:v>
+      </x:c>
+      <x:c r="K212" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B213" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B213" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C213" s="30"/>
       <x:c r="D213" s="30"/>
       <x:c r="E213" s="30"/>
@@ -60092,11 +60218,29 @@
       <x:c r="G213" s="30"/>
       <x:c r="H213" s="30"/>
       <x:c r="I213" s="30"/>
-      <x:c r="J213" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
-        <x:v>52.3</x:v>
+      <x:c r="J213" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J212),1)</x:f>
+        <x:v>414.4</x:v>
       </x:c>
       <x:c r="K213" s="30"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B214" s="30"/>
+      <x:c r="C214" s="30"/>
+      <x:c r="D214" s="30"/>
+      <x:c r="E214" s="30"/>
+      <x:c r="F214" s="30"/>
+      <x:c r="G214" s="30"/>
+      <x:c r="H214" s="30"/>
+      <x:c r="I214" s="30"/>
+      <x:c r="J214" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
+        <x:v>51.8</x:v>
+      </x:c>
+      <x:c r="K214" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -66904,30 +67048,48 @@
       </x:c>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B212" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C212" s="30"/>
-      <x:c r="D212" s="30"/>
-      <x:c r="E212" s="30"/>
-      <x:c r="F212" s="30"/>
-      <x:c r="G212" s="30"/>
-      <x:c r="H212" s="30"/>
-      <x:c r="I212" s="30"/>
-      <x:c r="J212" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J211),1)</x:f>
-        <x:v>220.4</x:v>
-      </x:c>
-      <x:c r="K212" s="30"/>
+      <x:c r="A212" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B212" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C212" s="22" t="str">
+        <x:v>9月10日</x:v>
+      </x:c>
+      <x:c r="D212" s="23" t="n">
+        <x:v>2892</x:v>
+      </x:c>
+      <x:c r="E212" s="23" t="n">
+        <x:v>2908.4</x:v>
+      </x:c>
+      <x:c r="F212" s="23" t="n">
+        <x:v>2879.2</x:v>
+      </x:c>
+      <x:c r="G212" s="23" t="n">
+        <x:v>2897</x:v>
+      </x:c>
+      <x:c r="H212" s="23" t="n">
+        <x:v>-4.2</x:v>
+      </x:c>
+      <x:c r="I212" s="24" t="n">
+        <x:v>-0.0014476768233833148</x:v>
+      </x:c>
+      <x:c r="J212" s="23" t="n">
+        <x:f>ROUND(E212-F212,1)</x:f>
+        <x:v>29.2</x:v>
+      </x:c>
+      <x:c r="K212" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B213" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B213" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C213" s="30"/>
       <x:c r="D213" s="30"/>
       <x:c r="E213" s="30"/>
@@ -66935,11 +67097,29 @@
       <x:c r="G213" s="30"/>
       <x:c r="H213" s="30"/>
       <x:c r="I213" s="30"/>
-      <x:c r="J213" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
-        <x:v>31.5</x:v>
+      <x:c r="J213" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J212),1)</x:f>
+        <x:v>249.6</x:v>
       </x:c>
       <x:c r="K213" s="30"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B214" s="30"/>
+      <x:c r="C214" s="30"/>
+      <x:c r="D214" s="30"/>
+      <x:c r="E214" s="30"/>
+      <x:c r="F214" s="30"/>
+      <x:c r="G214" s="30"/>
+      <x:c r="H214" s="30"/>
+      <x:c r="I214" s="30"/>
+      <x:c r="J214" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
+        <x:v>31.2</x:v>
+      </x:c>
+      <x:c r="K214" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rcc8dff2184b04c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Re6fd934221c54177"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R0994ff9a89ef4ff4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R17d2dbc586834072"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Raba888b2e2ec4388"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rf90da8fc6ad4405e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Radf12ab8170a4f4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rb11f368185084d84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R3b2f66bfc2514df4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R13e37608116d409a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rca56c6375406430d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R5f9f8b8dda604674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Re1cb21be87ea4f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rafc0f5859c404ae5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb0435c9e65464384"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rcbf09d6bb5da4aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R682e30ecb44d40aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R11d961b8b33e483a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rab245fdb39764627"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R33156d4bb56d4fa4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7705</x:v>
+        <x:v>7627.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7575</x:v>
+        <x:v>7534</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>130</x:v>
+        <x:v>93.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>31477</x:v>
+        <x:v>31570.8</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>188.5</x:v>
+        <x:v>187.9</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7804.8</x:v>
+        <x:v>7754.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7695.4</x:v>
+        <x:v>7664</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>109.4</x:v>
+        <x:v>90.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>32773</x:v>
+        <x:v>32863.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>196.2</x:v>
+        <x:v>195.6</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>142880</x:v>
+        <x:v>142500</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>139800</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>3080</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1395860</x:v>
+        <x:v>1399360</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8358.4</x:v>
+        <x:v>8329.5</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -7669,30 +7669,48 @@
       </x:c>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B212" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C212" s="30"/>
-      <x:c r="D212" s="30"/>
-      <x:c r="E212" s="30"/>
-      <x:c r="F212" s="30"/>
-      <x:c r="G212" s="30"/>
-      <x:c r="H212" s="30"/>
-      <x:c r="I212" s="30"/>
-      <x:c r="J212" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J211),1)</x:f>
-        <x:v>34100</x:v>
-      </x:c>
-      <x:c r="K212" s="30"/>
+      <x:c r="A212" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B212" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C212" s="22" t="str">
+        <x:v>9月10日</x:v>
+      </x:c>
+      <x:c r="D212" s="23" t="n">
+        <x:v>141220</x:v>
+      </x:c>
+      <x:c r="E212" s="23" t="n">
+        <x:v>142500</x:v>
+      </x:c>
+      <x:c r="F212" s="23" t="n">
+        <x:v>139000</x:v>
+      </x:c>
+      <x:c r="G212" s="23" t="n">
+        <x:v>140520</x:v>
+      </x:c>
+      <x:c r="H212" s="28" t="n">
+        <x:v>-740</x:v>
+      </x:c>
+      <x:c r="I212" s="24" t="n">
+        <x:v>-0.005238567181084508</x:v>
+      </x:c>
+      <x:c r="J212" s="23" t="n">
+        <x:f>ROUND(E212-F212,1)</x:f>
+        <x:v>3500</x:v>
+      </x:c>
+      <x:c r="K212" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B213" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B213" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C213" s="30"/>
       <x:c r="D213" s="30"/>
       <x:c r="E213" s="30"/>
@@ -7700,11 +7718,29 @@
       <x:c r="G213" s="30"/>
       <x:c r="H213" s="30"/>
       <x:c r="I213" s="30"/>
-      <x:c r="J213" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
-        <x:v>4871.4</x:v>
+      <x:c r="J213" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J212),1)</x:f>
+        <x:v>37600</x:v>
       </x:c>
       <x:c r="K213" s="30"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B214" s="30"/>
+      <x:c r="C214" s="30"/>
+      <x:c r="D214" s="30"/>
+      <x:c r="E214" s="30"/>
+      <x:c r="F214" s="30"/>
+      <x:c r="G214" s="30"/>
+      <x:c r="H214" s="30"/>
+      <x:c r="I214" s="30"/>
+      <x:c r="J214" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
+        <x:v>4700</x:v>
+      </x:c>
+      <x:c r="K214" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13322,7 +13358,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B159" s="22" t="str">
-        <x:v>9月7日-9月9日</x:v>
+        <x:v>9月7日-9月10日</x:v>
       </x:c>
       <x:c r="C159" s="23" t="n">
         <x:v>7527.2</x:v>
@@ -13334,15 +13370,15 @@
         <x:v>7512.6</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>7618.6</x:v>
-      </x:c>
-      <x:c r="G159" s="28" t="n">
+        <x:v>7574</x:v>
+      </x:c>
+      <x:c r="G159" s="23" t="n">
         <x:f>ROUND(F159-F158,1)</x:f>
-        <x:v>150.4</x:v>
+        <x:v>105.8</x:v>
       </x:c>
       <x:c r="H159" s="24" t="n">
         <x:f>IFERROR(F159/F158-1,"")</x:f>
-        <x:v>0.020138721512546587</x:v>
+        <x:v>0.014166733617203553</x:v>
       </x:c>
       <x:c r="I159" s="26" t="n">
         <x:f>ROUND(D159-E159,1)</x:f>
@@ -13352,7 +13388,7 @@
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K159" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -14734,7 +14770,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B199" s="22" t="str">
-        <x:v>9月7日-9月9日</x:v>
+        <x:v>9月7日-9月10日</x:v>
       </x:c>
       <x:c r="C199" s="23" t="n">
         <x:v>7665.6</x:v>
@@ -14746,15 +14782,15 @@
         <x:v>7651.2</x:v>
       </x:c>
       <x:c r="F199" s="23" t="n">
-        <x:v>7738.6</x:v>
+        <x:v>7705.8</x:v>
       </x:c>
       <x:c r="G199" s="23" t="n">
         <x:f>ROUND(F199-F198,1)</x:f>
-        <x:v>130.6</x:v>
+        <x:v>97.8</x:v>
       </x:c>
       <x:c r="H199" s="24" t="n">
         <x:f>IFERROR(F199/F198-1,"")</x:f>
-        <x:v>0.017166140904311344</x:v>
+        <x:v>0.012854889589905438</x:v>
       </x:c>
       <x:c r="I199" s="26" t="n">
         <x:f>ROUND(D199-E199,1)</x:f>
@@ -14764,7 +14800,7 @@
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K199" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -18970,7 +19006,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B319" s="22" t="str">
-        <x:v>9月7日-9月9日</x:v>
+        <x:v>9月7日-9月10日</x:v>
       </x:c>
       <x:c r="C319" s="23" t="n">
         <x:v>142120</x:v>
@@ -18979,28 +19015,28 @@
         <x:v>143200</x:v>
       </x:c>
       <x:c r="E319" s="23" t="n">
-        <x:v>139800</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="F319" s="23" t="n">
-        <x:v>141260</x:v>
+        <x:v>140520</x:v>
       </x:c>
       <x:c r="G319" s="28" t="n">
         <x:f>ROUND(F319-F318,1)</x:f>
-        <x:v>280</x:v>
+        <x:v>-460</x:v>
       </x:c>
       <x:c r="H319" s="24" t="n">
         <x:f>IFERROR(F319/F318-1,"")</x:f>
-        <x:v>0.0019860973187686426</x:v>
+        <x:v>-0.0032628741665484684</x:v>
       </x:c>
       <x:c r="I319" s="23" t="n">
         <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>3400</x:v>
+        <x:v>4200</x:v>
       </x:c>
       <x:c r="J319" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K319" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
@@ -19018,7 +19054,7 @@
       <x:c r="H320" s="30"/>
       <x:c r="I320" s="32" t="n">
         <x:f>ROUND(SUM(I285:I319),1)</x:f>
-        <x:v>712620</x:v>
+        <x:v>713420</x:v>
       </x:c>
       <x:c r="J320" s="30"/>
       <x:c r="K320" s="30"/>
@@ -19036,7 +19072,7 @@
       <x:c r="H321" s="30"/>
       <x:c r="I321" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I285:I319),0),1)</x:f>
-        <x:v>20360.6</x:v>
+        <x:v>20383.4</x:v>
       </x:c>
       <x:c r="J321" s="30"/>
       <x:c r="K321" s="30"/>
@@ -46483,30 +46519,48 @@
       </x:c>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B212" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C212" s="30"/>
-      <x:c r="D212" s="30"/>
-      <x:c r="E212" s="30"/>
-      <x:c r="F212" s="30"/>
-      <x:c r="G212" s="30"/>
-      <x:c r="H212" s="30"/>
-      <x:c r="I212" s="30"/>
-      <x:c r="J212" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J211),1)</x:f>
-        <x:v>1033.2</x:v>
-      </x:c>
-      <x:c r="K212" s="30"/>
+      <x:c r="A212" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B212" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C212" s="22" t="str">
+        <x:v>9月10日</x:v>
+      </x:c>
+      <x:c r="D212" s="23" t="n">
+        <x:v>7575</x:v>
+      </x:c>
+      <x:c r="E212" s="23" t="n">
+        <x:v>7627.8</x:v>
+      </x:c>
+      <x:c r="F212" s="23" t="n">
+        <x:v>7534</x:v>
+      </x:c>
+      <x:c r="G212" s="23" t="n">
+        <x:v>7574</x:v>
+      </x:c>
+      <x:c r="H212" s="23" t="n">
+        <x:v>-44.6</x:v>
+      </x:c>
+      <x:c r="I212" s="24" t="n">
+        <x:v>-0.005854093928018278</x:v>
+      </x:c>
+      <x:c r="J212" s="23" t="n">
+        <x:f>ROUND(E212-F212,1)</x:f>
+        <x:v>93.8</x:v>
+      </x:c>
+      <x:c r="K212" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B213" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B213" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C213" s="30"/>
       <x:c r="D213" s="30"/>
       <x:c r="E213" s="30"/>
@@ -46514,11 +46568,29 @@
       <x:c r="G213" s="30"/>
       <x:c r="H213" s="30"/>
       <x:c r="I213" s="30"/>
-      <x:c r="J213" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
-        <x:v>147.6</x:v>
+      <x:c r="J213" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J212),1)</x:f>
+        <x:v>1127</x:v>
       </x:c>
       <x:c r="K213" s="30"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B214" s="30"/>
+      <x:c r="C214" s="30"/>
+      <x:c r="D214" s="30"/>
+      <x:c r="E214" s="30"/>
+      <x:c r="F214" s="30"/>
+      <x:c r="G214" s="30"/>
+      <x:c r="H214" s="30"/>
+      <x:c r="I214" s="30"/>
+      <x:c r="J214" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
+        <x:v>140.9</x:v>
+      </x:c>
+      <x:c r="K214" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -53326,30 +53398,48 @@
       </x:c>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B212" s="30" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C212" s="30"/>
-      <x:c r="D212" s="30"/>
-      <x:c r="E212" s="30"/>
-      <x:c r="F212" s="30"/>
-      <x:c r="G212" s="30"/>
-      <x:c r="H212" s="30"/>
-      <x:c r="I212" s="30"/>
-      <x:c r="J212" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J211),1)</x:f>
-        <x:v>1028.8</x:v>
-      </x:c>
-      <x:c r="K212" s="30"/>
+      <x:c r="A212" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B212" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C212" s="22" t="str">
+        <x:v>9月10日</x:v>
+      </x:c>
+      <x:c r="D212" s="23" t="n">
+        <x:v>7696.8</x:v>
+      </x:c>
+      <x:c r="E212" s="23" t="n">
+        <x:v>7754.8</x:v>
+      </x:c>
+      <x:c r="F212" s="23" t="n">
+        <x:v>7664</x:v>
+      </x:c>
+      <x:c r="G212" s="23" t="n">
+        <x:v>7705.8</x:v>
+      </x:c>
+      <x:c r="H212" s="23" t="n">
+        <x:v>-32.8</x:v>
+      </x:c>
+      <x:c r="I212" s="24" t="n">
+        <x:v>-0.00423849275062671</x:v>
+      </x:c>
+      <x:c r="J212" s="23" t="n">
+        <x:f>ROUND(E212-F212,1)</x:f>
+        <x:v>90.8</x:v>
+      </x:c>
+      <x:c r="K212" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B213" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B213" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="C213" s="30"/>
       <x:c r="D213" s="30"/>
       <x:c r="E213" s="30"/>
@@ -53357,11 +53447,29 @@
       <x:c r="G213" s="30"/>
       <x:c r="H213" s="30"/>
       <x:c r="I213" s="30"/>
-      <x:c r="J213" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J211),0),1)</x:f>
-        <x:v>147</x:v>
+      <x:c r="J213" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J212),1)</x:f>
+        <x:v>1119.6</x:v>
       </x:c>
       <x:c r="K213" s="30"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B214" s="30"/>
+      <x:c r="C214" s="30"/>
+      <x:c r="D214" s="30"/>
+      <x:c r="E214" s="30"/>
+      <x:c r="F214" s="30"/>
+      <x:c r="G214" s="30"/>
+      <x:c r="H214" s="30"/>
+      <x:c r="I214" s="30"/>
+      <x:c r="J214" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="K214" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rca56c6375406430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R5f9f8b8dda604674"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Re1cb21be87ea4f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rafc0f5859c404ae5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb0435c9e65464384"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rcbf09d6bb5da4aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R682e30ecb44d40aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R11d961b8b33e483a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rab245fdb39764627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R33156d4bb56d4fa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R1b3539ecd6dc474b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Raa82bd3f0d0f49f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R81e67842137d4e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R9ac1112975a14d6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rfc9f430514174aa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc57e0a19a2f346c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd0b0f7d3ccde482f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R7b8da246b1d94e42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R480dcb8733234031"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R901f804833504a0e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7641.86</x:v>
+        <x:v>7506.24</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7564.67</x:v>
+        <x:v>7284.53</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>77.2</x:v>
+        <x:v>221.7</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>29721.7</x:v>
+        <x:v>29943.4</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>176.9</x:v>
+        <x:v>177.2</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7766.35</x:v>
+        <x:v>7638.63</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7696.55</x:v>
+        <x:v>7451.12</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>69.8</x:v>
+        <x:v>187.5</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>29705.4</x:v>
+        <x:v>29892.9</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>176.8</x:v>
+        <x:v>176.9</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,22 +577,22 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3949.25</x:v>
+        <x:v>3912.32</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3927.35</x:v>
+        <x:v>3852.03</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>21.9</x:v>
+        <x:v>60.3</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8140.2</x:v>
+        <x:v>8200.5</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>48.5</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7627.8</x:v>
+        <x:v>7488.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7534</x:v>
+        <x:v>7259.4</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>93.8</x:v>
+        <x:v>229.4</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>31570.8</x:v>
+        <x:v>31800.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>187.9</x:v>
+        <x:v>188.2</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7754.8</x:v>
+        <x:v>7626</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7664</x:v>
+        <x:v>7418.8</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>90.8</x:v>
+        <x:v>207.2</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>32863.8</x:v>
+        <x:v>33071</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>195.6</x:v>
+        <x:v>195.7</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,22 +664,22 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4565.8</x:v>
+        <x:v>4514</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4517.6</x:v>
+        <x:v>4451.6</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>48.2</x:v>
+        <x:v>62.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12301</x:v>
+        <x:v>12363.4</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
         <x:v>73.2</x:v>
@@ -693,22 +693,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2908.4</x:v>
+        <x:v>2876.6</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2879.2</x:v>
+        <x:v>2836.8</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>29.2</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6826.2</x:v>
+        <x:v>6866</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>40.6</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>142500</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>139000</x:v>
+        <x:v>131900</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>3500</x:v>
+        <x:v>3600</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1399360</x:v>
+        <x:v>1402960</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8329.5</x:v>
+        <x:v>8301.5</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -7705,30 +7705,48 @@
       </x:c>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B213" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C213" s="30"/>
-      <x:c r="D213" s="30"/>
-      <x:c r="E213" s="30"/>
-      <x:c r="F213" s="30"/>
-      <x:c r="G213" s="30"/>
-      <x:c r="H213" s="30"/>
-      <x:c r="I213" s="30"/>
-      <x:c r="J213" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J212),1)</x:f>
-        <x:v>37600</x:v>
-      </x:c>
-      <x:c r="K213" s="30"/>
+      <x:c r="A213" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B213" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C213" s="22" t="str">
+        <x:v>9月11日</x:v>
+      </x:c>
+      <x:c r="D213" s="23" t="n">
+        <x:v>134480</x:v>
+      </x:c>
+      <x:c r="E213" s="23" t="n">
+        <x:v>135500</x:v>
+      </x:c>
+      <x:c r="F213" s="23" t="n">
+        <x:v>131900</x:v>
+      </x:c>
+      <x:c r="G213" s="23" t="n">
+        <x:v>135500</x:v>
+      </x:c>
+      <x:c r="H213" s="28" t="n">
+        <x:v>-5020</x:v>
+      </x:c>
+      <x:c r="I213" s="24" t="n">
+        <x:v>-0.035724452035297505</x:v>
+      </x:c>
+      <x:c r="J213" s="23" t="n">
+        <x:f>ROUND(E213-F213,1)</x:f>
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="K213" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B214" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B214" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C214" s="30"/>
       <x:c r="D214" s="30"/>
       <x:c r="E214" s="30"/>
@@ -7736,11 +7754,29 @@
       <x:c r="G214" s="30"/>
       <x:c r="H214" s="30"/>
       <x:c r="I214" s="30"/>
-      <x:c r="J214" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
-        <x:v>4700</x:v>
+      <x:c r="J214" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J213),1)</x:f>
+        <x:v>41200</x:v>
       </x:c>
       <x:c r="K214" s="30"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B215" s="30"/>
+      <x:c r="C215" s="30"/>
+      <x:c r="D215" s="30"/>
+      <x:c r="E215" s="30"/>
+      <x:c r="F215" s="30"/>
+      <x:c r="G215" s="30"/>
+      <x:c r="H215" s="30"/>
+      <x:c r="I215" s="30"/>
+      <x:c r="J215" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
+        <x:v>4577.8</x:v>
+      </x:c>
+      <x:c r="K215" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9122,7 +9158,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" s="22" t="str">
-        <x:v>9月7日-9月10日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C39" s="23" t="n">
         <x:v>7551.02</x:v>
@@ -9131,28 +9167,28 @@
         <x:v>7724.94</x:v>
       </x:c>
       <x:c r="E39" s="23" t="n">
-        <x:v>7541.14</x:v>
+        <x:v>7284.53</x:v>
       </x:c>
       <x:c r="F39" s="23" t="n">
-        <x:v>7587.75</x:v>
+        <x:v>7427.24</x:v>
       </x:c>
       <x:c r="G39" s="23" t="n">
         <x:f>ROUND(F39-F38,1)</x:f>
-        <x:v>79.7</x:v>
+        <x:v>-80.9</x:v>
       </x:c>
       <x:c r="H39" s="24" t="n">
         <x:f>IFERROR(F39/F38-1,"")</x:f>
-        <x:v>0.010609888799947731</x:v>
+        <x:v>-0.010768384502583217</x:v>
       </x:c>
       <x:c r="I39" s="26" t="n">
         <x:f>ROUND(D39-E39,1)</x:f>
-        <x:v>183.8</x:v>
+        <x:v>440.4</x:v>
       </x:c>
       <x:c r="J39" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K39" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -9170,7 +9206,7 @@
       <x:c r="H40" s="30"/>
       <x:c r="I40" s="32" t="n">
         <x:f>ROUND(SUM(I5:I39),1)</x:f>
-        <x:v>14440</x:v>
+        <x:v>14696.6</x:v>
       </x:c>
       <x:c r="J40" s="30"/>
       <x:c r="K40" s="30"/>
@@ -9188,7 +9224,7 @@
       <x:c r="H41" s="30"/>
       <x:c r="I41" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I39),0),1)</x:f>
-        <x:v>412.6</x:v>
+        <x:v>419.9</x:v>
       </x:c>
       <x:c r="J41" s="30"/>
       <x:c r="K41" s="30"/>
@@ -10534,7 +10570,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="22" t="str">
-        <x:v>9月7日-9月10日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C79" s="23" t="n">
         <x:v>7687.47</x:v>
@@ -10543,28 +10579,28 @@
         <x:v>7830.16</x:v>
       </x:c>
       <x:c r="E79" s="23" t="n">
-        <x:v>7672.99</x:v>
+        <x:v>7451.12</x:v>
       </x:c>
       <x:c r="F79" s="23" t="n">
-        <x:v>7717.8</x:v>
+        <x:v>7580.54</x:v>
       </x:c>
       <x:c r="G79" s="23" t="n">
         <x:f>ROUND(F79-F78,1)</x:f>
-        <x:v>65.1</x:v>
+        <x:v>-72.1</x:v>
       </x:c>
       <x:c r="H79" s="24" t="n">
         <x:f>IFERROR(F79/F78-1,"")</x:f>
-        <x:v>0.00850811936717677</x:v>
-      </x:c>
-      <x:c r="I79" s="23" t="n">
+        <x:v>-0.009428057323633832</x:v>
+      </x:c>
+      <x:c r="I79" s="26" t="n">
         <x:f>ROUND(D79-E79,1)</x:f>
-        <x:v>157.2</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="J79" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K79" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -10582,7 +10618,7 @@
       <x:c r="H80" s="30"/>
       <x:c r="I80" s="32" t="n">
         <x:f>ROUND(SUM(I45:I79),1)</x:f>
-        <x:v>14496.2</x:v>
+        <x:v>14718</x:v>
       </x:c>
       <x:c r="J80" s="30"/>
       <x:c r="K80" s="30"/>
@@ -10600,7 +10636,7 @@
       <x:c r="H81" s="30"/>
       <x:c r="I81" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I45:I79),0),1)</x:f>
-        <x:v>414.2</x:v>
+        <x:v>420.5</x:v>
       </x:c>
       <x:c r="J81" s="30"/>
       <x:c r="K81" s="30"/>
@@ -11946,7 +11982,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B119" s="22" t="str">
-        <x:v>9月7日-9月10日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C119" s="23" t="n">
         <x:v>3942.51</x:v>
@@ -11955,28 +11991,28 @@
         <x:v>3958.12</x:v>
       </x:c>
       <x:c r="E119" s="23" t="n">
-        <x:v>3916.49</x:v>
+        <x:v>3852.03</x:v>
       </x:c>
       <x:c r="F119" s="23" t="n">
-        <x:v>3934.4</x:v>
+        <x:v>3888.11</x:v>
       </x:c>
       <x:c r="G119" s="23" t="n">
         <x:f>ROUND(F119-F118,1)</x:f>
-        <x:v>4.3</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="H119" s="24" t="n">
         <x:f>IFERROR(F119/F118-1,"")</x:f>
-        <x:v>0.001089025271493016</x:v>
-      </x:c>
-      <x:c r="I119" s="23" t="n">
+        <x:v>-0.010689241040986008</x:v>
+      </x:c>
+      <x:c r="I119" s="26" t="n">
         <x:f>ROUND(D119-E119,1)</x:f>
-        <x:v>41.6</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="J119" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K119" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -11994,7 +12030,7 @@
       <x:c r="H120" s="30"/>
       <x:c r="I120" s="32" t="n">
         <x:f>ROUND(SUM(I85:I119),1)</x:f>
-        <x:v>3799.6</x:v>
+        <x:v>3864.1</x:v>
       </x:c>
       <x:c r="J120" s="30"/>
       <x:c r="K120" s="30"/>
@@ -12012,7 +12048,7 @@
       <x:c r="H121" s="30"/>
       <x:c r="I121" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I85:I119),0),1)</x:f>
-        <x:v>108.6</x:v>
+        <x:v>110.4</x:v>
       </x:c>
       <x:c r="J121" s="30"/>
       <x:c r="K121" s="30"/>
@@ -13358,7 +13394,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B159" s="22" t="str">
-        <x:v>9月7日-9月10日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C159" s="23" t="n">
         <x:v>7527.2</x:v>
@@ -13367,28 +13403,28 @@
         <x:v>7714.6</x:v>
       </x:c>
       <x:c r="E159" s="23" t="n">
-        <x:v>7512.6</x:v>
+        <x:v>7259.4</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>7574</x:v>
+        <x:v>7415.2</x:v>
       </x:c>
       <x:c r="G159" s="23" t="n">
         <x:f>ROUND(F159-F158,1)</x:f>
-        <x:v>105.8</x:v>
+        <x:v>-53</x:v>
       </x:c>
       <x:c r="H159" s="24" t="n">
         <x:f>IFERROR(F159/F158-1,"")</x:f>
-        <x:v>0.014166733617203553</x:v>
+        <x:v>-0.007096756915990432</x:v>
       </x:c>
       <x:c r="I159" s="26" t="n">
         <x:f>ROUND(D159-E159,1)</x:f>
-        <x:v>202</x:v>
+        <x:v>455.2</x:v>
       </x:c>
       <x:c r="J159" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K159" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -13406,7 +13442,7 @@
       <x:c r="H160" s="30"/>
       <x:c r="I160" s="32" t="n">
         <x:f>ROUND(SUM(I125:I159),1)</x:f>
-        <x:v>15030.6</x:v>
+        <x:v>15283.8</x:v>
       </x:c>
       <x:c r="J160" s="30"/>
       <x:c r="K160" s="30"/>
@@ -13424,7 +13460,7 @@
       <x:c r="H161" s="30"/>
       <x:c r="I161" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I125:I159),0),1)</x:f>
-        <x:v>429.4</x:v>
+        <x:v>436.7</x:v>
       </x:c>
       <x:c r="J161" s="30"/>
       <x:c r="K161" s="30"/>
@@ -14770,7 +14806,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B199" s="22" t="str">
-        <x:v>9月7日-9月10日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C199" s="23" t="n">
         <x:v>7665.6</x:v>
@@ -14779,28 +14815,28 @@
         <x:v>7817.2</x:v>
       </x:c>
       <x:c r="E199" s="23" t="n">
-        <x:v>7651.2</x:v>
+        <x:v>7418.8</x:v>
       </x:c>
       <x:c r="F199" s="23" t="n">
-        <x:v>7705.8</x:v>
+        <x:v>7569</x:v>
       </x:c>
       <x:c r="G199" s="23" t="n">
         <x:f>ROUND(F199-F198,1)</x:f>
-        <x:v>97.8</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="H199" s="24" t="n">
         <x:f>IFERROR(F199/F198-1,"")</x:f>
-        <x:v>0.012854889589905438</x:v>
+        <x:v>-0.005126182965299653</x:v>
       </x:c>
       <x:c r="I199" s="26" t="n">
         <x:f>ROUND(D199-E199,1)</x:f>
-        <x:v>166</x:v>
+        <x:v>398.4</x:v>
       </x:c>
       <x:c r="J199" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K199" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -14818,7 +14854,7 @@
       <x:c r="H200" s="30"/>
       <x:c r="I200" s="32" t="n">
         <x:f>ROUND(SUM(I165:I199),1)</x:f>
-        <x:v>15593</x:v>
+        <x:v>15825.4</x:v>
       </x:c>
       <x:c r="J200" s="30"/>
       <x:c r="K200" s="30"/>
@@ -14836,7 +14872,7 @@
       <x:c r="H201" s="30"/>
       <x:c r="I201" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I165:I199),0),1)</x:f>
-        <x:v>445.5</x:v>
+        <x:v>452.2</x:v>
       </x:c>
       <x:c r="J201" s="30"/>
       <x:c r="K201" s="30"/>
@@ -16182,7 +16218,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>9月7日-9月10日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
         <x:v>4562</x:v>
@@ -16191,28 +16227,28 @@
         <x:v>4584</x:v>
       </x:c>
       <x:c r="E239" s="23" t="n">
-        <x:v>4517.6</x:v>
+        <x:v>4451.6</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>4542.2</x:v>
+        <x:v>4503.4</x:v>
       </x:c>
       <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>4.8</x:v>
+        <x:v>-34</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>0.0010578745537093148</x:v>
-      </x:c>
-      <x:c r="I239" s="23" t="n">
+        <x:v>-0.007493278088773314</x:v>
+      </x:c>
+      <x:c r="I239" s="26" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
-        <x:v>66.4</x:v>
+        <x:v>132.4</x:v>
       </x:c>
       <x:c r="J239" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K239" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -16230,7 +16266,7 @@
       <x:c r="H240" s="30"/>
       <x:c r="I240" s="32" t="n">
         <x:f>ROUND(SUM(I205:I239),1)</x:f>
-        <x:v>5539.2</x:v>
+        <x:v>5605.2</x:v>
       </x:c>
       <x:c r="J240" s="30"/>
       <x:c r="K240" s="30"/>
@@ -16248,7 +16284,7 @@
       <x:c r="H241" s="30"/>
       <x:c r="I241" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I205:I239),0),1)</x:f>
-        <x:v>158.3</x:v>
+        <x:v>160.1</x:v>
       </x:c>
       <x:c r="J241" s="30"/>
       <x:c r="K241" s="30"/>
@@ -17594,7 +17630,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>9月7日-9月10日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
         <x:v>2923.2</x:v>
@@ -17603,28 +17639,28 @@
         <x:v>2931.4</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>2879.2</x:v>
+        <x:v>2836.8</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>2897</x:v>
+        <x:v>2867</x:v>
       </x:c>
       <x:c r="G279" s="23" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>-18.8</x:v>
+        <x:v>-48.8</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>-0.0064476301529597935</x:v>
-      </x:c>
-      <x:c r="I279" s="23" t="n">
+        <x:v>-0.01673640167364021</x:v>
+      </x:c>
+      <x:c r="I279" s="26" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>52.2</x:v>
+        <x:v>94.6</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -17642,7 +17678,7 @@
       <x:c r="H280" s="30"/>
       <x:c r="I280" s="32" t="n">
         <x:f>ROUND(SUM(I245:I279),1)</x:f>
-        <x:v>3173.2</x:v>
+        <x:v>3215.6</x:v>
       </x:c>
       <x:c r="J280" s="30"/>
       <x:c r="K280" s="30"/>
@@ -17660,7 +17696,7 @@
       <x:c r="H281" s="30"/>
       <x:c r="I281" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I245:I279),0),1)</x:f>
-        <x:v>90.7</x:v>
+        <x:v>91.9</x:v>
       </x:c>
       <x:c r="J281" s="30"/>
       <x:c r="K281" s="30"/>
@@ -19006,7 +19042,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B319" s="22" t="str">
-        <x:v>9月7日-9月10日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C319" s="23" t="n">
         <x:v>142120</x:v>
@@ -19015,28 +19051,28 @@
         <x:v>143200</x:v>
       </x:c>
       <x:c r="E319" s="23" t="n">
-        <x:v>139000</x:v>
+        <x:v>131900</x:v>
       </x:c>
       <x:c r="F319" s="23" t="n">
-        <x:v>140520</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="G319" s="28" t="n">
         <x:f>ROUND(F319-F318,1)</x:f>
-        <x:v>-460</x:v>
+        <x:v>-5480</x:v>
       </x:c>
       <x:c r="H319" s="24" t="n">
         <x:f>IFERROR(F319/F318-1,"")</x:f>
-        <x:v>-0.0032628741665484684</x:v>
-      </x:c>
-      <x:c r="I319" s="23" t="n">
+        <x:v>-0.038870761810185894</x:v>
+      </x:c>
+      <x:c r="I319" s="26" t="n">
         <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>4200</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="J319" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K319" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
@@ -19054,7 +19090,7 @@
       <x:c r="H320" s="30"/>
       <x:c r="I320" s="32" t="n">
         <x:f>ROUND(SUM(I285:I319),1)</x:f>
-        <x:v>713420</x:v>
+        <x:v>720520</x:v>
       </x:c>
       <x:c r="J320" s="30"/>
       <x:c r="K320" s="30"/>
@@ -19072,7 +19108,7 @@
       <x:c r="H321" s="30"/>
       <x:c r="I321" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I285:I319),0),1)</x:f>
-        <x:v>20383.4</x:v>
+        <x:v>20586.3</x:v>
       </x:c>
       <x:c r="J321" s="30"/>
       <x:c r="K321" s="30"/>
@@ -25918,30 +25954,48 @@
       </x:c>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B213" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C213" s="30"/>
-      <x:c r="D213" s="30"/>
-      <x:c r="E213" s="30"/>
-      <x:c r="F213" s="30"/>
-      <x:c r="G213" s="30"/>
-      <x:c r="H213" s="30"/>
-      <x:c r="I213" s="30"/>
-      <x:c r="J213" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J212),1)</x:f>
-        <x:v>990.9</x:v>
-      </x:c>
-      <x:c r="K213" s="30"/>
+      <x:c r="A213" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B213" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C213" s="22" t="str">
+        <x:v>9月11日</x:v>
+      </x:c>
+      <x:c r="D213" s="23" t="n">
+        <x:v>7504.66</x:v>
+      </x:c>
+      <x:c r="E213" s="23" t="n">
+        <x:v>7506.24</x:v>
+      </x:c>
+      <x:c r="F213" s="23" t="n">
+        <x:v>7284.53</x:v>
+      </x:c>
+      <x:c r="G213" s="23" t="n">
+        <x:v>7427.24</x:v>
+      </x:c>
+      <x:c r="H213" s="28" t="n">
+        <x:v>-160.5</x:v>
+      </x:c>
+      <x:c r="I213" s="24" t="n">
+        <x:v>-0.021153833481598605</x:v>
+      </x:c>
+      <x:c r="J213" s="26" t="n">
+        <x:f>ROUND(E213-F213,1)</x:f>
+        <x:v>221.7</x:v>
+      </x:c>
+      <x:c r="K213" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B214" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B214" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C214" s="30"/>
       <x:c r="D214" s="30"/>
       <x:c r="E214" s="30"/>
@@ -25949,11 +26003,29 @@
       <x:c r="G214" s="30"/>
       <x:c r="H214" s="30"/>
       <x:c r="I214" s="30"/>
-      <x:c r="J214" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
-        <x:v>123.9</x:v>
+      <x:c r="J214" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J213),1)</x:f>
+        <x:v>1212.6</x:v>
       </x:c>
       <x:c r="K214" s="30"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B215" s="30"/>
+      <x:c r="C215" s="30"/>
+      <x:c r="D215" s="30"/>
+      <x:c r="E215" s="30"/>
+      <x:c r="F215" s="30"/>
+      <x:c r="G215" s="30"/>
+      <x:c r="H215" s="30"/>
+      <x:c r="I215" s="30"/>
+      <x:c r="J215" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
+        <x:v>134.7</x:v>
+      </x:c>
+      <x:c r="K215" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -32797,30 +32869,48 @@
       </x:c>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B213" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C213" s="30"/>
-      <x:c r="D213" s="30"/>
-      <x:c r="E213" s="30"/>
-      <x:c r="F213" s="30"/>
-      <x:c r="G213" s="30"/>
-      <x:c r="H213" s="30"/>
-      <x:c r="I213" s="30"/>
-      <x:c r="J213" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J212),1)</x:f>
-        <x:v>921.7</x:v>
-      </x:c>
-      <x:c r="K213" s="30"/>
+      <x:c r="A213" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B213" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C213" s="22" t="str">
+        <x:v>9月11日</x:v>
+      </x:c>
+      <x:c r="D213" s="23" t="n">
+        <x:v>7638.63</x:v>
+      </x:c>
+      <x:c r="E213" s="23" t="n">
+        <x:v>7638.63</x:v>
+      </x:c>
+      <x:c r="F213" s="23" t="n">
+        <x:v>7451.12</x:v>
+      </x:c>
+      <x:c r="G213" s="23" t="n">
+        <x:v>7580.54</x:v>
+      </x:c>
+      <x:c r="H213" s="23" t="n">
+        <x:v>-137.3</x:v>
+      </x:c>
+      <x:c r="I213" s="24" t="n">
+        <x:v>-0.017784860970742944</x:v>
+      </x:c>
+      <x:c r="J213" s="26" t="n">
+        <x:f>ROUND(E213-F213,1)</x:f>
+        <x:v>187.5</x:v>
+      </x:c>
+      <x:c r="K213" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B214" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B214" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C214" s="30"/>
       <x:c r="D214" s="30"/>
       <x:c r="E214" s="30"/>
@@ -32828,11 +32918,29 @@
       <x:c r="G214" s="30"/>
       <x:c r="H214" s="30"/>
       <x:c r="I214" s="30"/>
-      <x:c r="J214" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
-        <x:v>115.2</x:v>
+      <x:c r="J214" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J213),1)</x:f>
+        <x:v>1109.2</x:v>
       </x:c>
       <x:c r="K214" s="30"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B215" s="30"/>
+      <x:c r="C215" s="30"/>
+      <x:c r="D215" s="30"/>
+      <x:c r="E215" s="30"/>
+      <x:c r="F215" s="30"/>
+      <x:c r="G215" s="30"/>
+      <x:c r="H215" s="30"/>
+      <x:c r="I215" s="30"/>
+      <x:c r="J215" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
+        <x:v>123.2</x:v>
+      </x:c>
+      <x:c r="K215" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -39676,30 +39784,48 @@
       </x:c>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B213" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C213" s="30"/>
-      <x:c r="D213" s="30"/>
-      <x:c r="E213" s="30"/>
-      <x:c r="F213" s="30"/>
-      <x:c r="G213" s="30"/>
-      <x:c r="H213" s="30"/>
-      <x:c r="I213" s="30"/>
-      <x:c r="J213" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J212),1)</x:f>
-        <x:v>259.1</x:v>
-      </x:c>
-      <x:c r="K213" s="30"/>
+      <x:c r="A213" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B213" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C213" s="22" t="str">
+        <x:v>9月11日</x:v>
+      </x:c>
+      <x:c r="D213" s="23" t="n">
+        <x:v>3910.92</x:v>
+      </x:c>
+      <x:c r="E213" s="23" t="n">
+        <x:v>3912.32</x:v>
+      </x:c>
+      <x:c r="F213" s="23" t="n">
+        <x:v>3852.03</x:v>
+      </x:c>
+      <x:c r="G213" s="23" t="n">
+        <x:v>3888.11</x:v>
+      </x:c>
+      <x:c r="H213" s="23" t="n">
+        <x:v>-46.3</x:v>
+      </x:c>
+      <x:c r="I213" s="24" t="n">
+        <x:v>-0.011765453436356266</x:v>
+      </x:c>
+      <x:c r="J213" s="26" t="n">
+        <x:f>ROUND(E213-F213,1)</x:f>
+        <x:v>60.3</x:v>
+      </x:c>
+      <x:c r="K213" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B214" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B214" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C214" s="30"/>
       <x:c r="D214" s="30"/>
       <x:c r="E214" s="30"/>
@@ -39707,11 +39833,29 @@
       <x:c r="G214" s="30"/>
       <x:c r="H214" s="30"/>
       <x:c r="I214" s="30"/>
-      <x:c r="J214" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
-        <x:v>32.4</x:v>
+      <x:c r="J214" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J213),1)</x:f>
+        <x:v>319.4</x:v>
       </x:c>
       <x:c r="K214" s="30"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B215" s="30"/>
+      <x:c r="C215" s="30"/>
+      <x:c r="D215" s="30"/>
+      <x:c r="E215" s="30"/>
+      <x:c r="F215" s="30"/>
+      <x:c r="G215" s="30"/>
+      <x:c r="H215" s="30"/>
+      <x:c r="I215" s="30"/>
+      <x:c r="J215" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
+        <x:v>35.5</x:v>
+      </x:c>
+      <x:c r="K215" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -46555,30 +46699,48 @@
       </x:c>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B213" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C213" s="30"/>
-      <x:c r="D213" s="30"/>
-      <x:c r="E213" s="30"/>
-      <x:c r="F213" s="30"/>
-      <x:c r="G213" s="30"/>
-      <x:c r="H213" s="30"/>
-      <x:c r="I213" s="30"/>
-      <x:c r="J213" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J212),1)</x:f>
-        <x:v>1127</x:v>
-      </x:c>
-      <x:c r="K213" s="30"/>
+      <x:c r="A213" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B213" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C213" s="22" t="str">
+        <x:v>9月11日</x:v>
+      </x:c>
+      <x:c r="D213" s="23" t="n">
+        <x:v>7480</x:v>
+      </x:c>
+      <x:c r="E213" s="23" t="n">
+        <x:v>7488.8</x:v>
+      </x:c>
+      <x:c r="F213" s="23" t="n">
+        <x:v>7259.4</x:v>
+      </x:c>
+      <x:c r="G213" s="23" t="n">
+        <x:v>7415.2</x:v>
+      </x:c>
+      <x:c r="H213" s="28" t="n">
+        <x:v>-158.8</x:v>
+      </x:c>
+      <x:c r="I213" s="24" t="n">
+        <x:v>-0.020966464219698944</x:v>
+      </x:c>
+      <x:c r="J213" s="26" t="n">
+        <x:f>ROUND(E213-F213,1)</x:f>
+        <x:v>229.4</x:v>
+      </x:c>
+      <x:c r="K213" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B214" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B214" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C214" s="30"/>
       <x:c r="D214" s="30"/>
       <x:c r="E214" s="30"/>
@@ -46586,11 +46748,29 @@
       <x:c r="G214" s="30"/>
       <x:c r="H214" s="30"/>
       <x:c r="I214" s="30"/>
-      <x:c r="J214" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
-        <x:v>140.9</x:v>
+      <x:c r="J214" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J213),1)</x:f>
+        <x:v>1356.4</x:v>
       </x:c>
       <x:c r="K214" s="30"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B215" s="30"/>
+      <x:c r="C215" s="30"/>
+      <x:c r="D215" s="30"/>
+      <x:c r="E215" s="30"/>
+      <x:c r="F215" s="30"/>
+      <x:c r="G215" s="30"/>
+      <x:c r="H215" s="30"/>
+      <x:c r="I215" s="30"/>
+      <x:c r="J215" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
+        <x:v>150.7</x:v>
+      </x:c>
+      <x:c r="K215" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -53434,30 +53614,48 @@
       </x:c>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B213" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C213" s="30"/>
-      <x:c r="D213" s="30"/>
-      <x:c r="E213" s="30"/>
-      <x:c r="F213" s="30"/>
-      <x:c r="G213" s="30"/>
-      <x:c r="H213" s="30"/>
-      <x:c r="I213" s="30"/>
-      <x:c r="J213" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J212),1)</x:f>
-        <x:v>1119.6</x:v>
-      </x:c>
-      <x:c r="K213" s="30"/>
+      <x:c r="A213" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B213" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C213" s="22" t="str">
+        <x:v>9月11日</x:v>
+      </x:c>
+      <x:c r="D213" s="23" t="n">
+        <x:v>7626</x:v>
+      </x:c>
+      <x:c r="E213" s="23" t="n">
+        <x:v>7626</x:v>
+      </x:c>
+      <x:c r="F213" s="23" t="n">
+        <x:v>7418.8</x:v>
+      </x:c>
+      <x:c r="G213" s="23" t="n">
+        <x:v>7569</x:v>
+      </x:c>
+      <x:c r="H213" s="23" t="n">
+        <x:v>-136.8</x:v>
+      </x:c>
+      <x:c r="I213" s="24" t="n">
+        <x:v>-0.017752861480962445</x:v>
+      </x:c>
+      <x:c r="J213" s="26" t="n">
+        <x:f>ROUND(E213-F213,1)</x:f>
+        <x:v>207.2</x:v>
+      </x:c>
+      <x:c r="K213" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B214" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B214" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C214" s="30"/>
       <x:c r="D214" s="30"/>
       <x:c r="E214" s="30"/>
@@ -53465,11 +53663,29 @@
       <x:c r="G214" s="30"/>
       <x:c r="H214" s="30"/>
       <x:c r="I214" s="30"/>
-      <x:c r="J214" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
-        <x:v>140</x:v>
+      <x:c r="J214" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J213),1)</x:f>
+        <x:v>1326.8</x:v>
       </x:c>
       <x:c r="K214" s="30"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B215" s="30"/>
+      <x:c r="C215" s="30"/>
+      <x:c r="D215" s="30"/>
+      <x:c r="E215" s="30"/>
+      <x:c r="F215" s="30"/>
+      <x:c r="G215" s="30"/>
+      <x:c r="H215" s="30"/>
+      <x:c r="I215" s="30"/>
+      <x:c r="J215" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
+        <x:v>147.4</x:v>
+      </x:c>
+      <x:c r="K215" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -60313,30 +60529,48 @@
       </x:c>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B213" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C213" s="30"/>
-      <x:c r="D213" s="30"/>
-      <x:c r="E213" s="30"/>
-      <x:c r="F213" s="30"/>
-      <x:c r="G213" s="30"/>
-      <x:c r="H213" s="30"/>
-      <x:c r="I213" s="30"/>
-      <x:c r="J213" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J212),1)</x:f>
-        <x:v>414.4</x:v>
-      </x:c>
-      <x:c r="K213" s="30"/>
+      <x:c r="A213" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B213" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C213" s="22" t="str">
+        <x:v>9月11日</x:v>
+      </x:c>
+      <x:c r="D213" s="23" t="n">
+        <x:v>4508.2</x:v>
+      </x:c>
+      <x:c r="E213" s="23" t="n">
+        <x:v>4514</x:v>
+      </x:c>
+      <x:c r="F213" s="23" t="n">
+        <x:v>4451.6</x:v>
+      </x:c>
+      <x:c r="G213" s="23" t="n">
+        <x:v>4503.4</x:v>
+      </x:c>
+      <x:c r="H213" s="23" t="n">
+        <x:v>-38.8</x:v>
+      </x:c>
+      <x:c r="I213" s="24" t="n">
+        <x:v>-0.00854211615516709</x:v>
+      </x:c>
+      <x:c r="J213" s="23" t="n">
+        <x:f>ROUND(E213-F213,1)</x:f>
+        <x:v>62.4</x:v>
+      </x:c>
+      <x:c r="K213" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B214" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B214" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C214" s="30"/>
       <x:c r="D214" s="30"/>
       <x:c r="E214" s="30"/>
@@ -60344,11 +60578,29 @@
       <x:c r="G214" s="30"/>
       <x:c r="H214" s="30"/>
       <x:c r="I214" s="30"/>
-      <x:c r="J214" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
-        <x:v>51.8</x:v>
+      <x:c r="J214" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J213),1)</x:f>
+        <x:v>476.8</x:v>
       </x:c>
       <x:c r="K214" s="30"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B215" s="30"/>
+      <x:c r="C215" s="30"/>
+      <x:c r="D215" s="30"/>
+      <x:c r="E215" s="30"/>
+      <x:c r="F215" s="30"/>
+      <x:c r="G215" s="30"/>
+      <x:c r="H215" s="30"/>
+      <x:c r="I215" s="30"/>
+      <x:c r="J215" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K215" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -67192,30 +67444,48 @@
       </x:c>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B213" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C213" s="30"/>
-      <x:c r="D213" s="30"/>
-      <x:c r="E213" s="30"/>
-      <x:c r="F213" s="30"/>
-      <x:c r="G213" s="30"/>
-      <x:c r="H213" s="30"/>
-      <x:c r="I213" s="30"/>
-      <x:c r="J213" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J212),1)</x:f>
-        <x:v>249.6</x:v>
-      </x:c>
-      <x:c r="K213" s="30"/>
+      <x:c r="A213" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B213" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C213" s="22" t="str">
+        <x:v>9月11日</x:v>
+      </x:c>
+      <x:c r="D213" s="23" t="n">
+        <x:v>2872.4</x:v>
+      </x:c>
+      <x:c r="E213" s="23" t="n">
+        <x:v>2876.6</x:v>
+      </x:c>
+      <x:c r="F213" s="23" t="n">
+        <x:v>2836.8</x:v>
+      </x:c>
+      <x:c r="G213" s="23" t="n">
+        <x:v>2867</x:v>
+      </x:c>
+      <x:c r="H213" s="23" t="n">
+        <x:v>-30</x:v>
+      </x:c>
+      <x:c r="I213" s="24" t="n">
+        <x:v>-0.010355540214014525</x:v>
+      </x:c>
+      <x:c r="J213" s="23" t="n">
+        <x:f>ROUND(E213-F213,1)</x:f>
+        <x:v>39.8</x:v>
+      </x:c>
+      <x:c r="K213" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B214" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B214" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C214" s="30"/>
       <x:c r="D214" s="30"/>
       <x:c r="E214" s="30"/>
@@ -67223,11 +67493,29 @@
       <x:c r="G214" s="30"/>
       <x:c r="H214" s="30"/>
       <x:c r="I214" s="30"/>
-      <x:c r="J214" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J212),0),1)</x:f>
-        <x:v>31.2</x:v>
+      <x:c r="J214" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J213),1)</x:f>
+        <x:v>289.4</x:v>
       </x:c>
       <x:c r="K214" s="30"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B215" s="30"/>
+      <x:c r="C215" s="30"/>
+      <x:c r="D215" s="30"/>
+      <x:c r="E215" s="30"/>
+      <x:c r="F215" s="30"/>
+      <x:c r="G215" s="30"/>
+      <x:c r="H215" s="30"/>
+      <x:c r="I215" s="30"/>
+      <x:c r="J215" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
+        <x:v>32.2</x:v>
+      </x:c>
+      <x:c r="K215" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R08fc055a8c2e482f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Ra41a74802cf4497a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rca683dbfbb7140a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R5be091d2cac7494a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rd2a57b3d77644d8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R38e0e0c7dbe44627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R82c78bd4b936429c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rf6e5e8c10b10415e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R7581e4a59a64438c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R7ca43715dab0429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R964c6c58398e4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R7c39e4f1785a4b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R516dcecd78374a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R40b01be2d42549bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R9d80209119ff434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R3c97c904d50c49f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R7f5d296a23f84767"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R4b9ef4b260e049dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R77f5534ac7b34e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Re41c7f51250b4d12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>2026-09-14</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7626</x:v>
+        <x:v>7595.2</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7418.8</x:v>
+        <x:v>7452.2</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>207.2</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>33071</x:v>
+        <x:v>33214</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>195.7</x:v>
+        <x:v>195.4</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -722,25 +722,23 @@
         <x:v>碳酸锂2609</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>2026-09-14</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>135500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>131900</x:v>
-      </x:c>
-      <x:c r="E11" s="12" t="n">
-        <x:v>3600</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="str"/>
       <x:c r="F11" s="9" t="n">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
         <x:v>1402960</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8301.5</x:v>
+        <x:v>8252.7</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -7741,30 +7739,48 @@
       </x:c>
     </x:row>
     <x:row r="214">
-      <x:c r="A214" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B214" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C214" s="30"/>
-      <x:c r="D214" s="30"/>
-      <x:c r="E214" s="30"/>
-      <x:c r="F214" s="30"/>
-      <x:c r="G214" s="30"/>
-      <x:c r="H214" s="30"/>
-      <x:c r="I214" s="30"/>
-      <x:c r="J214" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J213),1)</x:f>
-        <x:v>41200</x:v>
-      </x:c>
-      <x:c r="K214" s="30"/>
+      <x:c r="A214" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B214" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C214" s="22" t="str">
+        <x:v>9月14日</x:v>
+      </x:c>
+      <x:c r="D214" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E214" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F214" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G214" s="23" t="n">
+        <x:v>135500</x:v>
+      </x:c>
+      <x:c r="H214" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I214" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J214" s="23" t="n">
+        <x:f>ROUND(E214-F214,1)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K214" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B215" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B215" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C215" s="30"/>
       <x:c r="D215" s="30"/>
       <x:c r="E215" s="30"/>
@@ -7772,11 +7788,29 @@
       <x:c r="G215" s="30"/>
       <x:c r="H215" s="30"/>
       <x:c r="I215" s="30"/>
-      <x:c r="J215" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
-        <x:v>4577.8</x:v>
+      <x:c r="J215" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J214),1)</x:f>
+        <x:v>41200</x:v>
       </x:c>
       <x:c r="K215" s="30"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B216" s="30"/>
+      <x:c r="C216" s="30"/>
+      <x:c r="D216" s="30"/>
+      <x:c r="E216" s="30"/>
+      <x:c r="F216" s="30"/>
+      <x:c r="G216" s="30"/>
+      <x:c r="H216" s="30"/>
+      <x:c r="I216" s="30"/>
+      <x:c r="J216" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
+        <x:v>4120</x:v>
+      </x:c>
+      <x:c r="K216" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -14992,155 +15026,155 @@
       </x:c>
     </x:row>
     <x:row r="204">
-      <x:c r="A204" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B204" s="30" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C204" s="30"/>
-      <x:c r="D204" s="30"/>
-      <x:c r="E204" s="30"/>
-      <x:c r="F204" s="30"/>
-      <x:c r="G204" s="30"/>
-      <x:c r="H204" s="30"/>
-      <x:c r="I204" s="32" t="n">
-        <x:f>ROUND(SUM(I169:I203),1)</x:f>
-        <x:v>15825.4</x:v>
-      </x:c>
-      <x:c r="J204" s="30"/>
-      <x:c r="K204" s="30"/>
+      <x:c r="A204" s="22" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B204" s="22" t="str">
+        <x:v>9月14日</x:v>
+      </x:c>
+      <x:c r="C204" s="23" t="n">
+        <x:v>7482.2</x:v>
+      </x:c>
+      <x:c r="D204" s="23" t="n">
+        <x:v>7595.2</x:v>
+      </x:c>
+      <x:c r="E204" s="23" t="n">
+        <x:v>7452.2</x:v>
+      </x:c>
+      <x:c r="F204" s="23" t="n">
+        <x:v>7573.6</x:v>
+      </x:c>
+      <x:c r="G204" s="23" t="n">
+        <x:f>ROUND(F204-F203,1)</x:f>
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="H204" s="24" t="n">
+        <x:f>IFERROR(F204/F203-1,"")</x:f>
+        <x:v>0.0006077421059584864</x:v>
+      </x:c>
+      <x:c r="I204" s="23" t="n">
+        <x:f>ROUND(D204-E204,1)</x:f>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="J204" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+      <x:c r="K204" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B205" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B205" s="30" t="n">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="C205" s="30"/>
       <x:c r="D205" s="30"/>
       <x:c r="E205" s="30"/>
       <x:c r="F205" s="30"/>
       <x:c r="G205" s="30"/>
       <x:c r="H205" s="30"/>
-      <x:c r="I205" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I169:I203),0),1)</x:f>
-        <x:v>452.2</x:v>
+      <x:c r="I205" s="32" t="n">
+        <x:f>ROUND(SUM(I169:I204),1)</x:f>
+        <x:v>15968.4</x:v>
       </x:c>
       <x:c r="J205" s="30"/>
       <x:c r="K205" s="30"/>
     </x:row>
-    <x:row r="207">
-      <x:c r="A207" s="17" t="str">
+    <x:row r="206">
+      <x:c r="A206" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B206" s="30"/>
+      <x:c r="C206" s="30"/>
+      <x:c r="D206" s="30"/>
+      <x:c r="E206" s="30"/>
+      <x:c r="F206" s="30"/>
+      <x:c r="G206" s="30"/>
+      <x:c r="H206" s="30"/>
+      <x:c r="I206" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I169:I204),0),1)</x:f>
+        <x:v>443.6</x:v>
+      </x:c>
+      <x:c r="J206" s="30"/>
+      <x:c r="K206" s="30"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" s="17" t="str">
         <x:v>IF主力</x:v>
       </x:c>
-      <x:c r="B207" s="17"/>
-      <x:c r="C207" s="17"/>
-      <x:c r="D207" s="17"/>
-      <x:c r="E207" s="17"/>
-      <x:c r="F207" s="17"/>
-      <x:c r="G207" s="17"/>
-      <x:c r="H207" s="17"/>
-      <x:c r="I207" s="17"/>
-      <x:c r="J207" s="17"/>
-      <x:c r="K207" s="17"/>
-    </x:row>
-    <x:row r="208">
-      <x:c r="A208" s="20" t="str">
+      <x:c r="B208" s="17"/>
+      <x:c r="C208" s="17"/>
+      <x:c r="D208" s="17"/>
+      <x:c r="E208" s="17"/>
+      <x:c r="F208" s="17"/>
+      <x:c r="G208" s="17"/>
+      <x:c r="H208" s="17"/>
+      <x:c r="I208" s="17"/>
+      <x:c r="J208" s="17"/>
+      <x:c r="K208" s="17"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B208" s="20" t="str">
+      <x:c r="B209" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C208" s="20" t="str">
+      <x:c r="C209" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D208" s="20" t="str">
+      <x:c r="D209" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E208" s="20" t="str">
+      <x:c r="E209" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F208" s="20" t="str">
+      <x:c r="F209" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G208" s="20" t="str">
+      <x:c r="G209" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H208" s="20" t="str">
+      <x:c r="H209" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I208" s="20" t="str">
+      <x:c r="I209" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J208" s="20" t="str">
+      <x:c r="J209" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K208" s="20" t="str">
+      <x:c r="K209" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209">
-      <x:c r="A209" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B209" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C209" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="D209" s="23" t="n">
-        <x:v>4785.8</x:v>
-      </x:c>
-      <x:c r="E209" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="F209" s="23" t="n">
-        <x:v>4743.8</x:v>
-      </x:c>
-      <x:c r="G209" s="23"/>
-      <x:c r="H209" s="24"/>
-      <x:c r="I209" s="26" t="n">
-        <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>158.8</x:v>
-      </x:c>
-      <x:c r="J209" s="22" t="str">
-        <x:v>IF2603</x:v>
-      </x:c>
-      <x:c r="K209" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B210" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C210" s="23" t="n">
-        <x:v>4762</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="D210" s="23" t="n">
-        <x:v>4833.2</x:v>
+        <x:v>4785.8</x:v>
       </x:c>
       <x:c r="E210" s="23" t="n">
-        <x:v>4707</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="F210" s="23" t="n">
-        <x:v>4723.2</x:v>
-      </x:c>
-      <x:c r="G210" s="23" t="n">
-        <x:f>ROUND(F210-F209,1)</x:f>
-        <x:v>-20.6</x:v>
-      </x:c>
-      <x:c r="H210" s="24" t="n">
-        <x:f>IFERROR(F210/F209-1,"")</x:f>
-        <x:v>-0.004342510223871221</x:v>
-      </x:c>
+        <x:v>4743.8</x:v>
+      </x:c>
+      <x:c r="G210" s="23"/>
+      <x:c r="H210" s="24"/>
       <x:c r="I210" s="26" t="n">
         <x:f>ROUND(D210-E210,1)</x:f>
-        <x:v>126.2</x:v>
+        <x:v>158.8</x:v>
       </x:c>
       <x:c r="J210" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15151,34 +15185,34 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B211" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C211" s="23" t="n">
-        <x:v>4711.8</x:v>
+        <x:v>4762</x:v>
       </x:c>
       <x:c r="D211" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4833.2</x:v>
       </x:c>
       <x:c r="E211" s="23" t="n">
-        <x:v>4672.8</x:v>
+        <x:v>4707</x:v>
       </x:c>
       <x:c r="F211" s="23" t="n">
-        <x:v>4709.2</x:v>
+        <x:v>4723.2</x:v>
       </x:c>
       <x:c r="G211" s="23" t="n">
         <x:f>ROUND(F211-F210,1)</x:f>
-        <x:v>-14</x:v>
+        <x:v>-20.6</x:v>
       </x:c>
       <x:c r="H211" s="24" t="n">
         <x:f>IFERROR(F211/F210-1,"")</x:f>
-        <x:v>-0.002964092140921415</x:v>
+        <x:v>-0.004342510223871221</x:v>
       </x:c>
       <x:c r="I211" s="26" t="n">
         <x:f>ROUND(D211-E211,1)</x:f>
-        <x:v>90.2</x:v>
+        <x:v>126.2</x:v>
       </x:c>
       <x:c r="J211" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15189,34 +15223,34 @@
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B212" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C212" s="23" t="n">
-        <x:v>4726.8</x:v>
+        <x:v>4711.8</x:v>
       </x:c>
       <x:c r="D212" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E212" s="23" t="n">
-        <x:v>4640</x:v>
+        <x:v>4672.8</x:v>
       </x:c>
       <x:c r="F212" s="23" t="n">
-        <x:v>4711</x:v>
+        <x:v>4709.2</x:v>
       </x:c>
       <x:c r="G212" s="23" t="n">
         <x:f>ROUND(F212-F211,1)</x:f>
-        <x:v>1.8</x:v>
+        <x:v>-14</x:v>
       </x:c>
       <x:c r="H212" s="24" t="n">
         <x:f>IFERROR(F212/F211-1,"")</x:f>
-        <x:v>0.00038223052747810016</x:v>
+        <x:v>-0.002964092140921415</x:v>
       </x:c>
       <x:c r="I212" s="26" t="n">
         <x:f>ROUND(D212-E212,1)</x:f>
-        <x:v>153</x:v>
+        <x:v>90.2</x:v>
       </x:c>
       <x:c r="J212" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15227,34 +15261,34 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B213" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C213" s="23" t="n">
-        <x:v>4680.6</x:v>
+        <x:v>4726.8</x:v>
       </x:c>
       <x:c r="D213" s="23" t="n">
-        <x:v>4724</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E213" s="23" t="n">
-        <x:v>4555.6</x:v>
+        <x:v>4640</x:v>
       </x:c>
       <x:c r="F213" s="23" t="n">
-        <x:v>4637.6</x:v>
+        <x:v>4711</x:v>
       </x:c>
       <x:c r="G213" s="23" t="n">
         <x:f>ROUND(F213-F212,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="H213" s="24" t="n">
         <x:f>IFERROR(F213/F212-1,"")</x:f>
-        <x:v>-0.015580556145192048</x:v>
+        <x:v>0.00038223052747810016</x:v>
       </x:c>
       <x:c r="I213" s="26" t="n">
         <x:f>ROUND(D213-E213,1)</x:f>
-        <x:v>168.4</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="J213" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15265,34 +15299,34 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B214" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C214" s="23" t="n">
-        <x:v>4688.8</x:v>
+        <x:v>4680.6</x:v>
       </x:c>
       <x:c r="D214" s="23" t="n">
-        <x:v>4733.8</x:v>
+        <x:v>4724</x:v>
       </x:c>
       <x:c r="E214" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4555.6</x:v>
       </x:c>
       <x:c r="F214" s="23" t="n">
-        <x:v>4627</x:v>
+        <x:v>4637.6</x:v>
       </x:c>
       <x:c r="G214" s="23" t="n">
         <x:f>ROUND(F214-F213,1)</x:f>
-        <x:v>-10.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H214" s="24" t="n">
         <x:f>IFERROR(F214/F213-1,"")</x:f>
-        <x:v>-0.0022856649991375155</x:v>
+        <x:v>-0.015580556145192048</x:v>
       </x:c>
       <x:c r="I214" s="26" t="n">
         <x:f>ROUND(D214-E214,1)</x:f>
-        <x:v>109.8</x:v>
+        <x:v>168.4</x:v>
       </x:c>
       <x:c r="J214" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15303,110 +15337,110 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B215" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C215" s="23" t="n">
-        <x:v>4680.2</x:v>
+        <x:v>4688.8</x:v>
       </x:c>
       <x:c r="D215" s="23" t="n">
-        <x:v>4768</x:v>
+        <x:v>4733.8</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
-        <x:v>4671.2</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>4713.8</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="G215" s="23" t="n">
         <x:f>ROUND(F215-F214,1)</x:f>
-        <x:v>86.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="H215" s="24" t="n">
         <x:f>IFERROR(F215/F214-1,"")</x:f>
-        <x:v>0.01875945537065049</x:v>
+        <x:v>-0.0022856649991375155</x:v>
       </x:c>
       <x:c r="I215" s="26" t="n">
         <x:f>ROUND(D215-E215,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J215" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K215" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B216" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C216" s="23" t="n">
-        <x:v>4681.2</x:v>
+        <x:v>4680.2</x:v>
       </x:c>
       <x:c r="D216" s="23" t="n">
-        <x:v>4725</x:v>
+        <x:v>4768</x:v>
       </x:c>
       <x:c r="E216" s="23" t="n">
-        <x:v>4560.2</x:v>
+        <x:v>4671.2</x:v>
       </x:c>
       <x:c r="F216" s="23" t="n">
-        <x:v>4646</x:v>
+        <x:v>4713.8</x:v>
       </x:c>
       <x:c r="G216" s="23" t="n">
         <x:f>ROUND(F216-F215,1)</x:f>
-        <x:v>-67.8</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="H216" s="24" t="n">
         <x:f>IFERROR(F216/F215-1,"")</x:f>
-        <x:v>-0.014383300097585816</x:v>
+        <x:v>0.01875945537065049</x:v>
       </x:c>
       <x:c r="I216" s="26" t="n">
         <x:f>ROUND(D216-E216,1)</x:f>
-        <x:v>164.8</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J216" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K216" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B217" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C217" s="23" t="n">
-        <x:v>4600</x:v>
+        <x:v>4681.2</x:v>
       </x:c>
       <x:c r="D217" s="23" t="n">
-        <x:v>4699</x:v>
+        <x:v>4725</x:v>
       </x:c>
       <x:c r="E217" s="23" t="n">
-        <x:v>4500</x:v>
+        <x:v>4560.2</x:v>
       </x:c>
       <x:c r="F217" s="23" t="n">
-        <x:v>4658</x:v>
+        <x:v>4646</x:v>
       </x:c>
       <x:c r="G217" s="23" t="n">
         <x:f>ROUND(F217-F216,1)</x:f>
-        <x:v>12</x:v>
+        <x:v>-67.8</x:v>
       </x:c>
       <x:c r="H217" s="24" t="n">
         <x:f>IFERROR(F217/F216-1,"")</x:f>
-        <x:v>0.00258286698235044</x:v>
+        <x:v>-0.014383300097585816</x:v>
       </x:c>
       <x:c r="I217" s="26" t="n">
         <x:f>ROUND(D217-E217,1)</x:f>
-        <x:v>199</x:v>
+        <x:v>164.8</x:v>
       </x:c>
       <x:c r="J217" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15417,34 +15451,34 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B218" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C218" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="D218" s="23" t="n">
-        <x:v>4718.4</x:v>
+        <x:v>4699</x:v>
       </x:c>
       <x:c r="E218" s="23" t="n">
-        <x:v>4570</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="F218" s="23" t="n">
-        <x:v>4596.8</x:v>
+        <x:v>4658</x:v>
       </x:c>
       <x:c r="G218" s="23" t="n">
         <x:f>ROUND(F218-F217,1)</x:f>
-        <x:v>-61.2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H218" s="24" t="n">
         <x:f>IFERROR(F218/F217-1,"")</x:f>
-        <x:v>-0.0131386861313868</x:v>
+        <x:v>0.00258286698235044</x:v>
       </x:c>
       <x:c r="I218" s="26" t="n">
         <x:f>ROUND(D218-E218,1)</x:f>
-        <x:v>148.4</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="J218" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15455,37 +15489,37 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B219" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C219" s="23" t="n">
-        <x:v>4434.4</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D219" s="23" t="n">
-        <x:v>4466.2</x:v>
+        <x:v>4718.4</x:v>
       </x:c>
       <x:c r="E219" s="23" t="n">
-        <x:v>4307.2</x:v>
+        <x:v>4570</x:v>
       </x:c>
       <x:c r="F219" s="23" t="n">
-        <x:v>4427.4</x:v>
-      </x:c>
-      <x:c r="G219" s="28" t="n">
+        <x:v>4596.8</x:v>
+      </x:c>
+      <x:c r="G219" s="23" t="n">
         <x:f>ROUND(F219-F218,1)</x:f>
-        <x:v>-169.4</x:v>
+        <x:v>-61.2</x:v>
       </x:c>
       <x:c r="H219" s="24" t="n">
         <x:f>IFERROR(F219/F218-1,"")</x:f>
-        <x:v>-0.0368517229376959</x:v>
+        <x:v>-0.0131386861313868</x:v>
       </x:c>
       <x:c r="I219" s="26" t="n">
         <x:f>ROUND(D219-E219,1)</x:f>
-        <x:v>159</x:v>
+        <x:v>148.4</x:v>
       </x:c>
       <x:c r="J219" s="22" t="str">
-        <x:v>IF2606</x:v>
+        <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K219" s="22" t="n">
         <x:v>5</x:v>
@@ -15493,34 +15527,34 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B220" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C220" s="23" t="n">
-        <x:v>4387.2</x:v>
+        <x:v>4434.4</x:v>
       </x:c>
       <x:c r="D220" s="23" t="n">
-        <x:v>4459.8</x:v>
+        <x:v>4466.2</x:v>
       </x:c>
       <x:c r="E220" s="23" t="n">
-        <x:v>4346</x:v>
+        <x:v>4307.2</x:v>
       </x:c>
       <x:c r="F220" s="23" t="n">
-        <x:v>4362.2</x:v>
-      </x:c>
-      <x:c r="G220" s="23" t="n">
+        <x:v>4427.4</x:v>
+      </x:c>
+      <x:c r="G220" s="28" t="n">
         <x:f>ROUND(F220-F219,1)</x:f>
-        <x:v>-65.2</x:v>
+        <x:v>-169.4</x:v>
       </x:c>
       <x:c r="H220" s="24" t="n">
         <x:f>IFERROR(F220/F219-1,"")</x:f>
-        <x:v>-0.014726476035596514</x:v>
+        <x:v>-0.0368517229376959</x:v>
       </x:c>
       <x:c r="I220" s="26" t="n">
         <x:f>ROUND(D220-E220,1)</x:f>
-        <x:v>113.8</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J220" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15531,110 +15565,110 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B221" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C221" s="23" t="n">
-        <x:v>4369.8</x:v>
+        <x:v>4387.2</x:v>
       </x:c>
       <x:c r="D221" s="23" t="n">
-        <x:v>4591.8</x:v>
+        <x:v>4459.8</x:v>
       </x:c>
       <x:c r="E221" s="23" t="n">
-        <x:v>4347</x:v>
+        <x:v>4346</x:v>
       </x:c>
       <x:c r="F221" s="23" t="n">
-        <x:v>4562</x:v>
-      </x:c>
-      <x:c r="G221" s="28" t="n">
+        <x:v>4362.2</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
         <x:f>ROUND(F221-F220,1)</x:f>
-        <x:v>199.8</x:v>
+        <x:v>-65.2</x:v>
       </x:c>
       <x:c r="H221" s="24" t="n">
         <x:f>IFERROR(F221/F220-1,"")</x:f>
-        <x:v>0.045802576681491125</x:v>
+        <x:v>-0.014726476035596514</x:v>
       </x:c>
       <x:c r="I221" s="26" t="n">
         <x:f>ROUND(D221-E221,1)</x:f>
-        <x:v>244.8</x:v>
+        <x:v>113.8</x:v>
       </x:c>
       <x:c r="J221" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K221" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B222" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C222" s="23" t="n">
-        <x:v>4542</x:v>
+        <x:v>4369.8</x:v>
       </x:c>
       <x:c r="D222" s="23" t="n">
-        <x:v>4685</x:v>
+        <x:v>4591.8</x:v>
       </x:c>
       <x:c r="E222" s="23" t="n">
-        <x:v>4541.6</x:v>
+        <x:v>4347</x:v>
       </x:c>
       <x:c r="F222" s="23" t="n">
-        <x:v>4667</x:v>
-      </x:c>
-      <x:c r="G222" s="23" t="n">
+        <x:v>4562</x:v>
+      </x:c>
+      <x:c r="G222" s="28" t="n">
         <x:f>ROUND(F222-F221,1)</x:f>
-        <x:v>105</x:v>
+        <x:v>199.8</x:v>
       </x:c>
       <x:c r="H222" s="24" t="n">
         <x:f>IFERROR(F222/F221-1,"")</x:f>
-        <x:v>0.0230162209557212</x:v>
+        <x:v>0.045802576681491125</x:v>
       </x:c>
       <x:c r="I222" s="26" t="n">
         <x:f>ROUND(D222-E222,1)</x:f>
-        <x:v>143.4</x:v>
+        <x:v>244.8</x:v>
       </x:c>
       <x:c r="J222" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K222" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B223" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C223" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4542</x:v>
       </x:c>
       <x:c r="D223" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4685</x:v>
       </x:c>
       <x:c r="E223" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4541.6</x:v>
       </x:c>
       <x:c r="F223" s="23" t="n">
-        <x:v>4713.6</x:v>
+        <x:v>4667</x:v>
       </x:c>
       <x:c r="G223" s="23" t="n">
         <x:f>ROUND(F223-F222,1)</x:f>
-        <x:v>46.6</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H223" s="24" t="n">
         <x:f>IFERROR(F223/F222-1,"")</x:f>
-        <x:v>0.009985001071352029</x:v>
+        <x:v>0.0230162209557212</x:v>
       </x:c>
       <x:c r="I223" s="26" t="n">
         <x:f>ROUND(D223-E223,1)</x:f>
-        <x:v>106.2</x:v>
+        <x:v>143.4</x:v>
       </x:c>
       <x:c r="J223" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15645,148 +15679,148 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B224" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C224" s="23" t="n">
-        <x:v>4720</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D224" s="23" t="n">
-        <x:v>4776.6</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E224" s="23" t="n">
-        <x:v>4687.2</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="F224" s="23" t="n">
-        <x:v>4763.4</x:v>
+        <x:v>4713.6</x:v>
       </x:c>
       <x:c r="G224" s="23" t="n">
         <x:f>ROUND(F224-F223,1)</x:f>
-        <x:v>49.8</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="H224" s="24" t="n">
         <x:f>IFERROR(F224/F223-1,"")</x:f>
-        <x:v>0.010565173116089399</x:v>
-      </x:c>
-      <x:c r="I224" s="23" t="n">
+        <x:v>0.009985001071352029</x:v>
+      </x:c>
+      <x:c r="I224" s="26" t="n">
         <x:f>ROUND(D224-E224,1)</x:f>
-        <x:v>89.4</x:v>
+        <x:v>106.2</x:v>
       </x:c>
       <x:c r="J224" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K224" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B225" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C225" s="23" t="n">
-        <x:v>4808.2</x:v>
+        <x:v>4720</x:v>
       </x:c>
       <x:c r="D225" s="23" t="n">
-        <x:v>4869</x:v>
+        <x:v>4776.6</x:v>
       </x:c>
       <x:c r="E225" s="23" t="n">
-        <x:v>4797</x:v>
+        <x:v>4687.2</x:v>
       </x:c>
       <x:c r="F225" s="23" t="n">
-        <x:v>4836.8</x:v>
+        <x:v>4763.4</x:v>
       </x:c>
       <x:c r="G225" s="23" t="n">
         <x:f>ROUND(F225-F224,1)</x:f>
-        <x:v>73.4</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="H225" s="24" t="n">
         <x:f>IFERROR(F225/F224-1,"")</x:f>
-        <x:v>0.015409161523281867</x:v>
+        <x:v>0.010565173116089399</x:v>
       </x:c>
       <x:c r="I225" s="23" t="n">
         <x:f>ROUND(D225-E225,1)</x:f>
-        <x:v>72</x:v>
+        <x:v>89.4</x:v>
       </x:c>
       <x:c r="J225" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K225" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B226" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C226" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4808.2</x:v>
       </x:c>
       <x:c r="D226" s="23" t="n">
-        <x:v>4995</x:v>
+        <x:v>4869</x:v>
       </x:c>
       <x:c r="E226" s="23" t="n">
-        <x:v>4794</x:v>
+        <x:v>4797</x:v>
       </x:c>
       <x:c r="F226" s="23" t="n">
-        <x:v>4824</x:v>
+        <x:v>4836.8</x:v>
       </x:c>
       <x:c r="G226" s="23" t="n">
         <x:f>ROUND(F226-F225,1)</x:f>
-        <x:v>-12.8</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="H226" s="24" t="n">
         <x:f>IFERROR(F226/F225-1,"")</x:f>
-        <x:v>-0.0026463777704267555</x:v>
-      </x:c>
-      <x:c r="I226" s="26" t="n">
+        <x:v>0.015409161523281867</x:v>
+      </x:c>
+      <x:c r="I226" s="23" t="n">
         <x:f>ROUND(D226-E226,1)</x:f>
-        <x:v>201</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J226" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K226" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B227" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C227" s="23" t="n">
-        <x:v>4810</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D227" s="23" t="n">
-        <x:v>4900.8</x:v>
+        <x:v>4995</x:v>
       </x:c>
       <x:c r="E227" s="23" t="n">
-        <x:v>4735</x:v>
+        <x:v>4794</x:v>
       </x:c>
       <x:c r="F227" s="23" t="n">
-        <x:v>4788.2</x:v>
+        <x:v>4824</x:v>
       </x:c>
       <x:c r="G227" s="23" t="n">
         <x:f>ROUND(F227-F226,1)</x:f>
-        <x:v>-35.8</x:v>
+        <x:v>-12.8</x:v>
       </x:c>
       <x:c r="H227" s="24" t="n">
         <x:f>IFERROR(F227/F226-1,"")</x:f>
-        <x:v>-0.007421227197346614</x:v>
+        <x:v>-0.0026463777704267555</x:v>
       </x:c>
       <x:c r="I227" s="26" t="n">
         <x:f>ROUND(D227-E227,1)</x:f>
-        <x:v>165.8</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="J227" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15797,34 +15831,34 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B228" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C228" s="23" t="n">
-        <x:v>4817.8</x:v>
+        <x:v>4810</x:v>
       </x:c>
       <x:c r="D228" s="23" t="n">
-        <x:v>4928.4</x:v>
+        <x:v>4900.8</x:v>
       </x:c>
       <x:c r="E228" s="23" t="n">
-        <x:v>4793.2</x:v>
+        <x:v>4735</x:v>
       </x:c>
       <x:c r="F228" s="23" t="n">
-        <x:v>4847.8</x:v>
+        <x:v>4788.2</x:v>
       </x:c>
       <x:c r="G228" s="23" t="n">
         <x:f>ROUND(F228-F227,1)</x:f>
-        <x:v>59.6</x:v>
+        <x:v>-35.8</x:v>
       </x:c>
       <x:c r="H228" s="24" t="n">
         <x:f>IFERROR(F228/F227-1,"")</x:f>
-        <x:v>0.01244726619606551</x:v>
+        <x:v>-0.007421227197346614</x:v>
       </x:c>
       <x:c r="I228" s="26" t="n">
         <x:f>ROUND(D228-E228,1)</x:f>
-        <x:v>135.2</x:v>
+        <x:v>165.8</x:v>
       </x:c>
       <x:c r="J228" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15835,34 +15869,34 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B229" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C229" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4817.8</x:v>
       </x:c>
       <x:c r="D229" s="23" t="n">
-        <x:v>4964.6</x:v>
+        <x:v>4928.4</x:v>
       </x:c>
       <x:c r="E229" s="23" t="n">
-        <x:v>4762.2</x:v>
+        <x:v>4793.2</x:v>
       </x:c>
       <x:c r="F229" s="23" t="n">
-        <x:v>4776.8</x:v>
+        <x:v>4847.8</x:v>
       </x:c>
       <x:c r="G229" s="23" t="n">
         <x:f>ROUND(F229-F228,1)</x:f>
-        <x:v>-71</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="H229" s="24" t="n">
         <x:f>IFERROR(F229/F228-1,"")</x:f>
-        <x:v>-0.014645818721894521</x:v>
+        <x:v>0.01244726619606551</x:v>
       </x:c>
       <x:c r="I229" s="26" t="n">
         <x:f>ROUND(D229-E229,1)</x:f>
-        <x:v>202.4</x:v>
+        <x:v>135.2</x:v>
       </x:c>
       <x:c r="J229" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15873,34 +15907,34 @@
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B230" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C230" s="23" t="n">
-        <x:v>4700</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D230" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4964.6</x:v>
       </x:c>
       <x:c r="E230" s="23" t="n">
-        <x:v>4640.2</x:v>
+        <x:v>4762.2</x:v>
       </x:c>
       <x:c r="F230" s="23" t="n">
-        <x:v>4769.8</x:v>
+        <x:v>4776.8</x:v>
       </x:c>
       <x:c r="G230" s="23" t="n">
         <x:f>ROUND(F230-F229,1)</x:f>
-        <x:v>-7</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="H230" s="24" t="n">
         <x:f>IFERROR(F230/F229-1,"")</x:f>
-        <x:v>-0.0014654161781946229</x:v>
+        <x:v>-0.014645818721894521</x:v>
       </x:c>
       <x:c r="I230" s="26" t="n">
         <x:f>ROUND(D230-E230,1)</x:f>
-        <x:v>152.8</x:v>
+        <x:v>202.4</x:v>
       </x:c>
       <x:c r="J230" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15911,113 +15945,113 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B231" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C231" s="23" t="n">
-        <x:v>4819</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="D231" s="23" t="n">
-        <x:v>4971</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E231" s="23" t="n">
-        <x:v>4804.8</x:v>
+        <x:v>4640.2</x:v>
       </x:c>
       <x:c r="F231" s="23" t="n">
-        <x:v>4960.6</x:v>
-      </x:c>
-      <x:c r="G231" s="28" t="n">
+        <x:v>4769.8</x:v>
+      </x:c>
+      <x:c r="G231" s="23" t="n">
         <x:f>ROUND(F231-F230,1)</x:f>
-        <x:v>190.8</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="H231" s="24" t="n">
         <x:f>IFERROR(F231/F230-1,"")</x:f>
-        <x:v>0.040001677219170695</x:v>
+        <x:v>-0.0014654161781946229</x:v>
       </x:c>
       <x:c r="I231" s="26" t="n">
         <x:f>ROUND(D231-E231,1)</x:f>
-        <x:v>166.2</x:v>
+        <x:v>152.8</x:v>
       </x:c>
       <x:c r="J231" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K231" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B232" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C232" s="23" t="n">
-        <x:v>4956</x:v>
+        <x:v>4819</x:v>
       </x:c>
       <x:c r="D232" s="23" t="n">
-        <x:v>5030.2</x:v>
+        <x:v>4971</x:v>
       </x:c>
       <x:c r="E232" s="23" t="n">
-        <x:v>4717</x:v>
+        <x:v>4804.8</x:v>
       </x:c>
       <x:c r="F232" s="23" t="n">
-        <x:v>4748.2</x:v>
+        <x:v>4960.6</x:v>
       </x:c>
       <x:c r="G232" s="28" t="n">
         <x:f>ROUND(F232-F231,1)</x:f>
-        <x:v>-212.4</x:v>
+        <x:v>190.8</x:v>
       </x:c>
       <x:c r="H232" s="24" t="n">
         <x:f>IFERROR(F232/F231-1,"")</x:f>
-        <x:v>-0.04281740112083221</x:v>
+        <x:v>0.040001677219170695</x:v>
       </x:c>
       <x:c r="I232" s="26" t="n">
         <x:f>ROUND(D232-E232,1)</x:f>
-        <x:v>313.2</x:v>
+        <x:v>166.2</x:v>
       </x:c>
       <x:c r="J232" s="22" t="str">
-        <x:v>IF2606/IF2609</x:v>
+        <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K232" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B233" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C233" s="23" t="n">
-        <x:v>4759.4</x:v>
+        <x:v>4956</x:v>
       </x:c>
       <x:c r="D233" s="23" t="n">
-        <x:v>4899.6</x:v>
+        <x:v>5030.2</x:v>
       </x:c>
       <x:c r="E233" s="23" t="n">
-        <x:v>4705</x:v>
+        <x:v>4717</x:v>
       </x:c>
       <x:c r="F233" s="23" t="n">
-        <x:v>4752.2</x:v>
-      </x:c>
-      <x:c r="G233" s="23" t="n">
+        <x:v>4748.2</x:v>
+      </x:c>
+      <x:c r="G233" s="28" t="n">
         <x:f>ROUND(F233-F232,1)</x:f>
-        <x:v>4</x:v>
+        <x:v>-212.4</x:v>
       </x:c>
       <x:c r="H233" s="24" t="n">
         <x:f>IFERROR(F233/F232-1,"")</x:f>
-        <x:v>0.0008424244977043305</x:v>
+        <x:v>-0.04281740112083221</x:v>
       </x:c>
       <x:c r="I233" s="26" t="n">
         <x:f>ROUND(D233-E233,1)</x:f>
-        <x:v>194.6</x:v>
+        <x:v>313.2</x:v>
       </x:c>
       <x:c r="J233" s="22" t="str">
-        <x:v>IF2609</x:v>
+        <x:v>IF2606/IF2609</x:v>
       </x:c>
       <x:c r="K233" s="22" t="n">
         <x:v>5</x:v>
@@ -16025,34 +16059,34 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B234" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C234" s="23" t="n">
-        <x:v>4781</x:v>
+        <x:v>4759.4</x:v>
       </x:c>
       <x:c r="D234" s="23" t="n">
-        <x:v>4822.2</x:v>
+        <x:v>4899.6</x:v>
       </x:c>
       <x:c r="E234" s="23" t="n">
-        <x:v>4665.2</x:v>
+        <x:v>4705</x:v>
       </x:c>
       <x:c r="F234" s="23" t="n">
-        <x:v>4704.6</x:v>
+        <x:v>4752.2</x:v>
       </x:c>
       <x:c r="G234" s="23" t="n">
         <x:f>ROUND(F234-F233,1)</x:f>
-        <x:v>-47.6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H234" s="24" t="n">
         <x:f>IFERROR(F234/F233-1,"")</x:f>
-        <x:v>-0.010016413450612216</x:v>
+        <x:v>0.0008424244977043305</x:v>
       </x:c>
       <x:c r="I234" s="26" t="n">
         <x:f>ROUND(D234-E234,1)</x:f>
-        <x:v>157</x:v>
+        <x:v>194.6</x:v>
       </x:c>
       <x:c r="J234" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16063,34 +16097,34 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B235" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C235" s="23" t="n">
-        <x:v>4691</x:v>
+        <x:v>4781</x:v>
       </x:c>
       <x:c r="D235" s="23" t="n">
-        <x:v>4739.4</x:v>
+        <x:v>4822.2</x:v>
       </x:c>
       <x:c r="E235" s="23" t="n">
-        <x:v>4441.4</x:v>
+        <x:v>4665.2</x:v>
       </x:c>
       <x:c r="F235" s="23" t="n">
-        <x:v>4473.8</x:v>
-      </x:c>
-      <x:c r="G235" s="28" t="n">
+        <x:v>4704.6</x:v>
+      </x:c>
+      <x:c r="G235" s="23" t="n">
         <x:f>ROUND(F235-F234,1)</x:f>
-        <x:v>-230.8</x:v>
+        <x:v>-47.6</x:v>
       </x:c>
       <x:c r="H235" s="24" t="n">
         <x:f>IFERROR(F235/F234-1,"")</x:f>
-        <x:v>-0.04905836840539046</x:v>
+        <x:v>-0.010016413450612216</x:v>
       </x:c>
       <x:c r="I235" s="26" t="n">
         <x:f>ROUND(D235-E235,1)</x:f>
-        <x:v>298</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="J235" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16101,34 +16135,34 @@
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B236" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C236" s="23" t="n">
-        <x:v>4530</x:v>
+        <x:v>4691</x:v>
       </x:c>
       <x:c r="D236" s="23" t="n">
-        <x:v>4707.8</x:v>
+        <x:v>4739.4</x:v>
       </x:c>
       <x:c r="E236" s="23" t="n">
-        <x:v>4465</x:v>
+        <x:v>4441.4</x:v>
       </x:c>
       <x:c r="F236" s="23" t="n">
-        <x:v>4578.2</x:v>
-      </x:c>
-      <x:c r="G236" s="23" t="n">
+        <x:v>4473.8</x:v>
+      </x:c>
+      <x:c r="G236" s="28" t="n">
         <x:f>ROUND(F236-F235,1)</x:f>
-        <x:v>104.4</x:v>
+        <x:v>-230.8</x:v>
       </x:c>
       <x:c r="H236" s="24" t="n">
         <x:f>IFERROR(F236/F235-1,"")</x:f>
-        <x:v>0.023335866601099653</x:v>
+        <x:v>-0.04905836840539046</x:v>
       </x:c>
       <x:c r="I236" s="26" t="n">
         <x:f>ROUND(D236-E236,1)</x:f>
-        <x:v>242.8</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="J236" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16139,34 +16173,34 @@
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B237" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C237" s="23" t="n">
-        <x:v>4589.4</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="D237" s="23" t="n">
-        <x:v>4652.2</x:v>
+        <x:v>4707.8</x:v>
       </x:c>
       <x:c r="E237" s="23" t="n">
-        <x:v>4420</x:v>
+        <x:v>4465</x:v>
       </x:c>
       <x:c r="F237" s="23" t="n">
-        <x:v>4538</x:v>
+        <x:v>4578.2</x:v>
       </x:c>
       <x:c r="G237" s="23" t="n">
         <x:f>ROUND(F237-F236,1)</x:f>
-        <x:v>-40.2</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="H237" s="24" t="n">
         <x:f>IFERROR(F237/F236-1,"")</x:f>
-        <x:v>-0.008780743523655543</x:v>
+        <x:v>0.023335866601099653</x:v>
       </x:c>
       <x:c r="I237" s="26" t="n">
         <x:f>ROUND(D237-E237,1)</x:f>
-        <x:v>232.2</x:v>
+        <x:v>242.8</x:v>
       </x:c>
       <x:c r="J237" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16177,34 +16211,34 @@
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B238" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C238" s="23" t="n">
-        <x:v>4526.4</x:v>
+        <x:v>4589.4</x:v>
       </x:c>
       <x:c r="D238" s="23" t="n">
-        <x:v>4656.2</x:v>
+        <x:v>4652.2</x:v>
       </x:c>
       <x:c r="E238" s="23" t="n">
-        <x:v>4494.2</x:v>
+        <x:v>4420</x:v>
       </x:c>
       <x:c r="F238" s="23" t="n">
-        <x:v>4645.6</x:v>
+        <x:v>4538</x:v>
       </x:c>
       <x:c r="G238" s="23" t="n">
         <x:f>ROUND(F238-F237,1)</x:f>
-        <x:v>107.6</x:v>
+        <x:v>-40.2</x:v>
       </x:c>
       <x:c r="H238" s="24" t="n">
         <x:f>IFERROR(F238/F237-1,"")</x:f>
-        <x:v>0.02371088585279857</x:v>
+        <x:v>-0.008780743523655543</x:v>
       </x:c>
       <x:c r="I238" s="26" t="n">
         <x:f>ROUND(D238-E238,1)</x:f>
-        <x:v>162</x:v>
+        <x:v>232.2</x:v>
       </x:c>
       <x:c r="J238" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16215,34 +16249,34 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4526.4</x:v>
       </x:c>
       <x:c r="D239" s="23" t="n">
-        <x:v>4681</x:v>
+        <x:v>4656.2</x:v>
       </x:c>
       <x:c r="E239" s="23" t="n">
-        <x:v>4598</x:v>
+        <x:v>4494.2</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>4620.4</x:v>
+        <x:v>4645.6</x:v>
       </x:c>
       <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>-25.2</x:v>
+        <x:v>107.6</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>-0.005424487687274104</x:v>
-      </x:c>
-      <x:c r="I239" s="23" t="n">
+        <x:v>0.02371088585279857</x:v>
+      </x:c>
+      <x:c r="I239" s="26" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
-        <x:v>83</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J239" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16253,34 +16287,34 @@
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B240" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C240" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="D240" s="23" t="n">
-        <x:v>4700.6</x:v>
+        <x:v>4681</x:v>
       </x:c>
       <x:c r="E240" s="23" t="n">
-        <x:v>4531.8</x:v>
+        <x:v>4598</x:v>
       </x:c>
       <x:c r="F240" s="23" t="n">
-        <x:v>4576</x:v>
+        <x:v>4620.4</x:v>
       </x:c>
       <x:c r="G240" s="23" t="n">
         <x:f>ROUND(F240-F239,1)</x:f>
-        <x:v>-44.4</x:v>
+        <x:v>-25.2</x:v>
       </x:c>
       <x:c r="H240" s="24" t="n">
         <x:f>IFERROR(F240/F239-1,"")</x:f>
-        <x:v>-0.00960955761405935</x:v>
-      </x:c>
-      <x:c r="I240" s="26" t="n">
+        <x:v>-0.005424487687274104</x:v>
+      </x:c>
+      <x:c r="I240" s="23" t="n">
         <x:f>ROUND(D240-E240,1)</x:f>
-        <x:v>168.8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J240" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16291,34 +16325,34 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B241" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C241" s="23" t="n">
-        <x:v>4607.4</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="D241" s="23" t="n">
-        <x:v>4620</x:v>
+        <x:v>4700.6</x:v>
       </x:c>
       <x:c r="E241" s="23" t="n">
-        <x:v>4486.4</x:v>
+        <x:v>4531.8</x:v>
       </x:c>
       <x:c r="F241" s="23" t="n">
-        <x:v>4593.6</x:v>
+        <x:v>4576</x:v>
       </x:c>
       <x:c r="G241" s="23" t="n">
         <x:f>ROUND(F241-F240,1)</x:f>
-        <x:v>17.6</x:v>
+        <x:v>-44.4</x:v>
       </x:c>
       <x:c r="H241" s="24" t="n">
         <x:f>IFERROR(F241/F240-1,"")</x:f>
-        <x:v>0.0038461538461538325</x:v>
+        <x:v>-0.00960955761405935</x:v>
       </x:c>
       <x:c r="I241" s="26" t="n">
         <x:f>ROUND(D241-E241,1)</x:f>
-        <x:v>133.6</x:v>
+        <x:v>168.8</x:v>
       </x:c>
       <x:c r="J241" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16329,34 +16363,34 @@
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B242" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C242" s="23" t="n">
-        <x:v>4553</x:v>
+        <x:v>4607.4</x:v>
       </x:c>
       <x:c r="D242" s="23" t="n">
-        <x:v>4617.8</x:v>
+        <x:v>4620</x:v>
       </x:c>
       <x:c r="E242" s="23" t="n">
-        <x:v>4497.6</x:v>
+        <x:v>4486.4</x:v>
       </x:c>
       <x:c r="F242" s="23" t="n">
-        <x:v>4537.4</x:v>
+        <x:v>4593.6</x:v>
       </x:c>
       <x:c r="G242" s="23" t="n">
         <x:f>ROUND(F242-F241,1)</x:f>
-        <x:v>-56.2</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="H242" s="24" t="n">
         <x:f>IFERROR(F242/F241-1,"")</x:f>
-        <x:v>-0.01223441309648221</x:v>
+        <x:v>0.0038461538461538325</x:v>
       </x:c>
       <x:c r="I242" s="26" t="n">
         <x:f>ROUND(D242-E242,1)</x:f>
-        <x:v>120.2</x:v>
+        <x:v>133.6</x:v>
       </x:c>
       <x:c r="J242" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16367,34 +16401,34 @@
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B243" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C243" s="23" t="n">
-        <x:v>4562</x:v>
+        <x:v>4553</x:v>
       </x:c>
       <x:c r="D243" s="23" t="n">
-        <x:v>4584</x:v>
+        <x:v>4617.8</x:v>
       </x:c>
       <x:c r="E243" s="23" t="n">
-        <x:v>4451.6</x:v>
+        <x:v>4497.6</x:v>
       </x:c>
       <x:c r="F243" s="23" t="n">
-        <x:v>4503.4</x:v>
+        <x:v>4537.4</x:v>
       </x:c>
       <x:c r="G243" s="23" t="n">
         <x:f>ROUND(F243-F242,1)</x:f>
-        <x:v>-34</x:v>
+        <x:v>-56.2</x:v>
       </x:c>
       <x:c r="H243" s="24" t="n">
         <x:f>IFERROR(F243/F242-1,"")</x:f>
-        <x:v>-0.007493278088773314</x:v>
+        <x:v>-0.01223441309648221</x:v>
       </x:c>
       <x:c r="I243" s="26" t="n">
         <x:f>ROUND(D243-E243,1)</x:f>
-        <x:v>132.4</x:v>
+        <x:v>120.2</x:v>
       </x:c>
       <x:c r="J243" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16405,192 +16439,192 @@
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B244" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C244" s="23" t="n">
-        <x:v>4468</x:v>
+        <x:v>4562</x:v>
       </x:c>
       <x:c r="D244" s="23" t="n">
-        <x:v>4500.6</x:v>
+        <x:v>4584</x:v>
       </x:c>
       <x:c r="E244" s="23" t="n">
-        <x:v>4458</x:v>
+        <x:v>4451.6</x:v>
       </x:c>
       <x:c r="F244" s="23" t="n">
-        <x:v>4480.2</x:v>
+        <x:v>4503.4</x:v>
       </x:c>
       <x:c r="G244" s="23" t="n">
         <x:f>ROUND(F244-F243,1)</x:f>
-        <x:v>-23.2</x:v>
+        <x:v>-34</x:v>
       </x:c>
       <x:c r="H244" s="24" t="n">
         <x:f>IFERROR(F244/F243-1,"")</x:f>
-        <x:v>-0.005151663187813571</x:v>
-      </x:c>
-      <x:c r="I244" s="23" t="n">
+        <x:v>-0.007493278088773314</x:v>
+      </x:c>
+      <x:c r="I244" s="26" t="n">
         <x:f>ROUND(D244-E244,1)</x:f>
-        <x:v>42.6</x:v>
+        <x:v>132.4</x:v>
       </x:c>
       <x:c r="J244" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K244" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="22" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B245" s="22" t="str">
+        <x:v>9月14日</x:v>
+      </x:c>
+      <x:c r="C245" s="23" t="n">
+        <x:v>4468</x:v>
+      </x:c>
+      <x:c r="D245" s="23" t="n">
+        <x:v>4500.6</x:v>
+      </x:c>
+      <x:c r="E245" s="23" t="n">
+        <x:v>4458</x:v>
+      </x:c>
+      <x:c r="F245" s="23" t="n">
+        <x:v>4480.2</x:v>
+      </x:c>
+      <x:c r="G245" s="23" t="n">
+        <x:f>ROUND(F245-F244,1)</x:f>
+        <x:v>-23.2</x:v>
+      </x:c>
+      <x:c r="H245" s="24" t="n">
+        <x:f>IFERROR(F245/F244-1,"")</x:f>
+        <x:v>-0.005151663187813571</x:v>
+      </x:c>
+      <x:c r="I245" s="23" t="n">
+        <x:f>ROUND(D245-E245,1)</x:f>
+        <x:v>42.6</x:v>
+      </x:c>
+      <x:c r="J245" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+      <x:c r="K245" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="245">
-      <x:c r="A245" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B245" s="30" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C245" s="30"/>
-      <x:c r="D245" s="30"/>
-      <x:c r="E245" s="30"/>
-      <x:c r="F245" s="30"/>
-      <x:c r="G245" s="30"/>
-      <x:c r="H245" s="30"/>
-      <x:c r="I245" s="32" t="n">
-        <x:f>ROUND(SUM(I209:I244),1)</x:f>
-        <x:v>5647.8</x:v>
-      </x:c>
-      <x:c r="J245" s="30"/>
-      <x:c r="K245" s="30"/>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B246" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B246" s="30" t="n">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="C246" s="30"/>
       <x:c r="D246" s="30"/>
       <x:c r="E246" s="30"/>
       <x:c r="F246" s="30"/>
       <x:c r="G246" s="30"/>
       <x:c r="H246" s="30"/>
-      <x:c r="I246" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I209:I244),0),1)</x:f>
-        <x:v>156.9</x:v>
+      <x:c r="I246" s="32" t="n">
+        <x:f>ROUND(SUM(I210:I245),1)</x:f>
+        <x:v>5647.8</x:v>
       </x:c>
       <x:c r="J246" s="30"/>
       <x:c r="K246" s="30"/>
     </x:row>
-    <x:row r="248">
-      <x:c r="A248" s="17" t="str">
+    <x:row r="247">
+      <x:c r="A247" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B247" s="30"/>
+      <x:c r="C247" s="30"/>
+      <x:c r="D247" s="30"/>
+      <x:c r="E247" s="30"/>
+      <x:c r="F247" s="30"/>
+      <x:c r="G247" s="30"/>
+      <x:c r="H247" s="30"/>
+      <x:c r="I247" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I210:I245),0),1)</x:f>
+        <x:v>156.9</x:v>
+      </x:c>
+      <x:c r="J247" s="30"/>
+      <x:c r="K247" s="30"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="17" t="str">
         <x:v>IH主力</x:v>
       </x:c>
-      <x:c r="B248" s="17"/>
-      <x:c r="C248" s="17"/>
-      <x:c r="D248" s="17"/>
-      <x:c r="E248" s="17"/>
-      <x:c r="F248" s="17"/>
-      <x:c r="G248" s="17"/>
-      <x:c r="H248" s="17"/>
-      <x:c r="I248" s="17"/>
-      <x:c r="J248" s="17"/>
-      <x:c r="K248" s="17"/>
-    </x:row>
-    <x:row r="249">
-      <x:c r="A249" s="20" t="str">
+      <x:c r="B249" s="17"/>
+      <x:c r="C249" s="17"/>
+      <x:c r="D249" s="17"/>
+      <x:c r="E249" s="17"/>
+      <x:c r="F249" s="17"/>
+      <x:c r="G249" s="17"/>
+      <x:c r="H249" s="17"/>
+      <x:c r="I249" s="17"/>
+      <x:c r="J249" s="17"/>
+      <x:c r="K249" s="17"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B249" s="20" t="str">
+      <x:c r="B250" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C249" s="20" t="str">
+      <x:c r="C250" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D249" s="20" t="str">
+      <x:c r="D250" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E249" s="20" t="str">
+      <x:c r="E250" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F249" s="20" t="str">
+      <x:c r="F250" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G249" s="20" t="str">
+      <x:c r="G250" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H249" s="20" t="str">
+      <x:c r="H250" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I249" s="20" t="str">
+      <x:c r="I250" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J249" s="20" t="str">
+      <x:c r="J250" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K249" s="20" t="str">
+      <x:c r="K250" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="250">
-      <x:c r="A250" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B250" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C250" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="D250" s="23" t="n">
-        <x:v>3165.6</x:v>
-      </x:c>
-      <x:c r="E250" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="F250" s="23" t="n">
-        <x:v>3134.8</x:v>
-      </x:c>
-      <x:c r="G250" s="23"/>
-      <x:c r="H250" s="24"/>
-      <x:c r="I250" s="26" t="n">
-        <x:f>ROUND(D250-E250,1)</x:f>
-        <x:v>124.8</x:v>
-      </x:c>
-      <x:c r="J250" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K250" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
-        <x:v>3148.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="D251" s="23" t="n">
-        <x:v>3181.2</x:v>
+        <x:v>3165.6</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
-        <x:v>3074.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>3084.4</x:v>
-      </x:c>
-      <x:c r="G251" s="23" t="n">
-        <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>-50.4</x:v>
-      </x:c>
-      <x:c r="H251" s="24" t="n">
-        <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>-0.016077580706903127</x:v>
-      </x:c>
+        <x:v>3134.8</x:v>
+      </x:c>
+      <x:c r="G251" s="23"/>
+      <x:c r="H251" s="24"/>
       <x:c r="I251" s="26" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>106.8</x:v>
+        <x:v>124.8</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16601,34 +16635,34 @@
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B252" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C252" s="23" t="n">
-        <x:v>3081.2</x:v>
+        <x:v>3148.4</x:v>
       </x:c>
       <x:c r="D252" s="23" t="n">
-        <x:v>3102.6</x:v>
+        <x:v>3181.2</x:v>
       </x:c>
       <x:c r="E252" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074.4</x:v>
       </x:c>
       <x:c r="F252" s="23" t="n">
-        <x:v>3037.8</x:v>
+        <x:v>3084.4</x:v>
       </x:c>
       <x:c r="G252" s="23" t="n">
         <x:f>ROUND(F252-F251,1)</x:f>
-        <x:v>-46.6</x:v>
+        <x:v>-50.4</x:v>
       </x:c>
       <x:c r="H252" s="24" t="n">
         <x:f>IFERROR(F252/F251-1,"")</x:f>
-        <x:v>-0.015108286862923093</x:v>
+        <x:v>-0.016077580706903127</x:v>
       </x:c>
       <x:c r="I252" s="26" t="n">
         <x:f>ROUND(D252-E252,1)</x:f>
-        <x:v>66.4</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J252" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16639,34 +16673,34 @@
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B253" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C253" s="23" t="n">
-        <x:v>3049.8</x:v>
+        <x:v>3081.2</x:v>
       </x:c>
       <x:c r="D253" s="23" t="n">
-        <x:v>3136.6</x:v>
+        <x:v>3102.6</x:v>
       </x:c>
       <x:c r="E253" s="23" t="n">
-        <x:v>3044</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="F253" s="23" t="n">
-        <x:v>3074</x:v>
+        <x:v>3037.8</x:v>
       </x:c>
       <x:c r="G253" s="23" t="n">
         <x:f>ROUND(F253-F252,1)</x:f>
-        <x:v>36.2</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H253" s="24" t="n">
         <x:f>IFERROR(F253/F252-1,"")</x:f>
-        <x:v>0.011916518533148901</x:v>
+        <x:v>-0.015108286862923093</x:v>
       </x:c>
       <x:c r="I253" s="26" t="n">
         <x:f>ROUND(D253-E253,1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J253" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16677,34 +16711,34 @@
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B254" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C254" s="23" t="n">
-        <x:v>3039.4</x:v>
+        <x:v>3049.8</x:v>
       </x:c>
       <x:c r="D254" s="23" t="n">
-        <x:v>3081</x:v>
+        <x:v>3136.6</x:v>
       </x:c>
       <x:c r="E254" s="23" t="n">
-        <x:v>2984</x:v>
+        <x:v>3044</x:v>
       </x:c>
       <x:c r="F254" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074</x:v>
       </x:c>
       <x:c r="G254" s="23" t="n">
         <x:f>ROUND(F254-F253,1)</x:f>
-        <x:v>-37.8</x:v>
+        <x:v>36.2</x:v>
       </x:c>
       <x:c r="H254" s="24" t="n">
         <x:f>IFERROR(F254/F253-1,"")</x:f>
-        <x:v>-0.012296681847755453</x:v>
+        <x:v>0.011916518533148901</x:v>
       </x:c>
       <x:c r="I254" s="26" t="n">
         <x:f>ROUND(D254-E254,1)</x:f>
-        <x:v>97</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="J254" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16715,34 +16749,34 @@
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B255" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C255" s="23" t="n">
-        <x:v>3060.6</x:v>
+        <x:v>3039.4</x:v>
       </x:c>
       <x:c r="D255" s="23" t="n">
-        <x:v>3098</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E255" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="F255" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="G255" s="23" t="n">
         <x:f>ROUND(F255-F254,1)</x:f>
-        <x:v>-16.2</x:v>
+        <x:v>-37.8</x:v>
       </x:c>
       <x:c r="H255" s="24" t="n">
         <x:f>IFERROR(F255/F254-1,"")</x:f>
-        <x:v>-0.005335616889532879</x:v>
+        <x:v>-0.012296681847755453</x:v>
       </x:c>
       <x:c r="I255" s="26" t="n">
         <x:f>ROUND(D255-E255,1)</x:f>
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J255" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16753,110 +16787,110 @@
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B256" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C256" s="23" t="n">
-        <x:v>3049.2</x:v>
+        <x:v>3060.6</x:v>
       </x:c>
       <x:c r="D256" s="23" t="n">
-        <x:v>3086.4</x:v>
+        <x:v>3098</x:v>
       </x:c>
       <x:c r="E256" s="23" t="n">
-        <x:v>3022</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="F256" s="23" t="n">
-        <x:v>3045.4</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="G256" s="23" t="n">
         <x:f>ROUND(F256-F255,1)</x:f>
-        <x:v>25.4</x:v>
+        <x:v>-16.2</x:v>
       </x:c>
       <x:c r="H256" s="24" t="n">
         <x:f>IFERROR(F256/F255-1,"")</x:f>
-        <x:v>0.008410596026490191</x:v>
+        <x:v>-0.005335616889532879</x:v>
       </x:c>
       <x:c r="I256" s="26" t="n">
         <x:f>ROUND(D256-E256,1)</x:f>
-        <x:v>64.4</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J256" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K256" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B257" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C257" s="23" t="n">
-        <x:v>3038</x:v>
+        <x:v>3049.2</x:v>
       </x:c>
       <x:c r="D257" s="23" t="n">
-        <x:v>3056</x:v>
+        <x:v>3086.4</x:v>
       </x:c>
       <x:c r="E257" s="23" t="n">
-        <x:v>2950</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="F257" s="23" t="n">
-        <x:v>2990</x:v>
+        <x:v>3045.4</x:v>
       </x:c>
       <x:c r="G257" s="23" t="n">
         <x:f>ROUND(F257-F256,1)</x:f>
-        <x:v>-55.4</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="H257" s="24" t="n">
         <x:f>IFERROR(F257/F256-1,"")</x:f>
-        <x:v>-0.018191370591712164</x:v>
+        <x:v>0.008410596026490191</x:v>
       </x:c>
       <x:c r="I257" s="26" t="n">
         <x:f>ROUND(D257-E257,1)</x:f>
-        <x:v>106</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="J257" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K257" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B258" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C258" s="23" t="n">
-        <x:v>2965.4</x:v>
+        <x:v>3038</x:v>
       </x:c>
       <x:c r="D258" s="23" t="n">
-        <x:v>2989</x:v>
+        <x:v>3056</x:v>
       </x:c>
       <x:c r="E258" s="23" t="n">
-        <x:v>2912.6</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="F258" s="23" t="n">
-        <x:v>2957</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="G258" s="23" t="n">
         <x:f>ROUND(F258-F257,1)</x:f>
-        <x:v>-33</x:v>
+        <x:v>-55.4</x:v>
       </x:c>
       <x:c r="H258" s="24" t="n">
         <x:f>IFERROR(F258/F257-1,"")</x:f>
-        <x:v>-0.011036789297658833</x:v>
+        <x:v>-0.018191370591712164</x:v>
       </x:c>
       <x:c r="I258" s="26" t="n">
         <x:f>ROUND(D258-E258,1)</x:f>
-        <x:v>76.4</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J258" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16867,34 +16901,34 @@
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B259" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C259" s="23" t="n">
-        <x:v>2953</x:v>
+        <x:v>2965.4</x:v>
       </x:c>
       <x:c r="D259" s="23" t="n">
-        <x:v>2996.6</x:v>
+        <x:v>2989</x:v>
       </x:c>
       <x:c r="E259" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2912.6</x:v>
       </x:c>
       <x:c r="F259" s="23" t="n">
-        <x:v>2898.4</x:v>
+        <x:v>2957</x:v>
       </x:c>
       <x:c r="G259" s="23" t="n">
         <x:f>ROUND(F259-F258,1)</x:f>
-        <x:v>-58.6</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="H259" s="24" t="n">
         <x:f>IFERROR(F259/F258-1,"")</x:f>
-        <x:v>-0.019817382482245516</x:v>
+        <x:v>-0.011036789297658833</x:v>
       </x:c>
       <x:c r="I259" s="26" t="n">
         <x:f>ROUND(D259-E259,1)</x:f>
-        <x:v>100.6</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="J259" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -16905,37 +16939,37 @@
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B260" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C260" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2953</x:v>
       </x:c>
       <x:c r="D260" s="23" t="n">
-        <x:v>2847.6</x:v>
+        <x:v>2996.6</x:v>
       </x:c>
       <x:c r="E260" s="23" t="n">
-        <x:v>2750.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="F260" s="23" t="n">
-        <x:v>2814.4</x:v>
+        <x:v>2898.4</x:v>
       </x:c>
       <x:c r="G260" s="23" t="n">
         <x:f>ROUND(F260-F259,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-58.6</x:v>
       </x:c>
       <x:c r="H260" s="24" t="n">
         <x:f>IFERROR(F260/F259-1,"")</x:f>
-        <x:v>-0.028981507038365995</x:v>
+        <x:v>-0.019817382482245516</x:v>
       </x:c>
       <x:c r="I260" s="26" t="n">
         <x:f>ROUND(D260-E260,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="J260" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K260" s="22" t="n">
         <x:v>5</x:v>
@@ -16943,34 +16977,34 @@
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B261" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C261" s="23" t="n">
-        <x:v>2794.8</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D261" s="23" t="n">
-        <x:v>2865.4</x:v>
+        <x:v>2847.6</x:v>
       </x:c>
       <x:c r="E261" s="23" t="n">
-        <x:v>2780.4</x:v>
+        <x:v>2750.8</x:v>
       </x:c>
       <x:c r="F261" s="23" t="n">
-        <x:v>2804.4</x:v>
+        <x:v>2814.4</x:v>
       </x:c>
       <x:c r="G261" s="23" t="n">
         <x:f>ROUND(F261-F260,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H261" s="24" t="n">
         <x:f>IFERROR(F261/F260-1,"")</x:f>
-        <x:v>-0.0035531552018192025</x:v>
+        <x:v>-0.028981507038365995</x:v>
       </x:c>
       <x:c r="I261" s="26" t="n">
         <x:f>ROUND(D261-E261,1)</x:f>
-        <x:v>85</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J261" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -16981,110 +17015,110 @@
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B262" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C262" s="23" t="n">
-        <x:v>2810.4</x:v>
+        <x:v>2794.8</x:v>
       </x:c>
       <x:c r="D262" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2865.4</x:v>
       </x:c>
       <x:c r="E262" s="23" t="n">
-        <x:v>2797.2</x:v>
+        <x:v>2780.4</x:v>
       </x:c>
       <x:c r="F262" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2804.4</x:v>
       </x:c>
       <x:c r="G262" s="23" t="n">
         <x:f>ROUND(F262-F261,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H262" s="24" t="n">
         <x:f>IFERROR(F262/F261-1,"")</x:f>
-        <x:v>0.02453287690771644</x:v>
+        <x:v>-0.0035531552018192025</x:v>
       </x:c>
       <x:c r="I262" s="26" t="n">
         <x:f>ROUND(D262-E262,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J262" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K262" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B263" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C263" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2810.4</x:v>
       </x:c>
       <x:c r="D263" s="23" t="n">
-        <x:v>2930.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="E263" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2797.2</x:v>
       </x:c>
       <x:c r="F263" s="23" t="n">
-        <x:v>2888</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="G263" s="23" t="n">
         <x:f>ROUND(F263-F262,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>68.8</x:v>
       </x:c>
       <x:c r="H263" s="24" t="n">
         <x:f>IFERROR(F263/F262-1,"")</x:f>
-        <x:v>0.005151051092858294</x:v>
+        <x:v>0.02453287690771644</x:v>
       </x:c>
       <x:c r="I263" s="26" t="n">
         <x:f>ROUND(D263-E263,1)</x:f>
-        <x:v>70.8</x:v>
+        <x:v>98.8</x:v>
       </x:c>
       <x:c r="J263" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K263" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B264" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C264" s="23" t="n">
-        <x:v>2900.8</x:v>
+        <x:v>2864.6</x:v>
       </x:c>
       <x:c r="D264" s="23" t="n">
-        <x:v>2934.2</x:v>
+        <x:v>2930.8</x:v>
       </x:c>
       <x:c r="E264" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="F264" s="23" t="n">
-        <x:v>2929</x:v>
+        <x:v>2888</x:v>
       </x:c>
       <x:c r="G264" s="23" t="n">
         <x:f>ROUND(F264-F263,1)</x:f>
-        <x:v>41</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H264" s="24" t="n">
         <x:f>IFERROR(F264/F263-1,"")</x:f>
-        <x:v>0.014196675900276956</x:v>
-      </x:c>
-      <x:c r="I264" s="23" t="n">
+        <x:v>0.005151051092858294</x:v>
+      </x:c>
+      <x:c r="I264" s="26" t="n">
         <x:f>ROUND(D264-E264,1)</x:f>
-        <x:v>43.2</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="J264" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17095,148 +17129,148 @@
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B265" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C265" s="23" t="n">
-        <x:v>2929.2</x:v>
+        <x:v>2900.8</x:v>
       </x:c>
       <x:c r="D265" s="23" t="n">
-        <x:v>2970</x:v>
+        <x:v>2934.2</x:v>
       </x:c>
       <x:c r="E265" s="23" t="n">
-        <x:v>2917</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F265" s="23" t="n">
-        <x:v>2968.8</x:v>
+        <x:v>2929</x:v>
       </x:c>
       <x:c r="G265" s="23" t="n">
         <x:f>ROUND(F265-F264,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H265" s="24" t="n">
         <x:f>IFERROR(F265/F264-1,"")</x:f>
-        <x:v>0.013588255377261937</x:v>
+        <x:v>0.014196675900276956</x:v>
       </x:c>
       <x:c r="I265" s="23" t="n">
         <x:f>ROUND(D265-E265,1)</x:f>
-        <x:v>53</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J265" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K265" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B266" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C266" s="23" t="n">
-        <x:v>2995.2</x:v>
+        <x:v>2929.2</x:v>
       </x:c>
       <x:c r="D266" s="23" t="n">
-        <x:v>3024.8</x:v>
+        <x:v>2970</x:v>
       </x:c>
       <x:c r="E266" s="23" t="n">
-        <x:v>2969.2</x:v>
+        <x:v>2917</x:v>
       </x:c>
       <x:c r="F266" s="23" t="n">
-        <x:v>2981.6</x:v>
+        <x:v>2968.8</x:v>
       </x:c>
       <x:c r="G266" s="23" t="n">
         <x:f>ROUND(F266-F265,1)</x:f>
-        <x:v>12.8</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="H266" s="24" t="n">
         <x:f>IFERROR(F266/F265-1,"")</x:f>
-        <x:v>0.0043115063325247505</x:v>
+        <x:v>0.013588255377261937</x:v>
       </x:c>
       <x:c r="I266" s="23" t="n">
         <x:f>ROUND(D266-E266,1)</x:f>
-        <x:v>55.6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J266" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K266" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B267" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C267" s="23" t="n">
-        <x:v>2997.6</x:v>
+        <x:v>2995.2</x:v>
       </x:c>
       <x:c r="D267" s="23" t="n">
-        <x:v>3041.8</x:v>
+        <x:v>3024.8</x:v>
       </x:c>
       <x:c r="E267" s="23" t="n">
-        <x:v>2927</x:v>
+        <x:v>2969.2</x:v>
       </x:c>
       <x:c r="F267" s="23" t="n">
-        <x:v>2945</x:v>
+        <x:v>2981.6</x:v>
       </x:c>
       <x:c r="G267" s="23" t="n">
         <x:f>ROUND(F267-F266,1)</x:f>
-        <x:v>-36.6</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="H267" s="24" t="n">
         <x:f>IFERROR(F267/F266-1,"")</x:f>
-        <x:v>-0.012275288435739218</x:v>
-      </x:c>
-      <x:c r="I267" s="26" t="n">
+        <x:v>0.0043115063325247505</x:v>
+      </x:c>
+      <x:c r="I267" s="23" t="n">
         <x:f>ROUND(D267-E267,1)</x:f>
-        <x:v>114.8</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="J267" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K267" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B268" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C268" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2997.6</x:v>
       </x:c>
       <x:c r="D268" s="23" t="n">
-        <x:v>2981.8</x:v>
+        <x:v>3041.8</x:v>
       </x:c>
       <x:c r="E268" s="23" t="n">
-        <x:v>2893.2</x:v>
+        <x:v>2927</x:v>
       </x:c>
       <x:c r="F268" s="23" t="n">
-        <x:v>2899.2</x:v>
+        <x:v>2945</x:v>
       </x:c>
       <x:c r="G268" s="23" t="n">
         <x:f>ROUND(F268-F267,1)</x:f>
-        <x:v>-45.8</x:v>
+        <x:v>-36.6</x:v>
       </x:c>
       <x:c r="H268" s="24" t="n">
         <x:f>IFERROR(F268/F267-1,"")</x:f>
-        <x:v>-0.015551782682512783</x:v>
+        <x:v>-0.012275288435739218</x:v>
       </x:c>
       <x:c r="I268" s="26" t="n">
         <x:f>ROUND(D268-E268,1)</x:f>
-        <x:v>88.6</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="J268" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17247,34 +17281,34 @@
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B269" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C269" s="23" t="n">
-        <x:v>2910.8</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D269" s="23" t="n">
-        <x:v>2960</x:v>
+        <x:v>2981.8</x:v>
       </x:c>
       <x:c r="E269" s="23" t="n">
-        <x:v>2871</x:v>
+        <x:v>2893.2</x:v>
       </x:c>
       <x:c r="F269" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2899.2</x:v>
       </x:c>
       <x:c r="G269" s="23" t="n">
         <x:f>ROUND(F269-F268,1)</x:f>
-        <x:v>1.4</x:v>
+        <x:v>-45.8</x:v>
       </x:c>
       <x:c r="H269" s="24" t="n">
         <x:f>IFERROR(F269/F268-1,"")</x:f>
-        <x:v>0.0004828918322297149</x:v>
+        <x:v>-0.015551782682512783</x:v>
       </x:c>
       <x:c r="I269" s="26" t="n">
         <x:f>ROUND(D269-E269,1)</x:f>
-        <x:v>89</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="J269" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17285,34 +17319,34 @@
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B270" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C270" s="23" t="n">
-        <x:v>2901</x:v>
+        <x:v>2910.8</x:v>
       </x:c>
       <x:c r="D270" s="23" t="n">
-        <x:v>2924.2</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="E270" s="23" t="n">
-        <x:v>2841.6</x:v>
+        <x:v>2871</x:v>
       </x:c>
       <x:c r="F270" s="23" t="n">
-        <x:v>2844</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="G270" s="23" t="n">
         <x:f>ROUND(F270-F269,1)</x:f>
-        <x:v>-56.6</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H270" s="24" t="n">
         <x:f>IFERROR(F270/F269-1,"")</x:f>
-        <x:v>-0.019513204164655518</x:v>
+        <x:v>0.0004828918322297149</x:v>
       </x:c>
       <x:c r="I270" s="26" t="n">
         <x:f>ROUND(D270-E270,1)</x:f>
-        <x:v>82.6</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J270" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17323,34 +17357,34 @@
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B271" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C271" s="23" t="n">
-        <x:v>2808.4</x:v>
+        <x:v>2901</x:v>
       </x:c>
       <x:c r="D271" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2924.2</x:v>
       </x:c>
       <x:c r="E271" s="23" t="n">
-        <x:v>2791.2</x:v>
+        <x:v>2841.6</x:v>
       </x:c>
       <x:c r="F271" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G271" s="23" t="n">
         <x:f>ROUND(F271-F270,1)</x:f>
-        <x:v>53.2</x:v>
+        <x:v>-56.6</x:v>
       </x:c>
       <x:c r="H271" s="24" t="n">
         <x:f>IFERROR(F271/F270-1,"")</x:f>
-        <x:v>0.01870604781997187</x:v>
+        <x:v>-0.019513204164655518</x:v>
       </x:c>
       <x:c r="I271" s="26" t="n">
         <x:f>ROUND(D271-E271,1)</x:f>
-        <x:v>111.4</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J271" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17361,113 +17395,113 @@
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B272" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C272" s="23" t="n">
-        <x:v>2926.2</x:v>
+        <x:v>2808.4</x:v>
       </x:c>
       <x:c r="D272" s="23" t="n">
-        <x:v>2954.6</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="E272" s="23" t="n">
-        <x:v>2903.4</x:v>
+        <x:v>2791.2</x:v>
       </x:c>
       <x:c r="F272" s="23" t="n">
-        <x:v>2941</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G272" s="23" t="n">
         <x:f>ROUND(F272-F271,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="H272" s="24" t="n">
         <x:f>IFERROR(F272/F271-1,"")</x:f>
-        <x:v>0.01511804500897429</x:v>
-      </x:c>
-      <x:c r="I272" s="23" t="n">
+        <x:v>0.01870604781997187</x:v>
+      </x:c>
+      <x:c r="I272" s="26" t="n">
         <x:f>ROUND(D272-E272,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="J272" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K272" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B273" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C273" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2926.2</x:v>
       </x:c>
       <x:c r="D273" s="23" t="n">
-        <x:v>2996</x:v>
+        <x:v>2954.6</x:v>
       </x:c>
       <x:c r="E273" s="23" t="n">
-        <x:v>2834.8</x:v>
+        <x:v>2903.4</x:v>
       </x:c>
       <x:c r="F273" s="23" t="n">
-        <x:v>2859</x:v>
+        <x:v>2941</x:v>
       </x:c>
       <x:c r="G273" s="23" t="n">
         <x:f>ROUND(F273-F272,1)</x:f>
-        <x:v>-82</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="H273" s="24" t="n">
         <x:f>IFERROR(F273/F272-1,"")</x:f>
-        <x:v>-0.02788167290037402</x:v>
-      </x:c>
-      <x:c r="I273" s="26" t="n">
+        <x:v>0.01511804500897429</x:v>
+      </x:c>
+      <x:c r="I273" s="23" t="n">
         <x:f>ROUND(D273-E273,1)</x:f>
-        <x:v>161.2</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J273" s="22" t="str">
-        <x:v>IH2606/IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K273" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B274" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C274" s="23" t="n">
-        <x:v>2870</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D274" s="23" t="n">
-        <x:v>2976</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="E274" s="23" t="n">
-        <x:v>2861.8</x:v>
+        <x:v>2834.8</x:v>
       </x:c>
       <x:c r="F274" s="23" t="n">
-        <x:v>2886.6</x:v>
+        <x:v>2859</x:v>
       </x:c>
       <x:c r="G274" s="23" t="n">
         <x:f>ROUND(F274-F273,1)</x:f>
-        <x:v>27.6</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="H274" s="24" t="n">
         <x:f>IFERROR(F274/F273-1,"")</x:f>
-        <x:v>0.009653725078698772</x:v>
+        <x:v>-0.02788167290037402</x:v>
       </x:c>
       <x:c r="I274" s="26" t="n">
         <x:f>ROUND(D274-E274,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>161.2</x:v>
       </x:c>
       <x:c r="J274" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606/IH2609</x:v>
       </x:c>
       <x:c r="K274" s="22" t="n">
         <x:v>5</x:v>
@@ -17475,34 +17509,34 @@
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B275" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C275" s="23" t="n">
-        <x:v>2899</x:v>
+        <x:v>2870</x:v>
       </x:c>
       <x:c r="D275" s="23" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="E275" s="23" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2861.8</x:v>
       </x:c>
       <x:c r="F275" s="23" t="n">
-        <x:v>2910.2</x:v>
+        <x:v>2886.6</x:v>
       </x:c>
       <x:c r="G275" s="23" t="n">
         <x:f>ROUND(F275-F274,1)</x:f>
-        <x:v>23.6</x:v>
+        <x:v>27.6</x:v>
       </x:c>
       <x:c r="H275" s="24" t="n">
         <x:f>IFERROR(F275/F274-1,"")</x:f>
-        <x:v>0.008175708445922414</x:v>
+        <x:v>0.009653725078698772</x:v>
       </x:c>
       <x:c r="I275" s="26" t="n">
         <x:f>ROUND(D275-E275,1)</x:f>
-        <x:v>121.4</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="J275" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17513,34 +17547,34 @@
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B276" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C276" s="23" t="n">
-        <x:v>2895.8</x:v>
+        <x:v>2899</x:v>
       </x:c>
       <x:c r="D276" s="23" t="n">
-        <x:v>2924</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="E276" s="23" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="F276" s="23" t="n">
-        <x:v>2796.4</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="G276" s="23" t="n">
         <x:f>ROUND(F276-F275,1)</x:f>
-        <x:v>-113.8</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="H276" s="24" t="n">
         <x:f>IFERROR(F276/F275-1,"")</x:f>
-        <x:v>-0.039103841660366845</x:v>
+        <x:v>0.008175708445922414</x:v>
       </x:c>
       <x:c r="I276" s="26" t="n">
         <x:f>ROUND(D276-E276,1)</x:f>
-        <x:v>141.4</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J276" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17551,34 +17585,34 @@
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B277" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C277" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2895.8</x:v>
       </x:c>
       <x:c r="D277" s="23" t="n">
-        <x:v>2978</x:v>
+        <x:v>2924</x:v>
       </x:c>
       <x:c r="E277" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="F277" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2796.4</x:v>
       </x:c>
       <x:c r="G277" s="23" t="n">
         <x:f>ROUND(F277-F276,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>-113.8</x:v>
       </x:c>
       <x:c r="H277" s="24" t="n">
         <x:f>IFERROR(F277/F276-1,"")</x:f>
-        <x:v>0.040623658990130096</x:v>
+        <x:v>-0.039103841660366845</x:v>
       </x:c>
       <x:c r="I277" s="26" t="n">
         <x:f>ROUND(D277-E277,1)</x:f>
-        <x:v>158</x:v>
+        <x:v>141.4</x:v>
       </x:c>
       <x:c r="J277" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17589,34 +17623,34 @@
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B278" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C278" s="23" t="n">
-        <x:v>2929.6</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="D278" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E278" s="23" t="n">
-        <x:v>2847.2</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="F278" s="23" t="n">
-        <x:v>2891.8</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G278" s="23" t="n">
         <x:f>ROUND(F278-F277,1)</x:f>
-        <x:v>-18.2</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="H278" s="24" t="n">
         <x:f>IFERROR(F278/F277-1,"")</x:f>
-        <x:v>-0.006254295532646004</x:v>
+        <x:v>0.040623658990130096</x:v>
       </x:c>
       <x:c r="I278" s="26" t="n">
         <x:f>ROUND(D278-E278,1)</x:f>
-        <x:v>82.8</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J278" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17627,34 +17661,34 @@
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
-        <x:v>2882.4</x:v>
+        <x:v>2929.6</x:v>
       </x:c>
       <x:c r="D279" s="23" t="n">
-        <x:v>2930.6</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2847.2</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2891.8</x:v>
       </x:c>
       <x:c r="G279" s="23" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>38.2</x:v>
+        <x:v>-18.2</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>0.013209765543951812</x:v>
+        <x:v>-0.006254295532646004</x:v>
       </x:c>
       <x:c r="I279" s="26" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>84.8</x:v>
+        <x:v>82.8</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17665,34 +17699,34 @@
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B280" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C280" s="23" t="n">
+        <x:v>2882.4</x:v>
+      </x:c>
+      <x:c r="D280" s="23" t="n">
+        <x:v>2930.6</x:v>
+      </x:c>
+      <x:c r="E280" s="23" t="n">
+        <x:v>2845.8</x:v>
+      </x:c>
+      <x:c r="F280" s="23" t="n">
         <x:v>2930</x:v>
-      </x:c>
-      <x:c r="D280" s="23" t="n">
-        <x:v>2949.6</x:v>
-      </x:c>
-      <x:c r="E280" s="23" t="n">
-        <x:v>2877</x:v>
-      </x:c>
-      <x:c r="F280" s="23" t="n">
-        <x:v>2890</x:v>
       </x:c>
       <x:c r="G280" s="23" t="n">
         <x:f>ROUND(F280-F279,1)</x:f>
-        <x:v>-40</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="H280" s="24" t="n">
         <x:f>IFERROR(F280/F279-1,"")</x:f>
-        <x:v>-0.013651877133105783</x:v>
+        <x:v>0.013209765543951812</x:v>
       </x:c>
       <x:c r="I280" s="26" t="n">
         <x:f>ROUND(D280-E280,1)</x:f>
-        <x:v>72.6</x:v>
+        <x:v>84.8</x:v>
       </x:c>
       <x:c r="J280" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17703,34 +17737,34 @@
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B281" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C281" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="D281" s="23" t="n">
-        <x:v>2921.2</x:v>
+        <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E281" s="23" t="n">
-        <x:v>2843</x:v>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="F281" s="23" t="n">
-        <x:v>2861</x:v>
+        <x:v>2890</x:v>
       </x:c>
       <x:c r="G281" s="23" t="n">
         <x:f>ROUND(F281-F280,1)</x:f>
-        <x:v>-29</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="H281" s="24" t="n">
         <x:f>IFERROR(F281/F280-1,"")</x:f>
-        <x:v>-0.01003460207612461</x:v>
+        <x:v>-0.013651877133105783</x:v>
       </x:c>
       <x:c r="I281" s="26" t="n">
         <x:f>ROUND(D281-E281,1)</x:f>
-        <x:v>78.2</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="J281" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17741,34 +17775,34 @@
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B282" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C282" s="23" t="n">
-        <x:v>2856.4</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D282" s="23" t="n">
-        <x:v>2918.2</x:v>
+        <x:v>2921.2</x:v>
       </x:c>
       <x:c r="E282" s="23" t="n">
-        <x:v>2837.4</x:v>
+        <x:v>2843</x:v>
       </x:c>
       <x:c r="F282" s="23" t="n">
-        <x:v>2911.4</x:v>
+        <x:v>2861</x:v>
       </x:c>
       <x:c r="G282" s="23" t="n">
         <x:f>ROUND(F282-F281,1)</x:f>
-        <x:v>50.4</x:v>
+        <x:v>-29</x:v>
       </x:c>
       <x:c r="H282" s="24" t="n">
         <x:f>IFERROR(F282/F281-1,"")</x:f>
-        <x:v>0.01761621810555747</x:v>
+        <x:v>-0.01003460207612461</x:v>
       </x:c>
       <x:c r="I282" s="26" t="n">
         <x:f>ROUND(D282-E282,1)</x:f>
-        <x:v>80.8</x:v>
+        <x:v>78.2</x:v>
       </x:c>
       <x:c r="J282" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17779,34 +17813,34 @@
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B283" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C283" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2856.4</x:v>
       </x:c>
       <x:c r="D283" s="23" t="n">
-        <x:v>2949.4</x:v>
+        <x:v>2918.2</x:v>
       </x:c>
       <x:c r="E283" s="23" t="n">
-        <x:v>2877.6</x:v>
+        <x:v>2837.4</x:v>
       </x:c>
       <x:c r="F283" s="23" t="n">
-        <x:v>2915.8</x:v>
+        <x:v>2911.4</x:v>
       </x:c>
       <x:c r="G283" s="23" t="n">
         <x:f>ROUND(F283-F282,1)</x:f>
-        <x:v>4.4</x:v>
+        <x:v>50.4</x:v>
       </x:c>
       <x:c r="H283" s="24" t="n">
         <x:f>IFERROR(F283/F282-1,"")</x:f>
-        <x:v>0.0015113004053033396</x:v>
+        <x:v>0.01761621810555747</x:v>
       </x:c>
       <x:c r="I283" s="26" t="n">
         <x:f>ROUND(D283-E283,1)</x:f>
-        <x:v>71.8</x:v>
+        <x:v>80.8</x:v>
       </x:c>
       <x:c r="J283" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17817,34 +17851,34 @@
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B284" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C284" s="23" t="n">
-        <x:v>2923.2</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D284" s="23" t="n">
-        <x:v>2931.4</x:v>
+        <x:v>2949.4</x:v>
       </x:c>
       <x:c r="E284" s="23" t="n">
-        <x:v>2836.8</x:v>
+        <x:v>2877.6</x:v>
       </x:c>
       <x:c r="F284" s="23" t="n">
-        <x:v>2867</x:v>
+        <x:v>2915.8</x:v>
       </x:c>
       <x:c r="G284" s="23" t="n">
         <x:f>ROUND(F284-F283,1)</x:f>
-        <x:v>-48.8</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="H284" s="24" t="n">
         <x:f>IFERROR(F284/F283-1,"")</x:f>
-        <x:v>-0.01673640167364021</x:v>
+        <x:v>0.0015113004053033396</x:v>
       </x:c>
       <x:c r="I284" s="26" t="n">
         <x:f>ROUND(D284-E284,1)</x:f>
-        <x:v>94.6</x:v>
+        <x:v>71.8</x:v>
       </x:c>
       <x:c r="J284" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17855,192 +17889,192 @@
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B285" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C285" s="23" t="n">
-        <x:v>2849.2</x:v>
+        <x:v>2923.2</x:v>
       </x:c>
       <x:c r="D285" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2931.4</x:v>
       </x:c>
       <x:c r="E285" s="23" t="n">
-        <x:v>2843.8</x:v>
+        <x:v>2836.8</x:v>
       </x:c>
       <x:c r="F285" s="23" t="n">
-        <x:v>2860.4</x:v>
+        <x:v>2867</x:v>
       </x:c>
       <x:c r="G285" s="23" t="n">
         <x:f>ROUND(F285-F284,1)</x:f>
-        <x:v>-6.6</x:v>
+        <x:v>-48.8</x:v>
       </x:c>
       <x:c r="H285" s="24" t="n">
         <x:f>IFERROR(F285/F284-1,"")</x:f>
-        <x:v>-0.002302057900244181</x:v>
-      </x:c>
-      <x:c r="I285" s="23" t="n">
+        <x:v>-0.01673640167364021</x:v>
+      </x:c>
+      <x:c r="I285" s="26" t="n">
         <x:f>ROUND(D285-E285,1)</x:f>
-        <x:v>20.8</x:v>
+        <x:v>94.6</x:v>
       </x:c>
       <x:c r="J285" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K285" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" s="22" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B286" s="22" t="str">
+        <x:v>9月14日</x:v>
+      </x:c>
+      <x:c r="C286" s="23" t="n">
+        <x:v>2849.2</x:v>
+      </x:c>
+      <x:c r="D286" s="23" t="n">
+        <x:v>2864.6</x:v>
+      </x:c>
+      <x:c r="E286" s="23" t="n">
+        <x:v>2843.8</x:v>
+      </x:c>
+      <x:c r="F286" s="23" t="n">
+        <x:v>2860.4</x:v>
+      </x:c>
+      <x:c r="G286" s="23" t="n">
+        <x:f>ROUND(F286-F285,1)</x:f>
+        <x:v>-6.6</x:v>
+      </x:c>
+      <x:c r="H286" s="24" t="n">
+        <x:f>IFERROR(F286/F285-1,"")</x:f>
+        <x:v>-0.002302057900244181</x:v>
+      </x:c>
+      <x:c r="I286" s="23" t="n">
+        <x:f>ROUND(D286-E286,1)</x:f>
+        <x:v>20.8</x:v>
+      </x:c>
+      <x:c r="J286" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K286" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="286">
-      <x:c r="A286" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B286" s="30" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C286" s="30"/>
-      <x:c r="D286" s="30"/>
-      <x:c r="E286" s="30"/>
-      <x:c r="F286" s="30"/>
-      <x:c r="G286" s="30"/>
-      <x:c r="H286" s="30"/>
-      <x:c r="I286" s="32" t="n">
-        <x:f>ROUND(SUM(I250:I285),1)</x:f>
-        <x:v>3236.4</x:v>
-      </x:c>
-      <x:c r="J286" s="30"/>
-      <x:c r="K286" s="30"/>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B287" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B287" s="30" t="n">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="C287" s="30"/>
       <x:c r="D287" s="30"/>
       <x:c r="E287" s="30"/>
       <x:c r="F287" s="30"/>
       <x:c r="G287" s="30"/>
       <x:c r="H287" s="30"/>
-      <x:c r="I287" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I250:I285),0),1)</x:f>
-        <x:v>89.9</x:v>
+      <x:c r="I287" s="32" t="n">
+        <x:f>ROUND(SUM(I251:I286),1)</x:f>
+        <x:v>3236.4</x:v>
       </x:c>
       <x:c r="J287" s="30"/>
       <x:c r="K287" s="30"/>
     </x:row>
-    <x:row r="289">
-      <x:c r="A289" s="17" t="str">
+    <x:row r="288">
+      <x:c r="A288" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B288" s="30"/>
+      <x:c r="C288" s="30"/>
+      <x:c r="D288" s="30"/>
+      <x:c r="E288" s="30"/>
+      <x:c r="F288" s="30"/>
+      <x:c r="G288" s="30"/>
+      <x:c r="H288" s="30"/>
+      <x:c r="I288" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I251:I286),0),1)</x:f>
+        <x:v>89.9</x:v>
+      </x:c>
+      <x:c r="J288" s="30"/>
+      <x:c r="K288" s="30"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" s="17" t="str">
         <x:v>碳酸锂2609</x:v>
       </x:c>
-      <x:c r="B289" s="17"/>
-      <x:c r="C289" s="17"/>
-      <x:c r="D289" s="17"/>
-      <x:c r="E289" s="17"/>
-      <x:c r="F289" s="17"/>
-      <x:c r="G289" s="17"/>
-      <x:c r="H289" s="17"/>
-      <x:c r="I289" s="17"/>
-      <x:c r="J289" s="17"/>
-      <x:c r="K289" s="17"/>
-    </x:row>
-    <x:row r="290">
-      <x:c r="A290" s="20" t="str">
+      <x:c r="B290" s="17"/>
+      <x:c r="C290" s="17"/>
+      <x:c r="D290" s="17"/>
+      <x:c r="E290" s="17"/>
+      <x:c r="F290" s="17"/>
+      <x:c r="G290" s="17"/>
+      <x:c r="H290" s="17"/>
+      <x:c r="I290" s="17"/>
+      <x:c r="J290" s="17"/>
+      <x:c r="K290" s="17"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B290" s="20" t="str">
+      <x:c r="B291" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C290" s="20" t="str">
+      <x:c r="C291" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D290" s="20" t="str">
+      <x:c r="D291" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E290" s="20" t="str">
+      <x:c r="E291" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F290" s="20" t="str">
+      <x:c r="F291" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G290" s="20" t="str">
+      <x:c r="G291" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H290" s="20" t="str">
+      <x:c r="H291" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I290" s="20" t="str">
+      <x:c r="I291" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J290" s="20" t="str">
+      <x:c r="J291" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K290" s="20" t="str">
+      <x:c r="K291" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="291">
-      <x:c r="A291" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B291" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C291" s="23" t="n">
-        <x:v>126360</x:v>
-      </x:c>
-      <x:c r="D291" s="23" t="n">
-        <x:v>150760</x:v>
-      </x:c>
-      <x:c r="E291" s="23" t="n">
-        <x:v>125160</x:v>
-      </x:c>
-      <x:c r="F291" s="23" t="n">
-        <x:v>145380</x:v>
-      </x:c>
-      <x:c r="G291" s="23"/>
-      <x:c r="H291" s="24"/>
-      <x:c r="I291" s="26" t="n">
-        <x:f>ROUND(D291-E291,1)</x:f>
-        <x:v>25600</x:v>
-      </x:c>
-      <x:c r="J291" s="22" t="str">
-        <x:v>LC2609</x:v>
-      </x:c>
-      <x:c r="K291" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B292" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C292" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>126360</x:v>
       </x:c>
       <x:c r="D292" s="23" t="n">
-        <x:v>176120</x:v>
+        <x:v>150760</x:v>
       </x:c>
       <x:c r="E292" s="23" t="n">
-        <x:v>147740</x:v>
+        <x:v>125160</x:v>
       </x:c>
       <x:c r="F292" s="23" t="n">
-        <x:v>147740</x:v>
-      </x:c>
-      <x:c r="G292" s="28" t="n">
-        <x:f>ROUND(F292-F291,1)</x:f>
-        <x:v>2360</x:v>
-      </x:c>
-      <x:c r="H292" s="24" t="n">
-        <x:f>IFERROR(F292/F291-1,"")</x:f>
-        <x:v>0.016233319576282934</x:v>
-      </x:c>
+        <x:v>145380</x:v>
+      </x:c>
+      <x:c r="G292" s="23"/>
+      <x:c r="H292" s="24"/>
       <x:c r="I292" s="26" t="n">
         <x:f>ROUND(D292-E292,1)</x:f>
-        <x:v>28380</x:v>
+        <x:v>25600</x:v>
       </x:c>
       <x:c r="J292" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18051,34 +18085,34 @@
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B293" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
-        <x:v>150720</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="D293" s="23" t="n">
-        <x:v>183780</x:v>
+        <x:v>176120</x:v>
       </x:c>
       <x:c r="E293" s="23" t="n">
-        <x:v>143820</x:v>
+        <x:v>147740</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>183380</x:v>
+        <x:v>147740</x:v>
       </x:c>
       <x:c r="G293" s="28" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>35640</x:v>
+        <x:v>2360</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>0.24123460132665486</x:v>
+        <x:v>0.016233319576282934</x:v>
       </x:c>
       <x:c r="I293" s="26" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
-        <x:v>39960</x:v>
+        <x:v>28380</x:v>
       </x:c>
       <x:c r="J293" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18089,34 +18123,34 @@
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B294" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C294" s="23" t="n">
-        <x:v>187000</x:v>
+        <x:v>150720</x:v>
       </x:c>
       <x:c r="D294" s="23" t="n">
-        <x:v>190600</x:v>
+        <x:v>183780</x:v>
       </x:c>
       <x:c r="E294" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>143820</x:v>
       </x:c>
       <x:c r="F294" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>183380</x:v>
       </x:c>
       <x:c r="G294" s="28" t="n">
         <x:f>ROUND(F294-F293,1)</x:f>
-        <x:v>-34820</x:v>
+        <x:v>35640</x:v>
       </x:c>
       <x:c r="H294" s="24" t="n">
         <x:f>IFERROR(F294/F293-1,"")</x:f>
-        <x:v>-0.18987893990620575</x:v>
+        <x:v>0.24123460132665486</x:v>
       </x:c>
       <x:c r="I294" s="26" t="n">
         <x:f>ROUND(D294-E294,1)</x:f>
-        <x:v>42040</x:v>
+        <x:v>39960</x:v>
       </x:c>
       <x:c r="J294" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18127,34 +18161,34 @@
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B295" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
-        <x:v>148040</x:v>
+        <x:v>187000</x:v>
       </x:c>
       <x:c r="D295" s="23" t="n">
-        <x:v>153200</x:v>
+        <x:v>190600</x:v>
       </x:c>
       <x:c r="E295" s="23" t="n">
-        <x:v>124480</x:v>
+        <x:v>148560</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>148560</x:v>
       </x:c>
       <x:c r="G295" s="28" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>-15060</x:v>
+        <x:v>-34820</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>-0.10137318255250405</x:v>
+        <x:v>-0.18987893990620575</x:v>
       </x:c>
       <x:c r="I295" s="26" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>28720</x:v>
+        <x:v>42040</x:v>
       </x:c>
       <x:c r="J295" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18165,34 +18199,34 @@
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B296" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C296" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>148040</x:v>
       </x:c>
       <x:c r="D296" s="23" t="n">
-        <x:v>153700</x:v>
+        <x:v>153200</x:v>
       </x:c>
       <x:c r="E296" s="23" t="n">
+        <x:v>124480</x:v>
+      </x:c>
+      <x:c r="F296" s="23" t="n">
         <x:v>133500</x:v>
-      </x:c>
-      <x:c r="F296" s="23" t="n">
-        <x:v>153500</x:v>
       </x:c>
       <x:c r="G296" s="28" t="n">
         <x:f>ROUND(F296-F295,1)</x:f>
-        <x:v>20000</x:v>
+        <x:v>-15060</x:v>
       </x:c>
       <x:c r="H296" s="24" t="n">
         <x:f>IFERROR(F296/F295-1,"")</x:f>
-        <x:v>0.14981273408239693</x:v>
+        <x:v>-0.10137318255250405</x:v>
       </x:c>
       <x:c r="I296" s="26" t="n">
         <x:f>ROUND(D296-E296,1)</x:f>
-        <x:v>20200</x:v>
+        <x:v>28720</x:v>
       </x:c>
       <x:c r="J296" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18203,110 +18237,110 @@
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B297" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C297" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="D297" s="23" t="n">
-        <x:v>186900</x:v>
+        <x:v>153700</x:v>
       </x:c>
       <x:c r="E297" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>133500</x:v>
       </x:c>
       <x:c r="F297" s="23" t="n">
-        <x:v>177200</x:v>
+        <x:v>153500</x:v>
       </x:c>
       <x:c r="G297" s="28" t="n">
         <x:f>ROUND(F297-F296,1)</x:f>
-        <x:v>23700</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="H297" s="24" t="n">
         <x:f>IFERROR(F297/F296-1,"")</x:f>
-        <x:v>0.15439739413680775</x:v>
+        <x:v>0.14981273408239693</x:v>
       </x:c>
       <x:c r="I297" s="26" t="n">
         <x:f>ROUND(D297-E297,1)</x:f>
-        <x:v>28560</x:v>
+        <x:v>20200</x:v>
       </x:c>
       <x:c r="J297" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K297" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B298" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C298" s="23" t="n">
-        <x:v>180000</x:v>
+        <x:v>158340</x:v>
       </x:c>
       <x:c r="D298" s="23" t="n">
-        <x:v>180060</x:v>
+        <x:v>186900</x:v>
       </x:c>
       <x:c r="E298" s="23" t="n">
-        <x:v>146040</x:v>
+        <x:v>158340</x:v>
       </x:c>
       <x:c r="F298" s="23" t="n">
-        <x:v>156700</x:v>
+        <x:v>177200</x:v>
       </x:c>
       <x:c r="G298" s="28" t="n">
         <x:f>ROUND(F298-F297,1)</x:f>
-        <x:v>-20500</x:v>
+        <x:v>23700</x:v>
       </x:c>
       <x:c r="H298" s="24" t="n">
         <x:f>IFERROR(F298/F297-1,"")</x:f>
-        <x:v>-0.11568848758465011</x:v>
+        <x:v>0.15439739413680775</x:v>
       </x:c>
       <x:c r="I298" s="26" t="n">
         <x:f>ROUND(D298-E298,1)</x:f>
-        <x:v>34020</x:v>
+        <x:v>28560</x:v>
       </x:c>
       <x:c r="J298" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K298" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B299" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C299" s="23" t="n">
-        <x:v>149000</x:v>
+        <x:v>180000</x:v>
       </x:c>
       <x:c r="D299" s="23" t="n">
-        <x:v>167400</x:v>
+        <x:v>180060</x:v>
       </x:c>
       <x:c r="E299" s="23" t="n">
-        <x:v>142600</x:v>
+        <x:v>146040</x:v>
       </x:c>
       <x:c r="F299" s="23" t="n">
-        <x:v>152100</x:v>
+        <x:v>156700</x:v>
       </x:c>
       <x:c r="G299" s="28" t="n">
         <x:f>ROUND(F299-F298,1)</x:f>
-        <x:v>-4600</x:v>
+        <x:v>-20500</x:v>
       </x:c>
       <x:c r="H299" s="24" t="n">
         <x:f>IFERROR(F299/F298-1,"")</x:f>
-        <x:v>-0.02935545628589664</x:v>
+        <x:v>-0.11568848758465011</x:v>
       </x:c>
       <x:c r="I299" s="26" t="n">
         <x:f>ROUND(D299-E299,1)</x:f>
-        <x:v>24800</x:v>
+        <x:v>34020</x:v>
       </x:c>
       <x:c r="J299" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18317,34 +18351,34 @@
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B300" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C300" s="23" t="n">
-        <x:v>150880</x:v>
+        <x:v>149000</x:v>
       </x:c>
       <x:c r="D300" s="23" t="n">
-        <x:v>160800</x:v>
+        <x:v>167400</x:v>
       </x:c>
       <x:c r="E300" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>142600</x:v>
       </x:c>
       <x:c r="F300" s="23" t="n">
-        <x:v>143520</x:v>
+        <x:v>152100</x:v>
       </x:c>
       <x:c r="G300" s="28" t="n">
         <x:f>ROUND(F300-F299,1)</x:f>
-        <x:v>-8580</x:v>
+        <x:v>-4600</x:v>
       </x:c>
       <x:c r="H300" s="24" t="n">
         <x:f>IFERROR(F300/F299-1,"")</x:f>
-        <x:v>-0.05641025641025643</x:v>
+        <x:v>-0.02935545628589664</x:v>
       </x:c>
       <x:c r="I300" s="26" t="n">
         <x:f>ROUND(D300-E300,1)</x:f>
-        <x:v>20800</x:v>
+        <x:v>24800</x:v>
       </x:c>
       <x:c r="J300" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18355,34 +18389,34 @@
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B301" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C301" s="23" t="n">
-        <x:v>141220</x:v>
+        <x:v>150880</x:v>
       </x:c>
       <x:c r="D301" s="23" t="n">
-        <x:v>172220</x:v>
+        <x:v>160800</x:v>
       </x:c>
       <x:c r="E301" s="23" t="n">
-        <x:v>140020</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="F301" s="23" t="n">
-        <x:v>169400</x:v>
+        <x:v>143520</x:v>
       </x:c>
       <x:c r="G301" s="28" t="n">
         <x:f>ROUND(F301-F300,1)</x:f>
-        <x:v>25880</x:v>
+        <x:v>-8580</x:v>
       </x:c>
       <x:c r="H301" s="24" t="n">
         <x:f>IFERROR(F301/F300-1,"")</x:f>
-        <x:v>0.18032329988851736</x:v>
+        <x:v>-0.05641025641025643</x:v>
       </x:c>
       <x:c r="I301" s="26" t="n">
         <x:f>ROUND(D301-E301,1)</x:f>
-        <x:v>32200</x:v>
+        <x:v>20800</x:v>
       </x:c>
       <x:c r="J301" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18393,34 +18427,34 @@
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B302" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C302" s="23" t="n">
-        <x:v>170000</x:v>
+        <x:v>141220</x:v>
       </x:c>
       <x:c r="D302" s="23" t="n">
-        <x:v>175000</x:v>
+        <x:v>172220</x:v>
       </x:c>
       <x:c r="E302" s="23" t="n">
-        <x:v>154560</x:v>
+        <x:v>140020</x:v>
       </x:c>
       <x:c r="F302" s="23" t="n">
-        <x:v>157860</x:v>
+        <x:v>169400</x:v>
       </x:c>
       <x:c r="G302" s="28" t="n">
         <x:f>ROUND(F302-F301,1)</x:f>
-        <x:v>-11540</x:v>
+        <x:v>25880</x:v>
       </x:c>
       <x:c r="H302" s="24" t="n">
         <x:f>IFERROR(F302/F301-1,"")</x:f>
-        <x:v>-0.06812278630460444</x:v>
+        <x:v>0.18032329988851736</x:v>
       </x:c>
       <x:c r="I302" s="26" t="n">
         <x:f>ROUND(D302-E302,1)</x:f>
-        <x:v>20440</x:v>
+        <x:v>32200</x:v>
       </x:c>
       <x:c r="J302" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18431,110 +18465,110 @@
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B303" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C303" s="23" t="n">
-        <x:v>158440</x:v>
+        <x:v>170000</x:v>
       </x:c>
       <x:c r="D303" s="23" t="n">
-        <x:v>165500</x:v>
+        <x:v>175000</x:v>
       </x:c>
       <x:c r="E303" s="23" t="n">
-        <x:v>152500</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="F303" s="23" t="n">
-        <x:v>157600</x:v>
+        <x:v>157860</x:v>
       </x:c>
       <x:c r="G303" s="28" t="n">
         <x:f>ROUND(F303-F302,1)</x:f>
-        <x:v>-260</x:v>
+        <x:v>-11540</x:v>
       </x:c>
       <x:c r="H303" s="24" t="n">
         <x:f>IFERROR(F303/F302-1,"")</x:f>
-        <x:v>-0.0016470290130495835</x:v>
+        <x:v>-0.06812278630460444</x:v>
       </x:c>
       <x:c r="I303" s="26" t="n">
         <x:f>ROUND(D303-E303,1)</x:f>
-        <x:v>13000</x:v>
+        <x:v>20440</x:v>
       </x:c>
       <x:c r="J303" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K303" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B304" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C304" s="23" t="n">
-        <x:v>155020</x:v>
+        <x:v>158440</x:v>
       </x:c>
       <x:c r="D304" s="23" t="n">
-        <x:v>178000</x:v>
+        <x:v>165500</x:v>
       </x:c>
       <x:c r="E304" s="23" t="n">
-        <x:v>154780</x:v>
+        <x:v>152500</x:v>
       </x:c>
       <x:c r="F304" s="23" t="n">
-        <x:v>177560</x:v>
+        <x:v>157600</x:v>
       </x:c>
       <x:c r="G304" s="28" t="n">
         <x:f>ROUND(F304-F303,1)</x:f>
-        <x:v>19960</x:v>
+        <x:v>-260</x:v>
       </x:c>
       <x:c r="H304" s="24" t="n">
         <x:f>IFERROR(F304/F303-1,"")</x:f>
-        <x:v>0.1266497461928935</x:v>
+        <x:v>-0.0016470290130495835</x:v>
       </x:c>
       <x:c r="I304" s="26" t="n">
         <x:f>ROUND(D304-E304,1)</x:f>
-        <x:v>23220</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="J304" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K304" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B305" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C305" s="23" t="n">
-        <x:v>177000</x:v>
+        <x:v>155020</x:v>
       </x:c>
       <x:c r="D305" s="23" t="n">
-        <x:v>181440</x:v>
+        <x:v>178000</x:v>
       </x:c>
       <x:c r="E305" s="23" t="n">
-        <x:v>169500</x:v>
+        <x:v>154780</x:v>
       </x:c>
       <x:c r="F305" s="23" t="n">
-        <x:v>177900</x:v>
+        <x:v>177560</x:v>
       </x:c>
       <x:c r="G305" s="28" t="n">
         <x:f>ROUND(F305-F304,1)</x:f>
-        <x:v>340</x:v>
+        <x:v>19960</x:v>
       </x:c>
       <x:c r="H305" s="24" t="n">
         <x:f>IFERROR(F305/F304-1,"")</x:f>
-        <x:v>0.0019148456859652274</x:v>
+        <x:v>0.1266497461928935</x:v>
       </x:c>
       <x:c r="I305" s="26" t="n">
         <x:f>ROUND(D305-E305,1)</x:f>
-        <x:v>11940</x:v>
+        <x:v>23220</x:v>
       </x:c>
       <x:c r="J305" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18545,148 +18579,148 @@
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B306" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C306" s="23" t="n">
-        <x:v>182000</x:v>
+        <x:v>177000</x:v>
       </x:c>
       <x:c r="D306" s="23" t="n">
-        <x:v>189500</x:v>
+        <x:v>181440</x:v>
       </x:c>
       <x:c r="E306" s="23" t="n">
-        <x:v>173400</x:v>
+        <x:v>169500</x:v>
       </x:c>
       <x:c r="F306" s="23" t="n">
-        <x:v>189080</x:v>
+        <x:v>177900</x:v>
       </x:c>
       <x:c r="G306" s="28" t="n">
         <x:f>ROUND(F306-F305,1)</x:f>
-        <x:v>11180</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="H306" s="24" t="n">
         <x:f>IFERROR(F306/F305-1,"")</x:f>
-        <x:v>0.06284429454749851</x:v>
+        <x:v>0.0019148456859652274</x:v>
       </x:c>
       <x:c r="I306" s="26" t="n">
         <x:f>ROUND(D306-E306,1)</x:f>
-        <x:v>16100</x:v>
+        <x:v>11940</x:v>
       </x:c>
       <x:c r="J306" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K306" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B307" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C307" s="23" t="n">
-        <x:v>191500</x:v>
+        <x:v>182000</x:v>
       </x:c>
       <x:c r="D307" s="23" t="n">
-        <x:v>201480</x:v>
+        <x:v>189500</x:v>
       </x:c>
       <x:c r="E307" s="23" t="n">
-        <x:v>191040</x:v>
+        <x:v>173400</x:v>
       </x:c>
       <x:c r="F307" s="23" t="n">
-        <x:v>196560</x:v>
+        <x:v>189080</x:v>
       </x:c>
       <x:c r="G307" s="28" t="n">
         <x:f>ROUND(F307-F306,1)</x:f>
-        <x:v>7480</x:v>
+        <x:v>11180</x:v>
       </x:c>
       <x:c r="H307" s="24" t="n">
         <x:f>IFERROR(F307/F306-1,"")</x:f>
-        <x:v>0.039559974613920135</x:v>
+        <x:v>0.06284429454749851</x:v>
       </x:c>
       <x:c r="I307" s="26" t="n">
         <x:f>ROUND(D307-E307,1)</x:f>
-        <x:v>10440</x:v>
+        <x:v>16100</x:v>
       </x:c>
       <x:c r="J307" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K307" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B308" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C308" s="23" t="n">
+        <x:v>191500</x:v>
+      </x:c>
+      <x:c r="D308" s="23" t="n">
+        <x:v>201480</x:v>
+      </x:c>
+      <x:c r="E308" s="23" t="n">
+        <x:v>191040</x:v>
+      </x:c>
+      <x:c r="F308" s="23" t="n">
         <x:v>196560</x:v>
-      </x:c>
-      <x:c r="D308" s="23" t="n">
-        <x:v>209880</x:v>
-      </x:c>
-      <x:c r="E308" s="23" t="n">
-        <x:v>186800</x:v>
-      </x:c>
-      <x:c r="F308" s="23" t="n">
-        <x:v>188800</x:v>
       </x:c>
       <x:c r="G308" s="28" t="n">
         <x:f>ROUND(F308-F307,1)</x:f>
-        <x:v>-7760</x:v>
+        <x:v>7480</x:v>
       </x:c>
       <x:c r="H308" s="24" t="n">
         <x:f>IFERROR(F308/F307-1,"")</x:f>
-        <x:v>-0.039479039479039524</x:v>
+        <x:v>0.039559974613920135</x:v>
       </x:c>
       <x:c r="I308" s="26" t="n">
         <x:f>ROUND(D308-E308,1)</x:f>
-        <x:v>23080</x:v>
+        <x:v>10440</x:v>
       </x:c>
       <x:c r="J308" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K308" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B309" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C309" s="23" t="n">
-        <x:v>189000</x:v>
+        <x:v>196560</x:v>
       </x:c>
       <x:c r="D309" s="23" t="n">
-        <x:v>193900</x:v>
+        <x:v>209880</x:v>
       </x:c>
       <x:c r="E309" s="23" t="n">
-        <x:v>175200</x:v>
+        <x:v>186800</x:v>
       </x:c>
       <x:c r="F309" s="23" t="n">
-        <x:v>184460</x:v>
+        <x:v>188800</x:v>
       </x:c>
       <x:c r="G309" s="28" t="n">
         <x:f>ROUND(F309-F308,1)</x:f>
-        <x:v>-4340</x:v>
+        <x:v>-7760</x:v>
       </x:c>
       <x:c r="H309" s="24" t="n">
         <x:f>IFERROR(F309/F308-1,"")</x:f>
-        <x:v>-0.022987288135593253</x:v>
+        <x:v>-0.039479039479039524</x:v>
       </x:c>
       <x:c r="I309" s="26" t="n">
         <x:f>ROUND(D309-E309,1)</x:f>
-        <x:v>18700</x:v>
+        <x:v>23080</x:v>
       </x:c>
       <x:c r="J309" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18697,34 +18731,34 @@
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B310" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C310" s="23" t="n">
-        <x:v>185500</x:v>
+        <x:v>189000</x:v>
       </x:c>
       <x:c r="D310" s="23" t="n">
-        <x:v>187900</x:v>
+        <x:v>193900</x:v>
       </x:c>
       <x:c r="E310" s="23" t="n">
-        <x:v>172080</x:v>
+        <x:v>175200</x:v>
       </x:c>
       <x:c r="F310" s="23" t="n">
-        <x:v>179740</x:v>
+        <x:v>184460</x:v>
       </x:c>
       <x:c r="G310" s="28" t="n">
         <x:f>ROUND(F310-F309,1)</x:f>
-        <x:v>-4720</x:v>
+        <x:v>-4340</x:v>
       </x:c>
       <x:c r="H310" s="24" t="n">
         <x:f>IFERROR(F310/F309-1,"")</x:f>
-        <x:v>-0.02558820340453216</x:v>
+        <x:v>-0.022987288135593253</x:v>
       </x:c>
       <x:c r="I310" s="26" t="n">
         <x:f>ROUND(D310-E310,1)</x:f>
-        <x:v>15820</x:v>
+        <x:v>18700</x:v>
       </x:c>
       <x:c r="J310" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18735,34 +18769,34 @@
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B311" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C311" s="23" t="n">
-        <x:v>181000</x:v>
+        <x:v>185500</x:v>
       </x:c>
       <x:c r="D311" s="23" t="n">
-        <x:v>182100</x:v>
+        <x:v>187900</x:v>
       </x:c>
       <x:c r="E311" s="23" t="n">
-        <x:v>157180</x:v>
+        <x:v>172080</x:v>
       </x:c>
       <x:c r="F311" s="23" t="n">
-        <x:v>164360</x:v>
+        <x:v>179740</x:v>
       </x:c>
       <x:c r="G311" s="28" t="n">
         <x:f>ROUND(F311-F310,1)</x:f>
-        <x:v>-15380</x:v>
+        <x:v>-4720</x:v>
       </x:c>
       <x:c r="H311" s="24" t="n">
         <x:f>IFERROR(F311/F310-1,"")</x:f>
-        <x:v>-0.08556804272838547</x:v>
+        <x:v>-0.02558820340453216</x:v>
       </x:c>
       <x:c r="I311" s="26" t="n">
         <x:f>ROUND(D311-E311,1)</x:f>
-        <x:v>24920</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="J311" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18773,34 +18807,34 @@
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B312" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C312" s="23" t="n">
-        <x:v>161500</x:v>
+        <x:v>181000</x:v>
       </x:c>
       <x:c r="D312" s="23" t="n">
-        <x:v>178740</x:v>
+        <x:v>182100</x:v>
       </x:c>
       <x:c r="E312" s="23" t="n">
-        <x:v>160260</x:v>
+        <x:v>157180</x:v>
       </x:c>
       <x:c r="F312" s="23" t="n">
-        <x:v>175300</x:v>
+        <x:v>164360</x:v>
       </x:c>
       <x:c r="G312" s="28" t="n">
         <x:f>ROUND(F312-F311,1)</x:f>
-        <x:v>10940</x:v>
+        <x:v>-15380</x:v>
       </x:c>
       <x:c r="H312" s="24" t="n">
         <x:f>IFERROR(F312/F311-1,"")</x:f>
-        <x:v>0.06656120710635194</x:v>
+        <x:v>-0.08556804272838547</x:v>
       </x:c>
       <x:c r="I312" s="26" t="n">
         <x:f>ROUND(D312-E312,1)</x:f>
-        <x:v>18480</x:v>
+        <x:v>24920</x:v>
       </x:c>
       <x:c r="J312" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18811,110 +18845,110 @@
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B313" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C313" s="23" t="n">
-        <x:v>177600</x:v>
+        <x:v>161500</x:v>
       </x:c>
       <x:c r="D313" s="23" t="n">
-        <x:v>177920</x:v>
+        <x:v>178740</x:v>
       </x:c>
       <x:c r="E313" s="23" t="n">
-        <x:v>160100</x:v>
+        <x:v>160260</x:v>
       </x:c>
       <x:c r="F313" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>175300</x:v>
       </x:c>
       <x:c r="G313" s="28" t="n">
         <x:f>ROUND(F313-F312,1)</x:f>
-        <x:v>-14800</x:v>
+        <x:v>10940</x:v>
       </x:c>
       <x:c r="H313" s="24" t="n">
         <x:f>IFERROR(F313/F312-1,"")</x:f>
-        <x:v>-0.08442669709070161</x:v>
+        <x:v>0.06656120710635194</x:v>
       </x:c>
       <x:c r="I313" s="26" t="n">
         <x:f>ROUND(D313-E313,1)</x:f>
-        <x:v>17820</x:v>
+        <x:v>18480</x:v>
       </x:c>
       <x:c r="J313" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K313" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B314" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C314" s="23" t="n">
-        <x:v>157220</x:v>
+        <x:v>177600</x:v>
       </x:c>
       <x:c r="D314" s="23" t="n">
-        <x:v>163940</x:v>
+        <x:v>177920</x:v>
       </x:c>
       <x:c r="E314" s="23" t="n">
-        <x:v>145000</x:v>
+        <x:v>160100</x:v>
       </x:c>
       <x:c r="F314" s="23" t="n">
-        <x:v>150220</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="G314" s="28" t="n">
         <x:f>ROUND(F314-F313,1)</x:f>
-        <x:v>-10280</x:v>
+        <x:v>-14800</x:v>
       </x:c>
       <x:c r="H314" s="24" t="n">
         <x:f>IFERROR(F314/F313-1,"")</x:f>
-        <x:v>-0.06404984423676008</x:v>
+        <x:v>-0.08442669709070161</x:v>
       </x:c>
       <x:c r="I314" s="26" t="n">
         <x:f>ROUND(D314-E314,1)</x:f>
-        <x:v>18940</x:v>
+        <x:v>17820</x:v>
       </x:c>
       <x:c r="J314" s="22" t="str">
         <x:v>LC2609</x:v>
       </x:c>
       <x:c r="K314" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B315" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C315" s="23" t="n">
-        <x:v>148000</x:v>
+        <x:v>157220</x:v>
       </x:c>
       <x:c r="D315" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>163940</x:v>
       </x:c>
       <x:c r="E315" s="23" t="n">
-        <x:v>145300</x:v>
+        <x:v>145000</x:v>
       </x:c>
       <x:c r="F315" s="23" t="n">
-        <x:v>168780</x:v>
+        <x:v>150220</x:v>
       </x:c>
       <x:c r="G315" s="28" t="n">
         <x:f>ROUND(F315-F314,1)</x:f>
-        <x:v>18560</x:v>
+        <x:v>-10280</x:v>
       </x:c>
       <x:c r="H315" s="24" t="n">
         <x:f>IFERROR(F315/F314-1,"")</x:f>
-        <x:v>0.12355212355212353</x:v>
+        <x:v>-0.06404984423676008</x:v>
       </x:c>
       <x:c r="I315" s="26" t="n">
         <x:f>ROUND(D315-E315,1)</x:f>
-        <x:v>26700</x:v>
+        <x:v>18940</x:v>
       </x:c>
       <x:c r="J315" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18925,34 +18959,34 @@
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B316" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C316" s="23" t="n">
-        <x:v>166980</x:v>
+        <x:v>148000</x:v>
       </x:c>
       <x:c r="D316" s="23" t="n">
-        <x:v>168720</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="E316" s="23" t="n">
-        <x:v>150260</x:v>
+        <x:v>145300</x:v>
       </x:c>
       <x:c r="F316" s="23" t="n">
-        <x:v>151600</x:v>
+        <x:v>168780</x:v>
       </x:c>
       <x:c r="G316" s="28" t="n">
         <x:f>ROUND(F316-F315,1)</x:f>
-        <x:v>-17180</x:v>
+        <x:v>18560</x:v>
       </x:c>
       <x:c r="H316" s="24" t="n">
         <x:f>IFERROR(F316/F315-1,"")</x:f>
-        <x:v>-0.10178931152980208</x:v>
+        <x:v>0.12355212355212353</x:v>
       </x:c>
       <x:c r="I316" s="26" t="n">
         <x:f>ROUND(D316-E316,1)</x:f>
-        <x:v>18460</x:v>
+        <x:v>26700</x:v>
       </x:c>
       <x:c r="J316" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -18963,34 +18997,34 @@
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B317" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C317" s="23" t="n">
-        <x:v>150500</x:v>
+        <x:v>166980</x:v>
       </x:c>
       <x:c r="D317" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>168720</x:v>
       </x:c>
       <x:c r="E317" s="23" t="n">
-        <x:v>145860</x:v>
+        <x:v>150260</x:v>
       </x:c>
       <x:c r="F317" s="23" t="n">
-        <x:v>150140</x:v>
+        <x:v>151600</x:v>
       </x:c>
       <x:c r="G317" s="28" t="n">
         <x:f>ROUND(F317-F316,1)</x:f>
-        <x:v>-1460</x:v>
+        <x:v>-17180</x:v>
       </x:c>
       <x:c r="H317" s="24" t="n">
         <x:f>IFERROR(F317/F316-1,"")</x:f>
-        <x:v>-0.009630606860158264</x:v>
+        <x:v>-0.10178931152980208</x:v>
       </x:c>
       <x:c r="I317" s="26" t="n">
         <x:f>ROUND(D317-E317,1)</x:f>
-        <x:v>10640</x:v>
+        <x:v>18460</x:v>
       </x:c>
       <x:c r="J317" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -19001,34 +19035,34 @@
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B318" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C318" s="23" t="n">
-        <x:v>151500</x:v>
+        <x:v>150500</x:v>
       </x:c>
       <x:c r="D318" s="23" t="n">
-        <x:v>154800</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="E318" s="23" t="n">
-        <x:v>136800</x:v>
+        <x:v>145860</x:v>
       </x:c>
       <x:c r="F318" s="23" t="n">
-        <x:v>144280</x:v>
+        <x:v>150140</x:v>
       </x:c>
       <x:c r="G318" s="28" t="n">
         <x:f>ROUND(F318-F317,1)</x:f>
-        <x:v>-5860</x:v>
+        <x:v>-1460</x:v>
       </x:c>
       <x:c r="H318" s="24" t="n">
         <x:f>IFERROR(F318/F317-1,"")</x:f>
-        <x:v>-0.03903023844411879</x:v>
+        <x:v>-0.009630606860158264</x:v>
       </x:c>
       <x:c r="I318" s="26" t="n">
         <x:f>ROUND(D318-E318,1)</x:f>
-        <x:v>18000</x:v>
+        <x:v>10640</x:v>
       </x:c>
       <x:c r="J318" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -19039,34 +19073,34 @@
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B319" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C319" s="23" t="n">
-        <x:v>145780</x:v>
+        <x:v>151500</x:v>
       </x:c>
       <x:c r="D319" s="23" t="n">
-        <x:v>149400</x:v>
+        <x:v>154800</x:v>
       </x:c>
       <x:c r="E319" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>136800</x:v>
       </x:c>
       <x:c r="F319" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>144280</x:v>
       </x:c>
       <x:c r="G319" s="28" t="n">
         <x:f>ROUND(F319-F318,1)</x:f>
-        <x:v>-6520</x:v>
+        <x:v>-5860</x:v>
       </x:c>
       <x:c r="H319" s="24" t="n">
         <x:f>IFERROR(F319/F318-1,"")</x:f>
-        <x:v>-0.04518990851122817</x:v>
+        <x:v>-0.03903023844411879</x:v>
       </x:c>
       <x:c r="I319" s="26" t="n">
         <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>11640</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="J319" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -19077,34 +19111,34 @@
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B320" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C320" s="23" t="n">
-        <x:v>137500</x:v>
+        <x:v>145780</x:v>
       </x:c>
       <x:c r="D320" s="23" t="n">
-        <x:v>144800</x:v>
+        <x:v>149400</x:v>
       </x:c>
       <x:c r="E320" s="23" t="n">
-        <x:v>135560</x:v>
+        <x:v>137760</x:v>
       </x:c>
       <x:c r="F320" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>137760</x:v>
       </x:c>
       <x:c r="G320" s="28" t="n">
         <x:f>ROUND(F320-F319,1)</x:f>
-        <x:v>2240</x:v>
+        <x:v>-6520</x:v>
       </x:c>
       <x:c r="H320" s="24" t="n">
         <x:f>IFERROR(F320/F319-1,"")</x:f>
-        <x:v>0.016260162601626105</x:v>
+        <x:v>-0.04518990851122817</x:v>
       </x:c>
       <x:c r="I320" s="26" t="n">
         <x:f>ROUND(D320-E320,1)</x:f>
-        <x:v>9240</x:v>
+        <x:v>11640</x:v>
       </x:c>
       <x:c r="J320" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -19115,34 +19149,34 @@
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B321" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C321" s="23" t="n">
-        <x:v>140500</x:v>
+        <x:v>137500</x:v>
       </x:c>
       <x:c r="D321" s="23" t="n">
-        <x:v>154500</x:v>
+        <x:v>144800</x:v>
       </x:c>
       <x:c r="E321" s="23" t="n">
-        <x:v>139280</x:v>
+        <x:v>135560</x:v>
       </x:c>
       <x:c r="F321" s="23" t="n">
-        <x:v>153940</x:v>
+        <x:v>140000</x:v>
       </x:c>
       <x:c r="G321" s="28" t="n">
         <x:f>ROUND(F321-F320,1)</x:f>
-        <x:v>13940</x:v>
+        <x:v>2240</x:v>
       </x:c>
       <x:c r="H321" s="24" t="n">
         <x:f>IFERROR(F321/F320-1,"")</x:f>
-        <x:v>0.09957142857142864</x:v>
+        <x:v>0.016260162601626105</x:v>
       </x:c>
       <x:c r="I321" s="26" t="n">
         <x:f>ROUND(D321-E321,1)</x:f>
-        <x:v>15220</x:v>
+        <x:v>9240</x:v>
       </x:c>
       <x:c r="J321" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -19153,34 +19187,34 @@
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B322" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C322" s="23" t="n">
-        <x:v>154300</x:v>
+        <x:v>140500</x:v>
       </x:c>
       <x:c r="D322" s="23" t="n">
-        <x:v>157000</x:v>
+        <x:v>154500</x:v>
       </x:c>
       <x:c r="E322" s="23" t="n">
-        <x:v>148400</x:v>
+        <x:v>139280</x:v>
       </x:c>
       <x:c r="F322" s="23" t="n">
-        <x:v>156140</x:v>
+        <x:v>153940</x:v>
       </x:c>
       <x:c r="G322" s="28" t="n">
         <x:f>ROUND(F322-F321,1)</x:f>
-        <x:v>2200</x:v>
+        <x:v>13940</x:v>
       </x:c>
       <x:c r="H322" s="24" t="n">
         <x:f>IFERROR(F322/F321-1,"")</x:f>
-        <x:v>0.014291282317786091</x:v>
+        <x:v>0.09957142857142864</x:v>
       </x:c>
       <x:c r="I322" s="26" t="n">
         <x:f>ROUND(D322-E322,1)</x:f>
-        <x:v>8600</x:v>
+        <x:v>15220</x:v>
       </x:c>
       <x:c r="J322" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -19191,34 +19225,34 @@
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B323" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C323" s="23" t="n">
-        <x:v>158500</x:v>
+        <x:v>154300</x:v>
       </x:c>
       <x:c r="D323" s="23" t="n">
-        <x:v>160000</x:v>
+        <x:v>157000</x:v>
       </x:c>
       <x:c r="E323" s="23" t="n">
-        <x:v>147000</x:v>
+        <x:v>148400</x:v>
       </x:c>
       <x:c r="F323" s="23" t="n">
-        <x:v>157080</x:v>
+        <x:v>156140</x:v>
       </x:c>
       <x:c r="G323" s="28" t="n">
         <x:f>ROUND(F323-F322,1)</x:f>
-        <x:v>940</x:v>
+        <x:v>2200</x:v>
       </x:c>
       <x:c r="H323" s="24" t="n">
         <x:f>IFERROR(F323/F322-1,"")</x:f>
-        <x:v>0.0060202382477263505</x:v>
+        <x:v>0.014291282317786091</x:v>
       </x:c>
       <x:c r="I323" s="26" t="n">
         <x:f>ROUND(D323-E323,1)</x:f>
-        <x:v>13000</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="J323" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -19229,34 +19263,34 @@
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B324" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C324" s="23" t="n">
-        <x:v>158000</x:v>
+        <x:v>158500</x:v>
       </x:c>
       <x:c r="D324" s="23" t="n">
-        <x:v>160480</x:v>
+        <x:v>160000</x:v>
       </x:c>
       <x:c r="E324" s="23" t="n">
-        <x:v>140940</x:v>
+        <x:v>147000</x:v>
       </x:c>
       <x:c r="F324" s="23" t="n">
-        <x:v>140980</x:v>
+        <x:v>157080</x:v>
       </x:c>
       <x:c r="G324" s="28" t="n">
         <x:f>ROUND(F324-F323,1)</x:f>
-        <x:v>-16100</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="H324" s="24" t="n">
         <x:f>IFERROR(F324/F323-1,"")</x:f>
-        <x:v>-0.1024955436720143</x:v>
+        <x:v>0.0060202382477263505</x:v>
       </x:c>
       <x:c r="I324" s="26" t="n">
         <x:f>ROUND(D324-E324,1)</x:f>
-        <x:v>19540</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="J324" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -19267,34 +19301,34 @@
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B325" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C325" s="23" t="n">
-        <x:v>142120</x:v>
+        <x:v>158000</x:v>
       </x:c>
       <x:c r="D325" s="23" t="n">
-        <x:v>143200</x:v>
+        <x:v>160480</x:v>
       </x:c>
       <x:c r="E325" s="23" t="n">
-        <x:v>131900</x:v>
+        <x:v>140940</x:v>
       </x:c>
       <x:c r="F325" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>140980</x:v>
       </x:c>
       <x:c r="G325" s="28" t="n">
         <x:f>ROUND(F325-F324,1)</x:f>
-        <x:v>-5480</x:v>
+        <x:v>-16100</x:v>
       </x:c>
       <x:c r="H325" s="24" t="n">
         <x:f>IFERROR(F325/F324-1,"")</x:f>
-        <x:v>-0.038870761810185894</x:v>
+        <x:v>-0.1024955436720143</x:v>
       </x:c>
       <x:c r="I325" s="26" t="n">
         <x:f>ROUND(D325-E325,1)</x:f>
-        <x:v>11300</x:v>
+        <x:v>19540</x:v>
       </x:c>
       <x:c r="J325" s="22" t="str">
         <x:v>LC2609</x:v>
@@ -19304,42 +19338,118 @@
       </x:c>
     </x:row>
     <x:row r="326">
-      <x:c r="A326" s="31" t="str">
+      <x:c r="A326" s="22" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B326" s="22" t="str">
+        <x:v>9月7日-9月11日</x:v>
+      </x:c>
+      <x:c r="C326" s="23" t="n">
+        <x:v>142120</x:v>
+      </x:c>
+      <x:c r="D326" s="23" t="n">
+        <x:v>143200</x:v>
+      </x:c>
+      <x:c r="E326" s="23" t="n">
+        <x:v>131900</x:v>
+      </x:c>
+      <x:c r="F326" s="23" t="n">
+        <x:v>135500</x:v>
+      </x:c>
+      <x:c r="G326" s="28" t="n">
+        <x:f>ROUND(F326-F325,1)</x:f>
+        <x:v>-5480</x:v>
+      </x:c>
+      <x:c r="H326" s="24" t="n">
+        <x:f>IFERROR(F326/F325-1,"")</x:f>
+        <x:v>-0.038870761810185894</x:v>
+      </x:c>
+      <x:c r="I326" s="26" t="n">
+        <x:f>ROUND(D326-E326,1)</x:f>
+        <x:v>11300</x:v>
+      </x:c>
+      <x:c r="J326" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K326" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327">
+      <x:c r="A327" s="22" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B327" s="22" t="str">
+        <x:v>9月14日</x:v>
+      </x:c>
+      <x:c r="C327" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D327" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E327" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F327" s="23" t="n">
+        <x:v>135500</x:v>
+      </x:c>
+      <x:c r="G327" s="23" t="n">
+        <x:f>ROUND(F327-F326,1)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H327" s="24" t="n">
+        <x:f>IFERROR(F327/F326-1,"")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I327" s="23" t="n">
+        <x:f>ROUND(D327-E327,1)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J327" s="22" t="str">
+        <x:v>LC2609</x:v>
+      </x:c>
+      <x:c r="K327" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328">
+      <x:c r="A328" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B326" s="30" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C326" s="30"/>
-      <x:c r="D326" s="30"/>
-      <x:c r="E326" s="30"/>
-      <x:c r="F326" s="30"/>
-      <x:c r="G326" s="30"/>
-      <x:c r="H326" s="30"/>
-      <x:c r="I326" s="32" t="n">
-        <x:f>ROUND(SUM(I291:I325),1)</x:f>
+      <x:c r="B328" s="30" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C328" s="30"/>
+      <x:c r="D328" s="30"/>
+      <x:c r="E328" s="30"/>
+      <x:c r="F328" s="30"/>
+      <x:c r="G328" s="30"/>
+      <x:c r="H328" s="30"/>
+      <x:c r="I328" s="32" t="n">
+        <x:f>ROUND(SUM(I292:I327),1)</x:f>
         <x:v>720520</x:v>
       </x:c>
-      <x:c r="J326" s="30"/>
-      <x:c r="K326" s="30"/>
-    </x:row>
-    <x:row r="327">
-      <x:c r="A327" s="31" t="str">
+      <x:c r="J328" s="30"/>
+      <x:c r="K328" s="30"/>
+    </x:row>
+    <x:row r="329">
+      <x:c r="A329" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B327" s="30"/>
-      <x:c r="C327" s="30"/>
-      <x:c r="D327" s="30"/>
-      <x:c r="E327" s="30"/>
-      <x:c r="F327" s="30"/>
-      <x:c r="G327" s="30"/>
-      <x:c r="H327" s="30"/>
-      <x:c r="I327" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I291:I325),0),1)</x:f>
-        <x:v>20586.3</x:v>
-      </x:c>
-      <x:c r="J327" s="30"/>
-      <x:c r="K327" s="30"/>
+      <x:c r="B329" s="30"/>
+      <x:c r="C329" s="30"/>
+      <x:c r="D329" s="30"/>
+      <x:c r="E329" s="30"/>
+      <x:c r="F329" s="30"/>
+      <x:c r="G329" s="30"/>
+      <x:c r="H329" s="30"/>
+      <x:c r="I329" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I292:I327),0),1)</x:f>
+        <x:v>20014.4</x:v>
+      </x:c>
+      <x:c r="J329" s="30"/>
+      <x:c r="K329" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -19349,9 +19459,9 @@
     <x:mergeCell ref="A85:K85"/>
     <x:mergeCell ref="A126:K126"/>
     <x:mergeCell ref="A167:K167"/>
-    <x:mergeCell ref="A207:K207"/>
-    <x:mergeCell ref="A248:K248"/>
-    <x:mergeCell ref="A289:K289"/>
+    <x:mergeCell ref="A208:K208"/>
+    <x:mergeCell ref="A249:K249"/>
+    <x:mergeCell ref="A290:K290"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -54022,30 +54132,48 @@
       </x:c>
     </x:row>
     <x:row r="214">
-      <x:c r="A214" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B214" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C214" s="30"/>
-      <x:c r="D214" s="30"/>
-      <x:c r="E214" s="30"/>
-      <x:c r="F214" s="30"/>
-      <x:c r="G214" s="30"/>
-      <x:c r="H214" s="30"/>
-      <x:c r="I214" s="30"/>
-      <x:c r="J214" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J213),1)</x:f>
-        <x:v>1326.8</x:v>
-      </x:c>
-      <x:c r="K214" s="30"/>
+      <x:c r="A214" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B214" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C214" s="22" t="str">
+        <x:v>9月14日</x:v>
+      </x:c>
+      <x:c r="D214" s="23" t="n">
+        <x:v>7482.2</x:v>
+      </x:c>
+      <x:c r="E214" s="23" t="n">
+        <x:v>7595.2</x:v>
+      </x:c>
+      <x:c r="F214" s="23" t="n">
+        <x:v>7452.2</x:v>
+      </x:c>
+      <x:c r="G214" s="23" t="n">
+        <x:v>7573.6</x:v>
+      </x:c>
+      <x:c r="H214" s="23" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="I214" s="24" t="n">
+        <x:v>0.0006077421059584864</x:v>
+      </x:c>
+      <x:c r="J214" s="23" t="n">
+        <x:f>ROUND(E214-F214,1)</x:f>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="K214" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B215" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B215" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C215" s="30"/>
       <x:c r="D215" s="30"/>
       <x:c r="E215" s="30"/>
@@ -54053,11 +54181,29 @@
       <x:c r="G215" s="30"/>
       <x:c r="H215" s="30"/>
       <x:c r="I215" s="30"/>
-      <x:c r="J215" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J213),0),1)</x:f>
-        <x:v>147.4</x:v>
+      <x:c r="J215" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J214),1)</x:f>
+        <x:v>1469.8</x:v>
       </x:c>
       <x:c r="K215" s="30"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B216" s="30"/>
+      <x:c r="C216" s="30"/>
+      <x:c r="D216" s="30"/>
+      <x:c r="E216" s="30"/>
+      <x:c r="F216" s="30"/>
+      <x:c r="G216" s="30"/>
+      <x:c r="H216" s="30"/>
+      <x:c r="I216" s="30"/>
+      <x:c r="J216" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="K216" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R964c6c58398e4536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R7c39e4f1785a4b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R516dcecd78374a93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R40b01be2d42549bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R9d80209119ff434e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R3c97c904d50c49f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R7f5d296a23f84767"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R4b9ef4b260e049dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R77f5534ac7b34e6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Re41c7f51250b4d12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R52d7b575524b4e3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R51ddcef6e2ca475b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R03896e2b87754d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R2cf22daddac145b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Re5ea151960e5445c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R45deddf554ff4e8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd6b9c370fb944e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rdb6612c63d364944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R079d01ab6f114a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R6d4799ed389e4268"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7501.14</x:v>
+        <x:v>7524.61</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7329.6</x:v>
+        <x:v>7426.9</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>171.5</x:v>
+        <x:v>97.7</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>30114.9</x:v>
+        <x:v>30212.6</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>177.1</x:v>
+        <x:v>176.7</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7610.03</x:v>
+        <x:v>7641.54</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7487.46</x:v>
+        <x:v>7543.95</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>122.6</x:v>
+        <x:v>97.6</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>30015.5</x:v>
+        <x:v>30113.1</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>176.6</x:v>
+        <x:v>176.1</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3895.51</x:v>
+        <x:v>3891.62</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3867.02</x:v>
+        <x:v>3858.15</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>28.5</x:v>
+        <x:v>33.5</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8229</x:v>
+        <x:v>8262.5</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>48.4</x:v>
+        <x:v>48.3</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7595.2</x:v>
+        <x:v>7418.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7452.2</x:v>
+        <x:v>7311</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>143</x:v>
+        <x:v>107.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>33214</x:v>
+        <x:v>33321.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>195.4</x:v>
+        <x:v>194.9</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4500.6</x:v>
+        <x:v>4405</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4458</x:v>
+        <x:v>4347.8</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>42.6</x:v>
+        <x:v>57.2</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12406</x:v>
+        <x:v>12463.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>73</x:v>
+        <x:v>72.9</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2867</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2843.8</x:v>
+        <x:v>2840</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>20.8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6886.8</x:v>
+        <x:v>6913.8</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.5</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -725,12 +725,14 @@
         <x:v>2026-09-14</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
+        <x:v>135500</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="n">
+        <x:v>135500</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D11" s="10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="12" t="str"/>
       <x:c r="F11" s="9" t="n">
         <x:v>170</x:v>
       </x:c>
@@ -752,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -7749,13 +7751,13 @@
         <x:v>9月14日</x:v>
       </x:c>
       <x:c r="D214" s="23" t="n">
-        <x:v>0</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="E214" s="23" t="n">
-        <x:v>0</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="F214" s="23" t="n">
-        <x:v>0</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="G214" s="23" t="n">
         <x:v>135500</x:v>
@@ -9230,37 +9232,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月14日-9月15日</x:v>
       </x:c>
       <x:c r="C40" s="23" t="n">
         <x:v>7363.42</x:v>
       </x:c>
       <x:c r="D40" s="23" t="n">
-        <x:v>7501.14</x:v>
+        <x:v>7524.61</x:v>
       </x:c>
       <x:c r="E40" s="23" t="n">
         <x:v>7329.6</x:v>
       </x:c>
       <x:c r="F40" s="23" t="n">
-        <x:v>7468.3</x:v>
+        <x:v>7437.7</x:v>
       </x:c>
       <x:c r="G40" s="23" t="n">
         <x:f>ROUND(F40-F39,1)</x:f>
-        <x:v>41.1</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="H40" s="24" t="n">
         <x:f>IFERROR(F40/F39-1,"")</x:f>
-        <x:v>0.005528298533506337</x:v>
-      </x:c>
-      <x:c r="I40" s="23" t="n">
+        <x:v>0.0014083293390276808</x:v>
+      </x:c>
+      <x:c r="I40" s="26" t="n">
         <x:f>ROUND(D40-E40,1)</x:f>
-        <x:v>171.5</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="J40" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K40" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -9278,7 +9280,7 @@
       <x:c r="H41" s="30"/>
       <x:c r="I41" s="32" t="n">
         <x:f>ROUND(SUM(I5:I40),1)</x:f>
-        <x:v>14868.1</x:v>
+        <x:v>14891.6</x:v>
       </x:c>
       <x:c r="J41" s="30"/>
       <x:c r="K41" s="30"/>
@@ -9296,7 +9298,7 @@
       <x:c r="H42" s="30"/>
       <x:c r="I42" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I40),0),1)</x:f>
-        <x:v>413</x:v>
+        <x:v>413.7</x:v>
       </x:c>
       <x:c r="J42" s="30"/>
       <x:c r="K42" s="30"/>
@@ -10680,37 +10682,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B81" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月14日-9月15日</x:v>
       </x:c>
       <x:c r="C81" s="23" t="n">
         <x:v>7511.04</x:v>
       </x:c>
       <x:c r="D81" s="23" t="n">
-        <x:v>7610.03</x:v>
+        <x:v>7641.54</x:v>
       </x:c>
       <x:c r="E81" s="23" t="n">
         <x:v>7487.46</x:v>
       </x:c>
       <x:c r="F81" s="23" t="n">
-        <x:v>7571.2</x:v>
+        <x:v>7561.59</x:v>
       </x:c>
       <x:c r="G81" s="23" t="n">
         <x:f>ROUND(F81-F80,1)</x:f>
-        <x:v>-9.3</x:v>
+        <x:v>-18.9</x:v>
       </x:c>
       <x:c r="H81" s="24" t="n">
         <x:f>IFERROR(F81/F80-1,"")</x:f>
-        <x:v>-0.0012321021985240987</x:v>
+        <x:v>-0.00249982191242315</x:v>
       </x:c>
       <x:c r="I81" s="23" t="n">
         <x:f>ROUND(D81-E81,1)</x:f>
-        <x:v>122.6</x:v>
+        <x:v>154.1</x:v>
       </x:c>
       <x:c r="J81" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K81" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -10728,7 +10730,7 @@
       <x:c r="H82" s="30"/>
       <x:c r="I82" s="32" t="n">
         <x:f>ROUND(SUM(I46:I81),1)</x:f>
-        <x:v>14840.6</x:v>
+        <x:v>14872.1</x:v>
       </x:c>
       <x:c r="J82" s="30"/>
       <x:c r="K82" s="30"/>
@@ -10746,7 +10748,7 @@
       <x:c r="H83" s="30"/>
       <x:c r="I83" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I46:I81),0),1)</x:f>
-        <x:v>412.2</x:v>
+        <x:v>413.1</x:v>
       </x:c>
       <x:c r="J83" s="30"/>
       <x:c r="K83" s="30"/>
@@ -12130,7 +12132,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B122" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月14日-9月15日</x:v>
       </x:c>
       <x:c r="C122" s="23" t="n">
         <x:v>3867.02</x:v>
@@ -12139,28 +12141,28 @@
         <x:v>3895.51</x:v>
       </x:c>
       <x:c r="E122" s="23" t="n">
-        <x:v>3867.02</x:v>
+        <x:v>3858.15</x:v>
       </x:c>
       <x:c r="F122" s="23" t="n">
-        <x:v>3885.33</x:v>
+        <x:v>3864.28</x:v>
       </x:c>
       <x:c r="G122" s="23" t="n">
         <x:f>ROUND(F122-F121,1)</x:f>
-        <x:v>-2.8</x:v>
+        <x:v>-23.8</x:v>
       </x:c>
       <x:c r="H122" s="24" t="n">
         <x:f>IFERROR(F122/F121-1,"")</x:f>
-        <x:v>-0.0007150003472125022</x:v>
+        <x:v>-0.006128941825205514</x:v>
       </x:c>
       <x:c r="I122" s="23" t="n">
         <x:f>ROUND(D122-E122,1)</x:f>
-        <x:v>28.5</x:v>
+        <x:v>37.4</x:v>
       </x:c>
       <x:c r="J122" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K122" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -12178,7 +12180,7 @@
       <x:c r="H123" s="30"/>
       <x:c r="I123" s="32" t="n">
         <x:f>ROUND(SUM(I87:I122),1)</x:f>
-        <x:v>3892.6</x:v>
+        <x:v>3901.5</x:v>
       </x:c>
       <x:c r="J123" s="30"/>
       <x:c r="K123" s="30"/>
@@ -12196,7 +12198,7 @@
       <x:c r="H124" s="30"/>
       <x:c r="I124" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I87:I122),0),1)</x:f>
-        <x:v>108.1</x:v>
+        <x:v>108.4</x:v>
       </x:c>
       <x:c r="J124" s="30"/>
       <x:c r="K124" s="30"/>
@@ -15030,7 +15032,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B204" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月14日-9月15日</x:v>
       </x:c>
       <x:c r="C204" s="23" t="n">
         <x:v>7482.2</x:v>
@@ -15039,28 +15041,28 @@
         <x:v>7595.2</x:v>
       </x:c>
       <x:c r="E204" s="23" t="n">
-        <x:v>7452.2</x:v>
+        <x:v>7311</x:v>
       </x:c>
       <x:c r="F204" s="23" t="n">
-        <x:v>7573.6</x:v>
-      </x:c>
-      <x:c r="G204" s="23" t="n">
+        <x:v>7350.8</x:v>
+      </x:c>
+      <x:c r="G204" s="28" t="n">
         <x:f>ROUND(F204-F203,1)</x:f>
-        <x:v>4.6</x:v>
+        <x:v>-218.2</x:v>
       </x:c>
       <x:c r="H204" s="24" t="n">
         <x:f>IFERROR(F204/F203-1,"")</x:f>
-        <x:v>0.0006077421059584864</x:v>
-      </x:c>
-      <x:c r="I204" s="23" t="n">
+        <x:v>-0.02882811467829305</x:v>
+      </x:c>
+      <x:c r="I204" s="26" t="n">
         <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>143</x:v>
+        <x:v>284.2</x:v>
       </x:c>
       <x:c r="J204" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K204" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -15078,7 +15080,7 @@
       <x:c r="H205" s="30"/>
       <x:c r="I205" s="32" t="n">
         <x:f>ROUND(SUM(I169:I204),1)</x:f>
-        <x:v>15968.4</x:v>
+        <x:v>16109.6</x:v>
       </x:c>
       <x:c r="J205" s="30"/>
       <x:c r="K205" s="30"/>
@@ -15096,7 +15098,7 @@
       <x:c r="H206" s="30"/>
       <x:c r="I206" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I169:I204),0),1)</x:f>
-        <x:v>443.6</x:v>
+        <x:v>447.5</x:v>
       </x:c>
       <x:c r="J206" s="30"/>
       <x:c r="K206" s="30"/>
@@ -16480,7 +16482,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B245" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月14日-9月15日</x:v>
       </x:c>
       <x:c r="C245" s="23" t="n">
         <x:v>4468</x:v>
@@ -16489,28 +16491,28 @@
         <x:v>4500.6</x:v>
       </x:c>
       <x:c r="E245" s="23" t="n">
-        <x:v>4458</x:v>
+        <x:v>4347.8</x:v>
       </x:c>
       <x:c r="F245" s="23" t="n">
-        <x:v>4480.2</x:v>
+        <x:v>4355.8</x:v>
       </x:c>
       <x:c r="G245" s="23" t="n">
         <x:f>ROUND(F245-F244,1)</x:f>
-        <x:v>-23.2</x:v>
+        <x:v>-147.6</x:v>
       </x:c>
       <x:c r="H245" s="24" t="n">
         <x:f>IFERROR(F245/F244-1,"")</x:f>
-        <x:v>-0.005151663187813571</x:v>
-      </x:c>
-      <x:c r="I245" s="23" t="n">
+        <x:v>-0.03277523648798675</x:v>
+      </x:c>
+      <x:c r="I245" s="26" t="n">
         <x:f>ROUND(D245-E245,1)</x:f>
-        <x:v>42.6</x:v>
+        <x:v>152.8</x:v>
       </x:c>
       <x:c r="J245" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K245" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
@@ -16528,7 +16530,7 @@
       <x:c r="H246" s="30"/>
       <x:c r="I246" s="32" t="n">
         <x:f>ROUND(SUM(I210:I245),1)</x:f>
-        <x:v>5647.8</x:v>
+        <x:v>5758</x:v>
       </x:c>
       <x:c r="J246" s="30"/>
       <x:c r="K246" s="30"/>
@@ -16546,7 +16548,7 @@
       <x:c r="H247" s="30"/>
       <x:c r="I247" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I210:I245),0),1)</x:f>
-        <x:v>156.9</x:v>
+        <x:v>159.9</x:v>
       </x:c>
       <x:c r="J247" s="30"/>
       <x:c r="K247" s="30"/>
@@ -17930,37 +17932,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B286" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月14日-9月15日</x:v>
       </x:c>
       <x:c r="C286" s="23" t="n">
         <x:v>2849.2</x:v>
       </x:c>
       <x:c r="D286" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2867</x:v>
       </x:c>
       <x:c r="E286" s="23" t="n">
-        <x:v>2843.8</x:v>
+        <x:v>2840</x:v>
       </x:c>
       <x:c r="F286" s="23" t="n">
-        <x:v>2860.4</x:v>
+        <x:v>2845</x:v>
       </x:c>
       <x:c r="G286" s="23" t="n">
         <x:f>ROUND(F286-F285,1)</x:f>
-        <x:v>-6.6</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="H286" s="24" t="n">
         <x:f>IFERROR(F286/F285-1,"")</x:f>
-        <x:v>-0.002302057900244181</x:v>
+        <x:v>-0.007673526334147196</x:v>
       </x:c>
       <x:c r="I286" s="23" t="n">
         <x:f>ROUND(D286-E286,1)</x:f>
-        <x:v>20.8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J286" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K286" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -17978,7 +17980,7 @@
       <x:c r="H287" s="30"/>
       <x:c r="I287" s="32" t="n">
         <x:f>ROUND(SUM(I251:I286),1)</x:f>
-        <x:v>3236.4</x:v>
+        <x:v>3242.6</x:v>
       </x:c>
       <x:c r="J287" s="30"/>
       <x:c r="K287" s="30"/>
@@ -17996,7 +17998,7 @@
       <x:c r="H288" s="30"/>
       <x:c r="I288" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I251:I286),0),1)</x:f>
-        <x:v>89.9</x:v>
+        <x:v>90.1</x:v>
       </x:c>
       <x:c r="J288" s="30"/>
       <x:c r="K288" s="30"/>
@@ -19383,13 +19385,13 @@
         <x:v>9月14日</x:v>
       </x:c>
       <x:c r="C327" s="23" t="n">
-        <x:v>0</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="D327" s="23" t="n">
-        <x:v>0</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="E327" s="23" t="n">
-        <x:v>0</x:v>
+        <x:v>135500</x:v>
       </x:c>
       <x:c r="F327" s="23" t="n">
         <x:v>135500</x:v>
@@ -26364,30 +26366,48 @@
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B215" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C215" s="30"/>
-      <x:c r="D215" s="30"/>
-      <x:c r="E215" s="30"/>
-      <x:c r="F215" s="30"/>
-      <x:c r="G215" s="30"/>
-      <x:c r="H215" s="30"/>
-      <x:c r="I215" s="30"/>
-      <x:c r="J215" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J214),1)</x:f>
-        <x:v>1384.1</x:v>
-      </x:c>
-      <x:c r="K215" s="30"/>
+      <x:c r="A215" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B215" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C215" s="22" t="str">
+        <x:v>9月15日</x:v>
+      </x:c>
+      <x:c r="D215" s="23" t="n">
+        <x:v>7453.47</x:v>
+      </x:c>
+      <x:c r="E215" s="23" t="n">
+        <x:v>7524.61</x:v>
+      </x:c>
+      <x:c r="F215" s="23" t="n">
+        <x:v>7426.9</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
+        <x:v>7437.7</x:v>
+      </x:c>
+      <x:c r="H215" s="23" t="n">
+        <x:v>-30.6</x:v>
+      </x:c>
+      <x:c r="I215" s="24" t="n">
+        <x:v>-0.004097317997402428</x:v>
+      </x:c>
+      <x:c r="J215" s="23" t="n">
+        <x:f>ROUND(E215-F215,1)</x:f>
+        <x:v>97.7</x:v>
+      </x:c>
+      <x:c r="K215" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B216" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B216" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="C216" s="30"/>
       <x:c r="D216" s="30"/>
       <x:c r="E216" s="30"/>
@@ -26395,11 +26415,29 @@
       <x:c r="G216" s="30"/>
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="30"/>
-      <x:c r="J216" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
-        <x:v>138.4</x:v>
+      <x:c r="J216" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J215),1)</x:f>
+        <x:v>1481.8</x:v>
       </x:c>
       <x:c r="K216" s="30"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B217" s="30"/>
+      <x:c r="C217" s="30"/>
+      <x:c r="D217" s="30"/>
+      <x:c r="E217" s="30"/>
+      <x:c r="F217" s="30"/>
+      <x:c r="G217" s="30"/>
+      <x:c r="H217" s="30"/>
+      <x:c r="I217" s="30"/>
+      <x:c r="J217" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
+        <x:v>134.7</x:v>
+      </x:c>
+      <x:c r="K217" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -33315,30 +33353,48 @@
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B215" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C215" s="30"/>
-      <x:c r="D215" s="30"/>
-      <x:c r="E215" s="30"/>
-      <x:c r="F215" s="30"/>
-      <x:c r="G215" s="30"/>
-      <x:c r="H215" s="30"/>
-      <x:c r="I215" s="30"/>
-      <x:c r="J215" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J214),1)</x:f>
-        <x:v>1231.8</x:v>
-      </x:c>
-      <x:c r="K215" s="30"/>
+      <x:c r="A215" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B215" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C215" s="22" t="str">
+        <x:v>9月15日</x:v>
+      </x:c>
+      <x:c r="D215" s="23" t="n">
+        <x:v>7550.68</x:v>
+      </x:c>
+      <x:c r="E215" s="23" t="n">
+        <x:v>7641.54</x:v>
+      </x:c>
+      <x:c r="F215" s="23" t="n">
+        <x:v>7543.95</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
+        <x:v>7561.59</x:v>
+      </x:c>
+      <x:c r="H215" s="23" t="n">
+        <x:v>-9.6</x:v>
+      </x:c>
+      <x:c r="I215" s="24" t="n">
+        <x:v>-0.0012692836010143038</x:v>
+      </x:c>
+      <x:c r="J215" s="23" t="n">
+        <x:f>ROUND(E215-F215,1)</x:f>
+        <x:v>97.6</x:v>
+      </x:c>
+      <x:c r="K215" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B216" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B216" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="C216" s="30"/>
       <x:c r="D216" s="30"/>
       <x:c r="E216" s="30"/>
@@ -33346,11 +33402,29 @@
       <x:c r="G216" s="30"/>
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="30"/>
-      <x:c r="J216" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
-        <x:v>123.2</x:v>
+      <x:c r="J216" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J215),1)</x:f>
+        <x:v>1329.4</x:v>
       </x:c>
       <x:c r="K216" s="30"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B217" s="30"/>
+      <x:c r="C217" s="30"/>
+      <x:c r="D217" s="30"/>
+      <x:c r="E217" s="30"/>
+      <x:c r="F217" s="30"/>
+      <x:c r="G217" s="30"/>
+      <x:c r="H217" s="30"/>
+      <x:c r="I217" s="30"/>
+      <x:c r="J217" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
+        <x:v>120.9</x:v>
+      </x:c>
+      <x:c r="K217" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -40266,30 +40340,48 @@
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B215" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C215" s="30"/>
-      <x:c r="D215" s="30"/>
-      <x:c r="E215" s="30"/>
-      <x:c r="F215" s="30"/>
-      <x:c r="G215" s="30"/>
-      <x:c r="H215" s="30"/>
-      <x:c r="I215" s="30"/>
-      <x:c r="J215" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J214),1)</x:f>
-        <x:v>347.9</x:v>
-      </x:c>
-      <x:c r="K215" s="30"/>
+      <x:c r="A215" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B215" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C215" s="22" t="str">
+        <x:v>9月15日</x:v>
+      </x:c>
+      <x:c r="D215" s="23" t="n">
+        <x:v>3879.73</x:v>
+      </x:c>
+      <x:c r="E215" s="23" t="n">
+        <x:v>3891.62</x:v>
+      </x:c>
+      <x:c r="F215" s="23" t="n">
+        <x:v>3858.15</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
+        <x:v>3864.28</x:v>
+      </x:c>
+      <x:c r="H215" s="23" t="n">
+        <x:v>-21</x:v>
+      </x:c>
+      <x:c r="I215" s="24" t="n">
+        <x:v>-0.005417815217754973</x:v>
+      </x:c>
+      <x:c r="J215" s="23" t="n">
+        <x:f>ROUND(E215-F215,1)</x:f>
+        <x:v>33.5</x:v>
+      </x:c>
+      <x:c r="K215" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B216" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B216" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="C216" s="30"/>
       <x:c r="D216" s="30"/>
       <x:c r="E216" s="30"/>
@@ -40297,11 +40389,29 @@
       <x:c r="G216" s="30"/>
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="30"/>
-      <x:c r="J216" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
-        <x:v>34.8</x:v>
+      <x:c r="J216" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J215),1)</x:f>
+        <x:v>381.4</x:v>
       </x:c>
       <x:c r="K216" s="30"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B217" s="30"/>
+      <x:c r="C217" s="30"/>
+      <x:c r="D217" s="30"/>
+      <x:c r="E217" s="30"/>
+      <x:c r="F217" s="30"/>
+      <x:c r="G217" s="30"/>
+      <x:c r="H217" s="30"/>
+      <x:c r="I217" s="30"/>
+      <x:c r="J217" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
+        <x:v>34.7</x:v>
+      </x:c>
+      <x:c r="K217" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -54168,30 +54278,48 @@
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B215" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C215" s="30"/>
-      <x:c r="D215" s="30"/>
-      <x:c r="E215" s="30"/>
-      <x:c r="F215" s="30"/>
-      <x:c r="G215" s="30"/>
-      <x:c r="H215" s="30"/>
-      <x:c r="I215" s="30"/>
-      <x:c r="J215" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J214),1)</x:f>
-        <x:v>1469.8</x:v>
-      </x:c>
-      <x:c r="K215" s="30"/>
+      <x:c r="A215" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B215" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C215" s="22" t="str">
+        <x:v>9月15日</x:v>
+      </x:c>
+      <x:c r="D215" s="23" t="n">
+        <x:v>7351.6</x:v>
+      </x:c>
+      <x:c r="E215" s="23" t="n">
+        <x:v>7418.8</x:v>
+      </x:c>
+      <x:c r="F215" s="23" t="n">
+        <x:v>7311</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
+        <x:v>7350.8</x:v>
+      </x:c>
+      <x:c r="H215" s="28" t="n">
+        <x:v>-222.8</x:v>
+      </x:c>
+      <x:c r="I215" s="24" t="n">
+        <x:v>-0.02941797824020287</x:v>
+      </x:c>
+      <x:c r="J215" s="23" t="n">
+        <x:f>ROUND(E215-F215,1)</x:f>
+        <x:v>107.8</x:v>
+      </x:c>
+      <x:c r="K215" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B216" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B216" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="C216" s="30"/>
       <x:c r="D216" s="30"/>
       <x:c r="E216" s="30"/>
@@ -54199,11 +54327,29 @@
       <x:c r="G216" s="30"/>
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="30"/>
-      <x:c r="J216" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
-        <x:v>147</x:v>
+      <x:c r="J216" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J215),1)</x:f>
+        <x:v>1577.6</x:v>
       </x:c>
       <x:c r="K216" s="30"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B217" s="30"/>
+      <x:c r="C217" s="30"/>
+      <x:c r="D217" s="30"/>
+      <x:c r="E217" s="30"/>
+      <x:c r="F217" s="30"/>
+      <x:c r="G217" s="30"/>
+      <x:c r="H217" s="30"/>
+      <x:c r="I217" s="30"/>
+      <x:c r="J217" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
+        <x:v>143.4</x:v>
+      </x:c>
+      <x:c r="K217" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -61119,30 +61265,48 @@
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B215" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C215" s="30"/>
-      <x:c r="D215" s="30"/>
-      <x:c r="E215" s="30"/>
-      <x:c r="F215" s="30"/>
-      <x:c r="G215" s="30"/>
-      <x:c r="H215" s="30"/>
-      <x:c r="I215" s="30"/>
-      <x:c r="J215" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J214),1)</x:f>
-        <x:v>519.4</x:v>
-      </x:c>
-      <x:c r="K215" s="30"/>
+      <x:c r="A215" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B215" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C215" s="22" t="str">
+        <x:v>9月15日</x:v>
+      </x:c>
+      <x:c r="D215" s="23" t="n">
+        <x:v>4383</x:v>
+      </x:c>
+      <x:c r="E215" s="23" t="n">
+        <x:v>4405</x:v>
+      </x:c>
+      <x:c r="F215" s="23" t="n">
+        <x:v>4347.8</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
+        <x:v>4355.8</x:v>
+      </x:c>
+      <x:c r="H215" s="23" t="n">
+        <x:v>-124.4</x:v>
+      </x:c>
+      <x:c r="I215" s="24" t="n">
+        <x:v>-0.027766617561715945</x:v>
+      </x:c>
+      <x:c r="J215" s="23" t="n">
+        <x:f>ROUND(E215-F215,1)</x:f>
+        <x:v>57.2</x:v>
+      </x:c>
+      <x:c r="K215" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B216" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B216" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="C216" s="30"/>
       <x:c r="D216" s="30"/>
       <x:c r="E216" s="30"/>
@@ -61150,11 +61314,29 @@
       <x:c r="G216" s="30"/>
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="30"/>
-      <x:c r="J216" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
-        <x:v>51.9</x:v>
+      <x:c r="J216" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J215),1)</x:f>
+        <x:v>576.6</x:v>
       </x:c>
       <x:c r="K216" s="30"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B217" s="30"/>
+      <x:c r="C217" s="30"/>
+      <x:c r="D217" s="30"/>
+      <x:c r="E217" s="30"/>
+      <x:c r="F217" s="30"/>
+      <x:c r="G217" s="30"/>
+      <x:c r="H217" s="30"/>
+      <x:c r="I217" s="30"/>
+      <x:c r="J217" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
+        <x:v>52.4</x:v>
+      </x:c>
+      <x:c r="K217" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -68070,30 +68252,48 @@
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B215" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C215" s="30"/>
-      <x:c r="D215" s="30"/>
-      <x:c r="E215" s="30"/>
-      <x:c r="F215" s="30"/>
-      <x:c r="G215" s="30"/>
-      <x:c r="H215" s="30"/>
-      <x:c r="I215" s="30"/>
-      <x:c r="J215" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J214),1)</x:f>
-        <x:v>310.2</x:v>
-      </x:c>
-      <x:c r="K215" s="30"/>
+      <x:c r="A215" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B215" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C215" s="22" t="str">
+        <x:v>9月15日</x:v>
+      </x:c>
+      <x:c r="D215" s="23" t="n">
+        <x:v>2858</x:v>
+      </x:c>
+      <x:c r="E215" s="23" t="n">
+        <x:v>2867</x:v>
+      </x:c>
+      <x:c r="F215" s="23" t="n">
+        <x:v>2840</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
+        <x:v>2845</x:v>
+      </x:c>
+      <x:c r="H215" s="23" t="n">
+        <x:v>-15.4</x:v>
+      </x:c>
+      <x:c r="I215" s="24" t="n">
+        <x:v>-0.005383862396867611</x:v>
+      </x:c>
+      <x:c r="J215" s="23" t="n">
+        <x:f>ROUND(E215-F215,1)</x:f>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K215" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B216" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B216" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="C216" s="30"/>
       <x:c r="D216" s="30"/>
       <x:c r="E216" s="30"/>
@@ -68101,11 +68301,29 @@
       <x:c r="G216" s="30"/>
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="30"/>
-      <x:c r="J216" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
-        <x:v>31</x:v>
+      <x:c r="J216" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J215),1)</x:f>
+        <x:v>337.2</x:v>
       </x:c>
       <x:c r="K216" s="30"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B217" s="30"/>
+      <x:c r="C217" s="30"/>
+      <x:c r="D217" s="30"/>
+      <x:c r="E217" s="30"/>
+      <x:c r="F217" s="30"/>
+      <x:c r="G217" s="30"/>
+      <x:c r="H217" s="30"/>
+      <x:c r="I217" s="30"/>
+      <x:c r="J217" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
+        <x:v>30.7</x:v>
+      </x:c>
+      <x:c r="K217" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R52d7b575524b4e3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R51ddcef6e2ca475b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R03896e2b87754d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R2cf22daddac145b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Re5ea151960e5445c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R45deddf554ff4e8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd6b9c370fb944e10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rdb6612c63d364944"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R079d01ab6f114a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="R6d4799ed389e4268"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R87356b81a0934918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rfdc96bba8ae24225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4e6dd5b6814847b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rae832cda3874451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R0a33dc8e6b30486c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rad41b73908644944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R232e08e03dfd440c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rdb8db6eaab9148f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re2f33337450c44e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rb88769f04cf94c75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7483</x:v>
+        <x:v>7523.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7283.4</x:v>
+        <x:v>7413.2</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>199.6</x:v>
+        <x:v>110.6</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>31999.8</x:v>
+        <x:v>32110.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>188.2</x:v>
+        <x:v>187.8</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -638,19 +638,19 @@
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7418.8</x:v>
+        <x:v>7641.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7311</x:v>
+        <x:v>7531</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>107.8</x:v>
+        <x:v>110.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>33321.8</x:v>
+        <x:v>33324.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
         <x:v>194.9</x:v>
@@ -667,19 +667,19 @@
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4405</x:v>
+        <x:v>4495.8</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4347.8</x:v>
+        <x:v>4441</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>57.2</x:v>
+        <x:v>54.8</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12463.2</x:v>
+        <x:v>12460.8</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
         <x:v>72.9</x:v>
@@ -13582,37 +13582,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B163" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月14日-9月15日</x:v>
       </x:c>
       <x:c r="C163" s="23" t="n">
         <x:v>7312</x:v>
       </x:c>
       <x:c r="D163" s="23" t="n">
-        <x:v>7483</x:v>
+        <x:v>7523.8</x:v>
       </x:c>
       <x:c r="E163" s="23" t="n">
         <x:v>7283.4</x:v>
       </x:c>
       <x:c r="F163" s="23" t="n">
-        <x:v>7470</x:v>
+        <x:v>7443.2</x:v>
       </x:c>
       <x:c r="G163" s="23" t="n">
         <x:f>ROUND(F163-F162,1)</x:f>
-        <x:v>54.8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H163" s="24" t="n">
         <x:f>IFERROR(F163/F162-1,"")</x:f>
-        <x:v>0.007390225482792223</x:v>
+        <x:v>0.0037760276189449105</x:v>
       </x:c>
       <x:c r="I163" s="26" t="n">
         <x:f>ROUND(D163-E163,1)</x:f>
-        <x:v>199.6</x:v>
+        <x:v>240.4</x:v>
       </x:c>
       <x:c r="J163" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K163" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -13630,7 +13630,7 @@
       <x:c r="H164" s="30"/>
       <x:c r="I164" s="32" t="n">
         <x:f>ROUND(SUM(I128:I163),1)</x:f>
-        <x:v>15483.4</x:v>
+        <x:v>15524.2</x:v>
       </x:c>
       <x:c r="J164" s="30"/>
       <x:c r="K164" s="30"/>
@@ -13648,7 +13648,7 @@
       <x:c r="H165" s="30"/>
       <x:c r="I165" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I128:I163),0),1)</x:f>
-        <x:v>430.1</x:v>
+        <x:v>431.2</x:v>
       </x:c>
       <x:c r="J165" s="30"/>
       <x:c r="K165" s="30"/>
@@ -15038,25 +15038,25 @@
         <x:v>7482.2</x:v>
       </x:c>
       <x:c r="D204" s="23" t="n">
-        <x:v>7595.2</x:v>
+        <x:v>7641.8</x:v>
       </x:c>
       <x:c r="E204" s="23" t="n">
-        <x:v>7311</x:v>
+        <x:v>7452.2</x:v>
       </x:c>
       <x:c r="F204" s="23" t="n">
-        <x:v>7350.8</x:v>
-      </x:c>
-      <x:c r="G204" s="28" t="n">
+        <x:v>7567.8</x:v>
+      </x:c>
+      <x:c r="G204" s="23" t="n">
         <x:f>ROUND(F204-F203,1)</x:f>
-        <x:v>-218.2</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="H204" s="24" t="n">
         <x:f>IFERROR(F204/F203-1,"")</x:f>
-        <x:v>-0.02882811467829305</x:v>
+        <x:v>-0.00015854141894566798</x:v>
       </x:c>
       <x:c r="I204" s="26" t="n">
         <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>284.2</x:v>
+        <x:v>189.6</x:v>
       </x:c>
       <x:c r="J204" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15080,7 +15080,7 @@
       <x:c r="H205" s="30"/>
       <x:c r="I205" s="32" t="n">
         <x:f>ROUND(SUM(I169:I204),1)</x:f>
-        <x:v>16109.6</x:v>
+        <x:v>16015</x:v>
       </x:c>
       <x:c r="J205" s="30"/>
       <x:c r="K205" s="30"/>
@@ -15098,7 +15098,7 @@
       <x:c r="H206" s="30"/>
       <x:c r="I206" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I169:I204),0),1)</x:f>
-        <x:v>447.5</x:v>
+        <x:v>444.9</x:v>
       </x:c>
       <x:c r="J206" s="30"/>
       <x:c r="K206" s="30"/>
@@ -16491,22 +16491,22 @@
         <x:v>4500.6</x:v>
       </x:c>
       <x:c r="E245" s="23" t="n">
-        <x:v>4347.8</x:v>
+        <x:v>4441</x:v>
       </x:c>
       <x:c r="F245" s="23" t="n">
-        <x:v>4355.8</x:v>
+        <x:v>4449.8</x:v>
       </x:c>
       <x:c r="G245" s="23" t="n">
         <x:f>ROUND(F245-F244,1)</x:f>
-        <x:v>-147.6</x:v>
+        <x:v>-53.6</x:v>
       </x:c>
       <x:c r="H245" s="24" t="n">
         <x:f>IFERROR(F245/F244-1,"")</x:f>
-        <x:v>-0.03277523648798675</x:v>
-      </x:c>
-      <x:c r="I245" s="26" t="n">
+        <x:v>-0.01190211839943145</x:v>
+      </x:c>
+      <x:c r="I245" s="23" t="n">
         <x:f>ROUND(D245-E245,1)</x:f>
-        <x:v>152.8</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="J245" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16530,7 +16530,7 @@
       <x:c r="H246" s="30"/>
       <x:c r="I246" s="32" t="n">
         <x:f>ROUND(SUM(I210:I245),1)</x:f>
-        <x:v>5758</x:v>
+        <x:v>5664.8</x:v>
       </x:c>
       <x:c r="J246" s="30"/>
       <x:c r="K246" s="30"/>
@@ -16548,7 +16548,7 @@
       <x:c r="H247" s="30"/>
       <x:c r="I247" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I210:I245),0),1)</x:f>
-        <x:v>159.9</x:v>
+        <x:v>157.4</x:v>
       </x:c>
       <x:c r="J247" s="30"/>
       <x:c r="K247" s="30"/>
@@ -47327,30 +47327,48 @@
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B215" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C215" s="30"/>
-      <x:c r="D215" s="30"/>
-      <x:c r="E215" s="30"/>
-      <x:c r="F215" s="30"/>
-      <x:c r="G215" s="30"/>
-      <x:c r="H215" s="30"/>
-      <x:c r="I215" s="30"/>
-      <x:c r="J215" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J214),1)</x:f>
-        <x:v>1556</x:v>
-      </x:c>
-      <x:c r="K215" s="30"/>
+      <x:c r="A215" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B215" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C215" s="22" t="str">
+        <x:v>9月15日</x:v>
+      </x:c>
+      <x:c r="D215" s="23" t="n">
+        <x:v>7471</x:v>
+      </x:c>
+      <x:c r="E215" s="23" t="n">
+        <x:v>7523.8</x:v>
+      </x:c>
+      <x:c r="F215" s="23" t="n">
+        <x:v>7413.2</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
+        <x:v>7443.2</x:v>
+      </x:c>
+      <x:c r="H215" s="23" t="n">
+        <x:v>-26.8</x:v>
+      </x:c>
+      <x:c r="I215" s="24" t="n">
+        <x:v>-0.0035876840696118517</x:v>
+      </x:c>
+      <x:c r="J215" s="23" t="n">
+        <x:f>ROUND(E215-F215,1)</x:f>
+        <x:v>110.6</x:v>
+      </x:c>
+      <x:c r="K215" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B216" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B216" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="C216" s="30"/>
       <x:c r="D216" s="30"/>
       <x:c r="E216" s="30"/>
@@ -47358,11 +47376,29 @@
       <x:c r="G216" s="30"/>
       <x:c r="H216" s="30"/>
       <x:c r="I216" s="30"/>
-      <x:c r="J216" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
-        <x:v>155.6</x:v>
+      <x:c r="J216" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J215),1)</x:f>
+        <x:v>1666.6</x:v>
       </x:c>
       <x:c r="K216" s="30"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B217" s="30"/>
+      <x:c r="C217" s="30"/>
+      <x:c r="D217" s="30"/>
+      <x:c r="E217" s="30"/>
+      <x:c r="F217" s="30"/>
+      <x:c r="G217" s="30"/>
+      <x:c r="H217" s="30"/>
+      <x:c r="I217" s="30"/>
+      <x:c r="J217" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
+        <x:v>151.5</x:v>
+      </x:c>
+      <x:c r="K217" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -54288,26 +54324,26 @@
         <x:v>9月15日</x:v>
       </x:c>
       <x:c r="D215" s="23" t="n">
-        <x:v>7351.6</x:v>
+        <x:v>7564.6</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
-        <x:v>7418.8</x:v>
+        <x:v>7641.8</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>7311</x:v>
+        <x:v>7531</x:v>
       </x:c>
       <x:c r="G215" s="23" t="n">
-        <x:v>7350.8</x:v>
-      </x:c>
-      <x:c r="H215" s="28" t="n">
-        <x:v>-222.8</x:v>
+        <x:v>7567.8</x:v>
+      </x:c>
+      <x:c r="H215" s="23" t="n">
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="I215" s="24" t="n">
-        <x:v>-0.02941797824020287</x:v>
+        <x:v>-0.0007658181049963186</x:v>
       </x:c>
       <x:c r="J215" s="23" t="n">
         <x:f>ROUND(E215-F215,1)</x:f>
-        <x:v>107.8</x:v>
+        <x:v>110.8</x:v>
       </x:c>
       <x:c r="K215" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -54329,7 +54365,7 @@
       <x:c r="I216" s="30"/>
       <x:c r="J216" s="32" t="n">
         <x:f>ROUND(SUM(J205:J215),1)</x:f>
-        <x:v>1577.6</x:v>
+        <x:v>1580.6</x:v>
       </x:c>
       <x:c r="K216" s="30"/>
     </x:row>
@@ -54347,7 +54383,7 @@
       <x:c r="I217" s="30"/>
       <x:c r="J217" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
-        <x:v>143.4</x:v>
+        <x:v>143.7</x:v>
       </x:c>
       <x:c r="K217" s="30"/>
     </x:row>
@@ -61275,26 +61311,26 @@
         <x:v>9月15日</x:v>
       </x:c>
       <x:c r="D215" s="23" t="n">
-        <x:v>4383</x:v>
+        <x:v>4479.4</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
-        <x:v>4405</x:v>
+        <x:v>4495.8</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>4347.8</x:v>
+        <x:v>4441</x:v>
       </x:c>
       <x:c r="G215" s="23" t="n">
-        <x:v>4355.8</x:v>
+        <x:v>4449.8</x:v>
       </x:c>
       <x:c r="H215" s="23" t="n">
-        <x:v>-124.4</x:v>
+        <x:v>-30.4</x:v>
       </x:c>
       <x:c r="I215" s="24" t="n">
-        <x:v>-0.027766617561715945</x:v>
+        <x:v>-0.006785411365563987</x:v>
       </x:c>
       <x:c r="J215" s="23" t="n">
         <x:f>ROUND(E215-F215,1)</x:f>
-        <x:v>57.2</x:v>
+        <x:v>54.8</x:v>
       </x:c>
       <x:c r="K215" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -61316,7 +61352,7 @@
       <x:c r="I216" s="30"/>
       <x:c r="J216" s="32" t="n">
         <x:f>ROUND(SUM(J205:J215),1)</x:f>
-        <x:v>576.6</x:v>
+        <x:v>574.2</x:v>
       </x:c>
       <x:c r="K216" s="30"/>
     </x:row>
@@ -61334,7 +61370,7 @@
       <x:c r="I217" s="30"/>
       <x:c r="J217" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
-        <x:v>52.4</x:v>
+        <x:v>52.2</x:v>
       </x:c>
       <x:c r="K217" s="30"/>
     </x:row>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R87356b81a0934918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rfdc96bba8ae24225"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4e6dd5b6814847b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rae832cda3874451b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R0a33dc8e6b30486c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rad41b73908644944"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R232e08e03dfd440c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rdb8db6eaab9148f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re2f33337450c44e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rb88769f04cf94c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rc644f5685e8a475e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R31fe5eb3d745486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R400d64554cdb4d7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Ref4de270daf04e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R4f0e5a61c5864a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R80d81c5c440a47f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R85e0527e566c4754"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R56e7fdb7e8634587"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rf55bb2559d3a458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rf8a1c215fcc84954"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7524.61</x:v>
+        <x:v>7607.89</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7426.9</x:v>
+        <x:v>7402.37</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>97.7</x:v>
+        <x:v>205.5</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>30212.6</x:v>
+        <x:v>30418.1</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>176.7</x:v>
+        <x:v>176.8</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,22 +548,22 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7641.54</x:v>
+        <x:v>7696.47</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7543.95</x:v>
+        <x:v>7523.82</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>97.6</x:v>
+        <x:v>172.7</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>30113.1</x:v>
+        <x:v>30285.8</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
         <x:v>176.1</x:v>
@@ -577,22 +577,22 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3891.62</x:v>
+        <x:v>3894.66</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3858.15</x:v>
+        <x:v>3842.72</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>33.5</x:v>
+        <x:v>51.9</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8262.5</x:v>
+        <x:v>8314.4</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>48.3</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7523.8</x:v>
+        <x:v>7623.6</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7413.2</x:v>
+        <x:v>7401.6</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>110.6</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>32110.4</x:v>
+        <x:v>32332.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>187.8</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,22 +635,22 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7641.8</x:v>
+        <x:v>7710</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7531</x:v>
+        <x:v>7516.2</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>110.8</x:v>
+        <x:v>193.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>33324.8</x:v>
+        <x:v>33518.6</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
         <x:v>194.9</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2867</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2840</x:v>
+        <x:v>2829.4</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>27</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6913.8</x:v>
+        <x:v>6957.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.4</x:v>
+        <x:v>40.5</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -9232,37 +9232,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" s="22" t="str">
-        <x:v>9月14日-9月15日</x:v>
+        <x:v>9月14日-9月16日</x:v>
       </x:c>
       <x:c r="C40" s="23" t="n">
         <x:v>7363.42</x:v>
       </x:c>
       <x:c r="D40" s="23" t="n">
-        <x:v>7524.61</x:v>
+        <x:v>7607.89</x:v>
       </x:c>
       <x:c r="E40" s="23" t="n">
         <x:v>7329.6</x:v>
       </x:c>
       <x:c r="F40" s="23" t="n">
-        <x:v>7437.7</x:v>
-      </x:c>
-      <x:c r="G40" s="23" t="n">
+        <x:v>7587.43</x:v>
+      </x:c>
+      <x:c r="G40" s="28" t="n">
         <x:f>ROUND(F40-F39,1)</x:f>
-        <x:v>10.5</x:v>
+        <x:v>160.2</x:v>
       </x:c>
       <x:c r="H40" s="24" t="n">
         <x:f>IFERROR(F40/F39-1,"")</x:f>
-        <x:v>0.0014083293390276808</x:v>
+        <x:v>0.021567904093579893</x:v>
       </x:c>
       <x:c r="I40" s="26" t="n">
         <x:f>ROUND(D40-E40,1)</x:f>
-        <x:v>195</x:v>
+        <x:v>278.3</x:v>
       </x:c>
       <x:c r="J40" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K40" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -9280,7 +9280,7 @@
       <x:c r="H41" s="30"/>
       <x:c r="I41" s="32" t="n">
         <x:f>ROUND(SUM(I5:I40),1)</x:f>
-        <x:v>14891.6</x:v>
+        <x:v>14974.9</x:v>
       </x:c>
       <x:c r="J41" s="30"/>
       <x:c r="K41" s="30"/>
@@ -9298,7 +9298,7 @@
       <x:c r="H42" s="30"/>
       <x:c r="I42" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I40),0),1)</x:f>
-        <x:v>413.7</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="J42" s="30"/>
       <x:c r="K42" s="30"/>
@@ -10682,37 +10682,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B81" s="22" t="str">
-        <x:v>9月14日-9月15日</x:v>
+        <x:v>9月14日-9月16日</x:v>
       </x:c>
       <x:c r="C81" s="23" t="n">
         <x:v>7511.04</x:v>
       </x:c>
       <x:c r="D81" s="23" t="n">
-        <x:v>7641.54</x:v>
+        <x:v>7696.47</x:v>
       </x:c>
       <x:c r="E81" s="23" t="n">
         <x:v>7487.46</x:v>
       </x:c>
       <x:c r="F81" s="23" t="n">
-        <x:v>7561.59</x:v>
+        <x:v>7683.47</x:v>
       </x:c>
       <x:c r="G81" s="23" t="n">
         <x:f>ROUND(F81-F80,1)</x:f>
-        <x:v>-18.9</x:v>
+        <x:v>102.9</x:v>
       </x:c>
       <x:c r="H81" s="24" t="n">
         <x:f>IFERROR(F81/F80-1,"")</x:f>
-        <x:v>-0.00249982191242315</x:v>
-      </x:c>
-      <x:c r="I81" s="23" t="n">
+        <x:v>0.013578188361251353</x:v>
+      </x:c>
+      <x:c r="I81" s="26" t="n">
         <x:f>ROUND(D81-E81,1)</x:f>
-        <x:v>154.1</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="J81" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K81" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -10730,7 +10730,7 @@
       <x:c r="H82" s="30"/>
       <x:c r="I82" s="32" t="n">
         <x:f>ROUND(SUM(I46:I81),1)</x:f>
-        <x:v>14872.1</x:v>
+        <x:v>14927</x:v>
       </x:c>
       <x:c r="J82" s="30"/>
       <x:c r="K82" s="30"/>
@@ -10748,7 +10748,7 @@
       <x:c r="H83" s="30"/>
       <x:c r="I83" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I46:I81),0),1)</x:f>
-        <x:v>413.1</x:v>
+        <x:v>414.6</x:v>
       </x:c>
       <x:c r="J83" s="30"/>
       <x:c r="K83" s="30"/>
@@ -12132,7 +12132,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B122" s="22" t="str">
-        <x:v>9月14日-9月15日</x:v>
+        <x:v>9月14日-9月16日</x:v>
       </x:c>
       <x:c r="C122" s="23" t="n">
         <x:v>3867.02</x:v>
@@ -12141,28 +12141,28 @@
         <x:v>3895.51</x:v>
       </x:c>
       <x:c r="E122" s="23" t="n">
-        <x:v>3858.15</x:v>
+        <x:v>3842.72</x:v>
       </x:c>
       <x:c r="F122" s="23" t="n">
-        <x:v>3864.28</x:v>
+        <x:v>3891.6</x:v>
       </x:c>
       <x:c r="G122" s="23" t="n">
         <x:f>ROUND(F122-F121,1)</x:f>
-        <x:v>-23.8</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="H122" s="24" t="n">
         <x:f>IFERROR(F122/F121-1,"")</x:f>
-        <x:v>-0.006128941825205514</x:v>
-      </x:c>
-      <x:c r="I122" s="23" t="n">
+        <x:v>0.0008976083495579879</x:v>
+      </x:c>
+      <x:c r="I122" s="26" t="n">
         <x:f>ROUND(D122-E122,1)</x:f>
-        <x:v>37.4</x:v>
+        <x:v>52.8</x:v>
       </x:c>
       <x:c r="J122" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K122" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -12180,7 +12180,7 @@
       <x:c r="H123" s="30"/>
       <x:c r="I123" s="32" t="n">
         <x:f>ROUND(SUM(I87:I122),1)</x:f>
-        <x:v>3901.5</x:v>
+        <x:v>3916.9</x:v>
       </x:c>
       <x:c r="J123" s="30"/>
       <x:c r="K123" s="30"/>
@@ -12198,7 +12198,7 @@
       <x:c r="H124" s="30"/>
       <x:c r="I124" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I87:I122),0),1)</x:f>
-        <x:v>108.4</x:v>
+        <x:v>108.8</x:v>
       </x:c>
       <x:c r="J124" s="30"/>
       <x:c r="K124" s="30"/>
@@ -13582,37 +13582,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B163" s="22" t="str">
-        <x:v>9月14日-9月15日</x:v>
+        <x:v>9月14日-9月16日</x:v>
       </x:c>
       <x:c r="C163" s="23" t="n">
         <x:v>7312</x:v>
       </x:c>
       <x:c r="D163" s="23" t="n">
-        <x:v>7523.8</x:v>
+        <x:v>7623.6</x:v>
       </x:c>
       <x:c r="E163" s="23" t="n">
         <x:v>7283.4</x:v>
       </x:c>
       <x:c r="F163" s="23" t="n">
-        <x:v>7443.2</x:v>
-      </x:c>
-      <x:c r="G163" s="23" t="n">
+        <x:v>7593</x:v>
+      </x:c>
+      <x:c r="G163" s="28" t="n">
         <x:f>ROUND(F163-F162,1)</x:f>
-        <x:v>28</x:v>
+        <x:v>177.8</x:v>
       </x:c>
       <x:c r="H163" s="24" t="n">
         <x:f>IFERROR(F163/F162-1,"")</x:f>
-        <x:v>0.0037760276189449105</x:v>
+        <x:v>0.02397777538029988</x:v>
       </x:c>
       <x:c r="I163" s="26" t="n">
         <x:f>ROUND(D163-E163,1)</x:f>
-        <x:v>240.4</x:v>
+        <x:v>340.2</x:v>
       </x:c>
       <x:c r="J163" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K163" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -13630,7 +13630,7 @@
       <x:c r="H164" s="30"/>
       <x:c r="I164" s="32" t="n">
         <x:f>ROUND(SUM(I128:I163),1)</x:f>
-        <x:v>15524.2</x:v>
+        <x:v>15624</x:v>
       </x:c>
       <x:c r="J164" s="30"/>
       <x:c r="K164" s="30"/>
@@ -13648,7 +13648,7 @@
       <x:c r="H165" s="30"/>
       <x:c r="I165" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I128:I163),0),1)</x:f>
-        <x:v>431.2</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="J165" s="30"/>
       <x:c r="K165" s="30"/>
@@ -15032,37 +15032,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B204" s="22" t="str">
-        <x:v>9月14日-9月15日</x:v>
+        <x:v>9月14日-9月16日</x:v>
       </x:c>
       <x:c r="C204" s="23" t="n">
         <x:v>7482.2</x:v>
       </x:c>
       <x:c r="D204" s="23" t="n">
-        <x:v>7641.8</x:v>
+        <x:v>7710</x:v>
       </x:c>
       <x:c r="E204" s="23" t="n">
         <x:v>7452.2</x:v>
       </x:c>
       <x:c r="F204" s="23" t="n">
-        <x:v>7567.8</x:v>
+        <x:v>7689.6</x:v>
       </x:c>
       <x:c r="G204" s="23" t="n">
         <x:f>ROUND(F204-F203,1)</x:f>
-        <x:v>-1.2</x:v>
+        <x:v>120.6</x:v>
       </x:c>
       <x:c r="H204" s="24" t="n">
         <x:f>IFERROR(F204/F203-1,"")</x:f>
-        <x:v>-0.00015854141894566798</x:v>
+        <x:v>0.015933412604042907</x:v>
       </x:c>
       <x:c r="I204" s="26" t="n">
         <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>189.6</x:v>
+        <x:v>257.8</x:v>
       </x:c>
       <x:c r="J204" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K204" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -15080,7 +15080,7 @@
       <x:c r="H205" s="30"/>
       <x:c r="I205" s="32" t="n">
         <x:f>ROUND(SUM(I169:I204),1)</x:f>
-        <x:v>16015</x:v>
+        <x:v>16083.2</x:v>
       </x:c>
       <x:c r="J205" s="30"/>
       <x:c r="K205" s="30"/>
@@ -15098,7 +15098,7 @@
       <x:c r="H206" s="30"/>
       <x:c r="I206" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I169:I204),0),1)</x:f>
-        <x:v>444.9</x:v>
+        <x:v>446.8</x:v>
       </x:c>
       <x:c r="J206" s="30"/>
       <x:c r="K206" s="30"/>
@@ -17932,37 +17932,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B286" s="22" t="str">
-        <x:v>9月14日-9月15日</x:v>
+        <x:v>9月14日-9月16日</x:v>
       </x:c>
       <x:c r="C286" s="23" t="n">
         <x:v>2849.2</x:v>
       </x:c>
       <x:c r="D286" s="23" t="n">
-        <x:v>2867</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="E286" s="23" t="n">
-        <x:v>2840</x:v>
+        <x:v>2829.4</x:v>
       </x:c>
       <x:c r="F286" s="23" t="n">
-        <x:v>2845</x:v>
+        <x:v>2865</x:v>
       </x:c>
       <x:c r="G286" s="23" t="n">
         <x:f>ROUND(F286-F285,1)</x:f>
-        <x:v>-22</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="H286" s="24" t="n">
         <x:f>IFERROR(F286/F285-1,"")</x:f>
-        <x:v>-0.007673526334147196</x:v>
+        <x:v>-0.0006975933031042603</x:v>
       </x:c>
       <x:c r="I286" s="23" t="n">
         <x:f>ROUND(D286-E286,1)</x:f>
-        <x:v>27</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="J286" s="22" t="str">
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K286" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -17980,7 +17980,7 @@
       <x:c r="H287" s="30"/>
       <x:c r="I287" s="32" t="n">
         <x:f>ROUND(SUM(I251:I286),1)</x:f>
-        <x:v>3242.6</x:v>
+        <x:v>3259.4</x:v>
       </x:c>
       <x:c r="J287" s="30"/>
       <x:c r="K287" s="30"/>
@@ -17998,7 +17998,7 @@
       <x:c r="H288" s="30"/>
       <x:c r="I288" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I251:I286),0),1)</x:f>
-        <x:v>90.1</x:v>
+        <x:v>90.5</x:v>
       </x:c>
       <x:c r="J288" s="30"/>
       <x:c r="K288" s="30"/>
@@ -26402,30 +26402,48 @@
       </x:c>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B216" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C216" s="30"/>
-      <x:c r="D216" s="30"/>
-      <x:c r="E216" s="30"/>
-      <x:c r="F216" s="30"/>
-      <x:c r="G216" s="30"/>
-      <x:c r="H216" s="30"/>
-      <x:c r="I216" s="30"/>
-      <x:c r="J216" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J215),1)</x:f>
-        <x:v>1481.8</x:v>
-      </x:c>
-      <x:c r="K216" s="30"/>
+      <x:c r="A216" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B216" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C216" s="22" t="str">
+        <x:v>9月16日</x:v>
+      </x:c>
+      <x:c r="D216" s="23" t="n">
+        <x:v>7437.82</x:v>
+      </x:c>
+      <x:c r="E216" s="23" t="n">
+        <x:v>7607.89</x:v>
+      </x:c>
+      <x:c r="F216" s="23" t="n">
+        <x:v>7402.37</x:v>
+      </x:c>
+      <x:c r="G216" s="23" t="n">
+        <x:v>7587.43</x:v>
+      </x:c>
+      <x:c r="H216" s="23" t="n">
+        <x:v>149.7</x:v>
+      </x:c>
+      <x:c r="I216" s="24" t="n">
+        <x:v>0.020131223362060968</x:v>
+      </x:c>
+      <x:c r="J216" s="26" t="n">
+        <x:f>ROUND(E216-F216,1)</x:f>
+        <x:v>205.5</x:v>
+      </x:c>
+      <x:c r="K216" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B217" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B217" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C217" s="30"/>
       <x:c r="D217" s="30"/>
       <x:c r="E217" s="30"/>
@@ -26433,11 +26451,29 @@
       <x:c r="G217" s="30"/>
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="30"/>
-      <x:c r="J217" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
-        <x:v>134.7</x:v>
+      <x:c r="J217" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J216),1)</x:f>
+        <x:v>1687.3</x:v>
       </x:c>
       <x:c r="K217" s="30"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B218" s="30"/>
+      <x:c r="C218" s="30"/>
+      <x:c r="D218" s="30"/>
+      <x:c r="E218" s="30"/>
+      <x:c r="F218" s="30"/>
+      <x:c r="G218" s="30"/>
+      <x:c r="H218" s="30"/>
+      <x:c r="I218" s="30"/>
+      <x:c r="J218" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
+        <x:v>140.6</x:v>
+      </x:c>
+      <x:c r="K218" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -33389,30 +33425,48 @@
       </x:c>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B216" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C216" s="30"/>
-      <x:c r="D216" s="30"/>
-      <x:c r="E216" s="30"/>
-      <x:c r="F216" s="30"/>
-      <x:c r="G216" s="30"/>
-      <x:c r="H216" s="30"/>
-      <x:c r="I216" s="30"/>
-      <x:c r="J216" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J215),1)</x:f>
-        <x:v>1329.4</x:v>
-      </x:c>
-      <x:c r="K216" s="30"/>
+      <x:c r="A216" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B216" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C216" s="22" t="str">
+        <x:v>9月16日</x:v>
+      </x:c>
+      <x:c r="D216" s="23" t="n">
+        <x:v>7556.9</x:v>
+      </x:c>
+      <x:c r="E216" s="23" t="n">
+        <x:v>7696.47</x:v>
+      </x:c>
+      <x:c r="F216" s="23" t="n">
+        <x:v>7523.82</x:v>
+      </x:c>
+      <x:c r="G216" s="23" t="n">
+        <x:v>7683.47</x:v>
+      </x:c>
+      <x:c r="H216" s="23" t="n">
+        <x:v>121.9</x:v>
+      </x:c>
+      <x:c r="I216" s="24" t="n">
+        <x:v>0.016118303161107628</x:v>
+      </x:c>
+      <x:c r="J216" s="26" t="n">
+        <x:f>ROUND(E216-F216,1)</x:f>
+        <x:v>172.7</x:v>
+      </x:c>
+      <x:c r="K216" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B217" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B217" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C217" s="30"/>
       <x:c r="D217" s="30"/>
       <x:c r="E217" s="30"/>
@@ -33420,11 +33474,29 @@
       <x:c r="G217" s="30"/>
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="30"/>
-      <x:c r="J217" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
-        <x:v>120.9</x:v>
+      <x:c r="J217" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J216),1)</x:f>
+        <x:v>1502.1</x:v>
       </x:c>
       <x:c r="K217" s="30"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B218" s="30"/>
+      <x:c r="C218" s="30"/>
+      <x:c r="D218" s="30"/>
+      <x:c r="E218" s="30"/>
+      <x:c r="F218" s="30"/>
+      <x:c r="G218" s="30"/>
+      <x:c r="H218" s="30"/>
+      <x:c r="I218" s="30"/>
+      <x:c r="J218" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
+        <x:v>125.2</x:v>
+      </x:c>
+      <x:c r="K218" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -40376,30 +40448,48 @@
       </x:c>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B216" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C216" s="30"/>
-      <x:c r="D216" s="30"/>
-      <x:c r="E216" s="30"/>
-      <x:c r="F216" s="30"/>
-      <x:c r="G216" s="30"/>
-      <x:c r="H216" s="30"/>
-      <x:c r="I216" s="30"/>
-      <x:c r="J216" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J215),1)</x:f>
-        <x:v>381.4</x:v>
-      </x:c>
-      <x:c r="K216" s="30"/>
+      <x:c r="A216" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B216" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C216" s="22" t="str">
+        <x:v>9月16日</x:v>
+      </x:c>
+      <x:c r="D216" s="23" t="n">
+        <x:v>3861.75</x:v>
+      </x:c>
+      <x:c r="E216" s="23" t="n">
+        <x:v>3894.66</x:v>
+      </x:c>
+      <x:c r="F216" s="23" t="n">
+        <x:v>3842.72</x:v>
+      </x:c>
+      <x:c r="G216" s="23" t="n">
+        <x:v>3891.6</x:v>
+      </x:c>
+      <x:c r="H216" s="23" t="n">
+        <x:v>27.3</x:v>
+      </x:c>
+      <x:c r="I216" s="24" t="n">
+        <x:v>0.007069881064519112</x:v>
+      </x:c>
+      <x:c r="J216" s="26" t="n">
+        <x:f>ROUND(E216-F216,1)</x:f>
+        <x:v>51.9</x:v>
+      </x:c>
+      <x:c r="K216" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B217" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B217" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C217" s="30"/>
       <x:c r="D217" s="30"/>
       <x:c r="E217" s="30"/>
@@ -40407,11 +40497,29 @@
       <x:c r="G217" s="30"/>
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="30"/>
-      <x:c r="J217" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
-        <x:v>34.7</x:v>
+      <x:c r="J217" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J216),1)</x:f>
+        <x:v>433.3</x:v>
       </x:c>
       <x:c r="K217" s="30"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B218" s="30"/>
+      <x:c r="C218" s="30"/>
+      <x:c r="D218" s="30"/>
+      <x:c r="E218" s="30"/>
+      <x:c r="F218" s="30"/>
+      <x:c r="G218" s="30"/>
+      <x:c r="H218" s="30"/>
+      <x:c r="I218" s="30"/>
+      <x:c r="J218" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
+        <x:v>36.1</x:v>
+      </x:c>
+      <x:c r="K218" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -47363,30 +47471,48 @@
       </x:c>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B216" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C216" s="30"/>
-      <x:c r="D216" s="30"/>
-      <x:c r="E216" s="30"/>
-      <x:c r="F216" s="30"/>
-      <x:c r="G216" s="30"/>
-      <x:c r="H216" s="30"/>
-      <x:c r="I216" s="30"/>
-      <x:c r="J216" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J215),1)</x:f>
-        <x:v>1666.6</x:v>
-      </x:c>
-      <x:c r="K216" s="30"/>
+      <x:c r="A216" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B216" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C216" s="22" t="str">
+        <x:v>9月16日</x:v>
+      </x:c>
+      <x:c r="D216" s="23" t="n">
+        <x:v>7456.2</x:v>
+      </x:c>
+      <x:c r="E216" s="23" t="n">
+        <x:v>7623.6</x:v>
+      </x:c>
+      <x:c r="F216" s="23" t="n">
+        <x:v>7401.6</x:v>
+      </x:c>
+      <x:c r="G216" s="23" t="n">
+        <x:v>7593</x:v>
+      </x:c>
+      <x:c r="H216" s="23" t="n">
+        <x:v>149.8</x:v>
+      </x:c>
+      <x:c r="I216" s="24" t="n">
+        <x:v>0.020125752364574367</x:v>
+      </x:c>
+      <x:c r="J216" s="26" t="n">
+        <x:f>ROUND(E216-F216,1)</x:f>
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="K216" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B217" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B217" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C217" s="30"/>
       <x:c r="D217" s="30"/>
       <x:c r="E217" s="30"/>
@@ -47394,11 +47520,29 @@
       <x:c r="G217" s="30"/>
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="30"/>
-      <x:c r="J217" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
-        <x:v>151.5</x:v>
+      <x:c r="J217" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J216),1)</x:f>
+        <x:v>1888.6</x:v>
       </x:c>
       <x:c r="K217" s="30"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B218" s="30"/>
+      <x:c r="C218" s="30"/>
+      <x:c r="D218" s="30"/>
+      <x:c r="E218" s="30"/>
+      <x:c r="F218" s="30"/>
+      <x:c r="G218" s="30"/>
+      <x:c r="H218" s="30"/>
+      <x:c r="I218" s="30"/>
+      <x:c r="J218" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
+        <x:v>157.4</x:v>
+      </x:c>
+      <x:c r="K218" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -54350,30 +54494,48 @@
       </x:c>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B216" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C216" s="30"/>
-      <x:c r="D216" s="30"/>
-      <x:c r="E216" s="30"/>
-      <x:c r="F216" s="30"/>
-      <x:c r="G216" s="30"/>
-      <x:c r="H216" s="30"/>
-      <x:c r="I216" s="30"/>
-      <x:c r="J216" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J215),1)</x:f>
-        <x:v>1580.6</x:v>
-      </x:c>
-      <x:c r="K216" s="30"/>
+      <x:c r="A216" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B216" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C216" s="22" t="str">
+        <x:v>9月16日</x:v>
+      </x:c>
+      <x:c r="D216" s="23" t="n">
+        <x:v>7571.8</x:v>
+      </x:c>
+      <x:c r="E216" s="23" t="n">
+        <x:v>7710</x:v>
+      </x:c>
+      <x:c r="F216" s="23" t="n">
+        <x:v>7516.2</x:v>
+      </x:c>
+      <x:c r="G216" s="23" t="n">
+        <x:v>7689.6</x:v>
+      </x:c>
+      <x:c r="H216" s="23" t="n">
+        <x:v>121.8</x:v>
+      </x:c>
+      <x:c r="I216" s="24" t="n">
+        <x:v>0.016094505668754477</x:v>
+      </x:c>
+      <x:c r="J216" s="26" t="n">
+        <x:f>ROUND(E216-F216,1)</x:f>
+        <x:v>193.8</x:v>
+      </x:c>
+      <x:c r="K216" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B217" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B217" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C217" s="30"/>
       <x:c r="D217" s="30"/>
       <x:c r="E217" s="30"/>
@@ -54381,11 +54543,29 @@
       <x:c r="G217" s="30"/>
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="30"/>
-      <x:c r="J217" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
-        <x:v>143.7</x:v>
+      <x:c r="J217" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J216),1)</x:f>
+        <x:v>1774.4</x:v>
       </x:c>
       <x:c r="K217" s="30"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B218" s="30"/>
+      <x:c r="C218" s="30"/>
+      <x:c r="D218" s="30"/>
+      <x:c r="E218" s="30"/>
+      <x:c r="F218" s="30"/>
+      <x:c r="G218" s="30"/>
+      <x:c r="H218" s="30"/>
+      <x:c r="I218" s="30"/>
+      <x:c r="J218" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
+        <x:v>147.9</x:v>
+      </x:c>
+      <x:c r="K218" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -68324,30 +68504,48 @@
       </x:c>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B216" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C216" s="30"/>
-      <x:c r="D216" s="30"/>
-      <x:c r="E216" s="30"/>
-      <x:c r="F216" s="30"/>
-      <x:c r="G216" s="30"/>
-      <x:c r="H216" s="30"/>
-      <x:c r="I216" s="30"/>
-      <x:c r="J216" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J215),1)</x:f>
-        <x:v>337.2</x:v>
-      </x:c>
-      <x:c r="K216" s="30"/>
+      <x:c r="A216" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B216" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C216" s="22" t="str">
+        <x:v>9月16日</x:v>
+      </x:c>
+      <x:c r="D216" s="23" t="n">
+        <x:v>2848.2</x:v>
+      </x:c>
+      <x:c r="E216" s="23" t="n">
+        <x:v>2873.2</x:v>
+      </x:c>
+      <x:c r="F216" s="23" t="n">
+        <x:v>2829.4</x:v>
+      </x:c>
+      <x:c r="G216" s="23" t="n">
+        <x:v>2865</x:v>
+      </x:c>
+      <x:c r="H216" s="23" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I216" s="24" t="n">
+        <x:v>0.007029876977152849</x:v>
+      </x:c>
+      <x:c r="J216" s="23" t="n">
+        <x:f>ROUND(E216-F216,1)</x:f>
+        <x:v>43.8</x:v>
+      </x:c>
+      <x:c r="K216" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B217" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B217" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C217" s="30"/>
       <x:c r="D217" s="30"/>
       <x:c r="E217" s="30"/>
@@ -68355,11 +68553,29 @@
       <x:c r="G217" s="30"/>
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="30"/>
-      <x:c r="J217" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
-        <x:v>30.7</x:v>
+      <x:c r="J217" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J216),1)</x:f>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="K217" s="30"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B218" s="30"/>
+      <x:c r="C218" s="30"/>
+      <x:c r="D218" s="30"/>
+      <x:c r="E218" s="30"/>
+      <x:c r="F218" s="30"/>
+      <x:c r="G218" s="30"/>
+      <x:c r="H218" s="30"/>
+      <x:c r="I218" s="30"/>
+      <x:c r="J218" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
+        <x:v>31.8</x:v>
+      </x:c>
+      <x:c r="K218" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rc644f5685e8a475e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R31fe5eb3d745486a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R400d64554cdb4d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Ref4de270daf04e14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R4f0e5a61c5864a48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R80d81c5c440a47f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R85e0527e566c4754"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R56e7fdb7e8634587"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rf55bb2559d3a458c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rf8a1c215fcc84954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rd5995deb967c49c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R55c9859f4f484062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R87c4e78d34f741bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R8a383313c8a84c18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R841bc4bf180e472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rf2f1b7de696e4d2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Ra0b05f9e352d40d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Raff9ce61092a4717"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R96a9edf25f244748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rb7a2c88f09d446a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -664,22 +664,22 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4495.8</x:v>
+        <x:v>4487</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4441</x:v>
+        <x:v>4412.2</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>54.8</x:v>
+        <x:v>74.8</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12460.8</x:v>
+        <x:v>12535.6</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
         <x:v>72.9</x:v>
@@ -16482,7 +16482,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B245" s="22" t="str">
-        <x:v>9月14日-9月15日</x:v>
+        <x:v>9月14日-9月16日</x:v>
       </x:c>
       <x:c r="C245" s="23" t="n">
         <x:v>4468</x:v>
@@ -16491,28 +16491,28 @@
         <x:v>4500.6</x:v>
       </x:c>
       <x:c r="E245" s="23" t="n">
-        <x:v>4441</x:v>
+        <x:v>4412.2</x:v>
       </x:c>
       <x:c r="F245" s="23" t="n">
-        <x:v>4449.8</x:v>
+        <x:v>4478</x:v>
       </x:c>
       <x:c r="G245" s="23" t="n">
         <x:f>ROUND(F245-F244,1)</x:f>
-        <x:v>-53.6</x:v>
+        <x:v>-25.4</x:v>
       </x:c>
       <x:c r="H245" s="24" t="n">
         <x:f>IFERROR(F245/F244-1,"")</x:f>
-        <x:v>-0.01190211839943145</x:v>
+        <x:v>-0.005640182972864838</x:v>
       </x:c>
       <x:c r="I245" s="23" t="n">
         <x:f>ROUND(D245-E245,1)</x:f>
-        <x:v>59.6</x:v>
+        <x:v>88.4</x:v>
       </x:c>
       <x:c r="J245" s="22" t="str">
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K245" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
@@ -16530,7 +16530,7 @@
       <x:c r="H246" s="30"/>
       <x:c r="I246" s="32" t="n">
         <x:f>ROUND(SUM(I210:I245),1)</x:f>
-        <x:v>5664.8</x:v>
+        <x:v>5693.6</x:v>
       </x:c>
       <x:c r="J246" s="30"/>
       <x:c r="K246" s="30"/>
@@ -16548,7 +16548,7 @@
       <x:c r="H247" s="30"/>
       <x:c r="I247" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I210:I245),0),1)</x:f>
-        <x:v>157.4</x:v>
+        <x:v>158.2</x:v>
       </x:c>
       <x:c r="J247" s="30"/>
       <x:c r="K247" s="30"/>
@@ -61517,30 +61517,48 @@
       </x:c>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B216" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C216" s="30"/>
-      <x:c r="D216" s="30"/>
-      <x:c r="E216" s="30"/>
-      <x:c r="F216" s="30"/>
-      <x:c r="G216" s="30"/>
-      <x:c r="H216" s="30"/>
-      <x:c r="I216" s="30"/>
-      <x:c r="J216" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J215),1)</x:f>
-        <x:v>574.2</x:v>
-      </x:c>
-      <x:c r="K216" s="30"/>
+      <x:c r="A216" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B216" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C216" s="22" t="str">
+        <x:v>9月16日</x:v>
+      </x:c>
+      <x:c r="D216" s="23" t="n">
+        <x:v>4452.2</x:v>
+      </x:c>
+      <x:c r="E216" s="23" t="n">
+        <x:v>4487</x:v>
+      </x:c>
+      <x:c r="F216" s="23" t="n">
+        <x:v>4412.2</x:v>
+      </x:c>
+      <x:c r="G216" s="23" t="n">
+        <x:v>4478</x:v>
+      </x:c>
+      <x:c r="H216" s="23" t="n">
+        <x:v>28.2</x:v>
+      </x:c>
+      <x:c r="I216" s="24" t="n">
+        <x:v>0.006337363477010083</x:v>
+      </x:c>
+      <x:c r="J216" s="23" t="n">
+        <x:f>ROUND(E216-F216,1)</x:f>
+        <x:v>74.8</x:v>
+      </x:c>
+      <x:c r="K216" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B217" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B217" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="C217" s="30"/>
       <x:c r="D217" s="30"/>
       <x:c r="E217" s="30"/>
@@ -61548,11 +61566,29 @@
       <x:c r="G217" s="30"/>
       <x:c r="H217" s="30"/>
       <x:c r="I217" s="30"/>
-      <x:c r="J217" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J215),0),1)</x:f>
-        <x:v>52.2</x:v>
+      <x:c r="J217" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J216),1)</x:f>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="K217" s="30"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B218" s="30"/>
+      <x:c r="C218" s="30"/>
+      <x:c r="D218" s="30"/>
+      <x:c r="E218" s="30"/>
+      <x:c r="F218" s="30"/>
+      <x:c r="G218" s="30"/>
+      <x:c r="H218" s="30"/>
+      <x:c r="I218" s="30"/>
+      <x:c r="J218" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
+        <x:v>54.1</x:v>
+      </x:c>
+      <x:c r="K218" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rd5995deb967c49c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R55c9859f4f484062"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R87c4e78d34f741bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R8a383313c8a84c18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R841bc4bf180e472c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rf2f1b7de696e4d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Ra0b05f9e352d40d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Raff9ce61092a4717"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R96a9edf25f244748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2609" sheetId="10" r:id="Rb7a2c88f09d446a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R676b62e0eaa54700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R62ce6d5f6df84fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R22361924cb60450f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Re43b6e0dddbb4dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R1c065f3117f04a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R4f5e6c1a7b4d4f77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rdce5b2dabb224a59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Reef1aada8fa349ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R5fd501c33fdd4dea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R1f18088bf2c147a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -719,28 +719,28 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="9" t="str">
-        <x:v>碳酸锂2609</x:v>
+        <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>135500</x:v>
+        <x:v>130660</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>135500</x:v>
+        <x:v>126200</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>4460</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1402960</x:v>
+        <x:v>1385840</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8252.7</x:v>
+        <x:v>8057.2</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -860,16 +860,16 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="7" t="str">
-        <x:v>碳酸锂2609</x:v>
+        <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="C22" s="7" t="str">
         <x:v>固定合约日线</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
-        <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=LC2609</x:v>
+        <x:v>https://stock2.finance.sina.com.cn/futures/api/json.php/InnerFuturesNewService.getDailyKLine?symbol=LC2610</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -899,7 +899,7 @@
   <x:sheetData>
     <x:row r="1" ht="38" customHeight="1">
       <x:c r="A1" s="15" t="str">
-        <x:v>2026年统计 - 碳酸锂2609</x:v>
+        <x:v>2026年统计 - 碳酸锂2610</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -963,29 +963,29 @@
         <x:v>1月5日</x:v>
       </x:c>
       <x:c r="D5" s="23" t="n">
-        <x:v>126360</x:v>
+        <x:v>132800</x:v>
       </x:c>
       <x:c r="E5" s="23" t="n">
-        <x:v>132400</x:v>
+        <x:v>132800</x:v>
       </x:c>
       <x:c r="F5" s="23" t="n">
-        <x:v>125160</x:v>
+        <x:v>123500</x:v>
       </x:c>
       <x:c r="G5" s="23" t="n">
-        <x:v>131940</x:v>
+        <x:v>131820</x:v>
       </x:c>
       <x:c r="H5" s="28" t="n">
-        <x:v>7980</x:v>
+        <x:v>8360</x:v>
       </x:c>
       <x:c r="I5" s="24" t="n">
-        <x:v>0.06437560503388196</x:v>
+        <x:v>0.06771423942977473</x:v>
       </x:c>
       <x:c r="J5" s="26" t="n">
         <x:f>ROUND(E5-F5,1)</x:f>
-        <x:v>7240</x:v>
+        <x:v>9300</x:v>
       </x:c>
       <x:c r="K5" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -999,29 +999,29 @@
         <x:v>1月6日</x:v>
       </x:c>
       <x:c r="D6" s="23" t="n">
-        <x:v>133860</x:v>
+        <x:v>134100</x:v>
       </x:c>
       <x:c r="E6" s="23" t="n">
-        <x:v>140020</x:v>
+        <x:v>138720</x:v>
       </x:c>
       <x:c r="F6" s="23" t="n">
-        <x:v>133860</x:v>
+        <x:v>134020</x:v>
       </x:c>
       <x:c r="G6" s="23" t="n">
-        <x:v>140020</x:v>
+        <x:v>138720</x:v>
       </x:c>
       <x:c r="H6" s="28" t="n">
-        <x:v>8080</x:v>
+        <x:v>6900</x:v>
       </x:c>
       <x:c r="I6" s="24" t="n">
-        <x:v>0.06123995755646505</x:v>
-      </x:c>
-      <x:c r="J6" s="26" t="n">
+        <x:v>0.05234410559854341</x:v>
+      </x:c>
+      <x:c r="J6" s="23" t="n">
         <x:f>ROUND(E6-F6,1)</x:f>
-        <x:v>6160</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="K6" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1035,29 +1035,29 @@
         <x:v>1月7日</x:v>
       </x:c>
       <x:c r="D7" s="23" t="n">
-        <x:v>144180</x:v>
+        <x:v>144500</x:v>
       </x:c>
       <x:c r="E7" s="23" t="n">
-        <x:v>149000</x:v>
+        <x:v>148420</x:v>
       </x:c>
       <x:c r="F7" s="23" t="n">
-        <x:v>140300</x:v>
+        <x:v>139700</x:v>
       </x:c>
       <x:c r="G7" s="23" t="n">
-        <x:v>144380</x:v>
+        <x:v>143880</x:v>
       </x:c>
       <x:c r="H7" s="28" t="n">
-        <x:v>4360</x:v>
+        <x:v>5160</x:v>
       </x:c>
       <x:c r="I7" s="24" t="n">
-        <x:v>0.031138408798742967</x:v>
+        <x:v>0.037197231833909994</x:v>
       </x:c>
       <x:c r="J7" s="26" t="n">
         <x:f>ROUND(E7-F7,1)</x:f>
-        <x:v>8700</x:v>
+        <x:v>8720</x:v>
       </x:c>
       <x:c r="K7" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1071,29 +1071,29 @@
         <x:v>1月8日</x:v>
       </x:c>
       <x:c r="D8" s="23" t="n">
-        <x:v>143900</x:v>
+        <x:v>143160</x:v>
       </x:c>
       <x:c r="E8" s="23" t="n">
-        <x:v>150760</x:v>
+        <x:v>150100</x:v>
       </x:c>
       <x:c r="F8" s="23" t="n">
-        <x:v>139120</x:v>
+        <x:v>138340</x:v>
       </x:c>
       <x:c r="G8" s="23" t="n">
-        <x:v>146940</x:v>
+        <x:v>146860</x:v>
       </x:c>
       <x:c r="H8" s="28" t="n">
-        <x:v>2560</x:v>
+        <x:v>2980</x:v>
       </x:c>
       <x:c r="I8" s="24" t="n">
-        <x:v>0.01773098767142267</x:v>
+        <x:v>0.02071170419794277</x:v>
       </x:c>
       <x:c r="J8" s="26" t="n">
         <x:f>ROUND(E8-F8,1)</x:f>
-        <x:v>11640</x:v>
+        <x:v>11760</x:v>
       </x:c>
       <x:c r="K8" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1107,29 +1107,29 @@
         <x:v>1月9日</x:v>
       </x:c>
       <x:c r="D9" s="23" t="n">
-        <x:v>147000</x:v>
+        <x:v>145280</x:v>
       </x:c>
       <x:c r="E9" s="23" t="n">
-        <x:v>149000</x:v>
+        <x:v>149240</x:v>
       </x:c>
       <x:c r="F9" s="23" t="n">
-        <x:v>141500</x:v>
+        <x:v>141560</x:v>
       </x:c>
       <x:c r="G9" s="23" t="n">
-        <x:v>145380</x:v>
+        <x:v>145600</x:v>
       </x:c>
       <x:c r="H9" s="28" t="n">
-        <x:v>-1560</x:v>
+        <x:v>-1260</x:v>
       </x:c>
       <x:c r="I9" s="24" t="n">
-        <x:v>-0.010616578195181692</x:v>
+        <x:v>-0.008579599618684486</x:v>
       </x:c>
       <x:c r="J9" s="26" t="n">
         <x:f>ROUND(E9-F9,1)</x:f>
-        <x:v>7500</x:v>
+        <x:v>7680</x:v>
       </x:c>
       <x:c r="K9" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1143,29 +1143,29 @@
         <x:v>1月12日</x:v>
       </x:c>
       <x:c r="D10" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>149180</x:v>
       </x:c>
       <x:c r="E10" s="23" t="n">
-        <x:v>158420</x:v>
+        <x:v>159000</x:v>
       </x:c>
       <x:c r="F10" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>149180</x:v>
       </x:c>
       <x:c r="G10" s="23" t="n">
-        <x:v>158420</x:v>
+        <x:v>159000</x:v>
       </x:c>
       <x:c r="H10" s="28" t="n">
-        <x:v>13040</x:v>
+        <x:v>13400</x:v>
       </x:c>
       <x:c r="I10" s="24" t="n">
-        <x:v>0.08969596918420697</x:v>
-      </x:c>
-      <x:c r="J10" s="23" t="n">
+        <x:v>0.09203296703296693</x:v>
+      </x:c>
+      <x:c r="J10" s="26" t="n">
         <x:f>ROUND(E10-F10,1)</x:f>
-        <x:v>5420</x:v>
+        <x:v>9820</x:v>
       </x:c>
       <x:c r="K10" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1179,29 +1179,29 @@
         <x:v>1月13日</x:v>
       </x:c>
       <x:c r="D11" s="23" t="n">
-        <x:v>168000</x:v>
+        <x:v>168840</x:v>
       </x:c>
       <x:c r="E11" s="23" t="n">
-        <x:v>176120</x:v>
+        <x:v>175360</x:v>
       </x:c>
       <x:c r="F11" s="23" t="n">
-        <x:v>163720</x:v>
+        <x:v>163140</x:v>
       </x:c>
       <x:c r="G11" s="23" t="n">
-        <x:v>169200</x:v>
+        <x:v>169520</x:v>
       </x:c>
       <x:c r="H11" s="28" t="n">
-        <x:v>10780</x:v>
+        <x:v>10520</x:v>
       </x:c>
       <x:c r="I11" s="24" t="n">
-        <x:v>0.06804696376720121</x:v>
+        <x:v>0.06616352201257869</x:v>
       </x:c>
       <x:c r="J11" s="26" t="n">
         <x:f>ROUND(E11-F11,1)</x:f>
-        <x:v>12400</x:v>
+        <x:v>12220</x:v>
       </x:c>
       <x:c r="K11" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1215,29 +1215,29 @@
         <x:v>1月14日</x:v>
       </x:c>
       <x:c r="D12" s="23" t="n">
-        <x:v>168800</x:v>
+        <x:v>169800</x:v>
       </x:c>
       <x:c r="E12" s="23" t="n">
-        <x:v>175220</x:v>
+        <x:v>175080</x:v>
       </x:c>
       <x:c r="F12" s="23" t="n">
-        <x:v>156700</x:v>
+        <x:v>157120</x:v>
       </x:c>
       <x:c r="G12" s="23" t="n">
-        <x:v>164000</x:v>
+        <x:v>163960</x:v>
       </x:c>
       <x:c r="H12" s="28" t="n">
-        <x:v>-5200</x:v>
+        <x:v>-5560</x:v>
       </x:c>
       <x:c r="I12" s="24" t="n">
-        <x:v>-0.030732860520094607</x:v>
+        <x:v>-0.03279848985370459</x:v>
       </x:c>
       <x:c r="J12" s="26" t="n">
         <x:f>ROUND(E12-F12,1)</x:f>
-        <x:v>18520</x:v>
+        <x:v>17960</x:v>
       </x:c>
       <x:c r="K12" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1251,29 +1251,29 @@
         <x:v>1月15日</x:v>
       </x:c>
       <x:c r="D13" s="23" t="n">
-        <x:v>166500</x:v>
+        <x:v>167340</x:v>
       </x:c>
       <x:c r="E13" s="23" t="n">
-        <x:v>166900</x:v>
+        <x:v>167340</x:v>
       </x:c>
       <x:c r="F13" s="23" t="n">
-        <x:v>157160</x:v>
+        <x:v>157360</x:v>
       </x:c>
       <x:c r="G13" s="23" t="n">
-        <x:v>164880</x:v>
+        <x:v>164320</x:v>
       </x:c>
       <x:c r="H13" s="28" t="n">
-        <x:v>880</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="I13" s="24" t="n">
-        <x:v>0.00536585365853659</x:v>
+        <x:v>0.0021956574774335547</x:v>
       </x:c>
       <x:c r="J13" s="26" t="n">
         <x:f>ROUND(E13-F13,1)</x:f>
-        <x:v>9740</x:v>
+        <x:v>9980</x:v>
       </x:c>
       <x:c r="K13" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1287,29 +1287,29 @@
         <x:v>1月16日</x:v>
       </x:c>
       <x:c r="D14" s="42" t="n">
-        <x:v>165000</x:v>
+        <x:v>164700</x:v>
       </x:c>
       <x:c r="E14" s="42" t="n">
-        <x:v>167500</x:v>
+        <x:v>167000</x:v>
       </x:c>
       <x:c r="F14" s="42" t="n">
-        <x:v>147740</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="G14" s="42" t="n">
-        <x:v>147740</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="H14" s="28" t="n">
-        <x:v>-17140</x:v>
+        <x:v>-16140</x:v>
       </x:c>
       <x:c r="I14" s="43" t="n">
-        <x:v>-0.10395439107229498</x:v>
+        <x:v>-0.09822297955209347</x:v>
       </x:c>
       <x:c r="J14" s="26" t="n">
         <x:f>ROUND(E14-F14,1)</x:f>
-        <x:v>19760</x:v>
+        <x:v>18820</x:v>
       </x:c>
       <x:c r="K14" s="41" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1323,29 +1323,29 @@
         <x:v>1月19日</x:v>
       </x:c>
       <x:c r="D15" s="23" t="n">
-        <x:v>150720</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="E15" s="23" t="n">
-        <x:v>152800</x:v>
+        <x:v>151800</x:v>
       </x:c>
       <x:c r="F15" s="23" t="n">
-        <x:v>143820</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="G15" s="23" t="n">
-        <x:v>149300</x:v>
+        <x:v>149160</x:v>
       </x:c>
       <x:c r="H15" s="28" t="n">
-        <x:v>1560</x:v>
+        <x:v>980</x:v>
       </x:c>
       <x:c r="I15" s="24" t="n">
-        <x:v>0.010559090293759343</x:v>
+        <x:v>0.006613578080712612</x:v>
       </x:c>
       <x:c r="J15" s="26" t="n">
         <x:f>ROUND(E15-F15,1)</x:f>
-        <x:v>8980</x:v>
+        <x:v>8800</x:v>
       </x:c>
       <x:c r="K15" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1359,29 +1359,29 @@
         <x:v>1月20日</x:v>
       </x:c>
       <x:c r="D16" s="23" t="n">
-        <x:v>152600</x:v>
+        <x:v>149860</x:v>
       </x:c>
       <x:c r="E16" s="23" t="n">
-        <x:v>162560</x:v>
+        <x:v>161180</x:v>
       </x:c>
       <x:c r="F16" s="23" t="n">
-        <x:v>151140</x:v>
+        <x:v>149860</x:v>
       </x:c>
       <x:c r="G16" s="23" t="n">
-        <x:v>161900</x:v>
+        <x:v>161000</x:v>
       </x:c>
       <x:c r="H16" s="28" t="n">
-        <x:v>12600</x:v>
+        <x:v>11840</x:v>
       </x:c>
       <x:c r="I16" s="24" t="n">
-        <x:v>0.0843938379102478</x:v>
+        <x:v>0.07937784928935376</x:v>
       </x:c>
       <x:c r="J16" s="26" t="n">
         <x:f>ROUND(E16-F16,1)</x:f>
-        <x:v>11420</x:v>
+        <x:v>11320</x:v>
       </x:c>
       <x:c r="K16" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1395,29 +1395,29 @@
         <x:v>1月21日</x:v>
       </x:c>
       <x:c r="D17" s="23" t="n">
-        <x:v>162640</x:v>
+        <x:v>161760</x:v>
       </x:c>
       <x:c r="E17" s="23" t="n">
-        <x:v>170600</x:v>
+        <x:v>170740</x:v>
       </x:c>
       <x:c r="F17" s="23" t="n">
-        <x:v>160000</x:v>
+        <x:v>160720</x:v>
       </x:c>
       <x:c r="G17" s="23" t="n">
-        <x:v>168320</x:v>
+        <x:v>169280</x:v>
       </x:c>
       <x:c r="H17" s="28" t="n">
-        <x:v>6420</x:v>
+        <x:v>8280</x:v>
       </x:c>
       <x:c r="I17" s="24" t="n">
-        <x:v>0.03965410747374931</x:v>
+        <x:v>0.05142857142857138</x:v>
       </x:c>
       <x:c r="J17" s="26" t="n">
         <x:f>ROUND(E17-F17,1)</x:f>
-        <x:v>10600</x:v>
+        <x:v>10020</x:v>
       </x:c>
       <x:c r="K17" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1431,29 +1431,29 @@
         <x:v>1月22日</x:v>
       </x:c>
       <x:c r="D18" s="23" t="n">
-        <x:v>168260</x:v>
+        <x:v>167340</x:v>
       </x:c>
       <x:c r="E18" s="23" t="n">
-        <x:v>175520</x:v>
+        <x:v>175180</x:v>
       </x:c>
       <x:c r="F18" s="23" t="n">
-        <x:v>165660</x:v>
+        <x:v>161200</x:v>
       </x:c>
       <x:c r="G18" s="23" t="n">
-        <x:v>170120</x:v>
+        <x:v>170320</x:v>
       </x:c>
       <x:c r="H18" s="28" t="n">
-        <x:v>1800</x:v>
+        <x:v>1040</x:v>
       </x:c>
       <x:c r="I18" s="24" t="n">
-        <x:v>0.010693916349809873</x:v>
+        <x:v>0.0061436672967862815</x:v>
       </x:c>
       <x:c r="J18" s="26" t="n">
         <x:f>ROUND(E18-F18,1)</x:f>
-        <x:v>9860</x:v>
+        <x:v>13980</x:v>
       </x:c>
       <x:c r="K18" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1467,29 +1467,29 @@
         <x:v>1月23日</x:v>
       </x:c>
       <x:c r="D19" s="23" t="n">
-        <x:v>173200</x:v>
+        <x:v>171680</x:v>
       </x:c>
       <x:c r="E19" s="23" t="n">
-        <x:v>183780</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="F19" s="23" t="n">
-        <x:v>173200</x:v>
+        <x:v>171680</x:v>
       </x:c>
       <x:c r="G19" s="23" t="n">
-        <x:v>183380</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="H19" s="28" t="n">
-        <x:v>13260</x:v>
+        <x:v>13140</x:v>
       </x:c>
       <x:c r="I19" s="24" t="n">
-        <x:v>0.07794498001410766</x:v>
+        <x:v>0.077148896195397</x:v>
       </x:c>
       <x:c r="J19" s="26" t="n">
         <x:f>ROUND(E19-F19,1)</x:f>
-        <x:v>10580</x:v>
+        <x:v>11780</x:v>
       </x:c>
       <x:c r="K19" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1503,29 +1503,29 @@
         <x:v>1月26日</x:v>
       </x:c>
       <x:c r="D20" s="23" t="n">
-        <x:v>187000</x:v>
+        <x:v>189980</x:v>
       </x:c>
       <x:c r="E20" s="23" t="n">
-        <x:v>190600</x:v>
+        <x:v>190020</x:v>
       </x:c>
       <x:c r="F20" s="23" t="n">
-        <x:v>165000</x:v>
+        <x:v>165560</x:v>
       </x:c>
       <x:c r="G20" s="23" t="n">
-        <x:v>167000</x:v>
+        <x:v>167820</x:v>
       </x:c>
       <x:c r="H20" s="28" t="n">
-        <x:v>-16380</x:v>
+        <x:v>-15640</x:v>
       </x:c>
       <x:c r="I20" s="24" t="n">
-        <x:v>-0.08932271785363721</x:v>
+        <x:v>-0.08525019077728113</x:v>
       </x:c>
       <x:c r="J20" s="26" t="n">
         <x:f>ROUND(E20-F20,1)</x:f>
-        <x:v>25600</x:v>
+        <x:v>24460</x:v>
       </x:c>
       <x:c r="K20" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1539,29 +1539,29 @@
         <x:v>1月27日</x:v>
       </x:c>
       <x:c r="D21" s="23" t="n">
-        <x:v>168000</x:v>
+        <x:v>174000</x:v>
       </x:c>
       <x:c r="E21" s="23" t="n">
-        <x:v>180800</x:v>
+        <x:v>182420</x:v>
       </x:c>
       <x:c r="F21" s="23" t="n">
-        <x:v>166140</x:v>
+        <x:v>167160</x:v>
       </x:c>
       <x:c r="G21" s="23" t="n">
-        <x:v>180080</x:v>
+        <x:v>182420</x:v>
       </x:c>
       <x:c r="H21" s="28" t="n">
-        <x:v>13080</x:v>
+        <x:v>14600</x:v>
       </x:c>
       <x:c r="I21" s="24" t="n">
-        <x:v>0.07832335329341311</x:v>
+        <x:v>0.08699797401978304</x:v>
       </x:c>
       <x:c r="J21" s="26" t="n">
         <x:f>ROUND(E21-F21,1)</x:f>
-        <x:v>14660</x:v>
+        <x:v>15260</x:v>
       </x:c>
       <x:c r="K21" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1575,29 +1575,29 @@
         <x:v>1月28日</x:v>
       </x:c>
       <x:c r="D22" s="23" t="n">
-        <x:v>182000</x:v>
+        <x:v>180400</x:v>
       </x:c>
       <x:c r="E22" s="23" t="n">
-        <x:v>182880</x:v>
+        <x:v>181060</x:v>
       </x:c>
       <x:c r="F22" s="23" t="n">
-        <x:v>165020</x:v>
+        <x:v>164140</x:v>
       </x:c>
       <x:c r="G22" s="23" t="n">
-        <x:v>166800</x:v>
+        <x:v>166100</x:v>
       </x:c>
       <x:c r="H22" s="28" t="n">
-        <x:v>-13280</x:v>
+        <x:v>-16320</x:v>
       </x:c>
       <x:c r="I22" s="24" t="n">
-        <x:v>-0.07374500222123503</x:v>
+        <x:v>-0.08946387457515625</x:v>
       </x:c>
       <x:c r="J22" s="26" t="n">
         <x:f>ROUND(E22-F22,1)</x:f>
-        <x:v>17860</x:v>
+        <x:v>16920</x:v>
       </x:c>
       <x:c r="K22" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1611,29 +1611,29 @@
         <x:v>1月29日</x:v>
       </x:c>
       <x:c r="D23" s="23" t="n">
-        <x:v>168000</x:v>
+        <x:v>170160</x:v>
       </x:c>
       <x:c r="E23" s="23" t="n">
-        <x:v>174200</x:v>
+        <x:v>174420</x:v>
       </x:c>
       <x:c r="F23" s="23" t="n">
-        <x:v>159400</x:v>
+        <x:v>159920</x:v>
       </x:c>
       <x:c r="G23" s="23" t="n">
-        <x:v>166240</x:v>
+        <x:v>165640</x:v>
       </x:c>
       <x:c r="H23" s="28" t="n">
-        <x:v>-560</x:v>
+        <x:v>-460</x:v>
       </x:c>
       <x:c r="I23" s="24" t="n">
-        <x:v>-0.003357314148681012</x:v>
+        <x:v>-0.002769416014449133</x:v>
       </x:c>
       <x:c r="J23" s="26" t="n">
         <x:f>ROUND(E23-F23,1)</x:f>
-        <x:v>14800</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="K23" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1647,29 +1647,29 @@
         <x:v>1月30日</x:v>
       </x:c>
       <x:c r="D24" s="23" t="n">
-        <x:v>164400</x:v>
+        <x:v>164200</x:v>
       </x:c>
       <x:c r="E24" s="23" t="n">
-        <x:v>165660</x:v>
+        <x:v>166020</x:v>
       </x:c>
       <x:c r="F24" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>148520</x:v>
       </x:c>
       <x:c r="G24" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>148540</x:v>
       </x:c>
       <x:c r="H24" s="28" t="n">
-        <x:v>-17680</x:v>
+        <x:v>-17100</x:v>
       </x:c>
       <x:c r="I24" s="24" t="n">
-        <x:v>-0.10635226179018287</x:v>
+        <x:v>-0.10323593334943248</x:v>
       </x:c>
       <x:c r="J24" s="26" t="n">
         <x:f>ROUND(E24-F24,1)</x:f>
-        <x:v>17100</x:v>
+        <x:v>17500</x:v>
       </x:c>
       <x:c r="K24" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1688,7 +1688,7 @@
       <x:c r="I25" s="30"/>
       <x:c r="J25" s="32" t="n">
         <x:f>ROUND(SUM(J5:J24),1)</x:f>
-        <x:v>248540</x:v>
+        <x:v>255500</x:v>
       </x:c>
       <x:c r="K25" s="30"/>
     </x:row>
@@ -1706,7 +1706,7 @@
       <x:c r="I26" s="30"/>
       <x:c r="J26" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J5:J24),0),1)</x:f>
-        <x:v>12427</x:v>
+        <x:v>12775</x:v>
       </x:c>
       <x:c r="K26" s="30"/>
     </x:row>
@@ -1771,29 +1771,29 @@
         <x:v>2月2日</x:v>
       </x:c>
       <x:c r="D30" s="23" t="n">
-        <x:v>148040</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="E30" s="23" t="n">
-        <x:v>153200</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="F30" s="23" t="n">
-        <x:v>132500</x:v>
+        <x:v>136300</x:v>
       </x:c>
       <x:c r="G30" s="23" t="n">
-        <x:v>132500</x:v>
+        <x:v>136300</x:v>
       </x:c>
       <x:c r="H30" s="28" t="n">
-        <x:v>-16060</x:v>
+        <x:v>-12240</x:v>
       </x:c>
       <x:c r="I30" s="24" t="n">
-        <x:v>-0.10810446957458264</x:v>
+        <x:v>-0.08240204658677797</x:v>
       </x:c>
       <x:c r="J30" s="26" t="n">
         <x:f>ROUND(E30-F30,1)</x:f>
-        <x:v>20700</x:v>
+        <x:v>16700</x:v>
       </x:c>
       <x:c r="K30" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1807,29 +1807,29 @@
         <x:v>2月3日</x:v>
       </x:c>
       <x:c r="D31" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>148300</x:v>
       </x:c>
       <x:c r="E31" s="23" t="n">
-        <x:v>152000</x:v>
+        <x:v>150660</x:v>
       </x:c>
       <x:c r="F31" s="23" t="n">
-        <x:v>137000</x:v>
+        <x:v>131360</x:v>
       </x:c>
       <x:c r="G31" s="23" t="n">
-        <x:v>147500</x:v>
+        <x:v>146220</x:v>
       </x:c>
       <x:c r="H31" s="28" t="n">
-        <x:v>15000</x:v>
+        <x:v>9920</x:v>
       </x:c>
       <x:c r="I31" s="24" t="n">
-        <x:v>0.1132075471698113</x:v>
+        <x:v>0.0727806309611152</x:v>
       </x:c>
       <x:c r="J31" s="26" t="n">
         <x:f>ROUND(E31-F31,1)</x:f>
-        <x:v>15000</x:v>
+        <x:v>19300</x:v>
       </x:c>
       <x:c r="K31" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1843,29 +1843,29 @@
         <x:v>2月4日</x:v>
       </x:c>
       <x:c r="D32" s="23" t="n">
-        <x:v>149200</x:v>
+        <x:v>144300</x:v>
       </x:c>
       <x:c r="E32" s="23" t="n">
-        <x:v>152600</x:v>
+        <x:v>152000</x:v>
       </x:c>
       <x:c r="F32" s="23" t="n">
-        <x:v>145720</x:v>
+        <x:v>144300</x:v>
       </x:c>
       <x:c r="G32" s="23" t="n">
-        <x:v>147200</x:v>
+        <x:v>147800</x:v>
       </x:c>
       <x:c r="H32" s="28" t="n">
-        <x:v>-300</x:v>
+        <x:v>1580</x:v>
       </x:c>
       <x:c r="I32" s="24" t="n">
-        <x:v>-0.0020338983050847137</x:v>
+        <x:v>0.010805635344002251</x:v>
       </x:c>
       <x:c r="J32" s="26" t="n">
         <x:f>ROUND(E32-F32,1)</x:f>
-        <x:v>6880</x:v>
+        <x:v>7700</x:v>
       </x:c>
       <x:c r="K32" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1879,29 +1879,29 @@
         <x:v>2月5日</x:v>
       </x:c>
       <x:c r="D33" s="23" t="n">
-        <x:v>145000</x:v>
+        <x:v>148160</x:v>
       </x:c>
       <x:c r="E33" s="23" t="n">
-        <x:v>147000</x:v>
+        <x:v>148160</x:v>
       </x:c>
       <x:c r="F33" s="23" t="n">
-        <x:v>132360</x:v>
+        <x:v>131880</x:v>
       </x:c>
       <x:c r="G33" s="23" t="n">
-        <x:v>132800</x:v>
+        <x:v>132900</x:v>
       </x:c>
       <x:c r="H33" s="28" t="n">
-        <x:v>-14400</x:v>
+        <x:v>-14900</x:v>
       </x:c>
       <x:c r="I33" s="24" t="n">
-        <x:v>-0.09782608695652173</x:v>
+        <x:v>-0.10081190798376183</x:v>
       </x:c>
       <x:c r="J33" s="26" t="n">
         <x:f>ROUND(E33-F33,1)</x:f>
-        <x:v>14640</x:v>
+        <x:v>16280</x:v>
       </x:c>
       <x:c r="K33" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1915,29 +1915,29 @@
         <x:v>2月6日</x:v>
       </x:c>
       <x:c r="D34" s="23" t="n">
-        <x:v>129780</x:v>
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="E34" s="23" t="n">
-        <x:v>139000</x:v>
+        <x:v>138860</x:v>
       </x:c>
       <x:c r="F34" s="23" t="n">
-        <x:v>124480</x:v>
+        <x:v>124760</x:v>
       </x:c>
       <x:c r="G34" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>131160</x:v>
       </x:c>
       <x:c r="H34" s="28" t="n">
-        <x:v>700</x:v>
+        <x:v>-1740</x:v>
       </x:c>
       <x:c r="I34" s="24" t="n">
-        <x:v>0.005271084337349352</x:v>
+        <x:v>-0.01309255079006777</x:v>
       </x:c>
       <x:c r="J34" s="26" t="n">
         <x:f>ROUND(E34-F34,1)</x:f>
-        <x:v>14520</x:v>
+        <x:v>14100</x:v>
       </x:c>
       <x:c r="K34" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1951,29 +1951,29 @@
         <x:v>2月9日</x:v>
       </x:c>
       <x:c r="D35" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>134660</x:v>
       </x:c>
       <x:c r="E35" s="23" t="n">
-        <x:v>139900</x:v>
+        <x:v>138960</x:v>
       </x:c>
       <x:c r="F35" s="23" t="n">
-        <x:v>135100</x:v>
+        <x:v>134640</x:v>
       </x:c>
       <x:c r="G35" s="23" t="n">
-        <x:v>137400</x:v>
+        <x:v>137820</x:v>
       </x:c>
       <x:c r="H35" s="28" t="n">
-        <x:v>3900</x:v>
+        <x:v>6660</x:v>
       </x:c>
       <x:c r="I35" s="24" t="n">
-        <x:v>0.02921348314606731</x:v>
+        <x:v>0.050777676120768556</x:v>
       </x:c>
       <x:c r="J35" s="23" t="n">
         <x:f>ROUND(E35-F35,1)</x:f>
-        <x:v>4800</x:v>
+        <x:v>4320</x:v>
       </x:c>
       <x:c r="K35" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1987,29 +1987,29 @@
         <x:v>2月10日</x:v>
       </x:c>
       <x:c r="D36" s="23" t="n">
-        <x:v>136220</x:v>
+        <x:v>137420</x:v>
       </x:c>
       <x:c r="E36" s="23" t="n">
-        <x:v>141220</x:v>
+        <x:v>139880</x:v>
       </x:c>
       <x:c r="F36" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>133580</x:v>
       </x:c>
       <x:c r="G36" s="23" t="n">
-        <x:v>137560</x:v>
-      </x:c>
-      <x:c r="H36" s="28" t="n">
-        <x:v>160</x:v>
+        <x:v>137700</x:v>
+      </x:c>
+      <x:c r="H36" s="23" t="n">
+        <x:v>-120</x:v>
       </x:c>
       <x:c r="I36" s="24" t="n">
-        <x:v>0.001164483260553073</x:v>
+        <x:v>-0.0008707009142359112</x:v>
       </x:c>
       <x:c r="J36" s="26" t="n">
         <x:f>ROUND(E36-F36,1)</x:f>
-        <x:v>7720</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="K36" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2023,29 +2023,29 @@
         <x:v>2月11日</x:v>
       </x:c>
       <x:c r="D37" s="23" t="n">
-        <x:v>137880</x:v>
+        <x:v>138580</x:v>
       </x:c>
       <x:c r="E37" s="23" t="n">
         <x:v>150720</x:v>
       </x:c>
       <x:c r="F37" s="23" t="n">
-        <x:v>137880</x:v>
+        <x:v>138580</x:v>
       </x:c>
       <x:c r="G37" s="23" t="n">
-        <x:v>150600</x:v>
+        <x:v>150720</x:v>
       </x:c>
       <x:c r="H37" s="28" t="n">
-        <x:v>13040</x:v>
+        <x:v>13020</x:v>
       </x:c>
       <x:c r="I37" s="24" t="n">
-        <x:v>0.09479499854608897</x:v>
+        <x:v>0.09455337690631804</x:v>
       </x:c>
       <x:c r="J37" s="26" t="n">
         <x:f>ROUND(E37-F37,1)</x:f>
-        <x:v>12840</x:v>
+        <x:v>12140</x:v>
       </x:c>
       <x:c r="K37" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2059,29 +2059,29 @@
         <x:v>2月12日</x:v>
       </x:c>
       <x:c r="D38" s="23" t="n">
-        <x:v>149200</x:v>
+        <x:v>149480</x:v>
       </x:c>
       <x:c r="E38" s="23" t="n">
-        <x:v>152720</x:v>
+        <x:v>152280</x:v>
       </x:c>
       <x:c r="F38" s="23" t="n">
-        <x:v>147000</x:v>
+        <x:v>147020</x:v>
       </x:c>
       <x:c r="G38" s="23" t="n">
-        <x:v>149380</x:v>
+        <x:v>148680</x:v>
       </x:c>
       <x:c r="H38" s="28" t="n">
-        <x:v>-1220</x:v>
+        <x:v>-2040</x:v>
       </x:c>
       <x:c r="I38" s="24" t="n">
-        <x:v>-0.008100929614873853</x:v>
+        <x:v>-0.013535031847133783</x:v>
       </x:c>
       <x:c r="J38" s="23" t="n">
         <x:f>ROUND(E38-F38,1)</x:f>
-        <x:v>5720</x:v>
+        <x:v>5260</x:v>
       </x:c>
       <x:c r="K38" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2095,29 +2095,29 @@
         <x:v>2月13日</x:v>
       </x:c>
       <x:c r="D39" s="23" t="n">
-        <x:v>143000</x:v>
+        <x:v>145460</x:v>
       </x:c>
       <x:c r="E39" s="23" t="n">
-        <x:v>153700</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="F39" s="23" t="n">
-        <x:v>142560</x:v>
+        <x:v>144360</x:v>
       </x:c>
       <x:c r="G39" s="23" t="n">
-        <x:v>153500</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="H39" s="28" t="n">
-        <x:v>4120</x:v>
+        <x:v>3700</x:v>
       </x:c>
       <x:c r="I39" s="24" t="n">
-        <x:v>0.02758066675592441</x:v>
+        <x:v>0.024885660478880745</x:v>
       </x:c>
       <x:c r="J39" s="26" t="n">
         <x:f>ROUND(E39-F39,1)</x:f>
-        <x:v>11140</x:v>
+        <x:v>8020</x:v>
       </x:c>
       <x:c r="K39" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2131,29 +2131,29 @@
         <x:v>2月24日</x:v>
       </x:c>
       <x:c r="D40" s="42" t="n">
-        <x:v>158340</x:v>
+        <x:v>165060</x:v>
       </x:c>
       <x:c r="E40" s="42" t="n">
-        <x:v>166800</x:v>
+        <x:v>165860</x:v>
       </x:c>
       <x:c r="F40" s="42" t="n">
-        <x:v>158340</x:v>
+        <x:v>155680</x:v>
       </x:c>
       <x:c r="G40" s="42" t="n">
-        <x:v>165920</x:v>
+        <x:v>164780</x:v>
       </x:c>
       <x:c r="H40" s="28" t="n">
-        <x:v>12420</x:v>
+        <x:v>12400</x:v>
       </x:c>
       <x:c r="I40" s="43" t="n">
-        <x:v>0.08091205211726393</x:v>
+        <x:v>0.08137550859692877</x:v>
       </x:c>
       <x:c r="J40" s="26" t="n">
         <x:f>ROUND(E40-F40,1)</x:f>
-        <x:v>8460</x:v>
+        <x:v>10180</x:v>
       </x:c>
       <x:c r="K40" s="41" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2167,29 +2167,29 @@
         <x:v>2月25日</x:v>
       </x:c>
       <x:c r="D41" s="23" t="n">
-        <x:v>165620</x:v>
+        <x:v>164920</x:v>
       </x:c>
       <x:c r="E41" s="23" t="n">
-        <x:v>172320</x:v>
+        <x:v>170900</x:v>
       </x:c>
       <x:c r="F41" s="23" t="n">
-        <x:v>165040</x:v>
+        <x:v>163080</x:v>
       </x:c>
       <x:c r="G41" s="23" t="n">
-        <x:v>167200</x:v>
+        <x:v>167400</x:v>
       </x:c>
       <x:c r="H41" s="28" t="n">
-        <x:v>1280</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="I41" s="24" t="n">
-        <x:v>0.0077145612343298975</x:v>
+        <x:v>0.015899987862604714</x:v>
       </x:c>
       <x:c r="J41" s="26" t="n">
         <x:f>ROUND(E41-F41,1)</x:f>
-        <x:v>7280</x:v>
+        <x:v>7820</x:v>
       </x:c>
       <x:c r="K41" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2203,29 +2203,29 @@
         <x:v>2月26日</x:v>
       </x:c>
       <x:c r="D42" s="23" t="n">
-        <x:v>186000</x:v>
+        <x:v>181980</x:v>
       </x:c>
       <x:c r="E42" s="23" t="n">
-        <x:v>186900</x:v>
+        <x:v>187920</x:v>
       </x:c>
       <x:c r="F42" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>171760</x:v>
       </x:c>
       <x:c r="G42" s="23" t="n">
-        <x:v>175080</x:v>
+        <x:v>172020</x:v>
       </x:c>
       <x:c r="H42" s="28" t="n">
-        <x:v>7880</x:v>
+        <x:v>4620</x:v>
       </x:c>
       <x:c r="I42" s="24" t="n">
-        <x:v>0.04712918660287091</x:v>
+        <x:v>0.027598566308243644</x:v>
       </x:c>
       <x:c r="J42" s="26" t="n">
         <x:f>ROUND(E42-F42,1)</x:f>
-        <x:v>14900</x:v>
+        <x:v>16160</x:v>
       </x:c>
       <x:c r="K42" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2239,29 +2239,29 @@
         <x:v>2月27日</x:v>
       </x:c>
       <x:c r="D43" s="23" t="n">
-        <x:v>175220</x:v>
+        <x:v>173340</x:v>
       </x:c>
       <x:c r="E43" s="23" t="n">
-        <x:v>177600</x:v>
+        <x:v>176000</x:v>
       </x:c>
       <x:c r="F43" s="23" t="n">
         <x:v>169160</x:v>
       </x:c>
       <x:c r="G43" s="23" t="n">
-        <x:v>177200</x:v>
+        <x:v>175400</x:v>
       </x:c>
       <x:c r="H43" s="28" t="n">
-        <x:v>2120</x:v>
+        <x:v>3380</x:v>
       </x:c>
       <x:c r="I43" s="24" t="n">
-        <x:v>0.01210875028558367</x:v>
+        <x:v>0.019648878037437534</x:v>
       </x:c>
       <x:c r="J43" s="26" t="n">
         <x:f>ROUND(E43-F43,1)</x:f>
-        <x:v>8440</x:v>
+        <x:v>6840</x:v>
       </x:c>
       <x:c r="K43" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2280,7 +2280,7 @@
       <x:c r="I44" s="30"/>
       <x:c r="J44" s="32" t="n">
         <x:f>ROUND(SUM(J30:J43),1)</x:f>
-        <x:v>153040</x:v>
+        <x:v>151120</x:v>
       </x:c>
       <x:c r="K44" s="30"/>
     </x:row>
@@ -2298,7 +2298,7 @@
       <x:c r="I45" s="30"/>
       <x:c r="J45" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J30:J43),0),1)</x:f>
-        <x:v>10931.4</x:v>
+        <x:v>10794.3</x:v>
       </x:c>
       <x:c r="K45" s="30"/>
     </x:row>
@@ -2363,29 +2363,29 @@
         <x:v>3月2日</x:v>
       </x:c>
       <x:c r="D49" s="23" t="n">
-        <x:v>180000</x:v>
+        <x:v>175800</x:v>
       </x:c>
       <x:c r="E49" s="23" t="n">
-        <x:v>180060</x:v>
+        <x:v>177260</x:v>
       </x:c>
       <x:c r="F49" s="23" t="n">
-        <x:v>170620</x:v>
+        <x:v>170500</x:v>
       </x:c>
       <x:c r="G49" s="23" t="n">
-        <x:v>172780</x:v>
+        <x:v>173120</x:v>
       </x:c>
       <x:c r="H49" s="28" t="n">
-        <x:v>-4420</x:v>
+        <x:v>-2280</x:v>
       </x:c>
       <x:c r="I49" s="24" t="n">
-        <x:v>-0.02494356659142216</x:v>
+        <x:v>-0.012998859749144831</x:v>
       </x:c>
       <x:c r="J49" s="26" t="n">
         <x:f>ROUND(E49-F49,1)</x:f>
-        <x:v>9440</x:v>
+        <x:v>6760</x:v>
       </x:c>
       <x:c r="K49" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -2399,29 +2399,29 @@
         <x:v>3月3日</x:v>
       </x:c>
       <x:c r="D50" s="23" t="n">
-        <x:v>170800</x:v>
+        <x:v>165620</x:v>
       </x:c>
       <x:c r="E50" s="23" t="n">
-        <x:v>171340</x:v>
+        <x:v>169600</x:v>
       </x:c>
       <x:c r="F50" s="23" t="n">
-        <x:v>151780</x:v>
+        <x:v>151620</x:v>
       </x:c>
       <x:c r="G50" s="23" t="n">
-        <x:v>151780</x:v>
+        <x:v>151620</x:v>
       </x:c>
       <x:c r="H50" s="28" t="n">
-        <x:v>-21000</x:v>
+        <x:v>-21500</x:v>
       </x:c>
       <x:c r="I50" s="24" t="n">
-        <x:v>-0.12154184512096311</x:v>
+        <x:v>-0.12419131238447323</x:v>
       </x:c>
       <x:c r="J50" s="26" t="n">
         <x:f>ROUND(E50-F50,1)</x:f>
-        <x:v>19560</x:v>
+        <x:v>17980</x:v>
       </x:c>
       <x:c r="K50" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -2435,29 +2435,29 @@
         <x:v>3月4日</x:v>
       </x:c>
       <x:c r="D51" s="23" t="n">
-        <x:v>151000</x:v>
+        <x:v>148060</x:v>
       </x:c>
       <x:c r="E51" s="23" t="n">
-        <x:v>156000</x:v>
+        <x:v>154500</x:v>
       </x:c>
       <x:c r="F51" s="23" t="n">
-        <x:v>146040</x:v>
+        <x:v>144980</x:v>
       </x:c>
       <x:c r="G51" s="23" t="n">
-        <x:v>153740</x:v>
+        <x:v>152460</x:v>
       </x:c>
       <x:c r="H51" s="28" t="n">
-        <x:v>1960</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="I51" s="24" t="n">
-        <x:v>0.012913427329028782</x:v>
+        <x:v>0.005540166204986097</x:v>
       </x:c>
       <x:c r="J51" s="26" t="n">
         <x:f>ROUND(E51-F51,1)</x:f>
-        <x:v>9960</x:v>
+        <x:v>9520</x:v>
       </x:c>
       <x:c r="K51" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -2471,29 +2471,29 @@
         <x:v>3月5日</x:v>
       </x:c>
       <x:c r="D52" s="23" t="n">
-        <x:v>155020</x:v>
+        <x:v>157160</x:v>
       </x:c>
       <x:c r="E52" s="23" t="n">
-        <x:v>161600</x:v>
+        <x:v>160000</x:v>
       </x:c>
       <x:c r="F52" s="23" t="n">
-        <x:v>149660</x:v>
+        <x:v>148980</x:v>
       </x:c>
       <x:c r="G52" s="23" t="n">
-        <x:v>156300</x:v>
+        <x:v>154200</x:v>
       </x:c>
       <x:c r="H52" s="28" t="n">
-        <x:v>2560</x:v>
+        <x:v>1740</x:v>
       </x:c>
       <x:c r="I52" s="24" t="n">
-        <x:v>0.016651489527774066</x:v>
+        <x:v>0.011412829594647844</x:v>
       </x:c>
       <x:c r="J52" s="26" t="n">
         <x:f>ROUND(E52-F52,1)</x:f>
-        <x:v>11940</x:v>
+        <x:v>11020</x:v>
       </x:c>
       <x:c r="K52" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -2507,29 +2507,29 @@
         <x:v>3月6日</x:v>
       </x:c>
       <x:c r="D53" s="23" t="n">
-        <x:v>155520</x:v>
+        <x:v>155040</x:v>
       </x:c>
       <x:c r="E53" s="23" t="n">
-        <x:v>160820</x:v>
+        <x:v>160000</x:v>
       </x:c>
       <x:c r="F53" s="23" t="n">
-        <x:v>151600</x:v>
+        <x:v>152500</x:v>
       </x:c>
       <x:c r="G53" s="23" t="n">
-        <x:v>156700</x:v>
+        <x:v>156580</x:v>
       </x:c>
       <x:c r="H53" s="28" t="n">
-        <x:v>400</x:v>
+        <x:v>2380</x:v>
       </x:c>
       <x:c r="I53" s="24" t="n">
-        <x:v>0.002559181062060212</x:v>
+        <x:v>0.015434500648508376</x:v>
       </x:c>
       <x:c r="J53" s="26" t="n">
         <x:f>ROUND(E53-F53,1)</x:f>
-        <x:v>9220</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="K53" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -2543,29 +2543,29 @@
         <x:v>3月9日</x:v>
       </x:c>
       <x:c r="D54" s="23" t="n">
-        <x:v>149000</x:v>
+        <x:v>145120</x:v>
       </x:c>
       <x:c r="E54" s="23" t="n">
-        <x:v>165600</x:v>
+        <x:v>164320</x:v>
       </x:c>
       <x:c r="F54" s="23" t="n">
-        <x:v>142600</x:v>
+        <x:v>139860</x:v>
       </x:c>
       <x:c r="G54" s="23" t="n">
-        <x:v>161500</x:v>
+        <x:v>161120</x:v>
       </x:c>
       <x:c r="H54" s="28" t="n">
-        <x:v>4800</x:v>
+        <x:v>4540</x:v>
       </x:c>
       <x:c r="I54" s="24" t="n">
-        <x:v>0.030631780472240022</x:v>
+        <x:v>0.028994763060416373</x:v>
       </x:c>
       <x:c r="J54" s="26" t="n">
         <x:f>ROUND(E54-F54,1)</x:f>
-        <x:v>23000</x:v>
+        <x:v>24460</x:v>
       </x:c>
       <x:c r="K54" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -2579,29 +2579,29 @@
         <x:v>3月10日</x:v>
       </x:c>
       <x:c r="D55" s="23" t="n">
-        <x:v>162000</x:v>
+        <x:v>157200</x:v>
       </x:c>
       <x:c r="E55" s="23" t="n">
-        <x:v>166980</x:v>
+        <x:v>165760</x:v>
       </x:c>
       <x:c r="F55" s="23" t="n">
-        <x:v>160020</x:v>
+        <x:v>157200</x:v>
       </x:c>
       <x:c r="G55" s="23" t="n">
-        <x:v>163000</x:v>
+        <x:v>161400</x:v>
       </x:c>
       <x:c r="H55" s="28" t="n">
-        <x:v>1500</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="I55" s="24" t="n">
-        <x:v>0.009287925696594534</x:v>
+        <x:v>0.0017378351539225623</x:v>
       </x:c>
       <x:c r="J55" s="26" t="n">
         <x:f>ROUND(E55-F55,1)</x:f>
-        <x:v>6960</x:v>
+        <x:v>8560</x:v>
       </x:c>
       <x:c r="K55" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -2615,29 +2615,29 @@
         <x:v>3月11日</x:v>
       </x:c>
       <x:c r="D56" s="23" t="n">
-        <x:v>163000</x:v>
+        <x:v>165440</x:v>
       </x:c>
       <x:c r="E56" s="23" t="n">
-        <x:v>167400</x:v>
+        <x:v>166800</x:v>
       </x:c>
       <x:c r="F56" s="23" t="n">
-        <x:v>155200</x:v>
+        <x:v>154900</x:v>
       </x:c>
       <x:c r="G56" s="23" t="n">
-        <x:v>155280</x:v>
+        <x:v>155020</x:v>
       </x:c>
       <x:c r="H56" s="28" t="n">
-        <x:v>-7720</x:v>
+        <x:v>-6380</x:v>
       </x:c>
       <x:c r="I56" s="24" t="n">
-        <x:v>-0.04736196319018404</x:v>
+        <x:v>-0.039529120198265155</x:v>
       </x:c>
       <x:c r="J56" s="26" t="n">
         <x:f>ROUND(E56-F56,1)</x:f>
-        <x:v>12200</x:v>
+        <x:v>11900</x:v>
       </x:c>
       <x:c r="K56" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -2651,29 +2651,29 @@
         <x:v>3月12日</x:v>
       </x:c>
       <x:c r="D57" s="23" t="n">
-        <x:v>156000</x:v>
+        <x:v>157460</x:v>
       </x:c>
       <x:c r="E57" s="23" t="n">
-        <x:v>159700</x:v>
+        <x:v>158860</x:v>
       </x:c>
       <x:c r="F57" s="23" t="n">
-        <x:v>153100</x:v>
+        <x:v>152340</x:v>
       </x:c>
       <x:c r="G57" s="23" t="n">
-        <x:v>157100</x:v>
+        <x:v>156220</x:v>
       </x:c>
       <x:c r="H57" s="28" t="n">
-        <x:v>1820</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="I57" s="24" t="n">
-        <x:v>0.011720762493560022</x:v>
+        <x:v>0.007740936653334973</x:v>
       </x:c>
       <x:c r="J57" s="26" t="n">
         <x:f>ROUND(E57-F57,1)</x:f>
-        <x:v>6600</x:v>
+        <x:v>6520</x:v>
       </x:c>
       <x:c r="K57" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -2687,29 +2687,29 @@
         <x:v>3月13日</x:v>
       </x:c>
       <x:c r="D58" s="23" t="n">
-        <x:v>155000</x:v>
+        <x:v>155120</x:v>
       </x:c>
       <x:c r="E58" s="23" t="n">
-        <x:v>162960</x:v>
+        <x:v>161800</x:v>
       </x:c>
       <x:c r="F58" s="23" t="n">
-        <x:v>150000</x:v>
+        <x:v>149740</x:v>
       </x:c>
       <x:c r="G58" s="23" t="n">
-        <x:v>152100</x:v>
+        <x:v>151880</x:v>
       </x:c>
       <x:c r="H58" s="28" t="n">
-        <x:v>-5000</x:v>
+        <x:v>-4340</x:v>
       </x:c>
       <x:c r="I58" s="24" t="n">
-        <x:v>-0.031826861871419476</x:v>
+        <x:v>-0.027781334016131143</x:v>
       </x:c>
       <x:c r="J58" s="26" t="n">
         <x:f>ROUND(E58-F58,1)</x:f>
-        <x:v>12960</x:v>
+        <x:v>12060</x:v>
       </x:c>
       <x:c r="K58" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -2723,29 +2723,29 @@
         <x:v>3月16日</x:v>
       </x:c>
       <x:c r="D59" s="23" t="n">
-        <x:v>150880</x:v>
+        <x:v>149140</x:v>
       </x:c>
       <x:c r="E59" s="23" t="n">
-        <x:v>160000</x:v>
+        <x:v>159120</x:v>
       </x:c>
       <x:c r="F59" s="23" t="n">
-        <x:v>149160</x:v>
+        <x:v>149100</x:v>
       </x:c>
       <x:c r="G59" s="23" t="n">
-        <x:v>159560</x:v>
+        <x:v>159000</x:v>
       </x:c>
       <x:c r="H59" s="28" t="n">
-        <x:v>7460</x:v>
+        <x:v>7120</x:v>
       </x:c>
       <x:c r="I59" s="24" t="n">
-        <x:v>0.0490466798159106</x:v>
+        <x:v>0.04687911509086118</x:v>
       </x:c>
       <x:c r="J59" s="26" t="n">
         <x:f>ROUND(E59-F59,1)</x:f>
-        <x:v>10840</x:v>
+        <x:v>10020</x:v>
       </x:c>
       <x:c r="K59" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -2759,29 +2759,29 @@
         <x:v>3月17日</x:v>
       </x:c>
       <x:c r="D60" s="23" t="n">
-        <x:v>159700</x:v>
+        <x:v>158080</x:v>
       </x:c>
       <x:c r="E60" s="23" t="n">
-        <x:v>160800</x:v>
+        <x:v>158080</x:v>
       </x:c>
       <x:c r="F60" s="23" t="n">
-        <x:v>154000</x:v>
+        <x:v>154360</x:v>
       </x:c>
       <x:c r="G60" s="23" t="n">
-        <x:v>155260</x:v>
+        <x:v>155100</x:v>
       </x:c>
       <x:c r="H60" s="28" t="n">
-        <x:v>-4300</x:v>
+        <x:v>-3900</x:v>
       </x:c>
       <x:c r="I60" s="24" t="n">
-        <x:v>-0.026949110052644776</x:v>
-      </x:c>
-      <x:c r="J60" s="26" t="n">
+        <x:v>-0.024528301886792447</x:v>
+      </x:c>
+      <x:c r="J60" s="23" t="n">
         <x:f>ROUND(E60-F60,1)</x:f>
-        <x:v>6800</x:v>
+        <x:v>3720</x:v>
       </x:c>
       <x:c r="K60" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -2795,29 +2795,29 @@
         <x:v>3月18日</x:v>
       </x:c>
       <x:c r="D61" s="23" t="n">
-        <x:v>154400</x:v>
+        <x:v>155160</x:v>
       </x:c>
       <x:c r="E61" s="23" t="n">
-        <x:v>156600</x:v>
+        <x:v>155560</x:v>
       </x:c>
       <x:c r="F61" s="23" t="n">
-        <x:v>149560</x:v>
+        <x:v>149400</x:v>
       </x:c>
       <x:c r="G61" s="23" t="n">
-        <x:v>150020</x:v>
+        <x:v>149700</x:v>
       </x:c>
       <x:c r="H61" s="28" t="n">
-        <x:v>-5240</x:v>
+        <x:v>-5400</x:v>
       </x:c>
       <x:c r="I61" s="24" t="n">
-        <x:v>-0.033749838979775904</x:v>
+        <x:v>-0.03481624758220503</x:v>
       </x:c>
       <x:c r="J61" s="26" t="n">
         <x:f>ROUND(E61-F61,1)</x:f>
-        <x:v>7040</x:v>
+        <x:v>6160</x:v>
       </x:c>
       <x:c r="K61" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -2831,29 +2831,29 @@
         <x:v>3月19日</x:v>
       </x:c>
       <x:c r="D62" s="23" t="n">
-        <x:v>147840</x:v>
+        <x:v>144000</x:v>
       </x:c>
       <x:c r="E62" s="23" t="n">
-        <x:v>150000</x:v>
+        <x:v>148500</x:v>
       </x:c>
       <x:c r="F62" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>139640</x:v>
       </x:c>
       <x:c r="G62" s="23" t="n">
-        <x:v>142500</x:v>
+        <x:v>142100</x:v>
       </x:c>
       <x:c r="H62" s="28" t="n">
-        <x:v>-7520</x:v>
+        <x:v>-7600</x:v>
       </x:c>
       <x:c r="I62" s="24" t="n">
-        <x:v>-0.05012664978002934</x:v>
+        <x:v>-0.05076820307281227</x:v>
       </x:c>
       <x:c r="J62" s="26" t="n">
         <x:f>ROUND(E62-F62,1)</x:f>
-        <x:v>10000</x:v>
+        <x:v>8860</x:v>
       </x:c>
       <x:c r="K62" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -2867,29 +2867,29 @@
         <x:v>3月20日</x:v>
       </x:c>
       <x:c r="D63" s="42" t="n">
-        <x:v>145500</x:v>
+        <x:v>145900</x:v>
       </x:c>
       <x:c r="E63" s="42" t="n">
-        <x:v>150800</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="F63" s="42" t="n">
-        <x:v>143300</x:v>
+        <x:v>143900</x:v>
       </x:c>
       <x:c r="G63" s="42" t="n">
-        <x:v>143520</x:v>
+        <x:v>143900</x:v>
       </x:c>
       <x:c r="H63" s="28" t="n">
-        <x:v>1020</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="I63" s="43" t="n">
-        <x:v>0.00715789473684203</x:v>
+        <x:v>0.012667135819845132</x:v>
       </x:c>
       <x:c r="J63" s="26" t="n">
         <x:f>ROUND(E63-F63,1)</x:f>
-        <x:v>7500</x:v>
+        <x:v>6100</x:v>
       </x:c>
       <x:c r="K63" s="41" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -2903,29 +2903,29 @@
         <x:v>3月23日</x:v>
       </x:c>
       <x:c r="D64" s="23" t="n">
-        <x:v>141220</x:v>
+        <x:v>144460</x:v>
       </x:c>
       <x:c r="E64" s="23" t="n">
-        <x:v>149300</x:v>
+        <x:v>149940</x:v>
       </x:c>
       <x:c r="F64" s="23" t="n">
-        <x:v>140020</x:v>
+        <x:v>139980</x:v>
       </x:c>
       <x:c r="G64" s="23" t="n">
-        <x:v>149040</x:v>
+        <x:v>149940</x:v>
       </x:c>
       <x:c r="H64" s="28" t="n">
-        <x:v>5520</x:v>
+        <x:v>6040</x:v>
       </x:c>
       <x:c r="I64" s="24" t="n">
-        <x:v>0.03846153846153855</x:v>
+        <x:v>0.041973592772758916</x:v>
       </x:c>
       <x:c r="J64" s="26" t="n">
         <x:f>ROUND(E64-F64,1)</x:f>
-        <x:v>9280</x:v>
+        <x:v>9960</x:v>
       </x:c>
       <x:c r="K64" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -2939,29 +2939,29 @@
         <x:v>3月24日</x:v>
       </x:c>
       <x:c r="D65" s="23" t="n">
-        <x:v>151700</x:v>
+        <x:v>151360</x:v>
       </x:c>
       <x:c r="E65" s="23" t="n">
-        <x:v>154660</x:v>
+        <x:v>153060</x:v>
       </x:c>
       <x:c r="F65" s="23" t="n">
-        <x:v>150220</x:v>
+        <x:v>150100</x:v>
       </x:c>
       <x:c r="G65" s="23" t="n">
-        <x:v>152900</x:v>
+        <x:v>152840</x:v>
       </x:c>
       <x:c r="H65" s="28" t="n">
-        <x:v>3860</x:v>
+        <x:v>2900</x:v>
       </x:c>
       <x:c r="I65" s="24" t="n">
-        <x:v>0.025899087493290285</x:v>
+        <x:v>0.019341069761237728</x:v>
       </x:c>
       <x:c r="J65" s="23" t="n">
         <x:f>ROUND(E65-F65,1)</x:f>
-        <x:v>4440</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="K65" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -2975,29 +2975,29 @@
         <x:v>3月25日</x:v>
       </x:c>
       <x:c r="D66" s="23" t="n">
-        <x:v>156000</x:v>
+        <x:v>159860</x:v>
       </x:c>
       <x:c r="E66" s="23" t="n">
-        <x:v>161500</x:v>
+        <x:v>161340</x:v>
       </x:c>
       <x:c r="F66" s="23" t="n">
-        <x:v>154500</x:v>
+        <x:v>153960</x:v>
       </x:c>
       <x:c r="G66" s="23" t="n">
-        <x:v>158960</x:v>
+        <x:v>159300</x:v>
       </x:c>
       <x:c r="H66" s="28" t="n">
-        <x:v>6060</x:v>
+        <x:v>6460</x:v>
       </x:c>
       <x:c r="I66" s="24" t="n">
-        <x:v>0.039633747547416665</x:v>
+        <x:v>0.04226642240251244</x:v>
       </x:c>
       <x:c r="J66" s="26" t="n">
         <x:f>ROUND(E66-F66,1)</x:f>
-        <x:v>7000</x:v>
+        <x:v>7380</x:v>
       </x:c>
       <x:c r="K66" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -3011,29 +3011,29 @@
         <x:v>3月26日</x:v>
       </x:c>
       <x:c r="D67" s="23" t="n">
-        <x:v>158980</x:v>
+        <x:v>157080</x:v>
       </x:c>
       <x:c r="E67" s="23" t="n">
-        <x:v>162860</x:v>
+        <x:v>162000</x:v>
       </x:c>
       <x:c r="F67" s="23" t="n">
-        <x:v>155600</x:v>
+        <x:v>155280</x:v>
       </x:c>
       <x:c r="G67" s="23" t="n">
-        <x:v>158040</x:v>
+        <x:v>156880</x:v>
       </x:c>
       <x:c r="H67" s="28" t="n">
-        <x:v>-920</x:v>
+        <x:v>-2420</x:v>
       </x:c>
       <x:c r="I67" s="24" t="n">
-        <x:v>-0.00578761952692497</x:v>
+        <x:v>-0.01519146264908977</x:v>
       </x:c>
       <x:c r="J67" s="26" t="n">
         <x:f>ROUND(E67-F67,1)</x:f>
-        <x:v>7260</x:v>
+        <x:v>6720</x:v>
       </x:c>
       <x:c r="K67" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -3047,29 +3047,29 @@
         <x:v>3月27日</x:v>
       </x:c>
       <x:c r="D68" s="23" t="n">
-        <x:v>157660</x:v>
+        <x:v>159500</x:v>
       </x:c>
       <x:c r="E68" s="23" t="n">
-        <x:v>172220</x:v>
+        <x:v>170800</x:v>
       </x:c>
       <x:c r="F68" s="23" t="n">
-        <x:v>157000</x:v>
+        <x:v>159500</x:v>
       </x:c>
       <x:c r="G68" s="23" t="n">
-        <x:v>169400</x:v>
+        <x:v>166540</x:v>
       </x:c>
       <x:c r="H68" s="28" t="n">
-        <x:v>11360</x:v>
+        <x:v>9660</x:v>
       </x:c>
       <x:c r="I68" s="24" t="n">
-        <x:v>0.07188053657301952</x:v>
+        <x:v>0.06157572667006628</x:v>
       </x:c>
       <x:c r="J68" s="26" t="n">
         <x:f>ROUND(E68-F68,1)</x:f>
-        <x:v>15220</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="K68" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -3083,29 +3083,29 @@
         <x:v>3月30日</x:v>
       </x:c>
       <x:c r="D69" s="23" t="n">
-        <x:v>170000</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="E69" s="23" t="n">
-        <x:v>175000</x:v>
+        <x:v>174540</x:v>
       </x:c>
       <x:c r="F69" s="23" t="n">
-        <x:v>169040</x:v>
+        <x:v>168840</x:v>
       </x:c>
       <x:c r="G69" s="23" t="n">
-        <x:v>172860</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="H69" s="28" t="n">
-        <x:v>3460</x:v>
+        <x:v>5460</x:v>
       </x:c>
       <x:c r="I69" s="24" t="n">
-        <x:v>0.020425029515938498</x:v>
+        <x:v>0.0327849165365679</x:v>
       </x:c>
       <x:c r="J69" s="23" t="n">
         <x:f>ROUND(E69-F69,1)</x:f>
-        <x:v>5960</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="K69" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -3119,29 +3119,29 @@
         <x:v>3月31日</x:v>
       </x:c>
       <x:c r="D70" s="23" t="n">
-        <x:v>170800</x:v>
+        <x:v>171920</x:v>
       </x:c>
       <x:c r="E70" s="23" t="n">
-        <x:v>173380</x:v>
+        <x:v>172180</x:v>
       </x:c>
       <x:c r="F70" s="23" t="n">
-        <x:v>157700</x:v>
+        <x:v>157080</x:v>
       </x:c>
       <x:c r="G70" s="23" t="n">
-        <x:v>158040</x:v>
+        <x:v>157600</x:v>
       </x:c>
       <x:c r="H70" s="28" t="n">
-        <x:v>-14820</x:v>
+        <x:v>-14400</x:v>
       </x:c>
       <x:c r="I70" s="24" t="n">
-        <x:v>-0.0857341200971885</x:v>
+        <x:v>-0.08372093023255811</x:v>
       </x:c>
       <x:c r="J70" s="26" t="n">
         <x:f>ROUND(E70-F70,1)</x:f>
-        <x:v>15680</x:v>
+        <x:v>15100</x:v>
       </x:c>
       <x:c r="K70" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -3160,7 +3160,7 @@
       <x:c r="I71" s="30"/>
       <x:c r="J71" s="32" t="n">
         <x:f>ROUND(SUM(J49:J70),1)</x:f>
-        <x:v>228860</x:v>
+        <x:v>210260</x:v>
       </x:c>
       <x:c r="K71" s="30"/>
     </x:row>
@@ -3178,7 +3178,7 @@
       <x:c r="I72" s="30"/>
       <x:c r="J72" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J49:J70),0),1)</x:f>
-        <x:v>10402.7</x:v>
+        <x:v>9557.3</x:v>
       </x:c>
       <x:c r="K72" s="30"/>
     </x:row>
@@ -3243,29 +3243,29 @@
         <x:v>4月1日</x:v>
       </x:c>
       <x:c r="D76" s="23" t="n">
-        <x:v>161000</x:v>
+        <x:v>160000</x:v>
       </x:c>
       <x:c r="E76" s="23" t="n">
-        <x:v>164500</x:v>
+        <x:v>163220</x:v>
       </x:c>
       <x:c r="F76" s="23" t="n">
-        <x:v>154560</x:v>
+        <x:v>153840</x:v>
       </x:c>
       <x:c r="G76" s="23" t="n">
-        <x:v>159060</x:v>
+        <x:v>158260</x:v>
       </x:c>
       <x:c r="H76" s="28" t="n">
-        <x:v>1020</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="I76" s="24" t="n">
-        <x:v>0.006454062262718274</x:v>
+        <x:v>0.004187817258883175</x:v>
       </x:c>
       <x:c r="J76" s="26" t="n">
         <x:f>ROUND(E76-F76,1)</x:f>
-        <x:v>9940</x:v>
+        <x:v>9380</x:v>
       </x:c>
       <x:c r="K76" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -3279,29 +3279,29 @@
         <x:v>4月2日</x:v>
       </x:c>
       <x:c r="D77" s="23" t="n">
-        <x:v>159800</x:v>
+        <x:v>158920</x:v>
       </x:c>
       <x:c r="E77" s="23" t="n">
-        <x:v>163800</x:v>
+        <x:v>162840</x:v>
       </x:c>
       <x:c r="F77" s="23" t="n">
-        <x:v>156000</x:v>
+        <x:v>156320</x:v>
       </x:c>
       <x:c r="G77" s="23" t="n">
-        <x:v>160180</x:v>
+        <x:v>159580</x:v>
       </x:c>
       <x:c r="H77" s="28" t="n">
-        <x:v>1120</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="I77" s="24" t="n">
-        <x:v>0.007041368037218554</x:v>
+        <x:v>0.008340705168709661</x:v>
       </x:c>
       <x:c r="J77" s="26" t="n">
         <x:f>ROUND(E77-F77,1)</x:f>
-        <x:v>7800</x:v>
+        <x:v>6520</x:v>
       </x:c>
       <x:c r="K77" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -3315,29 +3315,29 @@
         <x:v>4月3日</x:v>
       </x:c>
       <x:c r="D78" s="23" t="n">
-        <x:v>161000</x:v>
+        <x:v>161140</x:v>
       </x:c>
       <x:c r="E78" s="23" t="n">
-        <x:v>163120</x:v>
+        <x:v>161660</x:v>
       </x:c>
       <x:c r="F78" s="23" t="n">
-        <x:v>157220</x:v>
+        <x:v>157000</x:v>
       </x:c>
       <x:c r="G78" s="23" t="n">
-        <x:v>157860</x:v>
+        <x:v>157680</x:v>
       </x:c>
       <x:c r="H78" s="28" t="n">
-        <x:v>-2320</x:v>
+        <x:v>-1900</x:v>
       </x:c>
       <x:c r="I78" s="24" t="n">
-        <x:v>-0.014483705830940163</x:v>
+        <x:v>-0.011906253916530884</x:v>
       </x:c>
       <x:c r="J78" s="23" t="n">
         <x:f>ROUND(E78-F78,1)</x:f>
-        <x:v>5900</x:v>
+        <x:v>4660</x:v>
       </x:c>
       <x:c r="K78" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -3351,29 +3351,29 @@
         <x:v>4月7日</x:v>
       </x:c>
       <x:c r="D79" s="23" t="n">
-        <x:v>158440</x:v>
+        <x:v>156200</x:v>
       </x:c>
       <x:c r="E79" s="23" t="n">
-        <x:v>165500</x:v>
+        <x:v>164160</x:v>
       </x:c>
       <x:c r="F79" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>156060</x:v>
       </x:c>
       <x:c r="G79" s="23" t="n">
-        <x:v>160860</x:v>
+        <x:v>161060</x:v>
       </x:c>
       <x:c r="H79" s="28" t="n">
-        <x:v>3000</x:v>
+        <x:v>3380</x:v>
       </x:c>
       <x:c r="I79" s="24" t="n">
-        <x:v>0.01900418091980227</x:v>
+        <x:v>0.0214358193810249</x:v>
       </x:c>
       <x:c r="J79" s="26" t="n">
         <x:f>ROUND(E79-F79,1)</x:f>
-        <x:v>9000</x:v>
+        <x:v>8100</x:v>
       </x:c>
       <x:c r="K79" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -3387,29 +3387,29 @@
         <x:v>4月8日</x:v>
       </x:c>
       <x:c r="D80" s="23" t="n">
-        <x:v>160000</x:v>
+        <x:v>160600</x:v>
       </x:c>
       <x:c r="E80" s="23" t="n">
-        <x:v>164700</x:v>
+        <x:v>162340</x:v>
       </x:c>
       <x:c r="F80" s="23" t="n">
-        <x:v>157000</x:v>
+        <x:v>156600</x:v>
       </x:c>
       <x:c r="G80" s="23" t="n">
-        <x:v>159620</x:v>
+        <x:v>158540</x:v>
       </x:c>
       <x:c r="H80" s="28" t="n">
-        <x:v>-1240</x:v>
+        <x:v>-2520</x:v>
       </x:c>
       <x:c r="I80" s="24" t="n">
-        <x:v>-0.007708566455302712</x:v>
-      </x:c>
-      <x:c r="J80" s="26" t="n">
+        <x:v>-0.015646342977772232</x:v>
+      </x:c>
+      <x:c r="J80" s="23" t="n">
         <x:f>ROUND(E80-F80,1)</x:f>
-        <x:v>7700</x:v>
+        <x:v>5740</x:v>
       </x:c>
       <x:c r="K80" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -3423,29 +3423,29 @@
         <x:v>4月9日</x:v>
       </x:c>
       <x:c r="D81" s="23" t="n">
-        <x:v>159000</x:v>
+        <x:v>157860</x:v>
       </x:c>
       <x:c r="E81" s="23" t="n">
-        <x:v>159740</x:v>
+        <x:v>157860</x:v>
       </x:c>
       <x:c r="F81" s="23" t="n">
-        <x:v>152500</x:v>
+        <x:v>151640</x:v>
       </x:c>
       <x:c r="G81" s="23" t="n">
-        <x:v>153560</x:v>
+        <x:v>152420</x:v>
       </x:c>
       <x:c r="H81" s="28" t="n">
-        <x:v>-6060</x:v>
+        <x:v>-6120</x:v>
       </x:c>
       <x:c r="I81" s="24" t="n">
-        <x:v>-0.037965167272271616</x:v>
+        <x:v>-0.038602245490097165</x:v>
       </x:c>
       <x:c r="J81" s="26" t="n">
         <x:f>ROUND(E81-F81,1)</x:f>
-        <x:v>7240</x:v>
+        <x:v>6220</x:v>
       </x:c>
       <x:c r="K81" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -3459,29 +3459,29 @@
         <x:v>4月10日</x:v>
       </x:c>
       <x:c r="D82" s="23" t="n">
-        <x:v>156300</x:v>
+        <x:v>157420</x:v>
       </x:c>
       <x:c r="E82" s="23" t="n">
-        <x:v>158900</x:v>
+        <x:v>159000</x:v>
       </x:c>
       <x:c r="F82" s="23" t="n">
-        <x:v>153800</x:v>
+        <x:v>153580</x:v>
       </x:c>
       <x:c r="G82" s="23" t="n">
-        <x:v>157600</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="H82" s="28" t="n">
-        <x:v>4040</x:v>
+        <x:v>4080</x:v>
       </x:c>
       <x:c r="I82" s="24" t="n">
-        <x:v>0.026308934618390234</x:v>
+        <x:v>0.02676814066395483</x:v>
       </x:c>
       <x:c r="J82" s="23" t="n">
         <x:f>ROUND(E82-F82,1)</x:f>
-        <x:v>5100</x:v>
+        <x:v>5420</x:v>
       </x:c>
       <x:c r="K82" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -3495,29 +3495,29 @@
         <x:v>4月13日</x:v>
       </x:c>
       <x:c r="D83" s="23" t="n">
-        <x:v>155020</x:v>
+        <x:v>156660</x:v>
       </x:c>
       <x:c r="E83" s="23" t="n">
-        <x:v>166600</x:v>
+        <x:v>165000</x:v>
       </x:c>
       <x:c r="F83" s="23" t="n">
-        <x:v>154780</x:v>
+        <x:v>153040</x:v>
       </x:c>
       <x:c r="G83" s="23" t="n">
-        <x:v>166500</x:v>
+        <x:v>165000</x:v>
       </x:c>
       <x:c r="H83" s="28" t="n">
-        <x:v>8900</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="I83" s="24" t="n">
-        <x:v>0.056472081218274184</x:v>
+        <x:v>0.054313099041533475</x:v>
       </x:c>
       <x:c r="J83" s="26" t="n">
         <x:f>ROUND(E83-F83,1)</x:f>
-        <x:v>11820</x:v>
+        <x:v>11960</x:v>
       </x:c>
       <x:c r="K83" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -3531,29 +3531,29 @@
         <x:v>4月14日</x:v>
       </x:c>
       <x:c r="D84" s="23" t="n">
-        <x:v>167000</x:v>
+        <x:v>164360</x:v>
       </x:c>
       <x:c r="E84" s="23" t="n">
-        <x:v>168400</x:v>
+        <x:v>166980</x:v>
       </x:c>
       <x:c r="F84" s="23" t="n">
-        <x:v>164100</x:v>
+        <x:v>163880</x:v>
       </x:c>
       <x:c r="G84" s="23" t="n">
-        <x:v>166840</x:v>
+        <x:v>165920</x:v>
       </x:c>
       <x:c r="H84" s="28" t="n">
-        <x:v>340</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="I84" s="24" t="n">
-        <x:v>0.002042042042041947</x:v>
+        <x:v>0.005575757575757567</x:v>
       </x:c>
       <x:c r="J84" s="23" t="n">
         <x:f>ROUND(E84-F84,1)</x:f>
-        <x:v>4300</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="K84" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -3567,29 +3567,29 @@
         <x:v>4月15日</x:v>
       </x:c>
       <x:c r="D85" s="23" t="n">
-        <x:v>168400</x:v>
+        <x:v>165360</x:v>
       </x:c>
       <x:c r="E85" s="23" t="n">
-        <x:v>171980</x:v>
+        <x:v>171380</x:v>
       </x:c>
       <x:c r="F85" s="23" t="n">
-        <x:v>165020</x:v>
+        <x:v>164080</x:v>
       </x:c>
       <x:c r="G85" s="23" t="n">
-        <x:v>168660</x:v>
+        <x:v>167540</x:v>
       </x:c>
       <x:c r="H85" s="28" t="n">
-        <x:v>1820</x:v>
+        <x:v>1620</x:v>
       </x:c>
       <x:c r="I85" s="24" t="n">
-        <x:v>0.010908654998801337</x:v>
+        <x:v>0.009763741562198724</x:v>
       </x:c>
       <x:c r="J85" s="26" t="n">
         <x:f>ROUND(E85-F85,1)</x:f>
-        <x:v>6960</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="K85" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -3603,29 +3603,29 @@
         <x:v>4月16日</x:v>
       </x:c>
       <x:c r="D86" s="23" t="n">
-        <x:v>170500</x:v>
+        <x:v>170920</x:v>
       </x:c>
       <x:c r="E86" s="23" t="n">
-        <x:v>176200</x:v>
+        <x:v>175000</x:v>
       </x:c>
       <x:c r="F86" s="23" t="n">
-        <x:v>169200</x:v>
+        <x:v>169700</x:v>
       </x:c>
       <x:c r="G86" s="23" t="n">
-        <x:v>176000</x:v>
+        <x:v>174820</x:v>
       </x:c>
       <x:c r="H86" s="28" t="n">
-        <x:v>7340</x:v>
+        <x:v>7280</x:v>
       </x:c>
       <x:c r="I86" s="24" t="n">
-        <x:v>0.04351950669986948</x:v>
-      </x:c>
-      <x:c r="J86" s="26" t="n">
+        <x:v>0.043452309896144126</x:v>
+      </x:c>
+      <x:c r="J86" s="23" t="n">
         <x:f>ROUND(E86-F86,1)</x:f>
-        <x:v>7000</x:v>
+        <x:v>5300</x:v>
       </x:c>
       <x:c r="K86" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -3639,29 +3639,29 @@
         <x:v>4月17日</x:v>
       </x:c>
       <x:c r="D87" s="42" t="n">
-        <x:v>177460</x:v>
+        <x:v>176400</x:v>
       </x:c>
       <x:c r="E87" s="42" t="n">
-        <x:v>178000</x:v>
+        <x:v>176500</x:v>
       </x:c>
       <x:c r="F87" s="42" t="n">
-        <x:v>173680</x:v>
+        <x:v>172700</x:v>
       </x:c>
       <x:c r="G87" s="42" t="n">
-        <x:v>177560</x:v>
+        <x:v>176360</x:v>
       </x:c>
       <x:c r="H87" s="28" t="n">
-        <x:v>1560</x:v>
+        <x:v>1540</x:v>
       </x:c>
       <x:c r="I87" s="43" t="n">
-        <x:v>0.008863636363636296</x:v>
+        <x:v>0.008809060748198094</x:v>
       </x:c>
       <x:c r="J87" s="42" t="n">
         <x:f>ROUND(E87-F87,1)</x:f>
-        <x:v>4320</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="K87" s="41" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -3675,29 +3675,29 @@
         <x:v>4月20日</x:v>
       </x:c>
       <x:c r="D88" s="23" t="n">
-        <x:v>177000</x:v>
+        <x:v>174080</x:v>
       </x:c>
       <x:c r="E88" s="23" t="n">
-        <x:v>181440</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="F88" s="23" t="n">
-        <x:v>174800</x:v>
+        <x:v>174080</x:v>
       </x:c>
       <x:c r="G88" s="23" t="n">
-        <x:v>180200</x:v>
+        <x:v>179520</x:v>
       </x:c>
       <x:c r="H88" s="28" t="n">
-        <x:v>2640</x:v>
+        <x:v>3160</x:v>
       </x:c>
       <x:c r="I88" s="24" t="n">
-        <x:v>0.014868213561612942</x:v>
+        <x:v>0.0179178952143344</x:v>
       </x:c>
       <x:c r="J88" s="26" t="n">
         <x:f>ROUND(E88-F88,1)</x:f>
-        <x:v>6640</x:v>
+        <x:v>6840</x:v>
       </x:c>
       <x:c r="K88" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -3711,29 +3711,29 @@
         <x:v>4月21日</x:v>
       </x:c>
       <x:c r="D89" s="23" t="n">
-        <x:v>180900</x:v>
+        <x:v>178540</x:v>
       </x:c>
       <x:c r="E89" s="23" t="n">
-        <x:v>180900</x:v>
+        <x:v>179860</x:v>
       </x:c>
       <x:c r="F89" s="23" t="n">
-        <x:v>169500</x:v>
+        <x:v>169000</x:v>
       </x:c>
       <x:c r="G89" s="23" t="n">
-        <x:v>174260</x:v>
+        <x:v>173260</x:v>
       </x:c>
       <x:c r="H89" s="28" t="n">
-        <x:v>-5940</x:v>
+        <x:v>-6260</x:v>
       </x:c>
       <x:c r="I89" s="24" t="n">
-        <x:v>-0.03296337402885685</x:v>
+        <x:v>-0.034870766488413585</x:v>
       </x:c>
       <x:c r="J89" s="26" t="n">
         <x:f>ROUND(E89-F89,1)</x:f>
-        <x:v>11400</x:v>
+        <x:v>10860</x:v>
       </x:c>
       <x:c r="K89" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -3747,29 +3747,29 @@
         <x:v>4月22日</x:v>
       </x:c>
       <x:c r="D90" s="23" t="n">
-        <x:v>173660</x:v>
+        <x:v>172580</x:v>
       </x:c>
       <x:c r="E90" s="23" t="n">
-        <x:v>176500</x:v>
+        <x:v>176160</x:v>
       </x:c>
       <x:c r="F90" s="23" t="n">
-        <x:v>172020</x:v>
+        <x:v>171580</x:v>
       </x:c>
       <x:c r="G90" s="23" t="n">
-        <x:v>175240</x:v>
+        <x:v>174000</x:v>
       </x:c>
       <x:c r="H90" s="28" t="n">
-        <x:v>980</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="I90" s="24" t="n">
-        <x:v>0.005623780557787228</x:v>
+        <x:v>0.0042710377467389815</x:v>
       </x:c>
       <x:c r="J90" s="23" t="n">
         <x:f>ROUND(E90-F90,1)</x:f>
-        <x:v>4480</x:v>
+        <x:v>4580</x:v>
       </x:c>
       <x:c r="K90" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -3783,29 +3783,29 @@
         <x:v>4月23日</x:v>
       </x:c>
       <x:c r="D91" s="23" t="n">
-        <x:v>175740</x:v>
+        <x:v>176000</x:v>
       </x:c>
       <x:c r="E91" s="23" t="n">
-        <x:v>178900</x:v>
+        <x:v>177380</x:v>
       </x:c>
       <x:c r="F91" s="23" t="n">
-        <x:v>172140</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="G91" s="23" t="n">
-        <x:v>177960</x:v>
+        <x:v>177000</x:v>
       </x:c>
       <x:c r="H91" s="28" t="n">
-        <x:v>2720</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="I91" s="24" t="n">
-        <x:v>0.01552157041771296</x:v>
-      </x:c>
-      <x:c r="J91" s="26" t="n">
+        <x:v>0.01724137931034475</x:v>
+      </x:c>
+      <x:c r="J91" s="23" t="n">
         <x:f>ROUND(E91-F91,1)</x:f>
-        <x:v>6760</x:v>
+        <x:v>5380</x:v>
       </x:c>
       <x:c r="K91" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -3819,29 +3819,29 @@
         <x:v>4月24日</x:v>
       </x:c>
       <x:c r="D92" s="23" t="n">
-        <x:v>178000</x:v>
+        <x:v>176720</x:v>
       </x:c>
       <x:c r="E92" s="23" t="n">
-        <x:v>179980</x:v>
+        <x:v>178660</x:v>
       </x:c>
       <x:c r="F92" s="23" t="n">
-        <x:v>174500</x:v>
+        <x:v>174300</x:v>
       </x:c>
       <x:c r="G92" s="23" t="n">
-        <x:v>177900</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="H92" s="23" t="n">
-        <x:v>-60</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="I92" s="24" t="n">
-        <x:v>-0.0003371544167228846</x:v>
+        <x:v>-0.0002259887005650052</x:v>
       </x:c>
       <x:c r="J92" s="23" t="n">
         <x:f>ROUND(E92-F92,1)</x:f>
-        <x:v>5480</x:v>
+        <x:v>4360</x:v>
       </x:c>
       <x:c r="K92" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -3855,29 +3855,29 @@
         <x:v>4月27日</x:v>
       </x:c>
       <x:c r="D93" s="23" t="n">
-        <x:v>182000</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="E93" s="23" t="n">
-        <x:v>184800</x:v>
+        <x:v>183120</x:v>
       </x:c>
       <x:c r="F93" s="23" t="n">
-        <x:v>178500</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="G93" s="23" t="n">
-        <x:v>180560</x:v>
+        <x:v>179500</x:v>
       </x:c>
       <x:c r="H93" s="28" t="n">
-        <x:v>2660</x:v>
+        <x:v>2540</x:v>
       </x:c>
       <x:c r="I93" s="24" t="n">
-        <x:v>0.014952220348510403</x:v>
+        <x:v>0.01435352622061492</x:v>
       </x:c>
       <x:c r="J93" s="26" t="n">
         <x:f>ROUND(E93-F93,1)</x:f>
-        <x:v>6300</x:v>
+        <x:v>6160</x:v>
       </x:c>
       <x:c r="K93" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -3891,29 +3891,29 @@
         <x:v>4月28日</x:v>
       </x:c>
       <x:c r="D94" s="23" t="n">
-        <x:v>179000</x:v>
+        <x:v>178800</x:v>
       </x:c>
       <x:c r="E94" s="23" t="n">
-        <x:v>180500</x:v>
+        <x:v>180720</x:v>
       </x:c>
       <x:c r="F94" s="23" t="n">
-        <x:v>173400</x:v>
+        <x:v>172640</x:v>
       </x:c>
       <x:c r="G94" s="23" t="n">
-        <x:v>178620</x:v>
+        <x:v>178380</x:v>
       </x:c>
       <x:c r="H94" s="28" t="n">
-        <x:v>-1940</x:v>
+        <x:v>-1120</x:v>
       </x:c>
       <x:c r="I94" s="24" t="n">
-        <x:v>-0.010744350908285294</x:v>
+        <x:v>-0.0062395543175487456</x:v>
       </x:c>
       <x:c r="J94" s="26" t="n">
         <x:f>ROUND(E94-F94,1)</x:f>
-        <x:v>7100</x:v>
+        <x:v>8080</x:v>
       </x:c>
       <x:c r="K94" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -3927,29 +3927,29 @@
         <x:v>4月29日</x:v>
       </x:c>
       <x:c r="D95" s="23" t="n">
-        <x:v>178700</x:v>
+        <x:v>177640</x:v>
       </x:c>
       <x:c r="E95" s="23" t="n">
-        <x:v>184440</x:v>
+        <x:v>183660</x:v>
       </x:c>
       <x:c r="F95" s="23" t="n">
-        <x:v>175260</x:v>
+        <x:v>174780</x:v>
       </x:c>
       <x:c r="G95" s="23" t="n">
-        <x:v>183880</x:v>
+        <x:v>183660</x:v>
       </x:c>
       <x:c r="H95" s="28" t="n">
-        <x:v>5260</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="I95" s="24" t="n">
-        <x:v>0.029447990146680203</x:v>
+        <x:v>0.029599730911537225</x:v>
       </x:c>
       <x:c r="J95" s="26" t="n">
         <x:f>ROUND(E95-F95,1)</x:f>
-        <x:v>9180</x:v>
+        <x:v>8880</x:v>
       </x:c>
       <x:c r="K95" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -3963,29 +3963,29 @@
         <x:v>4月30日</x:v>
       </x:c>
       <x:c r="D96" s="23" t="n">
-        <x:v>184000</x:v>
+        <x:v>183140</x:v>
       </x:c>
       <x:c r="E96" s="23" t="n">
-        <x:v>189500</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="F96" s="23" t="n">
-        <x:v>182460</x:v>
+        <x:v>180200</x:v>
       </x:c>
       <x:c r="G96" s="23" t="n">
-        <x:v>189080</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="H96" s="28" t="n">
-        <x:v>5200</x:v>
+        <x:v>5180</x:v>
       </x:c>
       <x:c r="I96" s="24" t="n">
-        <x:v>0.028279312595170802</x:v>
+        <x:v>0.028204290536861576</x:v>
       </x:c>
       <x:c r="J96" s="26" t="n">
         <x:f>ROUND(E96-F96,1)</x:f>
-        <x:v>7040</x:v>
+        <x:v>8640</x:v>
       </x:c>
       <x:c r="K96" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -4004,7 +4004,7 @@
       <x:c r="I97" s="30"/>
       <x:c r="J97" s="32" t="n">
         <x:f>ROUND(SUM(J76:J96),1)</x:f>
-        <x:v>151460</x:v>
+        <x:v>141280</x:v>
       </x:c>
       <x:c r="K97" s="30"/>
     </x:row>
@@ -4022,7 +4022,7 @@
       <x:c r="I98" s="30"/>
       <x:c r="J98" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J76:J96),0),1)</x:f>
-        <x:v>7212.4</x:v>
+        <x:v>6727.6</x:v>
       </x:c>
       <x:c r="K98" s="30"/>
     </x:row>
@@ -4087,29 +4087,29 @@
         <x:v>5月6日</x:v>
       </x:c>
       <x:c r="D102" s="23" t="n">
-        <x:v>191500</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="E102" s="23" t="n">
-        <x:v>199560</x:v>
+        <x:v>204640</x:v>
       </x:c>
       <x:c r="F102" s="23" t="n">
-        <x:v>191040</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="G102" s="23" t="n">
-        <x:v>199400</x:v>
+        <x:v>199260</x:v>
       </x:c>
       <x:c r="H102" s="28" t="n">
-        <x:v>10320</x:v>
+        <x:v>10420</x:v>
       </x:c>
       <x:c r="I102" s="24" t="n">
-        <x:v>0.05458007192722647</x:v>
+        <x:v>0.055178987502647825</x:v>
       </x:c>
       <x:c r="J102" s="26" t="n">
         <x:f>ROUND(E102-F102,1)</x:f>
-        <x:v>8520</x:v>
+        <x:v>13340</x:v>
       </x:c>
       <x:c r="K102" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -4123,29 +4123,29 @@
         <x:v>5月7日</x:v>
       </x:c>
       <x:c r="D103" s="23" t="n">
-        <x:v>199000</x:v>
+        <x:v>198980</x:v>
       </x:c>
       <x:c r="E103" s="23" t="n">
-        <x:v>200440</x:v>
+        <x:v>200040</x:v>
       </x:c>
       <x:c r="F103" s="23" t="n">
-        <x:v>193400</x:v>
+        <x:v>192940</x:v>
       </x:c>
       <x:c r="G103" s="23" t="n">
-        <x:v>199060</x:v>
+        <x:v>198500</x:v>
       </x:c>
       <x:c r="H103" s="28" t="n">
-        <x:v>-340</x:v>
+        <x:v>-760</x:v>
       </x:c>
       <x:c r="I103" s="24" t="n">
-        <x:v>-0.0017051153460381219</x:v>
+        <x:v>-0.0038141122151962303</x:v>
       </x:c>
       <x:c r="J103" s="26" t="n">
         <x:f>ROUND(E103-F103,1)</x:f>
-        <x:v>7040</x:v>
+        <x:v>7100</x:v>
       </x:c>
       <x:c r="K103" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -4159,29 +4159,29 @@
         <x:v>5月8日</x:v>
       </x:c>
       <x:c r="D104" s="23" t="n">
-        <x:v>197120</x:v>
+        <x:v>197080</x:v>
       </x:c>
       <x:c r="E104" s="23" t="n">
-        <x:v>201480</x:v>
+        <x:v>200140</x:v>
       </x:c>
       <x:c r="F104" s="23" t="n">
-        <x:v>195100</x:v>
+        <x:v>194040</x:v>
       </x:c>
       <x:c r="G104" s="23" t="n">
-        <x:v>196560</x:v>
+        <x:v>196100</x:v>
       </x:c>
       <x:c r="H104" s="28" t="n">
-        <x:v>-2500</x:v>
+        <x:v>-2400</x:v>
       </x:c>
       <x:c r="I104" s="24" t="n">
-        <x:v>-0.012559027428915903</x:v>
+        <x:v>-0.012090680100755646</x:v>
       </x:c>
       <x:c r="J104" s="26" t="n">
         <x:f>ROUND(E104-F104,1)</x:f>
-        <x:v>6380</x:v>
+        <x:v>6100</x:v>
       </x:c>
       <x:c r="K104" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -4195,29 +4195,29 @@
         <x:v>5月11日</x:v>
       </x:c>
       <x:c r="D105" s="23" t="n">
-        <x:v>196560</x:v>
+        <x:v>195080</x:v>
       </x:c>
       <x:c r="E105" s="23" t="n">
-        <x:v>205600</x:v>
+        <x:v>204660</x:v>
       </x:c>
       <x:c r="F105" s="23" t="n">
-        <x:v>195200</x:v>
+        <x:v>195000</x:v>
       </x:c>
       <x:c r="G105" s="23" t="n">
-        <x:v>205020</x:v>
+        <x:v>203920</x:v>
       </x:c>
       <x:c r="H105" s="28" t="n">
-        <x:v>8460</x:v>
+        <x:v>7820</x:v>
       </x:c>
       <x:c r="I105" s="24" t="n">
-        <x:v>0.04304029304029311</x:v>
+        <x:v>0.03987761346251917</x:v>
       </x:c>
       <x:c r="J105" s="26" t="n">
         <x:f>ROUND(E105-F105,1)</x:f>
-        <x:v>10400</x:v>
+        <x:v>9660</x:v>
       </x:c>
       <x:c r="K105" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -4231,29 +4231,29 @@
         <x:v>5月12日</x:v>
       </x:c>
       <x:c r="D106" s="23" t="n">
-        <x:v>208000</x:v>
+        <x:v>205340</x:v>
       </x:c>
       <x:c r="E106" s="23" t="n">
-        <x:v>208800</x:v>
+        <x:v>207980</x:v>
       </x:c>
       <x:c r="F106" s="23" t="n">
-        <x:v>203300</x:v>
+        <x:v>202160</x:v>
       </x:c>
       <x:c r="G106" s="23" t="n">
-        <x:v>205260</x:v>
+        <x:v>204080</x:v>
       </x:c>
       <x:c r="H106" s="28" t="n">
-        <x:v>240</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="I106" s="24" t="n">
-        <x:v>0.0011706175007315522</x:v>
+        <x:v>0.0007846214201647772</x:v>
       </x:c>
       <x:c r="J106" s="23" t="n">
         <x:f>ROUND(E106-F106,1)</x:f>
-        <x:v>5500</x:v>
+        <x:v>5820</x:v>
       </x:c>
       <x:c r="K106" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -4267,29 +4267,29 @@
         <x:v>5月13日</x:v>
       </x:c>
       <x:c r="D107" s="23" t="n">
-        <x:v>206520</x:v>
+        <x:v>208000</x:v>
       </x:c>
       <x:c r="E107" s="23" t="n">
-        <x:v>209880</x:v>
+        <x:v>209040</x:v>
       </x:c>
       <x:c r="F107" s="23" t="n">
-        <x:v>195000</x:v>
+        <x:v>194300</x:v>
       </x:c>
       <x:c r="G107" s="23" t="n">
-        <x:v>201960</x:v>
+        <x:v>202000</x:v>
       </x:c>
       <x:c r="H107" s="28" t="n">
-        <x:v>-3300</x:v>
+        <x:v>-2080</x:v>
       </x:c>
       <x:c r="I107" s="24" t="n">
-        <x:v>-0.01607717041800638</x:v>
+        <x:v>-0.010192081536652298</x:v>
       </x:c>
       <x:c r="J107" s="26" t="n">
         <x:f>ROUND(E107-F107,1)</x:f>
-        <x:v>14880</x:v>
+        <x:v>14740</x:v>
       </x:c>
       <x:c r="K107" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -4303,29 +4303,29 @@
         <x:v>5月14日</x:v>
       </x:c>
       <x:c r="D108" s="23" t="n">
-        <x:v>203000</x:v>
+        <x:v>203720</x:v>
       </x:c>
       <x:c r="E108" s="23" t="n">
-        <x:v>204400</x:v>
+        <x:v>203720</x:v>
       </x:c>
       <x:c r="F108" s="23" t="n">
-        <x:v>190080</x:v>
+        <x:v>190040</x:v>
       </x:c>
       <x:c r="G108" s="23" t="n">
-        <x:v>191760</x:v>
+        <x:v>191540</x:v>
       </x:c>
       <x:c r="H108" s="28" t="n">
-        <x:v>-10200</x:v>
+        <x:v>-10460</x:v>
       </x:c>
       <x:c r="I108" s="24" t="n">
-        <x:v>-0.0505050505050505</x:v>
+        <x:v>-0.05178217821782183</x:v>
       </x:c>
       <x:c r="J108" s="26" t="n">
         <x:f>ROUND(E108-F108,1)</x:f>
-        <x:v>14320</x:v>
+        <x:v>13680</x:v>
       </x:c>
       <x:c r="K108" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -4339,29 +4339,29 @@
         <x:v>5月15日</x:v>
       </x:c>
       <x:c r="D109" s="42" t="n">
-        <x:v>190000</x:v>
+        <x:v>190100</x:v>
       </x:c>
       <x:c r="E109" s="42" t="n">
-        <x:v>194900</x:v>
+        <x:v>195360</x:v>
       </x:c>
       <x:c r="F109" s="42" t="n">
-        <x:v>186800</x:v>
+        <x:v>187240</x:v>
       </x:c>
       <x:c r="G109" s="42" t="n">
-        <x:v>188800</x:v>
+        <x:v>189440</x:v>
       </x:c>
       <x:c r="H109" s="28" t="n">
-        <x:v>-2960</x:v>
+        <x:v>-2100</x:v>
       </x:c>
       <x:c r="I109" s="43" t="n">
-        <x:v>-0.015435961618689986</x:v>
+        <x:v>-0.010963767359298271</x:v>
       </x:c>
       <x:c r="J109" s="26" t="n">
         <x:f>ROUND(E109-F109,1)</x:f>
-        <x:v>8100</x:v>
+        <x:v>8120</x:v>
       </x:c>
       <x:c r="K109" s="41" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -4375,29 +4375,29 @@
         <x:v>5月18日</x:v>
       </x:c>
       <x:c r="D110" s="23" t="n">
-        <x:v>189000</x:v>
+        <x:v>190060</x:v>
       </x:c>
       <x:c r="E110" s="23" t="n">
-        <x:v>193900</x:v>
+        <x:v>193820</x:v>
       </x:c>
       <x:c r="F110" s="23" t="n">
-        <x:v>187600</x:v>
+        <x:v>188480</x:v>
       </x:c>
       <x:c r="G110" s="23" t="n">
-        <x:v>192180</x:v>
+        <x:v>192420</x:v>
       </x:c>
       <x:c r="H110" s="28" t="n">
-        <x:v>3380</x:v>
+        <x:v>2980</x:v>
       </x:c>
       <x:c r="I110" s="24" t="n">
-        <x:v>0.017902542372881358</x:v>
-      </x:c>
-      <x:c r="J110" s="26" t="n">
+        <x:v>0.015730574324324342</x:v>
+      </x:c>
+      <x:c r="J110" s="23" t="n">
         <x:f>ROUND(E110-F110,1)</x:f>
-        <x:v>6300</x:v>
+        <x:v>5340</x:v>
       </x:c>
       <x:c r="K110" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -4411,29 +4411,29 @@
         <x:v>5月19日</x:v>
       </x:c>
       <x:c r="D111" s="23" t="n">
-        <x:v>190980</x:v>
+        <x:v>190740</x:v>
       </x:c>
       <x:c r="E111" s="23" t="n">
-        <x:v>192120</x:v>
+        <x:v>192360</x:v>
       </x:c>
       <x:c r="F111" s="23" t="n">
-        <x:v>182060</x:v>
+        <x:v>182320</x:v>
       </x:c>
       <x:c r="G111" s="23" t="n">
-        <x:v>184400</x:v>
+        <x:v>184620</x:v>
       </x:c>
       <x:c r="H111" s="28" t="n">
-        <x:v>-7780</x:v>
+        <x:v>-7800</x:v>
       </x:c>
       <x:c r="I111" s="24" t="n">
-        <x:v>-0.04048288063274019</x:v>
+        <x:v>-0.040536326785157506</x:v>
       </x:c>
       <x:c r="J111" s="26" t="n">
         <x:f>ROUND(E111-F111,1)</x:f>
-        <x:v>10060</x:v>
+        <x:v>10040</x:v>
       </x:c>
       <x:c r="K111" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -4447,29 +4447,29 @@
         <x:v>5月20日</x:v>
       </x:c>
       <x:c r="D112" s="23" t="n">
-        <x:v>182120</x:v>
+        <x:v>185300</x:v>
       </x:c>
       <x:c r="E112" s="23" t="n">
-        <x:v>184800</x:v>
+        <x:v>185860</x:v>
       </x:c>
       <x:c r="F112" s="23" t="n">
-        <x:v>175200</x:v>
+        <x:v>175520</x:v>
       </x:c>
       <x:c r="G112" s="23" t="n">
-        <x:v>183100</x:v>
+        <x:v>183120</x:v>
       </x:c>
       <x:c r="H112" s="28" t="n">
-        <x:v>-1300</x:v>
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="I112" s="24" t="n">
-        <x:v>-0.007049891540130138</x:v>
+        <x:v>-0.008124796880077945</x:v>
       </x:c>
       <x:c r="J112" s="26" t="n">
         <x:f>ROUND(E112-F112,1)</x:f>
-        <x:v>9600</x:v>
+        <x:v>10340</x:v>
       </x:c>
       <x:c r="K112" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -4483,29 +4483,29 @@
         <x:v>5月21日</x:v>
       </x:c>
       <x:c r="D113" s="23" t="n">
-        <x:v>184100</x:v>
+        <x:v>185220</x:v>
       </x:c>
       <x:c r="E113" s="23" t="n">
-        <x:v>186200</x:v>
+        <x:v>185940</x:v>
       </x:c>
       <x:c r="F113" s="23" t="n">
-        <x:v>177160</x:v>
+        <x:v>177420</x:v>
       </x:c>
       <x:c r="G113" s="23" t="n">
-        <x:v>177600</x:v>
+        <x:v>177420</x:v>
       </x:c>
       <x:c r="H113" s="28" t="n">
-        <x:v>-5500</x:v>
+        <x:v>-5700</x:v>
       </x:c>
       <x:c r="I113" s="24" t="n">
-        <x:v>-0.030038230475150196</x:v>
+        <x:v>-0.031127129750982974</x:v>
       </x:c>
       <x:c r="J113" s="26" t="n">
         <x:f>ROUND(E113-F113,1)</x:f>
-        <x:v>9040</x:v>
+        <x:v>8520</x:v>
       </x:c>
       <x:c r="K113" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -4519,29 +4519,29 @@
         <x:v>5月22日</x:v>
       </x:c>
       <x:c r="D114" s="23" t="n">
-        <x:v>178720</x:v>
+        <x:v>180420</x:v>
       </x:c>
       <x:c r="E114" s="23" t="n">
-        <x:v>185300</x:v>
+        <x:v>185280</x:v>
       </x:c>
       <x:c r="F114" s="23" t="n">
-        <x:v>176500</x:v>
+        <x:v>177760</x:v>
       </x:c>
       <x:c r="G114" s="23" t="n">
-        <x:v>184460</x:v>
+        <x:v>185280</x:v>
       </x:c>
       <x:c r="H114" s="28" t="n">
-        <x:v>6860</x:v>
+        <x:v>7860</x:v>
       </x:c>
       <x:c r="I114" s="24" t="n">
-        <x:v>0.03862612612612604</x:v>
+        <x:v>0.04430165708488332</x:v>
       </x:c>
       <x:c r="J114" s="26" t="n">
         <x:f>ROUND(E114-F114,1)</x:f>
-        <x:v>8800</x:v>
+        <x:v>7520</x:v>
       </x:c>
       <x:c r="K114" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -4555,29 +4555,29 @@
         <x:v>5月25日</x:v>
       </x:c>
       <x:c r="D115" s="23" t="n">
-        <x:v>185500</x:v>
+        <x:v>185380</x:v>
       </x:c>
       <x:c r="E115" s="23" t="n">
-        <x:v>187900</x:v>
+        <x:v>188320</x:v>
       </x:c>
       <x:c r="F115" s="23" t="n">
-        <x:v>179300</x:v>
+        <x:v>179620</x:v>
       </x:c>
       <x:c r="G115" s="23" t="n">
-        <x:v>181200</x:v>
+        <x:v>181380</x:v>
       </x:c>
       <x:c r="H115" s="28" t="n">
-        <x:v>-3260</x:v>
+        <x:v>-3900</x:v>
       </x:c>
       <x:c r="I115" s="24" t="n">
-        <x:v>-0.01767320828363872</x:v>
+        <x:v>-0.021049222797927425</x:v>
       </x:c>
       <x:c r="J115" s="26" t="n">
         <x:f>ROUND(E115-F115,1)</x:f>
-        <x:v>8600</x:v>
+        <x:v>8700</x:v>
       </x:c>
       <x:c r="K115" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -4591,29 +4591,29 @@
         <x:v>5月26日</x:v>
       </x:c>
       <x:c r="D116" s="23" t="n">
-        <x:v>182000</x:v>
+        <x:v>181320</x:v>
       </x:c>
       <x:c r="E116" s="23" t="n">
-        <x:v>182720</x:v>
+        <x:v>182940</x:v>
       </x:c>
       <x:c r="F116" s="23" t="n">
-        <x:v>175260</x:v>
+        <x:v>175820</x:v>
       </x:c>
       <x:c r="G116" s="23" t="n">
-        <x:v>175960</x:v>
+        <x:v>176100</x:v>
       </x:c>
       <x:c r="H116" s="28" t="n">
-        <x:v>-5240</x:v>
+        <x:v>-5280</x:v>
       </x:c>
       <x:c r="I116" s="24" t="n">
-        <x:v>-0.02891832229580571</x:v>
+        <x:v>-0.029110155474693977</x:v>
       </x:c>
       <x:c r="J116" s="26" t="n">
         <x:f>ROUND(E116-F116,1)</x:f>
-        <x:v>7460</x:v>
+        <x:v>7120</x:v>
       </x:c>
       <x:c r="K116" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -4627,29 +4627,29 @@
         <x:v>5月27日</x:v>
       </x:c>
       <x:c r="D117" s="23" t="n">
-        <x:v>175000</x:v>
+        <x:v>176400</x:v>
       </x:c>
       <x:c r="E117" s="23" t="n">
-        <x:v>178920</x:v>
+        <x:v>179020</x:v>
       </x:c>
       <x:c r="F117" s="23" t="n">
-        <x:v>172080</x:v>
+        <x:v>172500</x:v>
       </x:c>
       <x:c r="G117" s="23" t="n">
-        <x:v>173000</x:v>
+        <x:v>173480</x:v>
       </x:c>
       <x:c r="H117" s="28" t="n">
-        <x:v>-2960</x:v>
+        <x:v>-2620</x:v>
       </x:c>
       <x:c r="I117" s="24" t="n">
-        <x:v>-0.01682200500113662</x:v>
+        <x:v>-0.014877910278251028</x:v>
       </x:c>
       <x:c r="J117" s="26" t="n">
         <x:f>ROUND(E117-F117,1)</x:f>
-        <x:v>6840</x:v>
+        <x:v>6520</x:v>
       </x:c>
       <x:c r="K117" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -4663,29 +4663,29 @@
         <x:v>5月28日</x:v>
       </x:c>
       <x:c r="D118" s="23" t="n">
-        <x:v>175000</x:v>
+        <x:v>174700</x:v>
       </x:c>
       <x:c r="E118" s="23" t="n">
-        <x:v>180880</x:v>
+        <x:v>180420</x:v>
       </x:c>
       <x:c r="F118" s="23" t="n">
-        <x:v>174000</x:v>
+        <x:v>174700</x:v>
       </x:c>
       <x:c r="G118" s="23" t="n">
-        <x:v>178860</x:v>
+        <x:v>178940</x:v>
       </x:c>
       <x:c r="H118" s="28" t="n">
-        <x:v>5860</x:v>
+        <x:v>5460</x:v>
       </x:c>
       <x:c r="I118" s="24" t="n">
-        <x:v>0.03387283236994221</x:v>
-      </x:c>
-      <x:c r="J118" s="26" t="n">
+        <x:v>0.0314733686880333</x:v>
+      </x:c>
+      <x:c r="J118" s="23" t="n">
         <x:f>ROUND(E118-F118,1)</x:f>
-        <x:v>6880</x:v>
+        <x:v>5720</x:v>
       </x:c>
       <x:c r="K118" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -4699,29 +4699,29 @@
         <x:v>5月29日</x:v>
       </x:c>
       <x:c r="D119" s="23" t="n">
-        <x:v>180000</x:v>
+        <x:v>177200</x:v>
       </x:c>
       <x:c r="E119" s="23" t="n">
-        <x:v>182500</x:v>
+        <x:v>182440</x:v>
       </x:c>
       <x:c r="F119" s="23" t="n">
-        <x:v>177760</x:v>
+        <x:v>177200</x:v>
       </x:c>
       <x:c r="G119" s="23" t="n">
-        <x:v>179740</x:v>
+        <x:v>178620</x:v>
       </x:c>
       <x:c r="H119" s="28" t="n">
-        <x:v>880</x:v>
+        <x:v>-320</x:v>
       </x:c>
       <x:c r="I119" s="24" t="n">
-        <x:v>0.004920049200491938</x:v>
+        <x:v>-0.0017883089303677435</x:v>
       </x:c>
       <x:c r="J119" s="23" t="n">
         <x:f>ROUND(E119-F119,1)</x:f>
-        <x:v>4740</x:v>
+        <x:v>5240</x:v>
       </x:c>
       <x:c r="K119" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -4740,7 +4740,7 @@
       <x:c r="I120" s="30"/>
       <x:c r="J120" s="32" t="n">
         <x:f>ROUND(SUM(J102:J119),1)</x:f>
-        <x:v>153460</x:v>
+        <x:v>153620</x:v>
       </x:c>
       <x:c r="K120" s="30"/>
     </x:row>
@@ -4758,7 +4758,7 @@
       <x:c r="I121" s="30"/>
       <x:c r="J121" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J102:J119),0),1)</x:f>
-        <x:v>8525.6</x:v>
+        <x:v>8534.4</x:v>
       </x:c>
       <x:c r="K121" s="30"/>
     </x:row>
@@ -4823,29 +4823,29 @@
         <x:v>6月1日</x:v>
       </x:c>
       <x:c r="D125" s="23" t="n">
-        <x:v>181000</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="E125" s="23" t="n">
-        <x:v>182100</x:v>
+        <x:v>182940</x:v>
       </x:c>
       <x:c r="F125" s="23" t="n">
-        <x:v>178000</x:v>
+        <x:v>178620</x:v>
       </x:c>
       <x:c r="G125" s="23" t="n">
-        <x:v>178900</x:v>
+        <x:v>179560</x:v>
       </x:c>
       <x:c r="H125" s="28" t="n">
-        <x:v>-840</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="I125" s="24" t="n">
-        <x:v>-0.00467341715811731</x:v>
+        <x:v>0.005262568581345883</x:v>
       </x:c>
       <x:c r="J125" s="23" t="n">
         <x:f>ROUND(E125-F125,1)</x:f>
-        <x:v>4100</x:v>
+        <x:v>4320</x:v>
       </x:c>
       <x:c r="K125" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -4859,29 +4859,29 @@
         <x:v>6月2日</x:v>
       </x:c>
       <x:c r="D126" s="23" t="n">
-        <x:v>179000</x:v>
+        <x:v>178280</x:v>
       </x:c>
       <x:c r="E126" s="23" t="n">
-        <x:v>179220</x:v>
+        <x:v>178280</x:v>
       </x:c>
       <x:c r="F126" s="23" t="n">
-        <x:v>171100</x:v>
+        <x:v>171800</x:v>
       </x:c>
       <x:c r="G126" s="23" t="n">
-        <x:v>172980</x:v>
+        <x:v>174180</x:v>
       </x:c>
       <x:c r="H126" s="28" t="n">
-        <x:v>-5920</x:v>
+        <x:v>-5380</x:v>
       </x:c>
       <x:c r="I126" s="24" t="n">
-        <x:v>-0.03309111235327</x:v>
+        <x:v>-0.02996212965025613</x:v>
       </x:c>
       <x:c r="J126" s="26" t="n">
         <x:f>ROUND(E126-F126,1)</x:f>
-        <x:v>8120</x:v>
+        <x:v>6480</x:v>
       </x:c>
       <x:c r="K126" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -4895,29 +4895,29 @@
         <x:v>6月3日</x:v>
       </x:c>
       <x:c r="D127" s="23" t="n">
-        <x:v>173100</x:v>
+        <x:v>171820</x:v>
       </x:c>
       <x:c r="E127" s="23" t="n">
-        <x:v>173100</x:v>
+        <x:v>171820</x:v>
       </x:c>
       <x:c r="F127" s="23" t="n">
-        <x:v>166100</x:v>
+        <x:v>167120</x:v>
       </x:c>
       <x:c r="G127" s="23" t="n">
-        <x:v>166760</x:v>
+        <x:v>167360</x:v>
       </x:c>
       <x:c r="H127" s="28" t="n">
-        <x:v>-6220</x:v>
+        <x:v>-6820</x:v>
       </x:c>
       <x:c r="I127" s="24" t="n">
-        <x:v>-0.035957914209735264</x:v>
-      </x:c>
-      <x:c r="J127" s="26" t="n">
+        <x:v>-0.03915489723274779</x:v>
+      </x:c>
+      <x:c r="J127" s="23" t="n">
         <x:f>ROUND(E127-F127,1)</x:f>
-        <x:v>7000</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="K127" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -4931,29 +4931,29 @@
         <x:v>6月4日</x:v>
       </x:c>
       <x:c r="D128" s="23" t="n">
-        <x:v>165660</x:v>
+        <x:v>165280</x:v>
       </x:c>
       <x:c r="E128" s="23" t="n">
-        <x:v>167580</x:v>
+        <x:v>168060</x:v>
       </x:c>
       <x:c r="F128" s="23" t="n">
-        <x:v>157560</x:v>
+        <x:v>158260</x:v>
       </x:c>
       <x:c r="G128" s="23" t="n">
-        <x:v>160740</x:v>
+        <x:v>161260</x:v>
       </x:c>
       <x:c r="H128" s="28" t="n">
-        <x:v>-6020</x:v>
+        <x:v>-6100</x:v>
       </x:c>
       <x:c r="I128" s="24" t="n">
-        <x:v>-0.03609978412089232</x:v>
+        <x:v>-0.03644837476099427</x:v>
       </x:c>
       <x:c r="J128" s="26" t="n">
         <x:f>ROUND(E128-F128,1)</x:f>
-        <x:v>10020</x:v>
+        <x:v>9800</x:v>
       </x:c>
       <x:c r="K128" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -4967,29 +4967,29 @@
         <x:v>6月5日</x:v>
       </x:c>
       <x:c r="D129" s="23" t="n">
-        <x:v>160040</x:v>
+        <x:v>161080</x:v>
       </x:c>
       <x:c r="E129" s="23" t="n">
-        <x:v>165580</x:v>
+        <x:v>166280</x:v>
       </x:c>
       <x:c r="F129" s="23" t="n">
-        <x:v>157180</x:v>
+        <x:v>158140</x:v>
       </x:c>
       <x:c r="G129" s="23" t="n">
-        <x:v>164360</x:v>
+        <x:v>165460</x:v>
       </x:c>
       <x:c r="H129" s="28" t="n">
-        <x:v>3620</x:v>
+        <x:v>4200</x:v>
       </x:c>
       <x:c r="I129" s="24" t="n">
-        <x:v>0.022520841109866963</x:v>
+        <x:v>0.026044896440530874</x:v>
       </x:c>
       <x:c r="J129" s="26" t="n">
         <x:f>ROUND(E129-F129,1)</x:f>
-        <x:v>8400</x:v>
+        <x:v>8140</x:v>
       </x:c>
       <x:c r="K129" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -5003,29 +5003,29 @@
         <x:v>6月8日</x:v>
       </x:c>
       <x:c r="D130" s="23" t="n">
-        <x:v>161500</x:v>
+        <x:v>162800</x:v>
       </x:c>
       <x:c r="E130" s="23" t="n">
-        <x:v>165800</x:v>
+        <x:v>166080</x:v>
       </x:c>
       <x:c r="F130" s="23" t="n">
-        <x:v>160260</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="G130" s="23" t="n">
-        <x:v>163340</x:v>
+        <x:v>163360</x:v>
       </x:c>
       <x:c r="H130" s="28" t="n">
-        <x:v>-1020</x:v>
+        <x:v>-2100</x:v>
       </x:c>
       <x:c r="I130" s="24" t="n">
-        <x:v>-0.006205889510829898</x:v>
+        <x:v>-0.01269188927837539</x:v>
       </x:c>
       <x:c r="J130" s="23" t="n">
         <x:f>ROUND(E130-F130,1)</x:f>
-        <x:v>5540</x:v>
+        <x:v>4800</x:v>
       </x:c>
       <x:c r="K130" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -5039,29 +5039,29 @@
         <x:v>6月9日</x:v>
       </x:c>
       <x:c r="D131" s="23" t="n">
-        <x:v>163600</x:v>
+        <x:v>163360</x:v>
       </x:c>
       <x:c r="E131" s="23" t="n">
-        <x:v>169000</x:v>
+        <x:v>169200</x:v>
       </x:c>
       <x:c r="F131" s="23" t="n">
-        <x:v>161600</x:v>
+        <x:v>162340</x:v>
       </x:c>
       <x:c r="G131" s="23" t="n">
-        <x:v>168460</x:v>
+        <x:v>169140</x:v>
       </x:c>
       <x:c r="H131" s="28" t="n">
-        <x:v>5120</x:v>
+        <x:v>5780</x:v>
       </x:c>
       <x:c r="I131" s="24" t="n">
-        <x:v>0.031345659360842326</x:v>
+        <x:v>0.035381978452497576</x:v>
       </x:c>
       <x:c r="J131" s="26" t="n">
         <x:f>ROUND(E131-F131,1)</x:f>
-        <x:v>7400</x:v>
+        <x:v>6860</x:v>
       </x:c>
       <x:c r="K131" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -5075,29 +5075,29 @@
         <x:v>6月10日</x:v>
       </x:c>
       <x:c r="D132" s="23" t="n">
-        <x:v>167980</x:v>
+        <x:v>167760</x:v>
       </x:c>
       <x:c r="E132" s="23" t="n">
-        <x:v>169300</x:v>
+        <x:v>169360</x:v>
       </x:c>
       <x:c r="F132" s="23" t="n">
-        <x:v>164800</x:v>
+        <x:v>165700</x:v>
       </x:c>
       <x:c r="G132" s="23" t="n">
-        <x:v>167400</x:v>
+        <x:v>168700</x:v>
       </x:c>
       <x:c r="H132" s="28" t="n">
-        <x:v>-1060</x:v>
+        <x:v>-440</x:v>
       </x:c>
       <x:c r="I132" s="24" t="n">
-        <x:v>-0.006292294906802831</x:v>
+        <x:v>-0.0026013952938394036</x:v>
       </x:c>
       <x:c r="J132" s="23" t="n">
         <x:f>ROUND(E132-F132,1)</x:f>
-        <x:v>4500</x:v>
+        <x:v>3660</x:v>
       </x:c>
       <x:c r="K132" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -5111,29 +5111,29 @@
         <x:v>6月11日</x:v>
       </x:c>
       <x:c r="D133" s="23" t="n">
-        <x:v>166780</x:v>
+        <x:v>166080</x:v>
       </x:c>
       <x:c r="E133" s="23" t="n">
-        <x:v>174960</x:v>
+        <x:v>175540</x:v>
       </x:c>
       <x:c r="F133" s="23" t="n">
-        <x:v>166500</x:v>
+        <x:v>166080</x:v>
       </x:c>
       <x:c r="G133" s="23" t="n">
-        <x:v>174600</x:v>
+        <x:v>175060</x:v>
       </x:c>
       <x:c r="H133" s="28" t="n">
-        <x:v>7200</x:v>
+        <x:v>6360</x:v>
       </x:c>
       <x:c r="I133" s="24" t="n">
-        <x:v>0.043010752688172005</x:v>
+        <x:v>0.03770005927682285</x:v>
       </x:c>
       <x:c r="J133" s="26" t="n">
         <x:f>ROUND(E133-F133,1)</x:f>
-        <x:v>8460</x:v>
+        <x:v>9460</x:v>
       </x:c>
       <x:c r="K133" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -5147,29 +5147,29 @@
         <x:v>6月12日</x:v>
       </x:c>
       <x:c r="D134" s="23" t="n">
-        <x:v>176000</x:v>
+        <x:v>177220</x:v>
       </x:c>
       <x:c r="E134" s="23" t="n">
-        <x:v>178740</x:v>
+        <x:v>178860</x:v>
       </x:c>
       <x:c r="F134" s="23" t="n">
-        <x:v>174600</x:v>
+        <x:v>175480</x:v>
       </x:c>
       <x:c r="G134" s="23" t="n">
-        <x:v>175300</x:v>
+        <x:v>175780</x:v>
       </x:c>
       <x:c r="H134" s="28" t="n">
-        <x:v>700</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="I134" s="24" t="n">
-        <x:v>0.004009163802978222</x:v>
+        <x:v>0.004112875585513542</x:v>
       </x:c>
       <x:c r="J134" s="23" t="n">
         <x:f>ROUND(E134-F134,1)</x:f>
-        <x:v>4140</x:v>
+        <x:v>3380</x:v>
       </x:c>
       <x:c r="K134" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -5183,29 +5183,29 @@
         <x:v>6月15日</x:v>
       </x:c>
       <x:c r="D135" s="23" t="n">
-        <x:v>177600</x:v>
+        <x:v>176460</x:v>
       </x:c>
       <x:c r="E135" s="23" t="n">
-        <x:v>177920</x:v>
+        <x:v>178560</x:v>
       </x:c>
       <x:c r="F135" s="23" t="n">
-        <x:v>172320</x:v>
+        <x:v>173300</x:v>
       </x:c>
       <x:c r="G135" s="23" t="n">
-        <x:v>174440</x:v>
+        <x:v>175180</x:v>
       </x:c>
       <x:c r="H135" s="28" t="n">
-        <x:v>-860</x:v>
+        <x:v>-600</x:v>
       </x:c>
       <x:c r="I135" s="24" t="n">
-        <x:v>-0.00490587564175704</x:v>
+        <x:v>-0.0034133576060985105</x:v>
       </x:c>
       <x:c r="J135" s="23" t="n">
         <x:f>ROUND(E135-F135,1)</x:f>
-        <x:v>5600</x:v>
+        <x:v>5260</x:v>
       </x:c>
       <x:c r="K135" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -5219,29 +5219,29 @@
         <x:v>6月16日</x:v>
       </x:c>
       <x:c r="D136" s="23" t="n">
-        <x:v>173800</x:v>
+        <x:v>173940</x:v>
       </x:c>
       <x:c r="E136" s="23" t="n">
-        <x:v>174200</x:v>
+        <x:v>173960</x:v>
       </x:c>
       <x:c r="F136" s="23" t="n">
-        <x:v>168420</x:v>
+        <x:v>169360</x:v>
       </x:c>
       <x:c r="G136" s="23" t="n">
-        <x:v>169980</x:v>
+        <x:v>170500</x:v>
       </x:c>
       <x:c r="H136" s="28" t="n">
-        <x:v>-4460</x:v>
+        <x:v>-4680</x:v>
       </x:c>
       <x:c r="I136" s="24" t="n">
-        <x:v>-0.025567530382939685</x:v>
+        <x:v>-0.02671537846786165</x:v>
       </x:c>
       <x:c r="J136" s="23" t="n">
         <x:f>ROUND(E136-F136,1)</x:f>
-        <x:v>5780</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="K136" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -5255,29 +5255,29 @@
         <x:v>6月17日</x:v>
       </x:c>
       <x:c r="D137" s="23" t="n">
-        <x:v>170100</x:v>
+        <x:v>170460</x:v>
       </x:c>
       <x:c r="E137" s="23" t="n">
-        <x:v>173600</x:v>
+        <x:v>173560</x:v>
       </x:c>
       <x:c r="F137" s="23" t="n">
-        <x:v>169000</x:v>
+        <x:v>170380</x:v>
       </x:c>
       <x:c r="G137" s="23" t="n">
-        <x:v>171300</x:v>
+        <x:v>171640</x:v>
       </x:c>
       <x:c r="H137" s="28" t="n">
-        <x:v>1320</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="I137" s="24" t="n">
-        <x:v>0.007765619484645159</x:v>
+        <x:v>0.006686217008797568</x:v>
       </x:c>
       <x:c r="J137" s="23" t="n">
         <x:f>ROUND(E137-F137,1)</x:f>
-        <x:v>4600</x:v>
+        <x:v>3180</x:v>
       </x:c>
       <x:c r="K137" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -5291,29 +5291,29 @@
         <x:v>6月18日</x:v>
       </x:c>
       <x:c r="D138" s="23" t="n">
-        <x:v>172020</x:v>
+        <x:v>171000</x:v>
       </x:c>
       <x:c r="E138" s="23" t="n">
-        <x:v>172500</x:v>
+        <x:v>172200</x:v>
       </x:c>
       <x:c r="F138" s="23" t="n">
-        <x:v>160100</x:v>
+        <x:v>160560</x:v>
       </x:c>
       <x:c r="G138" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>161400</x:v>
       </x:c>
       <x:c r="H138" s="28" t="n">
-        <x:v>-10800</x:v>
+        <x:v>-10240</x:v>
       </x:c>
       <x:c r="I138" s="24" t="n">
-        <x:v>-0.0630472854640981</x:v>
+        <x:v>-0.0596597529713353</x:v>
       </x:c>
       <x:c r="J138" s="26" t="n">
         <x:f>ROUND(E138-F138,1)</x:f>
-        <x:v>12400</x:v>
+        <x:v>11640</x:v>
       </x:c>
       <x:c r="K138" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -5327,29 +5327,29 @@
         <x:v>6月22日</x:v>
       </x:c>
       <x:c r="D139" s="42" t="n">
-        <x:v>157220</x:v>
+        <x:v>161000</x:v>
       </x:c>
       <x:c r="E139" s="42" t="n">
-        <x:v>161800</x:v>
+        <x:v>162000</x:v>
       </x:c>
       <x:c r="F139" s="42" t="n">
-        <x:v>150860</x:v>
+        <x:v>151640</x:v>
       </x:c>
       <x:c r="G139" s="42" t="n">
-        <x:v>161740</x:v>
+        <x:v>162000</x:v>
       </x:c>
       <x:c r="H139" s="28" t="n">
-        <x:v>1240</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I139" s="43" t="n">
-        <x:v>0.007725856697819333</x:v>
+        <x:v>0.0037174721189590088</x:v>
       </x:c>
       <x:c r="J139" s="26" t="n">
         <x:f>ROUND(E139-F139,1)</x:f>
-        <x:v>10940</x:v>
+        <x:v>10360</x:v>
       </x:c>
       <x:c r="K139" s="41" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -5363,29 +5363,29 @@
         <x:v>6月23日</x:v>
       </x:c>
       <x:c r="D140" s="23" t="n">
-        <x:v>158000</x:v>
+        <x:v>159220</x:v>
       </x:c>
       <x:c r="E140" s="23" t="n">
-        <x:v>159460</x:v>
+        <x:v>159860</x:v>
       </x:c>
       <x:c r="F140" s="23" t="n">
-        <x:v>153700</x:v>
+        <x:v>154720</x:v>
       </x:c>
       <x:c r="G140" s="23" t="n">
-        <x:v>157220</x:v>
+        <x:v>157540</x:v>
       </x:c>
       <x:c r="H140" s="28" t="n">
-        <x:v>-4520</x:v>
+        <x:v>-4460</x:v>
       </x:c>
       <x:c r="I140" s="24" t="n">
-        <x:v>-0.02794608631136397</x:v>
+        <x:v>-0.027530864197530813</x:v>
       </x:c>
       <x:c r="J140" s="23" t="n">
         <x:f>ROUND(E140-F140,1)</x:f>
-        <x:v>5760</x:v>
+        <x:v>5140</x:v>
       </x:c>
       <x:c r="K140" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -5399,29 +5399,29 @@
         <x:v>6月24日</x:v>
       </x:c>
       <x:c r="D141" s="23" t="n">
-        <x:v>156000</x:v>
+        <x:v>155420</x:v>
       </x:c>
       <x:c r="E141" s="23" t="n">
-        <x:v>163940</x:v>
+        <x:v>163880</x:v>
       </x:c>
       <x:c r="F141" s="23" t="n">
-        <x:v>154600</x:v>
+        <x:v>155360</x:v>
       </x:c>
       <x:c r="G141" s="23" t="n">
-        <x:v>162740</x:v>
+        <x:v>163420</x:v>
       </x:c>
       <x:c r="H141" s="28" t="n">
-        <x:v>5520</x:v>
+        <x:v>5880</x:v>
       </x:c>
       <x:c r="I141" s="24" t="n">
-        <x:v>0.03511003689098069</x:v>
+        <x:v>0.03732385425923579</x:v>
       </x:c>
       <x:c r="J141" s="26" t="n">
         <x:f>ROUND(E141-F141,1)</x:f>
-        <x:v>9340</x:v>
+        <x:v>8520</x:v>
       </x:c>
       <x:c r="K141" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -5435,29 +5435,29 @@
         <x:v>6月25日</x:v>
       </x:c>
       <x:c r="D142" s="23" t="n">
-        <x:v>160000</x:v>
+        <x:v>161000</x:v>
       </x:c>
       <x:c r="E142" s="23" t="n">
-        <x:v>161200</x:v>
+        <x:v>161160</x:v>
       </x:c>
       <x:c r="F142" s="23" t="n">
-        <x:v>150320</x:v>
+        <x:v>150820</x:v>
       </x:c>
       <x:c r="G142" s="23" t="n">
-        <x:v>150840</x:v>
+        <x:v>151020</x:v>
       </x:c>
       <x:c r="H142" s="28" t="n">
-        <x:v>-11900</x:v>
+        <x:v>-12400</x:v>
       </x:c>
       <x:c r="I142" s="24" t="n">
-        <x:v>-0.07312277252058497</x:v>
+        <x:v>-0.07587810549504348</x:v>
       </x:c>
       <x:c r="J142" s="26" t="n">
         <x:f>ROUND(E142-F142,1)</x:f>
-        <x:v>10880</x:v>
+        <x:v>10340</x:v>
       </x:c>
       <x:c r="K142" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -5471,29 +5471,29 @@
         <x:v>6月26日</x:v>
       </x:c>
       <x:c r="D143" s="23" t="n">
-        <x:v>149000</x:v>
+        <x:v>149500</x:v>
       </x:c>
       <x:c r="E143" s="23" t="n">
-        <x:v>152880</x:v>
+        <x:v>152800</x:v>
       </x:c>
       <x:c r="F143" s="23" t="n">
-        <x:v>145000</x:v>
+        <x:v>145360</x:v>
       </x:c>
       <x:c r="G143" s="23" t="n">
-        <x:v>150220</x:v>
-      </x:c>
-      <x:c r="H143" s="28" t="n">
-        <x:v>-620</x:v>
+        <x:v>151140</x:v>
+      </x:c>
+      <x:c r="H143" s="23" t="n">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="I143" s="24" t="n">
-        <x:v>-0.004110315566162814</x:v>
+        <x:v>0.0007945967421534306</x:v>
       </x:c>
       <x:c r="J143" s="26" t="n">
         <x:f>ROUND(E143-F143,1)</x:f>
-        <x:v>7880</x:v>
+        <x:v>7440</x:v>
       </x:c>
       <x:c r="K143" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -5507,29 +5507,29 @@
         <x:v>6月29日</x:v>
       </x:c>
       <x:c r="D144" s="23" t="n">
-        <x:v>148000</x:v>
+        <x:v>148420</x:v>
       </x:c>
       <x:c r="E144" s="23" t="n">
-        <x:v>154700</x:v>
+        <x:v>154860</x:v>
       </x:c>
       <x:c r="F144" s="23" t="n">
-        <x:v>145300</x:v>
+        <x:v>146000</x:v>
       </x:c>
       <x:c r="G144" s="23" t="n">
-        <x:v>153920</x:v>
+        <x:v>154120</x:v>
       </x:c>
       <x:c r="H144" s="28" t="n">
-        <x:v>3700</x:v>
+        <x:v>2980</x:v>
       </x:c>
       <x:c r="I144" s="24" t="n">
-        <x:v>0.024630541871921263</x:v>
+        <x:v>0.01971681884345644</x:v>
       </x:c>
       <x:c r="J144" s="26" t="n">
         <x:f>ROUND(E144-F144,1)</x:f>
-        <x:v>9400</x:v>
+        <x:v>8860</x:v>
       </x:c>
       <x:c r="K144" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -5543,29 +5543,29 @@
         <x:v>6月30日</x:v>
       </x:c>
       <x:c r="D145" s="23" t="n">
-        <x:v>148020</x:v>
+        <x:v>148480</x:v>
       </x:c>
       <x:c r="E145" s="23" t="n">
-        <x:v>163900</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="F145" s="23" t="n">
-        <x:v>148020</x:v>
+        <x:v>148480</x:v>
       </x:c>
       <x:c r="G145" s="23" t="n">
-        <x:v>163360</x:v>
+        <x:v>163080</x:v>
       </x:c>
       <x:c r="H145" s="28" t="n">
-        <x:v>9440</x:v>
+        <x:v>8960</x:v>
       </x:c>
       <x:c r="I145" s="24" t="n">
-        <x:v>0.06133056133056125</x:v>
+        <x:v>0.05813651699974054</x:v>
       </x:c>
       <x:c r="J145" s="26" t="n">
         <x:f>ROUND(E145-F145,1)</x:f>
-        <x:v>15880</x:v>
+        <x:v>15320</x:v>
       </x:c>
       <x:c r="K145" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -5584,7 +5584,7 @@
       <x:c r="I146" s="30"/>
       <x:c r="J146" s="32" t="n">
         <x:f>ROUND(SUM(J125:J145),1)</x:f>
-        <x:v>166140</x:v>
+        <x:v>152260</x:v>
       </x:c>
       <x:c r="K146" s="30"/>
     </x:row>
@@ -5602,7 +5602,7 @@
       <x:c r="I147" s="30"/>
       <x:c r="J147" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J125:J145),0),1)</x:f>
-        <x:v>7911.4</x:v>
+        <x:v>7250.5</x:v>
       </x:c>
       <x:c r="K147" s="30"/>
     </x:row>
@@ -5667,29 +5667,29 @@
         <x:v>7月1日</x:v>
       </x:c>
       <x:c r="D151" s="23" t="n">
-        <x:v>164000</x:v>
+        <x:v>164780</x:v>
       </x:c>
       <x:c r="E151" s="23" t="n">
-        <x:v>166500</x:v>
+        <x:v>166200</x:v>
       </x:c>
       <x:c r="F151" s="23" t="n">
-        <x:v>161500</x:v>
+        <x:v>161800</x:v>
       </x:c>
       <x:c r="G151" s="23" t="n">
-        <x:v>164560</x:v>
+        <x:v>164540</x:v>
       </x:c>
       <x:c r="H151" s="28" t="n">
-        <x:v>1200</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="I151" s="24" t="n">
-        <x:v>0.007345739471106727</x:v>
+        <x:v>0.008952661270542173</x:v>
       </x:c>
       <x:c r="J151" s="23" t="n">
         <x:f>ROUND(E151-F151,1)</x:f>
-        <x:v>5000</x:v>
+        <x:v>4400</x:v>
       </x:c>
       <x:c r="K151" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -5703,29 +5703,29 @@
         <x:v>7月2日</x:v>
       </x:c>
       <x:c r="D152" s="23" t="n">
-        <x:v>163500</x:v>
+        <x:v>165220</x:v>
       </x:c>
       <x:c r="E152" s="23" t="n">
-        <x:v>167800</x:v>
+        <x:v>167480</x:v>
       </x:c>
       <x:c r="F152" s="23" t="n">
-        <x:v>162220</x:v>
+        <x:v>162360</x:v>
       </x:c>
       <x:c r="G152" s="23" t="n">
-        <x:v>164040</x:v>
+        <x:v>164180</x:v>
       </x:c>
       <x:c r="H152" s="28" t="n">
-        <x:v>-520</x:v>
+        <x:v>-360</x:v>
       </x:c>
       <x:c r="I152" s="24" t="n">
-        <x:v>-0.003159941662615462</x:v>
+        <x:v>-0.0021879178315302727</x:v>
       </x:c>
       <x:c r="J152" s="23" t="n">
         <x:f>ROUND(E152-F152,1)</x:f>
-        <x:v>5580</x:v>
+        <x:v>5120</x:v>
       </x:c>
       <x:c r="K152" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -5739,29 +5739,29 @@
         <x:v>7月3日</x:v>
       </x:c>
       <x:c r="D153" s="23" t="n">
-        <x:v>170600</x:v>
+        <x:v>166380</x:v>
       </x:c>
       <x:c r="E153" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>172120</x:v>
       </x:c>
       <x:c r="F153" s="23" t="n">
-        <x:v>166300</x:v>
+        <x:v>166380</x:v>
       </x:c>
       <x:c r="G153" s="23" t="n">
-        <x:v>168780</x:v>
+        <x:v>168600</x:v>
       </x:c>
       <x:c r="H153" s="28" t="n">
-        <x:v>4740</x:v>
+        <x:v>4420</x:v>
       </x:c>
       <x:c r="I153" s="24" t="n">
-        <x:v>0.028895391367959045</x:v>
+        <x:v>0.02692167133633827</x:v>
       </x:c>
       <x:c r="J153" s="23" t="n">
         <x:f>ROUND(E153-F153,1)</x:f>
-        <x:v>5700</x:v>
+        <x:v>5740</x:v>
       </x:c>
       <x:c r="K153" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -5775,29 +5775,29 @@
         <x:v>7月6日</x:v>
       </x:c>
       <x:c r="D154" s="23" t="n">
-        <x:v>166980</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="E154" s="23" t="n">
-        <x:v>168720</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="F154" s="23" t="n">
-        <x:v>163280</x:v>
+        <x:v>164200</x:v>
       </x:c>
       <x:c r="G154" s="23" t="n">
-        <x:v>164560</x:v>
+        <x:v>165100</x:v>
       </x:c>
       <x:c r="H154" s="28" t="n">
-        <x:v>-4220</x:v>
+        <x:v>-3500</x:v>
       </x:c>
       <x:c r="I154" s="24" t="n">
-        <x:v>-0.02500296243630762</x:v>
-      </x:c>
-      <x:c r="J154" s="23" t="n">
+        <x:v>-0.020759193357058114</x:v>
+      </x:c>
+      <x:c r="J154" s="26" t="n">
         <x:f>ROUND(E154-F154,1)</x:f>
-        <x:v>5440</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="K154" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -5811,29 +5811,29 @@
         <x:v>7月7日</x:v>
       </x:c>
       <x:c r="D155" s="23" t="n">
-        <x:v>165000</x:v>
+        <x:v>166280</x:v>
       </x:c>
       <x:c r="E155" s="23" t="n">
-        <x:v>166380</x:v>
+        <x:v>166280</x:v>
       </x:c>
       <x:c r="F155" s="23" t="n">
-        <x:v>160660</x:v>
+        <x:v>161300</x:v>
       </x:c>
       <x:c r="G155" s="23" t="n">
-        <x:v>163360</x:v>
+        <x:v>163560</x:v>
       </x:c>
       <x:c r="H155" s="28" t="n">
-        <x:v>-1200</x:v>
+        <x:v>-1540</x:v>
       </x:c>
       <x:c r="I155" s="24" t="n">
-        <x:v>-0.007292173067574126</x:v>
+        <x:v>-0.009327680193821908</x:v>
       </x:c>
       <x:c r="J155" s="23" t="n">
         <x:f>ROUND(E155-F155,1)</x:f>
-        <x:v>5720</x:v>
+        <x:v>4980</x:v>
       </x:c>
       <x:c r="K155" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -5847,29 +5847,29 @@
         <x:v>7月8日</x:v>
       </x:c>
       <x:c r="D156" s="23" t="n">
-        <x:v>164220</x:v>
+        <x:v>164700</x:v>
       </x:c>
       <x:c r="E156" s="23" t="n">
-        <x:v>165200</x:v>
+        <x:v>164700</x:v>
       </x:c>
       <x:c r="F156" s="23" t="n">
-        <x:v>158400</x:v>
+        <x:v>159680</x:v>
       </x:c>
       <x:c r="G156" s="23" t="n">
-        <x:v>158440</x:v>
+        <x:v>159680</x:v>
       </x:c>
       <x:c r="H156" s="28" t="n">
-        <x:v>-4920</x:v>
+        <x:v>-3880</x:v>
       </x:c>
       <x:c r="I156" s="24" t="n">
-        <x:v>-0.030117531831537758</x:v>
-      </x:c>
-      <x:c r="J156" s="26" t="n">
+        <x:v>-0.0237221814624603</x:v>
+      </x:c>
+      <x:c r="J156" s="23" t="n">
         <x:f>ROUND(E156-F156,1)</x:f>
-        <x:v>6800</x:v>
+        <x:v>5020</x:v>
       </x:c>
       <x:c r="K156" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -5883,29 +5883,29 @@
         <x:v>7月9日</x:v>
       </x:c>
       <x:c r="D157" s="23" t="n">
-        <x:v>159600</x:v>
+        <x:v>160540</x:v>
       </x:c>
       <x:c r="E157" s="23" t="n">
-        <x:v>159940</x:v>
+        <x:v>160540</x:v>
       </x:c>
       <x:c r="F157" s="23" t="n">
-        <x:v>151020</x:v>
+        <x:v>151600</x:v>
       </x:c>
       <x:c r="G157" s="23" t="n">
-        <x:v>153020</x:v>
+        <x:v>153140</x:v>
       </x:c>
       <x:c r="H157" s="28" t="n">
-        <x:v>-5420</x:v>
+        <x:v>-6540</x:v>
       </x:c>
       <x:c r="I157" s="24" t="n">
-        <x:v>-0.03420853319868722</x:v>
+        <x:v>-0.04095691382765532</x:v>
       </x:c>
       <x:c r="J157" s="26" t="n">
         <x:f>ROUND(E157-F157,1)</x:f>
-        <x:v>8920</x:v>
+        <x:v>8940</x:v>
       </x:c>
       <x:c r="K157" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -5919,29 +5919,29 @@
         <x:v>7月10日</x:v>
       </x:c>
       <x:c r="D158" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>153180</x:v>
       </x:c>
       <x:c r="E158" s="23" t="n">
-        <x:v>153920</x:v>
+        <x:v>153760</x:v>
       </x:c>
       <x:c r="F158" s="23" t="n">
-        <x:v>150260</x:v>
+        <x:v>150860</x:v>
       </x:c>
       <x:c r="G158" s="23" t="n">
         <x:v>151600</x:v>
       </x:c>
       <x:c r="H158" s="28" t="n">
-        <x:v>-1420</x:v>
+        <x:v>-1540</x:v>
       </x:c>
       <x:c r="I158" s="24" t="n">
-        <x:v>-0.009279832701607593</x:v>
+        <x:v>-0.010056157764137374</x:v>
       </x:c>
       <x:c r="J158" s="23" t="n">
         <x:f>ROUND(E158-F158,1)</x:f>
-        <x:v>3660</x:v>
+        <x:v>2900</x:v>
       </x:c>
       <x:c r="K158" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -5955,29 +5955,29 @@
         <x:v>7月13日</x:v>
       </x:c>
       <x:c r="D159" s="23" t="n">
-        <x:v>150500</x:v>
+        <x:v>150300</x:v>
       </x:c>
       <x:c r="E159" s="23" t="n">
-        <x:v>153580</x:v>
+        <x:v>152960</x:v>
       </x:c>
       <x:c r="F159" s="23" t="n">
-        <x:v>147840</x:v>
+        <x:v>147960</x:v>
       </x:c>
       <x:c r="G159" s="23" t="n">
-        <x:v>152240</x:v>
+        <x:v>152000</x:v>
       </x:c>
       <x:c r="H159" s="28" t="n">
-        <x:v>640</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="I159" s="24" t="n">
-        <x:v>0.004221635883905117</x:v>
+        <x:v>0.0026385224274405594</x:v>
       </x:c>
       <x:c r="J159" s="23" t="n">
         <x:f>ROUND(E159-F159,1)</x:f>
-        <x:v>5740</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="K159" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -5991,29 +5991,29 @@
         <x:v>7月14日</x:v>
       </x:c>
       <x:c r="D160" s="23" t="n">
-        <x:v>152000</x:v>
+        <x:v>152340</x:v>
       </x:c>
       <x:c r="E160" s="23" t="n">
-        <x:v>154000</x:v>
+        <x:v>153520</x:v>
       </x:c>
       <x:c r="F160" s="23" t="n">
-        <x:v>150720</x:v>
+        <x:v>150500</x:v>
       </x:c>
       <x:c r="G160" s="23" t="n">
-        <x:v>153180</x:v>
+        <x:v>152500</x:v>
       </x:c>
       <x:c r="H160" s="28" t="n">
-        <x:v>940</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="I160" s="24" t="n">
-        <x:v>0.006174461376773577</x:v>
+        <x:v>0.00328947368421062</x:v>
       </x:c>
       <x:c r="J160" s="23" t="n">
         <x:f>ROUND(E160-F160,1)</x:f>
-        <x:v>3280</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="K160" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -6027,29 +6027,29 @@
         <x:v>7月15日</x:v>
       </x:c>
       <x:c r="D161" s="23" t="n">
-        <x:v>153880</x:v>
+        <x:v>154320</x:v>
       </x:c>
       <x:c r="E161" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>155660</x:v>
       </x:c>
       <x:c r="F161" s="23" t="n">
-        <x:v>147540</x:v>
+        <x:v>147400</x:v>
       </x:c>
       <x:c r="G161" s="23" t="n">
-        <x:v>149240</x:v>
+        <x:v>148960</x:v>
       </x:c>
       <x:c r="H161" s="28" t="n">
-        <x:v>-3940</x:v>
+        <x:v>-3540</x:v>
       </x:c>
       <x:c r="I161" s="24" t="n">
-        <x:v>-0.025721373547460513</x:v>
+        <x:v>-0.023213114754098374</x:v>
       </x:c>
       <x:c r="J161" s="26" t="n">
         <x:f>ROUND(E161-F161,1)</x:f>
-        <x:v>8960</x:v>
+        <x:v>8260</x:v>
       </x:c>
       <x:c r="K161" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -6063,29 +6063,29 @@
         <x:v>7月16日</x:v>
       </x:c>
       <x:c r="D162" s="23" t="n">
-        <x:v>148980</x:v>
+        <x:v>148220</x:v>
       </x:c>
       <x:c r="E162" s="23" t="n">
-        <x:v>153340</x:v>
+        <x:v>152540</x:v>
       </x:c>
       <x:c r="F162" s="23" t="n">
-        <x:v>145860</x:v>
+        <x:v>145460</x:v>
       </x:c>
       <x:c r="G162" s="23" t="n">
-        <x:v>151660</x:v>
+        <x:v>151080</x:v>
       </x:c>
       <x:c r="H162" s="28" t="n">
-        <x:v>2420</x:v>
+        <x:v>2120</x:v>
       </x:c>
       <x:c r="I162" s="24" t="n">
-        <x:v>0.016215491825247952</x:v>
+        <x:v>0.01423200859291085</x:v>
       </x:c>
       <x:c r="J162" s="26" t="n">
         <x:f>ROUND(E162-F162,1)</x:f>
-        <x:v>7480</x:v>
+        <x:v>7080</x:v>
       </x:c>
       <x:c r="K162" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -6099,29 +6099,29 @@
         <x:v>7月17日</x:v>
       </x:c>
       <x:c r="D163" s="42" t="n">
-        <x:v>153100</x:v>
+        <x:v>153180</x:v>
       </x:c>
       <x:c r="E163" s="42" t="n">
-        <x:v>155300</x:v>
+        <x:v>154600</x:v>
       </x:c>
       <x:c r="F163" s="42" t="n">
-        <x:v>149000</x:v>
+        <x:v>148720</x:v>
       </x:c>
       <x:c r="G163" s="42" t="n">
-        <x:v>150140</x:v>
+        <x:v>149740</x:v>
       </x:c>
       <x:c r="H163" s="28" t="n">
-        <x:v>-1520</x:v>
+        <x:v>-1340</x:v>
       </x:c>
       <x:c r="I163" s="43" t="n">
-        <x:v>-0.010022418567849134</x:v>
-      </x:c>
-      <x:c r="J163" s="26" t="n">
+        <x:v>-0.008869473126820182</x:v>
+      </x:c>
+      <x:c r="J163" s="42" t="n">
         <x:f>ROUND(E163-F163,1)</x:f>
-        <x:v>6300</x:v>
+        <x:v>5880</x:v>
       </x:c>
       <x:c r="K163" s="41" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -6135,29 +6135,29 @@
         <x:v>7月20日</x:v>
       </x:c>
       <x:c r="D164" s="23" t="n">
-        <x:v>151500</x:v>
+        <x:v>152520</x:v>
       </x:c>
       <x:c r="E164" s="23" t="n">
-        <x:v>154800</x:v>
+        <x:v>153880</x:v>
       </x:c>
       <x:c r="F164" s="23" t="n">
-        <x:v>141400</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="G164" s="23" t="n">
-        <x:v>143900</x:v>
+        <x:v>140980</x:v>
       </x:c>
       <x:c r="H164" s="28" t="n">
-        <x:v>-6240</x:v>
+        <x:v>-8760</x:v>
       </x:c>
       <x:c r="I164" s="24" t="n">
-        <x:v>-0.041561209537764765</x:v>
+        <x:v>-0.0585014024308802</x:v>
       </x:c>
       <x:c r="J164" s="26" t="n">
         <x:f>ROUND(E164-F164,1)</x:f>
-        <x:v>13400</x:v>
+        <x:v>14880</x:v>
       </x:c>
       <x:c r="K164" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -6171,29 +6171,29 @@
         <x:v>7月21日</x:v>
       </x:c>
       <x:c r="D165" s="23" t="n">
-        <x:v>143800</x:v>
+        <x:v>140940</x:v>
       </x:c>
       <x:c r="E165" s="23" t="n">
-        <x:v>144300</x:v>
+        <x:v>141340</x:v>
       </x:c>
       <x:c r="F165" s="23" t="n">
-        <x:v>136800</x:v>
+        <x:v>135040</x:v>
       </x:c>
       <x:c r="G165" s="23" t="n">
-        <x:v>141620</x:v>
+        <x:v>140120</x:v>
       </x:c>
       <x:c r="H165" s="28" t="n">
-        <x:v>-2280</x:v>
+        <x:v>-860</x:v>
       </x:c>
       <x:c r="I165" s="24" t="n">
-        <x:v>-0.01584433634468385</x:v>
+        <x:v>-0.0061001560505036245</x:v>
       </x:c>
       <x:c r="J165" s="26" t="n">
         <x:f>ROUND(E165-F165,1)</x:f>
-        <x:v>7500</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="K165" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -6207,29 +6207,29 @@
         <x:v>7月22日</x:v>
       </x:c>
       <x:c r="D166" s="23" t="n">
-        <x:v>142980</x:v>
+        <x:v>141340</x:v>
       </x:c>
       <x:c r="E166" s="23" t="n">
-        <x:v>145200</x:v>
+        <x:v>143120</x:v>
       </x:c>
       <x:c r="F166" s="23" t="n">
-        <x:v>137220</x:v>
+        <x:v>135460</x:v>
       </x:c>
       <x:c r="G166" s="23" t="n">
-        <x:v>143300</x:v>
+        <x:v>141580</x:v>
       </x:c>
       <x:c r="H166" s="28" t="n">
-        <x:v>1680</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="I166" s="24" t="n">
-        <x:v>0.011862731252648029</x:v>
+        <x:v>0.010419640308307221</x:v>
       </x:c>
       <x:c r="J166" s="26" t="n">
         <x:f>ROUND(E166-F166,1)</x:f>
-        <x:v>7980</x:v>
+        <x:v>7660</x:v>
       </x:c>
       <x:c r="K166" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -6243,29 +6243,29 @@
         <x:v>7月23日</x:v>
       </x:c>
       <x:c r="D167" s="23" t="n">
-        <x:v>143380</x:v>
+        <x:v>141980</x:v>
       </x:c>
       <x:c r="E167" s="23" t="n">
-        <x:v>148480</x:v>
+        <x:v>146620</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>142240</x:v>
+        <x:v>140740</x:v>
       </x:c>
       <x:c r="G167" s="23" t="n">
-        <x:v>145000</x:v>
+        <x:v>142800</x:v>
       </x:c>
       <x:c r="H167" s="28" t="n">
-        <x:v>1700</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="I167" s="24" t="n">
-        <x:v>0.011863224005582707</x:v>
-      </x:c>
-      <x:c r="J167" s="26" t="n">
+        <x:v>0.008617036304562786</x:v>
+      </x:c>
+      <x:c r="J167" s="23" t="n">
         <x:f>ROUND(E167-F167,1)</x:f>
-        <x:v>6240</x:v>
+        <x:v>5880</x:v>
       </x:c>
       <x:c r="K167" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -6279,29 +6279,29 @@
         <x:v>7月24日</x:v>
       </x:c>
       <x:c r="D168" s="23" t="n">
-        <x:v>144200</x:v>
+        <x:v>142360</x:v>
       </x:c>
       <x:c r="E168" s="23" t="n">
-        <x:v>145800</x:v>
+        <x:v>144000</x:v>
       </x:c>
       <x:c r="F168" s="23" t="n">
-        <x:v>141320</x:v>
+        <x:v>139760</x:v>
       </x:c>
       <x:c r="G168" s="23" t="n">
-        <x:v>144280</x:v>
-      </x:c>
-      <x:c r="H168" s="28" t="n">
-        <x:v>-720</x:v>
+        <x:v>142920</x:v>
+      </x:c>
+      <x:c r="H168" s="23" t="n">
+        <x:v>120</x:v>
       </x:c>
       <x:c r="I168" s="24" t="n">
-        <x:v>-0.00496551724137928</x:v>
+        <x:v>0.0008403361344537785</x:v>
       </x:c>
       <x:c r="J168" s="23" t="n">
         <x:f>ROUND(E168-F168,1)</x:f>
-        <x:v>4480</x:v>
+        <x:v>4240</x:v>
       </x:c>
       <x:c r="K168" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -6315,29 +6315,29 @@
         <x:v>7月27日</x:v>
       </x:c>
       <x:c r="D169" s="23" t="n">
-        <x:v>145780</x:v>
+        <x:v>144340</x:v>
       </x:c>
       <x:c r="E169" s="23" t="n">
-        <x:v>148220</x:v>
+        <x:v>146400</x:v>
       </x:c>
       <x:c r="F169" s="23" t="n">
-        <x:v>143260</x:v>
+        <x:v>142600</x:v>
       </x:c>
       <x:c r="G169" s="23" t="n">
-        <x:v>147220</x:v>
+        <x:v>145600</x:v>
       </x:c>
       <x:c r="H169" s="28" t="n">
-        <x:v>2940</x:v>
+        <x:v>2680</x:v>
       </x:c>
       <x:c r="I169" s="24" t="n">
-        <x:v>0.020377044635430996</x:v>
+        <x:v>0.01875174923033862</x:v>
       </x:c>
       <x:c r="J169" s="23" t="n">
         <x:f>ROUND(E169-F169,1)</x:f>
-        <x:v>4960</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="K169" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -6351,29 +6351,29 @@
         <x:v>7月28日</x:v>
       </x:c>
       <x:c r="D170" s="23" t="n">
-        <x:v>146560</x:v>
+        <x:v>145320</x:v>
       </x:c>
       <x:c r="E170" s="23" t="n">
-        <x:v>147680</x:v>
+        <x:v>146400</x:v>
       </x:c>
       <x:c r="F170" s="23" t="n">
-        <x:v>142000</x:v>
+        <x:v>141280</x:v>
       </x:c>
       <x:c r="G170" s="23" t="n">
-        <x:v>143480</x:v>
+        <x:v>142500</x:v>
       </x:c>
       <x:c r="H170" s="28" t="n">
-        <x:v>-3740</x:v>
+        <x:v>-3100</x:v>
       </x:c>
       <x:c r="I170" s="24" t="n">
-        <x:v>-0.025404157043879882</x:v>
+        <x:v>-0.021291208791208827</x:v>
       </x:c>
       <x:c r="J170" s="23" t="n">
         <x:f>ROUND(E170-F170,1)</x:f>
-        <x:v>5680</x:v>
+        <x:v>5120</x:v>
       </x:c>
       <x:c r="K170" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -6387,29 +6387,29 @@
         <x:v>7月29日</x:v>
       </x:c>
       <x:c r="D171" s="23" t="n">
-        <x:v>143480</x:v>
+        <x:v>142480</x:v>
       </x:c>
       <x:c r="E171" s="23" t="n">
-        <x:v>149400</x:v>
+        <x:v>148600</x:v>
       </x:c>
       <x:c r="F171" s="23" t="n">
-        <x:v>142500</x:v>
+        <x:v>141800</x:v>
       </x:c>
       <x:c r="G171" s="23" t="n">
-        <x:v>147900</x:v>
+        <x:v>147220</x:v>
       </x:c>
       <x:c r="H171" s="28" t="n">
-        <x:v>4420</x:v>
+        <x:v>4720</x:v>
       </x:c>
       <x:c r="I171" s="24" t="n">
-        <x:v>0.0308056872037914</x:v>
+        <x:v>0.033122807017543776</x:v>
       </x:c>
       <x:c r="J171" s="26" t="n">
         <x:f>ROUND(E171-F171,1)</x:f>
-        <x:v>6900</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="K171" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -6423,29 +6423,29 @@
         <x:v>7月30日</x:v>
       </x:c>
       <x:c r="D172" s="23" t="n">
-        <x:v>147980</x:v>
+        <x:v>147720</x:v>
       </x:c>
       <x:c r="E172" s="23" t="n">
-        <x:v>148080</x:v>
+        <x:v>147720</x:v>
       </x:c>
       <x:c r="F172" s="23" t="n">
-        <x:v>140620</x:v>
+        <x:v>140480</x:v>
       </x:c>
       <x:c r="G172" s="23" t="n">
-        <x:v>141060</x:v>
+        <x:v>140480</x:v>
       </x:c>
       <x:c r="H172" s="28" t="n">
-        <x:v>-6840</x:v>
+        <x:v>-6740</x:v>
       </x:c>
       <x:c r="I172" s="24" t="n">
-        <x:v>-0.04624746450304262</x:v>
+        <x:v>-0.04578182312185841</x:v>
       </x:c>
       <x:c r="J172" s="26" t="n">
         <x:f>ROUND(E172-F172,1)</x:f>
-        <x:v>7460</x:v>
+        <x:v>7240</x:v>
       </x:c>
       <x:c r="K172" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -6459,29 +6459,29 @@
         <x:v>7月31日</x:v>
       </x:c>
       <x:c r="D173" s="23" t="n">
-        <x:v>143880</x:v>
+        <x:v>143200</x:v>
       </x:c>
       <x:c r="E173" s="23" t="n">
-        <x:v>144400</x:v>
+        <x:v>143800</x:v>
       </x:c>
       <x:c r="F173" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="G173" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="H173" s="28" t="n">
-        <x:v>-3300</x:v>
+        <x:v>-3480</x:v>
       </x:c>
       <x:c r="I173" s="24" t="n">
-        <x:v>-0.023394300297745585</x:v>
+        <x:v>-0.024772209567198167</x:v>
       </x:c>
       <x:c r="J173" s="26" t="n">
         <x:f>ROUND(E173-F173,1)</x:f>
-        <x:v>6640</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="K173" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -6500,7 +6500,7 @@
       <x:c r="I174" s="30"/>
       <x:c r="J174" s="32" t="n">
         <x:f>ROUND(SUM(J151:J173),1)</x:f>
-        <x:v>149820</x:v>
+        <x:v>145760</x:v>
       </x:c>
       <x:c r="K174" s="30"/>
     </x:row>
@@ -6518,7 +6518,7 @@
       <x:c r="I175" s="30"/>
       <x:c r="J175" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J151:J173),0),1)</x:f>
-        <x:v>6513.9</x:v>
+        <x:v>6337.4</x:v>
       </x:c>
       <x:c r="K175" s="30"/>
     </x:row>
@@ -6583,29 +6583,29 @@
         <x:v>8月3日</x:v>
       </x:c>
       <x:c r="D179" s="23" t="n">
-        <x:v>137500</x:v>
+        <x:v>137200</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
-        <x:v>140840</x:v>
+        <x:v>140020</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>135560</x:v>
+        <x:v>135040</x:v>
       </x:c>
       <x:c r="G179" s="23" t="n">
-        <x:v>138900</x:v>
+        <x:v>138100</x:v>
       </x:c>
       <x:c r="H179" s="28" t="n">
-        <x:v>1140</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="I179" s="24" t="n">
-        <x:v>0.008275261324041772</x:v>
+        <x:v>0.008029197080291928</x:v>
       </x:c>
       <x:c r="J179" s="23" t="n">
         <x:f>ROUND(E179-F179,1)</x:f>
-        <x:v>5280</x:v>
+        <x:v>4980</x:v>
       </x:c>
       <x:c r="K179" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -6619,29 +6619,29 @@
         <x:v>8月4日</x:v>
       </x:c>
       <x:c r="D180" s="23" t="n">
-        <x:v>138780</x:v>
+        <x:v>138080</x:v>
       </x:c>
       <x:c r="E180" s="23" t="n">
-        <x:v>141360</x:v>
+        <x:v>140800</x:v>
       </x:c>
       <x:c r="F180" s="23" t="n">
-        <x:v>137340</x:v>
+        <x:v>136740</x:v>
       </x:c>
       <x:c r="G180" s="23" t="n">
-        <x:v>139380</x:v>
+        <x:v>138940</x:v>
       </x:c>
       <x:c r="H180" s="28" t="n">
-        <x:v>480</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="I180" s="24" t="n">
-        <x:v>0.003455723542116651</x:v>
+        <x:v>0.006082548877624827</x:v>
       </x:c>
       <x:c r="J180" s="23" t="n">
         <x:f>ROUND(E180-F180,1)</x:f>
-        <x:v>4020</x:v>
+        <x:v>4060</x:v>
       </x:c>
       <x:c r="K180" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -6655,29 +6655,29 @@
         <x:v>8月5日</x:v>
       </x:c>
       <x:c r="D181" s="23" t="n">
-        <x:v>139720</x:v>
+        <x:v>138940</x:v>
       </x:c>
       <x:c r="E181" s="23" t="n">
-        <x:v>144300</x:v>
+        <x:v>143600</x:v>
       </x:c>
       <x:c r="F181" s="23" t="n">
-        <x:v>138320</x:v>
+        <x:v>138100</x:v>
       </x:c>
       <x:c r="G181" s="23" t="n">
-        <x:v>143220</x:v>
+        <x:v>142940</x:v>
       </x:c>
       <x:c r="H181" s="28" t="n">
-        <x:v>3840</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="I181" s="24" t="n">
-        <x:v>0.027550581145070918</x:v>
+        <x:v>0.02878940549877651</x:v>
       </x:c>
       <x:c r="J181" s="23" t="n">
         <x:f>ROUND(E181-F181,1)</x:f>
-        <x:v>5980</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="K181" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -6691,29 +6691,29 @@
         <x:v>8月6日</x:v>
       </x:c>
       <x:c r="D182" s="23" t="n">
+        <x:v>142940</x:v>
+      </x:c>
+      <x:c r="E182" s="23" t="n">
         <x:v>143200</x:v>
       </x:c>
-      <x:c r="E182" s="23" t="n">
-        <x:v>143860</x:v>
-      </x:c>
       <x:c r="F182" s="23" t="n">
-        <x:v>139240</x:v>
+        <x:v>138900</x:v>
       </x:c>
       <x:c r="G182" s="23" t="n">
-        <x:v>141460</x:v>
+        <x:v>140580</x:v>
       </x:c>
       <x:c r="H182" s="28" t="n">
-        <x:v>-1760</x:v>
+        <x:v>-2360</x:v>
       </x:c>
       <x:c r="I182" s="24" t="n">
-        <x:v>-0.01228878648233489</x:v>
+        <x:v>-0.016510423954106623</x:v>
       </x:c>
       <x:c r="J182" s="23" t="n">
         <x:f>ROUND(E182-F182,1)</x:f>
-        <x:v>4620</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="K182" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -6727,29 +6727,29 @@
         <x:v>8月7日</x:v>
       </x:c>
       <x:c r="D183" s="23" t="n">
-        <x:v>142920</x:v>
+        <x:v>140600</x:v>
       </x:c>
       <x:c r="E183" s="23" t="n">
-        <x:v>144800</x:v>
+        <x:v>144100</x:v>
       </x:c>
       <x:c r="F183" s="23" t="n">
-        <x:v>139600</x:v>
+        <x:v>139020</x:v>
       </x:c>
       <x:c r="G183" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="H183" s="28" t="n">
-        <x:v>-1460</x:v>
+        <x:v>-1260</x:v>
       </x:c>
       <x:c r="I183" s="24" t="n">
-        <x:v>-0.01032093878128093</x:v>
+        <x:v>-0.008962868117797673</x:v>
       </x:c>
       <x:c r="J183" s="23" t="n">
         <x:f>ROUND(E183-F183,1)</x:f>
-        <x:v>5200</x:v>
+        <x:v>5080</x:v>
       </x:c>
       <x:c r="K183" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -6763,29 +6763,29 @@
         <x:v>8月10日</x:v>
       </x:c>
       <x:c r="D184" s="23" t="n">
-        <x:v>140500</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="E184" s="23" t="n">
-        <x:v>146380</x:v>
+        <x:v>145640</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
-        <x:v>139280</x:v>
+        <x:v>139300</x:v>
       </x:c>
       <x:c r="G184" s="23" t="n">
-        <x:v>146360</x:v>
+        <x:v>145620</x:v>
       </x:c>
       <x:c r="H184" s="28" t="n">
-        <x:v>6360</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="I184" s="24" t="n">
-        <x:v>0.045428571428571374</x:v>
+        <x:v>0.04521963824289399</x:v>
       </x:c>
       <x:c r="J184" s="26" t="n">
         <x:f>ROUND(E184-F184,1)</x:f>
-        <x:v>7100</x:v>
+        <x:v>6340</x:v>
       </x:c>
       <x:c r="K184" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -6799,29 +6799,29 @@
         <x:v>8月11日</x:v>
       </x:c>
       <x:c r="D185" s="23" t="n">
-        <x:v>146500</x:v>
+        <x:v>145980</x:v>
       </x:c>
       <x:c r="E185" s="23" t="n">
-        <x:v>146680</x:v>
+        <x:v>146120</x:v>
       </x:c>
       <x:c r="F185" s="23" t="n">
         <x:v>143500</x:v>
       </x:c>
       <x:c r="G185" s="23" t="n">
-        <x:v>145860</x:v>
+        <x:v>145440</x:v>
       </x:c>
       <x:c r="H185" s="28" t="n">
-        <x:v>-500</x:v>
+        <x:v>-180</x:v>
       </x:c>
       <x:c r="I185" s="24" t="n">
-        <x:v>-0.0034162339437004974</x:v>
+        <x:v>-0.0012360939431397266</x:v>
       </x:c>
       <x:c r="J185" s="23" t="n">
         <x:f>ROUND(E185-F185,1)</x:f>
-        <x:v>3180</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="K185" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -6835,29 +6835,29 @@
         <x:v>8月12日</x:v>
       </x:c>
       <x:c r="D186" s="23" t="n">
-        <x:v>146200</x:v>
+        <x:v>144400</x:v>
       </x:c>
       <x:c r="E186" s="23" t="n">
-        <x:v>150880</x:v>
+        <x:v>150540</x:v>
       </x:c>
       <x:c r="F186" s="23" t="n">
-        <x:v>146060</x:v>
+        <x:v>144400</x:v>
       </x:c>
       <x:c r="G186" s="23" t="n">
-        <x:v>149700</x:v>
+        <x:v>149000</x:v>
       </x:c>
       <x:c r="H186" s="28" t="n">
-        <x:v>3840</x:v>
+        <x:v>3560</x:v>
       </x:c>
       <x:c r="I186" s="24" t="n">
-        <x:v>0.026326614561908768</x:v>
-      </x:c>
-      <x:c r="J186" s="23" t="n">
+        <x:v>0.02447744774477445</x:v>
+      </x:c>
+      <x:c r="J186" s="26" t="n">
         <x:f>ROUND(E186-F186,1)</x:f>
-        <x:v>4820</x:v>
+        <x:v>6140</x:v>
       </x:c>
       <x:c r="K186" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -6871,29 +6871,29 @@
         <x:v>8月13日</x:v>
       </x:c>
       <x:c r="D187" s="23" t="n">
-        <x:v>150100</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="E187" s="23" t="n">
-        <x:v>152440</x:v>
+        <x:v>152140</x:v>
       </x:c>
       <x:c r="F187" s="23" t="n">
-        <x:v>147100</x:v>
+        <x:v>147000</x:v>
       </x:c>
       <x:c r="G187" s="23" t="n">
-        <x:v>151420</x:v>
+        <x:v>151340</x:v>
       </x:c>
       <x:c r="H187" s="28" t="n">
-        <x:v>1720</x:v>
+        <x:v>2340</x:v>
       </x:c>
       <x:c r="I187" s="24" t="n">
-        <x:v>0.011489645958583816</x:v>
+        <x:v>0.015704697986577143</x:v>
       </x:c>
       <x:c r="J187" s="23" t="n">
         <x:f>ROUND(E187-F187,1)</x:f>
-        <x:v>5340</x:v>
+        <x:v>5140</x:v>
       </x:c>
       <x:c r="K187" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -6907,29 +6907,29 @@
         <x:v>8月14日</x:v>
       </x:c>
       <x:c r="D188" s="23" t="n">
-        <x:v>149700</x:v>
+        <x:v>150100</x:v>
       </x:c>
       <x:c r="E188" s="23" t="n">
-        <x:v>154500</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="F188" s="23" t="n">
-        <x:v>149700</x:v>
+        <x:v>150100</x:v>
       </x:c>
       <x:c r="G188" s="23" t="n">
-        <x:v>153940</x:v>
+        <x:v>153980</x:v>
       </x:c>
       <x:c r="H188" s="28" t="n">
-        <x:v>2520</x:v>
+        <x:v>2640</x:v>
       </x:c>
       <x:c r="I188" s="24" t="n">
-        <x:v>0.016642451459516483</x:v>
+        <x:v>0.01744416545526639</x:v>
       </x:c>
       <x:c r="J188" s="23" t="n">
         <x:f>ROUND(E188-F188,1)</x:f>
-        <x:v>4800</x:v>
+        <x:v>4460</x:v>
       </x:c>
       <x:c r="K188" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -6943,29 +6943,29 @@
         <x:v>8月17日</x:v>
       </x:c>
       <x:c r="D189" s="23" t="n">
-        <x:v>154300</x:v>
+        <x:v>152940</x:v>
       </x:c>
       <x:c r="E189" s="23" t="n">
-        <x:v>155220</x:v>
+        <x:v>155480</x:v>
       </x:c>
       <x:c r="F189" s="23" t="n">
-        <x:v>150520</x:v>
+        <x:v>150500</x:v>
       </x:c>
       <x:c r="G189" s="23" t="n">
-        <x:v>152860</x:v>
+        <x:v>152340</x:v>
       </x:c>
       <x:c r="H189" s="28" t="n">
-        <x:v>-1080</x:v>
+        <x:v>-1640</x:v>
       </x:c>
       <x:c r="I189" s="24" t="n">
-        <x:v>-0.007015720410549542</x:v>
+        <x:v>-0.010650733861540473</x:v>
       </x:c>
       <x:c r="J189" s="23" t="n">
         <x:f>ROUND(E189-F189,1)</x:f>
-        <x:v>4700</x:v>
+        <x:v>4980</x:v>
       </x:c>
       <x:c r="K189" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -6979,29 +6979,29 @@
         <x:v>8月18日</x:v>
       </x:c>
       <x:c r="D190" s="23" t="n">
-        <x:v>153500</x:v>
+        <x:v>152460</x:v>
       </x:c>
       <x:c r="E190" s="23" t="n">
-        <x:v>155980</x:v>
+        <x:v>156260</x:v>
       </x:c>
       <x:c r="F190" s="23" t="n">
-        <x:v>151520</x:v>
+        <x:v>151340</x:v>
       </x:c>
       <x:c r="G190" s="23" t="n">
-        <x:v>153940</x:v>
+        <x:v>153980</x:v>
       </x:c>
       <x:c r="H190" s="28" t="n">
-        <x:v>1080</x:v>
+        <x:v>1640</x:v>
       </x:c>
       <x:c r="I190" s="24" t="n">
-        <x:v>0.007065288499280342</x:v>
+        <x:v>0.010765393199422268</x:v>
       </x:c>
       <x:c r="J190" s="23" t="n">
         <x:f>ROUND(E190-F190,1)</x:f>
-        <x:v>4460</x:v>
+        <x:v>4920</x:v>
       </x:c>
       <x:c r="K190" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -7015,29 +7015,29 @@
         <x:v>8月19日</x:v>
       </x:c>
       <x:c r="D191" s="23" t="n">
-        <x:v>152260</x:v>
+        <x:v>152640</x:v>
       </x:c>
       <x:c r="E191" s="23" t="n">
-        <x:v>153220</x:v>
+        <x:v>153280</x:v>
       </x:c>
       <x:c r="F191" s="23" t="n">
-        <x:v>148400</x:v>
+        <x:v>148700</x:v>
       </x:c>
       <x:c r="G191" s="23" t="n">
-        <x:v>149480</x:v>
+        <x:v>149740</x:v>
       </x:c>
       <x:c r="H191" s="28" t="n">
-        <x:v>-4460</x:v>
+        <x:v>-4240</x:v>
       </x:c>
       <x:c r="I191" s="24" t="n">
-        <x:v>-0.028972326880602806</x:v>
+        <x:v>-0.027536043642031438</x:v>
       </x:c>
       <x:c r="J191" s="23" t="n">
         <x:f>ROUND(E191-F191,1)</x:f>
-        <x:v>4820</x:v>
+        <x:v>4580</x:v>
       </x:c>
       <x:c r="K191" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -7051,29 +7051,29 @@
         <x:v>8月20日</x:v>
       </x:c>
       <x:c r="D192" s="23" t="n">
-        <x:v>150800</x:v>
+        <x:v>151740</x:v>
       </x:c>
       <x:c r="E192" s="23" t="n">
-        <x:v>152600</x:v>
+        <x:v>152900</x:v>
       </x:c>
       <x:c r="F192" s="23" t="n">
-        <x:v>149800</x:v>
+        <x:v>149960</x:v>
       </x:c>
       <x:c r="G192" s="23" t="n">
-        <x:v>151500</x:v>
+        <x:v>151460</x:v>
       </x:c>
       <x:c r="H192" s="28" t="n">
-        <x:v>2020</x:v>
+        <x:v>1720</x:v>
       </x:c>
       <x:c r="I192" s="24" t="n">
-        <x:v>0.013513513513513598</x:v>
+        <x:v>0.011486576733003906</x:v>
       </x:c>
       <x:c r="J192" s="23" t="n">
         <x:f>ROUND(E192-F192,1)</x:f>
-        <x:v>2800</x:v>
+        <x:v>2940</x:v>
       </x:c>
       <x:c r="K192" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -7087,29 +7087,29 @@
         <x:v>8月21日</x:v>
       </x:c>
       <x:c r="D193" s="42" t="n">
-        <x:v>151500</x:v>
+        <x:v>151120</x:v>
       </x:c>
       <x:c r="E193" s="42" t="n">
-        <x:v>157000</x:v>
+        <x:v>157400</x:v>
       </x:c>
       <x:c r="F193" s="42" t="n">
-        <x:v>150020</x:v>
+        <x:v>150260</x:v>
       </x:c>
       <x:c r="G193" s="42" t="n">
-        <x:v>156140</x:v>
+        <x:v>156380</x:v>
       </x:c>
       <x:c r="H193" s="28" t="n">
-        <x:v>4640</x:v>
+        <x:v>4920</x:v>
       </x:c>
       <x:c r="I193" s="43" t="n">
-        <x:v>0.03062706270627058</x:v>
+        <x:v>0.0324838241119767</x:v>
       </x:c>
       <x:c r="J193" s="26" t="n">
         <x:f>ROUND(E193-F193,1)</x:f>
-        <x:v>6980</x:v>
+        <x:v>7140</x:v>
       </x:c>
       <x:c r="K193" s="41" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -7123,29 +7123,29 @@
         <x:v>8月24日</x:v>
       </x:c>
       <x:c r="D194" s="23" t="n">
-        <x:v>158500</x:v>
+        <x:v>158800</x:v>
       </x:c>
       <x:c r="E194" s="23" t="n">
-        <x:v>160000</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="F194" s="23" t="n">
-        <x:v>154280</x:v>
+        <x:v>154340</x:v>
       </x:c>
       <x:c r="G194" s="23" t="n">
-        <x:v>157000</x:v>
+        <x:v>157320</x:v>
       </x:c>
       <x:c r="H194" s="28" t="n">
-        <x:v>860</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="I194" s="24" t="n">
-        <x:v>0.005507877545792184</x:v>
-      </x:c>
-      <x:c r="J194" s="23" t="n">
+        <x:v>0.006010998848957616</x:v>
+      </x:c>
+      <x:c r="J194" s="26" t="n">
         <x:f>ROUND(E194-F194,1)</x:f>
-        <x:v>5720</x:v>
+        <x:v>6160</x:v>
       </x:c>
       <x:c r="K194" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -7159,29 +7159,29 @@
         <x:v>8月25日</x:v>
       </x:c>
       <x:c r="D195" s="23" t="n">
-        <x:v>156000</x:v>
+        <x:v>157440</x:v>
       </x:c>
       <x:c r="E195" s="23" t="n">
-        <x:v>157980</x:v>
+        <x:v>158480</x:v>
       </x:c>
       <x:c r="F195" s="23" t="n">
-        <x:v>149300</x:v>
+        <x:v>149780</x:v>
       </x:c>
       <x:c r="G195" s="23" t="n">
-        <x:v>149300</x:v>
+        <x:v>149860</x:v>
       </x:c>
       <x:c r="H195" s="28" t="n">
-        <x:v>-7700</x:v>
+        <x:v>-7460</x:v>
       </x:c>
       <x:c r="I195" s="24" t="n">
-        <x:v>-0.049044585987261136</x:v>
+        <x:v>-0.04741927281973046</x:v>
       </x:c>
       <x:c r="J195" s="26" t="n">
         <x:f>ROUND(E195-F195,1)</x:f>
-        <x:v>8680</x:v>
+        <x:v>8700</x:v>
       </x:c>
       <x:c r="K195" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -7195,29 +7195,29 @@
         <x:v>8月26日</x:v>
       </x:c>
       <x:c r="D196" s="23" t="n">
-        <x:v>147000</x:v>
+        <x:v>150500</x:v>
       </x:c>
       <x:c r="E196" s="23" t="n">
-        <x:v>153380</x:v>
+        <x:v>153860</x:v>
       </x:c>
       <x:c r="F196" s="23" t="n">
-        <x:v>147000</x:v>
+        <x:v>147600</x:v>
       </x:c>
       <x:c r="G196" s="23" t="n">
-        <x:v>150580</x:v>
+        <x:v>151000</x:v>
       </x:c>
       <x:c r="H196" s="28" t="n">
-        <x:v>1280</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="I196" s="24" t="n">
-        <x:v>0.008573342263898276</x:v>
+        <x:v>0.007607099959962671</x:v>
       </x:c>
       <x:c r="J196" s="26" t="n">
         <x:f>ROUND(E196-F196,1)</x:f>
-        <x:v>6380</x:v>
+        <x:v>6260</x:v>
       </x:c>
       <x:c r="K196" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -7231,29 +7231,29 @@
         <x:v>8月27日</x:v>
       </x:c>
       <x:c r="D197" s="23" t="n">
-        <x:v>149860</x:v>
+        <x:v>151480</x:v>
       </x:c>
       <x:c r="E197" s="23" t="n">
-        <x:v>153140</x:v>
+        <x:v>153540</x:v>
       </x:c>
       <x:c r="F197" s="23" t="n">
-        <x:v>149120</x:v>
+        <x:v>149740</x:v>
       </x:c>
       <x:c r="G197" s="23" t="n">
-        <x:v>150300</x:v>
+        <x:v>150680</x:v>
       </x:c>
       <x:c r="H197" s="28" t="n">
-        <x:v>-280</x:v>
+        <x:v>-320</x:v>
       </x:c>
       <x:c r="I197" s="24" t="n">
-        <x:v>-0.001859476690131534</x:v>
+        <x:v>-0.002119205298013238</x:v>
       </x:c>
       <x:c r="J197" s="23" t="n">
         <x:f>ROUND(E197-F197,1)</x:f>
-        <x:v>4020</x:v>
+        <x:v>3800</x:v>
       </x:c>
       <x:c r="K197" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -7267,29 +7267,29 @@
         <x:v>8月28日</x:v>
       </x:c>
       <x:c r="D198" s="23" t="n">
-        <x:v>149380</x:v>
+        <x:v>151360</x:v>
       </x:c>
       <x:c r="E198" s="23" t="n">
-        <x:v>157200</x:v>
+        <x:v>157940</x:v>
       </x:c>
       <x:c r="F198" s="23" t="n">
-        <x:v>149380</x:v>
+        <x:v>151020</x:v>
       </x:c>
       <x:c r="G198" s="23" t="n">
-        <x:v>157080</x:v>
+        <x:v>157940</x:v>
       </x:c>
       <x:c r="H198" s="28" t="n">
-        <x:v>6780</x:v>
+        <x:v>7260</x:v>
       </x:c>
       <x:c r="I198" s="24" t="n">
-        <x:v>0.04510978043912184</x:v>
+        <x:v>0.04818157685160607</x:v>
       </x:c>
       <x:c r="J198" s="26" t="n">
         <x:f>ROUND(E198-F198,1)</x:f>
-        <x:v>7820</x:v>
+        <x:v>6920</x:v>
       </x:c>
       <x:c r="K198" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -7303,29 +7303,29 @@
         <x:v>8月31日</x:v>
       </x:c>
       <x:c r="D199" s="23" t="n">
-        <x:v>158000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="E199" s="23" t="n">
-        <x:v>159900</x:v>
+        <x:v>160360</x:v>
       </x:c>
       <x:c r="F199" s="23" t="n">
-        <x:v>156180</x:v>
+        <x:v>156700</x:v>
       </x:c>
       <x:c r="G199" s="23" t="n">
-        <x:v>159000</x:v>
+        <x:v>159280</x:v>
       </x:c>
       <x:c r="H199" s="28" t="n">
-        <x:v>1920</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="I199" s="24" t="n">
-        <x:v>0.012223071046600475</x:v>
+        <x:v>0.008484234519437805</x:v>
       </x:c>
       <x:c r="J199" s="23" t="n">
         <x:f>ROUND(E199-F199,1)</x:f>
-        <x:v>3720</x:v>
+        <x:v>3660</x:v>
       </x:c>
       <x:c r="K199" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -7344,7 +7344,7 @@
       <x:c r="I200" s="30"/>
       <x:c r="J200" s="32" t="n">
         <x:f>ROUND(SUM(J179:J199),1)</x:f>
-        <x:v>110440</x:v>
+        <x:v>108680</x:v>
       </x:c>
       <x:c r="K200" s="30"/>
     </x:row>
@@ -7362,7 +7362,7 @@
       <x:c r="I201" s="30"/>
       <x:c r="J201" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(J179:J199),0),1)</x:f>
-        <x:v>5259</x:v>
+        <x:v>5175.2</x:v>
       </x:c>
       <x:c r="K201" s="30"/>
     </x:row>
@@ -7427,29 +7427,29 @@
         <x:v>9月1日</x:v>
       </x:c>
       <x:c r="D205" s="23" t="n">
-        <x:v>159000</x:v>
+        <x:v>159280</x:v>
       </x:c>
       <x:c r="E205" s="23" t="n">
-        <x:v>160480</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="F205" s="23" t="n">
-        <x:v>155800</x:v>
+        <x:v>156100</x:v>
       </x:c>
       <x:c r="G205" s="23" t="n">
-        <x:v>155820</x:v>
+        <x:v>156920</x:v>
       </x:c>
       <x:c r="H205" s="28" t="n">
-        <x:v>-3180</x:v>
+        <x:v>-2360</x:v>
       </x:c>
       <x:c r="I205" s="24" t="n">
-        <x:v>-0.020000000000000018</x:v>
+        <x:v>-0.01481667503766948</x:v>
       </x:c>
       <x:c r="J205" s="23" t="n">
         <x:f>ROUND(E205-F205,1)</x:f>
-        <x:v>4680</x:v>
+        <x:v>5180</x:v>
       </x:c>
       <x:c r="K205" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -7463,29 +7463,29 @@
         <x:v>9月2日</x:v>
       </x:c>
       <x:c r="D206" s="23" t="n">
-        <x:v>156200</x:v>
+        <x:v>156760</x:v>
       </x:c>
       <x:c r="E206" s="23" t="n">
-        <x:v>156200</x:v>
+        <x:v>156760</x:v>
       </x:c>
       <x:c r="F206" s="23" t="n">
-        <x:v>152840</x:v>
+        <x:v>152500</x:v>
       </x:c>
       <x:c r="G206" s="23" t="n">
-        <x:v>155000</x:v>
+        <x:v>153680</x:v>
       </x:c>
       <x:c r="H206" s="28" t="n">
-        <x:v>-820</x:v>
+        <x:v>-3240</x:v>
       </x:c>
       <x:c r="I206" s="24" t="n">
-        <x:v>-0.005262482351431119</x:v>
+        <x:v>-0.020647463675758315</x:v>
       </x:c>
       <x:c r="J206" s="23" t="n">
         <x:f>ROUND(E206-F206,1)</x:f>
-        <x:v>3360</x:v>
+        <x:v>4260</x:v>
       </x:c>
       <x:c r="K206" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -7499,29 +7499,29 @@
         <x:v>9月3日</x:v>
       </x:c>
       <x:c r="D207" s="23" t="n">
-        <x:v>154860</x:v>
+        <x:v>154200</x:v>
       </x:c>
       <x:c r="E207" s="23" t="n">
-        <x:v>155600</x:v>
+        <x:v>156640</x:v>
       </x:c>
       <x:c r="F207" s="23" t="n">
-        <x:v>148880</x:v>
+        <x:v>149080</x:v>
       </x:c>
       <x:c r="G207" s="23" t="n">
-        <x:v>148900</x:v>
+        <x:v>149080</x:v>
       </x:c>
       <x:c r="H207" s="28" t="n">
-        <x:v>-6100</x:v>
+        <x:v>-4600</x:v>
       </x:c>
       <x:c r="I207" s="24" t="n">
-        <x:v>-0.039354838709677376</x:v>
+        <x:v>-0.029932326913066132</x:v>
       </x:c>
       <x:c r="J207" s="26" t="n">
         <x:f>ROUND(E207-F207,1)</x:f>
-        <x:v>6720</x:v>
+        <x:v>7560</x:v>
       </x:c>
       <x:c r="K207" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -7535,29 +7535,29 @@
         <x:v>9月4日</x:v>
       </x:c>
       <x:c r="D208" s="23" t="n">
-        <x:v>152400</x:v>
+        <x:v>150440</x:v>
       </x:c>
       <x:c r="E208" s="23" t="n">
-        <x:v>152400</x:v>
+        <x:v>151480</x:v>
       </x:c>
       <x:c r="F208" s="23" t="n">
-        <x:v>140940</x:v>
+        <x:v>140220</x:v>
       </x:c>
       <x:c r="G208" s="23" t="n">
-        <x:v>140980</x:v>
+        <x:v>142000</x:v>
       </x:c>
       <x:c r="H208" s="28" t="n">
-        <x:v>-7920</x:v>
+        <x:v>-7080</x:v>
       </x:c>
       <x:c r="I208" s="24" t="n">
-        <x:v>-0.053190060443250475</x:v>
+        <x:v>-0.047491279849745105</x:v>
       </x:c>
       <x:c r="J208" s="26" t="n">
         <x:f>ROUND(E208-F208,1)</x:f>
-        <x:v>11460</x:v>
+        <x:v>11260</x:v>
       </x:c>
       <x:c r="K208" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -7571,29 +7571,29 @@
         <x:v>9月7日</x:v>
       </x:c>
       <x:c r="D209" s="23" t="n">
-        <x:v>142120</x:v>
+        <x:v>141000</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
-        <x:v>142800</x:v>
+        <x:v>142860</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>139880</x:v>
+        <x:v>139760</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
-        <x:v>140500</x:v>
+        <x:v>141140</x:v>
       </x:c>
       <x:c r="H209" s="28" t="n">
-        <x:v>-480</x:v>
+        <x:v>-860</x:v>
       </x:c>
       <x:c r="I209" s="24" t="n">
-        <x:v>-0.003404738260746165</x:v>
+        <x:v>-0.006056338028168962</x:v>
       </x:c>
       <x:c r="J209" s="23" t="n">
         <x:f>ROUND(E209-F209,1)</x:f>
-        <x:v>2920</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="K209" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -7607,29 +7607,29 @@
         <x:v>9月8日</x:v>
       </x:c>
       <x:c r="D210" s="23" t="n">
-        <x:v>143200</x:v>
+        <x:v>140960</x:v>
       </x:c>
       <x:c r="E210" s="23" t="n">
-        <x:v>143200</x:v>
+        <x:v>143540</x:v>
       </x:c>
       <x:c r="F210" s="23" t="n">
-        <x:v>141320</x:v>
+        <x:v>140960</x:v>
       </x:c>
       <x:c r="G210" s="23" t="n">
-        <x:v>141320</x:v>
+        <x:v>142640</x:v>
       </x:c>
       <x:c r="H210" s="28" t="n">
-        <x:v>820</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="I210" s="24" t="n">
-        <x:v>0.005836298932384354</x:v>
+        <x:v>0.01062774550092116</x:v>
       </x:c>
       <x:c r="J210" s="23" t="n">
         <x:f>ROUND(E210-F210,1)</x:f>
-        <x:v>1880</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="K210" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -7643,29 +7643,29 @@
         <x:v>9月9日</x:v>
       </x:c>
       <x:c r="D211" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>142100</x:v>
       </x:c>
       <x:c r="E211" s="23" t="n">
-        <x:v>142880</x:v>
+        <x:v>143220</x:v>
       </x:c>
       <x:c r="F211" s="23" t="n">
         <x:v>139800</x:v>
       </x:c>
       <x:c r="G211" s="23" t="n">
-        <x:v>141260</x:v>
-      </x:c>
-      <x:c r="H211" s="23" t="n">
-        <x:v>-60</x:v>
+        <x:v>141140</x:v>
+      </x:c>
+      <x:c r="H211" s="28" t="n">
+        <x:v>-1500</x:v>
       </x:c>
       <x:c r="I211" s="24" t="n">
-        <x:v>-0.0004245683555051949</x:v>
+        <x:v>-0.010515984296130099</x:v>
       </x:c>
       <x:c r="J211" s="23" t="n">
         <x:f>ROUND(E211-F211,1)</x:f>
-        <x:v>3080</x:v>
+        <x:v>3420</x:v>
       </x:c>
       <x:c r="K211" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -7679,29 +7679,29 @@
         <x:v>9月10日</x:v>
       </x:c>
       <x:c r="D212" s="23" t="n">
-        <x:v>141220</x:v>
+        <x:v>141340</x:v>
       </x:c>
       <x:c r="E212" s="23" t="n">
-        <x:v>142500</x:v>
+        <x:v>142880</x:v>
       </x:c>
       <x:c r="F212" s="23" t="n">
-        <x:v>139000</x:v>
+        <x:v>139020</x:v>
       </x:c>
       <x:c r="G212" s="23" t="n">
-        <x:v>140520</x:v>
+        <x:v>140960</x:v>
       </x:c>
       <x:c r="H212" s="28" t="n">
-        <x:v>-740</x:v>
+        <x:v>-180</x:v>
       </x:c>
       <x:c r="I212" s="24" t="n">
-        <x:v>-0.005238567181084508</x:v>
+        <x:v>-0.0012753294601105525</x:v>
       </x:c>
       <x:c r="J212" s="23" t="n">
         <x:f>ROUND(E212-F212,1)</x:f>
-        <x:v>3500</x:v>
+        <x:v>3860</x:v>
       </x:c>
       <x:c r="K212" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -7715,29 +7715,29 @@
         <x:v>9月11日</x:v>
       </x:c>
       <x:c r="D213" s="23" t="n">
-        <x:v>134480</x:v>
+        <x:v>140300</x:v>
       </x:c>
       <x:c r="E213" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>140300</x:v>
       </x:c>
       <x:c r="F213" s="23" t="n">
-        <x:v>131900</x:v>
+        <x:v>127120</x:v>
       </x:c>
       <x:c r="G213" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>134340</x:v>
       </x:c>
       <x:c r="H213" s="28" t="n">
-        <x:v>-5020</x:v>
+        <x:v>-6620</x:v>
       </x:c>
       <x:c r="I213" s="24" t="n">
-        <x:v>-0.035724452035297505</x:v>
-      </x:c>
-      <x:c r="J213" s="23" t="n">
+        <x:v>-0.04696367763904652</x:v>
+      </x:c>
+      <x:c r="J213" s="26" t="n">
         <x:f>ROUND(E213-F213,1)</x:f>
-        <x:v>3600</x:v>
+        <x:v>13180</x:v>
       </x:c>
       <x:c r="K213" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -7751,68 +7751,140 @@
         <x:v>9月14日</x:v>
       </x:c>
       <x:c r="D214" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>133600</x:v>
       </x:c>
       <x:c r="E214" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>134840</x:v>
       </x:c>
       <x:c r="F214" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>132020</x:v>
       </x:c>
       <x:c r="G214" s="23" t="n">
-        <x:v>135500</x:v>
-      </x:c>
-      <x:c r="H214" s="23" t="n">
-        <x:v>0</x:v>
+        <x:v>132580</x:v>
+      </x:c>
+      <x:c r="H214" s="28" t="n">
+        <x:v>-1760</x:v>
       </x:c>
       <x:c r="I214" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-0.013101086794700012</x:v>
       </x:c>
       <x:c r="J214" s="23" t="n">
         <x:f>ROUND(E214-F214,1)</x:f>
-        <x:v>0</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="K214" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="31" t="str">
+      <x:c r="A215" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B215" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C215" s="22" t="str">
+        <x:v>9月15日</x:v>
+      </x:c>
+      <x:c r="D215" s="23" t="n">
+        <x:v>133680</x:v>
+      </x:c>
+      <x:c r="E215" s="23" t="n">
+        <x:v>133680</x:v>
+      </x:c>
+      <x:c r="F215" s="23" t="n">
+        <x:v>128000</x:v>
+      </x:c>
+      <x:c r="G215" s="23" t="n">
+        <x:v>130000</x:v>
+      </x:c>
+      <x:c r="H215" s="28" t="n">
+        <x:v>-2580</x:v>
+      </x:c>
+      <x:c r="I215" s="24" t="n">
+        <x:v>-0.019459948710212727</x:v>
+      </x:c>
+      <x:c r="J215" s="23" t="n">
+        <x:f>ROUND(E215-F215,1)</x:f>
+        <x:v>5680</x:v>
+      </x:c>
+      <x:c r="K215" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B216" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C216" s="22" t="str">
+        <x:v>9月16日</x:v>
+      </x:c>
+      <x:c r="D216" s="23" t="n">
+        <x:v>128500</x:v>
+      </x:c>
+      <x:c r="E216" s="23" t="n">
+        <x:v>130660</x:v>
+      </x:c>
+      <x:c r="F216" s="23" t="n">
+        <x:v>126200</x:v>
+      </x:c>
+      <x:c r="G216" s="23" t="n">
+        <x:v>127460</x:v>
+      </x:c>
+      <x:c r="H216" s="28" t="n">
+        <x:v>-2540</x:v>
+      </x:c>
+      <x:c r="I216" s="24" t="n">
+        <x:v>-0.019538461538461505</x:v>
+      </x:c>
+      <x:c r="J216" s="23" t="n">
+        <x:f>ROUND(E216-F216,1)</x:f>
+        <x:v>4460</x:v>
+      </x:c>
+      <x:c r="K216" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B215" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C215" s="30"/>
-      <x:c r="D215" s="30"/>
-      <x:c r="E215" s="30"/>
-      <x:c r="F215" s="30"/>
-      <x:c r="G215" s="30"/>
-      <x:c r="H215" s="30"/>
-      <x:c r="I215" s="30"/>
-      <x:c r="J215" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J214),1)</x:f>
-        <x:v>41200</x:v>
-      </x:c>
-      <x:c r="K215" s="30"/>
-    </x:row>
-    <x:row r="216">
-      <x:c r="A216" s="31" t="str">
+      <x:c r="B217" s="30" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C217" s="30"/>
+      <x:c r="D217" s="30"/>
+      <x:c r="E217" s="30"/>
+      <x:c r="F217" s="30"/>
+      <x:c r="G217" s="30"/>
+      <x:c r="H217" s="30"/>
+      <x:c r="I217" s="30"/>
+      <x:c r="J217" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J216),1)</x:f>
+        <x:v>67360</x:v>
+      </x:c>
+      <x:c r="K217" s="30"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B216" s="30"/>
-      <x:c r="C216" s="30"/>
-      <x:c r="D216" s="30"/>
-      <x:c r="E216" s="30"/>
-      <x:c r="F216" s="30"/>
-      <x:c r="G216" s="30"/>
-      <x:c r="H216" s="30"/>
-      <x:c r="I216" s="30"/>
-      <x:c r="J216" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J214),0),1)</x:f>
-        <x:v>4120</x:v>
-      </x:c>
-      <x:c r="K216" s="30"/>
+      <x:c r="B218" s="30"/>
+      <x:c r="C218" s="30"/>
+      <x:c r="D218" s="30"/>
+      <x:c r="E218" s="30"/>
+      <x:c r="F218" s="30"/>
+      <x:c r="G218" s="30"/>
+      <x:c r="H218" s="30"/>
+      <x:c r="I218" s="30"/>
+      <x:c r="J218" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
+        <x:v>5613.3</x:v>
+      </x:c>
+      <x:c r="K218" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -18005,7 +18077,7 @@
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="17" t="str">
-        <x:v>碳酸锂2609</x:v>
+        <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B290" s="17"/>
       <x:c r="C290" s="17"/>
@@ -18061,25 +18133,25 @@
         <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C292" s="23" t="n">
-        <x:v>126360</x:v>
+        <x:v>132800</x:v>
       </x:c>
       <x:c r="D292" s="23" t="n">
-        <x:v>150760</x:v>
+        <x:v>150100</x:v>
       </x:c>
       <x:c r="E292" s="23" t="n">
-        <x:v>125160</x:v>
+        <x:v>123500</x:v>
       </x:c>
       <x:c r="F292" s="23" t="n">
-        <x:v>145380</x:v>
+        <x:v>145600</x:v>
       </x:c>
       <x:c r="G292" s="23"/>
       <x:c r="H292" s="24"/>
       <x:c r="I292" s="26" t="n">
         <x:f>ROUND(D292-E292,1)</x:f>
-        <x:v>25600</x:v>
+        <x:v>26600</x:v>
       </x:c>
       <x:c r="J292" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K292" s="22" t="n">
         <x:v>5</x:v>
@@ -18093,31 +18165,31 @@
         <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>149180</x:v>
       </x:c>
       <x:c r="D293" s="23" t="n">
-        <x:v>176120</x:v>
+        <x:v>175360</x:v>
       </x:c>
       <x:c r="E293" s="23" t="n">
-        <x:v>147740</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>147740</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="G293" s="28" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>2360</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>0.016233319576282934</x:v>
+        <x:v>0.017719780219780157</x:v>
       </x:c>
       <x:c r="I293" s="26" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
-        <x:v>28380</x:v>
+        <x:v>27180</x:v>
       </x:c>
       <x:c r="J293" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K293" s="22" t="n">
         <x:v>5</x:v>
@@ -18131,31 +18203,31 @@
         <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C294" s="23" t="n">
-        <x:v>150720</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="D294" s="23" t="n">
-        <x:v>183780</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="E294" s="23" t="n">
-        <x:v>143820</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="F294" s="23" t="n">
-        <x:v>183380</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="G294" s="28" t="n">
         <x:f>ROUND(F294-F293,1)</x:f>
-        <x:v>35640</x:v>
+        <x:v>35280</x:v>
       </x:c>
       <x:c r="H294" s="24" t="n">
         <x:f>IFERROR(F294/F293-1,"")</x:f>
-        <x:v>0.24123460132665486</x:v>
+        <x:v>0.23808881090565537</x:v>
       </x:c>
       <x:c r="I294" s="26" t="n">
         <x:f>ROUND(D294-E294,1)</x:f>
-        <x:v>39960</x:v>
+        <x:v>40460</x:v>
       </x:c>
       <x:c r="J294" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K294" s="22" t="n">
         <x:v>5</x:v>
@@ -18169,31 +18241,31 @@
         <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
-        <x:v>187000</x:v>
+        <x:v>189980</x:v>
       </x:c>
       <x:c r="D295" s="23" t="n">
-        <x:v>190600</x:v>
+        <x:v>190020</x:v>
       </x:c>
       <x:c r="E295" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>148520</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>148560</x:v>
+        <x:v>148540</x:v>
       </x:c>
       <x:c r="G295" s="28" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>-34820</x:v>
+        <x:v>-34920</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>-0.18987893990620575</x:v>
+        <x:v>-0.19034121879428756</x:v>
       </x:c>
       <x:c r="I295" s="26" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>42040</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="J295" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K295" s="22" t="n">
         <x:v>5</x:v>
@@ -18207,31 +18279,31 @@
         <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C296" s="23" t="n">
-        <x:v>148040</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="D296" s="23" t="n">
-        <x:v>153200</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="E296" s="23" t="n">
-        <x:v>124480</x:v>
+        <x:v>124760</x:v>
       </x:c>
       <x:c r="F296" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>131160</x:v>
       </x:c>
       <x:c r="G296" s="28" t="n">
         <x:f>ROUND(F296-F295,1)</x:f>
-        <x:v>-15060</x:v>
+        <x:v>-17380</x:v>
       </x:c>
       <x:c r="H296" s="24" t="n">
         <x:f>IFERROR(F296/F295-1,"")</x:f>
-        <x:v>-0.10137318255250405</x:v>
+        <x:v>-0.11700552039854584</x:v>
       </x:c>
       <x:c r="I296" s="26" t="n">
         <x:f>ROUND(D296-E296,1)</x:f>
-        <x:v>28720</x:v>
+        <x:v>28240</x:v>
       </x:c>
       <x:c r="J296" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K296" s="22" t="n">
         <x:v>5</x:v>
@@ -18245,31 +18317,31 @@
         <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C297" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>134660</x:v>
       </x:c>
       <x:c r="D297" s="23" t="n">
-        <x:v>153700</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="E297" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>133580</x:v>
       </x:c>
       <x:c r="F297" s="23" t="n">
-        <x:v>153500</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="G297" s="28" t="n">
         <x:f>ROUND(F297-F296,1)</x:f>
-        <x:v>20000</x:v>
+        <x:v>21220</x:v>
       </x:c>
       <x:c r="H297" s="24" t="n">
         <x:f>IFERROR(F297/F296-1,"")</x:f>
-        <x:v>0.14981273408239693</x:v>
+        <x:v>0.1617871302226288</x:v>
       </x:c>
       <x:c r="I297" s="26" t="n">
         <x:f>ROUND(D297-E297,1)</x:f>
-        <x:v>20200</x:v>
+        <x:v>18800</x:v>
       </x:c>
       <x:c r="J297" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K297" s="22" t="n">
         <x:v>5</x:v>
@@ -18283,31 +18355,31 @@
         <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C298" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>165060</x:v>
       </x:c>
       <x:c r="D298" s="23" t="n">
-        <x:v>186900</x:v>
+        <x:v>187920</x:v>
       </x:c>
       <x:c r="E298" s="23" t="n">
-        <x:v>158340</x:v>
+        <x:v>155680</x:v>
       </x:c>
       <x:c r="F298" s="23" t="n">
-        <x:v>177200</x:v>
+        <x:v>175400</x:v>
       </x:c>
       <x:c r="G298" s="28" t="n">
         <x:f>ROUND(F298-F297,1)</x:f>
-        <x:v>23700</x:v>
+        <x:v>23020</x:v>
       </x:c>
       <x:c r="H298" s="24" t="n">
         <x:f>IFERROR(F298/F297-1,"")</x:f>
-        <x:v>0.15439739413680775</x:v>
+        <x:v>0.1510696941855887</x:v>
       </x:c>
       <x:c r="I298" s="26" t="n">
         <x:f>ROUND(D298-E298,1)</x:f>
-        <x:v>28560</x:v>
+        <x:v>32240</x:v>
       </x:c>
       <x:c r="J298" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K298" s="22" t="n">
         <x:v>4</x:v>
@@ -18321,31 +18393,31 @@
         <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C299" s="23" t="n">
-        <x:v>180000</x:v>
+        <x:v>175800</x:v>
       </x:c>
       <x:c r="D299" s="23" t="n">
-        <x:v>180060</x:v>
+        <x:v>177260</x:v>
       </x:c>
       <x:c r="E299" s="23" t="n">
-        <x:v>146040</x:v>
+        <x:v>144980</x:v>
       </x:c>
       <x:c r="F299" s="23" t="n">
-        <x:v>156700</x:v>
+        <x:v>156580</x:v>
       </x:c>
       <x:c r="G299" s="28" t="n">
         <x:f>ROUND(F299-F298,1)</x:f>
-        <x:v>-20500</x:v>
+        <x:v>-18820</x:v>
       </x:c>
       <x:c r="H299" s="24" t="n">
         <x:f>IFERROR(F299/F298-1,"")</x:f>
-        <x:v>-0.11568848758465011</x:v>
+        <x:v>-0.1072976054732041</x:v>
       </x:c>
       <x:c r="I299" s="26" t="n">
         <x:f>ROUND(D299-E299,1)</x:f>
-        <x:v>34020</x:v>
+        <x:v>32280</x:v>
       </x:c>
       <x:c r="J299" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K299" s="22" t="n">
         <x:v>5</x:v>
@@ -18359,31 +18431,31 @@
         <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C300" s="23" t="n">
-        <x:v>149000</x:v>
+        <x:v>145120</x:v>
       </x:c>
       <x:c r="D300" s="23" t="n">
-        <x:v>167400</x:v>
+        <x:v>166800</x:v>
       </x:c>
       <x:c r="E300" s="23" t="n">
-        <x:v>142600</x:v>
+        <x:v>139860</x:v>
       </x:c>
       <x:c r="F300" s="23" t="n">
-        <x:v>152100</x:v>
+        <x:v>151880</x:v>
       </x:c>
       <x:c r="G300" s="28" t="n">
         <x:f>ROUND(F300-F299,1)</x:f>
-        <x:v>-4600</x:v>
+        <x:v>-4700</x:v>
       </x:c>
       <x:c r="H300" s="24" t="n">
         <x:f>IFERROR(F300/F299-1,"")</x:f>
-        <x:v>-0.02935545628589664</x:v>
+        <x:v>-0.030016604930387047</x:v>
       </x:c>
       <x:c r="I300" s="26" t="n">
         <x:f>ROUND(D300-E300,1)</x:f>
-        <x:v>24800</x:v>
+        <x:v>26940</x:v>
       </x:c>
       <x:c r="J300" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K300" s="22" t="n">
         <x:v>5</x:v>
@@ -18397,31 +18469,31 @@
         <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C301" s="23" t="n">
-        <x:v>150880</x:v>
+        <x:v>149140</x:v>
       </x:c>
       <x:c r="D301" s="23" t="n">
-        <x:v>160800</x:v>
+        <x:v>159120</x:v>
       </x:c>
       <x:c r="E301" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>139640</x:v>
       </x:c>
       <x:c r="F301" s="23" t="n">
-        <x:v>143520</x:v>
+        <x:v>143900</x:v>
       </x:c>
       <x:c r="G301" s="28" t="n">
         <x:f>ROUND(F301-F300,1)</x:f>
-        <x:v>-8580</x:v>
+        <x:v>-7980</x:v>
       </x:c>
       <x:c r="H301" s="24" t="n">
         <x:f>IFERROR(F301/F300-1,"")</x:f>
-        <x:v>-0.05641025641025643</x:v>
+        <x:v>-0.052541480115881</x:v>
       </x:c>
       <x:c r="I301" s="26" t="n">
         <x:f>ROUND(D301-E301,1)</x:f>
-        <x:v>20800</x:v>
+        <x:v>19480</x:v>
       </x:c>
       <x:c r="J301" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K301" s="22" t="n">
         <x:v>5</x:v>
@@ -18435,31 +18507,31 @@
         <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C302" s="23" t="n">
-        <x:v>141220</x:v>
+        <x:v>144460</x:v>
       </x:c>
       <x:c r="D302" s="23" t="n">
-        <x:v>172220</x:v>
+        <x:v>170800</x:v>
       </x:c>
       <x:c r="E302" s="23" t="n">
-        <x:v>140020</x:v>
+        <x:v>139980</x:v>
       </x:c>
       <x:c r="F302" s="23" t="n">
-        <x:v>169400</x:v>
+        <x:v>166540</x:v>
       </x:c>
       <x:c r="G302" s="28" t="n">
         <x:f>ROUND(F302-F301,1)</x:f>
-        <x:v>25880</x:v>
+        <x:v>22640</x:v>
       </x:c>
       <x:c r="H302" s="24" t="n">
         <x:f>IFERROR(F302/F301-1,"")</x:f>
-        <x:v>0.18032329988851736</x:v>
+        <x:v>0.15733148019457954</x:v>
       </x:c>
       <x:c r="I302" s="26" t="n">
         <x:f>ROUND(D302-E302,1)</x:f>
-        <x:v>32200</x:v>
+        <x:v>30820</x:v>
       </x:c>
       <x:c r="J302" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K302" s="22" t="n">
         <x:v>5</x:v>
@@ -18473,31 +18545,31 @@
         <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C303" s="23" t="n">
-        <x:v>170000</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="D303" s="23" t="n">
-        <x:v>175000</x:v>
+        <x:v>174540</x:v>
       </x:c>
       <x:c r="E303" s="23" t="n">
-        <x:v>154560</x:v>
+        <x:v>153840</x:v>
       </x:c>
       <x:c r="F303" s="23" t="n">
-        <x:v>157860</x:v>
+        <x:v>157680</x:v>
       </x:c>
       <x:c r="G303" s="28" t="n">
         <x:f>ROUND(F303-F302,1)</x:f>
-        <x:v>-11540</x:v>
+        <x:v>-8860</x:v>
       </x:c>
       <x:c r="H303" s="24" t="n">
         <x:f>IFERROR(F303/F302-1,"")</x:f>
-        <x:v>-0.06812278630460444</x:v>
+        <x:v>-0.05320043232856975</x:v>
       </x:c>
       <x:c r="I303" s="26" t="n">
         <x:f>ROUND(D303-E303,1)</x:f>
-        <x:v>20440</x:v>
+        <x:v>20700</x:v>
       </x:c>
       <x:c r="J303" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K303" s="22" t="n">
         <x:v>5</x:v>
@@ -18511,31 +18583,31 @@
         <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C304" s="23" t="n">
-        <x:v>158440</x:v>
+        <x:v>156200</x:v>
       </x:c>
       <x:c r="D304" s="23" t="n">
-        <x:v>165500</x:v>
+        <x:v>164160</x:v>
       </x:c>
       <x:c r="E304" s="23" t="n">
-        <x:v>152500</x:v>
+        <x:v>151640</x:v>
       </x:c>
       <x:c r="F304" s="23" t="n">
-        <x:v>157600</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="G304" s="28" t="n">
         <x:f>ROUND(F304-F303,1)</x:f>
-        <x:v>-260</x:v>
+        <x:v>-1180</x:v>
       </x:c>
       <x:c r="H304" s="24" t="n">
         <x:f>IFERROR(F304/F303-1,"")</x:f>
-        <x:v>-0.0016470290130495835</x:v>
+        <x:v>-0.007483510908168456</x:v>
       </x:c>
       <x:c r="I304" s="26" t="n">
         <x:f>ROUND(D304-E304,1)</x:f>
-        <x:v>13000</x:v>
+        <x:v>12520</x:v>
       </x:c>
       <x:c r="J304" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K304" s="22" t="n">
         <x:v>4</x:v>
@@ -18549,31 +18621,31 @@
         <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C305" s="23" t="n">
-        <x:v>155020</x:v>
+        <x:v>156660</x:v>
       </x:c>
       <x:c r="D305" s="23" t="n">
-        <x:v>178000</x:v>
+        <x:v>176500</x:v>
       </x:c>
       <x:c r="E305" s="23" t="n">
-        <x:v>154780</x:v>
+        <x:v>153040</x:v>
       </x:c>
       <x:c r="F305" s="23" t="n">
-        <x:v>177560</x:v>
+        <x:v>176360</x:v>
       </x:c>
       <x:c r="G305" s="28" t="n">
         <x:f>ROUND(F305-F304,1)</x:f>
-        <x:v>19960</x:v>
+        <x:v>19860</x:v>
       </x:c>
       <x:c r="H305" s="24" t="n">
         <x:f>IFERROR(F305/F304-1,"")</x:f>
-        <x:v>0.1266497461928935</x:v>
+        <x:v>0.12690095846645377</x:v>
       </x:c>
       <x:c r="I305" s="26" t="n">
         <x:f>ROUND(D305-E305,1)</x:f>
-        <x:v>23220</x:v>
+        <x:v>23460</x:v>
       </x:c>
       <x:c r="J305" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K305" s="22" t="n">
         <x:v>5</x:v>
@@ -18587,31 +18659,31 @@
         <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C306" s="23" t="n">
-        <x:v>177000</x:v>
+        <x:v>174080</x:v>
       </x:c>
       <x:c r="D306" s="23" t="n">
-        <x:v>181440</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="E306" s="23" t="n">
-        <x:v>169500</x:v>
+        <x:v>169000</x:v>
       </x:c>
       <x:c r="F306" s="23" t="n">
-        <x:v>177900</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="G306" s="28" t="n">
         <x:f>ROUND(F306-F305,1)</x:f>
-        <x:v>340</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H306" s="24" t="n">
         <x:f>IFERROR(F306/F305-1,"")</x:f>
-        <x:v>0.0019148456859652274</x:v>
+        <x:v>0.0034021320027217694</x:v>
       </x:c>
       <x:c r="I306" s="26" t="n">
         <x:f>ROUND(D306-E306,1)</x:f>
-        <x:v>11940</x:v>
+        <x:v>11920</x:v>
       </x:c>
       <x:c r="J306" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K306" s="22" t="n">
         <x:v>5</x:v>
@@ -18625,31 +18697,31 @@
         <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C307" s="23" t="n">
-        <x:v>182000</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="D307" s="23" t="n">
-        <x:v>189500</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="E307" s="23" t="n">
-        <x:v>173400</x:v>
+        <x:v>172640</x:v>
       </x:c>
       <x:c r="F307" s="23" t="n">
-        <x:v>189080</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="G307" s="28" t="n">
         <x:f>ROUND(F307-F306,1)</x:f>
-        <x:v>11180</x:v>
+        <x:v>11880</x:v>
       </x:c>
       <x:c r="H307" s="24" t="n">
         <x:f>IFERROR(F307/F306-1,"")</x:f>
-        <x:v>0.06284429454749851</x:v>
+        <x:v>0.06713381555153708</x:v>
       </x:c>
       <x:c r="I307" s="26" t="n">
         <x:f>ROUND(D307-E307,1)</x:f>
-        <x:v>16100</x:v>
+        <x:v>16200</x:v>
       </x:c>
       <x:c r="J307" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K307" s="22" t="n">
         <x:v>4</x:v>
@@ -18663,31 +18735,31 @@
         <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C308" s="23" t="n">
-        <x:v>191500</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="D308" s="23" t="n">
-        <x:v>201480</x:v>
+        <x:v>204640</x:v>
       </x:c>
       <x:c r="E308" s="23" t="n">
-        <x:v>191040</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="F308" s="23" t="n">
-        <x:v>196560</x:v>
+        <x:v>196100</x:v>
       </x:c>
       <x:c r="G308" s="28" t="n">
         <x:f>ROUND(F308-F307,1)</x:f>
-        <x:v>7480</x:v>
+        <x:v>7260</x:v>
       </x:c>
       <x:c r="H308" s="24" t="n">
         <x:f>IFERROR(F308/F307-1,"")</x:f>
-        <x:v>0.039559974613920135</x:v>
+        <x:v>0.038445244651556854</x:v>
       </x:c>
       <x:c r="I308" s="26" t="n">
         <x:f>ROUND(D308-E308,1)</x:f>
-        <x:v>10440</x:v>
+        <x:v>13340</x:v>
       </x:c>
       <x:c r="J308" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K308" s="22" t="n">
         <x:v>3</x:v>
@@ -18701,31 +18773,31 @@
         <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C309" s="23" t="n">
-        <x:v>196560</x:v>
+        <x:v>195080</x:v>
       </x:c>
       <x:c r="D309" s="23" t="n">
-        <x:v>209880</x:v>
+        <x:v>209040</x:v>
       </x:c>
       <x:c r="E309" s="23" t="n">
-        <x:v>186800</x:v>
+        <x:v>187240</x:v>
       </x:c>
       <x:c r="F309" s="23" t="n">
-        <x:v>188800</x:v>
+        <x:v>189440</x:v>
       </x:c>
       <x:c r="G309" s="28" t="n">
         <x:f>ROUND(F309-F308,1)</x:f>
-        <x:v>-7760</x:v>
+        <x:v>-6660</x:v>
       </x:c>
       <x:c r="H309" s="24" t="n">
         <x:f>IFERROR(F309/F308-1,"")</x:f>
-        <x:v>-0.039479039479039524</x:v>
+        <x:v>-0.03396226415094339</x:v>
       </x:c>
       <x:c r="I309" s="26" t="n">
         <x:f>ROUND(D309-E309,1)</x:f>
-        <x:v>23080</x:v>
+        <x:v>21800</x:v>
       </x:c>
       <x:c r="J309" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K309" s="22" t="n">
         <x:v>5</x:v>
@@ -18739,31 +18811,31 @@
         <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C310" s="23" t="n">
-        <x:v>189000</x:v>
+        <x:v>190060</x:v>
       </x:c>
       <x:c r="D310" s="23" t="n">
-        <x:v>193900</x:v>
+        <x:v>193820</x:v>
       </x:c>
       <x:c r="E310" s="23" t="n">
-        <x:v>175200</x:v>
+        <x:v>175520</x:v>
       </x:c>
       <x:c r="F310" s="23" t="n">
-        <x:v>184460</x:v>
+        <x:v>185280</x:v>
       </x:c>
       <x:c r="G310" s="28" t="n">
         <x:f>ROUND(F310-F309,1)</x:f>
-        <x:v>-4340</x:v>
+        <x:v>-4160</x:v>
       </x:c>
       <x:c r="H310" s="24" t="n">
         <x:f>IFERROR(F310/F309-1,"")</x:f>
-        <x:v>-0.022987288135593253</x:v>
+        <x:v>-0.02195945945945943</x:v>
       </x:c>
       <x:c r="I310" s="26" t="n">
         <x:f>ROUND(D310-E310,1)</x:f>
-        <x:v>18700</x:v>
+        <x:v>18300</x:v>
       </x:c>
       <x:c r="J310" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K310" s="22" t="n">
         <x:v>5</x:v>
@@ -18777,31 +18849,31 @@
         <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C311" s="23" t="n">
-        <x:v>185500</x:v>
+        <x:v>185380</x:v>
       </x:c>
       <x:c r="D311" s="23" t="n">
-        <x:v>187900</x:v>
+        <x:v>188320</x:v>
       </x:c>
       <x:c r="E311" s="23" t="n">
-        <x:v>172080</x:v>
+        <x:v>172500</x:v>
       </x:c>
       <x:c r="F311" s="23" t="n">
-        <x:v>179740</x:v>
+        <x:v>178620</x:v>
       </x:c>
       <x:c r="G311" s="28" t="n">
         <x:f>ROUND(F311-F310,1)</x:f>
-        <x:v>-4720</x:v>
+        <x:v>-6660</x:v>
       </x:c>
       <x:c r="H311" s="24" t="n">
         <x:f>IFERROR(F311/F310-1,"")</x:f>
-        <x:v>-0.02558820340453216</x:v>
+        <x:v>-0.035945595854922296</x:v>
       </x:c>
       <x:c r="I311" s="26" t="n">
         <x:f>ROUND(D311-E311,1)</x:f>
         <x:v>15820</x:v>
       </x:c>
       <x:c r="J311" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K311" s="22" t="n">
         <x:v>5</x:v>
@@ -18815,31 +18887,31 @@
         <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C312" s="23" t="n">
-        <x:v>181000</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="D312" s="23" t="n">
-        <x:v>182100</x:v>
+        <x:v>182940</x:v>
       </x:c>
       <x:c r="E312" s="23" t="n">
-        <x:v>157180</x:v>
+        <x:v>158140</x:v>
       </x:c>
       <x:c r="F312" s="23" t="n">
-        <x:v>164360</x:v>
+        <x:v>165460</x:v>
       </x:c>
       <x:c r="G312" s="28" t="n">
         <x:f>ROUND(F312-F311,1)</x:f>
-        <x:v>-15380</x:v>
+        <x:v>-13160</x:v>
       </x:c>
       <x:c r="H312" s="24" t="n">
         <x:f>IFERROR(F312/F311-1,"")</x:f>
-        <x:v>-0.08556804272838547</x:v>
+        <x:v>-0.07367596013884226</x:v>
       </x:c>
       <x:c r="I312" s="26" t="n">
         <x:f>ROUND(D312-E312,1)</x:f>
-        <x:v>24920</x:v>
+        <x:v>24800</x:v>
       </x:c>
       <x:c r="J312" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K312" s="22" t="n">
         <x:v>5</x:v>
@@ -18853,31 +18925,31 @@
         <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C313" s="23" t="n">
-        <x:v>161500</x:v>
+        <x:v>162800</x:v>
       </x:c>
       <x:c r="D313" s="23" t="n">
-        <x:v>178740</x:v>
+        <x:v>178860</x:v>
       </x:c>
       <x:c r="E313" s="23" t="n">
-        <x:v>160260</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="F313" s="23" t="n">
-        <x:v>175300</x:v>
+        <x:v>175780</x:v>
       </x:c>
       <x:c r="G313" s="28" t="n">
         <x:f>ROUND(F313-F312,1)</x:f>
-        <x:v>10940</x:v>
+        <x:v>10320</x:v>
       </x:c>
       <x:c r="H313" s="24" t="n">
         <x:f>IFERROR(F313/F312-1,"")</x:f>
-        <x:v>0.06656120710635194</x:v>
+        <x:v>0.06237157016801653</x:v>
       </x:c>
       <x:c r="I313" s="26" t="n">
         <x:f>ROUND(D313-E313,1)</x:f>
-        <x:v>18480</x:v>
+        <x:v>17580</x:v>
       </x:c>
       <x:c r="J313" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K313" s="22" t="n">
         <x:v>5</x:v>
@@ -18891,31 +18963,31 @@
         <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C314" s="23" t="n">
-        <x:v>177600</x:v>
+        <x:v>176460</x:v>
       </x:c>
       <x:c r="D314" s="23" t="n">
-        <x:v>177920</x:v>
+        <x:v>178560</x:v>
       </x:c>
       <x:c r="E314" s="23" t="n">
-        <x:v>160100</x:v>
+        <x:v>160560</x:v>
       </x:c>
       <x:c r="F314" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>161400</x:v>
       </x:c>
       <x:c r="G314" s="28" t="n">
         <x:f>ROUND(F314-F313,1)</x:f>
-        <x:v>-14800</x:v>
+        <x:v>-14380</x:v>
       </x:c>
       <x:c r="H314" s="24" t="n">
         <x:f>IFERROR(F314/F313-1,"")</x:f>
-        <x:v>-0.08442669709070161</x:v>
+        <x:v>-0.0818068039594948</x:v>
       </x:c>
       <x:c r="I314" s="26" t="n">
         <x:f>ROUND(D314-E314,1)</x:f>
-        <x:v>17820</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="J314" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K314" s="22" t="n">
         <x:v>4</x:v>
@@ -18929,31 +19001,31 @@
         <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C315" s="23" t="n">
-        <x:v>157220</x:v>
+        <x:v>161000</x:v>
       </x:c>
       <x:c r="D315" s="23" t="n">
-        <x:v>163940</x:v>
+        <x:v>163880</x:v>
       </x:c>
       <x:c r="E315" s="23" t="n">
-        <x:v>145000</x:v>
+        <x:v>145360</x:v>
       </x:c>
       <x:c r="F315" s="23" t="n">
-        <x:v>150220</x:v>
+        <x:v>151140</x:v>
       </x:c>
       <x:c r="G315" s="28" t="n">
         <x:f>ROUND(F315-F314,1)</x:f>
-        <x:v>-10280</x:v>
+        <x:v>-10260</x:v>
       </x:c>
       <x:c r="H315" s="24" t="n">
         <x:f>IFERROR(F315/F314-1,"")</x:f>
-        <x:v>-0.06404984423676008</x:v>
+        <x:v>-0.06356877323420074</x:v>
       </x:c>
       <x:c r="I315" s="26" t="n">
         <x:f>ROUND(D315-E315,1)</x:f>
-        <x:v>18940</x:v>
+        <x:v>18520</x:v>
       </x:c>
       <x:c r="J315" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K315" s="22" t="n">
         <x:v>5</x:v>
@@ -18967,31 +19039,31 @@
         <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C316" s="23" t="n">
-        <x:v>148000</x:v>
+        <x:v>148420</x:v>
       </x:c>
       <x:c r="D316" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>172120</x:v>
       </x:c>
       <x:c r="E316" s="23" t="n">
-        <x:v>145300</x:v>
+        <x:v>146000</x:v>
       </x:c>
       <x:c r="F316" s="23" t="n">
-        <x:v>168780</x:v>
+        <x:v>168600</x:v>
       </x:c>
       <x:c r="G316" s="28" t="n">
         <x:f>ROUND(F316-F315,1)</x:f>
-        <x:v>18560</x:v>
+        <x:v>17460</x:v>
       </x:c>
       <x:c r="H316" s="24" t="n">
         <x:f>IFERROR(F316/F315-1,"")</x:f>
-        <x:v>0.12355212355212353</x:v>
+        <x:v>0.1155220325526003</x:v>
       </x:c>
       <x:c r="I316" s="26" t="n">
         <x:f>ROUND(D316-E316,1)</x:f>
-        <x:v>26700</x:v>
+        <x:v>26120</x:v>
       </x:c>
       <x:c r="J316" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K316" s="22" t="n">
         <x:v>5</x:v>
@@ -19005,31 +19077,31 @@
         <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C317" s="23" t="n">
-        <x:v>166980</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="D317" s="23" t="n">
-        <x:v>168720</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="E317" s="23" t="n">
-        <x:v>150260</x:v>
+        <x:v>150860</x:v>
       </x:c>
       <x:c r="F317" s="23" t="n">
         <x:v>151600</x:v>
       </x:c>
       <x:c r="G317" s="28" t="n">
         <x:f>ROUND(F317-F316,1)</x:f>
-        <x:v>-17180</x:v>
+        <x:v>-17000</x:v>
       </x:c>
       <x:c r="H317" s="24" t="n">
         <x:f>IFERROR(F317/F316-1,"")</x:f>
-        <x:v>-0.10178931152980208</x:v>
+        <x:v>-0.10083036773428233</x:v>
       </x:c>
       <x:c r="I317" s="26" t="n">
         <x:f>ROUND(D317-E317,1)</x:f>
-        <x:v>18460</x:v>
+        <x:v>24040</x:v>
       </x:c>
       <x:c r="J317" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K317" s="22" t="n">
         <x:v>5</x:v>
@@ -19043,31 +19115,31 @@
         <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C318" s="23" t="n">
-        <x:v>150500</x:v>
+        <x:v>150300</x:v>
       </x:c>
       <x:c r="D318" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>155660</x:v>
       </x:c>
       <x:c r="E318" s="23" t="n">
-        <x:v>145860</x:v>
+        <x:v>145460</x:v>
       </x:c>
       <x:c r="F318" s="23" t="n">
-        <x:v>150140</x:v>
+        <x:v>149740</x:v>
       </x:c>
       <x:c r="G318" s="28" t="n">
         <x:f>ROUND(F318-F317,1)</x:f>
-        <x:v>-1460</x:v>
+        <x:v>-1860</x:v>
       </x:c>
       <x:c r="H318" s="24" t="n">
         <x:f>IFERROR(F318/F317-1,"")</x:f>
-        <x:v>-0.009630606860158264</x:v>
+        <x:v>-0.012269129287598934</x:v>
       </x:c>
       <x:c r="I318" s="26" t="n">
         <x:f>ROUND(D318-E318,1)</x:f>
-        <x:v>10640</x:v>
+        <x:v>10200</x:v>
       </x:c>
       <x:c r="J318" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K318" s="22" t="n">
         <x:v>5</x:v>
@@ -19081,31 +19153,31 @@
         <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C319" s="23" t="n">
-        <x:v>151500</x:v>
+        <x:v>152520</x:v>
       </x:c>
       <x:c r="D319" s="23" t="n">
-        <x:v>154800</x:v>
+        <x:v>153880</x:v>
       </x:c>
       <x:c r="E319" s="23" t="n">
-        <x:v>136800</x:v>
+        <x:v>135040</x:v>
       </x:c>
       <x:c r="F319" s="23" t="n">
-        <x:v>144280</x:v>
+        <x:v>142920</x:v>
       </x:c>
       <x:c r="G319" s="28" t="n">
         <x:f>ROUND(F319-F318,1)</x:f>
-        <x:v>-5860</x:v>
+        <x:v>-6820</x:v>
       </x:c>
       <x:c r="H319" s="24" t="n">
         <x:f>IFERROR(F319/F318-1,"")</x:f>
-        <x:v>-0.03903023844411879</x:v>
+        <x:v>-0.04554561239481769</x:v>
       </x:c>
       <x:c r="I319" s="26" t="n">
         <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>18000</x:v>
+        <x:v>18840</x:v>
       </x:c>
       <x:c r="J319" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K319" s="22" t="n">
         <x:v>5</x:v>
@@ -19119,31 +19191,31 @@
         <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C320" s="23" t="n">
-        <x:v>145780</x:v>
+        <x:v>144340</x:v>
       </x:c>
       <x:c r="D320" s="23" t="n">
-        <x:v>149400</x:v>
+        <x:v>148600</x:v>
       </x:c>
       <x:c r="E320" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="F320" s="23" t="n">
-        <x:v>137760</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="G320" s="28" t="n">
         <x:f>ROUND(F320-F319,1)</x:f>
-        <x:v>-6520</x:v>
+        <x:v>-5920</x:v>
       </x:c>
       <x:c r="H320" s="24" t="n">
         <x:f>IFERROR(F320/F319-1,"")</x:f>
-        <x:v>-0.04518990851122817</x:v>
+        <x:v>-0.04142177441925554</x:v>
       </x:c>
       <x:c r="I320" s="26" t="n">
         <x:f>ROUND(D320-E320,1)</x:f>
-        <x:v>11640</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="J320" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K320" s="22" t="n">
         <x:v>5</x:v>
@@ -19157,31 +19229,31 @@
         <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C321" s="23" t="n">
-        <x:v>137500</x:v>
+        <x:v>137200</x:v>
       </x:c>
       <x:c r="D321" s="23" t="n">
-        <x:v>144800</x:v>
+        <x:v>144100</x:v>
       </x:c>
       <x:c r="E321" s="23" t="n">
-        <x:v>135560</x:v>
+        <x:v>135040</x:v>
       </x:c>
       <x:c r="F321" s="23" t="n">
-        <x:v>140000</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="G321" s="28" t="n">
         <x:f>ROUND(F321-F320,1)</x:f>
-        <x:v>2240</x:v>
+        <x:v>2320</x:v>
       </x:c>
       <x:c r="H321" s="24" t="n">
         <x:f>IFERROR(F321/F320-1,"")</x:f>
-        <x:v>0.016260162601626105</x:v>
+        <x:v>0.016934306569343027</x:v>
       </x:c>
       <x:c r="I321" s="26" t="n">
         <x:f>ROUND(D321-E321,1)</x:f>
-        <x:v>9240</x:v>
+        <x:v>9060</x:v>
       </x:c>
       <x:c r="J321" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K321" s="22" t="n">
         <x:v>5</x:v>
@@ -19195,31 +19267,31 @@
         <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C322" s="23" t="n">
-        <x:v>140500</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="D322" s="23" t="n">
-        <x:v>154500</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="E322" s="23" t="n">
-        <x:v>139280</x:v>
+        <x:v>139300</x:v>
       </x:c>
       <x:c r="F322" s="23" t="n">
-        <x:v>153940</x:v>
+        <x:v>153980</x:v>
       </x:c>
       <x:c r="G322" s="28" t="n">
         <x:f>ROUND(F322-F321,1)</x:f>
-        <x:v>13940</x:v>
+        <x:v>14660</x:v>
       </x:c>
       <x:c r="H322" s="24" t="n">
         <x:f>IFERROR(F322/F321-1,"")</x:f>
-        <x:v>0.09957142857142864</x:v>
+        <x:v>0.10522538041917895</x:v>
       </x:c>
       <x:c r="I322" s="26" t="n">
         <x:f>ROUND(D322-E322,1)</x:f>
-        <x:v>15220</x:v>
+        <x:v>15260</x:v>
       </x:c>
       <x:c r="J322" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K322" s="22" t="n">
         <x:v>5</x:v>
@@ -19233,31 +19305,31 @@
         <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C323" s="23" t="n">
-        <x:v>154300</x:v>
+        <x:v>152940</x:v>
       </x:c>
       <x:c r="D323" s="23" t="n">
-        <x:v>157000</x:v>
+        <x:v>157400</x:v>
       </x:c>
       <x:c r="E323" s="23" t="n">
-        <x:v>148400</x:v>
+        <x:v>148700</x:v>
       </x:c>
       <x:c r="F323" s="23" t="n">
-        <x:v>156140</x:v>
+        <x:v>156380</x:v>
       </x:c>
       <x:c r="G323" s="28" t="n">
         <x:f>ROUND(F323-F322,1)</x:f>
-        <x:v>2200</x:v>
+        <x:v>2400</x:v>
       </x:c>
       <x:c r="H323" s="24" t="n">
         <x:f>IFERROR(F323/F322-1,"")</x:f>
-        <x:v>0.014291282317786091</x:v>
+        <x:v>0.015586439797376173</x:v>
       </x:c>
       <x:c r="I323" s="26" t="n">
         <x:f>ROUND(D323-E323,1)</x:f>
-        <x:v>8600</x:v>
+        <x:v>8700</x:v>
       </x:c>
       <x:c r="J323" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K323" s="22" t="n">
         <x:v>5</x:v>
@@ -19271,31 +19343,31 @@
         <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C324" s="23" t="n">
-        <x:v>158500</x:v>
+        <x:v>158800</x:v>
       </x:c>
       <x:c r="D324" s="23" t="n">
-        <x:v>160000</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="E324" s="23" t="n">
-        <x:v>147000</x:v>
+        <x:v>147600</x:v>
       </x:c>
       <x:c r="F324" s="23" t="n">
-        <x:v>157080</x:v>
+        <x:v>157940</x:v>
       </x:c>
       <x:c r="G324" s="28" t="n">
         <x:f>ROUND(F324-F323,1)</x:f>
-        <x:v>940</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="H324" s="24" t="n">
         <x:f>IFERROR(F324/F323-1,"")</x:f>
-        <x:v>0.0060202382477263505</x:v>
+        <x:v>0.009975700217419003</x:v>
       </x:c>
       <x:c r="I324" s="26" t="n">
         <x:f>ROUND(D324-E324,1)</x:f>
-        <x:v>13000</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="J324" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K324" s="22" t="n">
         <x:v>5</x:v>
@@ -19309,31 +19381,31 @@
         <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C325" s="23" t="n">
-        <x:v>158000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D325" s="23" t="n">
-        <x:v>160480</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="E325" s="23" t="n">
-        <x:v>140940</x:v>
+        <x:v>140220</x:v>
       </x:c>
       <x:c r="F325" s="23" t="n">
-        <x:v>140980</x:v>
+        <x:v>142000</x:v>
       </x:c>
       <x:c r="G325" s="28" t="n">
         <x:f>ROUND(F325-F324,1)</x:f>
-        <x:v>-16100</x:v>
+        <x:v>-15940</x:v>
       </x:c>
       <x:c r="H325" s="24" t="n">
         <x:f>IFERROR(F325/F324-1,"")</x:f>
-        <x:v>-0.1024955436720143</x:v>
+        <x:v>-0.10092440167152084</x:v>
       </x:c>
       <x:c r="I325" s="26" t="n">
         <x:f>ROUND(D325-E325,1)</x:f>
-        <x:v>19540</x:v>
+        <x:v>21060</x:v>
       </x:c>
       <x:c r="J325" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K325" s="22" t="n">
         <x:v>5</x:v>
@@ -19347,31 +19419,31 @@
         <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C326" s="23" t="n">
-        <x:v>142120</x:v>
+        <x:v>141000</x:v>
       </x:c>
       <x:c r="D326" s="23" t="n">
-        <x:v>143200</x:v>
+        <x:v>143540</x:v>
       </x:c>
       <x:c r="E326" s="23" t="n">
-        <x:v>131900</x:v>
+        <x:v>127120</x:v>
       </x:c>
       <x:c r="F326" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>134340</x:v>
       </x:c>
       <x:c r="G326" s="28" t="n">
         <x:f>ROUND(F326-F325,1)</x:f>
-        <x:v>-5480</x:v>
+        <x:v>-7660</x:v>
       </x:c>
       <x:c r="H326" s="24" t="n">
         <x:f>IFERROR(F326/F325-1,"")</x:f>
-        <x:v>-0.038870761810185894</x:v>
+        <x:v>-0.05394366197183098</x:v>
       </x:c>
       <x:c r="I326" s="26" t="n">
         <x:f>ROUND(D326-E326,1)</x:f>
-        <x:v>11300</x:v>
+        <x:v>16420</x:v>
       </x:c>
       <x:c r="J326" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K326" s="22" t="n">
         <x:v>5</x:v>
@@ -19382,37 +19454,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B327" s="22" t="str">
-        <x:v>9月14日</x:v>
+        <x:v>9月14日-9月16日</x:v>
       </x:c>
       <x:c r="C327" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>133600</x:v>
       </x:c>
       <x:c r="D327" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>134840</x:v>
       </x:c>
       <x:c r="E327" s="23" t="n">
-        <x:v>135500</x:v>
+        <x:v>126200</x:v>
       </x:c>
       <x:c r="F327" s="23" t="n">
-        <x:v>135500</x:v>
-      </x:c>
-      <x:c r="G327" s="23" t="n">
+        <x:v>127460</x:v>
+      </x:c>
+      <x:c r="G327" s="28" t="n">
         <x:f>ROUND(F327-F326,1)</x:f>
-        <x:v>0</x:v>
+        <x:v>-6880</x:v>
       </x:c>
       <x:c r="H327" s="24" t="n">
         <x:f>IFERROR(F327/F326-1,"")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I327" s="23" t="n">
+        <x:v>-0.051213339288372794</x:v>
+      </x:c>
+      <x:c r="I327" s="26" t="n">
         <x:f>ROUND(D327-E327,1)</x:f>
-        <x:v>0</x:v>
+        <x:v>8640</x:v>
       </x:c>
       <x:c r="J327" s="22" t="str">
-        <x:v>LC2609</x:v>
+        <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K327" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="328">
@@ -19430,7 +19502,7 @@
       <x:c r="H328" s="30"/>
       <x:c r="I328" s="32" t="n">
         <x:f>ROUND(SUM(I292:I327),1)</x:f>
-        <x:v>720520</x:v>
+        <x:v>740340</x:v>
       </x:c>
       <x:c r="J328" s="30"/>
       <x:c r="K328" s="30"/>
@@ -19448,7 +19520,7 @@
       <x:c r="H329" s="30"/>
       <x:c r="I329" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I292:I327),0),1)</x:f>
-        <x:v>20014.4</x:v>
+        <x:v>20565</x:v>
       </x:c>
       <x:c r="J329" s="30"/>
       <x:c r="K329" s="30"/>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R676b62e0eaa54700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R62ce6d5f6df84fe3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R22361924cb60450f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Re43b6e0dddbb4dde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R1c065f3117f04a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R4f5e6c1a7b4d4f77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rdce5b2dabb224a59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Reef1aada8fa349ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R5fd501c33fdd4dea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R1f18088bf2c147a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rbed6022c632a4d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rb6c175a6cbec4cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R8c0c820ff7e94b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc448077ec74c4744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R20160eb606df400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R92de8ed3425d4c37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R88d7565265f74ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R3e5078662c584240"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R993b509db6a54b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rb08ddfdb71a04c23"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7607.89</x:v>
+        <x:v>7632.53</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7402.37</x:v>
+        <x:v>7522.77</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>205.5</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>30418.1</x:v>
+        <x:v>30527.9</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>176.8</x:v>
+        <x:v>176.5</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7696.47</x:v>
+        <x:v>7738.03</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7523.82</x:v>
+        <x:v>7622.55</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>172.7</x:v>
+        <x:v>115.5</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>30285.8</x:v>
+        <x:v>30401.3</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>176.1</x:v>
+        <x:v>175.7</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3894.66</x:v>
+        <x:v>3898.84</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3842.72</x:v>
+        <x:v>3866.89</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>51.9</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8314.4</x:v>
+        <x:v>8346.4</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>48.3</x:v>
+        <x:v>48.2</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>130660</x:v>
+        <x:v>133760</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>126200</x:v>
+        <x:v>127900</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>4460</x:v>
+        <x:v>5860</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1385840</x:v>
+        <x:v>1391700</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8057.2</x:v>
+        <x:v>8044.5</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -7849,30 +7849,48 @@
       </x:c>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B217" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C217" s="30"/>
-      <x:c r="D217" s="30"/>
-      <x:c r="E217" s="30"/>
-      <x:c r="F217" s="30"/>
-      <x:c r="G217" s="30"/>
-      <x:c r="H217" s="30"/>
-      <x:c r="I217" s="30"/>
-      <x:c r="J217" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J216),1)</x:f>
-        <x:v>67360</x:v>
-      </x:c>
-      <x:c r="K217" s="30"/>
+      <x:c r="A217" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B217" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C217" s="22" t="str">
+        <x:v>9月17日</x:v>
+      </x:c>
+      <x:c r="D217" s="23" t="n">
+        <x:v>129900</x:v>
+      </x:c>
+      <x:c r="E217" s="23" t="n">
+        <x:v>133760</x:v>
+      </x:c>
+      <x:c r="F217" s="23" t="n">
+        <x:v>127900</x:v>
+      </x:c>
+      <x:c r="G217" s="23" t="n">
+        <x:v>132280</x:v>
+      </x:c>
+      <x:c r="H217" s="28" t="n">
+        <x:v>4820</x:v>
+      </x:c>
+      <x:c r="I217" s="24" t="n">
+        <x:v>0.03781578534442187</x:v>
+      </x:c>
+      <x:c r="J217" s="23" t="n">
+        <x:f>ROUND(E217-F217,1)</x:f>
+        <x:v>5860</x:v>
+      </x:c>
+      <x:c r="K217" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B218" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B218" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C218" s="30"/>
       <x:c r="D218" s="30"/>
       <x:c r="E218" s="30"/>
@@ -7880,11 +7898,29 @@
       <x:c r="G218" s="30"/>
       <x:c r="H218" s="30"/>
       <x:c r="I218" s="30"/>
-      <x:c r="J218" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
-        <x:v>5613.3</x:v>
+      <x:c r="J218" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J217),1)</x:f>
+        <x:v>73220</x:v>
       </x:c>
       <x:c r="K218" s="30"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B219" s="30"/>
+      <x:c r="C219" s="30"/>
+      <x:c r="D219" s="30"/>
+      <x:c r="E219" s="30"/>
+      <x:c r="F219" s="30"/>
+      <x:c r="G219" s="30"/>
+      <x:c r="H219" s="30"/>
+      <x:c r="I219" s="30"/>
+      <x:c r="J219" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
+        <x:v>5632.3</x:v>
+      </x:c>
+      <x:c r="K219" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9304,37 +9340,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" s="22" t="str">
-        <x:v>9月14日-9月16日</x:v>
+        <x:v>9月14日-9月17日</x:v>
       </x:c>
       <x:c r="C40" s="23" t="n">
         <x:v>7363.42</x:v>
       </x:c>
       <x:c r="D40" s="23" t="n">
-        <x:v>7607.89</x:v>
+        <x:v>7632.53</x:v>
       </x:c>
       <x:c r="E40" s="23" t="n">
         <x:v>7329.6</x:v>
       </x:c>
       <x:c r="F40" s="23" t="n">
-        <x:v>7587.43</x:v>
-      </x:c>
-      <x:c r="G40" s="28" t="n">
+        <x:v>7548.82</x:v>
+      </x:c>
+      <x:c r="G40" s="23" t="n">
         <x:f>ROUND(F40-F39,1)</x:f>
-        <x:v>160.2</x:v>
+        <x:v>121.6</x:v>
       </x:c>
       <x:c r="H40" s="24" t="n">
         <x:f>IFERROR(F40/F39-1,"")</x:f>
-        <x:v>0.021567904093579893</x:v>
+        <x:v>0.01636947237466413</x:v>
       </x:c>
       <x:c r="I40" s="26" t="n">
         <x:f>ROUND(D40-E40,1)</x:f>
-        <x:v>278.3</x:v>
+        <x:v>302.9</x:v>
       </x:c>
       <x:c r="J40" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K40" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -9352,7 +9388,7 @@
       <x:c r="H41" s="30"/>
       <x:c r="I41" s="32" t="n">
         <x:f>ROUND(SUM(I5:I40),1)</x:f>
-        <x:v>14974.9</x:v>
+        <x:v>14999.5</x:v>
       </x:c>
       <x:c r="J41" s="30"/>
       <x:c r="K41" s="30"/>
@@ -9370,7 +9406,7 @@
       <x:c r="H42" s="30"/>
       <x:c r="I42" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I40),0),1)</x:f>
-        <x:v>416</x:v>
+        <x:v>416.7</x:v>
       </x:c>
       <x:c r="J42" s="30"/>
       <x:c r="K42" s="30"/>
@@ -10754,37 +10790,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B81" s="22" t="str">
-        <x:v>9月14日-9月16日</x:v>
+        <x:v>9月14日-9月17日</x:v>
       </x:c>
       <x:c r="C81" s="23" t="n">
         <x:v>7511.04</x:v>
       </x:c>
       <x:c r="D81" s="23" t="n">
-        <x:v>7696.47</x:v>
+        <x:v>7738.03</x:v>
       </x:c>
       <x:c r="E81" s="23" t="n">
         <x:v>7487.46</x:v>
       </x:c>
       <x:c r="F81" s="23" t="n">
-        <x:v>7683.47</x:v>
+        <x:v>7654.98</x:v>
       </x:c>
       <x:c r="G81" s="23" t="n">
         <x:f>ROUND(F81-F80,1)</x:f>
-        <x:v>102.9</x:v>
+        <x:v>74.4</x:v>
       </x:c>
       <x:c r="H81" s="24" t="n">
         <x:f>IFERROR(F81/F80-1,"")</x:f>
-        <x:v>0.013578188361251353</x:v>
+        <x:v>0.009819880905581835</x:v>
       </x:c>
       <x:c r="I81" s="26" t="n">
         <x:f>ROUND(D81-E81,1)</x:f>
-        <x:v>209</x:v>
+        <x:v>250.6</x:v>
       </x:c>
       <x:c r="J81" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K81" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -10802,7 +10838,7 @@
       <x:c r="H82" s="30"/>
       <x:c r="I82" s="32" t="n">
         <x:f>ROUND(SUM(I46:I81),1)</x:f>
-        <x:v>14927</x:v>
+        <x:v>14968.6</x:v>
       </x:c>
       <x:c r="J82" s="30"/>
       <x:c r="K82" s="30"/>
@@ -10820,7 +10856,7 @@
       <x:c r="H83" s="30"/>
       <x:c r="I83" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I46:I81),0),1)</x:f>
-        <x:v>414.6</x:v>
+        <x:v>415.8</x:v>
       </x:c>
       <x:c r="J83" s="30"/>
       <x:c r="K83" s="30"/>
@@ -12204,37 +12240,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B122" s="22" t="str">
-        <x:v>9月14日-9月16日</x:v>
+        <x:v>9月14日-9月17日</x:v>
       </x:c>
       <x:c r="C122" s="23" t="n">
         <x:v>3867.02</x:v>
       </x:c>
       <x:c r="D122" s="23" t="n">
-        <x:v>3895.51</x:v>
+        <x:v>3898.84</x:v>
       </x:c>
       <x:c r="E122" s="23" t="n">
         <x:v>3842.72</x:v>
       </x:c>
       <x:c r="F122" s="23" t="n">
-        <x:v>3891.6</x:v>
+        <x:v>3875.6</x:v>
       </x:c>
       <x:c r="G122" s="23" t="n">
         <x:f>ROUND(F122-F121,1)</x:f>
-        <x:v>3.5</x:v>
+        <x:v>-12.5</x:v>
       </x:c>
       <x:c r="H122" s="24" t="n">
         <x:f>IFERROR(F122/F121-1,"")</x:f>
-        <x:v>0.0008976083495579879</x:v>
+        <x:v>-0.0032175015624558156</x:v>
       </x:c>
       <x:c r="I122" s="26" t="n">
         <x:f>ROUND(D122-E122,1)</x:f>
-        <x:v>52.8</x:v>
+        <x:v>56.1</x:v>
       </x:c>
       <x:c r="J122" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K122" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -12252,7 +12288,7 @@
       <x:c r="H123" s="30"/>
       <x:c r="I123" s="32" t="n">
         <x:f>ROUND(SUM(I87:I122),1)</x:f>
-        <x:v>3916.9</x:v>
+        <x:v>3920.2</x:v>
       </x:c>
       <x:c r="J123" s="30"/>
       <x:c r="K123" s="30"/>
@@ -12270,7 +12306,7 @@
       <x:c r="H124" s="30"/>
       <x:c r="I124" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I87:I122),0),1)</x:f>
-        <x:v>108.8</x:v>
+        <x:v>108.9</x:v>
       </x:c>
       <x:c r="J124" s="30"/>
       <x:c r="K124" s="30"/>
@@ -19454,7 +19490,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B327" s="22" t="str">
-        <x:v>9月14日-9月16日</x:v>
+        <x:v>9月14日-9月17日</x:v>
       </x:c>
       <x:c r="C327" s="23" t="n">
         <x:v>133600</x:v>
@@ -19466,15 +19502,15 @@
         <x:v>126200</x:v>
       </x:c>
       <x:c r="F327" s="23" t="n">
-        <x:v>127460</x:v>
+        <x:v>132280</x:v>
       </x:c>
       <x:c r="G327" s="28" t="n">
         <x:f>ROUND(F327-F326,1)</x:f>
-        <x:v>-6880</x:v>
+        <x:v>-2060</x:v>
       </x:c>
       <x:c r="H327" s="24" t="n">
         <x:f>IFERROR(F327/F326-1,"")</x:f>
-        <x:v>-0.051213339288372794</x:v>
+        <x:v>-0.015334226589251099</x:v>
       </x:c>
       <x:c r="I327" s="26" t="n">
         <x:f>ROUND(D327-E327,1)</x:f>
@@ -19484,7 +19520,7 @@
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K327" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="328">
@@ -26510,30 +26546,48 @@
       </x:c>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B217" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C217" s="30"/>
-      <x:c r="D217" s="30"/>
-      <x:c r="E217" s="30"/>
-      <x:c r="F217" s="30"/>
-      <x:c r="G217" s="30"/>
-      <x:c r="H217" s="30"/>
-      <x:c r="I217" s="30"/>
-      <x:c r="J217" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J216),1)</x:f>
-        <x:v>1687.3</x:v>
-      </x:c>
-      <x:c r="K217" s="30"/>
+      <x:c r="A217" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B217" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C217" s="22" t="str">
+        <x:v>9月17日</x:v>
+      </x:c>
+      <x:c r="D217" s="23" t="n">
+        <x:v>7555.79</x:v>
+      </x:c>
+      <x:c r="E217" s="23" t="n">
+        <x:v>7632.53</x:v>
+      </x:c>
+      <x:c r="F217" s="23" t="n">
+        <x:v>7522.77</x:v>
+      </x:c>
+      <x:c r="G217" s="23" t="n">
+        <x:v>7548.82</x:v>
+      </x:c>
+      <x:c r="H217" s="23" t="n">
+        <x:v>-38.6</x:v>
+      </x:c>
+      <x:c r="I217" s="24" t="n">
+        <x:v>-0.005088679566071841</x:v>
+      </x:c>
+      <x:c r="J217" s="23" t="n">
+        <x:f>ROUND(E217-F217,1)</x:f>
+        <x:v>109.8</x:v>
+      </x:c>
+      <x:c r="K217" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B218" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B218" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C218" s="30"/>
       <x:c r="D218" s="30"/>
       <x:c r="E218" s="30"/>
@@ -26541,11 +26595,29 @@
       <x:c r="G218" s="30"/>
       <x:c r="H218" s="30"/>
       <x:c r="I218" s="30"/>
-      <x:c r="J218" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
-        <x:v>140.6</x:v>
+      <x:c r="J218" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J217),1)</x:f>
+        <x:v>1797.1</x:v>
       </x:c>
       <x:c r="K218" s="30"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B219" s="30"/>
+      <x:c r="C219" s="30"/>
+      <x:c r="D219" s="30"/>
+      <x:c r="E219" s="30"/>
+      <x:c r="F219" s="30"/>
+      <x:c r="G219" s="30"/>
+      <x:c r="H219" s="30"/>
+      <x:c r="I219" s="30"/>
+      <x:c r="J219" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
+        <x:v>138.2</x:v>
+      </x:c>
+      <x:c r="K219" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -33533,30 +33605,48 @@
       </x:c>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B217" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C217" s="30"/>
-      <x:c r="D217" s="30"/>
-      <x:c r="E217" s="30"/>
-      <x:c r="F217" s="30"/>
-      <x:c r="G217" s="30"/>
-      <x:c r="H217" s="30"/>
-      <x:c r="I217" s="30"/>
-      <x:c r="J217" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J216),1)</x:f>
-        <x:v>1502.1</x:v>
-      </x:c>
-      <x:c r="K217" s="30"/>
+      <x:c r="A217" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B217" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C217" s="22" t="str">
+        <x:v>9月17日</x:v>
+      </x:c>
+      <x:c r="D217" s="23" t="n">
+        <x:v>7651.46</x:v>
+      </x:c>
+      <x:c r="E217" s="23" t="n">
+        <x:v>7738.03</x:v>
+      </x:c>
+      <x:c r="F217" s="23" t="n">
+        <x:v>7622.55</x:v>
+      </x:c>
+      <x:c r="G217" s="23" t="n">
+        <x:v>7654.98</x:v>
+      </x:c>
+      <x:c r="H217" s="23" t="n">
+        <x:v>-28.5</x:v>
+      </x:c>
+      <x:c r="I217" s="24" t="n">
+        <x:v>-0.0037079600753305852</x:v>
+      </x:c>
+      <x:c r="J217" s="23" t="n">
+        <x:f>ROUND(E217-F217,1)</x:f>
+        <x:v>115.5</x:v>
+      </x:c>
+      <x:c r="K217" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B218" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B218" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C218" s="30"/>
       <x:c r="D218" s="30"/>
       <x:c r="E218" s="30"/>
@@ -33564,11 +33654,29 @@
       <x:c r="G218" s="30"/>
       <x:c r="H218" s="30"/>
       <x:c r="I218" s="30"/>
-      <x:c r="J218" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
-        <x:v>125.2</x:v>
+      <x:c r="J218" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J217),1)</x:f>
+        <x:v>1617.6</x:v>
       </x:c>
       <x:c r="K218" s="30"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B219" s="30"/>
+      <x:c r="C219" s="30"/>
+      <x:c r="D219" s="30"/>
+      <x:c r="E219" s="30"/>
+      <x:c r="F219" s="30"/>
+      <x:c r="G219" s="30"/>
+      <x:c r="H219" s="30"/>
+      <x:c r="I219" s="30"/>
+      <x:c r="J219" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
+        <x:v>124.4</x:v>
+      </x:c>
+      <x:c r="K219" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -40556,30 +40664,48 @@
       </x:c>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B217" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C217" s="30"/>
-      <x:c r="D217" s="30"/>
-      <x:c r="E217" s="30"/>
-      <x:c r="F217" s="30"/>
-      <x:c r="G217" s="30"/>
-      <x:c r="H217" s="30"/>
-      <x:c r="I217" s="30"/>
-      <x:c r="J217" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J216),1)</x:f>
-        <x:v>433.3</x:v>
-      </x:c>
-      <x:c r="K217" s="30"/>
+      <x:c r="A217" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B217" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C217" s="22" t="str">
+        <x:v>9月17日</x:v>
+      </x:c>
+      <x:c r="D217" s="23" t="n">
+        <x:v>3877</x:v>
+      </x:c>
+      <x:c r="E217" s="23" t="n">
+        <x:v>3898.84</x:v>
+      </x:c>
+      <x:c r="F217" s="23" t="n">
+        <x:v>3866.89</x:v>
+      </x:c>
+      <x:c r="G217" s="23" t="n">
+        <x:v>3875.6</x:v>
+      </x:c>
+      <x:c r="H217" s="23" t="n">
+        <x:v>-16</x:v>
+      </x:c>
+      <x:c r="I217" s="24" t="n">
+        <x:v>-0.004111419467571209</x:v>
+      </x:c>
+      <x:c r="J217" s="23" t="n">
+        <x:f>ROUND(E217-F217,1)</x:f>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K217" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B218" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B218" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C218" s="30"/>
       <x:c r="D218" s="30"/>
       <x:c r="E218" s="30"/>
@@ -40587,11 +40713,29 @@
       <x:c r="G218" s="30"/>
       <x:c r="H218" s="30"/>
       <x:c r="I218" s="30"/>
-      <x:c r="J218" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
-        <x:v>36.1</x:v>
+      <x:c r="J218" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J217),1)</x:f>
+        <x:v>465.3</x:v>
       </x:c>
       <x:c r="K218" s="30"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B219" s="30"/>
+      <x:c r="C219" s="30"/>
+      <x:c r="D219" s="30"/>
+      <x:c r="E219" s="30"/>
+      <x:c r="F219" s="30"/>
+      <x:c r="G219" s="30"/>
+      <x:c r="H219" s="30"/>
+      <x:c r="I219" s="30"/>
+      <x:c r="J219" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
+        <x:v>35.8</x:v>
+      </x:c>
+      <x:c r="K219" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rbed6022c632a4d07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rb6c175a6cbec4cdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R8c0c820ff7e94b31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc448077ec74c4744"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R20160eb606df400e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R92de8ed3425d4c37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R88d7565265f74ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R3e5078662c584240"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R993b509db6a54b5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rb08ddfdb71a04c23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R0c4007267ed74108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R29c2bbdd5b4b4f93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rd6d670baebcd4ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rdbea9e06e2b34951"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R57f1230161084054"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R1afe4bf18f8642d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rf78b450e485345b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2a97765699a44142"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rd4ab9f60afa24762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R416dfef56a36425a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7623.6</x:v>
+        <x:v>7648</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7401.6</x:v>
+        <x:v>7522.2</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>222</x:v>
+        <x:v>125.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>32332.4</x:v>
+        <x:v>32458.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>188</x:v>
+        <x:v>187.6</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7710</x:v>
+        <x:v>7754</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7516.2</x:v>
+        <x:v>7617.2</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>193.8</x:v>
+        <x:v>136.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>33518.6</x:v>
+        <x:v>33655.4</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>194.9</x:v>
+        <x:v>194.5</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4487</x:v>
+        <x:v>4500.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4412.2</x:v>
+        <x:v>4452.2</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>74.8</x:v>
+        <x:v>48.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12535.6</x:v>
+        <x:v>12584</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.9</x:v>
+        <x:v>72.7</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-17</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2872.4</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2829.4</x:v>
+        <x:v>2838.4</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>43.8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>6957.6</x:v>
+        <x:v>6991.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.5</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -13690,37 +13690,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B163" s="22" t="str">
-        <x:v>9月14日-9月16日</x:v>
+        <x:v>9月14日-9月17日</x:v>
       </x:c>
       <x:c r="C163" s="23" t="n">
         <x:v>7312</x:v>
       </x:c>
       <x:c r="D163" s="23" t="n">
-        <x:v>7623.6</x:v>
+        <x:v>7648</x:v>
       </x:c>
       <x:c r="E163" s="23" t="n">
         <x:v>7283.4</x:v>
       </x:c>
       <x:c r="F163" s="23" t="n">
-        <x:v>7593</x:v>
-      </x:c>
-      <x:c r="G163" s="28" t="n">
+        <x:v>7559.8</x:v>
+      </x:c>
+      <x:c r="G163" s="23" t="n">
         <x:f>ROUND(F163-F162,1)</x:f>
-        <x:v>177.8</x:v>
+        <x:v>144.6</x:v>
       </x:c>
       <x:c r="H163" s="24" t="n">
         <x:f>IFERROR(F163/F162-1,"")</x:f>
-        <x:v>0.02397777538029988</x:v>
+        <x:v>0.019500485489265307</x:v>
       </x:c>
       <x:c r="I163" s="26" t="n">
         <x:f>ROUND(D163-E163,1)</x:f>
-        <x:v>340.2</x:v>
+        <x:v>364.6</x:v>
       </x:c>
       <x:c r="J163" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K163" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -13738,7 +13738,7 @@
       <x:c r="H164" s="30"/>
       <x:c r="I164" s="32" t="n">
         <x:f>ROUND(SUM(I128:I163),1)</x:f>
-        <x:v>15624</x:v>
+        <x:v>15648.4</x:v>
       </x:c>
       <x:c r="J164" s="30"/>
       <x:c r="K164" s="30"/>
@@ -13756,7 +13756,7 @@
       <x:c r="H165" s="30"/>
       <x:c r="I165" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I128:I163),0),1)</x:f>
-        <x:v>434</x:v>
+        <x:v>434.7</x:v>
       </x:c>
       <x:c r="J165" s="30"/>
       <x:c r="K165" s="30"/>
@@ -15140,37 +15140,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B204" s="22" t="str">
-        <x:v>9月14日-9月16日</x:v>
+        <x:v>9月14日-9月17日</x:v>
       </x:c>
       <x:c r="C204" s="23" t="n">
         <x:v>7482.2</x:v>
       </x:c>
       <x:c r="D204" s="23" t="n">
-        <x:v>7710</x:v>
+        <x:v>7754</x:v>
       </x:c>
       <x:c r="E204" s="23" t="n">
         <x:v>7452.2</x:v>
       </x:c>
       <x:c r="F204" s="23" t="n">
-        <x:v>7689.6</x:v>
+        <x:v>7664.6</x:v>
       </x:c>
       <x:c r="G204" s="23" t="n">
         <x:f>ROUND(F204-F203,1)</x:f>
-        <x:v>120.6</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="H204" s="24" t="n">
         <x:f>IFERROR(F204/F203-1,"")</x:f>
-        <x:v>0.015933412604042907</x:v>
+        <x:v>0.01263046637600751</x:v>
       </x:c>
       <x:c r="I204" s="26" t="n">
         <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>257.8</x:v>
+        <x:v>301.8</x:v>
       </x:c>
       <x:c r="J204" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K204" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -15188,7 +15188,7 @@
       <x:c r="H205" s="30"/>
       <x:c r="I205" s="32" t="n">
         <x:f>ROUND(SUM(I169:I204),1)</x:f>
-        <x:v>16083.2</x:v>
+        <x:v>16127.2</x:v>
       </x:c>
       <x:c r="J205" s="30"/>
       <x:c r="K205" s="30"/>
@@ -15206,7 +15206,7 @@
       <x:c r="H206" s="30"/>
       <x:c r="I206" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I169:I204),0),1)</x:f>
-        <x:v>446.8</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="J206" s="30"/>
       <x:c r="K206" s="30"/>
@@ -16590,7 +16590,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B245" s="22" t="str">
-        <x:v>9月14日-9月16日</x:v>
+        <x:v>9月14日-9月17日</x:v>
       </x:c>
       <x:c r="C245" s="23" t="n">
         <x:v>4468</x:v>
@@ -16602,15 +16602,15 @@
         <x:v>4412.2</x:v>
       </x:c>
       <x:c r="F245" s="23" t="n">
-        <x:v>4478</x:v>
+        <x:v>4460.2</x:v>
       </x:c>
       <x:c r="G245" s="23" t="n">
         <x:f>ROUND(F245-F244,1)</x:f>
-        <x:v>-25.4</x:v>
+        <x:v>-43.2</x:v>
       </x:c>
       <x:c r="H245" s="24" t="n">
         <x:f>IFERROR(F245/F244-1,"")</x:f>
-        <x:v>-0.005640182972864838</x:v>
+        <x:v>-0.0095927521428254</x:v>
       </x:c>
       <x:c r="I245" s="23" t="n">
         <x:f>ROUND(D245-E245,1)</x:f>
@@ -16620,7 +16620,7 @@
         <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K245" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
@@ -18040,7 +18040,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B286" s="22" t="str">
-        <x:v>9月14日-9月16日</x:v>
+        <x:v>9月14日-9月17日</x:v>
       </x:c>
       <x:c r="C286" s="23" t="n">
         <x:v>2849.2</x:v>
@@ -18052,15 +18052,15 @@
         <x:v>2829.4</x:v>
       </x:c>
       <x:c r="F286" s="23" t="n">
-        <x:v>2865</x:v>
+        <x:v>2845.8</x:v>
       </x:c>
       <x:c r="G286" s="23" t="n">
         <x:f>ROUND(F286-F285,1)</x:f>
-        <x:v>-2</x:v>
+        <x:v>-21.2</x:v>
       </x:c>
       <x:c r="H286" s="24" t="n">
         <x:f>IFERROR(F286/F285-1,"")</x:f>
-        <x:v>-0.0006975933031042603</x:v>
+        <x:v>-0.007394489012905403</x:v>
       </x:c>
       <x:c r="I286" s="23" t="n">
         <x:f>ROUND(D286-E286,1)</x:f>
@@ -18070,7 +18070,7 @@
         <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K286" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -47723,30 +47723,48 @@
       </x:c>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B217" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C217" s="30"/>
-      <x:c r="D217" s="30"/>
-      <x:c r="E217" s="30"/>
-      <x:c r="F217" s="30"/>
-      <x:c r="G217" s="30"/>
-      <x:c r="H217" s="30"/>
-      <x:c r="I217" s="30"/>
-      <x:c r="J217" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J216),1)</x:f>
-        <x:v>1888.6</x:v>
-      </x:c>
-      <x:c r="K217" s="30"/>
+      <x:c r="A217" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B217" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C217" s="22" t="str">
+        <x:v>9月17日</x:v>
+      </x:c>
+      <x:c r="D217" s="23" t="n">
+        <x:v>7570</x:v>
+      </x:c>
+      <x:c r="E217" s="23" t="n">
+        <x:v>7648</x:v>
+      </x:c>
+      <x:c r="F217" s="23" t="n">
+        <x:v>7522.2</x:v>
+      </x:c>
+      <x:c r="G217" s="23" t="n">
+        <x:v>7559.8</x:v>
+      </x:c>
+      <x:c r="H217" s="23" t="n">
+        <x:v>-33.2</x:v>
+      </x:c>
+      <x:c r="I217" s="24" t="n">
+        <x:v>-0.004372448307651711</x:v>
+      </x:c>
+      <x:c r="J217" s="23" t="n">
+        <x:f>ROUND(E217-F217,1)</x:f>
+        <x:v>125.8</x:v>
+      </x:c>
+      <x:c r="K217" s="22" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B218" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B218" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C218" s="30"/>
       <x:c r="D218" s="30"/>
       <x:c r="E218" s="30"/>
@@ -47754,11 +47772,29 @@
       <x:c r="G218" s="30"/>
       <x:c r="H218" s="30"/>
       <x:c r="I218" s="30"/>
-      <x:c r="J218" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
-        <x:v>157.4</x:v>
+      <x:c r="J218" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J217),1)</x:f>
+        <x:v>2014.4</x:v>
       </x:c>
       <x:c r="K218" s="30"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B219" s="30"/>
+      <x:c r="C219" s="30"/>
+      <x:c r="D219" s="30"/>
+      <x:c r="E219" s="30"/>
+      <x:c r="F219" s="30"/>
+      <x:c r="G219" s="30"/>
+      <x:c r="H219" s="30"/>
+      <x:c r="I219" s="30"/>
+      <x:c r="J219" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="K219" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -54746,30 +54782,48 @@
       </x:c>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B217" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C217" s="30"/>
-      <x:c r="D217" s="30"/>
-      <x:c r="E217" s="30"/>
-      <x:c r="F217" s="30"/>
-      <x:c r="G217" s="30"/>
-      <x:c r="H217" s="30"/>
-      <x:c r="I217" s="30"/>
-      <x:c r="J217" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J216),1)</x:f>
-        <x:v>1774.4</x:v>
-      </x:c>
-      <x:c r="K217" s="30"/>
+      <x:c r="A217" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B217" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C217" s="22" t="str">
+        <x:v>9月17日</x:v>
+      </x:c>
+      <x:c r="D217" s="23" t="n">
+        <x:v>7678.4</x:v>
+      </x:c>
+      <x:c r="E217" s="23" t="n">
+        <x:v>7754</x:v>
+      </x:c>
+      <x:c r="F217" s="23" t="n">
+        <x:v>7617.2</x:v>
+      </x:c>
+      <x:c r="G217" s="23" t="n">
+        <x:v>7664.6</x:v>
+      </x:c>
+      <x:c r="H217" s="23" t="n">
+        <x:v>-25</x:v>
+      </x:c>
+      <x:c r="I217" s="24" t="n">
+        <x:v>-0.0032511444028298087</x:v>
+      </x:c>
+      <x:c r="J217" s="23" t="n">
+        <x:f>ROUND(E217-F217,1)</x:f>
+        <x:v>136.8</x:v>
+      </x:c>
+      <x:c r="K217" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B218" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B218" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C218" s="30"/>
       <x:c r="D218" s="30"/>
       <x:c r="E218" s="30"/>
@@ -54777,11 +54831,29 @@
       <x:c r="G218" s="30"/>
       <x:c r="H218" s="30"/>
       <x:c r="I218" s="30"/>
-      <x:c r="J218" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
-        <x:v>147.9</x:v>
+      <x:c r="J218" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J217),1)</x:f>
+        <x:v>1911.2</x:v>
       </x:c>
       <x:c r="K218" s="30"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B219" s="30"/>
+      <x:c r="C219" s="30"/>
+      <x:c r="D219" s="30"/>
+      <x:c r="E219" s="30"/>
+      <x:c r="F219" s="30"/>
+      <x:c r="G219" s="30"/>
+      <x:c r="H219" s="30"/>
+      <x:c r="I219" s="30"/>
+      <x:c r="J219" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="K219" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -61769,30 +61841,48 @@
       </x:c>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B217" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C217" s="30"/>
-      <x:c r="D217" s="30"/>
-      <x:c r="E217" s="30"/>
-      <x:c r="F217" s="30"/>
-      <x:c r="G217" s="30"/>
-      <x:c r="H217" s="30"/>
-      <x:c r="I217" s="30"/>
-      <x:c r="J217" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J216),1)</x:f>
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="K217" s="30"/>
+      <x:c r="A217" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B217" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C217" s="22" t="str">
+        <x:v>9月17日</x:v>
+      </x:c>
+      <x:c r="D217" s="23" t="n">
+        <x:v>4475.6</x:v>
+      </x:c>
+      <x:c r="E217" s="23" t="n">
+        <x:v>4500.6</x:v>
+      </x:c>
+      <x:c r="F217" s="23" t="n">
+        <x:v>4452.2</x:v>
+      </x:c>
+      <x:c r="G217" s="23" t="n">
+        <x:v>4460.2</x:v>
+      </x:c>
+      <x:c r="H217" s="23" t="n">
+        <x:v>-17.8</x:v>
+      </x:c>
+      <x:c r="I217" s="24" t="n">
+        <x:v>-0.00397498883430103</x:v>
+      </x:c>
+      <x:c r="J217" s="23" t="n">
+        <x:f>ROUND(E217-F217,1)</x:f>
+        <x:v>48.4</x:v>
+      </x:c>
+      <x:c r="K217" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B218" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B218" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C218" s="30"/>
       <x:c r="D218" s="30"/>
       <x:c r="E218" s="30"/>
@@ -61800,11 +61890,29 @@
       <x:c r="G218" s="30"/>
       <x:c r="H218" s="30"/>
       <x:c r="I218" s="30"/>
-      <x:c r="J218" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
-        <x:v>54.1</x:v>
+      <x:c r="J218" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J217),1)</x:f>
+        <x:v>697.4</x:v>
       </x:c>
       <x:c r="K218" s="30"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B219" s="30"/>
+      <x:c r="C219" s="30"/>
+      <x:c r="D219" s="30"/>
+      <x:c r="E219" s="30"/>
+      <x:c r="F219" s="30"/>
+      <x:c r="G219" s="30"/>
+      <x:c r="H219" s="30"/>
+      <x:c r="I219" s="30"/>
+      <x:c r="J219" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
+        <x:v>53.6</x:v>
+      </x:c>
+      <x:c r="K219" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -68792,30 +68900,48 @@
       </x:c>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B217" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C217" s="30"/>
-      <x:c r="D217" s="30"/>
-      <x:c r="E217" s="30"/>
-      <x:c r="F217" s="30"/>
-      <x:c r="G217" s="30"/>
-      <x:c r="H217" s="30"/>
-      <x:c r="I217" s="30"/>
-      <x:c r="J217" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J216),1)</x:f>
-        <x:v>381</x:v>
-      </x:c>
-      <x:c r="K217" s="30"/>
+      <x:c r="A217" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B217" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C217" s="22" t="str">
+        <x:v>9月17日</x:v>
+      </x:c>
+      <x:c r="D217" s="23" t="n">
+        <x:v>2860</x:v>
+      </x:c>
+      <x:c r="E217" s="23" t="n">
+        <x:v>2872.4</x:v>
+      </x:c>
+      <x:c r="F217" s="23" t="n">
+        <x:v>2838.4</x:v>
+      </x:c>
+      <x:c r="G217" s="23" t="n">
+        <x:v>2845.8</x:v>
+      </x:c>
+      <x:c r="H217" s="23" t="n">
+        <x:v>-19.2</x:v>
+      </x:c>
+      <x:c r="I217" s="24" t="n">
+        <x:v>-0.006701570680628155</x:v>
+      </x:c>
+      <x:c r="J217" s="23" t="n">
+        <x:f>ROUND(E217-F217,1)</x:f>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K217" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B218" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B218" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C218" s="30"/>
       <x:c r="D218" s="30"/>
       <x:c r="E218" s="30"/>
@@ -68823,11 +68949,29 @@
       <x:c r="G218" s="30"/>
       <x:c r="H218" s="30"/>
       <x:c r="I218" s="30"/>
-      <x:c r="J218" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J216),0),1)</x:f>
-        <x:v>31.8</x:v>
+      <x:c r="J218" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J217),1)</x:f>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="K218" s="30"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B219" s="30"/>
+      <x:c r="C219" s="30"/>
+      <x:c r="D219" s="30"/>
+      <x:c r="E219" s="30"/>
+      <x:c r="F219" s="30"/>
+      <x:c r="G219" s="30"/>
+      <x:c r="H219" s="30"/>
+      <x:c r="I219" s="30"/>
+      <x:c r="J219" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
+        <x:v>31.9</x:v>
+      </x:c>
+      <x:c r="K219" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R0c4007267ed74108"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R29c2bbdd5b4b4f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rd6d670baebcd4ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rdbea9e06e2b34951"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R57f1230161084054"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R1afe4bf18f8642d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rf78b450e485345b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2a97765699a44142"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rd4ab9f60afa24762"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R416dfef56a36425a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R1f9dcff413674ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R9a7f38ed4a2e483b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rd6e98f53506d4488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R4e5de9d25fe248ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R5da9ad0829914ec4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rb32f047080ae48a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R94885d7f739c4616"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R16611a0cd055469a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R655e45c4140e4526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R8da233a21dbe4a4f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R1f9dcff413674ffa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R9a7f38ed4a2e483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rd6e98f53506d4488"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R4e5de9d25fe248ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R5da9ad0829914ec4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rb32f047080ae48a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R94885d7f739c4616"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R16611a0cd055469a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R655e45c4140e4526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R8da233a21dbe4a4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rac76af5be27f456b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rc4a8e3d51e2944f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R9870538d70f44d9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R6a8c5808b25141b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rea540e34b15141f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R1037534745374705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rda20f8ee16fb4da3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rfe1a445e33864f01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rf6c44ae124754c5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R797ba531aded40f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-17</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7632.53</x:v>
+        <x:v>7706.9</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7522.77</x:v>
+        <x:v>7603.37</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>109.8</x:v>
+        <x:v>103.5</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>30527.9</x:v>
+        <x:v>30631.4</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>176.5</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-17</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7738.03</x:v>
+        <x:v>7819.98</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7622.55</x:v>
+        <x:v>7710.24</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>115.5</x:v>
+        <x:v>109.7</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>30401.3</x:v>
+        <x:v>30511</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>175.7</x:v>
+        <x:v>175.4</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-17</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3898.84</x:v>
+        <x:v>3919.67</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3866.89</x:v>
+        <x:v>3888.5</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>32</x:v>
+        <x:v>31.2</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8346.4</x:v>
+        <x:v>8377.6</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>48.2</x:v>
+        <x:v>48.1</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-17</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7648</x:v>
+        <x:v>7712.4</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7522.2</x:v>
+        <x:v>7606.6</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>125.8</x:v>
+        <x:v>105.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>32458.2</x:v>
+        <x:v>32564</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>187.6</x:v>
+        <x:v>187.1</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-17</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7754</x:v>
+        <x:v>7820</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7617.2</x:v>
+        <x:v>7709.2</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>136.8</x:v>
+        <x:v>110.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>33655.4</x:v>
+        <x:v>33766.2</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>194.5</x:v>
+        <x:v>194.1</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-17</x:v>
+        <x:v>2026-09-18</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -9340,37 +9340,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" s="22" t="str">
-        <x:v>9月14日-9月17日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C40" s="23" t="n">
         <x:v>7363.42</x:v>
       </x:c>
       <x:c r="D40" s="23" t="n">
-        <x:v>7632.53</x:v>
+        <x:v>7706.9</x:v>
       </x:c>
       <x:c r="E40" s="23" t="n">
         <x:v>7329.6</x:v>
       </x:c>
       <x:c r="F40" s="23" t="n">
-        <x:v>7548.82</x:v>
-      </x:c>
-      <x:c r="G40" s="23" t="n">
+        <x:v>7687.59</x:v>
+      </x:c>
+      <x:c r="G40" s="28" t="n">
         <x:f>ROUND(F40-F39,1)</x:f>
-        <x:v>121.6</x:v>
+        <x:v>260.4</x:v>
       </x:c>
       <x:c r="H40" s="24" t="n">
         <x:f>IFERROR(F40/F39-1,"")</x:f>
-        <x:v>0.01636947237466413</x:v>
+        <x:v>0.03505339803210883</x:v>
       </x:c>
       <x:c r="I40" s="26" t="n">
         <x:f>ROUND(D40-E40,1)</x:f>
-        <x:v>302.9</x:v>
+        <x:v>377.3</x:v>
       </x:c>
       <x:c r="J40" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K40" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -9388,7 +9388,7 @@
       <x:c r="H41" s="30"/>
       <x:c r="I41" s="32" t="n">
         <x:f>ROUND(SUM(I5:I40),1)</x:f>
-        <x:v>14999.5</x:v>
+        <x:v>15073.9</x:v>
       </x:c>
       <x:c r="J41" s="30"/>
       <x:c r="K41" s="30"/>
@@ -9406,7 +9406,7 @@
       <x:c r="H42" s="30"/>
       <x:c r="I42" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I40),0),1)</x:f>
-        <x:v>416.7</x:v>
+        <x:v>418.7</x:v>
       </x:c>
       <x:c r="J42" s="30"/>
       <x:c r="K42" s="30"/>
@@ -10790,37 +10790,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B81" s="22" t="str">
-        <x:v>9月14日-9月17日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C81" s="23" t="n">
         <x:v>7511.04</x:v>
       </x:c>
       <x:c r="D81" s="23" t="n">
-        <x:v>7738.03</x:v>
+        <x:v>7819.98</x:v>
       </x:c>
       <x:c r="E81" s="23" t="n">
         <x:v>7487.46</x:v>
       </x:c>
       <x:c r="F81" s="23" t="n">
-        <x:v>7654.98</x:v>
-      </x:c>
-      <x:c r="G81" s="23" t="n">
+        <x:v>7799.61</x:v>
+      </x:c>
+      <x:c r="G81" s="28" t="n">
         <x:f>ROUND(F81-F80,1)</x:f>
-        <x:v>74.4</x:v>
+        <x:v>219.1</x:v>
       </x:c>
       <x:c r="H81" s="24" t="n">
         <x:f>IFERROR(F81/F80-1,"")</x:f>
-        <x:v>0.009819880905581835</x:v>
+        <x:v>0.028898996641400165</x:v>
       </x:c>
       <x:c r="I81" s="26" t="n">
         <x:f>ROUND(D81-E81,1)</x:f>
-        <x:v>250.6</x:v>
+        <x:v>332.5</x:v>
       </x:c>
       <x:c r="J81" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K81" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -10838,7 +10838,7 @@
       <x:c r="H82" s="30"/>
       <x:c r="I82" s="32" t="n">
         <x:f>ROUND(SUM(I46:I81),1)</x:f>
-        <x:v>14968.6</x:v>
+        <x:v>15050.5</x:v>
       </x:c>
       <x:c r="J82" s="30"/>
       <x:c r="K82" s="30"/>
@@ -10856,7 +10856,7 @@
       <x:c r="H83" s="30"/>
       <x:c r="I83" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I46:I81),0),1)</x:f>
-        <x:v>415.8</x:v>
+        <x:v>418.1</x:v>
       </x:c>
       <x:c r="J83" s="30"/>
       <x:c r="K83" s="30"/>
@@ -12240,37 +12240,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B122" s="22" t="str">
-        <x:v>9月14日-9月17日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C122" s="23" t="n">
         <x:v>3867.02</x:v>
       </x:c>
       <x:c r="D122" s="23" t="n">
-        <x:v>3898.84</x:v>
+        <x:v>3919.67</x:v>
       </x:c>
       <x:c r="E122" s="23" t="n">
         <x:v>3842.72</x:v>
       </x:c>
       <x:c r="F122" s="23" t="n">
-        <x:v>3875.6</x:v>
+        <x:v>3911.87</x:v>
       </x:c>
       <x:c r="G122" s="23" t="n">
         <x:f>ROUND(F122-F121,1)</x:f>
-        <x:v>-12.5</x:v>
+        <x:v>23.8</x:v>
       </x:c>
       <x:c r="H122" s="24" t="n">
         <x:f>IFERROR(F122/F121-1,"")</x:f>
-        <x:v>-0.0032175015624558156</x:v>
+        <x:v>0.0061109382193405</x:v>
       </x:c>
       <x:c r="I122" s="26" t="n">
         <x:f>ROUND(D122-E122,1)</x:f>
-        <x:v>56.1</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="J122" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K122" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -12288,7 +12288,7 @@
       <x:c r="H123" s="30"/>
       <x:c r="I123" s="32" t="n">
         <x:f>ROUND(SUM(I87:I122),1)</x:f>
-        <x:v>3920.2</x:v>
+        <x:v>3941.1</x:v>
       </x:c>
       <x:c r="J123" s="30"/>
       <x:c r="K123" s="30"/>
@@ -12306,7 +12306,7 @@
       <x:c r="H124" s="30"/>
       <x:c r="I124" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I87:I122),0),1)</x:f>
-        <x:v>108.9</x:v>
+        <x:v>109.5</x:v>
       </x:c>
       <x:c r="J124" s="30"/>
       <x:c r="K124" s="30"/>
@@ -13690,37 +13690,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B163" s="22" t="str">
-        <x:v>9月14日-9月17日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C163" s="23" t="n">
         <x:v>7312</x:v>
       </x:c>
       <x:c r="D163" s="23" t="n">
-        <x:v>7648</x:v>
+        <x:v>7712.4</x:v>
       </x:c>
       <x:c r="E163" s="23" t="n">
         <x:v>7283.4</x:v>
       </x:c>
       <x:c r="F163" s="23" t="n">
-        <x:v>7559.8</x:v>
-      </x:c>
-      <x:c r="G163" s="23" t="n">
+        <x:v>7679.2</x:v>
+      </x:c>
+      <x:c r="G163" s="28" t="n">
         <x:f>ROUND(F163-F162,1)</x:f>
-        <x:v>144.6</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H163" s="24" t="n">
         <x:f>IFERROR(F163/F162-1,"")</x:f>
-        <x:v>0.019500485489265307</x:v>
+        <x:v>0.03560254612148017</x:v>
       </x:c>
       <x:c r="I163" s="26" t="n">
         <x:f>ROUND(D163-E163,1)</x:f>
-        <x:v>364.6</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="J163" s="22" t="str">
         <x:v>IM2609</x:v>
       </x:c>
       <x:c r="K163" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -13738,7 +13738,7 @@
       <x:c r="H164" s="30"/>
       <x:c r="I164" s="32" t="n">
         <x:f>ROUND(SUM(I128:I163),1)</x:f>
-        <x:v>15648.4</x:v>
+        <x:v>15712.8</x:v>
       </x:c>
       <x:c r="J164" s="30"/>
       <x:c r="K164" s="30"/>
@@ -13756,7 +13756,7 @@
       <x:c r="H165" s="30"/>
       <x:c r="I165" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I128:I163),0),1)</x:f>
-        <x:v>434.7</x:v>
+        <x:v>436.5</x:v>
       </x:c>
       <x:c r="J165" s="30"/>
       <x:c r="K165" s="30"/>
@@ -15140,37 +15140,37 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B204" s="22" t="str">
-        <x:v>9月14日-9月17日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C204" s="23" t="n">
         <x:v>7482.2</x:v>
       </x:c>
       <x:c r="D204" s="23" t="n">
-        <x:v>7754</x:v>
+        <x:v>7820</x:v>
       </x:c>
       <x:c r="E204" s="23" t="n">
         <x:v>7452.2</x:v>
       </x:c>
       <x:c r="F204" s="23" t="n">
-        <x:v>7664.6</x:v>
-      </x:c>
-      <x:c r="G204" s="23" t="n">
+        <x:v>7789.8</x:v>
+      </x:c>
+      <x:c r="G204" s="28" t="n">
         <x:f>ROUND(F204-F203,1)</x:f>
-        <x:v>95.6</x:v>
+        <x:v>220.8</x:v>
       </x:c>
       <x:c r="H204" s="24" t="n">
         <x:f>IFERROR(F204/F203-1,"")</x:f>
-        <x:v>0.01263046637600751</x:v>
+        <x:v>0.02917162108600868</x:v>
       </x:c>
       <x:c r="I204" s="26" t="n">
         <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>301.8</x:v>
+        <x:v>367.8</x:v>
       </x:c>
       <x:c r="J204" s="22" t="str">
         <x:v>IC2609</x:v>
       </x:c>
       <x:c r="K204" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -15188,7 +15188,7 @@
       <x:c r="H205" s="30"/>
       <x:c r="I205" s="32" t="n">
         <x:f>ROUND(SUM(I169:I204),1)</x:f>
-        <x:v>16127.2</x:v>
+        <x:v>16193.2</x:v>
       </x:c>
       <x:c r="J205" s="30"/>
       <x:c r="K205" s="30"/>
@@ -15206,7 +15206,7 @@
       <x:c r="H206" s="30"/>
       <x:c r="I206" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I169:I204),0),1)</x:f>
-        <x:v>448</x:v>
+        <x:v>449.8</x:v>
       </x:c>
       <x:c r="J206" s="30"/>
       <x:c r="K206" s="30"/>
@@ -26582,30 +26582,48 @@
       </x:c>
     </x:row>
     <x:row r="218">
-      <x:c r="A218" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B218" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C218" s="30"/>
-      <x:c r="D218" s="30"/>
-      <x:c r="E218" s="30"/>
-      <x:c r="F218" s="30"/>
-      <x:c r="G218" s="30"/>
-      <x:c r="H218" s="30"/>
-      <x:c r="I218" s="30"/>
-      <x:c r="J218" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J217),1)</x:f>
-        <x:v>1797.1</x:v>
-      </x:c>
-      <x:c r="K218" s="30"/>
+      <x:c r="A218" s="41" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B218" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C218" s="41" t="str">
+        <x:v>9月18日</x:v>
+      </x:c>
+      <x:c r="D218" s="42" t="n">
+        <x:v>7621.24</x:v>
+      </x:c>
+      <x:c r="E218" s="42" t="n">
+        <x:v>7706.9</x:v>
+      </x:c>
+      <x:c r="F218" s="42" t="n">
+        <x:v>7603.37</x:v>
+      </x:c>
+      <x:c r="G218" s="42" t="n">
+        <x:v>7687.59</x:v>
+      </x:c>
+      <x:c r="H218" s="42" t="n">
+        <x:v>138.8</x:v>
+      </x:c>
+      <x:c r="I218" s="43" t="n">
+        <x:v>0.018383005555835386</x:v>
+      </x:c>
+      <x:c r="J218" s="42" t="n">
+        <x:f>ROUND(E218-F218,1)</x:f>
+        <x:v>103.5</x:v>
+      </x:c>
+      <x:c r="K218" s="41" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B219" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B219" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C219" s="30"/>
       <x:c r="D219" s="30"/>
       <x:c r="E219" s="30"/>
@@ -26613,11 +26631,29 @@
       <x:c r="G219" s="30"/>
       <x:c r="H219" s="30"/>
       <x:c r="I219" s="30"/>
-      <x:c r="J219" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
-        <x:v>138.2</x:v>
+      <x:c r="J219" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J218),1)</x:f>
+        <x:v>1900.6</x:v>
       </x:c>
       <x:c r="K219" s="30"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B220" s="30"/>
+      <x:c r="C220" s="30"/>
+      <x:c r="D220" s="30"/>
+      <x:c r="E220" s="30"/>
+      <x:c r="F220" s="30"/>
+      <x:c r="G220" s="30"/>
+      <x:c r="H220" s="30"/>
+      <x:c r="I220" s="30"/>
+      <x:c r="J220" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J218),0),1)</x:f>
+        <x:v>135.8</x:v>
+      </x:c>
+      <x:c r="K220" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -33641,30 +33677,48 @@
       </x:c>
     </x:row>
     <x:row r="218">
-      <x:c r="A218" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B218" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C218" s="30"/>
-      <x:c r="D218" s="30"/>
-      <x:c r="E218" s="30"/>
-      <x:c r="F218" s="30"/>
-      <x:c r="G218" s="30"/>
-      <x:c r="H218" s="30"/>
-      <x:c r="I218" s="30"/>
-      <x:c r="J218" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J217),1)</x:f>
-        <x:v>1617.6</x:v>
-      </x:c>
-      <x:c r="K218" s="30"/>
+      <x:c r="A218" s="41" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B218" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C218" s="41" t="str">
+        <x:v>9月18日</x:v>
+      </x:c>
+      <x:c r="D218" s="42" t="n">
+        <x:v>7731.07</x:v>
+      </x:c>
+      <x:c r="E218" s="42" t="n">
+        <x:v>7819.98</x:v>
+      </x:c>
+      <x:c r="F218" s="42" t="n">
+        <x:v>7710.24</x:v>
+      </x:c>
+      <x:c r="G218" s="42" t="n">
+        <x:v>7799.61</x:v>
+      </x:c>
+      <x:c r="H218" s="42" t="n">
+        <x:v>144.6</x:v>
+      </x:c>
+      <x:c r="I218" s="43" t="n">
+        <x:v>0.018893583000870073</x:v>
+      </x:c>
+      <x:c r="J218" s="42" t="n">
+        <x:f>ROUND(E218-F218,1)</x:f>
+        <x:v>109.7</x:v>
+      </x:c>
+      <x:c r="K218" s="41" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B219" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B219" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C219" s="30"/>
       <x:c r="D219" s="30"/>
       <x:c r="E219" s="30"/>
@@ -33672,11 +33726,29 @@
       <x:c r="G219" s="30"/>
       <x:c r="H219" s="30"/>
       <x:c r="I219" s="30"/>
-      <x:c r="J219" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
-        <x:v>124.4</x:v>
+      <x:c r="J219" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J218),1)</x:f>
+        <x:v>1727.3</x:v>
       </x:c>
       <x:c r="K219" s="30"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B220" s="30"/>
+      <x:c r="C220" s="30"/>
+      <x:c r="D220" s="30"/>
+      <x:c r="E220" s="30"/>
+      <x:c r="F220" s="30"/>
+      <x:c r="G220" s="30"/>
+      <x:c r="H220" s="30"/>
+      <x:c r="I220" s="30"/>
+      <x:c r="J220" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J218),0),1)</x:f>
+        <x:v>123.4</x:v>
+      </x:c>
+      <x:c r="K220" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -40700,30 +40772,48 @@
       </x:c>
     </x:row>
     <x:row r="218">
-      <x:c r="A218" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B218" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C218" s="30"/>
-      <x:c r="D218" s="30"/>
-      <x:c r="E218" s="30"/>
-      <x:c r="F218" s="30"/>
-      <x:c r="G218" s="30"/>
-      <x:c r="H218" s="30"/>
-      <x:c r="I218" s="30"/>
-      <x:c r="J218" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J217),1)</x:f>
-        <x:v>465.3</x:v>
-      </x:c>
-      <x:c r="K218" s="30"/>
+      <x:c r="A218" s="41" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B218" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C218" s="41" t="str">
+        <x:v>9月18日</x:v>
+      </x:c>
+      <x:c r="D218" s="42" t="n">
+        <x:v>3891.96</x:v>
+      </x:c>
+      <x:c r="E218" s="42" t="n">
+        <x:v>3919.67</x:v>
+      </x:c>
+      <x:c r="F218" s="42" t="n">
+        <x:v>3888.5</x:v>
+      </x:c>
+      <x:c r="G218" s="42" t="n">
+        <x:v>3911.87</x:v>
+      </x:c>
+      <x:c r="H218" s="42" t="n">
+        <x:v>36.3</x:v>
+      </x:c>
+      <x:c r="I218" s="43" t="n">
+        <x:v>0.009358550934049026</x:v>
+      </x:c>
+      <x:c r="J218" s="42" t="n">
+        <x:f>ROUND(E218-F218,1)</x:f>
+        <x:v>31.2</x:v>
+      </x:c>
+      <x:c r="K218" s="41" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B219" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B219" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C219" s="30"/>
       <x:c r="D219" s="30"/>
       <x:c r="E219" s="30"/>
@@ -40731,11 +40821,29 @@
       <x:c r="G219" s="30"/>
       <x:c r="H219" s="30"/>
       <x:c r="I219" s="30"/>
-      <x:c r="J219" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
-        <x:v>35.8</x:v>
+      <x:c r="J219" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J218),1)</x:f>
+        <x:v>496.5</x:v>
       </x:c>
       <x:c r="K219" s="30"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B220" s="30"/>
+      <x:c r="C220" s="30"/>
+      <x:c r="D220" s="30"/>
+      <x:c r="E220" s="30"/>
+      <x:c r="F220" s="30"/>
+      <x:c r="G220" s="30"/>
+      <x:c r="H220" s="30"/>
+      <x:c r="I220" s="30"/>
+      <x:c r="J220" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J218),0),1)</x:f>
+        <x:v>35.5</x:v>
+      </x:c>
+      <x:c r="K220" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -47759,30 +47867,48 @@
       </x:c>
     </x:row>
     <x:row r="218">
-      <x:c r="A218" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B218" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C218" s="30"/>
-      <x:c r="D218" s="30"/>
-      <x:c r="E218" s="30"/>
-      <x:c r="F218" s="30"/>
-      <x:c r="G218" s="30"/>
-      <x:c r="H218" s="30"/>
-      <x:c r="I218" s="30"/>
-      <x:c r="J218" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J217),1)</x:f>
-        <x:v>2014.4</x:v>
-      </x:c>
-      <x:c r="K218" s="30"/>
+      <x:c r="A218" s="41" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B218" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C218" s="41" t="str">
+        <x:v>9月18日</x:v>
+      </x:c>
+      <x:c r="D218" s="42" t="n">
+        <x:v>7626.6</x:v>
+      </x:c>
+      <x:c r="E218" s="42" t="n">
+        <x:v>7712.4</x:v>
+      </x:c>
+      <x:c r="F218" s="42" t="n">
+        <x:v>7606.6</x:v>
+      </x:c>
+      <x:c r="G218" s="42" t="n">
+        <x:v>7679.2</x:v>
+      </x:c>
+      <x:c r="H218" s="42" t="n">
+        <x:v>119.4</x:v>
+      </x:c>
+      <x:c r="I218" s="43" t="n">
+        <x:v>0.01579406862615418</x:v>
+      </x:c>
+      <x:c r="J218" s="42" t="n">
+        <x:f>ROUND(E218-F218,1)</x:f>
+        <x:v>105.8</x:v>
+      </x:c>
+      <x:c r="K218" s="41" t="str">
+        <x:v>IM2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B219" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B219" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C219" s="30"/>
       <x:c r="D219" s="30"/>
       <x:c r="E219" s="30"/>
@@ -47790,11 +47916,29 @@
       <x:c r="G219" s="30"/>
       <x:c r="H219" s="30"/>
       <x:c r="I219" s="30"/>
-      <x:c r="J219" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
-        <x:v>155</x:v>
+      <x:c r="J219" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J218),1)</x:f>
+        <x:v>2120.2</x:v>
       </x:c>
       <x:c r="K219" s="30"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B220" s="30"/>
+      <x:c r="C220" s="30"/>
+      <x:c r="D220" s="30"/>
+      <x:c r="E220" s="30"/>
+      <x:c r="F220" s="30"/>
+      <x:c r="G220" s="30"/>
+      <x:c r="H220" s="30"/>
+      <x:c r="I220" s="30"/>
+      <x:c r="J220" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J218),0),1)</x:f>
+        <x:v>151.4</x:v>
+      </x:c>
+      <x:c r="K220" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -54818,30 +54962,48 @@
       </x:c>
     </x:row>
     <x:row r="218">
-      <x:c r="A218" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B218" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C218" s="30"/>
-      <x:c r="D218" s="30"/>
-      <x:c r="E218" s="30"/>
-      <x:c r="F218" s="30"/>
-      <x:c r="G218" s="30"/>
-      <x:c r="H218" s="30"/>
-      <x:c r="I218" s="30"/>
-      <x:c r="J218" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J217),1)</x:f>
-        <x:v>1911.2</x:v>
-      </x:c>
-      <x:c r="K218" s="30"/>
+      <x:c r="A218" s="41" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B218" s="41" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C218" s="41" t="str">
+        <x:v>9月18日</x:v>
+      </x:c>
+      <x:c r="D218" s="42" t="n">
+        <x:v>7723</x:v>
+      </x:c>
+      <x:c r="E218" s="42" t="n">
+        <x:v>7820</x:v>
+      </x:c>
+      <x:c r="F218" s="42" t="n">
+        <x:v>7709.2</x:v>
+      </x:c>
+      <x:c r="G218" s="42" t="n">
+        <x:v>7789.8</x:v>
+      </x:c>
+      <x:c r="H218" s="42" t="n">
+        <x:v>125.2</x:v>
+      </x:c>
+      <x:c r="I218" s="43" t="n">
+        <x:v>0.016334838086788483</x:v>
+      </x:c>
+      <x:c r="J218" s="42" t="n">
+        <x:f>ROUND(E218-F218,1)</x:f>
+        <x:v>110.8</x:v>
+      </x:c>
+      <x:c r="K218" s="41" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B219" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B219" s="30" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C219" s="30"/>
       <x:c r="D219" s="30"/>
       <x:c r="E219" s="30"/>
@@ -54849,11 +55011,29 @@
       <x:c r="G219" s="30"/>
       <x:c r="H219" s="30"/>
       <x:c r="I219" s="30"/>
-      <x:c r="J219" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J217),0),1)</x:f>
-        <x:v>147</x:v>
+      <x:c r="J219" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J218),1)</x:f>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="K219" s="30"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B220" s="30"/>
+      <x:c r="C220" s="30"/>
+      <x:c r="D220" s="30"/>
+      <x:c r="E220" s="30"/>
+      <x:c r="F220" s="30"/>
+      <x:c r="G220" s="30"/>
+      <x:c r="H220" s="30"/>
+      <x:c r="I220" s="30"/>
+      <x:c r="J220" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J218),0),1)</x:f>
+        <x:v>144.4</x:v>
+      </x:c>
+      <x:c r="K220" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R53926cdf453747bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R579f67fd917b4d5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R8843407c764c436c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R57368cf8fc2e4946"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rcceb10ee8da24355"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rdc4549e2763b4682"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R802dd1599f5948ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R3abe2f1c26c544c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R218207b4c71f4c45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R54e1c227f60b4596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R5ea45d39959a4237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R951a4d4e333643a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R926ee00e66434f59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R304f79f52cbc4bd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R8db1e49565d2404f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc1231a5ac1ae4ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R982c430863b04bbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rad6755f6ab284ec8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rf61a1795e54e48c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R41b1c1afd34b4dac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-18</x:v>
+        <x:v>2026-09-21</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7712.4</x:v>
+        <x:v>7599</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7606.6</x:v>
+        <x:v>7527</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>105.8</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>32564</x:v>
+        <x:v>32636</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>187.1</x:v>
+        <x:v>186.5</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-18</x:v>
+        <x:v>2026-09-21</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7820</x:v>
+        <x:v>7728</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7709.2</x:v>
+        <x:v>7640</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>110.8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>33766.2</x:v>
+        <x:v>33854.2</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>194.1</x:v>
+        <x:v>193.5</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-18</x:v>
+        <x:v>2026-09-21</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4520.6</x:v>
+        <x:v>4474.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4481</x:v>
+        <x:v>4434.8</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>39.6</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12623.6</x:v>
+        <x:v>12663.4</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.5</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-18</x:v>
+        <x:v>2026-09-21</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2870.8</x:v>
+        <x:v>2849.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2853.4</x:v>
+        <x:v>2822</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>17.4</x:v>
+        <x:v>27.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7009</x:v>
+        <x:v>7036.8</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.3</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -13910,155 +13910,155 @@
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B167" s="30" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C167" s="30"/>
-      <x:c r="D167" s="30"/>
-      <x:c r="E167" s="30"/>
-      <x:c r="F167" s="30"/>
-      <x:c r="G167" s="30"/>
-      <x:c r="H167" s="30"/>
-      <x:c r="I167" s="32" t="n">
-        <x:f>ROUND(SUM(I131:I166),1)</x:f>
-        <x:v>15712.8</x:v>
-      </x:c>
-      <x:c r="J167" s="30"/>
-      <x:c r="K167" s="30"/>
+      <x:c r="A167" s="22" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B167" s="22" t="str">
+        <x:v>9月21日</x:v>
+      </x:c>
+      <x:c r="C167" s="23" t="n">
+        <x:v>7549</x:v>
+      </x:c>
+      <x:c r="D167" s="23" t="n">
+        <x:v>7599</x:v>
+      </x:c>
+      <x:c r="E167" s="23" t="n">
+        <x:v>7527</x:v>
+      </x:c>
+      <x:c r="F167" s="23" t="n">
+        <x:v>7560.6</x:v>
+      </x:c>
+      <x:c r="G167" s="23" t="n">
+        <x:f>ROUND(F167-F166,1)</x:f>
+        <x:v>-118.6</x:v>
+      </x:c>
+      <x:c r="H167" s="24" t="n">
+        <x:f>IFERROR(F167/F166-1,"")</x:f>
+        <x:v>-0.01544431711636618</x:v>
+      </x:c>
+      <x:c r="I167" s="23" t="n">
+        <x:f>ROUND(D167-E167,1)</x:f>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="J167" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
+      <x:c r="K167" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B168" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B168" s="30" t="n">
+        <x:v>37</x:v>
+      </x:c>
       <x:c r="C168" s="30"/>
       <x:c r="D168" s="30"/>
       <x:c r="E168" s="30"/>
       <x:c r="F168" s="30"/>
       <x:c r="G168" s="30"/>
       <x:c r="H168" s="30"/>
-      <x:c r="I168" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I131:I166),0),1)</x:f>
-        <x:v>436.5</x:v>
+      <x:c r="I168" s="32" t="n">
+        <x:f>ROUND(SUM(I131:I167),1)</x:f>
+        <x:v>15784.8</x:v>
       </x:c>
       <x:c r="J168" s="30"/>
       <x:c r="K168" s="30"/>
     </x:row>
-    <x:row r="170">
-      <x:c r="A170" s="17" t="str">
+    <x:row r="169">
+      <x:c r="A169" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B169" s="30"/>
+      <x:c r="C169" s="30"/>
+      <x:c r="D169" s="30"/>
+      <x:c r="E169" s="30"/>
+      <x:c r="F169" s="30"/>
+      <x:c r="G169" s="30"/>
+      <x:c r="H169" s="30"/>
+      <x:c r="I169" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I131:I167),0),1)</x:f>
+        <x:v>426.6</x:v>
+      </x:c>
+      <x:c r="J169" s="30"/>
+      <x:c r="K169" s="30"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="17" t="str">
         <x:v>IC主力</x:v>
       </x:c>
-      <x:c r="B170" s="17"/>
-      <x:c r="C170" s="17"/>
-      <x:c r="D170" s="17"/>
-      <x:c r="E170" s="17"/>
-      <x:c r="F170" s="17"/>
-      <x:c r="G170" s="17"/>
-      <x:c r="H170" s="17"/>
-      <x:c r="I170" s="17"/>
-      <x:c r="J170" s="17"/>
-      <x:c r="K170" s="17"/>
-    </x:row>
-    <x:row r="171">
-      <x:c r="A171" s="20" t="str">
+      <x:c r="B171" s="17"/>
+      <x:c r="C171" s="17"/>
+      <x:c r="D171" s="17"/>
+      <x:c r="E171" s="17"/>
+      <x:c r="F171" s="17"/>
+      <x:c r="G171" s="17"/>
+      <x:c r="H171" s="17"/>
+      <x:c r="I171" s="17"/>
+      <x:c r="J171" s="17"/>
+      <x:c r="K171" s="17"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B171" s="20" t="str">
+      <x:c r="B172" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C171" s="20" t="str">
+      <x:c r="C172" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D171" s="20" t="str">
+      <x:c r="D172" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E171" s="20" t="str">
+      <x:c r="E172" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F171" s="20" t="str">
+      <x:c r="F172" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G171" s="20" t="str">
+      <x:c r="G172" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H171" s="20" t="str">
+      <x:c r="H172" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I171" s="20" t="str">
+      <x:c r="I172" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J171" s="20" t="str">
+      <x:c r="J172" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K171" s="20" t="str">
+      <x:c r="K172" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172">
-      <x:c r="A172" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B172" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C172" s="23" t="n">
-        <x:v>7424.4</x:v>
-      </x:c>
-      <x:c r="D172" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="E172" s="23" t="n">
-        <x:v>7422</x:v>
-      </x:c>
-      <x:c r="F172" s="23" t="n">
-        <x:v>8037.8</x:v>
-      </x:c>
-      <x:c r="G172" s="23"/>
-      <x:c r="H172" s="24"/>
-      <x:c r="I172" s="26" t="n">
-        <x:f>ROUND(D172-E172,1)</x:f>
-        <x:v>615.8</x:v>
-      </x:c>
-      <x:c r="J172" s="22" t="str">
-        <x:v>IC2603</x:v>
-      </x:c>
-      <x:c r="K172" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B173" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C173" s="23" t="n">
-        <x:v>8099</x:v>
+        <x:v>7424.4</x:v>
       </x:c>
       <x:c r="D173" s="23" t="n">
-        <x:v>8388.6</x:v>
+        <x:v>8037.8</x:v>
       </x:c>
       <x:c r="E173" s="23" t="n">
-        <x:v>8044</x:v>
+        <x:v>7422</x:v>
       </x:c>
       <x:c r="F173" s="23" t="n">
-        <x:v>8210.4</x:v>
-      </x:c>
-      <x:c r="G173" s="28" t="n">
-        <x:f>ROUND(F173-F172,1)</x:f>
-        <x:v>172.6</x:v>
-      </x:c>
-      <x:c r="H173" s="24" t="n">
-        <x:f>IFERROR(F173/F172-1,"")</x:f>
-        <x:v>0.02147353753514647</x:v>
-      </x:c>
+        <x:v>8037.8</x:v>
+      </x:c>
+      <x:c r="G173" s="23"/>
+      <x:c r="H173" s="24"/>
       <x:c r="I173" s="26" t="n">
         <x:f>ROUND(D173-E173,1)</x:f>
-        <x:v>344.6</x:v>
+        <x:v>615.8</x:v>
       </x:c>
       <x:c r="J173" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -14069,34 +14069,34 @@
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B174" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C174" s="23" t="n">
-        <x:v>8182.6</x:v>
+        <x:v>8099</x:v>
       </x:c>
       <x:c r="D174" s="23" t="n">
-        <x:v>8660</x:v>
+        <x:v>8388.6</x:v>
       </x:c>
       <x:c r="E174" s="23" t="n">
-        <x:v>8112</x:v>
+        <x:v>8044</x:v>
       </x:c>
       <x:c r="F174" s="23" t="n">
-        <x:v>8658.2</x:v>
+        <x:v>8210.4</x:v>
       </x:c>
       <x:c r="G174" s="28" t="n">
         <x:f>ROUND(F174-F173,1)</x:f>
-        <x:v>447.8</x:v>
+        <x:v>172.6</x:v>
       </x:c>
       <x:c r="H174" s="24" t="n">
         <x:f>IFERROR(F174/F173-1,"")</x:f>
-        <x:v>0.05454058267563111</x:v>
+        <x:v>0.02147353753514647</x:v>
       </x:c>
       <x:c r="I174" s="26" t="n">
         <x:f>ROUND(D174-E174,1)</x:f>
-        <x:v>548</x:v>
+        <x:v>344.6</x:v>
       </x:c>
       <x:c r="J174" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -14107,34 +14107,34 @@
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B175" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C175" s="23" t="n">
-        <x:v>8695</x:v>
+        <x:v>8182.6</x:v>
       </x:c>
       <x:c r="D175" s="23" t="n">
-        <x:v>8728.2</x:v>
+        <x:v>8660</x:v>
       </x:c>
       <x:c r="E175" s="23" t="n">
-        <x:v>8135</x:v>
+        <x:v>8112</x:v>
       </x:c>
       <x:c r="F175" s="23" t="n">
-        <x:v>8362.4</x:v>
+        <x:v>8658.2</x:v>
       </x:c>
       <x:c r="G175" s="28" t="n">
         <x:f>ROUND(F175-F174,1)</x:f>
-        <x:v>-295.8</x:v>
+        <x:v>447.8</x:v>
       </x:c>
       <x:c r="H175" s="24" t="n">
         <x:f>IFERROR(F175/F174-1,"")</x:f>
-        <x:v>-0.03416414497239628</x:v>
+        <x:v>0.05454058267563111</x:v>
       </x:c>
       <x:c r="I175" s="26" t="n">
         <x:f>ROUND(D175-E175,1)</x:f>
-        <x:v>593.2</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="J175" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -14145,34 +14145,34 @@
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B176" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C176" s="23" t="n">
-        <x:v>8262.2</x:v>
+        <x:v>8695</x:v>
       </x:c>
       <x:c r="D176" s="23" t="n">
-        <x:v>8334.4</x:v>
+        <x:v>8728.2</x:v>
       </x:c>
       <x:c r="E176" s="23" t="n">
-        <x:v>7832</x:v>
+        <x:v>8135</x:v>
       </x:c>
       <x:c r="F176" s="23" t="n">
-        <x:v>8117.4</x:v>
+        <x:v>8362.4</x:v>
       </x:c>
       <x:c r="G176" s="28" t="n">
         <x:f>ROUND(F176-F175,1)</x:f>
-        <x:v>-245</x:v>
+        <x:v>-295.8</x:v>
       </x:c>
       <x:c r="H176" s="24" t="n">
         <x:f>IFERROR(F176/F175-1,"")</x:f>
-        <x:v>-0.029297809241366157</x:v>
+        <x:v>-0.03416414497239628</x:v>
       </x:c>
       <x:c r="I176" s="26" t="n">
         <x:f>ROUND(D176-E176,1)</x:f>
-        <x:v>502.4</x:v>
+        <x:v>593.2</x:v>
       </x:c>
       <x:c r="J176" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -14183,34 +14183,34 @@
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B177" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C177" s="23" t="n">
-        <x:v>8260</x:v>
+        <x:v>8262.2</x:v>
       </x:c>
       <x:c r="D177" s="23" t="n">
-        <x:v>8458.8</x:v>
+        <x:v>8334.4</x:v>
       </x:c>
       <x:c r="E177" s="23" t="n">
-        <x:v>8220</x:v>
+        <x:v>7832</x:v>
       </x:c>
       <x:c r="F177" s="23" t="n">
-        <x:v>8274.8</x:v>
+        <x:v>8117.4</x:v>
       </x:c>
       <x:c r="G177" s="28" t="n">
         <x:f>ROUND(F177-F176,1)</x:f>
-        <x:v>157.4</x:v>
+        <x:v>-245</x:v>
       </x:c>
       <x:c r="H177" s="24" t="n">
         <x:f>IFERROR(F177/F176-1,"")</x:f>
-        <x:v>0.019390445216448615</x:v>
+        <x:v>-0.029297809241366157</x:v>
       </x:c>
       <x:c r="I177" s="26" t="n">
         <x:f>ROUND(D177-E177,1)</x:f>
-        <x:v>238.8</x:v>
+        <x:v>502.4</x:v>
       </x:c>
       <x:c r="J177" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -14221,110 +14221,110 @@
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B178" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C178" s="23" t="n">
-        <x:v>8360</x:v>
+        <x:v>8260</x:v>
       </x:c>
       <x:c r="D178" s="23" t="n">
-        <x:v>8650</x:v>
+        <x:v>8458.8</x:v>
       </x:c>
       <x:c r="E178" s="23" t="n">
-        <x:v>8314</x:v>
+        <x:v>8220</x:v>
       </x:c>
       <x:c r="F178" s="23" t="n">
-        <x:v>8645.4</x:v>
+        <x:v>8274.8</x:v>
       </x:c>
       <x:c r="G178" s="28" t="n">
         <x:f>ROUND(F178-F177,1)</x:f>
-        <x:v>370.6</x:v>
+        <x:v>157.4</x:v>
       </x:c>
       <x:c r="H178" s="24" t="n">
         <x:f>IFERROR(F178/F177-1,"")</x:f>
-        <x:v>0.04478658094455468</x:v>
+        <x:v>0.019390445216448615</x:v>
       </x:c>
       <x:c r="I178" s="26" t="n">
         <x:f>ROUND(D178-E178,1)</x:f>
-        <x:v>336</x:v>
+        <x:v>238.8</x:v>
       </x:c>
       <x:c r="J178" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K178" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B179" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C179" s="23" t="n">
-        <x:v>8600</x:v>
+        <x:v>8360</x:v>
       </x:c>
       <x:c r="D179" s="23" t="n">
-        <x:v>8686</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
-        <x:v>8180.6</x:v>
+        <x:v>8314</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>8322.6</x:v>
+        <x:v>8645.4</x:v>
       </x:c>
       <x:c r="G179" s="28" t="n">
         <x:f>ROUND(F179-F178,1)</x:f>
-        <x:v>-322.8</x:v>
+        <x:v>370.6</x:v>
       </x:c>
       <x:c r="H179" s="24" t="n">
         <x:f>IFERROR(F179/F178-1,"")</x:f>
-        <x:v>-0.03733777500173496</x:v>
+        <x:v>0.04478658094455468</x:v>
       </x:c>
       <x:c r="I179" s="26" t="n">
         <x:f>ROUND(D179-E179,1)</x:f>
-        <x:v>505.4</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="J179" s="22" t="str">
         <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K179" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B180" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C180" s="23" t="n">
-        <x:v>8201.8</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="D180" s="23" t="n">
-        <x:v>8434.4</x:v>
+        <x:v>8686</x:v>
       </x:c>
       <x:c r="E180" s="23" t="n">
-        <x:v>7710</x:v>
+        <x:v>8180.6</x:v>
       </x:c>
       <x:c r="F180" s="23" t="n">
-        <x:v>8213.8</x:v>
-      </x:c>
-      <x:c r="G180" s="23" t="n">
+        <x:v>8322.6</x:v>
+      </x:c>
+      <x:c r="G180" s="28" t="n">
         <x:f>ROUND(F180-F179,1)</x:f>
-        <x:v>-108.8</x:v>
+        <x:v>-322.8</x:v>
       </x:c>
       <x:c r="H180" s="24" t="n">
         <x:f>IFERROR(F180/F179-1,"")</x:f>
-        <x:v>-0.013072837815106042</x:v>
+        <x:v>-0.03733777500173496</x:v>
       </x:c>
       <x:c r="I180" s="26" t="n">
         <x:f>ROUND(D180-E180,1)</x:f>
-        <x:v>724.4</x:v>
+        <x:v>505.4</x:v>
       </x:c>
       <x:c r="J180" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -14335,34 +14335,34 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B181" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C181" s="23" t="n">
-        <x:v>8225.2</x:v>
+        <x:v>8201.8</x:v>
       </x:c>
       <x:c r="D181" s="23" t="n">
-        <x:v>8229.6</x:v>
+        <x:v>8434.4</x:v>
       </x:c>
       <x:c r="E181" s="23" t="n">
-        <x:v>7827.8</x:v>
+        <x:v>7710</x:v>
       </x:c>
       <x:c r="F181" s="23" t="n">
-        <x:v>7844.4</x:v>
-      </x:c>
-      <x:c r="G181" s="28" t="n">
+        <x:v>8213.8</x:v>
+      </x:c>
+      <x:c r="G181" s="23" t="n">
         <x:f>ROUND(F181-F180,1)</x:f>
-        <x:v>-369.4</x:v>
+        <x:v>-108.8</x:v>
       </x:c>
       <x:c r="H181" s="24" t="n">
         <x:f>IFERROR(F181/F180-1,"")</x:f>
-        <x:v>-0.04497309406121397</x:v>
+        <x:v>-0.013072837815106042</x:v>
       </x:c>
       <x:c r="I181" s="26" t="n">
         <x:f>ROUND(D181-E181,1)</x:f>
-        <x:v>401.8</x:v>
+        <x:v>724.4</x:v>
       </x:c>
       <x:c r="J181" s="22" t="str">
         <x:v>IC2603</x:v>
@@ -14373,37 +14373,37 @@
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B182" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C182" s="23" t="n">
-        <x:v>7460</x:v>
+        <x:v>8225.2</x:v>
       </x:c>
       <x:c r="D182" s="23" t="n">
-        <x:v>7652</x:v>
+        <x:v>8229.6</x:v>
       </x:c>
       <x:c r="E182" s="23" t="n">
-        <x:v>7171</x:v>
+        <x:v>7827.8</x:v>
       </x:c>
       <x:c r="F182" s="23" t="n">
-        <x:v>7559.2</x:v>
+        <x:v>7844.4</x:v>
       </x:c>
       <x:c r="G182" s="28" t="n">
         <x:f>ROUND(F182-F181,1)</x:f>
-        <x:v>-285.2</x:v>
+        <x:v>-369.4</x:v>
       </x:c>
       <x:c r="H182" s="24" t="n">
         <x:f>IFERROR(F182/F181-1,"")</x:f>
-        <x:v>-0.03635714649941357</x:v>
+        <x:v>-0.04497309406121397</x:v>
       </x:c>
       <x:c r="I182" s="26" t="n">
         <x:f>ROUND(D182-E182,1)</x:f>
-        <x:v>481</x:v>
+        <x:v>401.8</x:v>
       </x:c>
       <x:c r="J182" s="22" t="str">
-        <x:v>IC2606</x:v>
+        <x:v>IC2603</x:v>
       </x:c>
       <x:c r="K182" s="22" t="n">
         <x:v>5</x:v>
@@ -14411,34 +14411,34 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B183" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C183" s="23" t="n">
-        <x:v>7470.8</x:v>
+        <x:v>7460</x:v>
       </x:c>
       <x:c r="D183" s="23" t="n">
-        <x:v>7619</x:v>
+        <x:v>7652</x:v>
       </x:c>
       <x:c r="E183" s="23" t="n">
-        <x:v>7325.2</x:v>
+        <x:v>7171</x:v>
       </x:c>
       <x:c r="F183" s="23" t="n">
-        <x:v>7352</x:v>
+        <x:v>7559.2</x:v>
       </x:c>
       <x:c r="G183" s="28" t="n">
         <x:f>ROUND(F183-F182,1)</x:f>
-        <x:v>-207.2</x:v>
+        <x:v>-285.2</x:v>
       </x:c>
       <x:c r="H183" s="24" t="n">
         <x:f>IFERROR(F183/F182-1,"")</x:f>
-        <x:v>-0.02741030796909727</x:v>
+        <x:v>-0.03635714649941357</x:v>
       </x:c>
       <x:c r="I183" s="26" t="n">
         <x:f>ROUND(D183-E183,1)</x:f>
-        <x:v>293.8</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="J183" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14449,110 +14449,110 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B184" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C184" s="23" t="n">
-        <x:v>7380</x:v>
+        <x:v>7470.8</x:v>
       </x:c>
       <x:c r="D184" s="23" t="n">
-        <x:v>7945.4</x:v>
+        <x:v>7619</x:v>
       </x:c>
       <x:c r="E184" s="23" t="n">
-        <x:v>7355.6</x:v>
+        <x:v>7325.2</x:v>
       </x:c>
       <x:c r="F184" s="23" t="n">
-        <x:v>7828.6</x:v>
+        <x:v>7352</x:v>
       </x:c>
       <x:c r="G184" s="28" t="n">
         <x:f>ROUND(F184-F183,1)</x:f>
-        <x:v>476.6</x:v>
+        <x:v>-207.2</x:v>
       </x:c>
       <x:c r="H184" s="24" t="n">
         <x:f>IFERROR(F184/F183-1,"")</x:f>
-        <x:v>0.06482589771490765</x:v>
+        <x:v>-0.02741030796909727</x:v>
       </x:c>
       <x:c r="I184" s="26" t="n">
         <x:f>ROUND(D184-E184,1)</x:f>
-        <x:v>589.8</x:v>
+        <x:v>293.8</x:v>
       </x:c>
       <x:c r="J184" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K184" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B185" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C185" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7380</x:v>
       </x:c>
       <x:c r="D185" s="23" t="n">
-        <x:v>8119.6</x:v>
+        <x:v>7945.4</x:v>
       </x:c>
       <x:c r="E185" s="23" t="n">
-        <x:v>7792</x:v>
+        <x:v>7355.6</x:v>
       </x:c>
       <x:c r="F185" s="23" t="n">
-        <x:v>8098.8</x:v>
+        <x:v>7828.6</x:v>
       </x:c>
       <x:c r="G185" s="28" t="n">
         <x:f>ROUND(F185-F184,1)</x:f>
-        <x:v>270.2</x:v>
+        <x:v>476.6</x:v>
       </x:c>
       <x:c r="H185" s="24" t="n">
         <x:f>IFERROR(F185/F184-1,"")</x:f>
-        <x:v>0.034514472574917576</x:v>
+        <x:v>0.06482589771490765</x:v>
       </x:c>
       <x:c r="I185" s="26" t="n">
         <x:f>ROUND(D185-E185,1)</x:f>
-        <x:v>327.6</x:v>
+        <x:v>589.8</x:v>
       </x:c>
       <x:c r="J185" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K185" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B186" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C186" s="23" t="n">
-        <x:v>8076.4</x:v>
+        <x:v>7792</x:v>
       </x:c>
       <x:c r="D186" s="23" t="n">
-        <x:v>8288.2</x:v>
+        <x:v>8119.6</x:v>
       </x:c>
       <x:c r="E186" s="23" t="n">
-        <x:v>8042</x:v>
+        <x:v>7792</x:v>
       </x:c>
       <x:c r="F186" s="23" t="n">
-        <x:v>8132.8</x:v>
-      </x:c>
-      <x:c r="G186" s="23" t="n">
+        <x:v>8098.8</x:v>
+      </x:c>
+      <x:c r="G186" s="28" t="n">
         <x:f>ROUND(F186-F185,1)</x:f>
-        <x:v>34</x:v>
+        <x:v>270.2</x:v>
       </x:c>
       <x:c r="H186" s="24" t="n">
         <x:f>IFERROR(F186/F185-1,"")</x:f>
-        <x:v>0.004198152812762368</x:v>
+        <x:v>0.034514472574917576</x:v>
       </x:c>
       <x:c r="I186" s="26" t="n">
         <x:f>ROUND(D186-E186,1)</x:f>
-        <x:v>246.2</x:v>
+        <x:v>327.6</x:v>
       </x:c>
       <x:c r="J186" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14563,148 +14563,148 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B187" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C187" s="23" t="n">
-        <x:v>8145.2</x:v>
+        <x:v>8076.4</x:v>
       </x:c>
       <x:c r="D187" s="23" t="n">
-        <x:v>8287.8</x:v>
+        <x:v>8288.2</x:v>
       </x:c>
       <x:c r="E187" s="23" t="n">
-        <x:v>8056.2</x:v>
+        <x:v>8042</x:v>
       </x:c>
       <x:c r="F187" s="23" t="n">
-        <x:v>8270</x:v>
+        <x:v>8132.8</x:v>
       </x:c>
       <x:c r="G187" s="23" t="n">
         <x:f>ROUND(F187-F186,1)</x:f>
-        <x:v>137.2</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H187" s="24" t="n">
         <x:f>IFERROR(F187/F186-1,"")</x:f>
-        <x:v>0.016869958685815423</x:v>
+        <x:v>0.004198152812762368</x:v>
       </x:c>
       <x:c r="I187" s="26" t="n">
         <x:f>ROUND(D187-E187,1)</x:f>
-        <x:v>231.6</x:v>
+        <x:v>246.2</x:v>
       </x:c>
       <x:c r="J187" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K187" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B188" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C188" s="23" t="n">
-        <x:v>8377.6</x:v>
+        <x:v>8145.2</x:v>
       </x:c>
       <x:c r="D188" s="23" t="n">
-        <x:v>8648</x:v>
+        <x:v>8287.8</x:v>
       </x:c>
       <x:c r="E188" s="23" t="n">
-        <x:v>8375.4</x:v>
+        <x:v>8056.2</x:v>
       </x:c>
       <x:c r="F188" s="23" t="n">
-        <x:v>8620.8</x:v>
-      </x:c>
-      <x:c r="G188" s="28" t="n">
+        <x:v>8270</x:v>
+      </x:c>
+      <x:c r="G188" s="23" t="n">
         <x:f>ROUND(F188-F187,1)</x:f>
-        <x:v>350.8</x:v>
+        <x:v>137.2</x:v>
       </x:c>
       <x:c r="H188" s="24" t="n">
         <x:f>IFERROR(F188/F187-1,"")</x:f>
-        <x:v>0.042418379685610574</x:v>
+        <x:v>0.016869958685815423</x:v>
       </x:c>
       <x:c r="I188" s="26" t="n">
         <x:f>ROUND(D188-E188,1)</x:f>
-        <x:v>272.6</x:v>
+        <x:v>231.6</x:v>
       </x:c>
       <x:c r="J188" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K188" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B189" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C189" s="23" t="n">
-        <x:v>8691</x:v>
+        <x:v>8377.6</x:v>
       </x:c>
       <x:c r="D189" s="23" t="n">
-        <x:v>8886.8</x:v>
+        <x:v>8648</x:v>
       </x:c>
       <x:c r="E189" s="23" t="n">
-        <x:v>8378.2</x:v>
+        <x:v>8375.4</x:v>
       </x:c>
       <x:c r="F189" s="23" t="n">
-        <x:v>8448.8</x:v>
+        <x:v>8620.8</x:v>
       </x:c>
       <x:c r="G189" s="28" t="n">
         <x:f>ROUND(F189-F188,1)</x:f>
-        <x:v>-172</x:v>
+        <x:v>350.8</x:v>
       </x:c>
       <x:c r="H189" s="24" t="n">
         <x:f>IFERROR(F189/F188-1,"")</x:f>
-        <x:v>-0.01995174461766891</x:v>
+        <x:v>0.042418379685610574</x:v>
       </x:c>
       <x:c r="I189" s="26" t="n">
         <x:f>ROUND(D189-E189,1)</x:f>
-        <x:v>508.6</x:v>
+        <x:v>272.6</x:v>
       </x:c>
       <x:c r="J189" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K189" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B190" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C190" s="23" t="n">
-        <x:v>8418.4</x:v>
+        <x:v>8691</x:v>
       </x:c>
       <x:c r="D190" s="23" t="n">
-        <x:v>8728</x:v>
+        <x:v>8886.8</x:v>
       </x:c>
       <x:c r="E190" s="23" t="n">
-        <x:v>8310</x:v>
+        <x:v>8378.2</x:v>
       </x:c>
       <x:c r="F190" s="23" t="n">
-        <x:v>8469.2</x:v>
-      </x:c>
-      <x:c r="G190" s="23" t="n">
+        <x:v>8448.8</x:v>
+      </x:c>
+      <x:c r="G190" s="28" t="n">
         <x:f>ROUND(F190-F189,1)</x:f>
-        <x:v>20.4</x:v>
+        <x:v>-172</x:v>
       </x:c>
       <x:c r="H190" s="24" t="n">
         <x:f>IFERROR(F190/F189-1,"")</x:f>
-        <x:v>0.0024145440772656013</x:v>
+        <x:v>-0.01995174461766891</x:v>
       </x:c>
       <x:c r="I190" s="26" t="n">
         <x:f>ROUND(D190-E190,1)</x:f>
-        <x:v>418</x:v>
+        <x:v>508.6</x:v>
       </x:c>
       <x:c r="J190" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14715,34 +14715,34 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B191" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C191" s="23" t="n">
-        <x:v>8543</x:v>
+        <x:v>8418.4</x:v>
       </x:c>
       <x:c r="D191" s="23" t="n">
-        <x:v>8658.2</x:v>
+        <x:v>8728</x:v>
       </x:c>
       <x:c r="E191" s="23" t="n">
-        <x:v>8218.2</x:v>
+        <x:v>8310</x:v>
       </x:c>
       <x:c r="F191" s="23" t="n">
-        <x:v>8274.6</x:v>
-      </x:c>
-      <x:c r="G191" s="28" t="n">
+        <x:v>8469.2</x:v>
+      </x:c>
+      <x:c r="G191" s="23" t="n">
         <x:f>ROUND(F191-F190,1)</x:f>
-        <x:v>-194.6</x:v>
+        <x:v>20.4</x:v>
       </x:c>
       <x:c r="H191" s="24" t="n">
         <x:f>IFERROR(F191/F190-1,"")</x:f>
-        <x:v>-0.022977376847872377</x:v>
+        <x:v>0.0024145440772656013</x:v>
       </x:c>
       <x:c r="I191" s="26" t="n">
         <x:f>ROUND(D191-E191,1)</x:f>
-        <x:v>440</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="J191" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14753,34 +14753,34 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B192" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C192" s="23" t="n">
-        <x:v>8298</x:v>
+        <x:v>8543</x:v>
       </x:c>
       <x:c r="D192" s="23" t="n">
-        <x:v>8425</x:v>
+        <x:v>8658.2</x:v>
       </x:c>
       <x:c r="E192" s="23" t="n">
-        <x:v>8101.6</x:v>
+        <x:v>8218.2</x:v>
       </x:c>
       <x:c r="F192" s="23" t="n">
-        <x:v>8190.6</x:v>
-      </x:c>
-      <x:c r="G192" s="23" t="n">
+        <x:v>8274.6</x:v>
+      </x:c>
+      <x:c r="G192" s="28" t="n">
         <x:f>ROUND(F192-F191,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-194.6</x:v>
       </x:c>
       <x:c r="H192" s="24" t="n">
         <x:f>IFERROR(F192/F191-1,"")</x:f>
-        <x:v>-0.010151548111086983</x:v>
+        <x:v>-0.022977376847872377</x:v>
       </x:c>
       <x:c r="I192" s="26" t="n">
         <x:f>ROUND(D192-E192,1)</x:f>
-        <x:v>323.4</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="J192" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14791,34 +14791,34 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B193" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C193" s="23" t="n">
-        <x:v>8050</x:v>
+        <x:v>8298</x:v>
       </x:c>
       <x:c r="D193" s="23" t="n">
-        <x:v>8237.6</x:v>
+        <x:v>8425</x:v>
       </x:c>
       <x:c r="E193" s="23" t="n">
-        <x:v>7838</x:v>
+        <x:v>8101.6</x:v>
       </x:c>
       <x:c r="F193" s="23" t="n">
-        <x:v>8117.2</x:v>
+        <x:v>8190.6</x:v>
       </x:c>
       <x:c r="G193" s="23" t="n">
         <x:f>ROUND(F193-F192,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H193" s="24" t="n">
         <x:f>IFERROR(F193/F192-1,"")</x:f>
-        <x:v>-0.008961492442556174</x:v>
+        <x:v>-0.010151548111086983</x:v>
       </x:c>
       <x:c r="I193" s="26" t="n">
         <x:f>ROUND(D193-E193,1)</x:f>
-        <x:v>399.6</x:v>
+        <x:v>323.4</x:v>
       </x:c>
       <x:c r="J193" s="22" t="str">
         <x:v>IC2606</x:v>
@@ -14829,113 +14829,113 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B194" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C194" s="23" t="n">
-        <x:v>8181.2</x:v>
+        <x:v>8050</x:v>
       </x:c>
       <x:c r="D194" s="23" t="n">
-        <x:v>8718</x:v>
+        <x:v>8237.6</x:v>
       </x:c>
       <x:c r="E194" s="23" t="n">
-        <x:v>8181.2</x:v>
+        <x:v>7838</x:v>
       </x:c>
       <x:c r="F194" s="23" t="n">
-        <x:v>8682.8</x:v>
-      </x:c>
-      <x:c r="G194" s="28" t="n">
+        <x:v>8117.2</x:v>
+      </x:c>
+      <x:c r="G194" s="23" t="n">
         <x:f>ROUND(F194-F193,1)</x:f>
-        <x:v>565.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H194" s="24" t="n">
         <x:f>IFERROR(F194/F193-1,"")</x:f>
-        <x:v>0.06967919972404268</x:v>
+        <x:v>-0.008961492442556174</x:v>
       </x:c>
       <x:c r="I194" s="26" t="n">
         <x:f>ROUND(D194-E194,1)</x:f>
-        <x:v>536.8</x:v>
+        <x:v>399.6</x:v>
       </x:c>
       <x:c r="J194" s="22" t="str">
         <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K194" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B195" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C195" s="23" t="n">
-        <x:v>8692.8</x:v>
+        <x:v>8181.2</x:v>
       </x:c>
       <x:c r="D195" s="23" t="n">
-        <x:v>8778.8</x:v>
+        <x:v>8718</x:v>
       </x:c>
       <x:c r="E195" s="23" t="n">
-        <x:v>8377</x:v>
+        <x:v>8181.2</x:v>
       </x:c>
       <x:c r="F195" s="23" t="n">
-        <x:v>8447</x:v>
+        <x:v>8682.8</x:v>
       </x:c>
       <x:c r="G195" s="28" t="n">
         <x:f>ROUND(F195-F194,1)</x:f>
-        <x:v>-235.8</x:v>
+        <x:v>565.6</x:v>
       </x:c>
       <x:c r="H195" s="24" t="n">
         <x:f>IFERROR(F195/F194-1,"")</x:f>
-        <x:v>-0.027157138250333945</x:v>
+        <x:v>0.06967919972404268</x:v>
       </x:c>
       <x:c r="I195" s="26" t="n">
         <x:f>ROUND(D195-E195,1)</x:f>
-        <x:v>401.8</x:v>
+        <x:v>536.8</x:v>
       </x:c>
       <x:c r="J195" s="22" t="str">
-        <x:v>IC2606/IC2609</x:v>
+        <x:v>IC2606</x:v>
       </x:c>
       <x:c r="K195" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B196" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C196" s="23" t="n">
-        <x:v>8463.8</x:v>
+        <x:v>8692.8</x:v>
       </x:c>
       <x:c r="D196" s="23" t="n">
-        <x:v>8873.8</x:v>
+        <x:v>8778.8</x:v>
       </x:c>
       <x:c r="E196" s="23" t="n">
-        <x:v>8350.4</x:v>
+        <x:v>8377</x:v>
       </x:c>
       <x:c r="F196" s="23" t="n">
-        <x:v>8538</x:v>
-      </x:c>
-      <x:c r="G196" s="23" t="n">
+        <x:v>8447</x:v>
+      </x:c>
+      <x:c r="G196" s="28" t="n">
         <x:f>ROUND(F196-F195,1)</x:f>
-        <x:v>91</x:v>
+        <x:v>-235.8</x:v>
       </x:c>
       <x:c r="H196" s="24" t="n">
         <x:f>IFERROR(F196/F195-1,"")</x:f>
-        <x:v>0.010773055522670827</x:v>
+        <x:v>-0.027157138250333945</x:v>
       </x:c>
       <x:c r="I196" s="26" t="n">
         <x:f>ROUND(D196-E196,1)</x:f>
-        <x:v>523.4</x:v>
+        <x:v>401.8</x:v>
       </x:c>
       <x:c r="J196" s="22" t="str">
-        <x:v>IC2609</x:v>
+        <x:v>IC2606/IC2609</x:v>
       </x:c>
       <x:c r="K196" s="22" t="n">
         <x:v>5</x:v>
@@ -14943,34 +14943,34 @@
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B197" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C197" s="23" t="n">
-        <x:v>8574.4</x:v>
+        <x:v>8463.8</x:v>
       </x:c>
       <x:c r="D197" s="23" t="n">
-        <x:v>8618</x:v>
+        <x:v>8873.8</x:v>
       </x:c>
       <x:c r="E197" s="23" t="n">
-        <x:v>8173</x:v>
+        <x:v>8350.4</x:v>
       </x:c>
       <x:c r="F197" s="23" t="n">
-        <x:v>8333</x:v>
-      </x:c>
-      <x:c r="G197" s="28" t="n">
+        <x:v>8538</x:v>
+      </x:c>
+      <x:c r="G197" s="23" t="n">
         <x:f>ROUND(F197-F196,1)</x:f>
-        <x:v>-205</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H197" s="24" t="n">
         <x:f>IFERROR(F197/F196-1,"")</x:f>
-        <x:v>-0.024010306863434083</x:v>
+        <x:v>0.010773055522670827</x:v>
       </x:c>
       <x:c r="I197" s="26" t="n">
         <x:f>ROUND(D197-E197,1)</x:f>
-        <x:v>445</x:v>
+        <x:v>523.4</x:v>
       </x:c>
       <x:c r="J197" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -14981,34 +14981,34 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B198" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C198" s="23" t="n">
-        <x:v>8303</x:v>
+        <x:v>8574.4</x:v>
       </x:c>
       <x:c r="D198" s="23" t="n">
-        <x:v>8328</x:v>
+        <x:v>8618</x:v>
       </x:c>
       <x:c r="E198" s="23" t="n">
-        <x:v>7362.8</x:v>
+        <x:v>8173</x:v>
       </x:c>
       <x:c r="F198" s="23" t="n">
-        <x:v>7389</x:v>
+        <x:v>8333</x:v>
       </x:c>
       <x:c r="G198" s="28" t="n">
         <x:f>ROUND(F198-F197,1)</x:f>
-        <x:v>-944</x:v>
+        <x:v>-205</x:v>
       </x:c>
       <x:c r="H198" s="24" t="n">
         <x:f>IFERROR(F198/F197-1,"")</x:f>
-        <x:v>-0.11328453138125527</x:v>
+        <x:v>-0.024010306863434083</x:v>
       </x:c>
       <x:c r="I198" s="26" t="n">
         <x:f>ROUND(D198-E198,1)</x:f>
-        <x:v>965.2</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="J198" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15019,34 +15019,34 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B199" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C199" s="23" t="n">
-        <x:v>7490</x:v>
+        <x:v>8303</x:v>
       </x:c>
       <x:c r="D199" s="23" t="n">
-        <x:v>7765.6</x:v>
+        <x:v>8328</x:v>
       </x:c>
       <x:c r="E199" s="23" t="n">
-        <x:v>7092</x:v>
+        <x:v>7362.8</x:v>
       </x:c>
       <x:c r="F199" s="23" t="n">
-        <x:v>7416</x:v>
-      </x:c>
-      <x:c r="G199" s="23" t="n">
+        <x:v>7389</x:v>
+      </x:c>
+      <x:c r="G199" s="28" t="n">
         <x:f>ROUND(F199-F198,1)</x:f>
-        <x:v>27</x:v>
+        <x:v>-944</x:v>
       </x:c>
       <x:c r="H199" s="24" t="n">
         <x:f>IFERROR(F199/F198-1,"")</x:f>
-        <x:v>0.0036540803897686658</x:v>
+        <x:v>-0.11328453138125527</x:v>
       </x:c>
       <x:c r="I199" s="26" t="n">
         <x:f>ROUND(D199-E199,1)</x:f>
-        <x:v>673.6</x:v>
+        <x:v>965.2</x:v>
       </x:c>
       <x:c r="J199" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15057,34 +15057,34 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B200" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C200" s="23" t="n">
-        <x:v>7447</x:v>
+        <x:v>7490</x:v>
       </x:c>
       <x:c r="D200" s="23" t="n">
-        <x:v>7666.6</x:v>
+        <x:v>7765.6</x:v>
       </x:c>
       <x:c r="E200" s="23" t="n">
-        <x:v>7106</x:v>
+        <x:v>7092</x:v>
       </x:c>
       <x:c r="F200" s="23" t="n">
-        <x:v>7395</x:v>
+        <x:v>7416</x:v>
       </x:c>
       <x:c r="G200" s="23" t="n">
         <x:f>ROUND(F200-F199,1)</x:f>
-        <x:v>-21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H200" s="24" t="n">
         <x:f>IFERROR(F200/F199-1,"")</x:f>
-        <x:v>-0.0028317152103559673</x:v>
+        <x:v>0.0036540803897686658</x:v>
       </x:c>
       <x:c r="I200" s="26" t="n">
         <x:f>ROUND(D200-E200,1)</x:f>
-        <x:v>560.6</x:v>
+        <x:v>673.6</x:v>
       </x:c>
       <x:c r="J200" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15095,34 +15095,34 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B201" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C201" s="23" t="n">
-        <x:v>7391</x:v>
+        <x:v>7447</x:v>
       </x:c>
       <x:c r="D201" s="23" t="n">
-        <x:v>7882.6</x:v>
+        <x:v>7666.6</x:v>
       </x:c>
       <x:c r="E201" s="23" t="n">
-        <x:v>7335</x:v>
+        <x:v>7106</x:v>
       </x:c>
       <x:c r="F201" s="23" t="n">
-        <x:v>7877.8</x:v>
-      </x:c>
-      <x:c r="G201" s="28" t="n">
+        <x:v>7395</x:v>
+      </x:c>
+      <x:c r="G201" s="23" t="n">
         <x:f>ROUND(F201-F200,1)</x:f>
-        <x:v>482.8</x:v>
+        <x:v>-21</x:v>
       </x:c>
       <x:c r="H201" s="24" t="n">
         <x:f>IFERROR(F201/F200-1,"")</x:f>
-        <x:v>0.06528735632183902</x:v>
+        <x:v>-0.0028317152103559673</x:v>
       </x:c>
       <x:c r="I201" s="26" t="n">
         <x:f>ROUND(D201-E201,1)</x:f>
-        <x:v>547.6</x:v>
+        <x:v>560.6</x:v>
       </x:c>
       <x:c r="J201" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15133,34 +15133,34 @@
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B202" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C202" s="23" t="n">
-        <x:v>7888</x:v>
+        <x:v>7391</x:v>
       </x:c>
       <x:c r="D202" s="23" t="n">
-        <x:v>8024</x:v>
+        <x:v>7882.6</x:v>
       </x:c>
       <x:c r="E202" s="23" t="n">
-        <x:v>7795.8</x:v>
+        <x:v>7335</x:v>
       </x:c>
       <x:c r="F202" s="23" t="n">
-        <x:v>7861.2</x:v>
-      </x:c>
-      <x:c r="G202" s="23" t="n">
+        <x:v>7877.8</x:v>
+      </x:c>
+      <x:c r="G202" s="28" t="n">
         <x:f>ROUND(F202-F201,1)</x:f>
-        <x:v>-16.6</x:v>
+        <x:v>482.8</x:v>
       </x:c>
       <x:c r="H202" s="24" t="n">
         <x:f>IFERROR(F202/F201-1,"")</x:f>
-        <x:v>-0.0021071872857905127</x:v>
+        <x:v>0.06528735632183902</x:v>
       </x:c>
       <x:c r="I202" s="26" t="n">
         <x:f>ROUND(D202-E202,1)</x:f>
-        <x:v>228.2</x:v>
+        <x:v>547.6</x:v>
       </x:c>
       <x:c r="J202" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15171,34 +15171,34 @@
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B203" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C203" s="23" t="n">
-        <x:v>7885</x:v>
+        <x:v>7888</x:v>
       </x:c>
       <x:c r="D203" s="23" t="n">
-        <x:v>8091.8</x:v>
+        <x:v>8024</x:v>
       </x:c>
       <x:c r="E203" s="23" t="n">
-        <x:v>7669.6</x:v>
+        <x:v>7795.8</x:v>
       </x:c>
       <x:c r="F203" s="23" t="n">
-        <x:v>7762</x:v>
+        <x:v>7861.2</x:v>
       </x:c>
       <x:c r="G203" s="23" t="n">
         <x:f>ROUND(F203-F202,1)</x:f>
-        <x:v>-99.2</x:v>
+        <x:v>-16.6</x:v>
       </x:c>
       <x:c r="H203" s="24" t="n">
         <x:f>IFERROR(F203/F202-1,"")</x:f>
-        <x:v>-0.012618938584439965</x:v>
+        <x:v>-0.0021071872857905127</x:v>
       </x:c>
       <x:c r="I203" s="26" t="n">
         <x:f>ROUND(D203-E203,1)</x:f>
-        <x:v>422.2</x:v>
+        <x:v>228.2</x:v>
       </x:c>
       <x:c r="J203" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15209,34 +15209,34 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B204" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C204" s="23" t="n">
-        <x:v>7757</x:v>
+        <x:v>7885</x:v>
       </x:c>
       <x:c r="D204" s="23" t="n">
-        <x:v>7931</x:v>
+        <x:v>8091.8</x:v>
       </x:c>
       <x:c r="E204" s="23" t="n">
-        <x:v>7496</x:v>
+        <x:v>7669.6</x:v>
       </x:c>
       <x:c r="F204" s="23" t="n">
-        <x:v>7853.8</x:v>
+        <x:v>7762</x:v>
       </x:c>
       <x:c r="G204" s="23" t="n">
         <x:f>ROUND(F204-F203,1)</x:f>
-        <x:v>91.8</x:v>
+        <x:v>-99.2</x:v>
       </x:c>
       <x:c r="H204" s="24" t="n">
         <x:f>IFERROR(F204/F203-1,"")</x:f>
-        <x:v>0.011826848750322139</x:v>
+        <x:v>-0.012618938584439965</x:v>
       </x:c>
       <x:c r="I204" s="26" t="n">
         <x:f>ROUND(D204-E204,1)</x:f>
-        <x:v>435</x:v>
+        <x:v>422.2</x:v>
       </x:c>
       <x:c r="J204" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15247,34 +15247,34 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B205" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C205" s="23" t="n">
-        <x:v>7761</x:v>
+        <x:v>7757</x:v>
       </x:c>
       <x:c r="D205" s="23" t="n">
-        <x:v>7913</x:v>
+        <x:v>7931</x:v>
       </x:c>
       <x:c r="E205" s="23" t="n">
-        <x:v>7568</x:v>
+        <x:v>7496</x:v>
       </x:c>
       <x:c r="F205" s="23" t="n">
-        <x:v>7608</x:v>
-      </x:c>
-      <x:c r="G205" s="28" t="n">
+        <x:v>7853.8</x:v>
+      </x:c>
+      <x:c r="G205" s="23" t="n">
         <x:f>ROUND(F205-F204,1)</x:f>
-        <x:v>-245.8</x:v>
+        <x:v>91.8</x:v>
       </x:c>
       <x:c r="H205" s="24" t="n">
         <x:f>IFERROR(F205/F204-1,"")</x:f>
-        <x:v>-0.03129695179403602</x:v>
+        <x:v>0.011826848750322139</x:v>
       </x:c>
       <x:c r="I205" s="26" t="n">
         <x:f>ROUND(D205-E205,1)</x:f>
-        <x:v>345</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="J205" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15285,34 +15285,34 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B206" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C206" s="23" t="n">
-        <x:v>7665.6</x:v>
+        <x:v>7761</x:v>
       </x:c>
       <x:c r="D206" s="23" t="n">
-        <x:v>7817.2</x:v>
+        <x:v>7913</x:v>
       </x:c>
       <x:c r="E206" s="23" t="n">
-        <x:v>7418.8</x:v>
+        <x:v>7568</x:v>
       </x:c>
       <x:c r="F206" s="23" t="n">
-        <x:v>7569</x:v>
-      </x:c>
-      <x:c r="G206" s="23" t="n">
+        <x:v>7608</x:v>
+      </x:c>
+      <x:c r="G206" s="28" t="n">
         <x:f>ROUND(F206-F205,1)</x:f>
-        <x:v>-39</x:v>
+        <x:v>-245.8</x:v>
       </x:c>
       <x:c r="H206" s="24" t="n">
         <x:f>IFERROR(F206/F205-1,"")</x:f>
-        <x:v>-0.005126182965299653</x:v>
+        <x:v>-0.03129695179403602</x:v>
       </x:c>
       <x:c r="I206" s="26" t="n">
         <x:f>ROUND(D206-E206,1)</x:f>
-        <x:v>398.4</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="J206" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15323,34 +15323,34 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B207" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C207" s="23" t="n">
-        <x:v>7482.2</x:v>
+        <x:v>7665.6</x:v>
       </x:c>
       <x:c r="D207" s="23" t="n">
-        <x:v>7820</x:v>
+        <x:v>7817.2</x:v>
       </x:c>
       <x:c r="E207" s="23" t="n">
-        <x:v>7452.2</x:v>
+        <x:v>7418.8</x:v>
       </x:c>
       <x:c r="F207" s="23" t="n">
-        <x:v>7789.8</x:v>
-      </x:c>
-      <x:c r="G207" s="28" t="n">
+        <x:v>7569</x:v>
+      </x:c>
+      <x:c r="G207" s="23" t="n">
         <x:f>ROUND(F207-F206,1)</x:f>
-        <x:v>220.8</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="H207" s="24" t="n">
         <x:f>IFERROR(F207/F206-1,"")</x:f>
-        <x:v>0.02917162108600868</x:v>
+        <x:v>-0.005126182965299653</x:v>
       </x:c>
       <x:c r="I207" s="26" t="n">
         <x:f>ROUND(D207-E207,1)</x:f>
-        <x:v>367.8</x:v>
+        <x:v>398.4</x:v>
       </x:c>
       <x:c r="J207" s="22" t="str">
         <x:v>IC2609</x:v>
@@ -15360,193 +15360,193 @@
       </x:c>
     </x:row>
     <x:row r="208">
-      <x:c r="A208" s="31" t="str">
+      <x:c r="A208" s="22" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B208" s="22" t="str">
+        <x:v>9月14日-9月18日</x:v>
+      </x:c>
+      <x:c r="C208" s="23" t="n">
+        <x:v>7482.2</x:v>
+      </x:c>
+      <x:c r="D208" s="23" t="n">
+        <x:v>7820</x:v>
+      </x:c>
+      <x:c r="E208" s="23" t="n">
+        <x:v>7452.2</x:v>
+      </x:c>
+      <x:c r="F208" s="23" t="n">
+        <x:v>7789.8</x:v>
+      </x:c>
+      <x:c r="G208" s="28" t="n">
+        <x:f>ROUND(F208-F207,1)</x:f>
+        <x:v>220.8</x:v>
+      </x:c>
+      <x:c r="H208" s="24" t="n">
+        <x:f>IFERROR(F208/F207-1,"")</x:f>
+        <x:v>0.02917162108600868</x:v>
+      </x:c>
+      <x:c r="I208" s="26" t="n">
+        <x:f>ROUND(D208-E208,1)</x:f>
+        <x:v>367.8</x:v>
+      </x:c>
+      <x:c r="J208" s="22" t="str">
+        <x:v>IC2609</x:v>
+      </x:c>
+      <x:c r="K208" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="22" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B209" s="22" t="str">
+        <x:v>9月21日</x:v>
+      </x:c>
+      <x:c r="C209" s="23" t="n">
+        <x:v>7688</x:v>
+      </x:c>
+      <x:c r="D209" s="23" t="n">
+        <x:v>7728</x:v>
+      </x:c>
+      <x:c r="E209" s="23" t="n">
+        <x:v>7640</x:v>
+      </x:c>
+      <x:c r="F209" s="23" t="n">
+        <x:v>7672.6</x:v>
+      </x:c>
+      <x:c r="G209" s="23" t="n">
+        <x:f>ROUND(F209-F208,1)</x:f>
+        <x:v>-117.2</x:v>
+      </x:c>
+      <x:c r="H209" s="24" t="n">
+        <x:f>IFERROR(F209/F208-1,"")</x:f>
+        <x:v>-0.015045315669208414</x:v>
+      </x:c>
+      <x:c r="I209" s="23" t="n">
+        <x:f>ROUND(D209-E209,1)</x:f>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="J209" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
+      <x:c r="K209" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B208" s="30" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C208" s="30"/>
-      <x:c r="D208" s="30"/>
-      <x:c r="E208" s="30"/>
-      <x:c r="F208" s="30"/>
-      <x:c r="G208" s="30"/>
-      <x:c r="H208" s="30"/>
-      <x:c r="I208" s="32" t="n">
-        <x:f>ROUND(SUM(I172:I207),1)</x:f>
-        <x:v>16193.2</x:v>
-      </x:c>
-      <x:c r="J208" s="30"/>
-      <x:c r="K208" s="30"/>
-    </x:row>
-    <x:row r="209">
-      <x:c r="A209" s="31" t="str">
+      <x:c r="B210" s="30" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C210" s="30"/>
+      <x:c r="D210" s="30"/>
+      <x:c r="E210" s="30"/>
+      <x:c r="F210" s="30"/>
+      <x:c r="G210" s="30"/>
+      <x:c r="H210" s="30"/>
+      <x:c r="I210" s="32" t="n">
+        <x:f>ROUND(SUM(I173:I209),1)</x:f>
+        <x:v>16281.2</x:v>
+      </x:c>
+      <x:c r="J210" s="30"/>
+      <x:c r="K210" s="30"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B209" s="30"/>
-      <x:c r="C209" s="30"/>
-      <x:c r="D209" s="30"/>
-      <x:c r="E209" s="30"/>
-      <x:c r="F209" s="30"/>
-      <x:c r="G209" s="30"/>
-      <x:c r="H209" s="30"/>
-      <x:c r="I209" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I172:I207),0),1)</x:f>
-        <x:v>449.8</x:v>
-      </x:c>
-      <x:c r="J209" s="30"/>
-      <x:c r="K209" s="30"/>
-    </x:row>
-    <x:row r="211">
-      <x:c r="A211" s="17" t="str">
+      <x:c r="B211" s="30"/>
+      <x:c r="C211" s="30"/>
+      <x:c r="D211" s="30"/>
+      <x:c r="E211" s="30"/>
+      <x:c r="F211" s="30"/>
+      <x:c r="G211" s="30"/>
+      <x:c r="H211" s="30"/>
+      <x:c r="I211" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I173:I209),0),1)</x:f>
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="J211" s="30"/>
+      <x:c r="K211" s="30"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="17" t="str">
         <x:v>IF主力</x:v>
       </x:c>
-      <x:c r="B211" s="17"/>
-      <x:c r="C211" s="17"/>
-      <x:c r="D211" s="17"/>
-      <x:c r="E211" s="17"/>
-      <x:c r="F211" s="17"/>
-      <x:c r="G211" s="17"/>
-      <x:c r="H211" s="17"/>
-      <x:c r="I211" s="17"/>
-      <x:c r="J211" s="17"/>
-      <x:c r="K211" s="17"/>
-    </x:row>
-    <x:row r="212">
-      <x:c r="A212" s="20" t="str">
+      <x:c r="B213" s="17"/>
+      <x:c r="C213" s="17"/>
+      <x:c r="D213" s="17"/>
+      <x:c r="E213" s="17"/>
+      <x:c r="F213" s="17"/>
+      <x:c r="G213" s="17"/>
+      <x:c r="H213" s="17"/>
+      <x:c r="I213" s="17"/>
+      <x:c r="J213" s="17"/>
+      <x:c r="K213" s="17"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B212" s="20" t="str">
+      <x:c r="B214" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C212" s="20" t="str">
+      <x:c r="C214" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D212" s="20" t="str">
+      <x:c r="D214" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E212" s="20" t="str">
+      <x:c r="E214" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F212" s="20" t="str">
+      <x:c r="F214" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G212" s="20" t="str">
+      <x:c r="G214" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H212" s="20" t="str">
+      <x:c r="H214" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I212" s="20" t="str">
+      <x:c r="I214" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J212" s="20" t="str">
+      <x:c r="J214" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K212" s="20" t="str">
+      <x:c r="K214" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213">
-      <x:c r="A213" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B213" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C213" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="D213" s="23" t="n">
-        <x:v>4785.8</x:v>
-      </x:c>
-      <x:c r="E213" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="F213" s="23" t="n">
-        <x:v>4743.8</x:v>
-      </x:c>
-      <x:c r="G213" s="23"/>
-      <x:c r="H213" s="24"/>
-      <x:c r="I213" s="26" t="n">
-        <x:f>ROUND(D213-E213,1)</x:f>
-        <x:v>158.8</x:v>
-      </x:c>
-      <x:c r="J213" s="22" t="str">
-        <x:v>IF2603</x:v>
-      </x:c>
-      <x:c r="K213" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214">
-      <x:c r="A214" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B214" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
-      </x:c>
-      <x:c r="C214" s="23" t="n">
-        <x:v>4762</x:v>
-      </x:c>
-      <x:c r="D214" s="23" t="n">
-        <x:v>4833.2</x:v>
-      </x:c>
-      <x:c r="E214" s="23" t="n">
-        <x:v>4707</x:v>
-      </x:c>
-      <x:c r="F214" s="23" t="n">
-        <x:v>4723.2</x:v>
-      </x:c>
-      <x:c r="G214" s="23" t="n">
-        <x:f>ROUND(F214-F213,1)</x:f>
-        <x:v>-20.6</x:v>
-      </x:c>
-      <x:c r="H214" s="24" t="n">
-        <x:f>IFERROR(F214/F213-1,"")</x:f>
-        <x:v>-0.004342510223871221</x:v>
-      </x:c>
-      <x:c r="I214" s="26" t="n">
-        <x:f>ROUND(D214-E214,1)</x:f>
-        <x:v>126.2</x:v>
-      </x:c>
-      <x:c r="J214" s="22" t="str">
-        <x:v>IF2603</x:v>
-      </x:c>
-      <x:c r="K214" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B215" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C215" s="23" t="n">
-        <x:v>4711.8</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="D215" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4785.8</x:v>
       </x:c>
       <x:c r="E215" s="23" t="n">
-        <x:v>4672.8</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="F215" s="23" t="n">
-        <x:v>4709.2</x:v>
-      </x:c>
-      <x:c r="G215" s="23" t="n">
-        <x:f>ROUND(F215-F214,1)</x:f>
-        <x:v>-14</x:v>
-      </x:c>
-      <x:c r="H215" s="24" t="n">
-        <x:f>IFERROR(F215/F214-1,"")</x:f>
-        <x:v>-0.002964092140921415</x:v>
-      </x:c>
+        <x:v>4743.8</x:v>
+      </x:c>
+      <x:c r="G215" s="23"/>
+      <x:c r="H215" s="24"/>
       <x:c r="I215" s="26" t="n">
         <x:f>ROUND(D215-E215,1)</x:f>
-        <x:v>90.2</x:v>
+        <x:v>158.8</x:v>
       </x:c>
       <x:c r="J215" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15557,34 +15557,34 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B216" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C216" s="23" t="n">
-        <x:v>4726.8</x:v>
+        <x:v>4762</x:v>
       </x:c>
       <x:c r="D216" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4833.2</x:v>
       </x:c>
       <x:c r="E216" s="23" t="n">
-        <x:v>4640</x:v>
+        <x:v>4707</x:v>
       </x:c>
       <x:c r="F216" s="23" t="n">
-        <x:v>4711</x:v>
+        <x:v>4723.2</x:v>
       </x:c>
       <x:c r="G216" s="23" t="n">
         <x:f>ROUND(F216-F215,1)</x:f>
-        <x:v>1.8</x:v>
+        <x:v>-20.6</x:v>
       </x:c>
       <x:c r="H216" s="24" t="n">
         <x:f>IFERROR(F216/F215-1,"")</x:f>
-        <x:v>0.00038223052747810016</x:v>
+        <x:v>-0.004342510223871221</x:v>
       </x:c>
       <x:c r="I216" s="26" t="n">
         <x:f>ROUND(D216-E216,1)</x:f>
-        <x:v>153</x:v>
+        <x:v>126.2</x:v>
       </x:c>
       <x:c r="J216" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15595,34 +15595,34 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B217" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C217" s="23" t="n">
-        <x:v>4680.6</x:v>
+        <x:v>4711.8</x:v>
       </x:c>
       <x:c r="D217" s="23" t="n">
-        <x:v>4724</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E217" s="23" t="n">
-        <x:v>4555.6</x:v>
+        <x:v>4672.8</x:v>
       </x:c>
       <x:c r="F217" s="23" t="n">
-        <x:v>4637.6</x:v>
+        <x:v>4709.2</x:v>
       </x:c>
       <x:c r="G217" s="23" t="n">
         <x:f>ROUND(F217-F216,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>-14</x:v>
       </x:c>
       <x:c r="H217" s="24" t="n">
         <x:f>IFERROR(F217/F216-1,"")</x:f>
-        <x:v>-0.015580556145192048</x:v>
+        <x:v>-0.002964092140921415</x:v>
       </x:c>
       <x:c r="I217" s="26" t="n">
         <x:f>ROUND(D217-E217,1)</x:f>
-        <x:v>168.4</x:v>
+        <x:v>90.2</x:v>
       </x:c>
       <x:c r="J217" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15633,34 +15633,34 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B218" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C218" s="23" t="n">
-        <x:v>4688.8</x:v>
+        <x:v>4726.8</x:v>
       </x:c>
       <x:c r="D218" s="23" t="n">
-        <x:v>4733.8</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E218" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4640</x:v>
       </x:c>
       <x:c r="F218" s="23" t="n">
-        <x:v>4627</x:v>
+        <x:v>4711</x:v>
       </x:c>
       <x:c r="G218" s="23" t="n">
         <x:f>ROUND(F218-F217,1)</x:f>
-        <x:v>-10.6</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="H218" s="24" t="n">
         <x:f>IFERROR(F218/F217-1,"")</x:f>
-        <x:v>-0.0022856649991375155</x:v>
+        <x:v>0.00038223052747810016</x:v>
       </x:c>
       <x:c r="I218" s="26" t="n">
         <x:f>ROUND(D218-E218,1)</x:f>
-        <x:v>109.8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="J218" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15671,72 +15671,72 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B219" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C219" s="23" t="n">
-        <x:v>4680.2</x:v>
+        <x:v>4680.6</x:v>
       </x:c>
       <x:c r="D219" s="23" t="n">
-        <x:v>4768</x:v>
+        <x:v>4724</x:v>
       </x:c>
       <x:c r="E219" s="23" t="n">
-        <x:v>4671.2</x:v>
+        <x:v>4555.6</x:v>
       </x:c>
       <x:c r="F219" s="23" t="n">
-        <x:v>4713.8</x:v>
+        <x:v>4637.6</x:v>
       </x:c>
       <x:c r="G219" s="23" t="n">
         <x:f>ROUND(F219-F218,1)</x:f>
-        <x:v>86.8</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H219" s="24" t="n">
         <x:f>IFERROR(F219/F218-1,"")</x:f>
-        <x:v>0.01875945537065049</x:v>
+        <x:v>-0.015580556145192048</x:v>
       </x:c>
       <x:c r="I219" s="26" t="n">
         <x:f>ROUND(D219-E219,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>168.4</x:v>
       </x:c>
       <x:c r="J219" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K219" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B220" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C220" s="23" t="n">
-        <x:v>4681.2</x:v>
+        <x:v>4688.8</x:v>
       </x:c>
       <x:c r="D220" s="23" t="n">
-        <x:v>4725</x:v>
+        <x:v>4733.8</x:v>
       </x:c>
       <x:c r="E220" s="23" t="n">
-        <x:v>4560.2</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="F220" s="23" t="n">
-        <x:v>4646</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="G220" s="23" t="n">
         <x:f>ROUND(F220-F219,1)</x:f>
-        <x:v>-67.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="H220" s="24" t="n">
         <x:f>IFERROR(F220/F219-1,"")</x:f>
-        <x:v>-0.014383300097585816</x:v>
+        <x:v>-0.0022856649991375155</x:v>
       </x:c>
       <x:c r="I220" s="26" t="n">
         <x:f>ROUND(D220-E220,1)</x:f>
-        <x:v>164.8</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J220" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15747,72 +15747,72 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B221" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C221" s="23" t="n">
-        <x:v>4600</x:v>
+        <x:v>4680.2</x:v>
       </x:c>
       <x:c r="D221" s="23" t="n">
-        <x:v>4699</x:v>
+        <x:v>4768</x:v>
       </x:c>
       <x:c r="E221" s="23" t="n">
-        <x:v>4500</x:v>
+        <x:v>4671.2</x:v>
       </x:c>
       <x:c r="F221" s="23" t="n">
-        <x:v>4658</x:v>
+        <x:v>4713.8</x:v>
       </x:c>
       <x:c r="G221" s="23" t="n">
         <x:f>ROUND(F221-F220,1)</x:f>
-        <x:v>12</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="H221" s="24" t="n">
         <x:f>IFERROR(F221/F220-1,"")</x:f>
-        <x:v>0.00258286698235044</x:v>
+        <x:v>0.01875945537065049</x:v>
       </x:c>
       <x:c r="I221" s="26" t="n">
         <x:f>ROUND(D221-E221,1)</x:f>
-        <x:v>199</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J221" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K221" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B222" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C222" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4681.2</x:v>
       </x:c>
       <x:c r="D222" s="23" t="n">
-        <x:v>4718.4</x:v>
+        <x:v>4725</x:v>
       </x:c>
       <x:c r="E222" s="23" t="n">
-        <x:v>4570</x:v>
+        <x:v>4560.2</x:v>
       </x:c>
       <x:c r="F222" s="23" t="n">
-        <x:v>4596.8</x:v>
+        <x:v>4646</x:v>
       </x:c>
       <x:c r="G222" s="23" t="n">
         <x:f>ROUND(F222-F221,1)</x:f>
-        <x:v>-61.2</x:v>
+        <x:v>-67.8</x:v>
       </x:c>
       <x:c r="H222" s="24" t="n">
         <x:f>IFERROR(F222/F221-1,"")</x:f>
-        <x:v>-0.0131386861313868</x:v>
+        <x:v>-0.014383300097585816</x:v>
       </x:c>
       <x:c r="I222" s="26" t="n">
         <x:f>ROUND(D222-E222,1)</x:f>
-        <x:v>148.4</x:v>
+        <x:v>164.8</x:v>
       </x:c>
       <x:c r="J222" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -15823,37 +15823,37 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B223" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C223" s="23" t="n">
-        <x:v>4434.4</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="D223" s="23" t="n">
-        <x:v>4466.2</x:v>
+        <x:v>4699</x:v>
       </x:c>
       <x:c r="E223" s="23" t="n">
-        <x:v>4307.2</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="F223" s="23" t="n">
-        <x:v>4427.4</x:v>
-      </x:c>
-      <x:c r="G223" s="28" t="n">
+        <x:v>4658</x:v>
+      </x:c>
+      <x:c r="G223" s="23" t="n">
         <x:f>ROUND(F223-F222,1)</x:f>
-        <x:v>-169.4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H223" s="24" t="n">
         <x:f>IFERROR(F223/F222-1,"")</x:f>
-        <x:v>-0.0368517229376959</x:v>
+        <x:v>0.00258286698235044</x:v>
       </x:c>
       <x:c r="I223" s="26" t="n">
         <x:f>ROUND(D223-E223,1)</x:f>
-        <x:v>159</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="J223" s="22" t="str">
-        <x:v>IF2606</x:v>
+        <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K223" s="22" t="n">
         <x:v>5</x:v>
@@ -15861,37 +15861,37 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B224" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C224" s="23" t="n">
-        <x:v>4387.2</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D224" s="23" t="n">
-        <x:v>4459.8</x:v>
+        <x:v>4718.4</x:v>
       </x:c>
       <x:c r="E224" s="23" t="n">
-        <x:v>4346</x:v>
+        <x:v>4570</x:v>
       </x:c>
       <x:c r="F224" s="23" t="n">
-        <x:v>4362.2</x:v>
+        <x:v>4596.8</x:v>
       </x:c>
       <x:c r="G224" s="23" t="n">
         <x:f>ROUND(F224-F223,1)</x:f>
-        <x:v>-65.2</x:v>
+        <x:v>-61.2</x:v>
       </x:c>
       <x:c r="H224" s="24" t="n">
         <x:f>IFERROR(F224/F223-1,"")</x:f>
-        <x:v>-0.014726476035596514</x:v>
+        <x:v>-0.0131386861313868</x:v>
       </x:c>
       <x:c r="I224" s="26" t="n">
         <x:f>ROUND(D224-E224,1)</x:f>
-        <x:v>113.8</x:v>
+        <x:v>148.4</x:v>
       </x:c>
       <x:c r="J224" s="22" t="str">
-        <x:v>IF2606</x:v>
+        <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K224" s="22" t="n">
         <x:v>5</x:v>
@@ -15899,72 +15899,72 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B225" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C225" s="23" t="n">
-        <x:v>4369.8</x:v>
+        <x:v>4434.4</x:v>
       </x:c>
       <x:c r="D225" s="23" t="n">
-        <x:v>4591.8</x:v>
+        <x:v>4466.2</x:v>
       </x:c>
       <x:c r="E225" s="23" t="n">
-        <x:v>4347</x:v>
+        <x:v>4307.2</x:v>
       </x:c>
       <x:c r="F225" s="23" t="n">
-        <x:v>4562</x:v>
+        <x:v>4427.4</x:v>
       </x:c>
       <x:c r="G225" s="28" t="n">
         <x:f>ROUND(F225-F224,1)</x:f>
-        <x:v>199.8</x:v>
+        <x:v>-169.4</x:v>
       </x:c>
       <x:c r="H225" s="24" t="n">
         <x:f>IFERROR(F225/F224-1,"")</x:f>
-        <x:v>0.045802576681491125</x:v>
+        <x:v>-0.0368517229376959</x:v>
       </x:c>
       <x:c r="I225" s="26" t="n">
         <x:f>ROUND(D225-E225,1)</x:f>
-        <x:v>244.8</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J225" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K225" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B226" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C226" s="23" t="n">
-        <x:v>4542</x:v>
+        <x:v>4387.2</x:v>
       </x:c>
       <x:c r="D226" s="23" t="n">
-        <x:v>4685</x:v>
+        <x:v>4459.8</x:v>
       </x:c>
       <x:c r="E226" s="23" t="n">
-        <x:v>4541.6</x:v>
+        <x:v>4346</x:v>
       </x:c>
       <x:c r="F226" s="23" t="n">
-        <x:v>4667</x:v>
+        <x:v>4362.2</x:v>
       </x:c>
       <x:c r="G226" s="23" t="n">
         <x:f>ROUND(F226-F225,1)</x:f>
-        <x:v>105</x:v>
+        <x:v>-65.2</x:v>
       </x:c>
       <x:c r="H226" s="24" t="n">
         <x:f>IFERROR(F226/F225-1,"")</x:f>
-        <x:v>0.0230162209557212</x:v>
+        <x:v>-0.014726476035596514</x:v>
       </x:c>
       <x:c r="I226" s="26" t="n">
         <x:f>ROUND(D226-E226,1)</x:f>
-        <x:v>143.4</x:v>
+        <x:v>113.8</x:v>
       </x:c>
       <x:c r="J226" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -15975,224 +15975,224 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B227" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C227" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4369.8</x:v>
       </x:c>
       <x:c r="D227" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4591.8</x:v>
       </x:c>
       <x:c r="E227" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4347</x:v>
       </x:c>
       <x:c r="F227" s="23" t="n">
-        <x:v>4713.6</x:v>
-      </x:c>
-      <x:c r="G227" s="23" t="n">
+        <x:v>4562</x:v>
+      </x:c>
+      <x:c r="G227" s="28" t="n">
         <x:f>ROUND(F227-F226,1)</x:f>
-        <x:v>46.6</x:v>
+        <x:v>199.8</x:v>
       </x:c>
       <x:c r="H227" s="24" t="n">
         <x:f>IFERROR(F227/F226-1,"")</x:f>
-        <x:v>0.009985001071352029</x:v>
+        <x:v>0.045802576681491125</x:v>
       </x:c>
       <x:c r="I227" s="26" t="n">
         <x:f>ROUND(D227-E227,1)</x:f>
-        <x:v>106.2</x:v>
+        <x:v>244.8</x:v>
       </x:c>
       <x:c r="J227" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K227" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B228" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C228" s="23" t="n">
-        <x:v>4720</x:v>
+        <x:v>4542</x:v>
       </x:c>
       <x:c r="D228" s="23" t="n">
-        <x:v>4776.6</x:v>
+        <x:v>4685</x:v>
       </x:c>
       <x:c r="E228" s="23" t="n">
-        <x:v>4687.2</x:v>
+        <x:v>4541.6</x:v>
       </x:c>
       <x:c r="F228" s="23" t="n">
-        <x:v>4763.4</x:v>
+        <x:v>4667</x:v>
       </x:c>
       <x:c r="G228" s="23" t="n">
         <x:f>ROUND(F228-F227,1)</x:f>
-        <x:v>49.8</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H228" s="24" t="n">
         <x:f>IFERROR(F228/F227-1,"")</x:f>
-        <x:v>0.010565173116089399</x:v>
-      </x:c>
-      <x:c r="I228" s="23" t="n">
+        <x:v>0.0230162209557212</x:v>
+      </x:c>
+      <x:c r="I228" s="26" t="n">
         <x:f>ROUND(D228-E228,1)</x:f>
-        <x:v>89.4</x:v>
+        <x:v>143.4</x:v>
       </x:c>
       <x:c r="J228" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K228" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B229" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C229" s="23" t="n">
-        <x:v>4808.2</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D229" s="23" t="n">
-        <x:v>4869</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E229" s="23" t="n">
-        <x:v>4797</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="F229" s="23" t="n">
-        <x:v>4836.8</x:v>
+        <x:v>4713.6</x:v>
       </x:c>
       <x:c r="G229" s="23" t="n">
         <x:f>ROUND(F229-F228,1)</x:f>
-        <x:v>73.4</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="H229" s="24" t="n">
         <x:f>IFERROR(F229/F228-1,"")</x:f>
-        <x:v>0.015409161523281867</x:v>
-      </x:c>
-      <x:c r="I229" s="23" t="n">
+        <x:v>0.009985001071352029</x:v>
+      </x:c>
+      <x:c r="I229" s="26" t="n">
         <x:f>ROUND(D229-E229,1)</x:f>
-        <x:v>72</x:v>
+        <x:v>106.2</x:v>
       </x:c>
       <x:c r="J229" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K229" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B230" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C230" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4720</x:v>
       </x:c>
       <x:c r="D230" s="23" t="n">
-        <x:v>4995</x:v>
+        <x:v>4776.6</x:v>
       </x:c>
       <x:c r="E230" s="23" t="n">
-        <x:v>4794</x:v>
+        <x:v>4687.2</x:v>
       </x:c>
       <x:c r="F230" s="23" t="n">
-        <x:v>4824</x:v>
+        <x:v>4763.4</x:v>
       </x:c>
       <x:c r="G230" s="23" t="n">
         <x:f>ROUND(F230-F229,1)</x:f>
-        <x:v>-12.8</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="H230" s="24" t="n">
         <x:f>IFERROR(F230/F229-1,"")</x:f>
-        <x:v>-0.0026463777704267555</x:v>
-      </x:c>
-      <x:c r="I230" s="26" t="n">
+        <x:v>0.010565173116089399</x:v>
+      </x:c>
+      <x:c r="I230" s="23" t="n">
         <x:f>ROUND(D230-E230,1)</x:f>
-        <x:v>201</x:v>
+        <x:v>89.4</x:v>
       </x:c>
       <x:c r="J230" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K230" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B231" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C231" s="23" t="n">
-        <x:v>4810</x:v>
+        <x:v>4808.2</x:v>
       </x:c>
       <x:c r="D231" s="23" t="n">
-        <x:v>4900.8</x:v>
+        <x:v>4869</x:v>
       </x:c>
       <x:c r="E231" s="23" t="n">
-        <x:v>4735</x:v>
+        <x:v>4797</x:v>
       </x:c>
       <x:c r="F231" s="23" t="n">
-        <x:v>4788.2</x:v>
+        <x:v>4836.8</x:v>
       </x:c>
       <x:c r="G231" s="23" t="n">
         <x:f>ROUND(F231-F230,1)</x:f>
-        <x:v>-35.8</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="H231" s="24" t="n">
         <x:f>IFERROR(F231/F230-1,"")</x:f>
-        <x:v>-0.007421227197346614</x:v>
-      </x:c>
-      <x:c r="I231" s="26" t="n">
+        <x:v>0.015409161523281867</x:v>
+      </x:c>
+      <x:c r="I231" s="23" t="n">
         <x:f>ROUND(D231-E231,1)</x:f>
-        <x:v>165.8</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J231" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K231" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B232" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C232" s="23" t="n">
-        <x:v>4817.8</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D232" s="23" t="n">
-        <x:v>4928.4</x:v>
+        <x:v>4995</x:v>
       </x:c>
       <x:c r="E232" s="23" t="n">
-        <x:v>4793.2</x:v>
+        <x:v>4794</x:v>
       </x:c>
       <x:c r="F232" s="23" t="n">
-        <x:v>4847.8</x:v>
+        <x:v>4824</x:v>
       </x:c>
       <x:c r="G232" s="23" t="n">
         <x:f>ROUND(F232-F231,1)</x:f>
-        <x:v>59.6</x:v>
+        <x:v>-12.8</x:v>
       </x:c>
       <x:c r="H232" s="24" t="n">
         <x:f>IFERROR(F232/F231-1,"")</x:f>
-        <x:v>0.01244726619606551</x:v>
+        <x:v>-0.0026463777704267555</x:v>
       </x:c>
       <x:c r="I232" s="26" t="n">
         <x:f>ROUND(D232-E232,1)</x:f>
-        <x:v>135.2</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="J232" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -16203,34 +16203,34 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B233" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C233" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4810</x:v>
       </x:c>
       <x:c r="D233" s="23" t="n">
-        <x:v>4964.6</x:v>
+        <x:v>4900.8</x:v>
       </x:c>
       <x:c r="E233" s="23" t="n">
-        <x:v>4762.2</x:v>
+        <x:v>4735</x:v>
       </x:c>
       <x:c r="F233" s="23" t="n">
-        <x:v>4776.8</x:v>
+        <x:v>4788.2</x:v>
       </x:c>
       <x:c r="G233" s="23" t="n">
         <x:f>ROUND(F233-F232,1)</x:f>
-        <x:v>-71</x:v>
+        <x:v>-35.8</x:v>
       </x:c>
       <x:c r="H233" s="24" t="n">
         <x:f>IFERROR(F233/F232-1,"")</x:f>
-        <x:v>-0.014645818721894521</x:v>
+        <x:v>-0.007421227197346614</x:v>
       </x:c>
       <x:c r="I233" s="26" t="n">
         <x:f>ROUND(D233-E233,1)</x:f>
-        <x:v>202.4</x:v>
+        <x:v>165.8</x:v>
       </x:c>
       <x:c r="J233" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -16241,34 +16241,34 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B234" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C234" s="23" t="n">
-        <x:v>4700</x:v>
+        <x:v>4817.8</x:v>
       </x:c>
       <x:c r="D234" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4928.4</x:v>
       </x:c>
       <x:c r="E234" s="23" t="n">
-        <x:v>4640.2</x:v>
+        <x:v>4793.2</x:v>
       </x:c>
       <x:c r="F234" s="23" t="n">
-        <x:v>4769.8</x:v>
+        <x:v>4847.8</x:v>
       </x:c>
       <x:c r="G234" s="23" t="n">
         <x:f>ROUND(F234-F233,1)</x:f>
-        <x:v>-7</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="H234" s="24" t="n">
         <x:f>IFERROR(F234/F233-1,"")</x:f>
-        <x:v>-0.0014654161781946229</x:v>
+        <x:v>0.01244726619606551</x:v>
       </x:c>
       <x:c r="I234" s="26" t="n">
         <x:f>ROUND(D234-E234,1)</x:f>
-        <x:v>152.8</x:v>
+        <x:v>135.2</x:v>
       </x:c>
       <x:c r="J234" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -16279,75 +16279,75 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B235" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C235" s="23" t="n">
-        <x:v>4819</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D235" s="23" t="n">
-        <x:v>4971</x:v>
+        <x:v>4964.6</x:v>
       </x:c>
       <x:c r="E235" s="23" t="n">
-        <x:v>4804.8</x:v>
+        <x:v>4762.2</x:v>
       </x:c>
       <x:c r="F235" s="23" t="n">
-        <x:v>4960.6</x:v>
-      </x:c>
-      <x:c r="G235" s="28" t="n">
+        <x:v>4776.8</x:v>
+      </x:c>
+      <x:c r="G235" s="23" t="n">
         <x:f>ROUND(F235-F234,1)</x:f>
-        <x:v>190.8</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="H235" s="24" t="n">
         <x:f>IFERROR(F235/F234-1,"")</x:f>
-        <x:v>0.040001677219170695</x:v>
+        <x:v>-0.014645818721894521</x:v>
       </x:c>
       <x:c r="I235" s="26" t="n">
         <x:f>ROUND(D235-E235,1)</x:f>
-        <x:v>166.2</x:v>
+        <x:v>202.4</x:v>
       </x:c>
       <x:c r="J235" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K235" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B236" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C236" s="23" t="n">
-        <x:v>4956</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="D236" s="23" t="n">
-        <x:v>5030.2</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E236" s="23" t="n">
-        <x:v>4717</x:v>
+        <x:v>4640.2</x:v>
       </x:c>
       <x:c r="F236" s="23" t="n">
-        <x:v>4748.2</x:v>
-      </x:c>
-      <x:c r="G236" s="28" t="n">
+        <x:v>4769.8</x:v>
+      </x:c>
+      <x:c r="G236" s="23" t="n">
         <x:f>ROUND(F236-F235,1)</x:f>
-        <x:v>-212.4</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="H236" s="24" t="n">
         <x:f>IFERROR(F236/F235-1,"")</x:f>
-        <x:v>-0.04281740112083221</x:v>
+        <x:v>-0.0014654161781946229</x:v>
       </x:c>
       <x:c r="I236" s="26" t="n">
         <x:f>ROUND(D236-E236,1)</x:f>
-        <x:v>313.2</x:v>
+        <x:v>152.8</x:v>
       </x:c>
       <x:c r="J236" s="22" t="str">
-        <x:v>IF2606/IF2609</x:v>
+        <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K236" s="22" t="n">
         <x:v>5</x:v>
@@ -16355,75 +16355,75 @@
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B237" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C237" s="23" t="n">
-        <x:v>4759.4</x:v>
+        <x:v>4819</x:v>
       </x:c>
       <x:c r="D237" s="23" t="n">
-        <x:v>4899.6</x:v>
+        <x:v>4971</x:v>
       </x:c>
       <x:c r="E237" s="23" t="n">
-        <x:v>4705</x:v>
+        <x:v>4804.8</x:v>
       </x:c>
       <x:c r="F237" s="23" t="n">
-        <x:v>4752.2</x:v>
-      </x:c>
-      <x:c r="G237" s="23" t="n">
+        <x:v>4960.6</x:v>
+      </x:c>
+      <x:c r="G237" s="28" t="n">
         <x:f>ROUND(F237-F236,1)</x:f>
-        <x:v>4</x:v>
+        <x:v>190.8</x:v>
       </x:c>
       <x:c r="H237" s="24" t="n">
         <x:f>IFERROR(F237/F236-1,"")</x:f>
-        <x:v>0.0008424244977043305</x:v>
+        <x:v>0.040001677219170695</x:v>
       </x:c>
       <x:c r="I237" s="26" t="n">
         <x:f>ROUND(D237-E237,1)</x:f>
-        <x:v>194.6</x:v>
+        <x:v>166.2</x:v>
       </x:c>
       <x:c r="J237" s="22" t="str">
-        <x:v>IF2609</x:v>
+        <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K237" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B238" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C238" s="23" t="n">
-        <x:v>4781</x:v>
+        <x:v>4956</x:v>
       </x:c>
       <x:c r="D238" s="23" t="n">
-        <x:v>4822.2</x:v>
+        <x:v>5030.2</x:v>
       </x:c>
       <x:c r="E238" s="23" t="n">
-        <x:v>4665.2</x:v>
+        <x:v>4717</x:v>
       </x:c>
       <x:c r="F238" s="23" t="n">
-        <x:v>4704.6</x:v>
-      </x:c>
-      <x:c r="G238" s="23" t="n">
+        <x:v>4748.2</x:v>
+      </x:c>
+      <x:c r="G238" s="28" t="n">
         <x:f>ROUND(F238-F237,1)</x:f>
-        <x:v>-47.6</x:v>
+        <x:v>-212.4</x:v>
       </x:c>
       <x:c r="H238" s="24" t="n">
         <x:f>IFERROR(F238/F237-1,"")</x:f>
-        <x:v>-0.010016413450612216</x:v>
+        <x:v>-0.04281740112083221</x:v>
       </x:c>
       <x:c r="I238" s="26" t="n">
         <x:f>ROUND(D238-E238,1)</x:f>
-        <x:v>157</x:v>
+        <x:v>313.2</x:v>
       </x:c>
       <x:c r="J238" s="22" t="str">
-        <x:v>IF2609</x:v>
+        <x:v>IF2606/IF2609</x:v>
       </x:c>
       <x:c r="K238" s="22" t="n">
         <x:v>5</x:v>
@@ -16431,34 +16431,34 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
-        <x:v>4691</x:v>
+        <x:v>4759.4</x:v>
       </x:c>
       <x:c r="D239" s="23" t="n">
-        <x:v>4739.4</x:v>
+        <x:v>4899.6</x:v>
       </x:c>
       <x:c r="E239" s="23" t="n">
-        <x:v>4441.4</x:v>
+        <x:v>4705</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>4473.8</x:v>
-      </x:c>
-      <x:c r="G239" s="28" t="n">
+        <x:v>4752.2</x:v>
+      </x:c>
+      <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>-230.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>-0.04905836840539046</x:v>
+        <x:v>0.0008424244977043305</x:v>
       </x:c>
       <x:c r="I239" s="26" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
-        <x:v>298</x:v>
+        <x:v>194.6</x:v>
       </x:c>
       <x:c r="J239" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16469,34 +16469,34 @@
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B240" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C240" s="23" t="n">
-        <x:v>4530</x:v>
+        <x:v>4781</x:v>
       </x:c>
       <x:c r="D240" s="23" t="n">
-        <x:v>4707.8</x:v>
+        <x:v>4822.2</x:v>
       </x:c>
       <x:c r="E240" s="23" t="n">
-        <x:v>4465</x:v>
+        <x:v>4665.2</x:v>
       </x:c>
       <x:c r="F240" s="23" t="n">
-        <x:v>4578.2</x:v>
+        <x:v>4704.6</x:v>
       </x:c>
       <x:c r="G240" s="23" t="n">
         <x:f>ROUND(F240-F239,1)</x:f>
-        <x:v>104.4</x:v>
+        <x:v>-47.6</x:v>
       </x:c>
       <x:c r="H240" s="24" t="n">
         <x:f>IFERROR(F240/F239-1,"")</x:f>
-        <x:v>0.023335866601099653</x:v>
+        <x:v>-0.010016413450612216</x:v>
       </x:c>
       <x:c r="I240" s="26" t="n">
         <x:f>ROUND(D240-E240,1)</x:f>
-        <x:v>242.8</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="J240" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16507,34 +16507,34 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B241" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C241" s="23" t="n">
-        <x:v>4589.4</x:v>
+        <x:v>4691</x:v>
       </x:c>
       <x:c r="D241" s="23" t="n">
-        <x:v>4652.2</x:v>
+        <x:v>4739.4</x:v>
       </x:c>
       <x:c r="E241" s="23" t="n">
-        <x:v>4420</x:v>
+        <x:v>4441.4</x:v>
       </x:c>
       <x:c r="F241" s="23" t="n">
-        <x:v>4538</x:v>
-      </x:c>
-      <x:c r="G241" s="23" t="n">
+        <x:v>4473.8</x:v>
+      </x:c>
+      <x:c r="G241" s="28" t="n">
         <x:f>ROUND(F241-F240,1)</x:f>
-        <x:v>-40.2</x:v>
+        <x:v>-230.8</x:v>
       </x:c>
       <x:c r="H241" s="24" t="n">
         <x:f>IFERROR(F241/F240-1,"")</x:f>
-        <x:v>-0.008780743523655543</x:v>
+        <x:v>-0.04905836840539046</x:v>
       </x:c>
       <x:c r="I241" s="26" t="n">
         <x:f>ROUND(D241-E241,1)</x:f>
-        <x:v>232.2</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="J241" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16545,34 +16545,34 @@
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B242" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C242" s="23" t="n">
-        <x:v>4526.4</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="D242" s="23" t="n">
-        <x:v>4656.2</x:v>
+        <x:v>4707.8</x:v>
       </x:c>
       <x:c r="E242" s="23" t="n">
-        <x:v>4494.2</x:v>
+        <x:v>4465</x:v>
       </x:c>
       <x:c r="F242" s="23" t="n">
-        <x:v>4645.6</x:v>
+        <x:v>4578.2</x:v>
       </x:c>
       <x:c r="G242" s="23" t="n">
         <x:f>ROUND(F242-F241,1)</x:f>
-        <x:v>107.6</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="H242" s="24" t="n">
         <x:f>IFERROR(F242/F241-1,"")</x:f>
-        <x:v>0.02371088585279857</x:v>
+        <x:v>0.023335866601099653</x:v>
       </x:c>
       <x:c r="I242" s="26" t="n">
         <x:f>ROUND(D242-E242,1)</x:f>
-        <x:v>162</x:v>
+        <x:v>242.8</x:v>
       </x:c>
       <x:c r="J242" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16583,34 +16583,34 @@
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B243" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C243" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4589.4</x:v>
       </x:c>
       <x:c r="D243" s="23" t="n">
-        <x:v>4681</x:v>
+        <x:v>4652.2</x:v>
       </x:c>
       <x:c r="E243" s="23" t="n">
-        <x:v>4598</x:v>
+        <x:v>4420</x:v>
       </x:c>
       <x:c r="F243" s="23" t="n">
-        <x:v>4620.4</x:v>
+        <x:v>4538</x:v>
       </x:c>
       <x:c r="G243" s="23" t="n">
         <x:f>ROUND(F243-F242,1)</x:f>
-        <x:v>-25.2</x:v>
+        <x:v>-40.2</x:v>
       </x:c>
       <x:c r="H243" s="24" t="n">
         <x:f>IFERROR(F243/F242-1,"")</x:f>
-        <x:v>-0.005424487687274104</x:v>
-      </x:c>
-      <x:c r="I243" s="23" t="n">
+        <x:v>-0.008780743523655543</x:v>
+      </x:c>
+      <x:c r="I243" s="26" t="n">
         <x:f>ROUND(D243-E243,1)</x:f>
-        <x:v>83</x:v>
+        <x:v>232.2</x:v>
       </x:c>
       <x:c r="J243" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16621,34 +16621,34 @@
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B244" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C244" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4526.4</x:v>
       </x:c>
       <x:c r="D244" s="23" t="n">
-        <x:v>4700.6</x:v>
+        <x:v>4656.2</x:v>
       </x:c>
       <x:c r="E244" s="23" t="n">
-        <x:v>4531.8</x:v>
+        <x:v>4494.2</x:v>
       </x:c>
       <x:c r="F244" s="23" t="n">
-        <x:v>4576</x:v>
+        <x:v>4645.6</x:v>
       </x:c>
       <x:c r="G244" s="23" t="n">
         <x:f>ROUND(F244-F243,1)</x:f>
-        <x:v>-44.4</x:v>
+        <x:v>107.6</x:v>
       </x:c>
       <x:c r="H244" s="24" t="n">
         <x:f>IFERROR(F244/F243-1,"")</x:f>
-        <x:v>-0.00960955761405935</x:v>
+        <x:v>0.02371088585279857</x:v>
       </x:c>
       <x:c r="I244" s="26" t="n">
         <x:f>ROUND(D244-E244,1)</x:f>
-        <x:v>168.8</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J244" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16659,34 +16659,34 @@
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B245" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C245" s="23" t="n">
-        <x:v>4607.4</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="D245" s="23" t="n">
-        <x:v>4620</x:v>
+        <x:v>4681</x:v>
       </x:c>
       <x:c r="E245" s="23" t="n">
-        <x:v>4486.4</x:v>
+        <x:v>4598</x:v>
       </x:c>
       <x:c r="F245" s="23" t="n">
-        <x:v>4593.6</x:v>
+        <x:v>4620.4</x:v>
       </x:c>
       <x:c r="G245" s="23" t="n">
         <x:f>ROUND(F245-F244,1)</x:f>
-        <x:v>17.6</x:v>
+        <x:v>-25.2</x:v>
       </x:c>
       <x:c r="H245" s="24" t="n">
         <x:f>IFERROR(F245/F244-1,"")</x:f>
-        <x:v>0.0038461538461538325</x:v>
-      </x:c>
-      <x:c r="I245" s="26" t="n">
+        <x:v>-0.005424487687274104</x:v>
+      </x:c>
+      <x:c r="I245" s="23" t="n">
         <x:f>ROUND(D245-E245,1)</x:f>
-        <x:v>133.6</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J245" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16697,34 +16697,34 @@
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B246" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C246" s="23" t="n">
-        <x:v>4553</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="D246" s="23" t="n">
-        <x:v>4617.8</x:v>
+        <x:v>4700.6</x:v>
       </x:c>
       <x:c r="E246" s="23" t="n">
-        <x:v>4497.6</x:v>
+        <x:v>4531.8</x:v>
       </x:c>
       <x:c r="F246" s="23" t="n">
-        <x:v>4537.4</x:v>
+        <x:v>4576</x:v>
       </x:c>
       <x:c r="G246" s="23" t="n">
         <x:f>ROUND(F246-F245,1)</x:f>
-        <x:v>-56.2</x:v>
+        <x:v>-44.4</x:v>
       </x:c>
       <x:c r="H246" s="24" t="n">
         <x:f>IFERROR(F246/F245-1,"")</x:f>
-        <x:v>-0.01223441309648221</x:v>
+        <x:v>-0.00960955761405935</x:v>
       </x:c>
       <x:c r="I246" s="26" t="n">
         <x:f>ROUND(D246-E246,1)</x:f>
-        <x:v>120.2</x:v>
+        <x:v>168.8</x:v>
       </x:c>
       <x:c r="J246" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16735,34 +16735,34 @@
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B247" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C247" s="23" t="n">
-        <x:v>4562</x:v>
+        <x:v>4607.4</x:v>
       </x:c>
       <x:c r="D247" s="23" t="n">
-        <x:v>4584</x:v>
+        <x:v>4620</x:v>
       </x:c>
       <x:c r="E247" s="23" t="n">
-        <x:v>4451.6</x:v>
+        <x:v>4486.4</x:v>
       </x:c>
       <x:c r="F247" s="23" t="n">
-        <x:v>4503.4</x:v>
+        <x:v>4593.6</x:v>
       </x:c>
       <x:c r="G247" s="23" t="n">
         <x:f>ROUND(F247-F246,1)</x:f>
-        <x:v>-34</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="H247" s="24" t="n">
         <x:f>IFERROR(F247/F246-1,"")</x:f>
-        <x:v>-0.007493278088773314</x:v>
+        <x:v>0.0038461538461538325</x:v>
       </x:c>
       <x:c r="I247" s="26" t="n">
         <x:f>ROUND(D247-E247,1)</x:f>
-        <x:v>132.4</x:v>
+        <x:v>133.6</x:v>
       </x:c>
       <x:c r="J247" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16773,34 +16773,34 @@
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B248" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C248" s="23" t="n">
-        <x:v>4468</x:v>
+        <x:v>4553</x:v>
       </x:c>
       <x:c r="D248" s="23" t="n">
-        <x:v>4520.6</x:v>
+        <x:v>4617.8</x:v>
       </x:c>
       <x:c r="E248" s="23" t="n">
-        <x:v>4412.2</x:v>
+        <x:v>4497.6</x:v>
       </x:c>
       <x:c r="F248" s="23" t="n">
-        <x:v>4508</x:v>
+        <x:v>4537.4</x:v>
       </x:c>
       <x:c r="G248" s="23" t="n">
         <x:f>ROUND(F248-F247,1)</x:f>
-        <x:v>4.6</x:v>
+        <x:v>-56.2</x:v>
       </x:c>
       <x:c r="H248" s="24" t="n">
         <x:f>IFERROR(F248/F247-1,"")</x:f>
-        <x:v>0.0010214504596528506</x:v>
+        <x:v>-0.01223441309648221</x:v>
       </x:c>
       <x:c r="I248" s="26" t="n">
         <x:f>ROUND(D248-E248,1)</x:f>
-        <x:v>108.4</x:v>
+        <x:v>120.2</x:v>
       </x:c>
       <x:c r="J248" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -16810,231 +16810,231 @@
       </x:c>
     </x:row>
     <x:row r="249">
-      <x:c r="A249" s="31" t="str">
+      <x:c r="A249" s="22" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B249" s="22" t="str">
+        <x:v>9月7日-9月11日</x:v>
+      </x:c>
+      <x:c r="C249" s="23" t="n">
+        <x:v>4562</x:v>
+      </x:c>
+      <x:c r="D249" s="23" t="n">
+        <x:v>4584</x:v>
+      </x:c>
+      <x:c r="E249" s="23" t="n">
+        <x:v>4451.6</x:v>
+      </x:c>
+      <x:c r="F249" s="23" t="n">
+        <x:v>4503.4</x:v>
+      </x:c>
+      <x:c r="G249" s="23" t="n">
+        <x:f>ROUND(F249-F248,1)</x:f>
+        <x:v>-34</x:v>
+      </x:c>
+      <x:c r="H249" s="24" t="n">
+        <x:f>IFERROR(F249/F248-1,"")</x:f>
+        <x:v>-0.007493278088773314</x:v>
+      </x:c>
+      <x:c r="I249" s="26" t="n">
+        <x:f>ROUND(D249-E249,1)</x:f>
+        <x:v>132.4</x:v>
+      </x:c>
+      <x:c r="J249" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+      <x:c r="K249" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="22" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B250" s="22" t="str">
+        <x:v>9月14日-9月18日</x:v>
+      </x:c>
+      <x:c r="C250" s="23" t="n">
+        <x:v>4468</x:v>
+      </x:c>
+      <x:c r="D250" s="23" t="n">
+        <x:v>4520.6</x:v>
+      </x:c>
+      <x:c r="E250" s="23" t="n">
+        <x:v>4412.2</x:v>
+      </x:c>
+      <x:c r="F250" s="23" t="n">
+        <x:v>4508</x:v>
+      </x:c>
+      <x:c r="G250" s="23" t="n">
+        <x:f>ROUND(F250-F249,1)</x:f>
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="H250" s="24" t="n">
+        <x:f>IFERROR(F250/F249-1,"")</x:f>
+        <x:v>0.0010214504596528506</x:v>
+      </x:c>
+      <x:c r="I250" s="26" t="n">
+        <x:f>ROUND(D250-E250,1)</x:f>
+        <x:v>108.4</x:v>
+      </x:c>
+      <x:c r="J250" s="22" t="str">
+        <x:v>IF2609</x:v>
+      </x:c>
+      <x:c r="K250" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="22" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B251" s="22" t="str">
+        <x:v>9月21日</x:v>
+      </x:c>
+      <x:c r="C251" s="23" t="n">
+        <x:v>4451</x:v>
+      </x:c>
+      <x:c r="D251" s="23" t="n">
+        <x:v>4474.6</x:v>
+      </x:c>
+      <x:c r="E251" s="23" t="n">
+        <x:v>4434.8</x:v>
+      </x:c>
+      <x:c r="F251" s="23" t="n">
+        <x:v>4464.8</x:v>
+      </x:c>
+      <x:c r="G251" s="23" t="n">
+        <x:f>ROUND(F251-F250,1)</x:f>
+        <x:v>-43.2</x:v>
+      </x:c>
+      <x:c r="H251" s="24" t="n">
+        <x:f>IFERROR(F251/F250-1,"")</x:f>
+        <x:v>-0.0095829636202307</x:v>
+      </x:c>
+      <x:c r="I251" s="23" t="n">
+        <x:f>ROUND(D251-E251,1)</x:f>
+        <x:v>39.8</x:v>
+      </x:c>
+      <x:c r="J251" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
+      <x:c r="K251" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B249" s="30" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C249" s="30"/>
-      <x:c r="D249" s="30"/>
-      <x:c r="E249" s="30"/>
-      <x:c r="F249" s="30"/>
-      <x:c r="G249" s="30"/>
-      <x:c r="H249" s="30"/>
-      <x:c r="I249" s="32" t="n">
-        <x:f>ROUND(SUM(I213:I248),1)</x:f>
-        <x:v>5713.6</x:v>
-      </x:c>
-      <x:c r="J249" s="30"/>
-      <x:c r="K249" s="30"/>
-    </x:row>
-    <x:row r="250">
-      <x:c r="A250" s="31" t="str">
+      <x:c r="B252" s="30" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C252" s="30"/>
+      <x:c r="D252" s="30"/>
+      <x:c r="E252" s="30"/>
+      <x:c r="F252" s="30"/>
+      <x:c r="G252" s="30"/>
+      <x:c r="H252" s="30"/>
+      <x:c r="I252" s="32" t="n">
+        <x:f>ROUND(SUM(I215:I251),1)</x:f>
+        <x:v>5753.4</x:v>
+      </x:c>
+      <x:c r="J252" s="30"/>
+      <x:c r="K252" s="30"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B250" s="30"/>
-      <x:c r="C250" s="30"/>
-      <x:c r="D250" s="30"/>
-      <x:c r="E250" s="30"/>
-      <x:c r="F250" s="30"/>
-      <x:c r="G250" s="30"/>
-      <x:c r="H250" s="30"/>
-      <x:c r="I250" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I213:I248),0),1)</x:f>
-        <x:v>158.7</x:v>
-      </x:c>
-      <x:c r="J250" s="30"/>
-      <x:c r="K250" s="30"/>
-    </x:row>
-    <x:row r="252">
-      <x:c r="A252" s="17" t="str">
+      <x:c r="B253" s="30"/>
+      <x:c r="C253" s="30"/>
+      <x:c r="D253" s="30"/>
+      <x:c r="E253" s="30"/>
+      <x:c r="F253" s="30"/>
+      <x:c r="G253" s="30"/>
+      <x:c r="H253" s="30"/>
+      <x:c r="I253" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I215:I251),0),1)</x:f>
+        <x:v>155.5</x:v>
+      </x:c>
+      <x:c r="J253" s="30"/>
+      <x:c r="K253" s="30"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="17" t="str">
         <x:v>IH主力</x:v>
       </x:c>
-      <x:c r="B252" s="17"/>
-      <x:c r="C252" s="17"/>
-      <x:c r="D252" s="17"/>
-      <x:c r="E252" s="17"/>
-      <x:c r="F252" s="17"/>
-      <x:c r="G252" s="17"/>
-      <x:c r="H252" s="17"/>
-      <x:c r="I252" s="17"/>
-      <x:c r="J252" s="17"/>
-      <x:c r="K252" s="17"/>
-    </x:row>
-    <x:row r="253">
-      <x:c r="A253" s="20" t="str">
+      <x:c r="B255" s="17"/>
+      <x:c r="C255" s="17"/>
+      <x:c r="D255" s="17"/>
+      <x:c r="E255" s="17"/>
+      <x:c r="F255" s="17"/>
+      <x:c r="G255" s="17"/>
+      <x:c r="H255" s="17"/>
+      <x:c r="I255" s="17"/>
+      <x:c r="J255" s="17"/>
+      <x:c r="K255" s="17"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B253" s="20" t="str">
+      <x:c r="B256" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C253" s="20" t="str">
+      <x:c r="C256" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D253" s="20" t="str">
+      <x:c r="D256" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E253" s="20" t="str">
+      <x:c r="E256" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F253" s="20" t="str">
+      <x:c r="F256" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G253" s="20" t="str">
+      <x:c r="G256" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H253" s="20" t="str">
+      <x:c r="H256" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I253" s="20" t="str">
+      <x:c r="I256" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J253" s="20" t="str">
+      <x:c r="J256" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K253" s="20" t="str">
+      <x:c r="K256" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="254">
-      <x:c r="A254" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B254" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C254" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="D254" s="23" t="n">
-        <x:v>3165.6</x:v>
-      </x:c>
-      <x:c r="E254" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="F254" s="23" t="n">
-        <x:v>3134.8</x:v>
-      </x:c>
-      <x:c r="G254" s="23"/>
-      <x:c r="H254" s="24"/>
-      <x:c r="I254" s="26" t="n">
-        <x:f>ROUND(D254-E254,1)</x:f>
-        <x:v>124.8</x:v>
-      </x:c>
-      <x:c r="J254" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K254" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="255">
-      <x:c r="A255" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B255" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
-      </x:c>
-      <x:c r="C255" s="23" t="n">
-        <x:v>3148.4</x:v>
-      </x:c>
-      <x:c r="D255" s="23" t="n">
-        <x:v>3181.2</x:v>
-      </x:c>
-      <x:c r="E255" s="23" t="n">
-        <x:v>3074.4</x:v>
-      </x:c>
-      <x:c r="F255" s="23" t="n">
-        <x:v>3084.4</x:v>
-      </x:c>
-      <x:c r="G255" s="23" t="n">
-        <x:f>ROUND(F255-F254,1)</x:f>
-        <x:v>-50.4</x:v>
-      </x:c>
-      <x:c r="H255" s="24" t="n">
-        <x:f>IFERROR(F255/F254-1,"")</x:f>
-        <x:v>-0.016077580706903127</x:v>
-      </x:c>
-      <x:c r="I255" s="26" t="n">
-        <x:f>ROUND(D255-E255,1)</x:f>
-        <x:v>106.8</x:v>
-      </x:c>
-      <x:c r="J255" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K255" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="256">
-      <x:c r="A256" s="22" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B256" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
-      </x:c>
-      <x:c r="C256" s="23" t="n">
-        <x:v>3081.2</x:v>
-      </x:c>
-      <x:c r="D256" s="23" t="n">
-        <x:v>3102.6</x:v>
-      </x:c>
-      <x:c r="E256" s="23" t="n">
-        <x:v>3036.2</x:v>
-      </x:c>
-      <x:c r="F256" s="23" t="n">
-        <x:v>3037.8</x:v>
-      </x:c>
-      <x:c r="G256" s="23" t="n">
-        <x:f>ROUND(F256-F255,1)</x:f>
-        <x:v>-46.6</x:v>
-      </x:c>
-      <x:c r="H256" s="24" t="n">
-        <x:f>IFERROR(F256/F255-1,"")</x:f>
-        <x:v>-0.015108286862923093</x:v>
-      </x:c>
-      <x:c r="I256" s="26" t="n">
-        <x:f>ROUND(D256-E256,1)</x:f>
-        <x:v>66.4</x:v>
-      </x:c>
-      <x:c r="J256" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K256" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B257" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C257" s="23" t="n">
-        <x:v>3049.8</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="D257" s="23" t="n">
-        <x:v>3136.6</x:v>
+        <x:v>3165.6</x:v>
       </x:c>
       <x:c r="E257" s="23" t="n">
-        <x:v>3044</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="F257" s="23" t="n">
-        <x:v>3074</x:v>
-      </x:c>
-      <x:c r="G257" s="23" t="n">
-        <x:f>ROUND(F257-F256,1)</x:f>
-        <x:v>36.2</x:v>
-      </x:c>
-      <x:c r="H257" s="24" t="n">
-        <x:f>IFERROR(F257/F256-1,"")</x:f>
-        <x:v>0.011916518533148901</x:v>
-      </x:c>
+        <x:v>3134.8</x:v>
+      </x:c>
+      <x:c r="G257" s="23"/>
+      <x:c r="H257" s="24"/>
       <x:c r="I257" s="26" t="n">
         <x:f>ROUND(D257-E257,1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>124.8</x:v>
       </x:c>
       <x:c r="J257" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17045,34 +17045,34 @@
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B258" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C258" s="23" t="n">
-        <x:v>3039.4</x:v>
+        <x:v>3148.4</x:v>
       </x:c>
       <x:c r="D258" s="23" t="n">
-        <x:v>3081</x:v>
+        <x:v>3181.2</x:v>
       </x:c>
       <x:c r="E258" s="23" t="n">
-        <x:v>2984</x:v>
+        <x:v>3074.4</x:v>
       </x:c>
       <x:c r="F258" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3084.4</x:v>
       </x:c>
       <x:c r="G258" s="23" t="n">
         <x:f>ROUND(F258-F257,1)</x:f>
-        <x:v>-37.8</x:v>
+        <x:v>-50.4</x:v>
       </x:c>
       <x:c r="H258" s="24" t="n">
         <x:f>IFERROR(F258/F257-1,"")</x:f>
-        <x:v>-0.012296681847755453</x:v>
+        <x:v>-0.016077580706903127</x:v>
       </x:c>
       <x:c r="I258" s="26" t="n">
         <x:f>ROUND(D258-E258,1)</x:f>
-        <x:v>97</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J258" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17083,34 +17083,34 @@
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B259" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C259" s="23" t="n">
-        <x:v>3060.6</x:v>
+        <x:v>3081.2</x:v>
       </x:c>
       <x:c r="D259" s="23" t="n">
-        <x:v>3098</x:v>
+        <x:v>3102.6</x:v>
       </x:c>
       <x:c r="E259" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="F259" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3037.8</x:v>
       </x:c>
       <x:c r="G259" s="23" t="n">
         <x:f>ROUND(F259-F258,1)</x:f>
-        <x:v>-16.2</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H259" s="24" t="n">
         <x:f>IFERROR(F259/F258-1,"")</x:f>
-        <x:v>-0.005335616889532879</x:v>
+        <x:v>-0.015108286862923093</x:v>
       </x:c>
       <x:c r="I259" s="26" t="n">
         <x:f>ROUND(D259-E259,1)</x:f>
-        <x:v>78</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J259" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17121,72 +17121,72 @@
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B260" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C260" s="23" t="n">
-        <x:v>3049.2</x:v>
+        <x:v>3049.8</x:v>
       </x:c>
       <x:c r="D260" s="23" t="n">
-        <x:v>3086.4</x:v>
+        <x:v>3136.6</x:v>
       </x:c>
       <x:c r="E260" s="23" t="n">
-        <x:v>3022</x:v>
+        <x:v>3044</x:v>
       </x:c>
       <x:c r="F260" s="23" t="n">
-        <x:v>3045.4</x:v>
+        <x:v>3074</x:v>
       </x:c>
       <x:c r="G260" s="23" t="n">
         <x:f>ROUND(F260-F259,1)</x:f>
-        <x:v>25.4</x:v>
+        <x:v>36.2</x:v>
       </x:c>
       <x:c r="H260" s="24" t="n">
         <x:f>IFERROR(F260/F259-1,"")</x:f>
-        <x:v>0.008410596026490191</x:v>
+        <x:v>0.011916518533148901</x:v>
       </x:c>
       <x:c r="I260" s="26" t="n">
         <x:f>ROUND(D260-E260,1)</x:f>
-        <x:v>64.4</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="J260" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K260" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B261" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C261" s="23" t="n">
-        <x:v>3038</x:v>
+        <x:v>3039.4</x:v>
       </x:c>
       <x:c r="D261" s="23" t="n">
-        <x:v>3056</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E261" s="23" t="n">
-        <x:v>2950</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="F261" s="23" t="n">
-        <x:v>2990</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="G261" s="23" t="n">
         <x:f>ROUND(F261-F260,1)</x:f>
-        <x:v>-55.4</x:v>
+        <x:v>-37.8</x:v>
       </x:c>
       <x:c r="H261" s="24" t="n">
         <x:f>IFERROR(F261/F260-1,"")</x:f>
-        <x:v>-0.018191370591712164</x:v>
+        <x:v>-0.012296681847755453</x:v>
       </x:c>
       <x:c r="I261" s="26" t="n">
         <x:f>ROUND(D261-E261,1)</x:f>
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J261" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17197,34 +17197,34 @@
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B262" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C262" s="23" t="n">
-        <x:v>2965.4</x:v>
+        <x:v>3060.6</x:v>
       </x:c>
       <x:c r="D262" s="23" t="n">
-        <x:v>2989</x:v>
+        <x:v>3098</x:v>
       </x:c>
       <x:c r="E262" s="23" t="n">
-        <x:v>2912.6</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="F262" s="23" t="n">
-        <x:v>2957</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="G262" s="23" t="n">
         <x:f>ROUND(F262-F261,1)</x:f>
-        <x:v>-33</x:v>
+        <x:v>-16.2</x:v>
       </x:c>
       <x:c r="H262" s="24" t="n">
         <x:f>IFERROR(F262/F261-1,"")</x:f>
-        <x:v>-0.011036789297658833</x:v>
+        <x:v>-0.005335616889532879</x:v>
       </x:c>
       <x:c r="I262" s="26" t="n">
         <x:f>ROUND(D262-E262,1)</x:f>
-        <x:v>76.4</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J262" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17235,75 +17235,75 @@
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B263" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C263" s="23" t="n">
-        <x:v>2953</x:v>
+        <x:v>3049.2</x:v>
       </x:c>
       <x:c r="D263" s="23" t="n">
-        <x:v>2996.6</x:v>
+        <x:v>3086.4</x:v>
       </x:c>
       <x:c r="E263" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="F263" s="23" t="n">
-        <x:v>2898.4</x:v>
+        <x:v>3045.4</x:v>
       </x:c>
       <x:c r="G263" s="23" t="n">
         <x:f>ROUND(F263-F262,1)</x:f>
-        <x:v>-58.6</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="H263" s="24" t="n">
         <x:f>IFERROR(F263/F262-1,"")</x:f>
-        <x:v>-0.019817382482245516</x:v>
+        <x:v>0.008410596026490191</x:v>
       </x:c>
       <x:c r="I263" s="26" t="n">
         <x:f>ROUND(D263-E263,1)</x:f>
-        <x:v>100.6</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="J263" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K263" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B264" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C264" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>3038</x:v>
       </x:c>
       <x:c r="D264" s="23" t="n">
-        <x:v>2847.6</x:v>
+        <x:v>3056</x:v>
       </x:c>
       <x:c r="E264" s="23" t="n">
-        <x:v>2750.8</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="F264" s="23" t="n">
-        <x:v>2814.4</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="G264" s="23" t="n">
         <x:f>ROUND(F264-F263,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-55.4</x:v>
       </x:c>
       <x:c r="H264" s="24" t="n">
         <x:f>IFERROR(F264/F263-1,"")</x:f>
-        <x:v>-0.028981507038365995</x:v>
+        <x:v>-0.018191370591712164</x:v>
       </x:c>
       <x:c r="I264" s="26" t="n">
         <x:f>ROUND(D264-E264,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J264" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K264" s="22" t="n">
         <x:v>5</x:v>
@@ -17311,37 +17311,37 @@
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B265" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C265" s="23" t="n">
-        <x:v>2794.8</x:v>
+        <x:v>2965.4</x:v>
       </x:c>
       <x:c r="D265" s="23" t="n">
-        <x:v>2865.4</x:v>
+        <x:v>2989</x:v>
       </x:c>
       <x:c r="E265" s="23" t="n">
-        <x:v>2780.4</x:v>
+        <x:v>2912.6</x:v>
       </x:c>
       <x:c r="F265" s="23" t="n">
-        <x:v>2804.4</x:v>
+        <x:v>2957</x:v>
       </x:c>
       <x:c r="G265" s="23" t="n">
         <x:f>ROUND(F265-F264,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="H265" s="24" t="n">
         <x:f>IFERROR(F265/F264-1,"")</x:f>
-        <x:v>-0.0035531552018192025</x:v>
+        <x:v>-0.011036789297658833</x:v>
       </x:c>
       <x:c r="I265" s="26" t="n">
         <x:f>ROUND(D265-E265,1)</x:f>
-        <x:v>85</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="J265" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K265" s="22" t="n">
         <x:v>5</x:v>
@@ -17349,72 +17349,72 @@
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B266" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C266" s="23" t="n">
-        <x:v>2810.4</x:v>
+        <x:v>2953</x:v>
       </x:c>
       <x:c r="D266" s="23" t="n">
+        <x:v>2996.6</x:v>
+      </x:c>
+      <x:c r="E266" s="23" t="n">
         <x:v>2896</x:v>
       </x:c>
-      <x:c r="E266" s="23" t="n">
-        <x:v>2797.2</x:v>
-      </x:c>
       <x:c r="F266" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2898.4</x:v>
       </x:c>
       <x:c r="G266" s="23" t="n">
         <x:f>ROUND(F266-F265,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>-58.6</x:v>
       </x:c>
       <x:c r="H266" s="24" t="n">
         <x:f>IFERROR(F266/F265-1,"")</x:f>
-        <x:v>0.02453287690771644</x:v>
+        <x:v>-0.019817382482245516</x:v>
       </x:c>
       <x:c r="I266" s="26" t="n">
         <x:f>ROUND(D266-E266,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="J266" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K266" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B267" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C267" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D267" s="23" t="n">
-        <x:v>2930.8</x:v>
+        <x:v>2847.6</x:v>
       </x:c>
       <x:c r="E267" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2750.8</x:v>
       </x:c>
       <x:c r="F267" s="23" t="n">
-        <x:v>2888</x:v>
+        <x:v>2814.4</x:v>
       </x:c>
       <x:c r="G267" s="23" t="n">
         <x:f>ROUND(F267-F266,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H267" s="24" t="n">
         <x:f>IFERROR(F267/F266-1,"")</x:f>
-        <x:v>0.005151051092858294</x:v>
+        <x:v>-0.028981507038365995</x:v>
       </x:c>
       <x:c r="I267" s="26" t="n">
         <x:f>ROUND(D267-E267,1)</x:f>
-        <x:v>70.8</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J267" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17425,34 +17425,34 @@
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B268" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C268" s="23" t="n">
-        <x:v>2900.8</x:v>
+        <x:v>2794.8</x:v>
       </x:c>
       <x:c r="D268" s="23" t="n">
-        <x:v>2934.2</x:v>
+        <x:v>2865.4</x:v>
       </x:c>
       <x:c r="E268" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2780.4</x:v>
       </x:c>
       <x:c r="F268" s="23" t="n">
-        <x:v>2929</x:v>
+        <x:v>2804.4</x:v>
       </x:c>
       <x:c r="G268" s="23" t="n">
         <x:f>ROUND(F268-F267,1)</x:f>
-        <x:v>41</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H268" s="24" t="n">
         <x:f>IFERROR(F268/F267-1,"")</x:f>
-        <x:v>0.014196675900276956</x:v>
-      </x:c>
-      <x:c r="I268" s="23" t="n">
+        <x:v>-0.0035531552018192025</x:v>
+      </x:c>
+      <x:c r="I268" s="26" t="n">
         <x:f>ROUND(D268-E268,1)</x:f>
-        <x:v>43.2</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J268" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17463,34 +17463,34 @@
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B269" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C269" s="23" t="n">
-        <x:v>2929.2</x:v>
+        <x:v>2810.4</x:v>
       </x:c>
       <x:c r="D269" s="23" t="n">
-        <x:v>2970</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="E269" s="23" t="n">
-        <x:v>2917</x:v>
+        <x:v>2797.2</x:v>
       </x:c>
       <x:c r="F269" s="23" t="n">
-        <x:v>2968.8</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="G269" s="23" t="n">
         <x:f>ROUND(F269-F268,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>68.8</x:v>
       </x:c>
       <x:c r="H269" s="24" t="n">
         <x:f>IFERROR(F269/F268-1,"")</x:f>
-        <x:v>0.013588255377261937</x:v>
-      </x:c>
-      <x:c r="I269" s="23" t="n">
+        <x:v>0.02453287690771644</x:v>
+      </x:c>
+      <x:c r="I269" s="26" t="n">
         <x:f>ROUND(D269-E269,1)</x:f>
-        <x:v>53</x:v>
+        <x:v>98.8</x:v>
       </x:c>
       <x:c r="J269" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17501,72 +17501,72 @@
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B270" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C270" s="23" t="n">
-        <x:v>2995.2</x:v>
+        <x:v>2864.6</x:v>
       </x:c>
       <x:c r="D270" s="23" t="n">
-        <x:v>3024.8</x:v>
+        <x:v>2930.8</x:v>
       </x:c>
       <x:c r="E270" s="23" t="n">
-        <x:v>2969.2</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="F270" s="23" t="n">
-        <x:v>2981.6</x:v>
+        <x:v>2888</x:v>
       </x:c>
       <x:c r="G270" s="23" t="n">
         <x:f>ROUND(F270-F269,1)</x:f>
-        <x:v>12.8</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H270" s="24" t="n">
         <x:f>IFERROR(F270/F269-1,"")</x:f>
-        <x:v>0.0043115063325247505</x:v>
-      </x:c>
-      <x:c r="I270" s="23" t="n">
+        <x:v>0.005151051092858294</x:v>
+      </x:c>
+      <x:c r="I270" s="26" t="n">
         <x:f>ROUND(D270-E270,1)</x:f>
-        <x:v>55.6</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="J270" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K270" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B271" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C271" s="23" t="n">
-        <x:v>2997.6</x:v>
+        <x:v>2900.8</x:v>
       </x:c>
       <x:c r="D271" s="23" t="n">
-        <x:v>3041.8</x:v>
+        <x:v>2934.2</x:v>
       </x:c>
       <x:c r="E271" s="23" t="n">
-        <x:v>2927</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F271" s="23" t="n">
-        <x:v>2945</x:v>
+        <x:v>2929</x:v>
       </x:c>
       <x:c r="G271" s="23" t="n">
         <x:f>ROUND(F271-F270,1)</x:f>
-        <x:v>-36.6</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H271" s="24" t="n">
         <x:f>IFERROR(F271/F270-1,"")</x:f>
-        <x:v>-0.012275288435739218</x:v>
-      </x:c>
-      <x:c r="I271" s="26" t="n">
+        <x:v>0.014196675900276956</x:v>
+      </x:c>
+      <x:c r="I271" s="23" t="n">
         <x:f>ROUND(D271-E271,1)</x:f>
-        <x:v>114.8</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J271" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17577,110 +17577,110 @@
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B272" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C272" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2929.2</x:v>
       </x:c>
       <x:c r="D272" s="23" t="n">
-        <x:v>2981.8</x:v>
+        <x:v>2970</x:v>
       </x:c>
       <x:c r="E272" s="23" t="n">
-        <x:v>2893.2</x:v>
+        <x:v>2917</x:v>
       </x:c>
       <x:c r="F272" s="23" t="n">
-        <x:v>2899.2</x:v>
+        <x:v>2968.8</x:v>
       </x:c>
       <x:c r="G272" s="23" t="n">
         <x:f>ROUND(F272-F271,1)</x:f>
-        <x:v>-45.8</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="H272" s="24" t="n">
         <x:f>IFERROR(F272/F271-1,"")</x:f>
-        <x:v>-0.015551782682512783</x:v>
-      </x:c>
-      <x:c r="I272" s="26" t="n">
+        <x:v>0.013588255377261937</x:v>
+      </x:c>
+      <x:c r="I272" s="23" t="n">
         <x:f>ROUND(D272-E272,1)</x:f>
-        <x:v>88.6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J272" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K272" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B273" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C273" s="23" t="n">
-        <x:v>2910.8</x:v>
+        <x:v>2995.2</x:v>
       </x:c>
       <x:c r="D273" s="23" t="n">
-        <x:v>2960</x:v>
+        <x:v>3024.8</x:v>
       </x:c>
       <x:c r="E273" s="23" t="n">
-        <x:v>2871</x:v>
+        <x:v>2969.2</x:v>
       </x:c>
       <x:c r="F273" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2981.6</x:v>
       </x:c>
       <x:c r="G273" s="23" t="n">
         <x:f>ROUND(F273-F272,1)</x:f>
-        <x:v>1.4</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="H273" s="24" t="n">
         <x:f>IFERROR(F273/F272-1,"")</x:f>
-        <x:v>0.0004828918322297149</x:v>
-      </x:c>
-      <x:c r="I273" s="26" t="n">
+        <x:v>0.0043115063325247505</x:v>
+      </x:c>
+      <x:c r="I273" s="23" t="n">
         <x:f>ROUND(D273-E273,1)</x:f>
-        <x:v>89</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="J273" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K273" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B274" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C274" s="23" t="n">
-        <x:v>2901</x:v>
+        <x:v>2997.6</x:v>
       </x:c>
       <x:c r="D274" s="23" t="n">
-        <x:v>2924.2</x:v>
+        <x:v>3041.8</x:v>
       </x:c>
       <x:c r="E274" s="23" t="n">
-        <x:v>2841.6</x:v>
+        <x:v>2927</x:v>
       </x:c>
       <x:c r="F274" s="23" t="n">
-        <x:v>2844</x:v>
+        <x:v>2945</x:v>
       </x:c>
       <x:c r="G274" s="23" t="n">
         <x:f>ROUND(F274-F273,1)</x:f>
-        <x:v>-56.6</x:v>
+        <x:v>-36.6</x:v>
       </x:c>
       <x:c r="H274" s="24" t="n">
         <x:f>IFERROR(F274/F273-1,"")</x:f>
-        <x:v>-0.019513204164655518</x:v>
+        <x:v>-0.012275288435739218</x:v>
       </x:c>
       <x:c r="I274" s="26" t="n">
         <x:f>ROUND(D274-E274,1)</x:f>
-        <x:v>82.6</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="J274" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17691,34 +17691,34 @@
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B275" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C275" s="23" t="n">
-        <x:v>2808.4</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D275" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2981.8</x:v>
       </x:c>
       <x:c r="E275" s="23" t="n">
-        <x:v>2791.2</x:v>
+        <x:v>2893.2</x:v>
       </x:c>
       <x:c r="F275" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2899.2</x:v>
       </x:c>
       <x:c r="G275" s="23" t="n">
         <x:f>ROUND(F275-F274,1)</x:f>
-        <x:v>53.2</x:v>
+        <x:v>-45.8</x:v>
       </x:c>
       <x:c r="H275" s="24" t="n">
         <x:f>IFERROR(F275/F274-1,"")</x:f>
-        <x:v>0.01870604781997187</x:v>
+        <x:v>-0.015551782682512783</x:v>
       </x:c>
       <x:c r="I275" s="26" t="n">
         <x:f>ROUND(D275-E275,1)</x:f>
-        <x:v>111.4</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="J275" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17729,75 +17729,75 @@
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B276" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C276" s="23" t="n">
-        <x:v>2926.2</x:v>
+        <x:v>2910.8</x:v>
       </x:c>
       <x:c r="D276" s="23" t="n">
-        <x:v>2954.6</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="E276" s="23" t="n">
-        <x:v>2903.4</x:v>
+        <x:v>2871</x:v>
       </x:c>
       <x:c r="F276" s="23" t="n">
-        <x:v>2941</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="G276" s="23" t="n">
         <x:f>ROUND(F276-F275,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H276" s="24" t="n">
         <x:f>IFERROR(F276/F275-1,"")</x:f>
-        <x:v>0.01511804500897429</x:v>
-      </x:c>
-      <x:c r="I276" s="23" t="n">
+        <x:v>0.0004828918322297149</x:v>
+      </x:c>
+      <x:c r="I276" s="26" t="n">
         <x:f>ROUND(D276-E276,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J276" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K276" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B277" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C277" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2901</x:v>
       </x:c>
       <x:c r="D277" s="23" t="n">
-        <x:v>2996</x:v>
+        <x:v>2924.2</x:v>
       </x:c>
       <x:c r="E277" s="23" t="n">
-        <x:v>2834.8</x:v>
+        <x:v>2841.6</x:v>
       </x:c>
       <x:c r="F277" s="23" t="n">
-        <x:v>2859</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G277" s="23" t="n">
         <x:f>ROUND(F277-F276,1)</x:f>
-        <x:v>-82</x:v>
+        <x:v>-56.6</x:v>
       </x:c>
       <x:c r="H277" s="24" t="n">
         <x:f>IFERROR(F277/F276-1,"")</x:f>
-        <x:v>-0.02788167290037402</x:v>
+        <x:v>-0.019513204164655518</x:v>
       </x:c>
       <x:c r="I277" s="26" t="n">
         <x:f>ROUND(D277-E277,1)</x:f>
-        <x:v>161.2</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J277" s="22" t="str">
-        <x:v>IH2606/IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K277" s="22" t="n">
         <x:v>5</x:v>
@@ -17805,37 +17805,37 @@
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B278" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C278" s="23" t="n">
-        <x:v>2870</x:v>
+        <x:v>2808.4</x:v>
       </x:c>
       <x:c r="D278" s="23" t="n">
-        <x:v>2976</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="E278" s="23" t="n">
-        <x:v>2861.8</x:v>
+        <x:v>2791.2</x:v>
       </x:c>
       <x:c r="F278" s="23" t="n">
-        <x:v>2886.6</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G278" s="23" t="n">
         <x:f>ROUND(F278-F277,1)</x:f>
-        <x:v>27.6</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="H278" s="24" t="n">
         <x:f>IFERROR(F278/F277-1,"")</x:f>
-        <x:v>0.009653725078698772</x:v>
+        <x:v>0.01870604781997187</x:v>
       </x:c>
       <x:c r="I278" s="26" t="n">
         <x:f>ROUND(D278-E278,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="J278" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K278" s="22" t="n">
         <x:v>5</x:v>
@@ -17843,75 +17843,75 @@
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
-        <x:v>2899</x:v>
+        <x:v>2926.2</x:v>
       </x:c>
       <x:c r="D279" s="23" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2954.6</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2903.4</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>2910.2</x:v>
+        <x:v>2941</x:v>
       </x:c>
       <x:c r="G279" s="23" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>23.6</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>0.008175708445922414</x:v>
-      </x:c>
-      <x:c r="I279" s="26" t="n">
+        <x:v>0.01511804500897429</x:v>
+      </x:c>
+      <x:c r="I279" s="23" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>121.4</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B280" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C280" s="23" t="n">
-        <x:v>2895.8</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D280" s="23" t="n">
-        <x:v>2924</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="E280" s="23" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2834.8</x:v>
       </x:c>
       <x:c r="F280" s="23" t="n">
-        <x:v>2796.4</x:v>
+        <x:v>2859</x:v>
       </x:c>
       <x:c r="G280" s="23" t="n">
         <x:f>ROUND(F280-F279,1)</x:f>
-        <x:v>-113.8</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="H280" s="24" t="n">
         <x:f>IFERROR(F280/F279-1,"")</x:f>
-        <x:v>-0.039103841660366845</x:v>
+        <x:v>-0.02788167290037402</x:v>
       </x:c>
       <x:c r="I280" s="26" t="n">
         <x:f>ROUND(D280-E280,1)</x:f>
-        <x:v>141.4</x:v>
+        <x:v>161.2</x:v>
       </x:c>
       <x:c r="J280" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606/IH2609</x:v>
       </x:c>
       <x:c r="K280" s="22" t="n">
         <x:v>5</x:v>
@@ -17919,34 +17919,34 @@
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B281" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C281" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2870</x:v>
       </x:c>
       <x:c r="D281" s="23" t="n">
-        <x:v>2978</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="E281" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2861.8</x:v>
       </x:c>
       <x:c r="F281" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2886.6</x:v>
       </x:c>
       <x:c r="G281" s="23" t="n">
         <x:f>ROUND(F281-F280,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>27.6</x:v>
       </x:c>
       <x:c r="H281" s="24" t="n">
         <x:f>IFERROR(F281/F280-1,"")</x:f>
-        <x:v>0.040623658990130096</x:v>
+        <x:v>0.009653725078698772</x:v>
       </x:c>
       <x:c r="I281" s="26" t="n">
         <x:f>ROUND(D281-E281,1)</x:f>
-        <x:v>158</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="J281" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17957,34 +17957,34 @@
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B282" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C282" s="23" t="n">
-        <x:v>2929.6</x:v>
+        <x:v>2899</x:v>
       </x:c>
       <x:c r="D282" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="E282" s="23" t="n">
-        <x:v>2847.2</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="F282" s="23" t="n">
-        <x:v>2891.8</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="G282" s="23" t="n">
         <x:f>ROUND(F282-F281,1)</x:f>
-        <x:v>-18.2</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="H282" s="24" t="n">
         <x:f>IFERROR(F282/F281-1,"")</x:f>
-        <x:v>-0.006254295532646004</x:v>
+        <x:v>0.008175708445922414</x:v>
       </x:c>
       <x:c r="I282" s="26" t="n">
         <x:f>ROUND(D282-E282,1)</x:f>
-        <x:v>82.8</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J282" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -17995,34 +17995,34 @@
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B283" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C283" s="23" t="n">
-        <x:v>2882.4</x:v>
+        <x:v>2895.8</x:v>
       </x:c>
       <x:c r="D283" s="23" t="n">
-        <x:v>2930.6</x:v>
+        <x:v>2924</x:v>
       </x:c>
       <x:c r="E283" s="23" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="F283" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2796.4</x:v>
       </x:c>
       <x:c r="G283" s="23" t="n">
         <x:f>ROUND(F283-F282,1)</x:f>
-        <x:v>38.2</x:v>
+        <x:v>-113.8</x:v>
       </x:c>
       <x:c r="H283" s="24" t="n">
         <x:f>IFERROR(F283/F282-1,"")</x:f>
-        <x:v>0.013209765543951812</x:v>
+        <x:v>-0.039103841660366845</x:v>
       </x:c>
       <x:c r="I283" s="26" t="n">
         <x:f>ROUND(D283-E283,1)</x:f>
-        <x:v>84.8</x:v>
+        <x:v>141.4</x:v>
       </x:c>
       <x:c r="J283" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18033,34 +18033,34 @@
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B284" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C284" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="D284" s="23" t="n">
-        <x:v>2949.6</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E284" s="23" t="n">
-        <x:v>2877</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="F284" s="23" t="n">
-        <x:v>2890</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G284" s="23" t="n">
         <x:f>ROUND(F284-F283,1)</x:f>
-        <x:v>-40</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="H284" s="24" t="n">
         <x:f>IFERROR(F284/F283-1,"")</x:f>
-        <x:v>-0.013651877133105783</x:v>
+        <x:v>0.040623658990130096</x:v>
       </x:c>
       <x:c r="I284" s="26" t="n">
         <x:f>ROUND(D284-E284,1)</x:f>
-        <x:v>72.6</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J284" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18071,34 +18071,34 @@
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B285" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C285" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2929.6</x:v>
       </x:c>
       <x:c r="D285" s="23" t="n">
-        <x:v>2921.2</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="E285" s="23" t="n">
-        <x:v>2843</x:v>
+        <x:v>2847.2</x:v>
       </x:c>
       <x:c r="F285" s="23" t="n">
-        <x:v>2861</x:v>
+        <x:v>2891.8</x:v>
       </x:c>
       <x:c r="G285" s="23" t="n">
         <x:f>ROUND(F285-F284,1)</x:f>
-        <x:v>-29</x:v>
+        <x:v>-18.2</x:v>
       </x:c>
       <x:c r="H285" s="24" t="n">
         <x:f>IFERROR(F285/F284-1,"")</x:f>
-        <x:v>-0.01003460207612461</x:v>
+        <x:v>-0.006254295532646004</x:v>
       </x:c>
       <x:c r="I285" s="26" t="n">
         <x:f>ROUND(D285-E285,1)</x:f>
-        <x:v>78.2</x:v>
+        <x:v>82.8</x:v>
       </x:c>
       <x:c r="J285" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18109,34 +18109,34 @@
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B286" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C286" s="23" t="n">
-        <x:v>2856.4</x:v>
+        <x:v>2882.4</x:v>
       </x:c>
       <x:c r="D286" s="23" t="n">
-        <x:v>2918.2</x:v>
+        <x:v>2930.6</x:v>
       </x:c>
       <x:c r="E286" s="23" t="n">
-        <x:v>2837.4</x:v>
+        <x:v>2845.8</x:v>
       </x:c>
       <x:c r="F286" s="23" t="n">
-        <x:v>2911.4</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="G286" s="23" t="n">
         <x:f>ROUND(F286-F285,1)</x:f>
-        <x:v>50.4</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="H286" s="24" t="n">
         <x:f>IFERROR(F286/F285-1,"")</x:f>
-        <x:v>0.01761621810555747</x:v>
+        <x:v>0.013209765543951812</x:v>
       </x:c>
       <x:c r="I286" s="26" t="n">
         <x:f>ROUND(D286-E286,1)</x:f>
-        <x:v>80.8</x:v>
+        <x:v>84.8</x:v>
       </x:c>
       <x:c r="J286" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18147,34 +18147,34 @@
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>2949.4</x:v>
+        <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
-        <x:v>2877.6</x:v>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>2915.8</x:v>
+        <x:v>2890</x:v>
       </x:c>
       <x:c r="G287" s="23" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>4.4</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>0.0015113004053033396</x:v>
+        <x:v>-0.013651877133105783</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>71.8</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18185,34 +18185,34 @@
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B288" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C288" s="23" t="n">
-        <x:v>2923.2</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D288" s="23" t="n">
-        <x:v>2931.4</x:v>
+        <x:v>2921.2</x:v>
       </x:c>
       <x:c r="E288" s="23" t="n">
-        <x:v>2836.8</x:v>
+        <x:v>2843</x:v>
       </x:c>
       <x:c r="F288" s="23" t="n">
-        <x:v>2867</x:v>
+        <x:v>2861</x:v>
       </x:c>
       <x:c r="G288" s="23" t="n">
         <x:f>ROUND(F288-F287,1)</x:f>
-        <x:v>-48.8</x:v>
+        <x:v>-29</x:v>
       </x:c>
       <x:c r="H288" s="24" t="n">
         <x:f>IFERROR(F288/F287-1,"")</x:f>
-        <x:v>-0.01673640167364021</x:v>
+        <x:v>-0.01003460207612461</x:v>
       </x:c>
       <x:c r="I288" s="26" t="n">
         <x:f>ROUND(D288-E288,1)</x:f>
-        <x:v>94.6</x:v>
+        <x:v>78.2</x:v>
       </x:c>
       <x:c r="J288" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18223,34 +18223,34 @@
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B289" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C289" s="23" t="n">
-        <x:v>2849.2</x:v>
+        <x:v>2856.4</x:v>
       </x:c>
       <x:c r="D289" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2918.2</x:v>
       </x:c>
       <x:c r="E289" s="23" t="n">
-        <x:v>2829.4</x:v>
+        <x:v>2837.4</x:v>
       </x:c>
       <x:c r="F289" s="23" t="n">
-        <x:v>2862.2</x:v>
+        <x:v>2911.4</x:v>
       </x:c>
       <x:c r="G289" s="23" t="n">
         <x:f>ROUND(F289-F288,1)</x:f>
-        <x:v>-4.8</x:v>
+        <x:v>50.4</x:v>
       </x:c>
       <x:c r="H289" s="24" t="n">
         <x:f>IFERROR(F289/F288-1,"")</x:f>
-        <x:v>-0.0016742239274503135</x:v>
-      </x:c>
-      <x:c r="I289" s="23" t="n">
+        <x:v>0.01761621810555747</x:v>
+      </x:c>
+      <x:c r="I289" s="26" t="n">
         <x:f>ROUND(D289-E289,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>80.8</x:v>
       </x:c>
       <x:c r="J289" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18260,269 +18260,269 @@
       </x:c>
     </x:row>
     <x:row r="290">
-      <x:c r="A290" s="31" t="str">
+      <x:c r="A290" s="22" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B290" s="22" t="str">
+        <x:v>8月31日-9月4日</x:v>
+      </x:c>
+      <x:c r="C290" s="23" t="n">
+        <x:v>2886</x:v>
+      </x:c>
+      <x:c r="D290" s="23" t="n">
+        <x:v>2949.4</x:v>
+      </x:c>
+      <x:c r="E290" s="23" t="n">
+        <x:v>2877.6</x:v>
+      </x:c>
+      <x:c r="F290" s="23" t="n">
+        <x:v>2915.8</x:v>
+      </x:c>
+      <x:c r="G290" s="23" t="n">
+        <x:f>ROUND(F290-F289,1)</x:f>
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="H290" s="24" t="n">
+        <x:f>IFERROR(F290/F289-1,"")</x:f>
+        <x:v>0.0015113004053033396</x:v>
+      </x:c>
+      <x:c r="I290" s="26" t="n">
+        <x:f>ROUND(D290-E290,1)</x:f>
+        <x:v>71.8</x:v>
+      </x:c>
+      <x:c r="J290" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K290" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="22" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B291" s="22" t="str">
+        <x:v>9月7日-9月11日</x:v>
+      </x:c>
+      <x:c r="C291" s="23" t="n">
+        <x:v>2923.2</x:v>
+      </x:c>
+      <x:c r="D291" s="23" t="n">
+        <x:v>2931.4</x:v>
+      </x:c>
+      <x:c r="E291" s="23" t="n">
+        <x:v>2836.8</x:v>
+      </x:c>
+      <x:c r="F291" s="23" t="n">
+        <x:v>2867</x:v>
+      </x:c>
+      <x:c r="G291" s="23" t="n">
+        <x:f>ROUND(F291-F290,1)</x:f>
+        <x:v>-48.8</x:v>
+      </x:c>
+      <x:c r="H291" s="24" t="n">
+        <x:f>IFERROR(F291/F290-1,"")</x:f>
+        <x:v>-0.01673640167364021</x:v>
+      </x:c>
+      <x:c r="I291" s="26" t="n">
+        <x:f>ROUND(D291-E291,1)</x:f>
+        <x:v>94.6</x:v>
+      </x:c>
+      <x:c r="J291" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K291" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" s="22" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B292" s="22" t="str">
+        <x:v>9月14日-9月18日</x:v>
+      </x:c>
+      <x:c r="C292" s="23" t="n">
+        <x:v>2849.2</x:v>
+      </x:c>
+      <x:c r="D292" s="23" t="n">
+        <x:v>2873.2</x:v>
+      </x:c>
+      <x:c r="E292" s="23" t="n">
+        <x:v>2829.4</x:v>
+      </x:c>
+      <x:c r="F292" s="23" t="n">
+        <x:v>2862.2</x:v>
+      </x:c>
+      <x:c r="G292" s="23" t="n">
+        <x:f>ROUND(F292-F291,1)</x:f>
+        <x:v>-4.8</x:v>
+      </x:c>
+      <x:c r="H292" s="24" t="n">
+        <x:f>IFERROR(F292/F291-1,"")</x:f>
+        <x:v>-0.0016742239274503135</x:v>
+      </x:c>
+      <x:c r="I292" s="23" t="n">
+        <x:f>ROUND(D292-E292,1)</x:f>
+        <x:v>43.8</x:v>
+      </x:c>
+      <x:c r="J292" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K292" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" s="22" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B293" s="22" t="str">
+        <x:v>9月21日</x:v>
+      </x:c>
+      <x:c r="C293" s="23" t="n">
+        <x:v>2830</x:v>
+      </x:c>
+      <x:c r="D293" s="23" t="n">
+        <x:v>2849.8</x:v>
+      </x:c>
+      <x:c r="E293" s="23" t="n">
+        <x:v>2822</x:v>
+      </x:c>
+      <x:c r="F293" s="23" t="n">
+        <x:v>2847.4</x:v>
+      </x:c>
+      <x:c r="G293" s="23" t="n">
+        <x:f>ROUND(F293-F292,1)</x:f>
+        <x:v>-14.8</x:v>
+      </x:c>
+      <x:c r="H293" s="24" t="n">
+        <x:f>IFERROR(F293/F292-1,"")</x:f>
+        <x:v>-0.005170847599748396</x:v>
+      </x:c>
+      <x:c r="I293" s="23" t="n">
+        <x:f>ROUND(D293-E293,1)</x:f>
+        <x:v>27.8</x:v>
+      </x:c>
+      <x:c r="J293" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
+      <x:c r="K293" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B290" s="30" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C290" s="30"/>
-      <x:c r="D290" s="30"/>
-      <x:c r="E290" s="30"/>
-      <x:c r="F290" s="30"/>
-      <x:c r="G290" s="30"/>
-      <x:c r="H290" s="30"/>
-      <x:c r="I290" s="32" t="n">
-        <x:f>ROUND(SUM(I254:I289),1)</x:f>
-        <x:v>3259.4</x:v>
-      </x:c>
-      <x:c r="J290" s="30"/>
-      <x:c r="K290" s="30"/>
-    </x:row>
-    <x:row r="291">
-      <x:c r="A291" s="31" t="str">
+      <x:c r="B294" s="30" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C294" s="30"/>
+      <x:c r="D294" s="30"/>
+      <x:c r="E294" s="30"/>
+      <x:c r="F294" s="30"/>
+      <x:c r="G294" s="30"/>
+      <x:c r="H294" s="30"/>
+      <x:c r="I294" s="32" t="n">
+        <x:f>ROUND(SUM(I257:I293),1)</x:f>
+        <x:v>3287.2</x:v>
+      </x:c>
+      <x:c r="J294" s="30"/>
+      <x:c r="K294" s="30"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B291" s="30"/>
-      <x:c r="C291" s="30"/>
-      <x:c r="D291" s="30"/>
-      <x:c r="E291" s="30"/>
-      <x:c r="F291" s="30"/>
-      <x:c r="G291" s="30"/>
-      <x:c r="H291" s="30"/>
-      <x:c r="I291" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I254:I289),0),1)</x:f>
-        <x:v>90.5</x:v>
-      </x:c>
-      <x:c r="J291" s="30"/>
-      <x:c r="K291" s="30"/>
-    </x:row>
-    <x:row r="293">
-      <x:c r="A293" s="17" t="str">
+      <x:c r="B295" s="30"/>
+      <x:c r="C295" s="30"/>
+      <x:c r="D295" s="30"/>
+      <x:c r="E295" s="30"/>
+      <x:c r="F295" s="30"/>
+      <x:c r="G295" s="30"/>
+      <x:c r="H295" s="30"/>
+      <x:c r="I295" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I257:I293),0),1)</x:f>
+        <x:v>88.8</x:v>
+      </x:c>
+      <x:c r="J295" s="30"/>
+      <x:c r="K295" s="30"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" s="17" t="str">
         <x:v>碳酸锂2610</x:v>
       </x:c>
-      <x:c r="B293" s="17"/>
-      <x:c r="C293" s="17"/>
-      <x:c r="D293" s="17"/>
-      <x:c r="E293" s="17"/>
-      <x:c r="F293" s="17"/>
-      <x:c r="G293" s="17"/>
-      <x:c r="H293" s="17"/>
-      <x:c r="I293" s="17"/>
-      <x:c r="J293" s="17"/>
-      <x:c r="K293" s="17"/>
-    </x:row>
-    <x:row r="294">
-      <x:c r="A294" s="20" t="str">
+      <x:c r="B297" s="17"/>
+      <x:c r="C297" s="17"/>
+      <x:c r="D297" s="17"/>
+      <x:c r="E297" s="17"/>
+      <x:c r="F297" s="17"/>
+      <x:c r="G297" s="17"/>
+      <x:c r="H297" s="17"/>
+      <x:c r="I297" s="17"/>
+      <x:c r="J297" s="17"/>
+      <x:c r="K297" s="17"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B294" s="20" t="str">
+      <x:c r="B298" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C294" s="20" t="str">
+      <x:c r="C298" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D294" s="20" t="str">
+      <x:c r="D298" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E294" s="20" t="str">
+      <x:c r="E298" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F294" s="20" t="str">
+      <x:c r="F298" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G294" s="20" t="str">
+      <x:c r="G298" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H294" s="20" t="str">
+      <x:c r="H298" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I294" s="20" t="str">
+      <x:c r="I298" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J294" s="20" t="str">
+      <x:c r="J298" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K294" s="20" t="str">
+      <x:c r="K298" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="295">
-      <x:c r="A295" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B295" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C295" s="23" t="n">
-        <x:v>132800</x:v>
-      </x:c>
-      <x:c r="D295" s="23" t="n">
-        <x:v>150100</x:v>
-      </x:c>
-      <x:c r="E295" s="23" t="n">
-        <x:v>123500</x:v>
-      </x:c>
-      <x:c r="F295" s="23" t="n">
-        <x:v>145600</x:v>
-      </x:c>
-      <x:c r="G295" s="23"/>
-      <x:c r="H295" s="24"/>
-      <x:c r="I295" s="26" t="n">
-        <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>26600</x:v>
-      </x:c>
-      <x:c r="J295" s="22" t="str">
-        <x:v>LC2610</x:v>
-      </x:c>
-      <x:c r="K295" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="296">
-      <x:c r="A296" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B296" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
-      </x:c>
-      <x:c r="C296" s="23" t="n">
-        <x:v>149180</x:v>
-      </x:c>
-      <x:c r="D296" s="23" t="n">
-        <x:v>175360</x:v>
-      </x:c>
-      <x:c r="E296" s="23" t="n">
-        <x:v>148180</x:v>
-      </x:c>
-      <x:c r="F296" s="23" t="n">
-        <x:v>148180</x:v>
-      </x:c>
-      <x:c r="G296" s="28" t="n">
-        <x:f>ROUND(F296-F295,1)</x:f>
-        <x:v>2580</x:v>
-      </x:c>
-      <x:c r="H296" s="24" t="n">
-        <x:f>IFERROR(F296/F295-1,"")</x:f>
-        <x:v>0.017719780219780157</x:v>
-      </x:c>
-      <x:c r="I296" s="26" t="n">
-        <x:f>ROUND(D296-E296,1)</x:f>
-        <x:v>27180</x:v>
-      </x:c>
-      <x:c r="J296" s="22" t="str">
-        <x:v>LC2610</x:v>
-      </x:c>
-      <x:c r="K296" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="297">
-      <x:c r="A297" s="22" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B297" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
-      </x:c>
-      <x:c r="C297" s="23" t="n">
-        <x:v>143000</x:v>
-      </x:c>
-      <x:c r="D297" s="23" t="n">
-        <x:v>183460</x:v>
-      </x:c>
-      <x:c r="E297" s="23" t="n">
-        <x:v>143000</x:v>
-      </x:c>
-      <x:c r="F297" s="23" t="n">
-        <x:v>183460</x:v>
-      </x:c>
-      <x:c r="G297" s="28" t="n">
-        <x:f>ROUND(F297-F296,1)</x:f>
-        <x:v>35280</x:v>
-      </x:c>
-      <x:c r="H297" s="24" t="n">
-        <x:f>IFERROR(F297/F296-1,"")</x:f>
-        <x:v>0.23808881090565537</x:v>
-      </x:c>
-      <x:c r="I297" s="26" t="n">
-        <x:f>ROUND(D297-E297,1)</x:f>
-        <x:v>40460</x:v>
-      </x:c>
-      <x:c r="J297" s="22" t="str">
-        <x:v>LC2610</x:v>
-      </x:c>
-      <x:c r="K297" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="298">
-      <x:c r="A298" s="22" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B298" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
-      </x:c>
-      <x:c r="C298" s="23" t="n">
-        <x:v>189980</x:v>
-      </x:c>
-      <x:c r="D298" s="23" t="n">
-        <x:v>190020</x:v>
-      </x:c>
-      <x:c r="E298" s="23" t="n">
-        <x:v>148520</x:v>
-      </x:c>
-      <x:c r="F298" s="23" t="n">
-        <x:v>148540</x:v>
-      </x:c>
-      <x:c r="G298" s="28" t="n">
-        <x:f>ROUND(F298-F297,1)</x:f>
-        <x:v>-34920</x:v>
-      </x:c>
-      <x:c r="H298" s="24" t="n">
-        <x:f>IFERROR(F298/F297-1,"")</x:f>
-        <x:v>-0.19034121879428756</x:v>
-      </x:c>
-      <x:c r="I298" s="26" t="n">
-        <x:f>ROUND(D298-E298,1)</x:f>
-        <x:v>41500</x:v>
-      </x:c>
-      <x:c r="J298" s="22" t="str">
-        <x:v>LC2610</x:v>
-      </x:c>
-      <x:c r="K298" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B299" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C299" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>132800</x:v>
       </x:c>
       <x:c r="D299" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>150100</x:v>
       </x:c>
       <x:c r="E299" s="23" t="n">
-        <x:v>124760</x:v>
+        <x:v>123500</x:v>
       </x:c>
       <x:c r="F299" s="23" t="n">
-        <x:v>131160</x:v>
-      </x:c>
-      <x:c r="G299" s="28" t="n">
-        <x:f>ROUND(F299-F298,1)</x:f>
-        <x:v>-17380</x:v>
-      </x:c>
-      <x:c r="H299" s="24" t="n">
-        <x:f>IFERROR(F299/F298-1,"")</x:f>
-        <x:v>-0.11700552039854584</x:v>
-      </x:c>
+        <x:v>145600</x:v>
+      </x:c>
+      <x:c r="G299" s="23"/>
+      <x:c r="H299" s="24"/>
       <x:c r="I299" s="26" t="n">
         <x:f>ROUND(D299-E299,1)</x:f>
-        <x:v>28240</x:v>
+        <x:v>26600</x:v>
       </x:c>
       <x:c r="J299" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18533,34 +18533,34 @@
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B300" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C300" s="23" t="n">
-        <x:v>134660</x:v>
+        <x:v>149180</x:v>
       </x:c>
       <x:c r="D300" s="23" t="n">
-        <x:v>152380</x:v>
+        <x:v>175360</x:v>
       </x:c>
       <x:c r="E300" s="23" t="n">
-        <x:v>133580</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="F300" s="23" t="n">
-        <x:v>152380</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="G300" s="28" t="n">
         <x:f>ROUND(F300-F299,1)</x:f>
-        <x:v>21220</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="H300" s="24" t="n">
         <x:f>IFERROR(F300/F299-1,"")</x:f>
-        <x:v>0.1617871302226288</x:v>
+        <x:v>0.017719780219780157</x:v>
       </x:c>
       <x:c r="I300" s="26" t="n">
         <x:f>ROUND(D300-E300,1)</x:f>
-        <x:v>18800</x:v>
+        <x:v>27180</x:v>
       </x:c>
       <x:c r="J300" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18571,72 +18571,72 @@
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B301" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C301" s="23" t="n">
-        <x:v>165060</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="D301" s="23" t="n">
-        <x:v>187920</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="E301" s="23" t="n">
-        <x:v>155680</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="F301" s="23" t="n">
-        <x:v>175400</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="G301" s="28" t="n">
         <x:f>ROUND(F301-F300,1)</x:f>
-        <x:v>23020</x:v>
+        <x:v>35280</x:v>
       </x:c>
       <x:c r="H301" s="24" t="n">
         <x:f>IFERROR(F301/F300-1,"")</x:f>
-        <x:v>0.1510696941855887</x:v>
+        <x:v>0.23808881090565537</x:v>
       </x:c>
       <x:c r="I301" s="26" t="n">
         <x:f>ROUND(D301-E301,1)</x:f>
-        <x:v>32240</x:v>
+        <x:v>40460</x:v>
       </x:c>
       <x:c r="J301" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K301" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B302" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C302" s="23" t="n">
-        <x:v>175800</x:v>
+        <x:v>189980</x:v>
       </x:c>
       <x:c r="D302" s="23" t="n">
-        <x:v>177260</x:v>
+        <x:v>190020</x:v>
       </x:c>
       <x:c r="E302" s="23" t="n">
-        <x:v>144980</x:v>
+        <x:v>148520</x:v>
       </x:c>
       <x:c r="F302" s="23" t="n">
-        <x:v>156580</x:v>
+        <x:v>148540</x:v>
       </x:c>
       <x:c r="G302" s="28" t="n">
         <x:f>ROUND(F302-F301,1)</x:f>
-        <x:v>-18820</x:v>
+        <x:v>-34920</x:v>
       </x:c>
       <x:c r="H302" s="24" t="n">
         <x:f>IFERROR(F302/F301-1,"")</x:f>
-        <x:v>-0.1072976054732041</x:v>
+        <x:v>-0.19034121879428756</x:v>
       </x:c>
       <x:c r="I302" s="26" t="n">
         <x:f>ROUND(D302-E302,1)</x:f>
-        <x:v>32280</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="J302" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18647,34 +18647,34 @@
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B303" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C303" s="23" t="n">
-        <x:v>145120</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="D303" s="23" t="n">
-        <x:v>166800</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="E303" s="23" t="n">
-        <x:v>139860</x:v>
+        <x:v>124760</x:v>
       </x:c>
       <x:c r="F303" s="23" t="n">
-        <x:v>151880</x:v>
+        <x:v>131160</x:v>
       </x:c>
       <x:c r="G303" s="28" t="n">
         <x:f>ROUND(F303-F302,1)</x:f>
-        <x:v>-4700</x:v>
+        <x:v>-17380</x:v>
       </x:c>
       <x:c r="H303" s="24" t="n">
         <x:f>IFERROR(F303/F302-1,"")</x:f>
-        <x:v>-0.030016604930387047</x:v>
+        <x:v>-0.11700552039854584</x:v>
       </x:c>
       <x:c r="I303" s="26" t="n">
         <x:f>ROUND(D303-E303,1)</x:f>
-        <x:v>26940</x:v>
+        <x:v>28240</x:v>
       </x:c>
       <x:c r="J303" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18685,34 +18685,34 @@
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B304" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C304" s="23" t="n">
-        <x:v>149140</x:v>
+        <x:v>134660</x:v>
       </x:c>
       <x:c r="D304" s="23" t="n">
-        <x:v>159120</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="E304" s="23" t="n">
-        <x:v>139640</x:v>
+        <x:v>133580</x:v>
       </x:c>
       <x:c r="F304" s="23" t="n">
-        <x:v>143900</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="G304" s="28" t="n">
         <x:f>ROUND(F304-F303,1)</x:f>
-        <x:v>-7980</x:v>
+        <x:v>21220</x:v>
       </x:c>
       <x:c r="H304" s="24" t="n">
         <x:f>IFERROR(F304/F303-1,"")</x:f>
-        <x:v>-0.052541480115881</x:v>
+        <x:v>0.1617871302226288</x:v>
       </x:c>
       <x:c r="I304" s="26" t="n">
         <x:f>ROUND(D304-E304,1)</x:f>
-        <x:v>19480</x:v>
+        <x:v>18800</x:v>
       </x:c>
       <x:c r="J304" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18723,72 +18723,72 @@
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B305" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C305" s="23" t="n">
-        <x:v>144460</x:v>
+        <x:v>165060</x:v>
       </x:c>
       <x:c r="D305" s="23" t="n">
-        <x:v>170800</x:v>
+        <x:v>187920</x:v>
       </x:c>
       <x:c r="E305" s="23" t="n">
-        <x:v>139980</x:v>
+        <x:v>155680</x:v>
       </x:c>
       <x:c r="F305" s="23" t="n">
-        <x:v>166540</x:v>
+        <x:v>175400</x:v>
       </x:c>
       <x:c r="G305" s="28" t="n">
         <x:f>ROUND(F305-F304,1)</x:f>
-        <x:v>22640</x:v>
+        <x:v>23020</x:v>
       </x:c>
       <x:c r="H305" s="24" t="n">
         <x:f>IFERROR(F305/F304-1,"")</x:f>
-        <x:v>0.15733148019457954</x:v>
+        <x:v>0.1510696941855887</x:v>
       </x:c>
       <x:c r="I305" s="26" t="n">
         <x:f>ROUND(D305-E305,1)</x:f>
-        <x:v>30820</x:v>
+        <x:v>32240</x:v>
       </x:c>
       <x:c r="J305" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K305" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B306" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C306" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>175800</x:v>
       </x:c>
       <x:c r="D306" s="23" t="n">
-        <x:v>174540</x:v>
+        <x:v>177260</x:v>
       </x:c>
       <x:c r="E306" s="23" t="n">
-        <x:v>153840</x:v>
+        <x:v>144980</x:v>
       </x:c>
       <x:c r="F306" s="23" t="n">
-        <x:v>157680</x:v>
+        <x:v>156580</x:v>
       </x:c>
       <x:c r="G306" s="28" t="n">
         <x:f>ROUND(F306-F305,1)</x:f>
-        <x:v>-8860</x:v>
+        <x:v>-18820</x:v>
       </x:c>
       <x:c r="H306" s="24" t="n">
         <x:f>IFERROR(F306/F305-1,"")</x:f>
-        <x:v>-0.05320043232856975</x:v>
+        <x:v>-0.1072976054732041</x:v>
       </x:c>
       <x:c r="I306" s="26" t="n">
         <x:f>ROUND(D306-E306,1)</x:f>
-        <x:v>20700</x:v>
+        <x:v>32280</x:v>
       </x:c>
       <x:c r="J306" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18799,72 +18799,72 @@
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B307" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C307" s="23" t="n">
-        <x:v>156200</x:v>
+        <x:v>145120</x:v>
       </x:c>
       <x:c r="D307" s="23" t="n">
-        <x:v>164160</x:v>
+        <x:v>166800</x:v>
       </x:c>
       <x:c r="E307" s="23" t="n">
-        <x:v>151640</x:v>
+        <x:v>139860</x:v>
       </x:c>
       <x:c r="F307" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>151880</x:v>
       </x:c>
       <x:c r="G307" s="28" t="n">
         <x:f>ROUND(F307-F306,1)</x:f>
-        <x:v>-1180</x:v>
+        <x:v>-4700</x:v>
       </x:c>
       <x:c r="H307" s="24" t="n">
         <x:f>IFERROR(F307/F306-1,"")</x:f>
-        <x:v>-0.007483510908168456</x:v>
+        <x:v>-0.030016604930387047</x:v>
       </x:c>
       <x:c r="I307" s="26" t="n">
         <x:f>ROUND(D307-E307,1)</x:f>
-        <x:v>12520</x:v>
+        <x:v>26940</x:v>
       </x:c>
       <x:c r="J307" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K307" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B308" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C308" s="23" t="n">
-        <x:v>156660</x:v>
+        <x:v>149140</x:v>
       </x:c>
       <x:c r="D308" s="23" t="n">
-        <x:v>176500</x:v>
+        <x:v>159120</x:v>
       </x:c>
       <x:c r="E308" s="23" t="n">
-        <x:v>153040</x:v>
+        <x:v>139640</x:v>
       </x:c>
       <x:c r="F308" s="23" t="n">
-        <x:v>176360</x:v>
+        <x:v>143900</x:v>
       </x:c>
       <x:c r="G308" s="28" t="n">
         <x:f>ROUND(F308-F307,1)</x:f>
-        <x:v>19860</x:v>
+        <x:v>-7980</x:v>
       </x:c>
       <x:c r="H308" s="24" t="n">
         <x:f>IFERROR(F308/F307-1,"")</x:f>
-        <x:v>0.12690095846645377</x:v>
+        <x:v>-0.052541480115881</x:v>
       </x:c>
       <x:c r="I308" s="26" t="n">
         <x:f>ROUND(D308-E308,1)</x:f>
-        <x:v>23460</x:v>
+        <x:v>19480</x:v>
       </x:c>
       <x:c r="J308" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18875,34 +18875,34 @@
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B309" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C309" s="23" t="n">
-        <x:v>174080</x:v>
+        <x:v>144460</x:v>
       </x:c>
       <x:c r="D309" s="23" t="n">
-        <x:v>180920</x:v>
+        <x:v>170800</x:v>
       </x:c>
       <x:c r="E309" s="23" t="n">
-        <x:v>169000</x:v>
+        <x:v>139980</x:v>
       </x:c>
       <x:c r="F309" s="23" t="n">
-        <x:v>176960</x:v>
+        <x:v>166540</x:v>
       </x:c>
       <x:c r="G309" s="28" t="n">
         <x:f>ROUND(F309-F308,1)</x:f>
-        <x:v>600</x:v>
+        <x:v>22640</x:v>
       </x:c>
       <x:c r="H309" s="24" t="n">
         <x:f>IFERROR(F309/F308-1,"")</x:f>
-        <x:v>0.0034021320027217694</x:v>
+        <x:v>0.15733148019457954</x:v>
       </x:c>
       <x:c r="I309" s="26" t="n">
         <x:f>ROUND(D309-E309,1)</x:f>
-        <x:v>11920</x:v>
+        <x:v>30820</x:v>
       </x:c>
       <x:c r="J309" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18913,110 +18913,110 @@
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B310" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C310" s="23" t="n">
-        <x:v>176960</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="D310" s="23" t="n">
-        <x:v>188840</x:v>
+        <x:v>174540</x:v>
       </x:c>
       <x:c r="E310" s="23" t="n">
-        <x:v>172640</x:v>
+        <x:v>153840</x:v>
       </x:c>
       <x:c r="F310" s="23" t="n">
-        <x:v>188840</x:v>
+        <x:v>157680</x:v>
       </x:c>
       <x:c r="G310" s="28" t="n">
         <x:f>ROUND(F310-F309,1)</x:f>
-        <x:v>11880</x:v>
+        <x:v>-8860</x:v>
       </x:c>
       <x:c r="H310" s="24" t="n">
         <x:f>IFERROR(F310/F309-1,"")</x:f>
-        <x:v>0.06713381555153708</x:v>
+        <x:v>-0.05320043232856975</x:v>
       </x:c>
       <x:c r="I310" s="26" t="n">
         <x:f>ROUND(D310-E310,1)</x:f>
-        <x:v>16200</x:v>
+        <x:v>20700</x:v>
       </x:c>
       <x:c r="J310" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K310" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B311" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C311" s="23" t="n">
-        <x:v>191300</x:v>
+        <x:v>156200</x:v>
       </x:c>
       <x:c r="D311" s="23" t="n">
-        <x:v>204640</x:v>
+        <x:v>164160</x:v>
       </x:c>
       <x:c r="E311" s="23" t="n">
-        <x:v>191300</x:v>
+        <x:v>151640</x:v>
       </x:c>
       <x:c r="F311" s="23" t="n">
-        <x:v>196100</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="G311" s="28" t="n">
         <x:f>ROUND(F311-F310,1)</x:f>
-        <x:v>7260</x:v>
+        <x:v>-1180</x:v>
       </x:c>
       <x:c r="H311" s="24" t="n">
         <x:f>IFERROR(F311/F310-1,"")</x:f>
-        <x:v>0.038445244651556854</x:v>
+        <x:v>-0.007483510908168456</x:v>
       </x:c>
       <x:c r="I311" s="26" t="n">
         <x:f>ROUND(D311-E311,1)</x:f>
-        <x:v>13340</x:v>
+        <x:v>12520</x:v>
       </x:c>
       <x:c r="J311" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K311" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B312" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C312" s="23" t="n">
-        <x:v>195080</x:v>
+        <x:v>156660</x:v>
       </x:c>
       <x:c r="D312" s="23" t="n">
-        <x:v>209040</x:v>
+        <x:v>176500</x:v>
       </x:c>
       <x:c r="E312" s="23" t="n">
-        <x:v>187240</x:v>
+        <x:v>153040</x:v>
       </x:c>
       <x:c r="F312" s="23" t="n">
-        <x:v>189440</x:v>
+        <x:v>176360</x:v>
       </x:c>
       <x:c r="G312" s="28" t="n">
         <x:f>ROUND(F312-F311,1)</x:f>
-        <x:v>-6660</x:v>
+        <x:v>19860</x:v>
       </x:c>
       <x:c r="H312" s="24" t="n">
         <x:f>IFERROR(F312/F311-1,"")</x:f>
-        <x:v>-0.03396226415094339</x:v>
+        <x:v>0.12690095846645377</x:v>
       </x:c>
       <x:c r="I312" s="26" t="n">
         <x:f>ROUND(D312-E312,1)</x:f>
-        <x:v>21800</x:v>
+        <x:v>23460</x:v>
       </x:c>
       <x:c r="J312" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19027,34 +19027,34 @@
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B313" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C313" s="23" t="n">
-        <x:v>190060</x:v>
+        <x:v>174080</x:v>
       </x:c>
       <x:c r="D313" s="23" t="n">
-        <x:v>193820</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="E313" s="23" t="n">
-        <x:v>175520</x:v>
+        <x:v>169000</x:v>
       </x:c>
       <x:c r="F313" s="23" t="n">
-        <x:v>185280</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="G313" s="28" t="n">
         <x:f>ROUND(F313-F312,1)</x:f>
-        <x:v>-4160</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H313" s="24" t="n">
         <x:f>IFERROR(F313/F312-1,"")</x:f>
-        <x:v>-0.02195945945945943</x:v>
+        <x:v>0.0034021320027217694</x:v>
       </x:c>
       <x:c r="I313" s="26" t="n">
         <x:f>ROUND(D313-E313,1)</x:f>
-        <x:v>18300</x:v>
+        <x:v>11920</x:v>
       </x:c>
       <x:c r="J313" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19065,110 +19065,110 @@
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B314" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C314" s="23" t="n">
-        <x:v>185380</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="D314" s="23" t="n">
-        <x:v>188320</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="E314" s="23" t="n">
-        <x:v>172500</x:v>
+        <x:v>172640</x:v>
       </x:c>
       <x:c r="F314" s="23" t="n">
-        <x:v>178620</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="G314" s="28" t="n">
         <x:f>ROUND(F314-F313,1)</x:f>
-        <x:v>-6660</x:v>
+        <x:v>11880</x:v>
       </x:c>
       <x:c r="H314" s="24" t="n">
         <x:f>IFERROR(F314/F313-1,"")</x:f>
-        <x:v>-0.035945595854922296</x:v>
+        <x:v>0.06713381555153708</x:v>
       </x:c>
       <x:c r="I314" s="26" t="n">
         <x:f>ROUND(D314-E314,1)</x:f>
-        <x:v>15820</x:v>
+        <x:v>16200</x:v>
       </x:c>
       <x:c r="J314" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K314" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B315" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C315" s="23" t="n">
-        <x:v>180920</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="D315" s="23" t="n">
-        <x:v>182940</x:v>
+        <x:v>204640</x:v>
       </x:c>
       <x:c r="E315" s="23" t="n">
-        <x:v>158140</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="F315" s="23" t="n">
-        <x:v>165460</x:v>
+        <x:v>196100</x:v>
       </x:c>
       <x:c r="G315" s="28" t="n">
         <x:f>ROUND(F315-F314,1)</x:f>
-        <x:v>-13160</x:v>
+        <x:v>7260</x:v>
       </x:c>
       <x:c r="H315" s="24" t="n">
         <x:f>IFERROR(F315/F314-1,"")</x:f>
-        <x:v>-0.07367596013884226</x:v>
+        <x:v>0.038445244651556854</x:v>
       </x:c>
       <x:c r="I315" s="26" t="n">
         <x:f>ROUND(D315-E315,1)</x:f>
-        <x:v>24800</x:v>
+        <x:v>13340</x:v>
       </x:c>
       <x:c r="J315" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K315" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B316" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C316" s="23" t="n">
-        <x:v>162800</x:v>
+        <x:v>195080</x:v>
       </x:c>
       <x:c r="D316" s="23" t="n">
-        <x:v>178860</x:v>
+        <x:v>209040</x:v>
       </x:c>
       <x:c r="E316" s="23" t="n">
-        <x:v>161280</x:v>
+        <x:v>187240</x:v>
       </x:c>
       <x:c r="F316" s="23" t="n">
-        <x:v>175780</x:v>
+        <x:v>189440</x:v>
       </x:c>
       <x:c r="G316" s="28" t="n">
         <x:f>ROUND(F316-F315,1)</x:f>
-        <x:v>10320</x:v>
+        <x:v>-6660</x:v>
       </x:c>
       <x:c r="H316" s="24" t="n">
         <x:f>IFERROR(F316/F315-1,"")</x:f>
-        <x:v>0.06237157016801653</x:v>
+        <x:v>-0.03396226415094339</x:v>
       </x:c>
       <x:c r="I316" s="26" t="n">
         <x:f>ROUND(D316-E316,1)</x:f>
-        <x:v>17580</x:v>
+        <x:v>21800</x:v>
       </x:c>
       <x:c r="J316" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19179,72 +19179,72 @@
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B317" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C317" s="23" t="n">
-        <x:v>176460</x:v>
+        <x:v>190060</x:v>
       </x:c>
       <x:c r="D317" s="23" t="n">
-        <x:v>178560</x:v>
+        <x:v>193820</x:v>
       </x:c>
       <x:c r="E317" s="23" t="n">
-        <x:v>160560</x:v>
+        <x:v>175520</x:v>
       </x:c>
       <x:c r="F317" s="23" t="n">
-        <x:v>161400</x:v>
+        <x:v>185280</x:v>
       </x:c>
       <x:c r="G317" s="28" t="n">
         <x:f>ROUND(F317-F316,1)</x:f>
-        <x:v>-14380</x:v>
+        <x:v>-4160</x:v>
       </x:c>
       <x:c r="H317" s="24" t="n">
         <x:f>IFERROR(F317/F316-1,"")</x:f>
-        <x:v>-0.0818068039594948</x:v>
+        <x:v>-0.02195945945945943</x:v>
       </x:c>
       <x:c r="I317" s="26" t="n">
         <x:f>ROUND(D317-E317,1)</x:f>
-        <x:v>18000</x:v>
+        <x:v>18300</x:v>
       </x:c>
       <x:c r="J317" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K317" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B318" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C318" s="23" t="n">
-        <x:v>161000</x:v>
+        <x:v>185380</x:v>
       </x:c>
       <x:c r="D318" s="23" t="n">
-        <x:v>163880</x:v>
+        <x:v>188320</x:v>
       </x:c>
       <x:c r="E318" s="23" t="n">
-        <x:v>145360</x:v>
+        <x:v>172500</x:v>
       </x:c>
       <x:c r="F318" s="23" t="n">
-        <x:v>151140</x:v>
+        <x:v>178620</x:v>
       </x:c>
       <x:c r="G318" s="28" t="n">
         <x:f>ROUND(F318-F317,1)</x:f>
-        <x:v>-10260</x:v>
+        <x:v>-6660</x:v>
       </x:c>
       <x:c r="H318" s="24" t="n">
         <x:f>IFERROR(F318/F317-1,"")</x:f>
-        <x:v>-0.06356877323420074</x:v>
+        <x:v>-0.035945595854922296</x:v>
       </x:c>
       <x:c r="I318" s="26" t="n">
         <x:f>ROUND(D318-E318,1)</x:f>
-        <x:v>18520</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="J318" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19255,34 +19255,34 @@
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B319" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C319" s="23" t="n">
-        <x:v>148420</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="D319" s="23" t="n">
-        <x:v>172120</x:v>
+        <x:v>182940</x:v>
       </x:c>
       <x:c r="E319" s="23" t="n">
-        <x:v>146000</x:v>
+        <x:v>158140</x:v>
       </x:c>
       <x:c r="F319" s="23" t="n">
-        <x:v>168600</x:v>
+        <x:v>165460</x:v>
       </x:c>
       <x:c r="G319" s="28" t="n">
         <x:f>ROUND(F319-F318,1)</x:f>
-        <x:v>17460</x:v>
+        <x:v>-13160</x:v>
       </x:c>
       <x:c r="H319" s="24" t="n">
         <x:f>IFERROR(F319/F318-1,"")</x:f>
-        <x:v>0.1155220325526003</x:v>
+        <x:v>-0.07367596013884226</x:v>
       </x:c>
       <x:c r="I319" s="26" t="n">
         <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>26120</x:v>
+        <x:v>24800</x:v>
       </x:c>
       <x:c r="J319" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19293,34 +19293,34 @@
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B320" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C320" s="23" t="n">
-        <x:v>174900</x:v>
+        <x:v>162800</x:v>
       </x:c>
       <x:c r="D320" s="23" t="n">
-        <x:v>174900</x:v>
+        <x:v>178860</x:v>
       </x:c>
       <x:c r="E320" s="23" t="n">
-        <x:v>150860</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="F320" s="23" t="n">
-        <x:v>151600</x:v>
+        <x:v>175780</x:v>
       </x:c>
       <x:c r="G320" s="28" t="n">
         <x:f>ROUND(F320-F319,1)</x:f>
-        <x:v>-17000</x:v>
+        <x:v>10320</x:v>
       </x:c>
       <x:c r="H320" s="24" t="n">
         <x:f>IFERROR(F320/F319-1,"")</x:f>
-        <x:v>-0.10083036773428233</x:v>
+        <x:v>0.06237157016801653</x:v>
       </x:c>
       <x:c r="I320" s="26" t="n">
         <x:f>ROUND(D320-E320,1)</x:f>
-        <x:v>24040</x:v>
+        <x:v>17580</x:v>
       </x:c>
       <x:c r="J320" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19331,72 +19331,72 @@
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B321" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C321" s="23" t="n">
-        <x:v>150300</x:v>
+        <x:v>176460</x:v>
       </x:c>
       <x:c r="D321" s="23" t="n">
-        <x:v>155660</x:v>
+        <x:v>178560</x:v>
       </x:c>
       <x:c r="E321" s="23" t="n">
-        <x:v>145460</x:v>
+        <x:v>160560</x:v>
       </x:c>
       <x:c r="F321" s="23" t="n">
-        <x:v>149740</x:v>
+        <x:v>161400</x:v>
       </x:c>
       <x:c r="G321" s="28" t="n">
         <x:f>ROUND(F321-F320,1)</x:f>
-        <x:v>-1860</x:v>
+        <x:v>-14380</x:v>
       </x:c>
       <x:c r="H321" s="24" t="n">
         <x:f>IFERROR(F321/F320-1,"")</x:f>
-        <x:v>-0.012269129287598934</x:v>
+        <x:v>-0.0818068039594948</x:v>
       </x:c>
       <x:c r="I321" s="26" t="n">
         <x:f>ROUND(D321-E321,1)</x:f>
-        <x:v>10200</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="J321" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K321" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B322" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C322" s="23" t="n">
-        <x:v>152520</x:v>
+        <x:v>161000</x:v>
       </x:c>
       <x:c r="D322" s="23" t="n">
-        <x:v>153880</x:v>
+        <x:v>163880</x:v>
       </x:c>
       <x:c r="E322" s="23" t="n">
-        <x:v>135040</x:v>
+        <x:v>145360</x:v>
       </x:c>
       <x:c r="F322" s="23" t="n">
-        <x:v>142920</x:v>
+        <x:v>151140</x:v>
       </x:c>
       <x:c r="G322" s="28" t="n">
         <x:f>ROUND(F322-F321,1)</x:f>
-        <x:v>-6820</x:v>
+        <x:v>-10260</x:v>
       </x:c>
       <x:c r="H322" s="24" t="n">
         <x:f>IFERROR(F322/F321-1,"")</x:f>
-        <x:v>-0.04554561239481769</x:v>
+        <x:v>-0.06356877323420074</x:v>
       </x:c>
       <x:c r="I322" s="26" t="n">
         <x:f>ROUND(D322-E322,1)</x:f>
-        <x:v>18840</x:v>
+        <x:v>18520</x:v>
       </x:c>
       <x:c r="J322" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19407,34 +19407,34 @@
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B323" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C323" s="23" t="n">
-        <x:v>144340</x:v>
+        <x:v>148420</x:v>
       </x:c>
       <x:c r="D323" s="23" t="n">
-        <x:v>148600</x:v>
+        <x:v>172120</x:v>
       </x:c>
       <x:c r="E323" s="23" t="n">
-        <x:v>137000</x:v>
+        <x:v>146000</x:v>
       </x:c>
       <x:c r="F323" s="23" t="n">
-        <x:v>137000</x:v>
+        <x:v>168600</x:v>
       </x:c>
       <x:c r="G323" s="28" t="n">
         <x:f>ROUND(F323-F322,1)</x:f>
-        <x:v>-5920</x:v>
+        <x:v>17460</x:v>
       </x:c>
       <x:c r="H323" s="24" t="n">
         <x:f>IFERROR(F323/F322-1,"")</x:f>
-        <x:v>-0.04142177441925554</x:v>
+        <x:v>0.1155220325526003</x:v>
       </x:c>
       <x:c r="I323" s="26" t="n">
         <x:f>ROUND(D323-E323,1)</x:f>
-        <x:v>11600</x:v>
+        <x:v>26120</x:v>
       </x:c>
       <x:c r="J323" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19445,34 +19445,34 @@
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B324" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C324" s="23" t="n">
-        <x:v>137200</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="D324" s="23" t="n">
-        <x:v>144100</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="E324" s="23" t="n">
-        <x:v>135040</x:v>
+        <x:v>150860</x:v>
       </x:c>
       <x:c r="F324" s="23" t="n">
-        <x:v>139320</x:v>
+        <x:v>151600</x:v>
       </x:c>
       <x:c r="G324" s="28" t="n">
         <x:f>ROUND(F324-F323,1)</x:f>
-        <x:v>2320</x:v>
+        <x:v>-17000</x:v>
       </x:c>
       <x:c r="H324" s="24" t="n">
         <x:f>IFERROR(F324/F323-1,"")</x:f>
-        <x:v>0.016934306569343027</x:v>
+        <x:v>-0.10083036773428233</x:v>
       </x:c>
       <x:c r="I324" s="26" t="n">
         <x:f>ROUND(D324-E324,1)</x:f>
-        <x:v>9060</x:v>
+        <x:v>24040</x:v>
       </x:c>
       <x:c r="J324" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19483,34 +19483,34 @@
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B325" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C325" s="23" t="n">
-        <x:v>139320</x:v>
+        <x:v>150300</x:v>
       </x:c>
       <x:c r="D325" s="23" t="n">
-        <x:v>154560</x:v>
+        <x:v>155660</x:v>
       </x:c>
       <x:c r="E325" s="23" t="n">
-        <x:v>139300</x:v>
+        <x:v>145460</x:v>
       </x:c>
       <x:c r="F325" s="23" t="n">
-        <x:v>153980</x:v>
+        <x:v>149740</x:v>
       </x:c>
       <x:c r="G325" s="28" t="n">
         <x:f>ROUND(F325-F324,1)</x:f>
-        <x:v>14660</x:v>
+        <x:v>-1860</x:v>
       </x:c>
       <x:c r="H325" s="24" t="n">
         <x:f>IFERROR(F325/F324-1,"")</x:f>
-        <x:v>0.10522538041917895</x:v>
+        <x:v>-0.012269129287598934</x:v>
       </x:c>
       <x:c r="I325" s="26" t="n">
         <x:f>ROUND(D325-E325,1)</x:f>
-        <x:v>15260</x:v>
+        <x:v>10200</x:v>
       </x:c>
       <x:c r="J325" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19521,34 +19521,34 @@
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B326" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C326" s="23" t="n">
-        <x:v>152940</x:v>
+        <x:v>152520</x:v>
       </x:c>
       <x:c r="D326" s="23" t="n">
-        <x:v>157400</x:v>
+        <x:v>153880</x:v>
       </x:c>
       <x:c r="E326" s="23" t="n">
-        <x:v>148700</x:v>
+        <x:v>135040</x:v>
       </x:c>
       <x:c r="F326" s="23" t="n">
-        <x:v>156380</x:v>
+        <x:v>142920</x:v>
       </x:c>
       <x:c r="G326" s="28" t="n">
         <x:f>ROUND(F326-F325,1)</x:f>
-        <x:v>2400</x:v>
+        <x:v>-6820</x:v>
       </x:c>
       <x:c r="H326" s="24" t="n">
         <x:f>IFERROR(F326/F325-1,"")</x:f>
-        <x:v>0.015586439797376173</x:v>
+        <x:v>-0.04554561239481769</x:v>
       </x:c>
       <x:c r="I326" s="26" t="n">
         <x:f>ROUND(D326-E326,1)</x:f>
-        <x:v>8700</x:v>
+        <x:v>18840</x:v>
       </x:c>
       <x:c r="J326" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19559,34 +19559,34 @@
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B327" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C327" s="23" t="n">
-        <x:v>158800</x:v>
+        <x:v>144340</x:v>
       </x:c>
       <x:c r="D327" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>148600</x:v>
       </x:c>
       <x:c r="E327" s="23" t="n">
-        <x:v>147600</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="F327" s="23" t="n">
-        <x:v>157940</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="G327" s="28" t="n">
         <x:f>ROUND(F327-F326,1)</x:f>
-        <x:v>1560</x:v>
+        <x:v>-5920</x:v>
       </x:c>
       <x:c r="H327" s="24" t="n">
         <x:f>IFERROR(F327/F326-1,"")</x:f>
-        <x:v>0.009975700217419003</x:v>
+        <x:v>-0.04142177441925554</x:v>
       </x:c>
       <x:c r="I327" s="26" t="n">
         <x:f>ROUND(D327-E327,1)</x:f>
-        <x:v>12900</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="J327" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19597,34 +19597,34 @@
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B328" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C328" s="23" t="n">
-        <x:v>157500</x:v>
+        <x:v>137200</x:v>
       </x:c>
       <x:c r="D328" s="23" t="n">
-        <x:v>161280</x:v>
+        <x:v>144100</x:v>
       </x:c>
       <x:c r="E328" s="23" t="n">
-        <x:v>140220</x:v>
+        <x:v>135040</x:v>
       </x:c>
       <x:c r="F328" s="23" t="n">
-        <x:v>142000</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="G328" s="28" t="n">
         <x:f>ROUND(F328-F327,1)</x:f>
-        <x:v>-15940</x:v>
+        <x:v>2320</x:v>
       </x:c>
       <x:c r="H328" s="24" t="n">
         <x:f>IFERROR(F328/F327-1,"")</x:f>
-        <x:v>-0.10092440167152084</x:v>
+        <x:v>0.016934306569343027</x:v>
       </x:c>
       <x:c r="I328" s="26" t="n">
         <x:f>ROUND(D328-E328,1)</x:f>
-        <x:v>21060</x:v>
+        <x:v>9060</x:v>
       </x:c>
       <x:c r="J328" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19635,34 +19635,34 @@
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B329" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C329" s="23" t="n">
-        <x:v>141000</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="D329" s="23" t="n">
-        <x:v>143540</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="E329" s="23" t="n">
-        <x:v>127120</x:v>
+        <x:v>139300</x:v>
       </x:c>
       <x:c r="F329" s="23" t="n">
-        <x:v>134340</x:v>
+        <x:v>153980</x:v>
       </x:c>
       <x:c r="G329" s="28" t="n">
         <x:f>ROUND(F329-F328,1)</x:f>
-        <x:v>-7660</x:v>
+        <x:v>14660</x:v>
       </x:c>
       <x:c r="H329" s="24" t="n">
         <x:f>IFERROR(F329/F328-1,"")</x:f>
-        <x:v>-0.05394366197183098</x:v>
+        <x:v>0.10522538041917895</x:v>
       </x:c>
       <x:c r="I329" s="26" t="n">
         <x:f>ROUND(D329-E329,1)</x:f>
-        <x:v>16420</x:v>
+        <x:v>15260</x:v>
       </x:c>
       <x:c r="J329" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19673,34 +19673,34 @@
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B330" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C330" s="23" t="n">
-        <x:v>133600</x:v>
+        <x:v>152940</x:v>
       </x:c>
       <x:c r="D330" s="23" t="n">
-        <x:v>135900</x:v>
+        <x:v>157400</x:v>
       </x:c>
       <x:c r="E330" s="23" t="n">
-        <x:v>126200</x:v>
+        <x:v>148700</x:v>
       </x:c>
       <x:c r="F330" s="23" t="n">
-        <x:v>128580</x:v>
+        <x:v>156380</x:v>
       </x:c>
       <x:c r="G330" s="28" t="n">
         <x:f>ROUND(F330-F329,1)</x:f>
-        <x:v>-5760</x:v>
+        <x:v>2400</x:v>
       </x:c>
       <x:c r="H330" s="24" t="n">
         <x:f>IFERROR(F330/F329-1,"")</x:f>
-        <x:v>-0.04287628405538191</x:v>
+        <x:v>0.015586439797376173</x:v>
       </x:c>
       <x:c r="I330" s="26" t="n">
         <x:f>ROUND(D330-E330,1)</x:f>
-        <x:v>9700</x:v>
+        <x:v>8700</x:v>
       </x:c>
       <x:c r="J330" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19711,79 +19711,231 @@
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="22" t="n">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B331" s="22" t="str">
-        <x:v>9月21日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C331" s="23" t="n">
-        <x:v>128500</x:v>
+        <x:v>158800</x:v>
       </x:c>
       <x:c r="D331" s="23" t="n">
-        <x:v>134800</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="E331" s="23" t="n">
-        <x:v>127100</x:v>
+        <x:v>147600</x:v>
       </x:c>
       <x:c r="F331" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>157940</x:v>
       </x:c>
       <x:c r="G331" s="28" t="n">
         <x:f>ROUND(F331-F330,1)</x:f>
-        <x:v>4920</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="H331" s="24" t="n">
         <x:f>IFERROR(F331/F330-1,"")</x:f>
-        <x:v>0.038264115725618275</x:v>
+        <x:v>0.009975700217419003</x:v>
       </x:c>
       <x:c r="I331" s="26" t="n">
         <x:f>ROUND(D331-E331,1)</x:f>
-        <x:v>7700</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="J331" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K331" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332">
+      <x:c r="A332" s="22" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B332" s="22" t="str">
+        <x:v>8月31日-9月4日</x:v>
+      </x:c>
+      <x:c r="C332" s="23" t="n">
+        <x:v>157500</x:v>
+      </x:c>
+      <x:c r="D332" s="23" t="n">
+        <x:v>161280</x:v>
+      </x:c>
+      <x:c r="E332" s="23" t="n">
+        <x:v>140220</x:v>
+      </x:c>
+      <x:c r="F332" s="23" t="n">
+        <x:v>142000</x:v>
+      </x:c>
+      <x:c r="G332" s="28" t="n">
+        <x:f>ROUND(F332-F331,1)</x:f>
+        <x:v>-15940</x:v>
+      </x:c>
+      <x:c r="H332" s="24" t="n">
+        <x:f>IFERROR(F332/F331-1,"")</x:f>
+        <x:v>-0.10092440167152084</x:v>
+      </x:c>
+      <x:c r="I332" s="26" t="n">
+        <x:f>ROUND(D332-E332,1)</x:f>
+        <x:v>21060</x:v>
+      </x:c>
+      <x:c r="J332" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K332" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333">
+      <x:c r="A333" s="22" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B333" s="22" t="str">
+        <x:v>9月7日-9月11日</x:v>
+      </x:c>
+      <x:c r="C333" s="23" t="n">
+        <x:v>141000</x:v>
+      </x:c>
+      <x:c r="D333" s="23" t="n">
+        <x:v>143540</x:v>
+      </x:c>
+      <x:c r="E333" s="23" t="n">
+        <x:v>127120</x:v>
+      </x:c>
+      <x:c r="F333" s="23" t="n">
+        <x:v>134340</x:v>
+      </x:c>
+      <x:c r="G333" s="28" t="n">
+        <x:f>ROUND(F333-F332,1)</x:f>
+        <x:v>-7660</x:v>
+      </x:c>
+      <x:c r="H333" s="24" t="n">
+        <x:f>IFERROR(F333/F332-1,"")</x:f>
+        <x:v>-0.05394366197183098</x:v>
+      </x:c>
+      <x:c r="I333" s="26" t="n">
+        <x:f>ROUND(D333-E333,1)</x:f>
+        <x:v>16420</x:v>
+      </x:c>
+      <x:c r="J333" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K333" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334">
+      <x:c r="A334" s="22" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B334" s="22" t="str">
+        <x:v>9月14日-9月18日</x:v>
+      </x:c>
+      <x:c r="C334" s="23" t="n">
+        <x:v>133600</x:v>
+      </x:c>
+      <x:c r="D334" s="23" t="n">
+        <x:v>135900</x:v>
+      </x:c>
+      <x:c r="E334" s="23" t="n">
+        <x:v>126200</x:v>
+      </x:c>
+      <x:c r="F334" s="23" t="n">
+        <x:v>128580</x:v>
+      </x:c>
+      <x:c r="G334" s="28" t="n">
+        <x:f>ROUND(F334-F333,1)</x:f>
+        <x:v>-5760</x:v>
+      </x:c>
+      <x:c r="H334" s="24" t="n">
+        <x:f>IFERROR(F334/F333-1,"")</x:f>
+        <x:v>-0.04287628405538191</x:v>
+      </x:c>
+      <x:c r="I334" s="26" t="n">
+        <x:f>ROUND(D334-E334,1)</x:f>
+        <x:v>9700</x:v>
+      </x:c>
+      <x:c r="J334" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K334" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335">
+      <x:c r="A335" s="22" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B335" s="22" t="str">
+        <x:v>9月21日</x:v>
+      </x:c>
+      <x:c r="C335" s="23" t="n">
+        <x:v>128500</x:v>
+      </x:c>
+      <x:c r="D335" s="23" t="n">
+        <x:v>134800</x:v>
+      </x:c>
+      <x:c r="E335" s="23" t="n">
+        <x:v>127100</x:v>
+      </x:c>
+      <x:c r="F335" s="23" t="n">
+        <x:v>133500</x:v>
+      </x:c>
+      <x:c r="G335" s="28" t="n">
+        <x:f>ROUND(F335-F334,1)</x:f>
+        <x:v>4920</x:v>
+      </x:c>
+      <x:c r="H335" s="24" t="n">
+        <x:f>IFERROR(F335/F334-1,"")</x:f>
+        <x:v>0.038264115725618275</x:v>
+      </x:c>
+      <x:c r="I335" s="26" t="n">
+        <x:f>ROUND(D335-E335,1)</x:f>
+        <x:v>7700</x:v>
+      </x:c>
+      <x:c r="J335" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K335" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="332">
-      <x:c r="A332" s="31" t="str">
+    <x:row r="336">
+      <x:c r="A336" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B332" s="30" t="n">
+      <x:c r="B336" s="30" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C332" s="30"/>
-      <x:c r="D332" s="30"/>
-      <x:c r="E332" s="30"/>
-      <x:c r="F332" s="30"/>
-      <x:c r="G332" s="30"/>
-      <x:c r="H332" s="30"/>
-      <x:c r="I332" s="32" t="n">
-        <x:f>ROUND(SUM(I295:I331),1)</x:f>
+      <x:c r="C336" s="30"/>
+      <x:c r="D336" s="30"/>
+      <x:c r="E336" s="30"/>
+      <x:c r="F336" s="30"/>
+      <x:c r="G336" s="30"/>
+      <x:c r="H336" s="30"/>
+      <x:c r="I336" s="32" t="n">
+        <x:f>ROUND(SUM(I299:I335),1)</x:f>
         <x:v>749100</x:v>
       </x:c>
-      <x:c r="J332" s="30"/>
-      <x:c r="K332" s="30"/>
-    </x:row>
-    <x:row r="333">
-      <x:c r="A333" s="31" t="str">
+      <x:c r="J336" s="30"/>
+      <x:c r="K336" s="30"/>
+    </x:row>
+    <x:row r="337">
+      <x:c r="A337" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B333" s="30"/>
-      <x:c r="C333" s="30"/>
-      <x:c r="D333" s="30"/>
-      <x:c r="E333" s="30"/>
-      <x:c r="F333" s="30"/>
-      <x:c r="G333" s="30"/>
-      <x:c r="H333" s="30"/>
-      <x:c r="I333" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I295:I331),0),1)</x:f>
+      <x:c r="B337" s="30"/>
+      <x:c r="C337" s="30"/>
+      <x:c r="D337" s="30"/>
+      <x:c r="E337" s="30"/>
+      <x:c r="F337" s="30"/>
+      <x:c r="G337" s="30"/>
+      <x:c r="H337" s="30"/>
+      <x:c r="I337" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I299:I335),0),1)</x:f>
         <x:v>20245.9</x:v>
       </x:c>
-      <x:c r="J333" s="30"/>
-      <x:c r="K333" s="30"/>
+      <x:c r="J337" s="30"/>
+      <x:c r="K337" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -19792,10 +19944,10 @@
     <x:mergeCell ref="A45:K45"/>
     <x:mergeCell ref="A87:K87"/>
     <x:mergeCell ref="A129:K129"/>
-    <x:mergeCell ref="A170:K170"/>
-    <x:mergeCell ref="A211:K211"/>
-    <x:mergeCell ref="A252:K252"/>
-    <x:mergeCell ref="A293:K293"/>
+    <x:mergeCell ref="A171:K171"/>
+    <x:mergeCell ref="A213:K213"/>
+    <x:mergeCell ref="A255:K255"/>
+    <x:mergeCell ref="A297:K297"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -48235,30 +48387,48 @@
       </x:c>
     </x:row>
     <x:row r="219">
-      <x:c r="A219" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B219" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C219" s="30"/>
-      <x:c r="D219" s="30"/>
-      <x:c r="E219" s="30"/>
-      <x:c r="F219" s="30"/>
-      <x:c r="G219" s="30"/>
-      <x:c r="H219" s="30"/>
-      <x:c r="I219" s="30"/>
-      <x:c r="J219" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J218),1)</x:f>
-        <x:v>2120.2</x:v>
-      </x:c>
-      <x:c r="K219" s="30"/>
+      <x:c r="A219" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B219" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C219" s="22" t="str">
+        <x:v>9月21日</x:v>
+      </x:c>
+      <x:c r="D219" s="23" t="n">
+        <x:v>7549</x:v>
+      </x:c>
+      <x:c r="E219" s="23" t="n">
+        <x:v>7599</x:v>
+      </x:c>
+      <x:c r="F219" s="23" t="n">
+        <x:v>7527</x:v>
+      </x:c>
+      <x:c r="G219" s="23" t="n">
+        <x:v>7560.6</x:v>
+      </x:c>
+      <x:c r="H219" s="23" t="n">
+        <x:v>-118.6</x:v>
+      </x:c>
+      <x:c r="I219" s="24" t="n">
+        <x:v>-0.01544431711636618</x:v>
+      </x:c>
+      <x:c r="J219" s="23" t="n">
+        <x:f>ROUND(E219-F219,1)</x:f>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K219" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B220" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B220" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C220" s="30"/>
       <x:c r="D220" s="30"/>
       <x:c r="E220" s="30"/>
@@ -48266,11 +48436,29 @@
       <x:c r="G220" s="30"/>
       <x:c r="H220" s="30"/>
       <x:c r="I220" s="30"/>
-      <x:c r="J220" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J218),0),1)</x:f>
-        <x:v>151.4</x:v>
+      <x:c r="J220" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J219),1)</x:f>
+        <x:v>2192.2</x:v>
       </x:c>
       <x:c r="K220" s="30"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B221" s="30"/>
+      <x:c r="C221" s="30"/>
+      <x:c r="D221" s="30"/>
+      <x:c r="E221" s="30"/>
+      <x:c r="F221" s="30"/>
+      <x:c r="G221" s="30"/>
+      <x:c r="H221" s="30"/>
+      <x:c r="I221" s="30"/>
+      <x:c r="J221" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
+        <x:v>146.1</x:v>
+      </x:c>
+      <x:c r="K221" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -55330,30 +55518,48 @@
       </x:c>
     </x:row>
     <x:row r="219">
-      <x:c r="A219" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B219" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C219" s="30"/>
-      <x:c r="D219" s="30"/>
-      <x:c r="E219" s="30"/>
-      <x:c r="F219" s="30"/>
-      <x:c r="G219" s="30"/>
-      <x:c r="H219" s="30"/>
-      <x:c r="I219" s="30"/>
-      <x:c r="J219" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J218),1)</x:f>
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c r="K219" s="30"/>
+      <x:c r="A219" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B219" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C219" s="22" t="str">
+        <x:v>9月21日</x:v>
+      </x:c>
+      <x:c r="D219" s="23" t="n">
+        <x:v>7688</x:v>
+      </x:c>
+      <x:c r="E219" s="23" t="n">
+        <x:v>7728</x:v>
+      </x:c>
+      <x:c r="F219" s="23" t="n">
+        <x:v>7640</x:v>
+      </x:c>
+      <x:c r="G219" s="23" t="n">
+        <x:v>7672.6</x:v>
+      </x:c>
+      <x:c r="H219" s="23" t="n">
+        <x:v>-117.2</x:v>
+      </x:c>
+      <x:c r="I219" s="24" t="n">
+        <x:v>-0.015045315669208414</x:v>
+      </x:c>
+      <x:c r="J219" s="23" t="n">
+        <x:f>ROUND(E219-F219,1)</x:f>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="K219" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B220" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B220" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C220" s="30"/>
       <x:c r="D220" s="30"/>
       <x:c r="E220" s="30"/>
@@ -55361,11 +55567,29 @@
       <x:c r="G220" s="30"/>
       <x:c r="H220" s="30"/>
       <x:c r="I220" s="30"/>
-      <x:c r="J220" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J218),0),1)</x:f>
-        <x:v>144.4</x:v>
+      <x:c r="J220" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J219),1)</x:f>
+        <x:v>2110</x:v>
       </x:c>
       <x:c r="K220" s="30"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B221" s="30"/>
+      <x:c r="C221" s="30"/>
+      <x:c r="D221" s="30"/>
+      <x:c r="E221" s="30"/>
+      <x:c r="F221" s="30"/>
+      <x:c r="G221" s="30"/>
+      <x:c r="H221" s="30"/>
+      <x:c r="I221" s="30"/>
+      <x:c r="J221" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
+        <x:v>140.7</x:v>
+      </x:c>
+      <x:c r="K221" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -62425,30 +62649,48 @@
       </x:c>
     </x:row>
     <x:row r="219">
-      <x:c r="A219" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B219" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C219" s="30"/>
-      <x:c r="D219" s="30"/>
-      <x:c r="E219" s="30"/>
-      <x:c r="F219" s="30"/>
-      <x:c r="G219" s="30"/>
-      <x:c r="H219" s="30"/>
-      <x:c r="I219" s="30"/>
-      <x:c r="J219" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J218),1)</x:f>
-        <x:v>737</x:v>
-      </x:c>
-      <x:c r="K219" s="30"/>
+      <x:c r="A219" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B219" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C219" s="22" t="str">
+        <x:v>9月21日</x:v>
+      </x:c>
+      <x:c r="D219" s="23" t="n">
+        <x:v>4451</x:v>
+      </x:c>
+      <x:c r="E219" s="23" t="n">
+        <x:v>4474.6</x:v>
+      </x:c>
+      <x:c r="F219" s="23" t="n">
+        <x:v>4434.8</x:v>
+      </x:c>
+      <x:c r="G219" s="23" t="n">
+        <x:v>4464.8</x:v>
+      </x:c>
+      <x:c r="H219" s="23" t="n">
+        <x:v>-43.2</x:v>
+      </x:c>
+      <x:c r="I219" s="24" t="n">
+        <x:v>-0.0095829636202307</x:v>
+      </x:c>
+      <x:c r="J219" s="23" t="n">
+        <x:f>ROUND(E219-F219,1)</x:f>
+        <x:v>39.8</x:v>
+      </x:c>
+      <x:c r="K219" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B220" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B220" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C220" s="30"/>
       <x:c r="D220" s="30"/>
       <x:c r="E220" s="30"/>
@@ -62456,11 +62698,29 @@
       <x:c r="G220" s="30"/>
       <x:c r="H220" s="30"/>
       <x:c r="I220" s="30"/>
-      <x:c r="J220" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J218),0),1)</x:f>
-        <x:v>52.6</x:v>
+      <x:c r="J220" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J219),1)</x:f>
+        <x:v>776.8</x:v>
       </x:c>
       <x:c r="K220" s="30"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B221" s="30"/>
+      <x:c r="C221" s="30"/>
+      <x:c r="D221" s="30"/>
+      <x:c r="E221" s="30"/>
+      <x:c r="F221" s="30"/>
+      <x:c r="G221" s="30"/>
+      <x:c r="H221" s="30"/>
+      <x:c r="I221" s="30"/>
+      <x:c r="J221" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
+        <x:v>51.8</x:v>
+      </x:c>
+      <x:c r="K221" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -69520,30 +69780,48 @@
       </x:c>
     </x:row>
     <x:row r="219">
-      <x:c r="A219" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B219" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C219" s="30"/>
-      <x:c r="D219" s="30"/>
-      <x:c r="E219" s="30"/>
-      <x:c r="F219" s="30"/>
-      <x:c r="G219" s="30"/>
-      <x:c r="H219" s="30"/>
-      <x:c r="I219" s="30"/>
-      <x:c r="J219" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J218),1)</x:f>
-        <x:v>432.4</x:v>
-      </x:c>
-      <x:c r="K219" s="30"/>
+      <x:c r="A219" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B219" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C219" s="22" t="str">
+        <x:v>9月21日</x:v>
+      </x:c>
+      <x:c r="D219" s="23" t="n">
+        <x:v>2830</x:v>
+      </x:c>
+      <x:c r="E219" s="23" t="n">
+        <x:v>2849.8</x:v>
+      </x:c>
+      <x:c r="F219" s="23" t="n">
+        <x:v>2822</x:v>
+      </x:c>
+      <x:c r="G219" s="23" t="n">
+        <x:v>2847.4</x:v>
+      </x:c>
+      <x:c r="H219" s="23" t="n">
+        <x:v>-14.8</x:v>
+      </x:c>
+      <x:c r="I219" s="24" t="n">
+        <x:v>-0.005170847599748396</x:v>
+      </x:c>
+      <x:c r="J219" s="23" t="n">
+        <x:f>ROUND(E219-F219,1)</x:f>
+        <x:v>27.8</x:v>
+      </x:c>
+      <x:c r="K219" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B220" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B220" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="C220" s="30"/>
       <x:c r="D220" s="30"/>
       <x:c r="E220" s="30"/>
@@ -69551,11 +69829,29 @@
       <x:c r="G220" s="30"/>
       <x:c r="H220" s="30"/>
       <x:c r="I220" s="30"/>
-      <x:c r="J220" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J218),0),1)</x:f>
-        <x:v>30.9</x:v>
+      <x:c r="J220" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J219),1)</x:f>
+        <x:v>460.2</x:v>
       </x:c>
       <x:c r="K220" s="30"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B221" s="30"/>
+      <x:c r="C221" s="30"/>
+      <x:c r="D221" s="30"/>
+      <x:c r="E221" s="30"/>
+      <x:c r="F221" s="30"/>
+      <x:c r="G221" s="30"/>
+      <x:c r="H221" s="30"/>
+      <x:c r="I221" s="30"/>
+      <x:c r="J221" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
+        <x:v>30.7</x:v>
+      </x:c>
+      <x:c r="K221" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R5ea45d39959a4237"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R951a4d4e333643a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R926ee00e66434f59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R304f79f52cbc4bd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R8db1e49565d2404f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc1231a5ac1ae4ad8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R982c430863b04bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rad6755f6ab284ec8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rf61a1795e54e48c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R41b1c1afd34b4dac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3edacfb2804444db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rad9da5e5539c49f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R7146c1a914a844dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc07e0eb2baaf4601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R7cc0a2864fb24a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rdd3ce0beb3ed4bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R13ec6751da9c43e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R7f4c521287054d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R955dde0a0afd4d55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R3e4353291b7a4942"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7777.91</x:v>
+        <x:v>7852.23</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7723.68</x:v>
+        <x:v>7734.35</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>54.2</x:v>
+        <x:v>117.9</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="n">
+        <x:v>30803.5</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="n">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="G4" s="10" t="n">
-        <x:v>30685.6</x:v>
-      </x:c>
-      <x:c r="H4" s="10" t="n">
-        <x:v>175.3</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7869.35</x:v>
+        <x:v>7922.62</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7809.59</x:v>
+        <x:v>7808.98</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>59.8</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>30570.8</x:v>
+        <x:v>30684.4</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>174.7</x:v>
+        <x:v>174.3</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3950.94</x:v>
+        <x:v>3967.68</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3918.13</x:v>
+        <x:v>3945.42</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>32.8</x:v>
+        <x:v>22.3</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8410.4</x:v>
+        <x:v>8432.7</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>48.1</x:v>
+        <x:v>47.9</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7599</x:v>
+        <x:v>7687</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7527</x:v>
+        <x:v>7563</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>72</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>32636</x:v>
+        <x:v>32760</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>186.5</x:v>
+        <x:v>186.1</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>134800</x:v>
+        <x:v>136560</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>127100</x:v>
+        <x:v>131400</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>7700</x:v>
+        <x:v>5160</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1408360</x:v>
+        <x:v>1413520</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8047.8</x:v>
+        <x:v>8031.4</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -7957,30 +7957,48 @@
       </x:c>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B220" s="30" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C220" s="30"/>
-      <x:c r="D220" s="30"/>
-      <x:c r="E220" s="30"/>
-      <x:c r="F220" s="30"/>
-      <x:c r="G220" s="30"/>
-      <x:c r="H220" s="30"/>
-      <x:c r="I220" s="30"/>
-      <x:c r="J220" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J219),1)</x:f>
-        <x:v>89880</x:v>
-      </x:c>
-      <x:c r="K220" s="30"/>
+      <x:c r="A220" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B220" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C220" s="22" t="str">
+        <x:v>9月22日</x:v>
+      </x:c>
+      <x:c r="D220" s="23" t="n">
+        <x:v>133040</x:v>
+      </x:c>
+      <x:c r="E220" s="23" t="n">
+        <x:v>136560</x:v>
+      </x:c>
+      <x:c r="F220" s="23" t="n">
+        <x:v>131400</x:v>
+      </x:c>
+      <x:c r="G220" s="23" t="n">
+        <x:v>135480</x:v>
+      </x:c>
+      <x:c r="H220" s="28" t="n">
+        <x:v>1980</x:v>
+      </x:c>
+      <x:c r="I220" s="24" t="n">
+        <x:v>0.014831460674157304</x:v>
+      </x:c>
+      <x:c r="J220" s="23" t="n">
+        <x:f>ROUND(E220-F220,1)</x:f>
+        <x:v>5160</x:v>
+      </x:c>
+      <x:c r="K220" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B221" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B221" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C221" s="30"/>
       <x:c r="D221" s="30"/>
       <x:c r="E221" s="30"/>
@@ -7988,11 +8006,29 @@
       <x:c r="G221" s="30"/>
       <x:c r="H221" s="30"/>
       <x:c r="I221" s="30"/>
-      <x:c r="J221" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
-        <x:v>5992</x:v>
+      <x:c r="J221" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J220),1)</x:f>
+        <x:v>95040</x:v>
       </x:c>
       <x:c r="K221" s="30"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B222" s="30"/>
+      <x:c r="C222" s="30"/>
+      <x:c r="D222" s="30"/>
+      <x:c r="E222" s="30"/>
+      <x:c r="F222" s="30"/>
+      <x:c r="G222" s="30"/>
+      <x:c r="H222" s="30"/>
+      <x:c r="I222" s="30"/>
+      <x:c r="J222" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
+        <x:v>5940</x:v>
+      </x:c>
+      <x:c r="K222" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9450,37 +9486,37 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" s="22" t="str">
-        <x:v>9月21日</x:v>
+        <x:v>9月21日-9月22日</x:v>
       </x:c>
       <x:c r="C41" s="23" t="n">
         <x:v>7723.68</x:v>
       </x:c>
       <x:c r="D41" s="23" t="n">
-        <x:v>7777.91</x:v>
+        <x:v>7852.23</x:v>
       </x:c>
       <x:c r="E41" s="23" t="n">
         <x:v>7723.68</x:v>
       </x:c>
       <x:c r="F41" s="23" t="n">
-        <x:v>7766.33</x:v>
+        <x:v>7759.03</x:v>
       </x:c>
       <x:c r="G41" s="23" t="n">
         <x:f>ROUND(F41-F40,1)</x:f>
-        <x:v>78.7</x:v>
+        <x:v>71.4</x:v>
       </x:c>
       <x:c r="H41" s="24" t="n">
         <x:f>IFERROR(F41/F40-1,"")</x:f>
-        <x:v>0.01024248171403519</x:v>
+        <x:v>0.009292899335162197</x:v>
       </x:c>
       <x:c r="I41" s="23" t="n">
         <x:f>ROUND(D41-E41,1)</x:f>
-        <x:v>54.2</x:v>
+        <x:v>128.5</x:v>
       </x:c>
       <x:c r="J41" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K41" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -9498,7 +9534,7 @@
       <x:c r="H42" s="30"/>
       <x:c r="I42" s="32" t="n">
         <x:f>ROUND(SUM(I5:I41),1)</x:f>
-        <x:v>15128.1</x:v>
+        <x:v>15202.4</x:v>
       </x:c>
       <x:c r="J42" s="30"/>
       <x:c r="K42" s="30"/>
@@ -9516,7 +9552,7 @@
       <x:c r="H43" s="30"/>
       <x:c r="I43" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I41),0),1)</x:f>
-        <x:v>408.9</x:v>
+        <x:v>410.9</x:v>
       </x:c>
       <x:c r="J43" s="30"/>
       <x:c r="K43" s="30"/>
@@ -10938,37 +10974,37 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B83" s="22" t="str">
-        <x:v>9月21日</x:v>
+        <x:v>9月21日-9月22日</x:v>
       </x:c>
       <x:c r="C83" s="23" t="n">
         <x:v>7829.82</x:v>
       </x:c>
       <x:c r="D83" s="23" t="n">
-        <x:v>7869.35</x:v>
+        <x:v>7922.62</x:v>
       </x:c>
       <x:c r="E83" s="23" t="n">
-        <x:v>7809.59</x:v>
+        <x:v>7808.98</x:v>
       </x:c>
       <x:c r="F83" s="23" t="n">
-        <x:v>7850.48</x:v>
+        <x:v>7828.94</x:v>
       </x:c>
       <x:c r="G83" s="23" t="n">
         <x:f>ROUND(F83-F82,1)</x:f>
-        <x:v>50.9</x:v>
+        <x:v>29.3</x:v>
       </x:c>
       <x:c r="H83" s="24" t="n">
         <x:f>IFERROR(F83/F82-1,"")</x:f>
-        <x:v>0.0065221209778436595</x:v>
+        <x:v>0.0037604444324779163</x:v>
       </x:c>
       <x:c r="I83" s="23" t="n">
         <x:f>ROUND(D83-E83,1)</x:f>
-        <x:v>59.8</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="J83" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K83" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -10986,7 +11022,7 @@
       <x:c r="H84" s="30"/>
       <x:c r="I84" s="32" t="n">
         <x:f>ROUND(SUM(I47:I83),1)</x:f>
-        <x:v>15110.3</x:v>
+        <x:v>15164.1</x:v>
       </x:c>
       <x:c r="J84" s="30"/>
       <x:c r="K84" s="30"/>
@@ -11004,7 +11040,7 @@
       <x:c r="H85" s="30"/>
       <x:c r="I85" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I47:I83),0),1)</x:f>
-        <x:v>408.4</x:v>
+        <x:v>409.8</x:v>
       </x:c>
       <x:c r="J85" s="30"/>
       <x:c r="K85" s="30"/>
@@ -12426,37 +12462,37 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B125" s="22" t="str">
-        <x:v>9月21日</x:v>
+        <x:v>9月21日-9月22日</x:v>
       </x:c>
       <x:c r="C125" s="23" t="n">
         <x:v>3920.27</x:v>
       </x:c>
       <x:c r="D125" s="23" t="n">
-        <x:v>3950.94</x:v>
+        <x:v>3967.68</x:v>
       </x:c>
       <x:c r="E125" s="23" t="n">
         <x:v>3918.13</x:v>
       </x:c>
       <x:c r="F125" s="23" t="n">
-        <x:v>3949.91</x:v>
+        <x:v>3952.13</x:v>
       </x:c>
       <x:c r="G125" s="23" t="n">
         <x:f>ROUND(F125-F124,1)</x:f>
-        <x:v>38</x:v>
+        <x:v>40.3</x:v>
       </x:c>
       <x:c r="H125" s="24" t="n">
         <x:f>IFERROR(F125/F124-1,"")</x:f>
-        <x:v>0.009724249527719442</x:v>
+        <x:v>0.010291753049053387</x:v>
       </x:c>
       <x:c r="I125" s="23" t="n">
         <x:f>ROUND(D125-E125,1)</x:f>
-        <x:v>32.8</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="J125" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K125" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -12474,7 +12510,7 @@
       <x:c r="H126" s="30"/>
       <x:c r="I126" s="32" t="n">
         <x:f>ROUND(SUM(I89:I125),1)</x:f>
-        <x:v>3973.9</x:v>
+        <x:v>3990.6</x:v>
       </x:c>
       <x:c r="J126" s="30"/>
       <x:c r="K126" s="30"/>
@@ -12492,7 +12528,7 @@
       <x:c r="H127" s="30"/>
       <x:c r="I127" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I89:I125),0),1)</x:f>
-        <x:v>107.4</x:v>
+        <x:v>107.9</x:v>
       </x:c>
       <x:c r="J127" s="30"/>
       <x:c r="K127" s="30"/>
@@ -13914,37 +13950,37 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B167" s="22" t="str">
-        <x:v>9月21日</x:v>
+        <x:v>9月21日-9月22日</x:v>
       </x:c>
       <x:c r="C167" s="23" t="n">
         <x:v>7549</x:v>
       </x:c>
       <x:c r="D167" s="23" t="n">
-        <x:v>7599</x:v>
+        <x:v>7687</x:v>
       </x:c>
       <x:c r="E167" s="23" t="n">
         <x:v>7527</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>7560.6</x:v>
+        <x:v>7580.2</x:v>
       </x:c>
       <x:c r="G167" s="23" t="n">
         <x:f>ROUND(F167-F166,1)</x:f>
-        <x:v>-118.6</x:v>
+        <x:v>-99</x:v>
       </x:c>
       <x:c r="H167" s="24" t="n">
         <x:f>IFERROR(F167/F166-1,"")</x:f>
-        <x:v>-0.01544431711636618</x:v>
+        <x:v>-0.012891967913324254</x:v>
       </x:c>
       <x:c r="I167" s="23" t="n">
         <x:f>ROUND(D167-E167,1)</x:f>
-        <x:v>72</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J167" s="22" t="str">
         <x:v>IM2612</x:v>
       </x:c>
       <x:c r="K167" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -13962,7 +13998,7 @@
       <x:c r="H168" s="30"/>
       <x:c r="I168" s="32" t="n">
         <x:f>ROUND(SUM(I131:I167),1)</x:f>
-        <x:v>15784.8</x:v>
+        <x:v>15872.8</x:v>
       </x:c>
       <x:c r="J168" s="30"/>
       <x:c r="K168" s="30"/>
@@ -13980,7 +14016,7 @@
       <x:c r="H169" s="30"/>
       <x:c r="I169" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I131:I167),0),1)</x:f>
-        <x:v>426.6</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="J169" s="30"/>
       <x:c r="K169" s="30"/>
@@ -19866,37 +19902,37 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B335" s="22" t="str">
-        <x:v>9月21日</x:v>
+        <x:v>9月21日-9月22日</x:v>
       </x:c>
       <x:c r="C335" s="23" t="n">
         <x:v>128500</x:v>
       </x:c>
       <x:c r="D335" s="23" t="n">
-        <x:v>134800</x:v>
+        <x:v>136560</x:v>
       </x:c>
       <x:c r="E335" s="23" t="n">
         <x:v>127100</x:v>
       </x:c>
       <x:c r="F335" s="23" t="n">
-        <x:v>133500</x:v>
+        <x:v>135480</x:v>
       </x:c>
       <x:c r="G335" s="28" t="n">
         <x:f>ROUND(F335-F334,1)</x:f>
-        <x:v>4920</x:v>
+        <x:v>6900</x:v>
       </x:c>
       <x:c r="H335" s="24" t="n">
         <x:f>IFERROR(F335/F334-1,"")</x:f>
-        <x:v>0.038264115725618275</x:v>
+        <x:v>0.05366308912739148</x:v>
       </x:c>
       <x:c r="I335" s="26" t="n">
         <x:f>ROUND(D335-E335,1)</x:f>
-        <x:v>7700</x:v>
+        <x:v>9460</x:v>
       </x:c>
       <x:c r="J335" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K335" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
@@ -19914,7 +19950,7 @@
       <x:c r="H336" s="30"/>
       <x:c r="I336" s="32" t="n">
         <x:f>ROUND(SUM(I299:I335),1)</x:f>
-        <x:v>749100</x:v>
+        <x:v>750860</x:v>
       </x:c>
       <x:c r="J336" s="30"/>
       <x:c r="K336" s="30"/>
@@ -19932,7 +19968,7 @@
       <x:c r="H337" s="30"/>
       <x:c r="I337" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I299:I335),0),1)</x:f>
-        <x:v>20245.9</x:v>
+        <x:v>20293.5</x:v>
       </x:c>
       <x:c r="J337" s="30"/>
       <x:c r="K337" s="30"/>
@@ -27030,30 +27066,48 @@
       </x:c>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B220" s="30" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C220" s="30"/>
-      <x:c r="D220" s="30"/>
-      <x:c r="E220" s="30"/>
-      <x:c r="F220" s="30"/>
-      <x:c r="G220" s="30"/>
-      <x:c r="H220" s="30"/>
-      <x:c r="I220" s="30"/>
-      <x:c r="J220" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J219),1)</x:f>
-        <x:v>1954.8</x:v>
-      </x:c>
-      <x:c r="K220" s="30"/>
+      <x:c r="A220" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B220" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C220" s="22" t="str">
+        <x:v>9月22日</x:v>
+      </x:c>
+      <x:c r="D220" s="23" t="n">
+        <x:v>7819.62</x:v>
+      </x:c>
+      <x:c r="E220" s="23" t="n">
+        <x:v>7852.23</x:v>
+      </x:c>
+      <x:c r="F220" s="23" t="n">
+        <x:v>7734.35</x:v>
+      </x:c>
+      <x:c r="G220" s="23" t="n">
+        <x:v>7759.03</x:v>
+      </x:c>
+      <x:c r="H220" s="23" t="n">
+        <x:v>-7.3</x:v>
+      </x:c>
+      <x:c r="I220" s="24" t="n">
+        <x:v>-0.0009399549079166514</x:v>
+      </x:c>
+      <x:c r="J220" s="23" t="n">
+        <x:f>ROUND(E220-F220,1)</x:f>
+        <x:v>117.9</x:v>
+      </x:c>
+      <x:c r="K220" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B221" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B221" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C221" s="30"/>
       <x:c r="D221" s="30"/>
       <x:c r="E221" s="30"/>
@@ -27061,11 +27115,29 @@
       <x:c r="G221" s="30"/>
       <x:c r="H221" s="30"/>
       <x:c r="I221" s="30"/>
-      <x:c r="J221" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
-        <x:v>130.3</x:v>
+      <x:c r="J221" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J220),1)</x:f>
+        <x:v>2072.7</x:v>
       </x:c>
       <x:c r="K221" s="30"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B222" s="30"/>
+      <x:c r="C222" s="30"/>
+      <x:c r="D222" s="30"/>
+      <x:c r="E222" s="30"/>
+      <x:c r="F222" s="30"/>
+      <x:c r="G222" s="30"/>
+      <x:c r="H222" s="30"/>
+      <x:c r="I222" s="30"/>
+      <x:c r="J222" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
+        <x:v>129.5</x:v>
+      </x:c>
+      <x:c r="K222" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -34161,30 +34233,48 @@
       </x:c>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B220" s="30" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C220" s="30"/>
-      <x:c r="D220" s="30"/>
-      <x:c r="E220" s="30"/>
-      <x:c r="F220" s="30"/>
-      <x:c r="G220" s="30"/>
-      <x:c r="H220" s="30"/>
-      <x:c r="I220" s="30"/>
-      <x:c r="J220" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J219),1)</x:f>
-        <x:v>1787.1</x:v>
-      </x:c>
-      <x:c r="K220" s="30"/>
+      <x:c r="A220" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B220" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C220" s="22" t="str">
+        <x:v>9月22日</x:v>
+      </x:c>
+      <x:c r="D220" s="23" t="n">
+        <x:v>7911.64</x:v>
+      </x:c>
+      <x:c r="E220" s="23" t="n">
+        <x:v>7922.62</x:v>
+      </x:c>
+      <x:c r="F220" s="23" t="n">
+        <x:v>7808.98</x:v>
+      </x:c>
+      <x:c r="G220" s="23" t="n">
+        <x:v>7828.94</x:v>
+      </x:c>
+      <x:c r="H220" s="23" t="n">
+        <x:v>-21.5</x:v>
+      </x:c>
+      <x:c r="I220" s="24" t="n">
+        <x:v>-0.002743781271973167</x:v>
+      </x:c>
+      <x:c r="J220" s="23" t="n">
+        <x:f>ROUND(E220-F220,1)</x:f>
+        <x:v>113.6</x:v>
+      </x:c>
+      <x:c r="K220" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B221" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B221" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C221" s="30"/>
       <x:c r="D221" s="30"/>
       <x:c r="E221" s="30"/>
@@ -34192,11 +34282,29 @@
       <x:c r="G221" s="30"/>
       <x:c r="H221" s="30"/>
       <x:c r="I221" s="30"/>
-      <x:c r="J221" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
-        <x:v>119.1</x:v>
+      <x:c r="J221" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J220),1)</x:f>
+        <x:v>1900.7</x:v>
       </x:c>
       <x:c r="K221" s="30"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B222" s="30"/>
+      <x:c r="C222" s="30"/>
+      <x:c r="D222" s="30"/>
+      <x:c r="E222" s="30"/>
+      <x:c r="F222" s="30"/>
+      <x:c r="G222" s="30"/>
+      <x:c r="H222" s="30"/>
+      <x:c r="I222" s="30"/>
+      <x:c r="J222" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
+        <x:v>118.8</x:v>
+      </x:c>
+      <x:c r="K222" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -41292,30 +41400,48 @@
       </x:c>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B220" s="30" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C220" s="30"/>
-      <x:c r="D220" s="30"/>
-      <x:c r="E220" s="30"/>
-      <x:c r="F220" s="30"/>
-      <x:c r="G220" s="30"/>
-      <x:c r="H220" s="30"/>
-      <x:c r="I220" s="30"/>
-      <x:c r="J220" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J219),1)</x:f>
-        <x:v>529.3</x:v>
-      </x:c>
-      <x:c r="K220" s="30"/>
+      <x:c r="A220" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B220" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C220" s="22" t="str">
+        <x:v>9月22日</x:v>
+      </x:c>
+      <x:c r="D220" s="23" t="n">
+        <x:v>3963.81</x:v>
+      </x:c>
+      <x:c r="E220" s="23" t="n">
+        <x:v>3967.68</x:v>
+      </x:c>
+      <x:c r="F220" s="23" t="n">
+        <x:v>3945.42</x:v>
+      </x:c>
+      <x:c r="G220" s="23" t="n">
+        <x:v>3952.13</x:v>
+      </x:c>
+      <x:c r="H220" s="23" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="I220" s="24" t="n">
+        <x:v>0.0005620381223876425</x:v>
+      </x:c>
+      <x:c r="J220" s="23" t="n">
+        <x:f>ROUND(E220-F220,1)</x:f>
+        <x:v>22.3</x:v>
+      </x:c>
+      <x:c r="K220" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B221" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B221" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C221" s="30"/>
       <x:c r="D221" s="30"/>
       <x:c r="E221" s="30"/>
@@ -41323,11 +41449,29 @@
       <x:c r="G221" s="30"/>
       <x:c r="H221" s="30"/>
       <x:c r="I221" s="30"/>
-      <x:c r="J221" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
-        <x:v>35.3</x:v>
+      <x:c r="J221" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J220),1)</x:f>
+        <x:v>551.6</x:v>
       </x:c>
       <x:c r="K221" s="30"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B222" s="30"/>
+      <x:c r="C222" s="30"/>
+      <x:c r="D222" s="30"/>
+      <x:c r="E222" s="30"/>
+      <x:c r="F222" s="30"/>
+      <x:c r="G222" s="30"/>
+      <x:c r="H222" s="30"/>
+      <x:c r="I222" s="30"/>
+      <x:c r="J222" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
+        <x:v>34.5</x:v>
+      </x:c>
+      <x:c r="K222" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -48423,30 +48567,48 @@
       </x:c>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B220" s="30" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C220" s="30"/>
-      <x:c r="D220" s="30"/>
-      <x:c r="E220" s="30"/>
-      <x:c r="F220" s="30"/>
-      <x:c r="G220" s="30"/>
-      <x:c r="H220" s="30"/>
-      <x:c r="I220" s="30"/>
-      <x:c r="J220" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J219),1)</x:f>
-        <x:v>2192.2</x:v>
-      </x:c>
-      <x:c r="K220" s="30"/>
+      <x:c r="A220" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B220" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C220" s="22" t="str">
+        <x:v>9月22日</x:v>
+      </x:c>
+      <x:c r="D220" s="23" t="n">
+        <x:v>7638.2</x:v>
+      </x:c>
+      <x:c r="E220" s="23" t="n">
+        <x:v>7687</x:v>
+      </x:c>
+      <x:c r="F220" s="23" t="n">
+        <x:v>7563</x:v>
+      </x:c>
+      <x:c r="G220" s="23" t="n">
+        <x:v>7580.2</x:v>
+      </x:c>
+      <x:c r="H220" s="23" t="n">
+        <x:v>19.6</x:v>
+      </x:c>
+      <x:c r="I220" s="24" t="n">
+        <x:v>0.002592386847604544</x:v>
+      </x:c>
+      <x:c r="J220" s="23" t="n">
+        <x:f>ROUND(E220-F220,1)</x:f>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="K220" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B221" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B221" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C221" s="30"/>
       <x:c r="D221" s="30"/>
       <x:c r="E221" s="30"/>
@@ -48454,11 +48616,29 @@
       <x:c r="G221" s="30"/>
       <x:c r="H221" s="30"/>
       <x:c r="I221" s="30"/>
-      <x:c r="J221" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
-        <x:v>146.1</x:v>
+      <x:c r="J221" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J220),1)</x:f>
+        <x:v>2316.2</x:v>
       </x:c>
       <x:c r="K221" s="30"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B222" s="30"/>
+      <x:c r="C222" s="30"/>
+      <x:c r="D222" s="30"/>
+      <x:c r="E222" s="30"/>
+      <x:c r="F222" s="30"/>
+      <x:c r="G222" s="30"/>
+      <x:c r="H222" s="30"/>
+      <x:c r="I222" s="30"/>
+      <x:c r="J222" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
+        <x:v>144.8</x:v>
+      </x:c>
+      <x:c r="K222" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3edacfb2804444db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rad9da5e5539c49f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R7146c1a914a844dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc07e0eb2baaf4601"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R7cc0a2864fb24a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rdd3ce0beb3ed4bf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R13ec6751da9c43e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R7f4c521287054d4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R955dde0a0afd4d55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R3e4353291b7a4942"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf6ab8d27320f4620"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R632d5548a8c2422c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R3983e92d27f54c88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R75e1d8bb4eea481b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R68b14aa4abd941ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rebfe64111af44747"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R29e4ed1d8ab344d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R50817b554a0a4aaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Ra1530552387c4cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R2908ba7579b743fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7728</x:v>
+        <x:v>7780</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7640</x:v>
+        <x:v>7657.4</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>88</x:v>
+        <x:v>122.6</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>33854.2</x:v>
+        <x:v>33976.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>193.5</x:v>
+        <x:v>193.1</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4474.6</x:v>
+        <x:v>4520</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4434.8</x:v>
+        <x:v>4477.6</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>39.8</x:v>
+        <x:v>42.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12663.4</x:v>
+        <x:v>12705.8</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.4</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-21</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2849.8</x:v>
+        <x:v>2881.2</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2822</x:v>
+        <x:v>2859.8</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>27.8</x:v>
+        <x:v>21.4</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7036.8</x:v>
+        <x:v>7058.2</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.2</x:v>
+        <x:v>40.1</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -15438,37 +15438,37 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>9月21日</x:v>
+        <x:v>9月21日-9月22日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
         <x:v>7688</x:v>
       </x:c>
       <x:c r="D209" s="23" t="n">
-        <x:v>7728</x:v>
+        <x:v>7780</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
         <x:v>7640</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>7672.6</x:v>
+        <x:v>7671</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>-117.2</x:v>
+        <x:v>-118.8</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>-0.015045315669208414</x:v>
+        <x:v>-0.015250712470153305</x:v>
       </x:c>
       <x:c r="I209" s="23" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>88</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J209" s="22" t="str">
         <x:v>IC2612</x:v>
       </x:c>
       <x:c r="K209" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -15486,7 +15486,7 @@
       <x:c r="H210" s="30"/>
       <x:c r="I210" s="32" t="n">
         <x:f>ROUND(SUM(I173:I209),1)</x:f>
-        <x:v>16281.2</x:v>
+        <x:v>16333.2</x:v>
       </x:c>
       <x:c r="J210" s="30"/>
       <x:c r="K210" s="30"/>
@@ -15504,7 +15504,7 @@
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I173:I209),0),1)</x:f>
-        <x:v>440</x:v>
+        <x:v>441.4</x:v>
       </x:c>
       <x:c r="J211" s="30"/>
       <x:c r="K211" s="30"/>
@@ -16926,37 +16926,37 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>9月21日</x:v>
+        <x:v>9月21日-9月22日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
         <x:v>4451</x:v>
       </x:c>
       <x:c r="D251" s="23" t="n">
-        <x:v>4474.6</x:v>
+        <x:v>4520</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
         <x:v>4434.8</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>4464.8</x:v>
+        <x:v>4480.6</x:v>
       </x:c>
       <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>-43.2</x:v>
+        <x:v>-27.4</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>-0.0095829636202307</x:v>
+        <x:v>-0.006078083407275892</x:v>
       </x:c>
       <x:c r="I251" s="23" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>85.2</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K251" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -16974,7 +16974,7 @@
       <x:c r="H252" s="30"/>
       <x:c r="I252" s="32" t="n">
         <x:f>ROUND(SUM(I215:I251),1)</x:f>
-        <x:v>5753.4</x:v>
+        <x:v>5798.8</x:v>
       </x:c>
       <x:c r="J252" s="30"/>
       <x:c r="K252" s="30"/>
@@ -16992,7 +16992,7 @@
       <x:c r="H253" s="30"/>
       <x:c r="I253" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I215:I251),0),1)</x:f>
-        <x:v>155.5</x:v>
+        <x:v>156.7</x:v>
       </x:c>
       <x:c r="J253" s="30"/>
       <x:c r="K253" s="30"/>
@@ -18414,37 +18414,37 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B293" s="22" t="str">
-        <x:v>9月21日</x:v>
+        <x:v>9月21日-9月22日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
         <x:v>2830</x:v>
       </x:c>
       <x:c r="D293" s="23" t="n">
-        <x:v>2849.8</x:v>
+        <x:v>2881.2</x:v>
       </x:c>
       <x:c r="E293" s="23" t="n">
         <x:v>2822</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>2847.4</x:v>
+        <x:v>2867</x:v>
       </x:c>
       <x:c r="G293" s="23" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>-14.8</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>-0.005170847599748396</x:v>
+        <x:v>0.0016770316539724828</x:v>
       </x:c>
       <x:c r="I293" s="23" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
-        <x:v>27.8</x:v>
+        <x:v>59.2</x:v>
       </x:c>
       <x:c r="J293" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K293" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -18462,7 +18462,7 @@
       <x:c r="H294" s="30"/>
       <x:c r="I294" s="32" t="n">
         <x:f>ROUND(SUM(I257:I293),1)</x:f>
-        <x:v>3287.2</x:v>
+        <x:v>3318.6</x:v>
       </x:c>
       <x:c r="J294" s="30"/>
       <x:c r="K294" s="30"/>
@@ -18480,7 +18480,7 @@
       <x:c r="H295" s="30"/>
       <x:c r="I295" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I257:I293),0),1)</x:f>
-        <x:v>88.8</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="J295" s="30"/>
       <x:c r="K295" s="30"/>
@@ -55734,30 +55734,48 @@
       </x:c>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B220" s="30" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C220" s="30"/>
-      <x:c r="D220" s="30"/>
-      <x:c r="E220" s="30"/>
-      <x:c r="F220" s="30"/>
-      <x:c r="G220" s="30"/>
-      <x:c r="H220" s="30"/>
-      <x:c r="I220" s="30"/>
-      <x:c r="J220" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J219),1)</x:f>
-        <x:v>2110</x:v>
-      </x:c>
-      <x:c r="K220" s="30"/>
+      <x:c r="A220" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B220" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C220" s="22" t="str">
+        <x:v>9月22日</x:v>
+      </x:c>
+      <x:c r="D220" s="23" t="n">
+        <x:v>7756</x:v>
+      </x:c>
+      <x:c r="E220" s="23" t="n">
+        <x:v>7780</x:v>
+      </x:c>
+      <x:c r="F220" s="23" t="n">
+        <x:v>7657.4</x:v>
+      </x:c>
+      <x:c r="G220" s="23" t="n">
+        <x:v>7671</x:v>
+      </x:c>
+      <x:c r="H220" s="23" t="n">
+        <x:v>-1.6</x:v>
+      </x:c>
+      <x:c r="I220" s="24" t="n">
+        <x:v>-0.00020853426478639747</x:v>
+      </x:c>
+      <x:c r="J220" s="23" t="n">
+        <x:f>ROUND(E220-F220,1)</x:f>
+        <x:v>122.6</x:v>
+      </x:c>
+      <x:c r="K220" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B221" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B221" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C221" s="30"/>
       <x:c r="D221" s="30"/>
       <x:c r="E221" s="30"/>
@@ -55765,11 +55783,29 @@
       <x:c r="G221" s="30"/>
       <x:c r="H221" s="30"/>
       <x:c r="I221" s="30"/>
-      <x:c r="J221" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
-        <x:v>140.7</x:v>
+      <x:c r="J221" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J220),1)</x:f>
+        <x:v>2232.6</x:v>
       </x:c>
       <x:c r="K221" s="30"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B222" s="30"/>
+      <x:c r="C222" s="30"/>
+      <x:c r="D222" s="30"/>
+      <x:c r="E222" s="30"/>
+      <x:c r="F222" s="30"/>
+      <x:c r="G222" s="30"/>
+      <x:c r="H222" s="30"/>
+      <x:c r="I222" s="30"/>
+      <x:c r="J222" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
+        <x:v>139.5</x:v>
+      </x:c>
+      <x:c r="K222" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -62865,30 +62901,48 @@
       </x:c>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B220" s="30" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C220" s="30"/>
-      <x:c r="D220" s="30"/>
-      <x:c r="E220" s="30"/>
-      <x:c r="F220" s="30"/>
-      <x:c r="G220" s="30"/>
-      <x:c r="H220" s="30"/>
-      <x:c r="I220" s="30"/>
-      <x:c r="J220" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J219),1)</x:f>
-        <x:v>776.8</x:v>
-      </x:c>
-      <x:c r="K220" s="30"/>
+      <x:c r="A220" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B220" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C220" s="22" t="str">
+        <x:v>9月22日</x:v>
+      </x:c>
+      <x:c r="D220" s="23" t="n">
+        <x:v>4489.8</x:v>
+      </x:c>
+      <x:c r="E220" s="23" t="n">
+        <x:v>4520</x:v>
+      </x:c>
+      <x:c r="F220" s="23" t="n">
+        <x:v>4477.6</x:v>
+      </x:c>
+      <x:c r="G220" s="23" t="n">
+        <x:v>4480.6</x:v>
+      </x:c>
+      <x:c r="H220" s="23" t="n">
+        <x:v>15.8</x:v>
+      </x:c>
+      <x:c r="I220" s="24" t="n">
+        <x:v>0.0035387923311234193</x:v>
+      </x:c>
+      <x:c r="J220" s="23" t="n">
+        <x:f>ROUND(E220-F220,1)</x:f>
+        <x:v>42.4</x:v>
+      </x:c>
+      <x:c r="K220" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B221" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B221" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C221" s="30"/>
       <x:c r="D221" s="30"/>
       <x:c r="E221" s="30"/>
@@ -62896,11 +62950,29 @@
       <x:c r="G221" s="30"/>
       <x:c r="H221" s="30"/>
       <x:c r="I221" s="30"/>
-      <x:c r="J221" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
-        <x:v>51.8</x:v>
+      <x:c r="J221" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J220),1)</x:f>
+        <x:v>819.2</x:v>
       </x:c>
       <x:c r="K221" s="30"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B222" s="30"/>
+      <x:c r="C222" s="30"/>
+      <x:c r="D222" s="30"/>
+      <x:c r="E222" s="30"/>
+      <x:c r="F222" s="30"/>
+      <x:c r="G222" s="30"/>
+      <x:c r="H222" s="30"/>
+      <x:c r="I222" s="30"/>
+      <x:c r="J222" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
+        <x:v>51.2</x:v>
+      </x:c>
+      <x:c r="K222" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -69996,30 +70068,48 @@
       </x:c>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B220" s="30" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C220" s="30"/>
-      <x:c r="D220" s="30"/>
-      <x:c r="E220" s="30"/>
-      <x:c r="F220" s="30"/>
-      <x:c r="G220" s="30"/>
-      <x:c r="H220" s="30"/>
-      <x:c r="I220" s="30"/>
-      <x:c r="J220" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J219),1)</x:f>
-        <x:v>460.2</x:v>
-      </x:c>
-      <x:c r="K220" s="30"/>
+      <x:c r="A220" s="22" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B220" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C220" s="22" t="str">
+        <x:v>9月22日</x:v>
+      </x:c>
+      <x:c r="D220" s="23" t="n">
+        <x:v>2860</x:v>
+      </x:c>
+      <x:c r="E220" s="23" t="n">
+        <x:v>2881.2</x:v>
+      </x:c>
+      <x:c r="F220" s="23" t="n">
+        <x:v>2859.8</x:v>
+      </x:c>
+      <x:c r="G220" s="23" t="n">
+        <x:v>2867</x:v>
+      </x:c>
+      <x:c r="H220" s="23" t="n">
+        <x:v>19.6</x:v>
+      </x:c>
+      <x:c r="I220" s="24" t="n">
+        <x:v>0.006883472641708188</x:v>
+      </x:c>
+      <x:c r="J220" s="23" t="n">
+        <x:f>ROUND(E220-F220,1)</x:f>
+        <x:v>21.4</x:v>
+      </x:c>
+      <x:c r="K220" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B221" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B221" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C221" s="30"/>
       <x:c r="D221" s="30"/>
       <x:c r="E221" s="30"/>
@@ -70027,11 +70117,29 @@
       <x:c r="G221" s="30"/>
       <x:c r="H221" s="30"/>
       <x:c r="I221" s="30"/>
-      <x:c r="J221" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J219),0),1)</x:f>
-        <x:v>30.7</x:v>
+      <x:c r="J221" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J220),1)</x:f>
+        <x:v>481.6</x:v>
       </x:c>
       <x:c r="K221" s="30"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B222" s="30"/>
+      <x:c r="C222" s="30"/>
+      <x:c r="D222" s="30"/>
+      <x:c r="E222" s="30"/>
+      <x:c r="F222" s="30"/>
+      <x:c r="G222" s="30"/>
+      <x:c r="H222" s="30"/>
+      <x:c r="I222" s="30"/>
+      <x:c r="J222" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
+        <x:v>30.1</x:v>
+      </x:c>
+      <x:c r="K222" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf6ab8d27320f4620"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R632d5548a8c2422c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R3983e92d27f54c88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R75e1d8bb4eea481b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R68b14aa4abd941ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rebfe64111af44747"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R29e4ed1d8ab344d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R50817b554a0a4aaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Ra1530552387c4cba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R2908ba7579b743fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rcf69391469924cc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Ra6b5ba1bae914c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R20956acb97574edf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R6cf4983132dd4fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R343cc9a066904385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R8e7162e883fc4f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R82c943d3b66a4af8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R785c5b326c0b43c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R747be48b42334be6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rd183218520ff4cac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7852.23</x:v>
+        <x:v>7769.96</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7734.35</x:v>
+        <x:v>7730.37</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>117.9</x:v>
+        <x:v>39.6</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>30803.5</x:v>
+        <x:v>30843.1</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>175</x:v>
+        <x:v>174.3</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7922.62</x:v>
+        <x:v>7839.94</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7808.98</x:v>
+        <x:v>7781.31</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>113.6</x:v>
+        <x:v>58.6</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>30684.4</x:v>
+        <x:v>30743</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>174.3</x:v>
+        <x:v>173.7</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3967.68</x:v>
+        <x:v>3951.52</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3945.42</x:v>
+        <x:v>3934.46</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>22.3</x:v>
+        <x:v>17.1</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8432.7</x:v>
+        <x:v>8449.8</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>47.9</x:v>
+        <x:v>47.7</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7687</x:v>
+        <x:v>7614.8</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7563</x:v>
+        <x:v>7572.6</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>124</x:v>
+        <x:v>42.2</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>32760</x:v>
+        <x:v>32802.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>186.1</x:v>
+        <x:v>185.3</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4520</x:v>
+        <x:v>4490.4</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4477.6</x:v>
+        <x:v>4457.2</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>42.4</x:v>
+        <x:v>33.2</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12705.8</x:v>
+        <x:v>12739</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.2</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>136560</x:v>
+        <x:v>136000</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>131400</x:v>
+        <x:v>129360</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>5160</x:v>
+        <x:v>6640</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1413520</x:v>
+        <x:v>1420160</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8031.4</x:v>
+        <x:v>8023.5</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -7993,30 +7993,48 @@
       </x:c>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B221" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C221" s="30"/>
-      <x:c r="D221" s="30"/>
-      <x:c r="E221" s="30"/>
-      <x:c r="F221" s="30"/>
-      <x:c r="G221" s="30"/>
-      <x:c r="H221" s="30"/>
-      <x:c r="I221" s="30"/>
-      <x:c r="J221" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J220),1)</x:f>
-        <x:v>95040</x:v>
-      </x:c>
-      <x:c r="K221" s="30"/>
+      <x:c r="A221" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B221" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C221" s="22" t="str">
+        <x:v>9月23日</x:v>
+      </x:c>
+      <x:c r="D221" s="23" t="n">
+        <x:v>136000</x:v>
+      </x:c>
+      <x:c r="E221" s="23" t="n">
+        <x:v>136000</x:v>
+      </x:c>
+      <x:c r="F221" s="23" t="n">
+        <x:v>129360</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
+        <x:v>129840</x:v>
+      </x:c>
+      <x:c r="H221" s="28" t="n">
+        <x:v>-5640</x:v>
+      </x:c>
+      <x:c r="I221" s="24" t="n">
+        <x:v>-0.041629760850310005</x:v>
+      </x:c>
+      <x:c r="J221" s="26" t="n">
+        <x:f>ROUND(E221-F221,1)</x:f>
+        <x:v>6640</x:v>
+      </x:c>
+      <x:c r="K221" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B222" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B222" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C222" s="30"/>
       <x:c r="D222" s="30"/>
       <x:c r="E222" s="30"/>
@@ -8024,11 +8042,29 @@
       <x:c r="G222" s="30"/>
       <x:c r="H222" s="30"/>
       <x:c r="I222" s="30"/>
-      <x:c r="J222" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
-        <x:v>5940</x:v>
+      <x:c r="J222" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J221),1)</x:f>
+        <x:v>101680</x:v>
       </x:c>
       <x:c r="K222" s="30"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B223" s="30"/>
+      <x:c r="C223" s="30"/>
+      <x:c r="D223" s="30"/>
+      <x:c r="E223" s="30"/>
+      <x:c r="F223" s="30"/>
+      <x:c r="G223" s="30"/>
+      <x:c r="H223" s="30"/>
+      <x:c r="I223" s="30"/>
+      <x:c r="J223" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
+        <x:v>5981.2</x:v>
+      </x:c>
+      <x:c r="K223" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9486,7 +9522,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" s="22" t="str">
-        <x:v>9月21日-9月22日</x:v>
+        <x:v>9月21日-9月23日</x:v>
       </x:c>
       <x:c r="C41" s="23" t="n">
         <x:v>7723.68</x:v>
@@ -9498,15 +9534,15 @@
         <x:v>7723.68</x:v>
       </x:c>
       <x:c r="F41" s="23" t="n">
-        <x:v>7759.03</x:v>
+        <x:v>7745.56</x:v>
       </x:c>
       <x:c r="G41" s="23" t="n">
         <x:f>ROUND(F41-F40,1)</x:f>
-        <x:v>71.4</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H41" s="24" t="n">
         <x:f>IFERROR(F41/F40-1,"")</x:f>
-        <x:v>0.009292899335162197</x:v>
+        <x:v>0.007540724726474712</x:v>
       </x:c>
       <x:c r="I41" s="23" t="n">
         <x:f>ROUND(D41-E41,1)</x:f>
@@ -9516,7 +9552,7 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K41" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -10974,7 +11010,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B83" s="22" t="str">
-        <x:v>9月21日-9月22日</x:v>
+        <x:v>9月21日-9月23日</x:v>
       </x:c>
       <x:c r="C83" s="23" t="n">
         <x:v>7829.82</x:v>
@@ -10983,28 +11019,28 @@
         <x:v>7922.62</x:v>
       </x:c>
       <x:c r="E83" s="23" t="n">
-        <x:v>7808.98</x:v>
+        <x:v>7781.31</x:v>
       </x:c>
       <x:c r="F83" s="23" t="n">
-        <x:v>7828.94</x:v>
+        <x:v>7791.82</x:v>
       </x:c>
       <x:c r="G83" s="23" t="n">
         <x:f>ROUND(F83-F82,1)</x:f>
-        <x:v>29.3</x:v>
+        <x:v>-7.8</x:v>
       </x:c>
       <x:c r="H83" s="24" t="n">
         <x:f>IFERROR(F83/F82-1,"")</x:f>
-        <x:v>0.0037604444324779163</x:v>
+        <x:v>-0.000998767887112284</x:v>
       </x:c>
       <x:c r="I83" s="23" t="n">
         <x:f>ROUND(D83-E83,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>141.3</x:v>
       </x:c>
       <x:c r="J83" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K83" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -11022,7 +11058,7 @@
       <x:c r="H84" s="30"/>
       <x:c r="I84" s="32" t="n">
         <x:f>ROUND(SUM(I47:I83),1)</x:f>
-        <x:v>15164.1</x:v>
+        <x:v>15191.8</x:v>
       </x:c>
       <x:c r="J84" s="30"/>
       <x:c r="K84" s="30"/>
@@ -11040,7 +11076,7 @@
       <x:c r="H85" s="30"/>
       <x:c r="I85" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I47:I83),0),1)</x:f>
-        <x:v>409.8</x:v>
+        <x:v>410.6</x:v>
       </x:c>
       <x:c r="J85" s="30"/>
       <x:c r="K85" s="30"/>
@@ -12462,7 +12498,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B125" s="22" t="str">
-        <x:v>9月21日-9月22日</x:v>
+        <x:v>9月21日-9月23日</x:v>
       </x:c>
       <x:c r="C125" s="23" t="n">
         <x:v>3920.27</x:v>
@@ -12474,15 +12510,15 @@
         <x:v>3918.13</x:v>
       </x:c>
       <x:c r="F125" s="23" t="n">
-        <x:v>3952.13</x:v>
+        <x:v>3936.52</x:v>
       </x:c>
       <x:c r="G125" s="23" t="n">
         <x:f>ROUND(F125-F124,1)</x:f>
-        <x:v>40.3</x:v>
+        <x:v>24.7</x:v>
       </x:c>
       <x:c r="H125" s="24" t="n">
         <x:f>IFERROR(F125/F124-1,"")</x:f>
-        <x:v>0.010291753049053387</x:v>
+        <x:v>0.006301334144539483</x:v>
       </x:c>
       <x:c r="I125" s="23" t="n">
         <x:f>ROUND(D125-E125,1)</x:f>
@@ -12492,7 +12528,7 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K125" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -13950,7 +13986,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B167" s="22" t="str">
-        <x:v>9月21日-9月22日</x:v>
+        <x:v>9月21日-9月23日</x:v>
       </x:c>
       <x:c r="C167" s="23" t="n">
         <x:v>7549</x:v>
@@ -13962,15 +13998,15 @@
         <x:v>7527</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>7580.2</x:v>
+        <x:v>7578</x:v>
       </x:c>
       <x:c r="G167" s="23" t="n">
         <x:f>ROUND(F167-F166,1)</x:f>
-        <x:v>-99</x:v>
+        <x:v>-101.2</x:v>
       </x:c>
       <x:c r="H167" s="24" t="n">
         <x:f>IFERROR(F167/F166-1,"")</x:f>
-        <x:v>-0.012891967913324254</x:v>
+        <x:v>-0.013178456089175894</x:v>
       </x:c>
       <x:c r="I167" s="23" t="n">
         <x:f>ROUND(D167-E167,1)</x:f>
@@ -13980,7 +14016,7 @@
         <x:v>IM2612</x:v>
       </x:c>
       <x:c r="K167" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -16926,7 +16962,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>9月21日-9月22日</x:v>
+        <x:v>9月21日-9月23日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
         <x:v>4451</x:v>
@@ -16938,15 +16974,15 @@
         <x:v>4434.8</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>4480.6</x:v>
+        <x:v>4461.8</x:v>
       </x:c>
       <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>-27.4</x:v>
+        <x:v>-46.2</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>-0.006078083407275892</x:v>
+        <x:v>-0.010248447204968869</x:v>
       </x:c>
       <x:c r="I251" s="23" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
@@ -16956,7 +16992,7 @@
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K251" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -19902,7 +19938,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B335" s="22" t="str">
-        <x:v>9月21日-9月22日</x:v>
+        <x:v>9月21日-9月23日</x:v>
       </x:c>
       <x:c r="C335" s="23" t="n">
         <x:v>128500</x:v>
@@ -19914,15 +19950,15 @@
         <x:v>127100</x:v>
       </x:c>
       <x:c r="F335" s="23" t="n">
-        <x:v>135480</x:v>
+        <x:v>129840</x:v>
       </x:c>
       <x:c r="G335" s="28" t="n">
         <x:f>ROUND(F335-F334,1)</x:f>
-        <x:v>6900</x:v>
+        <x:v>1260</x:v>
       </x:c>
       <x:c r="H335" s="24" t="n">
         <x:f>IFERROR(F335/F334-1,"")</x:f>
-        <x:v>0.05366308912739148</x:v>
+        <x:v>0.009799346710219314</x:v>
       </x:c>
       <x:c r="I335" s="26" t="n">
         <x:f>ROUND(D335-E335,1)</x:f>
@@ -19932,7 +19968,7 @@
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K335" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
@@ -27102,30 +27138,48 @@
       </x:c>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B221" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C221" s="30"/>
-      <x:c r="D221" s="30"/>
-      <x:c r="E221" s="30"/>
-      <x:c r="F221" s="30"/>
-      <x:c r="G221" s="30"/>
-      <x:c r="H221" s="30"/>
-      <x:c r="I221" s="30"/>
-      <x:c r="J221" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J220),1)</x:f>
-        <x:v>2072.7</x:v>
-      </x:c>
-      <x:c r="K221" s="30"/>
+      <x:c r="A221" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B221" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C221" s="22" t="str">
+        <x:v>9月23日</x:v>
+      </x:c>
+      <x:c r="D221" s="23" t="n">
+        <x:v>7762.68</x:v>
+      </x:c>
+      <x:c r="E221" s="23" t="n">
+        <x:v>7769.96</x:v>
+      </x:c>
+      <x:c r="F221" s="23" t="n">
+        <x:v>7730.37</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
+        <x:v>7745.56</x:v>
+      </x:c>
+      <x:c r="H221" s="23" t="n">
+        <x:v>-13.5</x:v>
+      </x:c>
+      <x:c r="I221" s="24" t="n">
+        <x:v>-0.0017360417474864276</x:v>
+      </x:c>
+      <x:c r="J221" s="23" t="n">
+        <x:f>ROUND(E221-F221,1)</x:f>
+        <x:v>39.6</x:v>
+      </x:c>
+      <x:c r="K221" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B222" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B222" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C222" s="30"/>
       <x:c r="D222" s="30"/>
       <x:c r="E222" s="30"/>
@@ -27133,11 +27187,29 @@
       <x:c r="G222" s="30"/>
       <x:c r="H222" s="30"/>
       <x:c r="I222" s="30"/>
-      <x:c r="J222" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
-        <x:v>129.5</x:v>
+      <x:c r="J222" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J221),1)</x:f>
+        <x:v>2112.3</x:v>
       </x:c>
       <x:c r="K222" s="30"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B223" s="30"/>
+      <x:c r="C223" s="30"/>
+      <x:c r="D223" s="30"/>
+      <x:c r="E223" s="30"/>
+      <x:c r="F223" s="30"/>
+      <x:c r="G223" s="30"/>
+      <x:c r="H223" s="30"/>
+      <x:c r="I223" s="30"/>
+      <x:c r="J223" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
+        <x:v>124.3</x:v>
+      </x:c>
+      <x:c r="K223" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -34269,30 +34341,48 @@
       </x:c>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B221" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C221" s="30"/>
-      <x:c r="D221" s="30"/>
-      <x:c r="E221" s="30"/>
-      <x:c r="F221" s="30"/>
-      <x:c r="G221" s="30"/>
-      <x:c r="H221" s="30"/>
-      <x:c r="I221" s="30"/>
-      <x:c r="J221" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J220),1)</x:f>
-        <x:v>1900.7</x:v>
-      </x:c>
-      <x:c r="K221" s="30"/>
+      <x:c r="A221" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B221" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C221" s="22" t="str">
+        <x:v>9月23日</x:v>
+      </x:c>
+      <x:c r="D221" s="23" t="n">
+        <x:v>7839.94</x:v>
+      </x:c>
+      <x:c r="E221" s="23" t="n">
+        <x:v>7839.94</x:v>
+      </x:c>
+      <x:c r="F221" s="23" t="n">
+        <x:v>7781.31</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
+        <x:v>7791.82</x:v>
+      </x:c>
+      <x:c r="H221" s="23" t="n">
+        <x:v>-37.1</x:v>
+      </x:c>
+      <x:c r="I221" s="24" t="n">
+        <x:v>-0.004741382613738243</x:v>
+      </x:c>
+      <x:c r="J221" s="23" t="n">
+        <x:f>ROUND(E221-F221,1)</x:f>
+        <x:v>58.6</x:v>
+      </x:c>
+      <x:c r="K221" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B222" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B222" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C222" s="30"/>
       <x:c r="D222" s="30"/>
       <x:c r="E222" s="30"/>
@@ -34300,11 +34390,29 @@
       <x:c r="G222" s="30"/>
       <x:c r="H222" s="30"/>
       <x:c r="I222" s="30"/>
-      <x:c r="J222" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
-        <x:v>118.8</x:v>
+      <x:c r="J222" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J221),1)</x:f>
+        <x:v>1959.3</x:v>
       </x:c>
       <x:c r="K222" s="30"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B223" s="30"/>
+      <x:c r="C223" s="30"/>
+      <x:c r="D223" s="30"/>
+      <x:c r="E223" s="30"/>
+      <x:c r="F223" s="30"/>
+      <x:c r="G223" s="30"/>
+      <x:c r="H223" s="30"/>
+      <x:c r="I223" s="30"/>
+      <x:c r="J223" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
+        <x:v>115.3</x:v>
+      </x:c>
+      <x:c r="K223" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -41436,30 +41544,48 @@
       </x:c>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B221" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C221" s="30"/>
-      <x:c r="D221" s="30"/>
-      <x:c r="E221" s="30"/>
-      <x:c r="F221" s="30"/>
-      <x:c r="G221" s="30"/>
-      <x:c r="H221" s="30"/>
-      <x:c r="I221" s="30"/>
-      <x:c r="J221" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J220),1)</x:f>
-        <x:v>551.6</x:v>
-      </x:c>
-      <x:c r="K221" s="30"/>
+      <x:c r="A221" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B221" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C221" s="22" t="str">
+        <x:v>9月23日</x:v>
+      </x:c>
+      <x:c r="D221" s="23" t="n">
+        <x:v>3951.37</x:v>
+      </x:c>
+      <x:c r="E221" s="23" t="n">
+        <x:v>3951.52</x:v>
+      </x:c>
+      <x:c r="F221" s="23" t="n">
+        <x:v>3934.46</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
+        <x:v>3936.52</x:v>
+      </x:c>
+      <x:c r="H221" s="23" t="n">
+        <x:v>-15.6</x:v>
+      </x:c>
+      <x:c r="I221" s="24" t="n">
+        <x:v>-0.003949768858817926</x:v>
+      </x:c>
+      <x:c r="J221" s="23" t="n">
+        <x:f>ROUND(E221-F221,1)</x:f>
+        <x:v>17.1</x:v>
+      </x:c>
+      <x:c r="K221" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B222" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B222" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C222" s="30"/>
       <x:c r="D222" s="30"/>
       <x:c r="E222" s="30"/>
@@ -41467,11 +41593,29 @@
       <x:c r="G222" s="30"/>
       <x:c r="H222" s="30"/>
       <x:c r="I222" s="30"/>
-      <x:c r="J222" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
-        <x:v>34.5</x:v>
+      <x:c r="J222" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J221),1)</x:f>
+        <x:v>568.7</x:v>
       </x:c>
       <x:c r="K222" s="30"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B223" s="30"/>
+      <x:c r="C223" s="30"/>
+      <x:c r="D223" s="30"/>
+      <x:c r="E223" s="30"/>
+      <x:c r="F223" s="30"/>
+      <x:c r="G223" s="30"/>
+      <x:c r="H223" s="30"/>
+      <x:c r="I223" s="30"/>
+      <x:c r="J223" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
+        <x:v>33.5</x:v>
+      </x:c>
+      <x:c r="K223" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -48603,30 +48747,48 @@
       </x:c>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B221" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C221" s="30"/>
-      <x:c r="D221" s="30"/>
-      <x:c r="E221" s="30"/>
-      <x:c r="F221" s="30"/>
-      <x:c r="G221" s="30"/>
-      <x:c r="H221" s="30"/>
-      <x:c r="I221" s="30"/>
-      <x:c r="J221" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J220),1)</x:f>
-        <x:v>2316.2</x:v>
-      </x:c>
-      <x:c r="K221" s="30"/>
+      <x:c r="A221" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B221" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C221" s="22" t="str">
+        <x:v>9月23日</x:v>
+      </x:c>
+      <x:c r="D221" s="23" t="n">
+        <x:v>7600</x:v>
+      </x:c>
+      <x:c r="E221" s="23" t="n">
+        <x:v>7614.8</x:v>
+      </x:c>
+      <x:c r="F221" s="23" t="n">
+        <x:v>7572.6</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
+        <x:v>7578</x:v>
+      </x:c>
+      <x:c r="H221" s="23" t="n">
+        <x:v>-2.2</x:v>
+      </x:c>
+      <x:c r="I221" s="24" t="n">
+        <x:v>-0.0002902298092398725</x:v>
+      </x:c>
+      <x:c r="J221" s="23" t="n">
+        <x:f>ROUND(E221-F221,1)</x:f>
+        <x:v>42.2</x:v>
+      </x:c>
+      <x:c r="K221" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B222" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B222" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C222" s="30"/>
       <x:c r="D222" s="30"/>
       <x:c r="E222" s="30"/>
@@ -48634,11 +48796,29 @@
       <x:c r="G222" s="30"/>
       <x:c r="H222" s="30"/>
       <x:c r="I222" s="30"/>
-      <x:c r="J222" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
-        <x:v>144.8</x:v>
+      <x:c r="J222" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J221),1)</x:f>
+        <x:v>2358.4</x:v>
       </x:c>
       <x:c r="K222" s="30"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B223" s="30"/>
+      <x:c r="C223" s="30"/>
+      <x:c r="D223" s="30"/>
+      <x:c r="E223" s="30"/>
+      <x:c r="F223" s="30"/>
+      <x:c r="G223" s="30"/>
+      <x:c r="H223" s="30"/>
+      <x:c r="I223" s="30"/>
+      <x:c r="J223" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
+        <x:v>138.7</x:v>
+      </x:c>
+      <x:c r="K223" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -62937,30 +63117,48 @@
       </x:c>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B221" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C221" s="30"/>
-      <x:c r="D221" s="30"/>
-      <x:c r="E221" s="30"/>
-      <x:c r="F221" s="30"/>
-      <x:c r="G221" s="30"/>
-      <x:c r="H221" s="30"/>
-      <x:c r="I221" s="30"/>
-      <x:c r="J221" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J220),1)</x:f>
-        <x:v>819.2</x:v>
-      </x:c>
-      <x:c r="K221" s="30"/>
+      <x:c r="A221" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B221" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C221" s="22" t="str">
+        <x:v>9月23日</x:v>
+      </x:c>
+      <x:c r="D221" s="23" t="n">
+        <x:v>4485</x:v>
+      </x:c>
+      <x:c r="E221" s="23" t="n">
+        <x:v>4490.4</x:v>
+      </x:c>
+      <x:c r="F221" s="23" t="n">
+        <x:v>4457.2</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
+        <x:v>4461.8</x:v>
+      </x:c>
+      <x:c r="H221" s="23" t="n">
+        <x:v>-18.8</x:v>
+      </x:c>
+      <x:c r="I221" s="24" t="n">
+        <x:v>-0.004195866625005595</x:v>
+      </x:c>
+      <x:c r="J221" s="23" t="n">
+        <x:f>ROUND(E221-F221,1)</x:f>
+        <x:v>33.2</x:v>
+      </x:c>
+      <x:c r="K221" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B222" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B222" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C222" s="30"/>
       <x:c r="D222" s="30"/>
       <x:c r="E222" s="30"/>
@@ -62968,11 +63166,29 @@
       <x:c r="G222" s="30"/>
       <x:c r="H222" s="30"/>
       <x:c r="I222" s="30"/>
-      <x:c r="J222" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
-        <x:v>51.2</x:v>
+      <x:c r="J222" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J221),1)</x:f>
+        <x:v>852.4</x:v>
       </x:c>
       <x:c r="K222" s="30"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B223" s="30"/>
+      <x:c r="C223" s="30"/>
+      <x:c r="D223" s="30"/>
+      <x:c r="E223" s="30"/>
+      <x:c r="F223" s="30"/>
+      <x:c r="G223" s="30"/>
+      <x:c r="H223" s="30"/>
+      <x:c r="I223" s="30"/>
+      <x:c r="J223" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
+        <x:v>50.1</x:v>
+      </x:c>
+      <x:c r="K223" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rcf69391469924cc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Ra6b5ba1bae914c62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R20956acb97574edf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R6cf4983132dd4fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R343cc9a066904385"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R8e7162e883fc4f87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R82c943d3b66a4af8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R785c5b326c0b43c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R747be48b42334be6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rd183218520ff4cac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rbc6a7eb9da8248e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R966a076741134ae7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R20f7b93ddd48420f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc28f3477ac0846ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R65641ca32d7f40f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R84592e0b92dc42da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R5ff2e48beab54549"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R72c15f8305764a66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re0852e82a1ba483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R2fb326863c0e462d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7780</x:v>
+        <x:v>7705.6</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7657.4</x:v>
+        <x:v>7638</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>122.6</x:v>
+        <x:v>67.6</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>33976.8</x:v>
+        <x:v>34044.4</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>193.1</x:v>
+        <x:v>192.3</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>2026-09-23</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2881.2</x:v>
+        <x:v>2875.6</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2859.8</x:v>
+        <x:v>2855.2</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>21.4</x:v>
+        <x:v>20.4</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7058.2</x:v>
+        <x:v>7078.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.1</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -15474,7 +15474,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>9月21日-9月22日</x:v>
+        <x:v>9月21日-9月23日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
         <x:v>7688</x:v>
@@ -15483,28 +15483,28 @@
         <x:v>7780</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
-        <x:v>7640</x:v>
+        <x:v>7638</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>7671</x:v>
+        <x:v>7650.4</x:v>
       </x:c>
       <x:c r="G209" s="23" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>-118.8</x:v>
+        <x:v>-139.4</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>-0.015250712470153305</x:v>
+        <x:v>-0.01789519628231795</x:v>
       </x:c>
       <x:c r="I209" s="23" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="J209" s="22" t="str">
         <x:v>IC2612</x:v>
       </x:c>
       <x:c r="K209" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -15522,7 +15522,7 @@
       <x:c r="H210" s="30"/>
       <x:c r="I210" s="32" t="n">
         <x:f>ROUND(SUM(I173:I209),1)</x:f>
-        <x:v>16333.2</x:v>
+        <x:v>16335.2</x:v>
       </x:c>
       <x:c r="J210" s="30"/>
       <x:c r="K210" s="30"/>
@@ -15540,7 +15540,7 @@
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I173:I209),0),1)</x:f>
-        <x:v>441.4</x:v>
+        <x:v>441.5</x:v>
       </x:c>
       <x:c r="J211" s="30"/>
       <x:c r="K211" s="30"/>
@@ -18450,7 +18450,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B293" s="22" t="str">
-        <x:v>9月21日-9月22日</x:v>
+        <x:v>9月21日-9月23日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
         <x:v>2830</x:v>
@@ -18462,15 +18462,15 @@
         <x:v>2822</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>2867</x:v>
+        <x:v>2859.4</x:v>
       </x:c>
       <x:c r="G293" s="23" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>4.8</x:v>
+        <x:v>-2.8</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>0.0016770316539724828</x:v>
+        <x:v>-0.000978268464817189</x:v>
       </x:c>
       <x:c r="I293" s="23" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
@@ -18480,7 +18480,7 @@
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K293" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -55950,30 +55950,48 @@
       </x:c>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B221" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C221" s="30"/>
-      <x:c r="D221" s="30"/>
-      <x:c r="E221" s="30"/>
-      <x:c r="F221" s="30"/>
-      <x:c r="G221" s="30"/>
-      <x:c r="H221" s="30"/>
-      <x:c r="I221" s="30"/>
-      <x:c r="J221" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J220),1)</x:f>
-        <x:v>2232.6</x:v>
-      </x:c>
-      <x:c r="K221" s="30"/>
+      <x:c r="A221" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B221" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C221" s="22" t="str">
+        <x:v>9月23日</x:v>
+      </x:c>
+      <x:c r="D221" s="23" t="n">
+        <x:v>7699.4</x:v>
+      </x:c>
+      <x:c r="E221" s="23" t="n">
+        <x:v>7705.6</x:v>
+      </x:c>
+      <x:c r="F221" s="23" t="n">
+        <x:v>7638</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
+        <x:v>7650.4</x:v>
+      </x:c>
+      <x:c r="H221" s="23" t="n">
+        <x:v>-20.6</x:v>
+      </x:c>
+      <x:c r="I221" s="24" t="n">
+        <x:v>-0.002685438665102402</x:v>
+      </x:c>
+      <x:c r="J221" s="23" t="n">
+        <x:f>ROUND(E221-F221,1)</x:f>
+        <x:v>67.6</x:v>
+      </x:c>
+      <x:c r="K221" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B222" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B222" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C222" s="30"/>
       <x:c r="D222" s="30"/>
       <x:c r="E222" s="30"/>
@@ -55981,11 +55999,29 @@
       <x:c r="G222" s="30"/>
       <x:c r="H222" s="30"/>
       <x:c r="I222" s="30"/>
-      <x:c r="J222" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
-        <x:v>139.5</x:v>
+      <x:c r="J222" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J221),1)</x:f>
+        <x:v>2300.2</x:v>
       </x:c>
       <x:c r="K222" s="30"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B223" s="30"/>
+      <x:c r="C223" s="30"/>
+      <x:c r="D223" s="30"/>
+      <x:c r="E223" s="30"/>
+      <x:c r="F223" s="30"/>
+      <x:c r="G223" s="30"/>
+      <x:c r="H223" s="30"/>
+      <x:c r="I223" s="30"/>
+      <x:c r="J223" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
+        <x:v>135.3</x:v>
+      </x:c>
+      <x:c r="K223" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -70320,30 +70356,48 @@
       </x:c>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B221" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C221" s="30"/>
-      <x:c r="D221" s="30"/>
-      <x:c r="E221" s="30"/>
-      <x:c r="F221" s="30"/>
-      <x:c r="G221" s="30"/>
-      <x:c r="H221" s="30"/>
-      <x:c r="I221" s="30"/>
-      <x:c r="J221" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J220),1)</x:f>
-        <x:v>481.6</x:v>
-      </x:c>
-      <x:c r="K221" s="30"/>
+      <x:c r="A221" s="22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B221" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C221" s="22" t="str">
+        <x:v>9月23日</x:v>
+      </x:c>
+      <x:c r="D221" s="23" t="n">
+        <x:v>2870.4</x:v>
+      </x:c>
+      <x:c r="E221" s="23" t="n">
+        <x:v>2875.6</x:v>
+      </x:c>
+      <x:c r="F221" s="23" t="n">
+        <x:v>2855.2</x:v>
+      </x:c>
+      <x:c r="G221" s="23" t="n">
+        <x:v>2859.4</x:v>
+      </x:c>
+      <x:c r="H221" s="23" t="n">
+        <x:v>-7.6</x:v>
+      </x:c>
+      <x:c r="I221" s="24" t="n">
+        <x:v>-0.0026508545517962556</x:v>
+      </x:c>
+      <x:c r="J221" s="23" t="n">
+        <x:f>ROUND(E221-F221,1)</x:f>
+        <x:v>20.4</x:v>
+      </x:c>
+      <x:c r="K221" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B222" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B222" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="C222" s="30"/>
       <x:c r="D222" s="30"/>
       <x:c r="E222" s="30"/>
@@ -70351,11 +70405,29 @@
       <x:c r="G222" s="30"/>
       <x:c r="H222" s="30"/>
       <x:c r="I222" s="30"/>
-      <x:c r="J222" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J220),0),1)</x:f>
-        <x:v>30.1</x:v>
+      <x:c r="J222" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J221),1)</x:f>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="K222" s="30"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B223" s="30"/>
+      <x:c r="C223" s="30"/>
+      <x:c r="D223" s="30"/>
+      <x:c r="E223" s="30"/>
+      <x:c r="F223" s="30"/>
+      <x:c r="G223" s="30"/>
+      <x:c r="H223" s="30"/>
+      <x:c r="I223" s="30"/>
+      <x:c r="J223" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
+        <x:v>29.5</x:v>
+      </x:c>
+      <x:c r="K223" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rbc6a7eb9da8248e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R966a076741134ae7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R20f7b93ddd48420f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc28f3477ac0846ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R65641ca32d7f40f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R84592e0b92dc42da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R5ff2e48beab54549"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R72c15f8305764a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re0852e82a1ba483f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R2fb326863c0e462d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rd1e22958a75345b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R1d38483bb9644a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R539c92d1a80844b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R029e2b508be84ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R2d4dced65555455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rba02fad02adc41ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R28a1d7ed92e0407a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rd591f79ae2854c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R2c5f5e9edd224724"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R78b2d1a7391640d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7769.96</x:v>
+        <x:v>7725.52</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7730.37</x:v>
+        <x:v>7569.51</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>39.6</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>30843.1</x:v>
+        <x:v>30999.1</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>174.3</x:v>
+        <x:v>174.2</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7839.94</x:v>
+        <x:v>7774.22</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7781.31</x:v>
+        <x:v>7624.07</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>58.6</x:v>
+        <x:v>150.2</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>30743</x:v>
+        <x:v>30893.2</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>173.7</x:v>
+        <x:v>173.6</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,22 +577,22 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3951.52</x:v>
+        <x:v>3930.5</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3934.46</x:v>
+        <x:v>3888.37</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>17.1</x:v>
+        <x:v>42.1</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8449.8</x:v>
+        <x:v>8491.9</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>47.7</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2875.6</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2855.2</x:v>
+        <x:v>2798</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>20.4</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7078.6</x:v>
+        <x:v>7130.6</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40</x:v>
+        <x:v>40.1</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>136000</x:v>
+        <x:v>131640</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>129360</x:v>
+        <x:v>125000</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
         <x:v>6640</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1420160</x:v>
+        <x:v>1426800</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>8023.5</x:v>
+        <x:v>8015.7</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -8029,30 +8029,48 @@
       </x:c>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B222" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C222" s="30"/>
-      <x:c r="D222" s="30"/>
-      <x:c r="E222" s="30"/>
-      <x:c r="F222" s="30"/>
-      <x:c r="G222" s="30"/>
-      <x:c r="H222" s="30"/>
-      <x:c r="I222" s="30"/>
-      <x:c r="J222" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J221),1)</x:f>
-        <x:v>101680</x:v>
-      </x:c>
-      <x:c r="K222" s="30"/>
+      <x:c r="A222" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B222" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C222" s="22" t="str">
+        <x:v>9月24日</x:v>
+      </x:c>
+      <x:c r="D222" s="23" t="n">
+        <x:v>131640</x:v>
+      </x:c>
+      <x:c r="E222" s="23" t="n">
+        <x:v>131640</x:v>
+      </x:c>
+      <x:c r="F222" s="23" t="n">
+        <x:v>125000</x:v>
+      </x:c>
+      <x:c r="G222" s="23" t="n">
+        <x:v>125980</x:v>
+      </x:c>
+      <x:c r="H222" s="28" t="n">
+        <x:v>-3860</x:v>
+      </x:c>
+      <x:c r="I222" s="24" t="n">
+        <x:v>-0.029728897104128182</x:v>
+      </x:c>
+      <x:c r="J222" s="26" t="n">
+        <x:f>ROUND(E222-F222,1)</x:f>
+        <x:v>6640</x:v>
+      </x:c>
+      <x:c r="K222" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B223" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B223" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="C223" s="30"/>
       <x:c r="D223" s="30"/>
       <x:c r="E223" s="30"/>
@@ -8060,11 +8078,29 @@
       <x:c r="G223" s="30"/>
       <x:c r="H223" s="30"/>
       <x:c r="I223" s="30"/>
-      <x:c r="J223" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
-        <x:v>5981.2</x:v>
+      <x:c r="J223" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J222),1)</x:f>
+        <x:v>108320</x:v>
       </x:c>
       <x:c r="K223" s="30"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B224" s="30"/>
+      <x:c r="C224" s="30"/>
+      <x:c r="D224" s="30"/>
+      <x:c r="E224" s="30"/>
+      <x:c r="F224" s="30"/>
+      <x:c r="G224" s="30"/>
+      <x:c r="H224" s="30"/>
+      <x:c r="I224" s="30"/>
+      <x:c r="J224" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
+        <x:v>6017.8</x:v>
+      </x:c>
+      <x:c r="K224" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9522,7 +9558,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" s="22" t="str">
-        <x:v>9月21日-9月23日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C41" s="23" t="n">
         <x:v>7723.68</x:v>
@@ -9531,28 +9567,28 @@
         <x:v>7852.23</x:v>
       </x:c>
       <x:c r="E41" s="23" t="n">
-        <x:v>7723.68</x:v>
+        <x:v>7569.51</x:v>
       </x:c>
       <x:c r="F41" s="23" t="n">
-        <x:v>7745.56</x:v>
+        <x:v>7570.14</x:v>
       </x:c>
       <x:c r="G41" s="23" t="n">
         <x:f>ROUND(F41-F40,1)</x:f>
-        <x:v>58</x:v>
+        <x:v>-117.4</x:v>
       </x:c>
       <x:c r="H41" s="24" t="n">
         <x:f>IFERROR(F41/F40-1,"")</x:f>
-        <x:v>0.007540724726474712</x:v>
-      </x:c>
-      <x:c r="I41" s="23" t="n">
+        <x:v>-0.015277869917620479</x:v>
+      </x:c>
+      <x:c r="I41" s="26" t="n">
         <x:f>ROUND(D41-E41,1)</x:f>
-        <x:v>128.5</x:v>
+        <x:v>282.7</x:v>
       </x:c>
       <x:c r="J41" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K41" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -9570,7 +9606,7 @@
       <x:c r="H42" s="30"/>
       <x:c r="I42" s="32" t="n">
         <x:f>ROUND(SUM(I5:I41),1)</x:f>
-        <x:v>15202.4</x:v>
+        <x:v>15356.6</x:v>
       </x:c>
       <x:c r="J42" s="30"/>
       <x:c r="K42" s="30"/>
@@ -9588,7 +9624,7 @@
       <x:c r="H43" s="30"/>
       <x:c r="I43" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I41),0),1)</x:f>
-        <x:v>410.9</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="J43" s="30"/>
       <x:c r="K43" s="30"/>
@@ -11010,7 +11046,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B83" s="22" t="str">
-        <x:v>9月21日-9月23日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C83" s="23" t="n">
         <x:v>7829.82</x:v>
@@ -11019,28 +11055,28 @@
         <x:v>7922.62</x:v>
       </x:c>
       <x:c r="E83" s="23" t="n">
-        <x:v>7781.31</x:v>
+        <x:v>7624.07</x:v>
       </x:c>
       <x:c r="F83" s="23" t="n">
-        <x:v>7791.82</x:v>
-      </x:c>
-      <x:c r="G83" s="23" t="n">
+        <x:v>7624.07</x:v>
+      </x:c>
+      <x:c r="G83" s="28" t="n">
         <x:f>ROUND(F83-F82,1)</x:f>
-        <x:v>-7.8</x:v>
+        <x:v>-175.5</x:v>
       </x:c>
       <x:c r="H83" s="24" t="n">
         <x:f>IFERROR(F83/F82-1,"")</x:f>
-        <x:v>-0.000998767887112284</x:v>
-      </x:c>
-      <x:c r="I83" s="23" t="n">
+        <x:v>-0.02250625351780411</x:v>
+      </x:c>
+      <x:c r="I83" s="26" t="n">
         <x:f>ROUND(D83-E83,1)</x:f>
-        <x:v>141.3</x:v>
+        <x:v>298.6</x:v>
       </x:c>
       <x:c r="J83" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K83" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -11058,7 +11094,7 @@
       <x:c r="H84" s="30"/>
       <x:c r="I84" s="32" t="n">
         <x:f>ROUND(SUM(I47:I83),1)</x:f>
-        <x:v>15191.8</x:v>
+        <x:v>15349.1</x:v>
       </x:c>
       <x:c r="J84" s="30"/>
       <x:c r="K84" s="30"/>
@@ -11076,7 +11112,7 @@
       <x:c r="H85" s="30"/>
       <x:c r="I85" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I47:I83),0),1)</x:f>
-        <x:v>410.6</x:v>
+        <x:v>414.8</x:v>
       </x:c>
       <x:c r="J85" s="30"/>
       <x:c r="K85" s="30"/>
@@ -12498,7 +12534,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B125" s="22" t="str">
-        <x:v>9月21日-9月23日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C125" s="23" t="n">
         <x:v>3920.27</x:v>
@@ -12507,28 +12543,28 @@
         <x:v>3967.68</x:v>
       </x:c>
       <x:c r="E125" s="23" t="n">
-        <x:v>3918.13</x:v>
+        <x:v>3888.37</x:v>
       </x:c>
       <x:c r="F125" s="23" t="n">
-        <x:v>3936.52</x:v>
+        <x:v>3888.37</x:v>
       </x:c>
       <x:c r="G125" s="23" t="n">
         <x:f>ROUND(F125-F124,1)</x:f>
-        <x:v>24.7</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="H125" s="24" t="n">
         <x:f>IFERROR(F125/F124-1,"")</x:f>
-        <x:v>0.006301334144539483</x:v>
-      </x:c>
-      <x:c r="I125" s="23" t="n">
+        <x:v>-0.00600735709519995</x:v>
+      </x:c>
+      <x:c r="I125" s="26" t="n">
         <x:f>ROUND(D125-E125,1)</x:f>
-        <x:v>49.5</x:v>
+        <x:v>79.3</x:v>
       </x:c>
       <x:c r="J125" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K125" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -12546,7 +12582,7 @@
       <x:c r="H126" s="30"/>
       <x:c r="I126" s="32" t="n">
         <x:f>ROUND(SUM(I89:I125),1)</x:f>
-        <x:v>3990.6</x:v>
+        <x:v>4020.4</x:v>
       </x:c>
       <x:c r="J126" s="30"/>
       <x:c r="K126" s="30"/>
@@ -12564,7 +12600,7 @@
       <x:c r="H127" s="30"/>
       <x:c r="I127" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I89:I125),0),1)</x:f>
-        <x:v>107.9</x:v>
+        <x:v>108.7</x:v>
       </x:c>
       <x:c r="J127" s="30"/>
       <x:c r="K127" s="30"/>
@@ -18450,7 +18486,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B293" s="22" t="str">
-        <x:v>9月21日-9月23日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
         <x:v>2830</x:v>
@@ -18459,28 +18495,28 @@
         <x:v>2881.2</x:v>
       </x:c>
       <x:c r="E293" s="23" t="n">
-        <x:v>2822</x:v>
+        <x:v>2798</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>2859.4</x:v>
+        <x:v>2804.6</x:v>
       </x:c>
       <x:c r="G293" s="23" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>-2.8</x:v>
+        <x:v>-57.6</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>-0.000978268464817189</x:v>
-      </x:c>
-      <x:c r="I293" s="23" t="n">
+        <x:v>-0.02012437984766957</x:v>
+      </x:c>
+      <x:c r="I293" s="26" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
-        <x:v>59.2</x:v>
+        <x:v>83.2</x:v>
       </x:c>
       <x:c r="J293" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K293" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -18498,7 +18534,7 @@
       <x:c r="H294" s="30"/>
       <x:c r="I294" s="32" t="n">
         <x:f>ROUND(SUM(I257:I293),1)</x:f>
-        <x:v>3318.6</x:v>
+        <x:v>3342.6</x:v>
       </x:c>
       <x:c r="J294" s="30"/>
       <x:c r="K294" s="30"/>
@@ -18516,7 +18552,7 @@
       <x:c r="H295" s="30"/>
       <x:c r="I295" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I257:I293),0),1)</x:f>
-        <x:v>89.7</x:v>
+        <x:v>90.3</x:v>
       </x:c>
       <x:c r="J295" s="30"/>
       <x:c r="K295" s="30"/>
@@ -19938,7 +19974,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B335" s="22" t="str">
-        <x:v>9月21日-9月23日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C335" s="23" t="n">
         <x:v>128500</x:v>
@@ -19947,28 +19983,28 @@
         <x:v>136560</x:v>
       </x:c>
       <x:c r="E335" s="23" t="n">
-        <x:v>127100</x:v>
+        <x:v>125000</x:v>
       </x:c>
       <x:c r="F335" s="23" t="n">
-        <x:v>129840</x:v>
+        <x:v>125980</x:v>
       </x:c>
       <x:c r="G335" s="28" t="n">
         <x:f>ROUND(F335-F334,1)</x:f>
-        <x:v>1260</x:v>
+        <x:v>-2600</x:v>
       </x:c>
       <x:c r="H335" s="24" t="n">
         <x:f>IFERROR(F335/F334-1,"")</x:f>
-        <x:v>0.009799346710219314</x:v>
+        <x:v>-0.02022087416394458</x:v>
       </x:c>
       <x:c r="I335" s="26" t="n">
         <x:f>ROUND(D335-E335,1)</x:f>
-        <x:v>9460</x:v>
+        <x:v>11560</x:v>
       </x:c>
       <x:c r="J335" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K335" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
@@ -19986,7 +20022,7 @@
       <x:c r="H336" s="30"/>
       <x:c r="I336" s="32" t="n">
         <x:f>ROUND(SUM(I299:I335),1)</x:f>
-        <x:v>750860</x:v>
+        <x:v>752960</x:v>
       </x:c>
       <x:c r="J336" s="30"/>
       <x:c r="K336" s="30"/>
@@ -20004,7 +20040,7 @@
       <x:c r="H337" s="30"/>
       <x:c r="I337" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I299:I335),0),1)</x:f>
-        <x:v>20293.5</x:v>
+        <x:v>20350.3</x:v>
       </x:c>
       <x:c r="J337" s="30"/>
       <x:c r="K337" s="30"/>
@@ -27174,30 +27210,48 @@
       </x:c>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B222" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C222" s="30"/>
-      <x:c r="D222" s="30"/>
-      <x:c r="E222" s="30"/>
-      <x:c r="F222" s="30"/>
-      <x:c r="G222" s="30"/>
-      <x:c r="H222" s="30"/>
-      <x:c r="I222" s="30"/>
-      <x:c r="J222" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J221),1)</x:f>
-        <x:v>2112.3</x:v>
-      </x:c>
-      <x:c r="K222" s="30"/>
+      <x:c r="A222" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B222" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C222" s="22" t="str">
+        <x:v>9月24日</x:v>
+      </x:c>
+      <x:c r="D222" s="23" t="n">
+        <x:v>7707.87</x:v>
+      </x:c>
+      <x:c r="E222" s="23" t="n">
+        <x:v>7725.52</x:v>
+      </x:c>
+      <x:c r="F222" s="23" t="n">
+        <x:v>7569.51</x:v>
+      </x:c>
+      <x:c r="G222" s="23" t="n">
+        <x:v>7570.14</x:v>
+      </x:c>
+      <x:c r="H222" s="28" t="n">
+        <x:v>-175.4</x:v>
+      </x:c>
+      <x:c r="I222" s="24" t="n">
+        <x:v>-0.022647813715212295</x:v>
+      </x:c>
+      <x:c r="J222" s="23" t="n">
+        <x:f>ROUND(E222-F222,1)</x:f>
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="K222" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B223" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B223" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="C223" s="30"/>
       <x:c r="D223" s="30"/>
       <x:c r="E223" s="30"/>
@@ -27205,11 +27259,29 @@
       <x:c r="G223" s="30"/>
       <x:c r="H223" s="30"/>
       <x:c r="I223" s="30"/>
-      <x:c r="J223" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
-        <x:v>124.3</x:v>
+      <x:c r="J223" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J222),1)</x:f>
+        <x:v>2268.3</x:v>
       </x:c>
       <x:c r="K223" s="30"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B224" s="30"/>
+      <x:c r="C224" s="30"/>
+      <x:c r="D224" s="30"/>
+      <x:c r="E224" s="30"/>
+      <x:c r="F224" s="30"/>
+      <x:c r="G224" s="30"/>
+      <x:c r="H224" s="30"/>
+      <x:c r="I224" s="30"/>
+      <x:c r="J224" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K224" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -34377,30 +34449,48 @@
       </x:c>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B222" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C222" s="30"/>
-      <x:c r="D222" s="30"/>
-      <x:c r="E222" s="30"/>
-      <x:c r="F222" s="30"/>
-      <x:c r="G222" s="30"/>
-      <x:c r="H222" s="30"/>
-      <x:c r="I222" s="30"/>
-      <x:c r="J222" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J221),1)</x:f>
-        <x:v>1959.3</x:v>
-      </x:c>
-      <x:c r="K222" s="30"/>
+      <x:c r="A222" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B222" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C222" s="22" t="str">
+        <x:v>9月24日</x:v>
+      </x:c>
+      <x:c r="D222" s="23" t="n">
+        <x:v>7763.73</x:v>
+      </x:c>
+      <x:c r="E222" s="23" t="n">
+        <x:v>7774.22</x:v>
+      </x:c>
+      <x:c r="F222" s="23" t="n">
+        <x:v>7624.07</x:v>
+      </x:c>
+      <x:c r="G222" s="23" t="n">
+        <x:v>7624.07</x:v>
+      </x:c>
+      <x:c r="H222" s="28" t="n">
+        <x:v>-167.7</x:v>
+      </x:c>
+      <x:c r="I222" s="24" t="n">
+        <x:v>-0.0215289880926407</x:v>
+      </x:c>
+      <x:c r="J222" s="23" t="n">
+        <x:f>ROUND(E222-F222,1)</x:f>
+        <x:v>150.2</x:v>
+      </x:c>
+      <x:c r="K222" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B223" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B223" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="C223" s="30"/>
       <x:c r="D223" s="30"/>
       <x:c r="E223" s="30"/>
@@ -34408,11 +34498,29 @@
       <x:c r="G223" s="30"/>
       <x:c r="H223" s="30"/>
       <x:c r="I223" s="30"/>
-      <x:c r="J223" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
-        <x:v>115.3</x:v>
+      <x:c r="J223" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J222),1)</x:f>
+        <x:v>2109.5</x:v>
       </x:c>
       <x:c r="K223" s="30"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B224" s="30"/>
+      <x:c r="C224" s="30"/>
+      <x:c r="D224" s="30"/>
+      <x:c r="E224" s="30"/>
+      <x:c r="F224" s="30"/>
+      <x:c r="G224" s="30"/>
+      <x:c r="H224" s="30"/>
+      <x:c r="I224" s="30"/>
+      <x:c r="J224" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
+        <x:v>117.2</x:v>
+      </x:c>
+      <x:c r="K224" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -41580,30 +41688,48 @@
       </x:c>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B222" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C222" s="30"/>
-      <x:c r="D222" s="30"/>
-      <x:c r="E222" s="30"/>
-      <x:c r="F222" s="30"/>
-      <x:c r="G222" s="30"/>
-      <x:c r="H222" s="30"/>
-      <x:c r="I222" s="30"/>
-      <x:c r="J222" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J221),1)</x:f>
-        <x:v>568.7</x:v>
-      </x:c>
-      <x:c r="K222" s="30"/>
+      <x:c r="A222" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B222" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C222" s="22" t="str">
+        <x:v>9月24日</x:v>
+      </x:c>
+      <x:c r="D222" s="23" t="n">
+        <x:v>3925.32</x:v>
+      </x:c>
+      <x:c r="E222" s="23" t="n">
+        <x:v>3930.5</x:v>
+      </x:c>
+      <x:c r="F222" s="23" t="n">
+        <x:v>3888.37</x:v>
+      </x:c>
+      <x:c r="G222" s="23" t="n">
+        <x:v>3888.37</x:v>
+      </x:c>
+      <x:c r="H222" s="23" t="n">
+        <x:v>-48.2</x:v>
+      </x:c>
+      <x:c r="I222" s="24" t="n">
+        <x:v>-0.012231615741822743</x:v>
+      </x:c>
+      <x:c r="J222" s="23" t="n">
+        <x:f>ROUND(E222-F222,1)</x:f>
+        <x:v>42.1</x:v>
+      </x:c>
+      <x:c r="K222" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B223" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B223" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="C223" s="30"/>
       <x:c r="D223" s="30"/>
       <x:c r="E223" s="30"/>
@@ -41611,11 +41737,29 @@
       <x:c r="G223" s="30"/>
       <x:c r="H223" s="30"/>
       <x:c r="I223" s="30"/>
-      <x:c r="J223" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
-        <x:v>33.5</x:v>
+      <x:c r="J223" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J222),1)</x:f>
+        <x:v>610.8</x:v>
       </x:c>
       <x:c r="K223" s="30"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B224" s="30"/>
+      <x:c r="C224" s="30"/>
+      <x:c r="D224" s="30"/>
+      <x:c r="E224" s="30"/>
+      <x:c r="F224" s="30"/>
+      <x:c r="G224" s="30"/>
+      <x:c r="H224" s="30"/>
+      <x:c r="I224" s="30"/>
+      <x:c r="J224" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
+        <x:v>33.9</x:v>
+      </x:c>
+      <x:c r="K224" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -70392,30 +70536,48 @@
       </x:c>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B222" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C222" s="30"/>
-      <x:c r="D222" s="30"/>
-      <x:c r="E222" s="30"/>
-      <x:c r="F222" s="30"/>
-      <x:c r="G222" s="30"/>
-      <x:c r="H222" s="30"/>
-      <x:c r="I222" s="30"/>
-      <x:c r="J222" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J221),1)</x:f>
-        <x:v>502</x:v>
-      </x:c>
-      <x:c r="K222" s="30"/>
+      <x:c r="A222" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B222" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C222" s="22" t="str">
+        <x:v>9月24日</x:v>
+      </x:c>
+      <x:c r="D222" s="23" t="n">
+        <x:v>2838</x:v>
+      </x:c>
+      <x:c r="E222" s="23" t="n">
+        <x:v>2850</x:v>
+      </x:c>
+      <x:c r="F222" s="23" t="n">
+        <x:v>2798</x:v>
+      </x:c>
+      <x:c r="G222" s="23" t="n">
+        <x:v>2804.6</x:v>
+      </x:c>
+      <x:c r="H222" s="23" t="n">
+        <x:v>-54.8</x:v>
+      </x:c>
+      <x:c r="I222" s="24" t="n">
+        <x:v>-0.019164859760789077</x:v>
+      </x:c>
+      <x:c r="J222" s="23" t="n">
+        <x:f>ROUND(E222-F222,1)</x:f>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K222" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B223" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B223" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="C223" s="30"/>
       <x:c r="D223" s="30"/>
       <x:c r="E223" s="30"/>
@@ -70423,11 +70585,29 @@
       <x:c r="G223" s="30"/>
       <x:c r="H223" s="30"/>
       <x:c r="I223" s="30"/>
-      <x:c r="J223" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
-        <x:v>29.5</x:v>
+      <x:c r="J223" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J222),1)</x:f>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="K223" s="30"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B224" s="30"/>
+      <x:c r="C224" s="30"/>
+      <x:c r="D224" s="30"/>
+      <x:c r="E224" s="30"/>
+      <x:c r="F224" s="30"/>
+      <x:c r="G224" s="30"/>
+      <x:c r="H224" s="30"/>
+      <x:c r="I224" s="30"/>
+      <x:c r="J224" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
+        <x:v>30.8</x:v>
+      </x:c>
+      <x:c r="K224" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rd1e22958a75345b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R1d38483bb9644a18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R539c92d1a80844b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R029e2b508be84ab7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R2d4dced65555455c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rba02fad02adc41ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R28a1d7ed92e0407a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rd591f79ae2854c36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R2c5f5e9edd224724"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R78b2d1a7391640d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra5966b3d53344960"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rd77337a790314baa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R3a7f8e5e98e0490f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R7ade6489606e45fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb3a9b7c6aa5841cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R6f51de44e70845e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R6c654b8068ac417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rbdc9d020baa9476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R983a5273a9974b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rcb40d4615a71493b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7614.8</x:v>
+        <x:v>7578</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7572.6</x:v>
+        <x:v>7386</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>42.2</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>32802.2</x:v>
+        <x:v>32994.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>185.3</x:v>
+        <x:v>185.4</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,22 +635,22 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7705.6</x:v>
+        <x:v>7639.6</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7638</x:v>
+        <x:v>7450</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>67.6</x:v>
+        <x:v>189.6</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>34044.4</x:v>
+        <x:v>34234</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
         <x:v>192.3</x:v>
@@ -664,22 +664,22 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-23</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4490.4</x:v>
+        <x:v>4443.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4457.2</x:v>
+        <x:v>4367</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>33.2</x:v>
+        <x:v>76.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12739</x:v>
+        <x:v>12815.6</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
         <x:v>72</x:v>
@@ -14022,7 +14022,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B167" s="22" t="str">
-        <x:v>9月21日-9月23日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C167" s="23" t="n">
         <x:v>7549</x:v>
@@ -14031,28 +14031,28 @@
         <x:v>7687</x:v>
       </x:c>
       <x:c r="E167" s="23" t="n">
-        <x:v>7527</x:v>
+        <x:v>7386</x:v>
       </x:c>
       <x:c r="F167" s="23" t="n">
-        <x:v>7578</x:v>
-      </x:c>
-      <x:c r="G167" s="23" t="n">
+        <x:v>7391</x:v>
+      </x:c>
+      <x:c r="G167" s="28" t="n">
         <x:f>ROUND(F167-F166,1)</x:f>
-        <x:v>-101.2</x:v>
+        <x:v>-288.2</x:v>
       </x:c>
       <x:c r="H167" s="24" t="n">
         <x:f>IFERROR(F167/F166-1,"")</x:f>
-        <x:v>-0.013178456089175894</x:v>
-      </x:c>
-      <x:c r="I167" s="23" t="n">
+        <x:v>-0.03752995103656631</x:v>
+      </x:c>
+      <x:c r="I167" s="26" t="n">
         <x:f>ROUND(D167-E167,1)</x:f>
-        <x:v>160</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="J167" s="22" t="str">
         <x:v>IM2612</x:v>
       </x:c>
       <x:c r="K167" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -14070,7 +14070,7 @@
       <x:c r="H168" s="30"/>
       <x:c r="I168" s="32" t="n">
         <x:f>ROUND(SUM(I131:I167),1)</x:f>
-        <x:v>15872.8</x:v>
+        <x:v>16013.8</x:v>
       </x:c>
       <x:c r="J168" s="30"/>
       <x:c r="K168" s="30"/>
@@ -14088,7 +14088,7 @@
       <x:c r="H169" s="30"/>
       <x:c r="I169" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I131:I167),0),1)</x:f>
-        <x:v>429</x:v>
+        <x:v>432.8</x:v>
       </x:c>
       <x:c r="J169" s="30"/>
       <x:c r="K169" s="30"/>
@@ -15510,7 +15510,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B209" s="22" t="str">
-        <x:v>9月21日-9月23日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C209" s="23" t="n">
         <x:v>7688</x:v>
@@ -15519,28 +15519,28 @@
         <x:v>7780</x:v>
       </x:c>
       <x:c r="E209" s="23" t="n">
-        <x:v>7638</x:v>
+        <x:v>7450</x:v>
       </x:c>
       <x:c r="F209" s="23" t="n">
-        <x:v>7650.4</x:v>
-      </x:c>
-      <x:c r="G209" s="23" t="n">
+        <x:v>7451.6</x:v>
+      </x:c>
+      <x:c r="G209" s="28" t="n">
         <x:f>ROUND(F209-F208,1)</x:f>
-        <x:v>-139.4</x:v>
+        <x:v>-338.2</x:v>
       </x:c>
       <x:c r="H209" s="24" t="n">
         <x:f>IFERROR(F209/F208-1,"")</x:f>
-        <x:v>-0.01789519628231795</x:v>
-      </x:c>
-      <x:c r="I209" s="23" t="n">
+        <x:v>-0.04341574879971244</x:v>
+      </x:c>
+      <x:c r="I209" s="26" t="n">
         <x:f>ROUND(D209-E209,1)</x:f>
-        <x:v>142</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="J209" s="22" t="str">
         <x:v>IC2612</x:v>
       </x:c>
       <x:c r="K209" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -15558,7 +15558,7 @@
       <x:c r="H210" s="30"/>
       <x:c r="I210" s="32" t="n">
         <x:f>ROUND(SUM(I173:I209),1)</x:f>
-        <x:v>16335.2</x:v>
+        <x:v>16523.2</x:v>
       </x:c>
       <x:c r="J210" s="30"/>
       <x:c r="K210" s="30"/>
@@ -15576,7 +15576,7 @@
       <x:c r="H211" s="30"/>
       <x:c r="I211" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I173:I209),0),1)</x:f>
-        <x:v>441.5</x:v>
+        <x:v>446.6</x:v>
       </x:c>
       <x:c r="J211" s="30"/>
       <x:c r="K211" s="30"/>
@@ -16998,7 +16998,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>9月21日-9月23日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
         <x:v>4451</x:v>
@@ -17007,28 +17007,28 @@
         <x:v>4520</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
-        <x:v>4434.8</x:v>
+        <x:v>4367</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>4461.8</x:v>
+        <x:v>4375</x:v>
       </x:c>
       <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>-46.2</x:v>
+        <x:v>-133</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>-0.010248447204968869</x:v>
-      </x:c>
-      <x:c r="I251" s="23" t="n">
+        <x:v>-0.029503105590062084</x:v>
+      </x:c>
+      <x:c r="I251" s="26" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>85.2</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K251" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -17046,7 +17046,7 @@
       <x:c r="H252" s="30"/>
       <x:c r="I252" s="32" t="n">
         <x:f>ROUND(SUM(I215:I251),1)</x:f>
-        <x:v>5798.8</x:v>
+        <x:v>5866.6</x:v>
       </x:c>
       <x:c r="J252" s="30"/>
       <x:c r="K252" s="30"/>
@@ -17064,7 +17064,7 @@
       <x:c r="H253" s="30"/>
       <x:c r="I253" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I215:I251),0),1)</x:f>
-        <x:v>156.7</x:v>
+        <x:v>158.6</x:v>
       </x:c>
       <x:c r="J253" s="30"/>
       <x:c r="K253" s="30"/>
@@ -48927,30 +48927,48 @@
       </x:c>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B222" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C222" s="30"/>
-      <x:c r="D222" s="30"/>
-      <x:c r="E222" s="30"/>
-      <x:c r="F222" s="30"/>
-      <x:c r="G222" s="30"/>
-      <x:c r="H222" s="30"/>
-      <x:c r="I222" s="30"/>
-      <x:c r="J222" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J221),1)</x:f>
-        <x:v>2358.4</x:v>
-      </x:c>
-      <x:c r="K222" s="30"/>
+      <x:c r="A222" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B222" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C222" s="22" t="str">
+        <x:v>9月24日</x:v>
+      </x:c>
+      <x:c r="D222" s="23" t="n">
+        <x:v>7551.2</x:v>
+      </x:c>
+      <x:c r="E222" s="23" t="n">
+        <x:v>7578</x:v>
+      </x:c>
+      <x:c r="F222" s="23" t="n">
+        <x:v>7386</x:v>
+      </x:c>
+      <x:c r="G222" s="23" t="n">
+        <x:v>7391</x:v>
+      </x:c>
+      <x:c r="H222" s="28" t="n">
+        <x:v>-187</x:v>
+      </x:c>
+      <x:c r="I222" s="24" t="n">
+        <x:v>-0.024676695698073403</x:v>
+      </x:c>
+      <x:c r="J222" s="26" t="n">
+        <x:f>ROUND(E222-F222,1)</x:f>
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="K222" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B223" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B223" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="C223" s="30"/>
       <x:c r="D223" s="30"/>
       <x:c r="E223" s="30"/>
@@ -48958,11 +48976,29 @@
       <x:c r="G223" s="30"/>
       <x:c r="H223" s="30"/>
       <x:c r="I223" s="30"/>
-      <x:c r="J223" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
-        <x:v>138.7</x:v>
+      <x:c r="J223" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J222),1)</x:f>
+        <x:v>2550.4</x:v>
       </x:c>
       <x:c r="K223" s="30"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B224" s="30"/>
+      <x:c r="C224" s="30"/>
+      <x:c r="D224" s="30"/>
+      <x:c r="E224" s="30"/>
+      <x:c r="F224" s="30"/>
+      <x:c r="G224" s="30"/>
+      <x:c r="H224" s="30"/>
+      <x:c r="I224" s="30"/>
+      <x:c r="J224" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
+        <x:v>141.7</x:v>
+      </x:c>
+      <x:c r="K224" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -56130,30 +56166,48 @@
       </x:c>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B222" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C222" s="30"/>
-      <x:c r="D222" s="30"/>
-      <x:c r="E222" s="30"/>
-      <x:c r="F222" s="30"/>
-      <x:c r="G222" s="30"/>
-      <x:c r="H222" s="30"/>
-      <x:c r="I222" s="30"/>
-      <x:c r="J222" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J221),1)</x:f>
-        <x:v>2300.2</x:v>
-      </x:c>
-      <x:c r="K222" s="30"/>
+      <x:c r="A222" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B222" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C222" s="22" t="str">
+        <x:v>9月24日</x:v>
+      </x:c>
+      <x:c r="D222" s="23" t="n">
+        <x:v>7615</x:v>
+      </x:c>
+      <x:c r="E222" s="23" t="n">
+        <x:v>7639.6</x:v>
+      </x:c>
+      <x:c r="F222" s="23" t="n">
+        <x:v>7450</x:v>
+      </x:c>
+      <x:c r="G222" s="23" t="n">
+        <x:v>7451.6</x:v>
+      </x:c>
+      <x:c r="H222" s="28" t="n">
+        <x:v>-198.8</x:v>
+      </x:c>
+      <x:c r="I222" s="24" t="n">
+        <x:v>-0.025985569381993034</x:v>
+      </x:c>
+      <x:c r="J222" s="26" t="n">
+        <x:f>ROUND(E222-F222,1)</x:f>
+        <x:v>189.6</x:v>
+      </x:c>
+      <x:c r="K222" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B223" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B223" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="C223" s="30"/>
       <x:c r="D223" s="30"/>
       <x:c r="E223" s="30"/>
@@ -56161,11 +56215,29 @@
       <x:c r="G223" s="30"/>
       <x:c r="H223" s="30"/>
       <x:c r="I223" s="30"/>
-      <x:c r="J223" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
-        <x:v>135.3</x:v>
+      <x:c r="J223" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J222),1)</x:f>
+        <x:v>2489.8</x:v>
       </x:c>
       <x:c r="K223" s="30"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B224" s="30"/>
+      <x:c r="C224" s="30"/>
+      <x:c r="D224" s="30"/>
+      <x:c r="E224" s="30"/>
+      <x:c r="F224" s="30"/>
+      <x:c r="G224" s="30"/>
+      <x:c r="H224" s="30"/>
+      <x:c r="I224" s="30"/>
+      <x:c r="J224" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
+        <x:v>138.3</x:v>
+      </x:c>
+      <x:c r="K224" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -63333,30 +63405,48 @@
       </x:c>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B222" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C222" s="30"/>
-      <x:c r="D222" s="30"/>
-      <x:c r="E222" s="30"/>
-      <x:c r="F222" s="30"/>
-      <x:c r="G222" s="30"/>
-      <x:c r="H222" s="30"/>
-      <x:c r="I222" s="30"/>
-      <x:c r="J222" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J221),1)</x:f>
-        <x:v>852.4</x:v>
-      </x:c>
-      <x:c r="K222" s="30"/>
+      <x:c r="A222" s="22" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B222" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C222" s="22" t="str">
+        <x:v>9月24日</x:v>
+      </x:c>
+      <x:c r="D222" s="23" t="n">
+        <x:v>4439</x:v>
+      </x:c>
+      <x:c r="E222" s="23" t="n">
+        <x:v>4443.6</x:v>
+      </x:c>
+      <x:c r="F222" s="23" t="n">
+        <x:v>4367</x:v>
+      </x:c>
+      <x:c r="G222" s="23" t="n">
+        <x:v>4375</x:v>
+      </x:c>
+      <x:c r="H222" s="23" t="n">
+        <x:v>-86.8</x:v>
+      </x:c>
+      <x:c r="I222" s="24" t="n">
+        <x:v>-0.019454032005020383</x:v>
+      </x:c>
+      <x:c r="J222" s="23" t="n">
+        <x:f>ROUND(E222-F222,1)</x:f>
+        <x:v>76.6</x:v>
+      </x:c>
+      <x:c r="K222" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B223" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B223" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="C223" s="30"/>
       <x:c r="D223" s="30"/>
       <x:c r="E223" s="30"/>
@@ -63364,11 +63454,29 @@
       <x:c r="G223" s="30"/>
       <x:c r="H223" s="30"/>
       <x:c r="I223" s="30"/>
-      <x:c r="J223" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J221),0),1)</x:f>
-        <x:v>50.1</x:v>
+      <x:c r="J223" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J222),1)</x:f>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="K223" s="30"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B224" s="30"/>
+      <x:c r="C224" s="30"/>
+      <x:c r="D224" s="30"/>
+      <x:c r="E224" s="30"/>
+      <x:c r="F224" s="30"/>
+      <x:c r="G224" s="30"/>
+      <x:c r="H224" s="30"/>
+      <x:c r="I224" s="30"/>
+      <x:c r="J224" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
+        <x:v>51.6</x:v>
+      </x:c>
+      <x:c r="K224" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Ra5966b3d53344960"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rd77337a790314baa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R3a7f8e5e98e0490f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R7ade6489606e45fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb3a9b7c6aa5841cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R6f51de44e70845e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R6c654b8068ac417e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rbdc9d020baa9476a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R983a5273a9974b0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rcb40d4615a71493b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R8d66696868f84bae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R40cd2d1c448d450a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rbb2520c8728c4fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R58dab43ffeab46b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R3a209cc2e7014a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc409a63b93e64aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R261dcc1971f641ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R515166788d56461e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R2cc8f4e59f0b4675"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rbbcb2324cafa4f19"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R8d66696868f84bae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R40cd2d1c448d450a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rbb2520c8728c4fab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R58dab43ffeab46b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R3a209cc2e7014a4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rc409a63b93e64aad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R261dcc1971f641ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R515166788d56461e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R2cc8f4e59f0b4675"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rbbcb2324cafa4f19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rdcb456890ff441af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R262eae97e1ac4c95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4f808407be924a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R6acd1ee9529d4567"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R73f7982626d04a50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R659368b71e2c46a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R680e9c9c12ad4e49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Ra225a27848004376"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Raea91dc667c04006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rd84e200373394e40"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Reaecf8b77ee14618"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R907f7e30a07742ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rbf0bbf8b898b45cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R6f95ae56d7704859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R81cf36a748dd4a10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R53bca3e19b4d4d9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd4415bb107334997"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R543694e630df4f8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R9dd9d518f1534300"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rb48d0f8194674d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R2710356e4437401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R55f79af1654942ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4cf3af400c664dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R0506a1e8871f433d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Ra696e6eba7fe4639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Re4b2e2ce1a1f43d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R07211a705e97432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R1fbc1da3469b4c00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R6878e56b43f546f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R36c6b102308342b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-28</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4443.6</x:v>
+        <x:v>4366.8</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4367</x:v>
+        <x:v>4246</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>76.6</x:v>
+        <x:v>120.8</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12815.6</x:v>
+        <x:v>12936.4</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72</x:v>
+        <x:v>72.3</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-28</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2850</x:v>
+        <x:v>2803.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2798</x:v>
+        <x:v>2746</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>52</x:v>
+        <x:v>57.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7130.6</x:v>
+        <x:v>7188.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.1</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -17258,155 +17258,155 @@
       </x:c>
     </x:row>
     <x:row r="257">
-      <x:c r="A257" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B257" s="30" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C257" s="30"/>
-      <x:c r="D257" s="30"/>
-      <x:c r="E257" s="30"/>
-      <x:c r="F257" s="30"/>
-      <x:c r="G257" s="30"/>
-      <x:c r="H257" s="30"/>
-      <x:c r="I257" s="32" t="n">
-        <x:f>ROUND(SUM(I220:I256),1)</x:f>
-        <x:v>5866.6</x:v>
-      </x:c>
-      <x:c r="J257" s="30"/>
-      <x:c r="K257" s="30"/>
+      <x:c r="A257" s="22" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B257" s="22" t="str">
+        <x:v>9月28日</x:v>
+      </x:c>
+      <x:c r="C257" s="23" t="n">
+        <x:v>4365</x:v>
+      </x:c>
+      <x:c r="D257" s="23" t="n">
+        <x:v>4366.8</x:v>
+      </x:c>
+      <x:c r="E257" s="23" t="n">
+        <x:v>4246</x:v>
+      </x:c>
+      <x:c r="F257" s="23" t="n">
+        <x:v>4280.8</x:v>
+      </x:c>
+      <x:c r="G257" s="23" t="n">
+        <x:f>ROUND(F257-F256,1)</x:f>
+        <x:v>-94.2</x:v>
+      </x:c>
+      <x:c r="H257" s="24" t="n">
+        <x:f>IFERROR(F257/F256-1,"")</x:f>
+        <x:v>-0.021531428571428535</x:v>
+      </x:c>
+      <x:c r="I257" s="26" t="n">
+        <x:f>ROUND(D257-E257,1)</x:f>
+        <x:v>120.8</x:v>
+      </x:c>
+      <x:c r="J257" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
+      <x:c r="K257" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B258" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B258" s="30" t="n">
+        <x:v>38</x:v>
+      </x:c>
       <x:c r="C258" s="30"/>
       <x:c r="D258" s="30"/>
       <x:c r="E258" s="30"/>
       <x:c r="F258" s="30"/>
       <x:c r="G258" s="30"/>
       <x:c r="H258" s="30"/>
-      <x:c r="I258" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I220:I256),0),1)</x:f>
-        <x:v>158.6</x:v>
+      <x:c r="I258" s="32" t="n">
+        <x:f>ROUND(SUM(I220:I257),1)</x:f>
+        <x:v>5987.4</x:v>
       </x:c>
       <x:c r="J258" s="30"/>
       <x:c r="K258" s="30"/>
     </x:row>
-    <x:row r="260">
-      <x:c r="A260" s="17" t="str">
+    <x:row r="259">
+      <x:c r="A259" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B259" s="30"/>
+      <x:c r="C259" s="30"/>
+      <x:c r="D259" s="30"/>
+      <x:c r="E259" s="30"/>
+      <x:c r="F259" s="30"/>
+      <x:c r="G259" s="30"/>
+      <x:c r="H259" s="30"/>
+      <x:c r="I259" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I220:I257),0),1)</x:f>
+        <x:v>157.6</x:v>
+      </x:c>
+      <x:c r="J259" s="30"/>
+      <x:c r="K259" s="30"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" s="17" t="str">
         <x:v>IH主力</x:v>
       </x:c>
-      <x:c r="B260" s="17"/>
-      <x:c r="C260" s="17"/>
-      <x:c r="D260" s="17"/>
-      <x:c r="E260" s="17"/>
-      <x:c r="F260" s="17"/>
-      <x:c r="G260" s="17"/>
-      <x:c r="H260" s="17"/>
-      <x:c r="I260" s="17"/>
-      <x:c r="J260" s="17"/>
-      <x:c r="K260" s="17"/>
-    </x:row>
-    <x:row r="261">
-      <x:c r="A261" s="20" t="str">
+      <x:c r="B261" s="17"/>
+      <x:c r="C261" s="17"/>
+      <x:c r="D261" s="17"/>
+      <x:c r="E261" s="17"/>
+      <x:c r="F261" s="17"/>
+      <x:c r="G261" s="17"/>
+      <x:c r="H261" s="17"/>
+      <x:c r="I261" s="17"/>
+      <x:c r="J261" s="17"/>
+      <x:c r="K261" s="17"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B261" s="20" t="str">
+      <x:c r="B262" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C261" s="20" t="str">
+      <x:c r="C262" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D261" s="20" t="str">
+      <x:c r="D262" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E261" s="20" t="str">
+      <x:c r="E262" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F261" s="20" t="str">
+      <x:c r="F262" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G261" s="20" t="str">
+      <x:c r="G262" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H261" s="20" t="str">
+      <x:c r="H262" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I261" s="20" t="str">
+      <x:c r="I262" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J261" s="20" t="str">
+      <x:c r="J262" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K261" s="20" t="str">
+      <x:c r="K262" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="262">
-      <x:c r="A262" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B262" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C262" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="D262" s="23" t="n">
-        <x:v>3165.6</x:v>
-      </x:c>
-      <x:c r="E262" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="F262" s="23" t="n">
-        <x:v>3134.8</x:v>
-      </x:c>
-      <x:c r="G262" s="23"/>
-      <x:c r="H262" s="24"/>
-      <x:c r="I262" s="26" t="n">
-        <x:f>ROUND(D262-E262,1)</x:f>
-        <x:v>124.8</x:v>
-      </x:c>
-      <x:c r="J262" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K262" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B263" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C263" s="23" t="n">
-        <x:v>3148.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="D263" s="23" t="n">
-        <x:v>3181.2</x:v>
+        <x:v>3165.6</x:v>
       </x:c>
       <x:c r="E263" s="23" t="n">
-        <x:v>3074.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="F263" s="23" t="n">
-        <x:v>3084.4</x:v>
-      </x:c>
-      <x:c r="G263" s="23" t="n">
-        <x:f>ROUND(F263-F262,1)</x:f>
-        <x:v>-50.4</x:v>
-      </x:c>
-      <x:c r="H263" s="24" t="n">
-        <x:f>IFERROR(F263/F262-1,"")</x:f>
-        <x:v>-0.016077580706903127</x:v>
-      </x:c>
+        <x:v>3134.8</x:v>
+      </x:c>
+      <x:c r="G263" s="23"/>
+      <x:c r="H263" s="24"/>
       <x:c r="I263" s="26" t="n">
         <x:f>ROUND(D263-E263,1)</x:f>
-        <x:v>106.8</x:v>
+        <x:v>124.8</x:v>
       </x:c>
       <x:c r="J263" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17417,34 +17417,34 @@
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B264" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C264" s="23" t="n">
-        <x:v>3081.2</x:v>
+        <x:v>3148.4</x:v>
       </x:c>
       <x:c r="D264" s="23" t="n">
-        <x:v>3102.6</x:v>
+        <x:v>3181.2</x:v>
       </x:c>
       <x:c r="E264" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074.4</x:v>
       </x:c>
       <x:c r="F264" s="23" t="n">
-        <x:v>3037.8</x:v>
+        <x:v>3084.4</x:v>
       </x:c>
       <x:c r="G264" s="23" t="n">
         <x:f>ROUND(F264-F263,1)</x:f>
-        <x:v>-46.6</x:v>
+        <x:v>-50.4</x:v>
       </x:c>
       <x:c r="H264" s="24" t="n">
         <x:f>IFERROR(F264/F263-1,"")</x:f>
-        <x:v>-0.015108286862923093</x:v>
+        <x:v>-0.016077580706903127</x:v>
       </x:c>
       <x:c r="I264" s="26" t="n">
         <x:f>ROUND(D264-E264,1)</x:f>
-        <x:v>66.4</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J264" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17455,34 +17455,34 @@
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B265" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C265" s="23" t="n">
-        <x:v>3049.8</x:v>
+        <x:v>3081.2</x:v>
       </x:c>
       <x:c r="D265" s="23" t="n">
-        <x:v>3136.6</x:v>
+        <x:v>3102.6</x:v>
       </x:c>
       <x:c r="E265" s="23" t="n">
-        <x:v>3044</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="F265" s="23" t="n">
-        <x:v>3074</x:v>
+        <x:v>3037.8</x:v>
       </x:c>
       <x:c r="G265" s="23" t="n">
         <x:f>ROUND(F265-F264,1)</x:f>
-        <x:v>36.2</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H265" s="24" t="n">
         <x:f>IFERROR(F265/F264-1,"")</x:f>
-        <x:v>0.011916518533148901</x:v>
+        <x:v>-0.015108286862923093</x:v>
       </x:c>
       <x:c r="I265" s="26" t="n">
         <x:f>ROUND(D265-E265,1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J265" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17493,34 +17493,34 @@
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B266" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C266" s="23" t="n">
-        <x:v>3039.4</x:v>
+        <x:v>3049.8</x:v>
       </x:c>
       <x:c r="D266" s="23" t="n">
-        <x:v>3081</x:v>
+        <x:v>3136.6</x:v>
       </x:c>
       <x:c r="E266" s="23" t="n">
-        <x:v>2984</x:v>
+        <x:v>3044</x:v>
       </x:c>
       <x:c r="F266" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074</x:v>
       </x:c>
       <x:c r="G266" s="23" t="n">
         <x:f>ROUND(F266-F265,1)</x:f>
-        <x:v>-37.8</x:v>
+        <x:v>36.2</x:v>
       </x:c>
       <x:c r="H266" s="24" t="n">
         <x:f>IFERROR(F266/F265-1,"")</x:f>
-        <x:v>-0.012296681847755453</x:v>
+        <x:v>0.011916518533148901</x:v>
       </x:c>
       <x:c r="I266" s="26" t="n">
         <x:f>ROUND(D266-E266,1)</x:f>
-        <x:v>97</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="J266" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17531,34 +17531,34 @@
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B267" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C267" s="23" t="n">
-        <x:v>3060.6</x:v>
+        <x:v>3039.4</x:v>
       </x:c>
       <x:c r="D267" s="23" t="n">
-        <x:v>3098</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E267" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="F267" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="G267" s="23" t="n">
         <x:f>ROUND(F267-F266,1)</x:f>
-        <x:v>-16.2</x:v>
+        <x:v>-37.8</x:v>
       </x:c>
       <x:c r="H267" s="24" t="n">
         <x:f>IFERROR(F267/F266-1,"")</x:f>
-        <x:v>-0.005335616889532879</x:v>
+        <x:v>-0.012296681847755453</x:v>
       </x:c>
       <x:c r="I267" s="26" t="n">
         <x:f>ROUND(D267-E267,1)</x:f>
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J267" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17569,110 +17569,110 @@
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B268" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C268" s="23" t="n">
-        <x:v>3049.2</x:v>
+        <x:v>3060.6</x:v>
       </x:c>
       <x:c r="D268" s="23" t="n">
-        <x:v>3086.4</x:v>
+        <x:v>3098</x:v>
       </x:c>
       <x:c r="E268" s="23" t="n">
-        <x:v>3022</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="F268" s="23" t="n">
-        <x:v>3045.4</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="G268" s="23" t="n">
         <x:f>ROUND(F268-F267,1)</x:f>
-        <x:v>25.4</x:v>
+        <x:v>-16.2</x:v>
       </x:c>
       <x:c r="H268" s="24" t="n">
         <x:f>IFERROR(F268/F267-1,"")</x:f>
-        <x:v>0.008410596026490191</x:v>
+        <x:v>-0.005335616889532879</x:v>
       </x:c>
       <x:c r="I268" s="26" t="n">
         <x:f>ROUND(D268-E268,1)</x:f>
-        <x:v>64.4</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J268" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K268" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B269" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C269" s="23" t="n">
-        <x:v>3038</x:v>
+        <x:v>3049.2</x:v>
       </x:c>
       <x:c r="D269" s="23" t="n">
-        <x:v>3056</x:v>
+        <x:v>3086.4</x:v>
       </x:c>
       <x:c r="E269" s="23" t="n">
-        <x:v>2950</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="F269" s="23" t="n">
-        <x:v>2990</x:v>
+        <x:v>3045.4</x:v>
       </x:c>
       <x:c r="G269" s="23" t="n">
         <x:f>ROUND(F269-F268,1)</x:f>
-        <x:v>-55.4</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="H269" s="24" t="n">
         <x:f>IFERROR(F269/F268-1,"")</x:f>
-        <x:v>-0.018191370591712164</x:v>
+        <x:v>0.008410596026490191</x:v>
       </x:c>
       <x:c r="I269" s="26" t="n">
         <x:f>ROUND(D269-E269,1)</x:f>
-        <x:v>106</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="J269" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K269" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B270" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C270" s="23" t="n">
-        <x:v>2965.4</x:v>
+        <x:v>3038</x:v>
       </x:c>
       <x:c r="D270" s="23" t="n">
-        <x:v>2989</x:v>
+        <x:v>3056</x:v>
       </x:c>
       <x:c r="E270" s="23" t="n">
-        <x:v>2912.6</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="F270" s="23" t="n">
-        <x:v>2957</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="G270" s="23" t="n">
         <x:f>ROUND(F270-F269,1)</x:f>
-        <x:v>-33</x:v>
+        <x:v>-55.4</x:v>
       </x:c>
       <x:c r="H270" s="24" t="n">
         <x:f>IFERROR(F270/F269-1,"")</x:f>
-        <x:v>-0.011036789297658833</x:v>
+        <x:v>-0.018191370591712164</x:v>
       </x:c>
       <x:c r="I270" s="26" t="n">
         <x:f>ROUND(D270-E270,1)</x:f>
-        <x:v>76.4</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J270" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17683,34 +17683,34 @@
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B271" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C271" s="23" t="n">
-        <x:v>2953</x:v>
+        <x:v>2965.4</x:v>
       </x:c>
       <x:c r="D271" s="23" t="n">
-        <x:v>2996.6</x:v>
+        <x:v>2989</x:v>
       </x:c>
       <x:c r="E271" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2912.6</x:v>
       </x:c>
       <x:c r="F271" s="23" t="n">
-        <x:v>2898.4</x:v>
+        <x:v>2957</x:v>
       </x:c>
       <x:c r="G271" s="23" t="n">
         <x:f>ROUND(F271-F270,1)</x:f>
-        <x:v>-58.6</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="H271" s="24" t="n">
         <x:f>IFERROR(F271/F270-1,"")</x:f>
-        <x:v>-0.019817382482245516</x:v>
+        <x:v>-0.011036789297658833</x:v>
       </x:c>
       <x:c r="I271" s="26" t="n">
         <x:f>ROUND(D271-E271,1)</x:f>
-        <x:v>100.6</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="J271" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17721,37 +17721,37 @@
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B272" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C272" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2953</x:v>
       </x:c>
       <x:c r="D272" s="23" t="n">
-        <x:v>2847.6</x:v>
+        <x:v>2996.6</x:v>
       </x:c>
       <x:c r="E272" s="23" t="n">
-        <x:v>2750.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="F272" s="23" t="n">
-        <x:v>2814.4</x:v>
+        <x:v>2898.4</x:v>
       </x:c>
       <x:c r="G272" s="23" t="n">
         <x:f>ROUND(F272-F271,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-58.6</x:v>
       </x:c>
       <x:c r="H272" s="24" t="n">
         <x:f>IFERROR(F272/F271-1,"")</x:f>
-        <x:v>-0.028981507038365995</x:v>
+        <x:v>-0.019817382482245516</x:v>
       </x:c>
       <x:c r="I272" s="26" t="n">
         <x:f>ROUND(D272-E272,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="J272" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K272" s="22" t="n">
         <x:v>5</x:v>
@@ -17759,34 +17759,34 @@
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B273" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C273" s="23" t="n">
-        <x:v>2794.8</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D273" s="23" t="n">
-        <x:v>2865.4</x:v>
+        <x:v>2847.6</x:v>
       </x:c>
       <x:c r="E273" s="23" t="n">
-        <x:v>2780.4</x:v>
+        <x:v>2750.8</x:v>
       </x:c>
       <x:c r="F273" s="23" t="n">
-        <x:v>2804.4</x:v>
+        <x:v>2814.4</x:v>
       </x:c>
       <x:c r="G273" s="23" t="n">
         <x:f>ROUND(F273-F272,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H273" s="24" t="n">
         <x:f>IFERROR(F273/F272-1,"")</x:f>
-        <x:v>-0.0035531552018192025</x:v>
+        <x:v>-0.028981507038365995</x:v>
       </x:c>
       <x:c r="I273" s="26" t="n">
         <x:f>ROUND(D273-E273,1)</x:f>
-        <x:v>85</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J273" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17797,110 +17797,110 @@
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B274" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C274" s="23" t="n">
-        <x:v>2810.4</x:v>
+        <x:v>2794.8</x:v>
       </x:c>
       <x:c r="D274" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2865.4</x:v>
       </x:c>
       <x:c r="E274" s="23" t="n">
-        <x:v>2797.2</x:v>
+        <x:v>2780.4</x:v>
       </x:c>
       <x:c r="F274" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2804.4</x:v>
       </x:c>
       <x:c r="G274" s="23" t="n">
         <x:f>ROUND(F274-F273,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H274" s="24" t="n">
         <x:f>IFERROR(F274/F273-1,"")</x:f>
-        <x:v>0.02453287690771644</x:v>
+        <x:v>-0.0035531552018192025</x:v>
       </x:c>
       <x:c r="I274" s="26" t="n">
         <x:f>ROUND(D274-E274,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J274" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K274" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B275" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C275" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2810.4</x:v>
       </x:c>
       <x:c r="D275" s="23" t="n">
-        <x:v>2930.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="E275" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2797.2</x:v>
       </x:c>
       <x:c r="F275" s="23" t="n">
-        <x:v>2888</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="G275" s="23" t="n">
         <x:f>ROUND(F275-F274,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>68.8</x:v>
       </x:c>
       <x:c r="H275" s="24" t="n">
         <x:f>IFERROR(F275/F274-1,"")</x:f>
-        <x:v>0.005151051092858294</x:v>
+        <x:v>0.02453287690771644</x:v>
       </x:c>
       <x:c r="I275" s="26" t="n">
         <x:f>ROUND(D275-E275,1)</x:f>
-        <x:v>70.8</x:v>
+        <x:v>98.8</x:v>
       </x:c>
       <x:c r="J275" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K275" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B276" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C276" s="23" t="n">
-        <x:v>2900.8</x:v>
+        <x:v>2864.6</x:v>
       </x:c>
       <x:c r="D276" s="23" t="n">
-        <x:v>2934.2</x:v>
+        <x:v>2930.8</x:v>
       </x:c>
       <x:c r="E276" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="F276" s="23" t="n">
-        <x:v>2929</x:v>
+        <x:v>2888</x:v>
       </x:c>
       <x:c r="G276" s="23" t="n">
         <x:f>ROUND(F276-F275,1)</x:f>
-        <x:v>41</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H276" s="24" t="n">
         <x:f>IFERROR(F276/F275-1,"")</x:f>
-        <x:v>0.014196675900276956</x:v>
-      </x:c>
-      <x:c r="I276" s="23" t="n">
+        <x:v>0.005151051092858294</x:v>
+      </x:c>
+      <x:c r="I276" s="26" t="n">
         <x:f>ROUND(D276-E276,1)</x:f>
-        <x:v>43.2</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="J276" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -17911,148 +17911,148 @@
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B277" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C277" s="23" t="n">
-        <x:v>2929.2</x:v>
+        <x:v>2900.8</x:v>
       </x:c>
       <x:c r="D277" s="23" t="n">
-        <x:v>2970</x:v>
+        <x:v>2934.2</x:v>
       </x:c>
       <x:c r="E277" s="23" t="n">
-        <x:v>2917</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F277" s="23" t="n">
-        <x:v>2968.8</x:v>
+        <x:v>2929</x:v>
       </x:c>
       <x:c r="G277" s="23" t="n">
         <x:f>ROUND(F277-F276,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H277" s="24" t="n">
         <x:f>IFERROR(F277/F276-1,"")</x:f>
-        <x:v>0.013588255377261937</x:v>
+        <x:v>0.014196675900276956</x:v>
       </x:c>
       <x:c r="I277" s="23" t="n">
         <x:f>ROUND(D277-E277,1)</x:f>
-        <x:v>53</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J277" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K277" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B278" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C278" s="23" t="n">
-        <x:v>2995.2</x:v>
+        <x:v>2929.2</x:v>
       </x:c>
       <x:c r="D278" s="23" t="n">
-        <x:v>3024.8</x:v>
+        <x:v>2970</x:v>
       </x:c>
       <x:c r="E278" s="23" t="n">
-        <x:v>2969.2</x:v>
+        <x:v>2917</x:v>
       </x:c>
       <x:c r="F278" s="23" t="n">
-        <x:v>2981.6</x:v>
+        <x:v>2968.8</x:v>
       </x:c>
       <x:c r="G278" s="23" t="n">
         <x:f>ROUND(F278-F277,1)</x:f>
-        <x:v>12.8</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="H278" s="24" t="n">
         <x:f>IFERROR(F278/F277-1,"")</x:f>
-        <x:v>0.0043115063325247505</x:v>
+        <x:v>0.013588255377261937</x:v>
       </x:c>
       <x:c r="I278" s="23" t="n">
         <x:f>ROUND(D278-E278,1)</x:f>
-        <x:v>55.6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J278" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K278" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
-        <x:v>2997.6</x:v>
+        <x:v>2995.2</x:v>
       </x:c>
       <x:c r="D279" s="23" t="n">
-        <x:v>3041.8</x:v>
+        <x:v>3024.8</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>2927</x:v>
+        <x:v>2969.2</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>2945</x:v>
+        <x:v>2981.6</x:v>
       </x:c>
       <x:c r="G279" s="23" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>-36.6</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>-0.012275288435739218</x:v>
-      </x:c>
-      <x:c r="I279" s="26" t="n">
+        <x:v>0.0043115063325247505</x:v>
+      </x:c>
+      <x:c r="I279" s="23" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>114.8</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K279" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B280" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C280" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2997.6</x:v>
       </x:c>
       <x:c r="D280" s="23" t="n">
-        <x:v>2981.8</x:v>
+        <x:v>3041.8</x:v>
       </x:c>
       <x:c r="E280" s="23" t="n">
-        <x:v>2893.2</x:v>
+        <x:v>2927</x:v>
       </x:c>
       <x:c r="F280" s="23" t="n">
-        <x:v>2899.2</x:v>
+        <x:v>2945</x:v>
       </x:c>
       <x:c r="G280" s="23" t="n">
         <x:f>ROUND(F280-F279,1)</x:f>
-        <x:v>-45.8</x:v>
+        <x:v>-36.6</x:v>
       </x:c>
       <x:c r="H280" s="24" t="n">
         <x:f>IFERROR(F280/F279-1,"")</x:f>
-        <x:v>-0.015551782682512783</x:v>
+        <x:v>-0.012275288435739218</x:v>
       </x:c>
       <x:c r="I280" s="26" t="n">
         <x:f>ROUND(D280-E280,1)</x:f>
-        <x:v>88.6</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="J280" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18063,34 +18063,34 @@
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B281" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C281" s="23" t="n">
-        <x:v>2910.8</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D281" s="23" t="n">
-        <x:v>2960</x:v>
+        <x:v>2981.8</x:v>
       </x:c>
       <x:c r="E281" s="23" t="n">
-        <x:v>2871</x:v>
+        <x:v>2893.2</x:v>
       </x:c>
       <x:c r="F281" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2899.2</x:v>
       </x:c>
       <x:c r="G281" s="23" t="n">
         <x:f>ROUND(F281-F280,1)</x:f>
-        <x:v>1.4</x:v>
+        <x:v>-45.8</x:v>
       </x:c>
       <x:c r="H281" s="24" t="n">
         <x:f>IFERROR(F281/F280-1,"")</x:f>
-        <x:v>0.0004828918322297149</x:v>
+        <x:v>-0.015551782682512783</x:v>
       </x:c>
       <x:c r="I281" s="26" t="n">
         <x:f>ROUND(D281-E281,1)</x:f>
-        <x:v>89</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="J281" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18101,34 +18101,34 @@
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B282" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C282" s="23" t="n">
-        <x:v>2901</x:v>
+        <x:v>2910.8</x:v>
       </x:c>
       <x:c r="D282" s="23" t="n">
-        <x:v>2924.2</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="E282" s="23" t="n">
-        <x:v>2841.6</x:v>
+        <x:v>2871</x:v>
       </x:c>
       <x:c r="F282" s="23" t="n">
-        <x:v>2844</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="G282" s="23" t="n">
         <x:f>ROUND(F282-F281,1)</x:f>
-        <x:v>-56.6</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H282" s="24" t="n">
         <x:f>IFERROR(F282/F281-1,"")</x:f>
-        <x:v>-0.019513204164655518</x:v>
+        <x:v>0.0004828918322297149</x:v>
       </x:c>
       <x:c r="I282" s="26" t="n">
         <x:f>ROUND(D282-E282,1)</x:f>
-        <x:v>82.6</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J282" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18139,34 +18139,34 @@
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B283" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C283" s="23" t="n">
-        <x:v>2808.4</x:v>
+        <x:v>2901</x:v>
       </x:c>
       <x:c r="D283" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2924.2</x:v>
       </x:c>
       <x:c r="E283" s="23" t="n">
-        <x:v>2791.2</x:v>
+        <x:v>2841.6</x:v>
       </x:c>
       <x:c r="F283" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G283" s="23" t="n">
         <x:f>ROUND(F283-F282,1)</x:f>
-        <x:v>53.2</x:v>
+        <x:v>-56.6</x:v>
       </x:c>
       <x:c r="H283" s="24" t="n">
         <x:f>IFERROR(F283/F282-1,"")</x:f>
-        <x:v>0.01870604781997187</x:v>
+        <x:v>-0.019513204164655518</x:v>
       </x:c>
       <x:c r="I283" s="26" t="n">
         <x:f>ROUND(D283-E283,1)</x:f>
-        <x:v>111.4</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J283" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18177,113 +18177,113 @@
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B284" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C284" s="23" t="n">
-        <x:v>2926.2</x:v>
+        <x:v>2808.4</x:v>
       </x:c>
       <x:c r="D284" s="23" t="n">
-        <x:v>2954.6</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="E284" s="23" t="n">
-        <x:v>2903.4</x:v>
+        <x:v>2791.2</x:v>
       </x:c>
       <x:c r="F284" s="23" t="n">
-        <x:v>2941</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G284" s="23" t="n">
         <x:f>ROUND(F284-F283,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="H284" s="24" t="n">
         <x:f>IFERROR(F284/F283-1,"")</x:f>
-        <x:v>0.01511804500897429</x:v>
-      </x:c>
-      <x:c r="I284" s="23" t="n">
+        <x:v>0.01870604781997187</x:v>
+      </x:c>
+      <x:c r="I284" s="26" t="n">
         <x:f>ROUND(D284-E284,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="J284" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K284" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B285" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C285" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2926.2</x:v>
       </x:c>
       <x:c r="D285" s="23" t="n">
-        <x:v>2996</x:v>
+        <x:v>2954.6</x:v>
       </x:c>
       <x:c r="E285" s="23" t="n">
-        <x:v>2834.8</x:v>
+        <x:v>2903.4</x:v>
       </x:c>
       <x:c r="F285" s="23" t="n">
-        <x:v>2859</x:v>
+        <x:v>2941</x:v>
       </x:c>
       <x:c r="G285" s="23" t="n">
         <x:f>ROUND(F285-F284,1)</x:f>
-        <x:v>-82</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="H285" s="24" t="n">
         <x:f>IFERROR(F285/F284-1,"")</x:f>
-        <x:v>-0.02788167290037402</x:v>
-      </x:c>
-      <x:c r="I285" s="26" t="n">
+        <x:v>0.01511804500897429</x:v>
+      </x:c>
+      <x:c r="I285" s="23" t="n">
         <x:f>ROUND(D285-E285,1)</x:f>
-        <x:v>161.2</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J285" s="22" t="str">
-        <x:v>IH2606/IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K285" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B286" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C286" s="23" t="n">
-        <x:v>2870</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D286" s="23" t="n">
-        <x:v>2976</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="E286" s="23" t="n">
-        <x:v>2861.8</x:v>
+        <x:v>2834.8</x:v>
       </x:c>
       <x:c r="F286" s="23" t="n">
-        <x:v>2886.6</x:v>
+        <x:v>2859</x:v>
       </x:c>
       <x:c r="G286" s="23" t="n">
         <x:f>ROUND(F286-F285,1)</x:f>
-        <x:v>27.6</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="H286" s="24" t="n">
         <x:f>IFERROR(F286/F285-1,"")</x:f>
-        <x:v>0.009653725078698772</x:v>
+        <x:v>-0.02788167290037402</x:v>
       </x:c>
       <x:c r="I286" s="26" t="n">
         <x:f>ROUND(D286-E286,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>161.2</x:v>
       </x:c>
       <x:c r="J286" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606/IH2609</x:v>
       </x:c>
       <x:c r="K286" s="22" t="n">
         <x:v>5</x:v>
@@ -18291,34 +18291,34 @@
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
-        <x:v>2899</x:v>
+        <x:v>2870</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2861.8</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>2910.2</x:v>
+        <x:v>2886.6</x:v>
       </x:c>
       <x:c r="G287" s="23" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>23.6</x:v>
+        <x:v>27.6</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>0.008175708445922414</x:v>
+        <x:v>0.009653725078698772</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>121.4</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18329,34 +18329,34 @@
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B288" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C288" s="23" t="n">
-        <x:v>2895.8</x:v>
+        <x:v>2899</x:v>
       </x:c>
       <x:c r="D288" s="23" t="n">
-        <x:v>2924</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="E288" s="23" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="F288" s="23" t="n">
-        <x:v>2796.4</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="G288" s="23" t="n">
         <x:f>ROUND(F288-F287,1)</x:f>
-        <x:v>-113.8</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="H288" s="24" t="n">
         <x:f>IFERROR(F288/F287-1,"")</x:f>
-        <x:v>-0.039103841660366845</x:v>
+        <x:v>0.008175708445922414</x:v>
       </x:c>
       <x:c r="I288" s="26" t="n">
         <x:f>ROUND(D288-E288,1)</x:f>
-        <x:v>141.4</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J288" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18367,34 +18367,34 @@
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B289" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C289" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2895.8</x:v>
       </x:c>
       <x:c r="D289" s="23" t="n">
-        <x:v>2978</x:v>
+        <x:v>2924</x:v>
       </x:c>
       <x:c r="E289" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="F289" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2796.4</x:v>
       </x:c>
       <x:c r="G289" s="23" t="n">
         <x:f>ROUND(F289-F288,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>-113.8</x:v>
       </x:c>
       <x:c r="H289" s="24" t="n">
         <x:f>IFERROR(F289/F288-1,"")</x:f>
-        <x:v>0.040623658990130096</x:v>
+        <x:v>-0.039103841660366845</x:v>
       </x:c>
       <x:c r="I289" s="26" t="n">
         <x:f>ROUND(D289-E289,1)</x:f>
-        <x:v>158</x:v>
+        <x:v>141.4</x:v>
       </x:c>
       <x:c r="J289" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18405,34 +18405,34 @@
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B290" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C290" s="23" t="n">
-        <x:v>2929.6</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="D290" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E290" s="23" t="n">
-        <x:v>2847.2</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="F290" s="23" t="n">
-        <x:v>2891.8</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G290" s="23" t="n">
         <x:f>ROUND(F290-F289,1)</x:f>
-        <x:v>-18.2</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="H290" s="24" t="n">
         <x:f>IFERROR(F290/F289-1,"")</x:f>
-        <x:v>-0.006254295532646004</x:v>
+        <x:v>0.040623658990130096</x:v>
       </x:c>
       <x:c r="I290" s="26" t="n">
         <x:f>ROUND(D290-E290,1)</x:f>
-        <x:v>82.8</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J290" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18443,34 +18443,34 @@
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B291" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C291" s="23" t="n">
-        <x:v>2882.4</x:v>
+        <x:v>2929.6</x:v>
       </x:c>
       <x:c r="D291" s="23" t="n">
-        <x:v>2930.6</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="E291" s="23" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2847.2</x:v>
       </x:c>
       <x:c r="F291" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2891.8</x:v>
       </x:c>
       <x:c r="G291" s="23" t="n">
         <x:f>ROUND(F291-F290,1)</x:f>
-        <x:v>38.2</x:v>
+        <x:v>-18.2</x:v>
       </x:c>
       <x:c r="H291" s="24" t="n">
         <x:f>IFERROR(F291/F290-1,"")</x:f>
-        <x:v>0.013209765543951812</x:v>
+        <x:v>-0.006254295532646004</x:v>
       </x:c>
       <x:c r="I291" s="26" t="n">
         <x:f>ROUND(D291-E291,1)</x:f>
-        <x:v>84.8</x:v>
+        <x:v>82.8</x:v>
       </x:c>
       <x:c r="J291" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18481,34 +18481,34 @@
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B292" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C292" s="23" t="n">
+        <x:v>2882.4</x:v>
+      </x:c>
+      <x:c r="D292" s="23" t="n">
+        <x:v>2930.6</x:v>
+      </x:c>
+      <x:c r="E292" s="23" t="n">
+        <x:v>2845.8</x:v>
+      </x:c>
+      <x:c r="F292" s="23" t="n">
         <x:v>2930</x:v>
-      </x:c>
-      <x:c r="D292" s="23" t="n">
-        <x:v>2949.6</x:v>
-      </x:c>
-      <x:c r="E292" s="23" t="n">
-        <x:v>2877</x:v>
-      </x:c>
-      <x:c r="F292" s="23" t="n">
-        <x:v>2890</x:v>
       </x:c>
       <x:c r="G292" s="23" t="n">
         <x:f>ROUND(F292-F291,1)</x:f>
-        <x:v>-40</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="H292" s="24" t="n">
         <x:f>IFERROR(F292/F291-1,"")</x:f>
-        <x:v>-0.013651877133105783</x:v>
+        <x:v>0.013209765543951812</x:v>
       </x:c>
       <x:c r="I292" s="26" t="n">
         <x:f>ROUND(D292-E292,1)</x:f>
-        <x:v>72.6</x:v>
+        <x:v>84.8</x:v>
       </x:c>
       <x:c r="J292" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18519,34 +18519,34 @@
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B293" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="D293" s="23" t="n">
-        <x:v>2921.2</x:v>
+        <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E293" s="23" t="n">
-        <x:v>2843</x:v>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>2861</x:v>
+        <x:v>2890</x:v>
       </x:c>
       <x:c r="G293" s="23" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>-29</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>-0.01003460207612461</x:v>
+        <x:v>-0.013651877133105783</x:v>
       </x:c>
       <x:c r="I293" s="26" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
-        <x:v>78.2</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="J293" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18557,34 +18557,34 @@
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B294" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C294" s="23" t="n">
-        <x:v>2856.4</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D294" s="23" t="n">
-        <x:v>2918.2</x:v>
+        <x:v>2921.2</x:v>
       </x:c>
       <x:c r="E294" s="23" t="n">
-        <x:v>2837.4</x:v>
+        <x:v>2843</x:v>
       </x:c>
       <x:c r="F294" s="23" t="n">
-        <x:v>2911.4</x:v>
+        <x:v>2861</x:v>
       </x:c>
       <x:c r="G294" s="23" t="n">
         <x:f>ROUND(F294-F293,1)</x:f>
-        <x:v>50.4</x:v>
+        <x:v>-29</x:v>
       </x:c>
       <x:c r="H294" s="24" t="n">
         <x:f>IFERROR(F294/F293-1,"")</x:f>
-        <x:v>0.01761621810555747</x:v>
+        <x:v>-0.01003460207612461</x:v>
       </x:c>
       <x:c r="I294" s="26" t="n">
         <x:f>ROUND(D294-E294,1)</x:f>
-        <x:v>80.8</x:v>
+        <x:v>78.2</x:v>
       </x:c>
       <x:c r="J294" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18595,34 +18595,34 @@
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B295" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2856.4</x:v>
       </x:c>
       <x:c r="D295" s="23" t="n">
-        <x:v>2949.4</x:v>
+        <x:v>2918.2</x:v>
       </x:c>
       <x:c r="E295" s="23" t="n">
-        <x:v>2877.6</x:v>
+        <x:v>2837.4</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>2915.8</x:v>
+        <x:v>2911.4</x:v>
       </x:c>
       <x:c r="G295" s="23" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>4.4</x:v>
+        <x:v>50.4</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>0.0015113004053033396</x:v>
+        <x:v>0.01761621810555747</x:v>
       </x:c>
       <x:c r="I295" s="26" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>71.8</x:v>
+        <x:v>80.8</x:v>
       </x:c>
       <x:c r="J295" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18633,34 +18633,34 @@
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B296" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C296" s="23" t="n">
-        <x:v>2923.2</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D296" s="23" t="n">
-        <x:v>2931.4</x:v>
+        <x:v>2949.4</x:v>
       </x:c>
       <x:c r="E296" s="23" t="n">
-        <x:v>2836.8</x:v>
+        <x:v>2877.6</x:v>
       </x:c>
       <x:c r="F296" s="23" t="n">
-        <x:v>2867</x:v>
+        <x:v>2915.8</x:v>
       </x:c>
       <x:c r="G296" s="23" t="n">
         <x:f>ROUND(F296-F295,1)</x:f>
-        <x:v>-48.8</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="H296" s="24" t="n">
         <x:f>IFERROR(F296/F295-1,"")</x:f>
-        <x:v>-0.01673640167364021</x:v>
+        <x:v>0.0015113004053033396</x:v>
       </x:c>
       <x:c r="I296" s="26" t="n">
         <x:f>ROUND(D296-E296,1)</x:f>
-        <x:v>94.6</x:v>
+        <x:v>71.8</x:v>
       </x:c>
       <x:c r="J296" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18671,34 +18671,34 @@
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B297" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C297" s="23" t="n">
-        <x:v>2849.2</x:v>
+        <x:v>2923.2</x:v>
       </x:c>
       <x:c r="D297" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2931.4</x:v>
       </x:c>
       <x:c r="E297" s="23" t="n">
-        <x:v>2829.4</x:v>
+        <x:v>2836.8</x:v>
       </x:c>
       <x:c r="F297" s="23" t="n">
-        <x:v>2862.2</x:v>
+        <x:v>2867</x:v>
       </x:c>
       <x:c r="G297" s="23" t="n">
         <x:f>ROUND(F297-F296,1)</x:f>
-        <x:v>-4.8</x:v>
+        <x:v>-48.8</x:v>
       </x:c>
       <x:c r="H297" s="24" t="n">
         <x:f>IFERROR(F297/F296-1,"")</x:f>
-        <x:v>-0.0016742239274503135</x:v>
-      </x:c>
-      <x:c r="I297" s="23" t="n">
+        <x:v>-0.01673640167364021</x:v>
+      </x:c>
+      <x:c r="I297" s="26" t="n">
         <x:f>ROUND(D297-E297,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>94.6</x:v>
       </x:c>
       <x:c r="J297" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18709,230 +18709,230 @@
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="22" t="n">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B298" s="22" t="str">
-        <x:v>9月21日-9月24日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C298" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2849.2</x:v>
       </x:c>
       <x:c r="D298" s="23" t="n">
-        <x:v>2881.2</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="E298" s="23" t="n">
-        <x:v>2798</x:v>
+        <x:v>2829.4</x:v>
       </x:c>
       <x:c r="F298" s="23" t="n">
-        <x:v>2804.6</x:v>
+        <x:v>2862.2</x:v>
       </x:c>
       <x:c r="G298" s="23" t="n">
         <x:f>ROUND(F298-F297,1)</x:f>
-        <x:v>-57.6</x:v>
+        <x:v>-4.8</x:v>
       </x:c>
       <x:c r="H298" s="24" t="n">
         <x:f>IFERROR(F298/F297-1,"")</x:f>
+        <x:v>-0.0016742239274503135</x:v>
+      </x:c>
+      <x:c r="I298" s="23" t="n">
+        <x:f>ROUND(D298-E298,1)</x:f>
+        <x:v>43.8</x:v>
+      </x:c>
+      <x:c r="J298" s="22" t="str">
+        <x:v>IH2609</x:v>
+      </x:c>
+      <x:c r="K298" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" s="22" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B299" s="22" t="str">
+        <x:v>9月21日-9月24日</x:v>
+      </x:c>
+      <x:c r="C299" s="23" t="n">
+        <x:v>2830</x:v>
+      </x:c>
+      <x:c r="D299" s="23" t="n">
+        <x:v>2881.2</x:v>
+      </x:c>
+      <x:c r="E299" s="23" t="n">
+        <x:v>2798</x:v>
+      </x:c>
+      <x:c r="F299" s="23" t="n">
+        <x:v>2804.6</x:v>
+      </x:c>
+      <x:c r="G299" s="23" t="n">
+        <x:f>ROUND(F299-F298,1)</x:f>
+        <x:v>-57.6</x:v>
+      </x:c>
+      <x:c r="H299" s="24" t="n">
+        <x:f>IFERROR(F299/F298-1,"")</x:f>
         <x:v>-0.02012437984766957</x:v>
       </x:c>
-      <x:c r="I298" s="26" t="n">
-        <x:f>ROUND(D298-E298,1)</x:f>
+      <x:c r="I299" s="26" t="n">
+        <x:f>ROUND(D299-E299,1)</x:f>
         <x:v>83.2</x:v>
       </x:c>
-      <x:c r="J298" s="22" t="str">
+      <x:c r="J299" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
-      <x:c r="K298" s="22" t="n">
+      <x:c r="K299" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="299">
-      <x:c r="A299" s="31" t="str">
+    <x:row r="300">
+      <x:c r="A300" s="22" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B300" s="22" t="str">
+        <x:v>9月28日</x:v>
+      </x:c>
+      <x:c r="C300" s="23" t="n">
+        <x:v>2802</x:v>
+      </x:c>
+      <x:c r="D300" s="23" t="n">
+        <x:v>2803.8</x:v>
+      </x:c>
+      <x:c r="E300" s="23" t="n">
+        <x:v>2746</x:v>
+      </x:c>
+      <x:c r="F300" s="23" t="n">
+        <x:v>2770.2</x:v>
+      </x:c>
+      <x:c r="G300" s="23" t="n">
+        <x:f>ROUND(F300-F299,1)</x:f>
+        <x:v>-34.4</x:v>
+      </x:c>
+      <x:c r="H300" s="24" t="n">
+        <x:f>IFERROR(F300/F299-1,"")</x:f>
+        <x:v>-0.012265563716751138</x:v>
+      </x:c>
+      <x:c r="I300" s="23" t="n">
+        <x:f>ROUND(D300-E300,1)</x:f>
+        <x:v>57.8</x:v>
+      </x:c>
+      <x:c r="J300" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
+      <x:c r="K300" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B299" s="30" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C299" s="30"/>
-      <x:c r="D299" s="30"/>
-      <x:c r="E299" s="30"/>
-      <x:c r="F299" s="30"/>
-      <x:c r="G299" s="30"/>
-      <x:c r="H299" s="30"/>
-      <x:c r="I299" s="32" t="n">
-        <x:f>ROUND(SUM(I262:I298),1)</x:f>
-        <x:v>3342.6</x:v>
-      </x:c>
-      <x:c r="J299" s="30"/>
-      <x:c r="K299" s="30"/>
-    </x:row>
-    <x:row r="300">
-      <x:c r="A300" s="31" t="str">
+      <x:c r="B301" s="30" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C301" s="30"/>
+      <x:c r="D301" s="30"/>
+      <x:c r="E301" s="30"/>
+      <x:c r="F301" s="30"/>
+      <x:c r="G301" s="30"/>
+      <x:c r="H301" s="30"/>
+      <x:c r="I301" s="32" t="n">
+        <x:f>ROUND(SUM(I263:I300),1)</x:f>
+        <x:v>3400.4</x:v>
+      </x:c>
+      <x:c r="J301" s="30"/>
+      <x:c r="K301" s="30"/>
+    </x:row>
+    <x:row r="302">
+      <x:c r="A302" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B300" s="30"/>
-      <x:c r="C300" s="30"/>
-      <x:c r="D300" s="30"/>
-      <x:c r="E300" s="30"/>
-      <x:c r="F300" s="30"/>
-      <x:c r="G300" s="30"/>
-      <x:c r="H300" s="30"/>
-      <x:c r="I300" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I262:I298),0),1)</x:f>
-        <x:v>90.3</x:v>
-      </x:c>
-      <x:c r="J300" s="30"/>
-      <x:c r="K300" s="30"/>
-    </x:row>
-    <x:row r="302">
-      <x:c r="A302" s="17" t="str">
+      <x:c r="B302" s="30"/>
+      <x:c r="C302" s="30"/>
+      <x:c r="D302" s="30"/>
+      <x:c r="E302" s="30"/>
+      <x:c r="F302" s="30"/>
+      <x:c r="G302" s="30"/>
+      <x:c r="H302" s="30"/>
+      <x:c r="I302" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I263:I300),0),1)</x:f>
+        <x:v>89.5</x:v>
+      </x:c>
+      <x:c r="J302" s="30"/>
+      <x:c r="K302" s="30"/>
+    </x:row>
+    <x:row r="304">
+      <x:c r="A304" s="17" t="str">
         <x:v>碳酸锂2610</x:v>
       </x:c>
-      <x:c r="B302" s="17"/>
-      <x:c r="C302" s="17"/>
-      <x:c r="D302" s="17"/>
-      <x:c r="E302" s="17"/>
-      <x:c r="F302" s="17"/>
-      <x:c r="G302" s="17"/>
-      <x:c r="H302" s="17"/>
-      <x:c r="I302" s="17"/>
-      <x:c r="J302" s="17"/>
-      <x:c r="K302" s="17"/>
-    </x:row>
-    <x:row r="303">
-      <x:c r="A303" s="20" t="str">
+      <x:c r="B304" s="17"/>
+      <x:c r="C304" s="17"/>
+      <x:c r="D304" s="17"/>
+      <x:c r="E304" s="17"/>
+      <x:c r="F304" s="17"/>
+      <x:c r="G304" s="17"/>
+      <x:c r="H304" s="17"/>
+      <x:c r="I304" s="17"/>
+      <x:c r="J304" s="17"/>
+      <x:c r="K304" s="17"/>
+    </x:row>
+    <x:row r="305">
+      <x:c r="A305" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B303" s="20" t="str">
+      <x:c r="B305" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C303" s="20" t="str">
+      <x:c r="C305" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D303" s="20" t="str">
+      <x:c r="D305" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E303" s="20" t="str">
+      <x:c r="E305" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F303" s="20" t="str">
+      <x:c r="F305" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G303" s="20" t="str">
+      <x:c r="G305" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H303" s="20" t="str">
+      <x:c r="H305" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I303" s="20" t="str">
+      <x:c r="I305" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J303" s="20" t="str">
+      <x:c r="J305" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K303" s="20" t="str">
+      <x:c r="K305" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="304">
-      <x:c r="A304" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B304" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C304" s="23" t="n">
-        <x:v>132800</x:v>
-      </x:c>
-      <x:c r="D304" s="23" t="n">
-        <x:v>150100</x:v>
-      </x:c>
-      <x:c r="E304" s="23" t="n">
-        <x:v>123500</x:v>
-      </x:c>
-      <x:c r="F304" s="23" t="n">
-        <x:v>145600</x:v>
-      </x:c>
-      <x:c r="G304" s="23"/>
-      <x:c r="H304" s="24"/>
-      <x:c r="I304" s="26" t="n">
-        <x:f>ROUND(D304-E304,1)</x:f>
-        <x:v>26600</x:v>
-      </x:c>
-      <x:c r="J304" s="22" t="str">
-        <x:v>LC2610</x:v>
-      </x:c>
-      <x:c r="K304" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="305">
-      <x:c r="A305" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B305" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
-      </x:c>
-      <x:c r="C305" s="23" t="n">
-        <x:v>149180</x:v>
-      </x:c>
-      <x:c r="D305" s="23" t="n">
-        <x:v>175360</x:v>
-      </x:c>
-      <x:c r="E305" s="23" t="n">
-        <x:v>148180</x:v>
-      </x:c>
-      <x:c r="F305" s="23" t="n">
-        <x:v>148180</x:v>
-      </x:c>
-      <x:c r="G305" s="28" t="n">
-        <x:f>ROUND(F305-F304,1)</x:f>
-        <x:v>2580</x:v>
-      </x:c>
-      <x:c r="H305" s="24" t="n">
-        <x:f>IFERROR(F305/F304-1,"")</x:f>
-        <x:v>0.017719780219780157</x:v>
-      </x:c>
-      <x:c r="I305" s="26" t="n">
-        <x:f>ROUND(D305-E305,1)</x:f>
-        <x:v>27180</x:v>
-      </x:c>
-      <x:c r="J305" s="22" t="str">
-        <x:v>LC2610</x:v>
-      </x:c>
-      <x:c r="K305" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B306" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C306" s="23" t="n">
-        <x:v>143000</x:v>
+        <x:v>132800</x:v>
       </x:c>
       <x:c r="D306" s="23" t="n">
-        <x:v>183460</x:v>
+        <x:v>150100</x:v>
       </x:c>
       <x:c r="E306" s="23" t="n">
-        <x:v>143000</x:v>
+        <x:v>123500</x:v>
       </x:c>
       <x:c r="F306" s="23" t="n">
-        <x:v>183460</x:v>
-      </x:c>
-      <x:c r="G306" s="28" t="n">
-        <x:f>ROUND(F306-F305,1)</x:f>
-        <x:v>35280</x:v>
-      </x:c>
-      <x:c r="H306" s="24" t="n">
-        <x:f>IFERROR(F306/F305-1,"")</x:f>
-        <x:v>0.23808881090565537</x:v>
-      </x:c>
+        <x:v>145600</x:v>
+      </x:c>
+      <x:c r="G306" s="23"/>
+      <x:c r="H306" s="24"/>
       <x:c r="I306" s="26" t="n">
         <x:f>ROUND(D306-E306,1)</x:f>
-        <x:v>40460</x:v>
+        <x:v>26600</x:v>
       </x:c>
       <x:c r="J306" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18943,34 +18943,34 @@
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B307" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C307" s="23" t="n">
-        <x:v>189980</x:v>
+        <x:v>149180</x:v>
       </x:c>
       <x:c r="D307" s="23" t="n">
-        <x:v>190020</x:v>
+        <x:v>175360</x:v>
       </x:c>
       <x:c r="E307" s="23" t="n">
-        <x:v>148520</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="F307" s="23" t="n">
-        <x:v>148540</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="G307" s="28" t="n">
         <x:f>ROUND(F307-F306,1)</x:f>
-        <x:v>-34920</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="H307" s="24" t="n">
         <x:f>IFERROR(F307/F306-1,"")</x:f>
-        <x:v>-0.19034121879428756</x:v>
+        <x:v>0.017719780219780157</x:v>
       </x:c>
       <x:c r="I307" s="26" t="n">
         <x:f>ROUND(D307-E307,1)</x:f>
-        <x:v>41500</x:v>
+        <x:v>27180</x:v>
       </x:c>
       <x:c r="J307" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -18981,34 +18981,34 @@
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B308" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C308" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="D308" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="E308" s="23" t="n">
-        <x:v>124760</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="F308" s="23" t="n">
-        <x:v>131160</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="G308" s="28" t="n">
         <x:f>ROUND(F308-F307,1)</x:f>
-        <x:v>-17380</x:v>
+        <x:v>35280</x:v>
       </x:c>
       <x:c r="H308" s="24" t="n">
         <x:f>IFERROR(F308/F307-1,"")</x:f>
-        <x:v>-0.11700552039854584</x:v>
+        <x:v>0.23808881090565537</x:v>
       </x:c>
       <x:c r="I308" s="26" t="n">
         <x:f>ROUND(D308-E308,1)</x:f>
-        <x:v>28240</x:v>
+        <x:v>40460</x:v>
       </x:c>
       <x:c r="J308" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19019,34 +19019,34 @@
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B309" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C309" s="23" t="n">
-        <x:v>134660</x:v>
+        <x:v>189980</x:v>
       </x:c>
       <x:c r="D309" s="23" t="n">
-        <x:v>152380</x:v>
+        <x:v>190020</x:v>
       </x:c>
       <x:c r="E309" s="23" t="n">
-        <x:v>133580</x:v>
+        <x:v>148520</x:v>
       </x:c>
       <x:c r="F309" s="23" t="n">
-        <x:v>152380</x:v>
+        <x:v>148540</x:v>
       </x:c>
       <x:c r="G309" s="28" t="n">
         <x:f>ROUND(F309-F308,1)</x:f>
-        <x:v>21220</x:v>
+        <x:v>-34920</x:v>
       </x:c>
       <x:c r="H309" s="24" t="n">
         <x:f>IFERROR(F309/F308-1,"")</x:f>
-        <x:v>0.1617871302226288</x:v>
+        <x:v>-0.19034121879428756</x:v>
       </x:c>
       <x:c r="I309" s="26" t="n">
         <x:f>ROUND(D309-E309,1)</x:f>
-        <x:v>18800</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="J309" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19057,72 +19057,72 @@
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B310" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C310" s="23" t="n">
-        <x:v>165060</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="D310" s="23" t="n">
-        <x:v>187920</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="E310" s="23" t="n">
-        <x:v>155680</x:v>
+        <x:v>124760</x:v>
       </x:c>
       <x:c r="F310" s="23" t="n">
-        <x:v>175400</x:v>
+        <x:v>131160</x:v>
       </x:c>
       <x:c r="G310" s="28" t="n">
         <x:f>ROUND(F310-F309,1)</x:f>
-        <x:v>23020</x:v>
+        <x:v>-17380</x:v>
       </x:c>
       <x:c r="H310" s="24" t="n">
         <x:f>IFERROR(F310/F309-1,"")</x:f>
-        <x:v>0.1510696941855887</x:v>
+        <x:v>-0.11700552039854584</x:v>
       </x:c>
       <x:c r="I310" s="26" t="n">
         <x:f>ROUND(D310-E310,1)</x:f>
-        <x:v>32240</x:v>
+        <x:v>28240</x:v>
       </x:c>
       <x:c r="J310" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K310" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B311" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C311" s="23" t="n">
-        <x:v>175800</x:v>
+        <x:v>134660</x:v>
       </x:c>
       <x:c r="D311" s="23" t="n">
-        <x:v>177260</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="E311" s="23" t="n">
-        <x:v>144980</x:v>
+        <x:v>133580</x:v>
       </x:c>
       <x:c r="F311" s="23" t="n">
-        <x:v>156580</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="G311" s="28" t="n">
         <x:f>ROUND(F311-F310,1)</x:f>
-        <x:v>-18820</x:v>
+        <x:v>21220</x:v>
       </x:c>
       <x:c r="H311" s="24" t="n">
         <x:f>IFERROR(F311/F310-1,"")</x:f>
-        <x:v>-0.1072976054732041</x:v>
+        <x:v>0.1617871302226288</x:v>
       </x:c>
       <x:c r="I311" s="26" t="n">
         <x:f>ROUND(D311-E311,1)</x:f>
-        <x:v>32280</x:v>
+        <x:v>18800</x:v>
       </x:c>
       <x:c r="J311" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19133,72 +19133,72 @@
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B312" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C312" s="23" t="n">
-        <x:v>145120</x:v>
+        <x:v>165060</x:v>
       </x:c>
       <x:c r="D312" s="23" t="n">
-        <x:v>166800</x:v>
+        <x:v>187920</x:v>
       </x:c>
       <x:c r="E312" s="23" t="n">
-        <x:v>139860</x:v>
+        <x:v>155680</x:v>
       </x:c>
       <x:c r="F312" s="23" t="n">
-        <x:v>151880</x:v>
+        <x:v>175400</x:v>
       </x:c>
       <x:c r="G312" s="28" t="n">
         <x:f>ROUND(F312-F311,1)</x:f>
-        <x:v>-4700</x:v>
+        <x:v>23020</x:v>
       </x:c>
       <x:c r="H312" s="24" t="n">
         <x:f>IFERROR(F312/F311-1,"")</x:f>
-        <x:v>-0.030016604930387047</x:v>
+        <x:v>0.1510696941855887</x:v>
       </x:c>
       <x:c r="I312" s="26" t="n">
         <x:f>ROUND(D312-E312,1)</x:f>
-        <x:v>26940</x:v>
+        <x:v>32240</x:v>
       </x:c>
       <x:c r="J312" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K312" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B313" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C313" s="23" t="n">
-        <x:v>149140</x:v>
+        <x:v>175800</x:v>
       </x:c>
       <x:c r="D313" s="23" t="n">
-        <x:v>159120</x:v>
+        <x:v>177260</x:v>
       </x:c>
       <x:c r="E313" s="23" t="n">
-        <x:v>139640</x:v>
+        <x:v>144980</x:v>
       </x:c>
       <x:c r="F313" s="23" t="n">
-        <x:v>143900</x:v>
+        <x:v>156580</x:v>
       </x:c>
       <x:c r="G313" s="28" t="n">
         <x:f>ROUND(F313-F312,1)</x:f>
-        <x:v>-7980</x:v>
+        <x:v>-18820</x:v>
       </x:c>
       <x:c r="H313" s="24" t="n">
         <x:f>IFERROR(F313/F312-1,"")</x:f>
-        <x:v>-0.052541480115881</x:v>
+        <x:v>-0.1072976054732041</x:v>
       </x:c>
       <x:c r="I313" s="26" t="n">
         <x:f>ROUND(D313-E313,1)</x:f>
-        <x:v>19480</x:v>
+        <x:v>32280</x:v>
       </x:c>
       <x:c r="J313" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19209,34 +19209,34 @@
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B314" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C314" s="23" t="n">
-        <x:v>144460</x:v>
+        <x:v>145120</x:v>
       </x:c>
       <x:c r="D314" s="23" t="n">
-        <x:v>170800</x:v>
+        <x:v>166800</x:v>
       </x:c>
       <x:c r="E314" s="23" t="n">
-        <x:v>139980</x:v>
+        <x:v>139860</x:v>
       </x:c>
       <x:c r="F314" s="23" t="n">
-        <x:v>166540</x:v>
+        <x:v>151880</x:v>
       </x:c>
       <x:c r="G314" s="28" t="n">
         <x:f>ROUND(F314-F313,1)</x:f>
-        <x:v>22640</x:v>
+        <x:v>-4700</x:v>
       </x:c>
       <x:c r="H314" s="24" t="n">
         <x:f>IFERROR(F314/F313-1,"")</x:f>
-        <x:v>0.15733148019457954</x:v>
+        <x:v>-0.030016604930387047</x:v>
       </x:c>
       <x:c r="I314" s="26" t="n">
         <x:f>ROUND(D314-E314,1)</x:f>
-        <x:v>30820</x:v>
+        <x:v>26940</x:v>
       </x:c>
       <x:c r="J314" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19247,34 +19247,34 @@
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B315" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C315" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>149140</x:v>
       </x:c>
       <x:c r="D315" s="23" t="n">
-        <x:v>174540</x:v>
+        <x:v>159120</x:v>
       </x:c>
       <x:c r="E315" s="23" t="n">
-        <x:v>153840</x:v>
+        <x:v>139640</x:v>
       </x:c>
       <x:c r="F315" s="23" t="n">
-        <x:v>157680</x:v>
+        <x:v>143900</x:v>
       </x:c>
       <x:c r="G315" s="28" t="n">
         <x:f>ROUND(F315-F314,1)</x:f>
-        <x:v>-8860</x:v>
+        <x:v>-7980</x:v>
       </x:c>
       <x:c r="H315" s="24" t="n">
         <x:f>IFERROR(F315/F314-1,"")</x:f>
-        <x:v>-0.05320043232856975</x:v>
+        <x:v>-0.052541480115881</x:v>
       </x:c>
       <x:c r="I315" s="26" t="n">
         <x:f>ROUND(D315-E315,1)</x:f>
-        <x:v>20700</x:v>
+        <x:v>19480</x:v>
       </x:c>
       <x:c r="J315" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19285,72 +19285,72 @@
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B316" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C316" s="23" t="n">
-        <x:v>156200</x:v>
+        <x:v>144460</x:v>
       </x:c>
       <x:c r="D316" s="23" t="n">
-        <x:v>164160</x:v>
+        <x:v>170800</x:v>
       </x:c>
       <x:c r="E316" s="23" t="n">
-        <x:v>151640</x:v>
+        <x:v>139980</x:v>
       </x:c>
       <x:c r="F316" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>166540</x:v>
       </x:c>
       <x:c r="G316" s="28" t="n">
         <x:f>ROUND(F316-F315,1)</x:f>
-        <x:v>-1180</x:v>
+        <x:v>22640</x:v>
       </x:c>
       <x:c r="H316" s="24" t="n">
         <x:f>IFERROR(F316/F315-1,"")</x:f>
-        <x:v>-0.007483510908168456</x:v>
+        <x:v>0.15733148019457954</x:v>
       </x:c>
       <x:c r="I316" s="26" t="n">
         <x:f>ROUND(D316-E316,1)</x:f>
-        <x:v>12520</x:v>
+        <x:v>30820</x:v>
       </x:c>
       <x:c r="J316" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K316" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B317" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C317" s="23" t="n">
-        <x:v>156660</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="D317" s="23" t="n">
-        <x:v>176500</x:v>
+        <x:v>174540</x:v>
       </x:c>
       <x:c r="E317" s="23" t="n">
-        <x:v>153040</x:v>
+        <x:v>153840</x:v>
       </x:c>
       <x:c r="F317" s="23" t="n">
-        <x:v>176360</x:v>
+        <x:v>157680</x:v>
       </x:c>
       <x:c r="G317" s="28" t="n">
         <x:f>ROUND(F317-F316,1)</x:f>
-        <x:v>19860</x:v>
+        <x:v>-8860</x:v>
       </x:c>
       <x:c r="H317" s="24" t="n">
         <x:f>IFERROR(F317/F316-1,"")</x:f>
-        <x:v>0.12690095846645377</x:v>
+        <x:v>-0.05320043232856975</x:v>
       </x:c>
       <x:c r="I317" s="26" t="n">
         <x:f>ROUND(D317-E317,1)</x:f>
-        <x:v>23460</x:v>
+        <x:v>20700</x:v>
       </x:c>
       <x:c r="J317" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19361,212 +19361,212 @@
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B318" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C318" s="23" t="n">
-        <x:v>174080</x:v>
+        <x:v>156200</x:v>
       </x:c>
       <x:c r="D318" s="23" t="n">
-        <x:v>180920</x:v>
+        <x:v>164160</x:v>
       </x:c>
       <x:c r="E318" s="23" t="n">
-        <x:v>169000</x:v>
+        <x:v>151640</x:v>
       </x:c>
       <x:c r="F318" s="23" t="n">
-        <x:v>176960</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="G318" s="28" t="n">
         <x:f>ROUND(F318-F317,1)</x:f>
-        <x:v>600</x:v>
+        <x:v>-1180</x:v>
       </x:c>
       <x:c r="H318" s="24" t="n">
         <x:f>IFERROR(F318/F317-1,"")</x:f>
-        <x:v>0.0034021320027217694</x:v>
+        <x:v>-0.007483510908168456</x:v>
       </x:c>
       <x:c r="I318" s="26" t="n">
         <x:f>ROUND(D318-E318,1)</x:f>
-        <x:v>11920</x:v>
+        <x:v>12520</x:v>
       </x:c>
       <x:c r="J318" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K318" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B319" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C319" s="23" t="n">
-        <x:v>176960</x:v>
+        <x:v>156660</x:v>
       </x:c>
       <x:c r="D319" s="23" t="n">
-        <x:v>188840</x:v>
+        <x:v>176500</x:v>
       </x:c>
       <x:c r="E319" s="23" t="n">
-        <x:v>172640</x:v>
+        <x:v>153040</x:v>
       </x:c>
       <x:c r="F319" s="23" t="n">
-        <x:v>188840</x:v>
+        <x:v>176360</x:v>
       </x:c>
       <x:c r="G319" s="28" t="n">
         <x:f>ROUND(F319-F318,1)</x:f>
-        <x:v>11880</x:v>
+        <x:v>19860</x:v>
       </x:c>
       <x:c r="H319" s="24" t="n">
         <x:f>IFERROR(F319/F318-1,"")</x:f>
-        <x:v>0.06713381555153708</x:v>
+        <x:v>0.12690095846645377</x:v>
       </x:c>
       <x:c r="I319" s="26" t="n">
         <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>16200</x:v>
+        <x:v>23460</x:v>
       </x:c>
       <x:c r="J319" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K319" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B320" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C320" s="23" t="n">
-        <x:v>191300</x:v>
+        <x:v>174080</x:v>
       </x:c>
       <x:c r="D320" s="23" t="n">
-        <x:v>204640</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="E320" s="23" t="n">
-        <x:v>191300</x:v>
+        <x:v>169000</x:v>
       </x:c>
       <x:c r="F320" s="23" t="n">
-        <x:v>196100</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="G320" s="28" t="n">
         <x:f>ROUND(F320-F319,1)</x:f>
-        <x:v>7260</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H320" s="24" t="n">
         <x:f>IFERROR(F320/F319-1,"")</x:f>
-        <x:v>0.038445244651556854</x:v>
+        <x:v>0.0034021320027217694</x:v>
       </x:c>
       <x:c r="I320" s="26" t="n">
         <x:f>ROUND(D320-E320,1)</x:f>
-        <x:v>13340</x:v>
+        <x:v>11920</x:v>
       </x:c>
       <x:c r="J320" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K320" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B321" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C321" s="23" t="n">
-        <x:v>195080</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="D321" s="23" t="n">
-        <x:v>209040</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="E321" s="23" t="n">
-        <x:v>187240</x:v>
+        <x:v>172640</x:v>
       </x:c>
       <x:c r="F321" s="23" t="n">
-        <x:v>189440</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="G321" s="28" t="n">
         <x:f>ROUND(F321-F320,1)</x:f>
-        <x:v>-6660</x:v>
+        <x:v>11880</x:v>
       </x:c>
       <x:c r="H321" s="24" t="n">
         <x:f>IFERROR(F321/F320-1,"")</x:f>
-        <x:v>-0.03396226415094339</x:v>
+        <x:v>0.06713381555153708</x:v>
       </x:c>
       <x:c r="I321" s="26" t="n">
         <x:f>ROUND(D321-E321,1)</x:f>
-        <x:v>21800</x:v>
+        <x:v>16200</x:v>
       </x:c>
       <x:c r="J321" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K321" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B322" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C322" s="23" t="n">
-        <x:v>190060</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="D322" s="23" t="n">
-        <x:v>193820</x:v>
+        <x:v>204640</x:v>
       </x:c>
       <x:c r="E322" s="23" t="n">
-        <x:v>175520</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="F322" s="23" t="n">
-        <x:v>185280</x:v>
+        <x:v>196100</x:v>
       </x:c>
       <x:c r="G322" s="28" t="n">
         <x:f>ROUND(F322-F321,1)</x:f>
-        <x:v>-4160</x:v>
+        <x:v>7260</x:v>
       </x:c>
       <x:c r="H322" s="24" t="n">
         <x:f>IFERROR(F322/F321-1,"")</x:f>
-        <x:v>-0.02195945945945943</x:v>
+        <x:v>0.038445244651556854</x:v>
       </x:c>
       <x:c r="I322" s="26" t="n">
         <x:f>ROUND(D322-E322,1)</x:f>
-        <x:v>18300</x:v>
+        <x:v>13340</x:v>
       </x:c>
       <x:c r="J322" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K322" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B323" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C323" s="23" t="n">
-        <x:v>185380</x:v>
+        <x:v>195080</x:v>
       </x:c>
       <x:c r="D323" s="23" t="n">
-        <x:v>188320</x:v>
+        <x:v>209040</x:v>
       </x:c>
       <x:c r="E323" s="23" t="n">
-        <x:v>172500</x:v>
+        <x:v>187240</x:v>
       </x:c>
       <x:c r="F323" s="23" t="n">
-        <x:v>178620</x:v>
+        <x:v>189440</x:v>
       </x:c>
       <x:c r="G323" s="28" t="n">
         <x:f>ROUND(F323-F322,1)</x:f>
@@ -19574,11 +19574,11 @@
       </x:c>
       <x:c r="H323" s="24" t="n">
         <x:f>IFERROR(F323/F322-1,"")</x:f>
-        <x:v>-0.035945595854922296</x:v>
+        <x:v>-0.03396226415094339</x:v>
       </x:c>
       <x:c r="I323" s="26" t="n">
         <x:f>ROUND(D323-E323,1)</x:f>
-        <x:v>15820</x:v>
+        <x:v>21800</x:v>
       </x:c>
       <x:c r="J323" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19589,34 +19589,34 @@
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B324" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C324" s="23" t="n">
-        <x:v>180920</x:v>
+        <x:v>190060</x:v>
       </x:c>
       <x:c r="D324" s="23" t="n">
-        <x:v>182940</x:v>
+        <x:v>193820</x:v>
       </x:c>
       <x:c r="E324" s="23" t="n">
-        <x:v>158140</x:v>
+        <x:v>175520</x:v>
       </x:c>
       <x:c r="F324" s="23" t="n">
-        <x:v>165460</x:v>
+        <x:v>185280</x:v>
       </x:c>
       <x:c r="G324" s="28" t="n">
         <x:f>ROUND(F324-F323,1)</x:f>
-        <x:v>-13160</x:v>
+        <x:v>-4160</x:v>
       </x:c>
       <x:c r="H324" s="24" t="n">
         <x:f>IFERROR(F324/F323-1,"")</x:f>
-        <x:v>-0.07367596013884226</x:v>
+        <x:v>-0.02195945945945943</x:v>
       </x:c>
       <x:c r="I324" s="26" t="n">
         <x:f>ROUND(D324-E324,1)</x:f>
-        <x:v>24800</x:v>
+        <x:v>18300</x:v>
       </x:c>
       <x:c r="J324" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19627,34 +19627,34 @@
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B325" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C325" s="23" t="n">
-        <x:v>162800</x:v>
+        <x:v>185380</x:v>
       </x:c>
       <x:c r="D325" s="23" t="n">
-        <x:v>178860</x:v>
+        <x:v>188320</x:v>
       </x:c>
       <x:c r="E325" s="23" t="n">
-        <x:v>161280</x:v>
+        <x:v>172500</x:v>
       </x:c>
       <x:c r="F325" s="23" t="n">
-        <x:v>175780</x:v>
+        <x:v>178620</x:v>
       </x:c>
       <x:c r="G325" s="28" t="n">
         <x:f>ROUND(F325-F324,1)</x:f>
-        <x:v>10320</x:v>
+        <x:v>-6660</x:v>
       </x:c>
       <x:c r="H325" s="24" t="n">
         <x:f>IFERROR(F325/F324-1,"")</x:f>
-        <x:v>0.06237157016801653</x:v>
+        <x:v>-0.035945595854922296</x:v>
       </x:c>
       <x:c r="I325" s="26" t="n">
         <x:f>ROUND(D325-E325,1)</x:f>
-        <x:v>17580</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="J325" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19665,72 +19665,72 @@
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B326" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C326" s="23" t="n">
-        <x:v>176460</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="D326" s="23" t="n">
-        <x:v>178560</x:v>
+        <x:v>182940</x:v>
       </x:c>
       <x:c r="E326" s="23" t="n">
-        <x:v>160560</x:v>
+        <x:v>158140</x:v>
       </x:c>
       <x:c r="F326" s="23" t="n">
-        <x:v>161400</x:v>
+        <x:v>165460</x:v>
       </x:c>
       <x:c r="G326" s="28" t="n">
         <x:f>ROUND(F326-F325,1)</x:f>
-        <x:v>-14380</x:v>
+        <x:v>-13160</x:v>
       </x:c>
       <x:c r="H326" s="24" t="n">
         <x:f>IFERROR(F326/F325-1,"")</x:f>
-        <x:v>-0.0818068039594948</x:v>
+        <x:v>-0.07367596013884226</x:v>
       </x:c>
       <x:c r="I326" s="26" t="n">
         <x:f>ROUND(D326-E326,1)</x:f>
-        <x:v>18000</x:v>
+        <x:v>24800</x:v>
       </x:c>
       <x:c r="J326" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K326" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B327" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C327" s="23" t="n">
-        <x:v>161000</x:v>
+        <x:v>162800</x:v>
       </x:c>
       <x:c r="D327" s="23" t="n">
-        <x:v>163880</x:v>
+        <x:v>178860</x:v>
       </x:c>
       <x:c r="E327" s="23" t="n">
-        <x:v>145360</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="F327" s="23" t="n">
-        <x:v>151140</x:v>
+        <x:v>175780</x:v>
       </x:c>
       <x:c r="G327" s="28" t="n">
         <x:f>ROUND(F327-F326,1)</x:f>
-        <x:v>-10260</x:v>
+        <x:v>10320</x:v>
       </x:c>
       <x:c r="H327" s="24" t="n">
         <x:f>IFERROR(F327/F326-1,"")</x:f>
-        <x:v>-0.06356877323420074</x:v>
+        <x:v>0.06237157016801653</x:v>
       </x:c>
       <x:c r="I327" s="26" t="n">
         <x:f>ROUND(D327-E327,1)</x:f>
-        <x:v>18520</x:v>
+        <x:v>17580</x:v>
       </x:c>
       <x:c r="J327" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19741,72 +19741,72 @@
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B328" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C328" s="23" t="n">
-        <x:v>148420</x:v>
+        <x:v>176460</x:v>
       </x:c>
       <x:c r="D328" s="23" t="n">
-        <x:v>172120</x:v>
+        <x:v>178560</x:v>
       </x:c>
       <x:c r="E328" s="23" t="n">
-        <x:v>146000</x:v>
+        <x:v>160560</x:v>
       </x:c>
       <x:c r="F328" s="23" t="n">
-        <x:v>168600</x:v>
+        <x:v>161400</x:v>
       </x:c>
       <x:c r="G328" s="28" t="n">
         <x:f>ROUND(F328-F327,1)</x:f>
-        <x:v>17460</x:v>
+        <x:v>-14380</x:v>
       </x:c>
       <x:c r="H328" s="24" t="n">
         <x:f>IFERROR(F328/F327-1,"")</x:f>
-        <x:v>0.1155220325526003</x:v>
+        <x:v>-0.0818068039594948</x:v>
       </x:c>
       <x:c r="I328" s="26" t="n">
         <x:f>ROUND(D328-E328,1)</x:f>
-        <x:v>26120</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="J328" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K328" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B329" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C329" s="23" t="n">
-        <x:v>174900</x:v>
+        <x:v>161000</x:v>
       </x:c>
       <x:c r="D329" s="23" t="n">
-        <x:v>174900</x:v>
+        <x:v>163880</x:v>
       </x:c>
       <x:c r="E329" s="23" t="n">
-        <x:v>150860</x:v>
+        <x:v>145360</x:v>
       </x:c>
       <x:c r="F329" s="23" t="n">
-        <x:v>151600</x:v>
+        <x:v>151140</x:v>
       </x:c>
       <x:c r="G329" s="28" t="n">
         <x:f>ROUND(F329-F328,1)</x:f>
-        <x:v>-17000</x:v>
+        <x:v>-10260</x:v>
       </x:c>
       <x:c r="H329" s="24" t="n">
         <x:f>IFERROR(F329/F328-1,"")</x:f>
-        <x:v>-0.10083036773428233</x:v>
+        <x:v>-0.06356877323420074</x:v>
       </x:c>
       <x:c r="I329" s="26" t="n">
         <x:f>ROUND(D329-E329,1)</x:f>
-        <x:v>24040</x:v>
+        <x:v>18520</x:v>
       </x:c>
       <x:c r="J329" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19817,34 +19817,34 @@
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B330" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C330" s="23" t="n">
-        <x:v>150300</x:v>
+        <x:v>148420</x:v>
       </x:c>
       <x:c r="D330" s="23" t="n">
-        <x:v>155660</x:v>
+        <x:v>172120</x:v>
       </x:c>
       <x:c r="E330" s="23" t="n">
-        <x:v>145460</x:v>
+        <x:v>146000</x:v>
       </x:c>
       <x:c r="F330" s="23" t="n">
-        <x:v>149740</x:v>
+        <x:v>168600</x:v>
       </x:c>
       <x:c r="G330" s="28" t="n">
         <x:f>ROUND(F330-F329,1)</x:f>
-        <x:v>-1860</x:v>
+        <x:v>17460</x:v>
       </x:c>
       <x:c r="H330" s="24" t="n">
         <x:f>IFERROR(F330/F329-1,"")</x:f>
-        <x:v>-0.012269129287598934</x:v>
+        <x:v>0.1155220325526003</x:v>
       </x:c>
       <x:c r="I330" s="26" t="n">
         <x:f>ROUND(D330-E330,1)</x:f>
-        <x:v>10200</x:v>
+        <x:v>26120</x:v>
       </x:c>
       <x:c r="J330" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19855,34 +19855,34 @@
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B331" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C331" s="23" t="n">
-        <x:v>152520</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="D331" s="23" t="n">
-        <x:v>153880</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="E331" s="23" t="n">
-        <x:v>135040</x:v>
+        <x:v>150860</x:v>
       </x:c>
       <x:c r="F331" s="23" t="n">
-        <x:v>142920</x:v>
+        <x:v>151600</x:v>
       </x:c>
       <x:c r="G331" s="28" t="n">
         <x:f>ROUND(F331-F330,1)</x:f>
-        <x:v>-6820</x:v>
+        <x:v>-17000</x:v>
       </x:c>
       <x:c r="H331" s="24" t="n">
         <x:f>IFERROR(F331/F330-1,"")</x:f>
-        <x:v>-0.04554561239481769</x:v>
+        <x:v>-0.10083036773428233</x:v>
       </x:c>
       <x:c r="I331" s="26" t="n">
         <x:f>ROUND(D331-E331,1)</x:f>
-        <x:v>18840</x:v>
+        <x:v>24040</x:v>
       </x:c>
       <x:c r="J331" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19893,34 +19893,34 @@
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B332" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C332" s="23" t="n">
-        <x:v>144340</x:v>
+        <x:v>150300</x:v>
       </x:c>
       <x:c r="D332" s="23" t="n">
-        <x:v>148600</x:v>
+        <x:v>155660</x:v>
       </x:c>
       <x:c r="E332" s="23" t="n">
-        <x:v>137000</x:v>
+        <x:v>145460</x:v>
       </x:c>
       <x:c r="F332" s="23" t="n">
-        <x:v>137000</x:v>
+        <x:v>149740</x:v>
       </x:c>
       <x:c r="G332" s="28" t="n">
         <x:f>ROUND(F332-F331,1)</x:f>
-        <x:v>-5920</x:v>
+        <x:v>-1860</x:v>
       </x:c>
       <x:c r="H332" s="24" t="n">
         <x:f>IFERROR(F332/F331-1,"")</x:f>
-        <x:v>-0.04142177441925554</x:v>
+        <x:v>-0.012269129287598934</x:v>
       </x:c>
       <x:c r="I332" s="26" t="n">
         <x:f>ROUND(D332-E332,1)</x:f>
-        <x:v>11600</x:v>
+        <x:v>10200</x:v>
       </x:c>
       <x:c r="J332" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19931,34 +19931,34 @@
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B333" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C333" s="23" t="n">
-        <x:v>137200</x:v>
+        <x:v>152520</x:v>
       </x:c>
       <x:c r="D333" s="23" t="n">
-        <x:v>144100</x:v>
+        <x:v>153880</x:v>
       </x:c>
       <x:c r="E333" s="23" t="n">
         <x:v>135040</x:v>
       </x:c>
       <x:c r="F333" s="23" t="n">
-        <x:v>139320</x:v>
+        <x:v>142920</x:v>
       </x:c>
       <x:c r="G333" s="28" t="n">
         <x:f>ROUND(F333-F332,1)</x:f>
-        <x:v>2320</x:v>
+        <x:v>-6820</x:v>
       </x:c>
       <x:c r="H333" s="24" t="n">
         <x:f>IFERROR(F333/F332-1,"")</x:f>
-        <x:v>0.016934306569343027</x:v>
+        <x:v>-0.04554561239481769</x:v>
       </x:c>
       <x:c r="I333" s="26" t="n">
         <x:f>ROUND(D333-E333,1)</x:f>
-        <x:v>9060</x:v>
+        <x:v>18840</x:v>
       </x:c>
       <x:c r="J333" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19969,34 +19969,34 @@
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B334" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C334" s="23" t="n">
-        <x:v>139320</x:v>
+        <x:v>144340</x:v>
       </x:c>
       <x:c r="D334" s="23" t="n">
-        <x:v>154560</x:v>
+        <x:v>148600</x:v>
       </x:c>
       <x:c r="E334" s="23" t="n">
-        <x:v>139300</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="F334" s="23" t="n">
-        <x:v>153980</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="G334" s="28" t="n">
         <x:f>ROUND(F334-F333,1)</x:f>
-        <x:v>14660</x:v>
+        <x:v>-5920</x:v>
       </x:c>
       <x:c r="H334" s="24" t="n">
         <x:f>IFERROR(F334/F333-1,"")</x:f>
-        <x:v>0.10522538041917895</x:v>
+        <x:v>-0.04142177441925554</x:v>
       </x:c>
       <x:c r="I334" s="26" t="n">
         <x:f>ROUND(D334-E334,1)</x:f>
-        <x:v>15260</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="J334" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20007,34 +20007,34 @@
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B335" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C335" s="23" t="n">
-        <x:v>152940</x:v>
+        <x:v>137200</x:v>
       </x:c>
       <x:c r="D335" s="23" t="n">
-        <x:v>157400</x:v>
+        <x:v>144100</x:v>
       </x:c>
       <x:c r="E335" s="23" t="n">
-        <x:v>148700</x:v>
+        <x:v>135040</x:v>
       </x:c>
       <x:c r="F335" s="23" t="n">
-        <x:v>156380</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="G335" s="28" t="n">
         <x:f>ROUND(F335-F334,1)</x:f>
-        <x:v>2400</x:v>
+        <x:v>2320</x:v>
       </x:c>
       <x:c r="H335" s="24" t="n">
         <x:f>IFERROR(F335/F334-1,"")</x:f>
-        <x:v>0.015586439797376173</x:v>
+        <x:v>0.016934306569343027</x:v>
       </x:c>
       <x:c r="I335" s="26" t="n">
         <x:f>ROUND(D335-E335,1)</x:f>
-        <x:v>8700</x:v>
+        <x:v>9060</x:v>
       </x:c>
       <x:c r="J335" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20045,34 +20045,34 @@
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B336" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C336" s="23" t="n">
-        <x:v>158800</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="D336" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="E336" s="23" t="n">
-        <x:v>147600</x:v>
+        <x:v>139300</x:v>
       </x:c>
       <x:c r="F336" s="23" t="n">
-        <x:v>157940</x:v>
+        <x:v>153980</x:v>
       </x:c>
       <x:c r="G336" s="28" t="n">
         <x:f>ROUND(F336-F335,1)</x:f>
-        <x:v>1560</x:v>
+        <x:v>14660</x:v>
       </x:c>
       <x:c r="H336" s="24" t="n">
         <x:f>IFERROR(F336/F335-1,"")</x:f>
-        <x:v>0.009975700217419003</x:v>
+        <x:v>0.10522538041917895</x:v>
       </x:c>
       <x:c r="I336" s="26" t="n">
         <x:f>ROUND(D336-E336,1)</x:f>
-        <x:v>12900</x:v>
+        <x:v>15260</x:v>
       </x:c>
       <x:c r="J336" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20083,34 +20083,34 @@
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B337" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C337" s="23" t="n">
-        <x:v>157500</x:v>
+        <x:v>152940</x:v>
       </x:c>
       <x:c r="D337" s="23" t="n">
-        <x:v>161280</x:v>
+        <x:v>157400</x:v>
       </x:c>
       <x:c r="E337" s="23" t="n">
-        <x:v>140220</x:v>
+        <x:v>148700</x:v>
       </x:c>
       <x:c r="F337" s="23" t="n">
-        <x:v>142000</x:v>
+        <x:v>156380</x:v>
       </x:c>
       <x:c r="G337" s="28" t="n">
         <x:f>ROUND(F337-F336,1)</x:f>
-        <x:v>-15940</x:v>
+        <x:v>2400</x:v>
       </x:c>
       <x:c r="H337" s="24" t="n">
         <x:f>IFERROR(F337/F336-1,"")</x:f>
-        <x:v>-0.10092440167152084</x:v>
+        <x:v>0.015586439797376173</x:v>
       </x:c>
       <x:c r="I337" s="26" t="n">
         <x:f>ROUND(D337-E337,1)</x:f>
-        <x:v>21060</x:v>
+        <x:v>8700</x:v>
       </x:c>
       <x:c r="J337" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20121,34 +20121,34 @@
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B338" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C338" s="23" t="n">
-        <x:v>141000</x:v>
+        <x:v>158800</x:v>
       </x:c>
       <x:c r="D338" s="23" t="n">
-        <x:v>143540</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="E338" s="23" t="n">
-        <x:v>127120</x:v>
+        <x:v>147600</x:v>
       </x:c>
       <x:c r="F338" s="23" t="n">
-        <x:v>134340</x:v>
+        <x:v>157940</x:v>
       </x:c>
       <x:c r="G338" s="28" t="n">
         <x:f>ROUND(F338-F337,1)</x:f>
-        <x:v>-7660</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="H338" s="24" t="n">
         <x:f>IFERROR(F338/F337-1,"")</x:f>
-        <x:v>-0.05394366197183098</x:v>
+        <x:v>0.009975700217419003</x:v>
       </x:c>
       <x:c r="I338" s="26" t="n">
         <x:f>ROUND(D338-E338,1)</x:f>
-        <x:v>16420</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="J338" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20159,34 +20159,34 @@
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B339" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C339" s="23" t="n">
-        <x:v>133600</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D339" s="23" t="n">
-        <x:v>135900</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="E339" s="23" t="n">
-        <x:v>126200</x:v>
+        <x:v>140220</x:v>
       </x:c>
       <x:c r="F339" s="23" t="n">
-        <x:v>128580</x:v>
+        <x:v>142000</x:v>
       </x:c>
       <x:c r="G339" s="28" t="n">
         <x:f>ROUND(F339-F338,1)</x:f>
-        <x:v>-5760</x:v>
+        <x:v>-15940</x:v>
       </x:c>
       <x:c r="H339" s="24" t="n">
         <x:f>IFERROR(F339/F338-1,"")</x:f>
-        <x:v>-0.04287628405538191</x:v>
+        <x:v>-0.10092440167152084</x:v>
       </x:c>
       <x:c r="I339" s="26" t="n">
         <x:f>ROUND(D339-E339,1)</x:f>
-        <x:v>9700</x:v>
+        <x:v>21060</x:v>
       </x:c>
       <x:c r="J339" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20197,117 +20197,193 @@
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="22" t="n">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B340" s="22" t="str">
-        <x:v>9月21日-9月24日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C340" s="23" t="n">
-        <x:v>128500</x:v>
+        <x:v>141000</x:v>
       </x:c>
       <x:c r="D340" s="23" t="n">
-        <x:v>136560</x:v>
+        <x:v>143540</x:v>
       </x:c>
       <x:c r="E340" s="23" t="n">
-        <x:v>125000</x:v>
+        <x:v>127120</x:v>
       </x:c>
       <x:c r="F340" s="23" t="n">
-        <x:v>125980</x:v>
+        <x:v>134340</x:v>
       </x:c>
       <x:c r="G340" s="28" t="n">
         <x:f>ROUND(F340-F339,1)</x:f>
-        <x:v>-2600</x:v>
+        <x:v>-7660</x:v>
       </x:c>
       <x:c r="H340" s="24" t="n">
         <x:f>IFERROR(F340/F339-1,"")</x:f>
-        <x:v>-0.02022087416394458</x:v>
+        <x:v>-0.05394366197183098</x:v>
       </x:c>
       <x:c r="I340" s="26" t="n">
         <x:f>ROUND(D340-E340,1)</x:f>
-        <x:v>11560</x:v>
+        <x:v>16420</x:v>
       </x:c>
       <x:c r="J340" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K340" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="22" t="n">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B341" s="22" t="str">
-        <x:v>9月28日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C341" s="23" t="n">
-        <x:v>124280</x:v>
+        <x:v>133600</x:v>
       </x:c>
       <x:c r="D341" s="23" t="n">
-        <x:v>124660</x:v>
+        <x:v>135900</x:v>
       </x:c>
       <x:c r="E341" s="23" t="n">
-        <x:v>119520</x:v>
+        <x:v>126200</x:v>
       </x:c>
       <x:c r="F341" s="23" t="n">
-        <x:v>119980</x:v>
+        <x:v>128580</x:v>
       </x:c>
       <x:c r="G341" s="28" t="n">
         <x:f>ROUND(F341-F340,1)</x:f>
-        <x:v>-6000</x:v>
+        <x:v>-5760</x:v>
       </x:c>
       <x:c r="H341" s="24" t="n">
         <x:f>IFERROR(F341/F340-1,"")</x:f>
-        <x:v>-0.04762660739799973</x:v>
-      </x:c>
-      <x:c r="I341" s="23" t="n">
+        <x:v>-0.04287628405538191</x:v>
+      </x:c>
+      <x:c r="I341" s="26" t="n">
         <x:f>ROUND(D341-E341,1)</x:f>
-        <x:v>5140</x:v>
+        <x:v>9700</x:v>
       </x:c>
       <x:c r="J341" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K341" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342">
+      <x:c r="A342" s="22" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B342" s="22" t="str">
+        <x:v>9月21日-9月24日</x:v>
+      </x:c>
+      <x:c r="C342" s="23" t="n">
+        <x:v>128500</x:v>
+      </x:c>
+      <x:c r="D342" s="23" t="n">
+        <x:v>136560</x:v>
+      </x:c>
+      <x:c r="E342" s="23" t="n">
+        <x:v>125000</x:v>
+      </x:c>
+      <x:c r="F342" s="23" t="n">
+        <x:v>125980</x:v>
+      </x:c>
+      <x:c r="G342" s="28" t="n">
+        <x:f>ROUND(F342-F341,1)</x:f>
+        <x:v>-2600</x:v>
+      </x:c>
+      <x:c r="H342" s="24" t="n">
+        <x:f>IFERROR(F342/F341-1,"")</x:f>
+        <x:v>-0.02022087416394458</x:v>
+      </x:c>
+      <x:c r="I342" s="26" t="n">
+        <x:f>ROUND(D342-E342,1)</x:f>
+        <x:v>11560</x:v>
+      </x:c>
+      <x:c r="J342" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K342" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343">
+      <x:c r="A343" s="22" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B343" s="22" t="str">
+        <x:v>9月28日</x:v>
+      </x:c>
+      <x:c r="C343" s="23" t="n">
+        <x:v>124280</x:v>
+      </x:c>
+      <x:c r="D343" s="23" t="n">
+        <x:v>124660</x:v>
+      </x:c>
+      <x:c r="E343" s="23" t="n">
+        <x:v>119520</x:v>
+      </x:c>
+      <x:c r="F343" s="23" t="n">
+        <x:v>119980</x:v>
+      </x:c>
+      <x:c r="G343" s="28" t="n">
+        <x:f>ROUND(F343-F342,1)</x:f>
+        <x:v>-6000</x:v>
+      </x:c>
+      <x:c r="H343" s="24" t="n">
+        <x:f>IFERROR(F343/F342-1,"")</x:f>
+        <x:v>-0.04762660739799973</x:v>
+      </x:c>
+      <x:c r="I343" s="23" t="n">
+        <x:f>ROUND(D343-E343,1)</x:f>
+        <x:v>5140</x:v>
+      </x:c>
+      <x:c r="J343" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K343" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="342">
-      <x:c r="A342" s="31" t="str">
+    <x:row r="344">
+      <x:c r="A344" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B342" s="30" t="n">
+      <x:c r="B344" s="30" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C342" s="30"/>
-      <x:c r="D342" s="30"/>
-      <x:c r="E342" s="30"/>
-      <x:c r="F342" s="30"/>
-      <x:c r="G342" s="30"/>
-      <x:c r="H342" s="30"/>
-      <x:c r="I342" s="32" t="n">
-        <x:f>ROUND(SUM(I304:I341),1)</x:f>
+      <x:c r="C344" s="30"/>
+      <x:c r="D344" s="30"/>
+      <x:c r="E344" s="30"/>
+      <x:c r="F344" s="30"/>
+      <x:c r="G344" s="30"/>
+      <x:c r="H344" s="30"/>
+      <x:c r="I344" s="32" t="n">
+        <x:f>ROUND(SUM(I306:I343),1)</x:f>
         <x:v>758100</x:v>
       </x:c>
-      <x:c r="J342" s="30"/>
-      <x:c r="K342" s="30"/>
-    </x:row>
-    <x:row r="343">
-      <x:c r="A343" s="31" t="str">
+      <x:c r="J344" s="30"/>
+      <x:c r="K344" s="30"/>
+    </x:row>
+    <x:row r="345">
+      <x:c r="A345" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B343" s="30"/>
-      <x:c r="C343" s="30"/>
-      <x:c r="D343" s="30"/>
-      <x:c r="E343" s="30"/>
-      <x:c r="F343" s="30"/>
-      <x:c r="G343" s="30"/>
-      <x:c r="H343" s="30"/>
-      <x:c r="I343" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I304:I341),0),1)</x:f>
+      <x:c r="B345" s="30"/>
+      <x:c r="C345" s="30"/>
+      <x:c r="D345" s="30"/>
+      <x:c r="E345" s="30"/>
+      <x:c r="F345" s="30"/>
+      <x:c r="G345" s="30"/>
+      <x:c r="H345" s="30"/>
+      <x:c r="I345" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I306:I343),0),1)</x:f>
         <x:v>19950</x:v>
       </x:c>
-      <x:c r="J343" s="30"/>
-      <x:c r="K343" s="30"/>
+      <x:c r="J345" s="30"/>
+      <x:c r="K345" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -20318,8 +20394,8 @@
     <x:mergeCell ref="A132:K132"/>
     <x:mergeCell ref="A175:K175"/>
     <x:mergeCell ref="A218:K218"/>
-    <x:mergeCell ref="A260:K260"/>
-    <x:mergeCell ref="A302:K302"/>
+    <x:mergeCell ref="A261:K261"/>
+    <x:mergeCell ref="A304:K304"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -63885,30 +63961,48 @@
       </x:c>
     </x:row>
     <x:row r="223">
-      <x:c r="A223" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B223" s="30" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C223" s="30"/>
-      <x:c r="D223" s="30"/>
-      <x:c r="E223" s="30"/>
-      <x:c r="F223" s="30"/>
-      <x:c r="G223" s="30"/>
-      <x:c r="H223" s="30"/>
-      <x:c r="I223" s="30"/>
-      <x:c r="J223" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J222),1)</x:f>
-        <x:v>929</x:v>
-      </x:c>
-      <x:c r="K223" s="30"/>
+      <x:c r="A223" s="22" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B223" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C223" s="22" t="str">
+        <x:v>9月28日</x:v>
+      </x:c>
+      <x:c r="D223" s="23" t="n">
+        <x:v>4365</x:v>
+      </x:c>
+      <x:c r="E223" s="23" t="n">
+        <x:v>4366.8</x:v>
+      </x:c>
+      <x:c r="F223" s="23" t="n">
+        <x:v>4246</x:v>
+      </x:c>
+      <x:c r="G223" s="23" t="n">
+        <x:v>4280.8</x:v>
+      </x:c>
+      <x:c r="H223" s="23" t="n">
+        <x:v>-94.2</x:v>
+      </x:c>
+      <x:c r="I223" s="24" t="n">
+        <x:v>-0.021531428571428535</x:v>
+      </x:c>
+      <x:c r="J223" s="26" t="n">
+        <x:f>ROUND(E223-F223,1)</x:f>
+        <x:v>120.8</x:v>
+      </x:c>
+      <x:c r="K223" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B224" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B224" s="30" t="n">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="C224" s="30"/>
       <x:c r="D224" s="30"/>
       <x:c r="E224" s="30"/>
@@ -63916,11 +64010,29 @@
       <x:c r="G224" s="30"/>
       <x:c r="H224" s="30"/>
       <x:c r="I224" s="30"/>
-      <x:c r="J224" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
-        <x:v>51.6</x:v>
+      <x:c r="J224" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J223),1)</x:f>
+        <x:v>1049.8</x:v>
       </x:c>
       <x:c r="K224" s="30"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B225" s="30"/>
+      <x:c r="C225" s="30"/>
+      <x:c r="D225" s="30"/>
+      <x:c r="E225" s="30"/>
+      <x:c r="F225" s="30"/>
+      <x:c r="G225" s="30"/>
+      <x:c r="H225" s="30"/>
+      <x:c r="I225" s="30"/>
+      <x:c r="J225" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
+        <x:v>55.3</x:v>
+      </x:c>
+      <x:c r="K225" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -71124,30 +71236,48 @@
       </x:c>
     </x:row>
     <x:row r="223">
-      <x:c r="A223" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B223" s="30" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C223" s="30"/>
-      <x:c r="D223" s="30"/>
-      <x:c r="E223" s="30"/>
-      <x:c r="F223" s="30"/>
-      <x:c r="G223" s="30"/>
-      <x:c r="H223" s="30"/>
-      <x:c r="I223" s="30"/>
-      <x:c r="J223" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J222),1)</x:f>
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="K223" s="30"/>
+      <x:c r="A223" s="22" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B223" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C223" s="22" t="str">
+        <x:v>9月28日</x:v>
+      </x:c>
+      <x:c r="D223" s="23" t="n">
+        <x:v>2802</x:v>
+      </x:c>
+      <x:c r="E223" s="23" t="n">
+        <x:v>2803.8</x:v>
+      </x:c>
+      <x:c r="F223" s="23" t="n">
+        <x:v>2746</x:v>
+      </x:c>
+      <x:c r="G223" s="23" t="n">
+        <x:v>2770.2</x:v>
+      </x:c>
+      <x:c r="H223" s="23" t="n">
+        <x:v>-34.4</x:v>
+      </x:c>
+      <x:c r="I223" s="24" t="n">
+        <x:v>-0.012265563716751138</x:v>
+      </x:c>
+      <x:c r="J223" s="23" t="n">
+        <x:f>ROUND(E223-F223,1)</x:f>
+        <x:v>57.8</x:v>
+      </x:c>
+      <x:c r="K223" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B224" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B224" s="30" t="n">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="C224" s="30"/>
       <x:c r="D224" s="30"/>
       <x:c r="E224" s="30"/>
@@ -71155,11 +71285,29 @@
       <x:c r="G224" s="30"/>
       <x:c r="H224" s="30"/>
       <x:c r="I224" s="30"/>
-      <x:c r="J224" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J222),0),1)</x:f>
-        <x:v>30.8</x:v>
+      <x:c r="J224" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J223),1)</x:f>
+        <x:v>611.8</x:v>
       </x:c>
       <x:c r="K224" s="30"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B225" s="30"/>
+      <x:c r="C225" s="30"/>
+      <x:c r="D225" s="30"/>
+      <x:c r="E225" s="30"/>
+      <x:c r="F225" s="30"/>
+      <x:c r="G225" s="30"/>
+      <x:c r="H225" s="30"/>
+      <x:c r="I225" s="30"/>
+      <x:c r="J225" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
+        <x:v>32.2</x:v>
+      </x:c>
+      <x:c r="K225" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R2710356e4437401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R55f79af1654942ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4cf3af400c664dfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R0506a1e8871f433d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Ra696e6eba7fe4639"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Re4b2e2ce1a1f43d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R07211a705e97432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R1fbc1da3469b4c00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R6878e56b43f546f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R36c6b102308342b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R66b8bfc40ad748ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R81191c0d6477474e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R642dcd8298464261"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc422f11cf93b4417"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R0f52df88565c424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R475e705719b041fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R0bc227dd2eda45bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R455e2c966a694ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R88426bc6a7134bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rfea4509a6981413c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R66b8bfc40ad748ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R81191c0d6477474e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R642dcd8298464261"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc422f11cf93b4417"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R0f52df88565c424e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R475e705719b041fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R0bc227dd2eda45bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R455e2c966a694ef0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R88426bc6a7134bf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rfea4509a6981413c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R40fbf13e50614fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R6e39936afe9d44dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Ra266b784c4c84521"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R37b738267fc3496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rcfc4f1ff96b24967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R32d1cba3aac44fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rf2bfae4b8b794536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R116c2a089f7f4b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R4814334320d943c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Ra463150ce63c4dbf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7551.22</x:v>
+        <x:v>7357.03</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7246.61</x:v>
+        <x:v>7256.25</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>304.6</x:v>
+        <x:v>100.8</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>31303.7</x:v>
+        <x:v>31404.5</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>174.9</x:v>
+        <x:v>174.5</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7601.09</x:v>
+        <x:v>7473.7</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7364.43</x:v>
+        <x:v>7386.14</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>236.7</x:v>
+        <x:v>87.6</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>31129.9</x:v>
+        <x:v>31217.5</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>173.9</x:v>
+        <x:v>173.4</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,22 +577,22 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3878.41</x:v>
+        <x:v>3843.84</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3806.67</x:v>
+        <x:v>3810.81</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>71.7</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8563.6</x:v>
+        <x:v>8596.6</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>47.8</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>124660</x:v>
+        <x:v>122480</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>119520</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>5140</x:v>
+        <x:v>4380</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1431940</x:v>
+        <x:v>1436320</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>7999.7</x:v>
+        <x:v>7979.6</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -8101,30 +8101,48 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B224" s="30" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C224" s="30"/>
-      <x:c r="D224" s="30"/>
-      <x:c r="E224" s="30"/>
-      <x:c r="F224" s="30"/>
-      <x:c r="G224" s="30"/>
-      <x:c r="H224" s="30"/>
-      <x:c r="I224" s="30"/>
-      <x:c r="J224" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J223),1)</x:f>
-        <x:v>113460</x:v>
-      </x:c>
-      <x:c r="K224" s="30"/>
+      <x:c r="A224" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B224" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C224" s="22" t="str">
+        <x:v>9月29日</x:v>
+      </x:c>
+      <x:c r="D224" s="23" t="n">
+        <x:v>119080</x:v>
+      </x:c>
+      <x:c r="E224" s="23" t="n">
+        <x:v>122480</x:v>
+      </x:c>
+      <x:c r="F224" s="23" t="n">
+        <x:v>118100</x:v>
+      </x:c>
+      <x:c r="G224" s="23" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="H224" s="23" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I224" s="24" t="n">
+        <x:v>0.00016669444907480013</x:v>
+      </x:c>
+      <x:c r="J224" s="23" t="n">
+        <x:f>ROUND(E224-F224,1)</x:f>
+        <x:v>4380</x:v>
+      </x:c>
+      <x:c r="K224" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B225" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B225" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="C225" s="30"/>
       <x:c r="D225" s="30"/>
       <x:c r="E225" s="30"/>
@@ -8132,11 +8150,29 @@
       <x:c r="G225" s="30"/>
       <x:c r="H225" s="30"/>
       <x:c r="I225" s="30"/>
-      <x:c r="J225" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
-        <x:v>5971.6</x:v>
+      <x:c r="J225" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J224),1)</x:f>
+        <x:v>117840</x:v>
       </x:c>
       <x:c r="K225" s="30"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B226" s="30"/>
+      <x:c r="C226" s="30"/>
+      <x:c r="D226" s="30"/>
+      <x:c r="E226" s="30"/>
+      <x:c r="F226" s="30"/>
+      <x:c r="G226" s="30"/>
+      <x:c r="H226" s="30"/>
+      <x:c r="I226" s="30"/>
+      <x:c r="J226" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
+        <x:v>5892</x:v>
+      </x:c>
+      <x:c r="K226" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9632,7 +9668,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" s="22" t="str">
-        <x:v>9月28日</x:v>
+        <x:v>9月28日-9月29日</x:v>
       </x:c>
       <x:c r="C42" s="23" t="n">
         <x:v>7551.22</x:v>
@@ -9644,15 +9680,15 @@
         <x:v>7246.61</x:v>
       </x:c>
       <x:c r="F42" s="23" t="n">
-        <x:v>7294.17</x:v>
+        <x:v>7325.35</x:v>
       </x:c>
       <x:c r="G42" s="28" t="n">
         <x:f>ROUND(F42-F41,1)</x:f>
-        <x:v>-276</x:v>
+        <x:v>-244.8</x:v>
       </x:c>
       <x:c r="H42" s="24" t="n">
         <x:f>IFERROR(F42/F41-1,"")</x:f>
-        <x:v>-0.0364550721651119</x:v>
+        <x:v>-0.03233625798201878</x:v>
       </x:c>
       <x:c r="I42" s="26" t="n">
         <x:f>ROUND(D42-E42,1)</x:f>
@@ -9662,7 +9698,7 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K42" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -11158,7 +11194,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B85" s="22" t="str">
-        <x:v>9月28日</x:v>
+        <x:v>9月28日-9月29日</x:v>
       </x:c>
       <x:c r="C85" s="23" t="n">
         <x:v>7599.2</x:v>
@@ -11170,15 +11206,15 @@
         <x:v>7364.43</x:v>
       </x:c>
       <x:c r="F85" s="23" t="n">
-        <x:v>7402.3</x:v>
+        <x:v>7439.63</x:v>
       </x:c>
       <x:c r="G85" s="28" t="n">
         <x:f>ROUND(F85-F84,1)</x:f>
-        <x:v>-221.8</x:v>
+        <x:v>-184.4</x:v>
       </x:c>
       <x:c r="H85" s="24" t="n">
         <x:f>IFERROR(F85/F84-1,"")</x:f>
-        <x:v>-0.029088137963056426</x:v>
+        <x:v>-0.024191803065816475</x:v>
       </x:c>
       <x:c r="I85" s="26" t="n">
         <x:f>ROUND(D85-E85,1)</x:f>
@@ -11188,7 +11224,7 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K85" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -12684,7 +12720,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B128" s="22" t="str">
-        <x:v>9月28日</x:v>
+        <x:v>9月28日-9月29日</x:v>
       </x:c>
       <x:c r="C128" s="23" t="n">
         <x:v>3878.41</x:v>
@@ -12696,15 +12732,15 @@
         <x:v>3806.67</x:v>
       </x:c>
       <x:c r="F128" s="23" t="n">
-        <x:v>3823.62</x:v>
+        <x:v>3830.45</x:v>
       </x:c>
       <x:c r="G128" s="23" t="n">
         <x:f>ROUND(F128-F127,1)</x:f>
-        <x:v>-64.7</x:v>
+        <x:v>-57.9</x:v>
       </x:c>
       <x:c r="H128" s="24" t="n">
         <x:f>IFERROR(F128/F127-1,"")</x:f>
-        <x:v>-0.016652221882176854</x:v>
+        <x:v>-0.014895701797925653</x:v>
       </x:c>
       <x:c r="I128" s="26" t="n">
         <x:f>ROUND(D128-E128,1)</x:f>
@@ -12714,7 +12750,7 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K128" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -20314,7 +20350,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B343" s="22" t="str">
-        <x:v>9月28日</x:v>
+        <x:v>9月28日-9月29日</x:v>
       </x:c>
       <x:c r="C343" s="23" t="n">
         <x:v>124280</x:v>
@@ -20323,28 +20359,28 @@
         <x:v>124660</x:v>
       </x:c>
       <x:c r="E343" s="23" t="n">
-        <x:v>119520</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="F343" s="23" t="n">
-        <x:v>119980</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="G343" s="28" t="n">
         <x:f>ROUND(F343-F342,1)</x:f>
-        <x:v>-6000</x:v>
+        <x:v>-5980</x:v>
       </x:c>
       <x:c r="H343" s="24" t="n">
         <x:f>IFERROR(F343/F342-1,"")</x:f>
-        <x:v>-0.04762660739799973</x:v>
-      </x:c>
-      <x:c r="I343" s="23" t="n">
+        <x:v>-0.047467852040006364</x:v>
+      </x:c>
+      <x:c r="I343" s="26" t="n">
         <x:f>ROUND(D343-E343,1)</x:f>
-        <x:v>5140</x:v>
+        <x:v>6560</x:v>
       </x:c>
       <x:c r="J343" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K343" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -20362,7 +20398,7 @@
       <x:c r="H344" s="30"/>
       <x:c r="I344" s="32" t="n">
         <x:f>ROUND(SUM(I306:I343),1)</x:f>
-        <x:v>758100</x:v>
+        <x:v>759520</x:v>
       </x:c>
       <x:c r="J344" s="30"/>
       <x:c r="K344" s="30"/>
@@ -20380,7 +20416,7 @@
       <x:c r="H345" s="30"/>
       <x:c r="I345" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I306:I343),0),1)</x:f>
-        <x:v>19950</x:v>
+        <x:v>19987.4</x:v>
       </x:c>
       <x:c r="J345" s="30"/>
       <x:c r="K345" s="30"/>
@@ -27622,30 +27658,48 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B224" s="30" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C224" s="30"/>
-      <x:c r="D224" s="30"/>
-      <x:c r="E224" s="30"/>
-      <x:c r="F224" s="30"/>
-      <x:c r="G224" s="30"/>
-      <x:c r="H224" s="30"/>
-      <x:c r="I224" s="30"/>
-      <x:c r="J224" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J223),1)</x:f>
-        <x:v>2572.9</x:v>
-      </x:c>
-      <x:c r="K224" s="30"/>
+      <x:c r="A224" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B224" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C224" s="22" t="str">
+        <x:v>9月29日</x:v>
+      </x:c>
+      <x:c r="D224" s="23" t="n">
+        <x:v>7265.51</x:v>
+      </x:c>
+      <x:c r="E224" s="23" t="n">
+        <x:v>7357.03</x:v>
+      </x:c>
+      <x:c r="F224" s="23" t="n">
+        <x:v>7256.25</x:v>
+      </x:c>
+      <x:c r="G224" s="23" t="n">
+        <x:v>7325.35</x:v>
+      </x:c>
+      <x:c r="H224" s="23" t="n">
+        <x:v>31.2</x:v>
+      </x:c>
+      <x:c r="I224" s="24" t="n">
+        <x:v>0.004274646738422705</x:v>
+      </x:c>
+      <x:c r="J224" s="23" t="n">
+        <x:f>ROUND(E224-F224,1)</x:f>
+        <x:v>100.8</x:v>
+      </x:c>
+      <x:c r="K224" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B225" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B225" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="C225" s="30"/>
       <x:c r="D225" s="30"/>
       <x:c r="E225" s="30"/>
@@ -27653,11 +27707,29 @@
       <x:c r="G225" s="30"/>
       <x:c r="H225" s="30"/>
       <x:c r="I225" s="30"/>
-      <x:c r="J225" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
-        <x:v>135.4</x:v>
+      <x:c r="J225" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J224),1)</x:f>
+        <x:v>2673.7</x:v>
       </x:c>
       <x:c r="K225" s="30"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B226" s="30"/>
+      <x:c r="C226" s="30"/>
+      <x:c r="D226" s="30"/>
+      <x:c r="E226" s="30"/>
+      <x:c r="F226" s="30"/>
+      <x:c r="G226" s="30"/>
+      <x:c r="H226" s="30"/>
+      <x:c r="I226" s="30"/>
+      <x:c r="J226" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
+        <x:v>133.7</x:v>
+      </x:c>
+      <x:c r="K226" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -34897,30 +34969,48 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B224" s="30" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C224" s="30"/>
-      <x:c r="D224" s="30"/>
-      <x:c r="E224" s="30"/>
-      <x:c r="F224" s="30"/>
-      <x:c r="G224" s="30"/>
-      <x:c r="H224" s="30"/>
-      <x:c r="I224" s="30"/>
-      <x:c r="J224" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J223),1)</x:f>
-        <x:v>2346.2</x:v>
-      </x:c>
-      <x:c r="K224" s="30"/>
+      <x:c r="A224" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B224" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C224" s="22" t="str">
+        <x:v>9月29日</x:v>
+      </x:c>
+      <x:c r="D224" s="23" t="n">
+        <x:v>7388.11</x:v>
+      </x:c>
+      <x:c r="E224" s="23" t="n">
+        <x:v>7473.7</x:v>
+      </x:c>
+      <x:c r="F224" s="23" t="n">
+        <x:v>7386.14</x:v>
+      </x:c>
+      <x:c r="G224" s="23" t="n">
+        <x:v>7439.63</x:v>
+      </x:c>
+      <x:c r="H224" s="23" t="n">
+        <x:v>37.3</x:v>
+      </x:c>
+      <x:c r="I224" s="24" t="n">
+        <x:v>0.005043027167231706</x:v>
+      </x:c>
+      <x:c r="J224" s="23" t="n">
+        <x:f>ROUND(E224-F224,1)</x:f>
+        <x:v>87.6</x:v>
+      </x:c>
+      <x:c r="K224" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B225" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B225" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="C225" s="30"/>
       <x:c r="D225" s="30"/>
       <x:c r="E225" s="30"/>
@@ -34928,11 +35018,29 @@
       <x:c r="G225" s="30"/>
       <x:c r="H225" s="30"/>
       <x:c r="I225" s="30"/>
-      <x:c r="J225" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
-        <x:v>123.5</x:v>
+      <x:c r="J225" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J224),1)</x:f>
+        <x:v>2433.8</x:v>
       </x:c>
       <x:c r="K225" s="30"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B226" s="30"/>
+      <x:c r="C226" s="30"/>
+      <x:c r="D226" s="30"/>
+      <x:c r="E226" s="30"/>
+      <x:c r="F226" s="30"/>
+      <x:c r="G226" s="30"/>
+      <x:c r="H226" s="30"/>
+      <x:c r="I226" s="30"/>
+      <x:c r="J226" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
+        <x:v>121.7</x:v>
+      </x:c>
+      <x:c r="K226" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -42172,30 +42280,48 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B224" s="30" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C224" s="30"/>
-      <x:c r="D224" s="30"/>
-      <x:c r="E224" s="30"/>
-      <x:c r="F224" s="30"/>
-      <x:c r="G224" s="30"/>
-      <x:c r="H224" s="30"/>
-      <x:c r="I224" s="30"/>
-      <x:c r="J224" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J223),1)</x:f>
-        <x:v>682.5</x:v>
-      </x:c>
-      <x:c r="K224" s="30"/>
+      <x:c r="A224" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B224" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C224" s="22" t="str">
+        <x:v>9月29日</x:v>
+      </x:c>
+      <x:c r="D224" s="23" t="n">
+        <x:v>3816.15</x:v>
+      </x:c>
+      <x:c r="E224" s="23" t="n">
+        <x:v>3843.84</x:v>
+      </x:c>
+      <x:c r="F224" s="23" t="n">
+        <x:v>3810.81</x:v>
+      </x:c>
+      <x:c r="G224" s="23" t="n">
+        <x:v>3830.45</x:v>
+      </x:c>
+      <x:c r="H224" s="23" t="n">
+        <x:v>6.8</x:v>
+      </x:c>
+      <x:c r="I224" s="24" t="n">
+        <x:v>0.0017862653715587928</x:v>
+      </x:c>
+      <x:c r="J224" s="23" t="n">
+        <x:f>ROUND(E224-F224,1)</x:f>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K224" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B225" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B225" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="C225" s="30"/>
       <x:c r="D225" s="30"/>
       <x:c r="E225" s="30"/>
@@ -42203,11 +42329,29 @@
       <x:c r="G225" s="30"/>
       <x:c r="H225" s="30"/>
       <x:c r="I225" s="30"/>
-      <x:c r="J225" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
-        <x:v>35.9</x:v>
+      <x:c r="J225" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J224),1)</x:f>
+        <x:v>715.5</x:v>
       </x:c>
       <x:c r="K225" s="30"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B226" s="30"/>
+      <x:c r="C226" s="30"/>
+      <x:c r="D226" s="30"/>
+      <x:c r="E226" s="30"/>
+      <x:c r="F226" s="30"/>
+      <x:c r="G226" s="30"/>
+      <x:c r="H226" s="30"/>
+      <x:c r="I226" s="30"/>
+      <x:c r="J226" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
+        <x:v>35.8</x:v>
+      </x:c>
+      <x:c r="K226" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R40fbf13e50614fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R6e39936afe9d44dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Ra266b784c4c84521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R37b738267fc3496a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rcfc4f1ff96b24967"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R32d1cba3aac44fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rf2bfae4b8b794536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R116c2a089f7f4b74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R4814334320d943c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Ra463150ce63c4dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R12def00e36934400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rc3fef61853824c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rde92252bc93441dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rbeb115566d9744eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R6e480c1f62404cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Re5198e21e4604f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R8bcd09b56c5a421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R75743e9a8b5649b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rd6b8620b86cc4c65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rc6b7275670894a02"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7393</x:v>
+        <x:v>7226.4</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7076.2</x:v>
+        <x:v>7123</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>316.8</x:v>
+        <x:v>103.4</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>33311</x:v>
+        <x:v>33414.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>186.1</x:v>
+        <x:v>185.6</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7458.4</x:v>
+        <x:v>7352.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7186</x:v>
+        <x:v>7238</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>272.4</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>34506.4</x:v>
+        <x:v>34621.2</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>192.8</x:v>
+        <x:v>192.3</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4366.8</x:v>
+        <x:v>4297.4</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4246</x:v>
+        <x:v>4257.6</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>120.8</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12936.4</x:v>
+        <x:v>12976.2</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.3</x:v>
+        <x:v>72.1</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-28</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2803.8</x:v>
+        <x:v>2777.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2746</x:v>
+        <x:v>2752</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>57.8</x:v>
+        <x:v>25.8</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7188.4</x:v>
+        <x:v>7214.2</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.2</x:v>
+        <x:v>40.1</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -14246,7 +14246,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B171" s="22" t="str">
-        <x:v>9月28日</x:v>
+        <x:v>9月28日-9月29日</x:v>
       </x:c>
       <x:c r="C171" s="23" t="n">
         <x:v>7390</x:v>
@@ -14258,15 +14258,15 @@
         <x:v>7076.2</x:v>
       </x:c>
       <x:c r="F171" s="23" t="n">
-        <x:v>7157.2</x:v>
+        <x:v>7191.2</x:v>
       </x:c>
       <x:c r="G171" s="28" t="n">
         <x:f>ROUND(F171-F170,1)</x:f>
-        <x:v>-233.8</x:v>
+        <x:v>-199.8</x:v>
       </x:c>
       <x:c r="H171" s="24" t="n">
         <x:f>IFERROR(F171/F170-1,"")</x:f>
-        <x:v>-0.03163306724394532</x:v>
+        <x:v>-0.02703287782438102</x:v>
       </x:c>
       <x:c r="I171" s="26" t="n">
         <x:f>ROUND(D171-E171,1)</x:f>
@@ -14276,7 +14276,7 @@
         <x:v>IM2612</x:v>
       </x:c>
       <x:c r="K171" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -15772,7 +15772,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B214" s="22" t="str">
-        <x:v>9月28日</x:v>
+        <x:v>9月28日-9月29日</x:v>
       </x:c>
       <x:c r="C214" s="23" t="n">
         <x:v>7440.8</x:v>
@@ -15784,15 +15784,15 @@
         <x:v>7186</x:v>
       </x:c>
       <x:c r="F214" s="23" t="n">
-        <x:v>7270</x:v>
-      </x:c>
-      <x:c r="G214" s="28" t="n">
+        <x:v>7309.6</x:v>
+      </x:c>
+      <x:c r="G214" s="23" t="n">
         <x:f>ROUND(F214-F213,1)</x:f>
-        <x:v>-181.6</x:v>
+        <x:v>-142</x:v>
       </x:c>
       <x:c r="H214" s="24" t="n">
         <x:f>IFERROR(F214/F213-1,"")</x:f>
-        <x:v>-0.024370604970744614</x:v>
+        <x:v>-0.019056310054216596</x:v>
       </x:c>
       <x:c r="I214" s="26" t="n">
         <x:f>ROUND(D214-E214,1)</x:f>
@@ -15802,7 +15802,7 @@
         <x:v>IC2612</x:v>
       </x:c>
       <x:c r="K214" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -17298,7 +17298,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B257" s="22" t="str">
-        <x:v>9月28日</x:v>
+        <x:v>9月28日-9月29日</x:v>
       </x:c>
       <x:c r="C257" s="23" t="n">
         <x:v>4365</x:v>
@@ -17310,15 +17310,15 @@
         <x:v>4246</x:v>
       </x:c>
       <x:c r="F257" s="23" t="n">
-        <x:v>4280.8</x:v>
+        <x:v>4277.2</x:v>
       </x:c>
       <x:c r="G257" s="23" t="n">
         <x:f>ROUND(F257-F256,1)</x:f>
-        <x:v>-94.2</x:v>
+        <x:v>-97.8</x:v>
       </x:c>
       <x:c r="H257" s="24" t="n">
         <x:f>IFERROR(F257/F256-1,"")</x:f>
-        <x:v>-0.021531428571428535</x:v>
+        <x:v>-0.02235428571428577</x:v>
       </x:c>
       <x:c r="I257" s="26" t="n">
         <x:f>ROUND(D257-E257,1)</x:f>
@@ -17328,7 +17328,7 @@
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K257" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -18824,7 +18824,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B300" s="22" t="str">
-        <x:v>9月28日</x:v>
+        <x:v>9月28日-9月29日</x:v>
       </x:c>
       <x:c r="C300" s="23" t="n">
         <x:v>2802</x:v>
@@ -18836,15 +18836,15 @@
         <x:v>2746</x:v>
       </x:c>
       <x:c r="F300" s="23" t="n">
-        <x:v>2770.2</x:v>
+        <x:v>2763.6</x:v>
       </x:c>
       <x:c r="G300" s="23" t="n">
         <x:f>ROUND(F300-F299,1)</x:f>
-        <x:v>-34.4</x:v>
+        <x:v>-41</x:v>
       </x:c>
       <x:c r="H300" s="24" t="n">
         <x:f>IFERROR(F300/F299-1,"")</x:f>
-        <x:v>-0.012265563716751138</x:v>
+        <x:v>-0.014618840476360306</x:v>
       </x:c>
       <x:c r="I300" s="23" t="n">
         <x:f>ROUND(D300-E300,1)</x:f>
@@ -18854,7 +18854,7 @@
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K300" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="301">
@@ -49591,30 +49591,48 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B224" s="30" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C224" s="30"/>
-      <x:c r="D224" s="30"/>
-      <x:c r="E224" s="30"/>
-      <x:c r="F224" s="30"/>
-      <x:c r="G224" s="30"/>
-      <x:c r="H224" s="30"/>
-      <x:c r="I224" s="30"/>
-      <x:c r="J224" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J223),1)</x:f>
-        <x:v>2867.2</x:v>
-      </x:c>
-      <x:c r="K224" s="30"/>
+      <x:c r="A224" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B224" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C224" s="22" t="str">
+        <x:v>9月29日</x:v>
+      </x:c>
+      <x:c r="D224" s="23" t="n">
+        <x:v>7144</x:v>
+      </x:c>
+      <x:c r="E224" s="23" t="n">
+        <x:v>7226.4</x:v>
+      </x:c>
+      <x:c r="F224" s="23" t="n">
+        <x:v>7123</x:v>
+      </x:c>
+      <x:c r="G224" s="23" t="n">
+        <x:v>7191.2</x:v>
+      </x:c>
+      <x:c r="H224" s="23" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I224" s="24" t="n">
+        <x:v>0.004750461074163104</x:v>
+      </x:c>
+      <x:c r="J224" s="23" t="n">
+        <x:f>ROUND(E224-F224,1)</x:f>
+        <x:v>103.4</x:v>
+      </x:c>
+      <x:c r="K224" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B225" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B225" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="C225" s="30"/>
       <x:c r="D225" s="30"/>
       <x:c r="E225" s="30"/>
@@ -49622,11 +49640,29 @@
       <x:c r="G225" s="30"/>
       <x:c r="H225" s="30"/>
       <x:c r="I225" s="30"/>
-      <x:c r="J225" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
-        <x:v>150.9</x:v>
+      <x:c r="J225" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J224),1)</x:f>
+        <x:v>2970.6</x:v>
       </x:c>
       <x:c r="K225" s="30"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B226" s="30"/>
+      <x:c r="C226" s="30"/>
+      <x:c r="D226" s="30"/>
+      <x:c r="E226" s="30"/>
+      <x:c r="F226" s="30"/>
+      <x:c r="G226" s="30"/>
+      <x:c r="H226" s="30"/>
+      <x:c r="I226" s="30"/>
+      <x:c r="J226" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
+        <x:v>148.5</x:v>
+      </x:c>
+      <x:c r="K226" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -56866,30 +56902,48 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B224" s="30" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C224" s="30"/>
-      <x:c r="D224" s="30"/>
-      <x:c r="E224" s="30"/>
-      <x:c r="F224" s="30"/>
-      <x:c r="G224" s="30"/>
-      <x:c r="H224" s="30"/>
-      <x:c r="I224" s="30"/>
-      <x:c r="J224" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J223),1)</x:f>
-        <x:v>2762.2</x:v>
-      </x:c>
-      <x:c r="K224" s="30"/>
+      <x:c r="A224" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B224" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C224" s="22" t="str">
+        <x:v>9月29日</x:v>
+      </x:c>
+      <x:c r="D224" s="23" t="n">
+        <x:v>7270</x:v>
+      </x:c>
+      <x:c r="E224" s="23" t="n">
+        <x:v>7352.8</x:v>
+      </x:c>
+      <x:c r="F224" s="23" t="n">
+        <x:v>7238</x:v>
+      </x:c>
+      <x:c r="G224" s="23" t="n">
+        <x:v>7309.6</x:v>
+      </x:c>
+      <x:c r="H224" s="23" t="n">
+        <x:v>39.6</x:v>
+      </x:c>
+      <x:c r="I224" s="24" t="n">
+        <x:v>0.005447042640990496</x:v>
+      </x:c>
+      <x:c r="J224" s="23" t="n">
+        <x:f>ROUND(E224-F224,1)</x:f>
+        <x:v>114.8</x:v>
+      </x:c>
+      <x:c r="K224" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B225" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B225" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="C225" s="30"/>
       <x:c r="D225" s="30"/>
       <x:c r="E225" s="30"/>
@@ -56897,11 +56951,29 @@
       <x:c r="G225" s="30"/>
       <x:c r="H225" s="30"/>
       <x:c r="I225" s="30"/>
-      <x:c r="J225" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
-        <x:v>145.4</x:v>
+      <x:c r="J225" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J224),1)</x:f>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="K225" s="30"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B226" s="30"/>
+      <x:c r="C226" s="30"/>
+      <x:c r="D226" s="30"/>
+      <x:c r="E226" s="30"/>
+      <x:c r="F226" s="30"/>
+      <x:c r="G226" s="30"/>
+      <x:c r="H226" s="30"/>
+      <x:c r="I226" s="30"/>
+      <x:c r="J226" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
+        <x:v>143.9</x:v>
+      </x:c>
+      <x:c r="K226" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -64141,30 +64213,48 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B224" s="30" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C224" s="30"/>
-      <x:c r="D224" s="30"/>
-      <x:c r="E224" s="30"/>
-      <x:c r="F224" s="30"/>
-      <x:c r="G224" s="30"/>
-      <x:c r="H224" s="30"/>
-      <x:c r="I224" s="30"/>
-      <x:c r="J224" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J223),1)</x:f>
-        <x:v>1049.8</x:v>
-      </x:c>
-      <x:c r="K224" s="30"/>
+      <x:c r="A224" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B224" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C224" s="22" t="str">
+        <x:v>9月29日</x:v>
+      </x:c>
+      <x:c r="D224" s="23" t="n">
+        <x:v>4271</x:v>
+      </x:c>
+      <x:c r="E224" s="23" t="n">
+        <x:v>4297.4</x:v>
+      </x:c>
+      <x:c r="F224" s="23" t="n">
+        <x:v>4257.6</x:v>
+      </x:c>
+      <x:c r="G224" s="23" t="n">
+        <x:v>4277.2</x:v>
+      </x:c>
+      <x:c r="H224" s="23" t="n">
+        <x:v>-3.6</x:v>
+      </x:c>
+      <x:c r="I224" s="24" t="n">
+        <x:v>-0.000840964305737324</x:v>
+      </x:c>
+      <x:c r="J224" s="23" t="n">
+        <x:f>ROUND(E224-F224,1)</x:f>
+        <x:v>39.8</x:v>
+      </x:c>
+      <x:c r="K224" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B225" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B225" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="C225" s="30"/>
       <x:c r="D225" s="30"/>
       <x:c r="E225" s="30"/>
@@ -64172,11 +64262,29 @@
       <x:c r="G225" s="30"/>
       <x:c r="H225" s="30"/>
       <x:c r="I225" s="30"/>
-      <x:c r="J225" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
-        <x:v>55.3</x:v>
+      <x:c r="J225" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J224),1)</x:f>
+        <x:v>1089.6</x:v>
       </x:c>
       <x:c r="K225" s="30"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B226" s="30"/>
+      <x:c r="C226" s="30"/>
+      <x:c r="D226" s="30"/>
+      <x:c r="E226" s="30"/>
+      <x:c r="F226" s="30"/>
+      <x:c r="G226" s="30"/>
+      <x:c r="H226" s="30"/>
+      <x:c r="I226" s="30"/>
+      <x:c r="J226" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
+        <x:v>54.5</x:v>
+      </x:c>
+      <x:c r="K226" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -71416,30 +71524,48 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B224" s="30" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C224" s="30"/>
-      <x:c r="D224" s="30"/>
-      <x:c r="E224" s="30"/>
-      <x:c r="F224" s="30"/>
-      <x:c r="G224" s="30"/>
-      <x:c r="H224" s="30"/>
-      <x:c r="I224" s="30"/>
-      <x:c r="J224" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J223),1)</x:f>
-        <x:v>611.8</x:v>
-      </x:c>
-      <x:c r="K224" s="30"/>
+      <x:c r="A224" s="22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B224" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C224" s="22" t="str">
+        <x:v>9月29日</x:v>
+      </x:c>
+      <x:c r="D224" s="23" t="n">
+        <x:v>2769.2</x:v>
+      </x:c>
+      <x:c r="E224" s="23" t="n">
+        <x:v>2777.8</x:v>
+      </x:c>
+      <x:c r="F224" s="23" t="n">
+        <x:v>2752</x:v>
+      </x:c>
+      <x:c r="G224" s="23" t="n">
+        <x:v>2763.6</x:v>
+      </x:c>
+      <x:c r="H224" s="23" t="n">
+        <x:v>-6.6</x:v>
+      </x:c>
+      <x:c r="I224" s="24" t="n">
+        <x:v>-0.0023824994585228687</x:v>
+      </x:c>
+      <x:c r="J224" s="23" t="n">
+        <x:f>ROUND(E224-F224,1)</x:f>
+        <x:v>25.8</x:v>
+      </x:c>
+      <x:c r="K224" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B225" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B225" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="C225" s="30"/>
       <x:c r="D225" s="30"/>
       <x:c r="E225" s="30"/>
@@ -71447,11 +71573,29 @@
       <x:c r="G225" s="30"/>
       <x:c r="H225" s="30"/>
       <x:c r="I225" s="30"/>
-      <x:c r="J225" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J223),0),1)</x:f>
-        <x:v>32.2</x:v>
+      <x:c r="J225" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J224),1)</x:f>
+        <x:v>637.6</x:v>
       </x:c>
       <x:c r="K225" s="30"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B226" s="30"/>
+      <x:c r="C226" s="30"/>
+      <x:c r="D226" s="30"/>
+      <x:c r="E226" s="30"/>
+      <x:c r="F226" s="30"/>
+      <x:c r="G226" s="30"/>
+      <x:c r="H226" s="30"/>
+      <x:c r="I226" s="30"/>
+      <x:c r="J226" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
+        <x:v>31.9</x:v>
+      </x:c>
+      <x:c r="K226" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R12def00e36934400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rc3fef61853824c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rde92252bc93441dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rbeb115566d9744eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R6e480c1f62404cc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Re5198e21e4604f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R8bcd09b56c5a421b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R75743e9a8b5649b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rd6b8620b86cc4c65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rc6b7275670894a02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf650e05079204ad9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R874be54d830c4e7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb129a578ee2e42da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R7b1be81a4e444eba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R6215700ee10143cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R232cb4b144334234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R32a2ae6b60414481"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R4291aa1f3c204d0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Ra747a87a2b584290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R9e3bebe03b96474f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7357.03</x:v>
+        <x:v>7375.44</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7256.25</x:v>
+        <x:v>7288.98</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>100.8</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>31404.5</x:v>
+        <x:v>31491</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>174.5</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7473.7</x:v>
+        <x:v>7485.11</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7386.14</x:v>
+        <x:v>7417.49</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>87.6</x:v>
+        <x:v>67.6</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>31217.5</x:v>
+        <x:v>31285.1</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>173.4</x:v>
+        <x:v>172.8</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3843.84</x:v>
+        <x:v>3851.22</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3810.81</x:v>
+        <x:v>3833.09</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>33</x:v>
+        <x:v>18.1</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8596.6</x:v>
+        <x:v>8614.7</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>47.8</x:v>
+        <x:v>47.6</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7226.4</x:v>
+        <x:v>7232</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>7123</x:v>
+        <x:v>7153</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>103.4</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>33414.4</x:v>
+        <x:v>33493.4</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>185.6</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7352.8</x:v>
+        <x:v>7344</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7238</x:v>
+        <x:v>7282</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>114.8</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>34621.2</x:v>
+        <x:v>34683.2</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>192.3</x:v>
+        <x:v>191.6</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2777.8</x:v>
+        <x:v>2782.2</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2752</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>25.8</x:v>
+        <x:v>20.2</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7214.2</x:v>
+        <x:v>7234.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40.1</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -9668,7 +9668,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" s="22" t="str">
-        <x:v>9月28日-9月29日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C42" s="23" t="n">
         <x:v>7551.22</x:v>
@@ -9680,15 +9680,15 @@
         <x:v>7246.61</x:v>
       </x:c>
       <x:c r="F42" s="23" t="n">
-        <x:v>7325.35</x:v>
+        <x:v>7298.82</x:v>
       </x:c>
       <x:c r="G42" s="28" t="n">
         <x:f>ROUND(F42-F41,1)</x:f>
-        <x:v>-244.8</x:v>
+        <x:v>-271.3</x:v>
       </x:c>
       <x:c r="H42" s="24" t="n">
         <x:f>IFERROR(F42/F41-1,"")</x:f>
-        <x:v>-0.03233625798201878</x:v>
+        <x:v>-0.03584081668238637</x:v>
       </x:c>
       <x:c r="I42" s="26" t="n">
         <x:f>ROUND(D42-E42,1)</x:f>
@@ -9698,7 +9698,7 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K42" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -11194,7 +11194,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B85" s="22" t="str">
-        <x:v>9月28日-9月29日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C85" s="23" t="n">
         <x:v>7599.2</x:v>
@@ -11206,15 +11206,15 @@
         <x:v>7364.43</x:v>
       </x:c>
       <x:c r="F85" s="23" t="n">
-        <x:v>7439.63</x:v>
+        <x:v>7435.16</x:v>
       </x:c>
       <x:c r="G85" s="28" t="n">
         <x:f>ROUND(F85-F84,1)</x:f>
-        <x:v>-184.4</x:v>
+        <x:v>-188.9</x:v>
       </x:c>
       <x:c r="H85" s="24" t="n">
         <x:f>IFERROR(F85/F84-1,"")</x:f>
-        <x:v>-0.024191803065816475</x:v>
+        <x:v>-0.02477810408351444</x:v>
       </x:c>
       <x:c r="I85" s="26" t="n">
         <x:f>ROUND(D85-E85,1)</x:f>
@@ -11224,7 +11224,7 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K85" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -12720,7 +12720,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B128" s="22" t="str">
-        <x:v>9月28日-9月29日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C128" s="23" t="n">
         <x:v>3878.41</x:v>
@@ -12732,15 +12732,15 @@
         <x:v>3806.67</x:v>
       </x:c>
       <x:c r="F128" s="23" t="n">
-        <x:v>3830.45</x:v>
+        <x:v>3842.19</x:v>
       </x:c>
       <x:c r="G128" s="23" t="n">
         <x:f>ROUND(F128-F127,1)</x:f>
-        <x:v>-57.9</x:v>
+        <x:v>-46.2</x:v>
       </x:c>
       <x:c r="H128" s="24" t="n">
         <x:f>IFERROR(F128/F127-1,"")</x:f>
-        <x:v>-0.014895701797925653</x:v>
+        <x:v>-0.011876441799520077</x:v>
       </x:c>
       <x:c r="I128" s="26" t="n">
         <x:f>ROUND(D128-E128,1)</x:f>
@@ -12750,7 +12750,7 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K128" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -14246,7 +14246,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B171" s="22" t="str">
-        <x:v>9月28日-9月29日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C171" s="23" t="n">
         <x:v>7390</x:v>
@@ -14258,15 +14258,15 @@
         <x:v>7076.2</x:v>
       </x:c>
       <x:c r="F171" s="23" t="n">
-        <x:v>7191.2</x:v>
+        <x:v>7168.8</x:v>
       </x:c>
       <x:c r="G171" s="28" t="n">
         <x:f>ROUND(F171-F170,1)</x:f>
-        <x:v>-199.8</x:v>
+        <x:v>-222.2</x:v>
       </x:c>
       <x:c r="H171" s="24" t="n">
         <x:f>IFERROR(F171/F170-1,"")</x:f>
-        <x:v>-0.02703287782438102</x:v>
+        <x:v>-0.030063590853740996</x:v>
       </x:c>
       <x:c r="I171" s="26" t="n">
         <x:f>ROUND(D171-E171,1)</x:f>
@@ -14276,7 +14276,7 @@
         <x:v>IM2612</x:v>
       </x:c>
       <x:c r="K171" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -15772,7 +15772,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B214" s="22" t="str">
-        <x:v>9月28日-9月29日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C214" s="23" t="n">
         <x:v>7440.8</x:v>
@@ -15784,15 +15784,15 @@
         <x:v>7186</x:v>
       </x:c>
       <x:c r="F214" s="23" t="n">
-        <x:v>7309.6</x:v>
+        <x:v>7310.2</x:v>
       </x:c>
       <x:c r="G214" s="23" t="n">
         <x:f>ROUND(F214-F213,1)</x:f>
-        <x:v>-142</x:v>
+        <x:v>-141.4</x:v>
       </x:c>
       <x:c r="H214" s="24" t="n">
         <x:f>IFERROR(F214/F213-1,"")</x:f>
-        <x:v>-0.019056310054216596</x:v>
+        <x:v>-0.018975790434269224</x:v>
       </x:c>
       <x:c r="I214" s="26" t="n">
         <x:f>ROUND(D214-E214,1)</x:f>
@@ -15802,7 +15802,7 @@
         <x:v>IC2612</x:v>
       </x:c>
       <x:c r="K214" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -18824,7 +18824,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B300" s="22" t="str">
-        <x:v>9月28日-9月29日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C300" s="23" t="n">
         <x:v>2802</x:v>
@@ -18836,15 +18836,15 @@
         <x:v>2746</x:v>
       </x:c>
       <x:c r="F300" s="23" t="n">
-        <x:v>2763.6</x:v>
+        <x:v>2778.8</x:v>
       </x:c>
       <x:c r="G300" s="23" t="n">
         <x:f>ROUND(F300-F299,1)</x:f>
-        <x:v>-41</x:v>
+        <x:v>-25.8</x:v>
       </x:c>
       <x:c r="H300" s="24" t="n">
         <x:f>IFERROR(F300/F299-1,"")</x:f>
-        <x:v>-0.014618840476360306</x:v>
+        <x:v>-0.009199172787563215</x:v>
       </x:c>
       <x:c r="I300" s="23" t="n">
         <x:f>ROUND(D300-E300,1)</x:f>
@@ -18854,7 +18854,7 @@
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K300" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="301">
@@ -27694,30 +27694,48 @@
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B225" s="30" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C225" s="30"/>
-      <x:c r="D225" s="30"/>
-      <x:c r="E225" s="30"/>
-      <x:c r="F225" s="30"/>
-      <x:c r="G225" s="30"/>
-      <x:c r="H225" s="30"/>
-      <x:c r="I225" s="30"/>
-      <x:c r="J225" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J224),1)</x:f>
-        <x:v>2673.7</x:v>
-      </x:c>
-      <x:c r="K225" s="30"/>
+      <x:c r="A225" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B225" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C225" s="22" t="str">
+        <x:v>9月30日</x:v>
+      </x:c>
+      <x:c r="D225" s="23" t="n">
+        <x:v>7361.14</x:v>
+      </x:c>
+      <x:c r="E225" s="23" t="n">
+        <x:v>7375.44</x:v>
+      </x:c>
+      <x:c r="F225" s="23" t="n">
+        <x:v>7288.98</x:v>
+      </x:c>
+      <x:c r="G225" s="23" t="n">
+        <x:v>7298.82</x:v>
+      </x:c>
+      <x:c r="H225" s="23" t="n">
+        <x:v>-26.5</x:v>
+      </x:c>
+      <x:c r="I225" s="24" t="n">
+        <x:v>-0.0036216699543367703</x:v>
+      </x:c>
+      <x:c r="J225" s="23" t="n">
+        <x:f>ROUND(E225-F225,1)</x:f>
+        <x:v>86.5</x:v>
+      </x:c>
+      <x:c r="K225" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B226" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B226" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C226" s="30"/>
       <x:c r="D226" s="30"/>
       <x:c r="E226" s="30"/>
@@ -27725,11 +27743,29 @@
       <x:c r="G226" s="30"/>
       <x:c r="H226" s="30"/>
       <x:c r="I226" s="30"/>
-      <x:c r="J226" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
-        <x:v>133.7</x:v>
+      <x:c r="J226" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J225),1)</x:f>
+        <x:v>2760.2</x:v>
       </x:c>
       <x:c r="K226" s="30"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B227" s="30"/>
+      <x:c r="C227" s="30"/>
+      <x:c r="D227" s="30"/>
+      <x:c r="E227" s="30"/>
+      <x:c r="F227" s="30"/>
+      <x:c r="G227" s="30"/>
+      <x:c r="H227" s="30"/>
+      <x:c r="I227" s="30"/>
+      <x:c r="J227" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J225),0),1)</x:f>
+        <x:v>131.4</x:v>
+      </x:c>
+      <x:c r="K227" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -35005,30 +35041,48 @@
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B225" s="30" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C225" s="30"/>
-      <x:c r="D225" s="30"/>
-      <x:c r="E225" s="30"/>
-      <x:c r="F225" s="30"/>
-      <x:c r="G225" s="30"/>
-      <x:c r="H225" s="30"/>
-      <x:c r="I225" s="30"/>
-      <x:c r="J225" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J224),1)</x:f>
-        <x:v>2433.8</x:v>
-      </x:c>
-      <x:c r="K225" s="30"/>
+      <x:c r="A225" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B225" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C225" s="22" t="str">
+        <x:v>9月30日</x:v>
+      </x:c>
+      <x:c r="D225" s="23" t="n">
+        <x:v>7469.05</x:v>
+      </x:c>
+      <x:c r="E225" s="23" t="n">
+        <x:v>7485.11</x:v>
+      </x:c>
+      <x:c r="F225" s="23" t="n">
+        <x:v>7417.49</x:v>
+      </x:c>
+      <x:c r="G225" s="23" t="n">
+        <x:v>7435.16</x:v>
+      </x:c>
+      <x:c r="H225" s="23" t="n">
+        <x:v>-4.5</x:v>
+      </x:c>
+      <x:c r="I225" s="24" t="n">
+        <x:v>-0.0006008363319144339</x:v>
+      </x:c>
+      <x:c r="J225" s="23" t="n">
+        <x:f>ROUND(E225-F225,1)</x:f>
+        <x:v>67.6</x:v>
+      </x:c>
+      <x:c r="K225" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B226" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B226" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C226" s="30"/>
       <x:c r="D226" s="30"/>
       <x:c r="E226" s="30"/>
@@ -35036,11 +35090,29 @@
       <x:c r="G226" s="30"/>
       <x:c r="H226" s="30"/>
       <x:c r="I226" s="30"/>
-      <x:c r="J226" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
-        <x:v>121.7</x:v>
+      <x:c r="J226" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J225),1)</x:f>
+        <x:v>2501.4</x:v>
       </x:c>
       <x:c r="K226" s="30"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B227" s="30"/>
+      <x:c r="C227" s="30"/>
+      <x:c r="D227" s="30"/>
+      <x:c r="E227" s="30"/>
+      <x:c r="F227" s="30"/>
+      <x:c r="G227" s="30"/>
+      <x:c r="H227" s="30"/>
+      <x:c r="I227" s="30"/>
+      <x:c r="J227" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J225),0),1)</x:f>
+        <x:v>119.1</x:v>
+      </x:c>
+      <x:c r="K227" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -42316,30 +42388,48 @@
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B225" s="30" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C225" s="30"/>
-      <x:c r="D225" s="30"/>
-      <x:c r="E225" s="30"/>
-      <x:c r="F225" s="30"/>
-      <x:c r="G225" s="30"/>
-      <x:c r="H225" s="30"/>
-      <x:c r="I225" s="30"/>
-      <x:c r="J225" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J224),1)</x:f>
-        <x:v>715.5</x:v>
-      </x:c>
-      <x:c r="K225" s="30"/>
+      <x:c r="A225" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B225" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C225" s="22" t="str">
+        <x:v>9月30日</x:v>
+      </x:c>
+      <x:c r="D225" s="23" t="n">
+        <x:v>3839.25</x:v>
+      </x:c>
+      <x:c r="E225" s="23" t="n">
+        <x:v>3851.22</x:v>
+      </x:c>
+      <x:c r="F225" s="23" t="n">
+        <x:v>3833.09</x:v>
+      </x:c>
+      <x:c r="G225" s="23" t="n">
+        <x:v>3842.19</x:v>
+      </x:c>
+      <x:c r="H225" s="23" t="n">
+        <x:v>11.7</x:v>
+      </x:c>
+      <x:c r="I225" s="24" t="n">
+        <x:v>0.0030649140440419664</x:v>
+      </x:c>
+      <x:c r="J225" s="23" t="n">
+        <x:f>ROUND(E225-F225,1)</x:f>
+        <x:v>18.1</x:v>
+      </x:c>
+      <x:c r="K225" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B226" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B226" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C226" s="30"/>
       <x:c r="D226" s="30"/>
       <x:c r="E226" s="30"/>
@@ -42347,11 +42437,29 @@
       <x:c r="G226" s="30"/>
       <x:c r="H226" s="30"/>
       <x:c r="I226" s="30"/>
-      <x:c r="J226" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
-        <x:v>35.8</x:v>
+      <x:c r="J226" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J225),1)</x:f>
+        <x:v>733.6</x:v>
       </x:c>
       <x:c r="K226" s="30"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B227" s="30"/>
+      <x:c r="C227" s="30"/>
+      <x:c r="D227" s="30"/>
+      <x:c r="E227" s="30"/>
+      <x:c r="F227" s="30"/>
+      <x:c r="G227" s="30"/>
+      <x:c r="H227" s="30"/>
+      <x:c r="I227" s="30"/>
+      <x:c r="J227" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J225),0),1)</x:f>
+        <x:v>34.9</x:v>
+      </x:c>
+      <x:c r="K227" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -49627,30 +49735,48 @@
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B225" s="30" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C225" s="30"/>
-      <x:c r="D225" s="30"/>
-      <x:c r="E225" s="30"/>
-      <x:c r="F225" s="30"/>
-      <x:c r="G225" s="30"/>
-      <x:c r="H225" s="30"/>
-      <x:c r="I225" s="30"/>
-      <x:c r="J225" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J224),1)</x:f>
-        <x:v>2970.6</x:v>
-      </x:c>
-      <x:c r="K225" s="30"/>
+      <x:c r="A225" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B225" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C225" s="22" t="str">
+        <x:v>9月30日</x:v>
+      </x:c>
+      <x:c r="D225" s="23" t="n">
+        <x:v>7223.6</x:v>
+      </x:c>
+      <x:c r="E225" s="23" t="n">
+        <x:v>7232</x:v>
+      </x:c>
+      <x:c r="F225" s="23" t="n">
+        <x:v>7153</x:v>
+      </x:c>
+      <x:c r="G225" s="23" t="n">
+        <x:v>7168.8</x:v>
+      </x:c>
+      <x:c r="H225" s="23" t="n">
+        <x:v>-22.4</x:v>
+      </x:c>
+      <x:c r="I225" s="24" t="n">
+        <x:v>-0.003114918233396269</x:v>
+      </x:c>
+      <x:c r="J225" s="23" t="n">
+        <x:f>ROUND(E225-F225,1)</x:f>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K225" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B226" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B226" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C226" s="30"/>
       <x:c r="D226" s="30"/>
       <x:c r="E226" s="30"/>
@@ -49658,11 +49784,29 @@
       <x:c r="G226" s="30"/>
       <x:c r="H226" s="30"/>
       <x:c r="I226" s="30"/>
-      <x:c r="J226" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
-        <x:v>148.5</x:v>
+      <x:c r="J226" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J225),1)</x:f>
+        <x:v>3049.6</x:v>
       </x:c>
       <x:c r="K226" s="30"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B227" s="30"/>
+      <x:c r="C227" s="30"/>
+      <x:c r="D227" s="30"/>
+      <x:c r="E227" s="30"/>
+      <x:c r="F227" s="30"/>
+      <x:c r="G227" s="30"/>
+      <x:c r="H227" s="30"/>
+      <x:c r="I227" s="30"/>
+      <x:c r="J227" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J225),0),1)</x:f>
+        <x:v>145.2</x:v>
+      </x:c>
+      <x:c r="K227" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -56938,30 +57082,48 @@
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B225" s="30" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C225" s="30"/>
-      <x:c r="D225" s="30"/>
-      <x:c r="E225" s="30"/>
-      <x:c r="F225" s="30"/>
-      <x:c r="G225" s="30"/>
-      <x:c r="H225" s="30"/>
-      <x:c r="I225" s="30"/>
-      <x:c r="J225" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J224),1)</x:f>
-        <x:v>2877</x:v>
-      </x:c>
-      <x:c r="K225" s="30"/>
+      <x:c r="A225" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B225" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C225" s="22" t="str">
+        <x:v>9月30日</x:v>
+      </x:c>
+      <x:c r="D225" s="23" t="n">
+        <x:v>7332</x:v>
+      </x:c>
+      <x:c r="E225" s="23" t="n">
+        <x:v>7344</x:v>
+      </x:c>
+      <x:c r="F225" s="23" t="n">
+        <x:v>7282</x:v>
+      </x:c>
+      <x:c r="G225" s="23" t="n">
+        <x:v>7310.2</x:v>
+      </x:c>
+      <x:c r="H225" s="23" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I225" s="24" t="n">
+        <x:v>0.00008208383495666993</x:v>
+      </x:c>
+      <x:c r="J225" s="23" t="n">
+        <x:f>ROUND(E225-F225,1)</x:f>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K225" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B226" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B226" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C226" s="30"/>
       <x:c r="D226" s="30"/>
       <x:c r="E226" s="30"/>
@@ -56969,11 +57131,29 @@
       <x:c r="G226" s="30"/>
       <x:c r="H226" s="30"/>
       <x:c r="I226" s="30"/>
-      <x:c r="J226" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
-        <x:v>143.9</x:v>
+      <x:c r="J226" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J225),1)</x:f>
+        <x:v>2939</x:v>
       </x:c>
       <x:c r="K226" s="30"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B227" s="30"/>
+      <x:c r="C227" s="30"/>
+      <x:c r="D227" s="30"/>
+      <x:c r="E227" s="30"/>
+      <x:c r="F227" s="30"/>
+      <x:c r="G227" s="30"/>
+      <x:c r="H227" s="30"/>
+      <x:c r="I227" s="30"/>
+      <x:c r="J227" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J225),0),1)</x:f>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="K227" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -71560,30 +71740,48 @@
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B225" s="30" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C225" s="30"/>
-      <x:c r="D225" s="30"/>
-      <x:c r="E225" s="30"/>
-      <x:c r="F225" s="30"/>
-      <x:c r="G225" s="30"/>
-      <x:c r="H225" s="30"/>
-      <x:c r="I225" s="30"/>
-      <x:c r="J225" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J224),1)</x:f>
-        <x:v>637.6</x:v>
-      </x:c>
-      <x:c r="K225" s="30"/>
+      <x:c r="A225" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B225" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C225" s="22" t="str">
+        <x:v>9月30日</x:v>
+      </x:c>
+      <x:c r="D225" s="23" t="n">
+        <x:v>2769.6</x:v>
+      </x:c>
+      <x:c r="E225" s="23" t="n">
+        <x:v>2782.2</x:v>
+      </x:c>
+      <x:c r="F225" s="23" t="n">
+        <x:v>2762</x:v>
+      </x:c>
+      <x:c r="G225" s="23" t="n">
+        <x:v>2778.8</x:v>
+      </x:c>
+      <x:c r="H225" s="23" t="n">
+        <x:v>15.2</x:v>
+      </x:c>
+      <x:c r="I225" s="24" t="n">
+        <x:v>0.005500072369373443</x:v>
+      </x:c>
+      <x:c r="J225" s="23" t="n">
+        <x:f>ROUND(E225-F225,1)</x:f>
+        <x:v>20.2</x:v>
+      </x:c>
+      <x:c r="K225" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B226" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B226" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C226" s="30"/>
       <x:c r="D226" s="30"/>
       <x:c r="E226" s="30"/>
@@ -71591,11 +71789,29 @@
       <x:c r="G226" s="30"/>
       <x:c r="H226" s="30"/>
       <x:c r="I226" s="30"/>
-      <x:c r="J226" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
-        <x:v>31.9</x:v>
+      <x:c r="J226" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J225),1)</x:f>
+        <x:v>657.8</x:v>
       </x:c>
       <x:c r="K226" s="30"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B227" s="30"/>
+      <x:c r="C227" s="30"/>
+      <x:c r="D227" s="30"/>
+      <x:c r="E227" s="30"/>
+      <x:c r="F227" s="30"/>
+      <x:c r="G227" s="30"/>
+      <x:c r="H227" s="30"/>
+      <x:c r="I227" s="30"/>
+      <x:c r="J227" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J225),0),1)</x:f>
+        <x:v>31.3</x:v>
+      </x:c>
+      <x:c r="K227" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rf650e05079204ad9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R874be54d830c4e7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb129a578ee2e42da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R7b1be81a4e444eba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R6215700ee10143cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R232cb4b144334234"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R32a2ae6b60414481"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R4291aa1f3c204d0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Ra747a87a2b584290"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R9e3bebe03b96474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R23ed20124a6a4224"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R590c14d3a8784ddc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Re894c3df7609458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rfe2264cb78834e68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rcef070865666423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Ra758181d7ec24bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Re27f8ab7e763412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R05a3c125be754c1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Reafb038924914267"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Re4fb5b4cd2ac4e85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4297.4</x:v>
+        <x:v>4310.4</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4257.6</x:v>
+        <x:v>4278</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>39.8</x:v>
+        <x:v>32.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>12976.2</x:v>
+        <x:v>13008.6</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.1</x:v>
+        <x:v>71.9</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-29</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>122480</x:v>
+        <x:v>121220</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>118100</x:v>
+        <x:v>119100</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>4380</x:v>
+        <x:v>2120</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1436320</x:v>
+        <x:v>1438440</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>7979.6</x:v>
+        <x:v>7947.2</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -8137,30 +8137,48 @@
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B225" s="30" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C225" s="30"/>
-      <x:c r="D225" s="30"/>
-      <x:c r="E225" s="30"/>
-      <x:c r="F225" s="30"/>
-      <x:c r="G225" s="30"/>
-      <x:c r="H225" s="30"/>
-      <x:c r="I225" s="30"/>
-      <x:c r="J225" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J224),1)</x:f>
-        <x:v>117840</x:v>
-      </x:c>
-      <x:c r="K225" s="30"/>
+      <x:c r="A225" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B225" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C225" s="22" t="str">
+        <x:v>9月30日</x:v>
+      </x:c>
+      <x:c r="D225" s="23" t="n">
+        <x:v>120060</x:v>
+      </x:c>
+      <x:c r="E225" s="23" t="n">
+        <x:v>121220</x:v>
+      </x:c>
+      <x:c r="F225" s="23" t="n">
+        <x:v>119100</x:v>
+      </x:c>
+      <x:c r="G225" s="23" t="n">
+        <x:v>119780</x:v>
+      </x:c>
+      <x:c r="H225" s="28" t="n">
+        <x:v>-220</x:v>
+      </x:c>
+      <x:c r="I225" s="24" t="n">
+        <x:v>-0.0018333333333333535</x:v>
+      </x:c>
+      <x:c r="J225" s="23" t="n">
+        <x:f>ROUND(E225-F225,1)</x:f>
+        <x:v>2120</x:v>
+      </x:c>
+      <x:c r="K225" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B226" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B226" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C226" s="30"/>
       <x:c r="D226" s="30"/>
       <x:c r="E226" s="30"/>
@@ -8168,11 +8186,29 @@
       <x:c r="G226" s="30"/>
       <x:c r="H226" s="30"/>
       <x:c r="I226" s="30"/>
-      <x:c r="J226" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
-        <x:v>5892</x:v>
+      <x:c r="J226" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J225),1)</x:f>
+        <x:v>119960</x:v>
       </x:c>
       <x:c r="K226" s="30"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B227" s="30"/>
+      <x:c r="C227" s="30"/>
+      <x:c r="D227" s="30"/>
+      <x:c r="E227" s="30"/>
+      <x:c r="F227" s="30"/>
+      <x:c r="G227" s="30"/>
+      <x:c r="H227" s="30"/>
+      <x:c r="I227" s="30"/>
+      <x:c r="J227" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J225),0),1)</x:f>
+        <x:v>5712.4</x:v>
+      </x:c>
+      <x:c r="K227" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -17298,7 +17334,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B257" s="22" t="str">
-        <x:v>9月28日-9月29日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C257" s="23" t="n">
         <x:v>4365</x:v>
@@ -17310,15 +17346,15 @@
         <x:v>4246</x:v>
       </x:c>
       <x:c r="F257" s="23" t="n">
-        <x:v>4277.2</x:v>
+        <x:v>4300.8</x:v>
       </x:c>
       <x:c r="G257" s="23" t="n">
         <x:f>ROUND(F257-F256,1)</x:f>
-        <x:v>-97.8</x:v>
+        <x:v>-74.2</x:v>
       </x:c>
       <x:c r="H257" s="24" t="n">
         <x:f>IFERROR(F257/F256-1,"")</x:f>
-        <x:v>-0.02235428571428577</x:v>
+        <x:v>-0.016959999999999975</x:v>
       </x:c>
       <x:c r="I257" s="26" t="n">
         <x:f>ROUND(D257-E257,1)</x:f>
@@ -17328,7 +17364,7 @@
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K257" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -20350,7 +20386,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B343" s="22" t="str">
-        <x:v>9月28日-9月29日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C343" s="23" t="n">
         <x:v>124280</x:v>
@@ -20362,15 +20398,15 @@
         <x:v>118100</x:v>
       </x:c>
       <x:c r="F343" s="23" t="n">
-        <x:v>120000</x:v>
+        <x:v>119780</x:v>
       </x:c>
       <x:c r="G343" s="28" t="n">
         <x:f>ROUND(F343-F342,1)</x:f>
-        <x:v>-5980</x:v>
+        <x:v>-6200</x:v>
       </x:c>
       <x:c r="H343" s="24" t="n">
         <x:f>IFERROR(F343/F342-1,"")</x:f>
-        <x:v>-0.047467852040006364</x:v>
+        <x:v>-0.049214160977932964</x:v>
       </x:c>
       <x:c r="I343" s="26" t="n">
         <x:f>ROUND(D343-E343,1)</x:f>
@@ -20380,7 +20416,7 @@
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K343" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -64429,30 +64465,48 @@
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B225" s="30" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C225" s="30"/>
-      <x:c r="D225" s="30"/>
-      <x:c r="E225" s="30"/>
-      <x:c r="F225" s="30"/>
-      <x:c r="G225" s="30"/>
-      <x:c r="H225" s="30"/>
-      <x:c r="I225" s="30"/>
-      <x:c r="J225" s="32" t="n">
-        <x:f>ROUND(SUM(J205:J224),1)</x:f>
-        <x:v>1089.6</x:v>
-      </x:c>
-      <x:c r="K225" s="30"/>
+      <x:c r="A225" s="22" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B225" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C225" s="22" t="str">
+        <x:v>9月30日</x:v>
+      </x:c>
+      <x:c r="D225" s="23" t="n">
+        <x:v>4292.4</x:v>
+      </x:c>
+      <x:c r="E225" s="23" t="n">
+        <x:v>4310.4</x:v>
+      </x:c>
+      <x:c r="F225" s="23" t="n">
+        <x:v>4278</x:v>
+      </x:c>
+      <x:c r="G225" s="23" t="n">
+        <x:v>4300.8</x:v>
+      </x:c>
+      <x:c r="H225" s="23" t="n">
+        <x:v>23.6</x:v>
+      </x:c>
+      <x:c r="I225" s="24" t="n">
+        <x:v>0.005517628354998694</x:v>
+      </x:c>
+      <x:c r="J225" s="23" t="n">
+        <x:f>ROUND(E225-F225,1)</x:f>
+        <x:v>32.4</x:v>
+      </x:c>
+      <x:c r="K225" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B226" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B226" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C226" s="30"/>
       <x:c r="D226" s="30"/>
       <x:c r="E226" s="30"/>
@@ -64460,11 +64514,29 @@
       <x:c r="G226" s="30"/>
       <x:c r="H226" s="30"/>
       <x:c r="I226" s="30"/>
-      <x:c r="J226" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J205:J224),0),1)</x:f>
-        <x:v>54.5</x:v>
+      <x:c r="J226" s="32" t="n">
+        <x:f>ROUND(SUM(J205:J225),1)</x:f>
+        <x:v>1122</x:v>
       </x:c>
       <x:c r="K226" s="30"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B227" s="30"/>
+      <x:c r="C227" s="30"/>
+      <x:c r="D227" s="30"/>
+      <x:c r="E227" s="30"/>
+      <x:c r="F227" s="30"/>
+      <x:c r="G227" s="30"/>
+      <x:c r="H227" s="30"/>
+      <x:c r="I227" s="30"/>
+      <x:c r="J227" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J205:J225),0),1)</x:f>
+        <x:v>53.4</x:v>
+      </x:c>
+      <x:c r="K227" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R23ed20124a6a4224"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R590c14d3a8784ddc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Re894c3df7609458a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rfe2264cb78834e68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rcef070865666423e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Ra758181d7ec24bf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Re27f8ab7e763412a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R05a3c125be754c1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Reafb038924914267"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Re4fb5b4cd2ac4e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rab5413d73b77452d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R5013d6b0447848d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R2d6b55bc21a24fee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R1c6c5f2d3c204364"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb9d1564938e94a49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rad9a2e8441514167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R94bcdaf42410423b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rd52af11e14404686"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Raa2e9ecda7e543a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Re0a6b05949c24f42"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rab5413d73b77452d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R5013d6b0447848d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R2d6b55bc21a24fee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R1c6c5f2d3c204364"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb9d1564938e94a49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rad9a2e8441514167"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R94bcdaf42410423b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rd52af11e14404686"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Raa2e9ecda7e543a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Re0a6b05949c24f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R62734a64920241b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rd170c8f1d5e7450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Ra54df0a4ac7d4c86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R5c65c0380f3c4a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R6b6aca0d4fb94006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R61b91188e0d448b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rab8d2b8494664326"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Re3d06c5666264494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R7e98ef4e4d7545b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R6ef65ce582464e1d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-09-30</x:v>
+        <x:v>2026-10-01</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R62734a64920241b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rd170c8f1d5e7450d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Ra54df0a4ac7d4c86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R5c65c0380f3c4a13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R6b6aca0d4fb94006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R61b91188e0d448b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rab8d2b8494664326"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Re3d06c5666264494"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R7e98ef4e4d7545b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R6ef65ce582464e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Reb022a16ee0b4802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R96482aa3969e46ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rdd13e910c29a4bac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rf9fe1811a0be4e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R724e23ce61f34746"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R82df6a0b48da4b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R4ba7c5b4866a428f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R50f822f4747b4fc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R4385f11a3c70460c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R82b663cee67a4e2e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Reb022a16ee0b4802"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R96482aa3969e46ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rdd13e910c29a4bac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rf9fe1811a0be4e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R724e23ce61f34746"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R82df6a0b48da4b87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R4ba7c5b4866a428f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R50f822f4747b4fc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R4385f11a3c70460c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R82b663cee67a4e2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rc5ee8b8b53694b6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R2dd9c1f51c414554"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rdf2349e7cf2147d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R908fb3a2237541b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R9a2f3ff46f3945ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2e17235b7eec4c78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Re1fcf66ba870487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R41b1a506c91248e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R3294a232044f4f73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R72ada355d5a347db"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-10-01</x:v>
+        <x:v>2026-10-02</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rc5ee8b8b53694b6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R2dd9c1f51c414554"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rdf2349e7cf2147d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R908fb3a2237541b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R9a2f3ff46f3945ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2e17235b7eec4c78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Re1fcf66ba870487a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R41b1a506c91248e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R3294a232044f4f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R72ada355d5a347db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rebbe631dfefe4823"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Ra9ff0ba035244e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R8210ecc971674b69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Re0d7bc5b2f064e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R01ae8a875ca944b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R577fae6022f74a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R39b2dc7a887442c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R07b4a4ee12b6460b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R59c3ae5ae5d14e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R7a67039c729b43c1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rebbe631dfefe4823"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Ra9ff0ba035244e7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R8210ecc971674b69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Re0d7bc5b2f064e23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R01ae8a875ca944b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R577fae6022f74a0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R39b2dc7a887442c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R07b4a4ee12b6460b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R59c3ae5ae5d14e74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R7a67039c729b43c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rd35297173fc8477c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R2e7109aa83eb4584"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4c716339613848e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R4228e925bda14569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R440176c3b1b74b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R4947b8966a5b48ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rb4eb3b8832324b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2113649f14e64a50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R8728e3a7d22c4415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rd6d1d3f52cf042a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-10-02</x:v>
+        <x:v>2026-10-05</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rd35297173fc8477c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R2e7109aa83eb4584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R4c716339613848e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R4228e925bda14569"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R440176c3b1b74b43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R4947b8966a5b48ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rb4eb3b8832324b43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2113649f14e64a50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R8728e3a7d22c4415"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rd6d1d3f52cf042a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R6d4473ac122e46db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R80fdebd26bdf46ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb2bfc1322cbd4f7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R85a9c19cc30640c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rfae57b7d6950455b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R0b889c5ff15c4014"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R7eae8daa5e864727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rb6a984c879c643fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R6034a0d7e62c4bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Ra99aadf064cf4f43"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R6d4473ac122e46db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R80fdebd26bdf46ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb2bfc1322cbd4f7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R85a9c19cc30640c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rfae57b7d6950455b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R0b889c5ff15c4014"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R7eae8daa5e864727"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rb6a984c879c643fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R6034a0d7e62c4bf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Ra99aadf064cf4f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3658e44ce65a43c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rcf1b0d0bf84e453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R2cb5a05821fb4d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R9e079690947f4dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R2f9050b3945c433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R8df6e8dec9354592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R7e9a178b6790443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R8d33b9029c0c4553"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R5cb05934126540ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R92d9482c6c57481e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-10-05</x:v>
+        <x:v>2026-10-06</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3658e44ce65a43c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rcf1b0d0bf84e453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R2cb5a05821fb4d60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R9e079690947f4dde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R2f9050b3945c433e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R8df6e8dec9354592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R7e9a178b6790443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R8d33b9029c0c4553"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R5cb05934126540ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R92d9482c6c57481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R05d367828cc84194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R7d6acf3379734c72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R5d6aa9ba6c7346df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R35ba42f6a44242e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R297b5a2364ef412a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R6aa4affc97464ff2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd3310dba433f4fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2a6a16fdc68e4c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Refb7d8b9816743d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R2a74a4981861420d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R05d367828cc84194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R7d6acf3379734c72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R5d6aa9ba6c7346df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R35ba42f6a44242e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R297b5a2364ef412a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R6aa4affc97464ff2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd3310dba433f4fc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2a6a16fdc68e4c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Refb7d8b9816743d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R2a74a4981861420d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R9aaadffc01924284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R894fe58a25b146a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rfb21876df0da489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc246a75302cd4b4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rbd5fec71fcfe42ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2bdd23350a7e4585"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rab9e6d8281984778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rab14dd7769e34a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R66faedf02070457a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R3d7c9389b52f4b68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-10-06</x:v>
+        <x:v>2026-10-07</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R9aaadffc01924284"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R894fe58a25b146a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rfb21876df0da489a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rc246a75302cd4b4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rbd5fec71fcfe42ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2bdd23350a7e4585"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rab9e6d8281984778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rab14dd7769e34a03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R66faedf02070457a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R3d7c9389b52f4b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R05f73db0848f46c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rf825c45c3b0c4d27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R59dd2002c4bd4c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R37ca5c87b6a247b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rfdaab986f60b4c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R367ae60e6c9e4395"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rf835d3777698407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R29505ee006c84d71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rfbd9fb8cb0cf4a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R7db3a17b23574605"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R1c7ab1a596b04b1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rf521ba8a85724a71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rea699e40cbe74326"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R421bb621b2ab44d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Ra5272d32ed6b4a28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R2142f9c4269d42ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rbd482cf3ed0248c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R45b71b5d207b4fd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R25a19949cef24c44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R07f6ba5b6ae74300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R00ed2e0ff6034bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R401a21c4fb5d4183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb44de31d4b844073"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R06145364d4094055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Re2f2c6423cbd4092"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R5cdaef5068c04ab3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R519892cbf1784a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R42b6d23cc64c44bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R2ccc7650e438471d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R12ca275c6ea544fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-09-30</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4310.4</x:v>
+        <x:v>4331.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4278</x:v>
+        <x:v>4218.6</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>32.4</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>13008.6</x:v>
+        <x:v>13121.6</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>71.9</x:v>
+        <x:v>72.1</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,22 +693,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-09-30</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2782.2</x:v>
+        <x:v>2798.4</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2762</x:v>
+        <x:v>2747.4</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>20.2</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7234.4</x:v>
+        <x:v>7285.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>40</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-09-30</x:v>
+        <x:v>2026-10-08</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>121220</x:v>
+        <x:v>126800</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>119100</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>2120</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1438440</x:v>
+        <x:v>1445240</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>7947.2</x:v>
+        <x:v>7940.9</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -8210,6 +8210,130 @@
       </x:c>
       <x:c r="K227" s="30"/>
     </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="17" t="str">
+        <x:v>10月</x:v>
+      </x:c>
+      <x:c r="B229" s="17"/>
+      <x:c r="C229" s="17"/>
+      <x:c r="D229" s="17"/>
+      <x:c r="E229" s="17"/>
+      <x:c r="F229" s="17"/>
+      <x:c r="G229" s="17"/>
+      <x:c r="H229" s="17"/>
+      <x:c r="I229" s="17"/>
+      <x:c r="J229" s="17"/>
+      <x:c r="K229" s="17"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B230" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C230" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D230" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E230" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F230" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G230" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H230" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I230" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J230" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K230" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B231" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C231" s="22" t="str">
+        <x:v>10月8日</x:v>
+      </x:c>
+      <x:c r="D231" s="23" t="n">
+        <x:v>120020</x:v>
+      </x:c>
+      <x:c r="E231" s="23" t="n">
+        <x:v>126800</x:v>
+      </x:c>
+      <x:c r="F231" s="23" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="G231" s="23" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="H231" s="28" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I231" s="24" t="n">
+        <x:v>0.0018367006177992806</x:v>
+      </x:c>
+      <x:c r="J231" s="26" t="n">
+        <x:f>ROUND(E231-F231,1)</x:f>
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="K231" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B232" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C232" s="30"/>
+      <x:c r="D232" s="30"/>
+      <x:c r="E232" s="30"/>
+      <x:c r="F232" s="30"/>
+      <x:c r="G232" s="30"/>
+      <x:c r="H232" s="30"/>
+      <x:c r="I232" s="30"/>
+      <x:c r="J232" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J231),1)</x:f>
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="K232" s="30"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B233" s="30"/>
+      <x:c r="C233" s="30"/>
+      <x:c r="D233" s="30"/>
+      <x:c r="E233" s="30"/>
+      <x:c r="F233" s="30"/>
+      <x:c r="G233" s="30"/>
+      <x:c r="H233" s="30"/>
+      <x:c r="I233" s="30"/>
+      <x:c r="J233" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="K233" s="30"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K1"/>
@@ -8222,6 +8346,7 @@
     <x:mergeCell ref="A149:K149"/>
     <x:mergeCell ref="A177:K177"/>
     <x:mergeCell ref="A203:K203"/>
+    <x:mergeCell ref="A229:K229"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -17558,155 +17683,155 @@
       </x:c>
     </x:row>
     <x:row r="263">
-      <x:c r="A263" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B263" s="30" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C263" s="30"/>
-      <x:c r="D263" s="30"/>
-      <x:c r="E263" s="30"/>
-      <x:c r="F263" s="30"/>
-      <x:c r="G263" s="30"/>
-      <x:c r="H263" s="30"/>
-      <x:c r="I263" s="32" t="n">
-        <x:f>ROUND(SUM(I225:I262),1)</x:f>
-        <x:v>5987.4</x:v>
-      </x:c>
-      <x:c r="J263" s="30"/>
-      <x:c r="K263" s="30"/>
+      <x:c r="A263" s="22" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B263" s="22" t="str">
+        <x:v>10月8日</x:v>
+      </x:c>
+      <x:c r="C263" s="23" t="n">
+        <x:v>4300.8</x:v>
+      </x:c>
+      <x:c r="D263" s="23" t="n">
+        <x:v>4331.6</x:v>
+      </x:c>
+      <x:c r="E263" s="23" t="n">
+        <x:v>4218.6</x:v>
+      </x:c>
+      <x:c r="F263" s="23" t="n">
+        <x:v>4248</x:v>
+      </x:c>
+      <x:c r="G263" s="23" t="n">
+        <x:f>ROUND(F263-F262,1)</x:f>
+        <x:v>-52.8</x:v>
+      </x:c>
+      <x:c r="H263" s="24" t="n">
+        <x:f>IFERROR(F263/F262-1,"")</x:f>
+        <x:v>-0.01227678571428581</x:v>
+      </x:c>
+      <x:c r="I263" s="26" t="n">
+        <x:f>ROUND(D263-E263,1)</x:f>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="J263" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
+      <x:c r="K263" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B264" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B264" s="30" t="n">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="C264" s="30"/>
       <x:c r="D264" s="30"/>
       <x:c r="E264" s="30"/>
       <x:c r="F264" s="30"/>
       <x:c r="G264" s="30"/>
       <x:c r="H264" s="30"/>
-      <x:c r="I264" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I225:I262),0),1)</x:f>
-        <x:v>157.6</x:v>
+      <x:c r="I264" s="32" t="n">
+        <x:f>ROUND(SUM(I225:I263),1)</x:f>
+        <x:v>6100.4</x:v>
       </x:c>
       <x:c r="J264" s="30"/>
       <x:c r="K264" s="30"/>
     </x:row>
-    <x:row r="266">
-      <x:c r="A266" s="17" t="str">
+    <x:row r="265">
+      <x:c r="A265" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B265" s="30"/>
+      <x:c r="C265" s="30"/>
+      <x:c r="D265" s="30"/>
+      <x:c r="E265" s="30"/>
+      <x:c r="F265" s="30"/>
+      <x:c r="G265" s="30"/>
+      <x:c r="H265" s="30"/>
+      <x:c r="I265" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I225:I263),0),1)</x:f>
+        <x:v>156.4</x:v>
+      </x:c>
+      <x:c r="J265" s="30"/>
+      <x:c r="K265" s="30"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="17" t="str">
         <x:v>IH主力</x:v>
       </x:c>
-      <x:c r="B266" s="17"/>
-      <x:c r="C266" s="17"/>
-      <x:c r="D266" s="17"/>
-      <x:c r="E266" s="17"/>
-      <x:c r="F266" s="17"/>
-      <x:c r="G266" s="17"/>
-      <x:c r="H266" s="17"/>
-      <x:c r="I266" s="17"/>
-      <x:c r="J266" s="17"/>
-      <x:c r="K266" s="17"/>
-    </x:row>
-    <x:row r="267">
-      <x:c r="A267" s="20" t="str">
+      <x:c r="B267" s="17"/>
+      <x:c r="C267" s="17"/>
+      <x:c r="D267" s="17"/>
+      <x:c r="E267" s="17"/>
+      <x:c r="F267" s="17"/>
+      <x:c r="G267" s="17"/>
+      <x:c r="H267" s="17"/>
+      <x:c r="I267" s="17"/>
+      <x:c r="J267" s="17"/>
+      <x:c r="K267" s="17"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B267" s="20" t="str">
+      <x:c r="B268" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C267" s="20" t="str">
+      <x:c r="C268" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D267" s="20" t="str">
+      <x:c r="D268" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E267" s="20" t="str">
+      <x:c r="E268" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F267" s="20" t="str">
+      <x:c r="F268" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G267" s="20" t="str">
+      <x:c r="G268" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H267" s="20" t="str">
+      <x:c r="H268" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I267" s="20" t="str">
+      <x:c r="I268" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J267" s="20" t="str">
+      <x:c r="J268" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K267" s="20" t="str">
+      <x:c r="K268" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="268">
-      <x:c r="A268" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B268" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C268" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="D268" s="23" t="n">
-        <x:v>3165.6</x:v>
-      </x:c>
-      <x:c r="E268" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="F268" s="23" t="n">
-        <x:v>3134.8</x:v>
-      </x:c>
-      <x:c r="G268" s="23"/>
-      <x:c r="H268" s="24"/>
-      <x:c r="I268" s="26" t="n">
-        <x:f>ROUND(D268-E268,1)</x:f>
-        <x:v>124.8</x:v>
-      </x:c>
-      <x:c r="J268" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K268" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B269" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C269" s="23" t="n">
-        <x:v>3148.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="D269" s="23" t="n">
-        <x:v>3181.2</x:v>
+        <x:v>3165.6</x:v>
       </x:c>
       <x:c r="E269" s="23" t="n">
-        <x:v>3074.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="F269" s="23" t="n">
-        <x:v>3084.4</x:v>
-      </x:c>
-      <x:c r="G269" s="23" t="n">
-        <x:f>ROUND(F269-F268,1)</x:f>
-        <x:v>-50.4</x:v>
-      </x:c>
-      <x:c r="H269" s="24" t="n">
-        <x:f>IFERROR(F269/F268-1,"")</x:f>
-        <x:v>-0.016077580706903127</x:v>
-      </x:c>
+        <x:v>3134.8</x:v>
+      </x:c>
+      <x:c r="G269" s="23"/>
+      <x:c r="H269" s="24"/>
       <x:c r="I269" s="26" t="n">
         <x:f>ROUND(D269-E269,1)</x:f>
-        <x:v>106.8</x:v>
+        <x:v>124.8</x:v>
       </x:c>
       <x:c r="J269" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17717,34 +17842,34 @@
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B270" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C270" s="23" t="n">
-        <x:v>3081.2</x:v>
+        <x:v>3148.4</x:v>
       </x:c>
       <x:c r="D270" s="23" t="n">
-        <x:v>3102.6</x:v>
+        <x:v>3181.2</x:v>
       </x:c>
       <x:c r="E270" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074.4</x:v>
       </x:c>
       <x:c r="F270" s="23" t="n">
-        <x:v>3037.8</x:v>
+        <x:v>3084.4</x:v>
       </x:c>
       <x:c r="G270" s="23" t="n">
         <x:f>ROUND(F270-F269,1)</x:f>
-        <x:v>-46.6</x:v>
+        <x:v>-50.4</x:v>
       </x:c>
       <x:c r="H270" s="24" t="n">
         <x:f>IFERROR(F270/F269-1,"")</x:f>
-        <x:v>-0.015108286862923093</x:v>
+        <x:v>-0.016077580706903127</x:v>
       </x:c>
       <x:c r="I270" s="26" t="n">
         <x:f>ROUND(D270-E270,1)</x:f>
-        <x:v>66.4</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J270" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17755,34 +17880,34 @@
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B271" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C271" s="23" t="n">
-        <x:v>3049.8</x:v>
+        <x:v>3081.2</x:v>
       </x:c>
       <x:c r="D271" s="23" t="n">
-        <x:v>3136.6</x:v>
+        <x:v>3102.6</x:v>
       </x:c>
       <x:c r="E271" s="23" t="n">
-        <x:v>3044</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="F271" s="23" t="n">
-        <x:v>3074</x:v>
+        <x:v>3037.8</x:v>
       </x:c>
       <x:c r="G271" s="23" t="n">
         <x:f>ROUND(F271-F270,1)</x:f>
-        <x:v>36.2</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H271" s="24" t="n">
         <x:f>IFERROR(F271/F270-1,"")</x:f>
-        <x:v>0.011916518533148901</x:v>
+        <x:v>-0.015108286862923093</x:v>
       </x:c>
       <x:c r="I271" s="26" t="n">
         <x:f>ROUND(D271-E271,1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J271" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17793,34 +17918,34 @@
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B272" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C272" s="23" t="n">
-        <x:v>3039.4</x:v>
+        <x:v>3049.8</x:v>
       </x:c>
       <x:c r="D272" s="23" t="n">
-        <x:v>3081</x:v>
+        <x:v>3136.6</x:v>
       </x:c>
       <x:c r="E272" s="23" t="n">
-        <x:v>2984</x:v>
+        <x:v>3044</x:v>
       </x:c>
       <x:c r="F272" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074</x:v>
       </x:c>
       <x:c r="G272" s="23" t="n">
         <x:f>ROUND(F272-F271,1)</x:f>
-        <x:v>-37.8</x:v>
+        <x:v>36.2</x:v>
       </x:c>
       <x:c r="H272" s="24" t="n">
         <x:f>IFERROR(F272/F271-1,"")</x:f>
-        <x:v>-0.012296681847755453</x:v>
+        <x:v>0.011916518533148901</x:v>
       </x:c>
       <x:c r="I272" s="26" t="n">
         <x:f>ROUND(D272-E272,1)</x:f>
-        <x:v>97</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="J272" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17831,34 +17956,34 @@
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B273" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C273" s="23" t="n">
-        <x:v>3060.6</x:v>
+        <x:v>3039.4</x:v>
       </x:c>
       <x:c r="D273" s="23" t="n">
-        <x:v>3098</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E273" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="F273" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="G273" s="23" t="n">
         <x:f>ROUND(F273-F272,1)</x:f>
-        <x:v>-16.2</x:v>
+        <x:v>-37.8</x:v>
       </x:c>
       <x:c r="H273" s="24" t="n">
         <x:f>IFERROR(F273/F272-1,"")</x:f>
-        <x:v>-0.005335616889532879</x:v>
+        <x:v>-0.012296681847755453</x:v>
       </x:c>
       <x:c r="I273" s="26" t="n">
         <x:f>ROUND(D273-E273,1)</x:f>
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J273" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17869,110 +17994,110 @@
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B274" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C274" s="23" t="n">
-        <x:v>3049.2</x:v>
+        <x:v>3060.6</x:v>
       </x:c>
       <x:c r="D274" s="23" t="n">
-        <x:v>3086.4</x:v>
+        <x:v>3098</x:v>
       </x:c>
       <x:c r="E274" s="23" t="n">
-        <x:v>3022</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="F274" s="23" t="n">
-        <x:v>3045.4</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="G274" s="23" t="n">
         <x:f>ROUND(F274-F273,1)</x:f>
-        <x:v>25.4</x:v>
+        <x:v>-16.2</x:v>
       </x:c>
       <x:c r="H274" s="24" t="n">
         <x:f>IFERROR(F274/F273-1,"")</x:f>
-        <x:v>0.008410596026490191</x:v>
+        <x:v>-0.005335616889532879</x:v>
       </x:c>
       <x:c r="I274" s="26" t="n">
         <x:f>ROUND(D274-E274,1)</x:f>
-        <x:v>64.4</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J274" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K274" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B275" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C275" s="23" t="n">
-        <x:v>3038</x:v>
+        <x:v>3049.2</x:v>
       </x:c>
       <x:c r="D275" s="23" t="n">
-        <x:v>3056</x:v>
+        <x:v>3086.4</x:v>
       </x:c>
       <x:c r="E275" s="23" t="n">
-        <x:v>2950</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="F275" s="23" t="n">
-        <x:v>2990</x:v>
+        <x:v>3045.4</x:v>
       </x:c>
       <x:c r="G275" s="23" t="n">
         <x:f>ROUND(F275-F274,1)</x:f>
-        <x:v>-55.4</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="H275" s="24" t="n">
         <x:f>IFERROR(F275/F274-1,"")</x:f>
-        <x:v>-0.018191370591712164</x:v>
+        <x:v>0.008410596026490191</x:v>
       </x:c>
       <x:c r="I275" s="26" t="n">
         <x:f>ROUND(D275-E275,1)</x:f>
-        <x:v>106</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="J275" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K275" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B276" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C276" s="23" t="n">
-        <x:v>2965.4</x:v>
+        <x:v>3038</x:v>
       </x:c>
       <x:c r="D276" s="23" t="n">
-        <x:v>2989</x:v>
+        <x:v>3056</x:v>
       </x:c>
       <x:c r="E276" s="23" t="n">
-        <x:v>2912.6</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="F276" s="23" t="n">
-        <x:v>2957</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="G276" s="23" t="n">
         <x:f>ROUND(F276-F275,1)</x:f>
-        <x:v>-33</x:v>
+        <x:v>-55.4</x:v>
       </x:c>
       <x:c r="H276" s="24" t="n">
         <x:f>IFERROR(F276/F275-1,"")</x:f>
-        <x:v>-0.011036789297658833</x:v>
+        <x:v>-0.018191370591712164</x:v>
       </x:c>
       <x:c r="I276" s="26" t="n">
         <x:f>ROUND(D276-E276,1)</x:f>
-        <x:v>76.4</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J276" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -17983,34 +18108,34 @@
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B277" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C277" s="23" t="n">
-        <x:v>2953</x:v>
+        <x:v>2965.4</x:v>
       </x:c>
       <x:c r="D277" s="23" t="n">
-        <x:v>2996.6</x:v>
+        <x:v>2989</x:v>
       </x:c>
       <x:c r="E277" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2912.6</x:v>
       </x:c>
       <x:c r="F277" s="23" t="n">
-        <x:v>2898.4</x:v>
+        <x:v>2957</x:v>
       </x:c>
       <x:c r="G277" s="23" t="n">
         <x:f>ROUND(F277-F276,1)</x:f>
-        <x:v>-58.6</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="H277" s="24" t="n">
         <x:f>IFERROR(F277/F276-1,"")</x:f>
-        <x:v>-0.019817382482245516</x:v>
+        <x:v>-0.011036789297658833</x:v>
       </x:c>
       <x:c r="I277" s="26" t="n">
         <x:f>ROUND(D277-E277,1)</x:f>
-        <x:v>100.6</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="J277" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -18021,37 +18146,37 @@
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B278" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C278" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2953</x:v>
       </x:c>
       <x:c r="D278" s="23" t="n">
-        <x:v>2847.6</x:v>
+        <x:v>2996.6</x:v>
       </x:c>
       <x:c r="E278" s="23" t="n">
-        <x:v>2750.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="F278" s="23" t="n">
-        <x:v>2814.4</x:v>
+        <x:v>2898.4</x:v>
       </x:c>
       <x:c r="G278" s="23" t="n">
         <x:f>ROUND(F278-F277,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-58.6</x:v>
       </x:c>
       <x:c r="H278" s="24" t="n">
         <x:f>IFERROR(F278/F277-1,"")</x:f>
-        <x:v>-0.028981507038365995</x:v>
+        <x:v>-0.019817382482245516</x:v>
       </x:c>
       <x:c r="I278" s="26" t="n">
         <x:f>ROUND(D278-E278,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="J278" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K278" s="22" t="n">
         <x:v>5</x:v>
@@ -18059,34 +18184,34 @@
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
-        <x:v>2794.8</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D279" s="23" t="n">
-        <x:v>2865.4</x:v>
+        <x:v>2847.6</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>2780.4</x:v>
+        <x:v>2750.8</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>2804.4</x:v>
+        <x:v>2814.4</x:v>
       </x:c>
       <x:c r="G279" s="23" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>-0.0035531552018192025</x:v>
+        <x:v>-0.028981507038365995</x:v>
       </x:c>
       <x:c r="I279" s="26" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>85</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18097,110 +18222,110 @@
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B280" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C280" s="23" t="n">
-        <x:v>2810.4</x:v>
+        <x:v>2794.8</x:v>
       </x:c>
       <x:c r="D280" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2865.4</x:v>
       </x:c>
       <x:c r="E280" s="23" t="n">
-        <x:v>2797.2</x:v>
+        <x:v>2780.4</x:v>
       </x:c>
       <x:c r="F280" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2804.4</x:v>
       </x:c>
       <x:c r="G280" s="23" t="n">
         <x:f>ROUND(F280-F279,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H280" s="24" t="n">
         <x:f>IFERROR(F280/F279-1,"")</x:f>
-        <x:v>0.02453287690771644</x:v>
+        <x:v>-0.0035531552018192025</x:v>
       </x:c>
       <x:c r="I280" s="26" t="n">
         <x:f>ROUND(D280-E280,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J280" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K280" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B281" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C281" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2810.4</x:v>
       </x:c>
       <x:c r="D281" s="23" t="n">
-        <x:v>2930.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="E281" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2797.2</x:v>
       </x:c>
       <x:c r="F281" s="23" t="n">
-        <x:v>2888</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="G281" s="23" t="n">
         <x:f>ROUND(F281-F280,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>68.8</x:v>
       </x:c>
       <x:c r="H281" s="24" t="n">
         <x:f>IFERROR(F281/F280-1,"")</x:f>
-        <x:v>0.005151051092858294</x:v>
+        <x:v>0.02453287690771644</x:v>
       </x:c>
       <x:c r="I281" s="26" t="n">
         <x:f>ROUND(D281-E281,1)</x:f>
-        <x:v>70.8</x:v>
+        <x:v>98.8</x:v>
       </x:c>
       <x:c r="J281" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K281" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B282" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C282" s="23" t="n">
-        <x:v>2900.8</x:v>
+        <x:v>2864.6</x:v>
       </x:c>
       <x:c r="D282" s="23" t="n">
-        <x:v>2934.2</x:v>
+        <x:v>2930.8</x:v>
       </x:c>
       <x:c r="E282" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="F282" s="23" t="n">
-        <x:v>2929</x:v>
+        <x:v>2888</x:v>
       </x:c>
       <x:c r="G282" s="23" t="n">
         <x:f>ROUND(F282-F281,1)</x:f>
-        <x:v>41</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H282" s="24" t="n">
         <x:f>IFERROR(F282/F281-1,"")</x:f>
-        <x:v>0.014196675900276956</x:v>
-      </x:c>
-      <x:c r="I282" s="23" t="n">
+        <x:v>0.005151051092858294</x:v>
+      </x:c>
+      <x:c r="I282" s="26" t="n">
         <x:f>ROUND(D282-E282,1)</x:f>
-        <x:v>43.2</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="J282" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18211,148 +18336,148 @@
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B283" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C283" s="23" t="n">
-        <x:v>2929.2</x:v>
+        <x:v>2900.8</x:v>
       </x:c>
       <x:c r="D283" s="23" t="n">
-        <x:v>2970</x:v>
+        <x:v>2934.2</x:v>
       </x:c>
       <x:c r="E283" s="23" t="n">
-        <x:v>2917</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F283" s="23" t="n">
-        <x:v>2968.8</x:v>
+        <x:v>2929</x:v>
       </x:c>
       <x:c r="G283" s="23" t="n">
         <x:f>ROUND(F283-F282,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H283" s="24" t="n">
         <x:f>IFERROR(F283/F282-1,"")</x:f>
-        <x:v>0.013588255377261937</x:v>
+        <x:v>0.014196675900276956</x:v>
       </x:c>
       <x:c r="I283" s="23" t="n">
         <x:f>ROUND(D283-E283,1)</x:f>
-        <x:v>53</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J283" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K283" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B284" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C284" s="23" t="n">
-        <x:v>2995.2</x:v>
+        <x:v>2929.2</x:v>
       </x:c>
       <x:c r="D284" s="23" t="n">
-        <x:v>3024.8</x:v>
+        <x:v>2970</x:v>
       </x:c>
       <x:c r="E284" s="23" t="n">
-        <x:v>2969.2</x:v>
+        <x:v>2917</x:v>
       </x:c>
       <x:c r="F284" s="23" t="n">
-        <x:v>2981.6</x:v>
+        <x:v>2968.8</x:v>
       </x:c>
       <x:c r="G284" s="23" t="n">
         <x:f>ROUND(F284-F283,1)</x:f>
-        <x:v>12.8</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="H284" s="24" t="n">
         <x:f>IFERROR(F284/F283-1,"")</x:f>
-        <x:v>0.0043115063325247505</x:v>
+        <x:v>0.013588255377261937</x:v>
       </x:c>
       <x:c r="I284" s="23" t="n">
         <x:f>ROUND(D284-E284,1)</x:f>
-        <x:v>55.6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J284" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K284" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B285" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C285" s="23" t="n">
-        <x:v>2997.6</x:v>
+        <x:v>2995.2</x:v>
       </x:c>
       <x:c r="D285" s="23" t="n">
-        <x:v>3041.8</x:v>
+        <x:v>3024.8</x:v>
       </x:c>
       <x:c r="E285" s="23" t="n">
-        <x:v>2927</x:v>
+        <x:v>2969.2</x:v>
       </x:c>
       <x:c r="F285" s="23" t="n">
-        <x:v>2945</x:v>
+        <x:v>2981.6</x:v>
       </x:c>
       <x:c r="G285" s="23" t="n">
         <x:f>ROUND(F285-F284,1)</x:f>
-        <x:v>-36.6</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="H285" s="24" t="n">
         <x:f>IFERROR(F285/F284-1,"")</x:f>
-        <x:v>-0.012275288435739218</x:v>
-      </x:c>
-      <x:c r="I285" s="26" t="n">
+        <x:v>0.0043115063325247505</x:v>
+      </x:c>
+      <x:c r="I285" s="23" t="n">
         <x:f>ROUND(D285-E285,1)</x:f>
-        <x:v>114.8</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="J285" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K285" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B286" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C286" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2997.6</x:v>
       </x:c>
       <x:c r="D286" s="23" t="n">
-        <x:v>2981.8</x:v>
+        <x:v>3041.8</x:v>
       </x:c>
       <x:c r="E286" s="23" t="n">
-        <x:v>2893.2</x:v>
+        <x:v>2927</x:v>
       </x:c>
       <x:c r="F286" s="23" t="n">
-        <x:v>2899.2</x:v>
+        <x:v>2945</x:v>
       </x:c>
       <x:c r="G286" s="23" t="n">
         <x:f>ROUND(F286-F285,1)</x:f>
-        <x:v>-45.8</x:v>
+        <x:v>-36.6</x:v>
       </x:c>
       <x:c r="H286" s="24" t="n">
         <x:f>IFERROR(F286/F285-1,"")</x:f>
-        <x:v>-0.015551782682512783</x:v>
+        <x:v>-0.012275288435739218</x:v>
       </x:c>
       <x:c r="I286" s="26" t="n">
         <x:f>ROUND(D286-E286,1)</x:f>
-        <x:v>88.6</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="J286" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18363,34 +18488,34 @@
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
-        <x:v>2910.8</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>2960</x:v>
+        <x:v>2981.8</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
-        <x:v>2871</x:v>
+        <x:v>2893.2</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2899.2</x:v>
       </x:c>
       <x:c r="G287" s="23" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>1.4</x:v>
+        <x:v>-45.8</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>0.0004828918322297149</x:v>
+        <x:v>-0.015551782682512783</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>89</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18401,34 +18526,34 @@
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B288" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C288" s="23" t="n">
-        <x:v>2901</x:v>
+        <x:v>2910.8</x:v>
       </x:c>
       <x:c r="D288" s="23" t="n">
-        <x:v>2924.2</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="E288" s="23" t="n">
-        <x:v>2841.6</x:v>
+        <x:v>2871</x:v>
       </x:c>
       <x:c r="F288" s="23" t="n">
-        <x:v>2844</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="G288" s="23" t="n">
         <x:f>ROUND(F288-F287,1)</x:f>
-        <x:v>-56.6</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H288" s="24" t="n">
         <x:f>IFERROR(F288/F287-1,"")</x:f>
-        <x:v>-0.019513204164655518</x:v>
+        <x:v>0.0004828918322297149</x:v>
       </x:c>
       <x:c r="I288" s="26" t="n">
         <x:f>ROUND(D288-E288,1)</x:f>
-        <x:v>82.6</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J288" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18439,34 +18564,34 @@
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B289" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C289" s="23" t="n">
-        <x:v>2808.4</x:v>
+        <x:v>2901</x:v>
       </x:c>
       <x:c r="D289" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2924.2</x:v>
       </x:c>
       <x:c r="E289" s="23" t="n">
-        <x:v>2791.2</x:v>
+        <x:v>2841.6</x:v>
       </x:c>
       <x:c r="F289" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G289" s="23" t="n">
         <x:f>ROUND(F289-F288,1)</x:f>
-        <x:v>53.2</x:v>
+        <x:v>-56.6</x:v>
       </x:c>
       <x:c r="H289" s="24" t="n">
         <x:f>IFERROR(F289/F288-1,"")</x:f>
-        <x:v>0.01870604781997187</x:v>
+        <x:v>-0.019513204164655518</x:v>
       </x:c>
       <x:c r="I289" s="26" t="n">
         <x:f>ROUND(D289-E289,1)</x:f>
-        <x:v>111.4</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J289" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18477,113 +18602,113 @@
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B290" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C290" s="23" t="n">
-        <x:v>2926.2</x:v>
+        <x:v>2808.4</x:v>
       </x:c>
       <x:c r="D290" s="23" t="n">
-        <x:v>2954.6</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="E290" s="23" t="n">
-        <x:v>2903.4</x:v>
+        <x:v>2791.2</x:v>
       </x:c>
       <x:c r="F290" s="23" t="n">
-        <x:v>2941</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G290" s="23" t="n">
         <x:f>ROUND(F290-F289,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="H290" s="24" t="n">
         <x:f>IFERROR(F290/F289-1,"")</x:f>
-        <x:v>0.01511804500897429</x:v>
-      </x:c>
-      <x:c r="I290" s="23" t="n">
+        <x:v>0.01870604781997187</x:v>
+      </x:c>
+      <x:c r="I290" s="26" t="n">
         <x:f>ROUND(D290-E290,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="J290" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K290" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B291" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C291" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2926.2</x:v>
       </x:c>
       <x:c r="D291" s="23" t="n">
-        <x:v>2996</x:v>
+        <x:v>2954.6</x:v>
       </x:c>
       <x:c r="E291" s="23" t="n">
-        <x:v>2834.8</x:v>
+        <x:v>2903.4</x:v>
       </x:c>
       <x:c r="F291" s="23" t="n">
-        <x:v>2859</x:v>
+        <x:v>2941</x:v>
       </x:c>
       <x:c r="G291" s="23" t="n">
         <x:f>ROUND(F291-F290,1)</x:f>
-        <x:v>-82</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="H291" s="24" t="n">
         <x:f>IFERROR(F291/F290-1,"")</x:f>
-        <x:v>-0.02788167290037402</x:v>
-      </x:c>
-      <x:c r="I291" s="26" t="n">
+        <x:v>0.01511804500897429</x:v>
+      </x:c>
+      <x:c r="I291" s="23" t="n">
         <x:f>ROUND(D291-E291,1)</x:f>
-        <x:v>161.2</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J291" s="22" t="str">
-        <x:v>IH2606/IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K291" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B292" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C292" s="23" t="n">
-        <x:v>2870</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D292" s="23" t="n">
-        <x:v>2976</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="E292" s="23" t="n">
-        <x:v>2861.8</x:v>
+        <x:v>2834.8</x:v>
       </x:c>
       <x:c r="F292" s="23" t="n">
-        <x:v>2886.6</x:v>
+        <x:v>2859</x:v>
       </x:c>
       <x:c r="G292" s="23" t="n">
         <x:f>ROUND(F292-F291,1)</x:f>
-        <x:v>27.6</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="H292" s="24" t="n">
         <x:f>IFERROR(F292/F291-1,"")</x:f>
-        <x:v>0.009653725078698772</x:v>
+        <x:v>-0.02788167290037402</x:v>
       </x:c>
       <x:c r="I292" s="26" t="n">
         <x:f>ROUND(D292-E292,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>161.2</x:v>
       </x:c>
       <x:c r="J292" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606/IH2609</x:v>
       </x:c>
       <x:c r="K292" s="22" t="n">
         <x:v>5</x:v>
@@ -18591,34 +18716,34 @@
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B293" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
-        <x:v>2899</x:v>
+        <x:v>2870</x:v>
       </x:c>
       <x:c r="D293" s="23" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="E293" s="23" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2861.8</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>2910.2</x:v>
+        <x:v>2886.6</x:v>
       </x:c>
       <x:c r="G293" s="23" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>23.6</x:v>
+        <x:v>27.6</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>0.008175708445922414</x:v>
+        <x:v>0.009653725078698772</x:v>
       </x:c>
       <x:c r="I293" s="26" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
-        <x:v>121.4</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="J293" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18629,34 +18754,34 @@
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B294" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C294" s="23" t="n">
-        <x:v>2895.8</x:v>
+        <x:v>2899</x:v>
       </x:c>
       <x:c r="D294" s="23" t="n">
-        <x:v>2924</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="E294" s="23" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="F294" s="23" t="n">
-        <x:v>2796.4</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="G294" s="23" t="n">
         <x:f>ROUND(F294-F293,1)</x:f>
-        <x:v>-113.8</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="H294" s="24" t="n">
         <x:f>IFERROR(F294/F293-1,"")</x:f>
-        <x:v>-0.039103841660366845</x:v>
+        <x:v>0.008175708445922414</x:v>
       </x:c>
       <x:c r="I294" s="26" t="n">
         <x:f>ROUND(D294-E294,1)</x:f>
-        <x:v>141.4</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J294" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18667,34 +18792,34 @@
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B295" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2895.8</x:v>
       </x:c>
       <x:c r="D295" s="23" t="n">
-        <x:v>2978</x:v>
+        <x:v>2924</x:v>
       </x:c>
       <x:c r="E295" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2796.4</x:v>
       </x:c>
       <x:c r="G295" s="23" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>-113.8</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>0.040623658990130096</x:v>
+        <x:v>-0.039103841660366845</x:v>
       </x:c>
       <x:c r="I295" s="26" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>158</x:v>
+        <x:v>141.4</x:v>
       </x:c>
       <x:c r="J295" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18705,34 +18830,34 @@
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B296" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C296" s="23" t="n">
-        <x:v>2929.6</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="D296" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E296" s="23" t="n">
-        <x:v>2847.2</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="F296" s="23" t="n">
-        <x:v>2891.8</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G296" s="23" t="n">
         <x:f>ROUND(F296-F295,1)</x:f>
-        <x:v>-18.2</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="H296" s="24" t="n">
         <x:f>IFERROR(F296/F295-1,"")</x:f>
-        <x:v>-0.006254295532646004</x:v>
+        <x:v>0.040623658990130096</x:v>
       </x:c>
       <x:c r="I296" s="26" t="n">
         <x:f>ROUND(D296-E296,1)</x:f>
-        <x:v>82.8</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J296" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18743,34 +18868,34 @@
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B297" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C297" s="23" t="n">
-        <x:v>2882.4</x:v>
+        <x:v>2929.6</x:v>
       </x:c>
       <x:c r="D297" s="23" t="n">
-        <x:v>2930.6</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="E297" s="23" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2847.2</x:v>
       </x:c>
       <x:c r="F297" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2891.8</x:v>
       </x:c>
       <x:c r="G297" s="23" t="n">
         <x:f>ROUND(F297-F296,1)</x:f>
-        <x:v>38.2</x:v>
+        <x:v>-18.2</x:v>
       </x:c>
       <x:c r="H297" s="24" t="n">
         <x:f>IFERROR(F297/F296-1,"")</x:f>
-        <x:v>0.013209765543951812</x:v>
+        <x:v>-0.006254295532646004</x:v>
       </x:c>
       <x:c r="I297" s="26" t="n">
         <x:f>ROUND(D297-E297,1)</x:f>
-        <x:v>84.8</x:v>
+        <x:v>82.8</x:v>
       </x:c>
       <x:c r="J297" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18781,34 +18906,34 @@
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B298" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C298" s="23" t="n">
+        <x:v>2882.4</x:v>
+      </x:c>
+      <x:c r="D298" s="23" t="n">
+        <x:v>2930.6</x:v>
+      </x:c>
+      <x:c r="E298" s="23" t="n">
+        <x:v>2845.8</x:v>
+      </x:c>
+      <x:c r="F298" s="23" t="n">
         <x:v>2930</x:v>
-      </x:c>
-      <x:c r="D298" s="23" t="n">
-        <x:v>2949.6</x:v>
-      </x:c>
-      <x:c r="E298" s="23" t="n">
-        <x:v>2877</x:v>
-      </x:c>
-      <x:c r="F298" s="23" t="n">
-        <x:v>2890</x:v>
       </x:c>
       <x:c r="G298" s="23" t="n">
         <x:f>ROUND(F298-F297,1)</x:f>
-        <x:v>-40</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="H298" s="24" t="n">
         <x:f>IFERROR(F298/F297-1,"")</x:f>
-        <x:v>-0.013651877133105783</x:v>
+        <x:v>0.013209765543951812</x:v>
       </x:c>
       <x:c r="I298" s="26" t="n">
         <x:f>ROUND(D298-E298,1)</x:f>
-        <x:v>72.6</x:v>
+        <x:v>84.8</x:v>
       </x:c>
       <x:c r="J298" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18819,34 +18944,34 @@
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B299" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C299" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="D299" s="23" t="n">
-        <x:v>2921.2</x:v>
+        <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E299" s="23" t="n">
-        <x:v>2843</x:v>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="F299" s="23" t="n">
-        <x:v>2861</x:v>
+        <x:v>2890</x:v>
       </x:c>
       <x:c r="G299" s="23" t="n">
         <x:f>ROUND(F299-F298,1)</x:f>
-        <x:v>-29</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="H299" s="24" t="n">
         <x:f>IFERROR(F299/F298-1,"")</x:f>
-        <x:v>-0.01003460207612461</x:v>
+        <x:v>-0.013651877133105783</x:v>
       </x:c>
       <x:c r="I299" s="26" t="n">
         <x:f>ROUND(D299-E299,1)</x:f>
-        <x:v>78.2</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="J299" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18857,34 +18982,34 @@
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B300" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C300" s="23" t="n">
-        <x:v>2856.4</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D300" s="23" t="n">
-        <x:v>2918.2</x:v>
+        <x:v>2921.2</x:v>
       </x:c>
       <x:c r="E300" s="23" t="n">
-        <x:v>2837.4</x:v>
+        <x:v>2843</x:v>
       </x:c>
       <x:c r="F300" s="23" t="n">
-        <x:v>2911.4</x:v>
+        <x:v>2861</x:v>
       </x:c>
       <x:c r="G300" s="23" t="n">
         <x:f>ROUND(F300-F299,1)</x:f>
-        <x:v>50.4</x:v>
+        <x:v>-29</x:v>
       </x:c>
       <x:c r="H300" s="24" t="n">
         <x:f>IFERROR(F300/F299-1,"")</x:f>
-        <x:v>0.01761621810555747</x:v>
+        <x:v>-0.01003460207612461</x:v>
       </x:c>
       <x:c r="I300" s="26" t="n">
         <x:f>ROUND(D300-E300,1)</x:f>
-        <x:v>80.8</x:v>
+        <x:v>78.2</x:v>
       </x:c>
       <x:c r="J300" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18895,34 +19020,34 @@
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B301" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C301" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2856.4</x:v>
       </x:c>
       <x:c r="D301" s="23" t="n">
-        <x:v>2949.4</x:v>
+        <x:v>2918.2</x:v>
       </x:c>
       <x:c r="E301" s="23" t="n">
-        <x:v>2877.6</x:v>
+        <x:v>2837.4</x:v>
       </x:c>
       <x:c r="F301" s="23" t="n">
-        <x:v>2915.8</x:v>
+        <x:v>2911.4</x:v>
       </x:c>
       <x:c r="G301" s="23" t="n">
         <x:f>ROUND(F301-F300,1)</x:f>
-        <x:v>4.4</x:v>
+        <x:v>50.4</x:v>
       </x:c>
       <x:c r="H301" s="24" t="n">
         <x:f>IFERROR(F301/F300-1,"")</x:f>
-        <x:v>0.0015113004053033396</x:v>
+        <x:v>0.01761621810555747</x:v>
       </x:c>
       <x:c r="I301" s="26" t="n">
         <x:f>ROUND(D301-E301,1)</x:f>
-        <x:v>71.8</x:v>
+        <x:v>80.8</x:v>
       </x:c>
       <x:c r="J301" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18933,34 +19058,34 @@
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B302" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C302" s="23" t="n">
-        <x:v>2923.2</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D302" s="23" t="n">
-        <x:v>2931.4</x:v>
+        <x:v>2949.4</x:v>
       </x:c>
       <x:c r="E302" s="23" t="n">
-        <x:v>2836.8</x:v>
+        <x:v>2877.6</x:v>
       </x:c>
       <x:c r="F302" s="23" t="n">
-        <x:v>2867</x:v>
+        <x:v>2915.8</x:v>
       </x:c>
       <x:c r="G302" s="23" t="n">
         <x:f>ROUND(F302-F301,1)</x:f>
-        <x:v>-48.8</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="H302" s="24" t="n">
         <x:f>IFERROR(F302/F301-1,"")</x:f>
-        <x:v>-0.01673640167364021</x:v>
+        <x:v>0.0015113004053033396</x:v>
       </x:c>
       <x:c r="I302" s="26" t="n">
         <x:f>ROUND(D302-E302,1)</x:f>
-        <x:v>94.6</x:v>
+        <x:v>71.8</x:v>
       </x:c>
       <x:c r="J302" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -18971,34 +19096,34 @@
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B303" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C303" s="23" t="n">
-        <x:v>2849.2</x:v>
+        <x:v>2923.2</x:v>
       </x:c>
       <x:c r="D303" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2931.4</x:v>
       </x:c>
       <x:c r="E303" s="23" t="n">
-        <x:v>2829.4</x:v>
+        <x:v>2836.8</x:v>
       </x:c>
       <x:c r="F303" s="23" t="n">
-        <x:v>2862.2</x:v>
+        <x:v>2867</x:v>
       </x:c>
       <x:c r="G303" s="23" t="n">
         <x:f>ROUND(F303-F302,1)</x:f>
-        <x:v>-4.8</x:v>
+        <x:v>-48.8</x:v>
       </x:c>
       <x:c r="H303" s="24" t="n">
         <x:f>IFERROR(F303/F302-1,"")</x:f>
-        <x:v>-0.0016742239274503135</x:v>
-      </x:c>
-      <x:c r="I303" s="23" t="n">
+        <x:v>-0.01673640167364021</x:v>
+      </x:c>
+      <x:c r="I303" s="26" t="n">
         <x:f>ROUND(D303-E303,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>94.6</x:v>
       </x:c>
       <x:c r="J303" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19009,268 +19134,268 @@
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="22" t="n">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B304" s="22" t="str">
-        <x:v>9月21日-9月24日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C304" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2849.2</x:v>
       </x:c>
       <x:c r="D304" s="23" t="n">
-        <x:v>2881.2</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="E304" s="23" t="n">
-        <x:v>2798</x:v>
+        <x:v>2829.4</x:v>
       </x:c>
       <x:c r="F304" s="23" t="n">
-        <x:v>2804.6</x:v>
+        <x:v>2862.2</x:v>
       </x:c>
       <x:c r="G304" s="23" t="n">
         <x:f>ROUND(F304-F303,1)</x:f>
-        <x:v>-57.6</x:v>
+        <x:v>-4.8</x:v>
       </x:c>
       <x:c r="H304" s="24" t="n">
         <x:f>IFERROR(F304/F303-1,"")</x:f>
-        <x:v>-0.02012437984766957</x:v>
-      </x:c>
-      <x:c r="I304" s="26" t="n">
+        <x:v>-0.0016742239274503135</x:v>
+      </x:c>
+      <x:c r="I304" s="23" t="n">
         <x:f>ROUND(D304-E304,1)</x:f>
-        <x:v>83.2</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="J304" s="22" t="str">
-        <x:v>IH2612</x:v>
+        <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K304" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="22" t="n">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B305" s="22" t="str">
-        <x:v>9月28日-9月30日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C305" s="23" t="n">
-        <x:v>2802</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D305" s="23" t="n">
-        <x:v>2803.8</x:v>
+        <x:v>2881.2</x:v>
       </x:c>
       <x:c r="E305" s="23" t="n">
-        <x:v>2746</x:v>
+        <x:v>2798</x:v>
       </x:c>
       <x:c r="F305" s="23" t="n">
-        <x:v>2778.8</x:v>
+        <x:v>2804.6</x:v>
       </x:c>
       <x:c r="G305" s="23" t="n">
         <x:f>ROUND(F305-F304,1)</x:f>
-        <x:v>-25.8</x:v>
+        <x:v>-57.6</x:v>
       </x:c>
       <x:c r="H305" s="24" t="n">
         <x:f>IFERROR(F305/F304-1,"")</x:f>
-        <x:v>-0.009199172787563215</x:v>
-      </x:c>
-      <x:c r="I305" s="23" t="n">
+        <x:v>-0.02012437984766957</x:v>
+      </x:c>
+      <x:c r="I305" s="26" t="n">
         <x:f>ROUND(D305-E305,1)</x:f>
-        <x:v>57.8</x:v>
+        <x:v>83.2</x:v>
       </x:c>
       <x:c r="J305" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K305" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306">
+      <x:c r="A306" s="22" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B306" s="22" t="str">
+        <x:v>9月28日-9月30日</x:v>
+      </x:c>
+      <x:c r="C306" s="23" t="n">
+        <x:v>2802</x:v>
+      </x:c>
+      <x:c r="D306" s="23" t="n">
+        <x:v>2803.8</x:v>
+      </x:c>
+      <x:c r="E306" s="23" t="n">
+        <x:v>2746</x:v>
+      </x:c>
+      <x:c r="F306" s="23" t="n">
+        <x:v>2778.8</x:v>
+      </x:c>
+      <x:c r="G306" s="23" t="n">
+        <x:f>ROUND(F306-F305,1)</x:f>
+        <x:v>-25.8</x:v>
+      </x:c>
+      <x:c r="H306" s="24" t="n">
+        <x:f>IFERROR(F306/F305-1,"")</x:f>
+        <x:v>-0.009199172787563215</x:v>
+      </x:c>
+      <x:c r="I306" s="23" t="n">
+        <x:f>ROUND(D306-E306,1)</x:f>
+        <x:v>57.8</x:v>
+      </x:c>
+      <x:c r="J306" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
+      <x:c r="K306" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="306">
-      <x:c r="A306" s="31" t="str">
+    <x:row r="307">
+      <x:c r="A307" s="22" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B307" s="22" t="str">
+        <x:v>10月8日</x:v>
+      </x:c>
+      <x:c r="C307" s="23" t="n">
+        <x:v>2764</x:v>
+      </x:c>
+      <x:c r="D307" s="23" t="n">
+        <x:v>2798.4</x:v>
+      </x:c>
+      <x:c r="E307" s="23" t="n">
+        <x:v>2747.4</x:v>
+      </x:c>
+      <x:c r="F307" s="23" t="n">
+        <x:v>2764.4</x:v>
+      </x:c>
+      <x:c r="G307" s="23" t="n">
+        <x:f>ROUND(F307-F306,1)</x:f>
+        <x:v>-14.4</x:v>
+      </x:c>
+      <x:c r="H307" s="24" t="n">
+        <x:f>IFERROR(F307/F306-1,"")</x:f>
+        <x:v>-0.005182092989779785</x:v>
+      </x:c>
+      <x:c r="I307" s="23" t="n">
+        <x:f>ROUND(D307-E307,1)</x:f>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J307" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
+      <x:c r="K307" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308">
+      <x:c r="A308" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B306" s="30" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C306" s="30"/>
-      <x:c r="D306" s="30"/>
-      <x:c r="E306" s="30"/>
-      <x:c r="F306" s="30"/>
-      <x:c r="G306" s="30"/>
-      <x:c r="H306" s="30"/>
-      <x:c r="I306" s="32" t="n">
-        <x:f>ROUND(SUM(I268:I305),1)</x:f>
-        <x:v>3400.4</x:v>
-      </x:c>
-      <x:c r="J306" s="30"/>
-      <x:c r="K306" s="30"/>
-    </x:row>
-    <x:row r="307">
-      <x:c r="A307" s="31" t="str">
+      <x:c r="B308" s="30" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C308" s="30"/>
+      <x:c r="D308" s="30"/>
+      <x:c r="E308" s="30"/>
+      <x:c r="F308" s="30"/>
+      <x:c r="G308" s="30"/>
+      <x:c r="H308" s="30"/>
+      <x:c r="I308" s="32" t="n">
+        <x:f>ROUND(SUM(I269:I307),1)</x:f>
+        <x:v>3451.4</x:v>
+      </x:c>
+      <x:c r="J308" s="30"/>
+      <x:c r="K308" s="30"/>
+    </x:row>
+    <x:row r="309">
+      <x:c r="A309" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B307" s="30"/>
-      <x:c r="C307" s="30"/>
-      <x:c r="D307" s="30"/>
-      <x:c r="E307" s="30"/>
-      <x:c r="F307" s="30"/>
-      <x:c r="G307" s="30"/>
-      <x:c r="H307" s="30"/>
-      <x:c r="I307" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I268:I305),0),1)</x:f>
-        <x:v>89.5</x:v>
-      </x:c>
-      <x:c r="J307" s="30"/>
-      <x:c r="K307" s="30"/>
-    </x:row>
-    <x:row r="309">
-      <x:c r="A309" s="17" t="str">
+      <x:c r="B309" s="30"/>
+      <x:c r="C309" s="30"/>
+      <x:c r="D309" s="30"/>
+      <x:c r="E309" s="30"/>
+      <x:c r="F309" s="30"/>
+      <x:c r="G309" s="30"/>
+      <x:c r="H309" s="30"/>
+      <x:c r="I309" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I269:I307),0),1)</x:f>
+        <x:v>88.5</x:v>
+      </x:c>
+      <x:c r="J309" s="30"/>
+      <x:c r="K309" s="30"/>
+    </x:row>
+    <x:row r="311">
+      <x:c r="A311" s="17" t="str">
         <x:v>碳酸锂2610</x:v>
       </x:c>
-      <x:c r="B309" s="17"/>
-      <x:c r="C309" s="17"/>
-      <x:c r="D309" s="17"/>
-      <x:c r="E309" s="17"/>
-      <x:c r="F309" s="17"/>
-      <x:c r="G309" s="17"/>
-      <x:c r="H309" s="17"/>
-      <x:c r="I309" s="17"/>
-      <x:c r="J309" s="17"/>
-      <x:c r="K309" s="17"/>
-    </x:row>
-    <x:row r="310">
-      <x:c r="A310" s="20" t="str">
+      <x:c r="B311" s="17"/>
+      <x:c r="C311" s="17"/>
+      <x:c r="D311" s="17"/>
+      <x:c r="E311" s="17"/>
+      <x:c r="F311" s="17"/>
+      <x:c r="G311" s="17"/>
+      <x:c r="H311" s="17"/>
+      <x:c r="I311" s="17"/>
+      <x:c r="J311" s="17"/>
+      <x:c r="K311" s="17"/>
+    </x:row>
+    <x:row r="312">
+      <x:c r="A312" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B310" s="20" t="str">
+      <x:c r="B312" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C310" s="20" t="str">
+      <x:c r="C312" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D310" s="20" t="str">
+      <x:c r="D312" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E310" s="20" t="str">
+      <x:c r="E312" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F310" s="20" t="str">
+      <x:c r="F312" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G310" s="20" t="str">
+      <x:c r="G312" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H310" s="20" t="str">
+      <x:c r="H312" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I310" s="20" t="str">
+      <x:c r="I312" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J310" s="20" t="str">
+      <x:c r="J312" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K310" s="20" t="str">
+      <x:c r="K312" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="311">
-      <x:c r="A311" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B311" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C311" s="23" t="n">
-        <x:v>132800</x:v>
-      </x:c>
-      <x:c r="D311" s="23" t="n">
-        <x:v>150100</x:v>
-      </x:c>
-      <x:c r="E311" s="23" t="n">
-        <x:v>123500</x:v>
-      </x:c>
-      <x:c r="F311" s="23" t="n">
-        <x:v>145600</x:v>
-      </x:c>
-      <x:c r="G311" s="23"/>
-      <x:c r="H311" s="24"/>
-      <x:c r="I311" s="26" t="n">
-        <x:f>ROUND(D311-E311,1)</x:f>
-        <x:v>26600</x:v>
-      </x:c>
-      <x:c r="J311" s="22" t="str">
-        <x:v>LC2610</x:v>
-      </x:c>
-      <x:c r="K311" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="312">
-      <x:c r="A312" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B312" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
-      </x:c>
-      <x:c r="C312" s="23" t="n">
-        <x:v>149180</x:v>
-      </x:c>
-      <x:c r="D312" s="23" t="n">
-        <x:v>175360</x:v>
-      </x:c>
-      <x:c r="E312" s="23" t="n">
-        <x:v>148180</x:v>
-      </x:c>
-      <x:c r="F312" s="23" t="n">
-        <x:v>148180</x:v>
-      </x:c>
-      <x:c r="G312" s="28" t="n">
-        <x:f>ROUND(F312-F311,1)</x:f>
-        <x:v>2580</x:v>
-      </x:c>
-      <x:c r="H312" s="24" t="n">
-        <x:f>IFERROR(F312/F311-1,"")</x:f>
-        <x:v>0.017719780219780157</x:v>
-      </x:c>
-      <x:c r="I312" s="26" t="n">
-        <x:f>ROUND(D312-E312,1)</x:f>
-        <x:v>27180</x:v>
-      </x:c>
-      <x:c r="J312" s="22" t="str">
-        <x:v>LC2610</x:v>
-      </x:c>
-      <x:c r="K312" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B313" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C313" s="23" t="n">
-        <x:v>143000</x:v>
+        <x:v>132800</x:v>
       </x:c>
       <x:c r="D313" s="23" t="n">
-        <x:v>183460</x:v>
+        <x:v>150100</x:v>
       </x:c>
       <x:c r="E313" s="23" t="n">
-        <x:v>143000</x:v>
+        <x:v>123500</x:v>
       </x:c>
       <x:c r="F313" s="23" t="n">
-        <x:v>183460</x:v>
-      </x:c>
-      <x:c r="G313" s="28" t="n">
-        <x:f>ROUND(F313-F312,1)</x:f>
-        <x:v>35280</x:v>
-      </x:c>
-      <x:c r="H313" s="24" t="n">
-        <x:f>IFERROR(F313/F312-1,"")</x:f>
-        <x:v>0.23808881090565537</x:v>
-      </x:c>
+        <x:v>145600</x:v>
+      </x:c>
+      <x:c r="G313" s="23"/>
+      <x:c r="H313" s="24"/>
       <x:c r="I313" s="26" t="n">
         <x:f>ROUND(D313-E313,1)</x:f>
-        <x:v>40460</x:v>
+        <x:v>26600</x:v>
       </x:c>
       <x:c r="J313" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19281,34 +19406,34 @@
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B314" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C314" s="23" t="n">
-        <x:v>189980</x:v>
+        <x:v>149180</x:v>
       </x:c>
       <x:c r="D314" s="23" t="n">
-        <x:v>190020</x:v>
+        <x:v>175360</x:v>
       </x:c>
       <x:c r="E314" s="23" t="n">
-        <x:v>148520</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="F314" s="23" t="n">
-        <x:v>148540</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="G314" s="28" t="n">
         <x:f>ROUND(F314-F313,1)</x:f>
-        <x:v>-34920</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="H314" s="24" t="n">
         <x:f>IFERROR(F314/F313-1,"")</x:f>
-        <x:v>-0.19034121879428756</x:v>
+        <x:v>0.017719780219780157</x:v>
       </x:c>
       <x:c r="I314" s="26" t="n">
         <x:f>ROUND(D314-E314,1)</x:f>
-        <x:v>41500</x:v>
+        <x:v>27180</x:v>
       </x:c>
       <x:c r="J314" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19319,34 +19444,34 @@
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B315" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C315" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="D315" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="E315" s="23" t="n">
-        <x:v>124760</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="F315" s="23" t="n">
-        <x:v>131160</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="G315" s="28" t="n">
         <x:f>ROUND(F315-F314,1)</x:f>
-        <x:v>-17380</x:v>
+        <x:v>35280</x:v>
       </x:c>
       <x:c r="H315" s="24" t="n">
         <x:f>IFERROR(F315/F314-1,"")</x:f>
-        <x:v>-0.11700552039854584</x:v>
+        <x:v>0.23808881090565537</x:v>
       </x:c>
       <x:c r="I315" s="26" t="n">
         <x:f>ROUND(D315-E315,1)</x:f>
-        <x:v>28240</x:v>
+        <x:v>40460</x:v>
       </x:c>
       <x:c r="J315" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19357,34 +19482,34 @@
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B316" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C316" s="23" t="n">
-        <x:v>134660</x:v>
+        <x:v>189980</x:v>
       </x:c>
       <x:c r="D316" s="23" t="n">
-        <x:v>152380</x:v>
+        <x:v>190020</x:v>
       </x:c>
       <x:c r="E316" s="23" t="n">
-        <x:v>133580</x:v>
+        <x:v>148520</x:v>
       </x:c>
       <x:c r="F316" s="23" t="n">
-        <x:v>152380</x:v>
+        <x:v>148540</x:v>
       </x:c>
       <x:c r="G316" s="28" t="n">
         <x:f>ROUND(F316-F315,1)</x:f>
-        <x:v>21220</x:v>
+        <x:v>-34920</x:v>
       </x:c>
       <x:c r="H316" s="24" t="n">
         <x:f>IFERROR(F316/F315-1,"")</x:f>
-        <x:v>0.1617871302226288</x:v>
+        <x:v>-0.19034121879428756</x:v>
       </x:c>
       <x:c r="I316" s="26" t="n">
         <x:f>ROUND(D316-E316,1)</x:f>
-        <x:v>18800</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="J316" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19395,72 +19520,72 @@
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B317" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C317" s="23" t="n">
-        <x:v>165060</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="D317" s="23" t="n">
-        <x:v>187920</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="E317" s="23" t="n">
-        <x:v>155680</x:v>
+        <x:v>124760</x:v>
       </x:c>
       <x:c r="F317" s="23" t="n">
-        <x:v>175400</x:v>
+        <x:v>131160</x:v>
       </x:c>
       <x:c r="G317" s="28" t="n">
         <x:f>ROUND(F317-F316,1)</x:f>
-        <x:v>23020</x:v>
+        <x:v>-17380</x:v>
       </x:c>
       <x:c r="H317" s="24" t="n">
         <x:f>IFERROR(F317/F316-1,"")</x:f>
-        <x:v>0.1510696941855887</x:v>
+        <x:v>-0.11700552039854584</x:v>
       </x:c>
       <x:c r="I317" s="26" t="n">
         <x:f>ROUND(D317-E317,1)</x:f>
-        <x:v>32240</x:v>
+        <x:v>28240</x:v>
       </x:c>
       <x:c r="J317" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K317" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B318" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C318" s="23" t="n">
-        <x:v>175800</x:v>
+        <x:v>134660</x:v>
       </x:c>
       <x:c r="D318" s="23" t="n">
-        <x:v>177260</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="E318" s="23" t="n">
-        <x:v>144980</x:v>
+        <x:v>133580</x:v>
       </x:c>
       <x:c r="F318" s="23" t="n">
-        <x:v>156580</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="G318" s="28" t="n">
         <x:f>ROUND(F318-F317,1)</x:f>
-        <x:v>-18820</x:v>
+        <x:v>21220</x:v>
       </x:c>
       <x:c r="H318" s="24" t="n">
         <x:f>IFERROR(F318/F317-1,"")</x:f>
-        <x:v>-0.1072976054732041</x:v>
+        <x:v>0.1617871302226288</x:v>
       </x:c>
       <x:c r="I318" s="26" t="n">
         <x:f>ROUND(D318-E318,1)</x:f>
-        <x:v>32280</x:v>
+        <x:v>18800</x:v>
       </x:c>
       <x:c r="J318" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19471,72 +19596,72 @@
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B319" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C319" s="23" t="n">
-        <x:v>145120</x:v>
+        <x:v>165060</x:v>
       </x:c>
       <x:c r="D319" s="23" t="n">
-        <x:v>166800</x:v>
+        <x:v>187920</x:v>
       </x:c>
       <x:c r="E319" s="23" t="n">
-        <x:v>139860</x:v>
+        <x:v>155680</x:v>
       </x:c>
       <x:c r="F319" s="23" t="n">
-        <x:v>151880</x:v>
+        <x:v>175400</x:v>
       </x:c>
       <x:c r="G319" s="28" t="n">
         <x:f>ROUND(F319-F318,1)</x:f>
-        <x:v>-4700</x:v>
+        <x:v>23020</x:v>
       </x:c>
       <x:c r="H319" s="24" t="n">
         <x:f>IFERROR(F319/F318-1,"")</x:f>
-        <x:v>-0.030016604930387047</x:v>
+        <x:v>0.1510696941855887</x:v>
       </x:c>
       <x:c r="I319" s="26" t="n">
         <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>26940</x:v>
+        <x:v>32240</x:v>
       </x:c>
       <x:c r="J319" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K319" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B320" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C320" s="23" t="n">
-        <x:v>149140</x:v>
+        <x:v>175800</x:v>
       </x:c>
       <x:c r="D320" s="23" t="n">
-        <x:v>159120</x:v>
+        <x:v>177260</x:v>
       </x:c>
       <x:c r="E320" s="23" t="n">
-        <x:v>139640</x:v>
+        <x:v>144980</x:v>
       </x:c>
       <x:c r="F320" s="23" t="n">
-        <x:v>143900</x:v>
+        <x:v>156580</x:v>
       </x:c>
       <x:c r="G320" s="28" t="n">
         <x:f>ROUND(F320-F319,1)</x:f>
-        <x:v>-7980</x:v>
+        <x:v>-18820</x:v>
       </x:c>
       <x:c r="H320" s="24" t="n">
         <x:f>IFERROR(F320/F319-1,"")</x:f>
-        <x:v>-0.052541480115881</x:v>
+        <x:v>-0.1072976054732041</x:v>
       </x:c>
       <x:c r="I320" s="26" t="n">
         <x:f>ROUND(D320-E320,1)</x:f>
-        <x:v>19480</x:v>
+        <x:v>32280</x:v>
       </x:c>
       <x:c r="J320" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19547,34 +19672,34 @@
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B321" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C321" s="23" t="n">
-        <x:v>144460</x:v>
+        <x:v>145120</x:v>
       </x:c>
       <x:c r="D321" s="23" t="n">
-        <x:v>170800</x:v>
+        <x:v>166800</x:v>
       </x:c>
       <x:c r="E321" s="23" t="n">
-        <x:v>139980</x:v>
+        <x:v>139860</x:v>
       </x:c>
       <x:c r="F321" s="23" t="n">
-        <x:v>166540</x:v>
+        <x:v>151880</x:v>
       </x:c>
       <x:c r="G321" s="28" t="n">
         <x:f>ROUND(F321-F320,1)</x:f>
-        <x:v>22640</x:v>
+        <x:v>-4700</x:v>
       </x:c>
       <x:c r="H321" s="24" t="n">
         <x:f>IFERROR(F321/F320-1,"")</x:f>
-        <x:v>0.15733148019457954</x:v>
+        <x:v>-0.030016604930387047</x:v>
       </x:c>
       <x:c r="I321" s="26" t="n">
         <x:f>ROUND(D321-E321,1)</x:f>
-        <x:v>30820</x:v>
+        <x:v>26940</x:v>
       </x:c>
       <x:c r="J321" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19585,34 +19710,34 @@
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B322" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C322" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>149140</x:v>
       </x:c>
       <x:c r="D322" s="23" t="n">
-        <x:v>174540</x:v>
+        <x:v>159120</x:v>
       </x:c>
       <x:c r="E322" s="23" t="n">
-        <x:v>153840</x:v>
+        <x:v>139640</x:v>
       </x:c>
       <x:c r="F322" s="23" t="n">
-        <x:v>157680</x:v>
+        <x:v>143900</x:v>
       </x:c>
       <x:c r="G322" s="28" t="n">
         <x:f>ROUND(F322-F321,1)</x:f>
-        <x:v>-8860</x:v>
+        <x:v>-7980</x:v>
       </x:c>
       <x:c r="H322" s="24" t="n">
         <x:f>IFERROR(F322/F321-1,"")</x:f>
-        <x:v>-0.05320043232856975</x:v>
+        <x:v>-0.052541480115881</x:v>
       </x:c>
       <x:c r="I322" s="26" t="n">
         <x:f>ROUND(D322-E322,1)</x:f>
-        <x:v>20700</x:v>
+        <x:v>19480</x:v>
       </x:c>
       <x:c r="J322" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19623,72 +19748,72 @@
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B323" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C323" s="23" t="n">
-        <x:v>156200</x:v>
+        <x:v>144460</x:v>
       </x:c>
       <x:c r="D323" s="23" t="n">
-        <x:v>164160</x:v>
+        <x:v>170800</x:v>
       </x:c>
       <x:c r="E323" s="23" t="n">
-        <x:v>151640</x:v>
+        <x:v>139980</x:v>
       </x:c>
       <x:c r="F323" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>166540</x:v>
       </x:c>
       <x:c r="G323" s="28" t="n">
         <x:f>ROUND(F323-F322,1)</x:f>
-        <x:v>-1180</x:v>
+        <x:v>22640</x:v>
       </x:c>
       <x:c r="H323" s="24" t="n">
         <x:f>IFERROR(F323/F322-1,"")</x:f>
-        <x:v>-0.007483510908168456</x:v>
+        <x:v>0.15733148019457954</x:v>
       </x:c>
       <x:c r="I323" s="26" t="n">
         <x:f>ROUND(D323-E323,1)</x:f>
-        <x:v>12520</x:v>
+        <x:v>30820</x:v>
       </x:c>
       <x:c r="J323" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K323" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B324" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C324" s="23" t="n">
-        <x:v>156660</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="D324" s="23" t="n">
-        <x:v>176500</x:v>
+        <x:v>174540</x:v>
       </x:c>
       <x:c r="E324" s="23" t="n">
-        <x:v>153040</x:v>
+        <x:v>153840</x:v>
       </x:c>
       <x:c r="F324" s="23" t="n">
-        <x:v>176360</x:v>
+        <x:v>157680</x:v>
       </x:c>
       <x:c r="G324" s="28" t="n">
         <x:f>ROUND(F324-F323,1)</x:f>
-        <x:v>19860</x:v>
+        <x:v>-8860</x:v>
       </x:c>
       <x:c r="H324" s="24" t="n">
         <x:f>IFERROR(F324/F323-1,"")</x:f>
-        <x:v>0.12690095846645377</x:v>
+        <x:v>-0.05320043232856975</x:v>
       </x:c>
       <x:c r="I324" s="26" t="n">
         <x:f>ROUND(D324-E324,1)</x:f>
-        <x:v>23460</x:v>
+        <x:v>20700</x:v>
       </x:c>
       <x:c r="J324" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19699,212 +19824,212 @@
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B325" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C325" s="23" t="n">
-        <x:v>174080</x:v>
+        <x:v>156200</x:v>
       </x:c>
       <x:c r="D325" s="23" t="n">
-        <x:v>180920</x:v>
+        <x:v>164160</x:v>
       </x:c>
       <x:c r="E325" s="23" t="n">
-        <x:v>169000</x:v>
+        <x:v>151640</x:v>
       </x:c>
       <x:c r="F325" s="23" t="n">
-        <x:v>176960</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="G325" s="28" t="n">
         <x:f>ROUND(F325-F324,1)</x:f>
-        <x:v>600</x:v>
+        <x:v>-1180</x:v>
       </x:c>
       <x:c r="H325" s="24" t="n">
         <x:f>IFERROR(F325/F324-1,"")</x:f>
-        <x:v>0.0034021320027217694</x:v>
+        <x:v>-0.007483510908168456</x:v>
       </x:c>
       <x:c r="I325" s="26" t="n">
         <x:f>ROUND(D325-E325,1)</x:f>
-        <x:v>11920</x:v>
+        <x:v>12520</x:v>
       </x:c>
       <x:c r="J325" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K325" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B326" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C326" s="23" t="n">
-        <x:v>176960</x:v>
+        <x:v>156660</x:v>
       </x:c>
       <x:c r="D326" s="23" t="n">
-        <x:v>188840</x:v>
+        <x:v>176500</x:v>
       </x:c>
       <x:c r="E326" s="23" t="n">
-        <x:v>172640</x:v>
+        <x:v>153040</x:v>
       </x:c>
       <x:c r="F326" s="23" t="n">
-        <x:v>188840</x:v>
+        <x:v>176360</x:v>
       </x:c>
       <x:c r="G326" s="28" t="n">
         <x:f>ROUND(F326-F325,1)</x:f>
-        <x:v>11880</x:v>
+        <x:v>19860</x:v>
       </x:c>
       <x:c r="H326" s="24" t="n">
         <x:f>IFERROR(F326/F325-1,"")</x:f>
-        <x:v>0.06713381555153708</x:v>
+        <x:v>0.12690095846645377</x:v>
       </x:c>
       <x:c r="I326" s="26" t="n">
         <x:f>ROUND(D326-E326,1)</x:f>
-        <x:v>16200</x:v>
+        <x:v>23460</x:v>
       </x:c>
       <x:c r="J326" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K326" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B327" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C327" s="23" t="n">
-        <x:v>191300</x:v>
+        <x:v>174080</x:v>
       </x:c>
       <x:c r="D327" s="23" t="n">
-        <x:v>204640</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="E327" s="23" t="n">
-        <x:v>191300</x:v>
+        <x:v>169000</x:v>
       </x:c>
       <x:c r="F327" s="23" t="n">
-        <x:v>196100</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="G327" s="28" t="n">
         <x:f>ROUND(F327-F326,1)</x:f>
-        <x:v>7260</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H327" s="24" t="n">
         <x:f>IFERROR(F327/F326-1,"")</x:f>
-        <x:v>0.038445244651556854</x:v>
+        <x:v>0.0034021320027217694</x:v>
       </x:c>
       <x:c r="I327" s="26" t="n">
         <x:f>ROUND(D327-E327,1)</x:f>
-        <x:v>13340</x:v>
+        <x:v>11920</x:v>
       </x:c>
       <x:c r="J327" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K327" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B328" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C328" s="23" t="n">
-        <x:v>195080</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="D328" s="23" t="n">
-        <x:v>209040</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="E328" s="23" t="n">
-        <x:v>187240</x:v>
+        <x:v>172640</x:v>
       </x:c>
       <x:c r="F328" s="23" t="n">
-        <x:v>189440</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="G328" s="28" t="n">
         <x:f>ROUND(F328-F327,1)</x:f>
-        <x:v>-6660</x:v>
+        <x:v>11880</x:v>
       </x:c>
       <x:c r="H328" s="24" t="n">
         <x:f>IFERROR(F328/F327-1,"")</x:f>
-        <x:v>-0.03396226415094339</x:v>
+        <x:v>0.06713381555153708</x:v>
       </x:c>
       <x:c r="I328" s="26" t="n">
         <x:f>ROUND(D328-E328,1)</x:f>
-        <x:v>21800</x:v>
+        <x:v>16200</x:v>
       </x:c>
       <x:c r="J328" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K328" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B329" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C329" s="23" t="n">
-        <x:v>190060</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="D329" s="23" t="n">
-        <x:v>193820</x:v>
+        <x:v>204640</x:v>
       </x:c>
       <x:c r="E329" s="23" t="n">
-        <x:v>175520</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="F329" s="23" t="n">
-        <x:v>185280</x:v>
+        <x:v>196100</x:v>
       </x:c>
       <x:c r="G329" s="28" t="n">
         <x:f>ROUND(F329-F328,1)</x:f>
-        <x:v>-4160</x:v>
+        <x:v>7260</x:v>
       </x:c>
       <x:c r="H329" s="24" t="n">
         <x:f>IFERROR(F329/F328-1,"")</x:f>
-        <x:v>-0.02195945945945943</x:v>
+        <x:v>0.038445244651556854</x:v>
       </x:c>
       <x:c r="I329" s="26" t="n">
         <x:f>ROUND(D329-E329,1)</x:f>
-        <x:v>18300</x:v>
+        <x:v>13340</x:v>
       </x:c>
       <x:c r="J329" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K329" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B330" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C330" s="23" t="n">
-        <x:v>185380</x:v>
+        <x:v>195080</x:v>
       </x:c>
       <x:c r="D330" s="23" t="n">
-        <x:v>188320</x:v>
+        <x:v>209040</x:v>
       </x:c>
       <x:c r="E330" s="23" t="n">
-        <x:v>172500</x:v>
+        <x:v>187240</x:v>
       </x:c>
       <x:c r="F330" s="23" t="n">
-        <x:v>178620</x:v>
+        <x:v>189440</x:v>
       </x:c>
       <x:c r="G330" s="28" t="n">
         <x:f>ROUND(F330-F329,1)</x:f>
@@ -19912,11 +20037,11 @@
       </x:c>
       <x:c r="H330" s="24" t="n">
         <x:f>IFERROR(F330/F329-1,"")</x:f>
-        <x:v>-0.035945595854922296</x:v>
+        <x:v>-0.03396226415094339</x:v>
       </x:c>
       <x:c r="I330" s="26" t="n">
         <x:f>ROUND(D330-E330,1)</x:f>
-        <x:v>15820</x:v>
+        <x:v>21800</x:v>
       </x:c>
       <x:c r="J330" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19927,34 +20052,34 @@
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B331" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C331" s="23" t="n">
-        <x:v>180920</x:v>
+        <x:v>190060</x:v>
       </x:c>
       <x:c r="D331" s="23" t="n">
-        <x:v>182940</x:v>
+        <x:v>193820</x:v>
       </x:c>
       <x:c r="E331" s="23" t="n">
-        <x:v>158140</x:v>
+        <x:v>175520</x:v>
       </x:c>
       <x:c r="F331" s="23" t="n">
-        <x:v>165460</x:v>
+        <x:v>185280</x:v>
       </x:c>
       <x:c r="G331" s="28" t="n">
         <x:f>ROUND(F331-F330,1)</x:f>
-        <x:v>-13160</x:v>
+        <x:v>-4160</x:v>
       </x:c>
       <x:c r="H331" s="24" t="n">
         <x:f>IFERROR(F331/F330-1,"")</x:f>
-        <x:v>-0.07367596013884226</x:v>
+        <x:v>-0.02195945945945943</x:v>
       </x:c>
       <x:c r="I331" s="26" t="n">
         <x:f>ROUND(D331-E331,1)</x:f>
-        <x:v>24800</x:v>
+        <x:v>18300</x:v>
       </x:c>
       <x:c r="J331" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19965,34 +20090,34 @@
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B332" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C332" s="23" t="n">
-        <x:v>162800</x:v>
+        <x:v>185380</x:v>
       </x:c>
       <x:c r="D332" s="23" t="n">
-        <x:v>178860</x:v>
+        <x:v>188320</x:v>
       </x:c>
       <x:c r="E332" s="23" t="n">
-        <x:v>161280</x:v>
+        <x:v>172500</x:v>
       </x:c>
       <x:c r="F332" s="23" t="n">
-        <x:v>175780</x:v>
+        <x:v>178620</x:v>
       </x:c>
       <x:c r="G332" s="28" t="n">
         <x:f>ROUND(F332-F331,1)</x:f>
-        <x:v>10320</x:v>
+        <x:v>-6660</x:v>
       </x:c>
       <x:c r="H332" s="24" t="n">
         <x:f>IFERROR(F332/F331-1,"")</x:f>
-        <x:v>0.06237157016801653</x:v>
+        <x:v>-0.035945595854922296</x:v>
       </x:c>
       <x:c r="I332" s="26" t="n">
         <x:f>ROUND(D332-E332,1)</x:f>
-        <x:v>17580</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="J332" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20003,72 +20128,72 @@
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B333" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C333" s="23" t="n">
-        <x:v>176460</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="D333" s="23" t="n">
-        <x:v>178560</x:v>
+        <x:v>182940</x:v>
       </x:c>
       <x:c r="E333" s="23" t="n">
-        <x:v>160560</x:v>
+        <x:v>158140</x:v>
       </x:c>
       <x:c r="F333" s="23" t="n">
-        <x:v>161400</x:v>
+        <x:v>165460</x:v>
       </x:c>
       <x:c r="G333" s="28" t="n">
         <x:f>ROUND(F333-F332,1)</x:f>
-        <x:v>-14380</x:v>
+        <x:v>-13160</x:v>
       </x:c>
       <x:c r="H333" s="24" t="n">
         <x:f>IFERROR(F333/F332-1,"")</x:f>
-        <x:v>-0.0818068039594948</x:v>
+        <x:v>-0.07367596013884226</x:v>
       </x:c>
       <x:c r="I333" s="26" t="n">
         <x:f>ROUND(D333-E333,1)</x:f>
-        <x:v>18000</x:v>
+        <x:v>24800</x:v>
       </x:c>
       <x:c r="J333" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K333" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B334" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C334" s="23" t="n">
-        <x:v>161000</x:v>
+        <x:v>162800</x:v>
       </x:c>
       <x:c r="D334" s="23" t="n">
-        <x:v>163880</x:v>
+        <x:v>178860</x:v>
       </x:c>
       <x:c r="E334" s="23" t="n">
-        <x:v>145360</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="F334" s="23" t="n">
-        <x:v>151140</x:v>
+        <x:v>175780</x:v>
       </x:c>
       <x:c r="G334" s="28" t="n">
         <x:f>ROUND(F334-F333,1)</x:f>
-        <x:v>-10260</x:v>
+        <x:v>10320</x:v>
       </x:c>
       <x:c r="H334" s="24" t="n">
         <x:f>IFERROR(F334/F333-1,"")</x:f>
-        <x:v>-0.06356877323420074</x:v>
+        <x:v>0.06237157016801653</x:v>
       </x:c>
       <x:c r="I334" s="26" t="n">
         <x:f>ROUND(D334-E334,1)</x:f>
-        <x:v>18520</x:v>
+        <x:v>17580</x:v>
       </x:c>
       <x:c r="J334" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20079,72 +20204,72 @@
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B335" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C335" s="23" t="n">
-        <x:v>148420</x:v>
+        <x:v>176460</x:v>
       </x:c>
       <x:c r="D335" s="23" t="n">
-        <x:v>172120</x:v>
+        <x:v>178560</x:v>
       </x:c>
       <x:c r="E335" s="23" t="n">
-        <x:v>146000</x:v>
+        <x:v>160560</x:v>
       </x:c>
       <x:c r="F335" s="23" t="n">
-        <x:v>168600</x:v>
+        <x:v>161400</x:v>
       </x:c>
       <x:c r="G335" s="28" t="n">
         <x:f>ROUND(F335-F334,1)</x:f>
-        <x:v>17460</x:v>
+        <x:v>-14380</x:v>
       </x:c>
       <x:c r="H335" s="24" t="n">
         <x:f>IFERROR(F335/F334-1,"")</x:f>
-        <x:v>0.1155220325526003</x:v>
+        <x:v>-0.0818068039594948</x:v>
       </x:c>
       <x:c r="I335" s="26" t="n">
         <x:f>ROUND(D335-E335,1)</x:f>
-        <x:v>26120</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="J335" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K335" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B336" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C336" s="23" t="n">
-        <x:v>174900</x:v>
+        <x:v>161000</x:v>
       </x:c>
       <x:c r="D336" s="23" t="n">
-        <x:v>174900</x:v>
+        <x:v>163880</x:v>
       </x:c>
       <x:c r="E336" s="23" t="n">
-        <x:v>150860</x:v>
+        <x:v>145360</x:v>
       </x:c>
       <x:c r="F336" s="23" t="n">
-        <x:v>151600</x:v>
+        <x:v>151140</x:v>
       </x:c>
       <x:c r="G336" s="28" t="n">
         <x:f>ROUND(F336-F335,1)</x:f>
-        <x:v>-17000</x:v>
+        <x:v>-10260</x:v>
       </x:c>
       <x:c r="H336" s="24" t="n">
         <x:f>IFERROR(F336/F335-1,"")</x:f>
-        <x:v>-0.10083036773428233</x:v>
+        <x:v>-0.06356877323420074</x:v>
       </x:c>
       <x:c r="I336" s="26" t="n">
         <x:f>ROUND(D336-E336,1)</x:f>
-        <x:v>24040</x:v>
+        <x:v>18520</x:v>
       </x:c>
       <x:c r="J336" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20155,34 +20280,34 @@
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B337" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C337" s="23" t="n">
-        <x:v>150300</x:v>
+        <x:v>148420</x:v>
       </x:c>
       <x:c r="D337" s="23" t="n">
-        <x:v>155660</x:v>
+        <x:v>172120</x:v>
       </x:c>
       <x:c r="E337" s="23" t="n">
-        <x:v>145460</x:v>
+        <x:v>146000</x:v>
       </x:c>
       <x:c r="F337" s="23" t="n">
-        <x:v>149740</x:v>
+        <x:v>168600</x:v>
       </x:c>
       <x:c r="G337" s="28" t="n">
         <x:f>ROUND(F337-F336,1)</x:f>
-        <x:v>-1860</x:v>
+        <x:v>17460</x:v>
       </x:c>
       <x:c r="H337" s="24" t="n">
         <x:f>IFERROR(F337/F336-1,"")</x:f>
-        <x:v>-0.012269129287598934</x:v>
+        <x:v>0.1155220325526003</x:v>
       </x:c>
       <x:c r="I337" s="26" t="n">
         <x:f>ROUND(D337-E337,1)</x:f>
-        <x:v>10200</x:v>
+        <x:v>26120</x:v>
       </x:c>
       <x:c r="J337" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20193,34 +20318,34 @@
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B338" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C338" s="23" t="n">
-        <x:v>152520</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="D338" s="23" t="n">
-        <x:v>153880</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="E338" s="23" t="n">
-        <x:v>135040</x:v>
+        <x:v>150860</x:v>
       </x:c>
       <x:c r="F338" s="23" t="n">
-        <x:v>142920</x:v>
+        <x:v>151600</x:v>
       </x:c>
       <x:c r="G338" s="28" t="n">
         <x:f>ROUND(F338-F337,1)</x:f>
-        <x:v>-6820</x:v>
+        <x:v>-17000</x:v>
       </x:c>
       <x:c r="H338" s="24" t="n">
         <x:f>IFERROR(F338/F337-1,"")</x:f>
-        <x:v>-0.04554561239481769</x:v>
+        <x:v>-0.10083036773428233</x:v>
       </x:c>
       <x:c r="I338" s="26" t="n">
         <x:f>ROUND(D338-E338,1)</x:f>
-        <x:v>18840</x:v>
+        <x:v>24040</x:v>
       </x:c>
       <x:c r="J338" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20231,34 +20356,34 @@
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B339" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C339" s="23" t="n">
-        <x:v>144340</x:v>
+        <x:v>150300</x:v>
       </x:c>
       <x:c r="D339" s="23" t="n">
-        <x:v>148600</x:v>
+        <x:v>155660</x:v>
       </x:c>
       <x:c r="E339" s="23" t="n">
-        <x:v>137000</x:v>
+        <x:v>145460</x:v>
       </x:c>
       <x:c r="F339" s="23" t="n">
-        <x:v>137000</x:v>
+        <x:v>149740</x:v>
       </x:c>
       <x:c r="G339" s="28" t="n">
         <x:f>ROUND(F339-F338,1)</x:f>
-        <x:v>-5920</x:v>
+        <x:v>-1860</x:v>
       </x:c>
       <x:c r="H339" s="24" t="n">
         <x:f>IFERROR(F339/F338-1,"")</x:f>
-        <x:v>-0.04142177441925554</x:v>
+        <x:v>-0.012269129287598934</x:v>
       </x:c>
       <x:c r="I339" s="26" t="n">
         <x:f>ROUND(D339-E339,1)</x:f>
-        <x:v>11600</x:v>
+        <x:v>10200</x:v>
       </x:c>
       <x:c r="J339" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20269,34 +20394,34 @@
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B340" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C340" s="23" t="n">
-        <x:v>137200</x:v>
+        <x:v>152520</x:v>
       </x:c>
       <x:c r="D340" s="23" t="n">
-        <x:v>144100</x:v>
+        <x:v>153880</x:v>
       </x:c>
       <x:c r="E340" s="23" t="n">
         <x:v>135040</x:v>
       </x:c>
       <x:c r="F340" s="23" t="n">
-        <x:v>139320</x:v>
+        <x:v>142920</x:v>
       </x:c>
       <x:c r="G340" s="28" t="n">
         <x:f>ROUND(F340-F339,1)</x:f>
-        <x:v>2320</x:v>
+        <x:v>-6820</x:v>
       </x:c>
       <x:c r="H340" s="24" t="n">
         <x:f>IFERROR(F340/F339-1,"")</x:f>
-        <x:v>0.016934306569343027</x:v>
+        <x:v>-0.04554561239481769</x:v>
       </x:c>
       <x:c r="I340" s="26" t="n">
         <x:f>ROUND(D340-E340,1)</x:f>
-        <x:v>9060</x:v>
+        <x:v>18840</x:v>
       </x:c>
       <x:c r="J340" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20307,34 +20432,34 @@
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B341" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C341" s="23" t="n">
-        <x:v>139320</x:v>
+        <x:v>144340</x:v>
       </x:c>
       <x:c r="D341" s="23" t="n">
-        <x:v>154560</x:v>
+        <x:v>148600</x:v>
       </x:c>
       <x:c r="E341" s="23" t="n">
-        <x:v>139300</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="F341" s="23" t="n">
-        <x:v>153980</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="G341" s="28" t="n">
         <x:f>ROUND(F341-F340,1)</x:f>
-        <x:v>14660</x:v>
+        <x:v>-5920</x:v>
       </x:c>
       <x:c r="H341" s="24" t="n">
         <x:f>IFERROR(F341/F340-1,"")</x:f>
-        <x:v>0.10522538041917895</x:v>
+        <x:v>-0.04142177441925554</x:v>
       </x:c>
       <x:c r="I341" s="26" t="n">
         <x:f>ROUND(D341-E341,1)</x:f>
-        <x:v>15260</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="J341" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20345,34 +20470,34 @@
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B342" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C342" s="23" t="n">
-        <x:v>152940</x:v>
+        <x:v>137200</x:v>
       </x:c>
       <x:c r="D342" s="23" t="n">
-        <x:v>157400</x:v>
+        <x:v>144100</x:v>
       </x:c>
       <x:c r="E342" s="23" t="n">
-        <x:v>148700</x:v>
+        <x:v>135040</x:v>
       </x:c>
       <x:c r="F342" s="23" t="n">
-        <x:v>156380</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="G342" s="28" t="n">
         <x:f>ROUND(F342-F341,1)</x:f>
-        <x:v>2400</x:v>
+        <x:v>2320</x:v>
       </x:c>
       <x:c r="H342" s="24" t="n">
         <x:f>IFERROR(F342/F341-1,"")</x:f>
-        <x:v>0.015586439797376173</x:v>
+        <x:v>0.016934306569343027</x:v>
       </x:c>
       <x:c r="I342" s="26" t="n">
         <x:f>ROUND(D342-E342,1)</x:f>
-        <x:v>8700</x:v>
+        <x:v>9060</x:v>
       </x:c>
       <x:c r="J342" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20383,34 +20508,34 @@
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B343" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C343" s="23" t="n">
-        <x:v>158800</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="D343" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="E343" s="23" t="n">
-        <x:v>147600</x:v>
+        <x:v>139300</x:v>
       </x:c>
       <x:c r="F343" s="23" t="n">
-        <x:v>157940</x:v>
+        <x:v>153980</x:v>
       </x:c>
       <x:c r="G343" s="28" t="n">
         <x:f>ROUND(F343-F342,1)</x:f>
-        <x:v>1560</x:v>
+        <x:v>14660</x:v>
       </x:c>
       <x:c r="H343" s="24" t="n">
         <x:f>IFERROR(F343/F342-1,"")</x:f>
-        <x:v>0.009975700217419003</x:v>
+        <x:v>0.10522538041917895</x:v>
       </x:c>
       <x:c r="I343" s="26" t="n">
         <x:f>ROUND(D343-E343,1)</x:f>
-        <x:v>12900</x:v>
+        <x:v>15260</x:v>
       </x:c>
       <x:c r="J343" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20421,34 +20546,34 @@
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B344" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C344" s="23" t="n">
-        <x:v>157500</x:v>
+        <x:v>152940</x:v>
       </x:c>
       <x:c r="D344" s="23" t="n">
-        <x:v>161280</x:v>
+        <x:v>157400</x:v>
       </x:c>
       <x:c r="E344" s="23" t="n">
-        <x:v>140220</x:v>
+        <x:v>148700</x:v>
       </x:c>
       <x:c r="F344" s="23" t="n">
-        <x:v>142000</x:v>
+        <x:v>156380</x:v>
       </x:c>
       <x:c r="G344" s="28" t="n">
         <x:f>ROUND(F344-F343,1)</x:f>
-        <x:v>-15940</x:v>
+        <x:v>2400</x:v>
       </x:c>
       <x:c r="H344" s="24" t="n">
         <x:f>IFERROR(F344/F343-1,"")</x:f>
-        <x:v>-0.10092440167152084</x:v>
+        <x:v>0.015586439797376173</x:v>
       </x:c>
       <x:c r="I344" s="26" t="n">
         <x:f>ROUND(D344-E344,1)</x:f>
-        <x:v>21060</x:v>
+        <x:v>8700</x:v>
       </x:c>
       <x:c r="J344" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20459,34 +20584,34 @@
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B345" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C345" s="23" t="n">
-        <x:v>141000</x:v>
+        <x:v>158800</x:v>
       </x:c>
       <x:c r="D345" s="23" t="n">
-        <x:v>143540</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="E345" s="23" t="n">
-        <x:v>127120</x:v>
+        <x:v>147600</x:v>
       </x:c>
       <x:c r="F345" s="23" t="n">
-        <x:v>134340</x:v>
+        <x:v>157940</x:v>
       </x:c>
       <x:c r="G345" s="28" t="n">
         <x:f>ROUND(F345-F344,1)</x:f>
-        <x:v>-7660</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="H345" s="24" t="n">
         <x:f>IFERROR(F345/F344-1,"")</x:f>
-        <x:v>-0.05394366197183098</x:v>
+        <x:v>0.009975700217419003</x:v>
       </x:c>
       <x:c r="I345" s="26" t="n">
         <x:f>ROUND(D345-E345,1)</x:f>
-        <x:v>16420</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="J345" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20497,34 +20622,34 @@
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B346" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C346" s="23" t="n">
-        <x:v>133600</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D346" s="23" t="n">
-        <x:v>135900</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="E346" s="23" t="n">
-        <x:v>126200</x:v>
+        <x:v>140220</x:v>
       </x:c>
       <x:c r="F346" s="23" t="n">
-        <x:v>128580</x:v>
+        <x:v>142000</x:v>
       </x:c>
       <x:c r="G346" s="28" t="n">
         <x:f>ROUND(F346-F345,1)</x:f>
-        <x:v>-5760</x:v>
+        <x:v>-15940</x:v>
       </x:c>
       <x:c r="H346" s="24" t="n">
         <x:f>IFERROR(F346/F345-1,"")</x:f>
-        <x:v>-0.04287628405538191</x:v>
+        <x:v>-0.10092440167152084</x:v>
       </x:c>
       <x:c r="I346" s="26" t="n">
         <x:f>ROUND(D346-E346,1)</x:f>
-        <x:v>9700</x:v>
+        <x:v>21060</x:v>
       </x:c>
       <x:c r="J346" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20535,117 +20660,231 @@
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="22" t="n">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B347" s="22" t="str">
-        <x:v>9月21日-9月24日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C347" s="23" t="n">
-        <x:v>128500</x:v>
+        <x:v>141000</x:v>
       </x:c>
       <x:c r="D347" s="23" t="n">
-        <x:v>136560</x:v>
+        <x:v>143540</x:v>
       </x:c>
       <x:c r="E347" s="23" t="n">
-        <x:v>125000</x:v>
+        <x:v>127120</x:v>
       </x:c>
       <x:c r="F347" s="23" t="n">
-        <x:v>125980</x:v>
+        <x:v>134340</x:v>
       </x:c>
       <x:c r="G347" s="28" t="n">
         <x:f>ROUND(F347-F346,1)</x:f>
-        <x:v>-2600</x:v>
+        <x:v>-7660</x:v>
       </x:c>
       <x:c r="H347" s="24" t="n">
         <x:f>IFERROR(F347/F346-1,"")</x:f>
-        <x:v>-0.02022087416394458</x:v>
+        <x:v>-0.05394366197183098</x:v>
       </x:c>
       <x:c r="I347" s="26" t="n">
         <x:f>ROUND(D347-E347,1)</x:f>
-        <x:v>11560</x:v>
+        <x:v>16420</x:v>
       </x:c>
       <x:c r="J347" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K347" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="22" t="n">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B348" s="22" t="str">
-        <x:v>9月28日-9月30日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C348" s="23" t="n">
-        <x:v>124280</x:v>
+        <x:v>133600</x:v>
       </x:c>
       <x:c r="D348" s="23" t="n">
-        <x:v>124660</x:v>
+        <x:v>135900</x:v>
       </x:c>
       <x:c r="E348" s="23" t="n">
-        <x:v>118100</x:v>
+        <x:v>126200</x:v>
       </x:c>
       <x:c r="F348" s="23" t="n">
-        <x:v>119780</x:v>
+        <x:v>128580</x:v>
       </x:c>
       <x:c r="G348" s="28" t="n">
         <x:f>ROUND(F348-F347,1)</x:f>
-        <x:v>-6200</x:v>
+        <x:v>-5760</x:v>
       </x:c>
       <x:c r="H348" s="24" t="n">
         <x:f>IFERROR(F348/F347-1,"")</x:f>
-        <x:v>-0.049214160977932964</x:v>
+        <x:v>-0.04287628405538191</x:v>
       </x:c>
       <x:c r="I348" s="26" t="n">
         <x:f>ROUND(D348-E348,1)</x:f>
-        <x:v>6560</x:v>
+        <x:v>9700</x:v>
       </x:c>
       <x:c r="J348" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K348" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349">
+      <x:c r="A349" s="22" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B349" s="22" t="str">
+        <x:v>9月21日-9月24日</x:v>
+      </x:c>
+      <x:c r="C349" s="23" t="n">
+        <x:v>128500</x:v>
+      </x:c>
+      <x:c r="D349" s="23" t="n">
+        <x:v>136560</x:v>
+      </x:c>
+      <x:c r="E349" s="23" t="n">
+        <x:v>125000</x:v>
+      </x:c>
+      <x:c r="F349" s="23" t="n">
+        <x:v>125980</x:v>
+      </x:c>
+      <x:c r="G349" s="28" t="n">
+        <x:f>ROUND(F349-F348,1)</x:f>
+        <x:v>-2600</x:v>
+      </x:c>
+      <x:c r="H349" s="24" t="n">
+        <x:f>IFERROR(F349/F348-1,"")</x:f>
+        <x:v>-0.02022087416394458</x:v>
+      </x:c>
+      <x:c r="I349" s="26" t="n">
+        <x:f>ROUND(D349-E349,1)</x:f>
+        <x:v>11560</x:v>
+      </x:c>
+      <x:c r="J349" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K349" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350">
+      <x:c r="A350" s="22" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B350" s="22" t="str">
+        <x:v>9月28日-9月30日</x:v>
+      </x:c>
+      <x:c r="C350" s="23" t="n">
+        <x:v>124280</x:v>
+      </x:c>
+      <x:c r="D350" s="23" t="n">
+        <x:v>124660</x:v>
+      </x:c>
+      <x:c r="E350" s="23" t="n">
+        <x:v>118100</x:v>
+      </x:c>
+      <x:c r="F350" s="23" t="n">
+        <x:v>119780</x:v>
+      </x:c>
+      <x:c r="G350" s="28" t="n">
+        <x:f>ROUND(F350-F349,1)</x:f>
+        <x:v>-6200</x:v>
+      </x:c>
+      <x:c r="H350" s="24" t="n">
+        <x:f>IFERROR(F350/F349-1,"")</x:f>
+        <x:v>-0.049214160977932964</x:v>
+      </x:c>
+      <x:c r="I350" s="26" t="n">
+        <x:f>ROUND(D350-E350,1)</x:f>
+        <x:v>6560</x:v>
+      </x:c>
+      <x:c r="J350" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K350" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="349">
-      <x:c r="A349" s="31" t="str">
+    <x:row r="351">
+      <x:c r="A351" s="22" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B351" s="22" t="str">
+        <x:v>10月8日</x:v>
+      </x:c>
+      <x:c r="C351" s="23" t="n">
+        <x:v>120020</x:v>
+      </x:c>
+      <x:c r="D351" s="23" t="n">
+        <x:v>126800</x:v>
+      </x:c>
+      <x:c r="E351" s="23" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="F351" s="23" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="G351" s="28" t="n">
+        <x:f>ROUND(F351-F350,1)</x:f>
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H351" s="24" t="n">
+        <x:f>IFERROR(F351/F350-1,"")</x:f>
+        <x:v>0.0018367006177992806</x:v>
+      </x:c>
+      <x:c r="I351" s="26" t="n">
+        <x:f>ROUND(D351-E351,1)</x:f>
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="J351" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K351" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352">
+      <x:c r="A352" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B349" s="30" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C349" s="30"/>
-      <x:c r="D349" s="30"/>
-      <x:c r="E349" s="30"/>
-      <x:c r="F349" s="30"/>
-      <x:c r="G349" s="30"/>
-      <x:c r="H349" s="30"/>
-      <x:c r="I349" s="32" t="n">
-        <x:f>ROUND(SUM(I311:I348),1)</x:f>
-        <x:v>759520</x:v>
-      </x:c>
-      <x:c r="J349" s="30"/>
-      <x:c r="K349" s="30"/>
-    </x:row>
-    <x:row r="350">
-      <x:c r="A350" s="31" t="str">
+      <x:c r="B352" s="30" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C352" s="30"/>
+      <x:c r="D352" s="30"/>
+      <x:c r="E352" s="30"/>
+      <x:c r="F352" s="30"/>
+      <x:c r="G352" s="30"/>
+      <x:c r="H352" s="30"/>
+      <x:c r="I352" s="32" t="n">
+        <x:f>ROUND(SUM(I313:I351),1)</x:f>
+        <x:v>766320</x:v>
+      </x:c>
+      <x:c r="J352" s="30"/>
+      <x:c r="K352" s="30"/>
+    </x:row>
+    <x:row r="353">
+      <x:c r="A353" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B350" s="30"/>
-      <x:c r="C350" s="30"/>
-      <x:c r="D350" s="30"/>
-      <x:c r="E350" s="30"/>
-      <x:c r="F350" s="30"/>
-      <x:c r="G350" s="30"/>
-      <x:c r="H350" s="30"/>
-      <x:c r="I350" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I311:I348),0),1)</x:f>
-        <x:v>19987.4</x:v>
-      </x:c>
-      <x:c r="J350" s="30"/>
-      <x:c r="K350" s="30"/>
+      <x:c r="B353" s="30"/>
+      <x:c r="C353" s="30"/>
+      <x:c r="D353" s="30"/>
+      <x:c r="E353" s="30"/>
+      <x:c r="F353" s="30"/>
+      <x:c r="G353" s="30"/>
+      <x:c r="H353" s="30"/>
+      <x:c r="I353" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I313:I351),0),1)</x:f>
+        <x:v>19649.2</x:v>
+      </x:c>
+      <x:c r="J353" s="30"/>
+      <x:c r="K353" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -20656,8 +20895,8 @@
     <x:mergeCell ref="A135:K135"/>
     <x:mergeCell ref="A179:K179"/>
     <x:mergeCell ref="A223:K223"/>
-    <x:mergeCell ref="A266:K266"/>
-    <x:mergeCell ref="A309:K309"/>
+    <x:mergeCell ref="A267:K267"/>
+    <x:mergeCell ref="A311:K311"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -65353,6 +65592,130 @@
       </x:c>
       <x:c r="K227" s="30"/>
     </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="17" t="str">
+        <x:v>10月</x:v>
+      </x:c>
+      <x:c r="B229" s="17"/>
+      <x:c r="C229" s="17"/>
+      <x:c r="D229" s="17"/>
+      <x:c r="E229" s="17"/>
+      <x:c r="F229" s="17"/>
+      <x:c r="G229" s="17"/>
+      <x:c r="H229" s="17"/>
+      <x:c r="I229" s="17"/>
+      <x:c r="J229" s="17"/>
+      <x:c r="K229" s="17"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B230" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C230" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D230" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E230" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F230" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G230" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H230" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I230" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J230" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K230" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B231" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C231" s="22" t="str">
+        <x:v>10月8日</x:v>
+      </x:c>
+      <x:c r="D231" s="23" t="n">
+        <x:v>4300.8</x:v>
+      </x:c>
+      <x:c r="E231" s="23" t="n">
+        <x:v>4331.6</x:v>
+      </x:c>
+      <x:c r="F231" s="23" t="n">
+        <x:v>4218.6</x:v>
+      </x:c>
+      <x:c r="G231" s="23" t="n">
+        <x:v>4248</x:v>
+      </x:c>
+      <x:c r="H231" s="23" t="n">
+        <x:v>-52.8</x:v>
+      </x:c>
+      <x:c r="I231" s="24" t="n">
+        <x:v>-0.01227678571428581</x:v>
+      </x:c>
+      <x:c r="J231" s="26" t="n">
+        <x:f>ROUND(E231-F231,1)</x:f>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="K231" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B232" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C232" s="30"/>
+      <x:c r="D232" s="30"/>
+      <x:c r="E232" s="30"/>
+      <x:c r="F232" s="30"/>
+      <x:c r="G232" s="30"/>
+      <x:c r="H232" s="30"/>
+      <x:c r="I232" s="30"/>
+      <x:c r="J232" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J231),1)</x:f>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="K232" s="30"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B233" s="30"/>
+      <x:c r="C233" s="30"/>
+      <x:c r="D233" s="30"/>
+      <x:c r="E233" s="30"/>
+      <x:c r="F233" s="30"/>
+      <x:c r="G233" s="30"/>
+      <x:c r="H233" s="30"/>
+      <x:c r="I233" s="30"/>
+      <x:c r="J233" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="K233" s="30"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K1"/>
@@ -65365,6 +65728,7 @@
     <x:mergeCell ref="A149:K149"/>
     <x:mergeCell ref="A177:K177"/>
     <x:mergeCell ref="A203:K203"/>
+    <x:mergeCell ref="A229:K229"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -72700,6 +73064,130 @@
       </x:c>
       <x:c r="K227" s="30"/>
     </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="17" t="str">
+        <x:v>10月</x:v>
+      </x:c>
+      <x:c r="B229" s="17"/>
+      <x:c r="C229" s="17"/>
+      <x:c r="D229" s="17"/>
+      <x:c r="E229" s="17"/>
+      <x:c r="F229" s="17"/>
+      <x:c r="G229" s="17"/>
+      <x:c r="H229" s="17"/>
+      <x:c r="I229" s="17"/>
+      <x:c r="J229" s="17"/>
+      <x:c r="K229" s="17"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="20" t="str">
+        <x:v>序号</x:v>
+      </x:c>
+      <x:c r="B230" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="C230" s="20" t="str">
+        <x:v>日期</x:v>
+      </x:c>
+      <x:c r="D230" s="20" t="str">
+        <x:v>开盘</x:v>
+      </x:c>
+      <x:c r="E230" s="20" t="str">
+        <x:v>高点</x:v>
+      </x:c>
+      <x:c r="F230" s="20" t="str">
+        <x:v>低点</x:v>
+      </x:c>
+      <x:c r="G230" s="20" t="str">
+        <x:v>收盘</x:v>
+      </x:c>
+      <x:c r="H230" s="20" t="str">
+        <x:v>涨跌点数</x:v>
+      </x:c>
+      <x:c r="I230" s="20" t="str">
+        <x:v>涨幅</x:v>
+      </x:c>
+      <x:c r="J230" s="20" t="str">
+        <x:v>振幅</x:v>
+      </x:c>
+      <x:c r="K230" s="20" t="str">
+        <x:v>标的</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B231" s="22" t="str">
+        <x:v>周四</x:v>
+      </x:c>
+      <x:c r="C231" s="22" t="str">
+        <x:v>10月8日</x:v>
+      </x:c>
+      <x:c r="D231" s="23" t="n">
+        <x:v>2764</x:v>
+      </x:c>
+      <x:c r="E231" s="23" t="n">
+        <x:v>2798.4</x:v>
+      </x:c>
+      <x:c r="F231" s="23" t="n">
+        <x:v>2747.4</x:v>
+      </x:c>
+      <x:c r="G231" s="23" t="n">
+        <x:v>2764.4</x:v>
+      </x:c>
+      <x:c r="H231" s="23" t="n">
+        <x:v>-14.4</x:v>
+      </x:c>
+      <x:c r="I231" s="24" t="n">
+        <x:v>-0.005182092989779785</x:v>
+      </x:c>
+      <x:c r="J231" s="23" t="n">
+        <x:f>ROUND(E231-F231,1)</x:f>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K231" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="31" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B232" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C232" s="30"/>
+      <x:c r="D232" s="30"/>
+      <x:c r="E232" s="30"/>
+      <x:c r="F232" s="30"/>
+      <x:c r="G232" s="30"/>
+      <x:c r="H232" s="30"/>
+      <x:c r="I232" s="30"/>
+      <x:c r="J232" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J231),1)</x:f>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K232" s="30"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B233" s="30"/>
+      <x:c r="C233" s="30"/>
+      <x:c r="D233" s="30"/>
+      <x:c r="E233" s="30"/>
+      <x:c r="F233" s="30"/>
+      <x:c r="G233" s="30"/>
+      <x:c r="H233" s="30"/>
+      <x:c r="I233" s="30"/>
+      <x:c r="J233" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K233" s="30"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K1"/>
@@ -72712,6 +73200,7 @@
     <x:mergeCell ref="A149:K149"/>
     <x:mergeCell ref="A177:K177"/>
     <x:mergeCell ref="A203:K203"/>
+    <x:mergeCell ref="A229:K229"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R00ed2e0ff6034bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R401a21c4fb5d4183"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb44de31d4b844073"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R06145364d4094055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Re2f2c6423cbd4092"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R5cdaef5068c04ab3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R519892cbf1784a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R42b6d23cc64c44bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R2ccc7650e438471d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R12ca275c6ea544fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R6835fa63099c415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rdaa6b917dd6e4d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R235311e5d9a341ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R06367dde116b461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb9bc9b268aaf4bc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R0027c0f5a3404c1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R2dbbca64067347a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R9a378c1bd8b342c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rcd4d34e5bb404cb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R1e3bb241e07b46c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7366.86</x:v>
+        <x:v>7175.33</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7087.8</x:v>
+        <x:v>6925.42</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>279.1</x:v>
+        <x:v>249.9</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>31770.1</x:v>
+        <x:v>32020</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>174.6</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7461.24</x:v>
+        <x:v>7277.14</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7206.06</x:v>
+        <x:v>7048.45</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>255.2</x:v>
+        <x:v>228.7</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>31540.3</x:v>
+        <x:v>31769</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>173.3</x:v>
+        <x:v>173.6</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3864.12</x:v>
+        <x:v>3824.71</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3795.37</x:v>
+        <x:v>3754.14</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>68.8</x:v>
+        <x:v>70.6</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8683.5</x:v>
+        <x:v>8754.1</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>47.7</x:v>
+        <x:v>47.8</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7251.8</x:v>
+        <x:v>7049</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>6948.2</x:v>
+        <x:v>6819.2</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>303.6</x:v>
+        <x:v>229.8</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>33797</x:v>
+        <x:v>34026.8</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>185.7</x:v>
+        <x:v>185.9</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>126800</x:v>
+        <x:v>123200</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>120000</x:v>
+        <x:v>119000</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>6800</x:v>
+        <x:v>4200</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1445240</x:v>
+        <x:v>1449440</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>7940.9</x:v>
+        <x:v>7920.4</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -8297,30 +8297,48 @@
       </x:c>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B232" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C232" s="30"/>
-      <x:c r="D232" s="30"/>
-      <x:c r="E232" s="30"/>
-      <x:c r="F232" s="30"/>
-      <x:c r="G232" s="30"/>
-      <x:c r="H232" s="30"/>
-      <x:c r="I232" s="30"/>
-      <x:c r="J232" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J231),1)</x:f>
-        <x:v>6800</x:v>
-      </x:c>
-      <x:c r="K232" s="30"/>
+      <x:c r="A232" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B232" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C232" s="22" t="str">
+        <x:v>10月9日</x:v>
+      </x:c>
+      <x:c r="D232" s="23" t="n">
+        <x:v>122300</x:v>
+      </x:c>
+      <x:c r="E232" s="23" t="n">
+        <x:v>123200</x:v>
+      </x:c>
+      <x:c r="F232" s="23" t="n">
+        <x:v>119000</x:v>
+      </x:c>
+      <x:c r="G232" s="23" t="n">
+        <x:v>121000</x:v>
+      </x:c>
+      <x:c r="H232" s="28" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I232" s="24" t="n">
+        <x:v>0.008333333333333304</x:v>
+      </x:c>
+      <x:c r="J232" s="23" t="n">
+        <x:f>ROUND(E232-F232,1)</x:f>
+        <x:v>4200</x:v>
+      </x:c>
+      <x:c r="K232" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B233" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B233" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C233" s="30"/>
       <x:c r="D233" s="30"/>
       <x:c r="E233" s="30"/>
@@ -8328,11 +8346,29 @@
       <x:c r="G233" s="30"/>
       <x:c r="H233" s="30"/>
       <x:c r="I233" s="30"/>
-      <x:c r="J233" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
-        <x:v>6800</x:v>
+      <x:c r="J233" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J232),1)</x:f>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="K233" s="30"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B234" s="30"/>
+      <x:c r="C234" s="30"/>
+      <x:c r="D234" s="30"/>
+      <x:c r="E234" s="30"/>
+      <x:c r="F234" s="30"/>
+      <x:c r="G234" s="30"/>
+      <x:c r="H234" s="30"/>
+      <x:c r="I234" s="30"/>
+      <x:c r="J234" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
+        <x:v>5500</x:v>
+      </x:c>
+      <x:c r="K234" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9867,7 +9903,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" s="22" t="str">
-        <x:v>10月8日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C43" s="23" t="n">
         <x:v>7306.74</x:v>
@@ -9876,28 +9912,28 @@
         <x:v>7366.86</x:v>
       </x:c>
       <x:c r="E43" s="23" t="n">
-        <x:v>7087.8</x:v>
+        <x:v>6925.42</x:v>
       </x:c>
       <x:c r="F43" s="23" t="n">
-        <x:v>7138.58</x:v>
-      </x:c>
-      <x:c r="G43" s="28" t="n">
+        <x:v>7155.91</x:v>
+      </x:c>
+      <x:c r="G43" s="23" t="n">
         <x:f>ROUND(F43-F42,1)</x:f>
-        <x:v>-160.2</x:v>
+        <x:v>-142.9</x:v>
       </x:c>
       <x:c r="H43" s="24" t="n">
         <x:f>IFERROR(F43/F42-1,"")</x:f>
-        <x:v>-0.02195423369804983</x:v>
+        <x:v>-0.019579877295234027</x:v>
       </x:c>
       <x:c r="I43" s="26" t="n">
         <x:f>ROUND(D43-E43,1)</x:f>
-        <x:v>279.1</x:v>
+        <x:v>441.4</x:v>
       </x:c>
       <x:c r="J43" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K43" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -9915,7 +9951,7 @@
       <x:c r="H44" s="30"/>
       <x:c r="I44" s="32" t="n">
         <x:f>ROUND(SUM(I5:I43),1)</x:f>
-        <x:v>15940.3</x:v>
+        <x:v>16102.6</x:v>
       </x:c>
       <x:c r="J44" s="30"/>
       <x:c r="K44" s="30"/>
@@ -9933,7 +9969,7 @@
       <x:c r="H45" s="30"/>
       <x:c r="I45" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I43),0),1)</x:f>
-        <x:v>408.7</x:v>
+        <x:v>412.9</x:v>
       </x:c>
       <x:c r="J45" s="30"/>
       <x:c r="K45" s="30"/>
@@ -11431,7 +11467,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B87" s="22" t="str">
-        <x:v>10月8日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C87" s="23" t="n">
         <x:v>7420.44</x:v>
@@ -11440,28 +11476,28 @@
         <x:v>7461.24</x:v>
       </x:c>
       <x:c r="E87" s="23" t="n">
-        <x:v>7206.06</x:v>
+        <x:v>7048.45</x:v>
       </x:c>
       <x:c r="F87" s="23" t="n">
-        <x:v>7248.43</x:v>
+        <x:v>7251.01</x:v>
       </x:c>
       <x:c r="G87" s="28" t="n">
         <x:f>ROUND(F87-F86,1)</x:f>
-        <x:v>-186.7</x:v>
+        <x:v>-184.1</x:v>
       </x:c>
       <x:c r="H87" s="24" t="n">
         <x:f>IFERROR(F87/F86-1,"")</x:f>
-        <x:v>-0.025114456178481626</x:v>
+        <x:v>-0.024767456248419584</x:v>
       </x:c>
       <x:c r="I87" s="26" t="n">
         <x:f>ROUND(D87-E87,1)</x:f>
-        <x:v>255.2</x:v>
+        <x:v>412.8</x:v>
       </x:c>
       <x:c r="J87" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K87" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -11479,7 +11515,7 @@
       <x:c r="H88" s="30"/>
       <x:c r="I88" s="32" t="n">
         <x:f>ROUND(SUM(I49:I87),1)</x:f>
-        <x:v>15841</x:v>
+        <x:v>15998.6</x:v>
       </x:c>
       <x:c r="J88" s="30"/>
       <x:c r="K88" s="30"/>
@@ -11497,7 +11533,7 @@
       <x:c r="H89" s="30"/>
       <x:c r="I89" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I49:I87),0),1)</x:f>
-        <x:v>406.2</x:v>
+        <x:v>410.2</x:v>
       </x:c>
       <x:c r="J89" s="30"/>
       <x:c r="K89" s="30"/>
@@ -12995,7 +13031,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B131" s="22" t="str">
-        <x:v>10月8日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C131" s="23" t="n">
         <x:v>3838.98</x:v>
@@ -13004,28 +13040,28 @@
         <x:v>3864.12</x:v>
       </x:c>
       <x:c r="E131" s="23" t="n">
-        <x:v>3795.37</x:v>
+        <x:v>3754.14</x:v>
       </x:c>
       <x:c r="F131" s="23" t="n">
-        <x:v>3811.9</x:v>
+        <x:v>3813.79</x:v>
       </x:c>
       <x:c r="G131" s="23" t="n">
         <x:f>ROUND(F131-F130,1)</x:f>
-        <x:v>-30.3</x:v>
+        <x:v>-28.4</x:v>
       </x:c>
       <x:c r="H131" s="24" t="n">
         <x:f>IFERROR(F131/F130-1,"")</x:f>
-        <x:v>-0.007883524760618266</x:v>
+        <x:v>-0.0073916178013060385</x:v>
       </x:c>
       <x:c r="I131" s="26" t="n">
         <x:f>ROUND(D131-E131,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J131" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K131" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -13043,7 +13079,7 @@
       <x:c r="H132" s="30"/>
       <x:c r="I132" s="32" t="n">
         <x:f>ROUND(SUM(I93:I131),1)</x:f>
-        <x:v>4160.9</x:v>
+        <x:v>4202.1</x:v>
       </x:c>
       <x:c r="J132" s="30"/>
       <x:c r="K132" s="30"/>
@@ -13061,7 +13097,7 @@
       <x:c r="H133" s="30"/>
       <x:c r="I133" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I93:I131),0),1)</x:f>
-        <x:v>106.7</x:v>
+        <x:v>107.7</x:v>
       </x:c>
       <x:c r="J133" s="30"/>
       <x:c r="K133" s="30"/>
@@ -14559,7 +14595,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B175" s="22" t="str">
-        <x:v>10月8日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C175" s="23" t="n">
         <x:v>7182.8</x:v>
@@ -14568,28 +14604,28 @@
         <x:v>7251.8</x:v>
       </x:c>
       <x:c r="E175" s="23" t="n">
-        <x:v>6948.2</x:v>
+        <x:v>6819.2</x:v>
       </x:c>
       <x:c r="F175" s="23" t="n">
-        <x:v>7022.2</x:v>
-      </x:c>
-      <x:c r="G175" s="23" t="n">
+        <x:v>7015.8</x:v>
+      </x:c>
+      <x:c r="G175" s="28" t="n">
         <x:f>ROUND(F175-F174,1)</x:f>
-        <x:v>-146.6</x:v>
+        <x:v>-153</x:v>
       </x:c>
       <x:c r="H175" s="24" t="n">
         <x:f>IFERROR(F175/F174-1,"")</x:f>
-        <x:v>-0.02044972659301425</x:v>
+        <x:v>-0.021342484097756964</x:v>
       </x:c>
       <x:c r="I175" s="26" t="n">
         <x:f>ROUND(D175-E175,1)</x:f>
-        <x:v>303.6</x:v>
+        <x:v>432.6</x:v>
       </x:c>
       <x:c r="J175" s="22" t="str">
         <x:v>IM2612</x:v>
       </x:c>
       <x:c r="K175" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -14607,7 +14643,7 @@
       <x:c r="H176" s="30"/>
       <x:c r="I176" s="32" t="n">
         <x:f>ROUND(SUM(I137:I175),1)</x:f>
-        <x:v>16634.2</x:v>
+        <x:v>16763.2</x:v>
       </x:c>
       <x:c r="J176" s="30"/>
       <x:c r="K176" s="30"/>
@@ -14625,7 +14661,7 @@
       <x:c r="H177" s="30"/>
       <x:c r="I177" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I137:I175),0),1)</x:f>
-        <x:v>426.5</x:v>
+        <x:v>429.8</x:v>
       </x:c>
       <x:c r="J177" s="30"/>
       <x:c r="K177" s="30"/>
@@ -20815,7 +20851,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B351" s="22" t="str">
-        <x:v>10月8日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C351" s="23" t="n">
         <x:v>120020</x:v>
@@ -20824,28 +20860,28 @@
         <x:v>126800</x:v>
       </x:c>
       <x:c r="E351" s="23" t="n">
-        <x:v>120000</x:v>
+        <x:v>119000</x:v>
       </x:c>
       <x:c r="F351" s="23" t="n">
-        <x:v>120000</x:v>
+        <x:v>121000</x:v>
       </x:c>
       <x:c r="G351" s="28" t="n">
         <x:f>ROUND(F351-F350,1)</x:f>
-        <x:v>220</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="H351" s="24" t="n">
         <x:f>IFERROR(F351/F350-1,"")</x:f>
-        <x:v>0.0018367006177992806</x:v>
+        <x:v>0.010185339789614334</x:v>
       </x:c>
       <x:c r="I351" s="26" t="n">
         <x:f>ROUND(D351-E351,1)</x:f>
-        <x:v>6800</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="J351" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K351" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="352">
@@ -20863,7 +20899,7 @@
       <x:c r="H352" s="30"/>
       <x:c r="I352" s="32" t="n">
         <x:f>ROUND(SUM(I313:I351),1)</x:f>
-        <x:v>766320</x:v>
+        <x:v>767320</x:v>
       </x:c>
       <x:c r="J352" s="30"/>
       <x:c r="K352" s="30"/>
@@ -20881,7 +20917,7 @@
       <x:c r="H353" s="30"/>
       <x:c r="I353" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I313:I351),0),1)</x:f>
-        <x:v>19649.2</x:v>
+        <x:v>19674.9</x:v>
       </x:c>
       <x:c r="J353" s="30"/>
       <x:c r="K353" s="30"/>
@@ -28319,30 +28355,48 @@
       </x:c>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B232" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C232" s="30"/>
-      <x:c r="D232" s="30"/>
-      <x:c r="E232" s="30"/>
-      <x:c r="F232" s="30"/>
-      <x:c r="G232" s="30"/>
-      <x:c r="H232" s="30"/>
-      <x:c r="I232" s="30"/>
-      <x:c r="J232" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J231),1)</x:f>
-        <x:v>279.1</x:v>
-      </x:c>
-      <x:c r="K232" s="30"/>
+      <x:c r="A232" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B232" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C232" s="22" t="str">
+        <x:v>10月9日</x:v>
+      </x:c>
+      <x:c r="D232" s="23" t="n">
+        <x:v>7107.54</x:v>
+      </x:c>
+      <x:c r="E232" s="23" t="n">
+        <x:v>7175.33</x:v>
+      </x:c>
+      <x:c r="F232" s="23" t="n">
+        <x:v>6925.42</x:v>
+      </x:c>
+      <x:c r="G232" s="23" t="n">
+        <x:v>7155.91</x:v>
+      </x:c>
+      <x:c r="H232" s="23" t="n">
+        <x:v>17.3</x:v>
+      </x:c>
+      <x:c r="I232" s="24" t="n">
+        <x:v>0.0024276536790230896</x:v>
+      </x:c>
+      <x:c r="J232" s="26" t="n">
+        <x:f>ROUND(E232-F232,1)</x:f>
+        <x:v>249.9</x:v>
+      </x:c>
+      <x:c r="K232" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B233" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B233" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C233" s="30"/>
       <x:c r="D233" s="30"/>
       <x:c r="E233" s="30"/>
@@ -28350,11 +28404,29 @@
       <x:c r="G233" s="30"/>
       <x:c r="H233" s="30"/>
       <x:c r="I233" s="30"/>
-      <x:c r="J233" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
-        <x:v>279.1</x:v>
+      <x:c r="J233" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J232),1)</x:f>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="K233" s="30"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B234" s="30"/>
+      <x:c r="C234" s="30"/>
+      <x:c r="D234" s="30"/>
+      <x:c r="E234" s="30"/>
+      <x:c r="F234" s="30"/>
+      <x:c r="G234" s="30"/>
+      <x:c r="H234" s="30"/>
+      <x:c r="I234" s="30"/>
+      <x:c r="J234" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
+        <x:v>264.5</x:v>
+      </x:c>
+      <x:c r="K234" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -35791,30 +35863,48 @@
       </x:c>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B232" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C232" s="30"/>
-      <x:c r="D232" s="30"/>
-      <x:c r="E232" s="30"/>
-      <x:c r="F232" s="30"/>
-      <x:c r="G232" s="30"/>
-      <x:c r="H232" s="30"/>
-      <x:c r="I232" s="30"/>
-      <x:c r="J232" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J231),1)</x:f>
-        <x:v>255.2</x:v>
-      </x:c>
-      <x:c r="K232" s="30"/>
+      <x:c r="A232" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B232" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C232" s="22" t="str">
+        <x:v>10月9日</x:v>
+      </x:c>
+      <x:c r="D232" s="23" t="n">
+        <x:v>7209.86</x:v>
+      </x:c>
+      <x:c r="E232" s="23" t="n">
+        <x:v>7277.14</x:v>
+      </x:c>
+      <x:c r="F232" s="23" t="n">
+        <x:v>7048.45</x:v>
+      </x:c>
+      <x:c r="G232" s="23" t="n">
+        <x:v>7251.01</x:v>
+      </x:c>
+      <x:c r="H232" s="23" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="I232" s="24" t="n">
+        <x:v>0.000355939148201756</x:v>
+      </x:c>
+      <x:c r="J232" s="26" t="n">
+        <x:f>ROUND(E232-F232,1)</x:f>
+        <x:v>228.7</x:v>
+      </x:c>
+      <x:c r="K232" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B233" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B233" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C233" s="30"/>
       <x:c r="D233" s="30"/>
       <x:c r="E233" s="30"/>
@@ -35822,11 +35912,29 @@
       <x:c r="G233" s="30"/>
       <x:c r="H233" s="30"/>
       <x:c r="I233" s="30"/>
-      <x:c r="J233" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
-        <x:v>255.2</x:v>
+      <x:c r="J233" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J232),1)</x:f>
+        <x:v>483.9</x:v>
       </x:c>
       <x:c r="K233" s="30"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B234" s="30"/>
+      <x:c r="C234" s="30"/>
+      <x:c r="D234" s="30"/>
+      <x:c r="E234" s="30"/>
+      <x:c r="F234" s="30"/>
+      <x:c r="G234" s="30"/>
+      <x:c r="H234" s="30"/>
+      <x:c r="I234" s="30"/>
+      <x:c r="J234" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="K234" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -43263,30 +43371,48 @@
       </x:c>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B232" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C232" s="30"/>
-      <x:c r="D232" s="30"/>
-      <x:c r="E232" s="30"/>
-      <x:c r="F232" s="30"/>
-      <x:c r="G232" s="30"/>
-      <x:c r="H232" s="30"/>
-      <x:c r="I232" s="30"/>
-      <x:c r="J232" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J231),1)</x:f>
-        <x:v>68.8</x:v>
-      </x:c>
-      <x:c r="K232" s="30"/>
+      <x:c r="A232" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B232" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C232" s="22" t="str">
+        <x:v>10月9日</x:v>
+      </x:c>
+      <x:c r="D232" s="23" t="n">
+        <x:v>3804.09</x:v>
+      </x:c>
+      <x:c r="E232" s="23" t="n">
+        <x:v>3824.71</x:v>
+      </x:c>
+      <x:c r="F232" s="23" t="n">
+        <x:v>3754.14</x:v>
+      </x:c>
+      <x:c r="G232" s="23" t="n">
+        <x:v>3813.79</x:v>
+      </x:c>
+      <x:c r="H232" s="23" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="I232" s="24" t="n">
+        <x:v>0.0004958157349352899</x:v>
+      </x:c>
+      <x:c r="J232" s="26" t="n">
+        <x:f>ROUND(E232-F232,1)</x:f>
+        <x:v>70.6</x:v>
+      </x:c>
+      <x:c r="K232" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B233" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B233" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C233" s="30"/>
       <x:c r="D233" s="30"/>
       <x:c r="E233" s="30"/>
@@ -43294,11 +43420,29 @@
       <x:c r="G233" s="30"/>
       <x:c r="H233" s="30"/>
       <x:c r="I233" s="30"/>
-      <x:c r="J233" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
-        <x:v>68.8</x:v>
+      <x:c r="J233" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J232),1)</x:f>
+        <x:v>139.4</x:v>
       </x:c>
       <x:c r="K233" s="30"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B234" s="30"/>
+      <x:c r="C234" s="30"/>
+      <x:c r="D234" s="30"/>
+      <x:c r="E234" s="30"/>
+      <x:c r="F234" s="30"/>
+      <x:c r="G234" s="30"/>
+      <x:c r="H234" s="30"/>
+      <x:c r="I234" s="30"/>
+      <x:c r="J234" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
+        <x:v>69.7</x:v>
+      </x:c>
+      <x:c r="K234" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -50735,30 +50879,48 @@
       </x:c>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B232" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C232" s="30"/>
-      <x:c r="D232" s="30"/>
-      <x:c r="E232" s="30"/>
-      <x:c r="F232" s="30"/>
-      <x:c r="G232" s="30"/>
-      <x:c r="H232" s="30"/>
-      <x:c r="I232" s="30"/>
-      <x:c r="J232" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J231),1)</x:f>
-        <x:v>303.6</x:v>
-      </x:c>
-      <x:c r="K232" s="30"/>
+      <x:c r="A232" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B232" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C232" s="22" t="str">
+        <x:v>10月9日</x:v>
+      </x:c>
+      <x:c r="D232" s="23" t="n">
+        <x:v>7001.4</x:v>
+      </x:c>
+      <x:c r="E232" s="23" t="n">
+        <x:v>7049</x:v>
+      </x:c>
+      <x:c r="F232" s="23" t="n">
+        <x:v>6819.2</x:v>
+      </x:c>
+      <x:c r="G232" s="23" t="n">
+        <x:v>7015.8</x:v>
+      </x:c>
+      <x:c r="H232" s="23" t="n">
+        <x:v>-6.4</x:v>
+      </x:c>
+      <x:c r="I232" s="24" t="n">
+        <x:v>-0.0009113952892255694</x:v>
+      </x:c>
+      <x:c r="J232" s="26" t="n">
+        <x:f>ROUND(E232-F232,1)</x:f>
+        <x:v>229.8</x:v>
+      </x:c>
+      <x:c r="K232" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B233" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B233" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C233" s="30"/>
       <x:c r="D233" s="30"/>
       <x:c r="E233" s="30"/>
@@ -50766,11 +50928,29 @@
       <x:c r="G233" s="30"/>
       <x:c r="H233" s="30"/>
       <x:c r="I233" s="30"/>
-      <x:c r="J233" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
-        <x:v>303.6</x:v>
+      <x:c r="J233" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J232),1)</x:f>
+        <x:v>533.4</x:v>
       </x:c>
       <x:c r="K233" s="30"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B234" s="30"/>
+      <x:c r="C234" s="30"/>
+      <x:c r="D234" s="30"/>
+      <x:c r="E234" s="30"/>
+      <x:c r="F234" s="30"/>
+      <x:c r="G234" s="30"/>
+      <x:c r="H234" s="30"/>
+      <x:c r="I234" s="30"/>
+      <x:c r="J234" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
+        <x:v>266.7</x:v>
+      </x:c>
+      <x:c r="K234" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R6835fa63099c415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="Rdaa6b917dd6e4d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R235311e5d9a341ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R06367dde116b461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb9bc9b268aaf4bc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R0027c0f5a3404c1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R2dbbca64067347a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R9a378c1bd8b342c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rcd4d34e5bb404cb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R1e3bb241e07b46c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R845d4f135c8c4d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R032ce7579c024f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R3bd7ff3d47514332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R036a25928bec4db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R328310a544c14d04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R40bd3e7a7a844446"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R20ebe76b8ddc40b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R76de3d6eb7094790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R72258a31d236492f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R00e3879dff7645ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7355</x:v>
+        <x:v>7148</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>7056.4</x:v>
+        <x:v>6932</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>298.6</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>34981.8</x:v>
+        <x:v>35197.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>192.2</x:v>
+        <x:v>192.3</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4331.6</x:v>
+        <x:v>4264.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4218.6</x:v>
+        <x:v>4180.4</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>113</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>13121.6</x:v>
+        <x:v>13205.8</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.1</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -693,22 +693,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-10-08</x:v>
+        <x:v>2026-10-09</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2798.4</x:v>
+        <x:v>2778.6</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2747.4</x:v>
+        <x:v>2735</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>51</x:v>
+        <x:v>43.6</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7285.4</x:v>
+        <x:v>7329</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>40</x:v>
@@ -16159,7 +16159,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B219" s="22" t="str">
-        <x:v>10月8日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C219" s="23" t="n">
         <x:v>7295</x:v>
@@ -16168,28 +16168,28 @@
         <x:v>7355</x:v>
       </x:c>
       <x:c r="E219" s="23" t="n">
-        <x:v>7056.4</x:v>
+        <x:v>6932</x:v>
       </x:c>
       <x:c r="F219" s="23" t="n">
-        <x:v>7122.8</x:v>
+        <x:v>7111</x:v>
       </x:c>
       <x:c r="G219" s="28" t="n">
         <x:f>ROUND(F219-F218,1)</x:f>
-        <x:v>-187.4</x:v>
+        <x:v>-199.2</x:v>
       </x:c>
       <x:c r="H219" s="24" t="n">
         <x:f>IFERROR(F219/F218-1,"")</x:f>
-        <x:v>-0.02563541353177745</x:v>
+        <x:v>-0.027249596454269387</x:v>
       </x:c>
       <x:c r="I219" s="26" t="n">
         <x:f>ROUND(D219-E219,1)</x:f>
-        <x:v>298.6</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="J219" s="22" t="str">
         <x:v>IC2612</x:v>
       </x:c>
       <x:c r="K219" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -16207,7 +16207,7 @@
       <x:c r="H220" s="30"/>
       <x:c r="I220" s="32" t="n">
         <x:f>ROUND(SUM(I181:I219),1)</x:f>
-        <x:v>17094.2</x:v>
+        <x:v>17218.6</x:v>
       </x:c>
       <x:c r="J220" s="30"/>
       <x:c r="K220" s="30"/>
@@ -16225,7 +16225,7 @@
       <x:c r="H221" s="30"/>
       <x:c r="I221" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I181:I219),0),1)</x:f>
-        <x:v>438.3</x:v>
+        <x:v>441.5</x:v>
       </x:c>
       <x:c r="J221" s="30"/>
       <x:c r="K221" s="30"/>
@@ -17723,7 +17723,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B263" s="22" t="str">
-        <x:v>10月8日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C263" s="23" t="n">
         <x:v>4300.8</x:v>
@@ -17732,28 +17732,28 @@
         <x:v>4331.6</x:v>
       </x:c>
       <x:c r="E263" s="23" t="n">
-        <x:v>4218.6</x:v>
+        <x:v>4180.4</x:v>
       </x:c>
       <x:c r="F263" s="23" t="n">
-        <x:v>4248</x:v>
+        <x:v>4244.8</x:v>
       </x:c>
       <x:c r="G263" s="23" t="n">
         <x:f>ROUND(F263-F262,1)</x:f>
-        <x:v>-52.8</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="H263" s="24" t="n">
         <x:f>IFERROR(F263/F262-1,"")</x:f>
-        <x:v>-0.01227678571428581</x:v>
+        <x:v>-0.01302083333333337</x:v>
       </x:c>
       <x:c r="I263" s="26" t="n">
         <x:f>ROUND(D263-E263,1)</x:f>
-        <x:v>113</x:v>
+        <x:v>151.2</x:v>
       </x:c>
       <x:c r="J263" s="22" t="str">
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K263" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
@@ -17771,7 +17771,7 @@
       <x:c r="H264" s="30"/>
       <x:c r="I264" s="32" t="n">
         <x:f>ROUND(SUM(I225:I263),1)</x:f>
-        <x:v>6100.4</x:v>
+        <x:v>6138.6</x:v>
       </x:c>
       <x:c r="J264" s="30"/>
       <x:c r="K264" s="30"/>
@@ -17789,7 +17789,7 @@
       <x:c r="H265" s="30"/>
       <x:c r="I265" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I225:I263),0),1)</x:f>
-        <x:v>156.4</x:v>
+        <x:v>157.4</x:v>
       </x:c>
       <x:c r="J265" s="30"/>
       <x:c r="K265" s="30"/>
@@ -19287,7 +19287,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B307" s="22" t="str">
-        <x:v>10月8日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C307" s="23" t="n">
         <x:v>2764</x:v>
@@ -19296,28 +19296,28 @@
         <x:v>2798.4</x:v>
       </x:c>
       <x:c r="E307" s="23" t="n">
-        <x:v>2747.4</x:v>
+        <x:v>2735</x:v>
       </x:c>
       <x:c r="F307" s="23" t="n">
-        <x:v>2764.4</x:v>
+        <x:v>2764</x:v>
       </x:c>
       <x:c r="G307" s="23" t="n">
         <x:f>ROUND(F307-F306,1)</x:f>
-        <x:v>-14.4</x:v>
+        <x:v>-14.8</x:v>
       </x:c>
       <x:c r="H307" s="24" t="n">
         <x:f>IFERROR(F307/F306-1,"")</x:f>
-        <x:v>-0.005182092989779785</x:v>
-      </x:c>
-      <x:c r="I307" s="23" t="n">
+        <x:v>-0.005326040017273659</x:v>
+      </x:c>
+      <x:c r="I307" s="26" t="n">
         <x:f>ROUND(D307-E307,1)</x:f>
-        <x:v>51</x:v>
+        <x:v>63.4</x:v>
       </x:c>
       <x:c r="J307" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K307" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="308">
@@ -19335,7 +19335,7 @@
       <x:c r="H308" s="30"/>
       <x:c r="I308" s="32" t="n">
         <x:f>ROUND(SUM(I269:I307),1)</x:f>
-        <x:v>3451.4</x:v>
+        <x:v>3463.8</x:v>
       </x:c>
       <x:c r="J308" s="30"/>
       <x:c r="K308" s="30"/>
@@ -19353,7 +19353,7 @@
       <x:c r="H309" s="30"/>
       <x:c r="I309" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I269:I307),0),1)</x:f>
-        <x:v>88.5</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="J309" s="30"/>
       <x:c r="K309" s="30"/>
@@ -58387,30 +58387,48 @@
       </x:c>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B232" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C232" s="30"/>
-      <x:c r="D232" s="30"/>
-      <x:c r="E232" s="30"/>
-      <x:c r="F232" s="30"/>
-      <x:c r="G232" s="30"/>
-      <x:c r="H232" s="30"/>
-      <x:c r="I232" s="30"/>
-      <x:c r="J232" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J231),1)</x:f>
-        <x:v>298.6</x:v>
-      </x:c>
-      <x:c r="K232" s="30"/>
+      <x:c r="A232" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B232" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C232" s="22" t="str">
+        <x:v>10月9日</x:v>
+      </x:c>
+      <x:c r="D232" s="23" t="n">
+        <x:v>7110</x:v>
+      </x:c>
+      <x:c r="E232" s="23" t="n">
+        <x:v>7148</x:v>
+      </x:c>
+      <x:c r="F232" s="23" t="n">
+        <x:v>6932</x:v>
+      </x:c>
+      <x:c r="G232" s="23" t="n">
+        <x:v>7111</x:v>
+      </x:c>
+      <x:c r="H232" s="23" t="n">
+        <x:v>-11.8</x:v>
+      </x:c>
+      <x:c r="I232" s="24" t="n">
+        <x:v>-0.0016566518784747464</x:v>
+      </x:c>
+      <x:c r="J232" s="26" t="n">
+        <x:f>ROUND(E232-F232,1)</x:f>
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="K232" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B233" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B233" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C233" s="30"/>
       <x:c r="D233" s="30"/>
       <x:c r="E233" s="30"/>
@@ -58418,11 +58436,29 @@
       <x:c r="G233" s="30"/>
       <x:c r="H233" s="30"/>
       <x:c r="I233" s="30"/>
-      <x:c r="J233" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
-        <x:v>298.6</x:v>
+      <x:c r="J233" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J232),1)</x:f>
+        <x:v>514.6</x:v>
       </x:c>
       <x:c r="K233" s="30"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B234" s="30"/>
+      <x:c r="C234" s="30"/>
+      <x:c r="D234" s="30"/>
+      <x:c r="E234" s="30"/>
+      <x:c r="F234" s="30"/>
+      <x:c r="G234" s="30"/>
+      <x:c r="H234" s="30"/>
+      <x:c r="I234" s="30"/>
+      <x:c r="J234" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
+        <x:v>257.3</x:v>
+      </x:c>
+      <x:c r="K234" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -65859,30 +65895,48 @@
       </x:c>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B232" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C232" s="30"/>
-      <x:c r="D232" s="30"/>
-      <x:c r="E232" s="30"/>
-      <x:c r="F232" s="30"/>
-      <x:c r="G232" s="30"/>
-      <x:c r="H232" s="30"/>
-      <x:c r="I232" s="30"/>
-      <x:c r="J232" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J231),1)</x:f>
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="K232" s="30"/>
+      <x:c r="A232" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B232" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C232" s="22" t="str">
+        <x:v>10月9日</x:v>
+      </x:c>
+      <x:c r="D232" s="23" t="n">
+        <x:v>4237.6</x:v>
+      </x:c>
+      <x:c r="E232" s="23" t="n">
+        <x:v>4264.6</x:v>
+      </x:c>
+      <x:c r="F232" s="23" t="n">
+        <x:v>4180.4</x:v>
+      </x:c>
+      <x:c r="G232" s="23" t="n">
+        <x:v>4244.8</x:v>
+      </x:c>
+      <x:c r="H232" s="23" t="n">
+        <x:v>-3.2</x:v>
+      </x:c>
+      <x:c r="I232" s="24" t="n">
+        <x:v>-0.0007532956685498693</x:v>
+      </x:c>
+      <x:c r="J232" s="23" t="n">
+        <x:f>ROUND(E232-F232,1)</x:f>
+        <x:v>84.2</x:v>
+      </x:c>
+      <x:c r="K232" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B233" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B233" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C233" s="30"/>
       <x:c r="D233" s="30"/>
       <x:c r="E233" s="30"/>
@@ -65890,11 +65944,29 @@
       <x:c r="G233" s="30"/>
       <x:c r="H233" s="30"/>
       <x:c r="I233" s="30"/>
-      <x:c r="J233" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
-        <x:v>113</x:v>
+      <x:c r="J233" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J232),1)</x:f>
+        <x:v>197.2</x:v>
       </x:c>
       <x:c r="K233" s="30"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B234" s="30"/>
+      <x:c r="C234" s="30"/>
+      <x:c r="D234" s="30"/>
+      <x:c r="E234" s="30"/>
+      <x:c r="F234" s="30"/>
+      <x:c r="G234" s="30"/>
+      <x:c r="H234" s="30"/>
+      <x:c r="I234" s="30"/>
+      <x:c r="J234" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
+        <x:v>98.6</x:v>
+      </x:c>
+      <x:c r="K234" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -73331,30 +73403,48 @@
       </x:c>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B232" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C232" s="30"/>
-      <x:c r="D232" s="30"/>
-      <x:c r="E232" s="30"/>
-      <x:c r="F232" s="30"/>
-      <x:c r="G232" s="30"/>
-      <x:c r="H232" s="30"/>
-      <x:c r="I232" s="30"/>
-      <x:c r="J232" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J231),1)</x:f>
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K232" s="30"/>
+      <x:c r="A232" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B232" s="22" t="str">
+        <x:v>周五</x:v>
+      </x:c>
+      <x:c r="C232" s="22" t="str">
+        <x:v>10月9日</x:v>
+      </x:c>
+      <x:c r="D232" s="23" t="n">
+        <x:v>2759</x:v>
+      </x:c>
+      <x:c r="E232" s="23" t="n">
+        <x:v>2778.6</x:v>
+      </x:c>
+      <x:c r="F232" s="23" t="n">
+        <x:v>2735</x:v>
+      </x:c>
+      <x:c r="G232" s="23" t="n">
+        <x:v>2764</x:v>
+      </x:c>
+      <x:c r="H232" s="23" t="n">
+        <x:v>-0.4</x:v>
+      </x:c>
+      <x:c r="I232" s="24" t="n">
+        <x:v>-0.00014469686007811955</x:v>
+      </x:c>
+      <x:c r="J232" s="23" t="n">
+        <x:f>ROUND(E232-F232,1)</x:f>
+        <x:v>43.6</x:v>
+      </x:c>
+      <x:c r="K232" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B233" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B233" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C233" s="30"/>
       <x:c r="D233" s="30"/>
       <x:c r="E233" s="30"/>
@@ -73362,11 +73452,29 @@
       <x:c r="G233" s="30"/>
       <x:c r="H233" s="30"/>
       <x:c r="I233" s="30"/>
-      <x:c r="J233" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J231),0),1)</x:f>
-        <x:v>51</x:v>
+      <x:c r="J233" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J232),1)</x:f>
+        <x:v>94.6</x:v>
       </x:c>
       <x:c r="K233" s="30"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B234" s="30"/>
+      <x:c r="C234" s="30"/>
+      <x:c r="D234" s="30"/>
+      <x:c r="E234" s="30"/>
+      <x:c r="F234" s="30"/>
+      <x:c r="G234" s="30"/>
+      <x:c r="H234" s="30"/>
+      <x:c r="I234" s="30"/>
+      <x:c r="J234" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
+        <x:v>47.3</x:v>
+      </x:c>
+      <x:c r="K234" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rb765c43368db432f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R901a9daddfb44270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R72187705d710477b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R5ae59ebe04354167"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R6625ce23083d43b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Ra253a198cce042f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Ra508da51b1434c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R182453ae7b5548cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="R8678ba91b41f4b5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R0886fcce23cd4b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3e596e04d6494180"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R682a5634401c457a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R835b21638804457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Reca6f85f8ea94298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rbc2ce11976b74544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rccb4de568b824d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rfb1efd62f28c4a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R8d4b511f0abb4955"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Ra3223df7eb60460f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R7bd4e34f0a44436b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-12</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7148</x:v>
+        <x:v>7115.6</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>6932</x:v>
+        <x:v>6943.6</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>216</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>35197.8</x:v>
+        <x:v>35369.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>192.3</x:v>
+        <x:v>192.2</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-12</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>123200</x:v>
+        <x:v>125960</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>119000</x:v>
+        <x:v>107100</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>4200</x:v>
+        <x:v>18860</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1449440</x:v>
+        <x:v>1468300</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>7920.4</x:v>
+        <x:v>7979.9</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -8333,30 +8333,48 @@
       </x:c>
     </x:row>
     <x:row r="233">
-      <x:c r="A233" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B233" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C233" s="30"/>
-      <x:c r="D233" s="30"/>
-      <x:c r="E233" s="30"/>
-      <x:c r="F233" s="30"/>
-      <x:c r="G233" s="30"/>
-      <x:c r="H233" s="30"/>
-      <x:c r="I233" s="30"/>
-      <x:c r="J233" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J232),1)</x:f>
-        <x:v>11000</x:v>
-      </x:c>
-      <x:c r="K233" s="30"/>
+      <x:c r="A233" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B233" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C233" s="22" t="str">
+        <x:v>10月12日</x:v>
+      </x:c>
+      <x:c r="D233" s="23" t="n">
+        <x:v>125960</x:v>
+      </x:c>
+      <x:c r="E233" s="23" t="n">
+        <x:v>125960</x:v>
+      </x:c>
+      <x:c r="F233" s="23" t="n">
+        <x:v>107100</x:v>
+      </x:c>
+      <x:c r="G233" s="23" t="n">
+        <x:v>107100</x:v>
+      </x:c>
+      <x:c r="H233" s="28" t="n">
+        <x:v>-13900</x:v>
+      </x:c>
+      <x:c r="I233" s="24" t="n">
+        <x:v>-0.11487603305785121</x:v>
+      </x:c>
+      <x:c r="J233" s="26" t="n">
+        <x:f>ROUND(E233-F233,1)</x:f>
+        <x:v>18860</x:v>
+      </x:c>
+      <x:c r="K233" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B234" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B234" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C234" s="30"/>
       <x:c r="D234" s="30"/>
       <x:c r="E234" s="30"/>
@@ -8364,11 +8382,29 @@
       <x:c r="G234" s="30"/>
       <x:c r="H234" s="30"/>
       <x:c r="I234" s="30"/>
-      <x:c r="J234" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
-        <x:v>5500</x:v>
+      <x:c r="J234" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J233),1)</x:f>
+        <x:v>29860</x:v>
       </x:c>
       <x:c r="K234" s="30"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B235" s="30"/>
+      <x:c r="C235" s="30"/>
+      <x:c r="D235" s="30"/>
+      <x:c r="E235" s="30"/>
+      <x:c r="F235" s="30"/>
+      <x:c r="G235" s="30"/>
+      <x:c r="H235" s="30"/>
+      <x:c r="I235" s="30"/>
+      <x:c r="J235" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
+        <x:v>9953.3</x:v>
+      </x:c>
+      <x:c r="K235" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -16345,155 +16381,155 @@
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B224" s="30" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C224" s="30"/>
-      <x:c r="D224" s="30"/>
-      <x:c r="E224" s="30"/>
-      <x:c r="F224" s="30"/>
-      <x:c r="G224" s="30"/>
-      <x:c r="H224" s="30"/>
-      <x:c r="I224" s="32" t="n">
-        <x:f>ROUND(SUM(I185:I223),1)</x:f>
-        <x:v>17218.6</x:v>
-      </x:c>
-      <x:c r="J224" s="30"/>
-      <x:c r="K224" s="30"/>
+      <x:c r="A224" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B224" s="22" t="str">
+        <x:v>10月12日</x:v>
+      </x:c>
+      <x:c r="C224" s="23" t="n">
+        <x:v>7076.6</x:v>
+      </x:c>
+      <x:c r="D224" s="23" t="n">
+        <x:v>7115.6</x:v>
+      </x:c>
+      <x:c r="E224" s="23" t="n">
+        <x:v>6943.6</x:v>
+      </x:c>
+      <x:c r="F224" s="23" t="n">
+        <x:v>6986</x:v>
+      </x:c>
+      <x:c r="G224" s="23" t="n">
+        <x:f>ROUND(F224-F223,1)</x:f>
+        <x:v>-125</x:v>
+      </x:c>
+      <x:c r="H224" s="24" t="n">
+        <x:f>IFERROR(F224/F223-1,"")</x:f>
+        <x:v>-0.017578399662494748</x:v>
+      </x:c>
+      <x:c r="I224" s="26" t="n">
+        <x:f>ROUND(D224-E224,1)</x:f>
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="J224" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
+      <x:c r="K224" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B225" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B225" s="30" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="C225" s="30"/>
       <x:c r="D225" s="30"/>
       <x:c r="E225" s="30"/>
       <x:c r="F225" s="30"/>
       <x:c r="G225" s="30"/>
       <x:c r="H225" s="30"/>
-      <x:c r="I225" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I185:I223),0),1)</x:f>
-        <x:v>441.5</x:v>
+      <x:c r="I225" s="32" t="n">
+        <x:f>ROUND(SUM(I185:I224),1)</x:f>
+        <x:v>17390.6</x:v>
       </x:c>
       <x:c r="J225" s="30"/>
       <x:c r="K225" s="30"/>
     </x:row>
-    <x:row r="227">
-      <x:c r="A227" s="17" t="str">
+    <x:row r="226">
+      <x:c r="A226" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B226" s="30"/>
+      <x:c r="C226" s="30"/>
+      <x:c r="D226" s="30"/>
+      <x:c r="E226" s="30"/>
+      <x:c r="F226" s="30"/>
+      <x:c r="G226" s="30"/>
+      <x:c r="H226" s="30"/>
+      <x:c r="I226" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I185:I224),0),1)</x:f>
+        <x:v>434.8</x:v>
+      </x:c>
+      <x:c r="J226" s="30"/>
+      <x:c r="K226" s="30"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="17" t="str">
         <x:v>IF主力</x:v>
       </x:c>
-      <x:c r="B227" s="17"/>
-      <x:c r="C227" s="17"/>
-      <x:c r="D227" s="17"/>
-      <x:c r="E227" s="17"/>
-      <x:c r="F227" s="17"/>
-      <x:c r="G227" s="17"/>
-      <x:c r="H227" s="17"/>
-      <x:c r="I227" s="17"/>
-      <x:c r="J227" s="17"/>
-      <x:c r="K227" s="17"/>
-    </x:row>
-    <x:row r="228">
-      <x:c r="A228" s="20" t="str">
+      <x:c r="B228" s="17"/>
+      <x:c r="C228" s="17"/>
+      <x:c r="D228" s="17"/>
+      <x:c r="E228" s="17"/>
+      <x:c r="F228" s="17"/>
+      <x:c r="G228" s="17"/>
+      <x:c r="H228" s="17"/>
+      <x:c r="I228" s="17"/>
+      <x:c r="J228" s="17"/>
+      <x:c r="K228" s="17"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B228" s="20" t="str">
+      <x:c r="B229" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C228" s="20" t="str">
+      <x:c r="C229" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D228" s="20" t="str">
+      <x:c r="D229" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E228" s="20" t="str">
+      <x:c r="E229" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F228" s="20" t="str">
+      <x:c r="F229" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G228" s="20" t="str">
+      <x:c r="G229" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H228" s="20" t="str">
+      <x:c r="H229" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I228" s="20" t="str">
+      <x:c r="I229" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J228" s="20" t="str">
+      <x:c r="J229" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K228" s="20" t="str">
+      <x:c r="K229" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="229">
-      <x:c r="A229" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B229" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C229" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="D229" s="23" t="n">
-        <x:v>4785.8</x:v>
-      </x:c>
-      <x:c r="E229" s="23" t="n">
-        <x:v>4627</x:v>
-      </x:c>
-      <x:c r="F229" s="23" t="n">
-        <x:v>4743.8</x:v>
-      </x:c>
-      <x:c r="G229" s="23"/>
-      <x:c r="H229" s="24"/>
-      <x:c r="I229" s="26" t="n">
-        <x:f>ROUND(D229-E229,1)</x:f>
-        <x:v>158.8</x:v>
-      </x:c>
-      <x:c r="J229" s="22" t="str">
-        <x:v>IF2603</x:v>
-      </x:c>
-      <x:c r="K229" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B230" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C230" s="23" t="n">
-        <x:v>4762</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="D230" s="23" t="n">
-        <x:v>4833.2</x:v>
+        <x:v>4785.8</x:v>
       </x:c>
       <x:c r="E230" s="23" t="n">
-        <x:v>4707</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="F230" s="23" t="n">
-        <x:v>4723.2</x:v>
-      </x:c>
-      <x:c r="G230" s="23" t="n">
-        <x:f>ROUND(F230-F229,1)</x:f>
-        <x:v>-20.6</x:v>
-      </x:c>
-      <x:c r="H230" s="24" t="n">
-        <x:f>IFERROR(F230/F229-1,"")</x:f>
-        <x:v>-0.004342510223871221</x:v>
-      </x:c>
+        <x:v>4743.8</x:v>
+      </x:c>
+      <x:c r="G230" s="23"/>
+      <x:c r="H230" s="24"/>
       <x:c r="I230" s="26" t="n">
         <x:f>ROUND(D230-E230,1)</x:f>
-        <x:v>126.2</x:v>
+        <x:v>158.8</x:v>
       </x:c>
       <x:c r="J230" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -16504,34 +16540,34 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B231" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C231" s="23" t="n">
-        <x:v>4711.8</x:v>
+        <x:v>4762</x:v>
       </x:c>
       <x:c r="D231" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4833.2</x:v>
       </x:c>
       <x:c r="E231" s="23" t="n">
-        <x:v>4672.8</x:v>
+        <x:v>4707</x:v>
       </x:c>
       <x:c r="F231" s="23" t="n">
-        <x:v>4709.2</x:v>
+        <x:v>4723.2</x:v>
       </x:c>
       <x:c r="G231" s="23" t="n">
         <x:f>ROUND(F231-F230,1)</x:f>
-        <x:v>-14</x:v>
+        <x:v>-20.6</x:v>
       </x:c>
       <x:c r="H231" s="24" t="n">
         <x:f>IFERROR(F231/F230-1,"")</x:f>
-        <x:v>-0.002964092140921415</x:v>
+        <x:v>-0.004342510223871221</x:v>
       </x:c>
       <x:c r="I231" s="26" t="n">
         <x:f>ROUND(D231-E231,1)</x:f>
-        <x:v>90.2</x:v>
+        <x:v>126.2</x:v>
       </x:c>
       <x:c r="J231" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -16542,34 +16578,34 @@
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B232" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C232" s="23" t="n">
-        <x:v>4726.8</x:v>
+        <x:v>4711.8</x:v>
       </x:c>
       <x:c r="D232" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E232" s="23" t="n">
-        <x:v>4640</x:v>
+        <x:v>4672.8</x:v>
       </x:c>
       <x:c r="F232" s="23" t="n">
-        <x:v>4711</x:v>
+        <x:v>4709.2</x:v>
       </x:c>
       <x:c r="G232" s="23" t="n">
         <x:f>ROUND(F232-F231,1)</x:f>
-        <x:v>1.8</x:v>
+        <x:v>-14</x:v>
       </x:c>
       <x:c r="H232" s="24" t="n">
         <x:f>IFERROR(F232/F231-1,"")</x:f>
-        <x:v>0.00038223052747810016</x:v>
+        <x:v>-0.002964092140921415</x:v>
       </x:c>
       <x:c r="I232" s="26" t="n">
         <x:f>ROUND(D232-E232,1)</x:f>
-        <x:v>153</x:v>
+        <x:v>90.2</x:v>
       </x:c>
       <x:c r="J232" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -16580,34 +16616,34 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B233" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C233" s="23" t="n">
-        <x:v>4680.6</x:v>
+        <x:v>4726.8</x:v>
       </x:c>
       <x:c r="D233" s="23" t="n">
-        <x:v>4724</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E233" s="23" t="n">
-        <x:v>4555.6</x:v>
+        <x:v>4640</x:v>
       </x:c>
       <x:c r="F233" s="23" t="n">
-        <x:v>4637.6</x:v>
+        <x:v>4711</x:v>
       </x:c>
       <x:c r="G233" s="23" t="n">
         <x:f>ROUND(F233-F232,1)</x:f>
-        <x:v>-73.4</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="H233" s="24" t="n">
         <x:f>IFERROR(F233/F232-1,"")</x:f>
-        <x:v>-0.015580556145192048</x:v>
+        <x:v>0.00038223052747810016</x:v>
       </x:c>
       <x:c r="I233" s="26" t="n">
         <x:f>ROUND(D233-E233,1)</x:f>
-        <x:v>168.4</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="J233" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -16618,34 +16654,34 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B234" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C234" s="23" t="n">
-        <x:v>4688.8</x:v>
+        <x:v>4680.6</x:v>
       </x:c>
       <x:c r="D234" s="23" t="n">
-        <x:v>4733.8</x:v>
+        <x:v>4724</x:v>
       </x:c>
       <x:c r="E234" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4555.6</x:v>
       </x:c>
       <x:c r="F234" s="23" t="n">
-        <x:v>4627</x:v>
+        <x:v>4637.6</x:v>
       </x:c>
       <x:c r="G234" s="23" t="n">
         <x:f>ROUND(F234-F233,1)</x:f>
-        <x:v>-10.6</x:v>
+        <x:v>-73.4</x:v>
       </x:c>
       <x:c r="H234" s="24" t="n">
         <x:f>IFERROR(F234/F233-1,"")</x:f>
-        <x:v>-0.0022856649991375155</x:v>
+        <x:v>-0.015580556145192048</x:v>
       </x:c>
       <x:c r="I234" s="26" t="n">
         <x:f>ROUND(D234-E234,1)</x:f>
-        <x:v>109.8</x:v>
+        <x:v>168.4</x:v>
       </x:c>
       <x:c r="J234" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -16656,110 +16692,110 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B235" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C235" s="23" t="n">
-        <x:v>4680.2</x:v>
+        <x:v>4688.8</x:v>
       </x:c>
       <x:c r="D235" s="23" t="n">
-        <x:v>4768</x:v>
+        <x:v>4733.8</x:v>
       </x:c>
       <x:c r="E235" s="23" t="n">
-        <x:v>4671.2</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="F235" s="23" t="n">
-        <x:v>4713.8</x:v>
+        <x:v>4627</x:v>
       </x:c>
       <x:c r="G235" s="23" t="n">
         <x:f>ROUND(F235-F234,1)</x:f>
-        <x:v>86.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="H235" s="24" t="n">
         <x:f>IFERROR(F235/F234-1,"")</x:f>
-        <x:v>0.01875945537065049</x:v>
+        <x:v>-0.0022856649991375155</x:v>
       </x:c>
       <x:c r="I235" s="26" t="n">
         <x:f>ROUND(D235-E235,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J235" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K235" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B236" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C236" s="23" t="n">
-        <x:v>4681.2</x:v>
+        <x:v>4680.2</x:v>
       </x:c>
       <x:c r="D236" s="23" t="n">
-        <x:v>4725</x:v>
+        <x:v>4768</x:v>
       </x:c>
       <x:c r="E236" s="23" t="n">
-        <x:v>4560.2</x:v>
+        <x:v>4671.2</x:v>
       </x:c>
       <x:c r="F236" s="23" t="n">
-        <x:v>4646</x:v>
+        <x:v>4713.8</x:v>
       </x:c>
       <x:c r="G236" s="23" t="n">
         <x:f>ROUND(F236-F235,1)</x:f>
-        <x:v>-67.8</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="H236" s="24" t="n">
         <x:f>IFERROR(F236/F235-1,"")</x:f>
-        <x:v>-0.014383300097585816</x:v>
+        <x:v>0.01875945537065049</x:v>
       </x:c>
       <x:c r="I236" s="26" t="n">
         <x:f>ROUND(D236-E236,1)</x:f>
-        <x:v>164.8</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J236" s="22" t="str">
         <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K236" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B237" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C237" s="23" t="n">
-        <x:v>4600</x:v>
+        <x:v>4681.2</x:v>
       </x:c>
       <x:c r="D237" s="23" t="n">
-        <x:v>4699</x:v>
+        <x:v>4725</x:v>
       </x:c>
       <x:c r="E237" s="23" t="n">
-        <x:v>4500</x:v>
+        <x:v>4560.2</x:v>
       </x:c>
       <x:c r="F237" s="23" t="n">
-        <x:v>4658</x:v>
+        <x:v>4646</x:v>
       </x:c>
       <x:c r="G237" s="23" t="n">
         <x:f>ROUND(F237-F236,1)</x:f>
-        <x:v>12</x:v>
+        <x:v>-67.8</x:v>
       </x:c>
       <x:c r="H237" s="24" t="n">
         <x:f>IFERROR(F237/F236-1,"")</x:f>
-        <x:v>0.00258286698235044</x:v>
+        <x:v>-0.014383300097585816</x:v>
       </x:c>
       <x:c r="I237" s="26" t="n">
         <x:f>ROUND(D237-E237,1)</x:f>
-        <x:v>199</x:v>
+        <x:v>164.8</x:v>
       </x:c>
       <x:c r="J237" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -16770,34 +16806,34 @@
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B238" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C238" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="D238" s="23" t="n">
-        <x:v>4718.4</x:v>
+        <x:v>4699</x:v>
       </x:c>
       <x:c r="E238" s="23" t="n">
-        <x:v>4570</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="F238" s="23" t="n">
-        <x:v>4596.8</x:v>
+        <x:v>4658</x:v>
       </x:c>
       <x:c r="G238" s="23" t="n">
         <x:f>ROUND(F238-F237,1)</x:f>
-        <x:v>-61.2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H238" s="24" t="n">
         <x:f>IFERROR(F238/F237-1,"")</x:f>
-        <x:v>-0.0131386861313868</x:v>
+        <x:v>0.00258286698235044</x:v>
       </x:c>
       <x:c r="I238" s="26" t="n">
         <x:f>ROUND(D238-E238,1)</x:f>
-        <x:v>148.4</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="J238" s="22" t="str">
         <x:v>IF2603</x:v>
@@ -16808,37 +16844,37 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B239" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C239" s="23" t="n">
-        <x:v>4434.4</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D239" s="23" t="n">
-        <x:v>4466.2</x:v>
+        <x:v>4718.4</x:v>
       </x:c>
       <x:c r="E239" s="23" t="n">
-        <x:v>4307.2</x:v>
+        <x:v>4570</x:v>
       </x:c>
       <x:c r="F239" s="23" t="n">
-        <x:v>4427.4</x:v>
-      </x:c>
-      <x:c r="G239" s="28" t="n">
+        <x:v>4596.8</x:v>
+      </x:c>
+      <x:c r="G239" s="23" t="n">
         <x:f>ROUND(F239-F238,1)</x:f>
-        <x:v>-169.4</x:v>
+        <x:v>-61.2</x:v>
       </x:c>
       <x:c r="H239" s="24" t="n">
         <x:f>IFERROR(F239/F238-1,"")</x:f>
-        <x:v>-0.0368517229376959</x:v>
+        <x:v>-0.0131386861313868</x:v>
       </x:c>
       <x:c r="I239" s="26" t="n">
         <x:f>ROUND(D239-E239,1)</x:f>
-        <x:v>159</x:v>
+        <x:v>148.4</x:v>
       </x:c>
       <x:c r="J239" s="22" t="str">
-        <x:v>IF2606</x:v>
+        <x:v>IF2603</x:v>
       </x:c>
       <x:c r="K239" s="22" t="n">
         <x:v>5</x:v>
@@ -16846,34 +16882,34 @@
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B240" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C240" s="23" t="n">
-        <x:v>4387.2</x:v>
+        <x:v>4434.4</x:v>
       </x:c>
       <x:c r="D240" s="23" t="n">
-        <x:v>4459.8</x:v>
+        <x:v>4466.2</x:v>
       </x:c>
       <x:c r="E240" s="23" t="n">
-        <x:v>4346</x:v>
+        <x:v>4307.2</x:v>
       </x:c>
       <x:c r="F240" s="23" t="n">
-        <x:v>4362.2</x:v>
-      </x:c>
-      <x:c r="G240" s="23" t="n">
+        <x:v>4427.4</x:v>
+      </x:c>
+      <x:c r="G240" s="28" t="n">
         <x:f>ROUND(F240-F239,1)</x:f>
-        <x:v>-65.2</x:v>
+        <x:v>-169.4</x:v>
       </x:c>
       <x:c r="H240" s="24" t="n">
         <x:f>IFERROR(F240/F239-1,"")</x:f>
-        <x:v>-0.014726476035596514</x:v>
+        <x:v>-0.0368517229376959</x:v>
       </x:c>
       <x:c r="I240" s="26" t="n">
         <x:f>ROUND(D240-E240,1)</x:f>
-        <x:v>113.8</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J240" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -16884,110 +16920,110 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B241" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C241" s="23" t="n">
-        <x:v>4369.8</x:v>
+        <x:v>4387.2</x:v>
       </x:c>
       <x:c r="D241" s="23" t="n">
-        <x:v>4591.8</x:v>
+        <x:v>4459.8</x:v>
       </x:c>
       <x:c r="E241" s="23" t="n">
-        <x:v>4347</x:v>
+        <x:v>4346</x:v>
       </x:c>
       <x:c r="F241" s="23" t="n">
-        <x:v>4562</x:v>
-      </x:c>
-      <x:c r="G241" s="28" t="n">
+        <x:v>4362.2</x:v>
+      </x:c>
+      <x:c r="G241" s="23" t="n">
         <x:f>ROUND(F241-F240,1)</x:f>
-        <x:v>199.8</x:v>
+        <x:v>-65.2</x:v>
       </x:c>
       <x:c r="H241" s="24" t="n">
         <x:f>IFERROR(F241/F240-1,"")</x:f>
-        <x:v>0.045802576681491125</x:v>
+        <x:v>-0.014726476035596514</x:v>
       </x:c>
       <x:c r="I241" s="26" t="n">
         <x:f>ROUND(D241-E241,1)</x:f>
-        <x:v>244.8</x:v>
+        <x:v>113.8</x:v>
       </x:c>
       <x:c r="J241" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K241" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B242" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C242" s="23" t="n">
-        <x:v>4542</x:v>
+        <x:v>4369.8</x:v>
       </x:c>
       <x:c r="D242" s="23" t="n">
-        <x:v>4685</x:v>
+        <x:v>4591.8</x:v>
       </x:c>
       <x:c r="E242" s="23" t="n">
-        <x:v>4541.6</x:v>
+        <x:v>4347</x:v>
       </x:c>
       <x:c r="F242" s="23" t="n">
-        <x:v>4667</x:v>
-      </x:c>
-      <x:c r="G242" s="23" t="n">
+        <x:v>4562</x:v>
+      </x:c>
+      <x:c r="G242" s="28" t="n">
         <x:f>ROUND(F242-F241,1)</x:f>
-        <x:v>105</x:v>
+        <x:v>199.8</x:v>
       </x:c>
       <x:c r="H242" s="24" t="n">
         <x:f>IFERROR(F242/F241-1,"")</x:f>
-        <x:v>0.0230162209557212</x:v>
+        <x:v>0.045802576681491125</x:v>
       </x:c>
       <x:c r="I242" s="26" t="n">
         <x:f>ROUND(D242-E242,1)</x:f>
-        <x:v>143.4</x:v>
+        <x:v>244.8</x:v>
       </x:c>
       <x:c r="J242" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K242" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B243" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C243" s="23" t="n">
-        <x:v>4665</x:v>
+        <x:v>4542</x:v>
       </x:c>
       <x:c r="D243" s="23" t="n">
-        <x:v>4763</x:v>
+        <x:v>4685</x:v>
       </x:c>
       <x:c r="E243" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4541.6</x:v>
       </x:c>
       <x:c r="F243" s="23" t="n">
-        <x:v>4713.6</x:v>
+        <x:v>4667</x:v>
       </x:c>
       <x:c r="G243" s="23" t="n">
         <x:f>ROUND(F243-F242,1)</x:f>
-        <x:v>46.6</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H243" s="24" t="n">
         <x:f>IFERROR(F243/F242-1,"")</x:f>
-        <x:v>0.009985001071352029</x:v>
+        <x:v>0.0230162209557212</x:v>
       </x:c>
       <x:c r="I243" s="26" t="n">
         <x:f>ROUND(D243-E243,1)</x:f>
-        <x:v>106.2</x:v>
+        <x:v>143.4</x:v>
       </x:c>
       <x:c r="J243" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -16998,148 +17034,148 @@
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B244" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C244" s="23" t="n">
-        <x:v>4720</x:v>
+        <x:v>4665</x:v>
       </x:c>
       <x:c r="D244" s="23" t="n">
-        <x:v>4776.6</x:v>
+        <x:v>4763</x:v>
       </x:c>
       <x:c r="E244" s="23" t="n">
-        <x:v>4687.2</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="F244" s="23" t="n">
-        <x:v>4763.4</x:v>
+        <x:v>4713.6</x:v>
       </x:c>
       <x:c r="G244" s="23" t="n">
         <x:f>ROUND(F244-F243,1)</x:f>
-        <x:v>49.8</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="H244" s="24" t="n">
         <x:f>IFERROR(F244/F243-1,"")</x:f>
-        <x:v>0.010565173116089399</x:v>
-      </x:c>
-      <x:c r="I244" s="23" t="n">
+        <x:v>0.009985001071352029</x:v>
+      </x:c>
+      <x:c r="I244" s="26" t="n">
         <x:f>ROUND(D244-E244,1)</x:f>
-        <x:v>89.4</x:v>
+        <x:v>106.2</x:v>
       </x:c>
       <x:c r="J244" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K244" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B245" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C245" s="23" t="n">
-        <x:v>4808.2</x:v>
+        <x:v>4720</x:v>
       </x:c>
       <x:c r="D245" s="23" t="n">
-        <x:v>4869</x:v>
+        <x:v>4776.6</x:v>
       </x:c>
       <x:c r="E245" s="23" t="n">
-        <x:v>4797</x:v>
+        <x:v>4687.2</x:v>
       </x:c>
       <x:c r="F245" s="23" t="n">
-        <x:v>4836.8</x:v>
+        <x:v>4763.4</x:v>
       </x:c>
       <x:c r="G245" s="23" t="n">
         <x:f>ROUND(F245-F244,1)</x:f>
-        <x:v>73.4</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="H245" s="24" t="n">
         <x:f>IFERROR(F245/F244-1,"")</x:f>
-        <x:v>0.015409161523281867</x:v>
+        <x:v>0.010565173116089399</x:v>
       </x:c>
       <x:c r="I245" s="23" t="n">
         <x:f>ROUND(D245-E245,1)</x:f>
-        <x:v>72</x:v>
+        <x:v>89.4</x:v>
       </x:c>
       <x:c r="J245" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K245" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B246" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C246" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4808.2</x:v>
       </x:c>
       <x:c r="D246" s="23" t="n">
-        <x:v>4995</x:v>
+        <x:v>4869</x:v>
       </x:c>
       <x:c r="E246" s="23" t="n">
-        <x:v>4794</x:v>
+        <x:v>4797</x:v>
       </x:c>
       <x:c r="F246" s="23" t="n">
-        <x:v>4824</x:v>
+        <x:v>4836.8</x:v>
       </x:c>
       <x:c r="G246" s="23" t="n">
         <x:f>ROUND(F246-F245,1)</x:f>
-        <x:v>-12.8</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="H246" s="24" t="n">
         <x:f>IFERROR(F246/F245-1,"")</x:f>
-        <x:v>-0.0026463777704267555</x:v>
-      </x:c>
-      <x:c r="I246" s="26" t="n">
+        <x:v>0.015409161523281867</x:v>
+      </x:c>
+      <x:c r="I246" s="23" t="n">
         <x:f>ROUND(D246-E246,1)</x:f>
-        <x:v>201</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J246" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K246" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B247" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C247" s="23" t="n">
-        <x:v>4810</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D247" s="23" t="n">
-        <x:v>4900.8</x:v>
+        <x:v>4995</x:v>
       </x:c>
       <x:c r="E247" s="23" t="n">
-        <x:v>4735</x:v>
+        <x:v>4794</x:v>
       </x:c>
       <x:c r="F247" s="23" t="n">
-        <x:v>4788.2</x:v>
+        <x:v>4824</x:v>
       </x:c>
       <x:c r="G247" s="23" t="n">
         <x:f>ROUND(F247-F246,1)</x:f>
-        <x:v>-35.8</x:v>
+        <x:v>-12.8</x:v>
       </x:c>
       <x:c r="H247" s="24" t="n">
         <x:f>IFERROR(F247/F246-1,"")</x:f>
-        <x:v>-0.007421227197346614</x:v>
+        <x:v>-0.0026463777704267555</x:v>
       </x:c>
       <x:c r="I247" s="26" t="n">
         <x:f>ROUND(D247-E247,1)</x:f>
-        <x:v>165.8</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="J247" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -17150,34 +17186,34 @@
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B248" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C248" s="23" t="n">
-        <x:v>4817.8</x:v>
+        <x:v>4810</x:v>
       </x:c>
       <x:c r="D248" s="23" t="n">
-        <x:v>4928.4</x:v>
+        <x:v>4900.8</x:v>
       </x:c>
       <x:c r="E248" s="23" t="n">
-        <x:v>4793.2</x:v>
+        <x:v>4735</x:v>
       </x:c>
       <x:c r="F248" s="23" t="n">
-        <x:v>4847.8</x:v>
+        <x:v>4788.2</x:v>
       </x:c>
       <x:c r="G248" s="23" t="n">
         <x:f>ROUND(F248-F247,1)</x:f>
-        <x:v>59.6</x:v>
+        <x:v>-35.8</x:v>
       </x:c>
       <x:c r="H248" s="24" t="n">
         <x:f>IFERROR(F248/F247-1,"")</x:f>
-        <x:v>0.01244726619606551</x:v>
+        <x:v>-0.007421227197346614</x:v>
       </x:c>
       <x:c r="I248" s="26" t="n">
         <x:f>ROUND(D248-E248,1)</x:f>
-        <x:v>135.2</x:v>
+        <x:v>165.8</x:v>
       </x:c>
       <x:c r="J248" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -17188,34 +17224,34 @@
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B249" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C249" s="23" t="n">
-        <x:v>4860</x:v>
+        <x:v>4817.8</x:v>
       </x:c>
       <x:c r="D249" s="23" t="n">
-        <x:v>4964.6</x:v>
+        <x:v>4928.4</x:v>
       </x:c>
       <x:c r="E249" s="23" t="n">
-        <x:v>4762.2</x:v>
+        <x:v>4793.2</x:v>
       </x:c>
       <x:c r="F249" s="23" t="n">
-        <x:v>4776.8</x:v>
+        <x:v>4847.8</x:v>
       </x:c>
       <x:c r="G249" s="23" t="n">
         <x:f>ROUND(F249-F248,1)</x:f>
-        <x:v>-71</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="H249" s="24" t="n">
         <x:f>IFERROR(F249/F248-1,"")</x:f>
-        <x:v>-0.014645818721894521</x:v>
+        <x:v>0.01244726619606551</x:v>
       </x:c>
       <x:c r="I249" s="26" t="n">
         <x:f>ROUND(D249-E249,1)</x:f>
-        <x:v>202.4</x:v>
+        <x:v>135.2</x:v>
       </x:c>
       <x:c r="J249" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -17226,34 +17262,34 @@
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B250" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C250" s="23" t="n">
-        <x:v>4700</x:v>
+        <x:v>4860</x:v>
       </x:c>
       <x:c r="D250" s="23" t="n">
-        <x:v>4793</x:v>
+        <x:v>4964.6</x:v>
       </x:c>
       <x:c r="E250" s="23" t="n">
-        <x:v>4640.2</x:v>
+        <x:v>4762.2</x:v>
       </x:c>
       <x:c r="F250" s="23" t="n">
-        <x:v>4769.8</x:v>
+        <x:v>4776.8</x:v>
       </x:c>
       <x:c r="G250" s="23" t="n">
         <x:f>ROUND(F250-F249,1)</x:f>
-        <x:v>-7</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="H250" s="24" t="n">
         <x:f>IFERROR(F250/F249-1,"")</x:f>
-        <x:v>-0.0014654161781946229</x:v>
+        <x:v>-0.014645818721894521</x:v>
       </x:c>
       <x:c r="I250" s="26" t="n">
         <x:f>ROUND(D250-E250,1)</x:f>
-        <x:v>152.8</x:v>
+        <x:v>202.4</x:v>
       </x:c>
       <x:c r="J250" s="22" t="str">
         <x:v>IF2606</x:v>
@@ -17264,113 +17300,113 @@
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B251" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C251" s="23" t="n">
-        <x:v>4819</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="D251" s="23" t="n">
-        <x:v>4971</x:v>
+        <x:v>4793</x:v>
       </x:c>
       <x:c r="E251" s="23" t="n">
-        <x:v>4804.8</x:v>
+        <x:v>4640.2</x:v>
       </x:c>
       <x:c r="F251" s="23" t="n">
-        <x:v>4960.6</x:v>
-      </x:c>
-      <x:c r="G251" s="28" t="n">
+        <x:v>4769.8</x:v>
+      </x:c>
+      <x:c r="G251" s="23" t="n">
         <x:f>ROUND(F251-F250,1)</x:f>
-        <x:v>190.8</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="H251" s="24" t="n">
         <x:f>IFERROR(F251/F250-1,"")</x:f>
-        <x:v>0.040001677219170695</x:v>
+        <x:v>-0.0014654161781946229</x:v>
       </x:c>
       <x:c r="I251" s="26" t="n">
         <x:f>ROUND(D251-E251,1)</x:f>
-        <x:v>166.2</x:v>
+        <x:v>152.8</x:v>
       </x:c>
       <x:c r="J251" s="22" t="str">
         <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K251" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B252" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C252" s="23" t="n">
-        <x:v>4956</x:v>
+        <x:v>4819</x:v>
       </x:c>
       <x:c r="D252" s="23" t="n">
-        <x:v>5030.2</x:v>
+        <x:v>4971</x:v>
       </x:c>
       <x:c r="E252" s="23" t="n">
-        <x:v>4717</x:v>
+        <x:v>4804.8</x:v>
       </x:c>
       <x:c r="F252" s="23" t="n">
-        <x:v>4748.2</x:v>
+        <x:v>4960.6</x:v>
       </x:c>
       <x:c r="G252" s="28" t="n">
         <x:f>ROUND(F252-F251,1)</x:f>
-        <x:v>-212.4</x:v>
+        <x:v>190.8</x:v>
       </x:c>
       <x:c r="H252" s="24" t="n">
         <x:f>IFERROR(F252/F251-1,"")</x:f>
-        <x:v>-0.04281740112083221</x:v>
+        <x:v>0.040001677219170695</x:v>
       </x:c>
       <x:c r="I252" s="26" t="n">
         <x:f>ROUND(D252-E252,1)</x:f>
-        <x:v>313.2</x:v>
+        <x:v>166.2</x:v>
       </x:c>
       <x:c r="J252" s="22" t="str">
-        <x:v>IF2606/IF2609</x:v>
+        <x:v>IF2606</x:v>
       </x:c>
       <x:c r="K252" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B253" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C253" s="23" t="n">
-        <x:v>4759.4</x:v>
+        <x:v>4956</x:v>
       </x:c>
       <x:c r="D253" s="23" t="n">
-        <x:v>4899.6</x:v>
+        <x:v>5030.2</x:v>
       </x:c>
       <x:c r="E253" s="23" t="n">
-        <x:v>4705</x:v>
+        <x:v>4717</x:v>
       </x:c>
       <x:c r="F253" s="23" t="n">
-        <x:v>4752.2</x:v>
-      </x:c>
-      <x:c r="G253" s="23" t="n">
+        <x:v>4748.2</x:v>
+      </x:c>
+      <x:c r="G253" s="28" t="n">
         <x:f>ROUND(F253-F252,1)</x:f>
-        <x:v>4</x:v>
+        <x:v>-212.4</x:v>
       </x:c>
       <x:c r="H253" s="24" t="n">
         <x:f>IFERROR(F253/F252-1,"")</x:f>
-        <x:v>0.0008424244977043305</x:v>
+        <x:v>-0.04281740112083221</x:v>
       </x:c>
       <x:c r="I253" s="26" t="n">
         <x:f>ROUND(D253-E253,1)</x:f>
-        <x:v>194.6</x:v>
+        <x:v>313.2</x:v>
       </x:c>
       <x:c r="J253" s="22" t="str">
-        <x:v>IF2609</x:v>
+        <x:v>IF2606/IF2609</x:v>
       </x:c>
       <x:c r="K253" s="22" t="n">
         <x:v>5</x:v>
@@ -17378,34 +17414,34 @@
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B254" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C254" s="23" t="n">
-        <x:v>4781</x:v>
+        <x:v>4759.4</x:v>
       </x:c>
       <x:c r="D254" s="23" t="n">
-        <x:v>4822.2</x:v>
+        <x:v>4899.6</x:v>
       </x:c>
       <x:c r="E254" s="23" t="n">
-        <x:v>4665.2</x:v>
+        <x:v>4705</x:v>
       </x:c>
       <x:c r="F254" s="23" t="n">
-        <x:v>4704.6</x:v>
+        <x:v>4752.2</x:v>
       </x:c>
       <x:c r="G254" s="23" t="n">
         <x:f>ROUND(F254-F253,1)</x:f>
-        <x:v>-47.6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H254" s="24" t="n">
         <x:f>IFERROR(F254/F253-1,"")</x:f>
-        <x:v>-0.010016413450612216</x:v>
+        <x:v>0.0008424244977043305</x:v>
       </x:c>
       <x:c r="I254" s="26" t="n">
         <x:f>ROUND(D254-E254,1)</x:f>
-        <x:v>157</x:v>
+        <x:v>194.6</x:v>
       </x:c>
       <x:c r="J254" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17416,34 +17452,34 @@
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B255" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C255" s="23" t="n">
-        <x:v>4691</x:v>
+        <x:v>4781</x:v>
       </x:c>
       <x:c r="D255" s="23" t="n">
-        <x:v>4739.4</x:v>
+        <x:v>4822.2</x:v>
       </x:c>
       <x:c r="E255" s="23" t="n">
-        <x:v>4441.4</x:v>
+        <x:v>4665.2</x:v>
       </x:c>
       <x:c r="F255" s="23" t="n">
-        <x:v>4473.8</x:v>
-      </x:c>
-      <x:c r="G255" s="28" t="n">
+        <x:v>4704.6</x:v>
+      </x:c>
+      <x:c r="G255" s="23" t="n">
         <x:f>ROUND(F255-F254,1)</x:f>
-        <x:v>-230.8</x:v>
+        <x:v>-47.6</x:v>
       </x:c>
       <x:c r="H255" s="24" t="n">
         <x:f>IFERROR(F255/F254-1,"")</x:f>
-        <x:v>-0.04905836840539046</x:v>
+        <x:v>-0.010016413450612216</x:v>
       </x:c>
       <x:c r="I255" s="26" t="n">
         <x:f>ROUND(D255-E255,1)</x:f>
-        <x:v>298</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="J255" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17454,34 +17490,34 @@
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B256" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C256" s="23" t="n">
-        <x:v>4530</x:v>
+        <x:v>4691</x:v>
       </x:c>
       <x:c r="D256" s="23" t="n">
-        <x:v>4707.8</x:v>
+        <x:v>4739.4</x:v>
       </x:c>
       <x:c r="E256" s="23" t="n">
-        <x:v>4465</x:v>
+        <x:v>4441.4</x:v>
       </x:c>
       <x:c r="F256" s="23" t="n">
-        <x:v>4578.2</x:v>
-      </x:c>
-      <x:c r="G256" s="23" t="n">
+        <x:v>4473.8</x:v>
+      </x:c>
+      <x:c r="G256" s="28" t="n">
         <x:f>ROUND(F256-F255,1)</x:f>
-        <x:v>104.4</x:v>
+        <x:v>-230.8</x:v>
       </x:c>
       <x:c r="H256" s="24" t="n">
         <x:f>IFERROR(F256/F255-1,"")</x:f>
-        <x:v>0.023335866601099653</x:v>
+        <x:v>-0.04905836840539046</x:v>
       </x:c>
       <x:c r="I256" s="26" t="n">
         <x:f>ROUND(D256-E256,1)</x:f>
-        <x:v>242.8</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="J256" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17492,34 +17528,34 @@
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B257" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C257" s="23" t="n">
-        <x:v>4589.4</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="D257" s="23" t="n">
-        <x:v>4652.2</x:v>
+        <x:v>4707.8</x:v>
       </x:c>
       <x:c r="E257" s="23" t="n">
-        <x:v>4420</x:v>
+        <x:v>4465</x:v>
       </x:c>
       <x:c r="F257" s="23" t="n">
-        <x:v>4538</x:v>
+        <x:v>4578.2</x:v>
       </x:c>
       <x:c r="G257" s="23" t="n">
         <x:f>ROUND(F257-F256,1)</x:f>
-        <x:v>-40.2</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="H257" s="24" t="n">
         <x:f>IFERROR(F257/F256-1,"")</x:f>
-        <x:v>-0.008780743523655543</x:v>
+        <x:v>0.023335866601099653</x:v>
       </x:c>
       <x:c r="I257" s="26" t="n">
         <x:f>ROUND(D257-E257,1)</x:f>
-        <x:v>232.2</x:v>
+        <x:v>242.8</x:v>
       </x:c>
       <x:c r="J257" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17530,34 +17566,34 @@
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B258" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C258" s="23" t="n">
-        <x:v>4526.4</x:v>
+        <x:v>4589.4</x:v>
       </x:c>
       <x:c r="D258" s="23" t="n">
-        <x:v>4656.2</x:v>
+        <x:v>4652.2</x:v>
       </x:c>
       <x:c r="E258" s="23" t="n">
-        <x:v>4494.2</x:v>
+        <x:v>4420</x:v>
       </x:c>
       <x:c r="F258" s="23" t="n">
-        <x:v>4645.6</x:v>
+        <x:v>4538</x:v>
       </x:c>
       <x:c r="G258" s="23" t="n">
         <x:f>ROUND(F258-F257,1)</x:f>
-        <x:v>107.6</x:v>
+        <x:v>-40.2</x:v>
       </x:c>
       <x:c r="H258" s="24" t="n">
         <x:f>IFERROR(F258/F257-1,"")</x:f>
-        <x:v>0.02371088585279857</x:v>
+        <x:v>-0.008780743523655543</x:v>
       </x:c>
       <x:c r="I258" s="26" t="n">
         <x:f>ROUND(D258-E258,1)</x:f>
-        <x:v>162</x:v>
+        <x:v>232.2</x:v>
       </x:c>
       <x:c r="J258" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17568,34 +17604,34 @@
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B259" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C259" s="23" t="n">
-        <x:v>4656.8</x:v>
+        <x:v>4526.4</x:v>
       </x:c>
       <x:c r="D259" s="23" t="n">
-        <x:v>4681</x:v>
+        <x:v>4656.2</x:v>
       </x:c>
       <x:c r="E259" s="23" t="n">
-        <x:v>4598</x:v>
+        <x:v>4494.2</x:v>
       </x:c>
       <x:c r="F259" s="23" t="n">
-        <x:v>4620.4</x:v>
+        <x:v>4645.6</x:v>
       </x:c>
       <x:c r="G259" s="23" t="n">
         <x:f>ROUND(F259-F258,1)</x:f>
-        <x:v>-25.2</x:v>
+        <x:v>107.6</x:v>
       </x:c>
       <x:c r="H259" s="24" t="n">
         <x:f>IFERROR(F259/F258-1,"")</x:f>
-        <x:v>-0.005424487687274104</x:v>
-      </x:c>
-      <x:c r="I259" s="23" t="n">
+        <x:v>0.02371088585279857</x:v>
+      </x:c>
+      <x:c r="I259" s="26" t="n">
         <x:f>ROUND(D259-E259,1)</x:f>
-        <x:v>83</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J259" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17606,34 +17642,34 @@
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B260" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C260" s="23" t="n">
-        <x:v>4624</x:v>
+        <x:v>4656.8</x:v>
       </x:c>
       <x:c r="D260" s="23" t="n">
-        <x:v>4700.6</x:v>
+        <x:v>4681</x:v>
       </x:c>
       <x:c r="E260" s="23" t="n">
-        <x:v>4531.8</x:v>
+        <x:v>4598</x:v>
       </x:c>
       <x:c r="F260" s="23" t="n">
-        <x:v>4576</x:v>
+        <x:v>4620.4</x:v>
       </x:c>
       <x:c r="G260" s="23" t="n">
         <x:f>ROUND(F260-F259,1)</x:f>
-        <x:v>-44.4</x:v>
+        <x:v>-25.2</x:v>
       </x:c>
       <x:c r="H260" s="24" t="n">
         <x:f>IFERROR(F260/F259-1,"")</x:f>
-        <x:v>-0.00960955761405935</x:v>
-      </x:c>
-      <x:c r="I260" s="26" t="n">
+        <x:v>-0.005424487687274104</x:v>
+      </x:c>
+      <x:c r="I260" s="23" t="n">
         <x:f>ROUND(D260-E260,1)</x:f>
-        <x:v>168.8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J260" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17644,34 +17680,34 @@
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B261" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C261" s="23" t="n">
-        <x:v>4607.4</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="D261" s="23" t="n">
-        <x:v>4620</x:v>
+        <x:v>4700.6</x:v>
       </x:c>
       <x:c r="E261" s="23" t="n">
-        <x:v>4486.4</x:v>
+        <x:v>4531.8</x:v>
       </x:c>
       <x:c r="F261" s="23" t="n">
-        <x:v>4593.6</x:v>
+        <x:v>4576</x:v>
       </x:c>
       <x:c r="G261" s="23" t="n">
         <x:f>ROUND(F261-F260,1)</x:f>
-        <x:v>17.6</x:v>
+        <x:v>-44.4</x:v>
       </x:c>
       <x:c r="H261" s="24" t="n">
         <x:f>IFERROR(F261/F260-1,"")</x:f>
-        <x:v>0.0038461538461538325</x:v>
+        <x:v>-0.00960955761405935</x:v>
       </x:c>
       <x:c r="I261" s="26" t="n">
         <x:f>ROUND(D261-E261,1)</x:f>
-        <x:v>133.6</x:v>
+        <x:v>168.8</x:v>
       </x:c>
       <x:c r="J261" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17682,34 +17718,34 @@
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B262" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C262" s="23" t="n">
-        <x:v>4553</x:v>
+        <x:v>4607.4</x:v>
       </x:c>
       <x:c r="D262" s="23" t="n">
-        <x:v>4617.8</x:v>
+        <x:v>4620</x:v>
       </x:c>
       <x:c r="E262" s="23" t="n">
-        <x:v>4497.6</x:v>
+        <x:v>4486.4</x:v>
       </x:c>
       <x:c r="F262" s="23" t="n">
-        <x:v>4537.4</x:v>
+        <x:v>4593.6</x:v>
       </x:c>
       <x:c r="G262" s="23" t="n">
         <x:f>ROUND(F262-F261,1)</x:f>
-        <x:v>-56.2</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="H262" s="24" t="n">
         <x:f>IFERROR(F262/F261-1,"")</x:f>
-        <x:v>-0.01223441309648221</x:v>
+        <x:v>0.0038461538461538325</x:v>
       </x:c>
       <x:c r="I262" s="26" t="n">
         <x:f>ROUND(D262-E262,1)</x:f>
-        <x:v>120.2</x:v>
+        <x:v>133.6</x:v>
       </x:c>
       <x:c r="J262" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17720,34 +17756,34 @@
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B263" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C263" s="23" t="n">
-        <x:v>4562</x:v>
+        <x:v>4553</x:v>
       </x:c>
       <x:c r="D263" s="23" t="n">
-        <x:v>4584</x:v>
+        <x:v>4617.8</x:v>
       </x:c>
       <x:c r="E263" s="23" t="n">
-        <x:v>4451.6</x:v>
+        <x:v>4497.6</x:v>
       </x:c>
       <x:c r="F263" s="23" t="n">
-        <x:v>4503.4</x:v>
+        <x:v>4537.4</x:v>
       </x:c>
       <x:c r="G263" s="23" t="n">
         <x:f>ROUND(F263-F262,1)</x:f>
-        <x:v>-34</x:v>
+        <x:v>-56.2</x:v>
       </x:c>
       <x:c r="H263" s="24" t="n">
         <x:f>IFERROR(F263/F262-1,"")</x:f>
-        <x:v>-0.007493278088773314</x:v>
+        <x:v>-0.01223441309648221</x:v>
       </x:c>
       <x:c r="I263" s="26" t="n">
         <x:f>ROUND(D263-E263,1)</x:f>
-        <x:v>132.4</x:v>
+        <x:v>120.2</x:v>
       </x:c>
       <x:c r="J263" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17758,34 +17794,34 @@
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B264" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C264" s="23" t="n">
-        <x:v>4468</x:v>
+        <x:v>4562</x:v>
       </x:c>
       <x:c r="D264" s="23" t="n">
-        <x:v>4520.6</x:v>
+        <x:v>4584</x:v>
       </x:c>
       <x:c r="E264" s="23" t="n">
-        <x:v>4412.2</x:v>
+        <x:v>4451.6</x:v>
       </x:c>
       <x:c r="F264" s="23" t="n">
-        <x:v>4508</x:v>
+        <x:v>4503.4</x:v>
       </x:c>
       <x:c r="G264" s="23" t="n">
         <x:f>ROUND(F264-F263,1)</x:f>
-        <x:v>4.6</x:v>
+        <x:v>-34</x:v>
       </x:c>
       <x:c r="H264" s="24" t="n">
         <x:f>IFERROR(F264/F263-1,"")</x:f>
-        <x:v>0.0010214504596528506</x:v>
+        <x:v>-0.007493278088773314</x:v>
       </x:c>
       <x:c r="I264" s="26" t="n">
         <x:f>ROUND(D264-E264,1)</x:f>
-        <x:v>108.4</x:v>
+        <x:v>132.4</x:v>
       </x:c>
       <x:c r="J264" s="22" t="str">
         <x:v>IF2609</x:v>
@@ -17796,306 +17832,306 @@
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="22" t="n">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B265" s="22" t="str">
-        <x:v>9月21日-9月24日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C265" s="23" t="n">
-        <x:v>4451</x:v>
+        <x:v>4468</x:v>
       </x:c>
       <x:c r="D265" s="23" t="n">
-        <x:v>4520</x:v>
+        <x:v>4520.6</x:v>
       </x:c>
       <x:c r="E265" s="23" t="n">
-        <x:v>4367</x:v>
+        <x:v>4412.2</x:v>
       </x:c>
       <x:c r="F265" s="23" t="n">
-        <x:v>4375</x:v>
+        <x:v>4508</x:v>
       </x:c>
       <x:c r="G265" s="23" t="n">
         <x:f>ROUND(F265-F264,1)</x:f>
-        <x:v>-133</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="H265" s="24" t="n">
         <x:f>IFERROR(F265/F264-1,"")</x:f>
-        <x:v>-0.029503105590062084</x:v>
+        <x:v>0.0010214504596528506</x:v>
       </x:c>
       <x:c r="I265" s="26" t="n">
         <x:f>ROUND(D265-E265,1)</x:f>
-        <x:v>153</x:v>
+        <x:v>108.4</x:v>
       </x:c>
       <x:c r="J265" s="22" t="str">
-        <x:v>IF2612</x:v>
+        <x:v>IF2609</x:v>
       </x:c>
       <x:c r="K265" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="22" t="n">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B266" s="22" t="str">
-        <x:v>9月28日-9月30日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C266" s="23" t="n">
-        <x:v>4365</x:v>
+        <x:v>4451</x:v>
       </x:c>
       <x:c r="D266" s="23" t="n">
-        <x:v>4366.8</x:v>
+        <x:v>4520</x:v>
       </x:c>
       <x:c r="E266" s="23" t="n">
-        <x:v>4246</x:v>
+        <x:v>4367</x:v>
       </x:c>
       <x:c r="F266" s="23" t="n">
-        <x:v>4300.8</x:v>
+        <x:v>4375</x:v>
       </x:c>
       <x:c r="G266" s="23" t="n">
         <x:f>ROUND(F266-F265,1)</x:f>
-        <x:v>-74.2</x:v>
+        <x:v>-133</x:v>
       </x:c>
       <x:c r="H266" s="24" t="n">
         <x:f>IFERROR(F266/F265-1,"")</x:f>
-        <x:v>-0.016959999999999975</x:v>
+        <x:v>-0.029503105590062084</x:v>
       </x:c>
       <x:c r="I266" s="26" t="n">
         <x:f>ROUND(D266-E266,1)</x:f>
-        <x:v>120.8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="J266" s="22" t="str">
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K266" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="22" t="n">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B267" s="22" t="str">
-        <x:v>10月8日-10月9日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C267" s="23" t="n">
+        <x:v>4365</x:v>
+      </x:c>
+      <x:c r="D267" s="23" t="n">
+        <x:v>4366.8</x:v>
+      </x:c>
+      <x:c r="E267" s="23" t="n">
+        <x:v>4246</x:v>
+      </x:c>
+      <x:c r="F267" s="23" t="n">
         <x:v>4300.8</x:v>
-      </x:c>
-      <x:c r="D267" s="23" t="n">
-        <x:v>4331.6</x:v>
-      </x:c>
-      <x:c r="E267" s="23" t="n">
-        <x:v>4180.4</x:v>
-      </x:c>
-      <x:c r="F267" s="23" t="n">
-        <x:v>4244.8</x:v>
       </x:c>
       <x:c r="G267" s="23" t="n">
         <x:f>ROUND(F267-F266,1)</x:f>
-        <x:v>-56</x:v>
+        <x:v>-74.2</x:v>
       </x:c>
       <x:c r="H267" s="24" t="n">
         <x:f>IFERROR(F267/F266-1,"")</x:f>
-        <x:v>-0.01302083333333337</x:v>
+        <x:v>-0.016959999999999975</x:v>
       </x:c>
       <x:c r="I267" s="26" t="n">
         <x:f>ROUND(D267-E267,1)</x:f>
-        <x:v>151.2</x:v>
+        <x:v>120.8</x:v>
       </x:c>
       <x:c r="J267" s="22" t="str">
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K267" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="22" t="n">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B268" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C268" s="23" t="n">
-        <x:v>4240.4</x:v>
+        <x:v>4300.8</x:v>
       </x:c>
       <x:c r="D268" s="23" t="n">
-        <x:v>4273.6</x:v>
+        <x:v>4331.6</x:v>
       </x:c>
       <x:c r="E268" s="23" t="n">
-        <x:v>4213.8</x:v>
+        <x:v>4180.4</x:v>
       </x:c>
       <x:c r="F268" s="23" t="n">
-        <x:v>4233.6</x:v>
+        <x:v>4244.8</x:v>
       </x:c>
       <x:c r="G268" s="23" t="n">
         <x:f>ROUND(F268-F267,1)</x:f>
-        <x:v>-11.2</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="H268" s="24" t="n">
         <x:f>IFERROR(F268/F267-1,"")</x:f>
-        <x:v>-0.0026385224274405594</x:v>
-      </x:c>
-      <x:c r="I268" s="23" t="n">
+        <x:v>-0.01302083333333337</x:v>
+      </x:c>
+      <x:c r="I268" s="26" t="n">
         <x:f>ROUND(D268-E268,1)</x:f>
-        <x:v>59.8</x:v>
+        <x:v>151.2</x:v>
       </x:c>
       <x:c r="J268" s="22" t="str">
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K268" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B269" s="22" t="str">
+        <x:v>10月12日</x:v>
+      </x:c>
+      <x:c r="C269" s="23" t="n">
+        <x:v>4240.4</x:v>
+      </x:c>
+      <x:c r="D269" s="23" t="n">
+        <x:v>4273.6</x:v>
+      </x:c>
+      <x:c r="E269" s="23" t="n">
+        <x:v>4213.8</x:v>
+      </x:c>
+      <x:c r="F269" s="23" t="n">
+        <x:v>4233.6</x:v>
+      </x:c>
+      <x:c r="G269" s="23" t="n">
+        <x:f>ROUND(F269-F268,1)</x:f>
+        <x:v>-11.2</x:v>
+      </x:c>
+      <x:c r="H269" s="24" t="n">
+        <x:f>IFERROR(F269/F268-1,"")</x:f>
+        <x:v>-0.0026385224274405594</x:v>
+      </x:c>
+      <x:c r="I269" s="23" t="n">
+        <x:f>ROUND(D269-E269,1)</x:f>
+        <x:v>59.8</x:v>
+      </x:c>
+      <x:c r="J269" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
+      <x:c r="K269" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="269">
-      <x:c r="A269" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B269" s="30" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C269" s="30"/>
-      <x:c r="D269" s="30"/>
-      <x:c r="E269" s="30"/>
-      <x:c r="F269" s="30"/>
-      <x:c r="G269" s="30"/>
-      <x:c r="H269" s="30"/>
-      <x:c r="I269" s="32" t="n">
-        <x:f>ROUND(SUM(I229:I268),1)</x:f>
-        <x:v>6198.4</x:v>
-      </x:c>
-      <x:c r="J269" s="30"/>
-      <x:c r="K269" s="30"/>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B270" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B270" s="30" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="C270" s="30"/>
       <x:c r="D270" s="30"/>
       <x:c r="E270" s="30"/>
       <x:c r="F270" s="30"/>
       <x:c r="G270" s="30"/>
       <x:c r="H270" s="30"/>
-      <x:c r="I270" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I229:I268),0),1)</x:f>
-        <x:v>155</x:v>
+      <x:c r="I270" s="32" t="n">
+        <x:f>ROUND(SUM(I230:I269),1)</x:f>
+        <x:v>6198.4</x:v>
       </x:c>
       <x:c r="J270" s="30"/>
       <x:c r="K270" s="30"/>
     </x:row>
-    <x:row r="272">
-      <x:c r="A272" s="17" t="str">
+    <x:row r="271">
+      <x:c r="A271" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B271" s="30"/>
+      <x:c r="C271" s="30"/>
+      <x:c r="D271" s="30"/>
+      <x:c r="E271" s="30"/>
+      <x:c r="F271" s="30"/>
+      <x:c r="G271" s="30"/>
+      <x:c r="H271" s="30"/>
+      <x:c r="I271" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I230:I269),0),1)</x:f>
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J271" s="30"/>
+      <x:c r="K271" s="30"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" s="17" t="str">
         <x:v>IH主力</x:v>
       </x:c>
-      <x:c r="B272" s="17"/>
-      <x:c r="C272" s="17"/>
-      <x:c r="D272" s="17"/>
-      <x:c r="E272" s="17"/>
-      <x:c r="F272" s="17"/>
-      <x:c r="G272" s="17"/>
-      <x:c r="H272" s="17"/>
-      <x:c r="I272" s="17"/>
-      <x:c r="J272" s="17"/>
-      <x:c r="K272" s="17"/>
-    </x:row>
-    <x:row r="273">
-      <x:c r="A273" s="20" t="str">
+      <x:c r="B273" s="17"/>
+      <x:c r="C273" s="17"/>
+      <x:c r="D273" s="17"/>
+      <x:c r="E273" s="17"/>
+      <x:c r="F273" s="17"/>
+      <x:c r="G273" s="17"/>
+      <x:c r="H273" s="17"/>
+      <x:c r="I273" s="17"/>
+      <x:c r="J273" s="17"/>
+      <x:c r="K273" s="17"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B273" s="20" t="str">
+      <x:c r="B274" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C273" s="20" t="str">
+      <x:c r="C274" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D273" s="20" t="str">
+      <x:c r="D274" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E273" s="20" t="str">
+      <x:c r="E274" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F273" s="20" t="str">
+      <x:c r="F274" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G273" s="20" t="str">
+      <x:c r="G274" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H273" s="20" t="str">
+      <x:c r="H274" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I273" s="20" t="str">
+      <x:c r="I274" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J273" s="20" t="str">
+      <x:c r="J274" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K273" s="20" t="str">
+      <x:c r="K274" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="274">
-      <x:c r="A274" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B274" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C274" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="D274" s="23" t="n">
-        <x:v>3165.6</x:v>
-      </x:c>
-      <x:c r="E274" s="23" t="n">
-        <x:v>3040.8</x:v>
-      </x:c>
-      <x:c r="F274" s="23" t="n">
-        <x:v>3134.8</x:v>
-      </x:c>
-      <x:c r="G274" s="23"/>
-      <x:c r="H274" s="24"/>
-      <x:c r="I274" s="26" t="n">
-        <x:f>ROUND(D274-E274,1)</x:f>
-        <x:v>124.8</x:v>
-      </x:c>
-      <x:c r="J274" s="22" t="str">
-        <x:v>IH2603</x:v>
-      </x:c>
-      <x:c r="K274" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B275" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C275" s="23" t="n">
-        <x:v>3148.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="D275" s="23" t="n">
-        <x:v>3181.2</x:v>
+        <x:v>3165.6</x:v>
       </x:c>
       <x:c r="E275" s="23" t="n">
-        <x:v>3074.4</x:v>
+        <x:v>3040.8</x:v>
       </x:c>
       <x:c r="F275" s="23" t="n">
-        <x:v>3084.4</x:v>
-      </x:c>
-      <x:c r="G275" s="23" t="n">
-        <x:f>ROUND(F275-F274,1)</x:f>
-        <x:v>-50.4</x:v>
-      </x:c>
-      <x:c r="H275" s="24" t="n">
-        <x:f>IFERROR(F275/F274-1,"")</x:f>
-        <x:v>-0.016077580706903127</x:v>
-      </x:c>
+        <x:v>3134.8</x:v>
+      </x:c>
+      <x:c r="G275" s="23"/>
+      <x:c r="H275" s="24"/>
       <x:c r="I275" s="26" t="n">
         <x:f>ROUND(D275-E275,1)</x:f>
-        <x:v>106.8</x:v>
+        <x:v>124.8</x:v>
       </x:c>
       <x:c r="J275" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -18106,34 +18142,34 @@
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B276" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C276" s="23" t="n">
-        <x:v>3081.2</x:v>
+        <x:v>3148.4</x:v>
       </x:c>
       <x:c r="D276" s="23" t="n">
-        <x:v>3102.6</x:v>
+        <x:v>3181.2</x:v>
       </x:c>
       <x:c r="E276" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074.4</x:v>
       </x:c>
       <x:c r="F276" s="23" t="n">
-        <x:v>3037.8</x:v>
+        <x:v>3084.4</x:v>
       </x:c>
       <x:c r="G276" s="23" t="n">
         <x:f>ROUND(F276-F275,1)</x:f>
-        <x:v>-46.6</x:v>
+        <x:v>-50.4</x:v>
       </x:c>
       <x:c r="H276" s="24" t="n">
         <x:f>IFERROR(F276/F275-1,"")</x:f>
-        <x:v>-0.015108286862923093</x:v>
+        <x:v>-0.016077580706903127</x:v>
       </x:c>
       <x:c r="I276" s="26" t="n">
         <x:f>ROUND(D276-E276,1)</x:f>
-        <x:v>66.4</x:v>
+        <x:v>106.8</x:v>
       </x:c>
       <x:c r="J276" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -18144,34 +18180,34 @@
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B277" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C277" s="23" t="n">
-        <x:v>3049.8</x:v>
+        <x:v>3081.2</x:v>
       </x:c>
       <x:c r="D277" s="23" t="n">
-        <x:v>3136.6</x:v>
+        <x:v>3102.6</x:v>
       </x:c>
       <x:c r="E277" s="23" t="n">
-        <x:v>3044</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="F277" s="23" t="n">
-        <x:v>3074</x:v>
+        <x:v>3037.8</x:v>
       </x:c>
       <x:c r="G277" s="23" t="n">
         <x:f>ROUND(F277-F276,1)</x:f>
-        <x:v>36.2</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H277" s="24" t="n">
         <x:f>IFERROR(F277/F276-1,"")</x:f>
-        <x:v>0.011916518533148901</x:v>
+        <x:v>-0.015108286862923093</x:v>
       </x:c>
       <x:c r="I277" s="26" t="n">
         <x:f>ROUND(D277-E277,1)</x:f>
-        <x:v>92.6</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="J277" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -18182,34 +18218,34 @@
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B278" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C278" s="23" t="n">
-        <x:v>3039.4</x:v>
+        <x:v>3049.8</x:v>
       </x:c>
       <x:c r="D278" s="23" t="n">
-        <x:v>3081</x:v>
+        <x:v>3136.6</x:v>
       </x:c>
       <x:c r="E278" s="23" t="n">
-        <x:v>2984</x:v>
+        <x:v>3044</x:v>
       </x:c>
       <x:c r="F278" s="23" t="n">
-        <x:v>3036.2</x:v>
+        <x:v>3074</x:v>
       </x:c>
       <x:c r="G278" s="23" t="n">
         <x:f>ROUND(F278-F277,1)</x:f>
-        <x:v>-37.8</x:v>
+        <x:v>36.2</x:v>
       </x:c>
       <x:c r="H278" s="24" t="n">
         <x:f>IFERROR(F278/F277-1,"")</x:f>
-        <x:v>-0.012296681847755453</x:v>
+        <x:v>0.011916518533148901</x:v>
       </x:c>
       <x:c r="I278" s="26" t="n">
         <x:f>ROUND(D278-E278,1)</x:f>
-        <x:v>97</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="J278" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -18220,34 +18256,34 @@
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B279" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C279" s="23" t="n">
-        <x:v>3060.6</x:v>
+        <x:v>3039.4</x:v>
       </x:c>
       <x:c r="D279" s="23" t="n">
-        <x:v>3098</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E279" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="F279" s="23" t="n">
-        <x:v>3020</x:v>
+        <x:v>3036.2</x:v>
       </x:c>
       <x:c r="G279" s="23" t="n">
         <x:f>ROUND(F279-F278,1)</x:f>
-        <x:v>-16.2</x:v>
+        <x:v>-37.8</x:v>
       </x:c>
       <x:c r="H279" s="24" t="n">
         <x:f>IFERROR(F279/F278-1,"")</x:f>
-        <x:v>-0.005335616889532879</x:v>
+        <x:v>-0.012296681847755453</x:v>
       </x:c>
       <x:c r="I279" s="26" t="n">
         <x:f>ROUND(D279-E279,1)</x:f>
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J279" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -18258,110 +18294,110 @@
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B280" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C280" s="23" t="n">
-        <x:v>3049.2</x:v>
+        <x:v>3060.6</x:v>
       </x:c>
       <x:c r="D280" s="23" t="n">
-        <x:v>3086.4</x:v>
+        <x:v>3098</x:v>
       </x:c>
       <x:c r="E280" s="23" t="n">
-        <x:v>3022</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="F280" s="23" t="n">
-        <x:v>3045.4</x:v>
+        <x:v>3020</x:v>
       </x:c>
       <x:c r="G280" s="23" t="n">
         <x:f>ROUND(F280-F279,1)</x:f>
-        <x:v>25.4</x:v>
+        <x:v>-16.2</x:v>
       </x:c>
       <x:c r="H280" s="24" t="n">
         <x:f>IFERROR(F280/F279-1,"")</x:f>
-        <x:v>0.008410596026490191</x:v>
+        <x:v>-0.005335616889532879</x:v>
       </x:c>
       <x:c r="I280" s="26" t="n">
         <x:f>ROUND(D280-E280,1)</x:f>
-        <x:v>64.4</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J280" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K280" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B281" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C281" s="23" t="n">
-        <x:v>3038</x:v>
+        <x:v>3049.2</x:v>
       </x:c>
       <x:c r="D281" s="23" t="n">
-        <x:v>3056</x:v>
+        <x:v>3086.4</x:v>
       </x:c>
       <x:c r="E281" s="23" t="n">
-        <x:v>2950</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="F281" s="23" t="n">
-        <x:v>2990</x:v>
+        <x:v>3045.4</x:v>
       </x:c>
       <x:c r="G281" s="23" t="n">
         <x:f>ROUND(F281-F280,1)</x:f>
-        <x:v>-55.4</x:v>
+        <x:v>25.4</x:v>
       </x:c>
       <x:c r="H281" s="24" t="n">
         <x:f>IFERROR(F281/F280-1,"")</x:f>
-        <x:v>-0.018191370591712164</x:v>
+        <x:v>0.008410596026490191</x:v>
       </x:c>
       <x:c r="I281" s="26" t="n">
         <x:f>ROUND(D281-E281,1)</x:f>
-        <x:v>106</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="J281" s="22" t="str">
         <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K281" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B282" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C282" s="23" t="n">
-        <x:v>2965.4</x:v>
+        <x:v>3038</x:v>
       </x:c>
       <x:c r="D282" s="23" t="n">
-        <x:v>2989</x:v>
+        <x:v>3056</x:v>
       </x:c>
       <x:c r="E282" s="23" t="n">
-        <x:v>2912.6</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="F282" s="23" t="n">
-        <x:v>2957</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="G282" s="23" t="n">
         <x:f>ROUND(F282-F281,1)</x:f>
-        <x:v>-33</x:v>
+        <x:v>-55.4</x:v>
       </x:c>
       <x:c r="H282" s="24" t="n">
         <x:f>IFERROR(F282/F281-1,"")</x:f>
-        <x:v>-0.011036789297658833</x:v>
+        <x:v>-0.018191370591712164</x:v>
       </x:c>
       <x:c r="I282" s="26" t="n">
         <x:f>ROUND(D282-E282,1)</x:f>
-        <x:v>76.4</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J282" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -18372,34 +18408,34 @@
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B283" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C283" s="23" t="n">
-        <x:v>2953</x:v>
+        <x:v>2965.4</x:v>
       </x:c>
       <x:c r="D283" s="23" t="n">
-        <x:v>2996.6</x:v>
+        <x:v>2989</x:v>
       </x:c>
       <x:c r="E283" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2912.6</x:v>
       </x:c>
       <x:c r="F283" s="23" t="n">
-        <x:v>2898.4</x:v>
+        <x:v>2957</x:v>
       </x:c>
       <x:c r="G283" s="23" t="n">
         <x:f>ROUND(F283-F282,1)</x:f>
-        <x:v>-58.6</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="H283" s="24" t="n">
         <x:f>IFERROR(F283/F282-1,"")</x:f>
-        <x:v>-0.019817382482245516</x:v>
+        <x:v>-0.011036789297658833</x:v>
       </x:c>
       <x:c r="I283" s="26" t="n">
         <x:f>ROUND(D283-E283,1)</x:f>
-        <x:v>100.6</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="J283" s="22" t="str">
         <x:v>IH2603</x:v>
@@ -18410,37 +18446,37 @@
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B284" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C284" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2953</x:v>
       </x:c>
       <x:c r="D284" s="23" t="n">
-        <x:v>2847.6</x:v>
+        <x:v>2996.6</x:v>
       </x:c>
       <x:c r="E284" s="23" t="n">
-        <x:v>2750.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="F284" s="23" t="n">
-        <x:v>2814.4</x:v>
+        <x:v>2898.4</x:v>
       </x:c>
       <x:c r="G284" s="23" t="n">
         <x:f>ROUND(F284-F283,1)</x:f>
-        <x:v>-84</x:v>
+        <x:v>-58.6</x:v>
       </x:c>
       <x:c r="H284" s="24" t="n">
         <x:f>IFERROR(F284/F283-1,"")</x:f>
-        <x:v>-0.028981507038365995</x:v>
+        <x:v>-0.019817382482245516</x:v>
       </x:c>
       <x:c r="I284" s="26" t="n">
         <x:f>ROUND(D284-E284,1)</x:f>
-        <x:v>96.8</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="J284" s="22" t="str">
-        <x:v>IH2606</x:v>
+        <x:v>IH2603</x:v>
       </x:c>
       <x:c r="K284" s="22" t="n">
         <x:v>5</x:v>
@@ -18448,34 +18484,34 @@
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B285" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C285" s="23" t="n">
-        <x:v>2794.8</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D285" s="23" t="n">
-        <x:v>2865.4</x:v>
+        <x:v>2847.6</x:v>
       </x:c>
       <x:c r="E285" s="23" t="n">
-        <x:v>2780.4</x:v>
+        <x:v>2750.8</x:v>
       </x:c>
       <x:c r="F285" s="23" t="n">
-        <x:v>2804.4</x:v>
+        <x:v>2814.4</x:v>
       </x:c>
       <x:c r="G285" s="23" t="n">
         <x:f>ROUND(F285-F284,1)</x:f>
-        <x:v>-10</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="H285" s="24" t="n">
         <x:f>IFERROR(F285/F284-1,"")</x:f>
-        <x:v>-0.0035531552018192025</x:v>
+        <x:v>-0.028981507038365995</x:v>
       </x:c>
       <x:c r="I285" s="26" t="n">
         <x:f>ROUND(D285-E285,1)</x:f>
-        <x:v>85</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="J285" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18486,110 +18522,110 @@
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B286" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C286" s="23" t="n">
-        <x:v>2810.4</x:v>
+        <x:v>2794.8</x:v>
       </x:c>
       <x:c r="D286" s="23" t="n">
-        <x:v>2896</x:v>
+        <x:v>2865.4</x:v>
       </x:c>
       <x:c r="E286" s="23" t="n">
-        <x:v>2797.2</x:v>
+        <x:v>2780.4</x:v>
       </x:c>
       <x:c r="F286" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2804.4</x:v>
       </x:c>
       <x:c r="G286" s="23" t="n">
         <x:f>ROUND(F286-F285,1)</x:f>
-        <x:v>68.8</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="H286" s="24" t="n">
         <x:f>IFERROR(F286/F285-1,"")</x:f>
-        <x:v>0.02453287690771644</x:v>
+        <x:v>-0.0035531552018192025</x:v>
       </x:c>
       <x:c r="I286" s="26" t="n">
         <x:f>ROUND(D286-E286,1)</x:f>
-        <x:v>98.8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J286" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K286" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B287" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C287" s="23" t="n">
-        <x:v>2864.6</x:v>
+        <x:v>2810.4</x:v>
       </x:c>
       <x:c r="D287" s="23" t="n">
-        <x:v>2930.8</x:v>
+        <x:v>2896</x:v>
       </x:c>
       <x:c r="E287" s="23" t="n">
-        <x:v>2860</x:v>
+        <x:v>2797.2</x:v>
       </x:c>
       <x:c r="F287" s="23" t="n">
-        <x:v>2888</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="G287" s="23" t="n">
         <x:f>ROUND(F287-F286,1)</x:f>
-        <x:v>14.8</x:v>
+        <x:v>68.8</x:v>
       </x:c>
       <x:c r="H287" s="24" t="n">
         <x:f>IFERROR(F287/F286-1,"")</x:f>
-        <x:v>0.005151051092858294</x:v>
+        <x:v>0.02453287690771644</x:v>
       </x:c>
       <x:c r="I287" s="26" t="n">
         <x:f>ROUND(D287-E287,1)</x:f>
-        <x:v>70.8</x:v>
+        <x:v>98.8</x:v>
       </x:c>
       <x:c r="J287" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K287" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B288" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C288" s="23" t="n">
-        <x:v>2900.8</x:v>
+        <x:v>2864.6</x:v>
       </x:c>
       <x:c r="D288" s="23" t="n">
-        <x:v>2934.2</x:v>
+        <x:v>2930.8</x:v>
       </x:c>
       <x:c r="E288" s="23" t="n">
-        <x:v>2891</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="F288" s="23" t="n">
-        <x:v>2929</x:v>
+        <x:v>2888</x:v>
       </x:c>
       <x:c r="G288" s="23" t="n">
         <x:f>ROUND(F288-F287,1)</x:f>
-        <x:v>41</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="H288" s="24" t="n">
         <x:f>IFERROR(F288/F287-1,"")</x:f>
-        <x:v>0.014196675900276956</x:v>
-      </x:c>
-      <x:c r="I288" s="23" t="n">
+        <x:v>0.005151051092858294</x:v>
+      </x:c>
+      <x:c r="I288" s="26" t="n">
         <x:f>ROUND(D288-E288,1)</x:f>
-        <x:v>43.2</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="J288" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18600,148 +18636,148 @@
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B289" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C289" s="23" t="n">
-        <x:v>2929.2</x:v>
+        <x:v>2900.8</x:v>
       </x:c>
       <x:c r="D289" s="23" t="n">
-        <x:v>2970</x:v>
+        <x:v>2934.2</x:v>
       </x:c>
       <x:c r="E289" s="23" t="n">
-        <x:v>2917</x:v>
+        <x:v>2891</x:v>
       </x:c>
       <x:c r="F289" s="23" t="n">
-        <x:v>2968.8</x:v>
+        <x:v>2929</x:v>
       </x:c>
       <x:c r="G289" s="23" t="n">
         <x:f>ROUND(F289-F288,1)</x:f>
-        <x:v>39.8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H289" s="24" t="n">
         <x:f>IFERROR(F289/F288-1,"")</x:f>
-        <x:v>0.013588255377261937</x:v>
+        <x:v>0.014196675900276956</x:v>
       </x:c>
       <x:c r="I289" s="23" t="n">
         <x:f>ROUND(D289-E289,1)</x:f>
-        <x:v>53</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J289" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K289" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B290" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C290" s="23" t="n">
-        <x:v>2995.2</x:v>
+        <x:v>2929.2</x:v>
       </x:c>
       <x:c r="D290" s="23" t="n">
-        <x:v>3024.8</x:v>
+        <x:v>2970</x:v>
       </x:c>
       <x:c r="E290" s="23" t="n">
-        <x:v>2969.2</x:v>
+        <x:v>2917</x:v>
       </x:c>
       <x:c r="F290" s="23" t="n">
-        <x:v>2981.6</x:v>
+        <x:v>2968.8</x:v>
       </x:c>
       <x:c r="G290" s="23" t="n">
         <x:f>ROUND(F290-F289,1)</x:f>
-        <x:v>12.8</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="H290" s="24" t="n">
         <x:f>IFERROR(F290/F289-1,"")</x:f>
-        <x:v>0.0043115063325247505</x:v>
+        <x:v>0.013588255377261937</x:v>
       </x:c>
       <x:c r="I290" s="23" t="n">
         <x:f>ROUND(D290-E290,1)</x:f>
-        <x:v>55.6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J290" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K290" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B291" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C291" s="23" t="n">
-        <x:v>2997.6</x:v>
+        <x:v>2995.2</x:v>
       </x:c>
       <x:c r="D291" s="23" t="n">
-        <x:v>3041.8</x:v>
+        <x:v>3024.8</x:v>
       </x:c>
       <x:c r="E291" s="23" t="n">
-        <x:v>2927</x:v>
+        <x:v>2969.2</x:v>
       </x:c>
       <x:c r="F291" s="23" t="n">
-        <x:v>2945</x:v>
+        <x:v>2981.6</x:v>
       </x:c>
       <x:c r="G291" s="23" t="n">
         <x:f>ROUND(F291-F290,1)</x:f>
-        <x:v>-36.6</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="H291" s="24" t="n">
         <x:f>IFERROR(F291/F290-1,"")</x:f>
-        <x:v>-0.012275288435739218</x:v>
-      </x:c>
-      <x:c r="I291" s="26" t="n">
+        <x:v>0.0043115063325247505</x:v>
+      </x:c>
+      <x:c r="I291" s="23" t="n">
         <x:f>ROUND(D291-E291,1)</x:f>
-        <x:v>114.8</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="J291" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K291" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B292" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C292" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2997.6</x:v>
       </x:c>
       <x:c r="D292" s="23" t="n">
-        <x:v>2981.8</x:v>
+        <x:v>3041.8</x:v>
       </x:c>
       <x:c r="E292" s="23" t="n">
-        <x:v>2893.2</x:v>
+        <x:v>2927</x:v>
       </x:c>
       <x:c r="F292" s="23" t="n">
-        <x:v>2899.2</x:v>
+        <x:v>2945</x:v>
       </x:c>
       <x:c r="G292" s="23" t="n">
         <x:f>ROUND(F292-F291,1)</x:f>
-        <x:v>-45.8</x:v>
+        <x:v>-36.6</x:v>
       </x:c>
       <x:c r="H292" s="24" t="n">
         <x:f>IFERROR(F292/F291-1,"")</x:f>
-        <x:v>-0.015551782682512783</x:v>
+        <x:v>-0.012275288435739218</x:v>
       </x:c>
       <x:c r="I292" s="26" t="n">
         <x:f>ROUND(D292-E292,1)</x:f>
-        <x:v>88.6</x:v>
+        <x:v>114.8</x:v>
       </x:c>
       <x:c r="J292" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18752,34 +18788,34 @@
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B293" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C293" s="23" t="n">
-        <x:v>2910.8</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D293" s="23" t="n">
-        <x:v>2960</x:v>
+        <x:v>2981.8</x:v>
       </x:c>
       <x:c r="E293" s="23" t="n">
-        <x:v>2871</x:v>
+        <x:v>2893.2</x:v>
       </x:c>
       <x:c r="F293" s="23" t="n">
-        <x:v>2900.6</x:v>
+        <x:v>2899.2</x:v>
       </x:c>
       <x:c r="G293" s="23" t="n">
         <x:f>ROUND(F293-F292,1)</x:f>
-        <x:v>1.4</x:v>
+        <x:v>-45.8</x:v>
       </x:c>
       <x:c r="H293" s="24" t="n">
         <x:f>IFERROR(F293/F292-1,"")</x:f>
-        <x:v>0.0004828918322297149</x:v>
+        <x:v>-0.015551782682512783</x:v>
       </x:c>
       <x:c r="I293" s="26" t="n">
         <x:f>ROUND(D293-E293,1)</x:f>
-        <x:v>89</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="J293" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18790,34 +18826,34 @@
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B294" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C294" s="23" t="n">
-        <x:v>2901</x:v>
+        <x:v>2910.8</x:v>
       </x:c>
       <x:c r="D294" s="23" t="n">
-        <x:v>2924.2</x:v>
+        <x:v>2960</x:v>
       </x:c>
       <x:c r="E294" s="23" t="n">
-        <x:v>2841.6</x:v>
+        <x:v>2871</x:v>
       </x:c>
       <x:c r="F294" s="23" t="n">
-        <x:v>2844</x:v>
+        <x:v>2900.6</x:v>
       </x:c>
       <x:c r="G294" s="23" t="n">
         <x:f>ROUND(F294-F293,1)</x:f>
-        <x:v>-56.6</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H294" s="24" t="n">
         <x:f>IFERROR(F294/F293-1,"")</x:f>
-        <x:v>-0.019513204164655518</x:v>
+        <x:v>0.0004828918322297149</x:v>
       </x:c>
       <x:c r="I294" s="26" t="n">
         <x:f>ROUND(D294-E294,1)</x:f>
-        <x:v>82.6</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J294" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18828,34 +18864,34 @@
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B295" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C295" s="23" t="n">
-        <x:v>2808.4</x:v>
+        <x:v>2901</x:v>
       </x:c>
       <x:c r="D295" s="23" t="n">
-        <x:v>2902.6</x:v>
+        <x:v>2924.2</x:v>
       </x:c>
       <x:c r="E295" s="23" t="n">
-        <x:v>2791.2</x:v>
+        <x:v>2841.6</x:v>
       </x:c>
       <x:c r="F295" s="23" t="n">
-        <x:v>2897.2</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G295" s="23" t="n">
         <x:f>ROUND(F295-F294,1)</x:f>
-        <x:v>53.2</x:v>
+        <x:v>-56.6</x:v>
       </x:c>
       <x:c r="H295" s="24" t="n">
         <x:f>IFERROR(F295/F294-1,"")</x:f>
-        <x:v>0.01870604781997187</x:v>
+        <x:v>-0.019513204164655518</x:v>
       </x:c>
       <x:c r="I295" s="26" t="n">
         <x:f>ROUND(D295-E295,1)</x:f>
-        <x:v>111.4</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="J295" s="22" t="str">
         <x:v>IH2606</x:v>
@@ -18866,113 +18902,113 @@
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B296" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C296" s="23" t="n">
-        <x:v>2926.2</x:v>
+        <x:v>2808.4</x:v>
       </x:c>
       <x:c r="D296" s="23" t="n">
-        <x:v>2954.6</x:v>
+        <x:v>2902.6</x:v>
       </x:c>
       <x:c r="E296" s="23" t="n">
-        <x:v>2903.4</x:v>
+        <x:v>2791.2</x:v>
       </x:c>
       <x:c r="F296" s="23" t="n">
-        <x:v>2941</x:v>
+        <x:v>2897.2</x:v>
       </x:c>
       <x:c r="G296" s="23" t="n">
         <x:f>ROUND(F296-F295,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>53.2</x:v>
       </x:c>
       <x:c r="H296" s="24" t="n">
         <x:f>IFERROR(F296/F295-1,"")</x:f>
-        <x:v>0.01511804500897429</x:v>
-      </x:c>
-      <x:c r="I296" s="23" t="n">
+        <x:v>0.01870604781997187</x:v>
+      </x:c>
+      <x:c r="I296" s="26" t="n">
         <x:f>ROUND(D296-E296,1)</x:f>
-        <x:v>51.2</x:v>
+        <x:v>111.4</x:v>
       </x:c>
       <x:c r="J296" s="22" t="str">
         <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K296" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B297" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C297" s="23" t="n">
-        <x:v>2936</x:v>
+        <x:v>2926.2</x:v>
       </x:c>
       <x:c r="D297" s="23" t="n">
-        <x:v>2996</x:v>
+        <x:v>2954.6</x:v>
       </x:c>
       <x:c r="E297" s="23" t="n">
-        <x:v>2834.8</x:v>
+        <x:v>2903.4</x:v>
       </x:c>
       <x:c r="F297" s="23" t="n">
-        <x:v>2859</x:v>
+        <x:v>2941</x:v>
       </x:c>
       <x:c r="G297" s="23" t="n">
         <x:f>ROUND(F297-F296,1)</x:f>
-        <x:v>-82</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="H297" s="24" t="n">
         <x:f>IFERROR(F297/F296-1,"")</x:f>
-        <x:v>-0.02788167290037402</x:v>
-      </x:c>
-      <x:c r="I297" s="26" t="n">
+        <x:v>0.01511804500897429</x:v>
+      </x:c>
+      <x:c r="I297" s="23" t="n">
         <x:f>ROUND(D297-E297,1)</x:f>
-        <x:v>161.2</x:v>
+        <x:v>51.2</x:v>
       </x:c>
       <x:c r="J297" s="22" t="str">
-        <x:v>IH2606/IH2609</x:v>
+        <x:v>IH2606</x:v>
       </x:c>
       <x:c r="K297" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B298" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C298" s="23" t="n">
-        <x:v>2870</x:v>
+        <x:v>2936</x:v>
       </x:c>
       <x:c r="D298" s="23" t="n">
-        <x:v>2976</x:v>
+        <x:v>2996</x:v>
       </x:c>
       <x:c r="E298" s="23" t="n">
-        <x:v>2861.8</x:v>
+        <x:v>2834.8</x:v>
       </x:c>
       <x:c r="F298" s="23" t="n">
-        <x:v>2886.6</x:v>
+        <x:v>2859</x:v>
       </x:c>
       <x:c r="G298" s="23" t="n">
         <x:f>ROUND(F298-F297,1)</x:f>
-        <x:v>27.6</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="H298" s="24" t="n">
         <x:f>IFERROR(F298/F297-1,"")</x:f>
-        <x:v>0.009653725078698772</x:v>
+        <x:v>-0.02788167290037402</x:v>
       </x:c>
       <x:c r="I298" s="26" t="n">
         <x:f>ROUND(D298-E298,1)</x:f>
-        <x:v>114.2</x:v>
+        <x:v>161.2</x:v>
       </x:c>
       <x:c r="J298" s="22" t="str">
-        <x:v>IH2609</x:v>
+        <x:v>IH2606/IH2609</x:v>
       </x:c>
       <x:c r="K298" s="22" t="n">
         <x:v>5</x:v>
@@ -18980,34 +19016,34 @@
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B299" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C299" s="23" t="n">
-        <x:v>2899</x:v>
+        <x:v>2870</x:v>
       </x:c>
       <x:c r="D299" s="23" t="n">
-        <x:v>2983.8</x:v>
+        <x:v>2976</x:v>
       </x:c>
       <x:c r="E299" s="23" t="n">
-        <x:v>2862.4</x:v>
+        <x:v>2861.8</x:v>
       </x:c>
       <x:c r="F299" s="23" t="n">
-        <x:v>2910.2</x:v>
+        <x:v>2886.6</x:v>
       </x:c>
       <x:c r="G299" s="23" t="n">
         <x:f>ROUND(F299-F298,1)</x:f>
-        <x:v>23.6</x:v>
+        <x:v>27.6</x:v>
       </x:c>
       <x:c r="H299" s="24" t="n">
         <x:f>IFERROR(F299/F298-1,"")</x:f>
-        <x:v>0.008175708445922414</x:v>
+        <x:v>0.009653725078698772</x:v>
       </x:c>
       <x:c r="I299" s="26" t="n">
         <x:f>ROUND(D299-E299,1)</x:f>
-        <x:v>121.4</x:v>
+        <x:v>114.2</x:v>
       </x:c>
       <x:c r="J299" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19018,34 +19054,34 @@
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B300" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C300" s="23" t="n">
-        <x:v>2895.8</x:v>
+        <x:v>2899</x:v>
       </x:c>
       <x:c r="D300" s="23" t="n">
-        <x:v>2924</x:v>
+        <x:v>2983.8</x:v>
       </x:c>
       <x:c r="E300" s="23" t="n">
-        <x:v>2782.6</x:v>
+        <x:v>2862.4</x:v>
       </x:c>
       <x:c r="F300" s="23" t="n">
-        <x:v>2796.4</x:v>
+        <x:v>2910.2</x:v>
       </x:c>
       <x:c r="G300" s="23" t="n">
         <x:f>ROUND(F300-F299,1)</x:f>
-        <x:v>-113.8</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="H300" s="24" t="n">
         <x:f>IFERROR(F300/F299-1,"")</x:f>
-        <x:v>-0.039103841660366845</x:v>
+        <x:v>0.008175708445922414</x:v>
       </x:c>
       <x:c r="I300" s="26" t="n">
         <x:f>ROUND(D300-E300,1)</x:f>
-        <x:v>141.4</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J300" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19056,34 +19092,34 @@
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B301" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C301" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2895.8</x:v>
       </x:c>
       <x:c r="D301" s="23" t="n">
-        <x:v>2978</x:v>
+        <x:v>2924</x:v>
       </x:c>
       <x:c r="E301" s="23" t="n">
-        <x:v>2820</x:v>
+        <x:v>2782.6</x:v>
       </x:c>
       <x:c r="F301" s="23" t="n">
-        <x:v>2910</x:v>
+        <x:v>2796.4</x:v>
       </x:c>
       <x:c r="G301" s="23" t="n">
         <x:f>ROUND(F301-F300,1)</x:f>
-        <x:v>113.6</x:v>
+        <x:v>-113.8</x:v>
       </x:c>
       <x:c r="H301" s="24" t="n">
         <x:f>IFERROR(F301/F300-1,"")</x:f>
-        <x:v>0.040623658990130096</x:v>
+        <x:v>-0.039103841660366845</x:v>
       </x:c>
       <x:c r="I301" s="26" t="n">
         <x:f>ROUND(D301-E301,1)</x:f>
-        <x:v>158</x:v>
+        <x:v>141.4</x:v>
       </x:c>
       <x:c r="J301" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19094,34 +19130,34 @@
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B302" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C302" s="23" t="n">
-        <x:v>2929.6</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="D302" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2978</x:v>
       </x:c>
       <x:c r="E302" s="23" t="n">
-        <x:v>2847.2</x:v>
+        <x:v>2820</x:v>
       </x:c>
       <x:c r="F302" s="23" t="n">
-        <x:v>2891.8</x:v>
+        <x:v>2910</x:v>
       </x:c>
       <x:c r="G302" s="23" t="n">
         <x:f>ROUND(F302-F301,1)</x:f>
-        <x:v>-18.2</x:v>
+        <x:v>113.6</x:v>
       </x:c>
       <x:c r="H302" s="24" t="n">
         <x:f>IFERROR(F302/F301-1,"")</x:f>
-        <x:v>-0.006254295532646004</x:v>
+        <x:v>0.040623658990130096</x:v>
       </x:c>
       <x:c r="I302" s="26" t="n">
         <x:f>ROUND(D302-E302,1)</x:f>
-        <x:v>82.8</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J302" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19132,34 +19168,34 @@
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B303" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C303" s="23" t="n">
-        <x:v>2882.4</x:v>
+        <x:v>2929.6</x:v>
       </x:c>
       <x:c r="D303" s="23" t="n">
-        <x:v>2930.6</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="E303" s="23" t="n">
-        <x:v>2845.8</x:v>
+        <x:v>2847.2</x:v>
       </x:c>
       <x:c r="F303" s="23" t="n">
-        <x:v>2930</x:v>
+        <x:v>2891.8</x:v>
       </x:c>
       <x:c r="G303" s="23" t="n">
         <x:f>ROUND(F303-F302,1)</x:f>
-        <x:v>38.2</x:v>
+        <x:v>-18.2</x:v>
       </x:c>
       <x:c r="H303" s="24" t="n">
         <x:f>IFERROR(F303/F302-1,"")</x:f>
-        <x:v>0.013209765543951812</x:v>
+        <x:v>-0.006254295532646004</x:v>
       </x:c>
       <x:c r="I303" s="26" t="n">
         <x:f>ROUND(D303-E303,1)</x:f>
-        <x:v>84.8</x:v>
+        <x:v>82.8</x:v>
       </x:c>
       <x:c r="J303" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19170,34 +19206,34 @@
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B304" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C304" s="23" t="n">
+        <x:v>2882.4</x:v>
+      </x:c>
+      <x:c r="D304" s="23" t="n">
+        <x:v>2930.6</x:v>
+      </x:c>
+      <x:c r="E304" s="23" t="n">
+        <x:v>2845.8</x:v>
+      </x:c>
+      <x:c r="F304" s="23" t="n">
         <x:v>2930</x:v>
-      </x:c>
-      <x:c r="D304" s="23" t="n">
-        <x:v>2949.6</x:v>
-      </x:c>
-      <x:c r="E304" s="23" t="n">
-        <x:v>2877</x:v>
-      </x:c>
-      <x:c r="F304" s="23" t="n">
-        <x:v>2890</x:v>
       </x:c>
       <x:c r="G304" s="23" t="n">
         <x:f>ROUND(F304-F303,1)</x:f>
-        <x:v>-40</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="H304" s="24" t="n">
         <x:f>IFERROR(F304/F303-1,"")</x:f>
-        <x:v>-0.013651877133105783</x:v>
+        <x:v>0.013209765543951812</x:v>
       </x:c>
       <x:c r="I304" s="26" t="n">
         <x:f>ROUND(D304-E304,1)</x:f>
-        <x:v>72.6</x:v>
+        <x:v>84.8</x:v>
       </x:c>
       <x:c r="J304" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19208,34 +19244,34 @@
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B305" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C305" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2930</x:v>
       </x:c>
       <x:c r="D305" s="23" t="n">
-        <x:v>2921.2</x:v>
+        <x:v>2949.6</x:v>
       </x:c>
       <x:c r="E305" s="23" t="n">
-        <x:v>2843</x:v>
+        <x:v>2877</x:v>
       </x:c>
       <x:c r="F305" s="23" t="n">
-        <x:v>2861</x:v>
+        <x:v>2890</x:v>
       </x:c>
       <x:c r="G305" s="23" t="n">
         <x:f>ROUND(F305-F304,1)</x:f>
-        <x:v>-29</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="H305" s="24" t="n">
         <x:f>IFERROR(F305/F304-1,"")</x:f>
-        <x:v>-0.01003460207612461</x:v>
+        <x:v>-0.013651877133105783</x:v>
       </x:c>
       <x:c r="I305" s="26" t="n">
         <x:f>ROUND(D305-E305,1)</x:f>
-        <x:v>78.2</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="J305" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19246,34 +19282,34 @@
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B306" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C306" s="23" t="n">
-        <x:v>2856.4</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D306" s="23" t="n">
-        <x:v>2918.2</x:v>
+        <x:v>2921.2</x:v>
       </x:c>
       <x:c r="E306" s="23" t="n">
-        <x:v>2837.4</x:v>
+        <x:v>2843</x:v>
       </x:c>
       <x:c r="F306" s="23" t="n">
-        <x:v>2911.4</x:v>
+        <x:v>2861</x:v>
       </x:c>
       <x:c r="G306" s="23" t="n">
         <x:f>ROUND(F306-F305,1)</x:f>
-        <x:v>50.4</x:v>
+        <x:v>-29</x:v>
       </x:c>
       <x:c r="H306" s="24" t="n">
         <x:f>IFERROR(F306/F305-1,"")</x:f>
-        <x:v>0.01761621810555747</x:v>
+        <x:v>-0.01003460207612461</x:v>
       </x:c>
       <x:c r="I306" s="26" t="n">
         <x:f>ROUND(D306-E306,1)</x:f>
-        <x:v>80.8</x:v>
+        <x:v>78.2</x:v>
       </x:c>
       <x:c r="J306" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19284,34 +19320,34 @@
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B307" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C307" s="23" t="n">
-        <x:v>2886</x:v>
+        <x:v>2856.4</x:v>
       </x:c>
       <x:c r="D307" s="23" t="n">
-        <x:v>2949.4</x:v>
+        <x:v>2918.2</x:v>
       </x:c>
       <x:c r="E307" s="23" t="n">
-        <x:v>2877.6</x:v>
+        <x:v>2837.4</x:v>
       </x:c>
       <x:c r="F307" s="23" t="n">
-        <x:v>2915.8</x:v>
+        <x:v>2911.4</x:v>
       </x:c>
       <x:c r="G307" s="23" t="n">
         <x:f>ROUND(F307-F306,1)</x:f>
-        <x:v>4.4</x:v>
+        <x:v>50.4</x:v>
       </x:c>
       <x:c r="H307" s="24" t="n">
         <x:f>IFERROR(F307/F306-1,"")</x:f>
-        <x:v>0.0015113004053033396</x:v>
+        <x:v>0.01761621810555747</x:v>
       </x:c>
       <x:c r="I307" s="26" t="n">
         <x:f>ROUND(D307-E307,1)</x:f>
-        <x:v>71.8</x:v>
+        <x:v>80.8</x:v>
       </x:c>
       <x:c r="J307" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19322,34 +19358,34 @@
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B308" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C308" s="23" t="n">
-        <x:v>2923.2</x:v>
+        <x:v>2886</x:v>
       </x:c>
       <x:c r="D308" s="23" t="n">
-        <x:v>2931.4</x:v>
+        <x:v>2949.4</x:v>
       </x:c>
       <x:c r="E308" s="23" t="n">
-        <x:v>2836.8</x:v>
+        <x:v>2877.6</x:v>
       </x:c>
       <x:c r="F308" s="23" t="n">
-        <x:v>2867</x:v>
+        <x:v>2915.8</x:v>
       </x:c>
       <x:c r="G308" s="23" t="n">
         <x:f>ROUND(F308-F307,1)</x:f>
-        <x:v>-48.8</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="H308" s="24" t="n">
         <x:f>IFERROR(F308/F307-1,"")</x:f>
-        <x:v>-0.01673640167364021</x:v>
+        <x:v>0.0015113004053033396</x:v>
       </x:c>
       <x:c r="I308" s="26" t="n">
         <x:f>ROUND(D308-E308,1)</x:f>
-        <x:v>94.6</x:v>
+        <x:v>71.8</x:v>
       </x:c>
       <x:c r="J308" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19360,34 +19396,34 @@
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B309" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C309" s="23" t="n">
-        <x:v>2849.2</x:v>
+        <x:v>2923.2</x:v>
       </x:c>
       <x:c r="D309" s="23" t="n">
-        <x:v>2873.2</x:v>
+        <x:v>2931.4</x:v>
       </x:c>
       <x:c r="E309" s="23" t="n">
-        <x:v>2829.4</x:v>
+        <x:v>2836.8</x:v>
       </x:c>
       <x:c r="F309" s="23" t="n">
-        <x:v>2862.2</x:v>
+        <x:v>2867</x:v>
       </x:c>
       <x:c r="G309" s="23" t="n">
         <x:f>ROUND(F309-F308,1)</x:f>
-        <x:v>-4.8</x:v>
+        <x:v>-48.8</x:v>
       </x:c>
       <x:c r="H309" s="24" t="n">
         <x:f>IFERROR(F309/F308-1,"")</x:f>
-        <x:v>-0.0016742239274503135</x:v>
-      </x:c>
-      <x:c r="I309" s="23" t="n">
+        <x:v>-0.01673640167364021</x:v>
+      </x:c>
+      <x:c r="I309" s="26" t="n">
         <x:f>ROUND(D309-E309,1)</x:f>
-        <x:v>43.8</x:v>
+        <x:v>94.6</x:v>
       </x:c>
       <x:c r="J309" s="22" t="str">
         <x:v>IH2609</x:v>
@@ -19398,306 +19434,306 @@
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="22" t="n">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B310" s="22" t="str">
-        <x:v>9月21日-9月24日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C310" s="23" t="n">
-        <x:v>2830</x:v>
+        <x:v>2849.2</x:v>
       </x:c>
       <x:c r="D310" s="23" t="n">
-        <x:v>2881.2</x:v>
+        <x:v>2873.2</x:v>
       </x:c>
       <x:c r="E310" s="23" t="n">
-        <x:v>2798</x:v>
+        <x:v>2829.4</x:v>
       </x:c>
       <x:c r="F310" s="23" t="n">
-        <x:v>2804.6</x:v>
+        <x:v>2862.2</x:v>
       </x:c>
       <x:c r="G310" s="23" t="n">
         <x:f>ROUND(F310-F309,1)</x:f>
-        <x:v>-57.6</x:v>
+        <x:v>-4.8</x:v>
       </x:c>
       <x:c r="H310" s="24" t="n">
         <x:f>IFERROR(F310/F309-1,"")</x:f>
-        <x:v>-0.02012437984766957</x:v>
-      </x:c>
-      <x:c r="I310" s="26" t="n">
+        <x:v>-0.0016742239274503135</x:v>
+      </x:c>
+      <x:c r="I310" s="23" t="n">
         <x:f>ROUND(D310-E310,1)</x:f>
-        <x:v>83.2</x:v>
+        <x:v>43.8</x:v>
       </x:c>
       <x:c r="J310" s="22" t="str">
-        <x:v>IH2612</x:v>
+        <x:v>IH2609</x:v>
       </x:c>
       <x:c r="K310" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="22" t="n">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B311" s="22" t="str">
-        <x:v>9月28日-9月30日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C311" s="23" t="n">
-        <x:v>2802</x:v>
+        <x:v>2830</x:v>
       </x:c>
       <x:c r="D311" s="23" t="n">
-        <x:v>2803.8</x:v>
+        <x:v>2881.2</x:v>
       </x:c>
       <x:c r="E311" s="23" t="n">
-        <x:v>2746</x:v>
+        <x:v>2798</x:v>
       </x:c>
       <x:c r="F311" s="23" t="n">
-        <x:v>2778.8</x:v>
+        <x:v>2804.6</x:v>
       </x:c>
       <x:c r="G311" s="23" t="n">
         <x:f>ROUND(F311-F310,1)</x:f>
-        <x:v>-25.8</x:v>
+        <x:v>-57.6</x:v>
       </x:c>
       <x:c r="H311" s="24" t="n">
         <x:f>IFERROR(F311/F310-1,"")</x:f>
-        <x:v>-0.009199172787563215</x:v>
-      </x:c>
-      <x:c r="I311" s="23" t="n">
+        <x:v>-0.02012437984766957</x:v>
+      </x:c>
+      <x:c r="I311" s="26" t="n">
         <x:f>ROUND(D311-E311,1)</x:f>
-        <x:v>57.8</x:v>
+        <x:v>83.2</x:v>
       </x:c>
       <x:c r="J311" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K311" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="22" t="n">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B312" s="22" t="str">
-        <x:v>10月8日-10月9日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C312" s="23" t="n">
-        <x:v>2764</x:v>
+        <x:v>2802</x:v>
       </x:c>
       <x:c r="D312" s="23" t="n">
-        <x:v>2798.4</x:v>
+        <x:v>2803.8</x:v>
       </x:c>
       <x:c r="E312" s="23" t="n">
-        <x:v>2735</x:v>
+        <x:v>2746</x:v>
       </x:c>
       <x:c r="F312" s="23" t="n">
-        <x:v>2764</x:v>
+        <x:v>2778.8</x:v>
       </x:c>
       <x:c r="G312" s="23" t="n">
         <x:f>ROUND(F312-F311,1)</x:f>
-        <x:v>-14.8</x:v>
+        <x:v>-25.8</x:v>
       </x:c>
       <x:c r="H312" s="24" t="n">
         <x:f>IFERROR(F312/F311-1,"")</x:f>
-        <x:v>-0.005326040017273659</x:v>
-      </x:c>
-      <x:c r="I312" s="26" t="n">
+        <x:v>-0.009199172787563215</x:v>
+      </x:c>
+      <x:c r="I312" s="23" t="n">
         <x:f>ROUND(D312-E312,1)</x:f>
-        <x:v>63.4</x:v>
+        <x:v>57.8</x:v>
       </x:c>
       <x:c r="J312" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K312" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="22" t="n">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B313" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月8日-10月9日</x:v>
       </x:c>
       <x:c r="C313" s="23" t="n">
-        <x:v>2762</x:v>
+        <x:v>2764</x:v>
       </x:c>
       <x:c r="D313" s="23" t="n">
-        <x:v>2794</x:v>
+        <x:v>2798.4</x:v>
       </x:c>
       <x:c r="E313" s="23" t="n">
-        <x:v>2761.2</x:v>
+        <x:v>2735</x:v>
       </x:c>
       <x:c r="F313" s="23" t="n">
-        <x:v>2779</x:v>
+        <x:v>2764</x:v>
       </x:c>
       <x:c r="G313" s="23" t="n">
         <x:f>ROUND(F313-F312,1)</x:f>
-        <x:v>15</x:v>
+        <x:v>-14.8</x:v>
       </x:c>
       <x:c r="H313" s="24" t="n">
         <x:f>IFERROR(F313/F312-1,"")</x:f>
-        <x:v>0.00542691751085389</x:v>
-      </x:c>
-      <x:c r="I313" s="23" t="n">
+        <x:v>-0.005326040017273659</x:v>
+      </x:c>
+      <x:c r="I313" s="26" t="n">
         <x:f>ROUND(D313-E313,1)</x:f>
-        <x:v>32.8</x:v>
+        <x:v>63.4</x:v>
       </x:c>
       <x:c r="J313" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K313" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314">
+      <x:c r="A314" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B314" s="22" t="str">
+        <x:v>10月12日</x:v>
+      </x:c>
+      <x:c r="C314" s="23" t="n">
+        <x:v>2762</x:v>
+      </x:c>
+      <x:c r="D314" s="23" t="n">
+        <x:v>2794</x:v>
+      </x:c>
+      <x:c r="E314" s="23" t="n">
+        <x:v>2761.2</x:v>
+      </x:c>
+      <x:c r="F314" s="23" t="n">
+        <x:v>2779</x:v>
+      </x:c>
+      <x:c r="G314" s="23" t="n">
+        <x:f>ROUND(F314-F313,1)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H314" s="24" t="n">
+        <x:f>IFERROR(F314/F313-1,"")</x:f>
+        <x:v>0.00542691751085389</x:v>
+      </x:c>
+      <x:c r="I314" s="23" t="n">
+        <x:f>ROUND(D314-E314,1)</x:f>
+        <x:v>32.8</x:v>
+      </x:c>
+      <x:c r="J314" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
+      <x:c r="K314" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="314">
-      <x:c r="A314" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B314" s="30" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C314" s="30"/>
-      <x:c r="D314" s="30"/>
-      <x:c r="E314" s="30"/>
-      <x:c r="F314" s="30"/>
-      <x:c r="G314" s="30"/>
-      <x:c r="H314" s="30"/>
-      <x:c r="I314" s="32" t="n">
-        <x:f>ROUND(SUM(I274:I313),1)</x:f>
-        <x:v>3496.6</x:v>
-      </x:c>
-      <x:c r="J314" s="30"/>
-      <x:c r="K314" s="30"/>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B315" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B315" s="30" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="C315" s="30"/>
       <x:c r="D315" s="30"/>
       <x:c r="E315" s="30"/>
       <x:c r="F315" s="30"/>
       <x:c r="G315" s="30"/>
       <x:c r="H315" s="30"/>
-      <x:c r="I315" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I274:I313),0),1)</x:f>
-        <x:v>87.4</x:v>
+      <x:c r="I315" s="32" t="n">
+        <x:f>ROUND(SUM(I275:I314),1)</x:f>
+        <x:v>3496.6</x:v>
       </x:c>
       <x:c r="J315" s="30"/>
       <x:c r="K315" s="30"/>
     </x:row>
-    <x:row r="317">
-      <x:c r="A317" s="17" t="str">
+    <x:row r="316">
+      <x:c r="A316" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B316" s="30"/>
+      <x:c r="C316" s="30"/>
+      <x:c r="D316" s="30"/>
+      <x:c r="E316" s="30"/>
+      <x:c r="F316" s="30"/>
+      <x:c r="G316" s="30"/>
+      <x:c r="H316" s="30"/>
+      <x:c r="I316" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I275:I314),0),1)</x:f>
+        <x:v>87.4</x:v>
+      </x:c>
+      <x:c r="J316" s="30"/>
+      <x:c r="K316" s="30"/>
+    </x:row>
+    <x:row r="318">
+      <x:c r="A318" s="17" t="str">
         <x:v>碳酸锂2610</x:v>
       </x:c>
-      <x:c r="B317" s="17"/>
-      <x:c r="C317" s="17"/>
-      <x:c r="D317" s="17"/>
-      <x:c r="E317" s="17"/>
-      <x:c r="F317" s="17"/>
-      <x:c r="G317" s="17"/>
-      <x:c r="H317" s="17"/>
-      <x:c r="I317" s="17"/>
-      <x:c r="J317" s="17"/>
-      <x:c r="K317" s="17"/>
-    </x:row>
-    <x:row r="318">
-      <x:c r="A318" s="20" t="str">
+      <x:c r="B318" s="17"/>
+      <x:c r="C318" s="17"/>
+      <x:c r="D318" s="17"/>
+      <x:c r="E318" s="17"/>
+      <x:c r="F318" s="17"/>
+      <x:c r="G318" s="17"/>
+      <x:c r="H318" s="17"/>
+      <x:c r="I318" s="17"/>
+      <x:c r="J318" s="17"/>
+      <x:c r="K318" s="17"/>
+    </x:row>
+    <x:row r="319">
+      <x:c r="A319" s="20" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B318" s="20" t="str">
+      <x:c r="B319" s="20" t="str">
         <x:v>周期</x:v>
       </x:c>
-      <x:c r="C318" s="20" t="str">
+      <x:c r="C319" s="20" t="str">
         <x:v>开盘</x:v>
       </x:c>
-      <x:c r="D318" s="20" t="str">
+      <x:c r="D319" s="20" t="str">
         <x:v>高点</x:v>
       </x:c>
-      <x:c r="E318" s="20" t="str">
+      <x:c r="E319" s="20" t="str">
         <x:v>低点</x:v>
       </x:c>
-      <x:c r="F318" s="20" t="str">
+      <x:c r="F319" s="20" t="str">
         <x:v>收盘</x:v>
       </x:c>
-      <x:c r="G318" s="20" t="str">
+      <x:c r="G319" s="20" t="str">
         <x:v>涨跌点数</x:v>
       </x:c>
-      <x:c r="H318" s="20" t="str">
+      <x:c r="H319" s="20" t="str">
         <x:v>涨幅</x:v>
       </x:c>
-      <x:c r="I318" s="20" t="str">
+      <x:c r="I319" s="20" t="str">
         <x:v>振幅</x:v>
       </x:c>
-      <x:c r="J318" s="20" t="str">
+      <x:c r="J319" s="20" t="str">
         <x:v>标的</x:v>
       </x:c>
-      <x:c r="K318" s="20" t="str">
+      <x:c r="K319" s="20" t="str">
         <x:v>交易日</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="319">
-      <x:c r="A319" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B319" s="22" t="str">
-        <x:v>1月5日-1月9日</x:v>
-      </x:c>
-      <x:c r="C319" s="23" t="n">
-        <x:v>132800</x:v>
-      </x:c>
-      <x:c r="D319" s="23" t="n">
-        <x:v>150100</x:v>
-      </x:c>
-      <x:c r="E319" s="23" t="n">
-        <x:v>123500</x:v>
-      </x:c>
-      <x:c r="F319" s="23" t="n">
-        <x:v>145600</x:v>
-      </x:c>
-      <x:c r="G319" s="23"/>
-      <x:c r="H319" s="24"/>
-      <x:c r="I319" s="26" t="n">
-        <x:f>ROUND(D319-E319,1)</x:f>
-        <x:v>26600</x:v>
-      </x:c>
-      <x:c r="J319" s="22" t="str">
-        <x:v>LC2610</x:v>
-      </x:c>
-      <x:c r="K319" s="22" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B320" s="22" t="str">
-        <x:v>1月12日-1月16日</x:v>
+        <x:v>1月5日-1月9日</x:v>
       </x:c>
       <x:c r="C320" s="23" t="n">
-        <x:v>149180</x:v>
+        <x:v>132800</x:v>
       </x:c>
       <x:c r="D320" s="23" t="n">
-        <x:v>175360</x:v>
+        <x:v>150100</x:v>
       </x:c>
       <x:c r="E320" s="23" t="n">
-        <x:v>148180</x:v>
+        <x:v>123500</x:v>
       </x:c>
       <x:c r="F320" s="23" t="n">
-        <x:v>148180</x:v>
-      </x:c>
-      <x:c r="G320" s="28" t="n">
-        <x:f>ROUND(F320-F319,1)</x:f>
-        <x:v>2580</x:v>
-      </x:c>
-      <x:c r="H320" s="24" t="n">
-        <x:f>IFERROR(F320/F319-1,"")</x:f>
-        <x:v>0.017719780219780157</x:v>
-      </x:c>
+        <x:v>145600</x:v>
+      </x:c>
+      <x:c r="G320" s="23"/>
+      <x:c r="H320" s="24"/>
       <x:c r="I320" s="26" t="n">
         <x:f>ROUND(D320-E320,1)</x:f>
-        <x:v>27180</x:v>
+        <x:v>26600</x:v>
       </x:c>
       <x:c r="J320" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19708,34 +19744,34 @@
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B321" s="22" t="str">
-        <x:v>1月19日-1月23日</x:v>
+        <x:v>1月12日-1月16日</x:v>
       </x:c>
       <x:c r="C321" s="23" t="n">
-        <x:v>143000</x:v>
+        <x:v>149180</x:v>
       </x:c>
       <x:c r="D321" s="23" t="n">
-        <x:v>183460</x:v>
+        <x:v>175360</x:v>
       </x:c>
       <x:c r="E321" s="23" t="n">
-        <x:v>143000</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="F321" s="23" t="n">
-        <x:v>183460</x:v>
+        <x:v>148180</x:v>
       </x:c>
       <x:c r="G321" s="28" t="n">
         <x:f>ROUND(F321-F320,1)</x:f>
-        <x:v>35280</x:v>
+        <x:v>2580</x:v>
       </x:c>
       <x:c r="H321" s="24" t="n">
         <x:f>IFERROR(F321/F320-1,"")</x:f>
-        <x:v>0.23808881090565537</x:v>
+        <x:v>0.017719780219780157</x:v>
       </x:c>
       <x:c r="I321" s="26" t="n">
         <x:f>ROUND(D321-E321,1)</x:f>
-        <x:v>40460</x:v>
+        <x:v>27180</x:v>
       </x:c>
       <x:c r="J321" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19746,34 +19782,34 @@
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B322" s="22" t="str">
-        <x:v>1月26日-1月30日</x:v>
+        <x:v>1月19日-1月23日</x:v>
       </x:c>
       <x:c r="C322" s="23" t="n">
-        <x:v>189980</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="D322" s="23" t="n">
-        <x:v>190020</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="E322" s="23" t="n">
-        <x:v>148520</x:v>
+        <x:v>143000</x:v>
       </x:c>
       <x:c r="F322" s="23" t="n">
-        <x:v>148540</x:v>
+        <x:v>183460</x:v>
       </x:c>
       <x:c r="G322" s="28" t="n">
         <x:f>ROUND(F322-F321,1)</x:f>
-        <x:v>-34920</x:v>
+        <x:v>35280</x:v>
       </x:c>
       <x:c r="H322" s="24" t="n">
         <x:f>IFERROR(F322/F321-1,"")</x:f>
-        <x:v>-0.19034121879428756</x:v>
+        <x:v>0.23808881090565537</x:v>
       </x:c>
       <x:c r="I322" s="26" t="n">
         <x:f>ROUND(D322-E322,1)</x:f>
-        <x:v>41500</x:v>
+        <x:v>40460</x:v>
       </x:c>
       <x:c r="J322" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19784,34 +19820,34 @@
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B323" s="22" t="str">
-        <x:v>2月2日-2月6日</x:v>
+        <x:v>1月26日-1月30日</x:v>
       </x:c>
       <x:c r="C323" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>189980</x:v>
       </x:c>
       <x:c r="D323" s="23" t="n">
-        <x:v>153000</x:v>
+        <x:v>190020</x:v>
       </x:c>
       <x:c r="E323" s="23" t="n">
-        <x:v>124760</x:v>
+        <x:v>148520</x:v>
       </x:c>
       <x:c r="F323" s="23" t="n">
-        <x:v>131160</x:v>
+        <x:v>148540</x:v>
       </x:c>
       <x:c r="G323" s="28" t="n">
         <x:f>ROUND(F323-F322,1)</x:f>
-        <x:v>-17380</x:v>
+        <x:v>-34920</x:v>
       </x:c>
       <x:c r="H323" s="24" t="n">
         <x:f>IFERROR(F323/F322-1,"")</x:f>
-        <x:v>-0.11700552039854584</x:v>
+        <x:v>-0.19034121879428756</x:v>
       </x:c>
       <x:c r="I323" s="26" t="n">
         <x:f>ROUND(D323-E323,1)</x:f>
-        <x:v>28240</x:v>
+        <x:v>41500</x:v>
       </x:c>
       <x:c r="J323" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19822,34 +19858,34 @@
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B324" s="22" t="str">
-        <x:v>2月9日-2月13日</x:v>
+        <x:v>2月2日-2月6日</x:v>
       </x:c>
       <x:c r="C324" s="23" t="n">
-        <x:v>134660</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="D324" s="23" t="n">
-        <x:v>152380</x:v>
+        <x:v>153000</x:v>
       </x:c>
       <x:c r="E324" s="23" t="n">
-        <x:v>133580</x:v>
+        <x:v>124760</x:v>
       </x:c>
       <x:c r="F324" s="23" t="n">
-        <x:v>152380</x:v>
+        <x:v>131160</x:v>
       </x:c>
       <x:c r="G324" s="28" t="n">
         <x:f>ROUND(F324-F323,1)</x:f>
-        <x:v>21220</x:v>
+        <x:v>-17380</x:v>
       </x:c>
       <x:c r="H324" s="24" t="n">
         <x:f>IFERROR(F324/F323-1,"")</x:f>
-        <x:v>0.1617871302226288</x:v>
+        <x:v>-0.11700552039854584</x:v>
       </x:c>
       <x:c r="I324" s="26" t="n">
         <x:f>ROUND(D324-E324,1)</x:f>
-        <x:v>18800</x:v>
+        <x:v>28240</x:v>
       </x:c>
       <x:c r="J324" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19860,110 +19896,110 @@
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B325" s="22" t="str">
-        <x:v>2月24日-2月27日</x:v>
+        <x:v>2月9日-2月13日</x:v>
       </x:c>
       <x:c r="C325" s="23" t="n">
-        <x:v>165060</x:v>
+        <x:v>134660</x:v>
       </x:c>
       <x:c r="D325" s="23" t="n">
-        <x:v>187920</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="E325" s="23" t="n">
-        <x:v>155680</x:v>
+        <x:v>133580</x:v>
       </x:c>
       <x:c r="F325" s="23" t="n">
-        <x:v>175400</x:v>
+        <x:v>152380</x:v>
       </x:c>
       <x:c r="G325" s="28" t="n">
         <x:f>ROUND(F325-F324,1)</x:f>
-        <x:v>23020</x:v>
+        <x:v>21220</x:v>
       </x:c>
       <x:c r="H325" s="24" t="n">
         <x:f>IFERROR(F325/F324-1,"")</x:f>
-        <x:v>0.1510696941855887</x:v>
+        <x:v>0.1617871302226288</x:v>
       </x:c>
       <x:c r="I325" s="26" t="n">
         <x:f>ROUND(D325-E325,1)</x:f>
-        <x:v>32240</x:v>
+        <x:v>18800</x:v>
       </x:c>
       <x:c r="J325" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K325" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B326" s="22" t="str">
-        <x:v>3月2日-3月6日</x:v>
+        <x:v>2月24日-2月27日</x:v>
       </x:c>
       <x:c r="C326" s="23" t="n">
-        <x:v>175800</x:v>
+        <x:v>165060</x:v>
       </x:c>
       <x:c r="D326" s="23" t="n">
-        <x:v>177260</x:v>
+        <x:v>187920</x:v>
       </x:c>
       <x:c r="E326" s="23" t="n">
-        <x:v>144980</x:v>
+        <x:v>155680</x:v>
       </x:c>
       <x:c r="F326" s="23" t="n">
-        <x:v>156580</x:v>
+        <x:v>175400</x:v>
       </x:c>
       <x:c r="G326" s="28" t="n">
         <x:f>ROUND(F326-F325,1)</x:f>
-        <x:v>-18820</x:v>
+        <x:v>23020</x:v>
       </x:c>
       <x:c r="H326" s="24" t="n">
         <x:f>IFERROR(F326/F325-1,"")</x:f>
-        <x:v>-0.1072976054732041</x:v>
+        <x:v>0.1510696941855887</x:v>
       </x:c>
       <x:c r="I326" s="26" t="n">
         <x:f>ROUND(D326-E326,1)</x:f>
-        <x:v>32280</x:v>
+        <x:v>32240</x:v>
       </x:c>
       <x:c r="J326" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K326" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B327" s="22" t="str">
-        <x:v>3月9日-3月13日</x:v>
+        <x:v>3月2日-3月6日</x:v>
       </x:c>
       <x:c r="C327" s="23" t="n">
-        <x:v>145120</x:v>
+        <x:v>175800</x:v>
       </x:c>
       <x:c r="D327" s="23" t="n">
-        <x:v>166800</x:v>
+        <x:v>177260</x:v>
       </x:c>
       <x:c r="E327" s="23" t="n">
-        <x:v>139860</x:v>
+        <x:v>144980</x:v>
       </x:c>
       <x:c r="F327" s="23" t="n">
-        <x:v>151880</x:v>
+        <x:v>156580</x:v>
       </x:c>
       <x:c r="G327" s="28" t="n">
         <x:f>ROUND(F327-F326,1)</x:f>
-        <x:v>-4700</x:v>
+        <x:v>-18820</x:v>
       </x:c>
       <x:c r="H327" s="24" t="n">
         <x:f>IFERROR(F327/F326-1,"")</x:f>
-        <x:v>-0.030016604930387047</x:v>
+        <x:v>-0.1072976054732041</x:v>
       </x:c>
       <x:c r="I327" s="26" t="n">
         <x:f>ROUND(D327-E327,1)</x:f>
-        <x:v>26940</x:v>
+        <x:v>32280</x:v>
       </x:c>
       <x:c r="J327" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -19974,34 +20010,34 @@
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B328" s="22" t="str">
-        <x:v>3月16日-3月20日</x:v>
+        <x:v>3月9日-3月13日</x:v>
       </x:c>
       <x:c r="C328" s="23" t="n">
-        <x:v>149140</x:v>
+        <x:v>145120</x:v>
       </x:c>
       <x:c r="D328" s="23" t="n">
-        <x:v>159120</x:v>
+        <x:v>166800</x:v>
       </x:c>
       <x:c r="E328" s="23" t="n">
-        <x:v>139640</x:v>
+        <x:v>139860</x:v>
       </x:c>
       <x:c r="F328" s="23" t="n">
-        <x:v>143900</x:v>
+        <x:v>151880</x:v>
       </x:c>
       <x:c r="G328" s="28" t="n">
         <x:f>ROUND(F328-F327,1)</x:f>
-        <x:v>-7980</x:v>
+        <x:v>-4700</x:v>
       </x:c>
       <x:c r="H328" s="24" t="n">
         <x:f>IFERROR(F328/F327-1,"")</x:f>
-        <x:v>-0.052541480115881</x:v>
+        <x:v>-0.030016604930387047</x:v>
       </x:c>
       <x:c r="I328" s="26" t="n">
         <x:f>ROUND(D328-E328,1)</x:f>
-        <x:v>19480</x:v>
+        <x:v>26940</x:v>
       </x:c>
       <x:c r="J328" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20012,34 +20048,34 @@
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B329" s="22" t="str">
-        <x:v>3月23日-3月27日</x:v>
+        <x:v>3月16日-3月20日</x:v>
       </x:c>
       <x:c r="C329" s="23" t="n">
-        <x:v>144460</x:v>
+        <x:v>149140</x:v>
       </x:c>
       <x:c r="D329" s="23" t="n">
-        <x:v>170800</x:v>
+        <x:v>159120</x:v>
       </x:c>
       <x:c r="E329" s="23" t="n">
-        <x:v>139980</x:v>
+        <x:v>139640</x:v>
       </x:c>
       <x:c r="F329" s="23" t="n">
-        <x:v>166540</x:v>
+        <x:v>143900</x:v>
       </x:c>
       <x:c r="G329" s="28" t="n">
         <x:f>ROUND(F329-F328,1)</x:f>
-        <x:v>22640</x:v>
+        <x:v>-7980</x:v>
       </x:c>
       <x:c r="H329" s="24" t="n">
         <x:f>IFERROR(F329/F328-1,"")</x:f>
-        <x:v>0.15733148019457954</x:v>
+        <x:v>-0.052541480115881</x:v>
       </x:c>
       <x:c r="I329" s="26" t="n">
         <x:f>ROUND(D329-E329,1)</x:f>
-        <x:v>30820</x:v>
+        <x:v>19480</x:v>
       </x:c>
       <x:c r="J329" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20050,34 +20086,34 @@
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B330" s="22" t="str">
-        <x:v>3月30日-4月3日</x:v>
+        <x:v>3月23日-3月27日</x:v>
       </x:c>
       <x:c r="C330" s="23" t="n">
-        <x:v>172000</x:v>
+        <x:v>144460</x:v>
       </x:c>
       <x:c r="D330" s="23" t="n">
-        <x:v>174540</x:v>
+        <x:v>170800</x:v>
       </x:c>
       <x:c r="E330" s="23" t="n">
-        <x:v>153840</x:v>
+        <x:v>139980</x:v>
       </x:c>
       <x:c r="F330" s="23" t="n">
-        <x:v>157680</x:v>
+        <x:v>166540</x:v>
       </x:c>
       <x:c r="G330" s="28" t="n">
         <x:f>ROUND(F330-F329,1)</x:f>
-        <x:v>-8860</x:v>
+        <x:v>22640</x:v>
       </x:c>
       <x:c r="H330" s="24" t="n">
         <x:f>IFERROR(F330/F329-1,"")</x:f>
-        <x:v>-0.05320043232856975</x:v>
+        <x:v>0.15733148019457954</x:v>
       </x:c>
       <x:c r="I330" s="26" t="n">
         <x:f>ROUND(D330-E330,1)</x:f>
-        <x:v>20700</x:v>
+        <x:v>30820</x:v>
       </x:c>
       <x:c r="J330" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20088,110 +20124,110 @@
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="22" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B331" s="22" t="str">
-        <x:v>4月7日-4月10日</x:v>
+        <x:v>3月30日-4月3日</x:v>
       </x:c>
       <x:c r="C331" s="23" t="n">
-        <x:v>156200</x:v>
+        <x:v>172000</x:v>
       </x:c>
       <x:c r="D331" s="23" t="n">
-        <x:v>164160</x:v>
+        <x:v>174540</x:v>
       </x:c>
       <x:c r="E331" s="23" t="n">
-        <x:v>151640</x:v>
+        <x:v>153840</x:v>
       </x:c>
       <x:c r="F331" s="23" t="n">
-        <x:v>156500</x:v>
+        <x:v>157680</x:v>
       </x:c>
       <x:c r="G331" s="28" t="n">
         <x:f>ROUND(F331-F330,1)</x:f>
-        <x:v>-1180</x:v>
+        <x:v>-8860</x:v>
       </x:c>
       <x:c r="H331" s="24" t="n">
         <x:f>IFERROR(F331/F330-1,"")</x:f>
-        <x:v>-0.007483510908168456</x:v>
+        <x:v>-0.05320043232856975</x:v>
       </x:c>
       <x:c r="I331" s="26" t="n">
         <x:f>ROUND(D331-E331,1)</x:f>
-        <x:v>12520</x:v>
+        <x:v>20700</x:v>
       </x:c>
       <x:c r="J331" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K331" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="22" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B332" s="22" t="str">
-        <x:v>4月13日-4月17日</x:v>
+        <x:v>4月7日-4月10日</x:v>
       </x:c>
       <x:c r="C332" s="23" t="n">
-        <x:v>156660</x:v>
+        <x:v>156200</x:v>
       </x:c>
       <x:c r="D332" s="23" t="n">
-        <x:v>176500</x:v>
+        <x:v>164160</x:v>
       </x:c>
       <x:c r="E332" s="23" t="n">
-        <x:v>153040</x:v>
+        <x:v>151640</x:v>
       </x:c>
       <x:c r="F332" s="23" t="n">
-        <x:v>176360</x:v>
+        <x:v>156500</x:v>
       </x:c>
       <x:c r="G332" s="28" t="n">
         <x:f>ROUND(F332-F331,1)</x:f>
-        <x:v>19860</x:v>
+        <x:v>-1180</x:v>
       </x:c>
       <x:c r="H332" s="24" t="n">
         <x:f>IFERROR(F332/F331-1,"")</x:f>
-        <x:v>0.12690095846645377</x:v>
+        <x:v>-0.007483510908168456</x:v>
       </x:c>
       <x:c r="I332" s="26" t="n">
         <x:f>ROUND(D332-E332,1)</x:f>
-        <x:v>23460</x:v>
+        <x:v>12520</x:v>
       </x:c>
       <x:c r="J332" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K332" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B333" s="22" t="str">
-        <x:v>4月20日-4月24日</x:v>
+        <x:v>4月13日-4月17日</x:v>
       </x:c>
       <x:c r="C333" s="23" t="n">
-        <x:v>174080</x:v>
+        <x:v>156660</x:v>
       </x:c>
       <x:c r="D333" s="23" t="n">
-        <x:v>180920</x:v>
+        <x:v>176500</x:v>
       </x:c>
       <x:c r="E333" s="23" t="n">
-        <x:v>169000</x:v>
+        <x:v>153040</x:v>
       </x:c>
       <x:c r="F333" s="23" t="n">
-        <x:v>176960</x:v>
+        <x:v>176360</x:v>
       </x:c>
       <x:c r="G333" s="28" t="n">
         <x:f>ROUND(F333-F332,1)</x:f>
-        <x:v>600</x:v>
+        <x:v>19860</x:v>
       </x:c>
       <x:c r="H333" s="24" t="n">
         <x:f>IFERROR(F333/F332-1,"")</x:f>
-        <x:v>0.0034021320027217694</x:v>
+        <x:v>0.12690095846645377</x:v>
       </x:c>
       <x:c r="I333" s="26" t="n">
         <x:f>ROUND(D333-E333,1)</x:f>
-        <x:v>11920</x:v>
+        <x:v>23460</x:v>
       </x:c>
       <x:c r="J333" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20202,148 +20238,148 @@
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B334" s="22" t="str">
-        <x:v>4月27日-4月30日</x:v>
+        <x:v>4月20日-4月24日</x:v>
       </x:c>
       <x:c r="C334" s="23" t="n">
+        <x:v>174080</x:v>
+      </x:c>
+      <x:c r="D334" s="23" t="n">
+        <x:v>180920</x:v>
+      </x:c>
+      <x:c r="E334" s="23" t="n">
+        <x:v>169000</x:v>
+      </x:c>
+      <x:c r="F334" s="23" t="n">
         <x:v>176960</x:v>
-      </x:c>
-      <x:c r="D334" s="23" t="n">
-        <x:v>188840</x:v>
-      </x:c>
-      <x:c r="E334" s="23" t="n">
-        <x:v>172640</x:v>
-      </x:c>
-      <x:c r="F334" s="23" t="n">
-        <x:v>188840</x:v>
       </x:c>
       <x:c r="G334" s="28" t="n">
         <x:f>ROUND(F334-F333,1)</x:f>
-        <x:v>11880</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H334" s="24" t="n">
         <x:f>IFERROR(F334/F333-1,"")</x:f>
-        <x:v>0.06713381555153708</x:v>
+        <x:v>0.0034021320027217694</x:v>
       </x:c>
       <x:c r="I334" s="26" t="n">
         <x:f>ROUND(D334-E334,1)</x:f>
-        <x:v>16200</x:v>
+        <x:v>11920</x:v>
       </x:c>
       <x:c r="J334" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K334" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B335" s="22" t="str">
-        <x:v>5月6日-5月8日</x:v>
+        <x:v>4月27日-4月30日</x:v>
       </x:c>
       <x:c r="C335" s="23" t="n">
-        <x:v>191300</x:v>
+        <x:v>176960</x:v>
       </x:c>
       <x:c r="D335" s="23" t="n">
-        <x:v>204640</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="E335" s="23" t="n">
-        <x:v>191300</x:v>
+        <x:v>172640</x:v>
       </x:c>
       <x:c r="F335" s="23" t="n">
-        <x:v>196100</x:v>
+        <x:v>188840</x:v>
       </x:c>
       <x:c r="G335" s="28" t="n">
         <x:f>ROUND(F335-F334,1)</x:f>
-        <x:v>7260</x:v>
+        <x:v>11880</x:v>
       </x:c>
       <x:c r="H335" s="24" t="n">
         <x:f>IFERROR(F335/F334-1,"")</x:f>
-        <x:v>0.038445244651556854</x:v>
+        <x:v>0.06713381555153708</x:v>
       </x:c>
       <x:c r="I335" s="26" t="n">
         <x:f>ROUND(D335-E335,1)</x:f>
-        <x:v>13340</x:v>
+        <x:v>16200</x:v>
       </x:c>
       <x:c r="J335" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K335" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="22" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B336" s="22" t="str">
-        <x:v>5月11日-5月15日</x:v>
+        <x:v>5月6日-5月8日</x:v>
       </x:c>
       <x:c r="C336" s="23" t="n">
-        <x:v>195080</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="D336" s="23" t="n">
-        <x:v>209040</x:v>
+        <x:v>204640</x:v>
       </x:c>
       <x:c r="E336" s="23" t="n">
-        <x:v>187240</x:v>
+        <x:v>191300</x:v>
       </x:c>
       <x:c r="F336" s="23" t="n">
-        <x:v>189440</x:v>
+        <x:v>196100</x:v>
       </x:c>
       <x:c r="G336" s="28" t="n">
         <x:f>ROUND(F336-F335,1)</x:f>
-        <x:v>-6660</x:v>
+        <x:v>7260</x:v>
       </x:c>
       <x:c r="H336" s="24" t="n">
         <x:f>IFERROR(F336/F335-1,"")</x:f>
-        <x:v>-0.03396226415094339</x:v>
+        <x:v>0.038445244651556854</x:v>
       </x:c>
       <x:c r="I336" s="26" t="n">
         <x:f>ROUND(D336-E336,1)</x:f>
-        <x:v>21800</x:v>
+        <x:v>13340</x:v>
       </x:c>
       <x:c r="J336" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K336" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="22" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B337" s="22" t="str">
-        <x:v>5月18日-5月22日</x:v>
+        <x:v>5月11日-5月15日</x:v>
       </x:c>
       <x:c r="C337" s="23" t="n">
-        <x:v>190060</x:v>
+        <x:v>195080</x:v>
       </x:c>
       <x:c r="D337" s="23" t="n">
-        <x:v>193820</x:v>
+        <x:v>209040</x:v>
       </x:c>
       <x:c r="E337" s="23" t="n">
-        <x:v>175520</x:v>
+        <x:v>187240</x:v>
       </x:c>
       <x:c r="F337" s="23" t="n">
-        <x:v>185280</x:v>
+        <x:v>189440</x:v>
       </x:c>
       <x:c r="G337" s="28" t="n">
         <x:f>ROUND(F337-F336,1)</x:f>
-        <x:v>-4160</x:v>
+        <x:v>-6660</x:v>
       </x:c>
       <x:c r="H337" s="24" t="n">
         <x:f>IFERROR(F337/F336-1,"")</x:f>
-        <x:v>-0.02195945945945943</x:v>
+        <x:v>-0.03396226415094339</x:v>
       </x:c>
       <x:c r="I337" s="26" t="n">
         <x:f>ROUND(D337-E337,1)</x:f>
-        <x:v>18300</x:v>
+        <x:v>21800</x:v>
       </x:c>
       <x:c r="J337" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20354,34 +20390,34 @@
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="22" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B338" s="22" t="str">
-        <x:v>5月25日-5月29日</x:v>
+        <x:v>5月18日-5月22日</x:v>
       </x:c>
       <x:c r="C338" s="23" t="n">
-        <x:v>185380</x:v>
+        <x:v>190060</x:v>
       </x:c>
       <x:c r="D338" s="23" t="n">
-        <x:v>188320</x:v>
+        <x:v>193820</x:v>
       </x:c>
       <x:c r="E338" s="23" t="n">
-        <x:v>172500</x:v>
+        <x:v>175520</x:v>
       </x:c>
       <x:c r="F338" s="23" t="n">
-        <x:v>178620</x:v>
+        <x:v>185280</x:v>
       </x:c>
       <x:c r="G338" s="28" t="n">
         <x:f>ROUND(F338-F337,1)</x:f>
-        <x:v>-6660</x:v>
+        <x:v>-4160</x:v>
       </x:c>
       <x:c r="H338" s="24" t="n">
         <x:f>IFERROR(F338/F337-1,"")</x:f>
-        <x:v>-0.035945595854922296</x:v>
+        <x:v>-0.02195945945945943</x:v>
       </x:c>
       <x:c r="I338" s="26" t="n">
         <x:f>ROUND(D338-E338,1)</x:f>
-        <x:v>15820</x:v>
+        <x:v>18300</x:v>
       </x:c>
       <x:c r="J338" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20392,34 +20428,34 @@
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="22" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B339" s="22" t="str">
-        <x:v>6月1日-6月5日</x:v>
+        <x:v>5月25日-5月29日</x:v>
       </x:c>
       <x:c r="C339" s="23" t="n">
-        <x:v>180920</x:v>
+        <x:v>185380</x:v>
       </x:c>
       <x:c r="D339" s="23" t="n">
-        <x:v>182940</x:v>
+        <x:v>188320</x:v>
       </x:c>
       <x:c r="E339" s="23" t="n">
-        <x:v>158140</x:v>
+        <x:v>172500</x:v>
       </x:c>
       <x:c r="F339" s="23" t="n">
-        <x:v>165460</x:v>
+        <x:v>178620</x:v>
       </x:c>
       <x:c r="G339" s="28" t="n">
         <x:f>ROUND(F339-F338,1)</x:f>
-        <x:v>-13160</x:v>
+        <x:v>-6660</x:v>
       </x:c>
       <x:c r="H339" s="24" t="n">
         <x:f>IFERROR(F339/F338-1,"")</x:f>
-        <x:v>-0.07367596013884226</x:v>
+        <x:v>-0.035945595854922296</x:v>
       </x:c>
       <x:c r="I339" s="26" t="n">
         <x:f>ROUND(D339-E339,1)</x:f>
-        <x:v>24800</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="J339" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20430,34 +20466,34 @@
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="22" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B340" s="22" t="str">
-        <x:v>6月8日-6月12日</x:v>
+        <x:v>6月1日-6月5日</x:v>
       </x:c>
       <x:c r="C340" s="23" t="n">
-        <x:v>162800</x:v>
+        <x:v>180920</x:v>
       </x:c>
       <x:c r="D340" s="23" t="n">
-        <x:v>178860</x:v>
+        <x:v>182940</x:v>
       </x:c>
       <x:c r="E340" s="23" t="n">
-        <x:v>161280</x:v>
+        <x:v>158140</x:v>
       </x:c>
       <x:c r="F340" s="23" t="n">
-        <x:v>175780</x:v>
+        <x:v>165460</x:v>
       </x:c>
       <x:c r="G340" s="28" t="n">
         <x:f>ROUND(F340-F339,1)</x:f>
-        <x:v>10320</x:v>
+        <x:v>-13160</x:v>
       </x:c>
       <x:c r="H340" s="24" t="n">
         <x:f>IFERROR(F340/F339-1,"")</x:f>
-        <x:v>0.06237157016801653</x:v>
+        <x:v>-0.07367596013884226</x:v>
       </x:c>
       <x:c r="I340" s="26" t="n">
         <x:f>ROUND(D340-E340,1)</x:f>
-        <x:v>17580</x:v>
+        <x:v>24800</x:v>
       </x:c>
       <x:c r="J340" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20468,110 +20504,110 @@
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="22" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B341" s="22" t="str">
-        <x:v>6月15日-6月18日</x:v>
+        <x:v>6月8日-6月12日</x:v>
       </x:c>
       <x:c r="C341" s="23" t="n">
-        <x:v>176460</x:v>
+        <x:v>162800</x:v>
       </x:c>
       <x:c r="D341" s="23" t="n">
-        <x:v>178560</x:v>
+        <x:v>178860</x:v>
       </x:c>
       <x:c r="E341" s="23" t="n">
-        <x:v>160560</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="F341" s="23" t="n">
-        <x:v>161400</x:v>
+        <x:v>175780</x:v>
       </x:c>
       <x:c r="G341" s="28" t="n">
         <x:f>ROUND(F341-F340,1)</x:f>
-        <x:v>-14380</x:v>
+        <x:v>10320</x:v>
       </x:c>
       <x:c r="H341" s="24" t="n">
         <x:f>IFERROR(F341/F340-1,"")</x:f>
-        <x:v>-0.0818068039594948</x:v>
+        <x:v>0.06237157016801653</x:v>
       </x:c>
       <x:c r="I341" s="26" t="n">
         <x:f>ROUND(D341-E341,1)</x:f>
-        <x:v>18000</x:v>
+        <x:v>17580</x:v>
       </x:c>
       <x:c r="J341" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K341" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="22" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B342" s="22" t="str">
-        <x:v>6月22日-6月26日</x:v>
+        <x:v>6月15日-6月18日</x:v>
       </x:c>
       <x:c r="C342" s="23" t="n">
-        <x:v>161000</x:v>
+        <x:v>176460</x:v>
       </x:c>
       <x:c r="D342" s="23" t="n">
-        <x:v>163880</x:v>
+        <x:v>178560</x:v>
       </x:c>
       <x:c r="E342" s="23" t="n">
-        <x:v>145360</x:v>
+        <x:v>160560</x:v>
       </x:c>
       <x:c r="F342" s="23" t="n">
-        <x:v>151140</x:v>
+        <x:v>161400</x:v>
       </x:c>
       <x:c r="G342" s="28" t="n">
         <x:f>ROUND(F342-F341,1)</x:f>
-        <x:v>-10260</x:v>
+        <x:v>-14380</x:v>
       </x:c>
       <x:c r="H342" s="24" t="n">
         <x:f>IFERROR(F342/F341-1,"")</x:f>
-        <x:v>-0.06356877323420074</x:v>
+        <x:v>-0.0818068039594948</x:v>
       </x:c>
       <x:c r="I342" s="26" t="n">
         <x:f>ROUND(D342-E342,1)</x:f>
-        <x:v>18520</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="J342" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K342" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="22" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B343" s="22" t="str">
-        <x:v>6月29日-7月3日</x:v>
+        <x:v>6月22日-6月26日</x:v>
       </x:c>
       <x:c r="C343" s="23" t="n">
-        <x:v>148420</x:v>
+        <x:v>161000</x:v>
       </x:c>
       <x:c r="D343" s="23" t="n">
-        <x:v>172120</x:v>
+        <x:v>163880</x:v>
       </x:c>
       <x:c r="E343" s="23" t="n">
-        <x:v>146000</x:v>
+        <x:v>145360</x:v>
       </x:c>
       <x:c r="F343" s="23" t="n">
-        <x:v>168600</x:v>
+        <x:v>151140</x:v>
       </x:c>
       <x:c r="G343" s="28" t="n">
         <x:f>ROUND(F343-F342,1)</x:f>
-        <x:v>17460</x:v>
+        <x:v>-10260</x:v>
       </x:c>
       <x:c r="H343" s="24" t="n">
         <x:f>IFERROR(F343/F342-1,"")</x:f>
-        <x:v>0.1155220325526003</x:v>
+        <x:v>-0.06356877323420074</x:v>
       </x:c>
       <x:c r="I343" s="26" t="n">
         <x:f>ROUND(D343-E343,1)</x:f>
-        <x:v>26120</x:v>
+        <x:v>18520</x:v>
       </x:c>
       <x:c r="J343" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20582,34 +20618,34 @@
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="22" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B344" s="22" t="str">
-        <x:v>7月6日-7月10日</x:v>
+        <x:v>6月29日-7月3日</x:v>
       </x:c>
       <x:c r="C344" s="23" t="n">
-        <x:v>174900</x:v>
+        <x:v>148420</x:v>
       </x:c>
       <x:c r="D344" s="23" t="n">
-        <x:v>174900</x:v>
+        <x:v>172120</x:v>
       </x:c>
       <x:c r="E344" s="23" t="n">
-        <x:v>150860</x:v>
+        <x:v>146000</x:v>
       </x:c>
       <x:c r="F344" s="23" t="n">
-        <x:v>151600</x:v>
+        <x:v>168600</x:v>
       </x:c>
       <x:c r="G344" s="28" t="n">
         <x:f>ROUND(F344-F343,1)</x:f>
-        <x:v>-17000</x:v>
+        <x:v>17460</x:v>
       </x:c>
       <x:c r="H344" s="24" t="n">
         <x:f>IFERROR(F344/F343-1,"")</x:f>
-        <x:v>-0.10083036773428233</x:v>
+        <x:v>0.1155220325526003</x:v>
       </x:c>
       <x:c r="I344" s="26" t="n">
         <x:f>ROUND(D344-E344,1)</x:f>
-        <x:v>24040</x:v>
+        <x:v>26120</x:v>
       </x:c>
       <x:c r="J344" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20620,34 +20656,34 @@
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="22" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B345" s="22" t="str">
-        <x:v>7月13日-7月17日</x:v>
+        <x:v>7月6日-7月10日</x:v>
       </x:c>
       <x:c r="C345" s="23" t="n">
-        <x:v>150300</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="D345" s="23" t="n">
-        <x:v>155660</x:v>
+        <x:v>174900</x:v>
       </x:c>
       <x:c r="E345" s="23" t="n">
-        <x:v>145460</x:v>
+        <x:v>150860</x:v>
       </x:c>
       <x:c r="F345" s="23" t="n">
-        <x:v>149740</x:v>
+        <x:v>151600</x:v>
       </x:c>
       <x:c r="G345" s="28" t="n">
         <x:f>ROUND(F345-F344,1)</x:f>
-        <x:v>-1860</x:v>
+        <x:v>-17000</x:v>
       </x:c>
       <x:c r="H345" s="24" t="n">
         <x:f>IFERROR(F345/F344-1,"")</x:f>
-        <x:v>-0.012269129287598934</x:v>
+        <x:v>-0.10083036773428233</x:v>
       </x:c>
       <x:c r="I345" s="26" t="n">
         <x:f>ROUND(D345-E345,1)</x:f>
-        <x:v>10200</x:v>
+        <x:v>24040</x:v>
       </x:c>
       <x:c r="J345" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20658,34 +20694,34 @@
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="22" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B346" s="22" t="str">
-        <x:v>7月20日-7月24日</x:v>
+        <x:v>7月13日-7月17日</x:v>
       </x:c>
       <x:c r="C346" s="23" t="n">
-        <x:v>152520</x:v>
+        <x:v>150300</x:v>
       </x:c>
       <x:c r="D346" s="23" t="n">
-        <x:v>153880</x:v>
+        <x:v>155660</x:v>
       </x:c>
       <x:c r="E346" s="23" t="n">
-        <x:v>135040</x:v>
+        <x:v>145460</x:v>
       </x:c>
       <x:c r="F346" s="23" t="n">
-        <x:v>142920</x:v>
+        <x:v>149740</x:v>
       </x:c>
       <x:c r="G346" s="28" t="n">
         <x:f>ROUND(F346-F345,1)</x:f>
-        <x:v>-6820</x:v>
+        <x:v>-1860</x:v>
       </x:c>
       <x:c r="H346" s="24" t="n">
         <x:f>IFERROR(F346/F345-1,"")</x:f>
-        <x:v>-0.04554561239481769</x:v>
+        <x:v>-0.012269129287598934</x:v>
       </x:c>
       <x:c r="I346" s="26" t="n">
         <x:f>ROUND(D346-E346,1)</x:f>
-        <x:v>18840</x:v>
+        <x:v>10200</x:v>
       </x:c>
       <x:c r="J346" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20696,34 +20732,34 @@
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="22" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B347" s="22" t="str">
-        <x:v>7月27日-7月31日</x:v>
+        <x:v>7月20日-7月24日</x:v>
       </x:c>
       <x:c r="C347" s="23" t="n">
-        <x:v>144340</x:v>
+        <x:v>152520</x:v>
       </x:c>
       <x:c r="D347" s="23" t="n">
-        <x:v>148600</x:v>
+        <x:v>153880</x:v>
       </x:c>
       <x:c r="E347" s="23" t="n">
-        <x:v>137000</x:v>
+        <x:v>135040</x:v>
       </x:c>
       <x:c r="F347" s="23" t="n">
-        <x:v>137000</x:v>
+        <x:v>142920</x:v>
       </x:c>
       <x:c r="G347" s="28" t="n">
         <x:f>ROUND(F347-F346,1)</x:f>
-        <x:v>-5920</x:v>
+        <x:v>-6820</x:v>
       </x:c>
       <x:c r="H347" s="24" t="n">
         <x:f>IFERROR(F347/F346-1,"")</x:f>
-        <x:v>-0.04142177441925554</x:v>
+        <x:v>-0.04554561239481769</x:v>
       </x:c>
       <x:c r="I347" s="26" t="n">
         <x:f>ROUND(D347-E347,1)</x:f>
-        <x:v>11600</x:v>
+        <x:v>18840</x:v>
       </x:c>
       <x:c r="J347" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20734,34 +20770,34 @@
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="22" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B348" s="22" t="str">
-        <x:v>8月3日-8月7日</x:v>
+        <x:v>7月27日-7月31日</x:v>
       </x:c>
       <x:c r="C348" s="23" t="n">
-        <x:v>137200</x:v>
+        <x:v>144340</x:v>
       </x:c>
       <x:c r="D348" s="23" t="n">
-        <x:v>144100</x:v>
+        <x:v>148600</x:v>
       </x:c>
       <x:c r="E348" s="23" t="n">
-        <x:v>135040</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="F348" s="23" t="n">
-        <x:v>139320</x:v>
+        <x:v>137000</x:v>
       </x:c>
       <x:c r="G348" s="28" t="n">
         <x:f>ROUND(F348-F347,1)</x:f>
-        <x:v>2320</x:v>
+        <x:v>-5920</x:v>
       </x:c>
       <x:c r="H348" s="24" t="n">
         <x:f>IFERROR(F348/F347-1,"")</x:f>
-        <x:v>0.016934306569343027</x:v>
+        <x:v>-0.04142177441925554</x:v>
       </x:c>
       <x:c r="I348" s="26" t="n">
         <x:f>ROUND(D348-E348,1)</x:f>
-        <x:v>9060</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="J348" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20772,34 +20808,34 @@
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="22" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B349" s="22" t="str">
-        <x:v>8月10日-8月14日</x:v>
+        <x:v>8月3日-8月7日</x:v>
       </x:c>
       <x:c r="C349" s="23" t="n">
+        <x:v>137200</x:v>
+      </x:c>
+      <x:c r="D349" s="23" t="n">
+        <x:v>144100</x:v>
+      </x:c>
+      <x:c r="E349" s="23" t="n">
+        <x:v>135040</x:v>
+      </x:c>
+      <x:c r="F349" s="23" t="n">
         <x:v>139320</x:v>
-      </x:c>
-      <x:c r="D349" s="23" t="n">
-        <x:v>154560</x:v>
-      </x:c>
-      <x:c r="E349" s="23" t="n">
-        <x:v>139300</x:v>
-      </x:c>
-      <x:c r="F349" s="23" t="n">
-        <x:v>153980</x:v>
       </x:c>
       <x:c r="G349" s="28" t="n">
         <x:f>ROUND(F349-F348,1)</x:f>
-        <x:v>14660</x:v>
+        <x:v>2320</x:v>
       </x:c>
       <x:c r="H349" s="24" t="n">
         <x:f>IFERROR(F349/F348-1,"")</x:f>
-        <x:v>0.10522538041917895</x:v>
+        <x:v>0.016934306569343027</x:v>
       </x:c>
       <x:c r="I349" s="26" t="n">
         <x:f>ROUND(D349-E349,1)</x:f>
-        <x:v>15260</x:v>
+        <x:v>9060</x:v>
       </x:c>
       <x:c r="J349" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20810,34 +20846,34 @@
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="22" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B350" s="22" t="str">
-        <x:v>8月17日-8月21日</x:v>
+        <x:v>8月10日-8月14日</x:v>
       </x:c>
       <x:c r="C350" s="23" t="n">
-        <x:v>152940</x:v>
+        <x:v>139320</x:v>
       </x:c>
       <x:c r="D350" s="23" t="n">
-        <x:v>157400</x:v>
+        <x:v>154560</x:v>
       </x:c>
       <x:c r="E350" s="23" t="n">
-        <x:v>148700</x:v>
+        <x:v>139300</x:v>
       </x:c>
       <x:c r="F350" s="23" t="n">
-        <x:v>156380</x:v>
+        <x:v>153980</x:v>
       </x:c>
       <x:c r="G350" s="28" t="n">
         <x:f>ROUND(F350-F349,1)</x:f>
-        <x:v>2400</x:v>
+        <x:v>14660</x:v>
       </x:c>
       <x:c r="H350" s="24" t="n">
         <x:f>IFERROR(F350/F349-1,"")</x:f>
-        <x:v>0.015586439797376173</x:v>
+        <x:v>0.10522538041917895</x:v>
       </x:c>
       <x:c r="I350" s="26" t="n">
         <x:f>ROUND(D350-E350,1)</x:f>
-        <x:v>8700</x:v>
+        <x:v>15260</x:v>
       </x:c>
       <x:c r="J350" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20848,34 +20884,34 @@
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="22" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B351" s="22" t="str">
-        <x:v>8月24日-8月28日</x:v>
+        <x:v>8月17日-8月21日</x:v>
       </x:c>
       <x:c r="C351" s="23" t="n">
-        <x:v>158800</x:v>
+        <x:v>152940</x:v>
       </x:c>
       <x:c r="D351" s="23" t="n">
-        <x:v>160500</x:v>
+        <x:v>157400</x:v>
       </x:c>
       <x:c r="E351" s="23" t="n">
-        <x:v>147600</x:v>
+        <x:v>148700</x:v>
       </x:c>
       <x:c r="F351" s="23" t="n">
-        <x:v>157940</x:v>
+        <x:v>156380</x:v>
       </x:c>
       <x:c r="G351" s="28" t="n">
         <x:f>ROUND(F351-F350,1)</x:f>
-        <x:v>1560</x:v>
+        <x:v>2400</x:v>
       </x:c>
       <x:c r="H351" s="24" t="n">
         <x:f>IFERROR(F351/F350-1,"")</x:f>
-        <x:v>0.009975700217419003</x:v>
+        <x:v>0.015586439797376173</x:v>
       </x:c>
       <x:c r="I351" s="26" t="n">
         <x:f>ROUND(D351-E351,1)</x:f>
-        <x:v>12900</x:v>
+        <x:v>8700</x:v>
       </x:c>
       <x:c r="J351" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20886,34 +20922,34 @@
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="22" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B352" s="22" t="str">
-        <x:v>8月31日-9月4日</x:v>
+        <x:v>8月24日-8月28日</x:v>
       </x:c>
       <x:c r="C352" s="23" t="n">
-        <x:v>157500</x:v>
+        <x:v>158800</x:v>
       </x:c>
       <x:c r="D352" s="23" t="n">
-        <x:v>161280</x:v>
+        <x:v>160500</x:v>
       </x:c>
       <x:c r="E352" s="23" t="n">
-        <x:v>140220</x:v>
+        <x:v>147600</x:v>
       </x:c>
       <x:c r="F352" s="23" t="n">
-        <x:v>142000</x:v>
+        <x:v>157940</x:v>
       </x:c>
       <x:c r="G352" s="28" t="n">
         <x:f>ROUND(F352-F351,1)</x:f>
-        <x:v>-15940</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="H352" s="24" t="n">
         <x:f>IFERROR(F352/F351-1,"")</x:f>
-        <x:v>-0.10092440167152084</x:v>
+        <x:v>0.009975700217419003</x:v>
       </x:c>
       <x:c r="I352" s="26" t="n">
         <x:f>ROUND(D352-E352,1)</x:f>
-        <x:v>21060</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="J352" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20924,34 +20960,34 @@
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="22" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B353" s="22" t="str">
-        <x:v>9月7日-9月11日</x:v>
+        <x:v>8月31日-9月4日</x:v>
       </x:c>
       <x:c r="C353" s="23" t="n">
-        <x:v>141000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D353" s="23" t="n">
-        <x:v>143540</x:v>
+        <x:v>161280</x:v>
       </x:c>
       <x:c r="E353" s="23" t="n">
-        <x:v>127120</x:v>
+        <x:v>140220</x:v>
       </x:c>
       <x:c r="F353" s="23" t="n">
-        <x:v>134340</x:v>
+        <x:v>142000</x:v>
       </x:c>
       <x:c r="G353" s="28" t="n">
         <x:f>ROUND(F353-F352,1)</x:f>
-        <x:v>-7660</x:v>
+        <x:v>-15940</x:v>
       </x:c>
       <x:c r="H353" s="24" t="n">
         <x:f>IFERROR(F353/F352-1,"")</x:f>
-        <x:v>-0.05394366197183098</x:v>
+        <x:v>-0.10092440167152084</x:v>
       </x:c>
       <x:c r="I353" s="26" t="n">
         <x:f>ROUND(D353-E353,1)</x:f>
-        <x:v>16420</x:v>
+        <x:v>21060</x:v>
       </x:c>
       <x:c r="J353" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -20962,34 +20998,34 @@
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="22" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B354" s="22" t="str">
-        <x:v>9月14日-9月18日</x:v>
+        <x:v>9月7日-9月11日</x:v>
       </x:c>
       <x:c r="C354" s="23" t="n">
-        <x:v>133600</x:v>
+        <x:v>141000</x:v>
       </x:c>
       <x:c r="D354" s="23" t="n">
-        <x:v>135900</x:v>
+        <x:v>143540</x:v>
       </x:c>
       <x:c r="E354" s="23" t="n">
-        <x:v>126200</x:v>
+        <x:v>127120</x:v>
       </x:c>
       <x:c r="F354" s="23" t="n">
-        <x:v>128580</x:v>
+        <x:v>134340</x:v>
       </x:c>
       <x:c r="G354" s="28" t="n">
         <x:f>ROUND(F354-F353,1)</x:f>
-        <x:v>-5760</x:v>
+        <x:v>-7660</x:v>
       </x:c>
       <x:c r="H354" s="24" t="n">
         <x:f>IFERROR(F354/F353-1,"")</x:f>
-        <x:v>-0.04287628405538191</x:v>
+        <x:v>-0.05394366197183098</x:v>
       </x:c>
       <x:c r="I354" s="26" t="n">
         <x:f>ROUND(D354-E354,1)</x:f>
-        <x:v>9700</x:v>
+        <x:v>16420</x:v>
       </x:c>
       <x:c r="J354" s="22" t="str">
         <x:v>LC2610</x:v>
@@ -21000,155 +21036,231 @@
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="22" t="n">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B355" s="22" t="str">
-        <x:v>9月21日-9月24日</x:v>
+        <x:v>9月14日-9月18日</x:v>
       </x:c>
       <x:c r="C355" s="23" t="n">
-        <x:v>128500</x:v>
+        <x:v>133600</x:v>
       </x:c>
       <x:c r="D355" s="23" t="n">
-        <x:v>136560</x:v>
+        <x:v>135900</x:v>
       </x:c>
       <x:c r="E355" s="23" t="n">
-        <x:v>125000</x:v>
+        <x:v>126200</x:v>
       </x:c>
       <x:c r="F355" s="23" t="n">
-        <x:v>125980</x:v>
+        <x:v>128580</x:v>
       </x:c>
       <x:c r="G355" s="28" t="n">
         <x:f>ROUND(F355-F354,1)</x:f>
-        <x:v>-2600</x:v>
+        <x:v>-5760</x:v>
       </x:c>
       <x:c r="H355" s="24" t="n">
         <x:f>IFERROR(F355/F354-1,"")</x:f>
-        <x:v>-0.02022087416394458</x:v>
+        <x:v>-0.04287628405538191</x:v>
       </x:c>
       <x:c r="I355" s="26" t="n">
         <x:f>ROUND(D355-E355,1)</x:f>
-        <x:v>11560</x:v>
+        <x:v>9700</x:v>
       </x:c>
       <x:c r="J355" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K355" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="22" t="n">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B356" s="22" t="str">
-        <x:v>9月28日-9月30日</x:v>
+        <x:v>9月21日-9月24日</x:v>
       </x:c>
       <x:c r="C356" s="23" t="n">
-        <x:v>124280</x:v>
+        <x:v>128500</x:v>
       </x:c>
       <x:c r="D356" s="23" t="n">
-        <x:v>124660</x:v>
+        <x:v>136560</x:v>
       </x:c>
       <x:c r="E356" s="23" t="n">
-        <x:v>118100</x:v>
+        <x:v>125000</x:v>
       </x:c>
       <x:c r="F356" s="23" t="n">
-        <x:v>119780</x:v>
+        <x:v>125980</x:v>
       </x:c>
       <x:c r="G356" s="28" t="n">
         <x:f>ROUND(F356-F355,1)</x:f>
-        <x:v>-6200</x:v>
+        <x:v>-2600</x:v>
       </x:c>
       <x:c r="H356" s="24" t="n">
         <x:f>IFERROR(F356/F355-1,"")</x:f>
-        <x:v>-0.049214160977932964</x:v>
+        <x:v>-0.02022087416394458</x:v>
       </x:c>
       <x:c r="I356" s="26" t="n">
         <x:f>ROUND(D356-E356,1)</x:f>
-        <x:v>6560</x:v>
+        <x:v>11560</x:v>
       </x:c>
       <x:c r="J356" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K356" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="22" t="n">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B357" s="22" t="str">
-        <x:v>10月8日-10月9日</x:v>
+        <x:v>9月28日-9月30日</x:v>
       </x:c>
       <x:c r="C357" s="23" t="n">
-        <x:v>120020</x:v>
+        <x:v>124280</x:v>
       </x:c>
       <x:c r="D357" s="23" t="n">
-        <x:v>126800</x:v>
+        <x:v>124660</x:v>
       </x:c>
       <x:c r="E357" s="23" t="n">
-        <x:v>119000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="F357" s="23" t="n">
-        <x:v>121000</x:v>
+        <x:v>119780</x:v>
       </x:c>
       <x:c r="G357" s="28" t="n">
         <x:f>ROUND(F357-F356,1)</x:f>
-        <x:v>1220</x:v>
+        <x:v>-6200</x:v>
       </x:c>
       <x:c r="H357" s="24" t="n">
         <x:f>IFERROR(F357/F356-1,"")</x:f>
-        <x:v>0.010185339789614334</x:v>
+        <x:v>-0.049214160977932964</x:v>
       </x:c>
       <x:c r="I357" s="26" t="n">
         <x:f>ROUND(D357-E357,1)</x:f>
-        <x:v>7800</x:v>
+        <x:v>6560</x:v>
       </x:c>
       <x:c r="J357" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K357" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358">
+      <x:c r="A358" s="22" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B358" s="22" t="str">
+        <x:v>10月8日-10月9日</x:v>
+      </x:c>
+      <x:c r="C358" s="23" t="n">
+        <x:v>120020</x:v>
+      </x:c>
+      <x:c r="D358" s="23" t="n">
+        <x:v>126800</x:v>
+      </x:c>
+      <x:c r="E358" s="23" t="n">
+        <x:v>119000</x:v>
+      </x:c>
+      <x:c r="F358" s="23" t="n">
+        <x:v>121000</x:v>
+      </x:c>
+      <x:c r="G358" s="28" t="n">
+        <x:f>ROUND(F358-F357,1)</x:f>
+        <x:v>1220</x:v>
+      </x:c>
+      <x:c r="H358" s="24" t="n">
+        <x:f>IFERROR(F358/F357-1,"")</x:f>
+        <x:v>0.010185339789614334</x:v>
+      </x:c>
+      <x:c r="I358" s="26" t="n">
+        <x:f>ROUND(D358-E358,1)</x:f>
+        <x:v>7800</x:v>
+      </x:c>
+      <x:c r="J358" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K358" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="358">
-      <x:c r="A358" s="31" t="str">
+    <x:row r="359">
+      <x:c r="A359" s="22" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B359" s="22" t="str">
+        <x:v>10月12日</x:v>
+      </x:c>
+      <x:c r="C359" s="23" t="n">
+        <x:v>125960</x:v>
+      </x:c>
+      <x:c r="D359" s="23" t="n">
+        <x:v>125960</x:v>
+      </x:c>
+      <x:c r="E359" s="23" t="n">
+        <x:v>107100</x:v>
+      </x:c>
+      <x:c r="F359" s="23" t="n">
+        <x:v>107100</x:v>
+      </x:c>
+      <x:c r="G359" s="28" t="n">
+        <x:f>ROUND(F359-F358,1)</x:f>
+        <x:v>-13900</x:v>
+      </x:c>
+      <x:c r="H359" s="24" t="n">
+        <x:f>IFERROR(F359/F358-1,"")</x:f>
+        <x:v>-0.11487603305785121</x:v>
+      </x:c>
+      <x:c r="I359" s="26" t="n">
+        <x:f>ROUND(D359-E359,1)</x:f>
+        <x:v>18860</x:v>
+      </x:c>
+      <x:c r="J359" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
+      <x:c r="K359" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360">
+      <x:c r="A360" s="31" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B358" s="30" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C358" s="30"/>
-      <x:c r="D358" s="30"/>
-      <x:c r="E358" s="30"/>
-      <x:c r="F358" s="30"/>
-      <x:c r="G358" s="30"/>
-      <x:c r="H358" s="30"/>
-      <x:c r="I358" s="32" t="n">
-        <x:f>ROUND(SUM(I319:I357),1)</x:f>
-        <x:v>767320</x:v>
-      </x:c>
-      <x:c r="J358" s="30"/>
-      <x:c r="K358" s="30"/>
-    </x:row>
-    <x:row r="359">
-      <x:c r="A359" s="31" t="str">
+      <x:c r="B360" s="30" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C360" s="30"/>
+      <x:c r="D360" s="30"/>
+      <x:c r="E360" s="30"/>
+      <x:c r="F360" s="30"/>
+      <x:c r="G360" s="30"/>
+      <x:c r="H360" s="30"/>
+      <x:c r="I360" s="32" t="n">
+        <x:f>ROUND(SUM(I320:I359),1)</x:f>
+        <x:v>786180</x:v>
+      </x:c>
+      <x:c r="J360" s="30"/>
+      <x:c r="K360" s="30"/>
+    </x:row>
+    <x:row r="361">
+      <x:c r="A361" s="31" t="str">
         <x:v>均值</x:v>
       </x:c>
-      <x:c r="B359" s="30"/>
-      <x:c r="C359" s="30"/>
-      <x:c r="D359" s="30"/>
-      <x:c r="E359" s="30"/>
-      <x:c r="F359" s="30"/>
-      <x:c r="G359" s="30"/>
-      <x:c r="H359" s="30"/>
-      <x:c r="I359" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(I319:I357),0),1)</x:f>
-        <x:v>19674.9</x:v>
-      </x:c>
-      <x:c r="J359" s="30"/>
-      <x:c r="K359" s="30"/>
+      <x:c r="B361" s="30"/>
+      <x:c r="C361" s="30"/>
+      <x:c r="D361" s="30"/>
+      <x:c r="E361" s="30"/>
+      <x:c r="F361" s="30"/>
+      <x:c r="G361" s="30"/>
+      <x:c r="H361" s="30"/>
+      <x:c r="I361" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(I320:I359),0),1)</x:f>
+        <x:v>19654.5</x:v>
+      </x:c>
+      <x:c r="J361" s="30"/>
+      <x:c r="K361" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -21158,9 +21270,9 @@
     <x:mergeCell ref="A93:K93"/>
     <x:mergeCell ref="A138:K138"/>
     <x:mergeCell ref="A183:K183"/>
-    <x:mergeCell ref="A227:K227"/>
-    <x:mergeCell ref="A272:K272"/>
-    <x:mergeCell ref="A317:K317"/>
+    <x:mergeCell ref="A228:K228"/>
+    <x:mergeCell ref="A273:K273"/>
+    <x:mergeCell ref="A318:K318"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -58795,30 +58907,48 @@
       </x:c>
     </x:row>
     <x:row r="233">
-      <x:c r="A233" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B233" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C233" s="30"/>
-      <x:c r="D233" s="30"/>
-      <x:c r="E233" s="30"/>
-      <x:c r="F233" s="30"/>
-      <x:c r="G233" s="30"/>
-      <x:c r="H233" s="30"/>
-      <x:c r="I233" s="30"/>
-      <x:c r="J233" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J232),1)</x:f>
-        <x:v>514.6</x:v>
-      </x:c>
-      <x:c r="K233" s="30"/>
+      <x:c r="A233" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B233" s="22" t="str">
+        <x:v>周一</x:v>
+      </x:c>
+      <x:c r="C233" s="22" t="str">
+        <x:v>10月12日</x:v>
+      </x:c>
+      <x:c r="D233" s="23" t="n">
+        <x:v>7076.6</x:v>
+      </x:c>
+      <x:c r="E233" s="23" t="n">
+        <x:v>7115.6</x:v>
+      </x:c>
+      <x:c r="F233" s="23" t="n">
+        <x:v>6943.6</x:v>
+      </x:c>
+      <x:c r="G233" s="23" t="n">
+        <x:v>6986</x:v>
+      </x:c>
+      <x:c r="H233" s="23" t="n">
+        <x:v>-125</x:v>
+      </x:c>
+      <x:c r="I233" s="24" t="n">
+        <x:v>-0.017578399662494748</x:v>
+      </x:c>
+      <x:c r="J233" s="26" t="n">
+        <x:f>ROUND(E233-F233,1)</x:f>
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="K233" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B234" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B234" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C234" s="30"/>
       <x:c r="D234" s="30"/>
       <x:c r="E234" s="30"/>
@@ -58826,11 +58956,29 @@
       <x:c r="G234" s="30"/>
       <x:c r="H234" s="30"/>
       <x:c r="I234" s="30"/>
-      <x:c r="J234" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J232),0),1)</x:f>
-        <x:v>257.3</x:v>
+      <x:c r="J234" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J233),1)</x:f>
+        <x:v>686.6</x:v>
       </x:c>
       <x:c r="K234" s="30"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B235" s="30"/>
+      <x:c r="C235" s="30"/>
+      <x:c r="D235" s="30"/>
+      <x:c r="E235" s="30"/>
+      <x:c r="F235" s="30"/>
+      <x:c r="G235" s="30"/>
+      <x:c r="H235" s="30"/>
+      <x:c r="I235" s="30"/>
+      <x:c r="J235" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
+        <x:v>228.9</x:v>
+      </x:c>
+      <x:c r="K235" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R3e596e04d6494180"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R682a5634401c457a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R835b21638804457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Reca6f85f8ea94298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rbc2ce11976b74544"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rccb4de568b824d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rfb1efd62f28c4a34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R8d4b511f0abb4955"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Ra3223df7eb60460f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R7bd4e34f0a44436b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rb03663d8a6064e39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R986aa8d4d01448d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R48d6969375b346bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R8e2f725df6f14933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R41c75bc339ed484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R87b3e6d3a4524426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R13ddbc9f9043461d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rf7b7c7f841c940a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rc8bc7fff3905472f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R85081f9a6678467b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7145.06</x:v>
+        <x:v>7087.89</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>7014.37</x:v>
+        <x:v>6796.58</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>130.7</x:v>
+        <x:v>291.3</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>32150.7</x:v>
+        <x:v>32442</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>174.7</x:v>
+        <x:v>175.4</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7236.78</x:v>
+        <x:v>7152.45</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>7085.92</x:v>
+        <x:v>6904.6</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>150.9</x:v>
+        <x:v>247.8</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>31919.9</x:v>
+        <x:v>32167.7</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>173.5</x:v>
+        <x:v>173.9</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,25 +577,25 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3828.22</x:v>
+        <x:v>3822.11</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3791</x:v>
+        <x:v>3741.53</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>37.2</x:v>
+        <x:v>80.6</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8791.3</x:v>
+        <x:v>8871.9</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
-        <x:v>47.8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
         <x:v>50</x:v>
@@ -664,25 +664,25 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4273.6</x:v>
+        <x:v>4257.4</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4213.8</x:v>
+        <x:v>4151</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>59.8</x:v>
+        <x:v>106.4</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>13265.6</x:v>
+        <x:v>13372</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
-        <x:v>72.1</x:v>
+        <x:v>72.3</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
         <x:v>90</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -9977,7 +9977,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月12日-10月13日</x:v>
       </x:c>
       <x:c r="C44" s="23" t="n">
         <x:v>7132.68</x:v>
@@ -9986,28 +9986,28 @@
         <x:v>7145.06</x:v>
       </x:c>
       <x:c r="E44" s="23" t="n">
-        <x:v>7014.37</x:v>
+        <x:v>6796.58</x:v>
       </x:c>
       <x:c r="F44" s="23" t="n">
-        <x:v>7021.47</x:v>
+        <x:v>7023.22</x:v>
       </x:c>
       <x:c r="G44" s="23" t="n">
         <x:f>ROUND(F44-F43,1)</x:f>
-        <x:v>-134.4</x:v>
+        <x:v>-132.7</x:v>
       </x:c>
       <x:c r="H44" s="24" t="n">
         <x:f>IFERROR(F44/F43-1,"")</x:f>
-        <x:v>-0.018787268146189584</x:v>
-      </x:c>
-      <x:c r="I44" s="23" t="n">
+        <x:v>-0.018542715042531244</x:v>
+      </x:c>
+      <x:c r="I44" s="26" t="n">
         <x:f>ROUND(D44-E44,1)</x:f>
-        <x:v>130.7</x:v>
+        <x:v>348.5</x:v>
       </x:c>
       <x:c r="J44" s="22" t="str">
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K44" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -10025,7 +10025,7 @@
       <x:c r="H45" s="30"/>
       <x:c r="I45" s="32" t="n">
         <x:f>ROUND(SUM(I5:I44),1)</x:f>
-        <x:v>16233.3</x:v>
+        <x:v>16451.1</x:v>
       </x:c>
       <x:c r="J45" s="30"/>
       <x:c r="K45" s="30"/>
@@ -10043,7 +10043,7 @@
       <x:c r="H46" s="30"/>
       <x:c r="I46" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I5:I44),0),1)</x:f>
-        <x:v>405.8</x:v>
+        <x:v>411.3</x:v>
       </x:c>
       <x:c r="J46" s="30"/>
       <x:c r="K46" s="30"/>
@@ -11579,7 +11579,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B89" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月12日-10月13日</x:v>
       </x:c>
       <x:c r="C89" s="23" t="n">
         <x:v>7226.07</x:v>
@@ -11588,28 +11588,28 @@
         <x:v>7236.78</x:v>
       </x:c>
       <x:c r="E89" s="23" t="n">
-        <x:v>7085.92</x:v>
+        <x:v>6904.6</x:v>
       </x:c>
       <x:c r="F89" s="23" t="n">
-        <x:v>7093.02</x:v>
+        <x:v>7085.09</x:v>
       </x:c>
       <x:c r="G89" s="28" t="n">
         <x:f>ROUND(F89-F88,1)</x:f>
-        <x:v>-158</x:v>
+        <x:v>-165.9</x:v>
       </x:c>
       <x:c r="H89" s="24" t="n">
         <x:f>IFERROR(F89/F88-1,"")</x:f>
-        <x:v>-0.02178868874818818</x:v>
-      </x:c>
-      <x:c r="I89" s="23" t="n">
+        <x:v>-0.022882329496166753</x:v>
+      </x:c>
+      <x:c r="I89" s="26" t="n">
         <x:f>ROUND(D89-E89,1)</x:f>
-        <x:v>150.9</x:v>
+        <x:v>332.2</x:v>
       </x:c>
       <x:c r="J89" s="22" t="str">
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K89" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -11627,7 +11627,7 @@
       <x:c r="H90" s="30"/>
       <x:c r="I90" s="32" t="n">
         <x:f>ROUND(SUM(I50:I89),1)</x:f>
-        <x:v>16149.5</x:v>
+        <x:v>16330.8</x:v>
       </x:c>
       <x:c r="J90" s="30"/>
       <x:c r="K90" s="30"/>
@@ -11645,7 +11645,7 @@
       <x:c r="H91" s="30"/>
       <x:c r="I91" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I50:I89),0),1)</x:f>
-        <x:v>403.7</x:v>
+        <x:v>408.3</x:v>
       </x:c>
       <x:c r="J91" s="30"/>
       <x:c r="K91" s="30"/>
@@ -13181,7 +13181,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B134" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月12日-10月13日</x:v>
       </x:c>
       <x:c r="C134" s="23" t="n">
         <x:v>3806.98</x:v>
@@ -13190,28 +13190,28 @@
         <x:v>3828.22</x:v>
       </x:c>
       <x:c r="E134" s="23" t="n">
-        <x:v>3791</x:v>
+        <x:v>3741.53</x:v>
       </x:c>
       <x:c r="F134" s="23" t="n">
-        <x:v>3797.24</x:v>
+        <x:v>3800.86</x:v>
       </x:c>
       <x:c r="G134" s="23" t="n">
         <x:f>ROUND(F134-F133,1)</x:f>
-        <x:v>-16.6</x:v>
+        <x:v>-12.9</x:v>
       </x:c>
       <x:c r="H134" s="24" t="n">
         <x:f>IFERROR(F134/F133-1,"")</x:f>
-        <x:v>-0.00433951528531995</x:v>
-      </x:c>
-      <x:c r="I134" s="23" t="n">
+        <x:v>-0.0033903282561441594</x:v>
+      </x:c>
+      <x:c r="I134" s="26" t="n">
         <x:f>ROUND(D134-E134,1)</x:f>
-        <x:v>37.2</x:v>
+        <x:v>86.7</x:v>
       </x:c>
       <x:c r="J134" s="22" t="str">
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K134" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -13229,7 +13229,7 @@
       <x:c r="H135" s="30"/>
       <x:c r="I135" s="32" t="n">
         <x:f>ROUND(SUM(I95:I134),1)</x:f>
-        <x:v>4239.3</x:v>
+        <x:v>4288.8</x:v>
       </x:c>
       <x:c r="J135" s="30"/>
       <x:c r="K135" s="30"/>
@@ -13247,7 +13247,7 @@
       <x:c r="H136" s="30"/>
       <x:c r="I136" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I95:I134),0),1)</x:f>
-        <x:v>106</x:v>
+        <x:v>107.2</x:v>
       </x:c>
       <x:c r="J136" s="30"/>
       <x:c r="K136" s="30"/>
@@ -17987,7 +17987,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B269" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月12日-10月13日</x:v>
       </x:c>
       <x:c r="C269" s="23" t="n">
         <x:v>4240.4</x:v>
@@ -17996,28 +17996,28 @@
         <x:v>4273.6</x:v>
       </x:c>
       <x:c r="E269" s="23" t="n">
-        <x:v>4213.8</x:v>
+        <x:v>4151</x:v>
       </x:c>
       <x:c r="F269" s="23" t="n">
-        <x:v>4233.6</x:v>
+        <x:v>4217.6</x:v>
       </x:c>
       <x:c r="G269" s="23" t="n">
         <x:f>ROUND(F269-F268,1)</x:f>
-        <x:v>-11.2</x:v>
+        <x:v>-27.2</x:v>
       </x:c>
       <x:c r="H269" s="24" t="n">
         <x:f>IFERROR(F269/F268-1,"")</x:f>
-        <x:v>-0.0026385224274405594</x:v>
-      </x:c>
-      <x:c r="I269" s="23" t="n">
+        <x:v>-0.006407840180927216</x:v>
+      </x:c>
+      <x:c r="I269" s="26" t="n">
         <x:f>ROUND(D269-E269,1)</x:f>
-        <x:v>59.8</x:v>
+        <x:v>122.6</x:v>
       </x:c>
       <x:c r="J269" s="22" t="str">
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K269" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -18035,7 +18035,7 @@
       <x:c r="H270" s="30"/>
       <x:c r="I270" s="32" t="n">
         <x:f>ROUND(SUM(I230:I269),1)</x:f>
-        <x:v>6198.4</x:v>
+        <x:v>6261.2</x:v>
       </x:c>
       <x:c r="J270" s="30"/>
       <x:c r="K270" s="30"/>
@@ -18053,7 +18053,7 @@
       <x:c r="H271" s="30"/>
       <x:c r="I271" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I230:I269),0),1)</x:f>
-        <x:v>155</x:v>
+        <x:v>156.5</x:v>
       </x:c>
       <x:c r="J271" s="30"/>
       <x:c r="K271" s="30"/>
@@ -28767,30 +28767,48 @@
       </x:c>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B234" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C234" s="30"/>
-      <x:c r="D234" s="30"/>
-      <x:c r="E234" s="30"/>
-      <x:c r="F234" s="30"/>
-      <x:c r="G234" s="30"/>
-      <x:c r="H234" s="30"/>
-      <x:c r="I234" s="30"/>
-      <x:c r="J234" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J233),1)</x:f>
-        <x:v>659.7</x:v>
-      </x:c>
-      <x:c r="K234" s="30"/>
+      <x:c r="A234" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B234" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C234" s="22" t="str">
+        <x:v>10月13日</x:v>
+      </x:c>
+      <x:c r="D234" s="23" t="n">
+        <x:v>6894.6</x:v>
+      </x:c>
+      <x:c r="E234" s="23" t="n">
+        <x:v>7087.89</x:v>
+      </x:c>
+      <x:c r="F234" s="23" t="n">
+        <x:v>6796.58</x:v>
+      </x:c>
+      <x:c r="G234" s="23" t="n">
+        <x:v>7023.22</x:v>
+      </x:c>
+      <x:c r="H234" s="23" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="I234" s="24" t="n">
+        <x:v>0.0002492355589356343</x:v>
+      </x:c>
+      <x:c r="J234" s="26" t="n">
+        <x:f>ROUND(E234-F234,1)</x:f>
+        <x:v>291.3</x:v>
+      </x:c>
+      <x:c r="K234" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B235" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B235" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C235" s="30"/>
       <x:c r="D235" s="30"/>
       <x:c r="E235" s="30"/>
@@ -28798,11 +28816,29 @@
       <x:c r="G235" s="30"/>
       <x:c r="H235" s="30"/>
       <x:c r="I235" s="30"/>
-      <x:c r="J235" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
-        <x:v>219.9</x:v>
+      <x:c r="J235" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J234),1)</x:f>
+        <x:v>951</x:v>
       </x:c>
       <x:c r="K235" s="30"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B236" s="30"/>
+      <x:c r="C236" s="30"/>
+      <x:c r="D236" s="30"/>
+      <x:c r="E236" s="30"/>
+      <x:c r="F236" s="30"/>
+      <x:c r="G236" s="30"/>
+      <x:c r="H236" s="30"/>
+      <x:c r="I236" s="30"/>
+      <x:c r="J236" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
+        <x:v>237.8</x:v>
+      </x:c>
+      <x:c r="K236" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -36311,30 +36347,48 @@
       </x:c>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B234" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C234" s="30"/>
-      <x:c r="D234" s="30"/>
-      <x:c r="E234" s="30"/>
-      <x:c r="F234" s="30"/>
-      <x:c r="G234" s="30"/>
-      <x:c r="H234" s="30"/>
-      <x:c r="I234" s="30"/>
-      <x:c r="J234" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J233),1)</x:f>
-        <x:v>634.8</x:v>
-      </x:c>
-      <x:c r="K234" s="30"/>
+      <x:c r="A234" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B234" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C234" s="22" t="str">
+        <x:v>10月13日</x:v>
+      </x:c>
+      <x:c r="D234" s="23" t="n">
+        <x:v>6976.63</x:v>
+      </x:c>
+      <x:c r="E234" s="23" t="n">
+        <x:v>7152.45</x:v>
+      </x:c>
+      <x:c r="F234" s="23" t="n">
+        <x:v>6904.6</x:v>
+      </x:c>
+      <x:c r="G234" s="23" t="n">
+        <x:v>7085.09</x:v>
+      </x:c>
+      <x:c r="H234" s="23" t="n">
+        <x:v>-7.9</x:v>
+      </x:c>
+      <x:c r="I234" s="24" t="n">
+        <x:v>-0.0011180005131805615</x:v>
+      </x:c>
+      <x:c r="J234" s="26" t="n">
+        <x:f>ROUND(E234-F234,1)</x:f>
+        <x:v>247.8</x:v>
+      </x:c>
+      <x:c r="K234" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B235" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B235" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C235" s="30"/>
       <x:c r="D235" s="30"/>
       <x:c r="E235" s="30"/>
@@ -36342,11 +36396,29 @@
       <x:c r="G235" s="30"/>
       <x:c r="H235" s="30"/>
       <x:c r="I235" s="30"/>
-      <x:c r="J235" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
-        <x:v>211.6</x:v>
+      <x:c r="J235" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J234),1)</x:f>
+        <x:v>882.6</x:v>
       </x:c>
       <x:c r="K235" s="30"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B236" s="30"/>
+      <x:c r="C236" s="30"/>
+      <x:c r="D236" s="30"/>
+      <x:c r="E236" s="30"/>
+      <x:c r="F236" s="30"/>
+      <x:c r="G236" s="30"/>
+      <x:c r="H236" s="30"/>
+      <x:c r="I236" s="30"/>
+      <x:c r="J236" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
+        <x:v>220.7</x:v>
+      </x:c>
+      <x:c r="K236" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -43855,30 +43927,48 @@
       </x:c>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B234" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C234" s="30"/>
-      <x:c r="D234" s="30"/>
-      <x:c r="E234" s="30"/>
-      <x:c r="F234" s="30"/>
-      <x:c r="G234" s="30"/>
-      <x:c r="H234" s="30"/>
-      <x:c r="I234" s="30"/>
-      <x:c r="J234" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J233),1)</x:f>
-        <x:v>176.6</x:v>
-      </x:c>
-      <x:c r="K234" s="30"/>
+      <x:c r="A234" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B234" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C234" s="22" t="str">
+        <x:v>10月13日</x:v>
+      </x:c>
+      <x:c r="D234" s="23" t="n">
+        <x:v>3760.8</x:v>
+      </x:c>
+      <x:c r="E234" s="23" t="n">
+        <x:v>3822.11</x:v>
+      </x:c>
+      <x:c r="F234" s="23" t="n">
+        <x:v>3741.53</x:v>
+      </x:c>
+      <x:c r="G234" s="23" t="n">
+        <x:v>3800.86</x:v>
+      </x:c>
+      <x:c r="H234" s="23" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="I234" s="24" t="n">
+        <x:v>0.0009533239932162374</x:v>
+      </x:c>
+      <x:c r="J234" s="26" t="n">
+        <x:f>ROUND(E234-F234,1)</x:f>
+        <x:v>80.6</x:v>
+      </x:c>
+      <x:c r="K234" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B235" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B235" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C235" s="30"/>
       <x:c r="D235" s="30"/>
       <x:c r="E235" s="30"/>
@@ -43886,11 +43976,29 @@
       <x:c r="G235" s="30"/>
       <x:c r="H235" s="30"/>
       <x:c r="I235" s="30"/>
-      <x:c r="J235" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
-        <x:v>58.9</x:v>
+      <x:c r="J235" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J234),1)</x:f>
+        <x:v>257.2</x:v>
       </x:c>
       <x:c r="K235" s="30"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B236" s="30"/>
+      <x:c r="C236" s="30"/>
+      <x:c r="D236" s="30"/>
+      <x:c r="E236" s="30"/>
+      <x:c r="F236" s="30"/>
+      <x:c r="G236" s="30"/>
+      <x:c r="H236" s="30"/>
+      <x:c r="I236" s="30"/>
+      <x:c r="J236" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
+        <x:v>64.3</x:v>
+      </x:c>
+      <x:c r="K236" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -66487,30 +66595,48 @@
       </x:c>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B234" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C234" s="30"/>
-      <x:c r="D234" s="30"/>
-      <x:c r="E234" s="30"/>
-      <x:c r="F234" s="30"/>
-      <x:c r="G234" s="30"/>
-      <x:c r="H234" s="30"/>
-      <x:c r="I234" s="30"/>
-      <x:c r="J234" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J233),1)</x:f>
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="K234" s="30"/>
+      <x:c r="A234" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B234" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C234" s="22" t="str">
+        <x:v>10月13日</x:v>
+      </x:c>
+      <x:c r="D234" s="23" t="n">
+        <x:v>4183.2</x:v>
+      </x:c>
+      <x:c r="E234" s="23" t="n">
+        <x:v>4257.4</x:v>
+      </x:c>
+      <x:c r="F234" s="23" t="n">
+        <x:v>4151</x:v>
+      </x:c>
+      <x:c r="G234" s="23" t="n">
+        <x:v>4217.6</x:v>
+      </x:c>
+      <x:c r="H234" s="23" t="n">
+        <x:v>-16</x:v>
+      </x:c>
+      <x:c r="I234" s="24" t="n">
+        <x:v>-0.0037792894935751997</x:v>
+      </x:c>
+      <x:c r="J234" s="26" t="n">
+        <x:f>ROUND(E234-F234,1)</x:f>
+        <x:v>106.4</x:v>
+      </x:c>
+      <x:c r="K234" s="22" t="str">
+        <x:v>IF2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B235" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B235" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C235" s="30"/>
       <x:c r="D235" s="30"/>
       <x:c r="E235" s="30"/>
@@ -66518,11 +66644,29 @@
       <x:c r="G235" s="30"/>
       <x:c r="H235" s="30"/>
       <x:c r="I235" s="30"/>
-      <x:c r="J235" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
-        <x:v>85.7</x:v>
+      <x:c r="J235" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J234),1)</x:f>
+        <x:v>363.4</x:v>
       </x:c>
       <x:c r="K235" s="30"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B236" s="30"/>
+      <x:c r="C236" s="30"/>
+      <x:c r="D236" s="30"/>
+      <x:c r="E236" s="30"/>
+      <x:c r="F236" s="30"/>
+      <x:c r="G236" s="30"/>
+      <x:c r="H236" s="30"/>
+      <x:c r="I236" s="30"/>
+      <x:c r="J236" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
+        <x:v>90.9</x:v>
+      </x:c>
+      <x:c r="K236" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="Rb03663d8a6064e39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R986aa8d4d01448d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R48d6969375b346bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R8e2f725df6f14933"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R41c75bc339ed484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R87b3e6d3a4524426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R13ddbc9f9043461d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="Rf7b7c7f841c940a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rc8bc7fff3905472f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R85081f9a6678467b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R1427454d3ff64e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R090131621edb466a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R014950725cad4e6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R634e260ca74f4e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb5559dc7818646b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rb0d4d5d538844814"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R45bd570977924b44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2d1b8c967d53467f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rb6cd41d64ae94e92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rbae1f462cbd84168"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>7031.2</x:v>
+        <x:v>6971.6</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>6886.6</x:v>
+        <x:v>6680</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>144.6</x:v>
+        <x:v>291.6</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>34171.4</x:v>
+        <x:v>34463</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>185.7</x:v>
+        <x:v>186.3</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7115.6</x:v>
+        <x:v>7029.2</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>6943.6</x:v>
+        <x:v>6778.4</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>172</x:v>
+        <x:v>250.8</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>35369.8</x:v>
+        <x:v>35620.6</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>192.2</x:v>
+        <x:v>192.5</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -693,25 +693,25 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2794</x:v>
+        <x:v>2785.4</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2761.2</x:v>
+        <x:v>2733.8</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>32.8</x:v>
+        <x:v>51.6</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7361.8</x:v>
+        <x:v>7413.4</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
-        <x:v>40</x:v>
+        <x:v>40.1</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
         <x:v>60</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-10-12</x:v>
+        <x:v>2026-10-13</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>125960</x:v>
+        <x:v>111320</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>107100</x:v>
+        <x:v>101000</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>18860</x:v>
+        <x:v>10320</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1468300</x:v>
+        <x:v>1478620</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>7979.9</x:v>
+        <x:v>7992.5</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -8369,30 +8369,48 @@
       </x:c>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B234" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C234" s="30"/>
-      <x:c r="D234" s="30"/>
-      <x:c r="E234" s="30"/>
-      <x:c r="F234" s="30"/>
-      <x:c r="G234" s="30"/>
-      <x:c r="H234" s="30"/>
-      <x:c r="I234" s="30"/>
-      <x:c r="J234" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J233),1)</x:f>
-        <x:v>29860</x:v>
-      </x:c>
-      <x:c r="K234" s="30"/>
+      <x:c r="A234" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B234" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C234" s="22" t="str">
+        <x:v>10月13日</x:v>
+      </x:c>
+      <x:c r="D234" s="23" t="n">
+        <x:v>101000</x:v>
+      </x:c>
+      <x:c r="E234" s="23" t="n">
+        <x:v>111320</x:v>
+      </x:c>
+      <x:c r="F234" s="23" t="n">
+        <x:v>101000</x:v>
+      </x:c>
+      <x:c r="G234" s="23" t="n">
+        <x:v>109500</x:v>
+      </x:c>
+      <x:c r="H234" s="28" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="I234" s="24" t="n">
+        <x:v>0.022408963585434094</x:v>
+      </x:c>
+      <x:c r="J234" s="26" t="n">
+        <x:f>ROUND(E234-F234,1)</x:f>
+        <x:v>10320</x:v>
+      </x:c>
+      <x:c r="K234" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B235" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B235" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C235" s="30"/>
       <x:c r="D235" s="30"/>
       <x:c r="E235" s="30"/>
@@ -8400,11 +8418,29 @@
       <x:c r="G235" s="30"/>
       <x:c r="H235" s="30"/>
       <x:c r="I235" s="30"/>
-      <x:c r="J235" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
-        <x:v>9953.3</x:v>
+      <x:c r="J235" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J234),1)</x:f>
+        <x:v>40180</x:v>
       </x:c>
       <x:c r="K235" s="30"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B236" s="30"/>
+      <x:c r="C236" s="30"/>
+      <x:c r="D236" s="30"/>
+      <x:c r="E236" s="30"/>
+      <x:c r="F236" s="30"/>
+      <x:c r="G236" s="30"/>
+      <x:c r="H236" s="30"/>
+      <x:c r="I236" s="30"/>
+      <x:c r="J236" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
+        <x:v>10045</x:v>
+      </x:c>
+      <x:c r="K236" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -14783,7 +14819,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B179" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月12日-10月13日</x:v>
       </x:c>
       <x:c r="C179" s="23" t="n">
         <x:v>7000</x:v>
@@ -14792,28 +14828,28 @@
         <x:v>7031.2</x:v>
       </x:c>
       <x:c r="E179" s="23" t="n">
-        <x:v>6886.6</x:v>
+        <x:v>6680</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>6921</x:v>
+        <x:v>6901.8</x:v>
       </x:c>
       <x:c r="G179" s="23" t="n">
         <x:f>ROUND(F179-F178,1)</x:f>
-        <x:v>-94.8</x:v>
+        <x:v>-114</x:v>
       </x:c>
       <x:c r="H179" s="24" t="n">
         <x:f>IFERROR(F179/F178-1,"")</x:f>
-        <x:v>-0.01351235782091853</x:v>
-      </x:c>
-      <x:c r="I179" s="23" t="n">
+        <x:v>-0.016249037885914697</x:v>
+      </x:c>
+      <x:c r="I179" s="26" t="n">
         <x:f>ROUND(D179-E179,1)</x:f>
-        <x:v>144.6</x:v>
+        <x:v>351.2</x:v>
       </x:c>
       <x:c r="J179" s="22" t="str">
         <x:v>IM2612</x:v>
       </x:c>
       <x:c r="K179" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -14831,7 +14867,7 @@
       <x:c r="H180" s="30"/>
       <x:c r="I180" s="32" t="n">
         <x:f>ROUND(SUM(I140:I179),1)</x:f>
-        <x:v>16907.8</x:v>
+        <x:v>17114.4</x:v>
       </x:c>
       <x:c r="J180" s="30"/>
       <x:c r="K180" s="30"/>
@@ -14849,7 +14885,7 @@
       <x:c r="H181" s="30"/>
       <x:c r="I181" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I140:I179),0),1)</x:f>
-        <x:v>422.7</x:v>
+        <x:v>427.9</x:v>
       </x:c>
       <x:c r="J181" s="30"/>
       <x:c r="K181" s="30"/>
@@ -16385,7 +16421,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B224" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月12日-10月13日</x:v>
       </x:c>
       <x:c r="C224" s="23" t="n">
         <x:v>7076.6</x:v>
@@ -16394,28 +16430,28 @@
         <x:v>7115.6</x:v>
       </x:c>
       <x:c r="E224" s="23" t="n">
-        <x:v>6943.6</x:v>
+        <x:v>6778.4</x:v>
       </x:c>
       <x:c r="F224" s="23" t="n">
-        <x:v>6986</x:v>
+        <x:v>6962.2</x:v>
       </x:c>
       <x:c r="G224" s="23" t="n">
         <x:f>ROUND(F224-F223,1)</x:f>
-        <x:v>-125</x:v>
+        <x:v>-148.8</x:v>
       </x:c>
       <x:c r="H224" s="24" t="n">
         <x:f>IFERROR(F224/F223-1,"")</x:f>
-        <x:v>-0.017578399662494748</x:v>
+        <x:v>-0.020925326958233792</x:v>
       </x:c>
       <x:c r="I224" s="26" t="n">
         <x:f>ROUND(D224-E224,1)</x:f>
-        <x:v>172</x:v>
+        <x:v>337.2</x:v>
       </x:c>
       <x:c r="J224" s="22" t="str">
         <x:v>IC2612</x:v>
       </x:c>
       <x:c r="K224" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -16433,7 +16469,7 @@
       <x:c r="H225" s="30"/>
       <x:c r="I225" s="32" t="n">
         <x:f>ROUND(SUM(I185:I224),1)</x:f>
-        <x:v>17390.6</x:v>
+        <x:v>17555.8</x:v>
       </x:c>
       <x:c r="J225" s="30"/>
       <x:c r="K225" s="30"/>
@@ -16451,7 +16487,7 @@
       <x:c r="H226" s="30"/>
       <x:c r="I226" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I185:I224),0),1)</x:f>
-        <x:v>434.8</x:v>
+        <x:v>438.9</x:v>
       </x:c>
       <x:c r="J226" s="30"/>
       <x:c r="K226" s="30"/>
@@ -19589,7 +19625,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B314" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月12日-10月13日</x:v>
       </x:c>
       <x:c r="C314" s="23" t="n">
         <x:v>2762</x:v>
@@ -19598,28 +19634,28 @@
         <x:v>2794</x:v>
       </x:c>
       <x:c r="E314" s="23" t="n">
-        <x:v>2761.2</x:v>
+        <x:v>2733.8</x:v>
       </x:c>
       <x:c r="F314" s="23" t="n">
-        <x:v>2779</x:v>
+        <x:v>2762</x:v>
       </x:c>
       <x:c r="G314" s="23" t="n">
         <x:f>ROUND(F314-F313,1)</x:f>
-        <x:v>15</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="H314" s="24" t="n">
         <x:f>IFERROR(F314/F313-1,"")</x:f>
-        <x:v>0.00542691751085389</x:v>
-      </x:c>
-      <x:c r="I314" s="23" t="n">
+        <x:v>-0.0007235890014472002</x:v>
+      </x:c>
+      <x:c r="I314" s="26" t="n">
         <x:f>ROUND(D314-E314,1)</x:f>
-        <x:v>32.8</x:v>
+        <x:v>60.2</x:v>
       </x:c>
       <x:c r="J314" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K314" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
@@ -19637,7 +19673,7 @@
       <x:c r="H315" s="30"/>
       <x:c r="I315" s="32" t="n">
         <x:f>ROUND(SUM(I275:I314),1)</x:f>
-        <x:v>3496.6</x:v>
+        <x:v>3524</x:v>
       </x:c>
       <x:c r="J315" s="30"/>
       <x:c r="K315" s="30"/>
@@ -19655,7 +19691,7 @@
       <x:c r="H316" s="30"/>
       <x:c r="I316" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I275:I314),0),1)</x:f>
-        <x:v>87.4</x:v>
+        <x:v>88.1</x:v>
       </x:c>
       <x:c r="J316" s="30"/>
       <x:c r="K316" s="30"/>
@@ -21191,7 +21227,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B359" s="22" t="str">
-        <x:v>10月12日</x:v>
+        <x:v>10月12日-10月13日</x:v>
       </x:c>
       <x:c r="C359" s="23" t="n">
         <x:v>125960</x:v>
@@ -21200,28 +21236,28 @@
         <x:v>125960</x:v>
       </x:c>
       <x:c r="E359" s="23" t="n">
-        <x:v>107100</x:v>
+        <x:v>101000</x:v>
       </x:c>
       <x:c r="F359" s="23" t="n">
-        <x:v>107100</x:v>
+        <x:v>109500</x:v>
       </x:c>
       <x:c r="G359" s="28" t="n">
         <x:f>ROUND(F359-F358,1)</x:f>
-        <x:v>-13900</x:v>
+        <x:v>-11500</x:v>
       </x:c>
       <x:c r="H359" s="24" t="n">
         <x:f>IFERROR(F359/F358-1,"")</x:f>
-        <x:v>-0.11487603305785121</x:v>
+        <x:v>-0.0950413223140496</x:v>
       </x:c>
       <x:c r="I359" s="26" t="n">
         <x:f>ROUND(D359-E359,1)</x:f>
-        <x:v>18860</x:v>
+        <x:v>24960</x:v>
       </x:c>
       <x:c r="J359" s="22" t="str">
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K359" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="360">
@@ -21239,7 +21275,7 @@
       <x:c r="H360" s="30"/>
       <x:c r="I360" s="32" t="n">
         <x:f>ROUND(SUM(I320:I359),1)</x:f>
-        <x:v>786180</x:v>
+        <x:v>792280</x:v>
       </x:c>
       <x:c r="J360" s="30"/>
       <x:c r="K360" s="30"/>
@@ -21257,7 +21293,7 @@
       <x:c r="H361" s="30"/>
       <x:c r="I361" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I320:I359),0),1)</x:f>
-        <x:v>19654.5</x:v>
+        <x:v>19807</x:v>
       </x:c>
       <x:c r="J361" s="30"/>
       <x:c r="K361" s="30"/>
@@ -51507,30 +51543,48 @@
       </x:c>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B234" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C234" s="30"/>
-      <x:c r="D234" s="30"/>
-      <x:c r="E234" s="30"/>
-      <x:c r="F234" s="30"/>
-      <x:c r="G234" s="30"/>
-      <x:c r="H234" s="30"/>
-      <x:c r="I234" s="30"/>
-      <x:c r="J234" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J233),1)</x:f>
-        <x:v>678</x:v>
-      </x:c>
-      <x:c r="K234" s="30"/>
+      <x:c r="A234" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B234" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C234" s="22" t="str">
+        <x:v>10月13日</x:v>
+      </x:c>
+      <x:c r="D234" s="23" t="n">
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="E234" s="23" t="n">
+        <x:v>6971.6</x:v>
+      </x:c>
+      <x:c r="F234" s="23" t="n">
+        <x:v>6680</x:v>
+      </x:c>
+      <x:c r="G234" s="23" t="n">
+        <x:v>6901.8</x:v>
+      </x:c>
+      <x:c r="H234" s="23" t="n">
+        <x:v>-19.2</x:v>
+      </x:c>
+      <x:c r="I234" s="24" t="n">
+        <x:v>-0.002774165583008248</x:v>
+      </x:c>
+      <x:c r="J234" s="26" t="n">
+        <x:f>ROUND(E234-F234,1)</x:f>
+        <x:v>291.6</x:v>
+      </x:c>
+      <x:c r="K234" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B235" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B235" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C235" s="30"/>
       <x:c r="D235" s="30"/>
       <x:c r="E235" s="30"/>
@@ -51538,11 +51592,29 @@
       <x:c r="G235" s="30"/>
       <x:c r="H235" s="30"/>
       <x:c r="I235" s="30"/>
-      <x:c r="J235" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
-        <x:v>226</x:v>
+      <x:c r="J235" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J234),1)</x:f>
+        <x:v>969.6</x:v>
       </x:c>
       <x:c r="K235" s="30"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B236" s="30"/>
+      <x:c r="C236" s="30"/>
+      <x:c r="D236" s="30"/>
+      <x:c r="E236" s="30"/>
+      <x:c r="F236" s="30"/>
+      <x:c r="G236" s="30"/>
+      <x:c r="H236" s="30"/>
+      <x:c r="I236" s="30"/>
+      <x:c r="J236" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
+        <x:v>242.4</x:v>
+      </x:c>
+      <x:c r="K236" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -59051,30 +59123,48 @@
       </x:c>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B234" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C234" s="30"/>
-      <x:c r="D234" s="30"/>
-      <x:c r="E234" s="30"/>
-      <x:c r="F234" s="30"/>
-      <x:c r="G234" s="30"/>
-      <x:c r="H234" s="30"/>
-      <x:c r="I234" s="30"/>
-      <x:c r="J234" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J233),1)</x:f>
-        <x:v>686.6</x:v>
-      </x:c>
-      <x:c r="K234" s="30"/>
+      <x:c r="A234" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B234" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C234" s="22" t="str">
+        <x:v>10月13日</x:v>
+      </x:c>
+      <x:c r="D234" s="23" t="n">
+        <x:v>6830</x:v>
+      </x:c>
+      <x:c r="E234" s="23" t="n">
+        <x:v>7029.2</x:v>
+      </x:c>
+      <x:c r="F234" s="23" t="n">
+        <x:v>6778.4</x:v>
+      </x:c>
+      <x:c r="G234" s="23" t="n">
+        <x:v>6962.2</x:v>
+      </x:c>
+      <x:c r="H234" s="23" t="n">
+        <x:v>-23.8</x:v>
+      </x:c>
+      <x:c r="I234" s="24" t="n">
+        <x:v>-0.00340681362725459</x:v>
+      </x:c>
+      <x:c r="J234" s="26" t="n">
+        <x:f>ROUND(E234-F234,1)</x:f>
+        <x:v>250.8</x:v>
+      </x:c>
+      <x:c r="K234" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B235" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B235" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C235" s="30"/>
       <x:c r="D235" s="30"/>
       <x:c r="E235" s="30"/>
@@ -59082,11 +59172,29 @@
       <x:c r="G235" s="30"/>
       <x:c r="H235" s="30"/>
       <x:c r="I235" s="30"/>
-      <x:c r="J235" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
-        <x:v>228.9</x:v>
+      <x:c r="J235" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J234),1)</x:f>
+        <x:v>937.4</x:v>
       </x:c>
       <x:c r="K235" s="30"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B236" s="30"/>
+      <x:c r="C236" s="30"/>
+      <x:c r="D236" s="30"/>
+      <x:c r="E236" s="30"/>
+      <x:c r="F236" s="30"/>
+      <x:c r="G236" s="30"/>
+      <x:c r="H236" s="30"/>
+      <x:c r="I236" s="30"/>
+      <x:c r="J236" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
+        <x:v>234.4</x:v>
+      </x:c>
+      <x:c r="K236" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -74175,30 +74283,48 @@
       </x:c>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B234" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C234" s="30"/>
-      <x:c r="D234" s="30"/>
-      <x:c r="E234" s="30"/>
-      <x:c r="F234" s="30"/>
-      <x:c r="G234" s="30"/>
-      <x:c r="H234" s="30"/>
-      <x:c r="I234" s="30"/>
-      <x:c r="J234" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J233),1)</x:f>
-        <x:v>127.4</x:v>
-      </x:c>
-      <x:c r="K234" s="30"/>
+      <x:c r="A234" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B234" s="22" t="str">
+        <x:v>周二</x:v>
+      </x:c>
+      <x:c r="C234" s="22" t="str">
+        <x:v>10月13日</x:v>
+      </x:c>
+      <x:c r="D234" s="23" t="n">
+        <x:v>2752.2</x:v>
+      </x:c>
+      <x:c r="E234" s="23" t="n">
+        <x:v>2785.4</x:v>
+      </x:c>
+      <x:c r="F234" s="23" t="n">
+        <x:v>2733.8</x:v>
+      </x:c>
+      <x:c r="G234" s="23" t="n">
+        <x:v>2762</x:v>
+      </x:c>
+      <x:c r="H234" s="23" t="n">
+        <x:v>-17</x:v>
+      </x:c>
+      <x:c r="I234" s="24" t="n">
+        <x:v>-0.006117308384310904</x:v>
+      </x:c>
+      <x:c r="J234" s="23" t="n">
+        <x:f>ROUND(E234-F234,1)</x:f>
+        <x:v>51.6</x:v>
+      </x:c>
+      <x:c r="K234" s="22" t="str">
+        <x:v>IH2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B235" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B235" s="30" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="C235" s="30"/>
       <x:c r="D235" s="30"/>
       <x:c r="E235" s="30"/>
@@ -74206,11 +74332,29 @@
       <x:c r="G235" s="30"/>
       <x:c r="H235" s="30"/>
       <x:c r="I235" s="30"/>
-      <x:c r="J235" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J233),0),1)</x:f>
-        <x:v>42.5</x:v>
+      <x:c r="J235" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J234),1)</x:f>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K235" s="30"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B236" s="30"/>
+      <x:c r="C236" s="30"/>
+      <x:c r="D236" s="30"/>
+      <x:c r="E236" s="30"/>
+      <x:c r="F236" s="30"/>
+      <x:c r="G236" s="30"/>
+      <x:c r="H236" s="30"/>
+      <x:c r="I236" s="30"/>
+      <x:c r="J236" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
+        <x:v>44.8</x:v>
+      </x:c>
+      <x:c r="K236" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R1427454d3ff64e8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R090131621edb466a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R014950725cad4e6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="R634e260ca74f4e9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="Rb5559dc7818646b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="Rb0d4d5d538844814"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R45bd570977924b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R2d1b8c967d53467f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rb6cd41d64ae94e92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="Rbae1f462cbd84168"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R0d575d806bd74f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R16e8b39902214662"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R30ebe03694304dab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rbfb7cb1ed167455a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R3bc174d9a4074d63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R0c995b17c81840e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R96b67bd17ac24b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R498db7758eb749bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re7757b862bf54ae3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R56dcf84734ca499e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -519,25 +519,25 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="B4" s="9" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="C4" s="10" t="n">
-        <x:v>7087.89</x:v>
+        <x:v>7035.18</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
-        <x:v>6796.58</x:v>
+        <x:v>6891.6</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>291.3</x:v>
+        <x:v>143.6</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>32442</x:v>
+        <x:v>32585.6</x:v>
       </x:c>
       <x:c r="H4" s="10" t="n">
-        <x:v>175.4</x:v>
+        <x:v>175.2</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
         <x:v>180</x:v>
@@ -548,25 +548,25 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
-        <x:v>7152.45</x:v>
+        <x:v>7120.11</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
-        <x:v>6904.6</x:v>
+        <x:v>6969.02</x:v>
       </x:c>
       <x:c r="E5" s="12" t="n">
-        <x:v>247.8</x:v>
+        <x:v>151.1</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>32167.7</x:v>
+        <x:v>32318.8</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
-        <x:v>173.9</x:v>
+        <x:v>173.8</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
         <x:v>160</x:v>
@@ -577,22 +577,22 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
-        <x:v>3822.11</x:v>
+        <x:v>3811.81</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
-        <x:v>3741.53</x:v>
+        <x:v>3761.96</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>80.6</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>8871.9</x:v>
+        <x:v>8921.7</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>48</x:v>
@@ -606,25 +606,25 @@
         <x:v>IM主力</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>6971.6</x:v>
+        <x:v>6925.2</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
-        <x:v>6680</x:v>
+        <x:v>6761</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>291.6</x:v>
+        <x:v>164.2</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>34463</x:v>
+        <x:v>34627.2</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
-        <x:v>186.3</x:v>
+        <x:v>186.2</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
         <x:v>190</x:v>
@@ -722,25 +722,25 @@
         <x:v>碳酸锂2610</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>111320</x:v>
+        <x:v>108380</x:v>
       </x:c>
       <x:c r="D11" s="10" t="n">
-        <x:v>101000</x:v>
+        <x:v>103000</x:v>
       </x:c>
       <x:c r="E11" s="12" t="n">
-        <x:v>10320</x:v>
+        <x:v>5380</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>1478620</x:v>
+        <x:v>1484000</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
-        <x:v>7992.5</x:v>
+        <x:v>7978.5</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
         <x:v>6000</x:v>
@@ -754,7 +754,7 @@
         <x:v>2026-01-01</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>数据源</x:v>
@@ -8405,30 +8405,48 @@
       </x:c>
     </x:row>
     <x:row r="235">
-      <x:c r="A235" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B235" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C235" s="30"/>
-      <x:c r="D235" s="30"/>
-      <x:c r="E235" s="30"/>
-      <x:c r="F235" s="30"/>
-      <x:c r="G235" s="30"/>
-      <x:c r="H235" s="30"/>
-      <x:c r="I235" s="30"/>
-      <x:c r="J235" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J234),1)</x:f>
-        <x:v>40180</x:v>
-      </x:c>
-      <x:c r="K235" s="30"/>
+      <x:c r="A235" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B235" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C235" s="22" t="str">
+        <x:v>10月14日</x:v>
+      </x:c>
+      <x:c r="D235" s="23" t="n">
+        <x:v>108380</x:v>
+      </x:c>
+      <x:c r="E235" s="23" t="n">
+        <x:v>108380</x:v>
+      </x:c>
+      <x:c r="F235" s="23" t="n">
+        <x:v>103000</x:v>
+      </x:c>
+      <x:c r="G235" s="23" t="n">
+        <x:v>103000</x:v>
+      </x:c>
+      <x:c r="H235" s="28" t="n">
+        <x:v>-6500</x:v>
+      </x:c>
+      <x:c r="I235" s="24" t="n">
+        <x:v>-0.05936073059360736</x:v>
+      </x:c>
+      <x:c r="J235" s="23" t="n">
+        <x:f>ROUND(E235-F235,1)</x:f>
+        <x:v>5380</x:v>
+      </x:c>
+      <x:c r="K235" s="22" t="str">
+        <x:v>LC2610</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B236" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B236" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C236" s="30"/>
       <x:c r="D236" s="30"/>
       <x:c r="E236" s="30"/>
@@ -8436,11 +8454,29 @@
       <x:c r="G236" s="30"/>
       <x:c r="H236" s="30"/>
       <x:c r="I236" s="30"/>
-      <x:c r="J236" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
-        <x:v>10045</x:v>
+      <x:c r="J236" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J235),1)</x:f>
+        <x:v>45560</x:v>
       </x:c>
       <x:c r="K236" s="30"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B237" s="30"/>
+      <x:c r="C237" s="30"/>
+      <x:c r="D237" s="30"/>
+      <x:c r="E237" s="30"/>
+      <x:c r="F237" s="30"/>
+      <x:c r="G237" s="30"/>
+      <x:c r="H237" s="30"/>
+      <x:c r="I237" s="30"/>
+      <x:c r="J237" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J235),0),1)</x:f>
+        <x:v>9112</x:v>
+      </x:c>
+      <x:c r="K237" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10013,7 +10049,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B44" s="22" t="str">
-        <x:v>10月12日-10月13日</x:v>
+        <x:v>10月12日-10月14日</x:v>
       </x:c>
       <x:c r="C44" s="23" t="n">
         <x:v>7132.68</x:v>
@@ -10025,15 +10061,15 @@
         <x:v>6796.58</x:v>
       </x:c>
       <x:c r="F44" s="23" t="n">
-        <x:v>7023.22</x:v>
-      </x:c>
-      <x:c r="G44" s="23" t="n">
+        <x:v>6905.17</x:v>
+      </x:c>
+      <x:c r="G44" s="28" t="n">
         <x:f>ROUND(F44-F43,1)</x:f>
-        <x:v>-132.7</x:v>
+        <x:v>-250.7</x:v>
       </x:c>
       <x:c r="H44" s="24" t="n">
         <x:f>IFERROR(F44/F43-1,"")</x:f>
-        <x:v>-0.018542715042531244</x:v>
+        <x:v>-0.03503956869217184</x:v>
       </x:c>
       <x:c r="I44" s="26" t="n">
         <x:f>ROUND(D44-E44,1)</x:f>
@@ -10043,7 +10079,7 @@
         <x:v>中证1000</x:v>
       </x:c>
       <x:c r="K44" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -11615,7 +11651,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B89" s="22" t="str">
-        <x:v>10月12日-10月13日</x:v>
+        <x:v>10月12日-10月14日</x:v>
       </x:c>
       <x:c r="C89" s="23" t="n">
         <x:v>7226.07</x:v>
@@ -11627,15 +11663,15 @@
         <x:v>6904.6</x:v>
       </x:c>
       <x:c r="F89" s="23" t="n">
-        <x:v>7085.09</x:v>
+        <x:v>6980.11</x:v>
       </x:c>
       <x:c r="G89" s="28" t="n">
         <x:f>ROUND(F89-F88,1)</x:f>
-        <x:v>-165.9</x:v>
+        <x:v>-270.9</x:v>
       </x:c>
       <x:c r="H89" s="24" t="n">
         <x:f>IFERROR(F89/F88-1,"")</x:f>
-        <x:v>-0.022882329496166753</x:v>
+        <x:v>-0.03736031256335337</x:v>
       </x:c>
       <x:c r="I89" s="26" t="n">
         <x:f>ROUND(D89-E89,1)</x:f>
@@ -11645,7 +11681,7 @@
         <x:v>中证500</x:v>
       </x:c>
       <x:c r="K89" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -13217,7 +13253,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B134" s="22" t="str">
-        <x:v>10月12日-10月13日</x:v>
+        <x:v>10月12日-10月14日</x:v>
       </x:c>
       <x:c r="C134" s="23" t="n">
         <x:v>3806.98</x:v>
@@ -13229,15 +13265,15 @@
         <x:v>3741.53</x:v>
       </x:c>
       <x:c r="F134" s="23" t="n">
-        <x:v>3800.86</x:v>
+        <x:v>3767.23</x:v>
       </x:c>
       <x:c r="G134" s="23" t="n">
         <x:f>ROUND(F134-F133,1)</x:f>
-        <x:v>-12.9</x:v>
+        <x:v>-46.6</x:v>
       </x:c>
       <x:c r="H134" s="24" t="n">
         <x:f>IFERROR(F134/F133-1,"")</x:f>
-        <x:v>-0.0033903282561441594</x:v>
+        <x:v>-0.01220832819845874</x:v>
       </x:c>
       <x:c r="I134" s="26" t="n">
         <x:f>ROUND(D134-E134,1)</x:f>
@@ -13247,7 +13283,7 @@
         <x:v>上证指数</x:v>
       </x:c>
       <x:c r="K134" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -14819,7 +14855,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B179" s="22" t="str">
-        <x:v>10月12日-10月13日</x:v>
+        <x:v>10月12日-10月14日</x:v>
       </x:c>
       <x:c r="C179" s="23" t="n">
         <x:v>7000</x:v>
@@ -14831,15 +14867,15 @@
         <x:v>6680</x:v>
       </x:c>
       <x:c r="F179" s="23" t="n">
-        <x:v>6901.8</x:v>
-      </x:c>
-      <x:c r="G179" s="23" t="n">
+        <x:v>6805.8</x:v>
+      </x:c>
+      <x:c r="G179" s="28" t="n">
         <x:f>ROUND(F179-F178,1)</x:f>
-        <x:v>-114</x:v>
+        <x:v>-210</x:v>
       </x:c>
       <x:c r="H179" s="24" t="n">
         <x:f>IFERROR(F179/F178-1,"")</x:f>
-        <x:v>-0.016249037885914697</x:v>
+        <x:v>-0.029932438210895418</x:v>
       </x:c>
       <x:c r="I179" s="26" t="n">
         <x:f>ROUND(D179-E179,1)</x:f>
@@ -14849,7 +14885,7 @@
         <x:v>IM2612</x:v>
       </x:c>
       <x:c r="K179" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -21227,7 +21263,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B359" s="22" t="str">
-        <x:v>10月12日-10月13日</x:v>
+        <x:v>10月12日-10月14日</x:v>
       </x:c>
       <x:c r="C359" s="23" t="n">
         <x:v>125960</x:v>
@@ -21239,15 +21275,15 @@
         <x:v>101000</x:v>
       </x:c>
       <x:c r="F359" s="23" t="n">
-        <x:v>109500</x:v>
+        <x:v>103000</x:v>
       </x:c>
       <x:c r="G359" s="28" t="n">
         <x:f>ROUND(F359-F358,1)</x:f>
-        <x:v>-11500</x:v>
+        <x:v>-18000</x:v>
       </x:c>
       <x:c r="H359" s="24" t="n">
         <x:f>IFERROR(F359/F358-1,"")</x:f>
-        <x:v>-0.0950413223140496</x:v>
+        <x:v>-0.14876033057851235</x:v>
       </x:c>
       <x:c r="I359" s="26" t="n">
         <x:f>ROUND(D359-E359,1)</x:f>
@@ -21257,7 +21293,7 @@
         <x:v>LC2610</x:v>
       </x:c>
       <x:c r="K359" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="360">
@@ -28839,30 +28875,48 @@
       </x:c>
     </x:row>
     <x:row r="235">
-      <x:c r="A235" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B235" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C235" s="30"/>
-      <x:c r="D235" s="30"/>
-      <x:c r="E235" s="30"/>
-      <x:c r="F235" s="30"/>
-      <x:c r="G235" s="30"/>
-      <x:c r="H235" s="30"/>
-      <x:c r="I235" s="30"/>
-      <x:c r="J235" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J234),1)</x:f>
-        <x:v>951</x:v>
-      </x:c>
-      <x:c r="K235" s="30"/>
+      <x:c r="A235" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B235" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C235" s="22" t="str">
+        <x:v>10月14日</x:v>
+      </x:c>
+      <x:c r="D235" s="23" t="n">
+        <x:v>7001.91</x:v>
+      </x:c>
+      <x:c r="E235" s="23" t="n">
+        <x:v>7035.18</x:v>
+      </x:c>
+      <x:c r="F235" s="23" t="n">
+        <x:v>6891.6</x:v>
+      </x:c>
+      <x:c r="G235" s="23" t="n">
+        <x:v>6905.17</x:v>
+      </x:c>
+      <x:c r="H235" s="23" t="n">
+        <x:v>-118.1</x:v>
+      </x:c>
+      <x:c r="I235" s="24" t="n">
+        <x:v>-0.01680852942097788</x:v>
+      </x:c>
+      <x:c r="J235" s="23" t="n">
+        <x:f>ROUND(E235-F235,1)</x:f>
+        <x:v>143.6</x:v>
+      </x:c>
+      <x:c r="K235" s="22" t="str">
+        <x:v>中证1000</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B236" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B236" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C236" s="30"/>
       <x:c r="D236" s="30"/>
       <x:c r="E236" s="30"/>
@@ -28870,11 +28924,29 @@
       <x:c r="G236" s="30"/>
       <x:c r="H236" s="30"/>
       <x:c r="I236" s="30"/>
-      <x:c r="J236" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
-        <x:v>237.8</x:v>
+      <x:c r="J236" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J235),1)</x:f>
+        <x:v>1094.6</x:v>
       </x:c>
       <x:c r="K236" s="30"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B237" s="30"/>
+      <x:c r="C237" s="30"/>
+      <x:c r="D237" s="30"/>
+      <x:c r="E237" s="30"/>
+      <x:c r="F237" s="30"/>
+      <x:c r="G237" s="30"/>
+      <x:c r="H237" s="30"/>
+      <x:c r="I237" s="30"/>
+      <x:c r="J237" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J235),0),1)</x:f>
+        <x:v>218.9</x:v>
+      </x:c>
+      <x:c r="K237" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -36419,30 +36491,48 @@
       </x:c>
     </x:row>
     <x:row r="235">
-      <x:c r="A235" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B235" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C235" s="30"/>
-      <x:c r="D235" s="30"/>
-      <x:c r="E235" s="30"/>
-      <x:c r="F235" s="30"/>
-      <x:c r="G235" s="30"/>
-      <x:c r="H235" s="30"/>
-      <x:c r="I235" s="30"/>
-      <x:c r="J235" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J234),1)</x:f>
-        <x:v>882.6</x:v>
-      </x:c>
-      <x:c r="K235" s="30"/>
+      <x:c r="A235" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B235" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C235" s="22" t="str">
+        <x:v>10月14日</x:v>
+      </x:c>
+      <x:c r="D235" s="23" t="n">
+        <x:v>7066.73</x:v>
+      </x:c>
+      <x:c r="E235" s="23" t="n">
+        <x:v>7120.11</x:v>
+      </x:c>
+      <x:c r="F235" s="23" t="n">
+        <x:v>6969.02</x:v>
+      </x:c>
+      <x:c r="G235" s="23" t="n">
+        <x:v>6980.11</x:v>
+      </x:c>
+      <x:c r="H235" s="23" t="n">
+        <x:v>-105</x:v>
+      </x:c>
+      <x:c r="I235" s="24" t="n">
+        <x:v>-0.014817031258600899</x:v>
+      </x:c>
+      <x:c r="J235" s="23" t="n">
+        <x:f>ROUND(E235-F235,1)</x:f>
+        <x:v>151.1</x:v>
+      </x:c>
+      <x:c r="K235" s="22" t="str">
+        <x:v>中证500</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B236" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B236" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C236" s="30"/>
       <x:c r="D236" s="30"/>
       <x:c r="E236" s="30"/>
@@ -36450,11 +36540,29 @@
       <x:c r="G236" s="30"/>
       <x:c r="H236" s="30"/>
       <x:c r="I236" s="30"/>
-      <x:c r="J236" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
-        <x:v>220.7</x:v>
+      <x:c r="J236" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J235),1)</x:f>
+        <x:v>1033.7</x:v>
       </x:c>
       <x:c r="K236" s="30"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B237" s="30"/>
+      <x:c r="C237" s="30"/>
+      <x:c r="D237" s="30"/>
+      <x:c r="E237" s="30"/>
+      <x:c r="F237" s="30"/>
+      <x:c r="G237" s="30"/>
+      <x:c r="H237" s="30"/>
+      <x:c r="I237" s="30"/>
+      <x:c r="J237" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J235),0),1)</x:f>
+        <x:v>206.7</x:v>
+      </x:c>
+      <x:c r="K237" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -43999,30 +44107,48 @@
       </x:c>
     </x:row>
     <x:row r="235">
-      <x:c r="A235" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B235" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C235" s="30"/>
-      <x:c r="D235" s="30"/>
-      <x:c r="E235" s="30"/>
-      <x:c r="F235" s="30"/>
-      <x:c r="G235" s="30"/>
-      <x:c r="H235" s="30"/>
-      <x:c r="I235" s="30"/>
-      <x:c r="J235" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J234),1)</x:f>
-        <x:v>257.2</x:v>
-      </x:c>
-      <x:c r="K235" s="30"/>
+      <x:c r="A235" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B235" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C235" s="22" t="str">
+        <x:v>10月14日</x:v>
+      </x:c>
+      <x:c r="D235" s="23" t="n">
+        <x:v>3790.63</x:v>
+      </x:c>
+      <x:c r="E235" s="23" t="n">
+        <x:v>3811.81</x:v>
+      </x:c>
+      <x:c r="F235" s="23" t="n">
+        <x:v>3761.96</x:v>
+      </x:c>
+      <x:c r="G235" s="23" t="n">
+        <x:v>3767.23</x:v>
+      </x:c>
+      <x:c r="H235" s="23" t="n">
+        <x:v>-33.6</x:v>
+      </x:c>
+      <x:c r="I235" s="24" t="n">
+        <x:v>-0.00884799755844734</x:v>
+      </x:c>
+      <x:c r="J235" s="23" t="n">
+        <x:f>ROUND(E235-F235,1)</x:f>
+        <x:v>49.8</x:v>
+      </x:c>
+      <x:c r="K235" s="22" t="str">
+        <x:v>上证指数</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B236" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B236" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C236" s="30"/>
       <x:c r="D236" s="30"/>
       <x:c r="E236" s="30"/>
@@ -44030,11 +44156,29 @@
       <x:c r="G236" s="30"/>
       <x:c r="H236" s="30"/>
       <x:c r="I236" s="30"/>
-      <x:c r="J236" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
-        <x:v>64.3</x:v>
+      <x:c r="J236" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J235),1)</x:f>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="K236" s="30"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B237" s="30"/>
+      <x:c r="C237" s="30"/>
+      <x:c r="D237" s="30"/>
+      <x:c r="E237" s="30"/>
+      <x:c r="F237" s="30"/>
+      <x:c r="G237" s="30"/>
+      <x:c r="H237" s="30"/>
+      <x:c r="I237" s="30"/>
+      <x:c r="J237" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J235),0),1)</x:f>
+        <x:v>61.4</x:v>
+      </x:c>
+      <x:c r="K237" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -51579,30 +51723,48 @@
       </x:c>
     </x:row>
     <x:row r="235">
-      <x:c r="A235" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B235" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C235" s="30"/>
-      <x:c r="D235" s="30"/>
-      <x:c r="E235" s="30"/>
-      <x:c r="F235" s="30"/>
-      <x:c r="G235" s="30"/>
-      <x:c r="H235" s="30"/>
-      <x:c r="I235" s="30"/>
-      <x:c r="J235" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J234),1)</x:f>
-        <x:v>969.6</x:v>
-      </x:c>
-      <x:c r="K235" s="30"/>
+      <x:c r="A235" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B235" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C235" s="22" t="str">
+        <x:v>10月14日</x:v>
+      </x:c>
+      <x:c r="D235" s="23" t="n">
+        <x:v>6895</x:v>
+      </x:c>
+      <x:c r="E235" s="23" t="n">
+        <x:v>6925.2</x:v>
+      </x:c>
+      <x:c r="F235" s="23" t="n">
+        <x:v>6761</x:v>
+      </x:c>
+      <x:c r="G235" s="23" t="n">
+        <x:v>6805.8</x:v>
+      </x:c>
+      <x:c r="H235" s="23" t="n">
+        <x:v>-96</x:v>
+      </x:c>
+      <x:c r="I235" s="24" t="n">
+        <x:v>-0.013909414935234232</x:v>
+      </x:c>
+      <x:c r="J235" s="23" t="n">
+        <x:f>ROUND(E235-F235,1)</x:f>
+        <x:v>164.2</x:v>
+      </x:c>
+      <x:c r="K235" s="22" t="str">
+        <x:v>IM2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B236" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B236" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C236" s="30"/>
       <x:c r="D236" s="30"/>
       <x:c r="E236" s="30"/>
@@ -51610,11 +51772,29 @@
       <x:c r="G236" s="30"/>
       <x:c r="H236" s="30"/>
       <x:c r="I236" s="30"/>
-      <x:c r="J236" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
-        <x:v>242.4</x:v>
+      <x:c r="J236" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J235),1)</x:f>
+        <x:v>1133.8</x:v>
       </x:c>
       <x:c r="K236" s="30"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B237" s="30"/>
+      <x:c r="C237" s="30"/>
+      <x:c r="D237" s="30"/>
+      <x:c r="E237" s="30"/>
+      <x:c r="F237" s="30"/>
+      <x:c r="G237" s="30"/>
+      <x:c r="H237" s="30"/>
+      <x:c r="I237" s="30"/>
+      <x:c r="J237" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J235),0),1)</x:f>
+        <x:v>226.8</x:v>
+      </x:c>
+      <x:c r="K237" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/每日振幅统计_2026.xlsx
+++ b/每日振幅统计_2026.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R0d575d806bd74f96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R16e8b39902214662"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="R30ebe03694304dab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rbfb7cb1ed167455a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R3bc174d9a4074d63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R0c995b17c81840e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="R96b67bd17ac24b0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R498db7758eb749bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Re7757b862bf54ae3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R56dcf84734ca499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="1" r:id="R0672664bd997443c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周振幅统计" sheetId="2" r:id="R6778a1c4e4494e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证1000" sheetId="3" r:id="Rb2602ea99f1f489d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="4" r:id="Rf4f1db16609c4c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上证指数" sheetId="5" r:id="R5970f753efa84c7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IM主力" sheetId="6" r:id="R3da2f6c06e5642d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC主力" sheetId="7" r:id="Rd663970eaf1c4032"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IF主力" sheetId="8" r:id="R5620653c9d0f4842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IH主力" sheetId="9" r:id="Rb0e63f5515eb4c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="碳酸锂2610" sheetId="10" r:id="R01e7669638654793"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,25 +635,25 @@
         <x:v>IC主力</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
-        <x:v>7029.2</x:v>
+        <x:v>6994.8</x:v>
       </x:c>
       <x:c r="D8" s="10" t="n">
-        <x:v>6778.4</x:v>
+        <x:v>6828.6</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>250.8</x:v>
+        <x:v>166.2</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>35620.6</x:v>
+        <x:v>35786.8</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
-        <x:v>192.5</x:v>
+        <x:v>192.4</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
         <x:v>150</x:v>
@@ -664,22 +664,22 @@
         <x:v>IF主力</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
-        <x:v>4257.4</x:v>
+        <x:v>4217.6</x:v>
       </x:c>
       <x:c r="D9" s="10" t="n">
-        <x:v>4151</x:v>
+        <x:v>4141</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>106.4</x:v>
+        <x:v>76.6</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>13372</x:v>
+        <x:v>13448.6</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
         <x:v>72.3</x:v>
@@ -693,22 +693,22 @@
         <x:v>IH主力</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>2026-10-13</x:v>
+        <x:v>2026-10-14</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>2785.4</x:v>
+        <x:v>2760.8</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>2733.8</x:v>
+        <x:v>2722.4</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>51.6</x:v>
+        <x:v>38.4</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>7413.4</x:v>
+        <x:v>7451.8</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>40.1</x:v>
@@ -16457,7 +16457,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B224" s="22" t="str">
-        <x:v>10月12日-10月13日</x:v>
+        <x:v>10月12日-10月14日</x:v>
       </x:c>
       <x:c r="C224" s="23" t="n">
         <x:v>7076.6</x:v>
@@ -16469,15 +16469,15 @@
         <x:v>6778.4</x:v>
       </x:c>
       <x:c r="F224" s="23" t="n">
-        <x:v>6962.2</x:v>
-      </x:c>
-      <x:c r="G224" s="23" t="n">
+        <x:v>6874.6</x:v>
+      </x:c>
+      <x:c r="G224" s="28" t="n">
         <x:f>ROUND(F224-F223,1)</x:f>
-        <x:v>-148.8</x:v>
+        <x:v>-236.4</x:v>
       </x:c>
       <x:c r="H224" s="24" t="n">
         <x:f>IFERROR(F224/F223-1,"")</x:f>
-        <x:v>-0.020925326958233792</x:v>
+        <x:v>-0.033244269441709995</x:v>
       </x:c>
       <x:c r="I224" s="26" t="n">
         <x:f>ROUND(D224-E224,1)</x:f>
@@ -16487,7 +16487,7 @@
         <x:v>IC2612</x:v>
       </x:c>
       <x:c r="K224" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -18059,7 +18059,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B269" s="22" t="str">
-        <x:v>10月12日-10月13日</x:v>
+        <x:v>10月12日-10月14日</x:v>
       </x:c>
       <x:c r="C269" s="23" t="n">
         <x:v>4240.4</x:v>
@@ -18068,28 +18068,28 @@
         <x:v>4273.6</x:v>
       </x:c>
       <x:c r="E269" s="23" t="n">
-        <x:v>4151</x:v>
+        <x:v>4141</x:v>
       </x:c>
       <x:c r="F269" s="23" t="n">
-        <x:v>4217.6</x:v>
+        <x:v>4160.6</x:v>
       </x:c>
       <x:c r="G269" s="23" t="n">
         <x:f>ROUND(F269-F268,1)</x:f>
-        <x:v>-27.2</x:v>
+        <x:v>-84.2</x:v>
       </x:c>
       <x:c r="H269" s="24" t="n">
         <x:f>IFERROR(F269/F268-1,"")</x:f>
-        <x:v>-0.006407840180927216</x:v>
+        <x:v>-0.019836034677723324</x:v>
       </x:c>
       <x:c r="I269" s="26" t="n">
         <x:f>ROUND(D269-E269,1)</x:f>
-        <x:v>122.6</x:v>
+        <x:v>132.6</x:v>
       </x:c>
       <x:c r="J269" s="22" t="str">
         <x:v>IF2612</x:v>
       </x:c>
       <x:c r="K269" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -18107,7 +18107,7 @@
       <x:c r="H270" s="30"/>
       <x:c r="I270" s="32" t="n">
         <x:f>ROUND(SUM(I230:I269),1)</x:f>
-        <x:v>6261.2</x:v>
+        <x:v>6271.2</x:v>
       </x:c>
       <x:c r="J270" s="30"/>
       <x:c r="K270" s="30"/>
@@ -18125,7 +18125,7 @@
       <x:c r="H271" s="30"/>
       <x:c r="I271" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I230:I269),0),1)</x:f>
-        <x:v>156.5</x:v>
+        <x:v>156.8</x:v>
       </x:c>
       <x:c r="J271" s="30"/>
       <x:c r="K271" s="30"/>
@@ -19661,7 +19661,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B314" s="22" t="str">
-        <x:v>10月12日-10月13日</x:v>
+        <x:v>10月12日-10月14日</x:v>
       </x:c>
       <x:c r="C314" s="23" t="n">
         <x:v>2762</x:v>
@@ -19670,28 +19670,28 @@
         <x:v>2794</x:v>
       </x:c>
       <x:c r="E314" s="23" t="n">
+        <x:v>2722.4</x:v>
+      </x:c>
+      <x:c r="F314" s="23" t="n">
         <x:v>2733.8</x:v>
-      </x:c>
-      <x:c r="F314" s="23" t="n">
-        <x:v>2762</x:v>
       </x:c>
       <x:c r="G314" s="23" t="n">
         <x:f>ROUND(F314-F313,1)</x:f>
-        <x:v>-2</x:v>
+        <x:v>-30.2</x:v>
       </x:c>
       <x:c r="H314" s="24" t="n">
         <x:f>IFERROR(F314/F313-1,"")</x:f>
-        <x:v>-0.0007235890014472002</x:v>
+        <x:v>-0.010926193921852345</x:v>
       </x:c>
       <x:c r="I314" s="26" t="n">
         <x:f>ROUND(D314-E314,1)</x:f>
-        <x:v>60.2</x:v>
+        <x:v>71.6</x:v>
       </x:c>
       <x:c r="J314" s="22" t="str">
         <x:v>IH2612</x:v>
       </x:c>
       <x:c r="K314" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
@@ -19709,7 +19709,7 @@
       <x:c r="H315" s="30"/>
       <x:c r="I315" s="32" t="n">
         <x:f>ROUND(SUM(I275:I314),1)</x:f>
-        <x:v>3524</x:v>
+        <x:v>3535.4</x:v>
       </x:c>
       <x:c r="J315" s="30"/>
       <x:c r="K315" s="30"/>
@@ -19727,7 +19727,7 @@
       <x:c r="H316" s="30"/>
       <x:c r="I316" s="34" t="n">
         <x:f>ROUND(IFERROR(AVERAGE(I275:I314),0),1)</x:f>
-        <x:v>88.1</x:v>
+        <x:v>88.4</x:v>
       </x:c>
       <x:c r="J316" s="30"/>
       <x:c r="K316" s="30"/>
@@ -59339,30 +59339,48 @@
       </x:c>
     </x:row>
     <x:row r="235">
-      <x:c r="A235" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B235" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C235" s="30"/>
-      <x:c r="D235" s="30"/>
-      <x:c r="E235" s="30"/>
-      <x:c r="F235" s="30"/>
-      <x:c r="G235" s="30"/>
-      <x:c r="H235" s="30"/>
-      <x:c r="I235" s="30"/>
-      <x:c r="J235" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J234),1)</x:f>
-        <x:v>937.4</x:v>
-      </x:c>
-      <x:c r="K235" s="30"/>
+      <x:c r="A235" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B235" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C235" s="22" t="str">
+        <x:v>10月14日</x:v>
+      </x:c>
+      <x:c r="D235" s="23" t="n">
+        <x:v>6952</x:v>
+      </x:c>
+      <x:c r="E235" s="23" t="n">
+        <x:v>6994.8</x:v>
+      </x:c>
+      <x:c r="F235" s="23" t="n">
+        <x:v>6828.6</x:v>
+      </x:c>
+      <x:c r="G235" s="23" t="n">
+        <x:v>6874.6</x:v>
+      </x:c>
+      <x:c r="H235" s="23" t="n">
+        <x:v>-87.6</x:v>
+      </x:c>
+      <x:c r="I235" s="24" t="n">
+        <x:v>-0.012582229754962482</x:v>
+      </x:c>
+      <x:c r="J235" s="26" t="n">
+        <x:f>ROUND(E235-F235,1)</x:f>
+        <x:v>166.2</x:v>
+      </x:c>
+      <x:c r="K235" s="22" t="str">
+        <x:v>IC2612</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="31" t="str">
-        <x:v>均值</x:v>
-      </x:c>
-      <x:c r="B236" s="30"/>
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B236" s="30" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C236" s="30"/>
       <x:c r="D236" s="30"/>
       <x:c r="E236" s="30"/>
@@ -59370,11 +59388,29 @@
       <x:c r="G236" s="30"/>
       <x:c r="H236" s="30"/>
       <x:c r="I236" s="30"/>
-      <x:c r="J236" s="34" t="n">
-        <x:f>ROUND(IFERROR(AVERAGE(J231:J234),0),1)</x:f>
-        <x:v>234.4</x:v>
+      <x:c r="J236" s="32" t="n">
+        <x:f>ROUND(SUM(J231:J235),1)</x:f>
+        <x:v>1103.6</x:v>
       </x:c>
       <x:c r="K236" s="30"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="31" t="str">
+        <x:v>均值</x:v>
+      </x:c>
+      <x:c r="B237" s="30"/>
+      <x:c r="C237" s="30"/>
+      <x:c r="D237" s="30"/>
+      <x:c r="E237" s="30"/>
+      <x:c r="F237" s="30"/>
+      <x:c r="G237" s="30"/>
+      <x:c r="H237" s="30"/>
+      <x:c r="I237" s="30"/>
+      <x:c r="J237" s="34" t="n">
+        <x:f>ROUND(IFERROR(AVERAGE(J231:J235),0),1)</x:f>
+        <x:v>220.7</x:v>
+      </x:c>
+      <x:c r="K237" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -66919,30 +66955,48 @@
       </x:c>
     </x:row>
     <x:row r="235">
-      <x:c r="A235" s="31" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="B235" s="30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C235" s="30"/>
-      <x:c r="D235" s="30"/>
-      <x:c r="E235" s="30"/>
-      <x:c r="F235" s="30"/>
-      <x:c r="G235" s="30"/>
-      <x:c r="H235" s="30"/>
-      <x:c r="I235" s="30"/>
-      <x:c r="J235" s="32" t="n">
-        <x:f>ROUND(SUM(J231:J234),1)</x:f>
-        <x:v>363.4</x:v>
-      </x:c>
-      <x:c r="K235" s="30"/>
+      <x:c r="A235" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B235" s="22" t="str">
+        <x:v>周三</x:v>
+      </x:c>
+      <x:c r="C235" s="22" t="str">
+        <x:v>10月14日</x:v>
+      </x:c>
+      <x:c r="D235" s="23" t="n">
+        <x:v>4203</x:v>
+      </x:c>
+      <x:c r="E235" s="23" t="n">
+        <x:v>4217.6</x:v>
+      </x:c>
+      <x:c r="F235" s="23" t="n">
+        <x:v>4141</x:v>
+      </x:c>
+      <x:c r="G235" s=